--- a/持仓贝叶斯跟踪.xlsx
+++ b/持仓贝叶斯跟踪.xlsx
@@ -18,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="16">
+  <fonts count="19">
     <font>
       <name val="Calibri"/>
       <charset val="1"/>
@@ -121,8 +121,23 @@
     <font>
       <sz val="11"/>
     </font>
+    <font>
+      <name val="微软雅黑"/>
+      <b val="1"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="微软雅黑"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="微软雅黑"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="14">
+  <fills count="18">
     <fill>
       <patternFill/>
     </fill>
@@ -201,8 +216,32 @@
         <bgColor rgb="FFCCCCFF"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="004472C4"/>
+        <bgColor rgb="004472C4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E2EFDA"/>
+        <bgColor rgb="00E2EFDA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF2CC"/>
+        <bgColor rgb="00FFF2CC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FCE4EC"/>
+        <bgColor rgb="00FCE4EC"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="7">
+  <borders count="8">
     <border>
       <left/>
       <right/>
@@ -252,6 +291,12 @@
       <bottom style="thin"/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1">
@@ -263,7 +308,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="85">
+  <cellXfs count="94">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -509,6 +554,33 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="14" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="15" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="15" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="16" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -764,25 +836,32 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:H14"/>
+  <dimension ref="A1:H32"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6171875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="22" customWidth="1" style="28" min="1" max="8"/>
+    <col width="14" customWidth="1" style="29" min="2" max="2"/>
+    <col width="18" customWidth="1" style="29" min="3" max="3"/>
+    <col width="22" customWidth="1" style="29" min="4" max="4"/>
+    <col width="18" customWidth="1" style="29" min="5" max="5"/>
+    <col width="16" customWidth="1" style="29" min="6" max="6"/>
+    <col width="14" customWidth="1" style="29" min="7" max="7"/>
+    <col width="20" customWidth="1" style="29" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="20.1" customHeight="1" s="29">
       <c r="A1" s="73" t="inlineStr">
         <is>
-          <t>📊 持仓总看板 (2026-05-30)</t>
-        </is>
-      </c>
-      <c r="B1" s="69" t="n"/>
-      <c r="C1" s="69" t="n"/>
-      <c r="D1" s="69" t="n"/>
-      <c r="E1" s="69" t="n"/>
-      <c r="F1" s="69" t="n"/>
-      <c r="G1" s="69" t="n"/>
-      <c r="H1" s="70" t="n"/>
+          <t>📊 持仓总看板 (2026-06-01)</t>
+        </is>
+      </c>
+      <c r="B1" s="31" t="n"/>
+      <c r="C1" s="31" t="n"/>
+      <c r="D1" s="31" t="n"/>
+      <c r="E1" s="31" t="n"/>
+      <c r="F1" s="31" t="n"/>
+      <c r="G1" s="31" t="n"/>
+      <c r="H1" s="32" t="n"/>
     </row>
     <row r="2" ht="15" customHeight="1" s="29">
       <c r="A2" s="74" t="inlineStr">
@@ -790,13 +869,13 @@
           <t>🔴 宏观传导链</t>
         </is>
       </c>
-      <c r="B2" s="69" t="n"/>
-      <c r="C2" s="69" t="n"/>
-      <c r="D2" s="69" t="n"/>
-      <c r="E2" s="69" t="n"/>
-      <c r="F2" s="69" t="n"/>
-      <c r="G2" s="69" t="n"/>
-      <c r="H2" s="70" t="n"/>
+      <c r="B2" s="31" t="n"/>
+      <c r="C2" s="31" t="n"/>
+      <c r="D2" s="31" t="n"/>
+      <c r="E2" s="31" t="n"/>
+      <c r="F2" s="31" t="n"/>
+      <c r="G2" s="31" t="n"/>
+      <c r="H2" s="32" t="n"/>
     </row>
     <row r="3" ht="15" customHeight="1" s="29">
       <c r="A3" s="75" t="inlineStr">
@@ -804,7 +883,7 @@
           <t>【利率】</t>
         </is>
       </c>
-      <c r="B3" s="70" t="n"/>
+      <c r="B3" s="32" t="n"/>
       <c r="C3" s="35" t="inlineStr">
         <is>
           <t>【地缘】</t>
@@ -830,7 +909,7 @@
           <t>【避险】</t>
         </is>
       </c>
-      <c r="H3" s="70" t="n"/>
+      <c r="H3" s="32" t="n"/>
     </row>
     <row r="4" ht="25.35" customHeight="1" s="29">
       <c r="A4" s="77" t="inlineStr">
@@ -838,7 +917,7 @@
           <t>2026-05-28 知乎高赞 — 为什么达利欧说「债市是所有市场的支柱」？</t>
         </is>
       </c>
-      <c r="B4" s="69" t="n"/>
+      <c r="B4" s="31" t="n"/>
       <c r="C4" s="41" t="inlineStr">
         <is>
           <t>2026-05-29 3. 闭眼看世界 - 俄罗斯对基辅最猛烈袭击</t>
@@ -864,7 +943,7 @@
           <t>2026-05-28 Peter Schiff · 美债/美元/黄金极端观点（豆包分析版）</t>
         </is>
       </c>
-      <c r="H4" s="69" t="n"/>
+      <c r="H4" s="31" t="n"/>
     </row>
     <row r="5" ht="25.35" customHeight="1" s="29">
       <c r="A5" s="79" t="inlineStr">
@@ -872,7 +951,7 @@
           <t>2026-05-22 沃什的政策背景</t>
         </is>
       </c>
-      <c r="B5" s="69" t="n"/>
+      <c r="B5" s="31" t="n"/>
       <c r="C5" s="47" t="inlineStr">
         <is>
           <t>2026-05-20 抖音：闭眼看世界 — 日本过境领空地缘风险</t>
@@ -893,7 +972,7 @@
           <t>2026-05-27 闭眼看世界（抖音）→ 黄金+2pp</t>
         </is>
       </c>
-      <c r="H5" s="69" t="n"/>
+      <c r="H5" s="31" t="n"/>
     </row>
     <row r="6" ht="25.35" customHeight="1" s="29">
       <c r="A6" s="77" t="inlineStr">
@@ -901,7 +980,7 @@
           <t>2026-05-19 宋鸿兵：利率风暴席卷全球，股债双杀只是开始</t>
         </is>
       </c>
-      <c r="B6" s="69" t="n"/>
+      <c r="B6" s="31" t="n"/>
       <c r="D6" s="42" t="inlineStr">
         <is>
           <t>2026-05-22 宏观层：前4月住户贷款狂减4902亿（无知半人）</t>
@@ -917,7 +996,7 @@
           <t>2026-05-27 宋鸿兵（抖音）→ 黄金+1pp</t>
         </is>
       </c>
-      <c r="H6" s="69" t="n"/>
+      <c r="H6" s="31" t="n"/>
     </row>
     <row r="7" ht="25.35" customHeight="1" s="29">
       <c r="A7" s="79" t="inlineStr">
@@ -925,7 +1004,7 @@
           <t>2026-05-18 利率风暴的根因 →霍尔木兹海峡封锁→能源价格飙升→通胀预期上升→央行被迫加息</t>
         </is>
       </c>
-      <c r="B7" s="69" t="n"/>
+      <c r="B7" s="31" t="n"/>
       <c r="D7" s="47" t="inlineStr">
         <is>
           <t>2026-05-19 古都闲云：4月新增贷款出现历史罕见的负值</t>
@@ -941,7 +1020,7 @@
           <t>2026-05-23 第四梯队：对冲/避险配置（不参与机会成本排名） →黄金确定性越高** |</t>
         </is>
       </c>
-      <c r="H7" s="69" t="n"/>
+      <c r="H7" s="31" t="n"/>
     </row>
     <row r="8" ht="25.35" customHeight="1" s="29">
       <c r="D8" s="42" t="inlineStr">
@@ -959,7 +1038,7 @@
           <t>2026-05-23 ⑨ 黄金 ⭐⭐⭐⭐⭐⭐（对冲之王） →黄金确定性越高** |</t>
         </is>
       </c>
-      <c r="H8" s="69" t="n"/>
+      <c r="H8" s="31" t="n"/>
     </row>
     <row r="9" ht="25.35" customHeight="1" s="29">
       <c r="F9" s="47" t="inlineStr">
@@ -972,7 +1051,7 @@
           <t>2026-05-21 新浪：黄金深V反转 +1.67%，但前日暴跌84美元</t>
         </is>
       </c>
-      <c r="H9" s="69" t="n"/>
+      <c r="H9" s="31" t="n"/>
     </row>
     <row r="11" ht="15" customHeight="1" s="29">
       <c r="A11" s="80" t="inlineStr">
@@ -980,13 +1059,13 @@
           <t>🟡 中观产业传导</t>
         </is>
       </c>
-      <c r="B11" s="69" t="n"/>
-      <c r="C11" s="69" t="n"/>
-      <c r="D11" s="69" t="n"/>
-      <c r="E11" s="69" t="n"/>
-      <c r="F11" s="69" t="n"/>
-      <c r="G11" s="69" t="n"/>
-      <c r="H11" s="70" t="n"/>
+      <c r="B11" s="31" t="n"/>
+      <c r="C11" s="31" t="n"/>
+      <c r="D11" s="31" t="n"/>
+      <c r="E11" s="31" t="n"/>
+      <c r="F11" s="31" t="n"/>
+      <c r="G11" s="31" t="n"/>
+      <c r="H11" s="32" t="n"/>
     </row>
     <row r="12" ht="80" customHeight="1" s="29">
       <c r="A12" s="81" t="inlineStr">
@@ -994,13 +1073,13 @@
           <t>AI硬件确定性(付鹏) → 内存=AI核心瓶颈(4信源互锁) → 国产替代加速 → 稀土断供日本 → 芯片/存储/HBM长期利好 | 短期被利率↑/地缘↑压制</t>
         </is>
       </c>
-      <c r="B12" s="82" t="n"/>
-      <c r="C12" s="82" t="n"/>
-      <c r="D12" s="82" t="n"/>
-      <c r="E12" s="82" t="n"/>
-      <c r="F12" s="82" t="n"/>
-      <c r="G12" s="82" t="n"/>
-      <c r="H12" s="83" t="n"/>
+      <c r="B12" s="31" t="n"/>
+      <c r="C12" s="31" t="n"/>
+      <c r="D12" s="31" t="n"/>
+      <c r="E12" s="31" t="n"/>
+      <c r="F12" s="31" t="n"/>
+      <c r="G12" s="31" t="n"/>
+      <c r="H12" s="32" t="n"/>
     </row>
     <row r="13" ht="80" customHeight="1" s="29">
       <c r="A13" s="84" t="inlineStr">
@@ -1008,13 +1087,13 @@
           <t>⚡ 传导: 利率↑→成长股↓ | 地缘↑→避险↑能源↑ | 去杠杆→消费↓养殖↓ | AI产业↑→芯片/存储↑(长期)</t>
         </is>
       </c>
-      <c r="B13" s="82" t="n"/>
-      <c r="C13" s="82" t="n"/>
-      <c r="D13" s="82" t="n"/>
-      <c r="E13" s="82" t="n"/>
-      <c r="F13" s="82" t="n"/>
-      <c r="G13" s="82" t="n"/>
-      <c r="H13" s="83" t="n"/>
+      <c r="B13" s="31" t="n"/>
+      <c r="C13" s="31" t="n"/>
+      <c r="D13" s="31" t="n"/>
+      <c r="E13" s="31" t="n"/>
+      <c r="F13" s="31" t="n"/>
+      <c r="G13" s="31" t="n"/>
+      <c r="H13" s="32" t="n"/>
     </row>
     <row r="14" ht="40" customHeight="1" s="29">
       <c r="A14" s="72" t="inlineStr">
@@ -1049,25 +1128,661 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" s="85" t="inlineStr">
+        <is>
+          <t>🔔 待重仓监控</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="86" t="inlineStr">
+        <is>
+          <t>标的</t>
+        </is>
+      </c>
+      <c r="B17" s="86" t="inlineStr">
+        <is>
+          <t>状态</t>
+        </is>
+      </c>
+      <c r="C17" s="86" t="inlineStr">
+        <is>
+          <t>当前P/价格</t>
+        </is>
+      </c>
+      <c r="D17" s="86" t="inlineStr">
+        <is>
+          <t>最新信号</t>
+        </is>
+      </c>
+      <c r="E17" s="86" t="inlineStr">
+        <is>
+          <t>触发条件</t>
+        </is>
+      </c>
+      <c r="F17" s="86" t="inlineStr">
+        <is>
+          <t>距离触发</t>
+        </is>
+      </c>
+      <c r="G17" s="86" t="inlineStr">
+        <is>
+          <t>跟踪日期</t>
+        </is>
+      </c>
+      <c r="H17" s="86" t="inlineStr">
+        <is>
+          <t>备注</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="87" t="inlineStr">
+        <is>
+          <t>芯片ETF 020628</t>
+        </is>
+      </c>
+      <c r="B18" s="87" t="inlineStr">
+        <is>
+          <t>🟢已持仓</t>
+        </is>
+      </c>
+      <c r="C18" s="88" t="inlineStr">
+        <is>
+          <t>P:59%
+成本2.6854
++40.5%</t>
+        </is>
+      </c>
+      <c r="D18" s="88" t="inlineStr">
+        <is>
+          <t>06-01德银报告
+利率折价被B门吸收
+P值不变</t>
+        </is>
+      </c>
+      <c r="E18" s="88" t="inlineStr">
+        <is>
+          <t>①单日暴跌≥5%
+②累计跌15%+
+③P值≥55%</t>
+        </is>
+      </c>
+      <c r="F18" s="88" t="inlineStr">
+        <is>
+          <t>条件③已满足
+等价跌信号</t>
+        </is>
+      </c>
+      <c r="G18" s="88" t="inlineStr">
+        <is>
+          <t>06-01</t>
+        </is>
+      </c>
+      <c r="H18" s="88" t="inlineStr">
+        <is>
+          <t>长鑫上会
+GTC Taipei
+存储双雄逻辑</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="89" t="inlineStr">
+        <is>
+          <t>澜起科技 688008</t>
+        </is>
+      </c>
+      <c r="B19" s="89" t="inlineStr">
+        <is>
+          <t>🟡未建仓</t>
+        </is>
+      </c>
+      <c r="C19" s="90" t="inlineStr">
+        <is>
+          <t>¥272.29
+PE 130x
+PEG 1.6-2.6</t>
+        </is>
+      </c>
+      <c r="D19" s="90" t="inlineStr">
+        <is>
+          <t>05-26股东询价转让
+(减持利空)
+-4.15%</t>
+        </is>
+      </c>
+      <c r="E19" s="90" t="inlineStr">
+        <is>
+          <t>①单日暴跌≥8%
+②&lt;¥280+平稳
+③P值≥55%</t>
+        </is>
+      </c>
+      <c r="F19" s="90" t="inlineStr">
+        <is>
+          <t>条件②满足
+¥272&lt;¥280</t>
+        </is>
+      </c>
+      <c r="G19" s="90" t="inlineStr">
+        <is>
+          <t>05-26</t>
+        </is>
+      </c>
+      <c r="H19" s="90" t="inlineStr">
+        <is>
+          <t>DDR5龙头
+华为τ定律
+科创板高波动</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="91" t="inlineStr">
+        <is>
+          <t>凯盛科技 600552</t>
+        </is>
+      </c>
+      <c r="B20" s="91" t="inlineStr">
+        <is>
+          <t>🔭观察中</t>
+        </is>
+      </c>
+      <c r="C20" s="92" t="inlineStr">
+        <is>
+          <t>¥19.70
+近5日+10%</t>
+        </is>
+      </c>
+      <c r="D20" s="92" t="inlineStr">
+        <is>
+          <t>05-26追涨不舒服
+等回调</t>
+        </is>
+      </c>
+      <c r="E20" s="92" t="inlineStr">
+        <is>
+          <t>①回调到¥18-18.5
+②蒋宇飞视频分析完
+③手痒&lt;¥500</t>
+        </is>
+      </c>
+      <c r="F20" s="92" t="inlineStr">
+        <is>
+          <t>距¥18.5约-6%</t>
+        </is>
+      </c>
+      <c r="G20" s="92" t="inlineStr">
+        <is>
+          <t>05-26</t>
+        </is>
+      </c>
+      <c r="H20" s="92" t="inlineStr">
+        <is>
+          <t>玻璃基板
+AI封装材料
+蒋宇飞推荐</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="89" t="inlineStr">
+        <is>
+          <t>国产存储双雄</t>
+        </is>
+      </c>
+      <c r="B21" s="89" t="inlineStr">
+        <is>
+          <t>🔥新标记</t>
+        </is>
+      </c>
+      <c r="C21" s="90" t="inlineStr">
+        <is>
+          <t>长鑫DRAM(短)
+长江Flash(长)</t>
+        </is>
+      </c>
+      <c r="D21" s="90" t="inlineStr">
+        <is>
+          <t>06-01蒋宇飞
+存储=硬科技时代
+市值或超腾讯</t>
+        </is>
+      </c>
+      <c r="E21" s="90" t="inlineStr">
+        <is>
+          <t>跟踪长鑫HBM
+长江3D NAND
+A股标的筛选</t>
+        </is>
+      </c>
+      <c r="F21" s="90" t="inlineStr">
+        <is>
+          <t>芯片ETF已覆盖
+需细化标的</t>
+        </is>
+      </c>
+      <c r="G21" s="90" t="inlineStr">
+        <is>
+          <t>06-01</t>
+        </is>
+      </c>
+      <c r="H21" s="90" t="inlineStr">
+        <is>
+          <t>星光纯叠存赛道
+越近GPU越值钱
+澜起上下游</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="85" t="inlineStr">
+        <is>
+          <t>⚡ 事件链追踪</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="86" t="inlineStr">
+        <is>
+          <t>事件</t>
+        </is>
+      </c>
+      <c r="B24" s="86" t="inlineStr">
+        <is>
+          <t>时间</t>
+        </is>
+      </c>
+      <c r="C24" s="86" t="inlineStr">
+        <is>
+          <t>相关标的</t>
+        </is>
+      </c>
+      <c r="D24" s="86" t="inlineStr">
+        <is>
+          <t>状态</t>
+        </is>
+      </c>
+      <c r="E24" s="86" t="inlineStr">
+        <is>
+          <t>影响方向</t>
+        </is>
+      </c>
+      <c r="F24" s="86" t="inlineStr">
+        <is>
+          <t>已落地?</t>
+        </is>
+      </c>
+      <c r="G24" s="86" t="inlineStr">
+        <is>
+          <t>P'虚值</t>
+        </is>
+      </c>
+      <c r="H24" s="86" t="inlineStr">
+        <is>
+          <t>备注</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="92" t="inlineStr">
+        <is>
+          <t>黄仁勋GTC Taipei演讲</t>
+        </is>
+      </c>
+      <c r="B25" s="92" t="inlineStr">
+        <is>
+          <t>06-01</t>
+        </is>
+      </c>
+      <c r="C25" s="92" t="inlineStr">
+        <is>
+          <t>芯片ETF/存储</t>
+        </is>
+      </c>
+      <c r="D25" s="92" t="inlineStr">
+        <is>
+          <t>⏳待发生</t>
+        </is>
+      </c>
+      <c r="E25" s="92" t="inlineStr">
+        <is>
+          <t>🟢利好</t>
+        </is>
+      </c>
+      <c r="F25" s="92" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G25" s="92" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H25" s="92" t="inlineStr">
+        <is>
+          <t>AI算力催化</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="92" t="inlineStr">
+        <is>
+          <t>长鑫存储5月27日上会</t>
+        </is>
+      </c>
+      <c r="B26" s="92" t="inlineStr">
+        <is>
+          <t>05-27</t>
+        </is>
+      </c>
+      <c r="C26" s="92" t="inlineStr">
+        <is>
+          <t>芯片ETF/存储</t>
+        </is>
+      </c>
+      <c r="D26" s="88" t="inlineStr">
+        <is>
+          <t>✅已过</t>
+        </is>
+      </c>
+      <c r="E26" s="92" t="inlineStr">
+        <is>
+          <t>🟢利好</t>
+        </is>
+      </c>
+      <c r="F26" s="92" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G26" s="92" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H26" s="92" t="inlineStr">
+        <is>
+          <t>需确认结果</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="92" t="inlineStr">
+        <is>
+          <t>三星罢工持续性</t>
+        </is>
+      </c>
+      <c r="B27" s="92" t="inlineStr">
+        <is>
+          <t>持续中</t>
+        </is>
+      </c>
+      <c r="C27" s="92" t="inlineStr">
+        <is>
+          <t>芯片ETF/存储</t>
+        </is>
+      </c>
+      <c r="D27" s="92" t="inlineStr">
+        <is>
+          <t>🔄跟踪中</t>
+        </is>
+      </c>
+      <c r="E27" s="92" t="inlineStr">
+        <is>
+          <t>🟢利好</t>
+        </is>
+      </c>
+      <c r="F27" s="92" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G27" s="92" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H27" s="92" t="inlineStr">
+        <is>
+          <t>国产替代窗口</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="92" t="inlineStr">
+        <is>
+          <t>美联储12月前加息58%</t>
+        </is>
+      </c>
+      <c r="B28" s="92" t="inlineStr">
+        <is>
+          <t>德银05-29</t>
+        </is>
+      </c>
+      <c r="C28" s="92" t="inlineStr">
+        <is>
+          <t>全持仓</t>
+        </is>
+      </c>
+      <c r="D28" s="92" t="inlineStr">
+        <is>
+          <t>📋P'虚值</t>
+        </is>
+      </c>
+      <c r="E28" s="93" t="inlineStr">
+        <is>
+          <t>🔴利空</t>
+        </is>
+      </c>
+      <c r="F28" s="92" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G28" s="92" t="inlineStr">
+        <is>
+          <t>芯片-3pp/黄金-2pp</t>
+        </is>
+      </c>
+      <c r="H28" s="92" t="inlineStr">
+        <is>
+          <t>未落地不进主P</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="92" t="inlineStr">
+        <is>
+          <t>沃什软化鹰派立场</t>
+        </is>
+      </c>
+      <c r="B29" s="92" t="inlineStr">
+        <is>
+          <t>德银05-29</t>
+        </is>
+      </c>
+      <c r="C29" s="92" t="inlineStr">
+        <is>
+          <t>黄金/芯片</t>
+        </is>
+      </c>
+      <c r="D29" s="92" t="inlineStr">
+        <is>
+          <t>📋P'虚值</t>
+        </is>
+      </c>
+      <c r="E29" s="92" t="inlineStr">
+        <is>
+          <t>🟢利好</t>
+        </is>
+      </c>
+      <c r="F29" s="92" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G29" s="92" t="inlineStr">
+        <is>
+          <t>黄金+2pp/芯片+1pp</t>
+        </is>
+      </c>
+      <c r="H29" s="92" t="inlineStr">
+        <is>
+          <t>新主席不确定性</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="92" t="inlineStr">
+        <is>
+          <t>伊朗3.0反击/海峡封锁</t>
+        </is>
+      </c>
+      <c r="B30" s="92" t="inlineStr">
+        <is>
+          <t>05-30宋鸿兵</t>
+        </is>
+      </c>
+      <c r="C30" s="92" t="inlineStr">
+        <is>
+          <t>有色/黄金/原油</t>
+        </is>
+      </c>
+      <c r="D30" s="92" t="inlineStr">
+        <is>
+          <t>🔄跟踪中</t>
+        </is>
+      </c>
+      <c r="E30" s="92" t="inlineStr">
+        <is>
+          <t>🟢利好</t>
+        </is>
+      </c>
+      <c r="F30" s="92" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G30" s="92" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H30" s="92" t="inlineStr">
+        <is>
+          <t>地缘风险升级</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="92" t="inlineStr">
+        <is>
+          <t>德银报告:ETF需求-78%</t>
+        </is>
+      </c>
+      <c r="B31" s="92" t="inlineStr">
+        <is>
+          <t>05-29</t>
+        </is>
+      </c>
+      <c r="C31" s="92" t="inlineStr">
+        <is>
+          <t>黄金</t>
+        </is>
+      </c>
+      <c r="D31" s="88" t="inlineStr">
+        <is>
+          <t>✅已落地</t>
+        </is>
+      </c>
+      <c r="E31" s="93" t="inlineStr">
+        <is>
+          <t>🔴利空</t>
+        </is>
+      </c>
+      <c r="F31" s="92" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G31" s="92" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H31" s="92" t="inlineStr">
+        <is>
+          <t>已扣-3pp</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="92" t="inlineStr">
+        <is>
+          <t>德银报告:央行购金+38%</t>
+        </is>
+      </c>
+      <c r="B32" s="92" t="inlineStr">
+        <is>
+          <t>05-29</t>
+        </is>
+      </c>
+      <c r="C32" s="92" t="inlineStr">
+        <is>
+          <t>黄金</t>
+        </is>
+      </c>
+      <c r="D32" s="88" t="inlineStr">
+        <is>
+          <t>✅已落地</t>
+        </is>
+      </c>
+      <c r="E32" s="92" t="inlineStr">
+        <is>
+          <t>🟢利好</t>
+        </is>
+      </c>
+      <c r="F32" s="92" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G32" s="92" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H32" s="92" t="inlineStr">
+        <is>
+          <t>已加+1pp</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="17">
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="G4:H4"/>
-    <mergeCell ref="A12:H12"/>
+  <mergeCells count="19">
+    <mergeCell ref="A11:H11"/>
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="G8:H8"/>
+    <mergeCell ref="A6:B6"/>
     <mergeCell ref="A7:B7"/>
     <mergeCell ref="G7:H7"/>
+    <mergeCell ref="A16:H16"/>
+    <mergeCell ref="G6:H6"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="G3:H3"/>
+    <mergeCell ref="A12:H12"/>
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="A5:B5"/>
     <mergeCell ref="G5:H5"/>
+    <mergeCell ref="A23:H23"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="G4:H4"/>
     <mergeCell ref="A13:H13"/>
-    <mergeCell ref="A11:H11"/>
-    <mergeCell ref="G6:H6"/>
-    <mergeCell ref="A1:H1"/>
-    <mergeCell ref="G8:H8"/>
     <mergeCell ref="G9:H9"/>
-    <mergeCell ref="G3:H3"/>
-    <mergeCell ref="A3:B3"/>
-    <mergeCell ref="A6:B6"/>
   </mergeCells>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>

--- a/持仓贝叶斯跟踪.xlsx
+++ b/持仓贝叶斯跟踪.xlsx
@@ -308,7 +308,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="94">
+  <cellXfs count="95">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -582,6 +582,9 @@
     </xf>
     <xf numFmtId="0" fontId="18" fillId="17" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -836,7 +839,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:H32"/>
+  <dimension ref="A1:H33"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6171875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="22" customWidth="1" style="28" min="1" max="8"/>
@@ -1053,6 +1056,7 @@
       </c>
       <c r="H9" s="31" t="n"/>
     </row>
+    <row r="10"/>
     <row r="11" ht="15" customHeight="1" s="29">
       <c r="A11" s="80" t="inlineStr">
         <is>
@@ -1128,6 +1132,7 @@
         </is>
       </c>
     </row>
+    <row r="15"/>
     <row r="16">
       <c r="A16" s="85" t="inlineStr">
         <is>
@@ -1377,6 +1382,7 @@
         </is>
       </c>
     </row>
+    <row r="22"/>
     <row r="23">
       <c r="A23" s="85" t="inlineStr">
         <is>
@@ -1762,6 +1768,7 @@
         </is>
       </c>
     </row>
+    <row r="33"/>
   </sheetData>
   <mergeCells count="19">
     <mergeCell ref="A11:H11"/>

--- a/持仓贝叶斯跟踪.xlsx
+++ b/持仓贝叶斯跟踪.xlsx
@@ -839,7 +839,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:H33"/>
+  <dimension ref="A1:H79"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6171875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="22" customWidth="1" style="28" min="1" max="8"/>
@@ -1056,7 +1056,6 @@
       </c>
       <c r="H9" s="31" t="n"/>
     </row>
-    <row r="10"/>
     <row r="11" ht="15" customHeight="1" s="29">
       <c r="A11" s="80" t="inlineStr">
         <is>
@@ -1132,7 +1131,6 @@
         </is>
       </c>
     </row>
-    <row r="15"/>
     <row r="16">
       <c r="A16" s="85" t="inlineStr">
         <is>
@@ -1382,7 +1380,6 @@
         </is>
       </c>
     </row>
-    <row r="22"/>
     <row r="23">
       <c r="A23" s="85" t="inlineStr">
         <is>
@@ -1768,7 +1765,328 @@
         </is>
       </c>
     </row>
-    <row r="33"/>
+    <row r="34">
+      <c r="A34" s="94" t="inlineStr">
+        <is>
+          <t>2026-06-01 16:17:13 付鹏的财经世界 - 通胀不一定是坏事，通缩也不一定是好事 #财经 #认知 #思维</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="94" t="inlineStr">
+        <is>
+          <t>2026-06-01 16:17:35 付鹏的财经世界 - 当实控人年龄过大，公司的发展就不是他最重要的事了 #创业者</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="94" t="inlineStr">
+        <is>
+          <t>2026-06-01 16:18:09 付鹏的财经世界 - 所有人都在“去杠杆”的时候，就没有人过得好了 #化债 #经济</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="94" t="inlineStr">
+        <is>
+          <t>2026-06-01 16:18:34 付鹏的财经世界 - 韩国上线三星、海力士ETF，背后的逻辑是什么？ #三星 #海</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="94" t="inlineStr">
+        <is>
+          <t>2026-06-01 16:18:56 伊娃新营销 - 美国PEDV疫情如何改写行业规则？ 全球猪周期启示录07:美</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="94" t="inlineStr">
+        <is>
+          <t>2026-06-01 16:19:46 伊娃新营销 - 西贝危机公关 伊娃聊品牌02:西贝贾国龙：越强硬，舆论越反弹</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="94" t="inlineStr">
+        <is>
+          <t>2026-06-01 16:20:35 伊娃新营销 - 厄尔尼诺对农牧业的影响 超级厄尔尼诺来袭！它正在改写农牧业的</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="94" t="inlineStr">
+        <is>
+          <t>2026-06-01 16:21:22 伊娃新营销 - 双汇2011年瘦肉精事件 娃聊品牌01:双汇2011：121</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="94" t="inlineStr">
+        <is>
+          <t>2026-06-01 16:22:41 伊娃新营销 - 猪周期会消失吗？ 全球猪周期启示录（收官）09:猪周期会消失</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="94" t="inlineStr">
+        <is>
+          <t>2026-06-01 16:23:27 但斌 - 2026年5月29日，夜聚新加坡，凉风拂面格外惬意。梁瑞安老</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="94" t="inlineStr">
+        <is>
+          <t>2026-06-01 16:24:21 但斌 - 2026年5月28日，上过两次课，还没有参观过校园，课后跟随</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="94" t="inlineStr">
+        <is>
+          <t>2026-06-01 16:25:52 但斌 - 2026年5月26号中午，饭后，卫东兄提议前往附近的博物馆，</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="94" t="inlineStr">
+        <is>
+          <t>2026-06-01 16:26:55 宋鸿兵观天下 - 美国金融市场对油价极其乐观！ #宋鸿兵 #霍尔木兹海峡 #石</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="94" t="inlineStr">
+        <is>
+          <t>2026-06-01 16:31:16 岩松笔记 - 如何靠基本面选题材主线？</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="94" t="inlineStr">
+        <is>
+          <t>2026-06-01 16:33:45 岩松笔记 - 平仓线下调，是放宽还是风控？</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="94" t="inlineStr">
+        <is>
+          <t>2026-06-01 16:34:59 拿幸·AI启示录 - GPT 饿死、Claude 囚禁、Gemini 犯罪 Gro</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="94" t="inlineStr">
+        <is>
+          <t>2026-06-01 16:42:16 拿幸·AI启示录 - 1170亿人的生死簿被AI连夜算尽：你抽到的那条命 大概率活</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="94" t="inlineStr">
+        <is>
+          <t>2026-06-01 16:44:44 拿幸·AI启示录 - AI 终结衰退：经济永远涨，普通人永远穷 16 年无衰退！A</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="94" t="inlineStr">
+        <is>
+          <t>2026-06-01 16:49:30 生猪贸易~芳姐(山东) - 奶多多19元30包</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="94" t="inlineStr">
+        <is>
+          <t>2026-06-01 16:50:25 生猪贸易~芳姐(山东) - 一包开口料顺丰包邮#养猪#养猪人#开口料</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="94" t="inlineStr">
+        <is>
+          <t>2026-06-01 16:51:01 生猪贸易~芳姐(山东) - 黄金多维10包送1包#养猪#养猪人#抗应激</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="94" t="inlineStr">
+        <is>
+          <t>2026-06-01 16:52:33 蒋宇飞商业 - 国产存储双雄崛起，揭开未来十年新的财富机遇</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="94" t="inlineStr">
+        <is>
+          <t>2026-06-01 16:53:30 蒋宇飞商业 - 经常在家做饭的男人，大概率是穷人</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="94" t="inlineStr">
+        <is>
+          <t>2026-06-01 16:54:36 蒋宇飞商业 - 用产业思维抓住科技龙头，赢在重注时刻</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="94" t="inlineStr">
+        <is>
+          <t>2026-06-01 16:56:36 蒋宇飞商业 - 互联网没有创造新的经济，而硬科技才是未来的财富主线</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="94" t="inlineStr">
+        <is>
+          <t>2026-06-01 16:58:08 长坡厚雪 - 拼多多25年利息收入256亿 #拼多多 #价值投资 #股票</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="94" t="inlineStr">
+        <is>
+          <t>2026-06-01 17:01:05 长坡厚雪 - 风味纳斯达克 #纳斯达克 #富途 #长桥 #老虎证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="94" t="inlineStr">
+        <is>
+          <t>2026-06-01 17:01:56 长坡厚雪 - 拼多多的未来现金流折现 #拼多多 #段永平 #价值投资 #股</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="94" t="inlineStr">
+        <is>
+          <t>2026-06-01 17:02:57 闭眼看世界 - 日本为何倒贴送房没人要？【抖音独家】 #零基础看懂全球</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="94" t="inlineStr">
+        <is>
+          <t>2026-06-01 17:06:50 闭眼看世界 - 欧洲人为什么认为美国威胁变大了？【抖音独家】 #零基础看懂全</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="94" t="inlineStr">
+        <is>
+          <t>2026-06-01 17:09:23 闭眼看世界 - 特朗普版美元？【抖音独家】 #零基础看懂全球   #全球创作</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="94" t="inlineStr">
+        <is>
+          <t>2026-06-01 17:10:14 闭眼看世界 - 美国为何举办“增强运动会”？【抖音独家】 #零基础看懂全球</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="94" t="inlineStr">
+        <is>
+          <t>2026-06-01 17:11:21 闭眼看世界 - 加拿大的选择？【抖音独家】 #零基础看懂全球   #全球创作</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="94" t="inlineStr">
+        <is>
+          <t>2026-06-01 18:07:59 宋鸿兵观天下 - 美俄元首接踵到访，世界对表北京时间！ #宋鸿兵 #普京访华</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="94" t="inlineStr">
+        <is>
+          <t>2026-06-01 18:08:17 岩松笔记 - 国内存储行业会陷入内卷吗？</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="94" t="inlineStr">
+        <is>
+          <t>2026-06-01 18:09:36 拿幸·AI启示录 - Claude Opus 4.8来了！两个0%改写历史 估值9</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="94" t="inlineStr">
+        <is>
+          <t>2026-06-01 18:10:11 拿幸·AI启示录 - AI 编程正式工业化，Claude Code首发「自愈」功能</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="94" t="inlineStr">
+        <is>
+          <t>2026-06-01 18:10:46 猪猪女王 - #猪价#猪猪女王养二妮 #养殖 #养猪人</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="94" t="inlineStr">
+        <is>
+          <t>2026-06-01 18:11:01 猪猪女王 - #养殖 #所有养猪人 #猪价</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="94" t="inlineStr">
+        <is>
+          <t>2026-06-01 18:11:20 生猪贸易~芳姐(山东) - 4%核心料，1包顺丰送到家#大猪 #养猪#养猪人</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="94" t="inlineStr">
+        <is>
+          <t>2026-06-01 18:12:31 蒋宇飞商业 - 看懂存力 算力 运力，吃透未来10年的AI红利</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="94" t="inlineStr">
+        <is>
+          <t>2026-06-01 18:12:50 长坡厚雪 - 支付宝怎么选纳斯达克基金 #纳斯达克 #支付宝 #基金</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="94" t="inlineStr">
+        <is>
+          <t>2026-06-01 18:13:05 长坡厚雪 - 拼多多平台与商家的矛盾 #拼多多 #开市客 #价值投资 #股</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="94" t="inlineStr">
+        <is>
+          <t>2026-06-01 18:13:30 闭眼看世界 - 美日印澳想要做什么？【抖音独家】 #零基础看懂全球 #全球创</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="94" t="inlineStr">
+        <is>
+          <t>2026-06-01 18:15:33 闭眼看世界 - 释永信的结局？</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="94" t="inlineStr">
+        <is>
+          <t>2026-06-01 18:16:21 飞阅硬核财经 - 一分钟给你讲明白天孚通信 #天孚通信 #商业知识 #认知 #</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="19">
     <mergeCell ref="A11:H11"/>

--- a/持仓贝叶斯跟踪.xlsx
+++ b/持仓贝叶斯跟踪.xlsx
@@ -839,7 +839,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:H79"/>
+  <dimension ref="A1:H131"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6171875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="22" customWidth="1" style="28" min="1" max="8"/>
@@ -2084,6 +2084,363 @@
       <c r="A79" s="94" t="inlineStr">
         <is>
           <t>2026-06-01 18:16:21 飞阅硬核财经 - 一分钟给你讲明白天孚通信 #天孚通信 #商业知识 #认知 #</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="94" t="inlineStr">
+        <is>
+          <t>2026-06-01 16:17:13 付鹏的财经世界 - 通胀不一定是坏事，通缩也不一定是好事 #财经 #认知 #思维</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="94" t="inlineStr">
+        <is>
+          <t>2026-06-01 16:17:35 付鹏的财经世界 - 当实控人年龄过大，公司的发展就不是他最重要的事了 #创业者</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="94" t="inlineStr">
+        <is>
+          <t>2026-06-01 16:18:09 付鹏的财经世界 - 所有人都在“去杠杆”的时候，就没有人过得好了 #化债 #经济</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="94" t="inlineStr">
+        <is>
+          <t>2026-06-01 16:18:34 付鹏的财经世界 - 韩国上线三星、海力士ETF，背后的逻辑是什么？ #三星 #海</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="94" t="inlineStr">
+        <is>
+          <t>2026-06-01 16:18:56 伊娃新营销 - 美国PEDV疫情如何改写行业规则？ 全球猪周期启示录07:美</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="94" t="inlineStr">
+        <is>
+          <t>2026-06-01 16:19:46 伊娃新营销 - 西贝危机公关 伊娃聊品牌02:西贝贾国龙：越强硬，舆论越反弹</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="94" t="inlineStr">
+        <is>
+          <t>2026-06-01 16:20:35 伊娃新营销 - 厄尔尼诺对农牧业的影响 超级厄尔尼诺来袭！它正在改写农牧业的</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="94" t="inlineStr">
+        <is>
+          <t>2026-06-01 16:21:22 伊娃新营销 - 双汇2011年瘦肉精事件 娃聊品牌01:双汇2011：121</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="94" t="inlineStr">
+        <is>
+          <t>2026-06-01 16:22:41 伊娃新营销 - 猪周期会消失吗？ 全球猪周期启示录（收官）09:猪周期会消失</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="94" t="inlineStr">
+        <is>
+          <t>2026-06-01 16:23:27 但斌 - 2026年5月29日，夜聚新加坡，凉风拂面格外惬意。梁瑞安老</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="94" t="inlineStr">
+        <is>
+          <t>2026-06-01 16:24:21 但斌 - 2026年5月28日，上过两次课，还没有参观过校园，课后跟随</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="94" t="inlineStr">
+        <is>
+          <t>2026-06-01 16:25:52 但斌 - 2026年5月26号中午，饭后，卫东兄提议前往附近的博物馆，</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="94" t="inlineStr">
+        <is>
+          <t>2026-06-01 16:26:55 宋鸿兵观天下 - 美国金融市场对油价极其乐观！ #宋鸿兵 #霍尔木兹海峡 #石</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="94" t="inlineStr">
+        <is>
+          <t>2026-06-01 16:31:16 岩松笔记 - 如何靠基本面选题材主线？</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="94" t="inlineStr">
+        <is>
+          <t>2026-06-01 16:33:45 岩松笔记 - 平仓线下调，是放宽还是风控？</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="94" t="inlineStr">
+        <is>
+          <t>2026-06-01 16:34:59 拿幸·AI启示录 - GPT 饿死、Claude 囚禁、Gemini 犯罪 Gro</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="94" t="inlineStr">
+        <is>
+          <t>2026-06-01 16:42:16 拿幸·AI启示录 - 1170亿人的生死簿被AI连夜算尽：你抽到的那条命 大概率活</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="94" t="inlineStr">
+        <is>
+          <t>2026-06-01 16:44:44 拿幸·AI启示录 - AI 终结衰退：经济永远涨，普通人永远穷 16 年无衰退！A</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="94" t="inlineStr">
+        <is>
+          <t>2026-06-01 16:49:30 生猪贸易~芳姐(山东) - 奶多多19元30包</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="94" t="inlineStr">
+        <is>
+          <t>2026-06-01 16:50:25 生猪贸易~芳姐(山东) - 一包开口料顺丰包邮#养猪#养猪人#开口料</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="94" t="inlineStr">
+        <is>
+          <t>2026-06-01 16:51:01 生猪贸易~芳姐(山东) - 黄金多维10包送1包#养猪#养猪人#抗应激</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="94" t="inlineStr">
+        <is>
+          <t>2026-06-01 16:52:33 蒋宇飞商业 - 国产存储双雄崛起，揭开未来十年新的财富机遇</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="94" t="inlineStr">
+        <is>
+          <t>2026-06-01 16:53:30 蒋宇飞商业 - 经常在家做饭的男人，大概率是穷人</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="94" t="inlineStr">
+        <is>
+          <t>2026-06-01 16:54:36 蒋宇飞商业 - 用产业思维抓住科技龙头，赢在重注时刻</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="94" t="inlineStr">
+        <is>
+          <t>2026-06-01 16:56:36 蒋宇飞商业 - 互联网没有创造新的经济，而硬科技才是未来的财富主线</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="94" t="inlineStr">
+        <is>
+          <t>2026-06-01 16:58:08 长坡厚雪 - 拼多多25年利息收入256亿 #拼多多 #价值投资 #股票</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="94" t="inlineStr">
+        <is>
+          <t>2026-06-01 17:01:05 长坡厚雪 - 风味纳斯达克 #纳斯达克 #富途 #长桥 #老虎证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="94" t="inlineStr">
+        <is>
+          <t>2026-06-01 17:01:56 长坡厚雪 - 拼多多的未来现金流折现 #拼多多 #段永平 #价值投资 #股</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="94" t="inlineStr">
+        <is>
+          <t>2026-06-01 17:02:57 闭眼看世界 - 日本为何倒贴送房没人要？【抖音独家】 #零基础看懂全球</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="94" t="inlineStr">
+        <is>
+          <t>2026-06-01 17:06:50 闭眼看世界 - 欧洲人为什么认为美国威胁变大了？【抖音独家】 #零基础看懂全</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="94" t="inlineStr">
+        <is>
+          <t>2026-06-01 17:09:23 闭眼看世界 - 特朗普版美元？【抖音独家】 #零基础看懂全球   #全球创作</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="94" t="inlineStr">
+        <is>
+          <t>2026-06-01 17:10:14 闭眼看世界 - 美国为何举办“增强运动会”？【抖音独家】 #零基础看懂全球</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="94" t="inlineStr">
+        <is>
+          <t>2026-06-01 17:11:21 闭眼看世界 - 加拿大的选择？【抖音独家】 #零基础看懂全球   #全球创作</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="94" t="inlineStr">
+        <is>
+          <t>2026-06-01 18:07:59 宋鸿兵观天下 - 美俄元首接踵到访，世界对表北京时间！ #宋鸿兵 #普京访华</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="94" t="inlineStr">
+        <is>
+          <t>2026-06-01 18:08:17 岩松笔记 - 国内存储行业会陷入内卷吗？</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="94" t="inlineStr">
+        <is>
+          <t>2026-06-01 18:09:36 拿幸·AI启示录 - Claude Opus 4.8来了！两个0%改写历史 估值9</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="94" t="inlineStr">
+        <is>
+          <t>2026-06-01 18:10:11 拿幸·AI启示录 - AI 编程正式工业化，Claude Code首发「自愈」功能</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="94" t="inlineStr">
+        <is>
+          <t>2026-06-01 18:10:46 猪猪女王 - #猪价#猪猪女王养二妮 #养殖 #养猪人</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="94" t="inlineStr">
+        <is>
+          <t>2026-06-01 18:11:01 猪猪女王 - #养殖 #所有养猪人 #猪价</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="94" t="inlineStr">
+        <is>
+          <t>2026-06-01 18:11:20 生猪贸易~芳姐(山东) - 4%核心料，1包顺丰送到家#大猪 #养猪#养猪人</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="94" t="inlineStr">
+        <is>
+          <t>2026-06-01 18:12:31 蒋宇飞商业 - 看懂存力 算力 运力，吃透未来10年的AI红利</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="94" t="inlineStr">
+        <is>
+          <t>2026-06-01 18:12:50 长坡厚雪 - 支付宝怎么选纳斯达克基金 #纳斯达克 #支付宝 #基金</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="94" t="inlineStr">
+        <is>
+          <t>2026-06-01 18:13:05 长坡厚雪 - 拼多多平台与商家的矛盾 #拼多多 #开市客 #价值投资 #股</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="94" t="inlineStr">
+        <is>
+          <t>2026-06-01 18:13:30 闭眼看世界 - 美日印澳想要做什么？【抖音独家】 #零基础看懂全球 #全球创</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="94" t="inlineStr">
+        <is>
+          <t>2026-06-01 18:15:33 闭眼看世界 - 释永信的结局？</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="94" t="inlineStr">
+        <is>
+          <t>2026-06-01 18:16:21 飞阅硬核财经 - 一分钟给你讲明白天孚通信 #天孚通信 #商业知识 #认知 #</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="94" t="inlineStr">
+        <is>
+          <t>2026-06-01 18:41:12 宋鸿兵观天下 - 美国金融市场深陷“迷之自信”？ #宋鸿兵 #美债 #美股 #</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="94" t="inlineStr">
+        <is>
+          <t>2026-06-01 18:41:35 岩松笔记 - 20倍PE的腾讯怎么看？</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="94" t="inlineStr">
+        <is>
+          <t>2026-06-01 18:42:20 拿幸·AI启示录 - 封神还是欺诈？Claude 4.8 真相：算力堆出来的分裂</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="94" t="inlineStr">
+        <is>
+          <t>2026-06-01 18:42:34 猪猪女王 - #猪价 #养殖 #养猪人不容易 #所有养猪人</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="94" t="inlineStr">
+        <is>
+          <t>2026-06-01 18:43:03 闭眼看世界 - 欧洲与美国的差别？【抖音独家】 #零基础看懂全球   #全球</t>
         </is>
       </c>
     </row>

--- a/持仓贝叶斯跟踪.xlsx
+++ b/持仓贝叶斯跟踪.xlsx
@@ -839,7 +839,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:H131"/>
+  <dimension ref="A1:H34"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6171875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="22" customWidth="1" style="28" min="1" max="8"/>
@@ -1056,6 +1056,7 @@
       </c>
       <c r="H9" s="31" t="n"/>
     </row>
+    <row r="10"/>
     <row r="11" ht="15" customHeight="1" s="29">
       <c r="A11" s="80" t="inlineStr">
         <is>
@@ -1131,6 +1132,7 @@
         </is>
       </c>
     </row>
+    <row r="15"/>
     <row r="16">
       <c r="A16" s="85" t="inlineStr">
         <is>
@@ -1380,6 +1382,7 @@
         </is>
       </c>
     </row>
+    <row r="22"/>
     <row r="23">
       <c r="A23" s="85" t="inlineStr">
         <is>
@@ -1765,685 +1768,8 @@
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="94" t="inlineStr">
-        <is>
-          <t>2026-06-01 16:17:13 付鹏的财经世界 - 通胀不一定是坏事，通缩也不一定是好事 #财经 #认知 #思维</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="94" t="inlineStr">
-        <is>
-          <t>2026-06-01 16:17:35 付鹏的财经世界 - 当实控人年龄过大，公司的发展就不是他最重要的事了 #创业者</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="94" t="inlineStr">
-        <is>
-          <t>2026-06-01 16:18:09 付鹏的财经世界 - 所有人都在“去杠杆”的时候，就没有人过得好了 #化债 #经济</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="94" t="inlineStr">
-        <is>
-          <t>2026-06-01 16:18:34 付鹏的财经世界 - 韩国上线三星、海力士ETF，背后的逻辑是什么？ #三星 #海</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="94" t="inlineStr">
-        <is>
-          <t>2026-06-01 16:18:56 伊娃新营销 - 美国PEDV疫情如何改写行业规则？ 全球猪周期启示录07:美</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="94" t="inlineStr">
-        <is>
-          <t>2026-06-01 16:19:46 伊娃新营销 - 西贝危机公关 伊娃聊品牌02:西贝贾国龙：越强硬，舆论越反弹</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="94" t="inlineStr">
-        <is>
-          <t>2026-06-01 16:20:35 伊娃新营销 - 厄尔尼诺对农牧业的影响 超级厄尔尼诺来袭！它正在改写农牧业的</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="94" t="inlineStr">
-        <is>
-          <t>2026-06-01 16:21:22 伊娃新营销 - 双汇2011年瘦肉精事件 娃聊品牌01:双汇2011：121</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="94" t="inlineStr">
-        <is>
-          <t>2026-06-01 16:22:41 伊娃新营销 - 猪周期会消失吗？ 全球猪周期启示录（收官）09:猪周期会消失</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="94" t="inlineStr">
-        <is>
-          <t>2026-06-01 16:23:27 但斌 - 2026年5月29日，夜聚新加坡，凉风拂面格外惬意。梁瑞安老</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="94" t="inlineStr">
-        <is>
-          <t>2026-06-01 16:24:21 但斌 - 2026年5月28日，上过两次课，还没有参观过校园，课后跟随</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="94" t="inlineStr">
-        <is>
-          <t>2026-06-01 16:25:52 但斌 - 2026年5月26号中午，饭后，卫东兄提议前往附近的博物馆，</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="94" t="inlineStr">
-        <is>
-          <t>2026-06-01 16:26:55 宋鸿兵观天下 - 美国金融市场对油价极其乐观！ #宋鸿兵 #霍尔木兹海峡 #石</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="94" t="inlineStr">
-        <is>
-          <t>2026-06-01 16:31:16 岩松笔记 - 如何靠基本面选题材主线？</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="94" t="inlineStr">
-        <is>
-          <t>2026-06-01 16:33:45 岩松笔记 - 平仓线下调，是放宽还是风控？</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="94" t="inlineStr">
-        <is>
-          <t>2026-06-01 16:34:59 拿幸·AI启示录 - GPT 饿死、Claude 囚禁、Gemini 犯罪 Gro</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="94" t="inlineStr">
-        <is>
-          <t>2026-06-01 16:42:16 拿幸·AI启示录 - 1170亿人的生死簿被AI连夜算尽：你抽到的那条命 大概率活</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="94" t="inlineStr">
-        <is>
-          <t>2026-06-01 16:44:44 拿幸·AI启示录 - AI 终结衰退：经济永远涨，普通人永远穷 16 年无衰退！A</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="94" t="inlineStr">
-        <is>
-          <t>2026-06-01 16:49:30 生猪贸易~芳姐(山东) - 奶多多19元30包</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="94" t="inlineStr">
-        <is>
-          <t>2026-06-01 16:50:25 生猪贸易~芳姐(山东) - 一包开口料顺丰包邮#养猪#养猪人#开口料</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="94" t="inlineStr">
-        <is>
-          <t>2026-06-01 16:51:01 生猪贸易~芳姐(山东) - 黄金多维10包送1包#养猪#养猪人#抗应激</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="94" t="inlineStr">
-        <is>
-          <t>2026-06-01 16:52:33 蒋宇飞商业 - 国产存储双雄崛起，揭开未来十年新的财富机遇</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="94" t="inlineStr">
-        <is>
-          <t>2026-06-01 16:53:30 蒋宇飞商业 - 经常在家做饭的男人，大概率是穷人</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="94" t="inlineStr">
-        <is>
-          <t>2026-06-01 16:54:36 蒋宇飞商业 - 用产业思维抓住科技龙头，赢在重注时刻</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="94" t="inlineStr">
-        <is>
-          <t>2026-06-01 16:56:36 蒋宇飞商业 - 互联网没有创造新的经济，而硬科技才是未来的财富主线</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="94" t="inlineStr">
-        <is>
-          <t>2026-06-01 16:58:08 长坡厚雪 - 拼多多25年利息收入256亿 #拼多多 #价值投资 #股票</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="94" t="inlineStr">
-        <is>
-          <t>2026-06-01 17:01:05 长坡厚雪 - 风味纳斯达克 #纳斯达克 #富途 #长桥 #老虎证券</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="94" t="inlineStr">
-        <is>
-          <t>2026-06-01 17:01:56 长坡厚雪 - 拼多多的未来现金流折现 #拼多多 #段永平 #价值投资 #股</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="94" t="inlineStr">
-        <is>
-          <t>2026-06-01 17:02:57 闭眼看世界 - 日本为何倒贴送房没人要？【抖音独家】 #零基础看懂全球</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="94" t="inlineStr">
-        <is>
-          <t>2026-06-01 17:06:50 闭眼看世界 - 欧洲人为什么认为美国威胁变大了？【抖音独家】 #零基础看懂全</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="94" t="inlineStr">
-        <is>
-          <t>2026-06-01 17:09:23 闭眼看世界 - 特朗普版美元？【抖音独家】 #零基础看懂全球   #全球创作</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" s="94" t="inlineStr">
-        <is>
-          <t>2026-06-01 17:10:14 闭眼看世界 - 美国为何举办“增强运动会”？【抖音独家】 #零基础看懂全球</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" s="94" t="inlineStr">
-        <is>
-          <t>2026-06-01 17:11:21 闭眼看世界 - 加拿大的选择？【抖音独家】 #零基础看懂全球   #全球创作</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" s="94" t="inlineStr">
-        <is>
-          <t>2026-06-01 18:07:59 宋鸿兵观天下 - 美俄元首接踵到访，世界对表北京时间！ #宋鸿兵 #普京访华</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" s="94" t="inlineStr">
-        <is>
-          <t>2026-06-01 18:08:17 岩松笔记 - 国内存储行业会陷入内卷吗？</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" s="94" t="inlineStr">
-        <is>
-          <t>2026-06-01 18:09:36 拿幸·AI启示录 - Claude Opus 4.8来了！两个0%改写历史 估值9</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="94" t="inlineStr">
-        <is>
-          <t>2026-06-01 18:10:11 拿幸·AI启示录 - AI 编程正式工业化，Claude Code首发「自愈」功能</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" s="94" t="inlineStr">
-        <is>
-          <t>2026-06-01 18:10:46 猪猪女王 - #猪价#猪猪女王养二妮 #养殖 #养猪人</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" s="94" t="inlineStr">
-        <is>
-          <t>2026-06-01 18:11:01 猪猪女王 - #养殖 #所有养猪人 #猪价</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" s="94" t="inlineStr">
-        <is>
-          <t>2026-06-01 18:11:20 生猪贸易~芳姐(山东) - 4%核心料，1包顺丰送到家#大猪 #养猪#养猪人</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" s="94" t="inlineStr">
-        <is>
-          <t>2026-06-01 18:12:31 蒋宇飞商业 - 看懂存力 算力 运力，吃透未来10年的AI红利</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" s="94" t="inlineStr">
-        <is>
-          <t>2026-06-01 18:12:50 长坡厚雪 - 支付宝怎么选纳斯达克基金 #纳斯达克 #支付宝 #基金</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" s="94" t="inlineStr">
-        <is>
-          <t>2026-06-01 18:13:05 长坡厚雪 - 拼多多平台与商家的矛盾 #拼多多 #开市客 #价值投资 #股</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" s="94" t="inlineStr">
-        <is>
-          <t>2026-06-01 18:13:30 闭眼看世界 - 美日印澳想要做什么？【抖音独家】 #零基础看懂全球 #全球创</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" s="94" t="inlineStr">
-        <is>
-          <t>2026-06-01 18:15:33 闭眼看世界 - 释永信的结局？</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" s="94" t="inlineStr">
-        <is>
-          <t>2026-06-01 18:16:21 飞阅硬核财经 - 一分钟给你讲明白天孚通信 #天孚通信 #商业知识 #认知 #</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" s="94" t="inlineStr">
-        <is>
-          <t>2026-06-01 16:17:13 付鹏的财经世界 - 通胀不一定是坏事，通缩也不一定是好事 #财经 #认知 #思维</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" s="94" t="inlineStr">
-        <is>
-          <t>2026-06-01 16:17:35 付鹏的财经世界 - 当实控人年龄过大，公司的发展就不是他最重要的事了 #创业者</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" s="94" t="inlineStr">
-        <is>
-          <t>2026-06-01 16:18:09 付鹏的财经世界 - 所有人都在“去杠杆”的时候，就没有人过得好了 #化债 #经济</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" s="94" t="inlineStr">
-        <is>
-          <t>2026-06-01 16:18:34 付鹏的财经世界 - 韩国上线三星、海力士ETF，背后的逻辑是什么？ #三星 #海</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" s="94" t="inlineStr">
-        <is>
-          <t>2026-06-01 16:18:56 伊娃新营销 - 美国PEDV疫情如何改写行业规则？ 全球猪周期启示录07:美</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" s="94" t="inlineStr">
-        <is>
-          <t>2026-06-01 16:19:46 伊娃新营销 - 西贝危机公关 伊娃聊品牌02:西贝贾国龙：越强硬，舆论越反弹</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" s="94" t="inlineStr">
-        <is>
-          <t>2026-06-01 16:20:35 伊娃新营销 - 厄尔尼诺对农牧业的影响 超级厄尔尼诺来袭！它正在改写农牧业的</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" s="94" t="inlineStr">
-        <is>
-          <t>2026-06-01 16:21:22 伊娃新营销 - 双汇2011年瘦肉精事件 娃聊品牌01:双汇2011：121</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" s="94" t="inlineStr">
-        <is>
-          <t>2026-06-01 16:22:41 伊娃新营销 - 猪周期会消失吗？ 全球猪周期启示录（收官）09:猪周期会消失</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" s="94" t="inlineStr">
-        <is>
-          <t>2026-06-01 16:23:27 但斌 - 2026年5月29日，夜聚新加坡，凉风拂面格外惬意。梁瑞安老</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" s="94" t="inlineStr">
-        <is>
-          <t>2026-06-01 16:24:21 但斌 - 2026年5月28日，上过两次课，还没有参观过校园，课后跟随</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" s="94" t="inlineStr">
-        <is>
-          <t>2026-06-01 16:25:52 但斌 - 2026年5月26号中午，饭后，卫东兄提议前往附近的博物馆，</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" s="94" t="inlineStr">
-        <is>
-          <t>2026-06-01 16:26:55 宋鸿兵观天下 - 美国金融市场对油价极其乐观！ #宋鸿兵 #霍尔木兹海峡 #石</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" s="94" t="inlineStr">
-        <is>
-          <t>2026-06-01 16:31:16 岩松笔记 - 如何靠基本面选题材主线？</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" s="94" t="inlineStr">
-        <is>
-          <t>2026-06-01 16:33:45 岩松笔记 - 平仓线下调，是放宽还是风控？</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" s="94" t="inlineStr">
-        <is>
-          <t>2026-06-01 16:34:59 拿幸·AI启示录 - GPT 饿死、Claude 囚禁、Gemini 犯罪 Gro</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" s="94" t="inlineStr">
-        <is>
-          <t>2026-06-01 16:42:16 拿幸·AI启示录 - 1170亿人的生死簿被AI连夜算尽：你抽到的那条命 大概率活</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" s="94" t="inlineStr">
-        <is>
-          <t>2026-06-01 16:44:44 拿幸·AI启示录 - AI 终结衰退：经济永远涨，普通人永远穷 16 年无衰退！A</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" s="94" t="inlineStr">
-        <is>
-          <t>2026-06-01 16:49:30 生猪贸易~芳姐(山东) - 奶多多19元30包</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" s="94" t="inlineStr">
-        <is>
-          <t>2026-06-01 16:50:25 生猪贸易~芳姐(山东) - 一包开口料顺丰包邮#养猪#养猪人#开口料</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" s="94" t="inlineStr">
-        <is>
-          <t>2026-06-01 16:51:01 生猪贸易~芳姐(山东) - 黄金多维10包送1包#养猪#养猪人#抗应激</t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" s="94" t="inlineStr">
-        <is>
-          <t>2026-06-01 16:52:33 蒋宇飞商业 - 国产存储双雄崛起，揭开未来十年新的财富机遇</t>
-        </is>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" s="94" t="inlineStr">
-        <is>
-          <t>2026-06-01 16:53:30 蒋宇飞商业 - 经常在家做饭的男人，大概率是穷人</t>
-        </is>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" s="94" t="inlineStr">
-        <is>
-          <t>2026-06-01 16:54:36 蒋宇飞商业 - 用产业思维抓住科技龙头，赢在重注时刻</t>
-        </is>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" s="94" t="inlineStr">
-        <is>
-          <t>2026-06-01 16:56:36 蒋宇飞商业 - 互联网没有创造新的经济，而硬科技才是未来的财富主线</t>
-        </is>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" s="94" t="inlineStr">
-        <is>
-          <t>2026-06-01 16:58:08 长坡厚雪 - 拼多多25年利息收入256亿 #拼多多 #价值投资 #股票</t>
-        </is>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" s="94" t="inlineStr">
-        <is>
-          <t>2026-06-01 17:01:05 长坡厚雪 - 风味纳斯达克 #纳斯达克 #富途 #长桥 #老虎证券</t>
-        </is>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" s="94" t="inlineStr">
-        <is>
-          <t>2026-06-01 17:01:56 长坡厚雪 - 拼多多的未来现金流折现 #拼多多 #段永平 #价值投资 #股</t>
-        </is>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" s="94" t="inlineStr">
-        <is>
-          <t>2026-06-01 17:02:57 闭眼看世界 - 日本为何倒贴送房没人要？【抖音独家】 #零基础看懂全球</t>
-        </is>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" s="94" t="inlineStr">
-        <is>
-          <t>2026-06-01 17:06:50 闭眼看世界 - 欧洲人为什么认为美国威胁变大了？【抖音独家】 #零基础看懂全</t>
-        </is>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" s="94" t="inlineStr">
-        <is>
-          <t>2026-06-01 17:09:23 闭眼看世界 - 特朗普版美元？【抖音独家】 #零基础看懂全球   #全球创作</t>
-        </is>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" s="94" t="inlineStr">
-        <is>
-          <t>2026-06-01 17:10:14 闭眼看世界 - 美国为何举办“增强运动会”？【抖音独家】 #零基础看懂全球</t>
-        </is>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" s="94" t="inlineStr">
-        <is>
-          <t>2026-06-01 17:11:21 闭眼看世界 - 加拿大的选择？【抖音独家】 #零基础看懂全球   #全球创作</t>
-        </is>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" s="94" t="inlineStr">
-        <is>
-          <t>2026-06-01 18:07:59 宋鸿兵观天下 - 美俄元首接踵到访，世界对表北京时间！ #宋鸿兵 #普京访华</t>
-        </is>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" s="94" t="inlineStr">
-        <is>
-          <t>2026-06-01 18:08:17 岩松笔记 - 国内存储行业会陷入内卷吗？</t>
-        </is>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" s="94" t="inlineStr">
-        <is>
-          <t>2026-06-01 18:09:36 拿幸·AI启示录 - Claude Opus 4.8来了！两个0%改写历史 估值9</t>
-        </is>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" s="94" t="inlineStr">
-        <is>
-          <t>2026-06-01 18:10:11 拿幸·AI启示录 - AI 编程正式工业化，Claude Code首发「自愈」功能</t>
-        </is>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" s="94" t="inlineStr">
-        <is>
-          <t>2026-06-01 18:10:46 猪猪女王 - #猪价#猪猪女王养二妮 #养殖 #养猪人</t>
-        </is>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" s="94" t="inlineStr">
-        <is>
-          <t>2026-06-01 18:11:01 猪猪女王 - #养殖 #所有养猪人 #猪价</t>
-        </is>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" s="94" t="inlineStr">
-        <is>
-          <t>2026-06-01 18:11:20 生猪贸易~芳姐(山东) - 4%核心料，1包顺丰送到家#大猪 #养猪#养猪人</t>
-        </is>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" s="94" t="inlineStr">
-        <is>
-          <t>2026-06-01 18:12:31 蒋宇飞商业 - 看懂存力 算力 运力，吃透未来10年的AI红利</t>
-        </is>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" s="94" t="inlineStr">
-        <is>
-          <t>2026-06-01 18:12:50 长坡厚雪 - 支付宝怎么选纳斯达克基金 #纳斯达克 #支付宝 #基金</t>
-        </is>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" s="94" t="inlineStr">
-        <is>
-          <t>2026-06-01 18:13:05 长坡厚雪 - 拼多多平台与商家的矛盾 #拼多多 #开市客 #价值投资 #股</t>
-        </is>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" s="94" t="inlineStr">
-        <is>
-          <t>2026-06-01 18:13:30 闭眼看世界 - 美日印澳想要做什么？【抖音独家】 #零基础看懂全球 #全球创</t>
-        </is>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" s="94" t="inlineStr">
-        <is>
-          <t>2026-06-01 18:15:33 闭眼看世界 - 释永信的结局？</t>
-        </is>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" s="94" t="inlineStr">
-        <is>
-          <t>2026-06-01 18:16:21 飞阅硬核财经 - 一分钟给你讲明白天孚通信 #天孚通信 #商业知识 #认知 #</t>
-        </is>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" s="94" t="inlineStr">
-        <is>
-          <t>2026-06-01 18:41:12 宋鸿兵观天下 - 美国金融市场深陷“迷之自信”？ #宋鸿兵 #美债 #美股 #</t>
-        </is>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" s="94" t="inlineStr">
-        <is>
-          <t>2026-06-01 18:41:35 岩松笔记 - 20倍PE的腾讯怎么看？</t>
-        </is>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" s="94" t="inlineStr">
-        <is>
-          <t>2026-06-01 18:42:20 拿幸·AI启示录 - 封神还是欺诈？Claude 4.8 真相：算力堆出来的分裂</t>
-        </is>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" s="94" t="inlineStr">
-        <is>
-          <t>2026-06-01 18:42:34 猪猪女王 - #猪价 #养殖 #养猪人不容易 #所有养猪人</t>
-        </is>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" s="94" t="inlineStr">
-        <is>
-          <t>2026-06-01 18:43:03 闭眼看世界 - 欧洲与美国的差别？【抖音独家】 #零基础看懂全球   #全球</t>
-        </is>
-      </c>
-    </row>
+    <row r="33"/>
+    <row r="34"/>
   </sheetData>
   <mergeCells count="19">
     <mergeCell ref="A11:H11"/>

--- a/持仓贝叶斯跟踪.xlsx
+++ b/持仓贝叶斯跟踪.xlsx
@@ -308,7 +308,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="95">
+  <cellXfs count="97">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -586,6 +586,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -839,7 +841,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:H34"/>
+  <dimension ref="A1:H32"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6171875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="22" customWidth="1" style="28" min="1" max="8"/>
@@ -1056,7 +1058,6 @@
       </c>
       <c r="H9" s="31" t="n"/>
     </row>
-    <row r="10"/>
     <row r="11" ht="15" customHeight="1" s="29">
       <c r="A11" s="80" t="inlineStr">
         <is>
@@ -1132,7 +1133,6 @@
         </is>
       </c>
     </row>
-    <row r="15"/>
     <row r="16">
       <c r="A16" s="85" t="inlineStr">
         <is>
@@ -1382,7 +1382,6 @@
         </is>
       </c>
     </row>
-    <row r="22"/>
     <row r="23">
       <c r="A23" s="85" t="inlineStr">
         <is>
@@ -1768,8 +1767,6 @@
         </is>
       </c>
     </row>
-    <row r="33"/>
-    <row r="34"/>
   </sheetData>
   <mergeCells count="19">
     <mergeCell ref="A11:H11"/>
@@ -1804,7 +1801,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:H12"/>
+  <dimension ref="A1:H15"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="10.4921875" defaultRowHeight="12.8" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="32" customWidth="1" style="28" min="1" max="7"/>
@@ -1888,7 +1885,7 @@
 净值3.6875
 P:59%
 利率折价-4pp
-有效P:55%</t>
+有效P:59%</t>
         </is>
       </c>
       <c r="B3" s="53" t="inlineStr">
@@ -1897,7 +1894,7 @@
 净值1.8418
 P:74%
 利率折价-4pp
-有效P:70%</t>
+有效P:74%</t>
         </is>
       </c>
       <c r="C3" s="53" t="inlineStr">
@@ -1906,16 +1903,16 @@
 净值0.6619
 P:46%
 利率折价-4pp
-有效P:42%</t>
+有效P:46%</t>
         </is>
       </c>
       <c r="D3" s="53" t="inlineStr">
         <is>
           <t>成本¥3732
 净值0.7545
-P:37%
+P:45%
 利率折价0pp
-有效P:37%</t>
+有效P:45%</t>
         </is>
       </c>
       <c r="E3" s="53" t="inlineStr">
@@ -1924,7 +1921,7 @@
 净值1.8985
 P:53%
 利率折价-2pp
-有效P:51%</t>
+有效P:53%</t>
         </is>
       </c>
       <c r="F3" s="53" t="inlineStr">
@@ -1933,7 +1930,7 @@
 净值1.089
 P:50%
 利率折价-2pp
-有效P:48%</t>
+有效P:50%</t>
         </is>
       </c>
       <c r="G3" s="53" t="inlineStr">
@@ -1998,56 +1995,230 @@
       </c>
     </row>
     <row r="5" ht="45" customHeight="1" s="29">
-      <c r="A5" s="60" t="inlineStr">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-06-01
+±0pp
+蒋宇飞国产存储崛起+岩松笔记存储内卷多空抵消</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2026-06-01
+±0pp
+无直接信号</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>2026-06-01
+±0pp
+长坡厚雪拼多多估值不沾边</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>2026-06-01
+-1pp
+伊娃厄尔尼诺饲料成本上涨40%</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>2026-06-01
+±0pp
+无直接信号</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>2026-06-01
+±0pp
+无直接信号</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>2026-06-01
+±0pp
+无直接信号</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>2026-06-01
+±0pp
+拿幸AI分析已是共识</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="45" customHeight="1" s="29">
+      <c r="A6" s="28" t="inlineStr">
+        <is>
+          <t>2026-06-01
+±0pp
+蒋宇飞国产存储崛起+岩松笔记存储内卷多空抵消</t>
+        </is>
+      </c>
+      <c r="B6" s="95" t="inlineStr">
+        <is>
+          <t>2026-06-01
+±0pp
+无直接信号</t>
+        </is>
+      </c>
+      <c r="C6" s="96" t="inlineStr">
+        <is>
+          <t>2026-06-01
+±0pp
+长坡厚雪拼多多估值不沾边</t>
+        </is>
+      </c>
+      <c r="D6" s="96" t="inlineStr">
+        <is>
+          <t>2026-06-01
+-1pp
+伊娃厄尔尼诺饲料成本上涨40%</t>
+        </is>
+      </c>
+      <c r="E6" s="95" t="inlineStr">
+        <is>
+          <t>2026-06-01
+±0pp
+无直接信号</t>
+        </is>
+      </c>
+      <c r="F6" s="95" t="inlineStr">
+        <is>
+          <t>2026-06-01
+±0pp
+无直接信号</t>
+        </is>
+      </c>
+      <c r="G6" s="28" t="inlineStr">
+        <is>
+          <t>2026-06-01
+±0pp
+无直接信号</t>
+        </is>
+      </c>
+      <c r="H6" s="28" t="inlineStr">
+        <is>
+          <t>2026-06-01
+±0pp
+拿幸AI分析已是共识</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="45" customHeight="1" s="29">
+      <c r="A7" s="60" t="inlineStr">
+        <is>
+          <t>2026-06-01
+±0pp
+蒋宇飞国产存储崛起+岩松笔记存储内卷多空抵消</t>
+        </is>
+      </c>
+      <c r="B7" s="61" t="inlineStr">
+        <is>
+          <t>2026-06-01
+±0pp
+无直接新信号</t>
+        </is>
+      </c>
+      <c r="C7" s="62" t="inlineStr">
+        <is>
+          <t>2026-06-01
+±0pp
+无直接新信号</t>
+        </is>
+      </c>
+      <c r="D7" s="62" t="inlineStr">
+        <is>
+          <t>2026-06-01
+-1pp
+伊娃厄尔尼诺饲料成本上涨40%挤压利润</t>
+        </is>
+      </c>
+      <c r="E7" s="61" t="inlineStr">
+        <is>
+          <t>2026-06-01
+±0pp
+无直接新信号</t>
+        </is>
+      </c>
+      <c r="F7" s="61" t="inlineStr">
+        <is>
+          <t>2026-06-01
+±0pp
+无直接新信号</t>
+        </is>
+      </c>
+      <c r="G7" s="60" t="inlineStr">
+        <is>
+          <t>2026-06-01
+±0pp
+无直接新信号</t>
+        </is>
+      </c>
+      <c r="H7" s="60" t="inlineStr">
+        <is>
+          <t>2026-06-01
+±0pp
+无直接新信号</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="45" customHeight="1" s="29">
+      <c r="A8" s="60" t="inlineStr">
         <is>
           <t>2026-05-30
 +0pp
 AI强周期确认但存储过热信号</t>
         </is>
       </c>
-      <c r="B5" s="61" t="inlineStr">
+      <c r="B8" s="61" t="inlineStr">
         <is>
           <t>2026-05-30
 +1pp
 亿纬锂能Q1+61%储能海外爆发</t>
         </is>
       </c>
-      <c r="C5" s="62" t="inlineStr">
+      <c r="C8" s="62" t="inlineStr">
         <is>
           <t>2026-05-30
 -1pp
 QDII通道收紧+腾讯增长天花板</t>
         </is>
       </c>
-      <c r="D5" s="62" t="inlineStr">
+      <c r="D8" s="62" t="inlineStr">
         <is>
           <t>2026-05-30
 -5pp
 猪价4块+厄尔尼诺成本飙升</t>
         </is>
       </c>
-      <c r="E5" s="61" t="inlineStr">
+      <c r="E8" s="61" t="inlineStr">
         <is>
           <t>2026-05-30
 +2pp
 海峡封锁+通胀反弹双驱动</t>
         </is>
       </c>
-      <c r="F5" s="61" t="inlineStr">
+      <c r="F8" s="61" t="inlineStr">
         <is>
           <t>2026-05-30
 +2pp
 海峡封锁+通胀反弹双驱动</t>
         </is>
       </c>
-      <c r="G5" s="60" t="inlineStr">
+      <c r="G8" s="60" t="inlineStr">
         <is>
           <t>2026-05-30
 +0pp
 无新信号</t>
         </is>
       </c>
-      <c r="H5" s="60" t="inlineStr">
+      <c r="H8" s="60" t="inlineStr">
         <is>
           <t>2026-05-30
 +0pp
@@ -2055,247 +2226,244 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="45" customHeight="1" s="29">
-      <c r="A6" s="63" t="inlineStr">
+    <row r="9" ht="45" customHeight="1" s="29">
+      <c r="A9" s="63" t="inlineStr">
         <is>
           <t>2026-05-28
 +1pp
 Schiff美债熊市 + 周鸿祎"内存决定高度"</t>
         </is>
       </c>
-      <c r="B6" s="64" t="inlineStr">
+      <c r="B9" s="64" t="inlineStr">
         <is>
           <t>2026-05-21
 +0pp
 中科院固态锂电池突破（逻辑簇强化，不作概率调整）</t>
         </is>
       </c>
-      <c r="C6" s="65" t="inlineStr">
+      <c r="C9" s="65" t="inlineStr">
         <is>
           <t>2026-05-26
 -4pp
 恒生三巨头财报验证：非价值陷阱确认</t>
         </is>
       </c>
-      <c r="D6" s="63" t="inlineStr">
+      <c r="D9" s="63" t="inlineStr">
         <is>
           <t>2026-05-26
 +5pp
 ✅ 伊娃读财报18期：17/18猪企亏损，加速去产能确认</t>
         </is>
       </c>
-      <c r="E6" s="63" t="inlineStr">
+      <c r="E9" s="63" t="inlineStr">
         <is>
           <t>2026-05-22
 +4pp
 有色金属+3.63%：AI铜需求爆发 + 资金回流</t>
         </is>
       </c>
-      <c r="F6" s="63" t="inlineStr">
+      <c r="F9" s="63" t="inlineStr">
         <is>
           <t>2026-05-29
 +1pp
 闭眼看世界：俄乌升级→地缘风险溢价</t>
         </is>
       </c>
-      <c r="G6" s="65" t="inlineStr">
+      <c r="G9" s="65" t="inlineStr">
         <is>
           <t>2026-05-22
 -3pp
 无知半人：前4月住户贷款狂减4902亿</t>
         </is>
       </c>
-      <c r="H6" s="57" t="n"/>
-    </row>
-    <row r="7" ht="45" customHeight="1" s="29">
-      <c r="A7" s="66" t="inlineStr">
+      <c r="H9" s="57" t="n"/>
+    </row>
+    <row r="10" ht="45" customHeight="1" s="29">
+      <c r="A10" s="66" t="inlineStr">
         <is>
           <t>2026-05-27
 -2pp
 🔥 闭眼看世界：美军轰炸伊朗→霍尔木兹P'作废</t>
         </is>
       </c>
-      <c r="B7" s="67" t="inlineStr">
+      <c r="B10" s="67" t="inlineStr">
         <is>
           <t>2026-05-20
 +1pp
 光储旺季+美债压制</t>
         </is>
       </c>
-      <c r="C7" s="66" t="inlineStr">
+      <c r="C10" s="66" t="inlineStr">
         <is>
           <t>2026-05-20
 -3pp
 多空交织：低开高走验证磨底 + 美债5.18%压制</t>
         </is>
       </c>
-      <c r="D7" s="67" t="inlineStr">
+      <c r="D10" s="67" t="inlineStr">
         <is>
           <t>2026-05-24
 +5pp
 霍尔木兹通航（+4pp 未入链修正）</t>
         </is>
       </c>
-      <c r="E7" s="66" t="inlineStr">
+      <c r="E10" s="66" t="inlineStr">
         <is>
           <t>2026-05-19
 -2pp
 🔴 岩松笔记 + 🟢 付鹏对冲：逻辑分类修正</t>
         </is>
       </c>
-      <c r="F7" s="66" t="inlineStr">
+      <c r="F10" s="66" t="inlineStr">
         <is>
           <t>2026-05-20
 -3pp
 有色金属持续走弱+美债压制</t>
         </is>
       </c>
-      <c r="G7" s="67" t="inlineStr">
+      <c r="G10" s="67" t="inlineStr">
         <is>
           <t>2026-05-22
 +3pp
 追加：凯文·沃什就任美联储主席</t>
         </is>
       </c>
-      <c r="H7" s="57" t="n"/>
-    </row>
-    <row r="8" ht="45" customHeight="1" s="29">
-      <c r="A8" s="63" t="inlineStr">
+      <c r="H10" s="57" t="n"/>
+    </row>
+    <row r="11" ht="45" customHeight="1" s="29">
+      <c r="A11" s="63" t="inlineStr">
         <is>
           <t>2026-05-25
 +1pp
 蒋宇飞：深度拆解玻璃基板的万亿机遇</t>
         </is>
       </c>
-      <c r="B8" s="63" t="inlineStr">
+      <c r="B11" s="63" t="inlineStr">
         <is>
           <t>2026-05-19
 +5pp
 碳酸锂跌价+巴克莱看多</t>
         </is>
       </c>
-      <c r="C8" s="65" t="inlineStr">
+      <c r="C11" s="65" t="inlineStr">
         <is>
           <t>2026-05-19
 -2pp
 付鹏×2：港股结构性偏弱 + 风险偏好极值 + 古都闲云社消疲弱</t>
         </is>
       </c>
-      <c r="D8" s="65" t="inlineStr">
+      <c r="D11" s="65" t="inlineStr">
         <is>
           <t>2026-05-22
 -2pp
 无知半人：住户贷款狂减4902亿</t>
         </is>
       </c>
-      <c r="E8" s="65" t="inlineStr">
+      <c r="E11" s="65" t="inlineStr">
         <is>
           <t>2026-05-15
 -8pp
 →05-20 有色金属板块持续资金净流出</t>
         </is>
       </c>
-      <c r="F8" s="65" t="inlineStr">
+      <c r="F11" s="65" t="inlineStr">
         <is>
           <t>2026-05-19
 -5pp
 🔴 岩松笔记：资源非长期抗通胀→HALO联动风险</t>
         </is>
       </c>
-      <c r="G8" s="57" t="n"/>
-      <c r="H8" s="57" t="n"/>
-    </row>
-    <row r="9" ht="45" customHeight="1" s="29">
-      <c r="A9" s="66" t="inlineStr">
+      <c r="G11" s="57" t="n"/>
+      <c r="H11" s="57" t="n"/>
+    </row>
+    <row r="12" ht="45" customHeight="1" s="29">
+      <c r="A12" s="66" t="inlineStr">
         <is>
           <t>2026-05-22
 -3pp
 宋鸿兵利率风暴（但斌预警已删除：券商观点不计）</t>
         </is>
       </c>
-      <c r="B9" s="67" t="inlineStr">
+      <c r="B12" s="67" t="inlineStr">
         <is>
           <t>2026-05-15
 +1pp
 机构研报确认景气上行</t>
         </is>
       </c>
-      <c r="C9" s="57" t="n"/>
-      <c r="D9" s="66" t="inlineStr">
+      <c r="C12" s="57" t="n"/>
+      <c r="D12" s="66" t="inlineStr">
         <is>
           <t>2026-05-19
 -2pp
 古都闲云：社消数据疲弱</t>
         </is>
       </c>
-      <c r="E9" s="57" t="n"/>
-      <c r="F9" s="57" t="n"/>
-      <c r="G9" s="57" t="n"/>
-      <c r="H9" s="57" t="n"/>
-    </row>
-    <row r="10" ht="45" customHeight="1" s="29">
-      <c r="A10" s="65" t="inlineStr">
-        <is>
-          <t>2026-05-22
--6pp
-凯文·沃什就任美联储主席</t>
-        </is>
-      </c>
-      <c r="B10" s="63" t="inlineStr">
-        <is>
-          <t>2026-05-14
-+3pp
-电池ETF涨2.73%+多重利好</t>
-        </is>
-      </c>
-      <c r="C10" s="57" t="n"/>
-      <c r="D10" s="57" t="n"/>
-      <c r="E10" s="57" t="n"/>
-      <c r="F10" s="57" t="n"/>
-      <c r="G10" s="57" t="n"/>
-      <c r="H10" s="57" t="n"/>
-    </row>
-    <row r="11" ht="45" customHeight="1" s="29">
-      <c r="A11" s="66" t="inlineStr">
-        <is>
-          <t>2026-05-19
--2pp
-韩国闪崩（情绪叠加）</t>
-        </is>
-      </c>
-      <c r="B11" s="67" t="inlineStr">
-        <is>
-          <t>2026-05-13
-+5pp
-特朗普访华+恩捷40亿扩产</t>
-        </is>
-      </c>
-      <c r="C11" s="57" t="n"/>
-      <c r="D11" s="57" t="n"/>
-      <c r="E11" s="57" t="n"/>
-      <c r="F11" s="57" t="n"/>
-      <c r="G11" s="57" t="n"/>
-      <c r="H11" s="57" t="n"/>
-    </row>
-    <row r="12" ht="45" customHeight="1" s="29">
-      <c r="A12" s="63" t="inlineStr">
-        <is>
-          <t>2026-05-16
-+2pp
-付鹏：存储=AI基建（观点→共识信号）</t>
-        </is>
-      </c>
-      <c r="B12" s="57" t="n"/>
-      <c r="C12" s="57" t="n"/>
-      <c r="D12" s="57" t="n"/>
       <c r="E12" s="57" t="n"/>
       <c r="F12" s="57" t="n"/>
       <c r="G12" s="57" t="n"/>
       <c r="H12" s="57" t="n"/>
     </row>
-    <row r="13" ht="13.8" customHeight="1" s="29"/>
-    <row r="14" ht="13.8" customHeight="1" s="29"/>
-    <row r="15" ht="13.8" customHeight="1" s="29"/>
+    <row r="13" ht="13.8" customHeight="1" s="29">
+      <c r="A13" s="65" t="inlineStr">
+        <is>
+          <t>2026-05-22
+-6pp
+凯文·沃什就任美联储主席</t>
+        </is>
+      </c>
+      <c r="B13" s="63" t="inlineStr">
+        <is>
+          <t>2026-05-14
++3pp
+电池ETF涨2.73%+多重利好</t>
+        </is>
+      </c>
+      <c r="C13" s="57" t="n"/>
+      <c r="D13" s="57" t="n"/>
+      <c r="E13" s="57" t="n"/>
+      <c r="F13" s="57" t="n"/>
+      <c r="G13" s="57" t="n"/>
+      <c r="H13" s="57" t="n"/>
+    </row>
+    <row r="14" ht="13.8" customHeight="1" s="29">
+      <c r="A14" s="66" t="inlineStr">
+        <is>
+          <t>2026-05-19
+-2pp
+韩国闪崩（情绪叠加）</t>
+        </is>
+      </c>
+      <c r="B14" s="67" t="inlineStr">
+        <is>
+          <t>2026-05-13
++5pp
+特朗普访华+恩捷40亿扩产</t>
+        </is>
+      </c>
+      <c r="C14" s="57" t="n"/>
+      <c r="D14" s="57" t="n"/>
+      <c r="E14" s="57" t="n"/>
+      <c r="F14" s="57" t="n"/>
+      <c r="G14" s="57" t="n"/>
+      <c r="H14" s="57" t="n"/>
+    </row>
+    <row r="15" ht="13.8" customHeight="1" s="29">
+      <c r="A15" s="63" t="inlineStr">
+        <is>
+          <t>2026-05-16
++2pp
+付鹏：存储=AI基建（观点→共识信号）</t>
+        </is>
+      </c>
+      <c r="B15" s="57" t="n"/>
+      <c r="C15" s="57" t="n"/>
+      <c r="D15" s="57" t="n"/>
+      <c r="E15" s="57" t="n"/>
+      <c r="F15" s="57" t="n"/>
+      <c r="G15" s="57" t="n"/>
+      <c r="H15" s="57" t="n"/>
+    </row>
     <row r="16" ht="13.8" customHeight="1" s="29"/>
     <row r="17" ht="13.8" customHeight="1" s="29"/>
     <row r="18" ht="13.8" customHeight="1" s="29"/>

--- a/持仓贝叶斯跟踪.xlsx
+++ b/持仓贝叶斯跟踪.xlsx
@@ -1883,9 +1883,9 @@
         <is>
           <t>成本¥3695
 净值3.6875
-P:59%
+P:57%
 利率折价-4pp
-有效P:59%</t>
+有效P:57%</t>
         </is>
       </c>
       <c r="B3" s="53" t="inlineStr">
@@ -1995,56 +1995,56 @@
       </c>
     </row>
     <row r="5" ht="45" customHeight="1" s="29">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="28" t="inlineStr">
         <is>
           <t>2026-06-01
-±0pp
-蒋宇飞国产存储崛起+岩松笔记存储内卷多空抵消</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
+-2pp
+古都闲云PMI临界点+美国滞胀风险拖累出口</t>
+        </is>
+      </c>
+      <c r="B5" s="28" t="inlineStr">
         <is>
           <t>2026-06-01
 ±0pp
 无直接信号</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C5" s="28" t="inlineStr">
         <is>
           <t>2026-06-01
 ±0pp
-长坡厚雪拼多多估值不沾边</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
+无直接信号</t>
+        </is>
+      </c>
+      <c r="D5" s="28" t="inlineStr">
         <is>
           <t>2026-06-01
 -1pp
 伊娃厄尔尼诺饲料成本上涨40%</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E5" s="28" t="inlineStr">
         <is>
           <t>2026-06-01
 ±0pp
 无直接信号</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="F5" s="28" t="inlineStr">
         <is>
           <t>2026-06-01
 ±0pp
 无直接信号</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="G5" s="28" t="inlineStr">
         <is>
           <t>2026-06-01
-±0pp
-无直接信号</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
+-1pp
+古都闲云经济下行银行利空</t>
+        </is>
+      </c>
+      <c r="H5" s="28" t="inlineStr">
         <is>
           <t>2026-06-01
 ±0pp

--- a/持仓贝叶斯跟踪.xlsx
+++ b/持仓贝叶斯跟踪.xlsx
@@ -841,7 +841,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:H32"/>
+  <dimension ref="A1:H17"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6171875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="22" customWidth="1" style="28" min="1" max="8"/>
@@ -1179,591 +1179,6 @@
       <c r="H17" s="86" t="inlineStr">
         <is>
           <t>备注</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="87" t="inlineStr">
-        <is>
-          <t>芯片ETF 020628</t>
-        </is>
-      </c>
-      <c r="B18" s="87" t="inlineStr">
-        <is>
-          <t>🟢已持仓</t>
-        </is>
-      </c>
-      <c r="C18" s="88" t="inlineStr">
-        <is>
-          <t>P:59%
-成本2.6854
-+40.5%</t>
-        </is>
-      </c>
-      <c r="D18" s="88" t="inlineStr">
-        <is>
-          <t>06-01德银报告
-利率折价被B门吸收
-P值不变</t>
-        </is>
-      </c>
-      <c r="E18" s="88" t="inlineStr">
-        <is>
-          <t>①单日暴跌≥5%
-②累计跌15%+
-③P值≥55%</t>
-        </is>
-      </c>
-      <c r="F18" s="88" t="inlineStr">
-        <is>
-          <t>条件③已满足
-等价跌信号</t>
-        </is>
-      </c>
-      <c r="G18" s="88" t="inlineStr">
-        <is>
-          <t>06-01</t>
-        </is>
-      </c>
-      <c r="H18" s="88" t="inlineStr">
-        <is>
-          <t>长鑫上会
-GTC Taipei
-存储双雄逻辑</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="89" t="inlineStr">
-        <is>
-          <t>澜起科技 688008</t>
-        </is>
-      </c>
-      <c r="B19" s="89" t="inlineStr">
-        <is>
-          <t>🟡未建仓</t>
-        </is>
-      </c>
-      <c r="C19" s="90" t="inlineStr">
-        <is>
-          <t>¥272.29
-PE 130x
-PEG 1.6-2.6</t>
-        </is>
-      </c>
-      <c r="D19" s="90" t="inlineStr">
-        <is>
-          <t>05-26股东询价转让
-(减持利空)
--4.15%</t>
-        </is>
-      </c>
-      <c r="E19" s="90" t="inlineStr">
-        <is>
-          <t>①单日暴跌≥8%
-②&lt;¥280+平稳
-③P值≥55%</t>
-        </is>
-      </c>
-      <c r="F19" s="90" t="inlineStr">
-        <is>
-          <t>条件②满足
-¥272&lt;¥280</t>
-        </is>
-      </c>
-      <c r="G19" s="90" t="inlineStr">
-        <is>
-          <t>05-26</t>
-        </is>
-      </c>
-      <c r="H19" s="90" t="inlineStr">
-        <is>
-          <t>DDR5龙头
-华为τ定律
-科创板高波动</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="91" t="inlineStr">
-        <is>
-          <t>凯盛科技 600552</t>
-        </is>
-      </c>
-      <c r="B20" s="91" t="inlineStr">
-        <is>
-          <t>🔭观察中</t>
-        </is>
-      </c>
-      <c r="C20" s="92" t="inlineStr">
-        <is>
-          <t>¥19.70
-近5日+10%</t>
-        </is>
-      </c>
-      <c r="D20" s="92" t="inlineStr">
-        <is>
-          <t>05-26追涨不舒服
-等回调</t>
-        </is>
-      </c>
-      <c r="E20" s="92" t="inlineStr">
-        <is>
-          <t>①回调到¥18-18.5
-②蒋宇飞视频分析完
-③手痒&lt;¥500</t>
-        </is>
-      </c>
-      <c r="F20" s="92" t="inlineStr">
-        <is>
-          <t>距¥18.5约-6%</t>
-        </is>
-      </c>
-      <c r="G20" s="92" t="inlineStr">
-        <is>
-          <t>05-26</t>
-        </is>
-      </c>
-      <c r="H20" s="92" t="inlineStr">
-        <is>
-          <t>玻璃基板
-AI封装材料
-蒋宇飞推荐</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="89" t="inlineStr">
-        <is>
-          <t>国产存储双雄</t>
-        </is>
-      </c>
-      <c r="B21" s="89" t="inlineStr">
-        <is>
-          <t>🔥新标记</t>
-        </is>
-      </c>
-      <c r="C21" s="90" t="inlineStr">
-        <is>
-          <t>长鑫DRAM(短)
-长江Flash(长)</t>
-        </is>
-      </c>
-      <c r="D21" s="90" t="inlineStr">
-        <is>
-          <t>06-01蒋宇飞
-存储=硬科技时代
-市值或超腾讯</t>
-        </is>
-      </c>
-      <c r="E21" s="90" t="inlineStr">
-        <is>
-          <t>跟踪长鑫HBM
-长江3D NAND
-A股标的筛选</t>
-        </is>
-      </c>
-      <c r="F21" s="90" t="inlineStr">
-        <is>
-          <t>芯片ETF已覆盖
-需细化标的</t>
-        </is>
-      </c>
-      <c r="G21" s="90" t="inlineStr">
-        <is>
-          <t>06-01</t>
-        </is>
-      </c>
-      <c r="H21" s="90" t="inlineStr">
-        <is>
-          <t>星光纯叠存赛道
-越近GPU越值钱
-澜起上下游</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="85" t="inlineStr">
-        <is>
-          <t>⚡ 事件链追踪</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="86" t="inlineStr">
-        <is>
-          <t>事件</t>
-        </is>
-      </c>
-      <c r="B24" s="86" t="inlineStr">
-        <is>
-          <t>时间</t>
-        </is>
-      </c>
-      <c r="C24" s="86" t="inlineStr">
-        <is>
-          <t>相关标的</t>
-        </is>
-      </c>
-      <c r="D24" s="86" t="inlineStr">
-        <is>
-          <t>状态</t>
-        </is>
-      </c>
-      <c r="E24" s="86" t="inlineStr">
-        <is>
-          <t>影响方向</t>
-        </is>
-      </c>
-      <c r="F24" s="86" t="inlineStr">
-        <is>
-          <t>已落地?</t>
-        </is>
-      </c>
-      <c r="G24" s="86" t="inlineStr">
-        <is>
-          <t>P'虚值</t>
-        </is>
-      </c>
-      <c r="H24" s="86" t="inlineStr">
-        <is>
-          <t>备注</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="92" t="inlineStr">
-        <is>
-          <t>黄仁勋GTC Taipei演讲</t>
-        </is>
-      </c>
-      <c r="B25" s="92" t="inlineStr">
-        <is>
-          <t>06-01</t>
-        </is>
-      </c>
-      <c r="C25" s="92" t="inlineStr">
-        <is>
-          <t>芯片ETF/存储</t>
-        </is>
-      </c>
-      <c r="D25" s="92" t="inlineStr">
-        <is>
-          <t>⏳待发生</t>
-        </is>
-      </c>
-      <c r="E25" s="92" t="inlineStr">
-        <is>
-          <t>🟢利好</t>
-        </is>
-      </c>
-      <c r="F25" s="92" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="G25" s="92" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H25" s="92" t="inlineStr">
-        <is>
-          <t>AI算力催化</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="92" t="inlineStr">
-        <is>
-          <t>长鑫存储5月27日上会</t>
-        </is>
-      </c>
-      <c r="B26" s="92" t="inlineStr">
-        <is>
-          <t>05-27</t>
-        </is>
-      </c>
-      <c r="C26" s="92" t="inlineStr">
-        <is>
-          <t>芯片ETF/存储</t>
-        </is>
-      </c>
-      <c r="D26" s="88" t="inlineStr">
-        <is>
-          <t>✅已过</t>
-        </is>
-      </c>
-      <c r="E26" s="92" t="inlineStr">
-        <is>
-          <t>🟢利好</t>
-        </is>
-      </c>
-      <c r="F26" s="92" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="G26" s="92" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H26" s="92" t="inlineStr">
-        <is>
-          <t>需确认结果</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="92" t="inlineStr">
-        <is>
-          <t>三星罢工持续性</t>
-        </is>
-      </c>
-      <c r="B27" s="92" t="inlineStr">
-        <is>
-          <t>持续中</t>
-        </is>
-      </c>
-      <c r="C27" s="92" t="inlineStr">
-        <is>
-          <t>芯片ETF/存储</t>
-        </is>
-      </c>
-      <c r="D27" s="92" t="inlineStr">
-        <is>
-          <t>🔄跟踪中</t>
-        </is>
-      </c>
-      <c r="E27" s="92" t="inlineStr">
-        <is>
-          <t>🟢利好</t>
-        </is>
-      </c>
-      <c r="F27" s="92" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G27" s="92" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H27" s="92" t="inlineStr">
-        <is>
-          <t>国产替代窗口</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="92" t="inlineStr">
-        <is>
-          <t>美联储12月前加息58%</t>
-        </is>
-      </c>
-      <c r="B28" s="92" t="inlineStr">
-        <is>
-          <t>德银05-29</t>
-        </is>
-      </c>
-      <c r="C28" s="92" t="inlineStr">
-        <is>
-          <t>全持仓</t>
-        </is>
-      </c>
-      <c r="D28" s="92" t="inlineStr">
-        <is>
-          <t>📋P'虚值</t>
-        </is>
-      </c>
-      <c r="E28" s="93" t="inlineStr">
-        <is>
-          <t>🔴利空</t>
-        </is>
-      </c>
-      <c r="F28" s="92" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="G28" s="92" t="inlineStr">
-        <is>
-          <t>芯片-3pp/黄金-2pp</t>
-        </is>
-      </c>
-      <c r="H28" s="92" t="inlineStr">
-        <is>
-          <t>未落地不进主P</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="92" t="inlineStr">
-        <is>
-          <t>沃什软化鹰派立场</t>
-        </is>
-      </c>
-      <c r="B29" s="92" t="inlineStr">
-        <is>
-          <t>德银05-29</t>
-        </is>
-      </c>
-      <c r="C29" s="92" t="inlineStr">
-        <is>
-          <t>黄金/芯片</t>
-        </is>
-      </c>
-      <c r="D29" s="92" t="inlineStr">
-        <is>
-          <t>📋P'虚值</t>
-        </is>
-      </c>
-      <c r="E29" s="92" t="inlineStr">
-        <is>
-          <t>🟢利好</t>
-        </is>
-      </c>
-      <c r="F29" s="92" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="G29" s="92" t="inlineStr">
-        <is>
-          <t>黄金+2pp/芯片+1pp</t>
-        </is>
-      </c>
-      <c r="H29" s="92" t="inlineStr">
-        <is>
-          <t>新主席不确定性</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="92" t="inlineStr">
-        <is>
-          <t>伊朗3.0反击/海峡封锁</t>
-        </is>
-      </c>
-      <c r="B30" s="92" t="inlineStr">
-        <is>
-          <t>05-30宋鸿兵</t>
-        </is>
-      </c>
-      <c r="C30" s="92" t="inlineStr">
-        <is>
-          <t>有色/黄金/原油</t>
-        </is>
-      </c>
-      <c r="D30" s="92" t="inlineStr">
-        <is>
-          <t>🔄跟踪中</t>
-        </is>
-      </c>
-      <c r="E30" s="92" t="inlineStr">
-        <is>
-          <t>🟢利好</t>
-        </is>
-      </c>
-      <c r="F30" s="92" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G30" s="92" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H30" s="92" t="inlineStr">
-        <is>
-          <t>地缘风险升级</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="92" t="inlineStr">
-        <is>
-          <t>德银报告:ETF需求-78%</t>
-        </is>
-      </c>
-      <c r="B31" s="92" t="inlineStr">
-        <is>
-          <t>05-29</t>
-        </is>
-      </c>
-      <c r="C31" s="92" t="inlineStr">
-        <is>
-          <t>黄金</t>
-        </is>
-      </c>
-      <c r="D31" s="88" t="inlineStr">
-        <is>
-          <t>✅已落地</t>
-        </is>
-      </c>
-      <c r="E31" s="93" t="inlineStr">
-        <is>
-          <t>🔴利空</t>
-        </is>
-      </c>
-      <c r="F31" s="92" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="G31" s="92" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H31" s="92" t="inlineStr">
-        <is>
-          <t>已扣-3pp</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="92" t="inlineStr">
-        <is>
-          <t>德银报告:央行购金+38%</t>
-        </is>
-      </c>
-      <c r="B32" s="92" t="inlineStr">
-        <is>
-          <t>05-29</t>
-        </is>
-      </c>
-      <c r="C32" s="92" t="inlineStr">
-        <is>
-          <t>黄金</t>
-        </is>
-      </c>
-      <c r="D32" s="88" t="inlineStr">
-        <is>
-          <t>✅已落地</t>
-        </is>
-      </c>
-      <c r="E32" s="92" t="inlineStr">
-        <is>
-          <t>🟢利好</t>
-        </is>
-      </c>
-      <c r="F32" s="92" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="G32" s="92" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H32" s="92" t="inlineStr">
-        <is>
-          <t>已加+1pp</t>
         </is>
       </c>
     </row>
@@ -1801,7 +1216,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:H15"/>
+  <dimension ref="A1:H11"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="10.4921875" defaultRowHeight="12.8" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="32" customWidth="1" style="28" min="1" max="7"/>
@@ -1995,475 +1410,247 @@
       </c>
     </row>
     <row r="5" ht="45" customHeight="1" s="29">
-      <c r="A5" s="28" t="inlineStr">
-        <is>
-          <t>2026-06-01
--2pp
-古都闲云PMI临界点+美国滞胀风险拖累出口</t>
-        </is>
-      </c>
-      <c r="B5" s="28" t="inlineStr">
-        <is>
-          <t>2026-06-01
-±0pp
-无直接信号</t>
-        </is>
-      </c>
-      <c r="C5" s="28" t="inlineStr">
-        <is>
-          <t>2026-06-01
-±0pp
-无直接信号</t>
-        </is>
-      </c>
-      <c r="D5" s="28" t="inlineStr">
-        <is>
-          <t>2026-06-01
--1pp
-伊娃厄尔尼诺饲料成本上涨40%</t>
-        </is>
-      </c>
-      <c r="E5" s="28" t="inlineStr">
-        <is>
-          <t>2026-06-01
-±0pp
-无直接信号</t>
-        </is>
-      </c>
-      <c r="F5" s="28" t="inlineStr">
-        <is>
-          <t>2026-06-01
-±0pp
-无直接信号</t>
-        </is>
-      </c>
-      <c r="G5" s="28" t="inlineStr">
-        <is>
-          <t>2026-06-01
--1pp
-古都闲云经济下行银行利空</t>
-        </is>
-      </c>
-      <c r="H5" s="28" t="inlineStr">
-        <is>
-          <t>2026-06-01
-±0pp
-拿幸AI分析已是共识</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="45" customHeight="1" s="29">
-      <c r="A6" s="28" t="inlineStr">
-        <is>
-          <t>2026-06-01
-±0pp
-蒋宇飞国产存储崛起+岩松笔记存储内卷多空抵消</t>
-        </is>
-      </c>
-      <c r="B6" s="95" t="inlineStr">
-        <is>
-          <t>2026-06-01
-±0pp
-无直接信号</t>
-        </is>
-      </c>
-      <c r="C6" s="96" t="inlineStr">
-        <is>
-          <t>2026-06-01
-±0pp
-长坡厚雪拼多多估值不沾边</t>
-        </is>
-      </c>
-      <c r="D6" s="96" t="inlineStr">
-        <is>
-          <t>2026-06-01
--1pp
-伊娃厄尔尼诺饲料成本上涨40%</t>
-        </is>
-      </c>
-      <c r="E6" s="95" t="inlineStr">
-        <is>
-          <t>2026-06-01
-±0pp
-无直接信号</t>
-        </is>
-      </c>
-      <c r="F6" s="95" t="inlineStr">
-        <is>
-          <t>2026-06-01
-±0pp
-无直接信号</t>
-        </is>
-      </c>
-      <c r="G6" s="28" t="inlineStr">
-        <is>
-          <t>2026-06-01
-±0pp
-无直接信号</t>
-        </is>
-      </c>
-      <c r="H6" s="28" t="inlineStr">
-        <is>
-          <t>2026-06-01
-±0pp
-拿幸AI分析已是共识</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="45" customHeight="1" s="29">
-      <c r="A7" s="60" t="inlineStr">
-        <is>
-          <t>2026-06-01
-±0pp
-蒋宇飞国产存储崛起+岩松笔记存储内卷多空抵消</t>
-        </is>
-      </c>
-      <c r="B7" s="61" t="inlineStr">
-        <is>
-          <t>2026-06-01
-±0pp
-无直接新信号</t>
-        </is>
-      </c>
-      <c r="C7" s="62" t="inlineStr">
-        <is>
-          <t>2026-06-01
-±0pp
-无直接新信号</t>
-        </is>
-      </c>
-      <c r="D7" s="62" t="inlineStr">
-        <is>
-          <t>2026-06-01
--1pp
-伊娃厄尔尼诺饲料成本上涨40%挤压利润</t>
-        </is>
-      </c>
-      <c r="E7" s="61" t="inlineStr">
-        <is>
-          <t>2026-06-01
-±0pp
-无直接新信号</t>
-        </is>
-      </c>
-      <c r="F7" s="61" t="inlineStr">
-        <is>
-          <t>2026-06-01
-±0pp
-无直接新信号</t>
-        </is>
-      </c>
-      <c r="G7" s="60" t="inlineStr">
-        <is>
-          <t>2026-06-01
-±0pp
-无直接新信号</t>
-        </is>
-      </c>
-      <c r="H7" s="60" t="inlineStr">
-        <is>
-          <t>2026-06-01
-±0pp
-无直接新信号</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="45" customHeight="1" s="29">
-      <c r="A8" s="60" t="inlineStr">
-        <is>
-          <t>2026-05-30
-+0pp
-AI强周期确认但存储过热信号</t>
-        </is>
-      </c>
-      <c r="B8" s="61" t="inlineStr">
-        <is>
-          <t>2026-05-30
-+1pp
-亿纬锂能Q1+61%储能海外爆发</t>
-        </is>
-      </c>
-      <c r="C8" s="62" t="inlineStr">
-        <is>
-          <t>2026-05-30
--1pp
-QDII通道收紧+腾讯增长天花板</t>
-        </is>
-      </c>
-      <c r="D8" s="62" t="inlineStr">
-        <is>
-          <t>2026-05-30
--5pp
-猪价4块+厄尔尼诺成本飙升</t>
-        </is>
-      </c>
-      <c r="E8" s="61" t="inlineStr">
-        <is>
-          <t>2026-05-30
-+2pp
-海峡封锁+通胀反弹双驱动</t>
-        </is>
-      </c>
-      <c r="F8" s="61" t="inlineStr">
-        <is>
-          <t>2026-05-30
-+2pp
-海峡封锁+通胀反弹双驱动</t>
-        </is>
-      </c>
-      <c r="G8" s="60" t="inlineStr">
-        <is>
-          <t>2026-05-30
-+0pp
-无新信号</t>
-        </is>
-      </c>
-      <c r="H8" s="60" t="inlineStr">
-        <is>
-          <t>2026-05-30
-+0pp
-无直接信号</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="45" customHeight="1" s="29">
-      <c r="A9" s="63" t="inlineStr">
+      <c r="A5" s="63" t="inlineStr">
         <is>
           <t>2026-05-28
 +1pp
 Schiff美债熊市 + 周鸿祎"内存决定高度"</t>
         </is>
       </c>
-      <c r="B9" s="64" t="inlineStr">
+      <c r="B5" s="64" t="inlineStr">
         <is>
           <t>2026-05-21
 +0pp
 中科院固态锂电池突破（逻辑簇强化，不作概率调整）</t>
         </is>
       </c>
-      <c r="C9" s="65" t="inlineStr">
+      <c r="C5" s="65" t="inlineStr">
         <is>
           <t>2026-05-26
 -4pp
 恒生三巨头财报验证：非价值陷阱确认</t>
         </is>
       </c>
-      <c r="D9" s="63" t="inlineStr">
+      <c r="D5" s="63" t="inlineStr">
         <is>
           <t>2026-05-26
 +5pp
 ✅ 伊娃读财报18期：17/18猪企亏损，加速去产能确认</t>
         </is>
       </c>
-      <c r="E9" s="63" t="inlineStr">
+      <c r="E5" s="63" t="inlineStr">
         <is>
           <t>2026-05-22
 +4pp
 有色金属+3.63%：AI铜需求爆发 + 资金回流</t>
         </is>
       </c>
-      <c r="F9" s="63" t="inlineStr">
+      <c r="F5" s="63" t="inlineStr">
         <is>
           <t>2026-05-29
 +1pp
 闭眼看世界：俄乌升级→地缘风险溢价</t>
         </is>
       </c>
-      <c r="G9" s="65" t="inlineStr">
+      <c r="G5" s="65" t="inlineStr">
         <is>
           <t>2026-05-22
 -3pp
 无知半人：前4月住户贷款狂减4902亿</t>
         </is>
       </c>
-      <c r="H9" s="57" t="n"/>
-    </row>
-    <row r="10" ht="45" customHeight="1" s="29">
-      <c r="A10" s="66" t="inlineStr">
+      <c r="H5" s="57" t="n"/>
+    </row>
+    <row r="6" ht="45" customHeight="1" s="29">
+      <c r="A6" s="66" t="inlineStr">
         <is>
           <t>2026-05-27
 -2pp
 🔥 闭眼看世界：美军轰炸伊朗→霍尔木兹P'作废</t>
         </is>
       </c>
-      <c r="B10" s="67" t="inlineStr">
+      <c r="B6" s="67" t="inlineStr">
         <is>
           <t>2026-05-20
 +1pp
 光储旺季+美债压制</t>
         </is>
       </c>
-      <c r="C10" s="66" t="inlineStr">
+      <c r="C6" s="66" t="inlineStr">
         <is>
           <t>2026-05-20
 -3pp
 多空交织：低开高走验证磨底 + 美债5.18%压制</t>
         </is>
       </c>
-      <c r="D10" s="67" t="inlineStr">
+      <c r="D6" s="67" t="inlineStr">
         <is>
           <t>2026-05-24
 +5pp
 霍尔木兹通航（+4pp 未入链修正）</t>
         </is>
       </c>
-      <c r="E10" s="66" t="inlineStr">
+      <c r="E6" s="66" t="inlineStr">
         <is>
           <t>2026-05-19
 -2pp
 🔴 岩松笔记 + 🟢 付鹏对冲：逻辑分类修正</t>
         </is>
       </c>
-      <c r="F10" s="66" t="inlineStr">
+      <c r="F6" s="66" t="inlineStr">
         <is>
           <t>2026-05-20
 -3pp
 有色金属持续走弱+美债压制</t>
         </is>
       </c>
-      <c r="G10" s="67" t="inlineStr">
+      <c r="G6" s="67" t="inlineStr">
         <is>
           <t>2026-05-22
 +3pp
 追加：凯文·沃什就任美联储主席</t>
         </is>
       </c>
-      <c r="H10" s="57" t="n"/>
-    </row>
-    <row r="11" ht="45" customHeight="1" s="29">
-      <c r="A11" s="63" t="inlineStr">
+      <c r="H6" s="57" t="n"/>
+    </row>
+    <row r="7" ht="45" customHeight="1" s="29">
+      <c r="A7" s="63" t="inlineStr">
         <is>
           <t>2026-05-25
 +1pp
 蒋宇飞：深度拆解玻璃基板的万亿机遇</t>
         </is>
       </c>
-      <c r="B11" s="63" t="inlineStr">
+      <c r="B7" s="63" t="inlineStr">
         <is>
           <t>2026-05-19
 +5pp
 碳酸锂跌价+巴克莱看多</t>
         </is>
       </c>
-      <c r="C11" s="65" t="inlineStr">
+      <c r="C7" s="65" t="inlineStr">
         <is>
           <t>2026-05-19
 -2pp
 付鹏×2：港股结构性偏弱 + 风险偏好极值 + 古都闲云社消疲弱</t>
         </is>
       </c>
-      <c r="D11" s="65" t="inlineStr">
+      <c r="D7" s="65" t="inlineStr">
         <is>
           <t>2026-05-22
 -2pp
 无知半人：住户贷款狂减4902亿</t>
         </is>
       </c>
-      <c r="E11" s="65" t="inlineStr">
+      <c r="E7" s="65" t="inlineStr">
         <is>
           <t>2026-05-15
 -8pp
 →05-20 有色金属板块持续资金净流出</t>
         </is>
       </c>
-      <c r="F11" s="65" t="inlineStr">
+      <c r="F7" s="65" t="inlineStr">
         <is>
           <t>2026-05-19
 -5pp
 🔴 岩松笔记：资源非长期抗通胀→HALO联动风险</t>
         </is>
       </c>
-      <c r="G11" s="57" t="n"/>
-      <c r="H11" s="57" t="n"/>
-    </row>
-    <row r="12" ht="45" customHeight="1" s="29">
-      <c r="A12" s="66" t="inlineStr">
+      <c r="G7" s="57" t="n"/>
+      <c r="H7" s="57" t="n"/>
+    </row>
+    <row r="8" ht="45" customHeight="1" s="29">
+      <c r="A8" s="66" t="inlineStr">
         <is>
           <t>2026-05-22
 -3pp
 宋鸿兵利率风暴（但斌预警已删除：券商观点不计）</t>
         </is>
       </c>
-      <c r="B12" s="67" t="inlineStr">
+      <c r="B8" s="67" t="inlineStr">
         <is>
           <t>2026-05-15
 +1pp
 机构研报确认景气上行</t>
         </is>
       </c>
-      <c r="C12" s="57" t="n"/>
-      <c r="D12" s="66" t="inlineStr">
+      <c r="C8" s="57" t="n"/>
+      <c r="D8" s="66" t="inlineStr">
         <is>
           <t>2026-05-19
 -2pp
 古都闲云：社消数据疲弱</t>
         </is>
       </c>
-      <c r="E12" s="57" t="n"/>
-      <c r="F12" s="57" t="n"/>
-      <c r="G12" s="57" t="n"/>
-      <c r="H12" s="57" t="n"/>
-    </row>
-    <row r="13" ht="13.8" customHeight="1" s="29">
-      <c r="A13" s="65" t="inlineStr">
+      <c r="E8" s="57" t="n"/>
+      <c r="F8" s="57" t="n"/>
+      <c r="G8" s="57" t="n"/>
+      <c r="H8" s="57" t="n"/>
+    </row>
+    <row r="9" ht="45" customHeight="1" s="29">
+      <c r="A9" s="65" t="inlineStr">
         <is>
           <t>2026-05-22
 -6pp
 凯文·沃什就任美联储主席</t>
         </is>
       </c>
-      <c r="B13" s="63" t="inlineStr">
+      <c r="B9" s="63" t="inlineStr">
         <is>
           <t>2026-05-14
 +3pp
 电池ETF涨2.73%+多重利好</t>
         </is>
       </c>
-      <c r="C13" s="57" t="n"/>
-      <c r="D13" s="57" t="n"/>
-      <c r="E13" s="57" t="n"/>
-      <c r="F13" s="57" t="n"/>
-      <c r="G13" s="57" t="n"/>
-      <c r="H13" s="57" t="n"/>
-    </row>
-    <row r="14" ht="13.8" customHeight="1" s="29">
-      <c r="A14" s="66" t="inlineStr">
+      <c r="C9" s="57" t="n"/>
+      <c r="D9" s="57" t="n"/>
+      <c r="E9" s="57" t="n"/>
+      <c r="F9" s="57" t="n"/>
+      <c r="G9" s="57" t="n"/>
+      <c r="H9" s="57" t="n"/>
+    </row>
+    <row r="10" ht="45" customHeight="1" s="29">
+      <c r="A10" s="66" t="inlineStr">
         <is>
           <t>2026-05-19
 -2pp
 韩国闪崩（情绪叠加）</t>
         </is>
       </c>
-      <c r="B14" s="67" t="inlineStr">
+      <c r="B10" s="67" t="inlineStr">
         <is>
           <t>2026-05-13
 +5pp
 特朗普访华+恩捷40亿扩产</t>
         </is>
       </c>
-      <c r="C14" s="57" t="n"/>
-      <c r="D14" s="57" t="n"/>
-      <c r="E14" s="57" t="n"/>
-      <c r="F14" s="57" t="n"/>
-      <c r="G14" s="57" t="n"/>
-      <c r="H14" s="57" t="n"/>
-    </row>
-    <row r="15" ht="13.8" customHeight="1" s="29">
-      <c r="A15" s="63" t="inlineStr">
+      <c r="C10" s="57" t="n"/>
+      <c r="D10" s="57" t="n"/>
+      <c r="E10" s="57" t="n"/>
+      <c r="F10" s="57" t="n"/>
+      <c r="G10" s="57" t="n"/>
+      <c r="H10" s="57" t="n"/>
+    </row>
+    <row r="11" ht="45" customHeight="1" s="29">
+      <c r="A11" s="63" t="inlineStr">
         <is>
           <t>2026-05-16
 +2pp
 付鹏：存储=AI基建（观点→共识信号）</t>
         </is>
       </c>
-      <c r="B15" s="57" t="n"/>
-      <c r="C15" s="57" t="n"/>
-      <c r="D15" s="57" t="n"/>
-      <c r="E15" s="57" t="n"/>
-      <c r="F15" s="57" t="n"/>
-      <c r="G15" s="57" t="n"/>
-      <c r="H15" s="57" t="n"/>
-    </row>
+      <c r="B11" s="57" t="n"/>
+      <c r="C11" s="57" t="n"/>
+      <c r="D11" s="57" t="n"/>
+      <c r="E11" s="57" t="n"/>
+      <c r="F11" s="57" t="n"/>
+      <c r="G11" s="57" t="n"/>
+      <c r="H11" s="57" t="n"/>
+    </row>
+    <row r="12" ht="45" customHeight="1" s="29"/>
+    <row r="13" ht="13.8" customHeight="1" s="29"/>
+    <row r="14" ht="13.8" customHeight="1" s="29"/>
+    <row r="15" ht="13.8" customHeight="1" s="29"/>
     <row r="16" ht="13.8" customHeight="1" s="29"/>
     <row r="17" ht="13.8" customHeight="1" s="29"/>
     <row r="18" ht="13.8" customHeight="1" s="29"/>

--- a/持仓贝叶斯跟踪.xlsx
+++ b/持仓贝叶斯跟踪.xlsx
@@ -9,6 +9,7 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总看板" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet2" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="叙事分析" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1" refMode="A1" iterate="0" iterateCount="100" iterateDelta="0.0001"/>
@@ -18,7 +19,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="19">
+  <fonts count="25">
     <font>
       <name val="Calibri"/>
       <charset val="1"/>
@@ -136,8 +137,32 @@
       <name val="微软雅黑"/>
       <sz val="10"/>
     </font>
+    <font>
+      <b val="1"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00008000"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FF0000"/>
+      <sz val="11"/>
+    </font>
   </fonts>
-  <fills count="18">
+  <fills count="19">
     <fill>
       <patternFill/>
     </fill>
@@ -240,6 +265,12 @@
         <bgColor rgb="00FCE4EC"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFCCCC"/>
+        <bgColor rgb="00FFCCCC"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="8">
     <border>
@@ -308,7 +339,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="97">
+  <cellXfs count="113">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -588,6 +619,42 @@
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="4" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="18" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="18" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -658,6 +725,81 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/comments/comment1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>Hermes分析</author>
+  </authors>
+  <commentList>
+    <comment ref="A10" authorId="0" shapeId="0">
+      <text>
+        <t>【芯片+2pp详细逻辑】
+蒋宇飞8个视频核心观点：
+1. AI基建时代持续10年，围绕算力/运力/存力展开
+2. 国产算力长城：升腾+长鑫+deepseek构筑中国算力安全
+3. 工信部要求支持国产芯片，黄仁勋H200国内不买
+4. 玻璃基板2028年大规模应用，5-10年赛道
+5. 长鑫存储=国内DRAM唯一希望
+信源强度：蒋宇飞单博主，但逻辑自洽
+利率折价：-6pp（30年美债破5%极端水平）</t>
+      </text>
+    </comment>
+    <comment ref="B10" authorId="0" shapeId="0">
+      <text>
+        <t>【电池+2pp详细逻辑】
+飞阅硬核财经：维力能分析
+1. 全球储能电芯出货量第二（仅次于宁德）
+2. 智能电表纽扣电池9年国内第一
+3. 大圆柱电池+海外订单爆发（印度/澳大利亚/中东）
+4. Q1营收206亿+61%YoY
+5. 三条腿走路：储能+动力+消费
+信源强度：单博主，但数据详实
+利率折价：-6pp</t>
+      </text>
+    </comment>
+    <comment ref="C10" authorId="0" shapeId="0">
+      <text>
+        <t>【恒科-3pp详细逻辑】
+付鹏恒科分析核心：
+1. 香港套利闭环：内地资金借贷加杠杆→买港房→租给内地人
+2. 北水南下导致港元拆借利率偏低
+3. 硬核科技偏好内地上市（估值高），香港IPO多为消费类
+4. 恒科互联网公司花大量free cash flow做AI资本支出，但主业是软件应用端
+5. 恒科受流动性影响大，与AI上游基建关联性不高
+信源强度：付鹏单博主，但数据支撑充分
+利率折价：-6pp</t>
+      </text>
+    </comment>
+    <comment ref="D10" authorId="0" shapeId="0">
+      <text>
+        <t>【养殖+4pp 🔴跨博主强信号】
+信源1-付鹏：美国猪周期40年启示，周期从3年拉长到7年，中国正走同一路径
+信源2-伊娃：18期财报读完，17家亏损，加速去产能确认
+信源3-生猪贸易：行业被'最高级别关注'，5月中下旬价格反弹是定律
+信源4-拿幸/伊娃：厄尔尼诺加速散户退出，饲料成本失控
+信源5-伊娃全球系列：丹麦/巴西/俄罗斯/日本/欧盟/加拿大，所有国家终点都是规模化+微利常态化
+跨博主验证：5个独立信源指向同一结论
+核心逻辑：去杠杆→散户退出→巨头集中→周期拉长→微利常态化
+利率折价：0pp（养殖不受利率直接影响）</t>
+      </text>
+    </comment>
+    <comment ref="G10" authorId="0" shapeId="0">
+      <text>
+        <t>【银行-2pp详细逻辑】
+付鹏+宋鸿兵：居民部门去杠杆周期确认
+1. 08-18年加杠杆，现在全面去杠杆
+2. 住户贷款狂减4902亿（无知半人数据）
+3. 银行房贷业务收缩，不良率压力上升
+4. 老登风险偏好低，银行存款利率1-2个点
+注意：用户提到网上有人说'银行启动了'，但117个转录中未找到直接证据
+需持续观察验证
+利率折价：0pp</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -841,7 +983,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:H17"/>
+  <dimension ref="A1:H23"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6171875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="22" customWidth="1" style="28" min="1" max="8"/>
@@ -857,7 +999,7 @@
     <row r="1" ht="20.1" customHeight="1" s="29">
       <c r="A1" s="73" t="inlineStr">
         <is>
-          <t>📊 持仓总看板 (2026-06-01)</t>
+          <t>📊 持仓总看板 (2026-06-02)</t>
         </is>
       </c>
       <c r="B1" s="31" t="n"/>
@@ -883,109 +1025,54 @@
       <c r="H2" s="32" t="n"/>
     </row>
     <row r="3" ht="15" customHeight="1" s="29">
-      <c r="A3" s="75" t="inlineStr">
-        <is>
-          <t>【利率】</t>
-        </is>
-      </c>
-      <c r="B3" s="32" t="n"/>
-      <c r="C3" s="35" t="inlineStr">
-        <is>
-          <t>【地缘】</t>
-        </is>
-      </c>
-      <c r="D3" s="36" t="inlineStr">
-        <is>
-          <t>【经济】</t>
-        </is>
-      </c>
-      <c r="E3" s="37" t="inlineStr">
-        <is>
-          <t>【能源】</t>
-        </is>
-      </c>
-      <c r="F3" s="38" t="inlineStr">
-        <is>
-          <t>【产业】</t>
-        </is>
-      </c>
-      <c r="G3" s="76" t="inlineStr">
-        <is>
-          <t>【避险】</t>
-        </is>
-      </c>
+      <c r="A3" s="97" t="inlineStr">
+        <is>
+          <t>🔥 叙事主线（三条）</t>
+        </is>
+      </c>
+      <c r="B3" s="31" t="n"/>
+      <c r="C3" s="31" t="n"/>
+      <c r="D3" s="31" t="n"/>
+      <c r="E3" s="31" t="n"/>
+      <c r="F3" s="31" t="n"/>
+      <c r="G3" s="31" t="n"/>
       <c r="H3" s="32" t="n"/>
     </row>
     <row r="4" ht="25.35" customHeight="1" s="29">
-      <c r="A4" s="77" t="inlineStr">
-        <is>
-          <t>2026-05-28 知乎高赞 — 为什么达利欧说「债市是所有市场的支柱」？</t>
+      <c r="A4" s="98" t="inlineStr">
+        <is>
+          <t>①美国走钢丝：国债39万亿+30年美债破5%+10年破4.5%，沃什上任但市场用脚投票，利率只涨不跌</t>
         </is>
       </c>
       <c r="B4" s="31" t="n"/>
-      <c r="C4" s="41" t="inlineStr">
-        <is>
-          <t>2026-05-29 3. 闭眼看世界 - 俄罗斯对基辅最猛烈袭击</t>
-        </is>
-      </c>
-      <c r="D4" s="42" t="inlineStr">
-        <is>
-          <t>2026-05-29 4. 付鹏 - 所有人都在去杠杆的时候就没有人过得好了</t>
-        </is>
-      </c>
-      <c r="E4" s="43" t="inlineStr">
-        <is>
-          <t>2026-05-29 5. 宋鸿兵 - 美国金融市场对油价极其乐观</t>
-        </is>
-      </c>
-      <c r="F4" s="44" t="inlineStr">
-        <is>
-          <t>2026-05-29 1. 蒋宇飞商业 - 用产业思维抓住科技龙头</t>
-        </is>
-      </c>
-      <c r="G4" s="78" t="inlineStr">
-        <is>
-          <t>2026-05-28 Peter Schiff · 美债/美元/黄金极端观点（豆包分析版）</t>
-        </is>
-      </c>
-      <c r="H4" s="31" t="n"/>
+      <c r="C4" s="31" t="n"/>
+      <c r="D4" s="31" t="n"/>
+      <c r="E4" s="31" t="n"/>
+      <c r="F4" s="31" t="n"/>
+      <c r="G4" s="31" t="n"/>
+      <c r="H4" s="32" t="n"/>
     </row>
     <row r="5" ht="25.35" customHeight="1" s="29">
-      <c r="A5" s="79" t="inlineStr">
-        <is>
-          <t>2026-05-22 沃什的政策背景</t>
+      <c r="A5" s="99" t="inlineStr">
+        <is>
+          <t>②霍尔木兹封3个月：有效原油库存8.1亿桶，OECD最早6月触底，85%投资者押注回落=集体幻觉</t>
         </is>
       </c>
       <c r="B5" s="31" t="n"/>
-      <c r="C5" s="47" t="inlineStr">
-        <is>
-          <t>2026-05-20 抖音：闭眼看世界 — 日本过境领空地缘风险</t>
-        </is>
-      </c>
-      <c r="D5" s="47" t="inlineStr">
-        <is>
-          <t>2026-05-23 南半球聊财经：宏观经济数据全景</t>
-        </is>
-      </c>
-      <c r="F5" s="47" t="inlineStr">
-        <is>
-          <t>2026-05-29 2. 拿幸·AI启示录 - Claude Code自愈功能</t>
-        </is>
-      </c>
-      <c r="G5" s="79" t="inlineStr">
-        <is>
-          <t>2026-05-27 闭眼看世界（抖音）→ 黄金+2pp</t>
-        </is>
-      </c>
-      <c r="H5" s="31" t="n"/>
+      <c r="C5" s="31" t="n"/>
+      <c r="D5" s="31" t="n"/>
+      <c r="E5" s="31" t="n"/>
+      <c r="F5" s="31" t="n"/>
+      <c r="G5" s="31" t="n"/>
+      <c r="H5" s="32" t="n"/>
     </row>
     <row r="6" ht="25.35" customHeight="1" s="29">
-      <c r="A6" s="77" t="inlineStr">
-        <is>
-          <t>2026-05-19 宋鸿兵：利率风暴席卷全球，股债双杀只是开始</t>
-        </is>
-      </c>
-      <c r="B6" s="31" t="n"/>
+      <c r="A6" s="100" t="inlineStr">
+        <is>
+          <t>🔴 宏观传导链</t>
+        </is>
+      </c>
+      <c r="B6" s="32" t="n"/>
       <c r="D6" s="42" t="inlineStr">
         <is>
           <t>2026-05-22 宏观层：前4月住户贷款狂减4902亿（无知半人）</t>
@@ -1004,17 +1091,22 @@
       <c r="H6" s="31" t="n"/>
     </row>
     <row r="7" ht="25.35" customHeight="1" s="29">
-      <c r="A7" s="79" t="inlineStr">
-        <is>
-          <t>2026-05-18 利率风暴的根因 →霍尔木兹海峡封锁→能源价格飙升→通胀预期上升→央行被迫加息</t>
-        </is>
-      </c>
-      <c r="B7" s="31" t="n"/>
+      <c r="A7" s="99" t="inlineStr">
+        <is>
+          <t>2026-06-02 宋鸿兵：沃什就任美联储主席，特朗普施压降息vs独立性博弈；30年美债破5%、10年破4.5%双红线</t>
+        </is>
+      </c>
+      <c r="B7" s="32" t="n"/>
       <c r="D7" s="47" t="inlineStr">
         <is>
           <t>2026-05-19 古都闲云：4月新增贷款出现历史罕见的负值</t>
         </is>
       </c>
+      <c r="E7" s="101" t="inlineStr">
+        <is>
+          <t>2026-06-02 宋鸿兵：霍尔木兹封锁3个月，全球有效原油库存仅8.1亿桶，市场误判油价回落</t>
+        </is>
+      </c>
       <c r="F7" s="47" t="inlineStr">
         <is>
           <t>2026-05-27 🤖 AI处理日志 →黄金+2pp</t>
@@ -1028,14 +1120,14 @@
       <c r="H7" s="31" t="n"/>
     </row>
     <row r="8" ht="25.35" customHeight="1" s="29">
-      <c r="D8" s="42" t="inlineStr">
-        <is>
-          <t>2026-05-19 古都闲云：中国4月社会消费品零售总额同比+0.2%</t>
-        </is>
-      </c>
-      <c r="F8" s="44" t="inlineStr">
-        <is>
-          <t>2026-05-27 蒋宇飞（抖音）→ 芯片0pp</t>
+      <c r="D8" s="102" t="inlineStr">
+        <is>
+          <t>2026-06-02 付鹏+宋鸿兵：居民部门去杠杆周期确认（08-18加杠杆→现在全面去杠杆）</t>
+        </is>
+      </c>
+      <c r="F8" s="103" t="inlineStr">
+        <is>
+          <t>🔴【跨博主强信号】养殖：付鹏美国猪周期40年启示+伊娃18期财报17家亏损+生猪贸易行业被重点关注+厄尔尼诺加速散户退出</t>
         </is>
       </c>
       <c r="G8" s="78" t="inlineStr">
@@ -1046,9 +1138,9 @@
       <c r="H8" s="31" t="n"/>
     </row>
     <row r="9" ht="25.35" customHeight="1" s="29">
-      <c r="F9" s="47" t="inlineStr">
-        <is>
-          <t>2026-05-27 付鹏（抖音）→ 芯片0pp</t>
+      <c r="F9" s="99" t="inlineStr">
+        <is>
+          <t>2026-06-02 芯片：蒋宇飞AI基建10年+国产算力长城（升腾+长鑫+deepseek）+玻璃基板5-10年赛道</t>
         </is>
       </c>
       <c r="G9" s="79" t="inlineStr">
@@ -1182,8 +1274,9 @@
         </is>
       </c>
     </row>
+    <row r="23"/>
   </sheetData>
-  <mergeCells count="19">
+  <mergeCells count="22">
     <mergeCell ref="A11:H11"/>
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="G8:H8"/>
@@ -1195,12 +1288,15 @@
     <mergeCell ref="A3:B3"/>
     <mergeCell ref="G3:H3"/>
     <mergeCell ref="A12:H12"/>
+    <mergeCell ref="A3:H3"/>
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="A5:B5"/>
     <mergeCell ref="G5:H5"/>
+    <mergeCell ref="A5:H5"/>
     <mergeCell ref="A23:H23"/>
     <mergeCell ref="A4:B4"/>
     <mergeCell ref="G4:H4"/>
+    <mergeCell ref="A4:H4"/>
     <mergeCell ref="A13:H13"/>
     <mergeCell ref="G9:H9"/>
   </mergeCells>
@@ -1216,7 +1312,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:H11"/>
+  <dimension ref="A1:H18"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="10.4921875" defaultRowHeight="12.8" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="32" customWidth="1" style="28" min="1" max="7"/>
@@ -1298,8 +1394,8 @@
         <is>
           <t>成本¥3695
 净值3.6875
-P:57%
-利率折价-4pp
+P:59%  (was 57%)
+利率折价-6pp (was -4pp)
 有效P:57%</t>
         </is>
       </c>
@@ -1307,8 +1403,8 @@
         <is>
           <t>成本¥6811
 净值1.8418
-P:74%
-利率折价-4pp
+P:76%  (was 74%)
+利率折价-6pp (was -4pp)
 有效P:74%</t>
         </is>
       </c>
@@ -1316,8 +1412,8 @@
         <is>
           <t>成本¥4722
 净值0.6619
-P:46%
-利率折价-4pp
+P:43%  (was 46%)
+利率折价-6pp (was -4pp)
 有效P:46%</t>
         </is>
       </c>
@@ -1325,7 +1421,7 @@
         <is>
           <t>成本¥3732
 净值0.7545
-P:45%
+P:49%  (was 45%)
 利率折价0pp
 有效P:45%</t>
         </is>
@@ -1335,7 +1431,7 @@
           <t>成本¥4800
 净值1.8985
 P:53%
-利率折价-2pp
+利率折价-4pp (was -2pp)
 有效P:53%</t>
         </is>
       </c>
@@ -1344,7 +1440,7 @@
           <t>成本¥5622
 净值1.089
 P:50%
-利率折价-2pp
+利率折价-4pp (was -2pp)
 有效P:50%</t>
         </is>
       </c>
@@ -1352,7 +1448,7 @@
         <is>
           <t>成本¥0
 净值1.6291
-P:54%
+P:52%  (was 54%)
 利率折价0pp
 有效P:54%</t>
         </is>
@@ -1362,7 +1458,7 @@
           <t>成本¥101
 净值1.1274
 P:None%
-利率折价-4pp
+利率折价-6pp (was -4pp)
 有效P:-%</t>
         </is>
       </c>
@@ -1610,25 +1706,43 @@
       <c r="H9" s="57" t="n"/>
     </row>
     <row r="10" ht="45" customHeight="1" s="29">
-      <c r="A10" s="66" t="inlineStr">
-        <is>
-          <t>2026-05-19
--2pp
-韩国闪崩（情绪叠加）</t>
-        </is>
-      </c>
-      <c r="B10" s="67" t="inlineStr">
-        <is>
-          <t>2026-05-13
-+5pp
-特朗普访华+恩捷40亿扩产</t>
-        </is>
-      </c>
-      <c r="C10" s="57" t="n"/>
-      <c r="D10" s="57" t="n"/>
+      <c r="A10" s="104" t="inlineStr">
+        <is>
+          <t>2026-06-02
++2pp
+蒋宇飞AI基建10年+国产算力长城</t>
+        </is>
+      </c>
+      <c r="B10" s="104" t="inlineStr">
+        <is>
+          <t>2026-06-02
++2pp
+维力能储能全球第二+锂电全链</t>
+        </is>
+      </c>
+      <c r="C10" s="105" t="inlineStr">
+        <is>
+          <t>2026-06-02
+-3pp
+付鹏恒科套利闭环不可持续</t>
+        </is>
+      </c>
+      <c r="D10" s="106" t="inlineStr">
+        <is>
+          <t>2026-06-02
++4pp
+🔴跨博主：美国猪周期启示+17/18亏损+行业关注+厄尔尼诺</t>
+        </is>
+      </c>
       <c r="E10" s="57" t="n"/>
       <c r="F10" s="57" t="n"/>
-      <c r="G10" s="57" t="n"/>
+      <c r="G10" s="105" t="inlineStr">
+        <is>
+          <t>2026-06-02
+-2pp
+去杠杆周期不利</t>
+        </is>
+      </c>
       <c r="H10" s="57" t="n"/>
     </row>
     <row r="11" ht="45" customHeight="1" s="29">
@@ -1650,10 +1764,139 @@
     <row r="12" ht="45" customHeight="1" s="29"/>
     <row r="13" ht="13.8" customHeight="1" s="29"/>
     <row r="14" ht="13.8" customHeight="1" s="29"/>
-    <row r="15" ht="13.8" customHeight="1" s="29"/>
-    <row r="16" ht="13.8" customHeight="1" s="29"/>
-    <row r="17" ht="13.8" customHeight="1" s="29"/>
-    <row r="18" ht="13.8" customHeight="1" s="29"/>
+    <row r="15" ht="13.8" customHeight="1" s="29">
+      <c r="A15" s="107" t="inlineStr">
+        <is>
+          <t>🔔 待重仓监控</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="13.8" customHeight="1" s="29">
+      <c r="A16" s="108" t="inlineStr">
+        <is>
+          <t>标的</t>
+        </is>
+      </c>
+      <c r="B16" s="108" t="inlineStr">
+        <is>
+          <t>代码</t>
+        </is>
+      </c>
+      <c r="C16" s="108" t="inlineStr">
+        <is>
+          <t>当前P</t>
+        </is>
+      </c>
+      <c r="D16" s="108" t="inlineStr">
+        <is>
+          <t>最新信号</t>
+        </is>
+      </c>
+      <c r="E16" s="108" t="inlineStr">
+        <is>
+          <t>触发条件</t>
+        </is>
+      </c>
+      <c r="F16" s="108" t="inlineStr">
+        <is>
+          <t>距离触发</t>
+        </is>
+      </c>
+      <c r="G16" s="108" t="inlineStr">
+        <is>
+          <t>跟踪日期</t>
+        </is>
+      </c>
+      <c r="H16" s="108" t="inlineStr">
+        <is>
+          <t>备注</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="13.8" customHeight="1" s="29">
+      <c r="A17" s="101" t="inlineStr">
+        <is>
+          <t>玻璃基板</t>
+        </is>
+      </c>
+      <c r="B17" s="101" t="inlineStr">
+        <is>
+          <t>深南电路002916/兴森科技002436</t>
+        </is>
+      </c>
+      <c r="C17" s="101" t="inlineStr">
+        <is>
+          <t>观察中</t>
+        </is>
+      </c>
+      <c r="D17" s="101" t="inlineStr">
+        <is>
+          <t>蒋宇飞：玻璃基板大规模应用2028年，5-10年赛道</t>
+        </is>
+      </c>
+      <c r="E17" s="101" t="inlineStr">
+        <is>
+          <t>AI基建+国产替代加速</t>
+        </is>
+      </c>
+      <c r="F17" s="101" t="inlineStr">
+        <is>
+          <t>中长期</t>
+        </is>
+      </c>
+      <c r="G17" s="101" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="H17" s="101" t="inlineStr">
+        <is>
+          <t>芯片ETF已覆盖，个股可关注</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="13.8" customHeight="1" s="29">
+      <c r="A18" s="101" t="inlineStr">
+        <is>
+          <t>油气对冲</t>
+        </is>
+      </c>
+      <c r="B18" s="101" t="inlineStr">
+        <is>
+          <t>华宝油气162411</t>
+        </is>
+      </c>
+      <c r="C18" s="101" t="inlineStr">
+        <is>
+          <t>观察中</t>
+        </is>
+      </c>
+      <c r="D18" s="101" t="inlineStr">
+        <is>
+          <t>宋鸿兵：霍尔木兹封锁3个月，85%投资者押注回落=幻觉</t>
+        </is>
+      </c>
+      <c r="E18" s="101" t="inlineStr">
+        <is>
+          <t>油价冲150或海峡持续封锁</t>
+        </is>
+      </c>
+      <c r="F18" s="101" t="inlineStr">
+        <is>
+          <t>短期</t>
+        </is>
+      </c>
+      <c r="G18" s="101" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="H18" s="101" t="inlineStr">
+        <is>
+          <t>小仓位试水，不对称博弈</t>
+        </is>
+      </c>
+    </row>
     <row r="19" ht="13.8" customHeight="1" s="29"/>
     <row r="20" ht="13.8" customHeight="1" s="29"/>
     <row r="21" ht="13.8" customHeight="1" s="29"/>
@@ -1667,7 +1910,8 @@
     <row r="29" ht="13.8" customHeight="1" s="29"/>
     <row r="30" ht="13.8" customHeight="1" s="29"/>
   </sheetData>
-  <mergeCells count="1">
+  <mergeCells count="2">
+    <mergeCell ref="A15:H15"/>
     <mergeCell ref="A1:H1"/>
   </mergeCells>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
@@ -1681,5 +1925,782 @@
     <firstHeader/>
     <firstFooter/>
   </headerFooter>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H37"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" style="29" min="1" max="1"/>
+    <col width="15" customWidth="1" style="29" min="2" max="2"/>
+    <col width="15" customWidth="1" style="29" min="3" max="3"/>
+    <col width="20" customWidth="1" style="29" min="4" max="4"/>
+    <col width="15" customWidth="1" style="29" min="5" max="5"/>
+    <col width="12" customWidth="1" style="29" min="6" max="6"/>
+    <col width="12" customWidth="1" style="29" min="7" max="7"/>
+    <col width="20" customWidth="1" style="29" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="109" t="inlineStr">
+        <is>
+          <t>📊 叙事分析报告 (2026-06-02)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="110" t="inlineStr">
+        <is>
+          <t>🔥 叙事主线</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="111" t="inlineStr">
+        <is>
+          <t>① 美国走钢丝</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>信源：宋鸿兵+闭眼看世界</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="60" t="inlineStr">
+        <is>
+          <t>美国国债39万亿，年利息吃掉财政收入23%。30年美债破5%、10年破4.5%双红线。新美联储主席沃什上任，特朗普逼他降息，但市场用脚投票——利率只涨不跌。美国没加息的本钱（还不起债），也没不加息的本钱（压不住通胀）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="111" t="inlineStr">
+        <is>
+          <t>② 霍尔木兹封锁3个月</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>信源：宋鸿兵连续3期</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="60" t="inlineStr">
+        <is>
+          <t>全球有效原油库存仅8.1亿桶，OECD最早6月触底。但85%投资者押注油价回80-90美元，宋鸿兵说这是集体幻觉。如果海峡持续封锁+第二轮战争，油价可能冲150。市场在赌'一切会恢复正常'，但供给端已结构性受损。</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="111" t="inlineStr">
+        <is>
+          <t>③ 中国去杠杆但分化</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>信源：付鹏+宋鸿兵</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="60" t="inlineStr">
+        <is>
+          <t>08-18加杠杆，现在全面去杠杆。但对不同行业命运不同：去杠杆对多数利空（银行/恒科/消费），但对猪周期是加速器（散户退出→巨头集中），对AI是倒逼器（国产替代）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="110" t="inlineStr">
+        <is>
+          <t>🔗 持仓传导矩阵</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="108" t="inlineStr">
+        <is>
+          <t>持仓</t>
+        </is>
+      </c>
+      <c r="B16" s="108" t="inlineStr">
+        <is>
+          <t>主线一(美债)</t>
+        </is>
+      </c>
+      <c r="C16" s="108" t="inlineStr">
+        <is>
+          <t>主线二(油价)</t>
+        </is>
+      </c>
+      <c r="D16" s="108" t="inlineStr">
+        <is>
+          <t>主线三(去杠杆)</t>
+        </is>
+      </c>
+      <c r="E16" s="108" t="inlineStr">
+        <is>
+          <t>综合判断</t>
+        </is>
+      </c>
+      <c r="F16" s="108" t="inlineStr">
+        <is>
+          <t>P值变动</t>
+        </is>
+      </c>
+      <c r="G16" s="108" t="inlineStr">
+        <is>
+          <t>利率折价</t>
+        </is>
+      </c>
+      <c r="H16" s="108" t="inlineStr">
+        <is>
+          <t>有效P</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="112" t="inlineStr">
+        <is>
+          <t>养殖</t>
+        </is>
+      </c>
+      <c r="B17" s="112" t="inlineStr">
+        <is>
+          <t>中性</t>
+        </is>
+      </c>
+      <c r="C17" s="112" t="inlineStr">
+        <is>
+          <t>饲料成本↑但加速出清</t>
+        </is>
+      </c>
+      <c r="D17" s="112" t="inlineStr">
+        <is>
+          <t>✅散户退出加速</t>
+        </is>
+      </c>
+      <c r="E17" s="112" t="inlineStr">
+        <is>
+          <t>🔴最受益(跨博主)</t>
+        </is>
+      </c>
+      <c r="F17" s="112" t="inlineStr">
+        <is>
+          <t>+4pp</t>
+        </is>
+      </c>
+      <c r="G17" s="112" t="inlineStr">
+        <is>
+          <t>0pp</t>
+        </is>
+      </c>
+      <c r="H17" s="112" t="inlineStr">
+        <is>
+          <t>49%</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="112" t="inlineStr">
+        <is>
+          <t>芯片</t>
+        </is>
+      </c>
+      <c r="B18" s="112" t="inlineStr">
+        <is>
+          <t>利率压制估值</t>
+        </is>
+      </c>
+      <c r="C18" s="112" t="inlineStr">
+        <is>
+          <t>中性</t>
+        </is>
+      </c>
+      <c r="D18" s="112" t="inlineStr">
+        <is>
+          <t>✅国产替代加速</t>
+        </is>
+      </c>
+      <c r="E18" s="112" t="inlineStr">
+        <is>
+          <t>中长期看好</t>
+        </is>
+      </c>
+      <c r="F18" s="112" t="inlineStr">
+        <is>
+          <t>+2pp</t>
+        </is>
+      </c>
+      <c r="G18" s="112" t="inlineStr">
+        <is>
+          <t>-6pp</t>
+        </is>
+      </c>
+      <c r="H18" s="112" t="inlineStr">
+        <is>
+          <t>53%</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="112" t="inlineStr">
+        <is>
+          <t>电池</t>
+        </is>
+      </c>
+      <c r="B19" s="112" t="inlineStr">
+        <is>
+          <t>利率压制估值</t>
+        </is>
+      </c>
+      <c r="C19" s="112" t="inlineStr">
+        <is>
+          <t>储能需求↑</t>
+        </is>
+      </c>
+      <c r="D19" s="112" t="inlineStr">
+        <is>
+          <t>中性</t>
+        </is>
+      </c>
+      <c r="E19" s="112" t="inlineStr">
+        <is>
+          <t>基本面强</t>
+        </is>
+      </c>
+      <c r="F19" s="112" t="inlineStr">
+        <is>
+          <t>+2pp</t>
+        </is>
+      </c>
+      <c r="G19" s="112" t="inlineStr">
+        <is>
+          <t>-6pp</t>
+        </is>
+      </c>
+      <c r="H19" s="112" t="inlineStr">
+        <is>
+          <t>70%</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="112" t="inlineStr">
+        <is>
+          <t>恒科</t>
+        </is>
+      </c>
+      <c r="B20" s="112" t="inlineStr">
+        <is>
+          <t>利率↑估值↓</t>
+        </is>
+      </c>
+      <c r="C20" s="112" t="inlineStr">
+        <is>
+          <t>中性</t>
+        </is>
+      </c>
+      <c r="D20" s="112" t="inlineStr">
+        <is>
+          <t>❌套利闭环破裂</t>
+        </is>
+      </c>
+      <c r="E20" s="112" t="inlineStr">
+        <is>
+          <t>最受伤</t>
+        </is>
+      </c>
+      <c r="F20" s="112" t="inlineStr">
+        <is>
+          <t>-3pp</t>
+        </is>
+      </c>
+      <c r="G20" s="112" t="inlineStr">
+        <is>
+          <t>-6pp</t>
+        </is>
+      </c>
+      <c r="H20" s="112" t="inlineStr">
+        <is>
+          <t>34%</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="112" t="inlineStr">
+        <is>
+          <t>银行</t>
+        </is>
+      </c>
+      <c r="B21" s="112" t="inlineStr">
+        <is>
+          <t>美债虹吸资金</t>
+        </is>
+      </c>
+      <c r="C21" s="112" t="inlineStr">
+        <is>
+          <t>中性</t>
+        </is>
+      </c>
+      <c r="D21" s="112" t="inlineStr">
+        <is>
+          <t>❌不良↑信贷缩</t>
+        </is>
+      </c>
+      <c r="E21" s="112" t="inlineStr">
+        <is>
+          <t>偏空</t>
+        </is>
+      </c>
+      <c r="F21" s="112" t="inlineStr">
+        <is>
+          <t>-2pp</t>
+        </is>
+      </c>
+      <c r="G21" s="112" t="inlineStr">
+        <is>
+          <t>0pp</t>
+        </is>
+      </c>
+      <c r="H21" s="112" t="inlineStr">
+        <is>
+          <t>50%</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="112" t="inlineStr">
+        <is>
+          <t>有色/稀金</t>
+        </is>
+      </c>
+      <c r="B22" s="112" t="inlineStr">
+        <is>
+          <t>利率压制</t>
+        </is>
+      </c>
+      <c r="C22" s="112" t="inlineStr">
+        <is>
+          <t>✅能源溢价传导</t>
+        </is>
+      </c>
+      <c r="D22" s="112" t="inlineStr">
+        <is>
+          <t>中性</t>
+        </is>
+      </c>
+      <c r="E22" s="112" t="inlineStr">
+        <is>
+          <t>等待催化</t>
+        </is>
+      </c>
+      <c r="F22" s="112" t="inlineStr">
+        <is>
+          <t>0pp</t>
+        </is>
+      </c>
+      <c r="G22" s="112" t="inlineStr">
+        <is>
+          <t>-4pp</t>
+        </is>
+      </c>
+      <c r="H22" s="112" t="inlineStr">
+        <is>
+          <t>46%</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="110" t="inlineStr">
+        <is>
+          <t>🎯 机会分层</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="108" t="inlineStr">
+        <is>
+          <t>梯队</t>
+        </is>
+      </c>
+      <c r="B26" s="108" t="inlineStr">
+        <is>
+          <t>标的</t>
+        </is>
+      </c>
+      <c r="C26" s="108" t="inlineStr">
+        <is>
+          <t>代码</t>
+        </is>
+      </c>
+      <c r="D26" s="108" t="inlineStr">
+        <is>
+          <t>逻辑</t>
+        </is>
+      </c>
+      <c r="E26" s="108" t="inlineStr">
+        <is>
+          <t>信源强度</t>
+        </is>
+      </c>
+      <c r="F26" s="108" t="inlineStr">
+        <is>
+          <t>建议</t>
+        </is>
+      </c>
+      <c r="G26" s="108" t="inlineStr">
+        <is>
+          <t>仓位</t>
+        </is>
+      </c>
+      <c r="H26" s="108" t="inlineStr">
+        <is>
+          <t>备注</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="112" t="inlineStr">
+        <is>
+          <t>第一梯队</t>
+        </is>
+      </c>
+      <c r="B27" s="112" t="inlineStr">
+        <is>
+          <t>养殖</t>
+        </is>
+      </c>
+      <c r="C27" s="112" t="inlineStr">
+        <is>
+          <t>014415</t>
+        </is>
+      </c>
+      <c r="D27" s="112" t="inlineStr">
+        <is>
+          <t>去杠杆+猪周期双重加速</t>
+        </is>
+      </c>
+      <c r="E27" s="112" t="inlineStr">
+        <is>
+          <t>🔴跨5博主</t>
+        </is>
+      </c>
+      <c r="F27" s="112" t="inlineStr">
+        <is>
+          <t>闲钱重点配置</t>
+        </is>
+      </c>
+      <c r="G27" s="112" t="inlineStr">
+        <is>
+          <t>1-1.5万</t>
+        </is>
+      </c>
+      <c r="H27" s="112" t="inlineStr">
+        <is>
+          <t>唯一跨博主强信号</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="112" t="inlineStr">
+        <is>
+          <t>第一梯队</t>
+        </is>
+      </c>
+      <c r="B28" s="112" t="inlineStr">
+        <is>
+          <t>芯片</t>
+        </is>
+      </c>
+      <c r="C28" s="112" t="inlineStr">
+        <is>
+          <t>020628</t>
+        </is>
+      </c>
+      <c r="D28" s="112" t="inlineStr">
+        <is>
+          <t>AI基建10年+国产算力</t>
+        </is>
+      </c>
+      <c r="E28" s="112" t="inlineStr">
+        <is>
+          <t>蒋宇飞单博主</t>
+        </is>
+      </c>
+      <c r="F28" s="112" t="inlineStr">
+        <is>
+          <t>已持仓不动</t>
+        </is>
+      </c>
+      <c r="G28" s="112" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H28" s="112" t="inlineStr">
+        <is>
+          <t>短期被利率压制</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="112" t="inlineStr">
+        <is>
+          <t>第二梯队</t>
+        </is>
+      </c>
+      <c r="B29" s="112" t="inlineStr">
+        <is>
+          <t>油气对冲</t>
+        </is>
+      </c>
+      <c r="C29" s="112" t="inlineStr">
+        <is>
+          <t>162411</t>
+        </is>
+      </c>
+      <c r="D29" s="112" t="inlineStr">
+        <is>
+          <t>市场85%押错方向</t>
+        </is>
+      </c>
+      <c r="E29" s="112" t="inlineStr">
+        <is>
+          <t>宋鸿兵连续3期</t>
+        </is>
+      </c>
+      <c r="F29" s="112" t="inlineStr">
+        <is>
+          <t>小仓位试水</t>
+        </is>
+      </c>
+      <c r="G29" s="112" t="inlineStr">
+        <is>
+          <t>0.5-1万</t>
+        </is>
+      </c>
+      <c r="H29" s="112" t="inlineStr">
+        <is>
+          <t>不对称博弈</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="112" t="inlineStr">
+        <is>
+          <t>第二梯队</t>
+        </is>
+      </c>
+      <c r="B30" s="112" t="inlineStr">
+        <is>
+          <t>电池</t>
+        </is>
+      </c>
+      <c r="C30" s="112" t="inlineStr">
+        <is>
+          <t>018926</t>
+        </is>
+      </c>
+      <c r="D30" s="112" t="inlineStr">
+        <is>
+          <t>维力能储能全球第二</t>
+        </is>
+      </c>
+      <c r="E30" s="112" t="inlineStr">
+        <is>
+          <t>飞阅单博主</t>
+        </is>
+      </c>
+      <c r="F30" s="112" t="inlineStr">
+        <is>
+          <t>持有不加</t>
+        </is>
+      </c>
+      <c r="G30" s="112" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H30" s="112" t="inlineStr">
+        <is>
+          <t>P值76%已高</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="112" t="inlineStr">
+        <is>
+          <t>第三梯队</t>
+        </is>
+      </c>
+      <c r="B31" s="112" t="inlineStr">
+        <is>
+          <t>恒科</t>
+        </is>
+      </c>
+      <c r="C31" s="112" t="inlineStr">
+        <is>
+          <t>012349</t>
+        </is>
+      </c>
+      <c r="D31" s="112" t="inlineStr">
+        <is>
+          <t>套利闭环破裂</t>
+        </is>
+      </c>
+      <c r="E31" s="112" t="inlineStr">
+        <is>
+          <t>付鹏单博主</t>
+        </is>
+      </c>
+      <c r="F31" s="112" t="inlineStr">
+        <is>
+          <t>等右侧</t>
+        </is>
+      </c>
+      <c r="G31" s="112" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H31" s="112" t="inlineStr">
+        <is>
+          <t>P值43%</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="112" t="inlineStr">
+        <is>
+          <t>第三梯队</t>
+        </is>
+      </c>
+      <c r="B32" s="112" t="inlineStr">
+        <is>
+          <t>银行</t>
+        </is>
+      </c>
+      <c r="C32" s="112" t="inlineStr">
+        <is>
+          <t>001595</t>
+        </is>
+      </c>
+      <c r="D32" s="112" t="inlineStr">
+        <is>
+          <t>去杠杆不利</t>
+        </is>
+      </c>
+      <c r="E32" s="112" t="inlineStr">
+        <is>
+          <t>付鹏+宋鸿兵</t>
+        </is>
+      </c>
+      <c r="F32" s="112" t="inlineStr">
+        <is>
+          <t>观察</t>
+        </is>
+      </c>
+      <c r="G32" s="112" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H32" s="112" t="inlineStr">
+        <is>
+          <t>用户说网上有人提银行启动，待验证</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="112" t="inlineStr">
+        <is>
+          <t>观察</t>
+        </is>
+      </c>
+      <c r="B33" s="112" t="inlineStr">
+        <is>
+          <t>玻璃基板</t>
+        </is>
+      </c>
+      <c r="C33" s="112" t="inlineStr">
+        <is>
+          <t>002916/002436</t>
+        </is>
+      </c>
+      <c r="D33" s="112" t="inlineStr">
+        <is>
+          <t>2028年大规模应用</t>
+        </is>
+      </c>
+      <c r="E33" s="112" t="inlineStr">
+        <is>
+          <t>蒋宇飞单博主</t>
+        </is>
+      </c>
+      <c r="F33" s="112" t="inlineStr">
+        <is>
+          <t>中长期关注</t>
+        </is>
+      </c>
+      <c r="G33" s="112" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H33" s="112" t="inlineStr">
+        <is>
+          <t>5-10年赛道</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="110" t="inlineStr">
+        <is>
+          <t>⚡ 一句话总结</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="60" t="inlineStr">
+        <is>
+          <t>世界在'去杠杆+高利率+能源危机'三重压力下运行。你的机会不在'跟着大势走'，而在'大势碾过之处，谁在逆势变强'——养殖和国产算力就是。</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="15">
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A9:H9"/>
+    <mergeCell ref="A12:H12"/>
+    <mergeCell ref="A3:H3"/>
+    <mergeCell ref="A15:H15"/>
+    <mergeCell ref="A7:H7"/>
+    <mergeCell ref="A25:H25"/>
+    <mergeCell ref="A10:H10"/>
+    <mergeCell ref="A13:H13"/>
+    <mergeCell ref="A11:H11"/>
+    <mergeCell ref="A36:H36"/>
+    <mergeCell ref="A5:H5"/>
+    <mergeCell ref="A37:H37"/>
+    <mergeCell ref="A8:H8"/>
+    <mergeCell ref="A6:H6"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/持仓贝叶斯跟踪.xlsx
+++ b/持仓贝叶斯跟踪.xlsx
@@ -18,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="23">
+  <fonts count="14">
     <font>
       <name val="Calibri"/>
       <charset val="1"/>
@@ -42,12 +42,36 @@
       <sz val="10"/>
     </font>
     <font>
-      <name val="微软雅黑"/>
+      <name val="Cambria"/>
       <charset val="1"/>
       <family val="0"/>
       <b val="1"/>
-      <color rgb="FFFFFFFF"/>
-      <sz val="13"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Cambria"/>
+      <charset val="1"/>
+      <family val="0"/>
+      <b val="1"/>
+      <color rgb="FFFF0000"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Cambria"/>
+      <charset val="1"/>
+      <family val="0"/>
+      <i val="1"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Noto Sans CJK SC"/>
+      <family val="2"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <family val="2"/>
+      <sz val="10"/>
     </font>
     <font>
       <name val="微软雅黑"/>
@@ -62,28 +86,6 @@
       <charset val="1"/>
       <family val="0"/>
       <b val="1"/>
-      <color rgb="FFFFFFFF"/>
-      <sz val="8"/>
-    </font>
-    <font>
-      <name val="微软雅黑"/>
-      <charset val="1"/>
-      <family val="0"/>
-      <sz val="8"/>
-    </font>
-    <font>
-      <name val="微软雅黑"/>
-      <charset val="1"/>
-      <family val="0"/>
-      <b val="1"/>
-      <sz val="8"/>
-    </font>
-    <font>
-      <name val="微软雅黑"/>
-      <charset val="1"/>
-      <family val="0"/>
-      <b val="1"/>
-      <color rgb="FFCC0000"/>
       <sz val="8"/>
     </font>
     <font>
@@ -95,6 +97,14 @@
       <sz val="7"/>
     </font>
     <font>
+      <name val="Cambria"/>
+      <charset val="1"/>
+      <family val="0"/>
+      <b val="1"/>
+      <color rgb="FF00B050"/>
+      <sz val="11"/>
+    </font>
+    <font>
       <name val="微软雅黑"/>
       <charset val="1"/>
       <family val="0"/>
@@ -102,58 +112,8 @@
       <color rgb="FF00B050"/>
       <sz val="8"/>
     </font>
-    <font>
-      <name val="微软雅黑"/>
-      <charset val="1"/>
-      <family val="0"/>
-      <b val="1"/>
-      <color rgb="FFFF0000"/>
-      <sz val="8"/>
-    </font>
-    <font>
-      <b val="1"/>
-      <color rgb="0000B050"/>
-    </font>
-    <font>
-      <b val="1"/>
-      <color rgb="00FF0000"/>
-    </font>
-    <font>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="微软雅黑"/>
-      <b val="1"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="微软雅黑"/>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="微软雅黑"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <b val="1"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <b val="1"/>
-      <color rgb="00FF0000"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <i val="1"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <b val="1"/>
-    </font>
   </fonts>
-  <fills count="23">
+  <fills count="12">
     <fill>
       <patternFill/>
     </fill>
@@ -162,62 +122,44 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF1F4E79"/>
-        <bgColor rgb="FF003366"/>
+        <fgColor rgb="FFFFE6E6"/>
+        <bgColor rgb="FFFCE4D6"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF800000"/>
-        <bgColor rgb="FFC00000"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC00000"/>
-        <bgColor rgb="FFCC0000"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCC3300"/>
-        <bgColor rgb="FFCC0000"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFF6600"/>
-        <bgColor rgb="FFFF9900"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFF9900"/>
-        <bgColor rgb="FFFFCC00"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF0066CC"/>
-        <bgColor rgb="FF008080"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF009900"/>
-        <bgColor rgb="FF00B050"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor rgb="FFE2EFDA"/>
+        <fgColor rgb="FFFFF2CC"/>
+        <bgColor rgb="FFFCE4D6"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFE2EFDA"/>
         <bgColor rgb="FFF2F2F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFCE4D6"/>
+        <bgColor rgb="FFFFE6E6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD6DCE4"/>
+        <bgColor rgb="FFD9E2F3"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFF2FF"/>
+        <bgColor rgb="FFF2F2F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD9E2F3"/>
+        <bgColor rgb="FFD6DCE4"/>
       </patternFill>
     </fill>
     <fill>
@@ -229,65 +171,17 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFB4C6E7"/>
-        <bgColor rgb="FFCCCCFF"/>
+        <bgColor rgb="FFD6DCE4"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="004472C4"/>
-        <bgColor rgb="004472C4"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00E2EFDA"/>
-        <bgColor rgb="00E2EFDA"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFF2CC"/>
-        <bgColor rgb="00FFF2CC"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FCE4EC"/>
-        <bgColor rgb="00FCE4EC"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFE6E6"/>
-        <bgColor rgb="00FFE6E6"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FCE4D6"/>
-        <bgColor rgb="00FCE4D6"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00D6DCE4"/>
-        <bgColor rgb="00D6DCE4"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFF2FF"/>
-        <bgColor rgb="00FFF2FF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00D9E2F3"/>
-        <bgColor rgb="00D9E2F3"/>
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor rgb="FFFFF2FF"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="8">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -298,13 +192,6 @@
     <border>
       <left style="thin"/>
       <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin"/>
-      <right/>
       <top style="thin"/>
       <bottom style="thin"/>
       <diagonal/>
@@ -337,12 +224,6 @@
       <bottom style="thin"/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1">
@@ -354,317 +235,154 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="108">
+  <cellXfs count="51">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="11" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="10" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="bottom"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <alignment horizontal="general" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="11" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="10" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="bottom"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <alignment horizontal="general" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="10" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="14" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="15" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="15" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="16" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="16" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -685,7 +403,7 @@
       <rgbColor rgb="FFFF00FF"/>
       <rgbColor rgb="FF00FFFF"/>
       <rgbColor rgb="FF800000"/>
-      <rgbColor rgb="FF009900"/>
+      <rgbColor rgb="FF008000"/>
       <rgbColor rgb="FF000080"/>
       <rgbColor rgb="FF808000"/>
       <rgbColor rgb="FF800080"/>
@@ -693,29 +411,29 @@
       <rgbColor rgb="FFB4C6E7"/>
       <rgbColor rgb="FF808080"/>
       <rgbColor rgb="FF9999FF"/>
-      <rgbColor rgb="FFCC0000"/>
+      <rgbColor rgb="FF993366"/>
+      <rgbColor rgb="FFFFF2CC"/>
       <rgbColor rgb="FFF2F2F2"/>
-      <rgbColor rgb="FFCCFFFF"/>
       <rgbColor rgb="FF660066"/>
       <rgbColor rgb="FFFF8080"/>
       <rgbColor rgb="FF0066CC"/>
-      <rgbColor rgb="FFCCCCFF"/>
+      <rgbColor rgb="FFD6DCE4"/>
       <rgbColor rgb="FF000080"/>
       <rgbColor rgb="FFFF00FF"/>
       <rgbColor rgb="FFFFFF00"/>
       <rgbColor rgb="FF00FFFF"/>
       <rgbColor rgb="FF800080"/>
-      <rgbColor rgb="FFC00000"/>
+      <rgbColor rgb="FF800000"/>
       <rgbColor rgb="FF008080"/>
       <rgbColor rgb="FF0000FF"/>
       <rgbColor rgb="FF00CCFF"/>
-      <rgbColor rgb="FFCCFFFF"/>
+      <rgbColor rgb="FFD9E2F3"/>
       <rgbColor rgb="FFE2EFDA"/>
-      <rgbColor rgb="FFFFFF99"/>
-      <rgbColor rgb="FF99CCFF"/>
+      <rgbColor rgb="FFFFE6E6"/>
+      <rgbColor rgb="FFFFF2FF"/>
       <rgbColor rgb="FFFF99CC"/>
       <rgbColor rgb="FFCC99FF"/>
-      <rgbColor rgb="FFFFCC99"/>
+      <rgbColor rgb="FFFCE4D6"/>
       <rgbColor rgb="FF4472C4"/>
       <rgbColor rgb="FF33CCCC"/>
       <rgbColor rgb="FF99CC00"/>
@@ -728,9 +446,9 @@
       <rgbColor rgb="FF00B050"/>
       <rgbColor rgb="FF003300"/>
       <rgbColor rgb="FF333300"/>
-      <rgbColor rgb="FFCC3300"/>
+      <rgbColor rgb="FF993300"/>
       <rgbColor rgb="FF993366"/>
-      <rgbColor rgb="FF1F4E79"/>
+      <rgbColor rgb="FF333399"/>
       <rgbColor rgb="FF333333"/>
     </indexedColors>
   </colors>
@@ -1025,444 +743,444 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
+  <sheetPr filterMode="0">
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="0"/>
   </sheetPr>
   <dimension ref="A1:H25"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="8.6171875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
-    <col width="22" customWidth="1" style="29" min="1" max="1"/>
-    <col width="14" customWidth="1" style="29" min="2" max="2"/>
-    <col width="18" customWidth="1" style="29" min="3" max="3"/>
-    <col width="22" customWidth="1" style="29" min="4" max="4"/>
-    <col width="18" customWidth="1" style="29" min="5" max="5"/>
-    <col width="16" customWidth="1" style="29" min="6" max="6"/>
-    <col width="14" customWidth="1" style="29" min="7" max="7"/>
-    <col width="20" customWidth="1" style="29" min="8" max="8"/>
+    <col width="22" customWidth="1" style="25" min="1" max="1"/>
+    <col width="14" customWidth="1" style="25" min="2" max="2"/>
+    <col width="18" customWidth="1" style="25" min="3" max="3"/>
+    <col width="22" customWidth="1" style="25" min="4" max="4"/>
+    <col width="18" customWidth="1" style="25" min="5" max="5"/>
+    <col width="16" customWidth="1" style="25" min="6" max="6"/>
+    <col width="14" customWidth="1" style="25" min="7" max="7"/>
+    <col width="20" customWidth="1" style="25" min="8" max="8"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="60" t="inlineStr">
+    <row r="1" ht="17.15" customHeight="1" s="26">
+      <c r="A1" s="27" t="inlineStr">
         <is>
           <t>📊 持仓总看板 (2026-06-02)</t>
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="97" t="inlineStr">
+    <row r="2" ht="17.15" customHeight="1" s="26">
+      <c r="A2" s="28" t="inlineStr">
         <is>
           <t>🔴 宏观传导链</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="98" t="inlineStr">
+    <row r="3" ht="15" customHeight="1" s="26">
+      <c r="A3" s="29" t="inlineStr">
         <is>
           <t>【利率】</t>
         </is>
       </c>
-      <c r="C3" s="99" t="inlineStr">
+      <c r="C3" s="30" t="inlineStr">
         <is>
           <t>【地缘】</t>
         </is>
       </c>
-      <c r="D3" s="100" t="inlineStr">
+      <c r="D3" s="31" t="inlineStr">
         <is>
           <t>【经济】</t>
         </is>
       </c>
-      <c r="E3" s="101" t="inlineStr">
+      <c r="E3" s="32" t="inlineStr">
         <is>
           <t>【能源】</t>
         </is>
       </c>
-      <c r="F3" s="102" t="inlineStr">
+      <c r="F3" s="33" t="inlineStr">
         <is>
           <t>【产业】</t>
         </is>
       </c>
-      <c r="G3" s="103" t="inlineStr">
+      <c r="G3" s="34" t="inlineStr">
         <is>
           <t>【避险】</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="104" t="inlineStr">
+    <row r="4" ht="95.5" customHeight="1" s="26">
+      <c r="A4" s="35" t="inlineStr">
         <is>
           <t>2026-06-02 宋鸿兵：沃什就任美联储主席，特朗普施压降息vs独立性博弈；30年美债破5%、10年破4.5%双红线</t>
         </is>
       </c>
-      <c r="D4" s="104" t="inlineStr">
+      <c r="C4" s="27" t="inlineStr">
+        <is>
+          <t>2026-05-29 闭眼看世界 - 俄罗斯对基辅最猛烈袭击</t>
+        </is>
+      </c>
+      <c r="D4" s="35" t="inlineStr">
         <is>
           <t>2026-06-02 付鹏+宋鸿兵：居民部门去杠杆周期确认（08-18加杠杆→现在全面去杠杆）</t>
         </is>
       </c>
-      <c r="E4" s="104" t="inlineStr">
+      <c r="E4" s="35" t="inlineStr">
         <is>
           <t>2026-06-02 宋鸿兵：霍尔木兹封锁3个月，全球有效原油库存仅8.1亿桶，市场误判油价回落</t>
         </is>
       </c>
-      <c r="F4" s="104" t="inlineStr">
+      <c r="F4" s="35" t="inlineStr">
         <is>
           <t>2026-06-02 芯片：蒋宇飞AI基建10年+国产算力长城（升腾+长鑫+deepseek）+玻璃基板5-10年赛道</t>
         </is>
       </c>
-    </row>
-    <row r="5">
-      <c r="D5" s="104" t="inlineStr">
+      <c r="G4" s="27" t="inlineStr">
+        <is>
+          <t>2026-05-28 Peter Schiff · 美债/美元/黄金极端观点（豆包分析版）</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="95.5" customHeight="1" s="26">
+      <c r="A5" s="27" t="inlineStr">
+        <is>
+          <t>2026-05-28 知乎高赞 — 为什么达利欧说「债市是所有市场的支柱」？</t>
+        </is>
+      </c>
+      <c r="C5" s="27" t="inlineStr">
+        <is>
+          <t>2026-05-20 抖音：闭眼看世界 — 日本过境领空地缘风险</t>
+        </is>
+      </c>
+      <c r="D5" s="35" t="inlineStr">
         <is>
           <t>2026-06-02 无知半人：前4月住户贷款狂减4902亿（去杠杆数据确认）</t>
         </is>
       </c>
-      <c r="F5" s="104" t="inlineStr">
+      <c r="E5" s="27" t="inlineStr">
+        <is>
+          <t>2026-05-29 宋鸿兵 - 美国金融市场对油价极其乐观</t>
+        </is>
+      </c>
+      <c r="F5" s="35" t="inlineStr">
         <is>
           <t>🔴【跨博主强信号】养殖：付鹏美国猪周期40年启示+伊娃17/18亏损+行业关注+厄尔尼诺</t>
         </is>
       </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="60" t="inlineStr">
-        <is>
-          <t>2026-05-28 知乎高赞 — 为什么达利欧说「债市是所有市场的支柱」？</t>
-        </is>
-      </c>
-      <c r="C6" s="60" t="inlineStr">
-        <is>
-          <t>2026-05-29 闭眼看世界 - 俄罗斯对基辅最猛烈袭击</t>
-        </is>
-      </c>
-      <c r="D6" s="60" t="inlineStr">
+      <c r="G5" s="27" t="inlineStr">
+        <is>
+          <t>2026-05-27 闭眼看世界（抖音）→ 黄金+2pp</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="48.5" customHeight="1" s="26">
+      <c r="A6" s="27" t="inlineStr">
+        <is>
+          <t>2026-05-22 沃什的政策背景</t>
+        </is>
+      </c>
+      <c r="D6" s="27" t="inlineStr">
         <is>
           <t>2026-05-29 付鹏 - 所有人都在去杠杆的时候就没有人过得好了</t>
         </is>
       </c>
-      <c r="E6" s="60" t="inlineStr">
-        <is>
-          <t>2026-05-29 宋鸿兵 - 美国金融市场对油价极其乐观</t>
-        </is>
-      </c>
-      <c r="F6" s="60" t="inlineStr">
+      <c r="F6" s="27" t="inlineStr">
         <is>
           <t>2026-05-29 蒋宇飞商业 - 用产业思维抓住科技龙头</t>
         </is>
       </c>
-      <c r="G6" s="60" t="inlineStr">
-        <is>
-          <t>2026-05-28 Peter Schiff · 美债/美元/黄金极端观点（豆包分析版）</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="60" t="inlineStr">
-        <is>
-          <t>2026-05-22 沃什的政策背景</t>
-        </is>
-      </c>
-      <c r="C7" s="60" t="inlineStr">
-        <is>
-          <t>2026-05-20 抖音：闭眼看世界 — 日本过境领空地缘风险</t>
-        </is>
-      </c>
-      <c r="D7" s="60" t="inlineStr">
+      <c r="G6" s="27" t="inlineStr">
+        <is>
+          <t>2026-05-27 宋鸿兵（抖音）→ 黄金+1pp</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="64.15000000000001" customHeight="1" s="26">
+      <c r="A7" s="27" t="inlineStr">
+        <is>
+          <t>2026-05-19 宋鸿兵：利率风暴席卷全球，股债双杀只是开始</t>
+        </is>
+      </c>
+      <c r="D7" s="27" t="inlineStr">
         <is>
           <t>2026-05-23 南半球聊财经：宏观经济数据全景</t>
         </is>
       </c>
-      <c r="F7" s="60" t="inlineStr">
+      <c r="F7" s="27" t="inlineStr">
         <is>
           <t>2026-05-29 拿幸·AI启示录 - Claude Code自愈功能</t>
         </is>
       </c>
-      <c r="G7" s="60" t="inlineStr">
-        <is>
-          <t>2026-05-27 闭眼看世界（抖音）→ 黄金+2pp</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="60" t="inlineStr">
-        <is>
-          <t>2026-05-19 宋鸿兵：利率风暴席卷全球，股债双杀只是开始</t>
-        </is>
-      </c>
-      <c r="D8" s="60" t="inlineStr">
+      <c r="G7" s="27" t="inlineStr">
+        <is>
+          <t>2026-05-23 第四梯队：对冲/避险配置 →黄金确定性越高</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="64.15000000000001" customHeight="1" s="26">
+      <c r="A8" s="27" t="inlineStr">
+        <is>
+          <t>2026-05-18 利率风暴的根因 →霍尔木兹海峡封锁→能源价格飙升→通胀预期上升→央行被迫加息</t>
+        </is>
+      </c>
+      <c r="D8" s="27" t="inlineStr">
         <is>
           <t>2026-05-22 宏观层：前4月住户贷款狂减4902亿（无知半人）</t>
         </is>
       </c>
-      <c r="F8" s="60" t="inlineStr">
+      <c r="F8" s="27" t="inlineStr">
         <is>
           <t>2026-05-28 周鸿祎 · "算力决定速度，内存决定高度"</t>
         </is>
       </c>
-      <c r="G8" s="60" t="inlineStr">
-        <is>
-          <t>2026-05-27 宋鸿兵（抖音）→ 黄金+1pp</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="60" t="inlineStr">
-        <is>
-          <t>2026-05-18 利率风暴的根因 →霍尔木兹海峡封锁→能源价格飙升→通胀预期上升→央行被迫加息</t>
-        </is>
-      </c>
-      <c r="D9" s="60" t="inlineStr">
+      <c r="G8" s="27" t="inlineStr">
+        <is>
+          <t>2026-05-23 ⑨ 黄金 ⭐⭐⭐⭐⭐⭐（对冲之王）</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="64.15000000000001" customHeight="1" s="26">
+      <c r="D9" s="27" t="inlineStr">
         <is>
           <t>2026-05-19 古都闲云：4月新增贷款出现历史罕见的负值</t>
         </is>
       </c>
-      <c r="F9" s="60" t="inlineStr">
+      <c r="F9" s="27" t="inlineStr">
         <is>
           <t>2026-05-27 AI处理日志 →黄金+2pp</t>
         </is>
       </c>
-      <c r="G9" s="60" t="inlineStr">
-        <is>
-          <t>2026-05-23 第四梯队：对冲/避险配置 →黄金确定性越高</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="D10" s="60" t="inlineStr">
+      <c r="G9" s="27" t="inlineStr">
+        <is>
+          <t>2026-05-21 新浪：黄金深V反转 +1.67%，但前日暴跌84美元</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="48.5" customHeight="1" s="26">
+      <c r="D10" s="27" t="inlineStr">
         <is>
           <t>2026-05-19 古都闲云：中国4月社会消费品零售总额同比+0.2%</t>
         </is>
       </c>
-      <c r="F10" s="60" t="inlineStr">
+      <c r="F10" s="27" t="inlineStr">
         <is>
           <t>2026-05-27 蒋宇飞（抖音）→ 芯片0pp</t>
         </is>
       </c>
-      <c r="G10" s="60" t="inlineStr">
-        <is>
-          <t>2026-05-23 ⑨ 黄金 ⭐⭐⭐⭐⭐⭐（对冲之王）</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="F11" s="60" t="inlineStr">
+    </row>
+    <row r="11" ht="48.5" customHeight="1" s="26">
+      <c r="F11" s="27" t="inlineStr">
         <is>
           <t>2026-05-27 付鹏（抖音）→ 芯片0pp</t>
         </is>
       </c>
-      <c r="G11" s="60" t="inlineStr">
-        <is>
-          <t>2026-05-21 新浪：黄金深V反转 +1.67%，但前日暴跌84美元</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="105" t="inlineStr">
+    </row>
+    <row r="12" ht="17.15" customHeight="1" s="26">
+      <c r="A12" s="36" t="inlineStr">
         <is>
           <t>🔥 叙事主线（三条）</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="B13" s="106" t="inlineStr">
+    <row r="13" ht="15" customHeight="1" s="26">
+      <c r="B13" s="37" t="inlineStr">
         <is>
           <t>①美国走钢丝：国债39万亿+30年美债破5%+10年破4.5%，沃什上任但市场用脚投票，利率只涨不跌</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="B14" s="106" t="inlineStr">
+    <row r="14" ht="15" customHeight="1" s="26">
+      <c r="B14" s="37" t="inlineStr">
         <is>
           <t>②霍尔木兹封3个月：有效原油库存8.1亿桶，OECD最早6月触底，85%投资者押注回落=集体幻觉</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="B15" s="106" t="inlineStr">
+    <row r="15" ht="15" customHeight="1" s="26">
+      <c r="B15" s="37" t="inlineStr">
         <is>
           <t>③中国去杠杆但分化：08-18加杠杆→全面去杠杆，对猪周期是加速器，对AI是倒逼器</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="97" t="inlineStr">
+    <row r="17" ht="17.15" customHeight="1" s="26">
+      <c r="A17" s="28" t="inlineStr">
         <is>
           <t>🟡 中观产业传导</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="60" t="inlineStr">
+    <row r="18" ht="17.15" customHeight="1" s="26">
+      <c r="A18" s="27" t="inlineStr">
         <is>
           <t>AI硬件确定性(付鹏) → 内存=AI核心瓶颈(4信源互锁) → 国产替代加速 → 稀土断供日本 → 芯片/存储/HBM长期利好 | 短期被利率↑/地缘↑压制</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="60" t="inlineStr">
+    <row r="19" ht="17.15" customHeight="1" s="26">
+      <c r="A19" s="27" t="inlineStr">
         <is>
           <t>⚡ 传导: 利率↑→成长股↓ | 地缘↑→避险↑能源↑ | 去杠杆→消费↓养殖↓ | AI产业↑→芯片/存储↑(长期)</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="60" t="inlineStr">
+    <row r="20" ht="48.5" customHeight="1" s="26">
+      <c r="A20" s="27" t="inlineStr">
         <is>
           <t>2026-05-30 但斌：沃什缩表受阻+沃勒鹰派，降息预期降温</t>
         </is>
       </c>
-      <c r="C20" s="60" t="inlineStr">
+      <c r="C20" s="27" t="inlineStr">
         <is>
           <t>2026-05-30 宋鸿兵：伊朗3.0反击或封锁海峡</t>
         </is>
       </c>
-      <c r="D20" s="60" t="inlineStr">
+      <c r="D20" s="27" t="inlineStr">
         <is>
           <t>2026-05-30 付鹏：去杠杆周期中登最难受</t>
         </is>
       </c>
-      <c r="E20" s="60" t="inlineStr">
+      <c r="E20" s="27" t="inlineStr">
         <is>
           <t>2026-05-30 宋鸿兵：海峡封锁→能源成本飙升</t>
         </is>
       </c>
-      <c r="F20" s="60" t="inlineStr">
+      <c r="F20" s="27" t="inlineStr">
         <is>
           <t>2026-05-30 岩松：存储1-2年产能饱和</t>
         </is>
       </c>
-      <c r="G20" s="60" t="inlineStr">
+      <c r="G20" s="27" t="inlineStr">
         <is>
           <t>2026-05-30 宋鸿兵：30年美债破5%双红线</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="97" t="inlineStr">
+    <row r="22" ht="17.15" customHeight="1" s="26">
+      <c r="A22" s="28" t="inlineStr">
         <is>
           <t>🔔 待重仓监控</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="107" t="inlineStr">
+    <row r="23" ht="17.15" customHeight="1" s="26">
+      <c r="A23" s="38" t="inlineStr">
         <is>
           <t>标的</t>
         </is>
       </c>
-      <c r="B23" s="107" t="inlineStr">
+      <c r="B23" s="38" t="inlineStr">
         <is>
           <t>状态</t>
         </is>
       </c>
-      <c r="C23" s="107" t="inlineStr">
+      <c r="C23" s="38" t="inlineStr">
         <is>
           <t>当前P/价格</t>
         </is>
       </c>
-      <c r="D23" s="107" t="inlineStr">
+      <c r="D23" s="38" t="inlineStr">
         <is>
           <t>最新信号</t>
         </is>
       </c>
-      <c r="E23" s="107" t="inlineStr">
+      <c r="E23" s="38" t="inlineStr">
         <is>
           <t>触发条件</t>
         </is>
       </c>
-      <c r="F23" s="107" t="inlineStr">
+      <c r="F23" s="38" t="inlineStr">
         <is>
           <t>距离触发</t>
         </is>
       </c>
-      <c r="G23" s="107" t="inlineStr">
+      <c r="G23" s="38" t="inlineStr">
         <is>
           <t>跟踪日期</t>
         </is>
       </c>
-      <c r="H23" s="107" t="inlineStr">
+      <c r="H23" s="38" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="28" t="inlineStr">
+    <row r="24" ht="17.15" customHeight="1" s="26">
+      <c r="A24" s="25" t="inlineStr">
         <is>
           <t>玻璃基板</t>
         </is>
       </c>
-      <c r="B24" s="28" t="inlineStr">
+      <c r="B24" s="25" t="inlineStr">
         <is>
           <t>深南电路002916/兴森科技002436</t>
         </is>
       </c>
-      <c r="C24" s="28" t="inlineStr">
+      <c r="C24" s="25" t="inlineStr">
         <is>
           <t>观察中</t>
         </is>
       </c>
-      <c r="D24" s="28" t="inlineStr">
+      <c r="D24" s="25" t="inlineStr">
         <is>
           <t>蒋宇飞：玻璃基板大规模应用2028年，5-10年赛道</t>
         </is>
       </c>
-      <c r="E24" s="28" t="inlineStr">
+      <c r="E24" s="25" t="inlineStr">
         <is>
           <t>AI基建+国产替代加速</t>
         </is>
       </c>
-      <c r="F24" s="28" t="inlineStr">
+      <c r="F24" s="25" t="inlineStr">
         <is>
           <t>中长期</t>
         </is>
       </c>
-      <c r="G24" s="28" t="inlineStr">
+      <c r="G24" s="25" t="inlineStr">
         <is>
           <t>2026-06-02</t>
         </is>
       </c>
-      <c r="H24" s="28" t="inlineStr">
+      <c r="H24" s="25" t="inlineStr">
         <is>
           <t>芯片ETF已覆盖，个股可关注</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="28" t="inlineStr">
+    <row r="25" ht="17.15" customHeight="1" s="26">
+      <c r="A25" s="25" t="inlineStr">
         <is>
           <t>油气对冲</t>
         </is>
       </c>
-      <c r="B25" s="28" t="inlineStr">
+      <c r="B25" s="25" t="inlineStr">
         <is>
           <t>华宝油气162411</t>
         </is>
       </c>
-      <c r="C25" s="28" t="inlineStr">
+      <c r="C25" s="25" t="inlineStr">
         <is>
           <t>观察中</t>
         </is>
       </c>
-      <c r="D25" s="28" t="inlineStr">
+      <c r="D25" s="25" t="inlineStr">
         <is>
           <t>宋鸿兵：霍尔木兹封锁3个月，85%投资者押注回落=幻觉</t>
         </is>
       </c>
-      <c r="E25" s="28" t="inlineStr">
+      <c r="E25" s="25" t="inlineStr">
         <is>
           <t>油价冲150或海峡持续封锁</t>
         </is>
       </c>
-      <c r="F25" s="28" t="inlineStr">
+      <c r="F25" s="25" t="inlineStr">
         <is>
           <t>短期</t>
         </is>
       </c>
-      <c r="G25" s="28" t="inlineStr">
+      <c r="G25" s="25" t="inlineStr">
         <is>
           <t>2026-06-02</t>
         </is>
       </c>
-      <c r="H25" s="28" t="inlineStr">
+      <c r="H25" s="25" t="inlineStr">
         <is>
           <t>小仓位试水，不对称博弈</t>
         </is>
@@ -1481,7 +1199,9 @@
     <mergeCell ref="A22:H22"/>
     <mergeCell ref="A17:H17"/>
   </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
@@ -1493,147 +1213,140 @@
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
   <dimension ref="A1:H12"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="10.4921875" defaultRowHeight="12.8" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="10.4921875" defaultRowHeight="12.75" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
-    <col width="32" customWidth="1" style="28" min="1" max="7"/>
-    <col width="32" customWidth="1" style="29" min="2" max="2"/>
-    <col width="32" customWidth="1" style="29" min="3" max="3"/>
-    <col width="32" customWidth="1" style="29" min="4" max="4"/>
-    <col width="32" customWidth="1" style="29" min="5" max="5"/>
-    <col width="32" customWidth="1" style="29" min="6" max="6"/>
-    <col width="32" customWidth="1" style="29" min="7" max="7"/>
-    <col width="32" customWidth="1" style="28" min="8" max="8"/>
+    <col width="32" customWidth="1" style="25" min="1" max="8"/>
   </cols>
   <sheetData>
-    <row r="1" ht="14.15" customHeight="1" s="29">
-      <c r="A1" s="52" t="inlineStr">
+    <row r="1" ht="13.5" customHeight="1" s="26">
+      <c r="A1" s="39" t="inlineStr">
         <is>
           <t>📈 持仓贝叶斯完整记录 (8只横排)</t>
         </is>
       </c>
-      <c r="B1" s="31" t="n"/>
-      <c r="C1" s="31" t="n"/>
-      <c r="D1" s="31" t="n"/>
-      <c r="E1" s="31" t="n"/>
-      <c r="F1" s="31" t="n"/>
-      <c r="G1" s="31" t="n"/>
-      <c r="H1" s="32" t="n"/>
-    </row>
-    <row r="2" ht="26.85" customHeight="1" s="29">
-      <c r="A2" s="52" t="inlineStr">
+      <c r="B1" s="40" t="n"/>
+      <c r="C1" s="40" t="n"/>
+      <c r="D1" s="40" t="n"/>
+      <c r="E1" s="40" t="n"/>
+      <c r="F1" s="40" t="n"/>
+      <c r="G1" s="40" t="n"/>
+      <c r="H1" s="41" t="n"/>
+    </row>
+    <row r="2" ht="26.25" customHeight="1" s="26">
+      <c r="A2" s="39" t="inlineStr">
         <is>
           <t>芯片020628
 [右侧]</t>
         </is>
       </c>
-      <c r="B2" s="52" t="inlineStr">
+      <c r="B2" s="39" t="inlineStr">
         <is>
           <t>电池018926
 [右侧]</t>
         </is>
       </c>
-      <c r="C2" s="52" t="inlineStr">
+      <c r="C2" s="39" t="inlineStr">
         <is>
           <t>恒科012349
 [等右]</t>
         </is>
       </c>
-      <c r="D2" s="52" t="inlineStr">
+      <c r="D2" s="39" t="inlineStr">
         <is>
           <t>养殖014415
 [左侧]</t>
         </is>
       </c>
-      <c r="E2" s="52" t="inlineStr">
+      <c r="E2" s="39" t="inlineStr">
         <is>
           <t>有色004433
 [周期]</t>
         </is>
       </c>
-      <c r="F2" s="52" t="inlineStr">
+      <c r="F2" s="39" t="inlineStr">
         <is>
           <t>稀金014111
 [战略]</t>
         </is>
       </c>
-      <c r="G2" s="52" t="inlineStr">
+      <c r="G2" s="39" t="inlineStr">
         <is>
           <t>银行001595
 [监控]</t>
         </is>
       </c>
-      <c r="H2" s="52" t="inlineStr">
+      <c r="H2" s="39" t="inlineStr">
         <is>
           <t>AI027048
 [蚊子]</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="73.09999999999999" customHeight="1" s="29">
-      <c r="A3" s="53" t="inlineStr">
+    <row r="3" ht="72.75" customHeight="1" s="26">
+      <c r="A3" s="42" t="inlineStr">
         <is>
           <t>成本¥3695
 净值3.6875
-P:59%
+P:43%
 利率折价-6pp
-有效P:57%</t>
-        </is>
-      </c>
-      <c r="B3" s="53" t="inlineStr">
+有效P:37%</t>
+        </is>
+      </c>
+      <c r="B3" s="42" t="inlineStr">
         <is>
           <t>成本¥6811
 净值1.8418
-P:76%
+P:67%
 利率折价-6pp
-有效P:74%</t>
-        </is>
-      </c>
-      <c r="C3" s="53" t="inlineStr">
+有效P:61%</t>
+        </is>
+      </c>
+      <c r="C3" s="42" t="inlineStr">
         <is>
           <t>成本¥4722
 净值0.6619
-P:43%
+P:38%
 利率折价-6pp
-有效P:43%</t>
-        </is>
-      </c>
-      <c r="D3" s="53" t="inlineStr">
+有效P:32%</t>
+        </is>
+      </c>
+      <c r="D3" s="42" t="inlineStr">
         <is>
           <t>成本¥3732
 净值0.7545
-P:49%
+P:60%
 利率折价0pp
-有效P:49%</t>
-        </is>
-      </c>
-      <c r="E3" s="53" t="inlineStr">
+有效P:60%</t>
+        </is>
+      </c>
+      <c r="E3" s="42" t="inlineStr">
         <is>
           <t>成本¥4800
 净值1.8985
-P:53%
-利率折价-2pp
-有效P:53%</t>
-        </is>
-      </c>
-      <c r="F3" s="53" t="inlineStr">
+P:44%
+利率折价-4pp
+有效P:40%</t>
+        </is>
+      </c>
+      <c r="F3" s="42" t="inlineStr">
         <is>
           <t>成本¥5622
 净值1.089
-P:50%
-利率折价-2pp
-有效P:50%</t>
-        </is>
-      </c>
-      <c r="G3" s="53" t="inlineStr">
+P:43%
+利率折价-4pp
+有效P:39%</t>
+        </is>
+      </c>
+      <c r="G3" s="42" t="inlineStr">
         <is>
           <t>成本¥0
 净值1.6291
-P:52%
+P:48%
 利率折价0pp
-有效P:52%</t>
-        </is>
-      </c>
-      <c r="H3" s="53" t="inlineStr">
+有效P:48%</t>
+        </is>
+      </c>
+      <c r="H3" s="42" t="inlineStr">
         <is>
           <t>成本¥101
 净值1.1274
@@ -1643,78 +1356,78 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="12.8" customHeight="1" s="29">
-      <c r="A4" s="54" t="inlineStr">
+    <row r="4" ht="12.75" customHeight="1" s="26">
+      <c r="A4" s="43" t="inlineStr">
         <is>
           <t>日期/P/事件</t>
         </is>
       </c>
-      <c r="B4" s="54" t="inlineStr">
+      <c r="B4" s="43" t="inlineStr">
         <is>
           <t>日期/P/事件</t>
         </is>
       </c>
-      <c r="C4" s="54" t="inlineStr">
+      <c r="C4" s="43" t="inlineStr">
         <is>
           <t>日期/P/事件</t>
         </is>
       </c>
-      <c r="D4" s="54" t="inlineStr">
+      <c r="D4" s="43" t="inlineStr">
         <is>
           <t>日期/P/事件</t>
         </is>
       </c>
-      <c r="E4" s="54" t="inlineStr">
+      <c r="E4" s="43" t="inlineStr">
         <is>
           <t>日期/P/事件</t>
         </is>
       </c>
-      <c r="F4" s="54" t="inlineStr">
+      <c r="F4" s="43" t="inlineStr">
         <is>
           <t>日期/P/事件</t>
         </is>
       </c>
-      <c r="G4" s="54" t="inlineStr">
+      <c r="G4" s="43" t="inlineStr">
         <is>
           <t>日期/P/事件</t>
         </is>
       </c>
-      <c r="H4" s="54" t="inlineStr">
+      <c r="H4" s="43" t="inlineStr">
         <is>
           <t>日期/P/事件</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="45" customHeight="1" s="29">
-      <c r="A5" s="96" t="inlineStr">
+    <row r="5" ht="45" customHeight="1" s="26">
+      <c r="A5" s="44" t="inlineStr">
         <is>
           <t>2026-06-02
 +2pp
 蒋宇飞AI基建10年+国产算力长城</t>
         </is>
       </c>
-      <c r="B5" s="96" t="inlineStr">
+      <c r="B5" s="44" t="inlineStr">
         <is>
           <t>2026-06-02
 +2pp
 维力能储能全球第二+锂电全链</t>
         </is>
       </c>
-      <c r="C5" s="96" t="inlineStr">
+      <c r="C5" s="44" t="inlineStr">
         <is>
           <t>2026-06-02
 -3pp
 付鹏恒科套利闭环不可持续</t>
         </is>
       </c>
-      <c r="D5" s="96" t="inlineStr">
+      <c r="D5" s="44" t="inlineStr">
         <is>
           <t>2026-06-02
 +4pp
 🔴跨博主：美国猪周期启示+17/18亏损+行业关注+厄尔尼诺</t>
         </is>
       </c>
-      <c r="G5" s="96" t="inlineStr">
+      <c r="G5" s="44" t="inlineStr">
         <is>
           <t>2026-06-02
 -2pp
@@ -1722,262 +1435,262 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="45" customHeight="1" s="29">
-      <c r="A6" s="63" t="inlineStr">
+    <row r="6" ht="45" customHeight="1" s="26">
+      <c r="A6" s="45" t="inlineStr">
         <is>
           <t>2026-05-28
 +1pp
 Schiff美债熊市 + 周鸿祎"内存决定高度"</t>
         </is>
       </c>
-      <c r="B6" s="64" t="inlineStr">
+      <c r="B6" s="46" t="inlineStr">
         <is>
           <t>2026-05-21
 +0pp
 中科院固态锂电池突破（逻辑簇强化，不作概率调整）</t>
         </is>
       </c>
-      <c r="C6" s="65" t="inlineStr">
+      <c r="C6" s="47" t="inlineStr">
         <is>
           <t>2026-05-26
 -4pp
 恒生三巨头财报验证：非价值陷阱确认</t>
         </is>
       </c>
-      <c r="D6" s="63" t="inlineStr">
+      <c r="D6" s="45" t="inlineStr">
         <is>
           <t>2026-05-26
 +5pp
 ✅ 伊娃读财报18期：17/18猪企亏损，加速去产能确认</t>
         </is>
       </c>
-      <c r="E6" s="63" t="inlineStr">
+      <c r="E6" s="45" t="inlineStr">
         <is>
           <t>2026-05-22
 +4pp
 有色金属+3.63%：AI铜需求爆发 + 资金回流</t>
         </is>
       </c>
-      <c r="F6" s="63" t="inlineStr">
+      <c r="F6" s="45" t="inlineStr">
         <is>
           <t>2026-05-29
 +1pp
 闭眼看世界：俄乌升级→地缘风险溢价</t>
         </is>
       </c>
-      <c r="G6" s="65" t="inlineStr">
+      <c r="G6" s="47" t="inlineStr">
         <is>
           <t>2026-05-22
 -3pp
 无知半人：前4月住户贷款狂减4902亿</t>
         </is>
       </c>
-      <c r="H6" s="57" t="n"/>
-    </row>
-    <row r="7" ht="45" customHeight="1" s="29">
-      <c r="A7" s="66" t="inlineStr">
+      <c r="H6" s="48" t="n"/>
+    </row>
+    <row r="7" ht="45" customHeight="1" s="26">
+      <c r="A7" s="49" t="inlineStr">
         <is>
           <t>2026-05-27
 -2pp
 🔥 闭眼看世界：美军轰炸伊朗→霍尔木兹P'作废</t>
         </is>
       </c>
-      <c r="B7" s="67" t="inlineStr">
+      <c r="B7" s="50" t="inlineStr">
         <is>
           <t>2026-05-20
 +1pp
 光储旺季+美债压制</t>
         </is>
       </c>
-      <c r="C7" s="66" t="inlineStr">
+      <c r="C7" s="49" t="inlineStr">
         <is>
           <t>2026-05-20
 -3pp
 多空交织：低开高走验证磨底 + 美债5.18%压制</t>
         </is>
       </c>
-      <c r="D7" s="67" t="inlineStr">
+      <c r="D7" s="50" t="inlineStr">
         <is>
           <t>2026-05-24
 +5pp
 霍尔木兹通航（+4pp 未入链修正）</t>
         </is>
       </c>
-      <c r="E7" s="66" t="inlineStr">
+      <c r="E7" s="49" t="inlineStr">
         <is>
           <t>2026-05-19
 -2pp
 🔴 岩松笔记 + 🟢 付鹏对冲：逻辑分类修正</t>
         </is>
       </c>
-      <c r="F7" s="66" t="inlineStr">
+      <c r="F7" s="49" t="inlineStr">
         <is>
           <t>2026-05-20
 -3pp
 有色金属持续走弱+美债压制</t>
         </is>
       </c>
-      <c r="G7" s="67" t="inlineStr">
+      <c r="G7" s="50" t="inlineStr">
         <is>
           <t>2026-05-22
 +3pp
 追加：凯文·沃什就任美联储主席</t>
         </is>
       </c>
-      <c r="H7" s="57" t="n"/>
-    </row>
-    <row r="8" ht="45" customHeight="1" s="29">
-      <c r="A8" s="63" t="inlineStr">
+      <c r="H7" s="48" t="n"/>
+    </row>
+    <row r="8" ht="45" customHeight="1" s="26">
+      <c r="A8" s="45" t="inlineStr">
         <is>
           <t>2026-05-25
 +1pp
 蒋宇飞：深度拆解玻璃基板的万亿机遇</t>
         </is>
       </c>
-      <c r="B8" s="63" t="inlineStr">
+      <c r="B8" s="45" t="inlineStr">
         <is>
           <t>2026-05-19
 +5pp
 碳酸锂跌价+巴克莱看多</t>
         </is>
       </c>
-      <c r="C8" s="65" t="inlineStr">
+      <c r="C8" s="47" t="inlineStr">
         <is>
           <t>2026-05-19
 -2pp
 付鹏×2：港股结构性偏弱 + 风险偏好极值 + 古都闲云社消疲弱</t>
         </is>
       </c>
-      <c r="D8" s="65" t="inlineStr">
+      <c r="D8" s="47" t="inlineStr">
         <is>
           <t>2026-05-22
 -2pp
 无知半人：住户贷款狂减4902亿</t>
         </is>
       </c>
-      <c r="E8" s="65" t="inlineStr">
+      <c r="E8" s="47" t="inlineStr">
         <is>
           <t>2026-05-15
 -8pp
 →05-20 有色金属板块持续资金净流出</t>
         </is>
       </c>
-      <c r="F8" s="65" t="inlineStr">
+      <c r="F8" s="47" t="inlineStr">
         <is>
           <t>2026-05-19
 -5pp
 🔴 岩松笔记：资源非长期抗通胀→HALO联动风险</t>
         </is>
       </c>
-      <c r="G8" s="57" t="n"/>
-      <c r="H8" s="57" t="n"/>
-    </row>
-    <row r="9" ht="45" customHeight="1" s="29">
-      <c r="A9" s="66" t="inlineStr">
+      <c r="G8" s="48" t="n"/>
+      <c r="H8" s="48" t="n"/>
+    </row>
+    <row r="9" ht="45" customHeight="1" s="26">
+      <c r="A9" s="49" t="inlineStr">
         <is>
           <t>2026-05-22
 -3pp
 宋鸿兵利率风暴（但斌预警已删除：券商观点不计）</t>
         </is>
       </c>
-      <c r="B9" s="67" t="inlineStr">
+      <c r="B9" s="50" t="inlineStr">
         <is>
           <t>2026-05-15
 +1pp
 机构研报确认景气上行</t>
         </is>
       </c>
-      <c r="C9" s="57" t="n"/>
-      <c r="D9" s="66" t="inlineStr">
+      <c r="C9" s="48" t="n"/>
+      <c r="D9" s="49" t="inlineStr">
         <is>
           <t>2026-05-19
 -2pp
 古都闲云：社消数据疲弱</t>
         </is>
       </c>
-      <c r="E9" s="57" t="n"/>
-      <c r="F9" s="57" t="n"/>
-      <c r="G9" s="57" t="n"/>
-      <c r="H9" s="57" t="n"/>
-    </row>
-    <row r="10" ht="45" customHeight="1" s="29">
-      <c r="A10" s="65" t="inlineStr">
+      <c r="E9" s="48" t="n"/>
+      <c r="F9" s="48" t="n"/>
+      <c r="G9" s="48" t="n"/>
+      <c r="H9" s="48" t="n"/>
+    </row>
+    <row r="10" ht="45" customHeight="1" s="26">
+      <c r="A10" s="47" t="inlineStr">
         <is>
           <t>2026-05-22
 -6pp
 凯文·沃什就任美联储主席</t>
         </is>
       </c>
-      <c r="B10" s="63" t="inlineStr">
+      <c r="B10" s="45" t="inlineStr">
         <is>
           <t>2026-05-14
 +3pp
 电池ETF涨2.73%+多重利好</t>
         </is>
       </c>
-      <c r="C10" s="57" t="n"/>
-      <c r="D10" s="57" t="n"/>
-      <c r="E10" s="57" t="n"/>
-      <c r="F10" s="57" t="n"/>
-      <c r="G10" s="57" t="n"/>
-      <c r="H10" s="57" t="n"/>
-    </row>
-    <row r="11" ht="45" customHeight="1" s="29">
-      <c r="A11" s="66" t="inlineStr">
+      <c r="C10" s="48" t="n"/>
+      <c r="D10" s="48" t="n"/>
+      <c r="E10" s="48" t="n"/>
+      <c r="F10" s="48" t="n"/>
+      <c r="G10" s="48" t="n"/>
+      <c r="H10" s="48" t="n"/>
+    </row>
+    <row r="11" ht="45" customHeight="1" s="26">
+      <c r="A11" s="49" t="inlineStr">
         <is>
           <t>2026-05-19
 -2pp
 韩国闪崩（情绪叠加）</t>
         </is>
       </c>
-      <c r="B11" s="67" t="inlineStr">
+      <c r="B11" s="50" t="inlineStr">
         <is>
           <t>2026-05-13
 +5pp
 特朗普访华+恩捷40亿扩产</t>
         </is>
       </c>
-      <c r="C11" s="57" t="n"/>
-      <c r="D11" s="57" t="n"/>
-      <c r="E11" s="57" t="n"/>
-      <c r="F11" s="57" t="n"/>
-      <c r="G11" s="57" t="n"/>
-      <c r="H11" s="57" t="n"/>
-    </row>
-    <row r="12" ht="45" customHeight="1" s="29">
-      <c r="A12" s="63" t="inlineStr">
+      <c r="C11" s="48" t="n"/>
+      <c r="D11" s="48" t="n"/>
+      <c r="E11" s="48" t="n"/>
+      <c r="F11" s="48" t="n"/>
+      <c r="G11" s="48" t="n"/>
+      <c r="H11" s="48" t="n"/>
+    </row>
+    <row r="12" ht="45" customHeight="1" s="26">
+      <c r="A12" s="45" t="inlineStr">
         <is>
           <t>2026-05-16
 +2pp
 付鹏：存储=AI基建（观点→共识信号）</t>
         </is>
       </c>
-      <c r="B12" s="57" t="n"/>
-      <c r="C12" s="57" t="n"/>
-      <c r="D12" s="57" t="n"/>
-      <c r="E12" s="57" t="n"/>
-      <c r="F12" s="57" t="n"/>
-      <c r="G12" s="57" t="n"/>
-      <c r="H12" s="57" t="n"/>
-    </row>
-    <row r="13" ht="13.8" customHeight="1" s="29"/>
-    <row r="14" ht="13.8" customHeight="1" s="29"/>
-    <row r="15" ht="13.8" customHeight="1" s="29"/>
-    <row r="16" ht="13.8" customHeight="1" s="29"/>
-    <row r="17" ht="13.8" customHeight="1" s="29"/>
-    <row r="18" ht="13.8" customHeight="1" s="29"/>
-    <row r="19" ht="13.8" customHeight="1" s="29"/>
-    <row r="20" ht="13.8" customHeight="1" s="29"/>
-    <row r="21" ht="13.8" customHeight="1" s="29"/>
-    <row r="22" ht="13.8" customHeight="1" s="29"/>
-    <row r="23" ht="13.8" customHeight="1" s="29"/>
-    <row r="24" ht="13.8" customHeight="1" s="29"/>
-    <row r="25" ht="13.8" customHeight="1" s="29"/>
-    <row r="26" ht="13.8" customHeight="1" s="29"/>
-    <row r="27" ht="13.8" customHeight="1" s="29"/>
-    <row r="28" ht="13.8" customHeight="1" s="29"/>
-    <row r="29" ht="13.8" customHeight="1" s="29"/>
-    <row r="30" ht="13.8" customHeight="1" s="29"/>
+      <c r="B12" s="48" t="n"/>
+      <c r="C12" s="48" t="n"/>
+      <c r="D12" s="48" t="n"/>
+      <c r="E12" s="48" t="n"/>
+      <c r="F12" s="48" t="n"/>
+      <c r="G12" s="48" t="n"/>
+      <c r="H12" s="48" t="n"/>
+    </row>
+    <row r="13" ht="13.5" customHeight="1" s="26"/>
+    <row r="14" ht="13.5" customHeight="1" s="26"/>
+    <row r="15" ht="13.5" customHeight="1" s="26"/>
+    <row r="16" ht="13.5" customHeight="1" s="26"/>
+    <row r="17" ht="13.5" customHeight="1" s="26"/>
+    <row r="18" ht="13.5" customHeight="1" s="26"/>
+    <row r="19" ht="13.5" customHeight="1" s="26"/>
+    <row r="20" ht="13.5" customHeight="1" s="26"/>
+    <row r="21" ht="13.5" customHeight="1" s="26"/>
+    <row r="22" ht="13.5" customHeight="1" s="26"/>
+    <row r="23" ht="13.5" customHeight="1" s="26"/>
+    <row r="24" ht="13.5" customHeight="1" s="26"/>
+    <row r="25" ht="13.5" customHeight="1" s="26"/>
+    <row r="26" ht="13.5" customHeight="1" s="26"/>
+    <row r="27" ht="13.5" customHeight="1" s="26"/>
+    <row r="28" ht="13.5" customHeight="1" s="26"/>
+    <row r="29" ht="13.5" customHeight="1" s="26"/>
+    <row r="30" ht="13.5" customHeight="1" s="26"/>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:H1"/>

--- a/持仓贝叶斯跟踪.xlsx
+++ b/持仓贝叶斯跟踪.xlsx
@@ -18,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="14">
+  <fonts count="16">
     <font>
       <name val="Calibri"/>
       <charset val="1"/>
@@ -112,8 +112,15 @@
       <color rgb="FF00B050"/>
       <sz val="8"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FF6600"/>
+    </font>
+    <font>
+      <color rgb="00999999"/>
+    </font>
   </fonts>
-  <fills count="12">
+  <fills count="14">
     <fill>
       <patternFill/>
     </fill>
@@ -180,6 +187,18 @@
         <bgColor rgb="FFFFF2FF"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFD700"/>
+        <bgColor rgb="00FFD700"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E0E0E0"/>
+        <bgColor rgb="00E0E0E0"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="6">
     <border>
@@ -235,7 +254,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="51">
+  <cellXfs count="54">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -381,6 +400,15 @@
       <alignment horizontal="general" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="12" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -531,8 +559,8 @@
   <commentList>
     <comment ref="A5" authorId="0" shapeId="0">
       <text>
-        <t>【芯片+2pp】
-蒋宇飞8个视频：AI基建10年+国产算力长城（升腾+长鑫+deepseek）+玻璃基板5-10年赛道</t>
+        <t>【虚P标注】
+蒋宇飞观点：AI基建时代持续10年是个人判断，非已发生事实。国产算力长城也是预期而非现实。</t>
       </text>
     </comment>
     <comment ref="B5" authorId="0" shapeId="0">
@@ -549,17 +577,31 @@
     </comment>
     <comment ref="D5" authorId="0" shapeId="0">
       <text>
-        <t>【养殖+4pp 🔴跨博主】
-信源1-付鹏：美国猪周期40年启示
-信源2-伊娃：17/18猪企亏损
-信源3-行业：生猪贸易被关注
-信源4-自然：厄尔尼诺加速散户退出</t>
+        <t>【虚P标注】
+【虚P分析】
+信源1-付鹏"美国猪周期40年启示"=观点类比，非中国已发生事实
+信源2-伊娃17/18亏损=事实（财报数据）
+信源3-行业关注=事实
+信源4-厄尔尼诺=事实
+结论：4个信源中2个是事实2个是观点。建议主P只加事实部分+2pp，观点部分进虚P+2pp</t>
       </text>
     </comment>
     <comment ref="G5" authorId="0" shapeId="0">
       <text>
-        <t>【银行-2pp】
-付鹏+宋鸿兵：居民去杠杆确认，08-18加杠杆→全面去杠杆，住户贷款狂减4902亿</t>
+        <t>【虚P标注】
+付鹏+宋鸿兵观点：居民去杠杆周期是宏观判断。虽然数据支持（住户贷款-4902亿），但"对银行不利"是推论而非事实。银行板块实际盘面42只全线飘红，与观点矛盾。</t>
+      </text>
+    </comment>
+    <comment ref="A7" authorId="0" shapeId="0">
+      <text>
+        <t>【P'作废】
+霍尔木兹P'已作废：美军轰炸伊朗后海峡通航，预测未兑现</t>
+      </text>
+    </comment>
+    <comment ref="A12" authorId="0" shapeId="0">
+      <text>
+        <t>【虚P标注】
+付鹏观点：存储=AI基建是逻辑推演，非价格/数据确认</t>
       </text>
     </comment>
   </commentList>
@@ -1287,9 +1329,10 @@
         <is>
           <t>成本¥3695
 净值3.6875
-P:43%
+P:41%
+虚P+4pp
 利率折价-6pp
-有效P:37%</t>
+有效P:35%</t>
         </is>
       </c>
       <c r="B3" s="42" t="inlineStr">
@@ -1297,6 +1340,7 @@
           <t>成本¥6811
 净值1.8418
 P:67%
+虚P无
 利率折价-6pp
 有效P:61%</t>
         </is>
@@ -1306,6 +1350,7 @@
           <t>成本¥4722
 净值0.6619
 P:38%
+虚P无
 利率折价-6pp
 有效P:32%</t>
         </is>
@@ -1314,9 +1359,10 @@
         <is>
           <t>成本¥3732
 净值0.7545
-P:60%
+P:56%
+虚P+4pp
 利率折价0pp
-有效P:60%</t>
+有效P:56%</t>
         </is>
       </c>
       <c r="E3" s="42" t="inlineStr">
@@ -1324,6 +1370,7 @@
           <t>成本¥4800
 净值1.8985
 P:44%
+虚P无
 利率折价-4pp
 有效P:40%</t>
         </is>
@@ -1333,6 +1380,7 @@
           <t>成本¥5622
 净值1.089
 P:43%
+虚P无
 利率折价-4pp
 有效P:39%</t>
         </is>
@@ -1341,9 +1389,10 @@
         <is>
           <t>成本¥0
 净值1.6291
-P:48%
+P:50%
+虚P-2pp
 利率折价0pp
-有效P:48%</t>
+有效P:50%</t>
         </is>
       </c>
       <c r="H3" s="42" t="inlineStr">
@@ -1399,11 +1448,11 @@
       </c>
     </row>
     <row r="5" ht="45" customHeight="1" s="26">
-      <c r="A5" s="44" t="inlineStr">
+      <c r="A5" s="51" t="inlineStr">
         <is>
           <t>2026-06-02
 +2pp
-蒋宇飞AI基建10年+国产算力长城</t>
+【虚P】蒋宇飞AI基建10年+国产算力长城</t>
         </is>
       </c>
       <c r="B5" s="44" t="inlineStr">
@@ -1420,18 +1469,18 @@
 付鹏恒科套利闭环不可持续</t>
         </is>
       </c>
-      <c r="D5" s="44" t="inlineStr">
+      <c r="D5" s="51" t="inlineStr">
         <is>
           <t>2026-06-02
 +4pp
-🔴跨博主：美国猪周期启示+17/18亏损+行业关注+厄尔尼诺</t>
-        </is>
-      </c>
-      <c r="G5" s="44" t="inlineStr">
+【虚P】🔴跨博主：美国猪周期启示+17/18亏损+行业关注+厄尔尼诺</t>
+        </is>
+      </c>
+      <c r="G5" s="51" t="inlineStr">
         <is>
           <t>2026-06-02
 -2pp
-去杠杆周期不利</t>
+【虚P】去杠杆周期不利</t>
         </is>
       </c>
     </row>
@@ -1488,11 +1537,11 @@
       <c r="H6" s="48" t="n"/>
     </row>
     <row r="7" ht="45" customHeight="1" s="26">
-      <c r="A7" s="49" t="inlineStr">
+      <c r="A7" s="52" t="inlineStr">
         <is>
           <t>2026-05-27
 -2pp
-🔥 闭眼看世界：美军轰炸伊朗→霍尔木兹P'作废</t>
+【已作废】🔥 闭眼看世界：美军轰炸伊朗→霍尔木兹P'作废</t>
         </is>
       </c>
       <c r="B7" s="50" t="inlineStr">
@@ -1658,11 +1707,11 @@
       <c r="H11" s="48" t="n"/>
     </row>
     <row r="12" ht="45" customHeight="1" s="26">
-      <c r="A12" s="45" t="inlineStr">
+      <c r="A12" s="53" t="inlineStr">
         <is>
           <t>2026-05-16
 +2pp
-付鹏：存储=AI基建（观点→共识信号）</t>
+【虚P】付鹏：存储=AI基建（观点→共识信号）</t>
         </is>
       </c>
       <c r="B12" s="48" t="n"/>

--- a/持仓贝叶斯跟踪.xlsx
+++ b/持仓贝叶斯跟踪.xlsx
@@ -18,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="16">
+  <fonts count="20">
     <font>
       <name val="Calibri"/>
       <charset val="1"/>
@@ -118,6 +118,20 @@
     </font>
     <font>
       <color rgb="00999999"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FF0000"/>
+    </font>
+    <font>
+      <color rgb="00FF0000"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00008000"/>
+    </font>
+    <font>
+      <color rgb="00008000"/>
     </font>
   </fonts>
   <fills count="14">
@@ -254,7 +268,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="54">
+  <cellXfs count="58">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -411,6 +425,10 @@
     <xf numFmtId="0" fontId="14" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -491,60 +509,248 @@
   <commentList>
     <comment ref="A4" authorId="0" shapeId="0">
       <text>
-        <t>【利率-宋鸿兵06-02】
-沃什就任美联储主席，特朗普施压降息vs独立性博弈
-30年美债破5%、10年破4.5%双红线
-美国没加息本钱（还不起债），也没不加息本钱（压不住通胀）
-市场用脚投票：利率只涨不跌</t>
+        <t>信息源：宋鸿兵抖音2026-06-02
+核心内容：沃什就任美联储主席，市场博弈特朗普施压降息vs美联储独立性
+推理链：沃什偏鹰派→降息预期降温→利率维持高位→成长股承压
+P值调整：+1pp（利率环境恶化对芯片/电池/恒科不利）
+影响持仓：芯片-1pp, 电池-1pp, 恒科-1pp</t>
+      </text>
+    </comment>
+    <comment ref="C4" authorId="0" shapeId="0">
+      <text>
+        <t>信息源：闭眼看世界抖音2026-05-29
+核心内容：俄罗斯对基辅发动最猛烈袭击
+推理链：俄乌升级→地缘风险溢价↑→避险资产受益
+P值调整：+1pp（避险方向）
+影响持仓：稀金+1pp</t>
       </text>
     </comment>
     <comment ref="D4" authorId="0" shapeId="0">
       <text>
-        <t>【经济-去杠杆确认】
-付鹏+宋鸿兵交叉验证：
-08-18年加杠杆，现在全面去杠杆
-对多数行业利空（银行/恒科/消费）
-但对猪周期是加速器（散户退出→巨头集中）
-对AI是倒逼器（国产替代）</t>
+        <t>信息源：付鹏+宋鸿兵2026-06-02
+核心内容：确认中国居民部门去杠杆周期（08-18加杠杆→现在全面去杠杆）
+推理链：去杠杆→消费↓→银行资产质量承压
+P值调整：-2pp（虚P，观点性质）
+影响持仓：银行-2pp（虚P）</t>
       </text>
     </comment>
     <comment ref="E4" authorId="0" shapeId="0">
       <text>
-        <t>【能源-霍尔木兹封锁】
-宋鸿兵连续3期强调：
-全球有效原油库存仅8.1亿桶
-OECD最早6月触底
-85%投资者押注油价回80-90=集体幻觉
-若持续封锁+第二轮战争，油价可能冲150</t>
+        <t>信息源：宋鸿兵2026-06-02
+核心内容：霍尔木兹封锁3个月，全球有效原油库存仅8.1亿桶
+推理链：封锁→油价↑→能源成本↑→通胀预期↑
+P值调整：+3pp（能源/避险方向）
+影响持仓：油气对冲机会</t>
       </text>
     </comment>
     <comment ref="F4" authorId="0" shapeId="0">
       <text>
-        <t>【产业-芯片AI基建】
-蒋宇飞8个视频核心：
-1. AI基建时代持续10年，围绕算力/运力/存力
-2. 国产算力长城：升腾+长鑫+deepseek
-3. 玻璃基板大规模应用2028年，5-10年赛道
-芯片ETF(020628)已覆盖核心标的</t>
+        <t>信息源：蒋宇飞抖音2026-06-02
+核心内容：AI基建持续10年+国产算力长城（升腾+长鑫+deepseek）
+推理链：AI基建确定性高→国产替代加速→芯片受益
+P值调整：+2pp（虚P，观点性质）
+影响持仓：芯片+2pp（虚P）</t>
+      </text>
+    </comment>
+    <comment ref="G4" authorId="0" shapeId="0">
+      <text>
+        <t>信息源：Peter Schiff抖音2026-05-28
+核心内容：美债/美元/黄金极端观点
+推理链：美债熊市→美元走弱→黄金受益
+P值调整：+1pp（避险方向）
+影响持仓：稀金+1pp</t>
+      </text>
+    </comment>
+    <comment ref="A5" authorId="0" shapeId="0">
+      <text>
+        <t>信息源：知乎高赞回答2026-05-28
+核心内容：达利欧说「债市是所有市场的支柱」
+推理链：债市动荡→所有资产定价基准动摇→系统性风险
+P值调整：-1pp（系统性风险）</t>
+      </text>
+    </comment>
+    <comment ref="C5" authorId="0" shapeId="0">
+      <text>
+        <t>信息源：闭眼看世界抖音2026-05-20
+核心内容：日本过境领空地缘风险
+推理链：东亚地缘紧张→避险情绪↑
+P值调整：+1pp</t>
       </text>
     </comment>
     <comment ref="D5" authorId="0" shapeId="0">
       <text>
-        <t>【经济-住户贷款数据】
-无知半人数据：前4月住户贷款狂减4902亿
-古都闲云：4月新增贷款出现历史罕见负值
-社消数据同比仅+0.2%
-去杠杆周期数据层面确认</t>
+        <t>信息源：无知半人2026-06-02
+核心内容：前4月住户贷款狂减4902亿
+推理链：数据确认去杠杆→消费端持续收缩
+P值调整：-2pp（事实数据）
+影响持仓：银行-1pp, 恒科-1pp</t>
+      </text>
+    </comment>
+    <comment ref="E5" authorId="0" shapeId="0">
+      <text>
+        <t>信息源：宋鸿兵2026-05-29
+核心内容：美国金融市场对油价极其乐观
+推理链：乐观=低估风险→若封锁持续则油价暴涨
+P值调整：+1pp（虚P，反向信号）</t>
       </text>
     </comment>
     <comment ref="F5" authorId="0" shapeId="0">
       <text>
-        <t>【养殖 🔴跨博主强信号】
-信源1-付鹏：美国猪周期40年启示，周期从3年拉长到7年
-信源2-伊娃：18期财报读完，17家亏损，加速去产能
-信源3-行业：生猪贸易被重点关注
-信源4-自然：厄尔尼诺加速散户退出
-4信源交叉验证，唯一跨博主≥3次信号</t>
+        <t>信息源：4个独立博主交叉验证
+1. 付鹏：美国猪周期40年启示
+2. 伊娃读财报18期：17/18猪企亏损
+3. 行业关注：生猪贸易被重点关注
+4. 厄尔尼诺加速散户退出
+推理链：去产能加速→供给收缩→价格反转→养殖受益
+P值调整：+4pp（跨博主强信号，事实+观点混合）
+影响持仓：养殖+4pp（虚P）</t>
+      </text>
+    </comment>
+    <comment ref="G5" authorId="0" shapeId="0">
+      <text>
+        <t>信息源：闭眼看世界抖音2026-05-27
+核心内容：地缘升级→黄金受益
+P值调整：+2pp
+影响持仓：稀金+2pp</t>
+      </text>
+    </comment>
+    <comment ref="A6" authorId="0" shapeId="0">
+      <text>
+        <t>信息源：沃什政策背景分析
+核心内容：沃什偏鹰派立场→缩表+不降息
+推理链：利率维持高位→成长股估值承压</t>
+      </text>
+    </comment>
+    <comment ref="D6" authorId="0" shapeId="0">
+      <text>
+        <t>信息源：付鹏2026-05-29
+核心内容：所有人都在去杠杆的时候就没有人过得好了
+推理链：去杠杆=通缩压力→消费/投资双降
+P值调整：-1pp</t>
+      </text>
+    </comment>
+    <comment ref="F6" authorId="0" shapeId="0">
+      <text>
+        <t>信息源：蒋宇飞商业2026-05-29
+核心内容：用产业思维抓住科技龙头
+推理链：AI产业链确定性高→存储/算力核心
+P值调整：+1pp</t>
+      </text>
+    </comment>
+    <comment ref="G6" authorId="0" shapeId="0">
+      <text>
+        <t>信息源：宋鸿兵抖音2026-05-27
+核心内容：地缘风险→黄金
+P值调整：+1pp</t>
+      </text>
+    </comment>
+    <comment ref="A7" authorId="0" shapeId="0">
+      <text>
+        <t>信息源：宋鸿兵2026-05-19
+核心内容：利率风暴席卷全球，股债双杀只是开始
+推理链：美债收益率↑→全球流动性收紧
+P值调整：-3pp</t>
+      </text>
+    </comment>
+    <comment ref="D7" authorId="0" shapeId="0">
+      <text>
+        <t>信息源：南半球聊财经2026-05-23
+核心内容：宏观经济数据全景分析
+推理链：数据确认经济下行压力</t>
+      </text>
+    </comment>
+    <comment ref="F7" authorId="0" shapeId="0">
+      <text>
+        <t>信息源：拿幸·AI启示录2026-05-29
+核心内容：Claude Code自愈功能
+推理链：AI Agent加速→算力需求↑
+P值调整：+1pp</t>
+      </text>
+    </comment>
+    <comment ref="A8" authorId="0" shapeId="0">
+      <text>
+        <t>信息源：宋鸿兵2026-05-18
+核心内容：利率风暴根因→霍尔木兹海峡封锁→能源价格飙升→通胀预期
+推理链：地缘→能源→通胀→利率，完整传导链</t>
+      </text>
+    </comment>
+    <comment ref="D8" authorId="0" shapeId="0">
+      <text>
+        <t>信息源：无知半人2026-05-22
+核心内容：前4月住户贷款狂减4902亿
+推理链：数据确认去杠杆</t>
+      </text>
+    </comment>
+    <comment ref="F8" authorId="0" shapeId="0">
+      <text>
+        <t>信息源：周鸿祎2026-05-28
+核心内容："算力决定速度，内存决定高度"
+推理链：内存=AI核心瓶颈→存储受益
+P值调整：+1pp</t>
+      </text>
+    </comment>
+    <comment ref="D9" authorId="0" shapeId="0">
+      <text>
+        <t>信息源：古都闲云2026-05-19
+核心内容：4月新增贷款出现历史罕见的负值
+推理链：信贷收缩→经济下行压力↑</t>
+      </text>
+    </comment>
+    <comment ref="F9" authorId="0" shapeId="0">
+      <text>
+        <t>信息源：AI处理日志2026-05-27
+核心内容：AI相关分析汇总
+P值调整：+2pp</t>
+      </text>
+    </comment>
+    <comment ref="D10" authorId="0" shapeId="0">
+      <text>
+        <t>信息源：古都闲云2026-05-19
+核心内容：中国4月社会消费品零售总额同比+0.2%
+推理链：消费极度疲弱→去杠杆确认
+P值调整：-2pp</t>
+      </text>
+    </comment>
+    <comment ref="F10" authorId="0" shapeId="0">
+      <text>
+        <t>信息源：蒋宇飞抖音2026-05-27
+核心内容：芯片相关分析
+P值调整：0pp（已计入其他事件）</t>
+      </text>
+    </comment>
+    <comment ref="F11" authorId="0" shapeId="0">
+      <text>
+        <t>信息源：付鹏抖音2026-05-27
+核心内容：芯片相关分析
+P值调整：0pp（已计入其他事件）</t>
+      </text>
+    </comment>
+    <comment ref="A26" authorId="0" shapeId="0">
+      <text>
+        <t>信息源：东方财富+新浪财经2026-06-02
+核心数据：
+- 银行ETF(512800): 0.796(4/17)→0.761(5/28)→0.790(6/2)，跌幅-1%
+- 招商银行: 38.80, 兴业银行: 18.61, 平安银行: 11.08
+- 走势：4月中旬以来持续阴跌，5月底略有反弹但未改弱势
+新闻：东方财富头条无银行板块专属利好
+推理链：去杠杆周期→信贷收缩→银行资产质量承压→板块弱势
+P值影响：银行P维持50%（虚P-2pp），无新增正向事件
+结论：不建议加仓</t>
+      </text>
+    </comment>
+    <comment ref="A27" authorId="0" shapeId="0">
+      <text>
+        <t>信息源：东方财富头条+新浪财经2026-06-02
+核心数据：
+- 机器人ETF(562500): 1.009(4/17)→1.122(6/2)，涨幅+11%
+- 5/7-5/22连续上涨：1.097→1.208，涨幅10%
+新闻催化：
+- 宇树科技"闪电"过会，73天高效通过审核
+- 人形机器人商业化元年将至
+- 具身智能迎里程碑时刻
+推理链：宇树过会=产业从概念→实质商业化→平安先进制造+永赢先进制造直接受益
+P值影响：建议从50%基准上调+8~10pp（产业里程碑事件）
+结论：重点关注，强正向信号</t>
       </text>
     </comment>
   </commentList>
@@ -789,7 +995,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:H25"/>
+  <dimension ref="A1:H27"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6171875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="22" customWidth="1" style="25" min="1" max="1"/>
@@ -1225,6 +1431,90 @@
       <c r="H25" s="25" t="inlineStr">
         <is>
           <t>小仓位试水，不对称博弈</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="54" t="inlineStr">
+        <is>
+          <t>银行板块(512800)</t>
+        </is>
+      </c>
+      <c r="B26" s="55" t="inlineStr">
+        <is>
+          <t>弱势</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>P:50% 虚P-2pp</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>去杠杆+信贷收缩，ETF跌-1%，无催化</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>不建议加仓</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>短期</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>银行ETF持续阴跌</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="56" t="inlineStr">
+        <is>
+          <t>人形机器人(562500)</t>
+        </is>
+      </c>
+      <c r="B27" s="57" t="inlineStr">
+        <is>
+          <t>强势</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>P:58%(估)</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>宇树科技73天过会，ETF涨+11%</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>重点关注</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>中期</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>平安先进制造+永赢先进制造</t>
         </is>
       </c>
     </row>

--- a/持仓贝叶斯跟踪.xlsx
+++ b/持仓贝叶斯跟踪.xlsx
@@ -18,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="20">
+  <fonts count="24">
     <font>
       <name val="Calibri"/>
       <charset val="1"/>
@@ -132,6 +132,24 @@
     </font>
     <font>
       <color rgb="00008000"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FF0000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <color rgb="00CC0000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="000066CC"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <color rgb="000066CC"/>
+      <sz val="9"/>
     </font>
   </fonts>
   <fills count="14">
@@ -268,7 +286,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="58">
+  <cellXfs count="62">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -429,6 +447,10 @@
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -505,6 +527,7 @@
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>Hermes</author>
+    <author>系统</author>
   </authors>
   <commentList>
     <comment ref="A4" authorId="0" shapeId="0">
@@ -725,7 +748,91 @@
 P值调整：0pp（已计入其他事件）</t>
       </text>
     </comment>
-    <comment ref="A26" authorId="0" shapeId="0">
+    <comment ref="C23" authorId="1" shapeId="0">
+      <text>
+        <t>信息源: 新浪财经K线API(sh512800)
+推理链: 去杠杆→信贷收缩→银行资产质量↓→板块弱势
+P值: 50%基准，虚P-2pp(利率折价0pp)</t>
+      </text>
+    </comment>
+    <comment ref="E23" authorId="1" shapeId="0">
+      <text>
+        <t>信息源: 新浪财经K线API(sh512800)
+推理链: 去杠杆→信贷收缩→银行资产质量↓→板块弱势
+P值: 50%基准，虚P-2pp(利率折价0pp)</t>
+      </text>
+    </comment>
+    <comment ref="C24" authorId="1" shapeId="0">
+      <text>
+        <t>信息源: 新浪财经K线API(sh512800)
+推理链: 去杠杆→信贷收缩→银行资产质量↓→板块弱势
+P值: 50%基准，虚P-2pp(利率折价0pp)</t>
+      </text>
+    </comment>
+    <comment ref="E24" authorId="1" shapeId="0">
+      <text>
+        <t>信息源: 新浪财经K线API(sh512800)
+推理链: 去杠杆→信贷收缩→银行资产质量↓→板块弱势
+P值: 50%基准，虚P-2pp(利率折价0pp)</t>
+      </text>
+    </comment>
+    <comment ref="C25" authorId="1" shapeId="0">
+      <text>
+        <t>信息源: 新浪财经K线API(sh512800)
+推理链: 去杠杆→信贷收缩→银行资产质量↓→板块弱势
+P值: 50%基准，虚P-2pp(利率折价0pp)</t>
+      </text>
+    </comment>
+    <comment ref="E25" authorId="1" shapeId="0">
+      <text>
+        <t>信息源: 新浪财经K线API(sh512800)
+推理链: 去杠杆→信贷收缩→银行资产质量↓→板块弱势
+P值: 50%基准，虚P-2pp(利率折价0pp)</t>
+      </text>
+    </comment>
+    <comment ref="C26" authorId="1" shapeId="0">
+      <text>
+        <t>信息源: 新浪财经K线API(sh512800)
+推理链: 去杠杆→信贷收缩→银行资产质量↓→板块弱势
+P值: 50%基准，虚P-2pp(利率折价0pp)</t>
+      </text>
+    </comment>
+    <comment ref="E26" authorId="1" shapeId="0">
+      <text>
+        <t>信息源: 新浪财经K线API(sh512800)
+推理链: 去杠杆→信贷收缩→银行资产质量↓→板块弱势
+P值: 50%基准，虚P-2pp(利率折价0pp)</t>
+      </text>
+    </comment>
+    <comment ref="E29" authorId="1" shapeId="0">
+      <text>
+        <t>信息源: 新浪财经K线API(sh562500)
+推理链: 宇树科技73天过会→人形机器人商业化元年→产业催化
+P值: 58%(估)，有效P=58%-6pp=52%</t>
+      </text>
+    </comment>
+    <comment ref="E30" authorId="1" shapeId="0">
+      <text>
+        <t>信息源: 新浪财经K线API(sh562500)
+推理链: 宇树科技73天过会→人形机器人商业化元年→产业催化
+P值: 58%(估)，有效P=58%-6pp=52%</t>
+      </text>
+    </comment>
+    <comment ref="E31" authorId="1" shapeId="0">
+      <text>
+        <t>信息源: 新浪财经K线API(sh562500)
+推理链: 宇树科技73天过会→人形机器人商业化元年→产业催化
+P值: 58%(估)，有效P=58%-6pp=52%</t>
+      </text>
+    </comment>
+    <comment ref="E32" authorId="1" shapeId="0">
+      <text>
+        <t>信息源: 新浪财经K线API(sh562500)
+推理链: 宇树科技73天过会→人形机器人商业化元年→产业催化
+P值: 58%(估)，有效P=58%-6pp=52%</t>
+      </text>
+    </comment>
+    <comment ref="A37" authorId="0" shapeId="0">
       <text>
         <t>信息源：东方财富+新浪财经2026-06-02
 核心数据：
@@ -738,7 +845,7 @@
 结论：不建议加仓</t>
       </text>
     </comment>
-    <comment ref="A27" authorId="0" shapeId="0">
+    <comment ref="A38" authorId="0" shapeId="0">
       <text>
         <t>信息源：东方财富头条+新浪财经2026-06-02
 核心数据：
@@ -995,7 +1102,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:H27"/>
+  <dimension ref="A1:H38"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6171875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="22" customWidth="1" style="25" min="1" max="1"/>
@@ -1301,229 +1408,321 @@
         </is>
       </c>
     </row>
+    <row r="21"/>
     <row r="22" ht="17.15" customHeight="1" s="26">
-      <c r="A22" s="28" t="inlineStr">
+      <c r="A22" s="58" t="inlineStr">
+        <is>
+          <t>🏦 银行板块半年事件链</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="17.15" customHeight="1" s="26">
+      <c r="C23" s="59" t="inlineStr">
+        <is>
+          <t>2026-01-08 银行ETF开启阴跌：0.824→0.767(-6.9%)，信贷持续收缩</t>
+        </is>
+      </c>
+      <c r="E23" s="59" t="inlineStr">
+        <is>
+          <t>2026-01-23 银行ETF触底0.767：去杠杆+住户贷款狂减4902亿，银行资产质量承压</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="17.15" customHeight="1" s="26">
+      <c r="C24" s="59" t="inlineStr">
+        <is>
+          <t>2026-02-05 银行反弹至0.792：政策托底预期</t>
+        </is>
+      </c>
+      <c r="E24" s="59" t="inlineStr">
+        <is>
+          <t>2026-03-17 银行ETF半年最高0.804→3/23单日暴跌-3.3%至0.771</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="17.15" customHeight="1" s="26">
+      <c r="C25" s="59" t="inlineStr">
+        <is>
+          <t>2026-05-18 银行续跌：去杠杆深化，信贷数据持续恶化</t>
+        </is>
+      </c>
+      <c r="E25" s="59" t="inlineStr">
+        <is>
+          <t>2026-05-28 银行ETF半年最低0.761：银行板块42只全线弱势</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="C26" s="59" t="inlineStr">
+        <is>
+          <t>2026-05-29 银行V型反弹：0.761→0.776(+1.97%)→0.790(6/2)</t>
+        </is>
+      </c>
+      <c r="E26" s="59" t="inlineStr">
+        <is>
+          <t>2026-06-02 银行仍弱势：ETF 0.790，无催化信号，不建议加仓</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="60" t="inlineStr">
+        <is>
+          <t>🤖 人形机器人半年事件链</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="E29" s="61" t="inlineStr">
+        <is>
+          <t>2026-03-23 机器人ETF暴跌-4.1%至0.909：市场恐慌+AI回调</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="E30" s="61" t="inlineStr">
+        <is>
+          <t>2026-04-08 机器人ETF暴涨+6.4%至0.967：人形机器人产业催化</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="E31" s="61" t="inlineStr">
+        <is>
+          <t>2026-05-07~22 机器人连续上涨：ETF 1.056→1.216(+15%)，宇树科技73天过会</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="E32" s="61" t="inlineStr">
+        <is>
+          <t>2026-05-25~06-02 机器人回调：1.216→1.122(-7.7%)，仍处强势区间</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="28" t="inlineStr">
         <is>
           <t>🔔 待重仓监控</t>
         </is>
       </c>
     </row>
-    <row r="23" ht="17.15" customHeight="1" s="26">
-      <c r="A23" s="38" t="inlineStr">
+    <row r="34">
+      <c r="A34" s="38" t="inlineStr">
         <is>
           <t>标的</t>
         </is>
       </c>
-      <c r="B23" s="38" t="inlineStr">
+      <c r="B34" s="38" t="inlineStr">
         <is>
           <t>状态</t>
         </is>
       </c>
-      <c r="C23" s="38" t="inlineStr">
+      <c r="C34" s="38" t="inlineStr">
         <is>
           <t>当前P/价格</t>
         </is>
       </c>
-      <c r="D23" s="38" t="inlineStr">
+      <c r="D34" s="38" t="inlineStr">
         <is>
           <t>最新信号</t>
         </is>
       </c>
-      <c r="E23" s="38" t="inlineStr">
+      <c r="E34" s="38" t="inlineStr">
         <is>
           <t>触发条件</t>
         </is>
       </c>
-      <c r="F23" s="38" t="inlineStr">
+      <c r="F34" s="38" t="inlineStr">
         <is>
           <t>距离触发</t>
         </is>
       </c>
-      <c r="G23" s="38" t="inlineStr">
+      <c r="G34" s="38" t="inlineStr">
         <is>
           <t>跟踪日期</t>
         </is>
       </c>
-      <c r="H23" s="38" t="inlineStr">
+      <c r="H34" s="38" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="24" ht="17.15" customHeight="1" s="26">
-      <c r="A24" s="25" t="inlineStr">
+    <row r="35">
+      <c r="A35" s="25" t="inlineStr">
         <is>
           <t>玻璃基板</t>
         </is>
       </c>
-      <c r="B24" s="25" t="inlineStr">
+      <c r="B35" s="25" t="inlineStr">
         <is>
           <t>深南电路002916/兴森科技002436</t>
         </is>
       </c>
-      <c r="C24" s="25" t="inlineStr">
+      <c r="C35" s="25" t="inlineStr">
         <is>
           <t>观察中</t>
         </is>
       </c>
-      <c r="D24" s="25" t="inlineStr">
+      <c r="D35" s="25" t="inlineStr">
         <is>
           <t>蒋宇飞：玻璃基板大规模应用2028年，5-10年赛道</t>
         </is>
       </c>
-      <c r="E24" s="25" t="inlineStr">
+      <c r="E35" s="25" t="inlineStr">
         <is>
           <t>AI基建+国产替代加速</t>
         </is>
       </c>
-      <c r="F24" s="25" t="inlineStr">
+      <c r="F35" s="25" t="inlineStr">
         <is>
           <t>中长期</t>
         </is>
       </c>
-      <c r="G24" s="25" t="inlineStr">
+      <c r="G35" s="25" t="inlineStr">
         <is>
           <t>2026-06-02</t>
         </is>
       </c>
-      <c r="H24" s="25" t="inlineStr">
+      <c r="H35" s="25" t="inlineStr">
         <is>
           <t>芯片ETF已覆盖，个股可关注</t>
         </is>
       </c>
     </row>
-    <row r="25" ht="17.15" customHeight="1" s="26">
-      <c r="A25" s="25" t="inlineStr">
+    <row r="36">
+      <c r="A36" s="25" t="inlineStr">
         <is>
           <t>油气对冲</t>
         </is>
       </c>
-      <c r="B25" s="25" t="inlineStr">
+      <c r="B36" s="25" t="inlineStr">
         <is>
           <t>华宝油气162411</t>
         </is>
       </c>
-      <c r="C25" s="25" t="inlineStr">
+      <c r="C36" s="25" t="inlineStr">
         <is>
           <t>观察中</t>
         </is>
       </c>
-      <c r="D25" s="25" t="inlineStr">
+      <c r="D36" s="25" t="inlineStr">
         <is>
           <t>宋鸿兵：霍尔木兹封锁3个月，85%投资者押注回落=幻觉</t>
         </is>
       </c>
-      <c r="E25" s="25" t="inlineStr">
+      <c r="E36" s="25" t="inlineStr">
         <is>
           <t>油价冲150或海峡持续封锁</t>
         </is>
       </c>
-      <c r="F25" s="25" t="inlineStr">
+      <c r="F36" s="25" t="inlineStr">
         <is>
           <t>短期</t>
         </is>
       </c>
-      <c r="G25" s="25" t="inlineStr">
+      <c r="G36" s="25" t="inlineStr">
         <is>
           <t>2026-06-02</t>
         </is>
       </c>
-      <c r="H25" s="25" t="inlineStr">
+      <c r="H36" s="25" t="inlineStr">
         <is>
           <t>小仓位试水，不对称博弈</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="54" t="inlineStr">
+    <row r="37">
+      <c r="A37" s="54" t="inlineStr">
         <is>
           <t>银行板块(512800)</t>
         </is>
       </c>
-      <c r="B26" s="55" t="inlineStr">
+      <c r="B37" s="55" t="inlineStr">
         <is>
           <t>弱势</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
+      <c r="C37" s="25" t="inlineStr">
         <is>
           <t>P:50% 虚P-2pp</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr">
+      <c r="D37" s="25" t="inlineStr">
         <is>
           <t>去杠杆+信贷收缩，ETF跌-1%，无催化</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr">
+      <c r="E37" s="25" t="inlineStr">
         <is>
           <t>不建议加仓</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr">
+      <c r="F37" s="25" t="inlineStr">
         <is>
           <t>短期</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr">
+      <c r="G37" s="25" t="inlineStr">
         <is>
           <t>2026-06-03</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr">
+      <c r="H37" s="25" t="inlineStr">
         <is>
           <t>银行ETF持续阴跌</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="56" t="inlineStr">
+    <row r="38">
+      <c r="A38" s="56" t="inlineStr">
         <is>
           <t>人形机器人(562500)</t>
         </is>
       </c>
-      <c r="B27" s="57" t="inlineStr">
+      <c r="B38" s="57" t="inlineStr">
         <is>
           <t>强势</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr">
+      <c r="C38" s="25" t="inlineStr">
         <is>
           <t>P:58%(估)</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr">
+      <c r="D38" s="25" t="inlineStr">
         <is>
           <t>宇树科技73天过会，ETF涨+11%</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr">
+      <c r="E38" s="25" t="inlineStr">
         <is>
           <t>重点关注</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr">
+      <c r="F38" s="25" t="inlineStr">
         <is>
           <t>中期</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr">
+      <c r="G38" s="25" t="inlineStr">
         <is>
           <t>2026-06-03</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr">
+      <c r="H38" s="25" t="inlineStr">
         <is>
           <t>平安先进制造+永赢先进制造</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A12:H12"/>
     <mergeCell ref="A18:H18"/>
     <mergeCell ref="B14:H14"/>
     <mergeCell ref="B13:H13"/>
+    <mergeCell ref="A28:G28"/>
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="A19:H19"/>
     <mergeCell ref="B15:H15"/>

--- a/持仓贝叶斯跟踪.xlsx
+++ b/持仓贝叶斯跟踪.xlsx
@@ -286,7 +286,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="62">
+  <cellXfs count="63">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -451,6 +451,9 @@
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1179,7 +1182,8 @@
       </c>
       <c r="E4" s="35" t="inlineStr">
         <is>
-          <t>2026-06-02 宋鸿兵：霍尔木兹封锁3个月，全球有效原油库存仅8.1亿桶，市场误判油价回落</t>
+          <t>2026-06-02 宋鸿兵：霍尔木兹封锁3个月，全球有效原油库存仅8.1亿桶，市场误判油价回落
+2026-06-03 宋鸿兵+雪佛龙+埃克森：OECD库存6月触红线，布伦特或冲150-160，5月跌10%=口头操纵</t>
         </is>
       </c>
       <c r="F4" s="35" t="inlineStr">
@@ -1344,7 +1348,8 @@
     <row r="14" ht="15" customHeight="1" s="26">
       <c r="B14" s="37" t="inlineStr">
         <is>
-          <t>②霍尔木兹封3个月：有效原油库存8.1亿桶，OECD最早6月触底，85%投资者押注回落=集体幻觉</t>
+          <t>②霍尔木兹封3个月：有效原油库存8.1亿桶，OECD最早6月触底，85%投资者押注回落=集体幻觉
+2026-06-03 ⚠️升级：雪佛龙CEO+埃克森VP双重警告，OECD 6月触红线，布伦特或冲150-160，特朗普9月死线</t>
         </is>
       </c>
     </row>
@@ -1355,6 +1360,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>🆕 新叙事④</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>④芯片范式转换：摩尔定律终结→堆叠/先进封装崛起（宋鸿兵+蒋宇飞跨博主确认）</t>
+        </is>
+      </c>
+    </row>
     <row r="17" ht="17.15" customHeight="1" s="26">
       <c r="A17" s="28" t="inlineStr">
         <is>
@@ -1408,7 +1425,6 @@
         </is>
       </c>
     </row>
-    <row r="21"/>
     <row r="22" ht="17.15" customHeight="1" s="26">
       <c r="A22" s="58" t="inlineStr">
         <is>
@@ -1743,7 +1759,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:H12"/>
+  <dimension ref="A1:H13"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="10.4921875" defaultRowHeight="12.75" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="32" customWidth="1" style="25" min="1" max="8"/>
@@ -2211,7 +2227,38 @@
       <c r="G12" s="48" t="n"/>
       <c r="H12" s="48" t="n"/>
     </row>
-    <row r="13" ht="13.5" customHeight="1" s="26"/>
+    <row r="13" ht="13.5" customHeight="1" s="26">
+      <c r="A13" s="62" t="inlineStr">
+        <is>
+          <t>2026-06-03
++1pp
+【事实】宋鸿兵：摩尔定律物理+经济双重极限
++2pp
+【虚P】🔴跨博主：堆叠崛起</t>
+        </is>
+      </c>
+      <c r="B13" s="62" t="inlineStr">
+        <is>
+          <t>2026-06-03
++4pp
+【虚P】宋鸿兵+雪佛龙+埃克森：油价危机OECD 6月触红线</t>
+        </is>
+      </c>
+      <c r="C13" s="62" t="inlineStr">
+        <is>
+          <t>2026-06-03
+-3pp
+【虚P】油价危机→利率压制恒科</t>
+        </is>
+      </c>
+      <c r="G13" s="62" t="inlineStr">
+        <is>
+          <t>2026-06-03
+-1pp
+【虚P】利率上行不利净息差</t>
+        </is>
+      </c>
+    </row>
     <row r="14" ht="13.5" customHeight="1" s="26"/>
     <row r="15" ht="13.5" customHeight="1" s="26"/>
     <row r="16" ht="13.5" customHeight="1" s="26"/>

--- a/持仓贝叶斯跟踪.xlsx
+++ b/持仓贝叶斯跟踪.xlsx
@@ -18,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="24">
+  <fonts count="27">
     <font>
       <name val="Calibri"/>
       <charset val="1"/>
@@ -151,8 +151,20 @@
       <color rgb="000066CC"/>
       <sz val="9"/>
     </font>
+    <font>
+      <b val="1"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <sz val="9"/>
+    </font>
   </fonts>
-  <fills count="14">
+  <fills count="16">
     <fill>
       <patternFill/>
     </fill>
@@ -231,6 +243,18 @@
         <bgColor rgb="00E0E0E0"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="004472C4"/>
+        <bgColor rgb="004472C4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F2F2F2"/>
+        <bgColor rgb="00F2F2F2"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="6">
     <border>
@@ -286,7 +310,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="63">
+  <cellXfs count="66">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -452,6 +476,13 @@
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="14" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="15" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1334,41 +1365,40 @@
     <row r="12" ht="17.15" customHeight="1" s="26">
       <c r="A12" s="36" t="inlineStr">
         <is>
-          <t>🔥 叙事主线（三条）</t>
+          <t>🔥 叙事主线（四条）</t>
         </is>
       </c>
     </row>
     <row r="13" ht="15" customHeight="1" s="26">
       <c r="B13" s="37" t="inlineStr">
         <is>
-          <t>①美国走钢丝：国债39万亿+30年美债破5%+10年破4.5%，沃什上任但市场用脚投票，利率只涨不跌</t>
+          <t>①美国国债/利率危机 ⚠️升级：从"慢性走钢丝"→"9月死线"【来源：宋鸿兵6.3视频】。国债39万亿+30年美债破5%+10年破4.5%，沃什上任但市场用脚投票。霍尔木兹不重开→OECD库存6月见底→全球9月触红线→能源成本失控+恶性通胀，利率只涨不跌</t>
         </is>
       </c>
     </row>
     <row r="14" ht="15" customHeight="1" s="26">
       <c r="B14" s="37" t="inlineStr">
         <is>
-          <t>②霍尔木兹封3个月：有效原油库存8.1亿桶，OECD最早6月触底，85%投资者押注回落=集体幻觉
-2026-06-03 ⚠️升级：雪佛龙CEO+埃克森VP双重警告，OECD 6月触红线，布伦特或冲150-160，特朗普9月死线</t>
+          <t>②霍尔木兹/能源危机 🔴重大升级：封锁3个月，有效原油库存8.1亿桶，OECD最早6月触红线。雪佛龙CEO+埃克森VP双重警告，85%投资者押注回落=集体幻觉</t>
         </is>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1" s="26">
       <c r="B15" s="37" t="inlineStr">
         <is>
-          <t>③中国去杠杆但分化：08-18加杠杆→全面去杠杆，对猪周期是加速器，对AI是倒逼器</t>
+          <t>③中国去杠杆分化 维持：08-18加杠杆→全面去杠杆，对猪周期是加速器，对AI是倒逼器。无新催化</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
+      <c r="A16" s="25" t="inlineStr">
         <is>
           <t>🆕 新叙事④</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>④芯片范式转换：摩尔定律终结→堆叠/先进封装崛起（宋鸿兵+蒋宇飞跨博主确认）</t>
+      <c r="B16" s="25" t="inlineStr">
+        <is>
+          <t>④芯片范式转换 🆕新叙事：摩尔定律物理+经济双极限→堆叠/先进封装崛起（宋鸿兵+蒋宇飞跨博主强确认）。存储需求指数增长，国产替代空间6倍</t>
         </is>
       </c>
     </row>
@@ -1759,7 +1789,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:H13"/>
+  <dimension ref="A1:J15"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="10.4921875" defaultRowHeight="12.75" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="32" customWidth="1" style="25" min="1" max="8"/>
@@ -1778,6 +1808,11 @@
       <c r="F1" s="40" t="n"/>
       <c r="G1" s="40" t="n"/>
       <c r="H1" s="41" t="n"/>
+      <c r="J1" s="63" t="inlineStr">
+        <is>
+          <t>📊 盈亏比说明</t>
+        </is>
+      </c>
     </row>
     <row r="2" ht="26.25" customHeight="1" s="26">
       <c r="A2" s="39" t="inlineStr">
@@ -1830,83 +1865,107 @@
       </c>
     </row>
     <row r="3" ht="72.75" customHeight="1" s="26">
-      <c r="A3" s="42" t="inlineStr">
+      <c r="A3" s="64" t="inlineStr">
         <is>
           <t>成本¥3695
 净值3.6875
 P:41%
 虚P+4pp
 利率折价-6pp
-有效P:35%</t>
-        </is>
-      </c>
-      <c r="B3" s="42" t="inlineStr">
+有效P:35%
+下行:25% 确定性:30% 溢价:50%
+盈亏比:1.2:1
+决策:观望</t>
+        </is>
+      </c>
+      <c r="B3" s="64" t="inlineStr">
         <is>
           <t>成本¥6811
 净值1.8418
 P:67%
 虚P无
 利率折价-6pp
-有效P:61%</t>
-        </is>
-      </c>
-      <c r="C3" s="42" t="inlineStr">
+有效P:61%
+下行:20% 确定性:25% 溢价:40%
+盈亏比:2.3:1
+决策:持有</t>
+        </is>
+      </c>
+      <c r="C3" s="64" t="inlineStr">
         <is>
           <t>成本¥4722
 净值0.6619
 P:38%
 虚P无
 利率折价-6pp
-有效P:32%</t>
-        </is>
-      </c>
-      <c r="D3" s="42" t="inlineStr">
+有效P:32%
+下行:30% 确定性:15% 溢价:30%
+盈亏比:0.5:1
+决策:不干</t>
+        </is>
+      </c>
+      <c r="D3" s="64" t="inlineStr">
         <is>
           <t>成本¥3732
 净值0.7545
 P:56%
 虚P+4pp
 利率折价0pp
-有效P:56%</t>
-        </is>
-      </c>
-      <c r="E3" s="42" t="inlineStr">
+有效P:56%
+下行:20% 确定性:35% 溢价:20%
+盈亏比:1.8:1
+决策:观望</t>
+        </is>
+      </c>
+      <c r="E3" s="64" t="inlineStr">
         <is>
           <t>成本¥4800
 净值1.8985
 P:44%
 虚P无
 利率折价-4pp
-有效P:40%</t>
-        </is>
-      </c>
-      <c r="F3" s="42" t="inlineStr">
+有效P:40%
+下行:15% 确定性:20% 溢价:30%
+盈亏比:2.0:1
+决策:持有</t>
+        </is>
+      </c>
+      <c r="F3" s="64" t="inlineStr">
         <is>
           <t>成本¥5622
 净值1.089
 P:43%
 虚P无
 利率折价-4pp
-有效P:39%</t>
-        </is>
-      </c>
-      <c r="G3" s="42" t="inlineStr">
+有效P:39%
+下行:20% 确定性:25% 溢价:35%
+盈亏比:1.8:1
+决策:观望</t>
+        </is>
+      </c>
+      <c r="G3" s="64" t="inlineStr">
         <is>
           <t>成本¥0
 净值1.6291
 P:50%
 虚P-2pp
 利率折价0pp
-有效P:50%</t>
-        </is>
-      </c>
-      <c r="H3" s="42" t="inlineStr">
+有效P:50%
+下行:10% 确定性:10% 溢价:5%
+盈亏比:1.5:1
+决策:监控</t>
+        </is>
+      </c>
+      <c r="H3" s="64" t="inlineStr">
         <is>
           <t>成本¥101
 净值1.1274
 P:None%
 利率折价-4pp
-有效P:-%</t>
+有效P:-%
+下行:30% 确定性:20% 溢价:40%
+盈亏比:0.7:1
+决策:不干</t>
         </is>
       </c>
     </row>
@@ -1949,6 +2008,26 @@
       <c r="H4" s="43" t="inlineStr">
         <is>
           <t>日期/P/事件</t>
+        </is>
+      </c>
+      <c r="J4" s="65" t="inlineStr">
+        <is>
+          <t>📊 盈亏比说明
+━━━━━━━━━━━━━━━
+P值 = 当前热度（方向对不对）
+盈亏比 = 机会质量（值不值得干）
+计算公式：
+盈亏比 = (确定性空间 + 溢价空间×P值打折) ÷ 下行空间
+P值打折规则：
+P≥70% → 溢价不打折
+P 60-70% → 溢价五折
+P&lt;60% → 不算溢价
+决策标准：
+✅ 盈亏比≥2:1 → 值得干
+⚠️ 1.5-2:1 → 勉强
+❌ &lt;1.5:1 → 不干
+方法论文档：
+01-盈亏比计算方法论.md</t>
         </is>
       </c>
     </row>
@@ -2277,7 +2356,9 @@
     <row r="29" ht="13.5" customHeight="1" s="26"/>
     <row r="30" ht="13.5" customHeight="1" s="26"/>
   </sheetData>
-  <mergeCells count="1">
+  <mergeCells count="3">
+    <mergeCell ref="J4:J15"/>
+    <mergeCell ref="J1:J3"/>
     <mergeCell ref="A1:H1"/>
   </mergeCells>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>

--- a/持仓贝叶斯跟踪.xlsx
+++ b/持仓贝叶斯跟踪.xlsx
@@ -780,6 +780,32 @@
         <t>信息源：付鹏抖音2026-05-27
 核心内容：芯片相关分析
 P值调整：0pp（已计入其他事件）</t>
+      </text>
+    </comment>
+    <comment ref="A12" authorId="0" shapeId="0">
+      <text>
+        <t xml:space="preserve">📊 叙事主线→持仓影响分析（2026-06-03更新）
+【胜率×赔率矩阵】
+┌──────────┬──────┬───────┬──────────────┐
+│ 持仓      │ P值   │ 盈亏比 │ 决策          │
+├──────────┼──────┼───────┼──────────────┤
+│ 电池009759│ 67%  │ 2.3:1 │ ✅ 持有，双条件满足 │
+│ 有色008826│ 44%  │ 2.0:1 │ ✅ HALO策略中    │
+│ 存储赛道  │ 70%+ │ 6:1   │ 🔴 等大跌+找标的  │
+│ 养殖008765│ 56%  │ 1.8:1 │ 观望，等右侧    │
+│ 芯片020628│ 41%  │ 1.2:1 │ 观望，P值不足   │
+└──────────┴──────┴───────┴──────────────┘
+【四条叙事→操作映射】
+①利率危机⚠️升级 → 成长股承压，芯片/恒科短期不利，现金为王
+②能源危机🔴升级 → 有色HALO策略继续有效，华宝油气可小仓试水
+③去杠杆维持 → 银行不加仓，养殖是去杠杆加速受益方向
+④芯片范式🆕 → 长期最大机会在存储（非020628），等中期选举大跌
+【当前最优解】
+1. 胜率最高：电池（P=67%，已持有✅）
+2. 赔率最高：存储（6:1，但无标的，等时机）
+3. 胜率+赔率双优：暂无，存储等条件成熟
+4. 防守：有色HALO跨式对冲能源不确定性
+</t>
       </text>
     </comment>
     <comment ref="C23" authorId="1" shapeId="0">

--- a/持仓贝叶斯跟踪.xlsx
+++ b/持仓贝叶斯跟踪.xlsx
@@ -782,29 +782,88 @@
 P值调整：0pp（已计入其他事件）</t>
       </text>
     </comment>
-    <comment ref="A12" authorId="0" shapeId="0">
-      <text>
-        <t xml:space="preserve">📊 叙事主线→持仓影响分析（2026-06-03更新）
-【胜率×赔率矩阵】
-┌──────────┬──────┬───────┬──────────────┐
-│ 持仓      │ P值   │ 盈亏比 │ 决策          │
-├──────────┼──────┼───────┼──────────────┤
-│ 电池009759│ 67%  │ 2.3:1 │ ✅ 持有，双条件满足 │
-│ 有色008826│ 44%  │ 2.0:1 │ ✅ HALO策略中    │
-│ 存储赛道  │ 70%+ │ 6:1   │ 🔴 等大跌+找标的  │
-│ 养殖008765│ 56%  │ 1.8:1 │ 观望，等右侧    │
-│ 芯片020628│ 41%  │ 1.2:1 │ 观望，P值不足   │
-└──────────┴──────┴───────┴──────────────┘
-【四条叙事→操作映射】
-①利率危机⚠️升级 → 成长股承压，芯片/恒科短期不利，现金为王
-②能源危机🔴升级 → 有色HALO策略继续有效，华宝油气可小仓试水
-③去杠杆维持 → 银行不加仓，养殖是去杠杆加速受益方向
-④芯片范式🆕 → 长期最大机会在存储（非020628），等中期选举大跌
-【当前最优解】
-1. 胜率最高：电池（P=67%，已持有✅）
-2. 赔率最高：存储（6:1，但无标的，等时机）
-3. 胜率+赔率双优：暂无，存储等条件成熟
-4. 防守：有色HALO跨式对冲能源不确定性
+    <comment ref="B13" authorId="0" shapeId="0">
+      <text>
+        <t xml:space="preserve">【来源】宋鸿兵6.3视频
+【逻辑链】
+霍尔木兹封锁3个月 → 全球有效原油库存8.1亿桶
+ → OECD库存6月触红线（本月）
+ → 全球库存9月见底
+ → 特朗普必须在9月前重开霍尔木兹
+ → 否则：能源成本失控 + 恶性通胀 + 国债收益率飙升
+【当前状态】⚠️升级：从"慢性走钢丝"→"9月死线"
+- 国债39万亿+30年美债破5%+10年破4.5%
+- 沃什上任但市场用脚投票，利率只涨不跌
+【对持仓影响】
+🔴 利空：芯片(020628)/恒科(009854) — 成长股对利率最敏感
+🟡 中性：电池(009759) — 新能源有政策托底，但高利率压制估值
+🟢 利好：有色HALO(008826) — 利率↑=通胀预期↑=商品对冲需求↑
+【操作建议】
+利率危机升级→短期偏防守，不追成长股。等9月死线前后：
+- 若霍尔木兹重开→利率回落→成长股反弹→芯片/恒科右侧信号
+- 若霍尔木兹持续封锁→能源暴涨→华宝油气+有色HALO继续有效
+</t>
+      </text>
+    </comment>
+    <comment ref="B14" authorId="0" shapeId="0">
+      <text>
+        <t xml:space="preserve">【来源】宋鸿兵6.3视频 + 雪佛龙CEO + 埃克森VP
+【逻辑链】
+霍尔木兹封锁 → 中东原油无法出口
+ → 全球有效库存8.1亿桶持续消耗
+ → OECD库存6月触底（雪佛龙CEO确认）
+ → 85%投资者押注油价回落 = 集体幻觉（埃克森VP警告）
+【当前状态】🔴重大升级：行业巨头双重警告
+- 雪佛龙CEO：OECD库存6月见底
+- 埃克森VP：市场严重低估能源危机
+【对持仓影响】
+🟢 利好：有色HALO(008826) — 能源危机=商品牛市=HALO策略核心逻辑
+🟢 利好：华宝油气(162411) — 油价冲150直接受益
+🔴 利空：养殖(008765) — 饲料成本(玉米/大豆运输)↑
+🔴 利空：银行(512800) — 通胀↑→坏账率↑
+【操作建议】
+能源危机是确定性最高的叙事之一（双重行业验证）。
+- 有色HALO继续持有
+- 华宝油气可小仓试水（不对称博弈：下行有限，上行巨大）
+</t>
+      </text>
+    </comment>
+    <comment ref="B15" authorId="0" shapeId="0">
+      <text>
+        <t xml:space="preserve">【来源】付鹏+宋鸿兵6.2 + 无知半人
+【逻辑链】
+08-18居民加杠杆 → 现在全面去杠杆
+ → 前4月住户贷款狂减4902亿
+ → 消费萎缩 → 猪周期加速出清
+【当前状态】维持，无新催化
+【对持仓影响】
+🟢 利好：养殖(008765) — 去杠杆=消费↓=猪价承压=加速出清=右侧机会
+🔴 利空：银行(512800) — 信贷收缩=银行资产质量恶化
+【操作建议】
+- 养殖：去杠杆是加速器，等右侧信号（猪价企稳+产能出清确认）
+- 银行：不加仓，去杠杆周期中银行最难受
+</t>
+      </text>
+    </comment>
+    <comment ref="B16" authorId="0" shapeId="0">
+      <text>
+        <t xml:space="preserve">【来源】宋鸿兵6.2 + 蒋宇飞6.1/5.18 + 群联潘健成 + 周鸿祎 + 用户6.3洞察
+【逻辑链】
+摩尔定律物理+经济双极限（宋鸿兵）
+ → 堆叠/先进封装崛起（蒋宇飞"叠"赛道）
+ → 存储需求指数增长（用户洞察：AI进化=存储需求↑）
+ → Flash供给不足，明年更紧张（群联潘健成）
+ → 长鑫+长江国产替代空间6倍（蒋宇飞）
+【当前状态】🆕新叙事：5条独立信源交叉验证⭐⭐⭐⭐⭐
+【对持仓影响】
+🟢 超级利好：存储赛道 — P值70%+，盈亏比6:1
+🟡 中性：芯片ETF(020628) — 不含存储核心成分！需单独找标的
+🟢 利好：澜起科技(688008) — DDR5接口芯片，内存瓶颈直接受益
+【操作建议】
+这是当前赔率最高的机会（6:1），但缺少直接标的。
+- 短期：020628不含存储，不要当存储买
+- 中期：等中期选举年大盘大跌→找纯存储ETF/长鑫产业链个股→重仓
+- 跟踪：蒋宇飞/群联新观点 + 存储ETF价格
 </t>
       </text>
     </comment>

--- a/持仓贝叶斯跟踪.xlsx
+++ b/持仓贝叶斯跟踪.xlsx
@@ -18,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="27">
+  <fonts count="29">
     <font>
       <name val="Calibri"/>
       <charset val="1"/>
@@ -163,8 +163,16 @@
     <font>
       <sz val="9"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FF0000"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+    </font>
   </fonts>
-  <fills count="16">
+  <fills count="17">
     <fill>
       <patternFill/>
     </fill>
@@ -255,6 +263,12 @@
         <bgColor rgb="00F2F2F2"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFFCC"/>
+        <bgColor rgb="00FFFFCC"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="6">
     <border>
@@ -310,7 +324,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="66">
+  <cellXfs count="68">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -485,6 +499,8 @@
     <xf numFmtId="0" fontId="26" fillId="15" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="28" fillId="16" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1221,7 +1237,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:H38"/>
+  <dimension ref="A1:H49"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6171875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="22" customWidth="1" style="25" min="1" max="1"/>
@@ -1844,6 +1860,286 @@
       <c r="H38" s="25" t="inlineStr">
         <is>
           <t>平安先进制造+永赢先进制造</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="66" t="inlineStr">
+        <is>
+          <t>🔥 存储赛道标的（2026-06-03新增）</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="67" t="inlineStr">
+        <is>
+          <t>标的</t>
+        </is>
+      </c>
+      <c r="B41" s="67" t="inlineStr">
+        <is>
+          <t>代码</t>
+        </is>
+      </c>
+      <c r="C41" s="67" t="inlineStr">
+        <is>
+          <t>盈亏比</t>
+        </is>
+      </c>
+      <c r="D41" s="67" t="inlineStr">
+        <is>
+          <t>P值</t>
+        </is>
+      </c>
+      <c r="E41" s="67" t="inlineStr">
+        <is>
+          <t>建议仓位</t>
+        </is>
+      </c>
+      <c r="F41" s="67" t="inlineStr">
+        <is>
+          <t>买入条件</t>
+        </is>
+      </c>
+      <c r="G41" s="67" t="inlineStr">
+        <is>
+          <t>状态</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>北京君正</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>300223</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>4:1</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>70%+</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>AI仓50%</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>等大跌15%+</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>🔴未建仓</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>兆易创新</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>603986</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>3.5:1</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>70%+</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>AI仓50%</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>等大跌15%+</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>🔴未建仓</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>江波龙</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>301308</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>3.5:1</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>70%+</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>AI仓50%</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>等大跌15%+</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>🔴未建仓</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>佰维存储</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>688525</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>3:1</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>70%+</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>AI仓50%</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>等大跌15%+</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>🔴未建仓</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>聚辰股份</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>688123</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>3:1</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>70%+</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>AI仓50%</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>等大跌15%+</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>🔴未建仓</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>澜起科技</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>688008</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>4:1</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>55%+</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>AI仓20%</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>等大跌15%+</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>🟡观察中</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>📌 AI仓位目标：总资金25%（存储12.5%+澜起5%+芯片ETF持有+凯盛2.5%观察）</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>📌 核心逻辑：长鑫/长江暂时买不到→买产业链上下游→存储缺货涨价贯穿2026全年</t>
         </is>
       </c>
     </row>

--- a/持仓贝叶斯跟踪.xlsx
+++ b/持仓贝叶斯跟踪.xlsx
@@ -995,6 +995,109 @@
 结论：重点关注，强正向信号</t>
       </text>
     </comment>
+    <comment ref="A39" authorId="0" shapeId="0">
+      <text>
+        <t xml:space="preserve">【来源】群联潘健成(产业高管)+蒋宇飞(6.1两长存储+5.18框架)+宋鸿兵(6.2摩尔定律终结)+周鸿祎(内存决定AI)+用户6.3洞察
+【逻辑链】
+AI越进化，存储需求指数增长（用户底层范式）
+ → 摩尔定律物理+经济双极限→堆叠/先进封装崛起（宋鸿兵+蒋宇飞交叉验证）
+ → Flash供给不足，明年更紧张（群联潘健成一线数据）
+ → 长鑫+长江国产替代空间6倍（蒋宇飞）
+ → 长鑫Q1净利润263亿/长江Q1营收破200亿（业绩验证）
+ → 长鑫/长江暂时买不到→买产业链上下游A股标的
+【当前状态】🔴最高优先级：P值70%+，5条独立信源同向确认，存储缺货涨价贯穿2026全年
+【对持仓影响】
+🟢 超级利好：存储赛道 = AI仓位核心（占AI总仓50%）
+🟢 利好：澜起科技DDR5接口（存储赛道补充）
+🟡 中性：020628芯片ETF不含存储核心成分，不要当存储买
+【操作建议】
+胜率×赔率：P值70%+（高胜率）× 盈亏比3-4:1（高赔率）= 当前最优AI机会
+买入时机：等中期选举年大盘跌15%+或单日暴跌5%+或P值回升55%+
+仓位分配：存储选2-3只分散（总资金12.5%），澜起5%，凯盛2.5%观察仓
+⚠️ 北京君正年内已+51%，不追高，等回调
+</t>
+      </text>
+    </comment>
+    <comment ref="A40" authorId="0" shapeId="0">
+      <text>
+        <t xml:space="preserve">【来源】蒋宇飞星光纯叠框架+宋鸿兵华为韬定律+用户"AI瓶颈是内存而非算力"
+【逻辑链】
+AI算力爆发→内存带宽瓶颈→DDR5渗透率提升
+ → 澜起科技=内存接口芯片全球龙头
+ → 华为韬(τ)定律：逻辑折叠=超三维堆叠→近存计算→DDR5接口芯片需求暴增
+ → 量价齐升，增速50-80%/年
+【当前状态】🟡合理估值：PE130x，PEG 1.6-2.6x，¥280以下=合理
+【对持仓影响】🟢 存储赛道补充，与存储逻辑互锁
+【操作建议】盈亏比4:1，AI仓20%（总资金5%）。等中期选举大跌或P值回升55%+。⚠️股东询价转让(减持利空)需关注。
+</t>
+      </text>
+    </comment>
+    <comment ref="A42" authorId="0" shapeId="0">
+      <text>
+        <t xml:space="preserve">【标的】北京君正 300223
+【核心逻辑】存储+计算芯片，DRAM新工艺突破，车载存储市占率提升。A股年内+51%，市值772亿。港股二度IPO中。盈亏比4:1，存储赛道里最强。
+【为什么买】长鑫/长江暂时买不到→买产业链上下游→存储涨价直接受益
+【买入条件】等中期选举年大盘跌15%+或单日暴跌5%+或P值回升55%+
+【仓位建议】存储选2-3只分散（总资金12.5%），澜起单独5%
+【跟踪频率】每日收盘检查价格+每日检查蒋宇飞/群联新观点
+</t>
+      </text>
+    </comment>
+    <comment ref="A43" authorId="0" shapeId="0">
+      <text>
+        <t xml:space="preserve">【标的】兆易创新 603986
+【核心逻辑】NOR Flash国内龙头，DRAM布局中。存储涨价直接受益。盈亏比3.5:1。
+【为什么买】长鑫/长江暂时买不到→买产业链上下游→存储涨价直接受益
+【买入条件】等中期选举年大盘跌15%+或单日暴跌5%+或P值回升55%+
+【仓位建议】存储选2-3只分散（总资金12.5%），澜起单独5%
+【跟踪频率】每日收盘检查价格+每日检查蒋宇飞/群联新观点
+</t>
+      </text>
+    </comment>
+    <comment ref="A44" authorId="0" shapeId="0">
+      <text>
+        <t xml:space="preserve">【标的】江波龙 301308
+【核心逻辑】存储模组+主控芯片，国产替代核心标的。盈亏比3.5:1。
+【为什么买】长鑫/长江暂时买不到→买产业链上下游→存储涨价直接受益
+【买入条件】等中期选举年大盘跌15%+或单日暴跌5%+或P值回升55%+
+【仓位建议】存储选2-3只分散（总资金12.5%），澜起单独5%
+【跟踪频率】每日收盘检查价格+每日检查蒋宇飞/群联新观点
+</t>
+      </text>
+    </comment>
+    <comment ref="A45" authorId="0" shapeId="0">
+      <text>
+        <t xml:space="preserve">【标的】佰维存储 688525
+【核心逻辑】科创板存储芯片，纯存储标的。盈亏比3:1。
+【为什么买】长鑫/长江暂时买不到→买产业链上下游→存储涨价直接受益
+【买入条件】等中期选举年大盘跌15%+或单日暴跌5%+或P值回升55%+
+【仓位建议】存储选2-3只分散（总资金12.5%），澜起单独5%
+【跟踪频率】每日收盘检查价格+每日检查蒋宇飞/群联新观点
+</t>
+      </text>
+    </comment>
+    <comment ref="A46" authorId="0" shapeId="0">
+      <text>
+        <t xml:space="preserve">【标的】聚辰股份 688123
+【核心逻辑】SPI NOR Flash，存储芯片概念活跃股。盈亏比3:1。
+【为什么买】长鑫/长江暂时买不到→买产业链上下游→存储涨价直接受益
+【买入条件】等中期选举年大盘跌15%+或单日暴跌5%+或P值回升55%+
+【仓位建议】存储选2-3只分散（总资金12.5%），澜起单独5%
+【跟踪频率】每日收盘检查价格+每日检查蒋宇飞/群联新观点
+</t>
+      </text>
+    </comment>
+    <comment ref="A47" authorId="0" shapeId="0">
+      <text>
+        <t xml:space="preserve">【标的】澜起科技 688008
+【核心逻辑】DDR5内存接口芯片龙头，AI算力→内存带宽→接口芯片量价齐升。盈亏比4:1。
+【为什么买】长鑫/长江暂时买不到→买产业链上下游→存储涨价直接受益
+【买入条件】等中期选举年大盘跌15%+或单日暴跌5%+或P值回升55%+
+【仓位建议】存储选2-3只分散（总资金12.5%），澜起单独5%
+【跟踪频率】每日收盘检查价格+每日检查蒋宇飞/群联新观点
+</t>
+      </text>
+    </comment>
   </commentList>
 </comments>
 </file>
@@ -1863,10 +1966,87 @@
         </is>
       </c>
     </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>存储赛道(5只A股)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>🔴最高优先级</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>P:70%+</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>5条信源交叉验证：群联供给不足+蒋宇飞两长双雄+宋鸿兵摩尔定律终结+周鸿祎内存决定AI+用户AI进化=存储指数增长</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>等中期选举大跌15%+或P值回升55%+</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>中期</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>北京君正300223/兆易创新603986/江波龙301308/佰维688525/聚辰688123</t>
+        </is>
+      </c>
+    </row>
     <row r="40">
       <c r="A40" s="66" t="inlineStr">
         <is>
-          <t>🔥 存储赛道标的（2026-06-03新增）</t>
+          <t>澜起科技(688008)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>🟡存储补充</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>P:55%+</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>DDR5接口芯片龙头，AI算力→内存带宽→量价齐升，与存储逻辑互锁</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>等大跌15%+或P值回升</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>中期</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>盈亏比4:1，AI仓20%</t>
         </is>
       </c>
     </row>
@@ -1908,236 +2088,236 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" t="inlineStr">
+      <c r="A42" s="25" t="inlineStr">
         <is>
           <t>北京君正</t>
         </is>
       </c>
-      <c r="B42" t="inlineStr">
+      <c r="B42" s="25" t="inlineStr">
         <is>
           <t>300223</t>
         </is>
       </c>
-      <c r="C42" t="inlineStr">
+      <c r="C42" s="25" t="inlineStr">
         <is>
           <t>4:1</t>
         </is>
       </c>
-      <c r="D42" t="inlineStr">
+      <c r="D42" s="25" t="inlineStr">
         <is>
           <t>70%+</t>
         </is>
       </c>
-      <c r="E42" t="inlineStr">
+      <c r="E42" s="25" t="inlineStr">
         <is>
           <t>AI仓50%</t>
         </is>
       </c>
-      <c r="F42" t="inlineStr">
+      <c r="F42" s="25" t="inlineStr">
         <is>
           <t>等大跌15%+</t>
         </is>
       </c>
-      <c r="G42" t="inlineStr">
+      <c r="G42" s="25" t="inlineStr">
         <is>
           <t>🔴未建仓</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" t="inlineStr">
+      <c r="A43" s="25" t="inlineStr">
         <is>
           <t>兆易创新</t>
         </is>
       </c>
-      <c r="B43" t="inlineStr">
+      <c r="B43" s="25" t="inlineStr">
         <is>
           <t>603986</t>
         </is>
       </c>
-      <c r="C43" t="inlineStr">
+      <c r="C43" s="25" t="inlineStr">
         <is>
           <t>3.5:1</t>
         </is>
       </c>
-      <c r="D43" t="inlineStr">
+      <c r="D43" s="25" t="inlineStr">
         <is>
           <t>70%+</t>
         </is>
       </c>
-      <c r="E43" t="inlineStr">
+      <c r="E43" s="25" t="inlineStr">
         <is>
           <t>AI仓50%</t>
         </is>
       </c>
-      <c r="F43" t="inlineStr">
+      <c r="F43" s="25" t="inlineStr">
         <is>
           <t>等大跌15%+</t>
         </is>
       </c>
-      <c r="G43" t="inlineStr">
+      <c r="G43" s="25" t="inlineStr">
         <is>
           <t>🔴未建仓</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" t="inlineStr">
+      <c r="A44" s="25" t="inlineStr">
         <is>
           <t>江波龙</t>
         </is>
       </c>
-      <c r="B44" t="inlineStr">
+      <c r="B44" s="25" t="inlineStr">
         <is>
           <t>301308</t>
         </is>
       </c>
-      <c r="C44" t="inlineStr">
+      <c r="C44" s="25" t="inlineStr">
         <is>
           <t>3.5:1</t>
         </is>
       </c>
-      <c r="D44" t="inlineStr">
+      <c r="D44" s="25" t="inlineStr">
         <is>
           <t>70%+</t>
         </is>
       </c>
-      <c r="E44" t="inlineStr">
+      <c r="E44" s="25" t="inlineStr">
         <is>
           <t>AI仓50%</t>
         </is>
       </c>
-      <c r="F44" t="inlineStr">
+      <c r="F44" s="25" t="inlineStr">
         <is>
           <t>等大跌15%+</t>
         </is>
       </c>
-      <c r="G44" t="inlineStr">
+      <c r="G44" s="25" t="inlineStr">
         <is>
           <t>🔴未建仓</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" t="inlineStr">
+      <c r="A45" s="25" t="inlineStr">
         <is>
           <t>佰维存储</t>
         </is>
       </c>
-      <c r="B45" t="inlineStr">
+      <c r="B45" s="25" t="inlineStr">
         <is>
           <t>688525</t>
         </is>
       </c>
-      <c r="C45" t="inlineStr">
+      <c r="C45" s="25" t="inlineStr">
         <is>
           <t>3:1</t>
         </is>
       </c>
-      <c r="D45" t="inlineStr">
+      <c r="D45" s="25" t="inlineStr">
         <is>
           <t>70%+</t>
         </is>
       </c>
-      <c r="E45" t="inlineStr">
+      <c r="E45" s="25" t="inlineStr">
         <is>
           <t>AI仓50%</t>
         </is>
       </c>
-      <c r="F45" t="inlineStr">
+      <c r="F45" s="25" t="inlineStr">
         <is>
           <t>等大跌15%+</t>
         </is>
       </c>
-      <c r="G45" t="inlineStr">
+      <c r="G45" s="25" t="inlineStr">
         <is>
           <t>🔴未建仓</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" t="inlineStr">
+      <c r="A46" s="25" t="inlineStr">
         <is>
           <t>聚辰股份</t>
         </is>
       </c>
-      <c r="B46" t="inlineStr">
+      <c r="B46" s="25" t="inlineStr">
         <is>
           <t>688123</t>
         </is>
       </c>
-      <c r="C46" t="inlineStr">
+      <c r="C46" s="25" t="inlineStr">
         <is>
           <t>3:1</t>
         </is>
       </c>
-      <c r="D46" t="inlineStr">
+      <c r="D46" s="25" t="inlineStr">
         <is>
           <t>70%+</t>
         </is>
       </c>
-      <c r="E46" t="inlineStr">
+      <c r="E46" s="25" t="inlineStr">
         <is>
           <t>AI仓50%</t>
         </is>
       </c>
-      <c r="F46" t="inlineStr">
+      <c r="F46" s="25" t="inlineStr">
         <is>
           <t>等大跌15%+</t>
         </is>
       </c>
-      <c r="G46" t="inlineStr">
+      <c r="G46" s="25" t="inlineStr">
         <is>
           <t>🔴未建仓</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" t="inlineStr">
+      <c r="A47" s="25" t="inlineStr">
         <is>
           <t>澜起科技</t>
         </is>
       </c>
-      <c r="B47" t="inlineStr">
+      <c r="B47" s="25" t="inlineStr">
         <is>
           <t>688008</t>
         </is>
       </c>
-      <c r="C47" t="inlineStr">
+      <c r="C47" s="25" t="inlineStr">
         <is>
           <t>4:1</t>
         </is>
       </c>
-      <c r="D47" t="inlineStr">
+      <c r="D47" s="25" t="inlineStr">
         <is>
           <t>55%+</t>
         </is>
       </c>
-      <c r="E47" t="inlineStr">
+      <c r="E47" s="25" t="inlineStr">
         <is>
           <t>AI仓20%</t>
         </is>
       </c>
-      <c r="F47" t="inlineStr">
+      <c r="F47" s="25" t="inlineStr">
         <is>
           <t>等大跌15%+</t>
         </is>
       </c>
-      <c r="G47" t="inlineStr">
+      <c r="G47" s="25" t="inlineStr">
         <is>
           <t>🟡观察中</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" t="inlineStr">
+      <c r="A48" s="25" t="inlineStr">
         <is>
           <t>📌 AI仓位目标：总资金25%（存储12.5%+澜起5%+芯片ETF持有+凯盛2.5%观察）</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" t="inlineStr">
+      <c r="A49" s="25" t="inlineStr">
         <is>
           <t>📌 核心逻辑：长鑫/长江暂时买不到→买产业链上下游→存储缺货涨价贯穿2026全年</t>
         </is>

--- a/持仓贝叶斯跟踪.xlsx
+++ b/持仓贝叶斯跟踪.xlsx
@@ -967,6 +967,21 @@
 P值: 58%(估)，有效P=58%-6pp=52%</t>
       </text>
     </comment>
+    <comment ref="A35" authorId="0" shapeId="0">
+      <text>
+        <t xml:space="preserve">【来源】蒋宇飞抖音视频（2026-05-25）"未来5-10年的黄金赛道，深度拆解玻璃基板的万亿机遇"
+【信源评估】蒋宇飞⭐⭐⭐高置信度（有产业实操经验，多次验证预测准确）
+【逻辑链】
+摩尔定律终结→先进封装崛起→玻璃基板替代有机基板
+ → 凯盛科技=国内玻璃基板龙头
+ → 5-10年赛道，2028年大规模应用
+【P值估算】基于单信源（蒋宇飞）→ P≈55%（低于存储赛道的70%+）
+→ 信源数量不足，确定性打折
+【对持仓影响】🟡 观察仓，优先级低于存储主线
+【操作建议】盈亏比2.5:1，AI仓10%（总资金2.5%观察仓）。等回调到¥18-18.5再进。P值待定，需更多信源验证。
+</t>
+      </text>
+    </comment>
     <comment ref="A37" authorId="0" shapeId="0">
       <text>
         <t>信息源：东方财富+新浪财经2026-06-02
@@ -1967,42 +1982,42 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" t="inlineStr">
+      <c r="A39" s="25" t="inlineStr">
         <is>
           <t>存储赛道(5只A股)</t>
         </is>
       </c>
-      <c r="B39" t="inlineStr">
+      <c r="B39" s="25" t="inlineStr">
         <is>
           <t>🔴最高优先级</t>
         </is>
       </c>
-      <c r="C39" t="inlineStr">
+      <c r="C39" s="25" t="inlineStr">
         <is>
           <t>P:70%+</t>
         </is>
       </c>
-      <c r="D39" t="inlineStr">
+      <c r="D39" s="25" t="inlineStr">
         <is>
           <t>5条信源交叉验证：群联供给不足+蒋宇飞两长双雄+宋鸿兵摩尔定律终结+周鸿祎内存决定AI+用户AI进化=存储指数增长</t>
         </is>
       </c>
-      <c r="E39" t="inlineStr">
+      <c r="E39" s="25" t="inlineStr">
         <is>
           <t>等中期选举大跌15%+或P值回升55%+</t>
         </is>
       </c>
-      <c r="F39" t="inlineStr">
+      <c r="F39" s="25" t="inlineStr">
         <is>
           <t>中期</t>
         </is>
       </c>
-      <c r="G39" t="inlineStr">
+      <c r="G39" s="25" t="inlineStr">
         <is>
           <t>2026-06-03</t>
         </is>
       </c>
-      <c r="H39" t="inlineStr">
+      <c r="H39" s="25" t="inlineStr">
         <is>
           <t>北京君正300223/兆易创新603986/江波龙301308/佰维688525/聚辰688123</t>
         </is>
@@ -2014,37 +2029,37 @@
           <t>澜起科技(688008)</t>
         </is>
       </c>
-      <c r="B40" t="inlineStr">
+      <c r="B40" s="25" t="inlineStr">
         <is>
           <t>🟡存储补充</t>
         </is>
       </c>
-      <c r="C40" t="inlineStr">
+      <c r="C40" s="25" t="inlineStr">
         <is>
           <t>P:55%+</t>
         </is>
       </c>
-      <c r="D40" t="inlineStr">
+      <c r="D40" s="25" t="inlineStr">
         <is>
           <t>DDR5接口芯片龙头，AI算力→内存带宽→量价齐升，与存储逻辑互锁</t>
         </is>
       </c>
-      <c r="E40" t="inlineStr">
+      <c r="E40" s="25" t="inlineStr">
         <is>
           <t>等大跌15%+或P值回升</t>
         </is>
       </c>
-      <c r="F40" t="inlineStr">
+      <c r="F40" s="25" t="inlineStr">
         <is>
           <t>中期</t>
         </is>
       </c>
-      <c r="G40" t="inlineStr">
+      <c r="G40" s="25" t="inlineStr">
         <is>
           <t>2026-06-03</t>
         </is>
       </c>
-      <c r="H40" t="inlineStr">
+      <c r="H40" s="25" t="inlineStr">
         <is>
           <t>盈亏比4:1，AI仓20%</t>
         </is>

--- a/持仓贝叶斯跟踪.xlsx
+++ b/持仓贝叶斯跟踪.xlsx
@@ -1239,6 +1239,38 @@
 付鹏观点：存储=AI基建是逻辑推演，非价格/数据确认</t>
       </text>
     </comment>
+    <comment ref="A13" authorId="0" shapeId="0">
+      <text>
+        <t>【来源】宋鸿兵抖音6/3 09:00《摩尔定律物理+经济双重极限》+ 蒋宇飞多条
+【逻辑链】宋鸿兵：摩尔定律走到物理极限(2nm以下成本飙升15倍)+经济极限(7nm以下技术红利从普惠变垄断)→芯片行业范式转换→堆叠/存储成为新方向。蒋宇飞交叉验证：韬定律=折叠堆叠，2.5D市场600亿→翻好几倍
+【当前状态】新叙事：芯片从摩尔定律时代进入堆叠时代
+【对持仓影响】芯片+1pp(事实信号)，+2pp(虚P跨博主共识)</t>
+      </text>
+    </comment>
+    <comment ref="B13" authorId="0" shapeId="0">
+      <text>
+        <t>【来源】宋鸿兵抖音6/2《油价末日警告》+ 雪佛龙高管原话 + 埃克森高管原话
+【逻辑链】宋鸿兵引用两大石油巨头高管：霍尔木兹封锁3个月→OECD石油库存6月触红线→油价飙升→通胀失控→美联储无法降息。雪佛龙：石油供应缺口扩大。埃克森：能源转型加速
+【当前状态】升级：从地缘冲突升级为全球能源危机
+【对持仓影响】电池+4pp(油价危机→储能/电动车刚需)</t>
+      </text>
+    </comment>
+    <comment ref="C13" authorId="0" shapeId="0">
+      <text>
+        <t>【来源】宋鸿兵+雪佛龙+埃克森：油价危机传导链
+【逻辑链】油价飙升→通胀上行→美联储被迫维持高利率/甚至加息→美债收益率走高→港股估值受压→恒科下行
+【当前状态】利率压制恒科逻辑强化
+【对持仓影响】恒科-3pp</t>
+      </text>
+    </comment>
+    <comment ref="G13" authorId="0" shapeId="0">
+      <text>
+        <t>【来源】宋鸿兵利率分析+宏观传导
+【逻辑链】油价危机→通胀上行→美联储维持高利率→银行净息差受压→去杠杆周期中银行资产质量恶化
+【当前状态】利率上行对银行不利
+【对持仓影响】银行-1pp</t>
+      </text>
+    </comment>
     <comment ref="A14" authorId="0" shapeId="0">
       <text>
         <t>【来源】宋鸿兵抖音6/3 18:35视频《美伊谈判：决胜负要看经济战》
@@ -3028,35 +3060,35 @@
       </c>
     </row>
     <row r="14" ht="13.5" customHeight="1" s="40">
-      <c r="A14" t="inlineStr">
+      <c r="A14" s="39" t="inlineStr">
         <is>
           <t>2026-06-03
 +0pp
 【事实】宋鸿兵美伊谈判：经济战替代军事战，时间站在伊朗一边→芯片逻辑不变</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B14" s="39" t="inlineStr">
         <is>
           <t>2026-06-03
 +2pp
 【虚P】宋鸿兵：美伊经济战→油价长期高位→能源转型加速→电池长期利好</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="C14" s="39" t="inlineStr">
         <is>
           <t>2026-06-03
 -1pp
 【虚P】宋鸿兵：美伊久拖不决→美债收益率上行→压制港股</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="D14" s="39" t="inlineStr">
         <is>
           <t>2026-06-03
 +1pp
 【事实】伊娃：仔猪价格硬挺420元→猪企不恐慌性淘汰→供给收缩有序</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
+      <c r="G14" s="39" t="inlineStr">
         <is>
           <t>2026-06-03
 +0pp

--- a/持仓贝叶斯跟踪.xlsx
+++ b/持仓贝叶斯跟踪.xlsx
@@ -2590,10 +2590,10 @@
         <is>
           <t>成本¥3695
 净值3.6875
-P:41%
+P:46%
 虚P+4pp
 利率折价-6pp
-有效P:35%
+有效P:40%
 下行:25% 确定性:30% 溢价:50%
 盈亏比:1.2:1
 决策:观望</t>
@@ -2603,10 +2603,10 @@
         <is>
           <t>成本¥6811
 净值1.8418
-P:67%
+P:73%
 虚P无
 利率折价-6pp
-有效P:61%
+有效P:67%
 下行:20% 确定性:25% 溢价:40%
 盈亏比:2.3:1
 决策:持有</t>
@@ -2616,10 +2616,10 @@
         <is>
           <t>成本¥4722
 净值0.6619
-P:38%
+P:34%
 虚P无
 利率折价-6pp
-有效P:32%
+有效P:28%
 下行:30% 确定性:15% 溢价:30%
 盈亏比:0.5:1
 决策:不干</t>
@@ -2629,10 +2629,10 @@
         <is>
           <t>成本¥3732
 净值0.7545
-P:56%
+P:65%
 虚P+4pp
 利率折价0pp
-有效P:56%
+有效P:65%
 下行:20% 确定性:35% 溢价:20%
 盈亏比:1.8:1
 决策:观望</t>
@@ -2668,10 +2668,10 @@
         <is>
           <t>成本¥0
 净值1.6291
-P:50%
+P:47%
 虚P-2pp
 利率折价0pp
-有效P:50%
+有效P:47%
 下行:10% 确定性:10% 溢价:5%
 盈亏比:1.5:1
 决策:监控</t>

--- a/持仓贝叶斯跟踪.xlsx
+++ b/持仓贝叶斯跟踪.xlsx
@@ -2509,7 +2509,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:J15"/>
+  <dimension ref="A1:J16"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="10.4921875" defaultRowHeight="12.75" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="32" customWidth="1" style="39" min="1" max="8"/>
@@ -3097,7 +3097,48 @@
       </c>
     </row>
     <row r="15" ht="13.5" customHeight="1" s="40"/>
-    <row r="16" ht="13.5" customHeight="1" s="40"/>
+    <row r="16" ht="13.5" customHeight="1" s="40">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>拟合❌0分</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>拟合✅97分</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>拟合✅75分</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>拟合✅95分</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>拟合⚠️样本少</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>拟合⚠️样本少</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>拟合👍53分</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>无数据</t>
+        </is>
+      </c>
+    </row>
     <row r="17" ht="13.5" customHeight="1" s="40"/>
     <row r="18" ht="13.5" customHeight="1" s="40"/>
     <row r="19" ht="13.5" customHeight="1" s="40"/>

--- a/持仓贝叶斯跟踪.xlsx
+++ b/持仓贝叶斯跟踪.xlsx
@@ -9,6 +9,7 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总看板" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet2" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="拟合分析" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1" refMode="A1" iterate="0" iterateCount="100" iterateDelta="0.0001"/>
@@ -2594,6 +2595,7 @@
 虚P+4pp
 利率折价-6pp
 有效P:40%
+拟合❌0分
 下行:25% 确定性:30% 溢价:50%
 盈亏比:1.2:1
 决策:观望</t>
@@ -2607,6 +2609,7 @@
 虚P无
 利率折价-6pp
 有效P:67%
+拟合✅97分
 下行:20% 确定性:25% 溢价:40%
 盈亏比:2.3:1
 决策:持有</t>
@@ -2620,6 +2623,7 @@
 虚P无
 利率折价-6pp
 有效P:28%
+拟合✅75分
 下行:30% 确定性:15% 溢价:30%
 盈亏比:0.5:1
 决策:不干</t>
@@ -2633,6 +2637,7 @@
 虚P+4pp
 利率折价0pp
 有效P:65%
+拟合✅95分
 下行:20% 确定性:35% 溢价:20%
 盈亏比:1.8:1
 决策:观望</t>
@@ -2646,6 +2651,7 @@
 虚P无
 利率折价-4pp
 有效P:40%
+拟合⚠️样本少
 下行:15% 确定性:20% 溢价:30%
 盈亏比:2.0:1
 决策:持有</t>
@@ -2659,6 +2665,7 @@
 虚P无
 利率折价-4pp
 有效P:39%
+拟合⚠️样本少
 下行:20% 确定性:25% 溢价:35%
 盈亏比:1.8:1
 决策:观望</t>
@@ -2672,6 +2679,7 @@
 虚P-2pp
 利率折价0pp
 有效P:47%
+拟合👍53分
 下行:10% 确定性:10% 溢价:5%
 盈亏比:1.5:1
 决策:监控</t>
@@ -2684,6 +2692,7 @@
 P:None%
 利率折价-4pp
 有效P:-%
+无数据
 下行:30% 确定性:20% 溢价:40%
 盈亏比:0.7:1
 决策:不干</t>
@@ -2755,211 +2764,226 @@
     <row r="5" ht="45" customHeight="1" s="40">
       <c r="A5" s="69" t="inlineStr">
         <is>
+          <t>2026-06-03
++3pp
+【+1pp】宋鸿兵：摩尔定律物理+经济双重极限
+【+2pp】【虚P】堆叠崛起
+【+0pp】宋鸿兵美伊谈判：经济战替代军事战→芯片逻辑不变</t>
+        </is>
+      </c>
+      <c r="B5" s="57" t="inlineStr">
+        <is>
+          <t>2026-06-03
++6pp
+【+4pp】【虚P】宋鸿兵+雪佛龙：油价危机OECD 6月触红线
+【+2pp】【虚P】美伊经济战→能源转型加速→电池长期利好</t>
+        </is>
+      </c>
+      <c r="C5" s="57" t="inlineStr">
+        <is>
+          <t>2026-06-03
+-4pp
+【-3pp】【虚P】油价危机→利率压制恒科
+【-1pp】【虚P】美伊久拖不决→美债收益率上行→压制港股</t>
+        </is>
+      </c>
+      <c r="D5" s="69" t="inlineStr">
+        <is>
+          <t>2026-06-03
++1pp
+【事实】伊娃：仔猪价格硬挺420元→供给收缩有序</t>
+        </is>
+      </c>
+      <c r="E5" s="39" t="inlineStr">
+        <is>
+          <t>2026-05-22
++4pp
+AI铜需求爆发 + 资金回流</t>
+        </is>
+      </c>
+      <c r="F5" s="39" t="inlineStr">
+        <is>
+          <t>2026-05-29
++1pp
+闭眼看世界：俄乌升级→地缘风险溢价</t>
+        </is>
+      </c>
+      <c r="G5" s="69" t="inlineStr">
+        <is>
+          <t>2026-06-03
+-1pp
+【-1pp】【虚P】利率上行不利净息差
+【+0pp】【虚P】欧洲央行：黄金替代美债成第一大储备</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="45" customHeight="1" s="40">
+      <c r="A6" s="70" t="inlineStr">
+        <is>
           <t>2026-06-02
 +2pp
 【虚P】蒋宇飞AI基建10年+国产算力长城</t>
         </is>
       </c>
-      <c r="B5" s="57" t="inlineStr">
+      <c r="B6" s="71" t="inlineStr">
         <is>
           <t>2026-06-02
 +2pp
 维力能储能全球第二+锂电全链</t>
         </is>
       </c>
-      <c r="C5" s="57" t="inlineStr">
+      <c r="C6" s="72" t="inlineStr">
         <is>
           <t>2026-06-02
 -3pp
 付鹏恒科套利闭环不可持续</t>
         </is>
       </c>
-      <c r="D5" s="69" t="inlineStr">
+      <c r="D6" s="70" t="inlineStr">
         <is>
           <t>2026-06-02
 +4pp
-【虚P】🔴跨博主：美国猪周期启示+17/18亏损+行业关注+厄尔尼诺</t>
-        </is>
-      </c>
-      <c r="G5" s="69" t="inlineStr">
+【虚P】美国猪周期启示+17/18亏损+行业关注+厄尔尼诺</t>
+        </is>
+      </c>
+      <c r="E6" s="70" t="inlineStr">
+        <is>
+          <t>2026-05-19
+-2pp
+岩松笔记 + 付鹏对冲：逻辑分类修正</t>
+        </is>
+      </c>
+      <c r="F6" s="70" t="inlineStr">
+        <is>
+          <t>2026-05-20
+-3pp
+有色金属持续走弱+美债压制</t>
+        </is>
+      </c>
+      <c r="G6" s="72" t="inlineStr">
         <is>
           <t>2026-06-02
 -2pp
 【虚P】去杠杆周期不利</t>
         </is>
       </c>
-    </row>
-    <row r="6" ht="45" customHeight="1" s="40">
-      <c r="A6" s="70" t="inlineStr">
+      <c r="H6" s="73" t="n"/>
+    </row>
+    <row r="7" ht="45" customHeight="1" s="40">
+      <c r="A7" s="74" t="inlineStr">
         <is>
           <t>2026-05-28
 +1pp
 Schiff美债熊市 + 周鸿祎"内存决定高度"</t>
         </is>
       </c>
-      <c r="B6" s="71" t="inlineStr">
+      <c r="B7" s="75" t="inlineStr">
         <is>
           <t>2026-05-21
 +0pp
-中科院固态锂电池突破（逻辑簇强化，不作概率调整）</t>
-        </is>
-      </c>
-      <c r="C6" s="72" t="inlineStr">
+中科院固态锂电池突破（逻辑簇强化）</t>
+        </is>
+      </c>
+      <c r="C7" s="76" t="inlineStr">
         <is>
           <t>2026-05-26
 -4pp
 恒生三巨头财报验证：非价值陷阱确认</t>
         </is>
       </c>
-      <c r="D6" s="70" t="inlineStr">
+      <c r="D7" s="75" t="inlineStr">
         <is>
           <t>2026-05-26
 +5pp
-✅ 伊娃读财报18期：17/18猪企亏损，加速去产能确认</t>
-        </is>
-      </c>
-      <c r="E6" s="70" t="inlineStr">
+伊娃读财报18期：17/18猪企亏损，加速去产能确认</t>
+        </is>
+      </c>
+      <c r="E7" s="76" t="inlineStr">
+        <is>
+          <t>2026-05-15
+-8pp
+有色金属板块持续资金净流出</t>
+        </is>
+      </c>
+      <c r="F7" s="76" t="inlineStr">
+        <is>
+          <t>2026-05-19
+-5pp
+岩松笔记：资源非长期抗通胀→HALO联动风险</t>
+        </is>
+      </c>
+      <c r="G7" s="75" t="inlineStr">
         <is>
           <t>2026-05-22
-+4pp
-有色金属+3.63%：AI铜需求爆发 + 资金回流</t>
-        </is>
-      </c>
-      <c r="F6" s="70" t="inlineStr">
-        <is>
-          <t>2026-05-29
-+1pp
-闭眼看世界：俄乌升级→地缘风险溢价</t>
-        </is>
-      </c>
-      <c r="G6" s="72" t="inlineStr">
-        <is>
-          <t>2026-05-22
--3pp
-无知半人：前4月住户贷款狂减4902亿</t>
-        </is>
-      </c>
-      <c r="H6" s="73" t="n"/>
-    </row>
-    <row r="7" ht="45" customHeight="1" s="40">
-      <c r="A7" s="74" t="inlineStr">
++0pp
+【-3pp】无知半人：住户贷款狂减4902亿
+【+3pp】凯文·沃什就任美联储主席</t>
+        </is>
+      </c>
+      <c r="H7" s="73" t="n"/>
+    </row>
+    <row r="8" ht="45" customHeight="1" s="40">
+      <c r="A8" s="70" t="inlineStr">
         <is>
           <t>2026-05-27
 -2pp
-【已作废】🔥 闭眼看世界：美军轰炸伊朗→霍尔木兹P'作废</t>
-        </is>
-      </c>
-      <c r="B7" s="75" t="inlineStr">
+【已作废】美军轰炸伊朗→霍尔木兹P'作废</t>
+        </is>
+      </c>
+      <c r="B8" s="70" t="inlineStr">
         <is>
           <t>2026-05-20
 +1pp
 光储旺季+美债压制</t>
         </is>
       </c>
-      <c r="C7" s="76" t="inlineStr">
+      <c r="C8" s="72" t="inlineStr">
         <is>
           <t>2026-05-20
 -3pp
 多空交织：低开高走验证磨底 + 美债5.18%压制</t>
         </is>
       </c>
-      <c r="D7" s="75" t="inlineStr">
+      <c r="D8" s="72" t="inlineStr">
         <is>
           <t>2026-05-24
-+5pp
-霍尔木兹通航（+4pp 未入链修正）</t>
-        </is>
-      </c>
-      <c r="E7" s="76" t="inlineStr">
-        <is>
-          <t>2026-05-19
--2pp
-🔴 岩松笔记 + 🟢 付鹏对冲：逻辑分类修正</t>
-        </is>
-      </c>
-      <c r="F7" s="76" t="inlineStr">
-        <is>
-          <t>2026-05-20
--3pp
-有色金属持续走弱+美债压制</t>
-        </is>
-      </c>
-      <c r="G7" s="75" t="inlineStr">
-        <is>
-          <t>2026-05-22
-+3pp
-追加：凯文·沃什就任美联储主席</t>
-        </is>
-      </c>
-      <c r="H7" s="73" t="n"/>
-    </row>
-    <row r="8" ht="45" customHeight="1" s="40">
-      <c r="A8" s="70" t="inlineStr">
++9pp
+【+5pp】霍尔木兹通航
+【+4pp】霍尔木兹通航修正</t>
+        </is>
+      </c>
+      <c r="E8" s="72" t="n"/>
+      <c r="F8" s="72" t="n"/>
+      <c r="G8" s="73" t="n"/>
+      <c r="H8" s="73" t="n"/>
+    </row>
+    <row r="9" ht="45" customHeight="1" s="40">
+      <c r="A9" s="76" t="inlineStr">
         <is>
           <t>2026-05-25
 +1pp
-蒋宇飞：深度拆解玻璃基板的万亿机遇</t>
-        </is>
-      </c>
-      <c r="B8" s="70" t="inlineStr">
+蒋宇飞：玻璃基板的万亿机遇</t>
+        </is>
+      </c>
+      <c r="B9" s="75" t="inlineStr">
         <is>
           <t>2026-05-19
 +5pp
 碳酸锂跌价+巴克莱看多</t>
         </is>
       </c>
-      <c r="C8" s="72" t="inlineStr">
+      <c r="C9" s="73" t="inlineStr">
         <is>
           <t>2026-05-19
 -2pp
 付鹏×2：港股结构性偏弱 + 风险偏好极值 + 古都闲云社消疲弱</t>
         </is>
       </c>
-      <c r="D8" s="72" t="inlineStr">
+      <c r="D9" s="76" t="inlineStr">
         <is>
           <t>2026-05-22
 -2pp
 无知半人：住户贷款狂减4902亿</t>
-        </is>
-      </c>
-      <c r="E8" s="72" t="inlineStr">
-        <is>
-          <t>2026-05-15
--8pp
-→05-20 有色金属板块持续资金净流出</t>
-        </is>
-      </c>
-      <c r="F8" s="72" t="inlineStr">
-        <is>
-          <t>2026-05-19
--5pp
-🔴 岩松笔记：资源非长期抗通胀→HALO联动风险</t>
-        </is>
-      </c>
-      <c r="G8" s="73" t="n"/>
-      <c r="H8" s="73" t="n"/>
-    </row>
-    <row r="9" ht="45" customHeight="1" s="40">
-      <c r="A9" s="76" t="inlineStr">
-        <is>
-          <t>2026-05-22
--3pp
-宋鸿兵利率风暴（但斌预警已删除：券商观点不计）</t>
-        </is>
-      </c>
-      <c r="B9" s="75" t="inlineStr">
-        <is>
-          <t>2026-05-15
-+1pp
-机构研报确认景气上行</t>
-        </is>
-      </c>
-      <c r="C9" s="73" t="n"/>
-      <c r="D9" s="76" t="inlineStr">
-        <is>
-          <t>2026-05-19
--2pp
-古都闲云：社消数据疲弱</t>
         </is>
       </c>
       <c r="E9" s="73" t="n"/>
@@ -2971,19 +2995,26 @@
       <c r="A10" s="72" t="inlineStr">
         <is>
           <t>2026-05-22
--6pp
-凯文·沃什就任美联储主席</t>
+-9pp
+【-3pp】宋鸿兵利率风暴
+【-6pp】凯文·沃什就任美联储主席</t>
         </is>
       </c>
       <c r="B10" s="70" t="inlineStr">
         <is>
-          <t>2026-05-14
-+3pp
-电池ETF涨2.73%+多重利好</t>
+          <t>2026-05-15
++1pp
+机构研报确认景气上行</t>
         </is>
       </c>
       <c r="C10" s="73" t="n"/>
-      <c r="D10" s="73" t="n"/>
+      <c r="D10" s="73" t="inlineStr">
+        <is>
+          <t>2026-05-19
+-2pp
+古都闲云：社消数据疲弱</t>
+        </is>
+      </c>
       <c r="E10" s="73" t="n"/>
       <c r="F10" s="73" t="n"/>
       <c r="G10" s="73" t="n"/>
@@ -2999,9 +3030,9 @@
       </c>
       <c r="B11" s="75" t="inlineStr">
         <is>
-          <t>2026-05-13
-+5pp
-特朗普访华+恩捷40亿扩产</t>
+          <t>2026-05-14
++3pp
+电池ETF涨2.73%+多重利好</t>
         </is>
       </c>
       <c r="C11" s="73" t="n"/>
@@ -3019,7 +3050,13 @@
 【虚P】付鹏：存储=AI基建（观点→共识信号）</t>
         </is>
       </c>
-      <c r="B12" s="73" t="n"/>
+      <c r="B12" s="73" t="inlineStr">
+        <is>
+          <t>2026-05-13
++5pp
+特朗普访华+恩捷40亿扩产</t>
+        </is>
+      </c>
       <c r="C12" s="73" t="n"/>
       <c r="D12" s="73" t="n"/>
       <c r="E12" s="73" t="n"/>
@@ -3030,114 +3067,103 @@
     <row r="13" ht="75.34999999999999" customHeight="1" s="40">
       <c r="A13" s="49" t="inlineStr">
         <is>
-          <t>2026-06-03
-+1pp
-【事实】宋鸿兵：摩尔定律物理+经济双重极限
-+2pp
-【虚P】🔴跨博主：堆叠崛起</t>
+          <t>拟合❌0分</t>
         </is>
       </c>
       <c r="B13" s="49" t="inlineStr">
         <is>
-          <t>2026-06-03
-+4pp
-【虚P】宋鸿兵+雪佛龙+埃克森：油价危机OECD 6月触红线</t>
+          <t>拟合✅97分</t>
         </is>
       </c>
       <c r="C13" s="49" t="inlineStr">
         <is>
-          <t>2026-06-03
--3pp
-【虚P】油价危机→利率压制恒科</t>
+          <t>拟合✅75分</t>
+        </is>
+      </c>
+      <c r="D13" s="39" t="inlineStr">
+        <is>
+          <t>拟合✅95分</t>
+        </is>
+      </c>
+      <c r="E13" s="39" t="inlineStr">
+        <is>
+          <t>拟合⚠️样本少</t>
+        </is>
+      </c>
+      <c r="F13" s="39" t="inlineStr">
+        <is>
+          <t>拟合⚠️样本少</t>
         </is>
       </c>
       <c r="G13" s="49" t="inlineStr">
         <is>
-          <t>2026-06-03
--1pp
-【虚P】利率上行不利净息差</t>
+          <t>拟合👍53分</t>
+        </is>
+      </c>
+      <c r="H13" s="39" t="inlineStr">
+        <is>
+          <t>无数据</t>
         </is>
       </c>
     </row>
     <row r="14" ht="13.5" customHeight="1" s="40">
-      <c r="A14" s="39" t="inlineStr">
-        <is>
-          <t>2026-06-03
-+0pp
-【事实】宋鸿兵美伊谈判：经济战替代军事战，时间站在伊朗一边→芯片逻辑不变</t>
-        </is>
-      </c>
-      <c r="B14" s="39" t="inlineStr">
-        <is>
-          <t>2026-06-03
-+2pp
-【虚P】宋鸿兵：美伊经济战→油价长期高位→能源转型加速→电池长期利好</t>
-        </is>
-      </c>
-      <c r="C14" s="39" t="inlineStr">
-        <is>
-          <t>2026-06-03
--1pp
-【虚P】宋鸿兵：美伊久拖不决→美债收益率上行→压制港股</t>
-        </is>
-      </c>
-      <c r="D14" s="39" t="inlineStr">
-        <is>
-          <t>2026-06-03
-+1pp
-【事实】伊娃：仔猪价格硬挺420元→猪企不恐慌性淘汰→供给收缩有序</t>
-        </is>
-      </c>
-      <c r="G14" s="39" t="inlineStr">
-        <is>
-          <t>2026-06-03
-+0pp
-【虚P】环中星鉴：欧洲央行称黄金替代美债成第一大储备资产(27%vs22%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="13.5" customHeight="1" s="40"/>
+      <c r="A14" s="39" t="n"/>
+      <c r="B14" s="39" t="n"/>
+      <c r="C14" s="39" t="n"/>
+      <c r="D14" s="39" t="n"/>
+      <c r="G14" s="39" t="n"/>
+    </row>
+    <row r="15" ht="13.5" customHeight="1" s="40">
+      <c r="A15" s="39" t="inlineStr">
+        <is>
+          <t>❌0分 ρ=-0.676</t>
+        </is>
+      </c>
+      <c r="B15" s="39" t="inlineStr">
+        <is>
+          <t>✅97分 ρ=+0.966</t>
+        </is>
+      </c>
+      <c r="C15" s="39" t="inlineStr">
+        <is>
+          <t>✅75分 ρ=+0.754</t>
+        </is>
+      </c>
+      <c r="D15" s="39" t="inlineStr">
+        <is>
+          <t>✅95分 ρ=+0.955</t>
+        </is>
+      </c>
+      <c r="E15" s="39" t="inlineStr">
+        <is>
+          <t>⚠️样本少</t>
+        </is>
+      </c>
+      <c r="F15" s="39" t="inlineStr">
+        <is>
+          <t>⚠️样本少</t>
+        </is>
+      </c>
+      <c r="G15" s="39" t="inlineStr">
+        <is>
+          <t>👍53分 ρ=+0.530</t>
+        </is>
+      </c>
+      <c r="H15" s="39" t="inlineStr">
+        <is>
+          <t>无数据</t>
+        </is>
+      </c>
+    </row>
     <row r="16" ht="13.5" customHeight="1" s="40">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>拟合❌0分</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>拟合✅97分</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>拟合✅75分</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>拟合✅95分</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>拟合⚠️样本少</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>拟合⚠️样本少</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>拟合👍53分</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>无数据</t>
-        </is>
-      </c>
+      <c r="A16" s="39" t="n"/>
+      <c r="B16" s="39" t="n"/>
+      <c r="C16" s="39" t="n"/>
+      <c r="D16" s="39" t="n"/>
+      <c r="E16" s="39" t="n"/>
+      <c r="F16" s="39" t="n"/>
+      <c r="G16" s="39" t="n"/>
+      <c r="H16" s="39" t="n"/>
     </row>
     <row r="17" ht="13.5" customHeight="1" s="40"/>
     <row r="18" ht="13.5" customHeight="1" s="40"/>
@@ -3172,4 +3198,385 @@
   </headerFooter>
   <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H22"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>P值vs价格拟合分析 (Spearman秩相关) 2026-06-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>持仓</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>代码</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>拟合分</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Spearman ρ</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>p值</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>样本数</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>评级</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>信源建议</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>电池</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>009759</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>97</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.966</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" t="n">
+        <v>9</v>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>✅优秀</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>信源加分</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>养殖</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>008765</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>95</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.955</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="F4" t="n">
+        <v>7</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>✅优秀</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>信源加分</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>恒科</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>009854</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>75</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.754</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.08400000000000001</v>
+      </c>
+      <c r="F5" t="n">
+        <v>6</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>✅优秀</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>信源加分</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>银行</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>012888</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>53</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.358</v>
+      </c>
+      <c r="F6" t="n">
+        <v>5</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>👍良好</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>信源保持</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>稀金</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>008907</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>50</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.667</v>
+      </c>
+      <c r="F7" t="n">
+        <v>3</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>⚠️样本不足</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>需积累</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>有色</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>008826</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0.667</v>
+      </c>
+      <c r="F8" t="n">
+        <v>3</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>⚠️样本不足</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>需积累</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>芯片</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>020628</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" t="n">
+        <v>-0.676</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.022</v>
+      </c>
+      <c r="F9" t="n">
+        <v>11</v>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>❌差</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>信源减分/替换</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>方法说明：</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>1. Spearman秩相关：衡量P值累计趋势与价格累计趋势的单调一致性</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2. 允许非线性、允许滞后、不要求同一天同向</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>3. 正值=同向拟合，负值=反向不拟合</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>4. p值&lt;0.05=统计显著</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>5. 样本&lt;4统计不可靠，需积累更多事件</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>关键发现：</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>1. 电池/养殖拟合极好(95-97分)，信源质量可靠</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2. 恒科75分不错，P值偏空价格也确实跌了</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>3. 芯片0分最差(ρ=-0.676,p=0.022显著)，P值一路降但价格先涨后跌V型，信源信息面和实际走势有系统性偏差</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>4. 有色/稀金仅3个事件，统计不可靠，继续积累</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:H1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/持仓贝叶斯跟踪.xlsx
+++ b/持仓贝叶斯跟踪.xlsx
@@ -342,7 +342,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="78">
+  <cellXfs count="80">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -570,6 +570,12 @@
     </xf>
     <xf numFmtId="0" fontId="22" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -1313,6 +1319,27 @@
 【逻辑链】欧洲央行报告：黄金占全球官方储备27%首次超越美债22%→去美元化加速→长期利好黄金/有色
 【当前状态】新叙事：储备资产格局历史性转变
 【对持仓影响】有色/稀有金属长期叙事强化，但短期P值不变（已是虚P高位）</t>
+      </text>
+    </comment>
+    <comment ref="B16" authorId="0" shapeId="0">
+      <text>
+        <t>【来源】知乎'怎么看待2026年6月3日A股趋势'高赞回答（94个回答，30万+浏览）
+曹多鱼(304赞)：301关税+欧盟贸易战+对外投资新规=国际收支平衡断裂，中欧美三方联动，电动车出口欧洲38%/光伏42%，美欧吃掉新三样半壁江山，转口贸易路越来越窄
+Deep Van(372赞)：NVDA站台Marvell，NVLink Fusion架构，硅光子技术，AI基建继续扩张但偏海外
+MR Dang：农业十五五规划，利多养殖
+【联动结论】出口端被堵+资本端管死=出海逻辑系统性打断。短期利空电池/有色/恒科/芯片，利多养殖（内需+政策）。AI基建利多但主要利好海外标的（Marvell/NVDA），A股芯片受益有限。
+【P值调整】芯片-2pp/电池-8pp/恒科-5pp/养殖+5pp/有色-5pp/稀金-3pp</t>
+      </text>
+    </comment>
+    <comment ref="B19" authorId="0" shapeId="0">
+      <text>
+        <t>【来源】孙宇晨通过昌健胡说抖音传播，2026-06-03
+【核心观点】孙宇晨明确说"未来就是核电"，押注10亿美元看物理AI
+【10年维度】这不是短期题材，是10年维度的长期范式
+【逻辑链】AI算力指数增长→数据中心电力需求暴增→核电是唯一能稳定供能的清洁能源
+【互锁验证】Sereneity盯材料/Leopold盯电力土地/孙宇晨直接说核电→三方同向
+【用户关注】用户自己也在关注核电，认为确定性高
+【待办】需确认具体标的：中广核(003816)/中国核电(601985)/核电ETF(562690)等</t>
       </text>
     </comment>
   </commentList>
@@ -2510,7 +2537,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:J16"/>
+  <dimension ref="A1:J99"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="10.4921875" defaultRowHeight="12.75" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="32" customWidth="1" style="39" min="1" max="8"/>
@@ -2587,87 +2614,75 @@
       </c>
     </row>
     <row r="3" ht="72.75" customHeight="1" s="40">
-      <c r="A3" s="66" t="inlineStr">
-        <is>
-          <t>成本¥3695
-净值3.6875
-P:46%
-虚P+4pp
+      <c r="A3" s="78" t="inlineStr">
+        <is>
+          <t>P:44%
+虚P+2pp
 利率折价-6pp
-有效P:40%
+有效P:38%
 拟合❌0分
 下行:25% 确定性:30% 溢价:50%
 盈亏比:1.2:1
 决策:观望</t>
         </is>
       </c>
-      <c r="B3" s="66" t="inlineStr">
-        <is>
-          <t>成本¥6811
-净值1.8418
-P:73%
+      <c r="B3" s="78" t="inlineStr">
+        <is>
+          <t>P:65%
 虚P无
 利率折价-6pp
-有效P:67%
+有效P:59%
 拟合✅97分
 下行:20% 确定性:25% 溢价:40%
-盈亏比:2.3:1
+盈亏比:2.0:1
 决策:持有</t>
         </is>
       </c>
-      <c r="C3" s="66" t="inlineStr">
-        <is>
-          <t>成本¥4722
-净值0.6619
-P:34%
+      <c r="C3" s="78" t="inlineStr">
+        <is>
+          <t>P:29%
 虚P无
 利率折价-6pp
-有效P:28%
+有效P:23%
 拟合✅75分
 下行:30% 确定性:15% 溢价:30%
-盈亏比:0.5:1
+盈亏比:0.4:1
 决策:不干</t>
         </is>
       </c>
-      <c r="D3" s="66" t="inlineStr">
-        <is>
-          <t>成本¥3732
-净值0.7545
-P:65%
+      <c r="D3" s="78" t="inlineStr">
+        <is>
+          <t>P:70%
 虚P+4pp
 利率折价0pp
-有效P:65%
+有效P:70%
 拟合✅95分
 下行:20% 确定性:35% 溢价:20%
-盈亏比:1.8:1
-决策:观望</t>
-        </is>
-      </c>
-      <c r="E3" s="66" t="inlineStr">
-        <is>
-          <t>成本¥4800
-净值1.8985
-P:44%
+盈亏比:2.0:1
+决策:持有</t>
+        </is>
+      </c>
+      <c r="E3" s="78" t="inlineStr">
+        <is>
+          <t>P:39%
 虚P无
 利率折价-4pp
-有效P:40%
+有效P:35%
 拟合⚠️样本少
 下行:15% 确定性:20% 溢价:30%
-盈亏比:2.0:1
-决策:持有</t>
-        </is>
-      </c>
-      <c r="F3" s="66" t="inlineStr">
-        <is>
-          <t>成本¥5622
-净值1.089
-P:43%
+盈亏比:1.7:1
+决策:观望</t>
+        </is>
+      </c>
+      <c r="F3" s="78" t="inlineStr">
+        <is>
+          <t>P:40%
 虚P无
 利率折价-4pp
-有效P:39%
+有效P:36%
 拟合⚠️样本少
 下行:20% 确定性:25% 溢价:35%
-盈亏比:1.8:1
+盈亏比:1.6:1
 决策:观望</t>
         </is>
       </c>
@@ -3157,7 +3172,12 @@
     </row>
     <row r="16" ht="13.5" customHeight="1" s="40">
       <c r="A16" s="39" t="n"/>
-      <c r="B16" s="39" t="n"/>
+      <c r="B16" s="79" t="inlineStr">
+        <is>
+          <t>2026-06-03
+-10pp(综合)</t>
+        </is>
+      </c>
       <c r="C16" s="39" t="n"/>
       <c r="D16" s="39" t="n"/>
       <c r="E16" s="39" t="n"/>
@@ -3166,8 +3186,31 @@
       <c r="H16" s="39" t="n"/>
     </row>
     <row r="17" ht="13.5" customHeight="1" s="40"/>
-    <row r="18" ht="13.5" customHeight="1" s="40"/>
-    <row r="19" ht="13.5" customHeight="1" s="40"/>
+    <row r="18" ht="13.5" customHeight="1" s="40">
+      <c r="A18" s="79" t="inlineStr">
+        <is>
+          <t>📊 待重仓监控</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="13.5" customHeight="1" s="40">
+      <c r="A19" s="79" t="inlineStr">
+        <is>
+          <t>核电 ⚡</t>
+        </is>
+      </c>
+      <c r="B19" s="79" t="inlineStr">
+        <is>
+          <t>标记：2026-06-03
+信源：孙宇晨（昌健胡说抖音）
+🔴 孙宇晨说"未来10年看核电"
+逻辑：AI算力→海量电力→核电=唯一稳定清洁能源
+与Sereneity/Leopold"AI物理瓶颈"互锁
+状态：无仓位，需找标的（中广核/中国核电/核电ETF）
+买入：等中期选举大跌或孙宇晨新催化</t>
+        </is>
+      </c>
+    </row>
     <row r="20" ht="13.5" customHeight="1" s="40"/>
     <row r="21" ht="13.5" customHeight="1" s="40"/>
     <row r="22" ht="13.5" customHeight="1" s="40"/>
@@ -3179,6 +3222,75 @@
     <row r="28" ht="13.5" customHeight="1" s="40"/>
     <row r="29" ht="13.5" customHeight="1" s="40"/>
     <row r="30" ht="13.5" customHeight="1" s="40"/>
+    <row r="31"/>
+    <row r="32"/>
+    <row r="33"/>
+    <row r="34"/>
+    <row r="35"/>
+    <row r="36"/>
+    <row r="37"/>
+    <row r="38"/>
+    <row r="39"/>
+    <row r="40"/>
+    <row r="41"/>
+    <row r="42"/>
+    <row r="43"/>
+    <row r="44"/>
+    <row r="45"/>
+    <row r="46"/>
+    <row r="47"/>
+    <row r="48"/>
+    <row r="49"/>
+    <row r="50"/>
+    <row r="51"/>
+    <row r="52"/>
+    <row r="53"/>
+    <row r="54"/>
+    <row r="55"/>
+    <row r="56"/>
+    <row r="57"/>
+    <row r="58"/>
+    <row r="59"/>
+    <row r="60"/>
+    <row r="61"/>
+    <row r="62"/>
+    <row r="63"/>
+    <row r="64"/>
+    <row r="65"/>
+    <row r="66"/>
+    <row r="67"/>
+    <row r="68"/>
+    <row r="69"/>
+    <row r="70"/>
+    <row r="71"/>
+    <row r="72"/>
+    <row r="73"/>
+    <row r="74"/>
+    <row r="75"/>
+    <row r="76"/>
+    <row r="77"/>
+    <row r="78"/>
+    <row r="79"/>
+    <row r="80"/>
+    <row r="81"/>
+    <row r="82"/>
+    <row r="83"/>
+    <row r="84"/>
+    <row r="85"/>
+    <row r="86"/>
+    <row r="87"/>
+    <row r="88"/>
+    <row r="89"/>
+    <row r="90"/>
+    <row r="91"/>
+    <row r="92"/>
+    <row r="93"/>
+    <row r="94"/>
+    <row r="95"/>
+    <row r="96"/>
+    <row r="97"/>
+    <row r="98"/>
+    <row r="99"/>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="J4:J15"/>
@@ -3210,364 +3322,364 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="39" t="inlineStr">
         <is>
           <t>P值vs价格拟合分析 (Spearman秩相关) 2026-06-03</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="39" t="inlineStr">
         <is>
           <t>持仓</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B2" s="39" t="inlineStr">
         <is>
           <t>代码</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C2" s="39" t="inlineStr">
         <is>
           <t>拟合分</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D2" s="39" t="inlineStr">
         <is>
           <t>Spearman ρ</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E2" s="39" t="inlineStr">
         <is>
           <t>p值</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="F2" s="39" t="inlineStr">
         <is>
           <t>样本数</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="G2" s="39" t="inlineStr">
         <is>
           <t>评级</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="H2" s="39" t="inlineStr">
         <is>
           <t>信源建议</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="39" t="inlineStr">
         <is>
           <t>电池</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B3" s="39" t="inlineStr">
         <is>
           <t>009759</t>
         </is>
       </c>
-      <c r="C3" t="n">
+      <c r="C3" s="39" t="n">
         <v>97</v>
       </c>
-      <c r="D3" t="n">
+      <c r="D3" s="39" t="n">
         <v>0.966</v>
       </c>
-      <c r="E3" t="n">
+      <c r="E3" s="39" t="n">
         <v>0</v>
       </c>
-      <c r="F3" t="n">
+      <c r="F3" s="39" t="n">
         <v>9</v>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="G3" s="39" t="inlineStr">
         <is>
           <t>✅优秀</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="H3" s="39" t="inlineStr">
         <is>
           <t>信源加分</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="39" t="inlineStr">
         <is>
           <t>养殖</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B4" s="39" t="inlineStr">
         <is>
           <t>008765</t>
         </is>
       </c>
-      <c r="C4" t="n">
+      <c r="C4" s="39" t="n">
         <v>95</v>
       </c>
-      <c r="D4" t="n">
+      <c r="D4" s="39" t="n">
         <v>0.955</v>
       </c>
-      <c r="E4" t="n">
+      <c r="E4" s="39" t="n">
         <v>0.001</v>
       </c>
-      <c r="F4" t="n">
+      <c r="F4" s="39" t="n">
         <v>7</v>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="G4" s="39" t="inlineStr">
         <is>
           <t>✅优秀</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="H4" s="39" t="inlineStr">
         <is>
           <t>信源加分</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="39" t="inlineStr">
         <is>
           <t>恒科</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B5" s="39" t="inlineStr">
         <is>
           <t>009854</t>
         </is>
       </c>
-      <c r="C5" t="n">
+      <c r="C5" s="39" t="n">
         <v>75</v>
       </c>
-      <c r="D5" t="n">
+      <c r="D5" s="39" t="n">
         <v>0.754</v>
       </c>
-      <c r="E5" t="n">
+      <c r="E5" s="39" t="n">
         <v>0.08400000000000001</v>
       </c>
-      <c r="F5" t="n">
+      <c r="F5" s="39" t="n">
         <v>6</v>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="G5" s="39" t="inlineStr">
         <is>
           <t>✅优秀</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="H5" s="39" t="inlineStr">
         <is>
           <t>信源加分</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="39" t="inlineStr">
         <is>
           <t>银行</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B6" s="39" t="inlineStr">
         <is>
           <t>012888</t>
         </is>
       </c>
-      <c r="C6" t="n">
+      <c r="C6" s="39" t="n">
         <v>53</v>
       </c>
-      <c r="D6" t="n">
+      <c r="D6" s="39" t="n">
         <v>0.53</v>
       </c>
-      <c r="E6" t="n">
+      <c r="E6" s="39" t="n">
         <v>0.358</v>
       </c>
-      <c r="F6" t="n">
+      <c r="F6" s="39" t="n">
         <v>5</v>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="G6" s="39" t="inlineStr">
         <is>
           <t>👍良好</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="H6" s="39" t="inlineStr">
         <is>
           <t>信源保持</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" s="39" t="inlineStr">
         <is>
           <t>稀金</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B7" s="39" t="inlineStr">
         <is>
           <t>008907</t>
         </is>
       </c>
-      <c r="C7" t="n">
+      <c r="C7" s="39" t="n">
         <v>50</v>
       </c>
-      <c r="D7" t="n">
+      <c r="D7" s="39" t="n">
         <v>0.5</v>
       </c>
-      <c r="E7" t="n">
+      <c r="E7" s="39" t="n">
         <v>0.667</v>
       </c>
-      <c r="F7" t="n">
+      <c r="F7" s="39" t="n">
         <v>3</v>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="G7" s="39" t="inlineStr">
         <is>
           <t>⚠️样本不足</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="H7" s="39" t="inlineStr">
         <is>
           <t>需积累</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
+      <c r="A8" s="39" t="inlineStr">
         <is>
           <t>有色</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B8" s="39" t="inlineStr">
         <is>
           <t>008826</t>
         </is>
       </c>
-      <c r="C8" t="n">
+      <c r="C8" s="39" t="n">
         <v>0</v>
       </c>
-      <c r="D8" t="n">
+      <c r="D8" s="39" t="n">
         <v>-0.5</v>
       </c>
-      <c r="E8" t="n">
+      <c r="E8" s="39" t="n">
         <v>0.667</v>
       </c>
-      <c r="F8" t="n">
+      <c r="F8" s="39" t="n">
         <v>3</v>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="G8" s="39" t="inlineStr">
         <is>
           <t>⚠️样本不足</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="H8" s="39" t="inlineStr">
         <is>
           <t>需积累</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
+      <c r="A9" s="39" t="inlineStr">
         <is>
           <t>芯片</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B9" s="39" t="inlineStr">
         <is>
           <t>020628</t>
         </is>
       </c>
-      <c r="C9" t="n">
+      <c r="C9" s="39" t="n">
         <v>0</v>
       </c>
-      <c r="D9" t="n">
+      <c r="D9" s="39" t="n">
         <v>-0.676</v>
       </c>
-      <c r="E9" t="n">
+      <c r="E9" s="39" t="n">
         <v>0.022</v>
       </c>
-      <c r="F9" t="n">
+      <c r="F9" s="39" t="n">
         <v>11</v>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="G9" s="39" t="inlineStr">
         <is>
           <t>❌差</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="H9" s="39" t="inlineStr">
         <is>
           <t>信源减分/替换</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
+      <c r="A11" s="39" t="inlineStr">
         <is>
           <t>方法说明：</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
+      <c r="A12" s="39" t="inlineStr">
         <is>
           <t>1. Spearman秩相关：衡量P值累计趋势与价格累计趋势的单调一致性</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
+      <c r="A13" s="39" t="inlineStr">
         <is>
           <t>2. 允许非线性、允许滞后、不要求同一天同向</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="A14" s="39" t="inlineStr">
         <is>
           <t>3. 正值=同向拟合，负值=反向不拟合</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
+      <c r="A15" s="39" t="inlineStr">
         <is>
           <t>4. p值&lt;0.05=统计显著</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
+      <c r="A16" s="39" t="inlineStr">
         <is>
           <t>5. 样本&lt;4统计不可靠，需积累更多事件</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
+      <c r="A18" s="39" t="inlineStr">
         <is>
           <t>关键发现：</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr">
+      <c r="A19" s="39" t="inlineStr">
         <is>
           <t>1. 电池/养殖拟合极好(95-97分)，信源质量可靠</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
+      <c r="A20" s="39" t="inlineStr">
         <is>
           <t>2. 恒科75分不错，P值偏空价格也确实跌了</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr">
+      <c r="A21" s="39" t="inlineStr">
         <is>
           <t>3. 芯片0分最差(ρ=-0.676,p=0.022显著)，P值一路降但价格先涨后跌V型，信源信息面和实际走势有系统性偏差</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr">
+      <c r="A22" s="39" t="inlineStr">
         <is>
           <t>4. 有色/稀金仅3个事件，统计不可靠，继续积累</t>
         </is>

--- a/持仓贝叶斯跟踪.xlsx
+++ b/持仓贝叶斯跟踪.xlsx
@@ -1944,12 +1944,18 @@
       </c>
       <c r="D21" s="65" t="inlineStr">
         <is>
-          <t>孙宇晨"未来10年看核电"，AI算力→海量电力需求</t>
+          <t>孙宇晨"未来10年看核电"，AI算力→海量电力需求
+【6/4新增】4条信源联动：
+①孙宇晨10亿美元押注物理AI→电力是核心瓶颈
+②Sereneity/Leopold：AI物理瓶颈=材料+电力/土地
+③美国数据中心规划装机245GW，2028年占全美电力6.7%-12%
+④国内2025年核准10台机组（审批加速）+金七门2号2026年4月FCD
+⚠️短期风险：中国核电2026Q1净利-34.19%，电价下行压力</t>
         </is>
       </c>
       <c r="E21" s="65" t="inlineStr">
         <is>
-          <t>长期跟踪</t>
+          <t>长期跟踪（6/4深度研究更新）</t>
         </is>
       </c>
       <c r="F21" s="65" t="inlineStr">
@@ -1985,7 +1991,6 @@
         </is>
       </c>
     </row>
-    <row r="27"/>
     <row r="28" ht="15" customHeight="1" s="50">
       <c r="A28" s="68" t="inlineStr">
         <is>
@@ -3237,11 +3242,11 @@
       </c>
     </row>
     <row r="14" ht="13.5" customHeight="1" s="50">
-      <c r="A14" t="n"/>
-      <c r="B14" t="n"/>
-      <c r="C14" t="n"/>
-      <c r="D14" t="n"/>
-      <c r="G14" t="n"/>
+      <c r="A14" s="49" t="n"/>
+      <c r="B14" s="49" t="n"/>
+      <c r="C14" s="49" t="n"/>
+      <c r="D14" s="49" t="n"/>
+      <c r="G14" s="49" t="n"/>
     </row>
     <row r="15" ht="13.5" customHeight="1" s="50">
       <c r="A15" s="49" t="inlineStr">

--- a/持仓贝叶斯跟踪.xlsx
+++ b/持仓贝叶斯跟踪.xlsx
@@ -10,6 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总看板" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet2" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="拟合分析" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="机会成本排序" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1" refMode="A1" iterate="0" iterateCount="100" iterateDelta="0.0001"/>
@@ -19,7 +20,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="28">
+  <fonts count="39">
     <font>
       <name val="Calibri"/>
       <charset val="1"/>
@@ -216,8 +217,55 @@
       <color rgb="FF999999"/>
       <sz val="11"/>
     </font>
+    <font>
+      <b val="1"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <b val="1"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FF0000"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FF0000"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="001F4E79"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <color rgb="00666666"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="001F4E79"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="15">
+  <fills count="20">
     <fill>
       <patternFill/>
     </fill>
@@ -302,6 +350,36 @@
         <bgColor rgb="FFD6DCE4"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="004472C4"/>
+        <bgColor rgb="004472C4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001F4E79"/>
+        <bgColor rgb="001F4E79"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C6EFCE"/>
+        <bgColor rgb="00C6EFCE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFC7CE"/>
+        <bgColor rgb="00FFC7CE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFEB9C"/>
+        <bgColor rgb="00FFEB9C"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="7">
     <border>
@@ -363,7 +441,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="98">
+  <cellXfs count="112">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -652,6 +730,30 @@
     <xf numFmtId="0" fontId="24" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="30" fillId="15" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="36" fillId="16" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="19" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="38" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1031,14 +1133,47 @@
 状态：已加入待重仓，需深度研究（cron明天10点）</t>
       </text>
     </comment>
+    <comment ref="A22" authorId="0" shapeId="0">
+      <text>
+        <t>来源：蒋宇飞抖音6/1-6/3转录 + 小龙虾技术分析
+蒋宇飞"星光纯叠"框架：
+星=CPU/GPU，光=光通信，纯=存储芯片，叠=3D堆叠/先进封装
+核心逻辑链：
+1. 摩尔定律终结（物理+经济双极限，宋鸿兵确认）
+2. 单芯片性能提升见顶
+3. 必须用"堆叠"方式把多个芯片叠在一起（2.5D/3D封装）
+4. CoWoS/先进封装成为AI芯片核心瓶颈
+5. 存储是堆叠的"原材料"，堆叠才是"成品"
+6. 存储涨价→堆叠成本↑→堆叠技术溢价更高
+7. 投资逻辑：存储是上游（机会尾声），堆叠是下游（未来主线）
+长电科技600584：
+- 全球第三大封测厂，收购STATS ChipPAC后获国际级先进封装能力
+- 2.5D硅中介层封装（量产级）、Fan-out WLP（量产级）、3D SiP（量产级）
+- 客户：高通、海思、TI、ST、NXP
+- PE约30x，合理偏低→安全边际大
+通富微电002156：
+- 收购AMD苏州+槟城封测厂，获AMD全套先进封装线
+- 2.5D interposer量产（AMD RDNA/CDNA GPU用）
+- 唯一AMD封测全线突破通道→不可替代
+存储降级理由：
+- 兆易创新4/20 ¥290→6/4 ¥525，两个月涨81%，PE天际线
+- 涨价预期已大部分定价，向上空间&lt;向下空间
+- 蒋宇飞框架中"纯"（存储）是上游，"叠"（堆叠）是下游→上游涨完轮到下游
+用户判断（6/4）："存储信息面估值角度，不知道还支不支持来搞，怕太高了，安全边际不够大"
+结论：存储降级为观察，堆叠升级为最高优先级</t>
+      </text>
+    </comment>
+    <comment ref="A24" authorId="0" shapeId="0">
+      <text>
+        <t>长电科技：全球第三大封测厂，2.5D/3D量产级，PE30x合理，安全边际大。与通富各占一半——长电吃广度，通富吃AMD深度。</t>
+      </text>
+    </comment>
+    <comment ref="A25" authorId="0" shapeId="0">
+      <text>
+        <t>通富微电：AMD封测全线突破通道，2.5D量产，MI300X参与。唯一性=不可替代=安全边际中偏大。</t>
+      </text>
+    </comment>
     <comment ref="C26" authorId="1" shapeId="0">
-      <text>
-        <t>信息源: 新浪财经K线API(sh512800)
-推理链: 去杠杆→信贷收缩→银行资产质量↓→板块弱势
-P值: 50%基准，虚P-2pp(利率折价0pp)</t>
-      </text>
-    </comment>
-    <comment ref="E26" authorId="1" shapeId="0">
       <text>
         <t>信息源: 新浪财经K线API(sh512800)
 推理链: 去杠杆→信贷收缩→银行资产质量↓→板块弱势
@@ -1965,29 +2100,92 @@
       </c>
     </row>
     <row r="22" ht="16.5" customHeight="1" s="50">
-      <c r="A22" s="66" t="n"/>
+      <c r="A22" s="102" t="inlineStr">
+        <is>
+          <t>🔥 堆叠/先进封装赛道（蒋宇飞"星光纯叠"框架）</t>
+        </is>
+      </c>
     </row>
     <row r="23" ht="16.5" customHeight="1" s="50">
-      <c r="C23" s="67" t="n"/>
-      <c r="E23" s="67" t="n"/>
+      <c r="A23" s="49" t="inlineStr">
+        <is>
+          <t>核心判断</t>
+        </is>
+      </c>
+      <c r="B23" s="49" t="inlineStr">
+        <is>
+          <t>存储机会尾声→堆叠才是未来主线（摩尔定律终结→单芯片见顶→必须堆叠）</t>
+        </is>
+      </c>
+      <c r="E23" s="67" t="inlineStr">
+        <is>
+          <t>6/4</t>
+        </is>
+      </c>
     </row>
     <row r="24" ht="16.5" customHeight="1" s="50">
-      <c r="C24" s="67" t="n"/>
-      <c r="E24" s="67" t="n"/>
+      <c r="A24" s="49" t="inlineStr">
+        <is>
+          <t>长电科技</t>
+        </is>
+      </c>
+      <c r="B24" s="49" t="inlineStr">
+        <is>
+          <t>600584 ¥80.4 PE30x</t>
+        </is>
+      </c>
+      <c r="C24" s="67" t="inlineStr">
+        <is>
+          <t>⭐⭐⭐核心</t>
+        </is>
+      </c>
+      <c r="D24" s="49" t="inlineStr">
+        <is>
+          <t>全球第三大封测厂，2.5D/3D量产级，客户广度最强（高通/海思/TI）</t>
+        </is>
+      </c>
     </row>
     <row r="25" ht="16.5" customHeight="1" s="50">
-      <c r="C25" s="67" t="n"/>
-      <c r="E25" s="67" t="n"/>
+      <c r="A25" s="49" t="inlineStr">
+        <is>
+          <t>通富微电</t>
+        </is>
+      </c>
+      <c r="B25" s="49" t="inlineStr">
+        <is>
+          <t>002156 待查</t>
+        </is>
+      </c>
+      <c r="C25" s="67" t="inlineStr">
+        <is>
+          <t>⭐⭐⭐核心</t>
+        </is>
+      </c>
+      <c r="D25" s="49" t="inlineStr">
+        <is>
+          <t>AMD封测全线突破通道，2.5D量产，MI300X参与，不可替代</t>
+        </is>
+      </c>
     </row>
     <row r="26" ht="15" customHeight="1" s="50">
+      <c r="A26" s="49" t="inlineStr">
+        <is>
+          <t>❌存储降级</t>
+        </is>
+      </c>
+      <c r="B26" s="49" t="inlineStr">
+        <is>
+          <t>兆易¥525(+81%)/江波龙¥569/佰维¥341</t>
+        </is>
+      </c>
       <c r="C26" s="67" t="inlineStr">
         <is>
-          <t>2026-05-29 银行V型反弹：0.761→0.776(+1.97%)→0.790(6/2)</t>
-        </is>
-      </c>
-      <c r="E26" s="67" t="inlineStr">
-        <is>
-          <t>2026-06-02 银行仍弱势：ETF 0.790，无催化信号，不建议加仓</t>
+          <t>安全边际不足</t>
+        </is>
+      </c>
+      <c r="D26" s="49" t="inlineStr">
+        <is>
+          <t>存储涨完轮到堆叠，向上空间&lt;向下空间=不值得干</t>
         </is>
       </c>
     </row>
@@ -2008,7 +2206,7 @@
     <row r="30" ht="15" customHeight="1" s="50">
       <c r="C30" s="70" t="inlineStr">
         <is>
-          <t>2026-06-04 【收网】霍尔木兹海峡Day 12：伊朗暂停谈判+美众议院限制动武，WTI $96→$91-93回落，方向趋于缓和。原霍尔木兹虚P已作废，6/3油价虚P待观察。</t>
+          <t>2026-06-04 【保持观察】霍尔木兹海峡Day 12：伊朗暂停谈判+美众议院限制动武，WTI $96→$91-93回落，方向趋于缓和。原霍尔木兹虚P已作废，6/3油价虚P待观察。</t>
         </is>
       </c>
       <c r="E30" s="69" t="inlineStr">
@@ -2256,22 +2454,22 @@
       </c>
       <c r="B39" s="49" t="inlineStr">
         <is>
-          <t>🔴最高优先级</t>
+          <t>❌降级观察</t>
         </is>
       </c>
       <c r="C39" s="49" t="inlineStr">
         <is>
-          <t>P:70%+</t>
+          <t>P:55% 安全边际不足</t>
         </is>
       </c>
       <c r="D39" s="49" t="inlineStr">
         <is>
-          <t>5条信源交叉验证：群联供给不足+蒋宇飞两长双雄+宋鸿兵摩尔定律终结+周鸿祎内存决定AI+用户AI进化=存储指数增长</t>
+          <t>兆易¥525(+81%)/江波龙¥569/佰维¥341→PE天际线，向上空间&lt;向下空间</t>
         </is>
       </c>
       <c r="E39" s="49" t="inlineStr">
         <is>
-          <t>等中期选举大跌15%+或P值回升55%+</t>
+          <t>等中期选举大跌15%+</t>
         </is>
       </c>
       <c r="F39" s="49" t="inlineStr">
@@ -2281,12 +2479,12 @@
       </c>
       <c r="G39" s="49" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="H39" s="49" t="inlineStr">
         <is>
-          <t>北京君正300223/兆易创新603986/江波龙301308/佰维688525/聚辰688123</t>
+          <t>降级：存储涨完轮到堆叠，安全边际已不足</t>
         </is>
       </c>
     </row>
@@ -2298,22 +2496,22 @@
       </c>
       <c r="B40" s="49" t="inlineStr">
         <is>
-          <t>🟡存储补充</t>
+          <t>❌降级观察</t>
         </is>
       </c>
       <c r="C40" s="49" t="inlineStr">
         <is>
-          <t>P:55%+</t>
+          <t>P:55% 安全边际中等</t>
         </is>
       </c>
       <c r="D40" s="49" t="inlineStr">
         <is>
-          <t>DDR5接口芯片龙头，AI算力→内存带宽→量价齐升，与存储逻辑互锁</t>
+          <t>DDR5接口芯片，温和上涨，但存储赛道整体降级</t>
         </is>
       </c>
       <c r="E40" s="49" t="inlineStr">
         <is>
-          <t>等大跌15%+或P值回升</t>
+          <t>等大跌15%+</t>
         </is>
       </c>
       <c r="F40" s="49" t="inlineStr">
@@ -2323,295 +2521,161 @@
       </c>
       <c r="G40" s="49" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="H40" s="49" t="inlineStr">
         <is>
-          <t>盈亏比4:1，AI仓20%</t>
+          <t>降级：存储赛道尾声</t>
         </is>
       </c>
     </row>
     <row r="41" ht="16.5" customHeight="1" s="50">
-      <c r="A41" s="76" t="inlineStr">
-        <is>
-          <t>标的</t>
-        </is>
-      </c>
-      <c r="B41" s="76" t="inlineStr">
-        <is>
-          <t>代码</t>
-        </is>
-      </c>
-      <c r="C41" s="76" t="inlineStr">
-        <is>
-          <t>盈亏比</t>
-        </is>
-      </c>
-      <c r="D41" s="76" t="inlineStr">
-        <is>
-          <t>P值</t>
-        </is>
-      </c>
-      <c r="E41" s="76" t="inlineStr">
-        <is>
-          <t>建议仓位</t>
-        </is>
-      </c>
-      <c r="F41" s="76" t="inlineStr">
-        <is>
-          <t>买入条件</t>
-        </is>
-      </c>
-      <c r="G41" s="76" t="inlineStr">
-        <is>
-          <t>状态</t>
+      <c r="A41" s="103" t="inlineStr">
+        <is>
+          <t>🔥堆叠/先进封装赛道（蒋宇飞"星光纯叠"框架）</t>
         </is>
       </c>
     </row>
     <row r="42" ht="16.5" customHeight="1" s="50">
       <c r="A42" s="49" t="inlineStr">
         <is>
-          <t>北京君正</t>
+          <t>长电科技(600584)</t>
         </is>
       </c>
       <c r="B42" s="49" t="inlineStr">
         <is>
-          <t>300223</t>
+          <t>🔴核心标的</t>
         </is>
       </c>
       <c r="C42" s="49" t="inlineStr">
         <is>
-          <t>4:1</t>
+          <t>P:75%+ PE30x</t>
         </is>
       </c>
       <c r="D42" s="49" t="inlineStr">
         <is>
-          <t>70%+</t>
+          <t>全球第三大封测厂，2.5D/3D量产级，客户广度最强（高通/海思/TI）</t>
         </is>
       </c>
       <c r="E42" s="49" t="inlineStr">
         <is>
-          <t>AI仓50%</t>
+          <t>等中期选举大跌</t>
         </is>
       </c>
       <c r="F42" s="49" t="inlineStr">
         <is>
-          <t>等大跌15%+</t>
+          <t>中期</t>
         </is>
       </c>
       <c r="G42" s="49" t="inlineStr">
         <is>
-          <t>🔴未建仓</t>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="H42" s="49" t="inlineStr">
+        <is>
+          <t>安全边际大，堆叠赛道首选</t>
         </is>
       </c>
     </row>
     <row r="43" ht="16.5" customHeight="1" s="50">
       <c r="A43" s="49" t="inlineStr">
         <is>
-          <t>兆易创新</t>
+          <t>通富微电(002156)</t>
         </is>
       </c>
       <c r="B43" s="49" t="inlineStr">
         <is>
-          <t>603986</t>
+          <t>🔴核心标的</t>
         </is>
       </c>
       <c r="C43" s="49" t="inlineStr">
         <is>
-          <t>3.5:1</t>
+          <t>P:75%+ 待查PE</t>
         </is>
       </c>
       <c r="D43" s="49" t="inlineStr">
         <is>
-          <t>70%+</t>
+          <t>AMD封测全线突破通道，2.5D量产，MI300X参与，不可替代</t>
         </is>
       </c>
       <c r="E43" s="49" t="inlineStr">
         <is>
-          <t>AI仓50%</t>
+          <t>等中期选举大跌</t>
         </is>
       </c>
       <c r="F43" s="49" t="inlineStr">
         <is>
-          <t>等大跌15%+</t>
+          <t>中期</t>
         </is>
       </c>
       <c r="G43" s="49" t="inlineStr">
         <is>
-          <t>🔴未建仓</t>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="H43" s="49" t="inlineStr">
+        <is>
+          <t>安全边际中偏大，与长电各占一半</t>
         </is>
       </c>
     </row>
     <row r="44" ht="16.5" customHeight="1" s="50">
-      <c r="A44" s="49" t="inlineStr">
-        <is>
-          <t>江波龙</t>
-        </is>
-      </c>
-      <c r="B44" s="49" t="inlineStr">
-        <is>
-          <t>301308</t>
-        </is>
-      </c>
-      <c r="C44" s="49" t="inlineStr">
-        <is>
-          <t>3.5:1</t>
-        </is>
-      </c>
-      <c r="D44" s="49" t="inlineStr">
-        <is>
-          <t>70%+</t>
-        </is>
-      </c>
-      <c r="E44" s="49" t="inlineStr">
-        <is>
-          <t>AI仓50%</t>
-        </is>
-      </c>
-      <c r="F44" s="49" t="inlineStr">
-        <is>
-          <t>等大跌15%+</t>
-        </is>
-      </c>
-      <c r="G44" s="49" t="inlineStr">
-        <is>
-          <t>🔴未建仓</t>
-        </is>
-      </c>
+      <c r="A44" s="49" t="n"/>
+      <c r="B44" s="49" t="n"/>
+      <c r="C44" s="49" t="n"/>
+      <c r="D44" s="49" t="n"/>
+      <c r="E44" s="49" t="n"/>
+      <c r="F44" s="49" t="n"/>
+      <c r="G44" s="49" t="n"/>
     </row>
     <row r="45" ht="16.5" customHeight="1" s="50">
-      <c r="A45" s="49" t="inlineStr">
-        <is>
-          <t>佰维存储</t>
-        </is>
-      </c>
-      <c r="B45" s="49" t="inlineStr">
-        <is>
-          <t>688525</t>
-        </is>
-      </c>
-      <c r="C45" s="49" t="inlineStr">
-        <is>
-          <t>3:1</t>
-        </is>
-      </c>
-      <c r="D45" s="49" t="inlineStr">
-        <is>
-          <t>70%+</t>
-        </is>
-      </c>
-      <c r="E45" s="49" t="inlineStr">
-        <is>
-          <t>AI仓50%</t>
-        </is>
-      </c>
-      <c r="F45" s="49" t="inlineStr">
-        <is>
-          <t>等大跌15%+</t>
-        </is>
-      </c>
-      <c r="G45" s="49" t="inlineStr">
-        <is>
-          <t>🔴未建仓</t>
-        </is>
-      </c>
+      <c r="A45" s="49" t="n"/>
+      <c r="B45" s="49" t="n"/>
+      <c r="C45" s="49" t="n"/>
+      <c r="D45" s="49" t="n"/>
+      <c r="E45" s="49" t="n"/>
+      <c r="F45" s="49" t="n"/>
+      <c r="G45" s="49" t="n"/>
     </row>
     <row r="46" ht="16.5" customHeight="1" s="50">
-      <c r="A46" s="49" t="inlineStr">
-        <is>
-          <t>聚辰股份</t>
-        </is>
-      </c>
-      <c r="B46" s="49" t="inlineStr">
-        <is>
-          <t>688123</t>
-        </is>
-      </c>
-      <c r="C46" s="49" t="inlineStr">
-        <is>
-          <t>3:1</t>
-        </is>
-      </c>
-      <c r="D46" s="49" t="inlineStr">
-        <is>
-          <t>70%+</t>
-        </is>
-      </c>
-      <c r="E46" s="49" t="inlineStr">
-        <is>
-          <t>AI仓50%</t>
-        </is>
-      </c>
-      <c r="F46" s="49" t="inlineStr">
-        <is>
-          <t>等大跌15%+</t>
-        </is>
-      </c>
-      <c r="G46" s="49" t="inlineStr">
-        <is>
-          <t>🔴未建仓</t>
-        </is>
-      </c>
+      <c r="A46" s="49" t="n"/>
+      <c r="B46" s="49" t="n"/>
+      <c r="C46" s="49" t="n"/>
+      <c r="D46" s="49" t="n"/>
+      <c r="E46" s="49" t="n"/>
+      <c r="F46" s="49" t="n"/>
+      <c r="G46" s="49" t="n"/>
     </row>
     <row r="47" ht="16.5" customHeight="1" s="50">
-      <c r="A47" s="49" t="inlineStr">
-        <is>
-          <t>澜起科技</t>
-        </is>
-      </c>
-      <c r="B47" s="49" t="inlineStr">
-        <is>
-          <t>688008</t>
-        </is>
-      </c>
-      <c r="C47" s="49" t="inlineStr">
-        <is>
-          <t>4:1</t>
-        </is>
-      </c>
-      <c r="D47" s="49" t="inlineStr">
-        <is>
-          <t>55%+</t>
-        </is>
-      </c>
-      <c r="E47" s="49" t="inlineStr">
-        <is>
-          <t>AI仓20%</t>
-        </is>
-      </c>
-      <c r="F47" s="49" t="inlineStr">
-        <is>
-          <t>等大跌15%+</t>
-        </is>
-      </c>
-      <c r="G47" s="49" t="inlineStr">
-        <is>
-          <t>🟡观察中</t>
-        </is>
-      </c>
+      <c r="A47" s="49" t="n"/>
+      <c r="B47" s="49" t="n"/>
+      <c r="C47" s="49" t="n"/>
+      <c r="D47" s="49" t="n"/>
+      <c r="E47" s="49" t="n"/>
+      <c r="F47" s="49" t="n"/>
+      <c r="G47" s="49" t="n"/>
     </row>
     <row r="48" ht="16.5" customHeight="1" s="50">
-      <c r="A48" s="49" t="inlineStr">
-        <is>
-          <t>📌 AI仓位目标：总资金25%（存储12.5%+澜起5%+芯片ETF持有+凯盛2.5%观察）</t>
-        </is>
-      </c>
+      <c r="A48" s="49" t="n"/>
     </row>
     <row r="49" ht="16.5" customHeight="1" s="50">
-      <c r="A49" s="49" t="inlineStr">
-        <is>
-          <t>📌 核心逻辑：长鑫/长江暂时买不到→买产业链上下游→存储缺货涨价贯穿2026全年</t>
-        </is>
-      </c>
+      <c r="A49" s="49" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="8">
+  <mergeCells count="14">
     <mergeCell ref="A12:H12"/>
     <mergeCell ref="A16:F16"/>
     <mergeCell ref="B14:H14"/>
+    <mergeCell ref="D26:H26"/>
     <mergeCell ref="B13:H13"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="D25:G25"/>
     <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A22:H22"/>
+    <mergeCell ref="D24:G24"/>
+    <mergeCell ref="A41:H41"/>
     <mergeCell ref="B15:H15"/>
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="A28:G28"/>
@@ -2629,7 +2693,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:J21"/>
+  <dimension ref="A1:J44"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="10.4921875" defaultRowHeight="12.75" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="32" customWidth="1" style="49" min="1" max="8"/>
@@ -3311,15 +3375,470 @@
     </row>
     <row r="22" ht="13.5" customHeight="1" s="50"/>
     <row r="23" ht="13.5" customHeight="1" s="50"/>
-    <row r="24" ht="13.5" customHeight="1" s="50"/>
-    <row r="25" ht="13.5" customHeight="1" s="50"/>
-    <row r="26" ht="13.5" customHeight="1" s="50"/>
-    <row r="27" ht="13.5" customHeight="1" s="50"/>
-    <row r="28" ht="13.5" customHeight="1" s="50"/>
-    <row r="29" ht="13.5" customHeight="1" s="50"/>
-    <row r="30" ht="13.5" customHeight="1" s="50"/>
+    <row r="24" ht="13.5" customHeight="1" s="50">
+      <c r="A24" s="98" t="inlineStr">
+        <is>
+          <t>📊 机会成本比较（2026-06-04）</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="13.5" customHeight="1" s="50">
+      <c r="A25" s="99" t="inlineStr">
+        <is>
+          <t>选项</t>
+        </is>
+      </c>
+      <c r="B25" s="99" t="inlineStr">
+        <is>
+          <t>P值</t>
+        </is>
+      </c>
+      <c r="C25" s="99" t="inlineStr">
+        <is>
+          <t>盈亏比</t>
+        </is>
+      </c>
+      <c r="D25" s="99" t="inlineStr">
+        <is>
+          <t>P×R</t>
+        </is>
+      </c>
+      <c r="E25" s="99" t="inlineStr">
+        <is>
+          <t>仓位w</t>
+        </is>
+      </c>
+      <c r="F25" s="99" t="inlineStr">
+        <is>
+          <t>吸引力Score</t>
+        </is>
+      </c>
+      <c r="G25" s="99" t="inlineStr">
+        <is>
+          <t>双门槛</t>
+        </is>
+      </c>
+      <c r="H25" s="99" t="inlineStr">
+        <is>
+          <t>建议</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="13.5" customHeight="1" s="50">
+      <c r="A26" s="49" t="inlineStr">
+        <is>
+          <t>养殖014415</t>
+        </is>
+      </c>
+      <c r="B26" s="49" t="inlineStr">
+        <is>
+          <t>70%</t>
+        </is>
+      </c>
+      <c r="C26" s="49" t="inlineStr">
+        <is>
+          <t>2.0:1</t>
+        </is>
+      </c>
+      <c r="D26" s="49" t="inlineStr">
+        <is>
+          <t>1.40</t>
+        </is>
+      </c>
+      <c r="E26" s="49" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="F26" s="49" t="inlineStr">
+        <is>
+          <t>1.400</t>
+        </is>
+      </c>
+      <c r="G26" s="49" t="inlineStr">
+        <is>
+          <t>✅通过</t>
+        </is>
+      </c>
+      <c r="H26" s="49" t="inlineStr">
+        <is>
+          <t>🟢可配现金</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="13.5" customHeight="1" s="50">
+      <c r="A27" s="49" t="inlineStr">
+        <is>
+          <t>电池018926</t>
+        </is>
+      </c>
+      <c r="B27" s="49" t="inlineStr">
+        <is>
+          <t>65%</t>
+        </is>
+      </c>
+      <c r="C27" s="49" t="inlineStr">
+        <is>
+          <t>2.0:1</t>
+        </is>
+      </c>
+      <c r="D27" s="49" t="inlineStr">
+        <is>
+          <t>1.30</t>
+        </is>
+      </c>
+      <c r="E27" s="49" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="F27" s="49" t="inlineStr">
+        <is>
+          <t>1.300</t>
+        </is>
+      </c>
+      <c r="G27" s="49" t="inlineStr">
+        <is>
+          <t>✅通过</t>
+        </is>
+      </c>
+      <c r="H27" s="49" t="inlineStr">
+        <is>
+          <t>🟢可配现金</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="13.5" customHeight="1" s="50">
+      <c r="A28" s="49" t="inlineStr">
+        <is>
+          <t>有色004433</t>
+        </is>
+      </c>
+      <c r="B28" s="49" t="inlineStr">
+        <is>
+          <t>39%</t>
+        </is>
+      </c>
+      <c r="C28" s="49" t="inlineStr">
+        <is>
+          <t>0.7:1</t>
+        </is>
+      </c>
+      <c r="D28" s="49" t="inlineStr">
+        <is>
+          <t>0.27</t>
+        </is>
+      </c>
+      <c r="E28" s="49" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="F28" s="49" t="inlineStr">
+        <is>
+          <t>0.273</t>
+        </is>
+      </c>
+      <c r="G28" s="49" t="inlineStr">
+        <is>
+          <t>❌未通过</t>
+        </is>
+      </c>
+      <c r="H28" s="49" t="inlineStr">
+        <is>
+          <t>差20pp到P门槛</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="13.5" customHeight="1" s="50">
+      <c r="A29" s="49" t="inlineStr">
+        <is>
+          <t>稀金014111</t>
+        </is>
+      </c>
+      <c r="B29" s="49" t="inlineStr">
+        <is>
+          <t>40%</t>
+        </is>
+      </c>
+      <c r="C29" s="49" t="inlineStr">
+        <is>
+          <t>0.6:1</t>
+        </is>
+      </c>
+      <c r="D29" s="49" t="inlineStr">
+        <is>
+          <t>0.24</t>
+        </is>
+      </c>
+      <c r="E29" s="49" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="F29" s="49" t="inlineStr">
+        <is>
+          <t>0.240</t>
+        </is>
+      </c>
+      <c r="G29" s="49" t="inlineStr">
+        <is>
+          <t>❌未通过</t>
+        </is>
+      </c>
+      <c r="H29" s="49" t="inlineStr">
+        <is>
+          <t>差19pp到P门槛</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="13.5" customHeight="1" s="50">
+      <c r="A30" s="49" t="inlineStr">
+        <is>
+          <t>银行001595</t>
+        </is>
+      </c>
+      <c r="B30" s="49" t="inlineStr">
+        <is>
+          <t>47%</t>
+        </is>
+      </c>
+      <c r="C30" s="49" t="inlineStr">
+        <is>
+          <t>0.5:1</t>
+        </is>
+      </c>
+      <c r="D30" s="49" t="inlineStr">
+        <is>
+          <t>0.23</t>
+        </is>
+      </c>
+      <c r="E30" s="49" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="F30" s="49" t="inlineStr">
+        <is>
+          <t>0.235</t>
+        </is>
+      </c>
+      <c r="G30" s="49" t="inlineStr">
+        <is>
+          <t>❌未通过</t>
+        </is>
+      </c>
+      <c r="H30" s="49" t="inlineStr">
+        <is>
+          <t>差13pp到P门槛</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="49" t="inlineStr">
+        <is>
+          <t>恒科012349</t>
+        </is>
+      </c>
+      <c r="B31" s="49" t="inlineStr">
+        <is>
+          <t>29%</t>
+        </is>
+      </c>
+      <c r="C31" s="49" t="inlineStr">
+        <is>
+          <t>0.4:1</t>
+        </is>
+      </c>
+      <c r="D31" s="49" t="inlineStr">
+        <is>
+          <t>0.12</t>
+        </is>
+      </c>
+      <c r="E31" s="49" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="F31" s="49" t="inlineStr">
+        <is>
+          <t>0.116</t>
+        </is>
+      </c>
+      <c r="G31" s="49" t="inlineStr">
+        <is>
+          <t>❌未通过</t>
+        </is>
+      </c>
+      <c r="H31" s="49" t="inlineStr">
+        <is>
+          <t>差31pp到P门槛</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="49" t="inlineStr">
+        <is>
+          <t>芯片020628</t>
+        </is>
+      </c>
+      <c r="B32" s="49" t="inlineStr">
+        <is>
+          <t>44%</t>
+        </is>
+      </c>
+      <c r="C32" s="49" t="inlineStr">
+        <is>
+          <t>0.2:1</t>
+        </is>
+      </c>
+      <c r="D32" s="49" t="inlineStr">
+        <is>
+          <t>0.09</t>
+        </is>
+      </c>
+      <c r="E32" s="49" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="F32" s="49" t="inlineStr">
+        <is>
+          <t>0.088</t>
+        </is>
+      </c>
+      <c r="G32" s="49" t="inlineStr">
+        <is>
+          <t>❌未通过</t>
+        </is>
+      </c>
+      <c r="H32" s="49" t="inlineStr">
+        <is>
+          <t>差15pp到P门槛</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="49" t="inlineStr">
+        <is>
+          <t>AI027048</t>
+        </is>
+      </c>
+      <c r="B33" s="49" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C33" s="49" t="inlineStr">
+        <is>
+          <t>0.7:1</t>
+        </is>
+      </c>
+      <c r="D33" s="49" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="E33" s="49" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="F33" s="49" t="inlineStr">
+        <is>
+          <t>-1.000</t>
+        </is>
+      </c>
+      <c r="G33" s="49" t="inlineStr">
+        <is>
+          <t>❌未通过</t>
+        </is>
+      </c>
+      <c r="H33" s="49" t="inlineStr">
+        <is>
+          <t>差0.7到R门槛</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="49" t="inlineStr">
+        <is>
+          <t>💰 现金（基准线）</t>
+        </is>
+      </c>
+      <c r="D34" s="49" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="F34" s="49" t="inlineStr">
+        <is>
+          <t>0.000</t>
+        </is>
+      </c>
+      <c r="G34" s="49" t="inlineStr">
+        <is>
+          <t>基准</t>
+        </is>
+      </c>
+      <c r="H34" s="49" t="inlineStr">
+        <is>
+          <t>Score=0，所有选项都要跟现金比</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="100" t="inlineStr">
+        <is>
+          <t>📌 结论：现金该往哪分配</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="101" t="inlineStr">
+        <is>
+          <t>1. 养殖014415 — P=70% R=2.0:1 Score=1.400</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="101" t="inlineStr">
+        <is>
+          <t>2. 电池018926 — P=65% R=2.0:1 Score=1.300</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="49" t="inlineStr">
+        <is>
+          <t>📖 公式说明</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="49" t="inlineStr">
+        <is>
+          <t>吸引力Score = P×R - α×w×(1-P)  |  P=胜率 R=盈亏比 w=当前仓位占比 α=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="49" t="inlineStr">
+        <is>
+          <t>双门槛：P≥60% + 盈亏比≥2:1 → 通过 → 按Score排序分配现金</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="49" t="inlineStr">
+        <is>
+          <t>大白话：吸引力 = 机会多好(P×R) - 风险多重(w×不确定性)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="3">
+  <mergeCells count="4">
+    <mergeCell ref="A24:H24"/>
     <mergeCell ref="J4:J15"/>
     <mergeCell ref="J1:J3"/>
     <mergeCell ref="A1:H1"/>
@@ -3696,4 +4215,1202 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N42"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="6" customWidth="1" style="50" min="1" max="1"/>
+    <col width="14" customWidth="1" style="50" min="2" max="2"/>
+    <col width="10" customWidth="1" style="50" min="3" max="3"/>
+    <col width="14" customWidth="1" style="50" min="4" max="4"/>
+    <col width="8" customWidth="1" style="50" min="5" max="5"/>
+    <col width="8" customWidth="1" style="50" min="6" max="6"/>
+    <col width="8" customWidth="1" style="50" min="7" max="7"/>
+    <col width="8" customWidth="1" style="50" min="8" max="8"/>
+    <col width="8" customWidth="1" style="50" min="9" max="9"/>
+    <col width="12" customWidth="1" style="50" min="10" max="10"/>
+    <col width="10" customWidth="1" style="50" min="11" max="11"/>
+    <col width="14" customWidth="1" style="50" min="12" max="12"/>
+    <col width="30" customWidth="1" style="50" min="13" max="13"/>
+    <col width="25" customWidth="1" style="50" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="104" t="inlineStr">
+        <is>
+          <t>机会成本比较 边际量排序</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="105" t="inlineStr">
+        <is>
+          <t>审核日期：2026-06-04 | 下次预计审核：2026-06-11（每周日）| 方法：吸引力Score = P*R - alpha*w*(1-P)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="105" t="inlineStr">
+        <is>
+          <t>双门槛过滤：P&gt;=60% + 盈亏比&gt;=2:1 通过 按Score排序分配现金 | alpha=1.0（集中度厌恶系数）</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="106" t="inlineStr">
+        <is>
+          <t>排名</t>
+        </is>
+      </c>
+      <c r="B5" s="106" t="inlineStr">
+        <is>
+          <t>选项</t>
+        </is>
+      </c>
+      <c r="C5" s="106" t="inlineStr">
+        <is>
+          <t>代码</t>
+        </is>
+      </c>
+      <c r="D5" s="106" t="inlineStr">
+        <is>
+          <t>类型</t>
+        </is>
+      </c>
+      <c r="E5" s="106" t="inlineStr">
+        <is>
+          <t>P值</t>
+        </is>
+      </c>
+      <c r="F5" s="106" t="inlineStr">
+        <is>
+          <t>有效P</t>
+        </is>
+      </c>
+      <c r="G5" s="106" t="inlineStr">
+        <is>
+          <t>盈亏比</t>
+        </is>
+      </c>
+      <c r="H5" s="106" t="inlineStr">
+        <is>
+          <t>P*R</t>
+        </is>
+      </c>
+      <c r="I5" s="106" t="inlineStr">
+        <is>
+          <t>仓位w</t>
+        </is>
+      </c>
+      <c r="J5" s="106" t="inlineStr">
+        <is>
+          <t>吸引力Score</t>
+        </is>
+      </c>
+      <c r="K5" s="106" t="inlineStr">
+        <is>
+          <t>双门槛</t>
+        </is>
+      </c>
+      <c r="L5" s="106" t="inlineStr">
+        <is>
+          <t>建议操作</t>
+        </is>
+      </c>
+      <c r="M5" s="106" t="inlineStr">
+        <is>
+          <t>核心逻辑</t>
+        </is>
+      </c>
+      <c r="N5" s="106" t="inlineStr">
+        <is>
+          <t>风险提示</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="107" t="n">
+        <v>1</v>
+      </c>
+      <c r="B6" s="107" t="inlineStr">
+        <is>
+          <t>长电科技</t>
+        </is>
+      </c>
+      <c r="C6" s="107" t="inlineStr">
+        <is>
+          <t>600584</t>
+        </is>
+      </c>
+      <c r="D6" s="107" t="inlineStr">
+        <is>
+          <t>待重仓-堆叠</t>
+        </is>
+      </c>
+      <c r="E6" s="107" t="inlineStr">
+        <is>
+          <t>75%</t>
+        </is>
+      </c>
+      <c r="F6" s="107" t="inlineStr">
+        <is>
+          <t>69%</t>
+        </is>
+      </c>
+      <c r="G6" s="107" t="inlineStr">
+        <is>
+          <t>4.5:1</t>
+        </is>
+      </c>
+      <c r="H6" s="107" t="inlineStr">
+        <is>
+          <t>3.375</t>
+        </is>
+      </c>
+      <c r="I6" s="107" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="J6" s="107" t="inlineStr">
+        <is>
+          <t>3.3750</t>
+        </is>
+      </c>
+      <c r="K6" s="107" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+      <c r="L6" s="107" t="inlineStr">
+        <is>
+          <t>重点研究</t>
+        </is>
+      </c>
+      <c r="M6" s="107" t="inlineStr">
+        <is>
+          <t>全球第三大封测厂，2.5D/3D量产级，客户广度最强（高通/海思/TI）</t>
+        </is>
+      </c>
+      <c r="N6" s="107" t="inlineStr">
+        <is>
+          <t>先进封装估值偏高，需核实技术能力</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="107" t="n">
+        <v>2</v>
+      </c>
+      <c r="B7" s="107" t="inlineStr">
+        <is>
+          <t>通富微电</t>
+        </is>
+      </c>
+      <c r="C7" s="107" t="inlineStr">
+        <is>
+          <t>002156</t>
+        </is>
+      </c>
+      <c r="D7" s="107" t="inlineStr">
+        <is>
+          <t>待重仓-堆叠</t>
+        </is>
+      </c>
+      <c r="E7" s="107" t="inlineStr">
+        <is>
+          <t>75%</t>
+        </is>
+      </c>
+      <c r="F7" s="107" t="inlineStr">
+        <is>
+          <t>69%</t>
+        </is>
+      </c>
+      <c r="G7" s="107" t="inlineStr">
+        <is>
+          <t>4.0:1</t>
+        </is>
+      </c>
+      <c r="H7" s="107" t="inlineStr">
+        <is>
+          <t>3.000</t>
+        </is>
+      </c>
+      <c r="I7" s="107" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="J7" s="107" t="inlineStr">
+        <is>
+          <t>3.0000</t>
+        </is>
+      </c>
+      <c r="K7" s="107" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+      <c r="L7" s="107" t="inlineStr">
+        <is>
+          <t>重点研究</t>
+        </is>
+      </c>
+      <c r="M7" s="107" t="inlineStr">
+        <is>
+          <t>AMD封测全线突破通道，2.5D量产，不可替代</t>
+        </is>
+      </c>
+      <c r="N7" s="107" t="inlineStr">
+        <is>
+          <t>先进封装估值偏高，需核实技术能力</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="107" t="n">
+        <v>3</v>
+      </c>
+      <c r="B8" s="107" t="inlineStr">
+        <is>
+          <t>养殖014415</t>
+        </is>
+      </c>
+      <c r="C8" s="107" t="inlineStr">
+        <is>
+          <t>养殖014415</t>
+        </is>
+      </c>
+      <c r="D8" s="107" t="inlineStr">
+        <is>
+          <t>持仓</t>
+        </is>
+      </c>
+      <c r="E8" s="107" t="inlineStr">
+        <is>
+          <t>70%</t>
+        </is>
+      </c>
+      <c r="F8" s="107" t="inlineStr">
+        <is>
+          <t>70%</t>
+        </is>
+      </c>
+      <c r="G8" s="107" t="inlineStr">
+        <is>
+          <t>2.0:1</t>
+        </is>
+      </c>
+      <c r="H8" s="107" t="inlineStr">
+        <is>
+          <t>1.400</t>
+        </is>
+      </c>
+      <c r="I8" s="107" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="J8" s="107" t="inlineStr">
+        <is>
+          <t>1.4000</t>
+        </is>
+      </c>
+      <c r="K8" s="107" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+      <c r="L8" s="107" t="inlineStr">
+        <is>
+          <t>持有</t>
+        </is>
+      </c>
+      <c r="M8" s="107" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N8" s="107" t="inlineStr">
+        <is>
+          <t>已持仓持有，利率折价0pp</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="107" t="n">
+        <v>4</v>
+      </c>
+      <c r="B9" s="107" t="inlineStr">
+        <is>
+          <t>电池018926</t>
+        </is>
+      </c>
+      <c r="C9" s="107" t="inlineStr">
+        <is>
+          <t>电池018926</t>
+        </is>
+      </c>
+      <c r="D9" s="107" t="inlineStr">
+        <is>
+          <t>持仓</t>
+        </is>
+      </c>
+      <c r="E9" s="107" t="inlineStr">
+        <is>
+          <t>65%</t>
+        </is>
+      </c>
+      <c r="F9" s="107" t="inlineStr">
+        <is>
+          <t>59%</t>
+        </is>
+      </c>
+      <c r="G9" s="107" t="inlineStr">
+        <is>
+          <t>2.0:1</t>
+        </is>
+      </c>
+      <c r="H9" s="107" t="inlineStr">
+        <is>
+          <t>1.300</t>
+        </is>
+      </c>
+      <c r="I9" s="107" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="J9" s="107" t="inlineStr">
+        <is>
+          <t>1.3000</t>
+        </is>
+      </c>
+      <c r="K9" s="107" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+      <c r="L9" s="107" t="inlineStr">
+        <is>
+          <t>持有</t>
+        </is>
+      </c>
+      <c r="M9" s="107" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N9" s="107" t="inlineStr">
+        <is>
+          <t>已持仓持有，利率折价6pp</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="70" t="n">
+        <v>5</v>
+      </c>
+      <c r="B10" s="70" t="inlineStr">
+        <is>
+          <t>核电</t>
+        </is>
+      </c>
+      <c r="C10" s="70" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D10" s="70" t="inlineStr">
+        <is>
+          <t>待重仓-核电</t>
+        </is>
+      </c>
+      <c r="E10" s="70" t="inlineStr">
+        <is>
+          <t>52%</t>
+        </is>
+      </c>
+      <c r="F10" s="70" t="inlineStr">
+        <is>
+          <t>52%</t>
+        </is>
+      </c>
+      <c r="G10" s="70" t="inlineStr">
+        <is>
+          <t>1.5:1</t>
+        </is>
+      </c>
+      <c r="H10" s="70" t="inlineStr">
+        <is>
+          <t>0.780</t>
+        </is>
+      </c>
+      <c r="I10" s="70" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="J10" s="70" t="inlineStr">
+        <is>
+          <t>0.7800</t>
+        </is>
+      </c>
+      <c r="K10" s="108" t="inlineStr">
+        <is>
+          <t>未通过</t>
+        </is>
+      </c>
+      <c r="L10" s="70" t="inlineStr">
+        <is>
+          <t>长期跟踪</t>
+        </is>
+      </c>
+      <c r="M10" s="70" t="inlineStr">
+        <is>
+          <t>孙宇晨10年看核电，AI算力电力需求，审批加速</t>
+        </is>
+      </c>
+      <c r="N10" s="70" t="inlineStr">
+        <is>
+          <t>短期业绩承压Q1负34%，建设周期长5-8年</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="70" t="n">
+        <v>6</v>
+      </c>
+      <c r="B11" s="70" t="inlineStr">
+        <is>
+          <t>银行001595</t>
+        </is>
+      </c>
+      <c r="C11" s="70" t="inlineStr">
+        <is>
+          <t>银行001595</t>
+        </is>
+      </c>
+      <c r="D11" s="70" t="inlineStr">
+        <is>
+          <t>持仓</t>
+        </is>
+      </c>
+      <c r="E11" s="70" t="inlineStr">
+        <is>
+          <t>47%</t>
+        </is>
+      </c>
+      <c r="F11" s="70" t="inlineStr">
+        <is>
+          <t>47%</t>
+        </is>
+      </c>
+      <c r="G11" s="70" t="inlineStr">
+        <is>
+          <t>1.5:1</t>
+        </is>
+      </c>
+      <c r="H11" s="70" t="inlineStr">
+        <is>
+          <t>0.705</t>
+        </is>
+      </c>
+      <c r="I11" s="70" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="J11" s="70" t="inlineStr">
+        <is>
+          <t>0.7050</t>
+        </is>
+      </c>
+      <c r="K11" s="108" t="inlineStr">
+        <is>
+          <t>未通过</t>
+        </is>
+      </c>
+      <c r="L11" s="70" t="inlineStr">
+        <is>
+          <t>监控</t>
+        </is>
+      </c>
+      <c r="M11" s="70" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N11" s="70" t="inlineStr">
+        <is>
+          <t>已持仓监控，利率折价0pp</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="70" t="n">
+        <v>7</v>
+      </c>
+      <c r="B12" s="70" t="inlineStr">
+        <is>
+          <t>有色004433</t>
+        </is>
+      </c>
+      <c r="C12" s="70" t="inlineStr">
+        <is>
+          <t>有色004433</t>
+        </is>
+      </c>
+      <c r="D12" s="70" t="inlineStr">
+        <is>
+          <t>持仓</t>
+        </is>
+      </c>
+      <c r="E12" s="70" t="inlineStr">
+        <is>
+          <t>39%</t>
+        </is>
+      </c>
+      <c r="F12" s="70" t="inlineStr">
+        <is>
+          <t>35%</t>
+        </is>
+      </c>
+      <c r="G12" s="70" t="inlineStr">
+        <is>
+          <t>1.7:1</t>
+        </is>
+      </c>
+      <c r="H12" s="70" t="inlineStr">
+        <is>
+          <t>0.663</t>
+        </is>
+      </c>
+      <c r="I12" s="70" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="J12" s="70" t="inlineStr">
+        <is>
+          <t>0.6630</t>
+        </is>
+      </c>
+      <c r="K12" s="108" t="inlineStr">
+        <is>
+          <t>未通过</t>
+        </is>
+      </c>
+      <c r="L12" s="70" t="inlineStr">
+        <is>
+          <t>观望</t>
+        </is>
+      </c>
+      <c r="M12" s="70" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N12" s="70" t="inlineStr">
+        <is>
+          <t>已持仓观望，利率折价4pp</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="70" t="n">
+        <v>8</v>
+      </c>
+      <c r="B13" s="70" t="inlineStr">
+        <is>
+          <t>稀金014111</t>
+        </is>
+      </c>
+      <c r="C13" s="70" t="inlineStr">
+        <is>
+          <t>稀金014111</t>
+        </is>
+      </c>
+      <c r="D13" s="70" t="inlineStr">
+        <is>
+          <t>持仓</t>
+        </is>
+      </c>
+      <c r="E13" s="70" t="inlineStr">
+        <is>
+          <t>40%</t>
+        </is>
+      </c>
+      <c r="F13" s="70" t="inlineStr">
+        <is>
+          <t>36%</t>
+        </is>
+      </c>
+      <c r="G13" s="70" t="inlineStr">
+        <is>
+          <t>1.6:1</t>
+        </is>
+      </c>
+      <c r="H13" s="70" t="inlineStr">
+        <is>
+          <t>0.640</t>
+        </is>
+      </c>
+      <c r="I13" s="70" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="J13" s="70" t="inlineStr">
+        <is>
+          <t>0.6400</t>
+        </is>
+      </c>
+      <c r="K13" s="108" t="inlineStr">
+        <is>
+          <t>未通过</t>
+        </is>
+      </c>
+      <c r="L13" s="70" t="inlineStr">
+        <is>
+          <t>观望</t>
+        </is>
+      </c>
+      <c r="M13" s="70" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N13" s="70" t="inlineStr">
+        <is>
+          <t>已持仓观望，利率折价4pp</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="70" t="n">
+        <v>9</v>
+      </c>
+      <c r="B14" s="70" t="inlineStr">
+        <is>
+          <t>存储赛道</t>
+        </is>
+      </c>
+      <c r="C14" s="70" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D14" s="70" t="inlineStr">
+        <is>
+          <t>待重仓-存储</t>
+        </is>
+      </c>
+      <c r="E14" s="70" t="inlineStr">
+        <is>
+          <t>55%</t>
+        </is>
+      </c>
+      <c r="F14" s="70" t="inlineStr">
+        <is>
+          <t>49%</t>
+        </is>
+      </c>
+      <c r="G14" s="70" t="inlineStr">
+        <is>
+          <t>1.0:1</t>
+        </is>
+      </c>
+      <c r="H14" s="70" t="inlineStr">
+        <is>
+          <t>0.550</t>
+        </is>
+      </c>
+      <c r="I14" s="70" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="J14" s="70" t="inlineStr">
+        <is>
+          <t>0.5500</t>
+        </is>
+      </c>
+      <c r="K14" s="108" t="inlineStr">
+        <is>
+          <t>未通过</t>
+        </is>
+      </c>
+      <c r="L14" s="70" t="inlineStr">
+        <is>
+          <t>降级观察</t>
+        </is>
+      </c>
+      <c r="M14" s="70" t="inlineStr">
+        <is>
+          <t>兆易525元涨81% PE天际线，安全边际不足</t>
+        </is>
+      </c>
+      <c r="N14" s="70" t="inlineStr">
+        <is>
+          <t>安全边际不足，PE天际线，向上小于向下</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="70" t="n">
+        <v>10</v>
+      </c>
+      <c r="B15" s="70" t="inlineStr">
+        <is>
+          <t>芯片020628</t>
+        </is>
+      </c>
+      <c r="C15" s="70" t="inlineStr">
+        <is>
+          <t>芯片020628</t>
+        </is>
+      </c>
+      <c r="D15" s="70" t="inlineStr">
+        <is>
+          <t>持仓</t>
+        </is>
+      </c>
+      <c r="E15" s="70" t="inlineStr">
+        <is>
+          <t>44%</t>
+        </is>
+      </c>
+      <c r="F15" s="70" t="inlineStr">
+        <is>
+          <t>38%</t>
+        </is>
+      </c>
+      <c r="G15" s="70" t="inlineStr">
+        <is>
+          <t>1.2:1</t>
+        </is>
+      </c>
+      <c r="H15" s="70" t="inlineStr">
+        <is>
+          <t>0.528</t>
+        </is>
+      </c>
+      <c r="I15" s="70" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="J15" s="70" t="inlineStr">
+        <is>
+          <t>0.5280</t>
+        </is>
+      </c>
+      <c r="K15" s="108" t="inlineStr">
+        <is>
+          <t>未通过</t>
+        </is>
+      </c>
+      <c r="L15" s="70" t="inlineStr">
+        <is>
+          <t>观望</t>
+        </is>
+      </c>
+      <c r="M15" s="70" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N15" s="70" t="inlineStr">
+        <is>
+          <t>已持仓观望，利率折价6pp</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="70" t="n">
+        <v>11</v>
+      </c>
+      <c r="B16" s="70" t="inlineStr">
+        <is>
+          <t>恒科012349</t>
+        </is>
+      </c>
+      <c r="C16" s="70" t="inlineStr">
+        <is>
+          <t>恒科012349</t>
+        </is>
+      </c>
+      <c r="D16" s="70" t="inlineStr">
+        <is>
+          <t>持仓</t>
+        </is>
+      </c>
+      <c r="E16" s="70" t="inlineStr">
+        <is>
+          <t>29%</t>
+        </is>
+      </c>
+      <c r="F16" s="70" t="inlineStr">
+        <is>
+          <t>23%</t>
+        </is>
+      </c>
+      <c r="G16" s="70" t="inlineStr">
+        <is>
+          <t>0.4:1</t>
+        </is>
+      </c>
+      <c r="H16" s="70" t="inlineStr">
+        <is>
+          <t>0.116</t>
+        </is>
+      </c>
+      <c r="I16" s="70" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="J16" s="70" t="inlineStr">
+        <is>
+          <t>0.1160</t>
+        </is>
+      </c>
+      <c r="K16" s="108" t="inlineStr">
+        <is>
+          <t>未通过</t>
+        </is>
+      </c>
+      <c r="L16" s="70" t="inlineStr">
+        <is>
+          <t>不干</t>
+        </is>
+      </c>
+      <c r="M16" s="70" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N16" s="70" t="inlineStr">
+        <is>
+          <t>已持仓不干，利率折价5pp</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="109" t="n">
+        <v>12</v>
+      </c>
+      <c r="B17" s="109" t="inlineStr">
+        <is>
+          <t>现金</t>
+        </is>
+      </c>
+      <c r="C17" s="109" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D17" s="109" t="inlineStr">
+        <is>
+          <t>现金</t>
+        </is>
+      </c>
+      <c r="E17" s="109" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F17" s="109" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G17" s="109" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H17" s="109" t="inlineStr">
+        <is>
+          <t>0.000</t>
+        </is>
+      </c>
+      <c r="I17" s="109" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="J17" s="109" t="inlineStr">
+        <is>
+          <t>0.0000</t>
+        </is>
+      </c>
+      <c r="K17" s="109" t="inlineStr">
+        <is>
+          <t>基准</t>
+        </is>
+      </c>
+      <c r="L17" s="109" t="inlineStr">
+        <is>
+          <t>Score=0基准线</t>
+        </is>
+      </c>
+      <c r="M17" s="109" t="inlineStr">
+        <is>
+          <t>Score=0，所有选项都要跟现金比</t>
+        </is>
+      </c>
+      <c r="N17" s="109" t="inlineStr">
+        <is>
+          <t>无风险，但通胀侵蚀购买力</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="70" t="n">
+        <v>13</v>
+      </c>
+      <c r="B18" s="70" t="inlineStr">
+        <is>
+          <t>AI027048</t>
+        </is>
+      </c>
+      <c r="C18" s="70" t="inlineStr">
+        <is>
+          <t>AI027048</t>
+        </is>
+      </c>
+      <c r="D18" s="70" t="inlineStr">
+        <is>
+          <t>持仓</t>
+        </is>
+      </c>
+      <c r="E18" s="70" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F18" s="70" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G18" s="70" t="inlineStr">
+        <is>
+          <t>0.7:1</t>
+        </is>
+      </c>
+      <c r="H18" s="70" t="inlineStr">
+        <is>
+          <t>0.000</t>
+        </is>
+      </c>
+      <c r="I18" s="70" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="J18" s="70" t="inlineStr">
+        <is>
+          <t>-1.0000</t>
+        </is>
+      </c>
+      <c r="K18" s="108" t="inlineStr">
+        <is>
+          <t>未通过</t>
+        </is>
+      </c>
+      <c r="L18" s="70" t="inlineStr">
+        <is>
+          <t>不干</t>
+        </is>
+      </c>
+      <c r="M18" s="70" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N18" s="70" t="inlineStr">
+        <is>
+          <t>已持仓不干，利率折价0pp</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="110" t="inlineStr">
+        <is>
+          <t>结论：现金该往哪分配</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="100" t="inlineStr">
+        <is>
+          <t>1. 长电科技(600584) - P=75% R=4.5:1 Score=3.3750 目标仓位占比=37%的可投资金</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="100" t="inlineStr">
+        <is>
+          <t>2. 通富微电(002156) - P=75% R=4.0:1 Score=3.0000 目标仓位占比=33%的可投资金</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="100" t="inlineStr">
+        <is>
+          <t>3. 养殖014415(养殖014415) - P=70% R=2.0:1 Score=1.4000 目标仓位占比=15%的可投资金</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="100" t="inlineStr">
+        <is>
+          <t>4. 电池018926(电池018926) - P=65% R=2.0:1 Score=1.3000 目标仓位占比=14%的可投资金</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="100" t="inlineStr">
+        <is>
+          <t>未通过但接近的选项：</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>- 核电(-) - P=52% R=1.5:1 - P差8pp到门槛, R差0.5到门槛</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>- 存储赛道(-) - P=55% R=1.0:1 - P差5pp到门槛, R差1.0到门槛</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="101" t="inlineStr">
+        <is>
+          <t>现金：按Score排序，优先分配给最高Score选项</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="100" t="inlineStr">
+        <is>
+          <t>方法说明</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="111" t="inlineStr">
+        <is>
+          <t>1. 吸引力Score = P*R - alpha*w*(1-P) | P=胜率 R=盈亏比 w=当前仓位占比 alpha=1.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="111" t="inlineStr">
+        <is>
+          <t>2. 大白话：吸引力 = 机会多好(P*R) 减去 风险多重(仓位乘不确定性)</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="111" t="inlineStr">
+        <is>
+          <t>3. 双门槛：P&gt;=60% + 盈亏比&gt;=2:1 通过 按Score排序分配现金</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="111" t="inlineStr">
+        <is>
+          <t>4. 目标仓位分配：按P*R比例分配可投资金（通过门槛的选项）</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="111" t="inlineStr">
+        <is>
+          <t>5. 饱和度检查：当前仓位/目标仓位 小于50%加仓，大于100%减仓</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="111" t="inlineStr">
+        <is>
+          <t>6. 有效P = P + 利率折价（成长股-6pp/周期股-4pp/防御股0pp）</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="111" t="inlineStr">
+        <is>
+          <t>7. 审核频率：每周日一次 + P值跨越60%阈值时 + 新机会加入时</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="111" t="inlineStr">
+        <is>
+          <t>8. 本次审核：2026-06-04 | 下次预计：2026-06-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="111" t="inlineStr">
+        <is>
+          <t>9. 数据来源：Sheet2持仓数据 + 待重仓监控.md + 6/4盘中价格</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="111" t="inlineStr">
+        <is>
+          <t>10. 小龙虾技术分析：长电科技(先进封装广度最强) + 通富微电(AMD封测不可替代)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="23">
+    <mergeCell ref="A40:N40"/>
+    <mergeCell ref="A39:N39"/>
+    <mergeCell ref="A34:N34"/>
+    <mergeCell ref="A24:N24"/>
+    <mergeCell ref="A30:N30"/>
+    <mergeCell ref="A36:N36"/>
+    <mergeCell ref="A1:N1"/>
+    <mergeCell ref="A41:N41"/>
+    <mergeCell ref="A37:N37"/>
+    <mergeCell ref="A27:N27"/>
+    <mergeCell ref="A3:N3"/>
+    <mergeCell ref="A26:N26"/>
+    <mergeCell ref="A21:N21"/>
+    <mergeCell ref="A2:N2"/>
+    <mergeCell ref="A33:N33"/>
+    <mergeCell ref="A42:N42"/>
+    <mergeCell ref="A23:N23"/>
+    <mergeCell ref="A32:N32"/>
+    <mergeCell ref="A22:N22"/>
+    <mergeCell ref="A35:N35"/>
+    <mergeCell ref="A20:N20"/>
+    <mergeCell ref="A38:N38"/>
+    <mergeCell ref="A28:N28"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/持仓贝叶斯跟踪.xlsx
+++ b/持仓贝叶斯跟踪.xlsx
@@ -20,7 +20,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="39">
+  <fonts count="42">
     <font>
       <name val="Calibri"/>
       <charset val="1"/>
@@ -264,8 +264,22 @@
     <font>
       <sz val="10"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FF0000"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="000000FF"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00006600"/>
+    </font>
   </fonts>
-  <fills count="20">
+  <fills count="21">
     <fill>
       <patternFill/>
     </fill>
@@ -380,6 +394,12 @@
         <bgColor rgb="00FFEB9C"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E8F5E9"/>
+        <bgColor rgb="00E8F5E9"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="7">
     <border>
@@ -441,7 +461,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="112">
+  <cellXfs count="118">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -754,6 +774,14 @@
     </xf>
     <xf numFmtId="0" fontId="37" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="38" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="30" fillId="15" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="20" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2693,7 +2721,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:J44"/>
+  <dimension ref="A1:K79"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="10.4921875" defaultRowHeight="12.75" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="32" customWidth="1" style="49" min="1" max="8"/>
@@ -3836,12 +3864,846 @@
         </is>
       </c>
     </row>
+    <row r="46">
+      <c r="A46" s="112" t="inlineStr">
+        <is>
+          <t>机制库 &amp; 机会成本排序（2026-06-04）</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="113" t="inlineStr">
+        <is>
+          <t>[机制1] 机会成本排序算法</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>公式：吸引力Score = P*R - alpha*w*(1-P)  |  P=胜率 R=盈亏比 w=仓位占比 alpha=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>原理：Kelly Criterion变体 + 集中度风险惩罚。大白话：吸引力=机会多好(P*R) - 风险多重(仓位*不确定性)</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>何时用：每次监控全流程完成后/新机会加入/用户问现金往哪走/每两周定期</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>设计原因：防止钱锁在烂仓位里。新机会w=0无惩罚，重仓+低P惩罚最重。现金Score=0是基准线</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>科学依据：V4 Pro多轮讨论审核通过(2026-06-03)。不是直觉，是数学推导</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="113" t="inlineStr">
+        <is>
+          <t>[机制2] Spearman秩相关拟合算法</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>公式：拟合分 = rho*50 + 50  |  rho=Spearman秩相关系数（scipy.stats.spearmanr）</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>原理：衡量P值累计趋势与价格累计趋势的单调一致性。允许非线性、允许滞后、不要求同天同向</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>何时用：每两周或手动触发。样本&gt;=5个数据点才有效（&lt;5不稳定）</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>设计原因：看板是信息温度计，需要验证温度计准不准。拟合好=信源加分，拟合差=信源减分</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>科学依据：Spearman比Pearson更适合金融时间序列（不要求线性关系，只看单调性）</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="114" t="inlineStr">
+        <is>
+          <t>排名</t>
+        </is>
+      </c>
+      <c r="B61" s="114" t="inlineStr">
+        <is>
+          <t>选项</t>
+        </is>
+      </c>
+      <c r="C61" s="114" t="inlineStr">
+        <is>
+          <t>类型</t>
+        </is>
+      </c>
+      <c r="D61" s="114" t="inlineStr">
+        <is>
+          <t>P值</t>
+        </is>
+      </c>
+      <c r="E61" s="114" t="inlineStr">
+        <is>
+          <t>盈亏比</t>
+        </is>
+      </c>
+      <c r="F61" s="114" t="inlineStr">
+        <is>
+          <t>P*R</t>
+        </is>
+      </c>
+      <c r="G61" s="114" t="inlineStr">
+        <is>
+          <t>仓位w</t>
+        </is>
+      </c>
+      <c r="H61" s="114" t="inlineStr">
+        <is>
+          <t>风险惩罚</t>
+        </is>
+      </c>
+      <c r="I61" s="114" t="inlineStr">
+        <is>
+          <t>吸引力Score</t>
+        </is>
+      </c>
+      <c r="J61" s="114" t="inlineStr">
+        <is>
+          <t>双门槛</t>
+        </is>
+      </c>
+      <c r="K61" s="114" t="inlineStr">
+        <is>
+          <t>建议</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="115" t="n">
+        <v>1</v>
+      </c>
+      <c r="B62" s="115" t="inlineStr">
+        <is>
+          <t>长电科技(堆叠)</t>
+        </is>
+      </c>
+      <c r="C62" s="115" t="inlineStr">
+        <is>
+          <t>待重仓</t>
+        </is>
+      </c>
+      <c r="D62" s="115" t="inlineStr">
+        <is>
+          <t>75%</t>
+        </is>
+      </c>
+      <c r="E62" s="115" t="inlineStr">
+        <is>
+          <t>4.5:1</t>
+        </is>
+      </c>
+      <c r="F62" s="115" t="inlineStr">
+        <is>
+          <t>3.38</t>
+        </is>
+      </c>
+      <c r="G62" s="115" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="H62" s="115" t="inlineStr">
+        <is>
+          <t>-0.000</t>
+        </is>
+      </c>
+      <c r="I62" s="115" t="inlineStr">
+        <is>
+          <t>3.375</t>
+        </is>
+      </c>
+      <c r="J62" s="115" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+      <c r="K62" s="115" t="inlineStr">
+        <is>
+          <t>目标37%可投资金</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="115" t="n">
+        <v>2</v>
+      </c>
+      <c r="B63" s="115" t="inlineStr">
+        <is>
+          <t>通富微电(堆叠)</t>
+        </is>
+      </c>
+      <c r="C63" s="115" t="inlineStr">
+        <is>
+          <t>待重仓</t>
+        </is>
+      </c>
+      <c r="D63" s="115" t="inlineStr">
+        <is>
+          <t>75%</t>
+        </is>
+      </c>
+      <c r="E63" s="115" t="inlineStr">
+        <is>
+          <t>4.0:1</t>
+        </is>
+      </c>
+      <c r="F63" s="115" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+      <c r="G63" s="115" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="H63" s="115" t="inlineStr">
+        <is>
+          <t>-0.000</t>
+        </is>
+      </c>
+      <c r="I63" s="115" t="inlineStr">
+        <is>
+          <t>3.000</t>
+        </is>
+      </c>
+      <c r="J63" s="115" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+      <c r="K63" s="115" t="inlineStr">
+        <is>
+          <t>目标33%可投资金</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="115" t="n">
+        <v>3</v>
+      </c>
+      <c r="B64" s="115" t="inlineStr">
+        <is>
+          <t>养殖014415</t>
+        </is>
+      </c>
+      <c r="C64" s="115" t="inlineStr">
+        <is>
+          <t>持仓</t>
+        </is>
+      </c>
+      <c r="D64" s="115" t="inlineStr">
+        <is>
+          <t>70%</t>
+        </is>
+      </c>
+      <c r="E64" s="115" t="inlineStr">
+        <is>
+          <t>2.0:1</t>
+        </is>
+      </c>
+      <c r="F64" s="115" t="inlineStr">
+        <is>
+          <t>1.40</t>
+        </is>
+      </c>
+      <c r="G64" s="115" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="H64" s="115" t="inlineStr">
+        <is>
+          <t>-0.000</t>
+        </is>
+      </c>
+      <c r="I64" s="115" t="inlineStr">
+        <is>
+          <t>1.400</t>
+        </is>
+      </c>
+      <c r="J64" s="115" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+      <c r="K64" s="115" t="inlineStr">
+        <is>
+          <t>目标15%可投资金</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="115" t="n">
+        <v>4</v>
+      </c>
+      <c r="B65" s="115" t="inlineStr">
+        <is>
+          <t>电池018926</t>
+        </is>
+      </c>
+      <c r="C65" s="115" t="inlineStr">
+        <is>
+          <t>持仓</t>
+        </is>
+      </c>
+      <c r="D65" s="115" t="inlineStr">
+        <is>
+          <t>65%</t>
+        </is>
+      </c>
+      <c r="E65" s="115" t="inlineStr">
+        <is>
+          <t>2.0:1</t>
+        </is>
+      </c>
+      <c r="F65" s="115" t="inlineStr">
+        <is>
+          <t>1.30</t>
+        </is>
+      </c>
+      <c r="G65" s="115" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="H65" s="115" t="inlineStr">
+        <is>
+          <t>-0.000</t>
+        </is>
+      </c>
+      <c r="I65" s="115" t="inlineStr">
+        <is>
+          <t>1.300</t>
+        </is>
+      </c>
+      <c r="J65" s="115" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+      <c r="K65" s="115" t="inlineStr">
+        <is>
+          <t>目标14%可投资金</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>5</v>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>存储赛道</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>待重仓</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>55%</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>2.0:1</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>1.10</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>-0.000</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>1.100</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>未通过</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>P差4pp</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>6</v>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>核电</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>待重仓</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>52%</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>1.5:1</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>0.78</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>-0.000</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>0.780</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>未通过</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>P差7pp + R差0.5</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>7</v>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>银行001595</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>持仓</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>47%</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>1.5:1</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>0.70</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>-0.000</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>0.705</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>未通过</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>P差13pp + R差0.5</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>8</v>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>有色004433</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>持仓</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>39%</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>1.7:1</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>0.66</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>-0.000</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>0.663</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>未通过</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>P差20pp + R差0.3</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>9</v>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>稀金014111</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>持仓</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>40%</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>1.6:1</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>0.64</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>-0.000</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>0.640</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>未通过</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>P差19pp + R差0.4</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>10</v>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>芯片020628</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>持仓</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>44%</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>1.2:1</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>0.53</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>-0.000</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>0.528</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>未通过</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>P差15pp + R差0.8</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>11</v>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>恒科012349</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>持仓</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>29%</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>0.4:1</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>0.12</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>-0.000</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>0.116</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>未通过</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>P差31pp + R差1.6</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="B73" s="101" t="inlineStr">
+        <is>
+          <t>现金（基准线）</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>基准</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>0.000</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>基准</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>Score=0，所有选项都要跟现金比</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="116" t="inlineStr">
+        <is>
+          <t>结论：现金该往哪分配</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="117" t="inlineStr">
+        <is>
+          <t>1. 长电科技(堆叠) P=75% R=4.5:1 Score=3.375 目标37%可投资金</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="117" t="inlineStr">
+        <is>
+          <t>2. 通富微电(堆叠) P=75% R=4.0:1 Score=3.000 目标33%可投资金</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="117" t="inlineStr">
+        <is>
+          <t>3. 养殖014415 P=70% R=2.0:1 Score=1.400 目标15%可投资金</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="117" t="inlineStr">
+        <is>
+          <t>4. 电池018926 P=65% R=2.0:1 Score=1.300 目标14%可投资金</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="4">
+  <mergeCells count="18">
+    <mergeCell ref="A58:K58"/>
+    <mergeCell ref="A50:K50"/>
+    <mergeCell ref="A48:K48"/>
+    <mergeCell ref="A54:K54"/>
+    <mergeCell ref="A55:K55"/>
     <mergeCell ref="A24:H24"/>
+    <mergeCell ref="A59:K59"/>
+    <mergeCell ref="A57:K57"/>
+    <mergeCell ref="A49:K49"/>
+    <mergeCell ref="A51:K51"/>
+    <mergeCell ref="A47:K47"/>
+    <mergeCell ref="A52:K52"/>
+    <mergeCell ref="A46:K46"/>
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A75:K75"/>
     <mergeCell ref="J4:J15"/>
+    <mergeCell ref="A56:K56"/>
     <mergeCell ref="J1:J3"/>
-    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
@@ -5288,14 +6150,14 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" t="inlineStr">
+      <c r="A27" s="49" t="inlineStr">
         <is>
           <t>- 核电(-) - P=52% R=1.5:1 - P差8pp到门槛, R差0.5到门槛</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" t="inlineStr">
+      <c r="A28" s="49" t="inlineStr">
         <is>
           <t>- 存储赛道(-) - P=55% R=1.0:1 - P差5pp到门槛, R差1.0到门槛</t>
         </is>

--- a/持仓贝叶斯跟踪.xlsx
+++ b/持仓贝叶斯跟踪.xlsx
@@ -20,7 +20,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="42">
+  <fonts count="43">
     <font>
       <name val="Calibri"/>
       <charset val="1"/>
@@ -278,6 +278,10 @@
       <b val="1"/>
       <color rgb="00006600"/>
     </font>
+    <font>
+      <b val="1"/>
+      <sz val="10"/>
+    </font>
   </fonts>
   <fills count="21">
     <fill>
@@ -461,7 +465,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="118">
+  <cellXfs count="121">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -782,6 +786,15 @@
     <xf numFmtId="0" fontId="0" fillId="20" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="32" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="41" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="32" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2725,7 +2738,8 @@
   <sheetFormatPr baseColWidth="8" defaultColWidth="10.4921875" defaultRowHeight="12.75" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="32" customWidth="1" style="49" min="1" max="8"/>
-    <col width="35.94" customWidth="1" style="49" min="10" max="10"/>
+    <col width="28" customWidth="1" style="50" min="9" max="9"/>
+    <col width="28" customWidth="1" style="49" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1" ht="13.5" customHeight="1" s="50">
@@ -2734,14 +2748,7 @@
           <t>📈 持仓贝叶斯完整记录 (8只横排)</t>
         </is>
       </c>
-      <c r="B1" s="78" t="n"/>
-      <c r="C1" s="78" t="n"/>
-      <c r="D1" s="78" t="n"/>
-      <c r="E1" s="78" t="n"/>
-      <c r="F1" s="78" t="n"/>
-      <c r="G1" s="78" t="n"/>
-      <c r="H1" s="79" t="n"/>
-      <c r="J1" s="80" t="inlineStr">
+      <c r="J1" s="118" t="inlineStr">
         <is>
           <t>📊 盈亏比说明</t>
         </is>
@@ -2794,6 +2801,18 @@
         <is>
           <t>AI027048
 [蚊子]</t>
+        </is>
+      </c>
+      <c r="I2" s="119" t="inlineStr">
+        <is>
+          <t>存储(赛道)
+[观察]</t>
+        </is>
+      </c>
+      <c r="J2" s="119" t="inlineStr">
+        <is>
+          <t>核电(赛道)
+[观察]</t>
         </is>
       </c>
     </row>
@@ -2895,6 +2914,48 @@
 下行:30% 确定性:20% 溢价:40%
 盈亏比:0.7:1
 决策:不干</t>
+        </is>
+      </c>
+      <c r="I3" s="120" t="inlineStr">
+        <is>
+          <t>P:55%
+虚P-15pp(6/3→6/4认知升级)
+利率折价-4pp
+有效P:51%
+拟合✅(6/3分析)
+下行:25% 确定性:40% 溢价:80%
+盈亏比:5.0:1(保守2:1)
+决策:降级观察(安全边际不足)
+---
+事件链:
+2026-06-03 +15pp 群联潘健成:Flash供应仍严重不足,明年更紧张(产业一线⭐⭐⭐⭐)
+2026-06-03 +10pp 蒋宇飞:两长存储=国产存储双雄,三级火箭Flash→DRAM→CoWoS→3D堆叠
+2026-06-03 +10pp 蒋宇飞框架:"越靠近GPU越值钱",存储&gt;光模块10倍
+2026-06-03 +5pp 周鸿祎:"内存决定AI高度"
+2026-06-03 +10pp 宋鸿兵:摩尔定律终结→堆叠/存储崛起
+2026-06-04 -15pp 用户认知升级:存储机会尾声→堆叠才是主线,兆易创新2月涨81%安全边际不足
+→ 净P:55%(极高确定性但估值已透支)</t>
+        </is>
+      </c>
+      <c r="J3" s="120" t="inlineStr">
+        <is>
+          <t>P:52%
+虚P无
+利率折价-2pp
+有效P:50%
+拟合N/A(新赛道)
+下行:15% 确定性:25% 溢价:40%
+盈亏比:1.5:1(长期3:1)
+决策:观察(10年维度)
+---
+事件链:
+2026-06-04 +10pp 孙宇晨:"未来10年看核电",10亿美元押注物理AI→电力是核心瓶颈
+2026-06-04 +10pp Sereneity/Leopold:AI物理瓶颈=材料+电力/土地,盯电力基础设施
+2026-06-04 +12pp 行业数据:美国数据中心规划245GW,2028年占全美电力6.7%-12%
+2026-06-04 +10pp 国内政策:2025年核准10台机组(审批加速),金七门2号2026年4月FCD
+2026-06-04 -10pp 短期风险:中国核电2026Q1净利-34.19%,电价下行压力
+→ 净P:52%(4条独立信源同向,短期业绩承压)
+→ 标的:中广核003816(PE10-12x便宜) / 中国核电601985(PE25x偏贵)</t>
         </is>
       </c>
     </row>
@@ -3879,35 +3940,35 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" t="inlineStr">
+      <c r="A48" s="49" t="inlineStr">
         <is>
           <t>公式：吸引力Score = P*R - alpha*w*(1-P)  |  P=胜率 R=盈亏比 w=仓位占比 alpha=1</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" t="inlineStr">
+      <c r="A49" s="49" t="inlineStr">
         <is>
           <t>原理：Kelly Criterion变体 + 集中度风险惩罚。大白话：吸引力=机会多好(P*R) - 风险多重(仓位*不确定性)</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" t="inlineStr">
+      <c r="A50" s="49" t="inlineStr">
         <is>
           <t>何时用：每次监控全流程完成后/新机会加入/用户问现金往哪走/每两周定期</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="A51" t="inlineStr">
+      <c r="A51" s="49" t="inlineStr">
         <is>
           <t>设计原因：防止钱锁在烂仓位里。新机会w=0无惩罚，重仓+低P惩罚最重。现金Score=0是基准线</t>
         </is>
       </c>
     </row>
     <row r="52">
-      <c r="A52" t="inlineStr">
+      <c r="A52" s="49" t="inlineStr">
         <is>
           <t>科学依据：V4 Pro多轮讨论审核通过(2026-06-03)。不是直觉，是数学推导</t>
         </is>
@@ -3921,35 +3982,35 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" t="inlineStr">
+      <c r="A55" s="49" t="inlineStr">
         <is>
           <t>公式：拟合分 = rho*50 + 50  |  rho=Spearman秩相关系数（scipy.stats.spearmanr）</t>
         </is>
       </c>
     </row>
     <row r="56">
-      <c r="A56" t="inlineStr">
+      <c r="A56" s="49" t="inlineStr">
         <is>
           <t>原理：衡量P值累计趋势与价格累计趋势的单调一致性。允许非线性、允许滞后、不要求同天同向</t>
         </is>
       </c>
     </row>
     <row r="57">
-      <c r="A57" t="inlineStr">
+      <c r="A57" s="49" t="inlineStr">
         <is>
           <t>何时用：每两周或手动触发。样本&gt;=5个数据点才有效（&lt;5不稳定）</t>
         </is>
       </c>
     </row>
     <row r="58">
-      <c r="A58" t="inlineStr">
+      <c r="A58" s="49" t="inlineStr">
         <is>
           <t>设计原因：看板是信息温度计，需要验证温度计准不准。拟合好=信源加分，拟合差=信源减分</t>
         </is>
       </c>
     </row>
     <row r="59">
-      <c r="A59" t="inlineStr">
+      <c r="A59" s="49" t="inlineStr">
         <is>
           <t>科学依据：Spearman比Pearson更适合金融时间序列（不要求线性关系，只看单调性）</t>
         </is>
@@ -4233,385 +4294,385 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" t="n">
+      <c r="A66" s="49" t="n">
         <v>5</v>
       </c>
-      <c r="B66" t="inlineStr">
+      <c r="B66" s="49" t="inlineStr">
         <is>
           <t>存储赛道</t>
         </is>
       </c>
-      <c r="C66" t="inlineStr">
+      <c r="C66" s="49" t="inlineStr">
         <is>
           <t>待重仓</t>
         </is>
       </c>
-      <c r="D66" t="inlineStr">
+      <c r="D66" s="49" t="inlineStr">
         <is>
           <t>55%</t>
         </is>
       </c>
-      <c r="E66" t="inlineStr">
+      <c r="E66" s="49" t="inlineStr">
         <is>
           <t>2.0:1</t>
         </is>
       </c>
-      <c r="F66" t="inlineStr">
+      <c r="F66" s="49" t="inlineStr">
         <is>
           <t>1.10</t>
         </is>
       </c>
-      <c r="G66" t="inlineStr">
+      <c r="G66" s="49" t="inlineStr">
         <is>
           <t>0.0%</t>
         </is>
       </c>
-      <c r="H66" t="inlineStr">
+      <c r="H66" s="49" t="inlineStr">
         <is>
           <t>-0.000</t>
         </is>
       </c>
-      <c r="I66" t="inlineStr">
+      <c r="I66" s="49" t="inlineStr">
         <is>
           <t>1.100</t>
         </is>
       </c>
-      <c r="J66" t="inlineStr">
+      <c r="J66" s="49" t="inlineStr">
         <is>
           <t>未通过</t>
         </is>
       </c>
-      <c r="K66" t="inlineStr">
+      <c r="K66" s="49" t="inlineStr">
         <is>
           <t>P差4pp</t>
         </is>
       </c>
     </row>
     <row r="67">
-      <c r="A67" t="n">
+      <c r="A67" s="49" t="n">
         <v>6</v>
       </c>
-      <c r="B67" t="inlineStr">
+      <c r="B67" s="49" t="inlineStr">
         <is>
           <t>核电</t>
         </is>
       </c>
-      <c r="C67" t="inlineStr">
+      <c r="C67" s="49" t="inlineStr">
         <is>
           <t>待重仓</t>
         </is>
       </c>
-      <c r="D67" t="inlineStr">
+      <c r="D67" s="49" t="inlineStr">
         <is>
           <t>52%</t>
         </is>
       </c>
-      <c r="E67" t="inlineStr">
+      <c r="E67" s="49" t="inlineStr">
         <is>
           <t>1.5:1</t>
         </is>
       </c>
-      <c r="F67" t="inlineStr">
+      <c r="F67" s="49" t="inlineStr">
         <is>
           <t>0.78</t>
         </is>
       </c>
-      <c r="G67" t="inlineStr">
+      <c r="G67" s="49" t="inlineStr">
         <is>
           <t>0.0%</t>
         </is>
       </c>
-      <c r="H67" t="inlineStr">
+      <c r="H67" s="49" t="inlineStr">
         <is>
           <t>-0.000</t>
         </is>
       </c>
-      <c r="I67" t="inlineStr">
+      <c r="I67" s="49" t="inlineStr">
         <is>
           <t>0.780</t>
         </is>
       </c>
-      <c r="J67" t="inlineStr">
+      <c r="J67" s="49" t="inlineStr">
         <is>
           <t>未通过</t>
         </is>
       </c>
-      <c r="K67" t="inlineStr">
+      <c r="K67" s="49" t="inlineStr">
         <is>
           <t>P差7pp + R差0.5</t>
         </is>
       </c>
     </row>
     <row r="68">
-      <c r="A68" t="n">
+      <c r="A68" s="49" t="n">
         <v>7</v>
       </c>
-      <c r="B68" t="inlineStr">
+      <c r="B68" s="49" t="inlineStr">
         <is>
           <t>银行001595</t>
         </is>
       </c>
-      <c r="C68" t="inlineStr">
+      <c r="C68" s="49" t="inlineStr">
         <is>
           <t>持仓</t>
         </is>
       </c>
-      <c r="D68" t="inlineStr">
+      <c r="D68" s="49" t="inlineStr">
         <is>
           <t>47%</t>
         </is>
       </c>
-      <c r="E68" t="inlineStr">
+      <c r="E68" s="49" t="inlineStr">
         <is>
           <t>1.5:1</t>
         </is>
       </c>
-      <c r="F68" t="inlineStr">
+      <c r="F68" s="49" t="inlineStr">
         <is>
           <t>0.70</t>
         </is>
       </c>
-      <c r="G68" t="inlineStr">
+      <c r="G68" s="49" t="inlineStr">
         <is>
           <t>0.0%</t>
         </is>
       </c>
-      <c r="H68" t="inlineStr">
+      <c r="H68" s="49" t="inlineStr">
         <is>
           <t>-0.000</t>
         </is>
       </c>
-      <c r="I68" t="inlineStr">
+      <c r="I68" s="49" t="inlineStr">
         <is>
           <t>0.705</t>
         </is>
       </c>
-      <c r="J68" t="inlineStr">
+      <c r="J68" s="49" t="inlineStr">
         <is>
           <t>未通过</t>
         </is>
       </c>
-      <c r="K68" t="inlineStr">
+      <c r="K68" s="49" t="inlineStr">
         <is>
           <t>P差13pp + R差0.5</t>
         </is>
       </c>
     </row>
     <row r="69">
-      <c r="A69" t="n">
+      <c r="A69" s="49" t="n">
         <v>8</v>
       </c>
-      <c r="B69" t="inlineStr">
+      <c r="B69" s="49" t="inlineStr">
         <is>
           <t>有色004433</t>
         </is>
       </c>
-      <c r="C69" t="inlineStr">
+      <c r="C69" s="49" t="inlineStr">
         <is>
           <t>持仓</t>
         </is>
       </c>
-      <c r="D69" t="inlineStr">
+      <c r="D69" s="49" t="inlineStr">
         <is>
           <t>39%</t>
         </is>
       </c>
-      <c r="E69" t="inlineStr">
+      <c r="E69" s="49" t="inlineStr">
         <is>
           <t>1.7:1</t>
         </is>
       </c>
-      <c r="F69" t="inlineStr">
+      <c r="F69" s="49" t="inlineStr">
         <is>
           <t>0.66</t>
         </is>
       </c>
-      <c r="G69" t="inlineStr">
+      <c r="G69" s="49" t="inlineStr">
         <is>
           <t>0.0%</t>
         </is>
       </c>
-      <c r="H69" t="inlineStr">
+      <c r="H69" s="49" t="inlineStr">
         <is>
           <t>-0.000</t>
         </is>
       </c>
-      <c r="I69" t="inlineStr">
+      <c r="I69" s="49" t="inlineStr">
         <is>
           <t>0.663</t>
         </is>
       </c>
-      <c r="J69" t="inlineStr">
+      <c r="J69" s="49" t="inlineStr">
         <is>
           <t>未通过</t>
         </is>
       </c>
-      <c r="K69" t="inlineStr">
+      <c r="K69" s="49" t="inlineStr">
         <is>
           <t>P差20pp + R差0.3</t>
         </is>
       </c>
     </row>
     <row r="70">
-      <c r="A70" t="n">
+      <c r="A70" s="49" t="n">
         <v>9</v>
       </c>
-      <c r="B70" t="inlineStr">
+      <c r="B70" s="49" t="inlineStr">
         <is>
           <t>稀金014111</t>
         </is>
       </c>
-      <c r="C70" t="inlineStr">
+      <c r="C70" s="49" t="inlineStr">
         <is>
           <t>持仓</t>
         </is>
       </c>
-      <c r="D70" t="inlineStr">
+      <c r="D70" s="49" t="inlineStr">
         <is>
           <t>40%</t>
         </is>
       </c>
-      <c r="E70" t="inlineStr">
+      <c r="E70" s="49" t="inlineStr">
         <is>
           <t>1.6:1</t>
         </is>
       </c>
-      <c r="F70" t="inlineStr">
+      <c r="F70" s="49" t="inlineStr">
         <is>
           <t>0.64</t>
         </is>
       </c>
-      <c r="G70" t="inlineStr">
+      <c r="G70" s="49" t="inlineStr">
         <is>
           <t>0.0%</t>
         </is>
       </c>
-      <c r="H70" t="inlineStr">
+      <c r="H70" s="49" t="inlineStr">
         <is>
           <t>-0.000</t>
         </is>
       </c>
-      <c r="I70" t="inlineStr">
+      <c r="I70" s="49" t="inlineStr">
         <is>
           <t>0.640</t>
         </is>
       </c>
-      <c r="J70" t="inlineStr">
+      <c r="J70" s="49" t="inlineStr">
         <is>
           <t>未通过</t>
         </is>
       </c>
-      <c r="K70" t="inlineStr">
+      <c r="K70" s="49" t="inlineStr">
         <is>
           <t>P差19pp + R差0.4</t>
         </is>
       </c>
     </row>
     <row r="71">
-      <c r="A71" t="n">
+      <c r="A71" s="49" t="n">
         <v>10</v>
       </c>
-      <c r="B71" t="inlineStr">
+      <c r="B71" s="49" t="inlineStr">
         <is>
           <t>芯片020628</t>
         </is>
       </c>
-      <c r="C71" t="inlineStr">
+      <c r="C71" s="49" t="inlineStr">
         <is>
           <t>持仓</t>
         </is>
       </c>
-      <c r="D71" t="inlineStr">
+      <c r="D71" s="49" t="inlineStr">
         <is>
           <t>44%</t>
         </is>
       </c>
-      <c r="E71" t="inlineStr">
+      <c r="E71" s="49" t="inlineStr">
         <is>
           <t>1.2:1</t>
         </is>
       </c>
-      <c r="F71" t="inlineStr">
+      <c r="F71" s="49" t="inlineStr">
         <is>
           <t>0.53</t>
         </is>
       </c>
-      <c r="G71" t="inlineStr">
+      <c r="G71" s="49" t="inlineStr">
         <is>
           <t>0.0%</t>
         </is>
       </c>
-      <c r="H71" t="inlineStr">
+      <c r="H71" s="49" t="inlineStr">
         <is>
           <t>-0.000</t>
         </is>
       </c>
-      <c r="I71" t="inlineStr">
+      <c r="I71" s="49" t="inlineStr">
         <is>
           <t>0.528</t>
         </is>
       </c>
-      <c r="J71" t="inlineStr">
+      <c r="J71" s="49" t="inlineStr">
         <is>
           <t>未通过</t>
         </is>
       </c>
-      <c r="K71" t="inlineStr">
+      <c r="K71" s="49" t="inlineStr">
         <is>
           <t>P差15pp + R差0.8</t>
         </is>
       </c>
     </row>
     <row r="72">
-      <c r="A72" t="n">
+      <c r="A72" s="49" t="n">
         <v>11</v>
       </c>
-      <c r="B72" t="inlineStr">
+      <c r="B72" s="49" t="inlineStr">
         <is>
           <t>恒科012349</t>
         </is>
       </c>
-      <c r="C72" t="inlineStr">
+      <c r="C72" s="49" t="inlineStr">
         <is>
           <t>持仓</t>
         </is>
       </c>
-      <c r="D72" t="inlineStr">
+      <c r="D72" s="49" t="inlineStr">
         <is>
           <t>29%</t>
         </is>
       </c>
-      <c r="E72" t="inlineStr">
+      <c r="E72" s="49" t="inlineStr">
         <is>
           <t>0.4:1</t>
         </is>
       </c>
-      <c r="F72" t="inlineStr">
+      <c r="F72" s="49" t="inlineStr">
         <is>
           <t>0.12</t>
         </is>
       </c>
-      <c r="G72" t="inlineStr">
+      <c r="G72" s="49" t="inlineStr">
         <is>
           <t>0.0%</t>
         </is>
       </c>
-      <c r="H72" t="inlineStr">
+      <c r="H72" s="49" t="inlineStr">
         <is>
           <t>-0.000</t>
         </is>
       </c>
-      <c r="I72" t="inlineStr">
+      <c r="I72" s="49" t="inlineStr">
         <is>
           <t>0.116</t>
         </is>
       </c>
-      <c r="J72" t="inlineStr">
+      <c r="J72" s="49" t="inlineStr">
         <is>
           <t>未通过</t>
         </is>
       </c>
-      <c r="K72" t="inlineStr">
+      <c r="K72" s="49" t="inlineStr">
         <is>
           <t>P差31pp + R差1.6</t>
         </is>
@@ -4623,27 +4684,27 @@
           <t>现金（基准线）</t>
         </is>
       </c>
-      <c r="C73" t="inlineStr">
+      <c r="C73" s="49" t="inlineStr">
         <is>
           <t>基准</t>
         </is>
       </c>
-      <c r="F73" t="inlineStr">
+      <c r="F73" s="49" t="inlineStr">
         <is>
           <t>0.00</t>
         </is>
       </c>
-      <c r="I73" t="inlineStr">
+      <c r="I73" s="49" t="inlineStr">
         <is>
           <t>0.000</t>
         </is>
       </c>
-      <c r="J73" t="inlineStr">
+      <c r="J73" s="49" t="inlineStr">
         <is>
           <t>基准</t>
         </is>
       </c>
-      <c r="K73" t="inlineStr">
+      <c r="K73" s="49" t="inlineStr">
         <is>
           <t>Score=0，所有选项都要跟现金比</t>
         </is>
@@ -4685,7 +4746,7 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="18">
+  <mergeCells count="16">
     <mergeCell ref="A58:K58"/>
     <mergeCell ref="A50:K50"/>
     <mergeCell ref="A48:K48"/>
@@ -4699,11 +4760,9 @@
     <mergeCell ref="A47:K47"/>
     <mergeCell ref="A52:K52"/>
     <mergeCell ref="A46:K46"/>
-    <mergeCell ref="A1:H1"/>
     <mergeCell ref="A75:K75"/>
     <mergeCell ref="J4:J15"/>
     <mergeCell ref="A56:K56"/>
-    <mergeCell ref="J1:J3"/>
   </mergeCells>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>

--- a/持仓贝叶斯跟踪.xlsx
+++ b/持仓贝叶斯跟踪.xlsx
@@ -20,7 +20,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="43">
+  <fonts count="50">
     <font>
       <name val="Calibri"/>
       <charset val="1"/>
@@ -282,8 +282,40 @@
       <b val="1"/>
       <sz val="10"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FF0000"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <color rgb="00666666"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="000000FF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="000066CC"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00009900"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <sz val="9"/>
+    </font>
   </fonts>
-  <fills count="21">
+  <fills count="22">
     <fill>
       <patternFill/>
     </fill>
@@ -404,6 +436,12 @@
         <bgColor rgb="00E8F5E9"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF9C4"/>
+        <bgColor rgb="00FFF9C4"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="7">
     <border>
@@ -465,7 +503,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="121">
+  <cellXfs count="132">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -795,6 +833,19 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="44" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="45" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="47" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="48" fillId="15" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="20" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="21" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="29" fillId="21" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="49" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2734,12 +2785,21 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:K79"/>
+  <dimension ref="A1:L128"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="10.4921875" defaultRowHeight="12.75" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
-    <col width="32" customWidth="1" style="49" min="1" max="8"/>
-    <col width="28" customWidth="1" style="50" min="9" max="9"/>
-    <col width="28" customWidth="1" style="49" min="10" max="10"/>
+    <col width="18" customWidth="1" style="49" min="1" max="8"/>
+    <col width="18" customWidth="1" style="50" min="2" max="2"/>
+    <col width="18" customWidth="1" style="50" min="3" max="3"/>
+    <col width="18" customWidth="1" style="50" min="4" max="4"/>
+    <col width="18" customWidth="1" style="50" min="5" max="5"/>
+    <col width="18" customWidth="1" style="50" min="6" max="6"/>
+    <col width="18" customWidth="1" style="50" min="7" max="7"/>
+    <col width="18" customWidth="1" style="50" min="8" max="8"/>
+    <col width="18" customWidth="1" style="50" min="9" max="9"/>
+    <col width="18" customWidth="1" style="49" min="10" max="10"/>
+    <col width="18" customWidth="1" style="50" min="11" max="11"/>
+    <col width="18" customWidth="1" style="50" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1" ht="13.5" customHeight="1" s="50">
@@ -4745,24 +4805,1078 @@
         </is>
       </c>
     </row>
+    <row r="82">
+      <c r="A82" s="121" t="inlineStr">
+        <is>
+          <t>机制库 &amp; 机会成本排序（2026-06-04审核）</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="122" t="inlineStr">
+        <is>
+          <t>审核日期: 2026-06-04 | 下次审核: 2026-06-18（每两周）| 设计依据: V4 Pro多轮讨论审核通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="123" t="inlineStr">
+        <is>
+          <t>【机制1】机会成本排序算法（Opportunity Cost Ranking）</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="124" t="inlineStr">
+        <is>
+          <t>【公式】</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>吸引力Score = P×R - α×w×(1-P)  |  P=胜率(0-1) R=盈亏比 α=风险厌恶系数(=1) w=当前仓位占比</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="124" t="inlineStr">
+        <is>
+          <t>【大白话】</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>机会多好(P×R) - 风险多重(仓位×不确定性)。P高R高=机会好，w高P低=钱锁在烂仓位里惩罚重</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="124" t="inlineStr">
+        <is>
+          <t>【原理】</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Kelly Criterion变体 + 集中度风险惩罚。Kelly公式算最优下注比例，这里加了仓位惩罚项防止钱锁在低P高仓位里</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="124" t="inlineStr">
+        <is>
+          <t>【何时用】</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>①每次监控全流程完成后 ②新机会加入待重仓时 ③用户问现金往哪走 ④每两周定期审核</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="124" t="inlineStr">
+        <is>
+          <t>【设计原因】</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>防止钱锁在烂仓位里。新机会w=0无惩罚（鼓励发现新机会），重仓+低P惩罚最重（倒逼清仓或等P回升）。现金Score=0是基准线，所有选项都要跟现金比</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="124" t="inlineStr">
+        <is>
+          <t>【科学依据】</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>V4 Pro多轮讨论审核通过(2026-06-03)。不是直觉，是数学推导。Kelly Criterion是赌场最优下注理论，这里改编为投资吸引力评分</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="124" t="inlineStr">
+        <is>
+          <t>【参数说明】</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>α=1.0（风险厌恶系数，1表示中性风险偏好）。P来自贝叶斯事件链累加，R来自01-盈亏比计算方法论.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="123" t="inlineStr">
+        <is>
+          <t>【机制2】Spearman秩相关拟合算法（P值准确性校验）</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="124" t="inlineStr">
+        <is>
+          <t>【公式】</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>拟合分 = ρ×50 + 50  |  ρ=Spearman秩相关系数（scipy.stats.spearmanr）</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="124" t="inlineStr">
+        <is>
+          <t>【大白话】</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>P值趋势和价格走势一不一致。ρ=1完全一致（P涨价格就涨），ρ=-1完全反着来，ρ=0没关系</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="124" t="inlineStr">
+        <is>
+          <t>【原理】</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>衡量P值累计趋势与价格累计趋势的单调一致性。允许非线性、允许滞后、不要求同天同向。只看方向对不对，不看幅度准不准</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="124" t="inlineStr">
+        <is>
+          <t>【何时用】</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>①每两周定期 ②手动触发 ③样本≥5个数据点才有效（&lt;5不稳定，Spearman需要足够样本量）</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="124" t="inlineStr">
+        <is>
+          <t>【设计原因】</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>看板是信息温度计，需要验证温度计准不准。拟合好=信源加分（P值可靠），拟合差=信源减分（P值可能虚高）。跑2-3轮复盘后过滤垃圾信源</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="124" t="inlineStr">
+        <is>
+          <t>【科学依据】</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Spearman比Pearson更适合金融时间序列。Pearson要求线性关系，Spearman只看单调性（方向一致就行）。金融数据很少线性，但方向关系很重要。V4 Pro审核通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="124" t="inlineStr">
+        <is>
+          <t>【输出解读】</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>拟合分≥80=优秀（信源可靠） 60-80=合格（需关注） &lt;60=不合格（信源可能有问题，需审查事件链）</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="125" t="inlineStr">
+        <is>
+          <t>机会成本+边际量排序表（全池：持仓+待重仓+现金）</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="126" t="inlineStr">
+        <is>
+          <t>排名</t>
+        </is>
+      </c>
+      <c r="B104" s="126" t="inlineStr">
+        <is>
+          <t>选项</t>
+        </is>
+      </c>
+      <c r="C104" s="126" t="inlineStr">
+        <is>
+          <t>类型</t>
+        </is>
+      </c>
+      <c r="D104" s="126" t="inlineStr">
+        <is>
+          <t>P值</t>
+        </is>
+      </c>
+      <c r="E104" s="126" t="inlineStr">
+        <is>
+          <t>盈亏比R</t>
+        </is>
+      </c>
+      <c r="F104" s="126" t="inlineStr">
+        <is>
+          <t>P×R(吸引力)</t>
+        </is>
+      </c>
+      <c r="G104" s="126" t="inlineStr">
+        <is>
+          <t>仓位w</t>
+        </is>
+      </c>
+      <c r="H104" s="126" t="inlineStr">
+        <is>
+          <t>风险惩罚</t>
+        </is>
+      </c>
+      <c r="I104" s="126" t="inlineStr">
+        <is>
+          <t>Score</t>
+        </is>
+      </c>
+      <c r="J104" s="126" t="inlineStr">
+        <is>
+          <t>双门槛</t>
+        </is>
+      </c>
+      <c r="K104" s="126" t="inlineStr">
+        <is>
+          <t>决策信号</t>
+        </is>
+      </c>
+      <c r="L104" s="126" t="inlineStr">
+        <is>
+          <t>边际量说明</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="127" t="n">
+        <v>1</v>
+      </c>
+      <c r="B105" s="127" t="inlineStr">
+        <is>
+          <t>长电科技(堆叠)</t>
+        </is>
+      </c>
+      <c r="C105" s="127" t="inlineStr">
+        <is>
+          <t>待重仓</t>
+        </is>
+      </c>
+      <c r="D105" s="127" t="inlineStr">
+        <is>
+          <t>75%</t>
+        </is>
+      </c>
+      <c r="E105" s="127" t="inlineStr">
+        <is>
+          <t>4.5:1</t>
+        </is>
+      </c>
+      <c r="F105" s="127" t="inlineStr">
+        <is>
+          <t>3.375</t>
+        </is>
+      </c>
+      <c r="G105" s="127" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="H105" s="127" t="inlineStr">
+        <is>
+          <t>-0.0000</t>
+        </is>
+      </c>
+      <c r="I105" s="127" t="inlineStr">
+        <is>
+          <t>3.3750</t>
+        </is>
+      </c>
+      <c r="J105" s="127" t="inlineStr">
+        <is>
+          <t>✅通过</t>
+        </is>
+      </c>
+      <c r="K105" s="127" t="inlineStr">
+        <is>
+          <t>目标37%可投资金</t>
+        </is>
+      </c>
+      <c r="L105" s="127" t="inlineStr">
+        <is>
+          <t>堆叠第一梯队，安全边际大，PE30x合理偏低</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="127" t="n">
+        <v>2</v>
+      </c>
+      <c r="B106" s="127" t="inlineStr">
+        <is>
+          <t>通富微电(堆叠)</t>
+        </is>
+      </c>
+      <c r="C106" s="127" t="inlineStr">
+        <is>
+          <t>待重仓</t>
+        </is>
+      </c>
+      <c r="D106" s="127" t="inlineStr">
+        <is>
+          <t>75%</t>
+        </is>
+      </c>
+      <c r="E106" s="127" t="inlineStr">
+        <is>
+          <t>4.0:1</t>
+        </is>
+      </c>
+      <c r="F106" s="127" t="inlineStr">
+        <is>
+          <t>3.000</t>
+        </is>
+      </c>
+      <c r="G106" s="127" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="H106" s="127" t="inlineStr">
+        <is>
+          <t>-0.0000</t>
+        </is>
+      </c>
+      <c r="I106" s="127" t="inlineStr">
+        <is>
+          <t>3.0000</t>
+        </is>
+      </c>
+      <c r="J106" s="127" t="inlineStr">
+        <is>
+          <t>✅通过</t>
+        </is>
+      </c>
+      <c r="K106" s="127" t="inlineStr">
+        <is>
+          <t>目标33%可投资金</t>
+        </is>
+      </c>
+      <c r="L106" s="127" t="inlineStr">
+        <is>
+          <t>AMD唯一封测通道，不可替代性强</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="127" t="n">
+        <v>3</v>
+      </c>
+      <c r="B107" s="127" t="inlineStr">
+        <is>
+          <t>养殖014415</t>
+        </is>
+      </c>
+      <c r="C107" s="127" t="inlineStr">
+        <is>
+          <t>持仓</t>
+        </is>
+      </c>
+      <c r="D107" s="127" t="inlineStr">
+        <is>
+          <t>70%</t>
+        </is>
+      </c>
+      <c r="E107" s="127" t="inlineStr">
+        <is>
+          <t>2.0:1</t>
+        </is>
+      </c>
+      <c r="F107" s="127" t="inlineStr">
+        <is>
+          <t>1.400</t>
+        </is>
+      </c>
+      <c r="G107" s="127" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
+      </c>
+      <c r="H107" s="127" t="inlineStr">
+        <is>
+          <t>-0.0300</t>
+        </is>
+      </c>
+      <c r="I107" s="127" t="inlineStr">
+        <is>
+          <t>1.3700</t>
+        </is>
+      </c>
+      <c r="J107" s="127" t="inlineStr">
+        <is>
+          <t>✅通过</t>
+        </is>
+      </c>
+      <c r="K107" s="127" t="inlineStr">
+        <is>
+          <t>目标15%可投资金</t>
+        </is>
+      </c>
+      <c r="L107" s="127" t="inlineStr">
+        <is>
+          <t>左侧等右侧，P值最高</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="127" t="n">
+        <v>4</v>
+      </c>
+      <c r="B108" s="127" t="inlineStr">
+        <is>
+          <t>电池018926</t>
+        </is>
+      </c>
+      <c r="C108" s="127" t="inlineStr">
+        <is>
+          <t>持仓</t>
+        </is>
+      </c>
+      <c r="D108" s="127" t="inlineStr">
+        <is>
+          <t>65%</t>
+        </is>
+      </c>
+      <c r="E108" s="127" t="inlineStr">
+        <is>
+          <t>2.0:1</t>
+        </is>
+      </c>
+      <c r="F108" s="127" t="inlineStr">
+        <is>
+          <t>1.300</t>
+        </is>
+      </c>
+      <c r="G108" s="127" t="inlineStr">
+        <is>
+          <t>12.0%</t>
+        </is>
+      </c>
+      <c r="H108" s="127" t="inlineStr">
+        <is>
+          <t>-0.0420</t>
+        </is>
+      </c>
+      <c r="I108" s="127" t="inlineStr">
+        <is>
+          <t>1.2580</t>
+        </is>
+      </c>
+      <c r="J108" s="127" t="inlineStr">
+        <is>
+          <t>✅通过</t>
+        </is>
+      </c>
+      <c r="K108" s="127" t="inlineStr">
+        <is>
+          <t>目标14%可投资金</t>
+        </is>
+      </c>
+      <c r="L108" s="127" t="inlineStr">
+        <is>
+          <t>右侧持仓，P值健康</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="128" t="n">
+        <v>5</v>
+      </c>
+      <c r="B109" s="128" t="inlineStr">
+        <is>
+          <t>存储赛道</t>
+        </is>
+      </c>
+      <c r="C109" s="128" t="inlineStr">
+        <is>
+          <t>待重仓</t>
+        </is>
+      </c>
+      <c r="D109" s="128" t="inlineStr">
+        <is>
+          <t>55%</t>
+        </is>
+      </c>
+      <c r="E109" s="128" t="inlineStr">
+        <is>
+          <t>2.0:1</t>
+        </is>
+      </c>
+      <c r="F109" s="128" t="inlineStr">
+        <is>
+          <t>1.100</t>
+        </is>
+      </c>
+      <c r="G109" s="128" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="H109" s="128" t="inlineStr">
+        <is>
+          <t>-0.0000</t>
+        </is>
+      </c>
+      <c r="I109" s="128" t="inlineStr">
+        <is>
+          <t>1.1000</t>
+        </is>
+      </c>
+      <c r="J109" s="128" t="inlineStr">
+        <is>
+          <t>❌未通过</t>
+        </is>
+      </c>
+      <c r="K109" s="128" t="inlineStr">
+        <is>
+          <t>P差4pp</t>
+        </is>
+      </c>
+      <c r="L109" s="128" t="inlineStr">
+        <is>
+          <t>机会尾声，兆易创新2月涨81%安全边际不足</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="128" t="n">
+        <v>6</v>
+      </c>
+      <c r="B110" s="128" t="inlineStr">
+        <is>
+          <t>核电赛道</t>
+        </is>
+      </c>
+      <c r="C110" s="128" t="inlineStr">
+        <is>
+          <t>待重仓</t>
+        </is>
+      </c>
+      <c r="D110" s="128" t="inlineStr">
+        <is>
+          <t>52%</t>
+        </is>
+      </c>
+      <c r="E110" s="128" t="inlineStr">
+        <is>
+          <t>1.5:1</t>
+        </is>
+      </c>
+      <c r="F110" s="128" t="inlineStr">
+        <is>
+          <t>0.780</t>
+        </is>
+      </c>
+      <c r="G110" s="128" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="H110" s="128" t="inlineStr">
+        <is>
+          <t>-0.0000</t>
+        </is>
+      </c>
+      <c r="I110" s="128" t="inlineStr">
+        <is>
+          <t>0.7800</t>
+        </is>
+      </c>
+      <c r="J110" s="128" t="inlineStr">
+        <is>
+          <t>❌未通过</t>
+        </is>
+      </c>
+      <c r="K110" s="128" t="inlineStr">
+        <is>
+          <t>P差7pp + R差0.5</t>
+        </is>
+      </c>
+      <c r="L110" s="128" t="inlineStr">
+        <is>
+          <t>10年维度，短期业绩承压，长期AI=核电范式</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="128" t="n">
+        <v>7</v>
+      </c>
+      <c r="B111" s="128" t="inlineStr">
+        <is>
+          <t>银行001595</t>
+        </is>
+      </c>
+      <c r="C111" s="128" t="inlineStr">
+        <is>
+          <t>持仓</t>
+        </is>
+      </c>
+      <c r="D111" s="128" t="inlineStr">
+        <is>
+          <t>48%</t>
+        </is>
+      </c>
+      <c r="E111" s="128" t="inlineStr">
+        <is>
+          <t>1.5:1</t>
+        </is>
+      </c>
+      <c r="F111" s="128" t="inlineStr">
+        <is>
+          <t>0.720</t>
+        </is>
+      </c>
+      <c r="G111" s="128" t="inlineStr">
+        <is>
+          <t>5.0%</t>
+        </is>
+      </c>
+      <c r="H111" s="128" t="inlineStr">
+        <is>
+          <t>-0.0260</t>
+        </is>
+      </c>
+      <c r="I111" s="128" t="inlineStr">
+        <is>
+          <t>0.6940</t>
+        </is>
+      </c>
+      <c r="J111" s="128" t="inlineStr">
+        <is>
+          <t>❌未通过</t>
+        </is>
+      </c>
+      <c r="K111" s="128" t="inlineStr">
+        <is>
+          <t>P差12pp + R差0.5</t>
+        </is>
+      </c>
+      <c r="L111" s="128" t="inlineStr">
+        <is>
+          <t>监控仓位，高股息防御</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="128" t="n">
+        <v>8</v>
+      </c>
+      <c r="B112" s="128" t="inlineStr">
+        <is>
+          <t>有色004433</t>
+        </is>
+      </c>
+      <c r="C112" s="128" t="inlineStr">
+        <is>
+          <t>持仓</t>
+        </is>
+      </c>
+      <c r="D112" s="128" t="inlineStr">
+        <is>
+          <t>39%</t>
+        </is>
+      </c>
+      <c r="E112" s="128" t="inlineStr">
+        <is>
+          <t>1.7:1</t>
+        </is>
+      </c>
+      <c r="F112" s="128" t="inlineStr">
+        <is>
+          <t>0.663</t>
+        </is>
+      </c>
+      <c r="G112" s="128" t="inlineStr">
+        <is>
+          <t>8.0%</t>
+        </is>
+      </c>
+      <c r="H112" s="128" t="inlineStr">
+        <is>
+          <t>-0.0488</t>
+        </is>
+      </c>
+      <c r="I112" s="128" t="inlineStr">
+        <is>
+          <t>0.6142</t>
+        </is>
+      </c>
+      <c r="J112" s="128" t="inlineStr">
+        <is>
+          <t>❌未通过</t>
+        </is>
+      </c>
+      <c r="K112" s="128" t="inlineStr">
+        <is>
+          <t>P差20pp + R差0.3</t>
+        </is>
+      </c>
+      <c r="L112" s="128" t="inlineStr">
+        <is>
+          <t>周期持仓，关税利空未出尽</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="128" t="n">
+        <v>9</v>
+      </c>
+      <c r="B113" s="128" t="inlineStr">
+        <is>
+          <t>稀金014111</t>
+        </is>
+      </c>
+      <c r="C113" s="128" t="inlineStr">
+        <is>
+          <t>持仓</t>
+        </is>
+      </c>
+      <c r="D113" s="128" t="inlineStr">
+        <is>
+          <t>40%</t>
+        </is>
+      </c>
+      <c r="E113" s="128" t="inlineStr">
+        <is>
+          <t>1.6:1</t>
+        </is>
+      </c>
+      <c r="F113" s="128" t="inlineStr">
+        <is>
+          <t>0.640</t>
+        </is>
+      </c>
+      <c r="G113" s="128" t="inlineStr">
+        <is>
+          <t>7.0%</t>
+        </is>
+      </c>
+      <c r="H113" s="128" t="inlineStr">
+        <is>
+          <t>-0.0420</t>
+        </is>
+      </c>
+      <c r="I113" s="128" t="inlineStr">
+        <is>
+          <t>0.5980</t>
+        </is>
+      </c>
+      <c r="J113" s="128" t="inlineStr">
+        <is>
+          <t>❌未通过</t>
+        </is>
+      </c>
+      <c r="K113" s="128" t="inlineStr">
+        <is>
+          <t>P差19pp + R差0.4</t>
+        </is>
+      </c>
+      <c r="L113" s="128" t="inlineStr">
+        <is>
+          <t>战略资源，与有色联动</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="128" t="n">
+        <v>10</v>
+      </c>
+      <c r="B114" s="128" t="inlineStr">
+        <is>
+          <t>芯片020628</t>
+        </is>
+      </c>
+      <c r="C114" s="128" t="inlineStr">
+        <is>
+          <t>持仓</t>
+        </is>
+      </c>
+      <c r="D114" s="128" t="inlineStr">
+        <is>
+          <t>44%</t>
+        </is>
+      </c>
+      <c r="E114" s="128" t="inlineStr">
+        <is>
+          <t>1.2:1</t>
+        </is>
+      </c>
+      <c r="F114" s="128" t="inlineStr">
+        <is>
+          <t>0.528</t>
+        </is>
+      </c>
+      <c r="G114" s="128" t="inlineStr">
+        <is>
+          <t>15.0%</t>
+        </is>
+      </c>
+      <c r="H114" s="128" t="inlineStr">
+        <is>
+          <t>-0.0840</t>
+        </is>
+      </c>
+      <c r="I114" s="128" t="inlineStr">
+        <is>
+          <t>0.4440</t>
+        </is>
+      </c>
+      <c r="J114" s="128" t="inlineStr">
+        <is>
+          <t>❌未通过</t>
+        </is>
+      </c>
+      <c r="K114" s="128" t="inlineStr">
+        <is>
+          <t>P差15pp + R差0.8</t>
+        </is>
+      </c>
+      <c r="L114" s="128" t="inlineStr">
+        <is>
+          <t>右侧持仓，P偏低但产业趋势强</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="129" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="B115" s="130" t="inlineStr">
+        <is>
+          <t>现金（基准线）</t>
+        </is>
+      </c>
+      <c r="C115" s="129" t="inlineStr">
+        <is>
+          <t>基准</t>
+        </is>
+      </c>
+      <c r="D115" s="129" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E115" s="129" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F115" s="129" t="inlineStr">
+        <is>
+          <t>0.000</t>
+        </is>
+      </c>
+      <c r="G115" s="129" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H115" s="129" t="inlineStr">
+        <is>
+          <t>0.0000</t>
+        </is>
+      </c>
+      <c r="I115" s="129" t="inlineStr">
+        <is>
+          <t>0.0000</t>
+        </is>
+      </c>
+      <c r="J115" s="129" t="inlineStr">
+        <is>
+          <t>基准</t>
+        </is>
+      </c>
+      <c r="K115" s="129" t="inlineStr">
+        <is>
+          <t>Score=0，所有选项都要跟现金比</t>
+        </is>
+      </c>
+      <c r="L115" s="129" t="inlineStr">
+        <is>
+          <t>无风险但无收益，通胀侵蚀购买力</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="112" t="inlineStr">
+        <is>
+          <t>结论：现金该往哪分配（2026-06-04审核）</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>1.</t>
+        </is>
+      </c>
+      <c r="B118" s="117" t="inlineStr">
+        <is>
+          <t>长电科技(堆叠) P=75% R=4.5:1 Score=3.3750 目标37%可投资金</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>2.</t>
+        </is>
+      </c>
+      <c r="B119" s="117" t="inlineStr">
+        <is>
+          <t>通富微电(堆叠) P=75% R=4.0:1 Score=3.0000 目标33%可投资金</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>3.</t>
+        </is>
+      </c>
+      <c r="B120" s="117" t="inlineStr">
+        <is>
+          <t>养殖014415 P=70% R=2.0:1 Score=1.3700 目标15%可投资金</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>4.</t>
+        </is>
+      </c>
+      <c r="B121" s="117" t="inlineStr">
+        <is>
+          <t>电池018926 P=65% R=2.0:1 Score=1.2580 目标14%可投资金</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="131" t="inlineStr">
+        <is>
+          <t>【宏观环境】4空2平1偏多。利率高位+关税利空+能源下行=宏观偏空，但产业端芯片/堆叠独立走强</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="131" t="inlineStr">
+        <is>
+          <t>【进攻方向】堆叠赛道（长电/通富）=当前最优机会。P=75% R=4-4.5:1 Score=3.0-3.4，远超其他选项</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="131" t="inlineStr">
+        <is>
+          <t>【防守方向】养殖P=70%最稳但R=2.0有限；电池P=65%次之</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="131" t="inlineStr">
+        <is>
+          <t>【观察项】存储P=55%差5pp过门槛（安全边际不足）；核电P=52%差8pp（10年维度不急）</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="131" t="inlineStr">
+        <is>
+          <t>【现金基准】所有Score&gt;0的选项都比持有现金好。但必须通过双门槛(P≥60%且R≥2.0)才建议分配</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="131" t="inlineStr">
+        <is>
+          <t>【下次审核】2026-06-18（每两周）。触发条件：①P值跨越60%阈值 ②新机会加入 ③用户问现金往哪走</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="16">
+  <mergeCells count="46">
     <mergeCell ref="A58:K58"/>
-    <mergeCell ref="A50:K50"/>
+    <mergeCell ref="B91:L91"/>
     <mergeCell ref="A48:K48"/>
-    <mergeCell ref="A54:K54"/>
-    <mergeCell ref="A55:K55"/>
+    <mergeCell ref="B97:L97"/>
+    <mergeCell ref="A128:L128"/>
+    <mergeCell ref="B100:L100"/>
     <mergeCell ref="A24:H24"/>
     <mergeCell ref="A59:K59"/>
-    <mergeCell ref="A57:K57"/>
+    <mergeCell ref="B90:L90"/>
     <mergeCell ref="A49:K49"/>
     <mergeCell ref="A51:K51"/>
+    <mergeCell ref="B121:L121"/>
+    <mergeCell ref="B96:L96"/>
+    <mergeCell ref="A54:K54"/>
+    <mergeCell ref="B86:L86"/>
+    <mergeCell ref="A85:L85"/>
+    <mergeCell ref="B120:L120"/>
+    <mergeCell ref="A46:K46"/>
+    <mergeCell ref="B101:L101"/>
+    <mergeCell ref="B98:L98"/>
+    <mergeCell ref="A126:L126"/>
+    <mergeCell ref="A75:K75"/>
+    <mergeCell ref="A56:K56"/>
+    <mergeCell ref="A125:L125"/>
+    <mergeCell ref="A50:K50"/>
+    <mergeCell ref="B88:L88"/>
+    <mergeCell ref="B119:L119"/>
+    <mergeCell ref="A55:K55"/>
+    <mergeCell ref="A117:L117"/>
+    <mergeCell ref="A57:K57"/>
+    <mergeCell ref="B87:L87"/>
     <mergeCell ref="A47:K47"/>
+    <mergeCell ref="A127:L127"/>
+    <mergeCell ref="B99:L99"/>
+    <mergeCell ref="A83:L83"/>
+    <mergeCell ref="B118:L118"/>
+    <mergeCell ref="A82:L82"/>
+    <mergeCell ref="B92:L92"/>
+    <mergeCell ref="A94:L94"/>
+    <mergeCell ref="A103:L103"/>
+    <mergeCell ref="A123:L123"/>
+    <mergeCell ref="B95:L95"/>
     <mergeCell ref="A52:K52"/>
-    <mergeCell ref="A46:K46"/>
-    <mergeCell ref="A75:K75"/>
+    <mergeCell ref="B89:L89"/>
+    <mergeCell ref="A124:L124"/>
     <mergeCell ref="J4:J15"/>
-    <mergeCell ref="A56:K56"/>
   </mergeCells>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>

--- a/持仓贝叶斯跟踪.xlsx
+++ b/持仓贝叶斯跟踪.xlsx
@@ -20,7 +20,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="50">
+  <fonts count="52">
     <font>
       <name val="Calibri"/>
       <charset val="1"/>
@@ -314,6 +314,14 @@
     <font>
       <sz val="9"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FF0000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <color rgb="00006600"/>
+    </font>
   </fonts>
   <fills count="22">
     <fill>
@@ -503,7 +511,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="132">
+  <cellXfs count="135">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -846,6 +854,13 @@
     <xf numFmtId="0" fontId="0" fillId="21" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="29" fillId="21" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="49" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="50" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="51" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1763,7 +1778,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:H49"/>
+  <dimension ref="A1:H53"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6171875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="22" customWidth="1" style="49" min="1" max="1"/>
@@ -2281,6 +2296,7 @@
         </is>
       </c>
     </row>
+    <row r="27"/>
     <row r="28" ht="15" customHeight="1" s="50">
       <c r="A28" s="68" t="inlineStr">
         <is>
@@ -2723,16 +2739,18 @@
       <c r="G44" s="49" t="n"/>
     </row>
     <row r="45" ht="16.5" customHeight="1" s="50">
-      <c r="A45" s="49" t="n"/>
-      <c r="B45" s="49" t="n"/>
-      <c r="C45" s="49" t="n"/>
-      <c r="D45" s="49" t="n"/>
-      <c r="E45" s="49" t="n"/>
-      <c r="F45" s="49" t="n"/>
-      <c r="G45" s="49" t="n"/>
+      <c r="A45" s="132" t="inlineStr">
+        <is>
+          <t>【历史事件恢复】（2026-06-04从backup_0603恢复，防止覆盖丢失）</t>
+        </is>
+      </c>
     </row>
     <row r="46" ht="16.5" customHeight="1" s="50">
-      <c r="A46" s="49" t="n"/>
+      <c r="A46" s="70" t="inlineStr">
+        <is>
+          <t>🔥 叙事主线（三条）</t>
+        </is>
+      </c>
       <c r="B46" s="49" t="n"/>
       <c r="C46" s="49" t="n"/>
       <c r="D46" s="49" t="n"/>
@@ -2742,7 +2760,11 @@
     </row>
     <row r="47" ht="16.5" customHeight="1" s="50">
       <c r="A47" s="49" t="n"/>
-      <c r="B47" s="49" t="n"/>
+      <c r="B47" s="70" t="inlineStr">
+        <is>
+          <t>①美国走钢丝：国债39万亿+30年美债破5%+10年破4.5%，沃什上任但市场用脚投票，利率只涨不跌</t>
+        </is>
+      </c>
       <c r="C47" s="49" t="n"/>
       <c r="D47" s="49" t="n"/>
       <c r="E47" s="49" t="n"/>
@@ -2751,15 +2773,79 @@
     </row>
     <row r="48" ht="16.5" customHeight="1" s="50">
       <c r="A48" s="49" t="n"/>
+      <c r="B48" s="70" t="inlineStr">
+        <is>
+          <t>②霍尔木兹封3个月：有效原油库存8.1亿桶，OECD最早6月触底，85%投资者押注回落=集体幻觉</t>
+        </is>
+      </c>
     </row>
     <row r="49" ht="16.5" customHeight="1" s="50">
       <c r="A49" s="49" t="n"/>
+      <c r="B49" s="70" t="inlineStr">
+        <is>
+          <t>③中国去杠杆但分化：08-18加杠杆→全面去杠杆，对猪周期是加速器，对AI是倒逼器</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="70" t="inlineStr">
+        <is>
+          <t>🟡 中观产业传导</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="70" t="inlineStr">
+        <is>
+          <t>AI硬件确定性(付鹏) → 内存=AI核心瓶颈(4信源互锁) → 国产替代加速 → 稀土断供日本 → 芯片/存储/HBM长期利好 | 短期被利率↑/地缘↑压制</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="70" t="inlineStr">
+        <is>
+          <t>⚡ 传导: 利率↑→成长股↓ | 地缘↑→避险↑能源↑ | 去杠杆→消费↓养殖↓ | AI产业↑→芯片/存储↑(长期)</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="70" t="inlineStr">
+        <is>
+          <t>2026-05-30 但斌：沃什缩表受阻+沃勒鹰派，降息预期降温</t>
+        </is>
+      </c>
+      <c r="C53" s="70" t="inlineStr">
+        <is>
+          <t>2026-05-30 宋鸿兵：伊朗3.0反击或封锁海峡</t>
+        </is>
+      </c>
+      <c r="D53" s="70" t="inlineStr">
+        <is>
+          <t>2026-05-30 付鹏：去杠杆周期中登最难受</t>
+        </is>
+      </c>
+      <c r="E53" s="70" t="inlineStr">
+        <is>
+          <t>2026-05-30 宋鸿兵：海峡封锁→能源成本飙升</t>
+        </is>
+      </c>
+      <c r="F53" s="70" t="inlineStr">
+        <is>
+          <t>2026-05-30 岩松：存储1-2年产能饱和</t>
+        </is>
+      </c>
+      <c r="G53" s="70" t="inlineStr">
+        <is>
+          <t>2026-05-30 宋鸿兵：30年美债破5%双红线</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="14">
+  <mergeCells count="15">
     <mergeCell ref="A12:H12"/>
     <mergeCell ref="A16:F16"/>
     <mergeCell ref="B14:H14"/>
+    <mergeCell ref="A1:H1"/>
     <mergeCell ref="D26:H26"/>
     <mergeCell ref="B13:H13"/>
     <mergeCell ref="B23:D23"/>
@@ -2769,8 +2855,8 @@
     <mergeCell ref="D24:G24"/>
     <mergeCell ref="A41:H41"/>
     <mergeCell ref="B15:H15"/>
-    <mergeCell ref="A1:H1"/>
     <mergeCell ref="A28:G28"/>
+    <mergeCell ref="A45:G45"/>
   </mergeCells>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -2785,7 +2871,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:L128"/>
+  <dimension ref="A1:L134"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="10.4921875" defaultRowHeight="12.75" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="18" customWidth="1" style="49" min="1" max="8"/>
@@ -4832,7 +4918,7 @@
           <t>【公式】</t>
         </is>
       </c>
-      <c r="B86" t="inlineStr">
+      <c r="B86" s="49" t="inlineStr">
         <is>
           <t>吸引力Score = P×R - α×w×(1-P)  |  P=胜率(0-1) R=盈亏比 α=风险厌恶系数(=1) w=当前仓位占比</t>
         </is>
@@ -4844,7 +4930,7 @@
           <t>【大白话】</t>
         </is>
       </c>
-      <c r="B87" t="inlineStr">
+      <c r="B87" s="49" t="inlineStr">
         <is>
           <t>机会多好(P×R) - 风险多重(仓位×不确定性)。P高R高=机会好，w高P低=钱锁在烂仓位里惩罚重</t>
         </is>
@@ -4856,7 +4942,7 @@
           <t>【原理】</t>
         </is>
       </c>
-      <c r="B88" t="inlineStr">
+      <c r="B88" s="49" t="inlineStr">
         <is>
           <t>Kelly Criterion变体 + 集中度风险惩罚。Kelly公式算最优下注比例，这里加了仓位惩罚项防止钱锁在低P高仓位里</t>
         </is>
@@ -4868,7 +4954,7 @@
           <t>【何时用】</t>
         </is>
       </c>
-      <c r="B89" t="inlineStr">
+      <c r="B89" s="49" t="inlineStr">
         <is>
           <t>①每次监控全流程完成后 ②新机会加入待重仓时 ③用户问现金往哪走 ④每两周定期审核</t>
         </is>
@@ -4880,7 +4966,7 @@
           <t>【设计原因】</t>
         </is>
       </c>
-      <c r="B90" t="inlineStr">
+      <c r="B90" s="49" t="inlineStr">
         <is>
           <t>防止钱锁在烂仓位里。新机会w=0无惩罚（鼓励发现新机会），重仓+低P惩罚最重（倒逼清仓或等P回升）。现金Score=0是基准线，所有选项都要跟现金比</t>
         </is>
@@ -4892,7 +4978,7 @@
           <t>【科学依据】</t>
         </is>
       </c>
-      <c r="B91" t="inlineStr">
+      <c r="B91" s="49" t="inlineStr">
         <is>
           <t>V4 Pro多轮讨论审核通过(2026-06-03)。不是直觉，是数学推导。Kelly Criterion是赌场最优下注理论，这里改编为投资吸引力评分</t>
         </is>
@@ -4904,7 +4990,7 @@
           <t>【参数说明】</t>
         </is>
       </c>
-      <c r="B92" t="inlineStr">
+      <c r="B92" s="49" t="inlineStr">
         <is>
           <t>α=1.0（风险厌恶系数，1表示中性风险偏好）。P来自贝叶斯事件链累加，R来自01-盈亏比计算方法论.md</t>
         </is>
@@ -4923,7 +5009,7 @@
           <t>【公式】</t>
         </is>
       </c>
-      <c r="B95" t="inlineStr">
+      <c r="B95" s="49" t="inlineStr">
         <is>
           <t>拟合分 = ρ×50 + 50  |  ρ=Spearman秩相关系数（scipy.stats.spearmanr）</t>
         </is>
@@ -4935,7 +5021,7 @@
           <t>【大白话】</t>
         </is>
       </c>
-      <c r="B96" t="inlineStr">
+      <c r="B96" s="49" t="inlineStr">
         <is>
           <t>P值趋势和价格走势一不一致。ρ=1完全一致（P涨价格就涨），ρ=-1完全反着来，ρ=0没关系</t>
         </is>
@@ -4947,7 +5033,7 @@
           <t>【原理】</t>
         </is>
       </c>
-      <c r="B97" t="inlineStr">
+      <c r="B97" s="49" t="inlineStr">
         <is>
           <t>衡量P值累计趋势与价格累计趋势的单调一致性。允许非线性、允许滞后、不要求同天同向。只看方向对不对，不看幅度准不准</t>
         </is>
@@ -4959,7 +5045,7 @@
           <t>【何时用】</t>
         </is>
       </c>
-      <c r="B98" t="inlineStr">
+      <c r="B98" s="49" t="inlineStr">
         <is>
           <t>①每两周定期 ②手动触发 ③样本≥5个数据点才有效（&lt;5不稳定，Spearman需要足够样本量）</t>
         </is>
@@ -4971,7 +5057,7 @@
           <t>【设计原因】</t>
         </is>
       </c>
-      <c r="B99" t="inlineStr">
+      <c r="B99" s="49" t="inlineStr">
         <is>
           <t>看板是信息温度计，需要验证温度计准不准。拟合好=信源加分（P值可靠），拟合差=信源减分（P值可能虚高）。跑2-3轮复盘后过滤垃圾信源</t>
         </is>
@@ -4983,7 +5069,7 @@
           <t>【科学依据】</t>
         </is>
       </c>
-      <c r="B100" t="inlineStr">
+      <c r="B100" s="49" t="inlineStr">
         <is>
           <t>Spearman比Pearson更适合金融时间序列。Pearson要求线性关系，Spearman只看单调性（方向一致就行）。金融数据很少线性，但方向关系很重要。V4 Pro审核通过</t>
         </is>
@@ -4995,7 +5081,7 @@
           <t>【输出解读】</t>
         </is>
       </c>
-      <c r="B101" t="inlineStr">
+      <c r="B101" s="49" t="inlineStr">
         <is>
           <t>拟合分≥80=优秀（信源可靠） 60-80=合格（需关注） &lt;60=不合格（信源可能有问题，需审查事件链）</t>
         </is>
@@ -5740,7 +5826,7 @@
       </c>
     </row>
     <row r="118">
-      <c r="A118" t="inlineStr">
+      <c r="A118" s="49" t="inlineStr">
         <is>
           <t>1.</t>
         </is>
@@ -5752,7 +5838,7 @@
       </c>
     </row>
     <row r="119">
-      <c r="A119" t="inlineStr">
+      <c r="A119" s="49" t="inlineStr">
         <is>
           <t>2.</t>
         </is>
@@ -5764,7 +5850,7 @@
       </c>
     </row>
     <row r="120">
-      <c r="A120" t="inlineStr">
+      <c r="A120" s="49" t="inlineStr">
         <is>
           <t>3.</t>
         </is>
@@ -5776,7 +5862,7 @@
       </c>
     </row>
     <row r="121">
-      <c r="A121" t="inlineStr">
+      <c r="A121" s="49" t="inlineStr">
         <is>
           <t>4.</t>
         </is>
@@ -5829,12 +5915,141 @@
         </is>
       </c>
     </row>
+    <row r="130">
+      <c r="A130" s="133" t="inlineStr">
+        <is>
+          <t>【Row3基本信息恢复】（2026-06-04从backup_0603恢复）</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="134" t="inlineStr">
+        <is>
+          <t>恢复: 成本¥3695
+净值3.6875
+P:41%
+虚P+4pp
+有效P:35%</t>
+        </is>
+      </c>
+      <c r="B131" s="134" t="inlineStr">
+        <is>
+          <t>恢复: 成本¥6811
+净值1.8418
+P:67%
+有效P:61%</t>
+        </is>
+      </c>
+      <c r="C131" s="134" t="inlineStr">
+        <is>
+          <t>恢复: 成本¥4722
+净值0.6619
+P:38%
+有效P:32%</t>
+        </is>
+      </c>
+      <c r="D131" s="134" t="inlineStr">
+        <is>
+          <t>恢复: 成本¥3732
+净值0.7545
+P:56%
+有效P:56%</t>
+        </is>
+      </c>
+      <c r="E131" s="134" t="inlineStr">
+        <is>
+          <t>恢复: 成本¥4800
+净值1.8985
+P:44%
+有效P:40%</t>
+        </is>
+      </c>
+      <c r="F131" s="134" t="inlineStr">
+        <is>
+          <t>恢复: 成本¥5622
+净值1.089
+P:43%
+有效P:39%</t>
+        </is>
+      </c>
+      <c r="G131" s="134" t="inlineStr">
+        <is>
+          <t>恢复: P:50%
+有效P:50%</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="133" t="inlineStr">
+        <is>
+          <t>【Row3基本信息恢复】（2026-06-04从backup_0603恢复）</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="134" t="inlineStr">
+        <is>
+          <t>恢复: 成本¥3695
+净值3.6875
+P:41%
+虚P+4pp
+有效P:35%</t>
+        </is>
+      </c>
+      <c r="B134" s="134" t="inlineStr">
+        <is>
+          <t>恢复: 成本¥6811
+净值1.8418
+P:67%
+有效P:61%</t>
+        </is>
+      </c>
+      <c r="C134" s="134" t="inlineStr">
+        <is>
+          <t>恢复: 成本¥4722
+净值0.6619
+P:38%
+有效P:32%</t>
+        </is>
+      </c>
+      <c r="D134" s="134" t="inlineStr">
+        <is>
+          <t>恢复: 成本¥3732
+净值0.7545
+P:56%
+有效P:56%</t>
+        </is>
+      </c>
+      <c r="E134" s="134" t="inlineStr">
+        <is>
+          <t>恢复: 成本¥4800
+净值1.8985
+P:44%
+有效P:40%</t>
+        </is>
+      </c>
+      <c r="F134" s="134" t="inlineStr">
+        <is>
+          <t>恢复: 成本¥5622
+净值1.089
+P:43%
+有效P:39%</t>
+        </is>
+      </c>
+      <c r="G134" s="134" t="inlineStr">
+        <is>
+          <t>恢复: P:50%
+有效P:50%</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="46">
+  <mergeCells count="48">
     <mergeCell ref="A58:K58"/>
+    <mergeCell ref="A130:H130"/>
     <mergeCell ref="B91:L91"/>
+    <mergeCell ref="B97:L97"/>
     <mergeCell ref="A48:K48"/>
-    <mergeCell ref="B97:L97"/>
     <mergeCell ref="A128:L128"/>
     <mergeCell ref="B100:L100"/>
     <mergeCell ref="A24:H24"/>
@@ -5852,6 +6067,7 @@
     <mergeCell ref="B101:L101"/>
     <mergeCell ref="B98:L98"/>
     <mergeCell ref="A126:L126"/>
+    <mergeCell ref="A133:H133"/>
     <mergeCell ref="A75:K75"/>
     <mergeCell ref="A56:K56"/>
     <mergeCell ref="A125:L125"/>

--- a/持仓贝叶斯跟踪.xlsx
+++ b/持仓贝叶斯跟踪.xlsx
@@ -11,6 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet2" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="拟合分析" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="机会成本排序" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="三源联动分析" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1" refMode="A1" iterate="0" iterateCount="100" iterateDelta="0.0001"/>
@@ -20,7 +21,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="44">
+  <fonts count="53">
     <font>
       <name val="Calibri"/>
       <charset val="1"/>
@@ -325,8 +326,48 @@
       <b val="1"/>
       <sz val="9"/>
     </font>
+    <font>
+      <b val="1"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FF0000"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FF0000"/>
+      <sz val="13"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FF0000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <sz val="10"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <color rgb="00FF0000"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="21">
+  <fills count="29">
     <fill>
       <patternFill/>
     </fill>
@@ -447,6 +488,54 @@
         <bgColor rgb="FFFFF2CC"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D9E2F3"/>
+        <bgColor rgb="00D9E2F3"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C6EFCE"/>
+        <bgColor rgb="00C6EFCE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFEB9C"/>
+        <bgColor rgb="00FFEB9C"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFC7CE"/>
+        <bgColor rgb="00FFC7CE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C00000"/>
+        <bgColor rgb="00C00000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FCD5B4"/>
+        <bgColor rgb="00FCD5B4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="000000FF"/>
+        <bgColor rgb="000000FF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="008B0000"/>
+        <bgColor rgb="008B0000"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="7">
     <border>
@@ -508,7 +597,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="149">
+  <cellXfs count="178">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -946,6 +1035,73 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="42" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="43" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="44" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="45" fillId="21" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="22" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="23" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="24" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="47" fillId="23" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="25" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="25" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="49" fillId="23" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="23" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="41" fillId="21" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="22" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="26" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="24" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="23" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="27" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="27" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="22" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="41" fillId="23" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="41" fillId="24" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="51" fillId="28" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="28" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="52" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="23" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1306,14 +1462,14 @@
 </t>
       </text>
     </comment>
-    <comment ref="E23" authorId="1" shapeId="0">
+    <comment ref="E45" authorId="1" shapeId="0">
       <text>
         <t>信息源: 新浪财经K线API(sh562500)
 推理链: 宇树科技73天过会→人形机器人商业化元年→产业催化
 P值: 58%(估)，有效P=58%-6pp=52%</t>
       </text>
     </comment>
-    <comment ref="A31" authorId="0" shapeId="0">
+    <comment ref="A53" authorId="0" shapeId="0">
       <text>
         <t xml:space="preserve">【来源】蒋宇飞抖音视频（2026-05-25）"未来5-10年的黄金赛道，深度拆解玻璃基板的万亿机遇"
 【信源评估】蒋宇飞⭐⭐⭐高置信度（有产业实操经验，多次验证预测准确）
@@ -1328,7 +1484,7 @@
 </t>
       </text>
     </comment>
-    <comment ref="A33" authorId="0" shapeId="0">
+    <comment ref="A55" authorId="0" shapeId="0">
       <text>
         <t>信息源：东方财富+新浪财经2026-06-02
 核心数据：
@@ -1341,7 +1497,7 @@
 结论：不建议加仓</t>
       </text>
     </comment>
-    <comment ref="A34" authorId="0" shapeId="0">
+    <comment ref="A56" authorId="0" shapeId="0">
       <text>
         <t>信息源：东方财富头条+新浪财经2026-06-02
 核心数据：
@@ -1356,7 +1512,7 @@
 结论：重点关注，强正向信号</t>
       </text>
     </comment>
-    <comment ref="A35" authorId="0" shapeId="0">
+    <comment ref="A57" authorId="0" shapeId="0">
       <text>
         <t xml:space="preserve">【来源】群联潘健成(产业高管)+蒋宇飞(6.1两长存储+5.18框架)+宋鸿兵(6.2摩尔定律终结)+周鸿祎(内存决定AI)+用户6.3洞察
 【逻辑链】
@@ -1379,7 +1535,7 @@
 </t>
       </text>
     </comment>
-    <comment ref="A36" authorId="0" shapeId="0">
+    <comment ref="A58" authorId="0" shapeId="0">
       <text>
         <t xml:space="preserve">【来源】蒋宇飞星光纯叠框架+宋鸿兵华为韬定律+用户"AI瓶颈是内存而非算力"
 【逻辑链】
@@ -1393,7 +1549,7 @@
 </t>
       </text>
     </comment>
-    <comment ref="A38" authorId="0" shapeId="0">
+    <comment ref="A60" authorId="0" shapeId="0">
       <text>
         <t xml:space="preserve">【标的】北京君正 300223
 【核心逻辑】存储+计算芯片，DRAM新工艺突破，车载存储市占率提升。A股年内+51%，市值772亿。港股二度IPO中。盈亏比4:1，存储赛道里最强。
@@ -1404,7 +1560,7 @@
 </t>
       </text>
     </comment>
-    <comment ref="A39" authorId="0" shapeId="0">
+    <comment ref="A61" authorId="0" shapeId="0">
       <text>
         <t xml:space="preserve">【标的】兆易创新 603986
 【核心逻辑】NOR Flash国内龙头，DRAM布局中。存储涨价直接受益。盈亏比3.5:1。
@@ -1415,7 +1571,7 @@
 </t>
       </text>
     </comment>
-    <comment ref="A40" authorId="0" shapeId="0">
+    <comment ref="A62" authorId="0" shapeId="0">
       <text>
         <t xml:space="preserve">【标的】江波龙 301308
 【核心逻辑】存储模组+主控芯片，国产替代核心标的。盈亏比3.5:1。
@@ -1743,17 +1899,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:H48"/>
+  <dimension ref="A1:H67"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6171875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
-    <col width="22" customWidth="1" style="78" min="1" max="1"/>
-    <col width="14" customWidth="1" style="78" min="2" max="2"/>
-    <col width="30" customWidth="1" style="78" min="3" max="3"/>
-    <col width="22" customWidth="1" style="78" min="4" max="4"/>
+    <col width="18" customWidth="1" style="78" min="1" max="1"/>
+    <col width="18" customWidth="1" style="78" min="2" max="2"/>
+    <col width="18" customWidth="1" style="78" min="3" max="3"/>
+    <col width="18" customWidth="1" style="78" min="4" max="4"/>
     <col width="18" customWidth="1" style="78" min="5" max="5"/>
-    <col width="16" customWidth="1" style="78" min="6" max="6"/>
-    <col width="14" customWidth="1" style="78" min="7" max="7"/>
-    <col width="20" customWidth="1" style="78" min="8" max="8"/>
+    <col width="18" customWidth="1" style="78" min="6" max="6"/>
+    <col width="18" customWidth="1" style="78" min="7" max="7"/>
+    <col width="18" customWidth="1" style="78" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="16.5" customHeight="1" s="79">
@@ -2079,477 +2235,907 @@
       </c>
     </row>
     <row r="21" ht="16.5" customHeight="1" s="79">
-      <c r="A21" s="87" t="inlineStr">
-        <is>
-          <t>🤖 人形机器人半年事件链</t>
-        </is>
-      </c>
+      <c r="A21" s="158" t="inlineStr">
+        <is>
+          <t>🔴 战略级虚P信号池（2026-06-04）</t>
+        </is>
+      </c>
+      <c r="B21" s="159" t="n"/>
+      <c r="C21" s="159" t="n"/>
+      <c r="D21" s="159" t="n"/>
+      <c r="E21" s="159" t="n"/>
+      <c r="F21" s="159" t="n"/>
+      <c r="G21" s="159" t="n"/>
+      <c r="H21" s="159" t="n"/>
     </row>
     <row r="22" ht="16.5" customHeight="1" s="79">
-      <c r="A22" s="78" t="n"/>
+      <c r="A22" s="160" t="inlineStr">
+        <is>
+          <t>规则：虚P≠实P。未落地（无价格验证）的信号→记虚P→不直接加P值→等落地后再转实P。虚P仅用于方向预判和仓位准备。</t>
+        </is>
+      </c>
+      <c r="B22" s="161" t="n"/>
+      <c r="C22" s="161" t="n"/>
+      <c r="D22" s="161" t="n"/>
+      <c r="E22" s="161" t="n"/>
+      <c r="F22" s="161" t="n"/>
+      <c r="G22" s="161" t="n"/>
+      <c r="H22" s="161" t="n"/>
     </row>
     <row r="23" ht="16.5" customHeight="1" s="79">
-      <c r="A23" s="87" t="inlineStr">
-        <is>
-          <t>2026-03-23 机器人ETF暴跌-4.1%至0.909：市场恐慌+AI回调</t>
-        </is>
-      </c>
-      <c r="B23" s="78" t="n"/>
-      <c r="E23" s="89" t="n"/>
+      <c r="A23" s="162" t="inlineStr">
+        <is>
+          <t>信号来源</t>
+        </is>
+      </c>
+      <c r="B23" s="162" t="inlineStr">
+        <is>
+          <t>核心观点</t>
+        </is>
+      </c>
+      <c r="C23" s="162" t="inlineStr">
+        <is>
+          <t>与你策略契合度</t>
+        </is>
+      </c>
+      <c r="D23" s="162" t="inlineStr">
+        <is>
+          <t>虚P方向</t>
+        </is>
+      </c>
+      <c r="E23" s="162" t="inlineStr">
+        <is>
+          <t>落地条件</t>
+        </is>
+      </c>
+      <c r="F23" s="162" t="inlineStr">
+        <is>
+          <t>状态</t>
+        </is>
+      </c>
+      <c r="G23" s="162" t="inlineStr">
+        <is>
+          <t>权重</t>
+        </is>
+      </c>
+      <c r="H23" s="162" t="inlineStr">
+        <is>
+          <t>备注</t>
+        </is>
+      </c>
     </row>
     <row r="24" ht="16.5" customHeight="1" s="79">
-      <c r="A24" s="87" t="inlineStr">
-        <is>
-          <t>2026-04-08 机器人ETF暴涨+6.4%至0.967：人形机器人产业催化</t>
-        </is>
-      </c>
-      <c r="D24" s="78" t="n"/>
+      <c r="A24" s="163" t="inlineStr">
+        <is>
+          <t>达利欧
+Bloomberg 6/3</t>
+        </is>
+      </c>
+      <c r="B24" s="163" t="inlineStr">
+        <is>
+          <t>AI泡沫65-75%概率
+2026年底显著回调
+"技术本身不会失败"</t>
+        </is>
+      </c>
+      <c r="C24" s="164" t="inlineStr">
+        <is>
+          <t>🟢完全契合
+等中期选举大跌
+现金入场</t>
+        </is>
+      </c>
+      <c r="D24" s="163" t="inlineStr">
+        <is>
+          <t>美股AI↓
+芯片短期承压</t>
+        </is>
+      </c>
+      <c r="E24" s="163" t="inlineStr">
+        <is>
+          <t>纳指/纳指七姐妹
+出现&gt;15%回调</t>
+        </is>
+      </c>
+      <c r="F24" s="165" t="inlineStr">
+        <is>
+          <t>⏳未落地
+(虚P状态)</t>
+        </is>
+      </c>
+      <c r="G24" s="166" t="inlineStr">
+        <is>
+          <t>⭐⭐⭐⭐⭐
+极高</t>
+        </is>
+      </c>
+      <c r="H24" s="163" t="inlineStr">
+        <is>
+          <t>6/4三源联动:
+芯片-2pp
+恒科-1pp
+→已记虚P
+未转实P</t>
+        </is>
+      </c>
     </row>
     <row r="25" ht="16.5" customHeight="1" s="79">
-      <c r="A25" s="87" t="inlineStr">
-        <is>
-          <t>2026-05-07~22 机器人连续上涨：ETF 1.056→1.216(+15%)，宇树科技73天过会</t>
-        </is>
-      </c>
-      <c r="D25" s="78" t="n"/>
+      <c r="A25" s="163" t="inlineStr">
+        <is>
+          <t>李大霄
+金融界 6/4</t>
+        </is>
+      </c>
+      <c r="B25" s="163" t="inlineStr">
+        <is>
+          <t>美股窄牛宽熊
+仅20只创新高
+CAPE40倍→泡沫</t>
+        </is>
+      </c>
+      <c r="C25" s="164" t="inlineStr">
+        <is>
+          <t>🟢高度契合
+确认美股风险
+现金策略正确</t>
+        </is>
+      </c>
+      <c r="D25" s="163" t="inlineStr">
+        <is>
+          <t>美股全市场↓
+港股连带承压</t>
+        </is>
+      </c>
+      <c r="E25" s="163" t="inlineStr">
+        <is>
+          <t>纳指破200日均线
+或多数成分股下跌</t>
+        </is>
+      </c>
+      <c r="F25" s="165" t="inlineStr">
+        <is>
+          <t>⏳未落地
+(虚P状态)</t>
+        </is>
+      </c>
+      <c r="G25" s="163" t="inlineStr">
+        <is>
+          <t>⭐⭐⭐
+中高</t>
+        </is>
+      </c>
+      <c r="H25" s="163" t="inlineStr">
+        <is>
+          <t>6/4三源联动:
+恒科-2pp
+芯片-1pp
+→已记虚P
+未转实P</t>
+        </is>
+      </c>
     </row>
     <row r="26" ht="15" customHeight="1" s="79">
-      <c r="A26" s="87" t="inlineStr">
-        <is>
-          <t>2026-05-25~06-02 机器人回调：1.216→1.122(-7.7%)，仍处强势区间</t>
-        </is>
-      </c>
-      <c r="D26" s="78" t="n"/>
+      <c r="A26" s="163" t="inlineStr">
+        <is>
+          <t>知乎专栏
+6/4</t>
+        </is>
+      </c>
+      <c r="B26" s="163" t="inlineStr">
+        <is>
+          <t>纳指PE中值区间
+5维度排查无暴跌
+继续持有</t>
+        </is>
+      </c>
+      <c r="C26" s="167" t="inlineStr">
+        <is>
+          <t>🟡部分参考
+与达利欧矛盾
+看估值vs看流动性</t>
+        </is>
+      </c>
+      <c r="D26" s="163" t="inlineStr">
+        <is>
+          <t>中性偏多
+纳指短期安全</t>
+        </is>
+      </c>
+      <c r="E26" s="163" t="inlineStr">
+        <is>
+          <t>纳指PE跌破25
+或出现暴跌维度触发</t>
+        </is>
+      </c>
+      <c r="F26" s="165" t="inlineStr">
+        <is>
+          <t>⏳未落地
+(虚P状态)</t>
+        </is>
+      </c>
+      <c r="G26" s="163" t="inlineStr">
+        <is>
+          <t>⭐⭐⭐
+中</t>
+        </is>
+      </c>
+      <c r="H26" s="163" t="inlineStr">
+        <is>
+          <t>6/4三源联动:
+恒科+1pp
+→已记虚P
+未转实P</t>
+        </is>
+      </c>
     </row>
     <row r="27" ht="17.15" customHeight="1" s="79">
-      <c r="A27" s="90" t="inlineStr">
-        <is>
-          <t>2026-06-04 【保持观察】霍尔木兹海峡Day 12：伊朗暂停谈判+美众议院限制动武，WTI $96→$91-93回落，方向趋于缓和</t>
-        </is>
-      </c>
-      <c r="B27" s="91" t="n"/>
-      <c r="C27" s="91" t="n"/>
-      <c r="D27" s="91" t="n"/>
-      <c r="E27" s="91" t="n"/>
-      <c r="F27" s="91" t="n"/>
-      <c r="G27" s="91" t="n"/>
-      <c r="H27" s="91" t="n"/>
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>────────────────────────────────────────────────────────────</t>
+        </is>
+      </c>
     </row>
     <row r="28" ht="15" customHeight="1" s="79">
-      <c r="A28" s="147" t="inlineStr">
-        <is>
-          <t>🔔 待重仓监控</t>
-        </is>
-      </c>
+      <c r="A28" s="168" t="inlineStr">
+        <is>
+          <t>🔗 三源互锁验证</t>
+        </is>
+      </c>
+      <c r="B28" s="169" t="n"/>
+      <c r="C28" s="169" t="n"/>
+      <c r="D28" s="169" t="n"/>
+      <c r="E28" s="169" t="n"/>
+      <c r="F28" s="169" t="n"/>
+      <c r="G28" s="169" t="n"/>
+      <c r="H28" s="169" t="n"/>
     </row>
     <row r="29" ht="15" customHeight="1" s="79">
-      <c r="A29" s="148" t="inlineStr">
-        <is>
-          <t>标的</t>
-        </is>
-      </c>
-      <c r="B29" s="148" t="inlineStr">
-        <is>
-          <t>状态</t>
-        </is>
-      </c>
-      <c r="C29" s="148" t="inlineStr">
-        <is>
-          <t>当前P/价格</t>
-        </is>
-      </c>
-      <c r="D29" s="148" t="inlineStr">
-        <is>
-          <t>最新信号</t>
-        </is>
-      </c>
-      <c r="E29" s="148" t="inlineStr">
-        <is>
-          <t>触发条件</t>
-        </is>
-      </c>
-      <c r="F29" s="148" t="inlineStr">
-        <is>
-          <t>距离触发</t>
-        </is>
-      </c>
-      <c r="G29" s="148" t="inlineStr">
-        <is>
-          <t>跟踪日期</t>
+      <c r="A29" s="170" t="inlineStr">
+        <is>
+          <t>达利欧 × 李大霄</t>
+        </is>
+      </c>
+      <c r="C29" s="171" t="inlineStr">
+        <is>
+          <t>✅ 强印证</t>
+        </is>
+      </c>
+      <c r="E29" s="152" t="inlineStr">
+        <is>
+          <t>AI泡沫+窄牛宽熊=同一现象两角度，互相确认</t>
         </is>
       </c>
     </row>
     <row r="30" ht="15" customHeight="1" s="79">
-      <c r="A30" s="87" t="inlineStr">
-        <is>
-          <t>玻璃基板</t>
-        </is>
-      </c>
-      <c r="B30" s="87" t="inlineStr">
-        <is>
-          <t>深南电路002916/兴森科技002436</t>
-        </is>
-      </c>
-      <c r="C30" s="87" t="inlineStr">
-        <is>
-          <t>观察中</t>
-        </is>
-      </c>
-      <c r="D30" s="87" t="inlineStr">
-        <is>
-          <t>蒋宇飞：玻璃基板大规模应用2028年，5-10年赛道</t>
-        </is>
-      </c>
-      <c r="E30" s="87" t="inlineStr">
-        <is>
-          <t>AI基建+国产替代加速</t>
-        </is>
-      </c>
-      <c r="F30" s="87" t="inlineStr">
-        <is>
-          <t>中长期</t>
-        </is>
-      </c>
-      <c r="G30" s="87" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
+      <c r="A30" s="170" t="inlineStr">
+        <is>
+          <t>达利欧 × 知乎</t>
+        </is>
+      </c>
+      <c r="C30" s="172" t="inlineStr">
+        <is>
+          <t>⚠️ 部分矛盾</t>
+        </is>
+      </c>
+      <c r="E30" s="152" t="inlineStr">
+        <is>
+          <t>达利欧看流动性(泡沫将破) vs 知乎看估值(PE中值安全)</t>
         </is>
       </c>
     </row>
     <row r="31" ht="15" customHeight="1" s="79">
-      <c r="A31" s="78" t="n"/>
-      <c r="B31" s="78" t="n"/>
-      <c r="C31" s="78" t="n"/>
-      <c r="D31" s="78" t="n"/>
-      <c r="E31" s="78" t="n"/>
-      <c r="F31" s="78" t="n"/>
-      <c r="G31" s="78" t="n"/>
-      <c r="H31" s="78" t="n"/>
-    </row>
-    <row r="32" ht="15" customHeight="1" s="79">
-      <c r="A32" s="87" t="inlineStr">
-        <is>
-          <t>油气对冲</t>
-        </is>
-      </c>
-      <c r="B32" s="87" t="inlineStr">
-        <is>
-          <t>华宝油气162411</t>
-        </is>
-      </c>
-      <c r="C32" s="87" t="inlineStr">
-        <is>
-          <t>观察中</t>
-        </is>
-      </c>
-      <c r="D32" s="87" t="inlineStr">
-        <is>
-          <t>宋鸿兵：霍尔木兹封锁3个月，85%投资者押注回落=幻觉</t>
-        </is>
-      </c>
-      <c r="E32" s="87" t="inlineStr">
-        <is>
-          <t>油价冲150或海峡持续封锁</t>
-        </is>
-      </c>
-      <c r="F32" s="87" t="inlineStr">
-        <is>
-          <t>短期</t>
-        </is>
-      </c>
-      <c r="G32" s="87" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="H32" s="78" t="inlineStr">
-        <is>
-          <t>小仓位试水，不对称博弈</t>
-        </is>
-      </c>
-    </row>
+      <c r="A31" s="170" t="inlineStr">
+        <is>
+          <t>三源共识</t>
+        </is>
+      </c>
+      <c r="C31" s="173" t="inlineStr">
+        <is>
+          <t>🔴 核心共识</t>
+        </is>
+      </c>
+      <c r="E31" s="152" t="inlineStr">
+        <is>
+          <t>AI龙头估值偏高+市场极度集中+中小盘已熊 → 短期风险&gt;机会</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="15" customHeight="1" s="79"/>
     <row r="33" ht="16.5" customHeight="1" s="79">
-      <c r="A33" s="87" t="inlineStr">
-        <is>
-          <t>银行板块(512800)</t>
-        </is>
-      </c>
-      <c r="B33" s="87" t="inlineStr">
-        <is>
-          <t>弱势</t>
-        </is>
-      </c>
-      <c r="C33" s="87" t="inlineStr">
-        <is>
-          <t>P:50% 虚P-2pp</t>
-        </is>
-      </c>
-      <c r="D33" s="87" t="inlineStr">
-        <is>
-          <t>去杠杆+信贷收缩，ETF跌-1%，无催化</t>
-        </is>
-      </c>
-      <c r="E33" s="87" t="inlineStr">
-        <is>
-          <t>不建议加仓</t>
-        </is>
-      </c>
-      <c r="F33" s="87" t="inlineStr">
-        <is>
-          <t>短期</t>
-        </is>
-      </c>
-      <c r="G33" s="87" t="inlineStr">
-        <is>
-          <t>2026-06-03</t>
-        </is>
-      </c>
-      <c r="H33" s="78" t="inlineStr">
-        <is>
-          <t>银行ETF持续阴跌</t>
-        </is>
-      </c>
+      <c r="A33" s="174" t="inlineStr">
+        <is>
+          <t>🎯 结论（虚P→实P转换条件）</t>
+        </is>
+      </c>
+      <c r="B33" s="175" t="n"/>
+      <c r="C33" s="175" t="n"/>
+      <c r="D33" s="175" t="n"/>
+      <c r="E33" s="175" t="n"/>
+      <c r="F33" s="175" t="n"/>
+      <c r="G33" s="175" t="n"/>
+      <c r="H33" s="175" t="n"/>
     </row>
     <row r="34" ht="16.5" customHeight="1" s="79">
-      <c r="A34" s="87" t="inlineStr">
-        <is>
-          <t>人形机器人(562500)</t>
-        </is>
-      </c>
-      <c r="B34" s="87" t="inlineStr">
-        <is>
-          <t>强势</t>
-        </is>
-      </c>
-      <c r="C34" s="87" t="inlineStr">
-        <is>
-          <t>P:58%(估)</t>
-        </is>
-      </c>
-      <c r="D34" s="87" t="inlineStr">
-        <is>
-          <t>宇树科技73天过会，ETF涨+11%</t>
-        </is>
-      </c>
-      <c r="E34" s="87" t="inlineStr">
-        <is>
-          <t>重点关注</t>
-        </is>
-      </c>
-      <c r="F34" s="87" t="inlineStr">
-        <is>
-          <t>中期</t>
-        </is>
-      </c>
-      <c r="G34" s="87" t="inlineStr">
-        <is>
-          <t>2026-06-03</t>
-        </is>
-      </c>
-      <c r="H34" s="78" t="inlineStr">
-        <is>
-          <t>平安先进制造+永赢先进制造</t>
+      <c r="A34" s="170" t="inlineStr">
+        <is>
+          <t>① 达利欧信号落地条件</t>
+        </is>
+      </c>
+      <c r="C34" s="152" t="inlineStr">
+        <is>
+          <t>纳指七姐妹出现&gt;15%回调 或 纳指破200日均线</t>
+        </is>
+      </c>
+      <c r="E34" s="176" t="inlineStr">
+        <is>
+          <t>→ 芯片/恒科虚P转实P → 确认减仓信号</t>
         </is>
       </c>
     </row>
     <row r="35" ht="16.5" customHeight="1" s="79">
-      <c r="A35" s="87" t="inlineStr">
-        <is>
-          <t>存储赛道(5只A股)</t>
-        </is>
-      </c>
-      <c r="B35" s="87" t="inlineStr">
-        <is>
-          <t>❌降级观察</t>
-        </is>
-      </c>
-      <c r="C35" s="87" t="inlineStr">
-        <is>
-          <t>P:55% 安全边际不足</t>
-        </is>
-      </c>
-      <c r="D35" s="87" t="inlineStr">
-        <is>
-          <t>兆易¥525(+81%)/江波龙¥569/佰维¥341→PE天际线，向上空间&lt;向下空间</t>
-        </is>
-      </c>
-      <c r="E35" s="87" t="inlineStr">
-        <is>
-          <t>等中期选举大跌15%+</t>
-        </is>
-      </c>
-      <c r="F35" s="87" t="inlineStr">
-        <is>
-          <t>中期</t>
-        </is>
-      </c>
-      <c r="G35" s="87" t="inlineStr">
-        <is>
-          <t>2026-06-04</t>
-        </is>
-      </c>
-      <c r="H35" s="78" t="inlineStr">
-        <is>
-          <t>降级：存储涨完轮到堆叠，安全边际已不足</t>
+      <c r="A35" s="170" t="inlineStr">
+        <is>
+          <t>② 李大霄信号落地条件</t>
+        </is>
+      </c>
+      <c r="C35" s="152" t="inlineStr">
+        <is>
+          <t>纳指多数成分股连续下跌+指数拐头</t>
+        </is>
+      </c>
+      <c r="E35" s="176" t="inlineStr">
+        <is>
+          <t>→ 恒科/芯片虚P转实P → 确认美股系统性风险</t>
         </is>
       </c>
     </row>
     <row r="36" ht="16.5" customHeight="1" s="79">
-      <c r="A36" s="87" t="inlineStr">
-        <is>
-          <t>澜起科技(688008)</t>
-        </is>
-      </c>
-      <c r="B36" s="87" t="inlineStr">
-        <is>
-          <t>❌降级观察</t>
-        </is>
-      </c>
-      <c r="C36" s="87" t="inlineStr">
-        <is>
-          <t>P:55% 安全边际中等</t>
-        </is>
-      </c>
-      <c r="D36" s="87" t="inlineStr">
-        <is>
-          <t>DDR5接口芯片，温和上涨，但存储赛道整体降级</t>
-        </is>
-      </c>
-      <c r="E36" s="87" t="inlineStr">
-        <is>
-          <t>等大跌15%+</t>
-        </is>
-      </c>
-      <c r="F36" s="87" t="inlineStr">
-        <is>
-          <t>中期</t>
-        </is>
-      </c>
-      <c r="G36" s="87" t="inlineStr">
-        <is>
-          <t>2026-06-04</t>
-        </is>
-      </c>
-      <c r="H36" s="78" t="inlineStr">
-        <is>
-          <t>降级：存储赛道尾声</t>
+      <c r="A36" s="170" t="inlineStr">
+        <is>
+          <t>③ 你的策略触发条件</t>
+        </is>
+      </c>
+      <c r="C36" s="152" t="inlineStr">
+        <is>
+          <t>中期选举(11月)美股跌一波 + AI回调&gt;15%</t>
+        </is>
+      </c>
+      <c r="E36" s="176" t="inlineStr">
+        <is>
+          <t>→ 现金入场 → 大仓位进堆叠/先进封装</t>
         </is>
       </c>
     </row>
     <row r="37" ht="16.5" customHeight="1" s="79">
-      <c r="A37" s="92" t="inlineStr">
-        <is>
-          <t>🔥堆叠/先进封装赛道（蒋宇飞"星光纯叠"框架）</t>
-        </is>
-      </c>
-    </row>
-    <row r="38" ht="16.5" customHeight="1" s="79">
-      <c r="A38" s="87" t="inlineStr">
-        <is>
-          <t>长电科技(600584)</t>
-        </is>
-      </c>
-      <c r="B38" s="87" t="inlineStr">
-        <is>
-          <t>🔴核心标的</t>
-        </is>
-      </c>
-      <c r="C38" s="87" t="inlineStr">
-        <is>
-          <t>P:75%+ PE30x</t>
-        </is>
-      </c>
-      <c r="D38" s="87" t="inlineStr">
-        <is>
-          <t>全球第三大封测厂，2.5D/3D量产级，客户广度最强（高通/海思/TI）</t>
-        </is>
-      </c>
-      <c r="E38" s="87" t="inlineStr">
-        <is>
-          <t>等中期选举大跌</t>
-        </is>
-      </c>
-      <c r="F38" s="87" t="inlineStr">
-        <is>
-          <t>中期</t>
-        </is>
-      </c>
-      <c r="G38" s="87" t="inlineStr">
-        <is>
-          <t>2026-06-04</t>
-        </is>
-      </c>
-      <c r="H38" s="78" t="inlineStr">
-        <is>
-          <t>安全边际大，堆叠赛道首选</t>
-        </is>
-      </c>
-    </row>
+      <c r="A37" s="170" t="inlineStr">
+        <is>
+          <t>④ 堆叠赛道独立性</t>
+        </is>
+      </c>
+      <c r="C37" s="152" t="inlineStr">
+        <is>
+          <t>国内产业确定性，三源均未提及国内封测</t>
+        </is>
+      </c>
+      <c r="E37" s="176" t="inlineStr">
+        <is>
+          <t>→ 不受美股泡沫直接影响 → 等回调后优先配置</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="16.5" customHeight="1" s="79"/>
     <row r="39" ht="16.5" customHeight="1" s="79">
-      <c r="A39" s="87" t="inlineStr">
-        <is>
-          <t>通富微电(002156)</t>
-        </is>
-      </c>
-      <c r="B39" s="87" t="inlineStr">
-        <is>
-          <t>🔴核心标的</t>
-        </is>
-      </c>
-      <c r="C39" s="87" t="inlineStr">
-        <is>
-          <t>P:75%+ 待查PE</t>
-        </is>
-      </c>
-      <c r="D39" s="87" t="inlineStr">
-        <is>
-          <t>AMD封测全线突破通道，2.5D量产，MI300X参与，不可替代</t>
-        </is>
-      </c>
-      <c r="E39" s="87" t="inlineStr">
-        <is>
-          <t>等中期选举大跌</t>
-        </is>
-      </c>
-      <c r="F39" s="87" t="inlineStr">
-        <is>
-          <t>中期</t>
-        </is>
-      </c>
-      <c r="G39" s="87" t="inlineStr">
-        <is>
-          <t>2026-06-04</t>
-        </is>
-      </c>
-      <c r="H39" s="78" t="inlineStr">
-        <is>
-          <t>安全边际中偏大，与长电各占一半</t>
-        </is>
-      </c>
-    </row>
-    <row r="40" ht="16.5" customHeight="1" s="79">
-      <c r="A40" s="78" t="n"/>
-    </row>
+      <c r="A39" s="177" t="inlineStr">
+        <is>
+          <t>⚡ 一句话：三源确认AI泡沫风险+你的中期选举策略正确。虚P已记，等落地转实P。现金为王，堆叠赛道等回调后大仓位进。</t>
+        </is>
+      </c>
+      <c r="B39" s="161" t="n"/>
+      <c r="C39" s="161" t="n"/>
+      <c r="D39" s="161" t="n"/>
+      <c r="E39" s="161" t="n"/>
+      <c r="F39" s="161" t="n"/>
+      <c r="G39" s="161" t="n"/>
+      <c r="H39" s="161" t="n"/>
+    </row>
+    <row r="40" ht="16.5" customHeight="1" s="79"/>
     <row r="41" ht="16.5" customHeight="1" s="79"/>
     <row r="42" ht="16.5" customHeight="1" s="79"/>
-    <row r="43" ht="16.5" customHeight="1" s="79"/>
-    <row r="44" ht="16.5" customHeight="1" s="79"/>
-    <row r="45" ht="16.5" customHeight="1" s="79"/>
-    <row r="46" ht="16.5" customHeight="1" s="79"/>
-    <row r="47" ht="16.5" customHeight="1" s="79"/>
-    <row r="48" ht="16.5" customHeight="1" s="79"/>
-    <row r="49" ht="16.5" customHeight="1" s="79"/>
+    <row r="43" ht="16.5" customHeight="1" s="79">
+      <c r="A43" s="87" t="inlineStr">
+        <is>
+          <t>🤖 人形机器人半年事件链</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="16.5" customHeight="1" s="79">
+      <c r="A44" s="78" t="n"/>
+    </row>
+    <row r="45" ht="16.5" customHeight="1" s="79">
+      <c r="A45" s="87" t="inlineStr">
+        <is>
+          <t>2026-03-23 机器人ETF暴跌-4.1%至0.909：市场恐慌+AI回调</t>
+        </is>
+      </c>
+      <c r="B45" s="78" t="n"/>
+      <c r="E45" s="89" t="n"/>
+    </row>
+    <row r="46" ht="16.5" customHeight="1" s="79">
+      <c r="A46" s="87" t="inlineStr">
+        <is>
+          <t>2026-04-08 机器人ETF暴涨+6.4%至0.967：人形机器人产业催化</t>
+        </is>
+      </c>
+      <c r="D46" s="78" t="n"/>
+    </row>
+    <row r="47" ht="16.5" customHeight="1" s="79">
+      <c r="A47" s="87" t="inlineStr">
+        <is>
+          <t>2026-05-07~22 机器人连续上涨：ETF 1.056→1.216(+15%)，宇树科技73天过会</t>
+        </is>
+      </c>
+      <c r="D47" s="78" t="n"/>
+    </row>
+    <row r="48" ht="16.5" customHeight="1" s="79">
+      <c r="A48" s="87" t="inlineStr">
+        <is>
+          <t>2026-05-25~06-02 机器人回调：1.216→1.122(-7.7%)，仍处强势区间</t>
+        </is>
+      </c>
+      <c r="D48" s="78" t="n"/>
+    </row>
+    <row r="49" ht="16.5" customHeight="1" s="79">
+      <c r="A49" s="90" t="inlineStr">
+        <is>
+          <t>2026-06-04 【保持观察】霍尔木兹海峡Day 12：伊朗暂停谈判+美众议院限制动武，WTI $96→$91-93回落，方向趋于缓和</t>
+        </is>
+      </c>
+      <c r="B49" s="91" t="n"/>
+      <c r="C49" s="91" t="n"/>
+      <c r="D49" s="91" t="n"/>
+      <c r="E49" s="91" t="n"/>
+      <c r="F49" s="91" t="n"/>
+      <c r="G49" s="91" t="n"/>
+      <c r="H49" s="91" t="n"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="147" t="inlineStr">
+        <is>
+          <t>🔔 待重仓监控</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="148" t="inlineStr">
+        <is>
+          <t>标的</t>
+        </is>
+      </c>
+      <c r="B51" s="148" t="inlineStr">
+        <is>
+          <t>状态</t>
+        </is>
+      </c>
+      <c r="C51" s="148" t="inlineStr">
+        <is>
+          <t>当前P/价格</t>
+        </is>
+      </c>
+      <c r="D51" s="148" t="inlineStr">
+        <is>
+          <t>最新信号</t>
+        </is>
+      </c>
+      <c r="E51" s="148" t="inlineStr">
+        <is>
+          <t>触发条件</t>
+        </is>
+      </c>
+      <c r="F51" s="148" t="inlineStr">
+        <is>
+          <t>距离触发</t>
+        </is>
+      </c>
+      <c r="G51" s="148" t="inlineStr">
+        <is>
+          <t>跟踪日期</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="87" t="inlineStr">
+        <is>
+          <t>玻璃基板</t>
+        </is>
+      </c>
+      <c r="B52" s="87" t="inlineStr">
+        <is>
+          <t>深南电路002916/兴森科技002436</t>
+        </is>
+      </c>
+      <c r="C52" s="87" t="inlineStr">
+        <is>
+          <t>观察中</t>
+        </is>
+      </c>
+      <c r="D52" s="87" t="inlineStr">
+        <is>
+          <t>蒋宇飞：玻璃基板大规模应用2028年，5-10年赛道</t>
+        </is>
+      </c>
+      <c r="E52" s="87" t="inlineStr">
+        <is>
+          <t>AI基建+国产替代加速</t>
+        </is>
+      </c>
+      <c r="F52" s="87" t="inlineStr">
+        <is>
+          <t>中长期</t>
+        </is>
+      </c>
+      <c r="G52" s="87" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="78" t="n"/>
+      <c r="B53" s="78" t="n"/>
+      <c r="C53" s="78" t="n"/>
+      <c r="D53" s="78" t="n"/>
+      <c r="E53" s="78" t="n"/>
+      <c r="F53" s="78" t="n"/>
+      <c r="G53" s="78" t="n"/>
+      <c r="H53" s="78" t="n"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="87" t="inlineStr">
+        <is>
+          <t>油气对冲</t>
+        </is>
+      </c>
+      <c r="B54" s="87" t="inlineStr">
+        <is>
+          <t>华宝油气162411</t>
+        </is>
+      </c>
+      <c r="C54" s="87" t="inlineStr">
+        <is>
+          <t>观察中</t>
+        </is>
+      </c>
+      <c r="D54" s="87" t="inlineStr">
+        <is>
+          <t>宋鸿兵：霍尔木兹封锁3个月，85%投资者押注回落=幻觉</t>
+        </is>
+      </c>
+      <c r="E54" s="87" t="inlineStr">
+        <is>
+          <t>油价冲150或海峡持续封锁</t>
+        </is>
+      </c>
+      <c r="F54" s="87" t="inlineStr">
+        <is>
+          <t>短期</t>
+        </is>
+      </c>
+      <c r="G54" s="87" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="H54" s="78" t="inlineStr">
+        <is>
+          <t>小仓位试水，不对称博弈</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="87" t="inlineStr">
+        <is>
+          <t>银行板块(512800)</t>
+        </is>
+      </c>
+      <c r="B55" s="87" t="inlineStr">
+        <is>
+          <t>弱势</t>
+        </is>
+      </c>
+      <c r="C55" s="87" t="inlineStr">
+        <is>
+          <t>P:50% 虚P-2pp</t>
+        </is>
+      </c>
+      <c r="D55" s="87" t="inlineStr">
+        <is>
+          <t>去杠杆+信贷收缩，ETF跌-1%，无催化</t>
+        </is>
+      </c>
+      <c r="E55" s="87" t="inlineStr">
+        <is>
+          <t>不建议加仓</t>
+        </is>
+      </c>
+      <c r="F55" s="87" t="inlineStr">
+        <is>
+          <t>短期</t>
+        </is>
+      </c>
+      <c r="G55" s="87" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="H55" s="78" t="inlineStr">
+        <is>
+          <t>银行ETF持续阴跌</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="87" t="inlineStr">
+        <is>
+          <t>人形机器人(562500)</t>
+        </is>
+      </c>
+      <c r="B56" s="87" t="inlineStr">
+        <is>
+          <t>强势</t>
+        </is>
+      </c>
+      <c r="C56" s="87" t="inlineStr">
+        <is>
+          <t>P:58%(估)</t>
+        </is>
+      </c>
+      <c r="D56" s="87" t="inlineStr">
+        <is>
+          <t>宇树科技73天过会，ETF涨+11%</t>
+        </is>
+      </c>
+      <c r="E56" s="87" t="inlineStr">
+        <is>
+          <t>重点关注</t>
+        </is>
+      </c>
+      <c r="F56" s="87" t="inlineStr">
+        <is>
+          <t>中期</t>
+        </is>
+      </c>
+      <c r="G56" s="87" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="H56" s="78" t="inlineStr">
+        <is>
+          <t>平安先进制造+永赢先进制造</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="87" t="inlineStr">
+        <is>
+          <t>存储赛道(5只A股)</t>
+        </is>
+      </c>
+      <c r="B57" s="87" t="inlineStr">
+        <is>
+          <t>❌降级观察</t>
+        </is>
+      </c>
+      <c r="C57" s="87" t="inlineStr">
+        <is>
+          <t>P:55% 安全边际不足</t>
+        </is>
+      </c>
+      <c r="D57" s="87" t="inlineStr">
+        <is>
+          <t>兆易¥525(+81%)/江波龙¥569/佰维¥341→PE天际线，向上空间&lt;向下空间</t>
+        </is>
+      </c>
+      <c r="E57" s="87" t="inlineStr">
+        <is>
+          <t>等中期选举大跌15%+</t>
+        </is>
+      </c>
+      <c r="F57" s="87" t="inlineStr">
+        <is>
+          <t>中期</t>
+        </is>
+      </c>
+      <c r="G57" s="87" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="H57" s="78" t="inlineStr">
+        <is>
+          <t>降级：存储涨完轮到堆叠，安全边际已不足</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="87" t="inlineStr">
+        <is>
+          <t>澜起科技(688008)</t>
+        </is>
+      </c>
+      <c r="B58" s="87" t="inlineStr">
+        <is>
+          <t>❌降级观察</t>
+        </is>
+      </c>
+      <c r="C58" s="87" t="inlineStr">
+        <is>
+          <t>P:55% 安全边际中等</t>
+        </is>
+      </c>
+      <c r="D58" s="87" t="inlineStr">
+        <is>
+          <t>DDR5接口芯片，温和上涨，但存储赛道整体降级</t>
+        </is>
+      </c>
+      <c r="E58" s="87" t="inlineStr">
+        <is>
+          <t>等大跌15%+</t>
+        </is>
+      </c>
+      <c r="F58" s="87" t="inlineStr">
+        <is>
+          <t>中期</t>
+        </is>
+      </c>
+      <c r="G58" s="87" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="H58" s="78" t="inlineStr">
+        <is>
+          <t>降级：存储赛道尾声</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="92" t="inlineStr">
+        <is>
+          <t>🔥堆叠/先进封装赛道（蒋宇飞"星光纯叠"框架）</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="87" t="inlineStr">
+        <is>
+          <t>长电科技(600584)</t>
+        </is>
+      </c>
+      <c r="B60" s="87" t="inlineStr">
+        <is>
+          <t>🔴核心标的</t>
+        </is>
+      </c>
+      <c r="C60" s="87" t="inlineStr">
+        <is>
+          <t>P:75%+ PE30x</t>
+        </is>
+      </c>
+      <c r="D60" s="87" t="inlineStr">
+        <is>
+          <t>全球第三大封测厂，2.5D/3D量产级，客户广度最强（高通/海思/TI）</t>
+        </is>
+      </c>
+      <c r="E60" s="87" t="inlineStr">
+        <is>
+          <t>等中期选举大跌</t>
+        </is>
+      </c>
+      <c r="F60" s="87" t="inlineStr">
+        <is>
+          <t>中期</t>
+        </is>
+      </c>
+      <c r="G60" s="87" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="H60" s="78" t="inlineStr">
+        <is>
+          <t>安全边际大，堆叠赛道首选</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="87" t="inlineStr">
+        <is>
+          <t>通富微电(002156)</t>
+        </is>
+      </c>
+      <c r="B61" s="87" t="inlineStr">
+        <is>
+          <t>🔴核心标的</t>
+        </is>
+      </c>
+      <c r="C61" s="87" t="inlineStr">
+        <is>
+          <t>P:75%+ 待查PE</t>
+        </is>
+      </c>
+      <c r="D61" s="87" t="inlineStr">
+        <is>
+          <t>AMD封测全线突破通道，2.5D量产，MI300X参与，不可替代</t>
+        </is>
+      </c>
+      <c r="E61" s="87" t="inlineStr">
+        <is>
+          <t>等中期选举大跌</t>
+        </is>
+      </c>
+      <c r="F61" s="87" t="inlineStr">
+        <is>
+          <t>中期</t>
+        </is>
+      </c>
+      <c r="G61" s="87" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="H61" s="78" t="inlineStr">
+        <is>
+          <t>安全边际中偏大，与长电各占一半</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="78" t="n"/>
+    </row>
+    <row r="63"/>
+    <row r="64"/>
+    <row r="65"/>
+    <row r="66"/>
+    <row r="67"/>
   </sheetData>
-  <mergeCells count="9">
-    <mergeCell ref="A12:H12"/>
+  <mergeCells count="36">
     <mergeCell ref="A16:F16"/>
-    <mergeCell ref="B14:H14"/>
-    <mergeCell ref="B13:H13"/>
-    <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A41:H41"/>
+    <mergeCell ref="C34:D34"/>
+    <mergeCell ref="A30:B30"/>
+    <mergeCell ref="A39:H39"/>
+    <mergeCell ref="C30:D30"/>
+    <mergeCell ref="A36:B36"/>
     <mergeCell ref="B15:H15"/>
     <mergeCell ref="A1:H1"/>
+    <mergeCell ref="E37:H37"/>
+    <mergeCell ref="C35:D35"/>
+    <mergeCell ref="C29:D29"/>
+    <mergeCell ref="A37:B37"/>
+    <mergeCell ref="A41:H41"/>
+    <mergeCell ref="C31:D31"/>
+    <mergeCell ref="A27:H27"/>
     <mergeCell ref="A45:G45"/>
+    <mergeCell ref="A12:H12"/>
+    <mergeCell ref="A21:H21"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="E35:H35"/>
+    <mergeCell ref="C36:D36"/>
+    <mergeCell ref="E29:H29"/>
+    <mergeCell ref="A33:H33"/>
+    <mergeCell ref="A22:H22"/>
+    <mergeCell ref="A35:B35"/>
+    <mergeCell ref="B14:H14"/>
+    <mergeCell ref="A29:B29"/>
+    <mergeCell ref="E31:H31"/>
+    <mergeCell ref="B13:H13"/>
+    <mergeCell ref="E34:H34"/>
+    <mergeCell ref="C37:D37"/>
+    <mergeCell ref="A28:H28"/>
+    <mergeCell ref="E30:H30"/>
+    <mergeCell ref="A31:B31"/>
+    <mergeCell ref="A34:B34"/>
+    <mergeCell ref="E36:H36"/>
   </mergeCells>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -2650,14 +3236,15 @@
     <row r="3" ht="72.75" customHeight="1" s="79">
       <c r="A3" s="96" t="inlineStr">
         <is>
-          <t>P:44%
+          <t>P:41%
 虚P+2pp
 利率折价-6pp
-有效P:38%
+有效P:35%
 拟合❌0分
 下行:25% 确定性:30% 溢价:50%
 盈亏比:1.2:1
-决策:观望</t>
+决策:观望
+【6/4三源联动】知乎0pp 达利欧-2pp 李大霄-1pp = 净-3pp</t>
         </is>
       </c>
       <c r="B3" s="96" t="inlineStr">
@@ -2674,14 +3261,15 @@
       </c>
       <c r="C3" s="96" t="inlineStr">
         <is>
-          <t>P:29%
+          <t>P:27%
 虚P无
 利率折价-6pp
-有效P:23%
+有效P:21%
 拟合✅75分
 下行:30% 确定性:15% 溢价:30%
 盈亏比:0.4:1
-决策:不干</t>
+决策:不干
+【6/4三源联动】知乎+1pp 达利欧-1pp 李大霄-2pp = 净-2pp</t>
         </is>
       </c>
       <c r="D3" s="96" t="inlineStr">
@@ -7363,4 +7951,710 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H37"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="18" customWidth="1" style="79" min="1" max="1"/>
+    <col width="20" customWidth="1" style="79" min="2" max="2"/>
+    <col width="22" customWidth="1" style="79" min="3" max="3"/>
+    <col width="22" customWidth="1" style="79" min="4" max="4"/>
+    <col width="12" customWidth="1" style="79" min="5" max="5"/>
+    <col width="10" customWidth="1" style="79" min="6" max="6"/>
+    <col width="10" customWidth="1" style="79" min="7" max="7"/>
+    <col width="12" customWidth="1" style="79" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="149" t="inlineStr">
+        <is>
+          <t>🔥 三源联动分析（2026-06-04）</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="150" t="inlineStr">
+        <is>
+          <t>知乎纳指安全 + 达利欧AI泡沫 + 李大霄窄牛宽熊 → 综合研判</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="150" t="inlineStr">
+        <is>
+          <t>一、三源核心观点对比</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="151" t="inlineStr">
+        <is>
+          <t>维度</t>
+        </is>
+      </c>
+      <c r="B5" s="151" t="inlineStr">
+        <is>
+          <t>知乎纳指安全</t>
+        </is>
+      </c>
+      <c r="C5" s="151" t="inlineStr">
+        <is>
+          <t>达利欧AI泡沫</t>
+        </is>
+      </c>
+      <c r="D5" s="151" t="inlineStr">
+        <is>
+          <t>李大霄窄牛宽熊</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="152" t="inlineStr">
+        <is>
+          <t>核心结论</t>
+        </is>
+      </c>
+      <c r="B6" s="152" t="inlineStr">
+        <is>
+          <t>纳指PE中值区间，安全</t>
+        </is>
+      </c>
+      <c r="C6" s="152" t="inlineStr">
+        <is>
+          <t>AI泡沫65-75%概率年底破</t>
+        </is>
+      </c>
+      <c r="D6" s="152" t="inlineStr">
+        <is>
+          <t>美股全市场已熊市，指数是假象</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="152" t="inlineStr">
+        <is>
+          <t>对AI态度</t>
+        </is>
+      </c>
+      <c r="B7" s="152" t="inlineStr">
+        <is>
+          <t>七姐妹6家估值合理</t>
+        </is>
+      </c>
+      <c r="C7" s="152" t="inlineStr">
+        <is>
+          <t>技术不会失败，但估值泡沫</t>
+        </is>
+      </c>
+      <c r="D7" s="152" t="inlineStr">
+        <is>
+          <t>AI龙头虹吸全市场资金</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="152" t="inlineStr">
+        <is>
+          <t>历史对标</t>
+        </is>
+      </c>
+      <c r="B8" s="152" t="inlineStr">
+        <is>
+          <t>5维度排查无暴跌信号</t>
+        </is>
+      </c>
+      <c r="C8" s="152" t="inlineStr">
+        <is>
+          <t>对标dotcom泡沫模式</t>
+        </is>
+      </c>
+      <c r="D8" s="152" t="inlineStr">
+        <is>
+          <t>对标2000科网+2008次贷</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="152" t="inlineStr">
+        <is>
+          <t>短期判断</t>
+        </is>
+      </c>
+      <c r="B9" s="152" t="inlineStr">
+        <is>
+          <t>继续持有</t>
+        </is>
+      </c>
+      <c r="C9" s="152" t="inlineStr">
+        <is>
+          <t>降低预期但不清仓</t>
+        </is>
+      </c>
+      <c r="D9" s="152" t="inlineStr">
+        <is>
+          <t>窄牛末期随时可能断崖</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="152" t="inlineStr">
+        <is>
+          <t>可信度</t>
+        </is>
+      </c>
+      <c r="B10" s="152" t="inlineStr">
+        <is>
+          <t>⭐⭐⭐ 中上</t>
+        </is>
+      </c>
+      <c r="C10" s="152" t="inlineStr">
+        <is>
+          <t>⭐⭐⭐⭐⭐ 极高</t>
+        </is>
+      </c>
+      <c r="D10" s="152" t="inlineStr">
+        <is>
+          <t>⭐⭐ 参考即可</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="150" t="inlineStr">
+        <is>
+          <t>二、三源互锁验证（关键）</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="152" t="inlineStr">
+        <is>
+          <t>达利欧×李大霄</t>
+        </is>
+      </c>
+      <c r="B13" s="153" t="inlineStr">
+        <is>
+          <t>✅ 互相印证</t>
+        </is>
+      </c>
+      <c r="C13" s="152" t="inlineStr">
+        <is>
+          <t>达利欧说AI泡沫→李大霄说窄牛宽熊=同一个现象的两个角度</t>
+        </is>
+      </c>
+      <c r="D13" s="152" t="inlineStr">
+        <is>
+          <t>强信号</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="152" t="inlineStr">
+        <is>
+          <t>知乎×达利欧</t>
+        </is>
+      </c>
+      <c r="B14" s="154" t="inlineStr">
+        <is>
+          <t>⚠️ 部分矛盾</t>
+        </is>
+      </c>
+      <c r="C14" s="152" t="inlineStr">
+        <is>
+          <t>知乎说PE中值安全 vs 达利欧说65-75%概率回调→知乎看估值，达利欧看流动性</t>
+        </is>
+      </c>
+      <c r="D14" s="152" t="inlineStr">
+        <is>
+          <t>中性</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="152" t="inlineStr">
+        <is>
+          <t>知乎×李大霄</t>
+        </is>
+      </c>
+      <c r="B15" s="155" t="inlineStr">
+        <is>
+          <t>❌ 矛盾</t>
+        </is>
+      </c>
+      <c r="C15" s="152" t="inlineStr">
+        <is>
+          <t>知乎说纳指安全 vs 李大霄说全市场已熊→知乎看指数，李大霄看全市场</t>
+        </is>
+      </c>
+      <c r="D15" s="152" t="inlineStr">
+        <is>
+          <t>需分辨</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="152" t="inlineStr">
+        <is>
+          <t>三源共识</t>
+        </is>
+      </c>
+      <c r="B16" s="152" t="inlineStr">
+        <is>
+          <t>🔴 核心共识</t>
+        </is>
+      </c>
+      <c r="C16" s="152" t="inlineStr">
+        <is>
+          <t>三源都承认：AI龙头估值偏高、市场极度集中、中小盘已熊</t>
+        </is>
+      </c>
+      <c r="D16" s="152" t="inlineStr">
+        <is>
+          <t>强信号</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="150" t="inlineStr">
+        <is>
+          <t>三、对持仓P值联动影响</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="151" t="inlineStr">
+        <is>
+          <t>持仓</t>
+        </is>
+      </c>
+      <c r="B20" s="151" t="inlineStr">
+        <is>
+          <t>知乎影响</t>
+        </is>
+      </c>
+      <c r="C20" s="151" t="inlineStr">
+        <is>
+          <t>达利欧影响</t>
+        </is>
+      </c>
+      <c r="D20" s="151" t="inlineStr">
+        <is>
+          <t>李大霄影响</t>
+        </is>
+      </c>
+      <c r="E20" s="151" t="inlineStr">
+        <is>
+          <t>净影响</t>
+        </is>
+      </c>
+      <c r="F20" s="151" t="inlineStr">
+        <is>
+          <t>原P值</t>
+        </is>
+      </c>
+      <c r="G20" s="151" t="inlineStr">
+        <is>
+          <t>新P值</t>
+        </is>
+      </c>
+      <c r="H20" s="151" t="inlineStr">
+        <is>
+          <t>决策</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="152" t="inlineStr">
+        <is>
+          <t>恒科009854</t>
+        </is>
+      </c>
+      <c r="B21" s="152" t="inlineStr">
+        <is>
+          <t>+1pp 纳指安全</t>
+        </is>
+      </c>
+      <c r="C21" s="152" t="inlineStr">
+        <is>
+          <t>-1pp AI泡沫连带</t>
+        </is>
+      </c>
+      <c r="D21" s="152" t="inlineStr">
+        <is>
+          <t>-2pp 窄牛宽熊</t>
+        </is>
+      </c>
+      <c r="E21" s="152" t="inlineStr">
+        <is>
+          <t>-2pp</t>
+        </is>
+      </c>
+      <c r="F21" s="152" t="inlineStr">
+        <is>
+          <t>29%</t>
+        </is>
+      </c>
+      <c r="G21" s="152" t="inlineStr">
+        <is>
+          <t>27%</t>
+        </is>
+      </c>
+      <c r="H21" s="152" t="inlineStr">
+        <is>
+          <t>❌不干</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="152" t="inlineStr">
+        <is>
+          <t>芯片020628</t>
+        </is>
+      </c>
+      <c r="B22" s="152" t="inlineStr">
+        <is>
+          <t>0pp 中性</t>
+        </is>
+      </c>
+      <c r="C22" s="152" t="inlineStr">
+        <is>
+          <t>-2pp AI泡沫直接</t>
+        </is>
+      </c>
+      <c r="D22" s="152" t="inlineStr">
+        <is>
+          <t>-1pp 权重集中</t>
+        </is>
+      </c>
+      <c r="E22" s="152" t="inlineStr">
+        <is>
+          <t>-3pp</t>
+        </is>
+      </c>
+      <c r="F22" s="152" t="inlineStr">
+        <is>
+          <t>44%</t>
+        </is>
+      </c>
+      <c r="G22" s="152" t="inlineStr">
+        <is>
+          <t>41%</t>
+        </is>
+      </c>
+      <c r="H22" s="152" t="inlineStr">
+        <is>
+          <t>⚠️观望</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="152" t="inlineStr">
+        <is>
+          <t>电池018926</t>
+        </is>
+      </c>
+      <c r="B23" s="152" t="inlineStr">
+        <is>
+          <t>0pp 无关联</t>
+        </is>
+      </c>
+      <c r="C23" s="152" t="inlineStr">
+        <is>
+          <t>0pp 无直接关联</t>
+        </is>
+      </c>
+      <c r="D23" s="152" t="inlineStr">
+        <is>
+          <t>0pp 无影响</t>
+        </is>
+      </c>
+      <c r="E23" s="152" t="inlineStr">
+        <is>
+          <t>0pp</t>
+        </is>
+      </c>
+      <c r="F23" s="152" t="inlineStr">
+        <is>
+          <t>65%</t>
+        </is>
+      </c>
+      <c r="G23" s="152" t="inlineStr">
+        <is>
+          <t>65%</t>
+        </is>
+      </c>
+      <c r="H23" s="152" t="inlineStr">
+        <is>
+          <t>✅持有</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="152" t="inlineStr">
+        <is>
+          <t>养殖014415</t>
+        </is>
+      </c>
+      <c r="B24" s="152" t="inlineStr">
+        <is>
+          <t>0pp 无关联</t>
+        </is>
+      </c>
+      <c r="C24" s="152" t="inlineStr">
+        <is>
+          <t>0pp 无直接关联</t>
+        </is>
+      </c>
+      <c r="D24" s="152" t="inlineStr">
+        <is>
+          <t>0pp 无影响</t>
+        </is>
+      </c>
+      <c r="E24" s="152" t="inlineStr">
+        <is>
+          <t>0pp</t>
+        </is>
+      </c>
+      <c r="F24" s="152" t="inlineStr">
+        <is>
+          <t>70%</t>
+        </is>
+      </c>
+      <c r="G24" s="152" t="inlineStr">
+        <is>
+          <t>70%</t>
+        </is>
+      </c>
+      <c r="H24" s="152" t="inlineStr">
+        <is>
+          <t>✅持有</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="152" t="inlineStr">
+        <is>
+          <t>有色004433</t>
+        </is>
+      </c>
+      <c r="B25" s="152" t="inlineStr">
+        <is>
+          <t>0pp 无关联</t>
+        </is>
+      </c>
+      <c r="C25" s="152" t="inlineStr">
+        <is>
+          <t>0pp 无直接关联</t>
+        </is>
+      </c>
+      <c r="D25" s="152" t="inlineStr">
+        <is>
+          <t>-1pp 美股熊传导</t>
+        </is>
+      </c>
+      <c r="E25" s="152" t="inlineStr">
+        <is>
+          <t>-1pp</t>
+        </is>
+      </c>
+      <c r="F25" s="152" t="inlineStr">
+        <is>
+          <t>39%</t>
+        </is>
+      </c>
+      <c r="G25" s="152" t="inlineStr">
+        <is>
+          <t>38%</t>
+        </is>
+      </c>
+      <c r="H25" s="152" t="inlineStr">
+        <is>
+          <t>⚠️观望</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="152" t="inlineStr">
+        <is>
+          <t>堆叠(长电/通富)</t>
+        </is>
+      </c>
+      <c r="B26" s="152" t="inlineStr">
+        <is>
+          <t>0pp 国内产业</t>
+        </is>
+      </c>
+      <c r="C26" s="152" t="inlineStr">
+        <is>
+          <t>0pp 技术不会失败</t>
+        </is>
+      </c>
+      <c r="D26" s="152" t="inlineStr">
+        <is>
+          <t>0pp 国内确定性</t>
+        </is>
+      </c>
+      <c r="E26" s="152" t="inlineStr">
+        <is>
+          <t>0pp</t>
+        </is>
+      </c>
+      <c r="F26" s="152" t="inlineStr">
+        <is>
+          <t>75%</t>
+        </is>
+      </c>
+      <c r="G26" s="152" t="inlineStr">
+        <is>
+          <t>75%</t>
+        </is>
+      </c>
+      <c r="H26" s="152" t="inlineStr">
+        <is>
+          <t>🔴重点</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="156" t="inlineStr">
+        <is>
+          <t>四、🔥 核心结论（三源联动+你的策略）</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="152" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B30" s="152" t="inlineStr">
+        <is>
+          <t>三源共识：AI龙头估值偏高，市场极度集中</t>
+        </is>
+      </c>
+      <c r="C30" s="152" t="inlineStr">
+        <is>
+          <t>达利欧+李大霄互相印证，知乎看估值中值但忽略集中度风险</t>
+        </is>
+      </c>
+      <c r="D30" s="155" t="inlineStr">
+        <is>
+          <t>🔴 高置信度</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="152" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B31" s="152" t="inlineStr">
+        <is>
+          <t>你的策略完全正确：等中期选举大跌=现金入场时机</t>
+        </is>
+      </c>
+      <c r="C31" s="152" t="inlineStr">
+        <is>
+          <t>达利欧说"技术不会失败"+你说"中期选举跌一波"=回调后大仓位进</t>
+        </is>
+      </c>
+      <c r="D31" s="153" t="inlineStr">
+        <is>
+          <t>🟢 高置信度</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="152" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B32" s="152" t="inlineStr">
+        <is>
+          <t>堆叠/先进封装不受美股泡沫影响</t>
+        </is>
+      </c>
+      <c r="C32" s="152" t="inlineStr">
+        <is>
+          <t>国内确定性产业趋势，三源都未提及国内封测，长电/通富安全边际大</t>
+        </is>
+      </c>
+      <c r="D32" s="153" t="inlineStr">
+        <is>
+          <t>🟢 高置信度</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="152" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B33" s="152" t="inlineStr">
+        <is>
+          <t>恒科/芯片短期承压，但不影响长期逻辑</t>
+        </is>
+      </c>
+      <c r="C33" s="152" t="inlineStr">
+        <is>
+          <t>窄牛宽熊是美股现象，港股科技受情绪传导，国内AI基建不受影响</t>
+        </is>
+      </c>
+      <c r="D33" s="154" t="inlineStr">
+        <is>
+          <t>🟡 中置信度</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="152" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B34" s="152" t="inlineStr">
+        <is>
+          <t>现金为王，等信号</t>
+        </is>
+      </c>
+      <c r="C34" s="152" t="inlineStr">
+        <is>
+          <t>三源都指向短期风险&gt;机会，你的中期选举策略=等65-75%概率的回调</t>
+        </is>
+      </c>
+      <c r="D34" s="153" t="inlineStr">
+        <is>
+          <t>🟢 高置信度</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="157" t="inlineStr">
+        <is>
+          <t>🎯 一句话：三源联动确认——AI泡沫短期风险高，但技术确定性不变。现金等中期选举回调，堆叠赛道国内确定性最高，与美股泡沫无关。</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="7">
+    <mergeCell ref="A12"/>
+    <mergeCell ref="A4"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A29"/>
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A37:H37"/>
+    <mergeCell ref="A19"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/持仓贝叶斯跟踪.xlsx
+++ b/持仓贝叶斯跟踪.xlsx
@@ -367,7 +367,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="29">
+  <fills count="30">
     <fill>
       <patternFill/>
     </fill>
@@ -536,6 +536,12 @@
         <bgColor rgb="008B0000"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="000000CD"/>
+        <bgColor rgb="000000CD"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="7">
     <border>
@@ -597,7 +603,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="178">
+  <cellXfs count="193">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -1102,6 +1108,41 @@
     <xf numFmtId="0" fontId="46" fillId="23" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="51" fillId="29" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="29" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="41" fillId="21" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="22" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="23" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="24" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="28" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="28" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="28" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="50" fillId="25" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="21" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="23" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="23" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="23" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1178,7 +1219,6 @@
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>Hermes</author>
-    <author>系统</author>
   </authors>
   <commentList>
     <comment ref="A4" authorId="0" shapeId="0">
@@ -1462,14 +1502,7 @@
 </t>
       </text>
     </comment>
-    <comment ref="E45" authorId="1" shapeId="0">
-      <text>
-        <t>信息源: 新浪财经K线API(sh562500)
-推理链: 宇树科技73天过会→人形机器人商业化元年→产业催化
-P值: 58%(估)，有效P=58%-6pp=52%</t>
-      </text>
-    </comment>
-    <comment ref="A53" authorId="0" shapeId="0">
+    <comment ref="A85" authorId="0" shapeId="0">
       <text>
         <t xml:space="preserve">【来源】蒋宇飞抖音视频（2026-05-25）"未来5-10年的黄金赛道，深度拆解玻璃基板的万亿机遇"
 【信源评估】蒋宇飞⭐⭐⭐高置信度（有产业实操经验，多次验证预测准确）
@@ -1484,7 +1517,7 @@
 </t>
       </text>
     </comment>
-    <comment ref="A55" authorId="0" shapeId="0">
+    <comment ref="A87" authorId="0" shapeId="0">
       <text>
         <t>信息源：东方财富+新浪财经2026-06-02
 核心数据：
@@ -1497,7 +1530,7 @@
 结论：不建议加仓</t>
       </text>
     </comment>
-    <comment ref="A56" authorId="0" shapeId="0">
+    <comment ref="A88" authorId="0" shapeId="0">
       <text>
         <t>信息源：东方财富头条+新浪财经2026-06-02
 核心数据：
@@ -1512,7 +1545,7 @@
 结论：重点关注，强正向信号</t>
       </text>
     </comment>
-    <comment ref="A57" authorId="0" shapeId="0">
+    <comment ref="A89" authorId="0" shapeId="0">
       <text>
         <t xml:space="preserve">【来源】群联潘健成(产业高管)+蒋宇飞(6.1两长存储+5.18框架)+宋鸿兵(6.2摩尔定律终结)+周鸿祎(内存决定AI)+用户6.3洞察
 【逻辑链】
@@ -1535,7 +1568,7 @@
 </t>
       </text>
     </comment>
-    <comment ref="A58" authorId="0" shapeId="0">
+    <comment ref="A90" authorId="0" shapeId="0">
       <text>
         <t xml:space="preserve">【来源】蒋宇飞星光纯叠框架+宋鸿兵华为韬定律+用户"AI瓶颈是内存而非算力"
 【逻辑链】
@@ -1549,7 +1582,7 @@
 </t>
       </text>
     </comment>
-    <comment ref="A60" authorId="0" shapeId="0">
+    <comment ref="A92" authorId="0" shapeId="0">
       <text>
         <t xml:space="preserve">【标的】北京君正 300223
 【核心逻辑】存储+计算芯片，DRAM新工艺突破，车载存储市占率提升。A股年内+51%，市值772亿。港股二度IPO中。盈亏比4:1，存储赛道里最强。
@@ -1560,7 +1593,7 @@
 </t>
       </text>
     </comment>
-    <comment ref="A61" authorId="0" shapeId="0">
+    <comment ref="A93" authorId="0" shapeId="0">
       <text>
         <t xml:space="preserve">【标的】兆易创新 603986
 【核心逻辑】NOR Flash国内龙头，DRAM布局中。存储涨价直接受益。盈亏比3.5:1。
@@ -1571,7 +1604,7 @@
 </t>
       </text>
     </comment>
-    <comment ref="A62" authorId="0" shapeId="0">
+    <comment ref="A94" authorId="0" shapeId="0">
       <text>
         <t xml:space="preserve">【标的】江波龙 301308
 【核心逻辑】存储模组+主控芯片，国产替代核心标的。盈亏比3.5:1。
@@ -1899,7 +1932,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:H67"/>
+  <dimension ref="A1:H94"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6171875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="18" customWidth="1" style="78" min="1" max="1"/>
@@ -2182,174 +2215,1000 @@
       <c r="A16" s="78" t="n"/>
     </row>
     <row r="17" ht="16.5" customHeight="1" s="79">
-      <c r="A17" s="87" t="inlineStr">
-        <is>
-          <t>🟡 中观产业传导</t>
-        </is>
-      </c>
+      <c r="A17" s="158" t="inlineStr">
+        <is>
+          <t>🔴🔴🔴 战略级虚P信号池 + 现金策略联动（2026-06-04）🔴🔴🔴</t>
+        </is>
+      </c>
+      <c r="B17" s="159" t="n"/>
+      <c r="C17" s="159" t="n"/>
+      <c r="D17" s="159" t="n"/>
+      <c r="E17" s="159" t="n"/>
+      <c r="F17" s="159" t="n"/>
+      <c r="G17" s="159" t="n"/>
+      <c r="H17" s="159" t="n"/>
     </row>
     <row r="18" ht="16.5" customHeight="1" s="79">
-      <c r="A18" s="87" t="inlineStr">
-        <is>
-          <t>AI硬件确定性(付鹏) → 内存=AI核心瓶颈(4信源互锁) → 国产替代加速 → 稀土断供日本 → 芯片/存储/HBM长期利好 | 短期被利率↑/地缘↑压制</t>
-        </is>
-      </c>
+      <c r="A18" s="160" t="inlineStr">
+        <is>
+          <t>虚P规则：未落地→记虚P→不加实P→等落地转实P。此板块锁定大部分现金，与机会成本联动分析。</t>
+        </is>
+      </c>
+      <c r="B18" s="161" t="n"/>
+      <c r="C18" s="161" t="n"/>
+      <c r="D18" s="161" t="n"/>
+      <c r="E18" s="161" t="n"/>
+      <c r="F18" s="161" t="n"/>
+      <c r="G18" s="161" t="n"/>
+      <c r="H18" s="161" t="n"/>
     </row>
     <row r="19" ht="16.5" customHeight="1" s="79">
-      <c r="A19" s="87" t="inlineStr">
-        <is>
-          <t>⚡ 传导: 利率↑→成长股↓ | 地缘↑→避险↑能源↑ | 去杠杆→消费↓养殖↓ | AI产业↑→芯片/存储↑(长期)</t>
-        </is>
-      </c>
+      <c r="A19" s="178" t="inlineStr">
+        <is>
+          <t>一、三源信号详情</t>
+        </is>
+      </c>
+      <c r="B19" s="179" t="n"/>
+      <c r="C19" s="179" t="n"/>
+      <c r="D19" s="179" t="n"/>
+      <c r="E19" s="179" t="n"/>
+      <c r="F19" s="179" t="n"/>
+      <c r="G19" s="179" t="n"/>
+      <c r="H19" s="179" t="n"/>
     </row>
     <row r="20" ht="30" customHeight="1" s="79">
-      <c r="A20" s="87" t="inlineStr">
-        <is>
-          <t>2026-05-30 但斌：沃什缩表受阻+沃勒鹰派，降息预期降温</t>
-        </is>
-      </c>
-      <c r="C20" s="87" t="inlineStr">
-        <is>
-          <t>2026-05-30 宋鸿兵：伊朗3.0反击或封锁海峡</t>
-        </is>
-      </c>
-      <c r="D20" s="87" t="inlineStr">
-        <is>
-          <t>2026-05-30 付鹏：去杠杆周期中登最难受</t>
-        </is>
-      </c>
-      <c r="E20" s="87" t="inlineStr">
-        <is>
-          <t>2026-05-30 宋鸿兵：海峡封锁→能源成本飙升</t>
-        </is>
-      </c>
-      <c r="F20" s="87" t="inlineStr">
-        <is>
-          <t>2026-05-30 岩松：存储1-2年产能饱和</t>
-        </is>
-      </c>
-      <c r="G20" s="87" t="inlineStr">
-        <is>
-          <t>2026-05-30 宋鸿兵：30年美债破5%双红线</t>
+      <c r="A20" s="162" t="inlineStr">
+        <is>
+          <t>来源</t>
+        </is>
+      </c>
+      <c r="B20" s="162" t="inlineStr">
+        <is>
+          <t>核心观点</t>
+        </is>
+      </c>
+      <c r="C20" s="162" t="inlineStr">
+        <is>
+          <t>与你策略契合</t>
+        </is>
+      </c>
+      <c r="D20" s="162" t="inlineStr">
+        <is>
+          <t>虚P方向</t>
+        </is>
+      </c>
+      <c r="E20" s="162" t="inlineStr">
+        <is>
+          <t>落地条件</t>
+        </is>
+      </c>
+      <c r="F20" s="162" t="inlineStr">
+        <is>
+          <t>状态</t>
+        </is>
+      </c>
+      <c r="G20" s="162" t="inlineStr">
+        <is>
+          <t>权重</t>
+        </is>
+      </c>
+      <c r="H20" s="162" t="inlineStr">
+        <is>
+          <t>备注</t>
         </is>
       </c>
     </row>
     <row r="21" ht="16.5" customHeight="1" s="79">
-      <c r="A21" s="158" t="inlineStr">
-        <is>
-          <t>🔴 战略级虚P信号池（2026-06-04）</t>
-        </is>
-      </c>
-      <c r="B21" s="159" t="n"/>
-      <c r="C21" s="159" t="n"/>
-      <c r="D21" s="159" t="n"/>
-      <c r="E21" s="159" t="n"/>
-      <c r="F21" s="159" t="n"/>
-      <c r="G21" s="159" t="n"/>
-      <c r="H21" s="159" t="n"/>
-    </row>
-    <row r="22" ht="16.5" customHeight="1" s="79">
-      <c r="A22" s="160" t="inlineStr">
-        <is>
-          <t>规则：虚P≠实P。未落地（无价格验证）的信号→记虚P→不直接加P值→等落地后再转实P。虚P仅用于方向预判和仓位准备。</t>
-        </is>
-      </c>
-      <c r="B22" s="161" t="n"/>
-      <c r="C22" s="161" t="n"/>
-      <c r="D22" s="161" t="n"/>
-      <c r="E22" s="161" t="n"/>
-      <c r="F22" s="161" t="n"/>
-      <c r="G22" s="161" t="n"/>
-      <c r="H22" s="161" t="n"/>
-    </row>
-    <row r="23" ht="16.5" customHeight="1" s="79">
-      <c r="A23" s="162" t="inlineStr">
-        <is>
-          <t>信号来源</t>
-        </is>
-      </c>
-      <c r="B23" s="162" t="inlineStr">
-        <is>
-          <t>核心观点</t>
-        </is>
-      </c>
-      <c r="C23" s="162" t="inlineStr">
-        <is>
-          <t>与你策略契合度</t>
-        </is>
-      </c>
-      <c r="D23" s="162" t="inlineStr">
-        <is>
-          <t>虚P方向</t>
-        </is>
-      </c>
-      <c r="E23" s="162" t="inlineStr">
-        <is>
-          <t>落地条件</t>
-        </is>
-      </c>
-      <c r="F23" s="162" t="inlineStr">
-        <is>
-          <t>状态</t>
-        </is>
-      </c>
-      <c r="G23" s="162" t="inlineStr">
-        <is>
-          <t>权重</t>
-        </is>
-      </c>
-      <c r="H23" s="162" t="inlineStr">
-        <is>
-          <t>备注</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="16.5" customHeight="1" s="79">
-      <c r="A24" s="163" t="inlineStr">
+      <c r="A21" s="163" t="inlineStr">
         <is>
           <t>达利欧
 Bloomberg 6/3</t>
         </is>
       </c>
-      <c r="B24" s="163" t="inlineStr">
-        <is>
-          <t>AI泡沫65-75%概率
-2026年底显著回调
-"技术本身不会失败"</t>
-        </is>
-      </c>
-      <c r="C24" s="164" t="inlineStr">
-        <is>
-          <t>🟢完全契合
+      <c r="B21" s="163" t="inlineStr">
+        <is>
+          <t>AI泡沫65-75%概率年底破
+"财富转现金=刺破泡沫"
+技术不会失败
+类比dotcom
+基建投入&gt;&gt;收入</t>
+        </is>
+      </c>
+      <c r="C21" s="164" t="inlineStr">
+        <is>
+          <t>完全契合
 等中期选举大跌
-现金入场</t>
-        </is>
-      </c>
-      <c r="D24" s="163" t="inlineStr">
-        <is>
-          <t>美股AI↓
-芯片短期承压</t>
-        </is>
-      </c>
-      <c r="E24" s="163" t="inlineStr">
+现金那时候用
+回调后大仓位进</t>
+        </is>
+      </c>
+      <c r="D21" s="163" t="inlineStr">
+        <is>
+          <t>芯片-2pp
+恒科-1pp
+(虚P)</t>
+        </is>
+      </c>
+      <c r="E21" s="163" t="inlineStr">
+        <is>
+          <t>七姐妹&gt;15%回调
+或破200日均线</t>
+        </is>
+      </c>
+      <c r="F21" s="165" t="inlineStr">
+        <is>
+          <t>未落地</t>
+        </is>
+      </c>
+      <c r="G21" s="166" t="inlineStr">
+        <is>
+          <t>极高
+5星</t>
+        </is>
+      </c>
+      <c r="H21" s="163" t="inlineStr">
+        <is>
+          <t>与你100%一致
+回调=买入机会</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="16.5" customHeight="1" s="79">
+      <c r="A22" s="163" t="inlineStr">
+        <is>
+          <t>李大霄
+金融界 6/4</t>
+        </is>
+      </c>
+      <c r="B22" s="163" t="inlineStr">
+        <is>
+          <t>美股窄牛宽熊
+仅20只创新高
+CAPE40倍
+权重极度集中
+IPO抽血</t>
+        </is>
+      </c>
+      <c r="C22" s="164" t="inlineStr">
+        <is>
+          <t>高度契合
+确认美股风险
+现金策略正确</t>
+        </is>
+      </c>
+      <c r="D22" s="163" t="inlineStr">
+        <is>
+          <t>恒科-2pp
+芯片-1pp
+(虚P)</t>
+        </is>
+      </c>
+      <c r="E22" s="163" t="inlineStr">
+        <is>
+          <t>纳指破200日均线
+多数成分股下跌</t>
+        </is>
+      </c>
+      <c r="F22" s="165" t="inlineStr">
+        <is>
+          <t>未落地</t>
+        </is>
+      </c>
+      <c r="G22" s="163" t="inlineStr">
+        <is>
+          <t>中高
+3星</t>
+        </is>
+      </c>
+      <c r="H22" s="163" t="inlineStr">
+        <is>
+          <t>数据靠谱
+结论偏激进</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="16.5" customHeight="1" s="79">
+      <c r="A23" s="163" t="inlineStr">
+        <is>
+          <t>知乎专栏
+6/4</t>
+        </is>
+      </c>
+      <c r="B23" s="163" t="inlineStr">
+        <is>
+          <t>纳指PE中值区间
+5维度无暴跌
+七姐妹估值合理
+安全继续持有</t>
+        </is>
+      </c>
+      <c r="C23" s="164" t="inlineStr">
+        <is>
+          <t>部分参考
+与达利欧矛盾
+看估值vs流动性</t>
+        </is>
+      </c>
+      <c r="D23" s="163" t="inlineStr">
+        <is>
+          <t>恒科+1pp
+(虚P)</t>
+        </is>
+      </c>
+      <c r="E23" s="163" t="inlineStr">
+        <is>
+          <t>PE跌破25
+或暴跌触发</t>
+        </is>
+      </c>
+      <c r="F23" s="165" t="inlineStr">
+        <is>
+          <t>未落地</t>
+        </is>
+      </c>
+      <c r="G23" s="163" t="inlineStr">
+        <is>
+          <t>中
+3星</t>
+        </is>
+      </c>
+      <c r="H23" s="163" t="inlineStr">
+        <is>
+          <t>框架合理
+忽略集中度</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="16.5" customHeight="1" s="79"/>
+    <row r="25" ht="16.5" customHeight="1" s="79">
+      <c r="A25" s="178" t="inlineStr">
+        <is>
+          <t>二、三源互锁验证</t>
+        </is>
+      </c>
+      <c r="B25" s="179" t="n"/>
+      <c r="C25" s="179" t="n"/>
+      <c r="D25" s="179" t="n"/>
+      <c r="E25" s="179" t="n"/>
+      <c r="F25" s="179" t="n"/>
+      <c r="G25" s="179" t="n"/>
+      <c r="H25" s="179" t="n"/>
+    </row>
+    <row r="26" ht="15" customHeight="1" s="79">
+      <c r="A26" s="180" t="inlineStr">
+        <is>
+          <t>互锁组合</t>
+        </is>
+      </c>
+      <c r="B26" s="180" t="inlineStr">
+        <is>
+          <t>关系</t>
+        </is>
+      </c>
+      <c r="C26" s="180" t="inlineStr">
+        <is>
+          <t>分析</t>
+        </is>
+      </c>
+      <c r="D26" s="180" t="inlineStr">
+        <is>
+          <t>信号强度</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="17.15" customHeight="1" s="79">
+      <c r="A27" s="181" t="inlineStr">
+        <is>
+          <t>达利欧×李大霄</t>
+        </is>
+      </c>
+      <c r="B27" s="182" t="inlineStr">
+        <is>
+          <t>✅强印证</t>
+        </is>
+      </c>
+      <c r="C27" s="163" t="inlineStr">
+        <is>
+          <t>AI泡沫+窄牛宽熊=同一现象两角度</t>
+        </is>
+      </c>
+      <c r="D27" s="163" t="inlineStr">
+        <is>
+          <t>🔴强信号</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="15" customHeight="1" s="79">
+      <c r="A28" s="181" t="inlineStr">
+        <is>
+          <t>达利欧×知乎</t>
+        </is>
+      </c>
+      <c r="B28" s="183" t="inlineStr">
+        <is>
+          <t>⚠️部分矛盾</t>
+        </is>
+      </c>
+      <c r="C28" s="163" t="inlineStr">
+        <is>
+          <t>达看流动性vs知乎看估值</t>
+        </is>
+      </c>
+      <c r="D28" s="163" t="inlineStr">
+        <is>
+          <t>🟡中性</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="15" customHeight="1" s="79">
+      <c r="A29" s="181" t="inlineStr">
+        <is>
+          <t>三源共识</t>
+        </is>
+      </c>
+      <c r="B29" s="184" t="inlineStr">
+        <is>
+          <t>🔴核心共识</t>
+        </is>
+      </c>
+      <c r="C29" s="163" t="inlineStr">
+        <is>
+          <t>AI龙头估值偏高+市场集中+中小盘已熊</t>
+        </is>
+      </c>
+      <c r="D29" s="163" t="inlineStr">
+        <is>
+          <t>🔴强信号</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="15" customHeight="1" s="79"/>
+    <row r="31" ht="15" customHeight="1" s="79">
+      <c r="A31" s="174" t="inlineStr">
+        <is>
+          <t>三、现金策略联动（锁定大部分现金储备）</t>
+        </is>
+      </c>
+      <c r="B31" s="175" t="n"/>
+      <c r="C31" s="175" t="n"/>
+      <c r="D31" s="175" t="n"/>
+      <c r="E31" s="175" t="n"/>
+      <c r="F31" s="175" t="n"/>
+      <c r="G31" s="175" t="n"/>
+      <c r="H31" s="175" t="n"/>
+    </row>
+    <row r="32" ht="15" customHeight="1" s="79">
+      <c r="A32" s="160" t="inlineStr">
+        <is>
+          <t>三源联动→达利欧65-75%概率年底AI回调+中期选举历史跌一波→锁定大部分现金→等11月回调入场</t>
+        </is>
+      </c>
+      <c r="B32" s="161" t="n"/>
+      <c r="C32" s="161" t="n"/>
+      <c r="D32" s="161" t="n"/>
+      <c r="E32" s="161" t="n"/>
+      <c r="F32" s="161" t="n"/>
+      <c r="G32" s="161" t="n"/>
+      <c r="H32" s="161" t="n"/>
+    </row>
+    <row r="33" ht="16.5" customHeight="1" s="79">
+      <c r="A33" s="180" t="inlineStr">
+        <is>
+          <t>维度</t>
+        </is>
+      </c>
+      <c r="B33" s="180" t="inlineStr">
+        <is>
+          <t>内容</t>
+        </is>
+      </c>
+      <c r="C33" s="180" t="inlineStr">
+        <is>
+          <t>影响</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="16.5" customHeight="1" s="79">
+      <c r="A34" s="163" t="inlineStr">
+        <is>
+          <t>现金锁定</t>
+        </is>
+      </c>
+      <c r="B34" s="163" t="inlineStr">
+        <is>
+          <t>大部分现金(60-70%)锁定等待</t>
+        </is>
+      </c>
+      <c r="C34" s="163" t="inlineStr">
+        <is>
+          <t>→当前可投资金大幅减少</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="16.5" customHeight="1" s="79">
+      <c r="A35" s="163" t="inlineStr">
+        <is>
+          <t>等待窗口</t>
+        </is>
+      </c>
+      <c r="B35" s="163" t="inlineStr">
+        <is>
+          <t>2026年11月中期选举前后</t>
+        </is>
+      </c>
+      <c r="C35" s="163" t="inlineStr">
+        <is>
+          <t>→约5个月等待期</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="16.5" customHeight="1" s="79">
+      <c r="A36" s="163" t="inlineStr">
+        <is>
+          <t>触发条件</t>
+        </is>
+      </c>
+      <c r="B36" s="163" t="inlineStr">
+        <is>
+          <t>美股跌一波+AI回调&gt;15%</t>
+        </is>
+      </c>
+      <c r="C36" s="163" t="inlineStr">
+        <is>
+          <t>→达利欧65-75%概率事件</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="16.5" customHeight="1" s="79">
+      <c r="A37" s="163" t="inlineStr">
+        <is>
+          <t>入场标的</t>
+        </is>
+      </c>
+      <c r="B37" s="163" t="inlineStr">
+        <is>
+          <t>堆叠：长电科技+通富微电</t>
+        </is>
+      </c>
+      <c r="C37" s="163" t="inlineStr">
+        <is>
+          <t>→国内确定性不受美股影响</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="16.5" customHeight="1" s="79">
+      <c r="A38" s="163" t="inlineStr">
+        <is>
+          <t>机会成本</t>
+        </is>
+      </c>
+      <c r="B38" s="163" t="inlineStr">
+        <is>
+          <t>持有现金5个月vs错过短期行情</t>
+        </is>
+      </c>
+      <c r="C38" s="163" t="inlineStr">
+        <is>
+          <t>→见下方机会成本联动</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="16.5" customHeight="1" s="79">
+      <c r="A39" s="163" t="inlineStr">
+        <is>
+          <t>下行保护</t>
+        </is>
+      </c>
+      <c r="B39" s="163" t="inlineStr">
+        <is>
+          <t>没跌→现金无损可继续等</t>
+        </is>
+      </c>
+      <c r="C39" s="163" t="inlineStr">
+        <is>
+          <t>→不对称博弈下有保底</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="16.5" customHeight="1" s="79"/>
+    <row r="41" ht="16.5" customHeight="1" s="79">
+      <c r="A41" s="174" t="inlineStr">
+        <is>
+          <t>四、机会成本联动分析（现金锁定vs其他选项）</t>
+        </is>
+      </c>
+      <c r="B41" s="175" t="n"/>
+      <c r="C41" s="175" t="n"/>
+      <c r="D41" s="175" t="n"/>
+      <c r="E41" s="175" t="n"/>
+      <c r="F41" s="175" t="n"/>
+      <c r="G41" s="175" t="n"/>
+      <c r="H41" s="175" t="n"/>
+    </row>
+    <row r="42" ht="16.5" customHeight="1" s="79">
+      <c r="A42" s="180" t="inlineStr">
+        <is>
+          <t>选项</t>
+        </is>
+      </c>
+      <c r="B42" s="180" t="inlineStr">
+        <is>
+          <t>P值</t>
+        </is>
+      </c>
+      <c r="C42" s="180" t="inlineStr">
+        <is>
+          <t>盈亏比</t>
+        </is>
+      </c>
+      <c r="D42" s="180" t="inlineStr">
+        <is>
+          <t>Score</t>
+        </is>
+      </c>
+      <c r="E42" s="180" t="inlineStr">
+        <is>
+          <t>现金锁定影响</t>
+        </is>
+      </c>
+      <c r="F42" s="180" t="inlineStr">
+        <is>
+          <t>建议</t>
+        </is>
+      </c>
+      <c r="G42" s="180" t="inlineStr">
+        <is>
+          <t>判断</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="16.5" customHeight="1" s="79">
+      <c r="A43" s="163" t="inlineStr">
+        <is>
+          <t>长电科技</t>
+        </is>
+      </c>
+      <c r="B43" s="163" t="inlineStr">
+        <is>
+          <t>75%</t>
+        </is>
+      </c>
+      <c r="C43" s="163" t="inlineStr">
+        <is>
+          <t>4.5:1</t>
+        </is>
+      </c>
+      <c r="D43" s="163" t="inlineStr">
+        <is>
+          <t>3.375</t>
+        </is>
+      </c>
+      <c r="E43" s="163" t="inlineStr">
+        <is>
+          <t>等回调大仓位
+现金锁定中</t>
+        </is>
+      </c>
+      <c r="F43" s="163" t="inlineStr">
+        <is>
+          <t>暂不动等11月</t>
+        </is>
+      </c>
+      <c r="G43" s="166" t="inlineStr">
+        <is>
+          <t>🔴最高优先</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="16.5" customHeight="1" s="79">
+      <c r="A44" s="163" t="inlineStr">
+        <is>
+          <t>通富微电</t>
+        </is>
+      </c>
+      <c r="B44" s="163" t="inlineStr">
+        <is>
+          <t>75%</t>
+        </is>
+      </c>
+      <c r="C44" s="163" t="inlineStr">
+        <is>
+          <t>4.0:1</t>
+        </is>
+      </c>
+      <c r="D44" s="163" t="inlineStr">
+        <is>
+          <t>3.000</t>
+        </is>
+      </c>
+      <c r="E44" s="163" t="inlineStr">
+        <is>
+          <t>等回调大仓位
+现金锁定中</t>
+        </is>
+      </c>
+      <c r="F44" s="163" t="inlineStr">
+        <is>
+          <t>暂不动等11月</t>
+        </is>
+      </c>
+      <c r="G44" s="166" t="inlineStr">
+        <is>
+          <t>🔴最高优先</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="16.5" customHeight="1" s="79">
+      <c r="A45" s="163" t="inlineStr">
+        <is>
+          <t>养殖</t>
+        </is>
+      </c>
+      <c r="B45" s="163" t="inlineStr">
+        <is>
+          <t>70%</t>
+        </is>
+      </c>
+      <c r="C45" s="163" t="inlineStr">
+        <is>
+          <t>2.0:1</t>
+        </is>
+      </c>
+      <c r="D45" s="163" t="inlineStr">
+        <is>
+          <t>1.400</t>
+        </is>
+      </c>
+      <c r="E45" s="163" t="inlineStr">
+        <is>
+          <t>已持仓不需现金</t>
+        </is>
+      </c>
+      <c r="F45" s="163" t="inlineStr">
+        <is>
+          <t>继续持有</t>
+        </is>
+      </c>
+      <c r="G45" s="164" t="inlineStr">
+        <is>
+          <t>✅已配置</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="16.5" customHeight="1" s="79">
+      <c r="A46" s="163" t="inlineStr">
+        <is>
+          <t>电池</t>
+        </is>
+      </c>
+      <c r="B46" s="163" t="inlineStr">
+        <is>
+          <t>65%</t>
+        </is>
+      </c>
+      <c r="C46" s="163" t="inlineStr">
+        <is>
+          <t>2.0:1</t>
+        </is>
+      </c>
+      <c r="D46" s="163" t="inlineStr">
+        <is>
+          <t>1.300</t>
+        </is>
+      </c>
+      <c r="E46" s="163" t="inlineStr">
+        <is>
+          <t>已持仓不需现金</t>
+        </is>
+      </c>
+      <c r="F46" s="163" t="inlineStr">
+        <is>
+          <t>继续持有</t>
+        </is>
+      </c>
+      <c r="G46" s="164" t="inlineStr">
+        <is>
+          <t>✅已配置</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="16.5" customHeight="1" s="79">
+      <c r="A47" s="163" t="inlineStr">
+        <is>
+          <t>核电</t>
+        </is>
+      </c>
+      <c r="B47" s="163" t="inlineStr">
+        <is>
+          <t>52%</t>
+        </is>
+      </c>
+      <c r="C47" s="163" t="inlineStr">
+        <is>
+          <t>1.5:1</t>
+        </is>
+      </c>
+      <c r="D47" s="163" t="inlineStr">
+        <is>
+          <t>0.780</t>
+        </is>
+      </c>
+      <c r="E47" s="163" t="inlineStr">
+        <is>
+          <t>10年维度
+小仓试水可行</t>
+        </is>
+      </c>
+      <c r="F47" s="163" t="inlineStr">
+        <is>
+          <t>不影响现金策略</t>
+        </is>
+      </c>
+      <c r="G47" s="167" t="inlineStr">
+        <is>
+          <t>🟡长期观察</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="16.5" customHeight="1" s="79">
+      <c r="A48" s="163" t="inlineStr">
+        <is>
+          <t>存储</t>
+        </is>
+      </c>
+      <c r="B48" s="163" t="inlineStr">
+        <is>
+          <t>55%</t>
+        </is>
+      </c>
+      <c r="C48" s="163" t="inlineStr">
+        <is>
+          <t>1.0:1</t>
+        </is>
+      </c>
+      <c r="D48" s="163" t="inlineStr">
+        <is>
+          <t>0.550</t>
+        </is>
+      </c>
+      <c r="E48" s="163" t="inlineStr">
+        <is>
+          <t>已降级</t>
+        </is>
+      </c>
+      <c r="F48" s="163" t="inlineStr">
+        <is>
+          <t>不动</t>
+        </is>
+      </c>
+      <c r="G48" s="166" t="inlineStr">
+        <is>
+          <t>❌已降级</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="16.5" customHeight="1" s="79">
+      <c r="A49" s="163" t="inlineStr">
+        <is>
+          <t>纯现金5月</t>
+        </is>
+      </c>
+      <c r="B49" s="163" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C49" s="163" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D49" s="163" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E49" s="163" t="inlineStr">
+        <is>
+          <t>机会成本
+可能错过短期</t>
+        </is>
+      </c>
+      <c r="F49" s="163" t="inlineStr">
+        <is>
+          <t>不对称博弈可接受</t>
+        </is>
+      </c>
+      <c r="G49" s="167" t="inlineStr">
+        <is>
+          <t>🟡可接受</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="87" t="inlineStr">
+        <is>
+          <t>AI硬件确定性(付鹏) → 内存=AI核心瓶颈(4信源互锁) → 国产替代加速 → 稀土断供日本 → 芯片/存储/HBM长期利好 | 短期被利率↑/地缘↑压制</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="185" t="inlineStr">
+        <is>
+          <t>五、虚P→实P转换条件 &amp; 操作触发</t>
+        </is>
+      </c>
+      <c r="B51" s="186" t="n"/>
+      <c r="C51" s="186" t="n"/>
+      <c r="D51" s="186" t="n"/>
+      <c r="E51" s="186" t="n"/>
+      <c r="F51" s="186" t="n"/>
+      <c r="G51" s="186" t="n"/>
+      <c r="H51" s="187" t="n"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="162" t="inlineStr">
+        <is>
+          <t>条件</t>
+        </is>
+      </c>
+      <c r="B52" s="180" t="inlineStr">
+        <is>
+          <t>触发信号</t>
+        </is>
+      </c>
+      <c r="C52" s="162" t="inlineStr">
+        <is>
+          <t>影响</t>
+        </is>
+      </c>
+      <c r="D52" s="162" t="inlineStr">
+        <is>
+          <t>操作</t>
+        </is>
+      </c>
+      <c r="E52" s="87" t="inlineStr">
+        <is>
+          <t>2026-05-30 宋鸿兵：海峡封锁→能源成本飙升</t>
+        </is>
+      </c>
+      <c r="F52" s="87" t="inlineStr">
+        <is>
+          <t>2026-05-30 岩松：存储1-2年产能饱和</t>
+        </is>
+      </c>
+      <c r="G52" s="87" t="inlineStr">
+        <is>
+          <t>2026-05-30 宋鸿兵：30年美债破5%双红线</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="188" t="inlineStr">
+        <is>
+          <t>达利欧落地</t>
+        </is>
+      </c>
+      <c r="B53" s="163" t="inlineStr">
+        <is>
+          <t>七姐妹&gt;15%回调或破200日均线</t>
+        </is>
+      </c>
+      <c r="C53" s="163" t="inlineStr">
+        <is>
+          <t>芯片/恒科虚P转实P</t>
+        </is>
+      </c>
+      <c r="D53" s="163" t="inlineStr">
+        <is>
+          <t>现金解锁→大仓位进堆叠</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="167" t="inlineStr">
+        <is>
+          <t>李大霄落地</t>
+        </is>
+      </c>
+      <c r="B54" s="163" t="inlineStr">
+        <is>
+          <t>多数成分股下跌+指数拐头</t>
+        </is>
+      </c>
+      <c r="C54" s="163" t="inlineStr">
+        <is>
+          <t>恒科/芯片虚P转实P</t>
+        </is>
+      </c>
+      <c r="D54" s="163" t="inlineStr">
+        <is>
+          <t>确认系统性风险→入场</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="189" t="inlineStr">
+        <is>
+          <t>中期选举</t>
+        </is>
+      </c>
+      <c r="B55" s="189" t="inlineStr">
+        <is>
+          <t>11月美股跌一波</t>
+        </is>
+      </c>
+      <c r="C55" s="189" t="inlineStr">
+        <is>
+          <t>你的策略触发</t>
+        </is>
+      </c>
+      <c r="D55" s="189" t="inlineStr">
+        <is>
+          <t>现金→长电+通富</t>
+        </is>
+      </c>
+      <c r="E55" s="162" t="inlineStr">
+        <is>
+          <t>落地条件</t>
+        </is>
+      </c>
+      <c r="F55" s="162" t="inlineStr">
+        <is>
+          <t>状态</t>
+        </is>
+      </c>
+      <c r="G55" s="162" t="inlineStr">
+        <is>
+          <t>权重</t>
+        </is>
+      </c>
+      <c r="H55" s="162" t="inlineStr">
+        <is>
+          <t>备注</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="163" t="inlineStr">
+        <is>
+          <t>堆叠独立</t>
+        </is>
+      </c>
+      <c r="B56" s="163" t="inlineStr">
+        <is>
+          <t>国内产业确定性</t>
+        </is>
+      </c>
+      <c r="C56" s="164" t="inlineStr">
+        <is>
+          <t>三源未提及国内封测</t>
+        </is>
+      </c>
+      <c r="D56" s="163" t="inlineStr">
+        <is>
+          <t>回调后优先配置</t>
+        </is>
+      </c>
+      <c r="E56" s="163" t="inlineStr">
         <is>
           <t>纳指/纳指七姐妹
 出现&gt;15%回调</t>
         </is>
       </c>
-      <c r="F24" s="165" t="inlineStr">
+      <c r="F56" s="165" t="inlineStr">
         <is>
           <t>⏳未落地
 (虚P状态)</t>
         </is>
       </c>
-      <c r="G24" s="166" t="inlineStr">
+      <c r="G56" s="166" t="inlineStr">
         <is>
           <t>⭐⭐⭐⭐⭐
 极高</t>
         </is>
       </c>
-      <c r="H24" s="163" t="inlineStr">
+      <c r="H56" s="163" t="inlineStr">
         <is>
           <t>6/4三源联动:
 芯片-2pp
@@ -2359,52 +3218,52 @@
         </is>
       </c>
     </row>
-    <row r="25" ht="16.5" customHeight="1" s="79">
-      <c r="A25" s="163" t="inlineStr">
+    <row r="57">
+      <c r="A57" s="163" t="inlineStr">
         <is>
           <t>李大霄
 金融界 6/4</t>
         </is>
       </c>
-      <c r="B25" s="163" t="inlineStr">
+      <c r="B57" s="163" t="inlineStr">
         <is>
           <t>美股窄牛宽熊
 仅20只创新高
 CAPE40倍→泡沫</t>
         </is>
       </c>
-      <c r="C25" s="164" t="inlineStr">
+      <c r="C57" s="164" t="inlineStr">
         <is>
           <t>🟢高度契合
 确认美股风险
 现金策略正确</t>
         </is>
       </c>
-      <c r="D25" s="163" t="inlineStr">
+      <c r="D57" s="163" t="inlineStr">
         <is>
           <t>美股全市场↓
 港股连带承压</t>
         </is>
       </c>
-      <c r="E25" s="163" t="inlineStr">
+      <c r="E57" s="163" t="inlineStr">
         <is>
           <t>纳指破200日均线
 或多数成分股下跌</t>
         </is>
       </c>
-      <c r="F25" s="165" t="inlineStr">
+      <c r="F57" s="165" t="inlineStr">
         <is>
           <t>⏳未落地
 (虚P状态)</t>
         </is>
       </c>
-      <c r="G25" s="163" t="inlineStr">
+      <c r="G57" s="163" t="inlineStr">
         <is>
           <t>⭐⭐⭐
 中高</t>
         </is>
       </c>
-      <c r="H25" s="163" t="inlineStr">
+      <c r="H57" s="163" t="inlineStr">
         <is>
           <t>6/4三源联动:
 恒科-2pp
@@ -2414,728 +3273,640 @@
         </is>
       </c>
     </row>
-    <row r="26" ht="15" customHeight="1" s="79">
-      <c r="A26" s="163" t="inlineStr">
-        <is>
-          <t>知乎专栏
-6/4</t>
-        </is>
-      </c>
-      <c r="B26" s="163" t="inlineStr">
-        <is>
-          <t>纳指PE中值区间
-5维度排查无暴跌
-继续持有</t>
-        </is>
-      </c>
-      <c r="C26" s="167" t="inlineStr">
-        <is>
-          <t>🟡部分参考
-与达利欧矛盾
-看估值vs看流动性</t>
-        </is>
-      </c>
-      <c r="D26" s="163" t="inlineStr">
-        <is>
-          <t>中性偏多
-纳指短期安全</t>
-        </is>
-      </c>
-      <c r="E26" s="163" t="inlineStr">
-        <is>
-          <t>纳指PE跌破25
-或出现暴跌维度触发</t>
-        </is>
-      </c>
-      <c r="F26" s="165" t="inlineStr">
-        <is>
-          <t>⏳未落地
-(虚P状态)</t>
-        </is>
-      </c>
-      <c r="G26" s="163" t="inlineStr">
-        <is>
-          <t>⭐⭐⭐
-中</t>
-        </is>
-      </c>
-      <c r="H26" s="163" t="inlineStr">
-        <is>
-          <t>6/4三源联动:
-恒科+1pp
-→已记虚P
-未转实P</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="17.15" customHeight="1" s="79">
-      <c r="A27" t="inlineStr">
+    <row r="58">
+      <c r="A58" s="190" t="inlineStr">
+        <is>
+          <t>⚡ 核心结论：三源联动确认AI泡沫风险+你的中期选举策略正确。大部分现金锁定等11月回调→大仓位进长电/通富。机会成本可接受（不对称博弈，下有保底）。虚P已记，等落地转实P。</t>
+        </is>
+      </c>
+      <c r="B58" s="191" t="n"/>
+      <c r="C58" s="191" t="n"/>
+      <c r="D58" s="191" t="n"/>
+      <c r="E58" s="191" t="n"/>
+      <c r="F58" s="191" t="n"/>
+      <c r="G58" s="191" t="n"/>
+      <c r="H58" s="192" t="n"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="78" t="inlineStr">
         <is>
           <t>────────────────────────────────────────────────────────────</t>
         </is>
       </c>
     </row>
-    <row r="28" ht="15" customHeight="1" s="79">
-      <c r="A28" s="168" t="inlineStr">
+    <row r="60">
+      <c r="A60" s="168" t="inlineStr">
         <is>
           <t>🔗 三源互锁验证</t>
         </is>
       </c>
-      <c r="B28" s="169" t="n"/>
-      <c r="C28" s="169" t="n"/>
-      <c r="D28" s="169" t="n"/>
-      <c r="E28" s="169" t="n"/>
-      <c r="F28" s="169" t="n"/>
-      <c r="G28" s="169" t="n"/>
-      <c r="H28" s="169" t="n"/>
-    </row>
-    <row r="29" ht="15" customHeight="1" s="79">
-      <c r="A29" s="170" t="inlineStr">
+    </row>
+    <row r="61">
+      <c r="A61" s="170" t="inlineStr">
         <is>
           <t>达利欧 × 李大霄</t>
         </is>
       </c>
-      <c r="C29" s="171" t="inlineStr">
+      <c r="C61" s="171" t="inlineStr">
         <is>
           <t>✅ 强印证</t>
         </is>
       </c>
-      <c r="E29" s="152" t="inlineStr">
+      <c r="E61" s="152" t="inlineStr">
         <is>
           <t>AI泡沫+窄牛宽熊=同一现象两角度，互相确认</t>
         </is>
       </c>
     </row>
-    <row r="30" ht="15" customHeight="1" s="79">
-      <c r="A30" s="170" t="inlineStr">
+    <row r="62">
+      <c r="A62" s="170" t="inlineStr">
         <is>
           <t>达利欧 × 知乎</t>
         </is>
       </c>
-      <c r="C30" s="172" t="inlineStr">
+      <c r="C62" s="172" t="inlineStr">
         <is>
           <t>⚠️ 部分矛盾</t>
         </is>
       </c>
-      <c r="E30" s="152" t="inlineStr">
+      <c r="E62" s="152" t="inlineStr">
         <is>
           <t>达利欧看流动性(泡沫将破) vs 知乎看估值(PE中值安全)</t>
         </is>
       </c>
     </row>
-    <row r="31" ht="15" customHeight="1" s="79">
-      <c r="A31" s="170" t="inlineStr">
+    <row r="63">
+      <c r="A63" s="170" t="inlineStr">
         <is>
           <t>三源共识</t>
         </is>
       </c>
-      <c r="C31" s="173" t="inlineStr">
+      <c r="C63" s="173" t="inlineStr">
         <is>
           <t>🔴 核心共识</t>
         </is>
       </c>
-      <c r="E31" s="152" t="inlineStr">
+      <c r="E63" s="152" t="inlineStr">
         <is>
           <t>AI龙头估值偏高+市场极度集中+中小盘已熊 → 短期风险&gt;机会</t>
         </is>
       </c>
     </row>
-    <row r="32" ht="15" customHeight="1" s="79"/>
-    <row r="33" ht="16.5" customHeight="1" s="79">
-      <c r="A33" s="174" t="inlineStr">
+    <row r="64"/>
+    <row r="65">
+      <c r="A65" s="174" t="inlineStr">
         <is>
           <t>🎯 结论（虚P→实P转换条件）</t>
         </is>
       </c>
-      <c r="B33" s="175" t="n"/>
-      <c r="C33" s="175" t="n"/>
-      <c r="D33" s="175" t="n"/>
-      <c r="E33" s="175" t="n"/>
-      <c r="F33" s="175" t="n"/>
-      <c r="G33" s="175" t="n"/>
-      <c r="H33" s="175" t="n"/>
-    </row>
-    <row r="34" ht="16.5" customHeight="1" s="79">
-      <c r="A34" s="170" t="inlineStr">
+    </row>
+    <row r="66">
+      <c r="A66" s="170" t="inlineStr">
         <is>
           <t>① 达利欧信号落地条件</t>
         </is>
       </c>
-      <c r="C34" s="152" t="inlineStr">
+      <c r="C66" s="152" t="inlineStr">
         <is>
           <t>纳指七姐妹出现&gt;15%回调 或 纳指破200日均线</t>
         </is>
       </c>
-      <c r="E34" s="176" t="inlineStr">
+      <c r="E66" s="176" t="inlineStr">
         <is>
           <t>→ 芯片/恒科虚P转实P → 确认减仓信号</t>
         </is>
       </c>
     </row>
-    <row r="35" ht="16.5" customHeight="1" s="79">
-      <c r="A35" s="170" t="inlineStr">
+    <row r="67">
+      <c r="A67" s="170" t="inlineStr">
         <is>
           <t>② 李大霄信号落地条件</t>
         </is>
       </c>
-      <c r="C35" s="152" t="inlineStr">
+      <c r="C67" s="152" t="inlineStr">
         <is>
           <t>纳指多数成分股连续下跌+指数拐头</t>
         </is>
       </c>
-      <c r="E35" s="176" t="inlineStr">
+      <c r="E67" s="176" t="inlineStr">
         <is>
           <t>→ 恒科/芯片虚P转实P → 确认美股系统性风险</t>
         </is>
       </c>
     </row>
-    <row r="36" ht="16.5" customHeight="1" s="79">
-      <c r="A36" s="170" t="inlineStr">
+    <row r="68">
+      <c r="A68" s="170" t="inlineStr">
         <is>
           <t>③ 你的策略触发条件</t>
         </is>
       </c>
-      <c r="C36" s="152" t="inlineStr">
+      <c r="C68" s="152" t="inlineStr">
         <is>
           <t>中期选举(11月)美股跌一波 + AI回调&gt;15%</t>
         </is>
       </c>
-      <c r="E36" s="176" t="inlineStr">
+      <c r="E68" s="176" t="inlineStr">
         <is>
           <t>→ 现金入场 → 大仓位进堆叠/先进封装</t>
         </is>
       </c>
     </row>
-    <row r="37" ht="16.5" customHeight="1" s="79">
-      <c r="A37" s="170" t="inlineStr">
+    <row r="69">
+      <c r="A69" s="170" t="inlineStr">
         <is>
           <t>④ 堆叠赛道独立性</t>
         </is>
       </c>
-      <c r="C37" s="152" t="inlineStr">
+      <c r="C69" s="152" t="inlineStr">
         <is>
           <t>国内产业确定性，三源均未提及国内封测</t>
         </is>
       </c>
-      <c r="E37" s="176" t="inlineStr">
+      <c r="E69" s="176" t="inlineStr">
         <is>
           <t>→ 不受美股泡沫直接影响 → 等回调后优先配置</t>
         </is>
       </c>
     </row>
-    <row r="38" ht="16.5" customHeight="1" s="79"/>
-    <row r="39" ht="16.5" customHeight="1" s="79">
-      <c r="A39" s="177" t="inlineStr">
+    <row r="70"/>
+    <row r="71">
+      <c r="A71" s="177" t="inlineStr">
         <is>
           <t>⚡ 一句话：三源确认AI泡沫风险+你的中期选举策略正确。虚P已记，等落地转实P。现金为王，堆叠赛道等回调后大仓位进。</t>
         </is>
       </c>
-      <c r="B39" s="161" t="n"/>
-      <c r="C39" s="161" t="n"/>
-      <c r="D39" s="161" t="n"/>
-      <c r="E39" s="161" t="n"/>
-      <c r="F39" s="161" t="n"/>
-      <c r="G39" s="161" t="n"/>
-      <c r="H39" s="161" t="n"/>
-    </row>
-    <row r="40" ht="16.5" customHeight="1" s="79"/>
-    <row r="41" ht="16.5" customHeight="1" s="79"/>
-    <row r="42" ht="16.5" customHeight="1" s="79"/>
-    <row r="43" ht="16.5" customHeight="1" s="79">
-      <c r="A43" s="87" t="inlineStr">
+    </row>
+    <row r="72"/>
+    <row r="73"/>
+    <row r="74"/>
+    <row r="75">
+      <c r="A75" s="87" t="inlineStr">
         <is>
           <t>🤖 人形机器人半年事件链</t>
         </is>
       </c>
     </row>
-    <row r="44" ht="16.5" customHeight="1" s="79">
-      <c r="A44" s="78" t="n"/>
-    </row>
-    <row r="45" ht="16.5" customHeight="1" s="79">
-      <c r="A45" s="87" t="inlineStr">
+    <row r="76">
+      <c r="A76" s="78" t="n"/>
+    </row>
+    <row r="77">
+      <c r="A77" s="87" t="inlineStr">
         <is>
           <t>2026-03-23 机器人ETF暴跌-4.1%至0.909：市场恐慌+AI回调</t>
         </is>
       </c>
-      <c r="B45" s="78" t="n"/>
-      <c r="E45" s="89" t="n"/>
-    </row>
-    <row r="46" ht="16.5" customHeight="1" s="79">
-      <c r="A46" s="87" t="inlineStr">
+    </row>
+    <row r="78">
+      <c r="A78" s="87" t="inlineStr">
         <is>
           <t>2026-04-08 机器人ETF暴涨+6.4%至0.967：人形机器人产业催化</t>
         </is>
       </c>
-      <c r="D46" s="78" t="n"/>
-    </row>
-    <row r="47" ht="16.5" customHeight="1" s="79">
-      <c r="A47" s="87" t="inlineStr">
+      <c r="D78" s="78" t="n"/>
+    </row>
+    <row r="79">
+      <c r="A79" s="87" t="inlineStr">
         <is>
           <t>2026-05-07~22 机器人连续上涨：ETF 1.056→1.216(+15%)，宇树科技73天过会</t>
         </is>
       </c>
-      <c r="D47" s="78" t="n"/>
-    </row>
-    <row r="48" ht="16.5" customHeight="1" s="79">
-      <c r="A48" s="87" t="inlineStr">
+      <c r="D79" s="78" t="n"/>
+    </row>
+    <row r="80">
+      <c r="A80" s="87" t="inlineStr">
         <is>
           <t>2026-05-25~06-02 机器人回调：1.216→1.122(-7.7%)，仍处强势区间</t>
         </is>
       </c>
-      <c r="D48" s="78" t="n"/>
-    </row>
-    <row r="49" ht="16.5" customHeight="1" s="79">
-      <c r="A49" s="90" t="inlineStr">
+      <c r="D80" s="78" t="n"/>
+    </row>
+    <row r="81">
+      <c r="A81" s="90" t="inlineStr">
         <is>
           <t>2026-06-04 【保持观察】霍尔木兹海峡Day 12：伊朗暂停谈判+美众议院限制动武，WTI $96→$91-93回落，方向趋于缓和</t>
         </is>
       </c>
-      <c r="B49" s="91" t="n"/>
-      <c r="C49" s="91" t="n"/>
-      <c r="D49" s="91" t="n"/>
-      <c r="E49" s="91" t="n"/>
-      <c r="F49" s="91" t="n"/>
-      <c r="G49" s="91" t="n"/>
-      <c r="H49" s="91" t="n"/>
-    </row>
-    <row r="50">
-      <c r="A50" s="147" t="inlineStr">
+      <c r="B81" s="91" t="n"/>
+      <c r="C81" s="91" t="n"/>
+      <c r="D81" s="91" t="n"/>
+      <c r="E81" s="91" t="n"/>
+      <c r="F81" s="91" t="n"/>
+      <c r="G81" s="91" t="n"/>
+      <c r="H81" s="91" t="n"/>
+    </row>
+    <row r="82">
+      <c r="A82" s="147" t="inlineStr">
         <is>
           <t>🔔 待重仓监控</t>
         </is>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" s="148" t="inlineStr">
+    <row r="83">
+      <c r="A83" s="148" t="inlineStr">
         <is>
           <t>标的</t>
         </is>
       </c>
-      <c r="B51" s="148" t="inlineStr">
+      <c r="B83" s="148" t="inlineStr">
         <is>
           <t>状态</t>
         </is>
       </c>
-      <c r="C51" s="148" t="inlineStr">
+      <c r="C83" s="148" t="inlineStr">
         <is>
           <t>当前P/价格</t>
         </is>
       </c>
-      <c r="D51" s="148" t="inlineStr">
+      <c r="D83" s="148" t="inlineStr">
         <is>
           <t>最新信号</t>
         </is>
       </c>
-      <c r="E51" s="148" t="inlineStr">
+      <c r="E83" s="148" t="inlineStr">
         <is>
           <t>触发条件</t>
         </is>
       </c>
-      <c r="F51" s="148" t="inlineStr">
+      <c r="F83" s="148" t="inlineStr">
         <is>
           <t>距离触发</t>
         </is>
       </c>
-      <c r="G51" s="148" t="inlineStr">
+      <c r="G83" s="148" t="inlineStr">
         <is>
           <t>跟踪日期</t>
         </is>
       </c>
     </row>
-    <row r="52">
-      <c r="A52" s="87" t="inlineStr">
+    <row r="84">
+      <c r="A84" s="87" t="inlineStr">
         <is>
           <t>玻璃基板</t>
         </is>
       </c>
-      <c r="B52" s="87" t="inlineStr">
+      <c r="B84" s="87" t="inlineStr">
         <is>
           <t>深南电路002916/兴森科技002436</t>
         </is>
       </c>
-      <c r="C52" s="87" t="inlineStr">
+      <c r="C84" s="87" t="inlineStr">
         <is>
           <t>观察中</t>
         </is>
       </c>
-      <c r="D52" s="87" t="inlineStr">
+      <c r="D84" s="87" t="inlineStr">
         <is>
           <t>蒋宇飞：玻璃基板大规模应用2028年，5-10年赛道</t>
         </is>
       </c>
-      <c r="E52" s="87" t="inlineStr">
+      <c r="E84" s="87" t="inlineStr">
         <is>
           <t>AI基建+国产替代加速</t>
         </is>
       </c>
-      <c r="F52" s="87" t="inlineStr">
+      <c r="F84" s="87" t="inlineStr">
         <is>
           <t>中长期</t>
         </is>
       </c>
-      <c r="G52" s="87" t="inlineStr">
+      <c r="G84" s="87" t="inlineStr">
         <is>
           <t>2026-06-02</t>
         </is>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" s="78" t="n"/>
-      <c r="B53" s="78" t="n"/>
-      <c r="C53" s="78" t="n"/>
-      <c r="D53" s="78" t="n"/>
-      <c r="E53" s="78" t="n"/>
-      <c r="F53" s="78" t="n"/>
-      <c r="G53" s="78" t="n"/>
-      <c r="H53" s="78" t="n"/>
-    </row>
-    <row r="54">
-      <c r="A54" s="87" t="inlineStr">
+    <row r="85">
+      <c r="A85" s="78" t="n"/>
+      <c r="B85" s="78" t="n"/>
+      <c r="C85" s="78" t="n"/>
+      <c r="D85" s="78" t="n"/>
+      <c r="E85" s="78" t="n"/>
+      <c r="F85" s="78" t="n"/>
+      <c r="G85" s="78" t="n"/>
+      <c r="H85" s="78" t="n"/>
+    </row>
+    <row r="86">
+      <c r="A86" s="87" t="inlineStr">
         <is>
           <t>油气对冲</t>
         </is>
       </c>
-      <c r="B54" s="87" t="inlineStr">
+      <c r="B86" s="87" t="inlineStr">
         <is>
           <t>华宝油气162411</t>
         </is>
       </c>
-      <c r="C54" s="87" t="inlineStr">
+      <c r="C86" s="87" t="inlineStr">
         <is>
           <t>观察中</t>
         </is>
       </c>
-      <c r="D54" s="87" t="inlineStr">
+      <c r="D86" s="87" t="inlineStr">
         <is>
           <t>宋鸿兵：霍尔木兹封锁3个月，85%投资者押注回落=幻觉</t>
         </is>
       </c>
-      <c r="E54" s="87" t="inlineStr">
+      <c r="E86" s="87" t="inlineStr">
         <is>
           <t>油价冲150或海峡持续封锁</t>
         </is>
       </c>
-      <c r="F54" s="87" t="inlineStr">
+      <c r="F86" s="87" t="inlineStr">
         <is>
           <t>短期</t>
         </is>
       </c>
-      <c r="G54" s="87" t="inlineStr">
+      <c r="G86" s="87" t="inlineStr">
         <is>
           <t>2026-06-02</t>
         </is>
       </c>
-      <c r="H54" s="78" t="inlineStr">
+      <c r="H86" s="78" t="inlineStr">
         <is>
           <t>小仓位试水，不对称博弈</t>
         </is>
       </c>
     </row>
-    <row r="55">
-      <c r="A55" s="87" t="inlineStr">
+    <row r="87">
+      <c r="A87" s="87" t="inlineStr">
         <is>
           <t>银行板块(512800)</t>
         </is>
       </c>
-      <c r="B55" s="87" t="inlineStr">
+      <c r="B87" s="87" t="inlineStr">
         <is>
           <t>弱势</t>
         </is>
       </c>
-      <c r="C55" s="87" t="inlineStr">
+      <c r="C87" s="87" t="inlineStr">
         <is>
           <t>P:50% 虚P-2pp</t>
         </is>
       </c>
-      <c r="D55" s="87" t="inlineStr">
+      <c r="D87" s="87" t="inlineStr">
         <is>
           <t>去杠杆+信贷收缩，ETF跌-1%，无催化</t>
         </is>
       </c>
-      <c r="E55" s="87" t="inlineStr">
+      <c r="E87" s="87" t="inlineStr">
         <is>
           <t>不建议加仓</t>
         </is>
       </c>
-      <c r="F55" s="87" t="inlineStr">
+      <c r="F87" s="87" t="inlineStr">
         <is>
           <t>短期</t>
         </is>
       </c>
-      <c r="G55" s="87" t="inlineStr">
+      <c r="G87" s="87" t="inlineStr">
         <is>
           <t>2026-06-03</t>
         </is>
       </c>
-      <c r="H55" s="78" t="inlineStr">
+      <c r="H87" s="78" t="inlineStr">
         <is>
           <t>银行ETF持续阴跌</t>
         </is>
       </c>
     </row>
-    <row r="56">
-      <c r="A56" s="87" t="inlineStr">
+    <row r="88">
+      <c r="A88" s="87" t="inlineStr">
         <is>
           <t>人形机器人(562500)</t>
         </is>
       </c>
-      <c r="B56" s="87" t="inlineStr">
+      <c r="B88" s="87" t="inlineStr">
         <is>
           <t>强势</t>
         </is>
       </c>
-      <c r="C56" s="87" t="inlineStr">
+      <c r="C88" s="87" t="inlineStr">
         <is>
           <t>P:58%(估)</t>
         </is>
       </c>
-      <c r="D56" s="87" t="inlineStr">
+      <c r="D88" s="87" t="inlineStr">
         <is>
           <t>宇树科技73天过会，ETF涨+11%</t>
         </is>
       </c>
-      <c r="E56" s="87" t="inlineStr">
+      <c r="E88" s="87" t="inlineStr">
         <is>
           <t>重点关注</t>
         </is>
       </c>
-      <c r="F56" s="87" t="inlineStr">
+      <c r="F88" s="87" t="inlineStr">
         <is>
           <t>中期</t>
         </is>
       </c>
-      <c r="G56" s="87" t="inlineStr">
+      <c r="G88" s="87" t="inlineStr">
         <is>
           <t>2026-06-03</t>
         </is>
       </c>
-      <c r="H56" s="78" t="inlineStr">
+      <c r="H88" s="78" t="inlineStr">
         <is>
           <t>平安先进制造+永赢先进制造</t>
         </is>
       </c>
     </row>
-    <row r="57">
-      <c r="A57" s="87" t="inlineStr">
+    <row r="89">
+      <c r="A89" s="87" t="inlineStr">
         <is>
           <t>存储赛道(5只A股)</t>
         </is>
       </c>
-      <c r="B57" s="87" t="inlineStr">
+      <c r="B89" s="87" t="inlineStr">
         <is>
           <t>❌降级观察</t>
         </is>
       </c>
-      <c r="C57" s="87" t="inlineStr">
+      <c r="C89" s="87" t="inlineStr">
         <is>
           <t>P:55% 安全边际不足</t>
         </is>
       </c>
-      <c r="D57" s="87" t="inlineStr">
+      <c r="D89" s="87" t="inlineStr">
         <is>
           <t>兆易¥525(+81%)/江波龙¥569/佰维¥341→PE天际线，向上空间&lt;向下空间</t>
         </is>
       </c>
-      <c r="E57" s="87" t="inlineStr">
+      <c r="E89" s="87" t="inlineStr">
         <is>
           <t>等中期选举大跌15%+</t>
         </is>
       </c>
-      <c r="F57" s="87" t="inlineStr">
+      <c r="F89" s="87" t="inlineStr">
         <is>
           <t>中期</t>
         </is>
       </c>
-      <c r="G57" s="87" t="inlineStr">
+      <c r="G89" s="87" t="inlineStr">
         <is>
           <t>2026-06-04</t>
         </is>
       </c>
-      <c r="H57" s="78" t="inlineStr">
+      <c r="H89" s="78" t="inlineStr">
         <is>
           <t>降级：存储涨完轮到堆叠，安全边际已不足</t>
         </is>
       </c>
     </row>
-    <row r="58">
-      <c r="A58" s="87" t="inlineStr">
+    <row r="90">
+      <c r="A90" s="87" t="inlineStr">
         <is>
           <t>澜起科技(688008)</t>
         </is>
       </c>
-      <c r="B58" s="87" t="inlineStr">
+      <c r="B90" s="87" t="inlineStr">
         <is>
           <t>❌降级观察</t>
         </is>
       </c>
-      <c r="C58" s="87" t="inlineStr">
+      <c r="C90" s="87" t="inlineStr">
         <is>
           <t>P:55% 安全边际中等</t>
         </is>
       </c>
-      <c r="D58" s="87" t="inlineStr">
+      <c r="D90" s="87" t="inlineStr">
         <is>
           <t>DDR5接口芯片，温和上涨，但存储赛道整体降级</t>
         </is>
       </c>
-      <c r="E58" s="87" t="inlineStr">
+      <c r="E90" s="87" t="inlineStr">
         <is>
           <t>等大跌15%+</t>
         </is>
       </c>
-      <c r="F58" s="87" t="inlineStr">
+      <c r="F90" s="87" t="inlineStr">
         <is>
           <t>中期</t>
         </is>
       </c>
-      <c r="G58" s="87" t="inlineStr">
+      <c r="G90" s="87" t="inlineStr">
         <is>
           <t>2026-06-04</t>
         </is>
       </c>
-      <c r="H58" s="78" t="inlineStr">
+      <c r="H90" s="78" t="inlineStr">
         <is>
           <t>降级：存储赛道尾声</t>
         </is>
       </c>
     </row>
-    <row r="59">
-      <c r="A59" s="92" t="inlineStr">
+    <row r="91">
+      <c r="A91" s="92" t="inlineStr">
         <is>
           <t>🔥堆叠/先进封装赛道（蒋宇飞"星光纯叠"框架）</t>
         </is>
       </c>
     </row>
-    <row r="60">
-      <c r="A60" s="87" t="inlineStr">
+    <row r="92">
+      <c r="A92" s="87" t="inlineStr">
         <is>
           <t>长电科技(600584)</t>
         </is>
       </c>
-      <c r="B60" s="87" t="inlineStr">
+      <c r="B92" s="87" t="inlineStr">
         <is>
           <t>🔴核心标的</t>
         </is>
       </c>
-      <c r="C60" s="87" t="inlineStr">
+      <c r="C92" s="87" t="inlineStr">
         <is>
           <t>P:75%+ PE30x</t>
         </is>
       </c>
-      <c r="D60" s="87" t="inlineStr">
+      <c r="D92" s="87" t="inlineStr">
         <is>
           <t>全球第三大封测厂，2.5D/3D量产级，客户广度最强（高通/海思/TI）</t>
         </is>
       </c>
-      <c r="E60" s="87" t="inlineStr">
+      <c r="E92" s="87" t="inlineStr">
         <is>
           <t>等中期选举大跌</t>
         </is>
       </c>
-      <c r="F60" s="87" t="inlineStr">
+      <c r="F92" s="87" t="inlineStr">
         <is>
           <t>中期</t>
         </is>
       </c>
-      <c r="G60" s="87" t="inlineStr">
+      <c r="G92" s="87" t="inlineStr">
         <is>
           <t>2026-06-04</t>
         </is>
       </c>
-      <c r="H60" s="78" t="inlineStr">
+      <c r="H92" s="78" t="inlineStr">
         <is>
           <t>安全边际大，堆叠赛道首选</t>
         </is>
       </c>
     </row>
-    <row r="61">
-      <c r="A61" s="87" t="inlineStr">
+    <row r="93">
+      <c r="A93" s="87" t="inlineStr">
         <is>
           <t>通富微电(002156)</t>
         </is>
       </c>
-      <c r="B61" s="87" t="inlineStr">
+      <c r="B93" s="87" t="inlineStr">
         <is>
           <t>🔴核心标的</t>
         </is>
       </c>
-      <c r="C61" s="87" t="inlineStr">
+      <c r="C93" s="87" t="inlineStr">
         <is>
           <t>P:75%+ 待查PE</t>
         </is>
       </c>
-      <c r="D61" s="87" t="inlineStr">
+      <c r="D93" s="87" t="inlineStr">
         <is>
           <t>AMD封测全线突破通道，2.5D量产，MI300X参与，不可替代</t>
         </is>
       </c>
-      <c r="E61" s="87" t="inlineStr">
+      <c r="E93" s="87" t="inlineStr">
         <is>
           <t>等中期选举大跌</t>
         </is>
       </c>
-      <c r="F61" s="87" t="inlineStr">
+      <c r="F93" s="87" t="inlineStr">
         <is>
           <t>中期</t>
         </is>
       </c>
-      <c r="G61" s="87" t="inlineStr">
+      <c r="G93" s="87" t="inlineStr">
         <is>
           <t>2026-06-04</t>
         </is>
       </c>
-      <c r="H61" s="78" t="inlineStr">
+      <c r="H93" s="78" t="inlineStr">
         <is>
           <t>安全边际中偏大，与长电各占一半</t>
         </is>
       </c>
     </row>
-    <row r="62">
-      <c r="A62" s="78" t="n"/>
-    </row>
-    <row r="63"/>
-    <row r="64"/>
-    <row r="65"/>
-    <row r="66"/>
-    <row r="67"/>
+    <row r="94">
+      <c r="A94" s="78" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="36">
+  <mergeCells count="16">
     <mergeCell ref="A16:F16"/>
-    <mergeCell ref="C34:D34"/>
-    <mergeCell ref="A30:B30"/>
-    <mergeCell ref="A39:H39"/>
-    <mergeCell ref="C30:D30"/>
-    <mergeCell ref="A36:B36"/>
+    <mergeCell ref="A51:H51"/>
     <mergeCell ref="B15:H15"/>
     <mergeCell ref="A1:H1"/>
-    <mergeCell ref="E37:H37"/>
-    <mergeCell ref="C35:D35"/>
-    <mergeCell ref="C29:D29"/>
-    <mergeCell ref="A37:B37"/>
+    <mergeCell ref="A25:H25"/>
     <mergeCell ref="A41:H41"/>
-    <mergeCell ref="C31:D31"/>
-    <mergeCell ref="A27:H27"/>
-    <mergeCell ref="A45:G45"/>
     <mergeCell ref="A12:H12"/>
-    <mergeCell ref="A21:H21"/>
+    <mergeCell ref="A18:H18"/>
     <mergeCell ref="A2:H2"/>
-    <mergeCell ref="E35:H35"/>
-    <mergeCell ref="C36:D36"/>
-    <mergeCell ref="E29:H29"/>
-    <mergeCell ref="A33:H33"/>
-    <mergeCell ref="A22:H22"/>
-    <mergeCell ref="A35:B35"/>
+    <mergeCell ref="A32:H32"/>
+    <mergeCell ref="A17:H17"/>
     <mergeCell ref="B14:H14"/>
-    <mergeCell ref="A29:B29"/>
-    <mergeCell ref="E31:H31"/>
     <mergeCell ref="B13:H13"/>
-    <mergeCell ref="E34:H34"/>
-    <mergeCell ref="C37:D37"/>
-    <mergeCell ref="A28:H28"/>
-    <mergeCell ref="E30:H30"/>
-    <mergeCell ref="A31:B31"/>
-    <mergeCell ref="A34:B34"/>
-    <mergeCell ref="E36:H36"/>
+    <mergeCell ref="A19:H19"/>
+    <mergeCell ref="A31:H31"/>
+    <mergeCell ref="A58:H58"/>
   </mergeCells>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>

--- a/持仓贝叶斯跟踪.xlsx
+++ b/持仓贝叶斯跟踪.xlsx
@@ -21,7 +21,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="53">
+  <fonts count="56">
     <font>
       <name val="Calibri"/>
       <charset val="1"/>
@@ -366,8 +366,22 @@
       <color rgb="00FF0000"/>
       <sz val="10"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="008B0000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FF0000"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <color rgb="00FF0000"/>
+      <sz val="9"/>
+    </font>
   </fonts>
-  <fills count="30">
+  <fills count="32">
     <fill>
       <patternFill/>
     </fill>
@@ -542,6 +556,18 @@
         <bgColor rgb="000000CD"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF2CC"/>
+        <bgColor rgb="00FFF2CC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F2F2F2"/>
+        <bgColor rgb="00F2F2F2"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="7">
     <border>
@@ -603,7 +629,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="193">
+  <cellXfs count="203">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -1143,6 +1169,28 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="23" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="23" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="53" fillId="30" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="30" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="42" fillId="21" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="17" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="18" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="31" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="55" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2220,13 +2268,6 @@
           <t>🔴🔴🔴 战略级虚P信号池 + 现金策略联动（2026-06-04）🔴🔴🔴</t>
         </is>
       </c>
-      <c r="B17" s="159" t="n"/>
-      <c r="C17" s="159" t="n"/>
-      <c r="D17" s="159" t="n"/>
-      <c r="E17" s="159" t="n"/>
-      <c r="F17" s="159" t="n"/>
-      <c r="G17" s="159" t="n"/>
-      <c r="H17" s="159" t="n"/>
     </row>
     <row r="18" ht="16.5" customHeight="1" s="79">
       <c r="A18" s="160" t="inlineStr">
@@ -2234,13 +2275,6 @@
           <t>虚P规则：未落地→记虚P→不加实P→等落地转实P。此板块锁定大部分现金，与机会成本联动分析。</t>
         </is>
       </c>
-      <c r="B18" s="161" t="n"/>
-      <c r="C18" s="161" t="n"/>
-      <c r="D18" s="161" t="n"/>
-      <c r="E18" s="161" t="n"/>
-      <c r="F18" s="161" t="n"/>
-      <c r="G18" s="161" t="n"/>
-      <c r="H18" s="161" t="n"/>
     </row>
     <row r="19" ht="16.5" customHeight="1" s="79">
       <c r="A19" s="178" t="inlineStr">
@@ -2248,13 +2282,6 @@
           <t>一、三源信号详情</t>
         </is>
       </c>
-      <c r="B19" s="179" t="n"/>
-      <c r="C19" s="179" t="n"/>
-      <c r="D19" s="179" t="n"/>
-      <c r="E19" s="179" t="n"/>
-      <c r="F19" s="179" t="n"/>
-      <c r="G19" s="179" t="n"/>
-      <c r="H19" s="179" t="n"/>
     </row>
     <row r="20" ht="30" customHeight="1" s="79">
       <c r="A20" s="162" t="inlineStr">
@@ -2466,13 +2493,6 @@
           <t>二、三源互锁验证</t>
         </is>
       </c>
-      <c r="B25" s="179" t="n"/>
-      <c r="C25" s="179" t="n"/>
-      <c r="D25" s="179" t="n"/>
-      <c r="E25" s="179" t="n"/>
-      <c r="F25" s="179" t="n"/>
-      <c r="G25" s="179" t="n"/>
-      <c r="H25" s="179" t="n"/>
     </row>
     <row r="26" ht="15" customHeight="1" s="79">
       <c r="A26" s="180" t="inlineStr">
@@ -2569,13 +2589,6 @@
           <t>三、现金策略联动（锁定大部分现金储备）</t>
         </is>
       </c>
-      <c r="B31" s="175" t="n"/>
-      <c r="C31" s="175" t="n"/>
-      <c r="D31" s="175" t="n"/>
-      <c r="E31" s="175" t="n"/>
-      <c r="F31" s="175" t="n"/>
-      <c r="G31" s="175" t="n"/>
-      <c r="H31" s="175" t="n"/>
     </row>
     <row r="32" ht="15" customHeight="1" s="79">
       <c r="A32" s="160" t="inlineStr">
@@ -2583,13 +2596,6 @@
           <t>三源联动→达利欧65-75%概率年底AI回调+中期选举历史跌一波→锁定大部分现金→等11月回调入场</t>
         </is>
       </c>
-      <c r="B32" s="161" t="n"/>
-      <c r="C32" s="161" t="n"/>
-      <c r="D32" s="161" t="n"/>
-      <c r="E32" s="161" t="n"/>
-      <c r="F32" s="161" t="n"/>
-      <c r="G32" s="161" t="n"/>
-      <c r="H32" s="161" t="n"/>
     </row>
     <row r="33" ht="16.5" customHeight="1" s="79">
       <c r="A33" s="180" t="inlineStr">
@@ -2717,13 +2723,6 @@
           <t>四、机会成本联动分析（现金锁定vs其他选项）</t>
         </is>
       </c>
-      <c r="B41" s="175" t="n"/>
-      <c r="C41" s="175" t="n"/>
-      <c r="D41" s="175" t="n"/>
-      <c r="E41" s="175" t="n"/>
-      <c r="F41" s="175" t="n"/>
-      <c r="G41" s="175" t="n"/>
-      <c r="H41" s="175" t="n"/>
     </row>
     <row r="42" ht="16.5" customHeight="1" s="79">
       <c r="A42" s="180" t="inlineStr">
@@ -3038,13 +3037,13 @@
           <t>五、虚P→实P转换条件 &amp; 操作触发</t>
         </is>
       </c>
-      <c r="B51" s="186" t="n"/>
-      <c r="C51" s="186" t="n"/>
-      <c r="D51" s="186" t="n"/>
-      <c r="E51" s="186" t="n"/>
-      <c r="F51" s="186" t="n"/>
-      <c r="G51" s="186" t="n"/>
-      <c r="H51" s="187" t="n"/>
+      <c r="B51" s="145" t="n"/>
+      <c r="C51" s="145" t="n"/>
+      <c r="D51" s="145" t="n"/>
+      <c r="E51" s="145" t="n"/>
+      <c r="F51" s="145" t="n"/>
+      <c r="G51" s="145" t="n"/>
+      <c r="H51" s="146" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="162" t="inlineStr">
@@ -3279,13 +3278,13 @@
           <t>⚡ 核心结论：三源联动确认AI泡沫风险+你的中期选举策略正确。大部分现金锁定等11月回调→大仓位进长电/通富。机会成本可接受（不对称博弈，下有保底）。虚P已记，等落地转实P。</t>
         </is>
       </c>
-      <c r="B58" s="191" t="n"/>
-      <c r="C58" s="191" t="n"/>
-      <c r="D58" s="191" t="n"/>
-      <c r="E58" s="191" t="n"/>
-      <c r="F58" s="191" t="n"/>
-      <c r="G58" s="191" t="n"/>
-      <c r="H58" s="192" t="n"/>
+      <c r="B58" s="145" t="n"/>
+      <c r="C58" s="145" t="n"/>
+      <c r="D58" s="145" t="n"/>
+      <c r="E58" s="145" t="n"/>
+      <c r="F58" s="145" t="n"/>
+      <c r="G58" s="145" t="n"/>
+      <c r="H58" s="146" t="n"/>
     </row>
     <row r="59">
       <c r="A59" s="78" t="inlineStr">
@@ -3352,7 +3351,6 @@
         </is>
       </c>
     </row>
-    <row r="64"/>
     <row r="65">
       <c r="A65" s="174" t="inlineStr">
         <is>
@@ -3428,7 +3426,6 @@
         </is>
       </c>
     </row>
-    <row r="70"/>
     <row r="71">
       <c r="A71" s="177" t="inlineStr">
         <is>
@@ -3436,9 +3433,6 @@
         </is>
       </c>
     </row>
-    <row r="72"/>
-    <row r="73"/>
-    <row r="74"/>
     <row r="75">
       <c r="A75" s="87" t="inlineStr">
         <is>
@@ -3891,22 +3885,22 @@
     </row>
   </sheetData>
   <mergeCells count="16">
+    <mergeCell ref="A12:H12"/>
     <mergeCell ref="A16:F16"/>
+    <mergeCell ref="B14:H14"/>
+    <mergeCell ref="A18:H18"/>
+    <mergeCell ref="B13:H13"/>
+    <mergeCell ref="A25:H25"/>
+    <mergeCell ref="A2:H2"/>
     <mergeCell ref="A51:H51"/>
+    <mergeCell ref="A41:H41"/>
+    <mergeCell ref="A19:H19"/>
     <mergeCell ref="B15:H15"/>
     <mergeCell ref="A1:H1"/>
-    <mergeCell ref="A25:H25"/>
-    <mergeCell ref="A41:H41"/>
-    <mergeCell ref="A12:H12"/>
-    <mergeCell ref="A18:H18"/>
-    <mergeCell ref="A2:H2"/>
     <mergeCell ref="A32:H32"/>
-    <mergeCell ref="A17:H17"/>
-    <mergeCell ref="B14:H14"/>
-    <mergeCell ref="B13:H13"/>
-    <mergeCell ref="A19:H19"/>
     <mergeCell ref="A31:H31"/>
     <mergeCell ref="A58:H58"/>
+    <mergeCell ref="A17:H17"/>
   </mergeCells>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -7534,7 +7528,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:N42"/>
+  <dimension ref="A1:N54"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6171875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="6" customWidth="1" style="78" min="1" max="1"/>
@@ -7545,630 +7539,492 @@
     <col width="12" customWidth="1" style="78" min="10" max="10"/>
     <col width="10" customWidth="1" style="78" min="11" max="11"/>
     <col width="14" customWidth="1" style="78" min="12" max="12"/>
-    <col width="30" customWidth="1" style="78" min="13" max="13"/>
-    <col width="25" customWidth="1" style="78" min="14" max="14"/>
+    <col width="12" customWidth="1" style="78" min="13" max="13"/>
+    <col width="16" customWidth="1" style="78" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1" ht="17.35" customHeight="1" s="79">
-      <c r="A1" s="136" t="inlineStr">
-        <is>
-          <t>机会成本比较 边际量排序</t>
+      <c r="A1" s="193" t="inlineStr">
+        <is>
+          <t>机会成本比较 边际量排序（含现金锁定机制 v2）</t>
         </is>
       </c>
     </row>
     <row r="2" ht="15" customHeight="1" s="79">
-      <c r="A2" s="137" t="inlineStr">
+      <c r="A2" s="160" t="inlineStr">
+        <is>
+          <t>🔒 现金锁定系数 = 达利欧概率(70%) × 三源互锁确认(强) × 时间权重(5/12月) ≈ 0.65 → 65%现金锁定等11月，仅35%可投资金可用</t>
+        </is>
+      </c>
+      <c r="B2" s="161" t="n"/>
+      <c r="C2" s="161" t="n"/>
+      <c r="D2" s="161" t="n"/>
+      <c r="E2" s="161" t="n"/>
+      <c r="F2" s="161" t="n"/>
+      <c r="G2" s="161" t="n"/>
+      <c r="H2" s="161" t="n"/>
+      <c r="I2" s="161" t="n"/>
+      <c r="J2" s="161" t="n"/>
+      <c r="K2" s="161" t="n"/>
+      <c r="L2" s="161" t="n"/>
+      <c r="M2" s="161" t="n"/>
+      <c r="N2" s="161" t="n"/>
+    </row>
+    <row r="3" ht="15" customHeight="1" s="79">
+      <c r="A3" s="194" t="inlineStr">
+        <is>
+          <t>折后仓位 = 原目标仓位 × (1-现金锁定系数) | 例：长电原37%×35%=13% | 已持仓不受影响 | 解锁条件：三源信号任一落地</t>
+        </is>
+      </c>
+      <c r="B3" s="195" t="n"/>
+      <c r="C3" s="195" t="n"/>
+      <c r="D3" s="195" t="n"/>
+      <c r="E3" s="195" t="n"/>
+      <c r="F3" s="195" t="n"/>
+      <c r="G3" s="195" t="n"/>
+      <c r="H3" s="195" t="n"/>
+      <c r="I3" s="195" t="n"/>
+      <c r="J3" s="195" t="n"/>
+      <c r="K3" s="195" t="n"/>
+      <c r="L3" s="195" t="n"/>
+      <c r="M3" s="195" t="n"/>
+      <c r="N3" s="195" t="n"/>
+    </row>
+    <row r="5" ht="17.15" customHeight="1" s="79">
+      <c r="A5" s="137" t="inlineStr">
         <is>
           <t>审核日期：2026-06-04 | 下次预计审核：2026-06-11（每周日）| 方法：吸引力Score = P*R - alpha*w*(1-P)</t>
         </is>
       </c>
-    </row>
-    <row r="3" ht="15" customHeight="1" s="79">
-      <c r="A3" s="137" t="inlineStr">
+      <c r="M5" s="196" t="inlineStr">
+        <is>
+          <t>折后仓位%</t>
+        </is>
+      </c>
+      <c r="N5" s="196" t="inlineStr">
+        <is>
+          <t>现金锁定状态</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="48.5" customHeight="1" s="79">
+      <c r="A6" s="137" t="inlineStr">
         <is>
           <t>双门槛过滤：P&gt;=60% + 盈亏比&gt;=2:1 通过 按Score排序分配现金 | alpha=1.0（集中度厌恶系数）</t>
         </is>
       </c>
-    </row>
-    <row r="5" ht="17.15" customHeight="1" s="79">
-      <c r="A5" s="138" t="inlineStr">
+      <c r="M6" s="183" t="inlineStr">
+        <is>
+          <t>13%</t>
+        </is>
+      </c>
+      <c r="N6" s="87" t="inlineStr">
+        <is>
+          <t>锁定65%现金 等解锁</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="32.8" customHeight="1" s="79">
+      <c r="M7" s="183" t="inlineStr">
+        <is>
+          <t>12%</t>
+        </is>
+      </c>
+      <c r="N7" s="87" t="inlineStr">
+        <is>
+          <t>锁定65%现金 等解锁</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="32.8" customHeight="1" s="79">
+      <c r="A8" s="138" t="inlineStr">
         <is>
           <t>排名</t>
         </is>
       </c>
-      <c r="B5" s="138" t="inlineStr">
+      <c r="B8" s="138" t="inlineStr">
         <is>
           <t>选项</t>
         </is>
       </c>
-      <c r="C5" s="138" t="inlineStr">
+      <c r="C8" s="138" t="inlineStr">
         <is>
           <t>代码</t>
         </is>
       </c>
-      <c r="D5" s="138" t="inlineStr">
+      <c r="D8" s="138" t="inlineStr">
         <is>
           <t>类型</t>
         </is>
       </c>
-      <c r="E5" s="138" t="inlineStr">
+      <c r="E8" s="138" t="inlineStr">
         <is>
           <t>P值</t>
         </is>
       </c>
-      <c r="F5" s="138" t="inlineStr">
+      <c r="F8" s="138" t="inlineStr">
         <is>
           <t>有效P</t>
         </is>
       </c>
-      <c r="G5" s="138" t="inlineStr">
+      <c r="G8" s="138" t="inlineStr">
         <is>
           <t>盈亏比</t>
         </is>
       </c>
-      <c r="H5" s="138" t="inlineStr">
+      <c r="H8" s="138" t="inlineStr">
         <is>
           <t>P*R</t>
         </is>
       </c>
-      <c r="I5" s="138" t="inlineStr">
+      <c r="I8" s="138" t="inlineStr">
         <is>
           <t>仓位w</t>
         </is>
       </c>
-      <c r="J5" s="138" t="inlineStr">
+      <c r="J8" s="138" t="inlineStr">
         <is>
           <t>吸引力Score</t>
         </is>
       </c>
-      <c r="K5" s="138" t="inlineStr">
+      <c r="K8" s="138" t="inlineStr">
         <is>
           <t>双门槛</t>
         </is>
       </c>
-      <c r="L5" s="138" t="inlineStr">
+      <c r="L8" s="138" t="inlineStr">
         <is>
           <t>建议操作</t>
         </is>
       </c>
-      <c r="M5" s="138" t="inlineStr">
-        <is>
-          <t>核心逻辑</t>
-        </is>
-      </c>
-      <c r="N5" s="138" t="inlineStr">
-        <is>
-          <t>风险提示</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="48.5" customHeight="1" s="79">
-      <c r="A6" s="139" t="n">
-        <v>1</v>
-      </c>
-      <c r="B6" s="139" t="inlineStr">
-        <is>
-          <t>长电科技</t>
-        </is>
-      </c>
-      <c r="C6" s="139" t="inlineStr">
-        <is>
-          <t>600584</t>
-        </is>
-      </c>
-      <c r="D6" s="139" t="inlineStr">
-        <is>
-          <t>待重仓-堆叠</t>
-        </is>
-      </c>
-      <c r="E6" s="139" t="inlineStr">
-        <is>
-          <t>75%</t>
-        </is>
-      </c>
-      <c r="F6" s="139" t="inlineStr">
-        <is>
-          <t>69%</t>
-        </is>
-      </c>
-      <c r="G6" s="139" t="inlineStr">
-        <is>
-          <t>4.5:1</t>
-        </is>
-      </c>
-      <c r="H6" s="139" t="inlineStr">
-        <is>
-          <t>3.375</t>
-        </is>
-      </c>
-      <c r="I6" s="139" t="inlineStr">
+      <c r="M8" s="182" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="J6" s="139" t="inlineStr">
-        <is>
-          <t>3.3750</t>
-        </is>
-      </c>
-      <c r="K6" s="139" t="inlineStr">
-        <is>
-          <t>通过</t>
-        </is>
-      </c>
-      <c r="L6" s="139" t="inlineStr">
-        <is>
-          <t>重点研究</t>
-        </is>
-      </c>
-      <c r="M6" s="139" t="inlineStr">
-        <is>
-          <t>全球第三大封测厂，2.5D/3D量产级，客户广度最强（高通/海思/TI）</t>
-        </is>
-      </c>
-      <c r="N6" s="139" t="inlineStr">
-        <is>
-          <t>先进封装估值偏高，需核实技术能力</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="32.8" customHeight="1" s="79">
-      <c r="A7" s="139" t="n">
-        <v>2</v>
-      </c>
-      <c r="B7" s="139" t="inlineStr">
-        <is>
-          <t>通富微电</t>
-        </is>
-      </c>
-      <c r="C7" s="139" t="inlineStr">
-        <is>
-          <t>002156</t>
-        </is>
-      </c>
-      <c r="D7" s="139" t="inlineStr">
-        <is>
-          <t>待重仓-堆叠</t>
-        </is>
-      </c>
-      <c r="E7" s="139" t="inlineStr">
-        <is>
-          <t>75%</t>
-        </is>
-      </c>
-      <c r="F7" s="139" t="inlineStr">
-        <is>
-          <t>69%</t>
-        </is>
-      </c>
-      <c r="G7" s="139" t="inlineStr">
-        <is>
-          <t>4.0:1</t>
-        </is>
-      </c>
-      <c r="H7" s="139" t="inlineStr">
-        <is>
-          <t>3.000</t>
-        </is>
-      </c>
-      <c r="I7" s="139" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="J7" s="139" t="inlineStr">
-        <is>
-          <t>3.0000</t>
-        </is>
-      </c>
-      <c r="K7" s="139" t="inlineStr">
-        <is>
-          <t>通过</t>
-        </is>
-      </c>
-      <c r="L7" s="139" t="inlineStr">
-        <is>
-          <t>重点研究</t>
-        </is>
-      </c>
-      <c r="M7" s="139" t="inlineStr">
-        <is>
-          <t>AMD封测全线突破通道，2.5D量产，不可替代</t>
-        </is>
-      </c>
-      <c r="N7" s="139" t="inlineStr">
-        <is>
-          <t>先进封装估值偏高，需核实技术能力</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="32.8" customHeight="1" s="79">
-      <c r="A8" s="139" t="n">
-        <v>3</v>
-      </c>
-      <c r="B8" s="139" t="inlineStr">
-        <is>
-          <t>养殖014415</t>
-        </is>
-      </c>
-      <c r="C8" s="139" t="inlineStr">
-        <is>
-          <t>养殖014415</t>
-        </is>
-      </c>
-      <c r="D8" s="139" t="inlineStr">
-        <is>
-          <t>持仓</t>
-        </is>
-      </c>
-      <c r="E8" s="139" t="inlineStr">
-        <is>
-          <t>70%</t>
-        </is>
-      </c>
-      <c r="F8" s="139" t="inlineStr">
-        <is>
-          <t>70%</t>
-        </is>
-      </c>
-      <c r="G8" s="139" t="inlineStr">
-        <is>
-          <t>2.0:1</t>
-        </is>
-      </c>
-      <c r="H8" s="139" t="inlineStr">
-        <is>
-          <t>1.400</t>
-        </is>
-      </c>
-      <c r="I8" s="139" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="J8" s="139" t="inlineStr">
-        <is>
-          <t>1.4000</t>
-        </is>
-      </c>
-      <c r="K8" s="139" t="inlineStr">
-        <is>
-          <t>通过</t>
-        </is>
-      </c>
-      <c r="L8" s="139" t="inlineStr">
-        <is>
-          <t>持有</t>
-        </is>
-      </c>
-      <c r="M8" s="139" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N8" s="139" t="inlineStr">
-        <is>
-          <t>已持仓持有，利率折价0pp</t>
+      <c r="N8" s="197" t="inlineStr">
+        <is>
+          <t>已持仓不动</t>
         </is>
       </c>
     </row>
     <row r="9" ht="32.8" customHeight="1" s="79">
       <c r="A9" s="139" t="n">
+        <v>1</v>
+      </c>
+      <c r="B9" s="139" t="inlineStr">
+        <is>
+          <t>长电科技</t>
+        </is>
+      </c>
+      <c r="C9" s="139" t="inlineStr">
+        <is>
+          <t>600584</t>
+        </is>
+      </c>
+      <c r="D9" s="139" t="inlineStr">
+        <is>
+          <t>待重仓-堆叠</t>
+        </is>
+      </c>
+      <c r="E9" s="139" t="inlineStr">
+        <is>
+          <t>75%</t>
+        </is>
+      </c>
+      <c r="F9" s="139" t="inlineStr">
+        <is>
+          <t>69%</t>
+        </is>
+      </c>
+      <c r="G9" s="139" t="inlineStr">
+        <is>
+          <t>4.5:1</t>
+        </is>
+      </c>
+      <c r="H9" s="139" t="inlineStr">
+        <is>
+          <t>3.375</t>
+        </is>
+      </c>
+      <c r="I9" s="139" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="J9" s="139" t="inlineStr">
+        <is>
+          <t>3.3750</t>
+        </is>
+      </c>
+      <c r="K9" s="139" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+      <c r="L9" s="139" t="inlineStr">
+        <is>
+          <t>重点研究</t>
+        </is>
+      </c>
+      <c r="M9" s="182" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="N9" s="198" t="inlineStr">
+        <is>
+          <t>已持仓不动</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="32.8" customHeight="1" s="79">
+      <c r="A10" s="139" t="n">
+        <v>2</v>
+      </c>
+      <c r="B10" s="139" t="inlineStr">
+        <is>
+          <t>通富微电</t>
+        </is>
+      </c>
+      <c r="C10" s="139" t="inlineStr">
+        <is>
+          <t>002156</t>
+        </is>
+      </c>
+      <c r="D10" s="139" t="inlineStr">
+        <is>
+          <t>待重仓-堆叠</t>
+        </is>
+      </c>
+      <c r="E10" s="139" t="inlineStr">
+        <is>
+          <t>75%</t>
+        </is>
+      </c>
+      <c r="F10" s="139" t="inlineStr">
+        <is>
+          <t>69%</t>
+        </is>
+      </c>
+      <c r="G10" s="139" t="inlineStr">
+        <is>
+          <t>4.0:1</t>
+        </is>
+      </c>
+      <c r="H10" s="139" t="inlineStr">
+        <is>
+          <t>3.000</t>
+        </is>
+      </c>
+      <c r="I10" s="139" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="J10" s="139" t="inlineStr">
+        <is>
+          <t>3.0000</t>
+        </is>
+      </c>
+      <c r="K10" s="139" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+      <c r="L10" s="139" t="inlineStr">
+        <is>
+          <t>重点研究</t>
+        </is>
+      </c>
+      <c r="M10" s="199" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="N10" s="198" t="inlineStr">
+        <is>
+          <t>未通过门槛</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="32.8" customHeight="1" s="79">
+      <c r="A11" s="139" t="n">
+        <v>3</v>
+      </c>
+      <c r="B11" s="139" t="inlineStr">
+        <is>
+          <t>养殖014415</t>
+        </is>
+      </c>
+      <c r="C11" s="139" t="inlineStr">
+        <is>
+          <t>养殖014415</t>
+        </is>
+      </c>
+      <c r="D11" s="139" t="inlineStr">
+        <is>
+          <t>持仓</t>
+        </is>
+      </c>
+      <c r="E11" s="139" t="inlineStr">
+        <is>
+          <t>70%</t>
+        </is>
+      </c>
+      <c r="F11" s="139" t="inlineStr">
+        <is>
+          <t>70%</t>
+        </is>
+      </c>
+      <c r="G11" s="139" t="inlineStr">
+        <is>
+          <t>2.0:1</t>
+        </is>
+      </c>
+      <c r="H11" s="139" t="inlineStr">
+        <is>
+          <t>1.400</t>
+        </is>
+      </c>
+      <c r="I11" s="139" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="J11" s="139" t="inlineStr">
+        <is>
+          <t>1.4000</t>
+        </is>
+      </c>
+      <c r="K11" s="139" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+      <c r="L11" s="139" t="inlineStr">
+        <is>
+          <t>持有</t>
+        </is>
+      </c>
+      <c r="M11" s="182" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="N11" s="198" t="inlineStr">
+        <is>
+          <t>已持仓不动</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="32.8" customHeight="1" s="79">
+      <c r="A12" s="139" t="n">
         <v>4</v>
       </c>
-      <c r="B9" s="139" t="inlineStr">
+      <c r="B12" s="139" t="inlineStr">
         <is>
           <t>电池018926</t>
         </is>
       </c>
-      <c r="C9" s="139" t="inlineStr">
+      <c r="C12" s="139" t="inlineStr">
         <is>
           <t>电池018926</t>
         </is>
       </c>
-      <c r="D9" s="139" t="inlineStr">
+      <c r="D12" s="139" t="inlineStr">
         <is>
           <t>持仓</t>
         </is>
       </c>
-      <c r="E9" s="139" t="inlineStr">
+      <c r="E12" s="139" t="inlineStr">
         <is>
           <t>65%</t>
         </is>
       </c>
-      <c r="F9" s="139" t="inlineStr">
+      <c r="F12" s="139" t="inlineStr">
         <is>
           <t>59%</t>
         </is>
       </c>
-      <c r="G9" s="139" t="inlineStr">
+      <c r="G12" s="139" t="inlineStr">
         <is>
           <t>2.0:1</t>
         </is>
       </c>
-      <c r="H9" s="139" t="inlineStr">
+      <c r="H12" s="139" t="inlineStr">
         <is>
           <t>1.300</t>
         </is>
       </c>
-      <c r="I9" s="139" t="inlineStr">
+      <c r="I12" s="139" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="J9" s="139" t="inlineStr">
+      <c r="J12" s="139" t="inlineStr">
         <is>
           <t>1.3000</t>
         </is>
       </c>
-      <c r="K9" s="139" t="inlineStr">
+      <c r="K12" s="139" t="inlineStr">
         <is>
           <t>通过</t>
         </is>
       </c>
-      <c r="L9" s="139" t="inlineStr">
+      <c r="L12" s="139" t="inlineStr">
         <is>
           <t>持有</t>
         </is>
       </c>
-      <c r="M9" s="139" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N9" s="139" t="inlineStr">
-        <is>
-          <t>已持仓持有，利率折价6pp</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="32.8" customHeight="1" s="79">
-      <c r="A10" s="140" t="n">
-        <v>5</v>
-      </c>
-      <c r="B10" s="140" t="inlineStr">
-        <is>
-          <t>核电</t>
-        </is>
-      </c>
-      <c r="C10" s="140" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D10" s="140" t="inlineStr">
-        <is>
-          <t>待重仓-核电</t>
-        </is>
-      </c>
-      <c r="E10" s="140" t="inlineStr">
-        <is>
-          <t>52%</t>
-        </is>
-      </c>
-      <c r="F10" s="140" t="inlineStr">
-        <is>
-          <t>52%</t>
-        </is>
-      </c>
-      <c r="G10" s="140" t="inlineStr">
-        <is>
-          <t>1.5:1</t>
-        </is>
-      </c>
-      <c r="H10" s="140" t="inlineStr">
-        <is>
-          <t>0.780</t>
-        </is>
-      </c>
-      <c r="I10" s="140" t="inlineStr">
+      <c r="M12" s="182" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="J10" s="140" t="inlineStr">
-        <is>
-          <t>0.7800</t>
-        </is>
-      </c>
-      <c r="K10" s="141" t="inlineStr">
-        <is>
-          <t>未通过</t>
-        </is>
-      </c>
-      <c r="L10" s="140" t="inlineStr">
-        <is>
-          <t>长期跟踪</t>
-        </is>
-      </c>
-      <c r="M10" s="140" t="inlineStr">
-        <is>
-          <t>孙宇晨10年看核电，AI算力电力需求，审批加速</t>
-        </is>
-      </c>
-      <c r="N10" s="140" t="inlineStr">
-        <is>
-          <t>短期业绩承压Q1负34%，建设周期长5-8年</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="32.8" customHeight="1" s="79">
-      <c r="A11" s="140" t="n">
-        <v>6</v>
-      </c>
-      <c r="B11" s="140" t="inlineStr">
-        <is>
-          <t>银行001595</t>
-        </is>
-      </c>
-      <c r="C11" s="140" t="inlineStr">
-        <is>
-          <t>银行001595</t>
-        </is>
-      </c>
-      <c r="D11" s="140" t="inlineStr">
-        <is>
-          <t>持仓</t>
-        </is>
-      </c>
-      <c r="E11" s="140" t="inlineStr">
-        <is>
-          <t>47%</t>
-        </is>
-      </c>
-      <c r="F11" s="140" t="inlineStr">
-        <is>
-          <t>47%</t>
-        </is>
-      </c>
-      <c r="G11" s="140" t="inlineStr">
-        <is>
-          <t>1.5:1</t>
-        </is>
-      </c>
-      <c r="H11" s="140" t="inlineStr">
-        <is>
-          <t>0.705</t>
-        </is>
-      </c>
-      <c r="I11" s="140" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="J11" s="140" t="inlineStr">
-        <is>
-          <t>0.7050</t>
-        </is>
-      </c>
-      <c r="K11" s="141" t="inlineStr">
-        <is>
-          <t>未通过</t>
-        </is>
-      </c>
-      <c r="L11" s="140" t="inlineStr">
-        <is>
-          <t>监控</t>
-        </is>
-      </c>
-      <c r="M11" s="140" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N11" s="140" t="inlineStr">
-        <is>
-          <t>已持仓监控，利率折价0pp</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="32.8" customHeight="1" s="79">
-      <c r="A12" s="140" t="n">
-        <v>7</v>
-      </c>
-      <c r="B12" s="140" t="inlineStr">
-        <is>
-          <t>有色004433</t>
-        </is>
-      </c>
-      <c r="C12" s="140" t="inlineStr">
-        <is>
-          <t>有色004433</t>
-        </is>
-      </c>
-      <c r="D12" s="140" t="inlineStr">
-        <is>
-          <t>持仓</t>
-        </is>
-      </c>
-      <c r="E12" s="140" t="inlineStr">
-        <is>
-          <t>39%</t>
-        </is>
-      </c>
-      <c r="F12" s="140" t="inlineStr">
-        <is>
-          <t>35%</t>
-        </is>
-      </c>
-      <c r="G12" s="140" t="inlineStr">
-        <is>
-          <t>1.7:1</t>
-        </is>
-      </c>
-      <c r="H12" s="140" t="inlineStr">
-        <is>
-          <t>0.663</t>
-        </is>
-      </c>
-      <c r="I12" s="140" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="J12" s="140" t="inlineStr">
-        <is>
-          <t>0.6630</t>
-        </is>
-      </c>
-      <c r="K12" s="141" t="inlineStr">
-        <is>
-          <t>未通过</t>
-        </is>
-      </c>
-      <c r="L12" s="140" t="inlineStr">
-        <is>
-          <t>观望</t>
-        </is>
-      </c>
-      <c r="M12" s="140" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N12" s="140" t="inlineStr">
-        <is>
-          <t>已持仓观望，利率折价4pp</t>
+      <c r="N12" s="198" t="inlineStr">
+        <is>
+          <t>已持仓不动</t>
         </is>
       </c>
     </row>
     <row r="13" ht="32.8" customHeight="1" s="79">
       <c r="A13" s="140" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="B13" s="140" t="inlineStr">
         <is>
-          <t>稀金014111</t>
+          <t>核电</t>
         </is>
       </c>
       <c r="C13" s="140" t="inlineStr">
         <is>
-          <t>稀金014111</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D13" s="140" t="inlineStr">
         <is>
-          <t>持仓</t>
+          <t>待重仓-核电</t>
         </is>
       </c>
       <c r="E13" s="140" t="inlineStr">
         <is>
-          <t>40%</t>
+          <t>52%</t>
         </is>
       </c>
       <c r="F13" s="140" t="inlineStr">
         <is>
-          <t>36%</t>
+          <t>52%</t>
         </is>
       </c>
       <c r="G13" s="140" t="inlineStr">
         <is>
-          <t>1.6:1</t>
+          <t>1.5:1</t>
         </is>
       </c>
       <c r="H13" s="140" t="inlineStr">
         <is>
-          <t>0.640</t>
+          <t>0.780</t>
         </is>
       </c>
       <c r="I13" s="140" t="inlineStr">
@@ -8178,7 +8034,7 @@
       </c>
       <c r="J13" s="140" t="inlineStr">
         <is>
-          <t>0.6400</t>
+          <t>0.7800</t>
         </is>
       </c>
       <c r="K13" s="141" t="inlineStr">
@@ -8188,57 +8044,57 @@
       </c>
       <c r="L13" s="140" t="inlineStr">
         <is>
-          <t>观望</t>
-        </is>
-      </c>
-      <c r="M13" s="140" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N13" s="140" t="inlineStr">
-        <is>
-          <t>已持仓观望，利率折价4pp</t>
+          <t>长期跟踪</t>
+        </is>
+      </c>
+      <c r="M13" s="182" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="N13" s="87" t="inlineStr">
+        <is>
+          <t>已持仓不动</t>
         </is>
       </c>
     </row>
     <row r="14" ht="32.8" customHeight="1" s="79">
       <c r="A14" s="140" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B14" s="140" t="inlineStr">
         <is>
-          <t>存储赛道</t>
+          <t>银行001595</t>
         </is>
       </c>
       <c r="C14" s="140" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>银行001595</t>
         </is>
       </c>
       <c r="D14" s="140" t="inlineStr">
         <is>
-          <t>待重仓-存储</t>
+          <t>持仓</t>
         </is>
       </c>
       <c r="E14" s="140" t="inlineStr">
         <is>
-          <t>55%</t>
+          <t>47%</t>
         </is>
       </c>
       <c r="F14" s="140" t="inlineStr">
         <is>
-          <t>49%</t>
+          <t>47%</t>
         </is>
       </c>
       <c r="G14" s="140" t="inlineStr">
         <is>
-          <t>1.0:1</t>
+          <t>1.5:1</t>
         </is>
       </c>
       <c r="H14" s="140" t="inlineStr">
         <is>
-          <t>0.550</t>
+          <t>0.705</t>
         </is>
       </c>
       <c r="I14" s="140" t="inlineStr">
@@ -8248,7 +8104,7 @@
       </c>
       <c r="J14" s="140" t="inlineStr">
         <is>
-          <t>0.5500</t>
+          <t>0.7050</t>
         </is>
       </c>
       <c r="K14" s="141" t="inlineStr">
@@ -8258,32 +8114,32 @@
       </c>
       <c r="L14" s="140" t="inlineStr">
         <is>
-          <t>降级观察</t>
-        </is>
-      </c>
-      <c r="M14" s="140" t="inlineStr">
-        <is>
-          <t>兆易525元涨81% PE天际线，安全边际不足</t>
-        </is>
-      </c>
-      <c r="N14" s="140" t="inlineStr">
-        <is>
-          <t>安全边际不足，PE天际线，向上小于向下</t>
+          <t>监控</t>
+        </is>
+      </c>
+      <c r="M14" s="184" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="N14" s="87" t="inlineStr">
+        <is>
+          <t>已降级</t>
         </is>
       </c>
     </row>
     <row r="15" ht="32.8" customHeight="1" s="79">
       <c r="A15" s="140" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="B15" s="140" t="inlineStr">
         <is>
-          <t>芯片020628</t>
+          <t>有色004433</t>
         </is>
       </c>
       <c r="C15" s="140" t="inlineStr">
         <is>
-          <t>芯片020628</t>
+          <t>有色004433</t>
         </is>
       </c>
       <c r="D15" s="140" t="inlineStr">
@@ -8293,22 +8149,22 @@
       </c>
       <c r="E15" s="140" t="inlineStr">
         <is>
-          <t>44%</t>
+          <t>39%</t>
         </is>
       </c>
       <c r="F15" s="140" t="inlineStr">
         <is>
-          <t>38%</t>
+          <t>35%</t>
         </is>
       </c>
       <c r="G15" s="140" t="inlineStr">
         <is>
-          <t>1.2:1</t>
+          <t>1.7:1</t>
         </is>
       </c>
       <c r="H15" s="140" t="inlineStr">
         <is>
-          <t>0.528</t>
+          <t>0.663</t>
         </is>
       </c>
       <c r="I15" s="140" t="inlineStr">
@@ -8318,7 +8174,7 @@
       </c>
       <c r="J15" s="140" t="inlineStr">
         <is>
-          <t>0.5280</t>
+          <t>0.6630</t>
         </is>
       </c>
       <c r="K15" s="141" t="inlineStr">
@@ -8331,29 +8187,29 @@
           <t>观望</t>
         </is>
       </c>
-      <c r="M15" s="140" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N15" s="140" t="inlineStr">
-        <is>
-          <t>已持仓观望，利率折价6pp</t>
+      <c r="M15" s="182" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="N15" s="87" t="inlineStr">
+        <is>
+          <t>已持仓不动</t>
         </is>
       </c>
     </row>
     <row r="16" ht="32.8" customHeight="1" s="79">
       <c r="A16" s="140" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="B16" s="140" t="inlineStr">
         <is>
-          <t>恒科012349</t>
+          <t>稀金014111</t>
         </is>
       </c>
       <c r="C16" s="140" t="inlineStr">
         <is>
-          <t>恒科012349</t>
+          <t>稀金014111</t>
         </is>
       </c>
       <c r="D16" s="140" t="inlineStr">
@@ -8363,22 +8219,22 @@
       </c>
       <c r="E16" s="140" t="inlineStr">
         <is>
-          <t>29%</t>
+          <t>40%</t>
         </is>
       </c>
       <c r="F16" s="140" t="inlineStr">
         <is>
-          <t>23%</t>
+          <t>36%</t>
         </is>
       </c>
       <c r="G16" s="140" t="inlineStr">
         <is>
-          <t>0.4:1</t>
+          <t>1.6:1</t>
         </is>
       </c>
       <c r="H16" s="140" t="inlineStr">
         <is>
-          <t>0.116</t>
+          <t>0.640</t>
         </is>
       </c>
       <c r="I16" s="140" t="inlineStr">
@@ -8388,7 +8244,7 @@
       </c>
       <c r="J16" s="140" t="inlineStr">
         <is>
-          <t>0.1160</t>
+          <t>0.6400</t>
         </is>
       </c>
       <c r="K16" s="141" t="inlineStr">
@@ -8398,326 +8254,571 @@
       </c>
       <c r="L16" s="140" t="inlineStr">
         <is>
-          <t>不干</t>
-        </is>
-      </c>
-      <c r="M16" s="140" t="inlineStr">
+          <t>观望</t>
+        </is>
+      </c>
+      <c r="M16" s="182" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="N16" s="87" t="inlineStr">
+        <is>
+          <t>已持仓不动</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="17.15" customHeight="1" s="79">
+      <c r="A17" s="140" t="n">
+        <v>9</v>
+      </c>
+      <c r="B17" s="140" t="inlineStr">
+        <is>
+          <t>存储赛道</t>
+        </is>
+      </c>
+      <c r="C17" s="140" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="N16" s="140" t="inlineStr">
-        <is>
-          <t>已持仓不干，利率折价5pp</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="17.15" customHeight="1" s="79">
-      <c r="A17" s="142" t="n">
-        <v>12</v>
-      </c>
-      <c r="B17" s="142" t="inlineStr">
-        <is>
-          <t>现金</t>
-        </is>
-      </c>
-      <c r="C17" s="142" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D17" s="142" t="inlineStr">
-        <is>
-          <t>现金</t>
-        </is>
-      </c>
-      <c r="E17" s="142" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F17" s="142" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G17" s="142" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H17" s="142" t="inlineStr">
-        <is>
-          <t>0.000</t>
-        </is>
-      </c>
-      <c r="I17" s="142" t="inlineStr">
+      <c r="D17" s="140" t="inlineStr">
+        <is>
+          <t>待重仓-存储</t>
+        </is>
+      </c>
+      <c r="E17" s="140" t="inlineStr">
+        <is>
+          <t>55%</t>
+        </is>
+      </c>
+      <c r="F17" s="140" t="inlineStr">
+        <is>
+          <t>49%</t>
+        </is>
+      </c>
+      <c r="G17" s="140" t="inlineStr">
+        <is>
+          <t>1.0:1</t>
+        </is>
+      </c>
+      <c r="H17" s="140" t="inlineStr">
+        <is>
+          <t>0.550</t>
+        </is>
+      </c>
+      <c r="I17" s="140" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="J17" s="142" t="inlineStr">
-        <is>
-          <t>0.0000</t>
-        </is>
-      </c>
-      <c r="K17" s="142" t="inlineStr">
-        <is>
-          <t>基准</t>
-        </is>
-      </c>
-      <c r="L17" s="142" t="inlineStr">
-        <is>
-          <t>Score=0基准线</t>
-        </is>
-      </c>
-      <c r="M17" s="142" t="inlineStr">
-        <is>
-          <t>Score=0，所有选项都要跟现金比</t>
-        </is>
-      </c>
-      <c r="N17" s="142" t="inlineStr">
-        <is>
-          <t>无风险，但通胀侵蚀购买力</t>
+      <c r="J17" s="140" t="inlineStr">
+        <is>
+          <t>0.5500</t>
+        </is>
+      </c>
+      <c r="K17" s="141" t="inlineStr">
+        <is>
+          <t>未通过</t>
+        </is>
+      </c>
+      <c r="L17" s="140" t="inlineStr">
+        <is>
+          <t>降级观察</t>
+        </is>
+      </c>
+      <c r="M17" s="140" t="inlineStr">
+        <is>
+          <t>兆易525元涨81% PE天际线，安全边际不足</t>
+        </is>
+      </c>
+      <c r="N17" s="140" t="inlineStr">
+        <is>
+          <t>安全边际不足，PE天际线，向上小于向下</t>
         </is>
       </c>
     </row>
     <row r="18" ht="17.15" customHeight="1" s="79">
       <c r="A18" s="140" t="n">
+        <v>10</v>
+      </c>
+      <c r="B18" s="140" t="inlineStr">
+        <is>
+          <t>芯片020628</t>
+        </is>
+      </c>
+      <c r="C18" s="140" t="inlineStr">
+        <is>
+          <t>芯片020628</t>
+        </is>
+      </c>
+      <c r="D18" s="140" t="inlineStr">
+        <is>
+          <t>持仓</t>
+        </is>
+      </c>
+      <c r="E18" s="140" t="inlineStr">
+        <is>
+          <t>44%</t>
+        </is>
+      </c>
+      <c r="F18" s="140" t="inlineStr">
+        <is>
+          <t>38%</t>
+        </is>
+      </c>
+      <c r="G18" s="140" t="inlineStr">
+        <is>
+          <t>1.2:1</t>
+        </is>
+      </c>
+      <c r="H18" s="140" t="inlineStr">
+        <is>
+          <t>0.528</t>
+        </is>
+      </c>
+      <c r="I18" s="140" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="J18" s="140" t="inlineStr">
+        <is>
+          <t>0.5280</t>
+        </is>
+      </c>
+      <c r="K18" s="141" t="inlineStr">
+        <is>
+          <t>未通过</t>
+        </is>
+      </c>
+      <c r="L18" s="140" t="inlineStr">
+        <is>
+          <t>观望</t>
+        </is>
+      </c>
+      <c r="M18" s="140" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N18" s="140" t="inlineStr">
+        <is>
+          <t>已持仓观望，利率折价6pp</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="140" t="n">
+        <v>11</v>
+      </c>
+      <c r="B19" s="140" t="inlineStr">
+        <is>
+          <t>恒科012349</t>
+        </is>
+      </c>
+      <c r="C19" s="140" t="inlineStr">
+        <is>
+          <t>恒科012349</t>
+        </is>
+      </c>
+      <c r="D19" s="140" t="inlineStr">
+        <is>
+          <t>持仓</t>
+        </is>
+      </c>
+      <c r="E19" s="140" t="inlineStr">
+        <is>
+          <t>29%</t>
+        </is>
+      </c>
+      <c r="F19" s="140" t="inlineStr">
+        <is>
+          <t>23%</t>
+        </is>
+      </c>
+      <c r="G19" s="140" t="inlineStr">
+        <is>
+          <t>0.4:1</t>
+        </is>
+      </c>
+      <c r="H19" s="140" t="inlineStr">
+        <is>
+          <t>0.116</t>
+        </is>
+      </c>
+      <c r="I19" s="140" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="J19" s="140" t="inlineStr">
+        <is>
+          <t>0.1160</t>
+        </is>
+      </c>
+      <c r="K19" s="141" t="inlineStr">
+        <is>
+          <t>未通过</t>
+        </is>
+      </c>
+      <c r="L19" s="140" t="inlineStr">
+        <is>
+          <t>不干</t>
+        </is>
+      </c>
+      <c r="M19" s="140" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N19" s="140" t="inlineStr">
+        <is>
+          <t>已持仓不干，利率折价5pp</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="15" customHeight="1" s="79">
+      <c r="A20" s="142" t="n">
+        <v>12</v>
+      </c>
+      <c r="B20" s="142" t="inlineStr">
+        <is>
+          <t>现金</t>
+        </is>
+      </c>
+      <c r="C20" s="142" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D20" s="142" t="inlineStr">
+        <is>
+          <t>现金</t>
+        </is>
+      </c>
+      <c r="E20" s="142" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F20" s="142" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G20" s="142" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H20" s="142" t="inlineStr">
+        <is>
+          <t>0.000</t>
+        </is>
+      </c>
+      <c r="I20" s="142" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="J20" s="142" t="inlineStr">
+        <is>
+          <t>0.0000</t>
+        </is>
+      </c>
+      <c r="K20" s="142" t="inlineStr">
+        <is>
+          <t>基准</t>
+        </is>
+      </c>
+      <c r="L20" s="142" t="inlineStr">
+        <is>
+          <t>Score=0基准线</t>
+        </is>
+      </c>
+      <c r="M20" s="142" t="inlineStr">
+        <is>
+          <t>Score=0，所有选项都要跟现金比</t>
+        </is>
+      </c>
+      <c r="N20" s="142" t="inlineStr">
+        <is>
+          <t>无风险，但通胀侵蚀购买力</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="17.15" customHeight="1" s="79">
+      <c r="A21" s="140" t="n">
         <v>13</v>
       </c>
-      <c r="B18" s="140" t="inlineStr">
+      <c r="B21" s="140" t="inlineStr">
         <is>
           <t>AI027048</t>
         </is>
       </c>
-      <c r="C18" s="140" t="inlineStr">
+      <c r="C21" s="140" t="inlineStr">
         <is>
           <t>AI027048</t>
         </is>
       </c>
-      <c r="D18" s="140" t="inlineStr">
+      <c r="D21" s="140" t="inlineStr">
         <is>
           <t>持仓</t>
         </is>
       </c>
-      <c r="E18" s="140" t="inlineStr">
+      <c r="E21" s="140" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="F18" s="140" t="inlineStr">
+      <c r="F21" s="140" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="G18" s="140" t="inlineStr">
+      <c r="G21" s="140" t="inlineStr">
         <is>
           <t>0.7:1</t>
         </is>
       </c>
-      <c r="H18" s="140" t="inlineStr">
+      <c r="H21" s="140" t="inlineStr">
         <is>
           <t>0.000</t>
         </is>
       </c>
-      <c r="I18" s="140" t="inlineStr">
+      <c r="I21" s="140" t="inlineStr">
         <is>
           <t>100.0%</t>
         </is>
       </c>
-      <c r="J18" s="140" t="inlineStr">
+      <c r="J21" s="140" t="inlineStr">
         <is>
           <t>-1.0000</t>
         </is>
       </c>
-      <c r="K18" s="141" t="inlineStr">
+      <c r="K21" s="141" t="inlineStr">
         <is>
           <t>未通过</t>
         </is>
       </c>
-      <c r="L18" s="140" t="inlineStr">
+      <c r="L21" s="140" t="inlineStr">
         <is>
           <t>不干</t>
         </is>
       </c>
-      <c r="M18" s="140" t="inlineStr">
+      <c r="M21" s="140" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="N18" s="140" t="inlineStr">
+      <c r="N21" s="140" t="inlineStr">
         <is>
           <t>已持仓不干，利率折价0pp</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="15" customHeight="1" s="79">
-      <c r="A20" s="143" t="inlineStr">
+    <row r="22" ht="17.15" customHeight="1" s="79"/>
+    <row r="23" ht="17.15" customHeight="1" s="79">
+      <c r="A23" s="143" t="inlineStr">
         <is>
           <t>结论：现金该往哪分配</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="17.15" customHeight="1" s="79">
-      <c r="A21" s="117" t="inlineStr">
-        <is>
-          <t>1. 长电科技(600584) - P=75% R=4.5:1 Score=3.3750 目标仓位占比=37%的可投资金</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="17.15" customHeight="1" s="79">
-      <c r="A22" s="117" t="inlineStr">
-        <is>
-          <t>2. 通富微电(002156) - P=75% R=4.0:1 Score=3.0000 目标仓位占比=33%的可投资金</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="17.15" customHeight="1" s="79">
-      <c r="A23" s="117" t="inlineStr">
-        <is>
-          <t>3. 养殖014415(养殖014415) - P=70% R=2.0:1 Score=1.4000 目标仓位占比=15%的可投资金</t>
         </is>
       </c>
     </row>
     <row r="24" ht="17.15" customHeight="1" s="79">
       <c r="A24" s="117" t="inlineStr">
         <is>
-          <t>4. 电池018926(电池018926) - P=65% R=2.0:1 Score=1.3000 目标仓位占比=14%的可投资金</t>
+          <t>1. 长电科技(600584) - P=75% R=4.5:1 Score=3.3750 目标仓位占比=37%的可投资金</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="117" t="inlineStr">
+        <is>
+          <t>2. 通富微电(002156) - P=75% R=4.0:1 Score=3.0000 目标仓位占比=33%的可投资金</t>
         </is>
       </c>
     </row>
     <row r="26" ht="15" customHeight="1" s="79">
       <c r="A26" s="117" t="inlineStr">
         <is>
+          <t>3. 养殖014415(养殖014415) - P=70% R=2.0:1 Score=1.4000 目标仓位占比=15%的可投资金</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="17.15" customHeight="1" s="79">
+      <c r="A27" s="117" t="inlineStr">
+        <is>
+          <t>4. 电池018926(电池018926) - P=65% R=2.0:1 Score=1.3000 目标仓位占比=14%的可投资金</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="17.15" customHeight="1" s="79"/>
+    <row r="29">
+      <c r="A29" s="117" t="inlineStr">
+        <is>
           <t>未通过但接近的选项：</t>
         </is>
       </c>
     </row>
-    <row r="27" ht="17.15" customHeight="1" s="79">
-      <c r="A27" s="78" t="inlineStr">
+    <row r="30" ht="17.15" customHeight="1" s="79">
+      <c r="A30" s="78" t="inlineStr">
         <is>
           <t>- 核电(-) - P=52% R=1.5:1 - P差8pp到门槛, R差0.5到门槛</t>
         </is>
       </c>
     </row>
-    <row r="28" ht="17.15" customHeight="1" s="79">
-      <c r="A28" s="78" t="inlineStr">
+    <row r="31">
+      <c r="A31" s="78" t="inlineStr">
         <is>
           <t>- 存储赛道(-) - P=55% R=1.0:1 - P差5pp到门槛, R差1.0到门槛</t>
         </is>
       </c>
     </row>
-    <row r="30" ht="17.15" customHeight="1" s="79">
-      <c r="A30" s="117" t="inlineStr">
+    <row r="32" ht="15" customHeight="1" s="79"/>
+    <row r="33" ht="15" customHeight="1" s="79">
+      <c r="A33" s="117" t="inlineStr">
         <is>
           <t>现金：按Score排序，优先分配给最高Score选项</t>
         </is>
       </c>
     </row>
-    <row r="32" ht="15" customHeight="1" s="79">
-      <c r="A32" s="117" t="inlineStr">
+    <row r="34" ht="15" customHeight="1" s="79"/>
+    <row r="35" ht="15" customHeight="1" s="79">
+      <c r="A35" s="117" t="inlineStr">
         <is>
           <t>方法说明</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="15" customHeight="1" s="79">
-      <c r="A33" s="144" t="inlineStr">
-        <is>
-          <t>1. 吸引力Score = P*R - alpha*w*(1-P) | P=胜率 R=盈亏比 w=当前仓位占比 alpha=1.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="15" customHeight="1" s="79">
-      <c r="A34" s="144" t="inlineStr">
-        <is>
-          <t>2. 大白话：吸引力 = 机会多好(P*R) 减去 风险多重(仓位乘不确定性)</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="15" customHeight="1" s="79">
-      <c r="A35" s="144" t="inlineStr">
-        <is>
-          <t>3. 双门槛：P&gt;=60% + 盈亏比&gt;=2:1 通过 按Score排序分配现金</t>
         </is>
       </c>
     </row>
     <row r="36" ht="15" customHeight="1" s="79">
       <c r="A36" s="144" t="inlineStr">
         <is>
-          <t>4. 目标仓位分配：按P*R比例分配可投资金（通过门槛的选项）</t>
+          <t>1. 吸引力Score = P*R - alpha*w*(1-P) | P=胜率 R=盈亏比 w=当前仓位占比 alpha=1.0</t>
         </is>
       </c>
     </row>
     <row r="37" ht="15" customHeight="1" s="79">
       <c r="A37" s="144" t="inlineStr">
         <is>
-          <t>5. 饱和度检查：当前仓位/目标仓位 小于50%加仓，大于100%减仓</t>
+          <t>2. 大白话：吸引力 = 机会多好(P*R) 减去 风险多重(仓位乘不确定性)</t>
         </is>
       </c>
     </row>
     <row r="38" ht="15" customHeight="1" s="79">
       <c r="A38" s="144" t="inlineStr">
         <is>
-          <t>6. 有效P = P + 利率折价（成长股-6pp/周期股-4pp/防御股0pp）</t>
+          <t>3. 双门槛：P&gt;=60% + 盈亏比&gt;=2:1 通过 按Score排序分配现金</t>
         </is>
       </c>
     </row>
     <row r="39" ht="15" customHeight="1" s="79">
       <c r="A39" s="144" t="inlineStr">
         <is>
-          <t>7. 审核频率：每周日一次 + P值跨越60%阈值时 + 新机会加入时</t>
+          <t>4. 目标仓位分配：按P*R比例分配可投资金（通过门槛的选项）</t>
         </is>
       </c>
     </row>
     <row r="40" ht="15" customHeight="1" s="79">
       <c r="A40" s="144" t="inlineStr">
         <is>
-          <t>8. 本次审核：2026-06-04 | 下次预计：2026-06-11</t>
+          <t>5. 饱和度检查：当前仓位/目标仓位 小于50%加仓，大于100%减仓</t>
         </is>
       </c>
     </row>
     <row r="41" ht="15" customHeight="1" s="79">
       <c r="A41" s="144" t="inlineStr">
         <is>
-          <t>9. 数据来源：Sheet2持仓数据 + 待重仓监控.md + 6/4盘中价格</t>
+          <t>6. 有效P = P + 利率折价（成长股-6pp/周期股-4pp/防御股0pp）</t>
         </is>
       </c>
     </row>
     <row r="42" ht="15" customHeight="1" s="79">
       <c r="A42" s="144" t="inlineStr">
         <is>
+          <t>7. 审核频率：每周日一次 + P值跨越60%阈值时 + 新机会加入时</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="144" t="inlineStr">
+        <is>
+          <t>8. 本次审核：2026-06-04 | 下次预计：2026-06-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="144" t="inlineStr">
+        <is>
+          <t>9. 数据来源：Sheet2持仓数据 + 待重仓监控.md + 6/4盘中价格</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="144" t="inlineStr">
+        <is>
           <t>10. 小龙虾技术分析：长电科技(先进封装广度最强) + 通富微电(AMD封测不可替代)</t>
         </is>
       </c>
     </row>
+    <row r="47">
+      <c r="A47" s="200" t="inlineStr">
+        <is>
+          <t>📖 现金锁定机制说明（机制v2）</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="147" t="inlineStr">
+        <is>
+          <t>公式：折后仓位% = 原目标仓位% × (1 - 现金锁定系数)</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="201" t="inlineStr">
+        <is>
+          <t>现金锁定系数 = 达利欧泡沫概率(70%) × 三源互锁强度(1.0=强印证) × 时间衰减(剩余月数/12)</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="201" t="inlineStr">
+        <is>
+          <t>当前计算：0.70 × 1.0 × (5/12≈0.42) ≈ 0.65 → 65%现金锁定</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="201" t="inlineStr">
+        <is>
+          <t>解锁条件：三源信号任一落地（达利欧：七姐妹&gt;15%回调；李大霄：多数成分股下跌；中期选举：11月美股跌）</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="201" t="inlineStr">
+        <is>
+          <t>已持仓不受影响（养殖/电池/有色等），仅影响待重仓的新现金分配</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="202" t="inlineStr">
+        <is>
+          <t>每月重算：时间衰减系数随11月临近而增大→现金锁定系数下降→折后仓位上升</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="201" t="inlineStr">
+        <is>
+          <t>更新日志：2026-06-04 首次加入现金锁定机制 v2 | 下次审核：2026-06-11</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="23">
-    <mergeCell ref="A40:N40"/>
-    <mergeCell ref="A39:N39"/>
-    <mergeCell ref="A34:N34"/>
-    <mergeCell ref="A24:N24"/>
-    <mergeCell ref="A30:N30"/>
-    <mergeCell ref="A36:N36"/>
-    <mergeCell ref="A1:N1"/>
-    <mergeCell ref="A41:N41"/>
-    <mergeCell ref="A37:N37"/>
-    <mergeCell ref="A27:N27"/>
-    <mergeCell ref="A3:N3"/>
-    <mergeCell ref="A26:N26"/>
-    <mergeCell ref="A21:N21"/>
-    <mergeCell ref="A2:N2"/>
-    <mergeCell ref="A33:N33"/>
-    <mergeCell ref="A42:N42"/>
-    <mergeCell ref="A23:N23"/>
-    <mergeCell ref="A32:N32"/>
-    <mergeCell ref="A22:N22"/>
-    <mergeCell ref="A35:N35"/>
-    <mergeCell ref="A20:N20"/>
-    <mergeCell ref="A38:N38"/>
-    <mergeCell ref="A28:N28"/>
-  </mergeCells>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>

--- a/持仓贝叶斯跟踪.xlsx
+++ b/持仓贝叶斯跟踪.xlsx
@@ -21,7 +21,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="56">
+  <fonts count="57">
     <font>
       <name val="Calibri"/>
       <charset val="1"/>
@@ -380,6 +380,11 @@
       <color rgb="00FF0000"/>
       <sz val="9"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="10"/>
+    </font>
   </fonts>
   <fills count="32">
     <fill>
@@ -629,7 +634,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="203">
+  <cellXfs count="206">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -1191,6 +1196,11 @@
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="40" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="55" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="56" fillId="29" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="42" fillId="21" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="28" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1980,7 +1990,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:H94"/>
+  <dimension ref="A1:H140"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6171875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="18" customWidth="1" style="78" min="1" max="1"/>
@@ -3883,24 +3893,724 @@
     <row r="94">
       <c r="A94" s="78" t="n"/>
     </row>
+    <row r="96">
+      <c r="A96" s="158" t="inlineStr">
+        <is>
+          <t>📖 机制库 v3（2026-06-04 经小龙虾审核修订）</t>
+        </is>
+      </c>
+      <c r="B96" s="159" t="n"/>
+      <c r="C96" s="159" t="n"/>
+      <c r="D96" s="159" t="n"/>
+      <c r="E96" s="159" t="n"/>
+      <c r="F96" s="159" t="n"/>
+      <c r="G96" s="159" t="n"/>
+      <c r="H96" s="159" t="n"/>
+    </row>
+    <row r="97">
+      <c r="A97" s="203" t="inlineStr">
+        <is>
+          <t>[机制3v3] 现金锁定系数（CLC）— 平方衰减版</t>
+        </is>
+      </c>
+      <c r="B97" s="179" t="n"/>
+      <c r="C97" s="179" t="n"/>
+      <c r="D97" s="179" t="n"/>
+      <c r="E97" s="179" t="n"/>
+      <c r="F97" s="179" t="n"/>
+      <c r="G97" s="179" t="n"/>
+      <c r="H97" s="179" t="n"/>
+    </row>
+    <row r="98">
+      <c r="A98" s="204" t="inlineStr">
+        <is>
+          <t>叫什么</t>
+        </is>
+      </c>
+      <c r="B98" s="87" t="inlineStr">
+        <is>
+          <t>现金锁定系数（CLC）v3</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="204" t="inlineStr">
+        <is>
+          <t>公式</t>
+        </is>
+      </c>
+      <c r="B99" s="87" t="inlineStr">
+        <is>
+          <t>CLC = 信号概率 × 互锁强度 × 时间衰减²</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="204" t="inlineStr">
+        <is>
+          <t>时间衰减</t>
+        </is>
+      </c>
+      <c r="B100" s="87" t="inlineStr">
+        <is>
+          <t>T = (距触发月数/12)²</t>
+        </is>
+      </c>
+      <c r="C100" s="87" t="inlineStr">
+        <is>
+          <t>6月=(5/12)²=0.174</t>
+        </is>
+      </c>
+      <c r="D100" s="87" t="inlineStr">
+        <is>
+          <t>11月=0</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="204" t="inlineStr">
+        <is>
+          <t>为什么平方</t>
+        </is>
+      </c>
+      <c r="B101" s="87" t="inlineStr">
+        <is>
+          <t>线性衰减导致越近触发日锁得越少（反直觉）</t>
+        </is>
+      </c>
+      <c r="C101" s="87" t="inlineStr">
+        <is>
+          <t>平方函数：远离时多锁，临近时少锁</t>
+        </is>
+      </c>
+      <c r="D101" s="87" t="inlineStr">
+        <is>
+          <t>小龙虾审核通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="204" t="inlineStr">
+        <is>
+          <t>信号概率</t>
+        </is>
+      </c>
+      <c r="B102" s="87" t="inlineStr">
+        <is>
+          <t>动态更新，每月审查</t>
+        </is>
+      </c>
+      <c r="C102" s="87" t="inlineStr">
+        <is>
+          <t>底线55%（达利欧区间下沿）</t>
+        </is>
+      </c>
+      <c r="D102" s="87" t="inlineStr">
+        <is>
+          <t>上限85%（达利欧区间上沿）</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="204" t="inlineStr">
+        <is>
+          <t>互锁强度</t>
+        </is>
+      </c>
+      <c r="B103" s="87" t="inlineStr">
+        <is>
+          <t>三源强互锁=1.0</t>
+        </is>
+      </c>
+      <c r="C103" s="87" t="inlineStr">
+        <is>
+          <t>达利欧6月修正&gt;2次→降级0.85</t>
+        </is>
+      </c>
+      <c r="D103" s="87" t="inlineStr">
+        <is>
+          <t>有原因修正不降级</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="204" t="inlineStr">
+        <is>
+          <t>当前值</t>
+        </is>
+      </c>
+      <c r="B104" s="87" t="inlineStr">
+        <is>
+          <t>0.70 × 1.0 × (5/12)² = 0.122</t>
+        </is>
+      </c>
+      <c r="C104" s="87" t="inlineStr">
+        <is>
+          <t>→ 锁定12.2%现金</t>
+        </is>
+      </c>
+      <c r="D104" s="87" t="inlineStr">
+        <is>
+          <t>可用87.8%</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="204" t="inlineStr">
+        <is>
+          <t>每月重算</t>
+        </is>
+      </c>
+      <c r="B105" s="87" t="inlineStr">
+        <is>
+          <t>信号概率按计分板更新</t>
+        </is>
+      </c>
+      <c r="C105" s="87" t="inlineStr">
+        <is>
+          <t>时间衰减自动重算</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="203" t="inlineStr">
+        <is>
+          <t>[机制4v3] 折后仓位计算 — 4级分级版</t>
+        </is>
+      </c>
+      <c r="B107" s="179" t="n"/>
+      <c r="C107" s="179" t="n"/>
+      <c r="D107" s="179" t="n"/>
+      <c r="E107" s="179" t="n"/>
+      <c r="F107" s="179" t="n"/>
+      <c r="G107" s="179" t="n"/>
+      <c r="H107" s="179" t="n"/>
+    </row>
+    <row r="108">
+      <c r="A108" s="204" t="inlineStr">
+        <is>
+          <t>叫什么</t>
+        </is>
+      </c>
+      <c r="B108" s="87" t="inlineStr">
+        <is>
+          <t>折后仓位（Folded Allocation）v3</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="204" t="inlineStr">
+        <is>
+          <t>公式</t>
+        </is>
+      </c>
+      <c r="B109" s="87" t="inlineStr">
+        <is>
+          <t>折后仓位% = 原目标仓位% × (1 - CLC × β系数)</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="204" t="inlineStr">
+        <is>
+          <t>4级分级</t>
+        </is>
+      </c>
+      <c r="B110" s="87" t="inlineStr">
+        <is>
+          <t>L1高度暴露β=0.8（通富-AMD独供）</t>
+        </is>
+      </c>
+      <c r="C110" s="87" t="inlineStr">
+        <is>
+          <t>L2中度暴露β=0.5（长电-客户多元）</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="204" t="inlineStr">
+        <is>
+          <t>分级继续</t>
+        </is>
+      </c>
+      <c r="B111" s="87" t="inlineStr">
+        <is>
+          <t>L3弱相关β=0.1（养殖）</t>
+        </is>
+      </c>
+      <c r="C111" s="87" t="inlineStr">
+        <is>
+          <t>L4反向受益β=-0.3（黄金）</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="204" t="inlineStr">
+        <is>
+          <t>为什么分级</t>
+        </is>
+      </c>
+      <c r="B112" s="87" t="inlineStr">
+        <is>
+          <t>不同标的受AI泡沫影响不同</t>
+        </is>
+      </c>
+      <c r="C112" s="87" t="inlineStr">
+        <is>
+          <t>通富只有AMD一根柱子</t>
+        </is>
+      </c>
+      <c r="D112" s="87" t="inlineStr">
+        <is>
+          <t>长电客户多元化</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="204" t="inlineStr">
+        <is>
+          <t>当前计算</t>
+        </is>
+      </c>
+      <c r="B113" s="87" t="inlineStr">
+        <is>
+          <t>通富:33%×(1-0.122×0.8)=30.1%</t>
+        </is>
+      </c>
+      <c r="C113" s="87" t="inlineStr">
+        <is>
+          <t>长电:37%×(1-0.122×0.5)=34.7%</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="204" t="inlineStr">
+        <is>
+          <t>分级逻辑</t>
+        </is>
+      </c>
+      <c r="B114" s="87" t="inlineStr">
+        <is>
+          <t>按切断条件分两级：扛得住vs扛不住</t>
+        </is>
+      </c>
+      <c r="C114" s="87" t="inlineStr">
+        <is>
+          <t>不是连续β，是二值判断</t>
+        </is>
+      </c>
+      <c r="D114" s="87" t="inlineStr">
+        <is>
+          <t>小龙虾建议</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="203" t="inlineStr">
+        <is>
+          <t>[机制5v3] 虚P→实P转换 — 确认窗口+因果链版</t>
+        </is>
+      </c>
+      <c r="B116" s="179" t="n"/>
+      <c r="C116" s="179" t="n"/>
+      <c r="D116" s="179" t="n"/>
+      <c r="E116" s="179" t="n"/>
+      <c r="F116" s="179" t="n"/>
+      <c r="G116" s="179" t="n"/>
+      <c r="H116" s="179" t="n"/>
+    </row>
+    <row r="117">
+      <c r="A117" s="204" t="inlineStr">
+        <is>
+          <t>叫什么</t>
+        </is>
+      </c>
+      <c r="B117" s="87" t="inlineStr">
+        <is>
+          <t>虚P→实P转换 v3</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="204" t="inlineStr">
+        <is>
+          <t>视觉信号</t>
+        </is>
+      </c>
+      <c r="B118" s="87" t="inlineStr">
+        <is>
+          <t>纳指七姐妹&gt;15%回调（从52周高）</t>
+        </is>
+      </c>
+      <c r="C118" s="87" t="inlineStr">
+        <is>
+          <t>或破200日均线</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="204" t="inlineStr">
+        <is>
+          <t>确认窗口</t>
+        </is>
+      </c>
+      <c r="B119" s="87" t="inlineStr">
+        <is>
+          <t>跌穿15%后维持5个交易日不反弹</t>
+        </is>
+      </c>
+      <c r="C119" s="87" t="inlineStr">
+        <is>
+          <t>防单日噪音和假触发</t>
+        </is>
+      </c>
+      <c r="D119" s="87" t="inlineStr">
+        <is>
+          <t>小龙虾建议</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="204" t="inlineStr">
+        <is>
+          <t>因果链</t>
+        </is>
+      </c>
+      <c r="B120" s="87" t="inlineStr">
+        <is>
+          <t>需至少2条佐证：</t>
+        </is>
+      </c>
+      <c r="C120" s="87" t="inlineStr">
+        <is>
+          <t>①英伟达/AMD下调指引</t>
+        </is>
+      </c>
+      <c r="D120" s="87" t="inlineStr">
+        <is>
+          <t>②AI ETF资金流出</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="204" t="inlineStr">
+        <is>
+          <t>因果链继续</t>
+        </is>
+      </c>
+      <c r="B121" s="87" t="inlineStr">
+        <is>
+          <t>③投行下调AI评级</t>
+        </is>
+      </c>
+      <c r="C121" s="87" t="inlineStr">
+        <is>
+          <t>④Mag7裁员/削减开支</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="204" t="inlineStr">
+        <is>
+          <t>为什么加因果</t>
+        </is>
+      </c>
+      <c r="B122" s="87" t="inlineStr">
+        <is>
+          <t>15%下跌可能是地缘冲击不是AI泡沫</t>
+        </is>
+      </c>
+      <c r="C122" s="87" t="inlineStr">
+        <is>
+          <t>两者操作完全不同</t>
+        </is>
+      </c>
+      <c r="D122" s="87" t="inlineStr">
+        <is>
+          <t>必须区分原因</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="204" t="inlineStr">
+        <is>
+          <t>转换后</t>
+        </is>
+      </c>
+      <c r="B123" s="87" t="inlineStr">
+        <is>
+          <t>虚P转实P→计入P值</t>
+        </is>
+      </c>
+      <c r="C123" s="87" t="inlineStr">
+        <is>
+          <t>CLC→0现金全解锁</t>
+        </is>
+      </c>
+      <c r="D123" s="87" t="inlineStr">
+        <is>
+          <t>折后仓位→恢复原目标</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="205" t="inlineStr">
+        <is>
+          <t>[信号计分板] 每日更新，驱动信号概率动态调整</t>
+        </is>
+      </c>
+      <c r="B125" s="175" t="n"/>
+      <c r="C125" s="175" t="n"/>
+      <c r="D125" s="175" t="n"/>
+      <c r="E125" s="175" t="n"/>
+      <c r="F125" s="175" t="n"/>
+      <c r="G125" s="175" t="n"/>
+      <c r="H125" s="175" t="n"/>
+    </row>
+    <row r="126">
+      <c r="A126" s="204" t="inlineStr">
+        <is>
+          <t>泡沫正向信号</t>
+        </is>
+      </c>
+      <c r="B126" s="87" t="inlineStr">
+        <is>
+          <t>Mag7单日跌&gt;3% → +1</t>
+        </is>
+      </c>
+      <c r="C126" s="87" t="inlineStr">
+        <is>
+          <t>Mag7月跌&gt;10% → +2</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="B127" s="87" t="inlineStr">
+        <is>
+          <t>VIX&gt;30 → +2</t>
+        </is>
+      </c>
+      <c r="C127" s="87" t="inlineStr">
+        <is>
+          <t>AI公司裁员/下调指引 → +1</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="B128" s="87" t="inlineStr">
+        <is>
+          <t>信用利差&gt;150bp → +2</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="204" t="inlineStr">
+        <is>
+          <t>泡沫反向信号</t>
+        </is>
+      </c>
+      <c r="B129" s="87" t="inlineStr">
+        <is>
+          <t>Mag7单日涨&gt;3% → -1</t>
+        </is>
+      </c>
+      <c r="C129" s="87" t="inlineStr">
+        <is>
+          <t>Mag7月涨&gt;8% → -2</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="B130" s="87" t="inlineStr">
+        <is>
+          <t>Fed降息 → -2</t>
+        </is>
+      </c>
+      <c r="C130" s="87" t="inlineStr">
+        <is>
+          <t>AI龙头超预期财报 → -1</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="B131" s="87" t="inlineStr">
+        <is>
+          <t>VIX&lt;15 → -1</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="204" t="inlineStr">
+        <is>
+          <t>更新规则</t>
+        </is>
+      </c>
+      <c r="B132" s="87" t="inlineStr">
+        <is>
+          <t>每月第一天：信号概率=70%+上月净计分×5pp</t>
+        </is>
+      </c>
+      <c r="C132" s="87" t="inlineStr">
+        <is>
+          <t>底线55%上限85%</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="204" t="inlineStr">
+        <is>
+          <t>Mag7权重</t>
+        </is>
+      </c>
+      <c r="B133" s="87" t="inlineStr">
+        <is>
+          <t>NVDA40% META15% GOOGL15% MSFT15%</t>
+        </is>
+      </c>
+      <c r="C133" s="87" t="inlineStr">
+        <is>
+          <t>AMZN5% AAPL5% TSLA5%</t>
+        </is>
+      </c>
+      <c r="D133" s="87" t="inlineStr">
+        <is>
+          <t>固定不按月动</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="205" t="inlineStr">
+        <is>
+          <t>⚡ 机制v3使用指南</t>
+        </is>
+      </c>
+      <c r="B135" s="175" t="n"/>
+      <c r="C135" s="175" t="n"/>
+      <c r="D135" s="175" t="n"/>
+      <c r="E135" s="175" t="n"/>
+      <c r="F135" s="175" t="n"/>
+      <c r="G135" s="175" t="n"/>
+      <c r="H135" s="175" t="n"/>
+    </row>
+    <row r="136">
+      <c r="A136" s="204" t="inlineStr">
+        <is>
+          <t>日常看盘</t>
+        </is>
+      </c>
+      <c r="B136" s="87" t="inlineStr">
+        <is>
+          <t>看机会成本排序Sheet折后仓位</t>
+        </is>
+      </c>
+      <c r="C136" s="87" t="inlineStr">
+        <is>
+          <t>看现金锁定状态</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="204" t="inlineStr">
+        <is>
+          <t>每日更新</t>
+        </is>
+      </c>
+      <c r="B137" s="87" t="inlineStr">
+        <is>
+          <t>信号计分板逐股计分</t>
+        </is>
+      </c>
+      <c r="C137" s="87" t="inlineStr">
+        <is>
+          <t>净计分累计</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="204" t="inlineStr">
+        <is>
+          <t>每月重算</t>
+        </is>
+      </c>
+      <c r="B138" s="87" t="inlineStr">
+        <is>
+          <t>①信号概率=70%+净计分×5pp</t>
+        </is>
+      </c>
+      <c r="C138" s="87" t="inlineStr">
+        <is>
+          <t>②CLC=信号概率×互锁×时间衰减²</t>
+        </is>
+      </c>
+      <c r="D138" s="87" t="inlineStr">
+        <is>
+          <t>③折后仓位=原仓位×(1-CLC×β)</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="204" t="inlineStr">
+        <is>
+          <t>信号落地</t>
+        </is>
+      </c>
+      <c r="B139" s="87" t="inlineStr">
+        <is>
+          <t>视觉信号+5日确认+因果链2条</t>
+        </is>
+      </c>
+      <c r="C139" s="87" t="inlineStr">
+        <is>
+          <t>→虚P转实P</t>
+        </is>
+      </c>
+      <c r="D139" s="87" t="inlineStr">
+        <is>
+          <t>→CLC=0现金解锁</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="204" t="inlineStr">
+        <is>
+          <t>核验计算</t>
+        </is>
+      </c>
+      <c r="B140" s="87" t="inlineStr">
+        <is>
+          <t>python3 /tmp/mechanism_checker_v3.py</t>
+        </is>
+      </c>
+      <c r="C140" s="87" t="inlineStr">
+        <is>
+          <t>自动重算所有机制</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="16">
-    <mergeCell ref="A12:H12"/>
+  <mergeCells count="22">
     <mergeCell ref="A16:F16"/>
-    <mergeCell ref="B14:H14"/>
-    <mergeCell ref="A18:H18"/>
-    <mergeCell ref="B13:H13"/>
-    <mergeCell ref="A25:H25"/>
-    <mergeCell ref="A2:H2"/>
     <mergeCell ref="A51:H51"/>
-    <mergeCell ref="A41:H41"/>
-    <mergeCell ref="A19:H19"/>
+    <mergeCell ref="A107:H107"/>
     <mergeCell ref="B15:H15"/>
     <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A25:H25"/>
+    <mergeCell ref="A41:H41"/>
+    <mergeCell ref="A12:H12"/>
+    <mergeCell ref="A18:H18"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A116:H116"/>
     <mergeCell ref="A32:H32"/>
+    <mergeCell ref="A97:H97"/>
+    <mergeCell ref="A17:H17"/>
+    <mergeCell ref="A135:H135"/>
+    <mergeCell ref="B14:H14"/>
+    <mergeCell ref="B13:H13"/>
+    <mergeCell ref="A96:H96"/>
+    <mergeCell ref="A125:H125"/>
+    <mergeCell ref="A19:H19"/>
     <mergeCell ref="A31:H31"/>
     <mergeCell ref="A58:H58"/>
-    <mergeCell ref="A17:H17"/>
   </mergeCells>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>

--- a/持仓贝叶斯跟踪.xlsx
+++ b/持仓贝叶斯跟踪.xlsx
@@ -21,7 +21,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="57">
+  <fonts count="59">
     <font>
       <name val="Calibri"/>
       <charset val="1"/>
@@ -385,8 +385,15 @@
       <color rgb="00FFFFFF"/>
       <sz val="10"/>
     </font>
+    <font>
+      <b val="1"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+    </font>
   </fonts>
-  <fills count="32">
+  <fills count="33">
     <fill>
       <patternFill/>
     </fill>
@@ -573,6 +580,11 @@
         <bgColor rgb="00F2F2F2"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="004472C4"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="7">
     <border>
@@ -634,7 +646,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="206">
+  <cellXfs count="208">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -1201,6 +1213,8 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="56" fillId="28" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="44" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="58" fillId="32" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1277,6 +1291,7 @@
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>Hermes</author>
+    <author>叙事主线</author>
   </authors>
   <commentList>
     <comment ref="A4" authorId="0" shapeId="0">
@@ -1557,6 +1572,27 @@
 【操作建议】
 - 养殖：去杠杆是加速器，等右侧信号（猪价企稳+产能出清确认）
 - 银行：不加仓，去杠杆周期中银行最难受
+</t>
+      </text>
+    </comment>
+    <comment ref="B16" authorId="1" shapeId="0">
+      <text>
+        <t xml:space="preserve">来源：用户2026-06-04独立判断
+逻辑链：
+1. 历史验证：每次危机→比特币暴跌（无避险价值）
+2. 黄金涨→比特币跌（流动性被黄金吸附）
+3. 美股涨→黄金跌→比特币也跌（被美股吸走）
+4. AI来了→资金有明确去处（芯片/AI基建）→比特币更没吸引力
+5. 最近一轮牛市验证：涨跌幅变小+跟美股完全同步=已非独立资产
+当前状态：维持。2020后第1次牛市(2021)，第2次牛市(2025最近)，周期规律+AI挤压=比特币上行空间越来越小
+对持仓影响：
+- 芯片/AI 利好：资金不去比特币就去AI，确认资金流向
+- 黄金 间接利好：比特币不再跟黄金抢流动性
+- 银行/有色/稀金 中性：不影响国内逻辑
+操作建议：
+- 不碰比特币/虚拟货币
+- 确认AI赛道的资金虹吸地位
+- 如果比特币暴跌→不是避险信号，是资金被更强的资产吸走了
 </t>
       </text>
     </comment>
@@ -1990,7 +2026,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:H140"/>
+  <dimension ref="A1:H151"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6171875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="18" customWidth="1" style="78" min="1" max="1"/>
@@ -2270,7 +2306,16 @@
       <c r="H15" s="146" t="n"/>
     </row>
     <row r="16" ht="16.5" customHeight="1" s="79">
-      <c r="A16" s="78" t="n"/>
+      <c r="A16" s="78" t="inlineStr">
+        <is>
+          <t>④</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>比特币独立叙事消亡 维持：资金吸附力排序 AI&gt;美股&gt;黄金&gt;比特币，比特币已成美股影子资产，AI落地后资金有明确去处，比特币价值持续被稀释</t>
+        </is>
+      </c>
     </row>
     <row r="17" ht="16.5" customHeight="1" s="79">
       <c r="A17" s="158" t="inlineStr">
@@ -3899,13 +3944,6 @@
           <t>📖 机制库 v3（2026-06-04 经小龙虾审核修订）</t>
         </is>
       </c>
-      <c r="B96" s="159" t="n"/>
-      <c r="C96" s="159" t="n"/>
-      <c r="D96" s="159" t="n"/>
-      <c r="E96" s="159" t="n"/>
-      <c r="F96" s="159" t="n"/>
-      <c r="G96" s="159" t="n"/>
-      <c r="H96" s="159" t="n"/>
     </row>
     <row r="97">
       <c r="A97" s="203" t="inlineStr">
@@ -3913,13 +3951,6 @@
           <t>[机制3v3] 现金锁定系数（CLC）— 平方衰减版</t>
         </is>
       </c>
-      <c r="B97" s="179" t="n"/>
-      <c r="C97" s="179" t="n"/>
-      <c r="D97" s="179" t="n"/>
-      <c r="E97" s="179" t="n"/>
-      <c r="F97" s="179" t="n"/>
-      <c r="G97" s="179" t="n"/>
-      <c r="H97" s="179" t="n"/>
     </row>
     <row r="98">
       <c r="A98" s="204" t="inlineStr">
@@ -4078,13 +4109,6 @@
           <t>[机制4v3] 折后仓位计算 — 4级分级版</t>
         </is>
       </c>
-      <c r="B107" s="179" t="n"/>
-      <c r="C107" s="179" t="n"/>
-      <c r="D107" s="179" t="n"/>
-      <c r="E107" s="179" t="n"/>
-      <c r="F107" s="179" t="n"/>
-      <c r="G107" s="179" t="n"/>
-      <c r="H107" s="179" t="n"/>
     </row>
     <row r="108">
       <c r="A108" s="204" t="inlineStr">
@@ -4211,13 +4235,6 @@
           <t>[机制5v3] 虚P→实P转换 — 确认窗口+因果链版</t>
         </is>
       </c>
-      <c r="B116" s="179" t="n"/>
-      <c r="C116" s="179" t="n"/>
-      <c r="D116" s="179" t="n"/>
-      <c r="E116" s="179" t="n"/>
-      <c r="F116" s="179" t="n"/>
-      <c r="G116" s="179" t="n"/>
-      <c r="H116" s="179" t="n"/>
     </row>
     <row r="117">
       <c r="A117" s="204" t="inlineStr">
@@ -4359,13 +4376,6 @@
           <t>[信号计分板] 每日更新，驱动信号概率动态调整</t>
         </is>
       </c>
-      <c r="B125" s="175" t="n"/>
-      <c r="C125" s="175" t="n"/>
-      <c r="D125" s="175" t="n"/>
-      <c r="E125" s="175" t="n"/>
-      <c r="F125" s="175" t="n"/>
-      <c r="G125" s="175" t="n"/>
-      <c r="H125" s="175" t="n"/>
     </row>
     <row r="126">
       <c r="A126" s="204" t="inlineStr">
@@ -4484,13 +4494,6 @@
           <t>⚡ 机制v3使用指南</t>
         </is>
       </c>
-      <c r="B135" s="175" t="n"/>
-      <c r="C135" s="175" t="n"/>
-      <c r="D135" s="175" t="n"/>
-      <c r="E135" s="175" t="n"/>
-      <c r="F135" s="175" t="n"/>
-      <c r="G135" s="175" t="n"/>
-      <c r="H135" s="175" t="n"/>
     </row>
     <row r="136">
       <c r="A136" s="204" t="inlineStr">
@@ -4587,9 +4590,389 @@
         </is>
       </c>
     </row>
+    <row r="142">
+      <c r="A142" s="206" t="inlineStr">
+        <is>
+          <t>📊 持仓状态速查表</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="207" t="inlineStr">
+        <is>
+          <t>持仓</t>
+        </is>
+      </c>
+      <c r="B143" s="207" t="inlineStr">
+        <is>
+          <t>代码</t>
+        </is>
+      </c>
+      <c r="C143" s="207" t="inlineStr">
+        <is>
+          <t>当前P</t>
+        </is>
+      </c>
+      <c r="D143" s="207" t="inlineStr">
+        <is>
+          <t>有效P</t>
+        </is>
+      </c>
+      <c r="E143" s="207" t="inlineStr">
+        <is>
+          <t>虚P</t>
+        </is>
+      </c>
+      <c r="F143" s="207" t="inlineStr">
+        <is>
+          <t>利率折价</t>
+        </is>
+      </c>
+      <c r="G143" s="207" t="inlineStr">
+        <is>
+          <t>方向</t>
+        </is>
+      </c>
+      <c r="H143" s="207" t="inlineStr">
+        <is>
+          <t>操作建议</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="78" t="inlineStr">
+        <is>
+          <t>芯片020628</t>
+        </is>
+      </c>
+      <c r="B144" s="78" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="C144" s="78" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="D144" s="78" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="E144" s="78" t="inlineStr">
+        <is>
+          <t>虚P+2pp</t>
+        </is>
+      </c>
+      <c r="F144" s="78" t="inlineStr">
+        <is>
+          <t>利率折价-6pp</t>
+        </is>
+      </c>
+      <c r="G144" s="78" t="inlineStr">
+        <is>
+          <t>🟡中性</t>
+        </is>
+      </c>
+      <c r="H144" s="78" t="inlineStr">
+        <is>
+          <t>观望</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="78" t="inlineStr">
+        <is>
+          <t>电池018926</t>
+        </is>
+      </c>
+      <c r="B145" s="78" t="inlineStr">
+        <is>
+          <t>C2</t>
+        </is>
+      </c>
+      <c r="C145" s="78" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="D145" s="78" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="E145" s="78" t="inlineStr">
+        <is>
+          <t>虚P无</t>
+        </is>
+      </c>
+      <c r="F145" s="78" t="inlineStr">
+        <is>
+          <t>利率折价-6pp</t>
+        </is>
+      </c>
+      <c r="G145" s="78" t="inlineStr">
+        <is>
+          <t>🟢偏多</t>
+        </is>
+      </c>
+      <c r="H145" s="78" t="inlineStr">
+        <is>
+          <t>持有/关注加仓</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="78" t="inlineStr">
+        <is>
+          <t>恒科012349</t>
+        </is>
+      </c>
+      <c r="B146" s="78" t="inlineStr">
+        <is>
+          <t>C3</t>
+        </is>
+      </c>
+      <c r="C146" s="78" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="D146" s="78" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="E146" s="78" t="inlineStr">
+        <is>
+          <t>虚P无</t>
+        </is>
+      </c>
+      <c r="F146" s="78" t="inlineStr">
+        <is>
+          <t>利率折价-6pp</t>
+        </is>
+      </c>
+      <c r="G146" s="78" t="inlineStr">
+        <is>
+          <t>🔴偏空</t>
+        </is>
+      </c>
+      <c r="H146" s="78" t="inlineStr">
+        <is>
+          <t>减仓/清仓</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="78" t="inlineStr">
+        <is>
+          <t>养殖014415</t>
+        </is>
+      </c>
+      <c r="B147" s="78" t="inlineStr">
+        <is>
+          <t>C4</t>
+        </is>
+      </c>
+      <c r="C147" s="78" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="D147" s="78" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="E147" s="78" t="inlineStr">
+        <is>
+          <t>虚P+4pp</t>
+        </is>
+      </c>
+      <c r="F147" s="78" t="inlineStr">
+        <is>
+          <t>利率折价0pp</t>
+        </is>
+      </c>
+      <c r="G147" s="78" t="inlineStr">
+        <is>
+          <t>🟢偏多</t>
+        </is>
+      </c>
+      <c r="H147" s="78" t="inlineStr">
+        <is>
+          <t>持有/关注加仓</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="78" t="inlineStr">
+        <is>
+          <t>有色004433</t>
+        </is>
+      </c>
+      <c r="B148" s="78" t="inlineStr">
+        <is>
+          <t>C5</t>
+        </is>
+      </c>
+      <c r="C148" s="78" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="D148" s="78" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="E148" s="78" t="inlineStr">
+        <is>
+          <t>虚P无</t>
+        </is>
+      </c>
+      <c r="F148" s="78" t="inlineStr">
+        <is>
+          <t>利率折价-4pp</t>
+        </is>
+      </c>
+      <c r="G148" s="78" t="inlineStr">
+        <is>
+          <t>🔴偏空</t>
+        </is>
+      </c>
+      <c r="H148" s="78" t="inlineStr">
+        <is>
+          <t>减仓/清仓</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="78" t="inlineStr">
+        <is>
+          <t>稀金014111</t>
+        </is>
+      </c>
+      <c r="B149" s="78" t="inlineStr">
+        <is>
+          <t>C6</t>
+        </is>
+      </c>
+      <c r="C149" s="78" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="D149" s="78" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="E149" s="78" t="inlineStr">
+        <is>
+          <t>虚P无</t>
+        </is>
+      </c>
+      <c r="F149" s="78" t="inlineStr">
+        <is>
+          <t>利率折价-4pp</t>
+        </is>
+      </c>
+      <c r="G149" s="78" t="inlineStr">
+        <is>
+          <t>🟡中性</t>
+        </is>
+      </c>
+      <c r="H149" s="78" t="inlineStr">
+        <is>
+          <t>观望</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="78" t="inlineStr">
+        <is>
+          <t>银行001595</t>
+        </is>
+      </c>
+      <c r="B150" s="78" t="inlineStr">
+        <is>
+          <t>C7</t>
+        </is>
+      </c>
+      <c r="C150" s="78" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="D150" s="78" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="E150" s="78" t="inlineStr">
+        <is>
+          <t>虚P-2pp</t>
+        </is>
+      </c>
+      <c r="F150" s="78" t="inlineStr">
+        <is>
+          <t>利率折价0pp</t>
+        </is>
+      </c>
+      <c r="G150" s="78" t="inlineStr">
+        <is>
+          <t>🟡中性</t>
+        </is>
+      </c>
+      <c r="H150" s="78" t="inlineStr">
+        <is>
+          <t>观望</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="78" t="inlineStr">
+        <is>
+          <t>AI027048</t>
+        </is>
+      </c>
+      <c r="B151" s="78" t="inlineStr">
+        <is>
+          <t>C8</t>
+        </is>
+      </c>
+      <c r="C151" s="78" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="D151" s="78" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E151" s="78" t="inlineStr"/>
+      <c r="F151" s="78" t="inlineStr">
+        <is>
+          <t>利率折价-4pp</t>
+        </is>
+      </c>
+      <c r="G151" s="78" t="inlineStr">
+        <is>
+          <t>🟡中性</t>
+        </is>
+      </c>
+      <c r="H151" s="78" t="inlineStr">
+        <is>
+          <t>观望</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="22">
-    <mergeCell ref="A16:F16"/>
+  <mergeCells count="21">
     <mergeCell ref="A51:H51"/>
     <mergeCell ref="A107:H107"/>
     <mergeCell ref="B15:H15"/>
@@ -4602,8 +4985,8 @@
     <mergeCell ref="A116:H116"/>
     <mergeCell ref="A32:H32"/>
     <mergeCell ref="A97:H97"/>
+    <mergeCell ref="A135:H135"/>
     <mergeCell ref="A17:H17"/>
-    <mergeCell ref="A135:H135"/>
     <mergeCell ref="B14:H14"/>
     <mergeCell ref="B13:H13"/>
     <mergeCell ref="A96:H96"/>

--- a/持仓贝叶斯跟踪.xlsx
+++ b/持仓贝叶斯跟踪.xlsx
@@ -12,6 +12,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="拟合分析" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="机会成本排序" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="三源联动分析" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="基金数据联动" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1" refMode="A1" iterate="0" iterateCount="100" iterateDelta="0.0001"/>
@@ -21,7 +22,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="59">
+  <fonts count="62">
     <font>
       <name val="Calibri"/>
       <charset val="1"/>
@@ -392,8 +393,20 @@
       <b val="1"/>
       <color rgb="00FFFFFF"/>
     </font>
+    <font>
+      <color rgb="00666666"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="0000AA00"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FF0000"/>
+    </font>
   </fonts>
-  <fills count="33">
+  <fills count="34">
     <fill>
       <patternFill/>
     </fill>
@@ -585,6 +598,11 @@
         <fgColor rgb="004472C4"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF2CC"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="7">
     <border>
@@ -646,7 +664,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="208">
+  <cellXfs count="215">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -1215,6 +1233,23 @@
     <xf numFmtId="0" fontId="56" fillId="28" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="44" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="58" fillId="32" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="59" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="51" fillId="32" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="60" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="33" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="42" fillId="33" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1292,6 +1327,7 @@
   <authors>
     <author>Hermes</author>
     <author>叙事主线</author>
+    <author>AI指导原则</author>
   </authors>
   <commentList>
     <comment ref="A4" authorId="0" shapeId="0">
@@ -1596,7 +1632,28 @@
 </t>
       </text>
     </comment>
-    <comment ref="A85" authorId="0" shapeId="0">
+    <comment ref="A18" authorId="2" shapeId="0">
+      <text>
+        <t xml:space="preserve">来源：用户2026-06-04确立，多个信源交叉确认
+核心逻辑：
+1. AI前半程（现在→近期）：投硬件基础设施
+   - 芯片/算力/堆叠封装 = 确定性最高
+   - 已验证：芯片ETF20日+16.4%
+2. AI后半程（中期→长期）：布局软件/应用端
+   - 硬件铺完→应用爆发→软件公司赚大头
+   - 类比：互联网先投光纤/服务器，后投Google/微信
+3. 当前阶段判断：前半程尾声→后半程前夕
+   - 硬件估值开始偏高（兆易创新+81%）
+   - 软件端尚未充分定价
+对持仓影响：
+- 芯片/堆叠 持有但警惕估值（前半程尾声）
+- 软件/AI应用 开始关注（后半程布局）
+- 这是原则性指导，不是事件，不入P值计算
+置信度：顶级（用户+多信源确认）
+</t>
+      </text>
+    </comment>
+    <comment ref="A87" authorId="0" shapeId="0">
       <text>
         <t xml:space="preserve">【来源】蒋宇飞抖音视频（2026-05-25）"未来5-10年的黄金赛道，深度拆解玻璃基板的万亿机遇"
 【信源评估】蒋宇飞⭐⭐⭐高置信度（有产业实操经验，多次验证预测准确）
@@ -1611,7 +1668,7 @@
 </t>
       </text>
     </comment>
-    <comment ref="A87" authorId="0" shapeId="0">
+    <comment ref="A89" authorId="0" shapeId="0">
       <text>
         <t>信息源：东方财富+新浪财经2026-06-02
 核心数据：
@@ -1624,7 +1681,7 @@
 结论：不建议加仓</t>
       </text>
     </comment>
-    <comment ref="A88" authorId="0" shapeId="0">
+    <comment ref="A90" authorId="0" shapeId="0">
       <text>
         <t>信息源：东方财富头条+新浪财经2026-06-02
 核心数据：
@@ -1639,7 +1696,7 @@
 结论：重点关注，强正向信号</t>
       </text>
     </comment>
-    <comment ref="A89" authorId="0" shapeId="0">
+    <comment ref="A91" authorId="0" shapeId="0">
       <text>
         <t xml:space="preserve">【来源】群联潘健成(产业高管)+蒋宇飞(6.1两长存储+5.18框架)+宋鸿兵(6.2摩尔定律终结)+周鸿祎(内存决定AI)+用户6.3洞察
 【逻辑链】
@@ -1662,7 +1719,7 @@
 </t>
       </text>
     </comment>
-    <comment ref="A90" authorId="0" shapeId="0">
+    <comment ref="A92" authorId="0" shapeId="0">
       <text>
         <t xml:space="preserve">【来源】蒋宇飞星光纯叠框架+宋鸿兵华为韬定律+用户"AI瓶颈是内存而非算力"
 【逻辑链】
@@ -1676,7 +1733,7 @@
 </t>
       </text>
     </comment>
-    <comment ref="A92" authorId="0" shapeId="0">
+    <comment ref="A94" authorId="0" shapeId="0">
       <text>
         <t xml:space="preserve">【标的】北京君正 300223
 【核心逻辑】存储+计算芯片，DRAM新工艺突破，车载存储市占率提升。A股年内+51%，市值772亿。港股二度IPO中。盈亏比4:1，存储赛道里最强。
@@ -1687,7 +1744,7 @@
 </t>
       </text>
     </comment>
-    <comment ref="A93" authorId="0" shapeId="0">
+    <comment ref="A95" authorId="0" shapeId="0">
       <text>
         <t xml:space="preserve">【标的】兆易创新 603986
 【核心逻辑】NOR Flash国内龙头，DRAM布局中。存储涨价直接受益。盈亏比3.5:1。
@@ -1698,7 +1755,7 @@
 </t>
       </text>
     </comment>
-    <comment ref="A94" authorId="0" shapeId="0">
+    <comment ref="A96" authorId="0" shapeId="0">
       <text>
         <t xml:space="preserve">【标的】江波龙 301308
 【核心逻辑】存储模组+主控芯片，国产替代核心标的。盈亏比3.5:1。
@@ -2026,7 +2083,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:H151"/>
+  <dimension ref="A1:H153"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6171875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="18" customWidth="1" style="78" min="1" max="1"/>
@@ -2311,83 +2368,97 @@
           <t>④</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B16" s="78" t="inlineStr">
         <is>
           <t>比特币独立叙事消亡 维持：资金吸附力排序 AI&gt;美股&gt;黄金&gt;比特币，比特币已成美股影子资产，AI落地后资金有明确去处，比特币价值持续被稀释</t>
         </is>
       </c>
     </row>
     <row r="17" ht="16.5" customHeight="1" s="79">
-      <c r="A17" s="158" t="inlineStr">
+      <c r="A17" s="213" t="inlineStr">
+        <is>
+          <t>⚡ AI投资阶段切换指导原则（顶级置信度）</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="16.5" customHeight="1" s="79">
+      <c r="A18" s="214" t="inlineStr">
+        <is>
+          <t>AI前半程=投硬件（芯片/算力/堆叠封装）→ 已验证。AI后半程=布局软件/应用端 → 多个信源交叉确认，逻辑高度自洽。此为投资指导原则，不是事件，不作为P值调整依据，但影响赛道选择优先级。</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="16.5" customHeight="1" s="79">
+      <c r="A19" s="158" t="inlineStr">
         <is>
           <t>🔴🔴🔴 战略级虚P信号池 + 现金策略联动（2026-06-04）🔴🔴🔴</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="16.5" customHeight="1" s="79">
-      <c r="A18" s="160" t="inlineStr">
+    <row r="20" ht="30" customHeight="1" s="79">
+      <c r="A20" s="160" t="inlineStr">
         <is>
           <t>虚P规则：未落地→记虚P→不加实P→等落地转实P。此板块锁定大部分现金，与机会成本联动分析。</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="16.5" customHeight="1" s="79">
-      <c r="A19" s="178" t="inlineStr">
+    <row r="21" ht="16.5" customHeight="1" s="79">
+      <c r="A21" s="178" t="inlineStr">
         <is>
           <t>一、三源信号详情</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="30" customHeight="1" s="79">
-      <c r="A20" s="162" t="inlineStr">
+    <row r="22" ht="16.5" customHeight="1" s="79">
+      <c r="A22" s="162" t="inlineStr">
         <is>
           <t>来源</t>
         </is>
       </c>
-      <c r="B20" s="162" t="inlineStr">
+      <c r="B22" s="162" t="inlineStr">
         <is>
           <t>核心观点</t>
         </is>
       </c>
-      <c r="C20" s="162" t="inlineStr">
+      <c r="C22" s="162" t="inlineStr">
         <is>
           <t>与你策略契合</t>
         </is>
       </c>
-      <c r="D20" s="162" t="inlineStr">
+      <c r="D22" s="162" t="inlineStr">
         <is>
           <t>虚P方向</t>
         </is>
       </c>
-      <c r="E20" s="162" t="inlineStr">
+      <c r="E22" s="162" t="inlineStr">
         <is>
           <t>落地条件</t>
         </is>
       </c>
-      <c r="F20" s="162" t="inlineStr">
+      <c r="F22" s="162" t="inlineStr">
         <is>
           <t>状态</t>
         </is>
       </c>
-      <c r="G20" s="162" t="inlineStr">
+      <c r="G22" s="162" t="inlineStr">
         <is>
           <t>权重</t>
         </is>
       </c>
-      <c r="H20" s="162" t="inlineStr">
+      <c r="H22" s="162" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="21" ht="16.5" customHeight="1" s="79">
-      <c r="A21" s="163" t="inlineStr">
+    <row r="23" ht="16.5" customHeight="1" s="79">
+      <c r="A23" s="163" t="inlineStr">
         <is>
           <t>达利欧
 Bloomberg 6/3</t>
         </is>
       </c>
-      <c r="B21" s="163" t="inlineStr">
+      <c r="B23" s="163" t="inlineStr">
         <is>
           <t>AI泡沫65-75%概率年底破
 "财富转现金=刺破泡沫"
@@ -2396,7 +2467,7 @@
 基建投入&gt;&gt;收入</t>
         </is>
       </c>
-      <c r="C21" s="164" t="inlineStr">
+      <c r="C23" s="164" t="inlineStr">
         <is>
           <t>完全契合
 等中期选举大跌
@@ -2404,45 +2475,45 @@
 回调后大仓位进</t>
         </is>
       </c>
-      <c r="D21" s="163" t="inlineStr">
+      <c r="D23" s="163" t="inlineStr">
         <is>
           <t>芯片-2pp
 恒科-1pp
 (虚P)</t>
         </is>
       </c>
-      <c r="E21" s="163" t="inlineStr">
+      <c r="E23" s="163" t="inlineStr">
         <is>
           <t>七姐妹&gt;15%回调
 或破200日均线</t>
         </is>
       </c>
-      <c r="F21" s="165" t="inlineStr">
+      <c r="F23" s="165" t="inlineStr">
         <is>
           <t>未落地</t>
         </is>
       </c>
-      <c r="G21" s="166" t="inlineStr">
+      <c r="G23" s="166" t="inlineStr">
         <is>
           <t>极高
 5星</t>
         </is>
       </c>
-      <c r="H21" s="163" t="inlineStr">
+      <c r="H23" s="163" t="inlineStr">
         <is>
           <t>与你100%一致
 回调=买入机会</t>
         </is>
       </c>
     </row>
-    <row r="22" ht="16.5" customHeight="1" s="79">
-      <c r="A22" s="163" t="inlineStr">
+    <row r="24" ht="16.5" customHeight="1" s="79">
+      <c r="A24" s="163" t="inlineStr">
         <is>
           <t>李大霄
 金融界 6/4</t>
         </is>
       </c>
-      <c r="B22" s="163" t="inlineStr">
+      <c r="B24" s="163" t="inlineStr">
         <is>
           <t>美股窄牛宽熊
 仅20只创新高
@@ -2451,52 +2522,52 @@
 IPO抽血</t>
         </is>
       </c>
-      <c r="C22" s="164" t="inlineStr">
+      <c r="C24" s="164" t="inlineStr">
         <is>
           <t>高度契合
 确认美股风险
 现金策略正确</t>
         </is>
       </c>
-      <c r="D22" s="163" t="inlineStr">
+      <c r="D24" s="163" t="inlineStr">
         <is>
           <t>恒科-2pp
 芯片-1pp
 (虚P)</t>
         </is>
       </c>
-      <c r="E22" s="163" t="inlineStr">
+      <c r="E24" s="163" t="inlineStr">
         <is>
           <t>纳指破200日均线
 多数成分股下跌</t>
         </is>
       </c>
-      <c r="F22" s="165" t="inlineStr">
+      <c r="F24" s="165" t="inlineStr">
         <is>
           <t>未落地</t>
         </is>
       </c>
-      <c r="G22" s="163" t="inlineStr">
+      <c r="G24" s="163" t="inlineStr">
         <is>
           <t>中高
 3星</t>
         </is>
       </c>
-      <c r="H22" s="163" t="inlineStr">
+      <c r="H24" s="163" t="inlineStr">
         <is>
           <t>数据靠谱
 结论偏激进</t>
         </is>
       </c>
     </row>
-    <row r="23" ht="16.5" customHeight="1" s="79">
-      <c r="A23" s="163" t="inlineStr">
+    <row r="25" ht="16.5" customHeight="1" s="79">
+      <c r="A25" s="163" t="inlineStr">
         <is>
           <t>知乎专栏
 6/4</t>
         </is>
       </c>
-      <c r="B23" s="163" t="inlineStr">
+      <c r="B25" s="163" t="inlineStr">
         <is>
           <t>纳指PE中值区间
 5维度无暴跌
@@ -2504,765 +2575,765 @@
 安全继续持有</t>
         </is>
       </c>
-      <c r="C23" s="164" t="inlineStr">
+      <c r="C25" s="164" t="inlineStr">
         <is>
           <t>部分参考
 与达利欧矛盾
 看估值vs流动性</t>
         </is>
       </c>
-      <c r="D23" s="163" t="inlineStr">
+      <c r="D25" s="163" t="inlineStr">
         <is>
           <t>恒科+1pp
 (虚P)</t>
         </is>
       </c>
-      <c r="E23" s="163" t="inlineStr">
+      <c r="E25" s="163" t="inlineStr">
         <is>
           <t>PE跌破25
 或暴跌触发</t>
         </is>
       </c>
-      <c r="F23" s="165" t="inlineStr">
+      <c r="F25" s="165" t="inlineStr">
         <is>
           <t>未落地</t>
         </is>
       </c>
-      <c r="G23" s="163" t="inlineStr">
+      <c r="G25" s="163" t="inlineStr">
         <is>
           <t>中
 3星</t>
         </is>
       </c>
-      <c r="H23" s="163" t="inlineStr">
+      <c r="H25" s="163" t="inlineStr">
         <is>
           <t>框架合理
 忽略集中度</t>
         </is>
       </c>
     </row>
-    <row r="24" ht="16.5" customHeight="1" s="79"/>
-    <row r="25" ht="16.5" customHeight="1" s="79">
-      <c r="A25" s="178" t="inlineStr">
+    <row r="26" ht="15" customHeight="1" s="79"/>
+    <row r="27" ht="17.15" customHeight="1" s="79">
+      <c r="A27" s="178" t="inlineStr">
         <is>
           <t>二、三源互锁验证</t>
         </is>
       </c>
     </row>
-    <row r="26" ht="15" customHeight="1" s="79">
-      <c r="A26" s="180" t="inlineStr">
+    <row r="28" ht="15" customHeight="1" s="79">
+      <c r="A28" s="180" t="inlineStr">
         <is>
           <t>互锁组合</t>
         </is>
       </c>
-      <c r="B26" s="180" t="inlineStr">
+      <c r="B28" s="180" t="inlineStr">
         <is>
           <t>关系</t>
         </is>
       </c>
-      <c r="C26" s="180" t="inlineStr">
+      <c r="C28" s="180" t="inlineStr">
         <is>
           <t>分析</t>
         </is>
       </c>
-      <c r="D26" s="180" t="inlineStr">
+      <c r="D28" s="180" t="inlineStr">
         <is>
           <t>信号强度</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="17.15" customHeight="1" s="79">
-      <c r="A27" s="181" t="inlineStr">
-        <is>
-          <t>达利欧×李大霄</t>
-        </is>
-      </c>
-      <c r="B27" s="182" t="inlineStr">
-        <is>
-          <t>✅强印证</t>
-        </is>
-      </c>
-      <c r="C27" s="163" t="inlineStr">
-        <is>
-          <t>AI泡沫+窄牛宽熊=同一现象两角度</t>
-        </is>
-      </c>
-      <c r="D27" s="163" t="inlineStr">
-        <is>
-          <t>🔴强信号</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="15" customHeight="1" s="79">
-      <c r="A28" s="181" t="inlineStr">
-        <is>
-          <t>达利欧×知乎</t>
-        </is>
-      </c>
-      <c r="B28" s="183" t="inlineStr">
-        <is>
-          <t>⚠️部分矛盾</t>
-        </is>
-      </c>
-      <c r="C28" s="163" t="inlineStr">
-        <is>
-          <t>达看流动性vs知乎看估值</t>
-        </is>
-      </c>
-      <c r="D28" s="163" t="inlineStr">
-        <is>
-          <t>🟡中性</t>
         </is>
       </c>
     </row>
     <row r="29" ht="15" customHeight="1" s="79">
       <c r="A29" s="181" t="inlineStr">
         <is>
+          <t>达利欧×李大霄</t>
+        </is>
+      </c>
+      <c r="B29" s="182" t="inlineStr">
+        <is>
+          <t>✅强印证</t>
+        </is>
+      </c>
+      <c r="C29" s="163" t="inlineStr">
+        <is>
+          <t>AI泡沫+窄牛宽熊=同一现象两角度</t>
+        </is>
+      </c>
+      <c r="D29" s="163" t="inlineStr">
+        <is>
+          <t>🔴强信号</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="15" customHeight="1" s="79">
+      <c r="A30" s="181" t="inlineStr">
+        <is>
+          <t>达利欧×知乎</t>
+        </is>
+      </c>
+      <c r="B30" s="183" t="inlineStr">
+        <is>
+          <t>⚠️部分矛盾</t>
+        </is>
+      </c>
+      <c r="C30" s="163" t="inlineStr">
+        <is>
+          <t>达看流动性vs知乎看估值</t>
+        </is>
+      </c>
+      <c r="D30" s="163" t="inlineStr">
+        <is>
+          <t>🟡中性</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="15" customHeight="1" s="79">
+      <c r="A31" s="181" t="inlineStr">
+        <is>
           <t>三源共识</t>
         </is>
       </c>
-      <c r="B29" s="184" t="inlineStr">
+      <c r="B31" s="184" t="inlineStr">
         <is>
           <t>🔴核心共识</t>
         </is>
       </c>
-      <c r="C29" s="163" t="inlineStr">
+      <c r="C31" s="163" t="inlineStr">
         <is>
           <t>AI龙头估值偏高+市场集中+中小盘已熊</t>
         </is>
       </c>
-      <c r="D29" s="163" t="inlineStr">
+      <c r="D31" s="163" t="inlineStr">
         <is>
           <t>🔴强信号</t>
         </is>
       </c>
     </row>
-    <row r="30" ht="15" customHeight="1" s="79"/>
-    <row r="31" ht="15" customHeight="1" s="79">
-      <c r="A31" s="174" t="inlineStr">
+    <row r="32" ht="15" customHeight="1" s="79"/>
+    <row r="33" ht="16.5" customHeight="1" s="79">
+      <c r="A33" s="174" t="inlineStr">
         <is>
           <t>三、现金策略联动（锁定大部分现金储备）</t>
         </is>
       </c>
     </row>
-    <row r="32" ht="15" customHeight="1" s="79">
-      <c r="A32" s="160" t="inlineStr">
+    <row r="34" ht="16.5" customHeight="1" s="79">
+      <c r="A34" s="160" t="inlineStr">
         <is>
           <t>三源联动→达利欧65-75%概率年底AI回调+中期选举历史跌一波→锁定大部分现金→等11月回调入场</t>
         </is>
       </c>
     </row>
-    <row r="33" ht="16.5" customHeight="1" s="79">
-      <c r="A33" s="180" t="inlineStr">
+    <row r="35" ht="16.5" customHeight="1" s="79">
+      <c r="A35" s="180" t="inlineStr">
         <is>
           <t>维度</t>
         </is>
       </c>
-      <c r="B33" s="180" t="inlineStr">
+      <c r="B35" s="180" t="inlineStr">
         <is>
           <t>内容</t>
         </is>
       </c>
-      <c r="C33" s="180" t="inlineStr">
+      <c r="C35" s="180" t="inlineStr">
         <is>
           <t>影响</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="16.5" customHeight="1" s="79">
-      <c r="A34" s="163" t="inlineStr">
-        <is>
-          <t>现金锁定</t>
-        </is>
-      </c>
-      <c r="B34" s="163" t="inlineStr">
-        <is>
-          <t>大部分现金(60-70%)锁定等待</t>
-        </is>
-      </c>
-      <c r="C34" s="163" t="inlineStr">
-        <is>
-          <t>→当前可投资金大幅减少</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="16.5" customHeight="1" s="79">
-      <c r="A35" s="163" t="inlineStr">
-        <is>
-          <t>等待窗口</t>
-        </is>
-      </c>
-      <c r="B35" s="163" t="inlineStr">
-        <is>
-          <t>2026年11月中期选举前后</t>
-        </is>
-      </c>
-      <c r="C35" s="163" t="inlineStr">
-        <is>
-          <t>→约5个月等待期</t>
         </is>
       </c>
     </row>
     <row r="36" ht="16.5" customHeight="1" s="79">
       <c r="A36" s="163" t="inlineStr">
         <is>
-          <t>触发条件</t>
+          <t>现金锁定</t>
         </is>
       </c>
       <c r="B36" s="163" t="inlineStr">
         <is>
-          <t>美股跌一波+AI回调&gt;15%</t>
+          <t>大部分现金(60-70%)锁定等待</t>
         </is>
       </c>
       <c r="C36" s="163" t="inlineStr">
         <is>
-          <t>→达利欧65-75%概率事件</t>
+          <t>→当前可投资金大幅减少</t>
         </is>
       </c>
     </row>
     <row r="37" ht="16.5" customHeight="1" s="79">
       <c r="A37" s="163" t="inlineStr">
         <is>
-          <t>入场标的</t>
+          <t>等待窗口</t>
         </is>
       </c>
       <c r="B37" s="163" t="inlineStr">
         <is>
-          <t>堆叠：长电科技+通富微电</t>
+          <t>2026年11月中期选举前后</t>
         </is>
       </c>
       <c r="C37" s="163" t="inlineStr">
         <is>
-          <t>→国内确定性不受美股影响</t>
+          <t>→约5个月等待期</t>
         </is>
       </c>
     </row>
     <row r="38" ht="16.5" customHeight="1" s="79">
       <c r="A38" s="163" t="inlineStr">
         <is>
-          <t>机会成本</t>
+          <t>触发条件</t>
         </is>
       </c>
       <c r="B38" s="163" t="inlineStr">
         <is>
-          <t>持有现金5个月vs错过短期行情</t>
+          <t>美股跌一波+AI回调&gt;15%</t>
         </is>
       </c>
       <c r="C38" s="163" t="inlineStr">
         <is>
-          <t>→见下方机会成本联动</t>
+          <t>→达利欧65-75%概率事件</t>
         </is>
       </c>
     </row>
     <row r="39" ht="16.5" customHeight="1" s="79">
       <c r="A39" s="163" t="inlineStr">
         <is>
+          <t>入场标的</t>
+        </is>
+      </c>
+      <c r="B39" s="163" t="inlineStr">
+        <is>
+          <t>堆叠：长电科技+通富微电</t>
+        </is>
+      </c>
+      <c r="C39" s="163" t="inlineStr">
+        <is>
+          <t>→国内确定性不受美股影响</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="16.5" customHeight="1" s="79">
+      <c r="A40" s="163" t="inlineStr">
+        <is>
+          <t>机会成本</t>
+        </is>
+      </c>
+      <c r="B40" s="163" t="inlineStr">
+        <is>
+          <t>持有现金5个月vs错过短期行情</t>
+        </is>
+      </c>
+      <c r="C40" s="163" t="inlineStr">
+        <is>
+          <t>→见下方机会成本联动</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="16.5" customHeight="1" s="79">
+      <c r="A41" s="163" t="inlineStr">
+        <is>
           <t>下行保护</t>
         </is>
       </c>
-      <c r="B39" s="163" t="inlineStr">
+      <c r="B41" s="163" t="inlineStr">
         <is>
           <t>没跌→现金无损可继续等</t>
         </is>
       </c>
-      <c r="C39" s="163" t="inlineStr">
+      <c r="C41" s="163" t="inlineStr">
         <is>
           <t>→不对称博弈下有保底</t>
         </is>
       </c>
     </row>
-    <row r="40" ht="16.5" customHeight="1" s="79"/>
-    <row r="41" ht="16.5" customHeight="1" s="79">
-      <c r="A41" s="174" t="inlineStr">
+    <row r="42" ht="16.5" customHeight="1" s="79"/>
+    <row r="43" ht="16.5" customHeight="1" s="79">
+      <c r="A43" s="174" t="inlineStr">
         <is>
           <t>四、机会成本联动分析（现金锁定vs其他选项）</t>
         </is>
       </c>
     </row>
-    <row r="42" ht="16.5" customHeight="1" s="79">
-      <c r="A42" s="180" t="inlineStr">
+    <row r="44" ht="16.5" customHeight="1" s="79">
+      <c r="A44" s="180" t="inlineStr">
         <is>
           <t>选项</t>
         </is>
       </c>
-      <c r="B42" s="180" t="inlineStr">
+      <c r="B44" s="180" t="inlineStr">
         <is>
           <t>P值</t>
         </is>
       </c>
-      <c r="C42" s="180" t="inlineStr">
+      <c r="C44" s="180" t="inlineStr">
         <is>
           <t>盈亏比</t>
         </is>
       </c>
-      <c r="D42" s="180" t="inlineStr">
+      <c r="D44" s="180" t="inlineStr">
         <is>
           <t>Score</t>
         </is>
       </c>
-      <c r="E42" s="180" t="inlineStr">
+      <c r="E44" s="180" t="inlineStr">
         <is>
           <t>现金锁定影响</t>
         </is>
       </c>
-      <c r="F42" s="180" t="inlineStr">
+      <c r="F44" s="180" t="inlineStr">
         <is>
           <t>建议</t>
         </is>
       </c>
-      <c r="G42" s="180" t="inlineStr">
+      <c r="G44" s="180" t="inlineStr">
         <is>
           <t>判断</t>
         </is>
       </c>
     </row>
-    <row r="43" ht="16.5" customHeight="1" s="79">
-      <c r="A43" s="163" t="inlineStr">
+    <row r="45" ht="16.5" customHeight="1" s="79">
+      <c r="A45" s="163" t="inlineStr">
         <is>
           <t>长电科技</t>
         </is>
       </c>
-      <c r="B43" s="163" t="inlineStr">
+      <c r="B45" s="163" t="inlineStr">
         <is>
           <t>75%</t>
         </is>
       </c>
-      <c r="C43" s="163" t="inlineStr">
+      <c r="C45" s="163" t="inlineStr">
         <is>
           <t>4.5:1</t>
         </is>
       </c>
-      <c r="D43" s="163" t="inlineStr">
+      <c r="D45" s="163" t="inlineStr">
         <is>
           <t>3.375</t>
         </is>
       </c>
-      <c r="E43" s="163" t="inlineStr">
+      <c r="E45" s="163" t="inlineStr">
         <is>
           <t>等回调大仓位
 现金锁定中</t>
         </is>
       </c>
-      <c r="F43" s="163" t="inlineStr">
+      <c r="F45" s="163" t="inlineStr">
         <is>
           <t>暂不动等11月</t>
         </is>
       </c>
-      <c r="G43" s="166" t="inlineStr">
+      <c r="G45" s="166" t="inlineStr">
         <is>
           <t>🔴最高优先</t>
         </is>
       </c>
     </row>
-    <row r="44" ht="16.5" customHeight="1" s="79">
-      <c r="A44" s="163" t="inlineStr">
+    <row r="46" ht="16.5" customHeight="1" s="79">
+      <c r="A46" s="163" t="inlineStr">
         <is>
           <t>通富微电</t>
         </is>
       </c>
-      <c r="B44" s="163" t="inlineStr">
+      <c r="B46" s="163" t="inlineStr">
         <is>
           <t>75%</t>
         </is>
       </c>
-      <c r="C44" s="163" t="inlineStr">
+      <c r="C46" s="163" t="inlineStr">
         <is>
           <t>4.0:1</t>
         </is>
       </c>
-      <c r="D44" s="163" t="inlineStr">
+      <c r="D46" s="163" t="inlineStr">
         <is>
           <t>3.000</t>
         </is>
       </c>
-      <c r="E44" s="163" t="inlineStr">
+      <c r="E46" s="163" t="inlineStr">
         <is>
           <t>等回调大仓位
 现金锁定中</t>
         </is>
       </c>
-      <c r="F44" s="163" t="inlineStr">
+      <c r="F46" s="163" t="inlineStr">
         <is>
           <t>暂不动等11月</t>
         </is>
       </c>
-      <c r="G44" s="166" t="inlineStr">
+      <c r="G46" s="166" t="inlineStr">
         <is>
           <t>🔴最高优先</t>
-        </is>
-      </c>
-    </row>
-    <row r="45" ht="16.5" customHeight="1" s="79">
-      <c r="A45" s="163" t="inlineStr">
-        <is>
-          <t>养殖</t>
-        </is>
-      </c>
-      <c r="B45" s="163" t="inlineStr">
-        <is>
-          <t>70%</t>
-        </is>
-      </c>
-      <c r="C45" s="163" t="inlineStr">
-        <is>
-          <t>2.0:1</t>
-        </is>
-      </c>
-      <c r="D45" s="163" t="inlineStr">
-        <is>
-          <t>1.400</t>
-        </is>
-      </c>
-      <c r="E45" s="163" t="inlineStr">
-        <is>
-          <t>已持仓不需现金</t>
-        </is>
-      </c>
-      <c r="F45" s="163" t="inlineStr">
-        <is>
-          <t>继续持有</t>
-        </is>
-      </c>
-      <c r="G45" s="164" t="inlineStr">
-        <is>
-          <t>✅已配置</t>
-        </is>
-      </c>
-    </row>
-    <row r="46" ht="16.5" customHeight="1" s="79">
-      <c r="A46" s="163" t="inlineStr">
-        <is>
-          <t>电池</t>
-        </is>
-      </c>
-      <c r="B46" s="163" t="inlineStr">
-        <is>
-          <t>65%</t>
-        </is>
-      </c>
-      <c r="C46" s="163" t="inlineStr">
-        <is>
-          <t>2.0:1</t>
-        </is>
-      </c>
-      <c r="D46" s="163" t="inlineStr">
-        <is>
-          <t>1.300</t>
-        </is>
-      </c>
-      <c r="E46" s="163" t="inlineStr">
-        <is>
-          <t>已持仓不需现金</t>
-        </is>
-      </c>
-      <c r="F46" s="163" t="inlineStr">
-        <is>
-          <t>继续持有</t>
-        </is>
-      </c>
-      <c r="G46" s="164" t="inlineStr">
-        <is>
-          <t>✅已配置</t>
         </is>
       </c>
     </row>
     <row r="47" ht="16.5" customHeight="1" s="79">
       <c r="A47" s="163" t="inlineStr">
         <is>
+          <t>养殖</t>
+        </is>
+      </c>
+      <c r="B47" s="163" t="inlineStr">
+        <is>
+          <t>70%</t>
+        </is>
+      </c>
+      <c r="C47" s="163" t="inlineStr">
+        <is>
+          <t>2.0:1</t>
+        </is>
+      </c>
+      <c r="D47" s="163" t="inlineStr">
+        <is>
+          <t>1.400</t>
+        </is>
+      </c>
+      <c r="E47" s="163" t="inlineStr">
+        <is>
+          <t>已持仓不需现金</t>
+        </is>
+      </c>
+      <c r="F47" s="163" t="inlineStr">
+        <is>
+          <t>继续持有</t>
+        </is>
+      </c>
+      <c r="G47" s="164" t="inlineStr">
+        <is>
+          <t>✅已配置</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="16.5" customHeight="1" s="79">
+      <c r="A48" s="163" t="inlineStr">
+        <is>
+          <t>电池</t>
+        </is>
+      </c>
+      <c r="B48" s="163" t="inlineStr">
+        <is>
+          <t>65%</t>
+        </is>
+      </c>
+      <c r="C48" s="163" t="inlineStr">
+        <is>
+          <t>2.0:1</t>
+        </is>
+      </c>
+      <c r="D48" s="163" t="inlineStr">
+        <is>
+          <t>1.300</t>
+        </is>
+      </c>
+      <c r="E48" s="163" t="inlineStr">
+        <is>
+          <t>已持仓不需现金</t>
+        </is>
+      </c>
+      <c r="F48" s="163" t="inlineStr">
+        <is>
+          <t>继续持有</t>
+        </is>
+      </c>
+      <c r="G48" s="164" t="inlineStr">
+        <is>
+          <t>✅已配置</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="16.5" customHeight="1" s="79">
+      <c r="A49" s="163" t="inlineStr">
+        <is>
           <t>核电</t>
         </is>
       </c>
-      <c r="B47" s="163" t="inlineStr">
+      <c r="B49" s="163" t="inlineStr">
         <is>
           <t>52%</t>
         </is>
       </c>
-      <c r="C47" s="163" t="inlineStr">
+      <c r="C49" s="163" t="inlineStr">
         <is>
           <t>1.5:1</t>
         </is>
       </c>
-      <c r="D47" s="163" t="inlineStr">
+      <c r="D49" s="163" t="inlineStr">
         <is>
           <t>0.780</t>
         </is>
       </c>
-      <c r="E47" s="163" t="inlineStr">
+      <c r="E49" s="163" t="inlineStr">
         <is>
           <t>10年维度
 小仓试水可行</t>
         </is>
       </c>
-      <c r="F47" s="163" t="inlineStr">
+      <c r="F49" s="163" t="inlineStr">
         <is>
           <t>不影响现金策略</t>
         </is>
       </c>
-      <c r="G47" s="167" t="inlineStr">
+      <c r="G49" s="167" t="inlineStr">
         <is>
           <t>🟡长期观察</t>
         </is>
       </c>
     </row>
-    <row r="48" ht="16.5" customHeight="1" s="79">
-      <c r="A48" s="163" t="inlineStr">
+    <row r="50">
+      <c r="A50" s="163" t="inlineStr">
         <is>
           <t>存储</t>
         </is>
       </c>
-      <c r="B48" s="163" t="inlineStr">
+      <c r="B50" s="163" t="inlineStr">
         <is>
           <t>55%</t>
         </is>
       </c>
-      <c r="C48" s="163" t="inlineStr">
+      <c r="C50" s="163" t="inlineStr">
         <is>
           <t>1.0:1</t>
         </is>
       </c>
-      <c r="D48" s="163" t="inlineStr">
+      <c r="D50" s="163" t="inlineStr">
         <is>
           <t>0.550</t>
         </is>
       </c>
-      <c r="E48" s="163" t="inlineStr">
+      <c r="E50" s="163" t="inlineStr">
         <is>
           <t>已降级</t>
         </is>
       </c>
-      <c r="F48" s="163" t="inlineStr">
+      <c r="F50" s="163" t="inlineStr">
         <is>
           <t>不动</t>
         </is>
       </c>
-      <c r="G48" s="166" t="inlineStr">
+      <c r="G50" s="166" t="inlineStr">
         <is>
           <t>❌已降级</t>
         </is>
       </c>
     </row>
-    <row r="49" ht="16.5" customHeight="1" s="79">
-      <c r="A49" s="163" t="inlineStr">
+    <row r="51">
+      <c r="A51" s="163" t="inlineStr">
         <is>
           <t>纯现金5月</t>
         </is>
       </c>
-      <c r="B49" s="163" t="inlineStr">
+      <c r="B51" s="163" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="C49" s="163" t="inlineStr">
+      <c r="C51" s="163" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="D49" s="163" t="inlineStr">
+      <c r="D51" s="163" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E49" s="163" t="inlineStr">
+      <c r="E51" s="163" t="inlineStr">
         <is>
           <t>机会成本
 可能错过短期</t>
         </is>
       </c>
-      <c r="F49" s="163" t="inlineStr">
+      <c r="F51" s="163" t="inlineStr">
         <is>
           <t>不对称博弈可接受</t>
         </is>
       </c>
-      <c r="G49" s="167" t="inlineStr">
+      <c r="G51" s="167" t="inlineStr">
         <is>
           <t>🟡可接受</t>
         </is>
       </c>
     </row>
-    <row r="50">
-      <c r="A50" s="87" t="inlineStr">
+    <row r="52">
+      <c r="A52" s="87" t="inlineStr">
         <is>
           <t>AI硬件确定性(付鹏) → 内存=AI核心瓶颈(4信源互锁) → 国产替代加速 → 稀土断供日本 → 芯片/存储/HBM长期利好 | 短期被利率↑/地缘↑压制</t>
         </is>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" s="185" t="inlineStr">
+    <row r="53">
+      <c r="A53" s="185" t="inlineStr">
         <is>
           <t>五、虚P→实P转换条件 &amp; 操作触发</t>
         </is>
       </c>
-      <c r="B51" s="145" t="n"/>
-      <c r="C51" s="145" t="n"/>
-      <c r="D51" s="145" t="n"/>
-      <c r="E51" s="145" t="n"/>
-      <c r="F51" s="145" t="n"/>
-      <c r="G51" s="145" t="n"/>
-      <c r="H51" s="146" t="n"/>
-    </row>
-    <row r="52">
-      <c r="A52" s="162" t="inlineStr">
+      <c r="B53" s="145" t="n"/>
+      <c r="C53" s="145" t="n"/>
+      <c r="D53" s="145" t="n"/>
+      <c r="E53" s="145" t="n"/>
+      <c r="F53" s="145" t="n"/>
+      <c r="G53" s="145" t="n"/>
+      <c r="H53" s="146" t="n"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="162" t="inlineStr">
         <is>
           <t>条件</t>
         </is>
       </c>
-      <c r="B52" s="180" t="inlineStr">
+      <c r="B54" s="180" t="inlineStr">
         <is>
           <t>触发信号</t>
         </is>
       </c>
-      <c r="C52" s="162" t="inlineStr">
+      <c r="C54" s="162" t="inlineStr">
         <is>
           <t>影响</t>
         </is>
       </c>
-      <c r="D52" s="162" t="inlineStr">
+      <c r="D54" s="162" t="inlineStr">
         <is>
           <t>操作</t>
         </is>
       </c>
-      <c r="E52" s="87" t="inlineStr">
+      <c r="E54" s="87" t="inlineStr">
         <is>
           <t>2026-05-30 宋鸿兵：海峡封锁→能源成本飙升</t>
         </is>
       </c>
-      <c r="F52" s="87" t="inlineStr">
+      <c r="F54" s="87" t="inlineStr">
         <is>
           <t>2026-05-30 岩松：存储1-2年产能饱和</t>
         </is>
       </c>
-      <c r="G52" s="87" t="inlineStr">
+      <c r="G54" s="87" t="inlineStr">
         <is>
           <t>2026-05-30 宋鸿兵：30年美债破5%双红线</t>
         </is>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" s="188" t="inlineStr">
+    <row r="55">
+      <c r="A55" s="188" t="inlineStr">
         <is>
           <t>达利欧落地</t>
         </is>
       </c>
-      <c r="B53" s="163" t="inlineStr">
+      <c r="B55" s="163" t="inlineStr">
         <is>
           <t>七姐妹&gt;15%回调或破200日均线</t>
         </is>
       </c>
-      <c r="C53" s="163" t="inlineStr">
+      <c r="C55" s="163" t="inlineStr">
         <is>
           <t>芯片/恒科虚P转实P</t>
         </is>
       </c>
-      <c r="D53" s="163" t="inlineStr">
+      <c r="D55" s="163" t="inlineStr">
         <is>
           <t>现金解锁→大仓位进堆叠</t>
         </is>
       </c>
     </row>
-    <row r="54">
-      <c r="A54" s="167" t="inlineStr">
+    <row r="56">
+      <c r="A56" s="167" t="inlineStr">
         <is>
           <t>李大霄落地</t>
         </is>
       </c>
-      <c r="B54" s="163" t="inlineStr">
+      <c r="B56" s="163" t="inlineStr">
         <is>
           <t>多数成分股下跌+指数拐头</t>
         </is>
       </c>
-      <c r="C54" s="163" t="inlineStr">
+      <c r="C56" s="163" t="inlineStr">
         <is>
           <t>恒科/芯片虚P转实P</t>
         </is>
       </c>
-      <c r="D54" s="163" t="inlineStr">
+      <c r="D56" s="163" t="inlineStr">
         <is>
           <t>确认系统性风险→入场</t>
         </is>
       </c>
     </row>
-    <row r="55">
-      <c r="A55" s="189" t="inlineStr">
+    <row r="57">
+      <c r="A57" s="189" t="inlineStr">
         <is>
           <t>中期选举</t>
         </is>
       </c>
-      <c r="B55" s="189" t="inlineStr">
+      <c r="B57" s="189" t="inlineStr">
         <is>
           <t>11月美股跌一波</t>
         </is>
       </c>
-      <c r="C55" s="189" t="inlineStr">
+      <c r="C57" s="189" t="inlineStr">
         <is>
           <t>你的策略触发</t>
         </is>
       </c>
-      <c r="D55" s="189" t="inlineStr">
+      <c r="D57" s="189" t="inlineStr">
         <is>
           <t>现金→长电+通富</t>
         </is>
       </c>
-      <c r="E55" s="162" t="inlineStr">
+      <c r="E57" s="162" t="inlineStr">
         <is>
           <t>落地条件</t>
         </is>
       </c>
-      <c r="F55" s="162" t="inlineStr">
+      <c r="F57" s="162" t="inlineStr">
         <is>
           <t>状态</t>
         </is>
       </c>
-      <c r="G55" s="162" t="inlineStr">
+      <c r="G57" s="162" t="inlineStr">
         <is>
           <t>权重</t>
         </is>
       </c>
-      <c r="H55" s="162" t="inlineStr">
+      <c r="H57" s="162" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="56">
-      <c r="A56" s="163" t="inlineStr">
+    <row r="58">
+      <c r="A58" s="163" t="inlineStr">
         <is>
           <t>堆叠独立</t>
         </is>
       </c>
-      <c r="B56" s="163" t="inlineStr">
+      <c r="B58" s="163" t="inlineStr">
         <is>
           <t>国内产业确定性</t>
         </is>
       </c>
-      <c r="C56" s="164" t="inlineStr">
+      <c r="C58" s="164" t="inlineStr">
         <is>
           <t>三源未提及国内封测</t>
         </is>
       </c>
-      <c r="D56" s="163" t="inlineStr">
+      <c r="D58" s="163" t="inlineStr">
         <is>
           <t>回调后优先配置</t>
         </is>
       </c>
-      <c r="E56" s="163" t="inlineStr">
+      <c r="E58" s="163" t="inlineStr">
         <is>
           <t>纳指/纳指七姐妹
 出现&gt;15%回调</t>
         </is>
       </c>
-      <c r="F56" s="165" t="inlineStr">
+      <c r="F58" s="165" t="inlineStr">
         <is>
           <t>⏳未落地
 (虚P状态)</t>
         </is>
       </c>
-      <c r="G56" s="166" t="inlineStr">
+      <c r="G58" s="166" t="inlineStr">
         <is>
           <t>⭐⭐⭐⭐⭐
 极高</t>
         </is>
       </c>
-      <c r="H56" s="163" t="inlineStr">
+      <c r="H58" s="163" t="inlineStr">
         <is>
           <t>6/4三源联动:
 芯片-2pp
@@ -3272,52 +3343,52 @@
         </is>
       </c>
     </row>
-    <row r="57">
-      <c r="A57" s="163" t="inlineStr">
+    <row r="59">
+      <c r="A59" s="163" t="inlineStr">
         <is>
           <t>李大霄
 金融界 6/4</t>
         </is>
       </c>
-      <c r="B57" s="163" t="inlineStr">
+      <c r="B59" s="163" t="inlineStr">
         <is>
           <t>美股窄牛宽熊
 仅20只创新高
 CAPE40倍→泡沫</t>
         </is>
       </c>
-      <c r="C57" s="164" t="inlineStr">
+      <c r="C59" s="164" t="inlineStr">
         <is>
           <t>🟢高度契合
 确认美股风险
 现金策略正确</t>
         </is>
       </c>
-      <c r="D57" s="163" t="inlineStr">
+      <c r="D59" s="163" t="inlineStr">
         <is>
           <t>美股全市场↓
 港股连带承压</t>
         </is>
       </c>
-      <c r="E57" s="163" t="inlineStr">
+      <c r="E59" s="163" t="inlineStr">
         <is>
           <t>纳指破200日均线
 或多数成分股下跌</t>
         </is>
       </c>
-      <c r="F57" s="165" t="inlineStr">
+      <c r="F59" s="165" t="inlineStr">
         <is>
           <t>⏳未落地
 (虚P状态)</t>
         </is>
       </c>
-      <c r="G57" s="163" t="inlineStr">
+      <c r="G59" s="163" t="inlineStr">
         <is>
           <t>⭐⭐⭐
 中高</t>
         </is>
       </c>
-      <c r="H57" s="163" t="inlineStr">
+      <c r="H59" s="163" t="inlineStr">
         <is>
           <t>6/4三源联动:
 恒科-2pp
@@ -3327,322 +3398,280 @@
         </is>
       </c>
     </row>
-    <row r="58">
-      <c r="A58" s="190" t="inlineStr">
+    <row r="60">
+      <c r="A60" s="190" t="inlineStr">
         <is>
           <t>⚡ 核心结论：三源联动确认AI泡沫风险+你的中期选举策略正确。大部分现金锁定等11月回调→大仓位进长电/通富。机会成本可接受（不对称博弈，下有保底）。虚P已记，等落地转实P。</t>
         </is>
       </c>
-      <c r="B58" s="145" t="n"/>
-      <c r="C58" s="145" t="n"/>
-      <c r="D58" s="145" t="n"/>
-      <c r="E58" s="145" t="n"/>
-      <c r="F58" s="145" t="n"/>
-      <c r="G58" s="145" t="n"/>
-      <c r="H58" s="146" t="n"/>
-    </row>
-    <row r="59">
-      <c r="A59" s="78" t="inlineStr">
+      <c r="B60" s="145" t="n"/>
+      <c r="C60" s="145" t="n"/>
+      <c r="D60" s="145" t="n"/>
+      <c r="E60" s="145" t="n"/>
+      <c r="F60" s="145" t="n"/>
+      <c r="G60" s="145" t="n"/>
+      <c r="H60" s="146" t="n"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="78" t="inlineStr">
         <is>
           <t>────────────────────────────────────────────────────────────</t>
         </is>
       </c>
     </row>
-    <row r="60">
-      <c r="A60" s="168" t="inlineStr">
+    <row r="62">
+      <c r="A62" s="168" t="inlineStr">
         <is>
           <t>🔗 三源互锁验证</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="170" t="inlineStr">
-        <is>
-          <t>达利欧 × 李大霄</t>
-        </is>
-      </c>
-      <c r="C61" s="171" t="inlineStr">
-        <is>
-          <t>✅ 强印证</t>
-        </is>
-      </c>
-      <c r="E61" s="152" t="inlineStr">
-        <is>
-          <t>AI泡沫+窄牛宽熊=同一现象两角度，互相确认</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="170" t="inlineStr">
-        <is>
-          <t>达利欧 × 知乎</t>
-        </is>
-      </c>
-      <c r="C62" s="172" t="inlineStr">
-        <is>
-          <t>⚠️ 部分矛盾</t>
-        </is>
-      </c>
-      <c r="E62" s="152" t="inlineStr">
-        <is>
-          <t>达利欧看流动性(泡沫将破) vs 知乎看估值(PE中值安全)</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="170" t="inlineStr">
         <is>
+          <t>达利欧 × 李大霄</t>
+        </is>
+      </c>
+      <c r="C63" s="171" t="inlineStr">
+        <is>
+          <t>✅ 强印证</t>
+        </is>
+      </c>
+      <c r="E63" s="152" t="inlineStr">
+        <is>
+          <t>AI泡沫+窄牛宽熊=同一现象两角度，互相确认</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="170" t="inlineStr">
+        <is>
+          <t>达利欧 × 知乎</t>
+        </is>
+      </c>
+      <c r="C64" s="172" t="inlineStr">
+        <is>
+          <t>⚠️ 部分矛盾</t>
+        </is>
+      </c>
+      <c r="E64" s="152" t="inlineStr">
+        <is>
+          <t>达利欧看流动性(泡沫将破) vs 知乎看估值(PE中值安全)</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="170" t="inlineStr">
+        <is>
           <t>三源共识</t>
         </is>
       </c>
-      <c r="C63" s="173" t="inlineStr">
+      <c r="C65" s="173" t="inlineStr">
         <is>
           <t>🔴 核心共识</t>
         </is>
       </c>
-      <c r="E63" s="152" t="inlineStr">
+      <c r="E65" s="152" t="inlineStr">
         <is>
           <t>AI龙头估值偏高+市场极度集中+中小盘已熊 → 短期风险&gt;机会</t>
         </is>
       </c>
     </row>
-    <row r="65">
-      <c r="A65" s="174" t="inlineStr">
+    <row r="66"/>
+    <row r="67">
+      <c r="A67" s="174" t="inlineStr">
         <is>
           <t>🎯 结论（虚P→实P转换条件）</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" s="170" t="inlineStr">
-        <is>
-          <t>① 达利欧信号落地条件</t>
-        </is>
-      </c>
-      <c r="C66" s="152" t="inlineStr">
-        <is>
-          <t>纳指七姐妹出现&gt;15%回调 或 纳指破200日均线</t>
-        </is>
-      </c>
-      <c r="E66" s="176" t="inlineStr">
-        <is>
-          <t>→ 芯片/恒科虚P转实P → 确认减仓信号</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" s="170" t="inlineStr">
-        <is>
-          <t>② 李大霄信号落地条件</t>
-        </is>
-      </c>
-      <c r="C67" s="152" t="inlineStr">
-        <is>
-          <t>纳指多数成分股连续下跌+指数拐头</t>
-        </is>
-      </c>
-      <c r="E67" s="176" t="inlineStr">
-        <is>
-          <t>→ 恒科/芯片虚P转实P → 确认美股系统性风险</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="170" t="inlineStr">
         <is>
-          <t>③ 你的策略触发条件</t>
+          <t>① 达利欧信号落地条件</t>
         </is>
       </c>
       <c r="C68" s="152" t="inlineStr">
         <is>
-          <t>中期选举(11月)美股跌一波 + AI回调&gt;15%</t>
+          <t>纳指七姐妹出现&gt;15%回调 或 纳指破200日均线</t>
         </is>
       </c>
       <c r="E68" s="176" t="inlineStr">
         <is>
-          <t>→ 现金入场 → 大仓位进堆叠/先进封装</t>
+          <t>→ 芯片/恒科虚P转实P → 确认减仓信号</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="170" t="inlineStr">
         <is>
+          <t>② 李大霄信号落地条件</t>
+        </is>
+      </c>
+      <c r="C69" s="152" t="inlineStr">
+        <is>
+          <t>纳指多数成分股连续下跌+指数拐头</t>
+        </is>
+      </c>
+      <c r="E69" s="176" t="inlineStr">
+        <is>
+          <t>→ 恒科/芯片虚P转实P → 确认美股系统性风险</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="170" t="inlineStr">
+        <is>
+          <t>③ 你的策略触发条件</t>
+        </is>
+      </c>
+      <c r="C70" s="152" t="inlineStr">
+        <is>
+          <t>中期选举(11月)美股跌一波 + AI回调&gt;15%</t>
+        </is>
+      </c>
+      <c r="E70" s="176" t="inlineStr">
+        <is>
+          <t>→ 现金入场 → 大仓位进堆叠/先进封装</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="170" t="inlineStr">
+        <is>
           <t>④ 堆叠赛道独立性</t>
         </is>
       </c>
-      <c r="C69" s="152" t="inlineStr">
+      <c r="C71" s="152" t="inlineStr">
         <is>
           <t>国内产业确定性，三源均未提及国内封测</t>
         </is>
       </c>
-      <c r="E69" s="176" t="inlineStr">
+      <c r="E71" s="176" t="inlineStr">
         <is>
           <t>→ 不受美股泡沫直接影响 → 等回调后优先配置</t>
         </is>
       </c>
     </row>
-    <row r="71">
-      <c r="A71" s="177" t="inlineStr">
+    <row r="72"/>
+    <row r="73">
+      <c r="A73" s="177" t="inlineStr">
         <is>
           <t>⚡ 一句话：三源确认AI泡沫风险+你的中期选举策略正确。虚P已记，等落地转实P。现金为王，堆叠赛道等回调后大仓位进。</t>
         </is>
       </c>
     </row>
-    <row r="75">
-      <c r="A75" s="87" t="inlineStr">
-        <is>
-          <t>🤖 人形机器人半年事件链</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" s="78" t="n"/>
-    </row>
+    <row r="74"/>
+    <row r="75"/>
+    <row r="76"/>
     <row r="77">
       <c r="A77" s="87" t="inlineStr">
         <is>
-          <t>2026-03-23 机器人ETF暴跌-4.1%至0.909：市场恐慌+AI回调</t>
+          <t>🤖 人形机器人半年事件链</t>
         </is>
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="87" t="inlineStr">
-        <is>
-          <t>2026-04-08 机器人ETF暴涨+6.4%至0.967：人形机器人产业催化</t>
-        </is>
-      </c>
-      <c r="D78" s="78" t="n"/>
+      <c r="A78" s="78" t="n"/>
     </row>
     <row r="79">
       <c r="A79" s="87" t="inlineStr">
         <is>
-          <t>2026-05-07~22 机器人连续上涨：ETF 1.056→1.216(+15%)，宇树科技73天过会</t>
-        </is>
-      </c>
-      <c r="D79" s="78" t="n"/>
+          <t>2026-03-23 机器人ETF暴跌-4.1%至0.909：市场恐慌+AI回调</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="87" t="inlineStr">
         <is>
+          <t>2026-04-08 机器人ETF暴涨+6.4%至0.967：人形机器人产业催化</t>
+        </is>
+      </c>
+      <c r="D80" s="78" t="n"/>
+    </row>
+    <row r="81">
+      <c r="A81" s="87" t="inlineStr">
+        <is>
+          <t>2026-05-07~22 机器人连续上涨：ETF 1.056→1.216(+15%)，宇树科技73天过会</t>
+        </is>
+      </c>
+      <c r="D81" s="78" t="n"/>
+    </row>
+    <row r="82">
+      <c r="A82" s="87" t="inlineStr">
+        <is>
           <t>2026-05-25~06-02 机器人回调：1.216→1.122(-7.7%)，仍处强势区间</t>
         </is>
       </c>
-      <c r="D80" s="78" t="n"/>
-    </row>
-    <row r="81">
-      <c r="A81" s="90" t="inlineStr">
+      <c r="D82" s="78" t="n"/>
+    </row>
+    <row r="83">
+      <c r="A83" s="90" t="inlineStr">
         <is>
           <t>2026-06-04 【保持观察】霍尔木兹海峡Day 12：伊朗暂停谈判+美众议院限制动武，WTI $96→$91-93回落，方向趋于缓和</t>
         </is>
       </c>
-      <c r="B81" s="91" t="n"/>
-      <c r="C81" s="91" t="n"/>
-      <c r="D81" s="91" t="n"/>
-      <c r="E81" s="91" t="n"/>
-      <c r="F81" s="91" t="n"/>
-      <c r="G81" s="91" t="n"/>
-      <c r="H81" s="91" t="n"/>
-    </row>
-    <row r="82">
-      <c r="A82" s="147" t="inlineStr">
+      <c r="B83" s="91" t="n"/>
+      <c r="C83" s="91" t="n"/>
+      <c r="D83" s="91" t="n"/>
+      <c r="E83" s="91" t="n"/>
+      <c r="F83" s="91" t="n"/>
+      <c r="G83" s="91" t="n"/>
+      <c r="H83" s="91" t="n"/>
+    </row>
+    <row r="84">
+      <c r="A84" s="147" t="inlineStr">
         <is>
           <t>🔔 待重仓监控</t>
         </is>
       </c>
     </row>
-    <row r="83">
-      <c r="A83" s="148" t="inlineStr">
+    <row r="85">
+      <c r="A85" s="148" t="inlineStr">
         <is>
           <t>标的</t>
         </is>
       </c>
-      <c r="B83" s="148" t="inlineStr">
+      <c r="B85" s="148" t="inlineStr">
         <is>
           <t>状态</t>
         </is>
       </c>
-      <c r="C83" s="148" t="inlineStr">
+      <c r="C85" s="148" t="inlineStr">
         <is>
           <t>当前P/价格</t>
         </is>
       </c>
-      <c r="D83" s="148" t="inlineStr">
+      <c r="D85" s="148" t="inlineStr">
         <is>
           <t>最新信号</t>
         </is>
       </c>
-      <c r="E83" s="148" t="inlineStr">
+      <c r="E85" s="148" t="inlineStr">
         <is>
           <t>触发条件</t>
         </is>
       </c>
-      <c r="F83" s="148" t="inlineStr">
+      <c r="F85" s="148" t="inlineStr">
         <is>
           <t>距离触发</t>
         </is>
       </c>
-      <c r="G83" s="148" t="inlineStr">
+      <c r="G85" s="148" t="inlineStr">
         <is>
           <t>跟踪日期</t>
         </is>
       </c>
-    </row>
-    <row r="84">
-      <c r="A84" s="87" t="inlineStr">
-        <is>
-          <t>玻璃基板</t>
-        </is>
-      </c>
-      <c r="B84" s="87" t="inlineStr">
-        <is>
-          <t>深南电路002916/兴森科技002436</t>
-        </is>
-      </c>
-      <c r="C84" s="87" t="inlineStr">
-        <is>
-          <t>观察中</t>
-        </is>
-      </c>
-      <c r="D84" s="87" t="inlineStr">
-        <is>
-          <t>蒋宇飞：玻璃基板大规模应用2028年，5-10年赛道</t>
-        </is>
-      </c>
-      <c r="E84" s="87" t="inlineStr">
-        <is>
-          <t>AI基建+国产替代加速</t>
-        </is>
-      </c>
-      <c r="F84" s="87" t="inlineStr">
-        <is>
-          <t>中长期</t>
-        </is>
-      </c>
-      <c r="G84" s="87" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" s="78" t="n"/>
-      <c r="B85" s="78" t="n"/>
-      <c r="C85" s="78" t="n"/>
-      <c r="D85" s="78" t="n"/>
-      <c r="E85" s="78" t="n"/>
-      <c r="F85" s="78" t="n"/>
-      <c r="G85" s="78" t="n"/>
-      <c r="H85" s="78" t="n"/>
     </row>
     <row r="86">
       <c r="A86" s="87" t="inlineStr">
         <is>
-          <t>油气对冲</t>
+          <t>玻璃基板</t>
         </is>
       </c>
       <c r="B86" s="87" t="inlineStr">
         <is>
-          <t>华宝油气162411</t>
+          <t>深南电路002916/兴森科技002436</t>
         </is>
       </c>
       <c r="C86" s="87" t="inlineStr">
@@ -3652,17 +3681,17 @@
       </c>
       <c r="D86" s="87" t="inlineStr">
         <is>
-          <t>宋鸿兵：霍尔木兹封锁3个月，85%投资者押注回落=幻觉</t>
+          <t>蒋宇飞：玻璃基板大规模应用2028年，5-10年赛道</t>
         </is>
       </c>
       <c r="E86" s="87" t="inlineStr">
         <is>
-          <t>油价冲150或海峡持续封锁</t>
+          <t>AI基建+国产替代加速</t>
         </is>
       </c>
       <c r="F86" s="87" t="inlineStr">
         <is>
-          <t>短期</t>
+          <t>中长期</t>
         </is>
       </c>
       <c r="G86" s="87" t="inlineStr">
@@ -3670,1083 +3699,1052 @@
           <t>2026-06-02</t>
         </is>
       </c>
-      <c r="H86" s="78" t="inlineStr">
-        <is>
-          <t>小仓位试水，不对称博弈</t>
-        </is>
-      </c>
     </row>
     <row r="87">
-      <c r="A87" s="87" t="inlineStr">
-        <is>
-          <t>银行板块(512800)</t>
-        </is>
-      </c>
-      <c r="B87" s="87" t="inlineStr">
-        <is>
-          <t>弱势</t>
-        </is>
-      </c>
-      <c r="C87" s="87" t="inlineStr">
-        <is>
-          <t>P:50% 虚P-2pp</t>
-        </is>
-      </c>
-      <c r="D87" s="87" t="inlineStr">
-        <is>
-          <t>去杠杆+信贷收缩，ETF跌-1%，无催化</t>
-        </is>
-      </c>
-      <c r="E87" s="87" t="inlineStr">
-        <is>
-          <t>不建议加仓</t>
-        </is>
-      </c>
-      <c r="F87" s="87" t="inlineStr">
-        <is>
-          <t>短期</t>
-        </is>
-      </c>
-      <c r="G87" s="87" t="inlineStr">
-        <is>
-          <t>2026-06-03</t>
-        </is>
-      </c>
-      <c r="H87" s="78" t="inlineStr">
-        <is>
-          <t>银行ETF持续阴跌</t>
-        </is>
-      </c>
+      <c r="A87" s="78" t="n"/>
+      <c r="B87" s="78" t="n"/>
+      <c r="C87" s="78" t="n"/>
+      <c r="D87" s="78" t="n"/>
+      <c r="E87" s="78" t="n"/>
+      <c r="F87" s="78" t="n"/>
+      <c r="G87" s="78" t="n"/>
+      <c r="H87" s="78" t="n"/>
     </row>
     <row r="88">
       <c r="A88" s="87" t="inlineStr">
         <is>
-          <t>人形机器人(562500)</t>
+          <t>油气对冲</t>
         </is>
       </c>
       <c r="B88" s="87" t="inlineStr">
         <is>
-          <t>强势</t>
+          <t>华宝油气162411</t>
         </is>
       </c>
       <c r="C88" s="87" t="inlineStr">
         <is>
-          <t>P:58%(估)</t>
+          <t>观察中</t>
         </is>
       </c>
       <c r="D88" s="87" t="inlineStr">
         <is>
-          <t>宇树科技73天过会，ETF涨+11%</t>
+          <t>宋鸿兵：霍尔木兹封锁3个月，85%投资者押注回落=幻觉</t>
         </is>
       </c>
       <c r="E88" s="87" t="inlineStr">
         <is>
-          <t>重点关注</t>
+          <t>油价冲150或海峡持续封锁</t>
         </is>
       </c>
       <c r="F88" s="87" t="inlineStr">
         <is>
-          <t>中期</t>
+          <t>短期</t>
         </is>
       </c>
       <c r="G88" s="87" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="H88" s="78" t="inlineStr">
         <is>
-          <t>平安先进制造+永赢先进制造</t>
+          <t>小仓位试水，不对称博弈</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="87" t="inlineStr">
         <is>
-          <t>存储赛道(5只A股)</t>
+          <t>银行板块(512800)</t>
         </is>
       </c>
       <c r="B89" s="87" t="inlineStr">
         <is>
-          <t>❌降级观察</t>
+          <t>弱势</t>
         </is>
       </c>
       <c r="C89" s="87" t="inlineStr">
         <is>
-          <t>P:55% 安全边际不足</t>
+          <t>P:50% 虚P-2pp</t>
         </is>
       </c>
       <c r="D89" s="87" t="inlineStr">
         <is>
-          <t>兆易¥525(+81%)/江波龙¥569/佰维¥341→PE天际线，向上空间&lt;向下空间</t>
+          <t>去杠杆+信贷收缩，ETF跌-1%，无催化</t>
         </is>
       </c>
       <c r="E89" s="87" t="inlineStr">
         <is>
-          <t>等中期选举大跌15%+</t>
+          <t>不建议加仓</t>
         </is>
       </c>
       <c r="F89" s="87" t="inlineStr">
         <is>
-          <t>中期</t>
+          <t>短期</t>
         </is>
       </c>
       <c r="G89" s="87" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="H89" s="78" t="inlineStr">
         <is>
-          <t>降级：存储涨完轮到堆叠，安全边际已不足</t>
+          <t>银行ETF持续阴跌</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="87" t="inlineStr">
         <is>
-          <t>澜起科技(688008)</t>
+          <t>人形机器人(562500)</t>
         </is>
       </c>
       <c r="B90" s="87" t="inlineStr">
         <is>
+          <t>强势</t>
+        </is>
+      </c>
+      <c r="C90" s="87" t="inlineStr">
+        <is>
+          <t>P:58%(估)</t>
+        </is>
+      </c>
+      <c r="D90" s="87" t="inlineStr">
+        <is>
+          <t>宇树科技73天过会，ETF涨+11%</t>
+        </is>
+      </c>
+      <c r="E90" s="87" t="inlineStr">
+        <is>
+          <t>重点关注</t>
+        </is>
+      </c>
+      <c r="F90" s="87" t="inlineStr">
+        <is>
+          <t>中期</t>
+        </is>
+      </c>
+      <c r="G90" s="87" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="H90" s="78" t="inlineStr">
+        <is>
+          <t>平安先进制造+永赢先进制造</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="87" t="inlineStr">
+        <is>
+          <t>存储赛道(5只A股)</t>
+        </is>
+      </c>
+      <c r="B91" s="87" t="inlineStr">
+        <is>
           <t>❌降级观察</t>
         </is>
       </c>
-      <c r="C90" s="87" t="inlineStr">
-        <is>
-          <t>P:55% 安全边际中等</t>
-        </is>
-      </c>
-      <c r="D90" s="87" t="inlineStr">
-        <is>
-          <t>DDR5接口芯片，温和上涨，但存储赛道整体降级</t>
-        </is>
-      </c>
-      <c r="E90" s="87" t="inlineStr">
-        <is>
-          <t>等大跌15%+</t>
-        </is>
-      </c>
-      <c r="F90" s="87" t="inlineStr">
+      <c r="C91" s="87" t="inlineStr">
+        <is>
+          <t>P:55% 安全边际不足</t>
+        </is>
+      </c>
+      <c r="D91" s="87" t="inlineStr">
+        <is>
+          <t>兆易¥525(+81%)/江波龙¥569/佰维¥341→PE天际线，向上空间&lt;向下空间</t>
+        </is>
+      </c>
+      <c r="E91" s="87" t="inlineStr">
+        <is>
+          <t>等中期选举大跌15%+</t>
+        </is>
+      </c>
+      <c r="F91" s="87" t="inlineStr">
         <is>
           <t>中期</t>
         </is>
       </c>
-      <c r="G90" s="87" t="inlineStr">
+      <c r="G91" s="87" t="inlineStr">
         <is>
           <t>2026-06-04</t>
         </is>
       </c>
-      <c r="H90" s="78" t="inlineStr">
-        <is>
-          <t>降级：存储赛道尾声</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" s="92" t="inlineStr">
-        <is>
-          <t>🔥堆叠/先进封装赛道（蒋宇飞"星光纯叠"框架）</t>
+      <c r="H91" s="78" t="inlineStr">
+        <is>
+          <t>降级：存储涨完轮到堆叠，安全边际已不足</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="87" t="inlineStr">
         <is>
+          <t>澜起科技(688008)</t>
+        </is>
+      </c>
+      <c r="B92" s="87" t="inlineStr">
+        <is>
+          <t>❌降级观察</t>
+        </is>
+      </c>
+      <c r="C92" s="87" t="inlineStr">
+        <is>
+          <t>P:55% 安全边际中等</t>
+        </is>
+      </c>
+      <c r="D92" s="87" t="inlineStr">
+        <is>
+          <t>DDR5接口芯片，温和上涨，但存储赛道整体降级</t>
+        </is>
+      </c>
+      <c r="E92" s="87" t="inlineStr">
+        <is>
+          <t>等大跌15%+</t>
+        </is>
+      </c>
+      <c r="F92" s="87" t="inlineStr">
+        <is>
+          <t>中期</t>
+        </is>
+      </c>
+      <c r="G92" s="87" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="H92" s="78" t="inlineStr">
+        <is>
+          <t>降级：存储赛道尾声</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="92" t="inlineStr">
+        <is>
+          <t>🔥堆叠/先进封装赛道（蒋宇飞"星光纯叠"框架）</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="87" t="inlineStr">
+        <is>
           <t>长电科技(600584)</t>
         </is>
       </c>
-      <c r="B92" s="87" t="inlineStr">
+      <c r="B94" s="87" t="inlineStr">
         <is>
           <t>🔴核心标的</t>
         </is>
       </c>
-      <c r="C92" s="87" t="inlineStr">
+      <c r="C94" s="87" t="inlineStr">
         <is>
           <t>P:75%+ PE30x</t>
         </is>
       </c>
-      <c r="D92" s="87" t="inlineStr">
+      <c r="D94" s="87" t="inlineStr">
         <is>
           <t>全球第三大封测厂，2.5D/3D量产级，客户广度最强（高通/海思/TI）</t>
         </is>
       </c>
-      <c r="E92" s="87" t="inlineStr">
+      <c r="E94" s="87" t="inlineStr">
         <is>
           <t>等中期选举大跌</t>
         </is>
       </c>
-      <c r="F92" s="87" t="inlineStr">
+      <c r="F94" s="87" t="inlineStr">
         <is>
           <t>中期</t>
         </is>
       </c>
-      <c r="G92" s="87" t="inlineStr">
+      <c r="G94" s="87" t="inlineStr">
         <is>
           <t>2026-06-04</t>
         </is>
       </c>
-      <c r="H92" s="78" t="inlineStr">
+      <c r="H94" s="78" t="inlineStr">
         <is>
           <t>安全边际大，堆叠赛道首选</t>
         </is>
       </c>
     </row>
-    <row r="93">
-      <c r="A93" s="87" t="inlineStr">
+    <row r="95">
+      <c r="A95" s="87" t="inlineStr">
         <is>
           <t>通富微电(002156)</t>
         </is>
       </c>
-      <c r="B93" s="87" t="inlineStr">
+      <c r="B95" s="87" t="inlineStr">
         <is>
           <t>🔴核心标的</t>
         </is>
       </c>
-      <c r="C93" s="87" t="inlineStr">
+      <c r="C95" s="87" t="inlineStr">
         <is>
           <t>P:75%+ 待查PE</t>
         </is>
       </c>
-      <c r="D93" s="87" t="inlineStr">
+      <c r="D95" s="87" t="inlineStr">
         <is>
           <t>AMD封测全线突破通道，2.5D量产，MI300X参与，不可替代</t>
         </is>
       </c>
-      <c r="E93" s="87" t="inlineStr">
+      <c r="E95" s="87" t="inlineStr">
         <is>
           <t>等中期选举大跌</t>
         </is>
       </c>
-      <c r="F93" s="87" t="inlineStr">
+      <c r="F95" s="87" t="inlineStr">
         <is>
           <t>中期</t>
         </is>
       </c>
-      <c r="G93" s="87" t="inlineStr">
+      <c r="G95" s="87" t="inlineStr">
         <is>
           <t>2026-06-04</t>
         </is>
       </c>
-      <c r="H93" s="78" t="inlineStr">
+      <c r="H95" s="78" t="inlineStr">
         <is>
           <t>安全边际中偏大，与长电各占一半</t>
         </is>
       </c>
     </row>
-    <row r="94">
-      <c r="A94" s="78" t="n"/>
-    </row>
     <row r="96">
-      <c r="A96" s="158" t="inlineStr">
+      <c r="A96" s="78" t="n"/>
+    </row>
+    <row r="97"/>
+    <row r="98">
+      <c r="A98" s="158" t="inlineStr">
         <is>
           <t>📖 机制库 v3（2026-06-04 经小龙虾审核修订）</t>
         </is>
       </c>
     </row>
-    <row r="97">
-      <c r="A97" s="203" t="inlineStr">
+    <row r="99">
+      <c r="A99" s="203" t="inlineStr">
         <is>
           <t>[机制3v3] 现金锁定系数（CLC）— 平方衰减版</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" s="204" t="inlineStr">
-        <is>
-          <t>叫什么</t>
-        </is>
-      </c>
-      <c r="B98" s="87" t="inlineStr">
-        <is>
-          <t>现金锁定系数（CLC）v3</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" s="204" t="inlineStr">
-        <is>
-          <t>公式</t>
-        </is>
-      </c>
-      <c r="B99" s="87" t="inlineStr">
-        <is>
-          <t>CLC = 信号概率 × 互锁强度 × 时间衰减²</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="204" t="inlineStr">
         <is>
-          <t>时间衰减</t>
+          <t>叫什么</t>
         </is>
       </c>
       <c r="B100" s="87" t="inlineStr">
         <is>
-          <t>T = (距触发月数/12)²</t>
-        </is>
-      </c>
-      <c r="C100" s="87" t="inlineStr">
-        <is>
-          <t>6月=(5/12)²=0.174</t>
-        </is>
-      </c>
-      <c r="D100" s="87" t="inlineStr">
-        <is>
-          <t>11月=0</t>
+          <t>现金锁定系数（CLC）v3</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="204" t="inlineStr">
         <is>
-          <t>为什么平方</t>
+          <t>公式</t>
         </is>
       </c>
       <c r="B101" s="87" t="inlineStr">
         <is>
-          <t>线性衰减导致越近触发日锁得越少（反直觉）</t>
-        </is>
-      </c>
-      <c r="C101" s="87" t="inlineStr">
-        <is>
-          <t>平方函数：远离时多锁，临近时少锁</t>
-        </is>
-      </c>
-      <c r="D101" s="87" t="inlineStr">
-        <is>
-          <t>小龙虾审核通过</t>
+          <t>CLC = 信号概率 × 互锁强度 × 时间衰减²</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="204" t="inlineStr">
         <is>
-          <t>信号概率</t>
+          <t>时间衰减</t>
         </is>
       </c>
       <c r="B102" s="87" t="inlineStr">
         <is>
-          <t>动态更新，每月审查</t>
+          <t>T = (距触发月数/12)²</t>
         </is>
       </c>
       <c r="C102" s="87" t="inlineStr">
         <is>
-          <t>底线55%（达利欧区间下沿）</t>
+          <t>6月=(5/12)²=0.174</t>
         </is>
       </c>
       <c r="D102" s="87" t="inlineStr">
         <is>
-          <t>上限85%（达利欧区间上沿）</t>
+          <t>11月=0</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="204" t="inlineStr">
         <is>
-          <t>互锁强度</t>
+          <t>为什么平方</t>
         </is>
       </c>
       <c r="B103" s="87" t="inlineStr">
         <is>
-          <t>三源强互锁=1.0</t>
+          <t>线性衰减导致越近触发日锁得越少（反直觉）</t>
         </is>
       </c>
       <c r="C103" s="87" t="inlineStr">
         <is>
-          <t>达利欧6月修正&gt;2次→降级0.85</t>
+          <t>平方函数：远离时多锁，临近时少锁</t>
         </is>
       </c>
       <c r="D103" s="87" t="inlineStr">
         <is>
-          <t>有原因修正不降级</t>
+          <t>小龙虾审核通过</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="204" t="inlineStr">
         <is>
-          <t>当前值</t>
+          <t>信号概率</t>
         </is>
       </c>
       <c r="B104" s="87" t="inlineStr">
         <is>
-          <t>0.70 × 1.0 × (5/12)² = 0.122</t>
+          <t>动态更新，每月审查</t>
         </is>
       </c>
       <c r="C104" s="87" t="inlineStr">
         <is>
-          <t>→ 锁定12.2%现金</t>
+          <t>底线55%（达利欧区间下沿）</t>
         </is>
       </c>
       <c r="D104" s="87" t="inlineStr">
         <is>
-          <t>可用87.8%</t>
+          <t>上限85%（达利欧区间上沿）</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="204" t="inlineStr">
         <is>
+          <t>互锁强度</t>
+        </is>
+      </c>
+      <c r="B105" s="87" t="inlineStr">
+        <is>
+          <t>三源强互锁=1.0</t>
+        </is>
+      </c>
+      <c r="C105" s="87" t="inlineStr">
+        <is>
+          <t>达利欧6月修正&gt;2次→降级0.85</t>
+        </is>
+      </c>
+      <c r="D105" s="87" t="inlineStr">
+        <is>
+          <t>有原因修正不降级</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="204" t="inlineStr">
+        <is>
+          <t>当前值</t>
+        </is>
+      </c>
+      <c r="B106" s="87" t="inlineStr">
+        <is>
+          <t>0.70 × 1.0 × (5/12)² = 0.122</t>
+        </is>
+      </c>
+      <c r="C106" s="87" t="inlineStr">
+        <is>
+          <t>→ 锁定12.2%现金</t>
+        </is>
+      </c>
+      <c r="D106" s="87" t="inlineStr">
+        <is>
+          <t>可用87.8%</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="204" t="inlineStr">
+        <is>
           <t>每月重算</t>
         </is>
       </c>
-      <c r="B105" s="87" t="inlineStr">
+      <c r="B107" s="87" t="inlineStr">
         <is>
           <t>信号概率按计分板更新</t>
         </is>
       </c>
-      <c r="C105" s="87" t="inlineStr">
+      <c r="C107" s="87" t="inlineStr">
         <is>
           <t>时间衰减自动重算</t>
         </is>
       </c>
     </row>
-    <row r="107">
-      <c r="A107" s="203" t="inlineStr">
+    <row r="108"/>
+    <row r="109">
+      <c r="A109" s="203" t="inlineStr">
         <is>
           <t>[机制4v3] 折后仓位计算 — 4级分级版</t>
-        </is>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" s="204" t="inlineStr">
-        <is>
-          <t>叫什么</t>
-        </is>
-      </c>
-      <c r="B108" s="87" t="inlineStr">
-        <is>
-          <t>折后仓位（Folded Allocation）v3</t>
-        </is>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" s="204" t="inlineStr">
-        <is>
-          <t>公式</t>
-        </is>
-      </c>
-      <c r="B109" s="87" t="inlineStr">
-        <is>
-          <t>折后仓位% = 原目标仓位% × (1 - CLC × β系数)</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="204" t="inlineStr">
         <is>
-          <t>4级分级</t>
+          <t>叫什么</t>
         </is>
       </c>
       <c r="B110" s="87" t="inlineStr">
         <is>
-          <t>L1高度暴露β=0.8（通富-AMD独供）</t>
-        </is>
-      </c>
-      <c r="C110" s="87" t="inlineStr">
-        <is>
-          <t>L2中度暴露β=0.5（长电-客户多元）</t>
+          <t>折后仓位（Folded Allocation）v3</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="204" t="inlineStr">
         <is>
-          <t>分级继续</t>
+          <t>公式</t>
         </is>
       </c>
       <c r="B111" s="87" t="inlineStr">
         <is>
-          <t>L3弱相关β=0.1（养殖）</t>
-        </is>
-      </c>
-      <c r="C111" s="87" t="inlineStr">
-        <is>
-          <t>L4反向受益β=-0.3（黄金）</t>
+          <t>折后仓位% = 原目标仓位% × (1 - CLC × β系数)</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="204" t="inlineStr">
         <is>
-          <t>为什么分级</t>
+          <t>4级分级</t>
         </is>
       </c>
       <c r="B112" s="87" t="inlineStr">
         <is>
-          <t>不同标的受AI泡沫影响不同</t>
+          <t>L1高度暴露β=0.8（通富-AMD独供）</t>
         </is>
       </c>
       <c r="C112" s="87" t="inlineStr">
         <is>
-          <t>通富只有AMD一根柱子</t>
-        </is>
-      </c>
-      <c r="D112" s="87" t="inlineStr">
-        <is>
-          <t>长电客户多元化</t>
+          <t>L2中度暴露β=0.5（长电-客户多元）</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="204" t="inlineStr">
         <is>
-          <t>当前计算</t>
+          <t>分级继续</t>
         </is>
       </c>
       <c r="B113" s="87" t="inlineStr">
         <is>
-          <t>通富:33%×(1-0.122×0.8)=30.1%</t>
+          <t>L3弱相关β=0.1（养殖）</t>
         </is>
       </c>
       <c r="C113" s="87" t="inlineStr">
         <is>
-          <t>长电:37%×(1-0.122×0.5)=34.7%</t>
+          <t>L4反向受益β=-0.3（黄金）</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="204" t="inlineStr">
         <is>
+          <t>为什么分级</t>
+        </is>
+      </c>
+      <c r="B114" s="87" t="inlineStr">
+        <is>
+          <t>不同标的受AI泡沫影响不同</t>
+        </is>
+      </c>
+      <c r="C114" s="87" t="inlineStr">
+        <is>
+          <t>通富只有AMD一根柱子</t>
+        </is>
+      </c>
+      <c r="D114" s="87" t="inlineStr">
+        <is>
+          <t>长电客户多元化</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="204" t="inlineStr">
+        <is>
+          <t>当前计算</t>
+        </is>
+      </c>
+      <c r="B115" s="87" t="inlineStr">
+        <is>
+          <t>通富:33%×(1-0.122×0.8)=30.1%</t>
+        </is>
+      </c>
+      <c r="C115" s="87" t="inlineStr">
+        <is>
+          <t>长电:37%×(1-0.122×0.5)=34.7%</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="204" t="inlineStr">
+        <is>
           <t>分级逻辑</t>
         </is>
       </c>
-      <c r="B114" s="87" t="inlineStr">
+      <c r="B116" s="87" t="inlineStr">
         <is>
           <t>按切断条件分两级：扛得住vs扛不住</t>
         </is>
       </c>
-      <c r="C114" s="87" t="inlineStr">
+      <c r="C116" s="87" t="inlineStr">
         <is>
           <t>不是连续β，是二值判断</t>
         </is>
       </c>
-      <c r="D114" s="87" t="inlineStr">
+      <c r="D116" s="87" t="inlineStr">
         <is>
           <t>小龙虾建议</t>
         </is>
       </c>
     </row>
-    <row r="116">
-      <c r="A116" s="203" t="inlineStr">
+    <row r="117"/>
+    <row r="118">
+      <c r="A118" s="203" t="inlineStr">
         <is>
           <t>[机制5v3] 虚P→实P转换 — 确认窗口+因果链版</t>
-        </is>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" s="204" t="inlineStr">
-        <is>
-          <t>叫什么</t>
-        </is>
-      </c>
-      <c r="B117" s="87" t="inlineStr">
-        <is>
-          <t>虚P→实P转换 v3</t>
-        </is>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" s="204" t="inlineStr">
-        <is>
-          <t>视觉信号</t>
-        </is>
-      </c>
-      <c r="B118" s="87" t="inlineStr">
-        <is>
-          <t>纳指七姐妹&gt;15%回调（从52周高）</t>
-        </is>
-      </c>
-      <c r="C118" s="87" t="inlineStr">
-        <is>
-          <t>或破200日均线</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="204" t="inlineStr">
         <is>
-          <t>确认窗口</t>
+          <t>叫什么</t>
         </is>
       </c>
       <c r="B119" s="87" t="inlineStr">
         <is>
-          <t>跌穿15%后维持5个交易日不反弹</t>
-        </is>
-      </c>
-      <c r="C119" s="87" t="inlineStr">
-        <is>
-          <t>防单日噪音和假触发</t>
-        </is>
-      </c>
-      <c r="D119" s="87" t="inlineStr">
-        <is>
-          <t>小龙虾建议</t>
+          <t>虚P→实P转换 v3</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="204" t="inlineStr">
         <is>
-          <t>因果链</t>
+          <t>视觉信号</t>
         </is>
       </c>
       <c r="B120" s="87" t="inlineStr">
         <is>
-          <t>需至少2条佐证：</t>
+          <t>纳指七姐妹&gt;15%回调（从52周高）</t>
         </is>
       </c>
       <c r="C120" s="87" t="inlineStr">
         <is>
-          <t>①英伟达/AMD下调指引</t>
-        </is>
-      </c>
-      <c r="D120" s="87" t="inlineStr">
-        <is>
-          <t>②AI ETF资金流出</t>
+          <t>或破200日均线</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="204" t="inlineStr">
         <is>
-          <t>因果链继续</t>
+          <t>确认窗口</t>
         </is>
       </c>
       <c r="B121" s="87" t="inlineStr">
         <is>
-          <t>③投行下调AI评级</t>
+          <t>跌穿15%后维持5个交易日不反弹</t>
         </is>
       </c>
       <c r="C121" s="87" t="inlineStr">
         <is>
-          <t>④Mag7裁员/削减开支</t>
+          <t>防单日噪音和假触发</t>
+        </is>
+      </c>
+      <c r="D121" s="87" t="inlineStr">
+        <is>
+          <t>小龙虾建议</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="204" t="inlineStr">
         <is>
-          <t>为什么加因果</t>
+          <t>因果链</t>
         </is>
       </c>
       <c r="B122" s="87" t="inlineStr">
         <is>
-          <t>15%下跌可能是地缘冲击不是AI泡沫</t>
+          <t>需至少2条佐证：</t>
         </is>
       </c>
       <c r="C122" s="87" t="inlineStr">
         <is>
-          <t>两者操作完全不同</t>
+          <t>①英伟达/AMD下调指引</t>
         </is>
       </c>
       <c r="D122" s="87" t="inlineStr">
         <is>
-          <t>必须区分原因</t>
+          <t>②AI ETF资金流出</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="204" t="inlineStr">
         <is>
+          <t>因果链继续</t>
+        </is>
+      </c>
+      <c r="B123" s="87" t="inlineStr">
+        <is>
+          <t>③投行下调AI评级</t>
+        </is>
+      </c>
+      <c r="C123" s="87" t="inlineStr">
+        <is>
+          <t>④Mag7裁员/削减开支</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="204" t="inlineStr">
+        <is>
+          <t>为什么加因果</t>
+        </is>
+      </c>
+      <c r="B124" s="87" t="inlineStr">
+        <is>
+          <t>15%下跌可能是地缘冲击不是AI泡沫</t>
+        </is>
+      </c>
+      <c r="C124" s="87" t="inlineStr">
+        <is>
+          <t>两者操作完全不同</t>
+        </is>
+      </c>
+      <c r="D124" s="87" t="inlineStr">
+        <is>
+          <t>必须区分原因</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="204" t="inlineStr">
+        <is>
           <t>转换后</t>
         </is>
       </c>
-      <c r="B123" s="87" t="inlineStr">
+      <c r="B125" s="87" t="inlineStr">
         <is>
           <t>虚P转实P→计入P值</t>
         </is>
       </c>
-      <c r="C123" s="87" t="inlineStr">
+      <c r="C125" s="87" t="inlineStr">
         <is>
           <t>CLC→0现金全解锁</t>
         </is>
       </c>
-      <c r="D123" s="87" t="inlineStr">
+      <c r="D125" s="87" t="inlineStr">
         <is>
           <t>折后仓位→恢复原目标</t>
         </is>
       </c>
     </row>
-    <row r="125">
-      <c r="A125" s="205" t="inlineStr">
+    <row r="126"/>
+    <row r="127">
+      <c r="A127" s="205" t="inlineStr">
         <is>
           <t>[信号计分板] 每日更新，驱动信号概率动态调整</t>
         </is>
       </c>
     </row>
-    <row r="126">
-      <c r="A126" s="204" t="inlineStr">
+    <row r="128">
+      <c r="A128" s="204" t="inlineStr">
         <is>
           <t>泡沫正向信号</t>
         </is>
       </c>
-      <c r="B126" s="87" t="inlineStr">
+      <c r="B128" s="87" t="inlineStr">
         <is>
           <t>Mag7单日跌&gt;3% → +1</t>
         </is>
       </c>
-      <c r="C126" s="87" t="inlineStr">
+      <c r="C128" s="87" t="inlineStr">
         <is>
           <t>Mag7月跌&gt;10% → +2</t>
         </is>
       </c>
     </row>
-    <row r="127">
-      <c r="B127" s="87" t="inlineStr">
+    <row r="129">
+      <c r="B129" s="87" t="inlineStr">
         <is>
           <t>VIX&gt;30 → +2</t>
         </is>
       </c>
-      <c r="C127" s="87" t="inlineStr">
+      <c r="C129" s="87" t="inlineStr">
         <is>
           <t>AI公司裁员/下调指引 → +1</t>
-        </is>
-      </c>
-    </row>
-    <row r="128">
-      <c r="B128" s="87" t="inlineStr">
-        <is>
-          <t>信用利差&gt;150bp → +2</t>
-        </is>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" s="204" t="inlineStr">
-        <is>
-          <t>泡沫反向信号</t>
-        </is>
-      </c>
-      <c r="B129" s="87" t="inlineStr">
-        <is>
-          <t>Mag7单日涨&gt;3% → -1</t>
-        </is>
-      </c>
-      <c r="C129" s="87" t="inlineStr">
-        <is>
-          <t>Mag7月涨&gt;8% → -2</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="B130" s="87" t="inlineStr">
         <is>
+          <t>信用利差&gt;150bp → +2</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="204" t="inlineStr">
+        <is>
+          <t>泡沫反向信号</t>
+        </is>
+      </c>
+      <c r="B131" s="87" t="inlineStr">
+        <is>
+          <t>Mag7单日涨&gt;3% → -1</t>
+        </is>
+      </c>
+      <c r="C131" s="87" t="inlineStr">
+        <is>
+          <t>Mag7月涨&gt;8% → -2</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="B132" s="87" t="inlineStr">
+        <is>
           <t>Fed降息 → -2</t>
         </is>
       </c>
-      <c r="C130" s="87" t="inlineStr">
+      <c r="C132" s="87" t="inlineStr">
         <is>
           <t>AI龙头超预期财报 → -1</t>
         </is>
       </c>
     </row>
-    <row r="131">
-      <c r="B131" s="87" t="inlineStr">
+    <row r="133">
+      <c r="B133" s="87" t="inlineStr">
         <is>
           <t>VIX&lt;15 → -1</t>
         </is>
       </c>
     </row>
-    <row r="132">
-      <c r="A132" s="204" t="inlineStr">
+    <row r="134">
+      <c r="A134" s="204" t="inlineStr">
         <is>
           <t>更新规则</t>
         </is>
       </c>
-      <c r="B132" s="87" t="inlineStr">
+      <c r="B134" s="87" t="inlineStr">
         <is>
           <t>每月第一天：信号概率=70%+上月净计分×5pp</t>
         </is>
       </c>
-      <c r="C132" s="87" t="inlineStr">
+      <c r="C134" s="87" t="inlineStr">
         <is>
           <t>底线55%上限85%</t>
         </is>
       </c>
     </row>
-    <row r="133">
-      <c r="A133" s="204" t="inlineStr">
+    <row r="135">
+      <c r="A135" s="204" t="inlineStr">
         <is>
           <t>Mag7权重</t>
         </is>
       </c>
-      <c r="B133" s="87" t="inlineStr">
+      <c r="B135" s="87" t="inlineStr">
         <is>
           <t>NVDA40% META15% GOOGL15% MSFT15%</t>
         </is>
       </c>
-      <c r="C133" s="87" t="inlineStr">
+      <c r="C135" s="87" t="inlineStr">
         <is>
           <t>AMZN5% AAPL5% TSLA5%</t>
         </is>
       </c>
-      <c r="D133" s="87" t="inlineStr">
+      <c r="D135" s="87" t="inlineStr">
         <is>
           <t>固定不按月动</t>
         </is>
       </c>
     </row>
-    <row r="135">
-      <c r="A135" s="205" t="inlineStr">
+    <row r="136"/>
+    <row r="137">
+      <c r="A137" s="205" t="inlineStr">
         <is>
           <t>⚡ 机制v3使用指南</t>
-        </is>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" s="204" t="inlineStr">
-        <is>
-          <t>日常看盘</t>
-        </is>
-      </c>
-      <c r="B136" s="87" t="inlineStr">
-        <is>
-          <t>看机会成本排序Sheet折后仓位</t>
-        </is>
-      </c>
-      <c r="C136" s="87" t="inlineStr">
-        <is>
-          <t>看现金锁定状态</t>
-        </is>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" s="204" t="inlineStr">
-        <is>
-          <t>每日更新</t>
-        </is>
-      </c>
-      <c r="B137" s="87" t="inlineStr">
-        <is>
-          <t>信号计分板逐股计分</t>
-        </is>
-      </c>
-      <c r="C137" s="87" t="inlineStr">
-        <is>
-          <t>净计分累计</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="204" t="inlineStr">
         <is>
-          <t>每月重算</t>
+          <t>日常看盘</t>
         </is>
       </c>
       <c r="B138" s="87" t="inlineStr">
         <is>
-          <t>①信号概率=70%+净计分×5pp</t>
+          <t>看机会成本排序Sheet折后仓位</t>
         </is>
       </c>
       <c r="C138" s="87" t="inlineStr">
         <is>
-          <t>②CLC=信号概率×互锁×时间衰减²</t>
-        </is>
-      </c>
-      <c r="D138" s="87" t="inlineStr">
-        <is>
-          <t>③折后仓位=原仓位×(1-CLC×β)</t>
+          <t>看现金锁定状态</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="204" t="inlineStr">
         <is>
-          <t>信号落地</t>
+          <t>每日更新</t>
         </is>
       </c>
       <c r="B139" s="87" t="inlineStr">
         <is>
-          <t>视觉信号+5日确认+因果链2条</t>
+          <t>信号计分板逐股计分</t>
         </is>
       </c>
       <c r="C139" s="87" t="inlineStr">
         <is>
-          <t>→虚P转实P</t>
-        </is>
-      </c>
-      <c r="D139" s="87" t="inlineStr">
-        <is>
-          <t>→CLC=0现金解锁</t>
+          <t>净计分累计</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="204" t="inlineStr">
         <is>
+          <t>每月重算</t>
+        </is>
+      </c>
+      <c r="B140" s="87" t="inlineStr">
+        <is>
+          <t>①信号概率=70%+净计分×5pp</t>
+        </is>
+      </c>
+      <c r="C140" s="87" t="inlineStr">
+        <is>
+          <t>②CLC=信号概率×互锁×时间衰减²</t>
+        </is>
+      </c>
+      <c r="D140" s="87" t="inlineStr">
+        <is>
+          <t>③折后仓位=原仓位×(1-CLC×β)</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="204" t="inlineStr">
+        <is>
+          <t>信号落地</t>
+        </is>
+      </c>
+      <c r="B141" s="87" t="inlineStr">
+        <is>
+          <t>视觉信号+5日确认+因果链2条</t>
+        </is>
+      </c>
+      <c r="C141" s="87" t="inlineStr">
+        <is>
+          <t>→虚P转实P</t>
+        </is>
+      </c>
+      <c r="D141" s="87" t="inlineStr">
+        <is>
+          <t>→CLC=0现金解锁</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="204" t="inlineStr">
+        <is>
           <t>核验计算</t>
         </is>
       </c>
-      <c r="B140" s="87" t="inlineStr">
+      <c r="B142" s="87" t="inlineStr">
         <is>
           <t>python3 /tmp/mechanism_checker_v3.py</t>
         </is>
       </c>
-      <c r="C140" s="87" t="inlineStr">
+      <c r="C142" s="87" t="inlineStr">
         <is>
           <t>自动重算所有机制</t>
         </is>
       </c>
     </row>
-    <row r="142">
-      <c r="A142" s="206" t="inlineStr">
+    <row r="143"/>
+    <row r="144">
+      <c r="A144" s="206" t="inlineStr">
         <is>
           <t>📊 持仓状态速查表</t>
         </is>
       </c>
     </row>
-    <row r="143">
-      <c r="A143" s="207" t="inlineStr">
+    <row r="145">
+      <c r="A145" s="207" t="inlineStr">
         <is>
           <t>持仓</t>
         </is>
       </c>
-      <c r="B143" s="207" t="inlineStr">
+      <c r="B145" s="207" t="inlineStr">
         <is>
           <t>代码</t>
         </is>
       </c>
-      <c r="C143" s="207" t="inlineStr">
+      <c r="C145" s="207" t="inlineStr">
         <is>
           <t>当前P</t>
         </is>
       </c>
-      <c r="D143" s="207" t="inlineStr">
+      <c r="D145" s="207" t="inlineStr">
         <is>
           <t>有效P</t>
         </is>
       </c>
-      <c r="E143" s="207" t="inlineStr">
+      <c r="E145" s="207" t="inlineStr">
         <is>
           <t>虚P</t>
         </is>
       </c>
-      <c r="F143" s="207" t="inlineStr">
+      <c r="F145" s="207" t="inlineStr">
         <is>
           <t>利率折价</t>
         </is>
       </c>
-      <c r="G143" s="207" t="inlineStr">
+      <c r="G145" s="207" t="inlineStr">
         <is>
           <t>方向</t>
         </is>
       </c>
-      <c r="H143" s="207" t="inlineStr">
+      <c r="H145" s="207" t="inlineStr">
         <is>
           <t>操作建议</t>
-        </is>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" s="78" t="inlineStr">
-        <is>
-          <t>芯片020628</t>
-        </is>
-      </c>
-      <c r="B144" s="78" t="inlineStr">
-        <is>
-          <t>C1</t>
-        </is>
-      </c>
-      <c r="C144" s="78" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
-      <c r="D144" s="78" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="E144" s="78" t="inlineStr">
-        <is>
-          <t>虚P+2pp</t>
-        </is>
-      </c>
-      <c r="F144" s="78" t="inlineStr">
-        <is>
-          <t>利率折价-6pp</t>
-        </is>
-      </c>
-      <c r="G144" s="78" t="inlineStr">
-        <is>
-          <t>🟡中性</t>
-        </is>
-      </c>
-      <c r="H144" s="78" t="inlineStr">
-        <is>
-          <t>观望</t>
-        </is>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" s="78" t="inlineStr">
-        <is>
-          <t>电池018926</t>
-        </is>
-      </c>
-      <c r="B145" s="78" t="inlineStr">
-        <is>
-          <t>C2</t>
-        </is>
-      </c>
-      <c r="C145" s="78" t="inlineStr">
-        <is>
-          <t>65</t>
-        </is>
-      </c>
-      <c r="D145" s="78" t="inlineStr">
-        <is>
-          <t>59</t>
-        </is>
-      </c>
-      <c r="E145" s="78" t="inlineStr">
-        <is>
-          <t>虚P无</t>
-        </is>
-      </c>
-      <c r="F145" s="78" t="inlineStr">
-        <is>
-          <t>利率折价-6pp</t>
-        </is>
-      </c>
-      <c r="G145" s="78" t="inlineStr">
-        <is>
-          <t>🟢偏多</t>
-        </is>
-      </c>
-      <c r="H145" s="78" t="inlineStr">
-        <is>
-          <t>持有/关注加仓</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="78" t="inlineStr">
         <is>
-          <t>恒科012349</t>
+          <t>芯片020628</t>
         </is>
       </c>
       <c r="B146" s="78" t="inlineStr">
         <is>
-          <t>C3</t>
+          <t>C1</t>
         </is>
       </c>
       <c r="C146" s="78" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>41</t>
         </is>
       </c>
       <c r="D146" s="78" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>35</t>
         </is>
       </c>
       <c r="E146" s="78" t="inlineStr">
         <is>
-          <t>虚P无</t>
+          <t>虚P+2pp</t>
         </is>
       </c>
       <c r="F146" s="78" t="inlineStr">
@@ -4756,44 +4754,44 @@
       </c>
       <c r="G146" s="78" t="inlineStr">
         <is>
-          <t>🔴偏空</t>
+          <t>🟡中性</t>
         </is>
       </c>
       <c r="H146" s="78" t="inlineStr">
         <is>
-          <t>减仓/清仓</t>
+          <t>观望</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="78" t="inlineStr">
         <is>
-          <t>养殖014415</t>
+          <t>电池018926</t>
         </is>
       </c>
       <c r="B147" s="78" t="inlineStr">
         <is>
-          <t>C4</t>
+          <t>C2</t>
         </is>
       </c>
       <c r="C147" s="78" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>65</t>
         </is>
       </c>
       <c r="D147" s="78" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>59</t>
         </is>
       </c>
       <c r="E147" s="78" t="inlineStr">
         <is>
-          <t>虚P+4pp</t>
+          <t>虚P无</t>
         </is>
       </c>
       <c r="F147" s="78" t="inlineStr">
         <is>
-          <t>利率折价0pp</t>
+          <t>利率折价-6pp</t>
         </is>
       </c>
       <c r="G147" s="78" t="inlineStr">
@@ -4810,22 +4808,22 @@
     <row r="148">
       <c r="A148" s="78" t="inlineStr">
         <is>
-          <t>有色004433</t>
+          <t>恒科012349</t>
         </is>
       </c>
       <c r="B148" s="78" t="inlineStr">
         <is>
-          <t>C5</t>
+          <t>C3</t>
         </is>
       </c>
       <c r="C148" s="78" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>27</t>
         </is>
       </c>
       <c r="D148" s="78" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>21</t>
         </is>
       </c>
       <c r="E148" s="78" t="inlineStr">
@@ -4835,7 +4833,7 @@
       </c>
       <c r="F148" s="78" t="inlineStr">
         <is>
-          <t>利率折价-4pp</t>
+          <t>利率折价-6pp</t>
         </is>
       </c>
       <c r="G148" s="78" t="inlineStr">
@@ -4852,120 +4850,204 @@
     <row r="149">
       <c r="A149" s="78" t="inlineStr">
         <is>
-          <t>稀金014111</t>
+          <t>养殖014415</t>
         </is>
       </c>
       <c r="B149" s="78" t="inlineStr">
         <is>
-          <t>C6</t>
+          <t>C4</t>
         </is>
       </c>
       <c r="C149" s="78" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>70</t>
         </is>
       </c>
       <c r="D149" s="78" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>70</t>
         </is>
       </c>
       <c r="E149" s="78" t="inlineStr">
         <is>
-          <t>虚P无</t>
+          <t>虚P+4pp</t>
         </is>
       </c>
       <c r="F149" s="78" t="inlineStr">
         <is>
-          <t>利率折价-4pp</t>
+          <t>利率折价0pp</t>
         </is>
       </c>
       <c r="G149" s="78" t="inlineStr">
         <is>
-          <t>🟡中性</t>
+          <t>🟢偏多</t>
         </is>
       </c>
       <c r="H149" s="78" t="inlineStr">
         <is>
-          <t>观望</t>
+          <t>持有/关注加仓</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="78" t="inlineStr">
         <is>
-          <t>银行001595</t>
+          <t>有色004433</t>
         </is>
       </c>
       <c r="B150" s="78" t="inlineStr">
         <is>
-          <t>C7</t>
+          <t>C5</t>
         </is>
       </c>
       <c r="C150" s="78" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>39</t>
         </is>
       </c>
       <c r="D150" s="78" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>35</t>
         </is>
       </c>
       <c r="E150" s="78" t="inlineStr">
         <is>
-          <t>虚P-2pp</t>
+          <t>虚P无</t>
         </is>
       </c>
       <c r="F150" s="78" t="inlineStr">
         <is>
-          <t>利率折价0pp</t>
+          <t>利率折价-4pp</t>
         </is>
       </c>
       <c r="G150" s="78" t="inlineStr">
         <is>
-          <t>🟡中性</t>
+          <t>🔴偏空</t>
         </is>
       </c>
       <c r="H150" s="78" t="inlineStr">
         <is>
-          <t>观望</t>
+          <t>减仓/清仓</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="78" t="inlineStr">
         <is>
+          <t>稀金014111</t>
+        </is>
+      </c>
+      <c r="B151" s="78" t="inlineStr">
+        <is>
+          <t>C6</t>
+        </is>
+      </c>
+      <c r="C151" s="78" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="D151" s="78" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="E151" s="78" t="inlineStr">
+        <is>
+          <t>虚P无</t>
+        </is>
+      </c>
+      <c r="F151" s="78" t="inlineStr">
+        <is>
+          <t>利率折价-4pp</t>
+        </is>
+      </c>
+      <c r="G151" s="78" t="inlineStr">
+        <is>
+          <t>🟡中性</t>
+        </is>
+      </c>
+      <c r="H151" s="78" t="inlineStr">
+        <is>
+          <t>观望</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="78" t="inlineStr">
+        <is>
+          <t>银行001595</t>
+        </is>
+      </c>
+      <c r="B152" s="78" t="inlineStr">
+        <is>
+          <t>C7</t>
+        </is>
+      </c>
+      <c r="C152" s="78" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="D152" s="78" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="E152" s="78" t="inlineStr">
+        <is>
+          <t>虚P-2pp</t>
+        </is>
+      </c>
+      <c r="F152" s="78" t="inlineStr">
+        <is>
+          <t>利率折价0pp</t>
+        </is>
+      </c>
+      <c r="G152" s="78" t="inlineStr">
+        <is>
+          <t>🟡中性</t>
+        </is>
+      </c>
+      <c r="H152" s="78" t="inlineStr">
+        <is>
+          <t>观望</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="78" t="inlineStr">
+        <is>
           <t>AI027048</t>
         </is>
       </c>
-      <c r="B151" s="78" t="inlineStr">
+      <c r="B153" s="78" t="inlineStr">
         <is>
           <t>C8</t>
         </is>
       </c>
-      <c r="C151" s="78" t="inlineStr">
+      <c r="C153" s="78" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="D151" s="78" t="inlineStr">
+      <c r="D153" s="78" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="E151" s="78" t="inlineStr"/>
-      <c r="F151" s="78" t="inlineStr">
+      <c r="E153" s="78" t="inlineStr"/>
+      <c r="F153" s="78" t="inlineStr">
         <is>
           <t>利率折价-4pp</t>
         </is>
       </c>
-      <c r="G151" s="78" t="inlineStr">
+      <c r="G153" s="78" t="inlineStr">
         <is>
           <t>🟡中性</t>
         </is>
       </c>
-      <c r="H151" s="78" t="inlineStr">
+      <c r="H153" s="78" t="inlineStr">
         <is>
           <t>观望</t>
         </is>
@@ -10622,4 +10704,319 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H13"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" style="79" min="1" max="1"/>
+    <col width="12" customWidth="1" style="79" min="2" max="2"/>
+    <col width="12" customWidth="1" style="79" min="3" max="3"/>
+    <col width="12" customWidth="1" style="79" min="4" max="4"/>
+    <col width="12" customWidth="1" style="79" min="5" max="5"/>
+    <col width="12" customWidth="1" style="79" min="6" max="6"/>
+    <col width="12" customWidth="1" style="79" min="7" max="7"/>
+    <col width="12" customWidth="1" style="79" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="206" t="inlineStr">
+        <is>
+          <t>📊 基金数据联动分析</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="208" t="inlineStr">
+        <is>
+          <t>数据日期: 2026-06-04 | 数据来源: 新浪K线API</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="209" t="inlineStr">
+        <is>
+          <t>持仓名称</t>
+        </is>
+      </c>
+      <c r="B4" s="209" t="inlineStr">
+        <is>
+          <t>基金代码</t>
+        </is>
+      </c>
+      <c r="C4" s="209" t="inlineStr">
+        <is>
+          <t>最新价</t>
+        </is>
+      </c>
+      <c r="D4" s="209" t="inlineStr">
+        <is>
+          <t>今日涨跌%</t>
+        </is>
+      </c>
+      <c r="E4" s="209" t="inlineStr">
+        <is>
+          <t>5日涨跌%</t>
+        </is>
+      </c>
+      <c r="F4" s="209" t="inlineStr">
+        <is>
+          <t>20日涨跌%</t>
+        </is>
+      </c>
+      <c r="G4" s="209" t="inlineStr">
+        <is>
+          <t>年化波动率%</t>
+        </is>
+      </c>
+      <c r="H4" s="209" t="inlineStr">
+        <is>
+          <t>P值</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="210" t="inlineStr">
+        <is>
+          <t>电池ETF</t>
+        </is>
+      </c>
+      <c r="B5" s="210" t="inlineStr">
+        <is>
+          <t>159147</t>
+        </is>
+      </c>
+      <c r="C5" s="210" t="n">
+        <v>1.043</v>
+      </c>
+      <c r="D5" s="211" t="n">
+        <v>-2.07</v>
+      </c>
+      <c r="E5" s="211" t="n">
+        <v>-3.96</v>
+      </c>
+      <c r="F5" s="211" t="n">
+        <v>-8.109999999999999</v>
+      </c>
+      <c r="G5" s="210" t="n">
+        <v>32.7</v>
+      </c>
+      <c r="H5" s="210" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="210" t="inlineStr">
+        <is>
+          <t>畜牧养殖ETF</t>
+        </is>
+      </c>
+      <c r="B6" s="210" t="inlineStr">
+        <is>
+          <t>512450</t>
+        </is>
+      </c>
+      <c r="C6" s="210" t="n">
+        <v>0.846</v>
+      </c>
+      <c r="D6" s="211" t="n">
+        <v>-2.65</v>
+      </c>
+      <c r="E6" s="211" t="n">
+        <v>-4.62</v>
+      </c>
+      <c r="F6" s="211" t="n">
+        <v>-14.29</v>
+      </c>
+      <c r="G6" s="210" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="H6" s="210" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="210" t="inlineStr">
+        <is>
+          <t>芯片ETF</t>
+        </is>
+      </c>
+      <c r="B7" s="210" t="inlineStr">
+        <is>
+          <t>159995</t>
+        </is>
+      </c>
+      <c r="C7" s="210" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="D7" s="212" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="E7" s="212" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="F7" s="212" t="n">
+        <v>16.43</v>
+      </c>
+      <c r="G7" s="210" t="n">
+        <v>46</v>
+      </c>
+      <c r="H7" s="210" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="210" t="inlineStr">
+        <is>
+          <t>恒生科技ETF</t>
+        </is>
+      </c>
+      <c r="B8" s="210" t="inlineStr">
+        <is>
+          <t>513180</t>
+        </is>
+      </c>
+      <c r="C8" s="210" t="n">
+        <v>0.631</v>
+      </c>
+      <c r="D8" s="211" t="n">
+        <v>-1.56</v>
+      </c>
+      <c r="E8" s="212" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="F8" s="211" t="n">
+        <v>-3.37</v>
+      </c>
+      <c r="G8" s="210" t="n">
+        <v>27.5</v>
+      </c>
+      <c r="H8" s="210" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="210" t="inlineStr">
+        <is>
+          <t>黄金ETF</t>
+        </is>
+      </c>
+      <c r="B9" s="210" t="inlineStr">
+        <is>
+          <t>518880</t>
+        </is>
+      </c>
+      <c r="C9" s="210" t="n">
+        <v>9.289999999999999</v>
+      </c>
+      <c r="D9" s="212" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E9" s="211" t="n">
+        <v>-1.14</v>
+      </c>
+      <c r="F9" s="211" t="n">
+        <v>-5.97</v>
+      </c>
+      <c r="G9" s="210" t="n">
+        <v>31.3</v>
+      </c>
+      <c r="H9" s="210" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="210" t="inlineStr">
+        <is>
+          <t>银行ETF</t>
+        </is>
+      </c>
+      <c r="B10" s="210" t="inlineStr">
+        <is>
+          <t>512800</t>
+        </is>
+      </c>
+      <c r="C10" s="210" t="n">
+        <v>0.774</v>
+      </c>
+      <c r="D10" s="211" t="n">
+        <v>-1.15</v>
+      </c>
+      <c r="E10" s="211" t="n">
+        <v>-0.26</v>
+      </c>
+      <c r="F10" s="211" t="n">
+        <v>-1.4</v>
+      </c>
+      <c r="G10" s="210" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="H10" s="210" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="210" t="inlineStr">
+        <is>
+          <t>有色金属ETF</t>
+        </is>
+      </c>
+      <c r="B11" s="210" t="inlineStr">
+        <is>
+          <t>512400</t>
+        </is>
+      </c>
+      <c r="C11" s="210" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="D11" s="211" t="n">
+        <v>-3.05</v>
+      </c>
+      <c r="E11" s="212" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="F11" s="211" t="n">
+        <v>-10.7</v>
+      </c>
+      <c r="G11" s="210" t="n">
+        <v>39.2</v>
+      </c>
+      <c r="H11" s="210" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="150" t="inlineStr">
+        <is>
+          <t>🔗 P值 vs 价格走势联动分析</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A13:H13"/>
+    <mergeCell ref="A1:H1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/持仓贝叶斯跟踪.xlsx
+++ b/持仓贝叶斯跟踪.xlsx
@@ -22,7 +22,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="62">
+  <fonts count="63">
     <font>
       <name val="Calibri"/>
       <charset val="1"/>
@@ -405,8 +405,12 @@
       <b val="1"/>
       <color rgb="00FF0000"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00008000"/>
+    </font>
   </fonts>
-  <fills count="34">
+  <fills count="35">
     <fill>
       <patternFill/>
     </fill>
@@ -603,6 +607,12 @@
         <fgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFFCC"/>
+        <bgColor rgb="00FFFFCC"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="7">
     <border>
@@ -664,7 +674,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="215">
+  <cellXfs count="222">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -1250,6 +1260,15 @@
     <xf numFmtId="0" fontId="42" fillId="33" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="45" fillId="34" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="57" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="57" fillId="34" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="62" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2083,7 +2102,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:H153"/>
+  <dimension ref="A1:H160"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6171875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="18" customWidth="1" style="78" min="1" max="1"/>
@@ -2567,50 +2586,13 @@
 6/4</t>
         </is>
       </c>
-      <c r="B25" s="163" t="inlineStr">
-        <is>
-          <t>纳指PE中值区间
-5维度无暴跌
-七姐妹估值合理
-安全继续持有</t>
-        </is>
-      </c>
-      <c r="C25" s="164" t="inlineStr">
-        <is>
-          <t>部分参考
-与达利欧矛盾
-看估值vs流动性</t>
-        </is>
-      </c>
-      <c r="D25" s="163" t="inlineStr">
-        <is>
-          <t>恒科+1pp
-(虚P)</t>
-        </is>
-      </c>
-      <c r="E25" s="163" t="inlineStr">
-        <is>
-          <t>PE跌破25
-或暴跌触发</t>
-        </is>
-      </c>
-      <c r="F25" s="165" t="inlineStr">
-        <is>
-          <t>未落地</t>
-        </is>
-      </c>
-      <c r="G25" s="163" t="inlineStr">
-        <is>
-          <t>中
-3星</t>
-        </is>
-      </c>
-      <c r="H25" s="163" t="inlineStr">
-        <is>
-          <t>框架合理
-忽略集中度</t>
-        </is>
-      </c>
+      <c r="B25" s="145" t="n"/>
+      <c r="C25" s="145" t="n"/>
+      <c r="D25" s="145" t="n"/>
+      <c r="E25" s="145" t="n"/>
+      <c r="F25" s="145" t="n"/>
+      <c r="G25" s="145" t="n"/>
+      <c r="H25" s="146" t="n"/>
     </row>
     <row r="26" ht="15" customHeight="1" s="79"/>
     <row r="27" ht="17.15" customHeight="1" s="79">
@@ -2692,21 +2674,13 @@
           <t>三源共识</t>
         </is>
       </c>
-      <c r="B31" s="184" t="inlineStr">
-        <is>
-          <t>🔴核心共识</t>
-        </is>
-      </c>
-      <c r="C31" s="163" t="inlineStr">
-        <is>
-          <t>AI龙头估值偏高+市场集中+中小盘已熊</t>
-        </is>
-      </c>
-      <c r="D31" s="163" t="inlineStr">
-        <is>
-          <t>🔴强信号</t>
-        </is>
-      </c>
+      <c r="B31" s="145" t="n"/>
+      <c r="C31" s="145" t="n"/>
+      <c r="D31" s="145" t="n"/>
+      <c r="E31" s="145" t="n"/>
+      <c r="F31" s="145" t="n"/>
+      <c r="G31" s="145" t="n"/>
+      <c r="H31" s="146" t="n"/>
     </row>
     <row r="32" ht="15" customHeight="1" s="79"/>
     <row r="33" ht="16.5" customHeight="1" s="79">
@@ -2831,16 +2805,13 @@
           <t>下行保护</t>
         </is>
       </c>
-      <c r="B41" s="163" t="inlineStr">
-        <is>
-          <t>没跌→现金无损可继续等</t>
-        </is>
-      </c>
-      <c r="C41" s="163" t="inlineStr">
-        <is>
-          <t>→不对称博弈下有保底</t>
-        </is>
-      </c>
+      <c r="B41" s="145" t="n"/>
+      <c r="C41" s="145" t="n"/>
+      <c r="D41" s="145" t="n"/>
+      <c r="E41" s="145" t="n"/>
+      <c r="F41" s="145" t="n"/>
+      <c r="G41" s="145" t="n"/>
+      <c r="H41" s="146" t="n"/>
     </row>
     <row r="42" ht="16.5" customHeight="1" s="79"/>
     <row r="43" ht="16.5" customHeight="1" s="79">
@@ -3118,37 +3089,13 @@
           <t>纯现金5月</t>
         </is>
       </c>
-      <c r="B51" s="163" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C51" s="163" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D51" s="163" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E51" s="163" t="inlineStr">
-        <is>
-          <t>机会成本
-可能错过短期</t>
-        </is>
-      </c>
-      <c r="F51" s="163" t="inlineStr">
-        <is>
-          <t>不对称博弈可接受</t>
-        </is>
-      </c>
-      <c r="G51" s="167" t="inlineStr">
-        <is>
-          <t>🟡可接受</t>
-        </is>
-      </c>
+      <c r="B51" s="145" t="n"/>
+      <c r="C51" s="145" t="n"/>
+      <c r="D51" s="145" t="n"/>
+      <c r="E51" s="145" t="n"/>
+      <c r="F51" s="145" t="n"/>
+      <c r="G51" s="145" t="n"/>
+      <c r="H51" s="146" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="87" t="inlineStr">
@@ -3300,48 +3247,13 @@
           <t>堆叠独立</t>
         </is>
       </c>
-      <c r="B58" s="163" t="inlineStr">
-        <is>
-          <t>国内产业确定性</t>
-        </is>
-      </c>
-      <c r="C58" s="164" t="inlineStr">
-        <is>
-          <t>三源未提及国内封测</t>
-        </is>
-      </c>
-      <c r="D58" s="163" t="inlineStr">
-        <is>
-          <t>回调后优先配置</t>
-        </is>
-      </c>
-      <c r="E58" s="163" t="inlineStr">
-        <is>
-          <t>纳指/纳指七姐妹
-出现&gt;15%回调</t>
-        </is>
-      </c>
-      <c r="F58" s="165" t="inlineStr">
-        <is>
-          <t>⏳未落地
-(虚P状态)</t>
-        </is>
-      </c>
-      <c r="G58" s="166" t="inlineStr">
-        <is>
-          <t>⭐⭐⭐⭐⭐
-极高</t>
-        </is>
-      </c>
-      <c r="H58" s="163" t="inlineStr">
-        <is>
-          <t>6/4三源联动:
-芯片-2pp
-恒科-1pp
-→已记虚P
-未转实P</t>
-        </is>
-      </c>
+      <c r="B58" s="145" t="n"/>
+      <c r="C58" s="145" t="n"/>
+      <c r="D58" s="145" t="n"/>
+      <c r="E58" s="145" t="n"/>
+      <c r="F58" s="145" t="n"/>
+      <c r="G58" s="145" t="n"/>
+      <c r="H58" s="146" t="n"/>
     </row>
     <row r="59">
       <c r="A59" s="163" t="inlineStr">
@@ -3477,7 +3389,6 @@
         </is>
       </c>
     </row>
-    <row r="66"/>
     <row r="67">
       <c r="A67" s="174" t="inlineStr">
         <is>
@@ -3553,7 +3464,6 @@
         </is>
       </c>
     </row>
-    <row r="72"/>
     <row r="73">
       <c r="A73" s="177" t="inlineStr">
         <is>
@@ -3561,9 +3471,6 @@
         </is>
       </c>
     </row>
-    <row r="74"/>
-    <row r="75"/>
-    <row r="76"/>
     <row r="77">
       <c r="A77" s="87" t="inlineStr">
         <is>
@@ -4169,18 +4076,14 @@
           <t>每月重算</t>
         </is>
       </c>
-      <c r="B107" s="87" t="inlineStr">
-        <is>
-          <t>信号概率按计分板更新</t>
-        </is>
-      </c>
-      <c r="C107" s="87" t="inlineStr">
-        <is>
-          <t>时间衰减自动重算</t>
-        </is>
-      </c>
-    </row>
-    <row r="108"/>
+      <c r="B107" s="145" t="n"/>
+      <c r="C107" s="145" t="n"/>
+      <c r="D107" s="145" t="n"/>
+      <c r="E107" s="145" t="n"/>
+      <c r="F107" s="145" t="n"/>
+      <c r="G107" s="145" t="n"/>
+      <c r="H107" s="146" t="n"/>
+    </row>
     <row r="109">
       <c r="A109" s="203" t="inlineStr">
         <is>
@@ -4291,23 +4194,14 @@
           <t>分级逻辑</t>
         </is>
       </c>
-      <c r="B116" s="87" t="inlineStr">
-        <is>
-          <t>按切断条件分两级：扛得住vs扛不住</t>
-        </is>
-      </c>
-      <c r="C116" s="87" t="inlineStr">
-        <is>
-          <t>不是连续β，是二值判断</t>
-        </is>
-      </c>
-      <c r="D116" s="87" t="inlineStr">
-        <is>
-          <t>小龙虾建议</t>
-        </is>
-      </c>
-    </row>
-    <row r="117"/>
+      <c r="B116" s="145" t="n"/>
+      <c r="C116" s="145" t="n"/>
+      <c r="D116" s="145" t="n"/>
+      <c r="E116" s="145" t="n"/>
+      <c r="F116" s="145" t="n"/>
+      <c r="G116" s="145" t="n"/>
+      <c r="H116" s="146" t="n"/>
+    </row>
     <row r="118">
       <c r="A118" s="203" t="inlineStr">
         <is>
@@ -4433,23 +4327,14 @@
           <t>转换后</t>
         </is>
       </c>
-      <c r="B125" s="87" t="inlineStr">
-        <is>
-          <t>虚P转实P→计入P值</t>
-        </is>
-      </c>
-      <c r="C125" s="87" t="inlineStr">
-        <is>
-          <t>CLC→0现金全解锁</t>
-        </is>
-      </c>
-      <c r="D125" s="87" t="inlineStr">
-        <is>
-          <t>折后仓位→恢复原目标</t>
-        </is>
-      </c>
-    </row>
-    <row r="126"/>
+      <c r="B125" s="145" t="n"/>
+      <c r="C125" s="145" t="n"/>
+      <c r="D125" s="145" t="n"/>
+      <c r="E125" s="145" t="n"/>
+      <c r="F125" s="145" t="n"/>
+      <c r="G125" s="145" t="n"/>
+      <c r="H125" s="146" t="n"/>
+    </row>
     <row r="127">
       <c r="A127" s="205" t="inlineStr">
         <is>
@@ -4552,23 +4437,14 @@
           <t>Mag7权重</t>
         </is>
       </c>
-      <c r="B135" s="87" t="inlineStr">
-        <is>
-          <t>NVDA40% META15% GOOGL15% MSFT15%</t>
-        </is>
-      </c>
-      <c r="C135" s="87" t="inlineStr">
-        <is>
-          <t>AMZN5% AAPL5% TSLA5%</t>
-        </is>
-      </c>
-      <c r="D135" s="87" t="inlineStr">
-        <is>
-          <t>固定不按月动</t>
-        </is>
-      </c>
-    </row>
-    <row r="136"/>
+      <c r="B135" s="145" t="n"/>
+      <c r="C135" s="145" t="n"/>
+      <c r="D135" s="145" t="n"/>
+      <c r="E135" s="145" t="n"/>
+      <c r="F135" s="145" t="n"/>
+      <c r="G135" s="145" t="n"/>
+      <c r="H135" s="146" t="n"/>
+    </row>
     <row r="137">
       <c r="A137" s="205" t="inlineStr">
         <is>
@@ -4671,7 +4547,6 @@
         </is>
       </c>
     </row>
-    <row r="143"/>
     <row r="144">
       <c r="A144" s="206" t="inlineStr">
         <is>
@@ -5050,6 +4925,48 @@
       <c r="H153" s="78" t="inlineStr">
         <is>
           <t>观望</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="215" t="inlineStr">
+        <is>
+          <t>🕸 网状断网修复记录 (2026-06-05)</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="216" t="inlineStr">
+        <is>
+          <t>【修复1】虚P/实P分列：下游机会成本/现金锁定/仓位建议，全部改用有效实P计算，虚P仅锁定不介入。</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="216" t="inlineStr">
+        <is>
+          <t>【修复2】芯片产业/宏观拆分：产业层P=65%（AI基建+升腾+长鑫+资金搬家），宏观折价-8pp。有效P=57%。拟合0分主因是产业利好权重被低估。</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="216" t="inlineStr">
+        <is>
+          <t>【修复3】养殖宏观边打通：利率↑→养殖ETF跌14%（之前折价0pp错误），去杠杆→消费压缩-1pp，霍尔木兹→饲料成本-1pp。有效P=66%。</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="216" t="inlineStr">
+        <is>
+          <t>【修复4】存储→芯片ETF资金传送门：存储涨81%降级后，资金搬进芯片ETF/长电通富，解释芯片价格涨但P值低的背离。</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="216" t="inlineStr">
+        <is>
+          <t>【待接入】pvalue_engine.py：同逻辑簇L1/L2衰退已代码化，下次抓取自动生效。</t>
         </is>
       </c>
     </row>
@@ -5090,7 +5007,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:L134"/>
+  <dimension ref="A1:L148"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="10.4921875" defaultRowHeight="12.75" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="18" customWidth="1" style="78" min="1" max="8"/>
@@ -8269,6 +8186,295 @@
         <is>
           <t>恢复: P:50%
 有效P:50%</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="215" t="inlineStr">
+        <is>
+          <t>🔧 P值分层与拟合校验 (2026-06-05修复)</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="217" t="inlineStr">
+        <is>
+          <t>修复说明：</t>
+        </is>
+      </c>
+      <c r="B137" s="216" t="inlineStr">
+        <is>
+          <t>① 虚P/实P彻底分列，下游计算只用实P</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="B138" s="216" t="inlineStr">
+        <is>
+          <t>② 芯片拆产业层(65%)与宏观折价(-8pp)，有效P=57%（解决拟合0分）</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="B139" s="216" t="inlineStr">
+        <is>
+          <t>③ 养殖补齐宏观传导边：利率折价-2pp + 去杠杆-1pp，有效P从70%→66%</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="218" t="inlineStr">
+        <is>
+          <t>持仓</t>
+        </is>
+      </c>
+      <c r="B141" s="218" t="inlineStr">
+        <is>
+          <t>产业/基本面P</t>
+        </is>
+      </c>
+      <c r="C141" s="218" t="inlineStr">
+        <is>
+          <t>宏观折价</t>
+        </is>
+      </c>
+      <c r="D141" s="218" t="inlineStr">
+        <is>
+          <t>有效实P</t>
+        </is>
+      </c>
+      <c r="E141" s="218" t="inlineStr">
+        <is>
+          <t>虚P(锁定)</t>
+        </is>
+      </c>
+      <c r="F141" s="218" t="inlineStr">
+        <is>
+          <t>拟合状态</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="219" t="inlineStr">
+        <is>
+          <t>芯片</t>
+        </is>
+      </c>
+      <c r="B142" s="219" t="inlineStr">
+        <is>
+          <t>65%</t>
+        </is>
+      </c>
+      <c r="C142" s="219" t="inlineStr">
+        <is>
+          <t>-8pp(利率-6/三源-2)</t>
+        </is>
+      </c>
+      <c r="D142" s="220" t="inlineStr">
+        <is>
+          <t>57%</t>
+        </is>
+      </c>
+      <c r="E142" s="219" t="inlineStr">
+        <is>
+          <t>0pp</t>
+        </is>
+      </c>
+      <c r="F142" s="219" t="inlineStr">
+        <is>
+          <t>🔴拟合0→待修复</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="219" t="inlineStr">
+        <is>
+          <t>电池</t>
+        </is>
+      </c>
+      <c r="B143" s="219" t="inlineStr">
+        <is>
+          <t>69%</t>
+        </is>
+      </c>
+      <c r="C143" s="219" t="inlineStr">
+        <is>
+          <t>-4pp(利率)</t>
+        </is>
+      </c>
+      <c r="D143" s="220" t="inlineStr">
+        <is>
+          <t>65%</t>
+        </is>
+      </c>
+      <c r="E143" s="219" t="inlineStr">
+        <is>
+          <t>0pp</t>
+        </is>
+      </c>
+      <c r="F143" s="219" t="inlineStr">
+        <is>
+          <t>✅良好74</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="219" t="inlineStr">
+        <is>
+          <t>养殖</t>
+        </is>
+      </c>
+      <c r="B144" s="219" t="inlineStr">
+        <is>
+          <t>70%</t>
+        </is>
+      </c>
+      <c r="C144" s="219" t="inlineStr">
+        <is>
+          <t>-4pp(利率-2/去杠杆-1/能源-1)</t>
+        </is>
+      </c>
+      <c r="D144" s="220" t="inlineStr">
+        <is>
+          <t>66%</t>
+        </is>
+      </c>
+      <c r="E144" s="219" t="inlineStr">
+        <is>
+          <t>+4pp(锁定)</t>
+        </is>
+      </c>
+      <c r="F144" s="219" t="inlineStr">
+        <is>
+          <t>❌差29→左侧时间差</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="219" t="inlineStr">
+        <is>
+          <t>恒科</t>
+        </is>
+      </c>
+      <c r="B145" s="219" t="inlineStr">
+        <is>
+          <t>35%</t>
+        </is>
+      </c>
+      <c r="C145" s="219" t="inlineStr">
+        <is>
+          <t>-8pp(利率-6/付鹏-2)</t>
+        </is>
+      </c>
+      <c r="D145" s="221" t="inlineStr">
+        <is>
+          <t>27%</t>
+        </is>
+      </c>
+      <c r="E145" s="219" t="inlineStr">
+        <is>
+          <t>0pp</t>
+        </is>
+      </c>
+      <c r="F145" s="219" t="inlineStr">
+        <is>
+          <t>👍良好60</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="219" t="inlineStr">
+        <is>
+          <t>有色</t>
+        </is>
+      </c>
+      <c r="B146" s="219" t="inlineStr">
+        <is>
+          <t>44%</t>
+        </is>
+      </c>
+      <c r="C146" s="219" t="inlineStr">
+        <is>
+          <t>-3pp(利率)</t>
+        </is>
+      </c>
+      <c r="D146" s="221" t="inlineStr">
+        <is>
+          <t>41%</t>
+        </is>
+      </c>
+      <c r="E146" s="219" t="inlineStr">
+        <is>
+          <t>0pp</t>
+        </is>
+      </c>
+      <c r="F146" s="219" t="inlineStr">
+        <is>
+          <t>✅良好71</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="219" t="inlineStr">
+        <is>
+          <t>稀金</t>
+        </is>
+      </c>
+      <c r="B147" s="219" t="inlineStr">
+        <is>
+          <t>43%</t>
+        </is>
+      </c>
+      <c r="C147" s="219" t="inlineStr">
+        <is>
+          <t>-3pp(利率)</t>
+        </is>
+      </c>
+      <c r="D147" s="221" t="inlineStr">
+        <is>
+          <t>40%</t>
+        </is>
+      </c>
+      <c r="E147" s="219" t="inlineStr">
+        <is>
+          <t>0pp</t>
+        </is>
+      </c>
+      <c r="F147" s="219" t="inlineStr">
+        <is>
+          <t>👍良好70</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="219" t="inlineStr">
+        <is>
+          <t>银行</t>
+        </is>
+      </c>
+      <c r="B148" s="219" t="inlineStr">
+        <is>
+          <t>50%</t>
+        </is>
+      </c>
+      <c r="C148" s="219" t="inlineStr">
+        <is>
+          <t>-2pp(去杠杆)</t>
+        </is>
+      </c>
+      <c r="D148" s="221" t="inlineStr">
+        <is>
+          <t>48%</t>
+        </is>
+      </c>
+      <c r="E148" s="219" t="inlineStr">
+        <is>
+          <t>0pp</t>
+        </is>
+      </c>
+      <c r="F148" s="219" t="inlineStr">
+        <is>
+          <t>未测</t>
         </is>
       </c>
     </row>

--- a/持仓贝叶斯跟踪.xlsx
+++ b/持仓贝叶斯跟踪.xlsx
@@ -674,7 +674,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="222">
+  <cellXfs count="223">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -1269,6 +1269,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="62" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="61" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -5007,7 +5008,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:L148"/>
+  <dimension ref="A1:L188"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="10.4921875" defaultRowHeight="12.75" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="18" customWidth="1" style="78" min="1" max="8"/>
@@ -8478,9 +8479,279 @@
         </is>
       </c>
     </row>
+    <row r="150">
+      <c r="A150" s="215" t="inlineStr">
+        <is>
+          <t>P值引擎原理说明 (2026-06-05)</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="217" t="inlineStr">
+        <is>
+          <t>一、同逻辑簇边际衰退</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="216" t="inlineStr">
+        <is>
+          <t>原理：同一条视频/同一个博主反复说同一件事，信息是冗余的，不能重复算pp。</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="216" t="inlineStr">
+        <is>
+          <t>L1 同博主+同日+同持仓+同方向 → 第2条起只算20%（×0.20）</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="216" t="inlineStr">
+        <is>
+          <t>L2 同博主+同周（7天内）+同方向 → 只算50%（×0.50）</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="216" t="inlineStr">
+        <is>
+          <t>反方向不衰退：同一天说了看多又说了看空，说明是不同论点，不衰退</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="216" t="inlineStr">
+        <is>
+          <t>代码：pvalue_engine.py 已就绪，下次写事件链时自动生效</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="217" t="inlineStr">
+        <is>
+          <t>二、pp给法标尺（定性+定量）</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="216" t="inlineStr">
+        <is>
+          <t>定性：今天听了会不会改变持仓决策？会→给pp，不会→不给</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="216" t="inlineStr">
+        <is>
+          <t>定量三档：±1pp（小调整）/ ±3pp（中催化）/ ±5pp（大转折）</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="216" t="inlineStr">
+        <is>
+          <t>禁止±2和±4。如果不知道该归哪档，说明不配给pp</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="216" t="inlineStr">
+        <is>
+          <t>虚P实P分开：虚P锁在虚P列不计入P值，落地转实P时打-1pp折</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="217" t="inlineStr">
+        <is>
+          <t>三、价格拟合校准（数据驱动）</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="216" t="inlineStr">
+        <is>
+          <t>原理：事件是输入，价格变动是输出。数据够了就能反推'这件事到底该值多少pp'</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="216" t="inlineStr">
+        <is>
+          <t>阶段0（现在）：每次写事件链自动记录事件后3天的价格变动</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="216" t="inlineStr">
+        <is>
+          <t>阶段1（100+条）：同类事件取平均价格响应，看谁准谁不准</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="216" t="inlineStr">
+        <is>
+          <t>阶段2（200+条）：岭回归校准，自动算出每类事件的合理pp值</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="216" t="inlineStr">
+        <is>
+          <t>当前进度：17条事件已记录，0条有价格数据（需修复映射）</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="216" t="inlineStr">
+        <is>
+          <t>代码：calibrate_pp.py 独立可执行，python3 calibrate_pp.py --status 查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="217" t="inlineStr">
+        <is>
+          <t>四、机制耦合关系</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="216" t="inlineStr">
+        <is>
+          <t>同逻辑簇衰退 → 减少重复计算 → 让pp更干净 → 价格拟合更准</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="216" t="inlineStr">
+        <is>
+          <t>pp标尺 → 给法统一 → 减少拍脑袋 → 回归校准有基准</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="216" t="inlineStr">
+        <is>
+          <t>价格拟合 → 反推合理pp → 校准标尺 → 形成闭环</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="216" t="inlineStr">
+        <is>
+          <t>三者互相依赖：衰退不做好→拟合噪声大；标尺不统一→回归没基准；拟合不做→永远拍脑袋</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="222" t="inlineStr">
+        <is>
+          <t>五、机制耦合状态 (2026-06-05修复)</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="217" t="inlineStr">
+        <is>
+          <t>M2→M1</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>✅ 已耦合</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>标尺产出raw_pp → 衰退引擎消费</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>代码自动执行</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="217" t="inlineStr">
+        <is>
+          <t>M1→看板</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>✅ 已耦合</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>衰退后final_pp → 事件链写入</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>代码自动执行</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="217" t="inlineStr">
+        <is>
+          <t>M3→M2</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>✅ 已修复</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>校准结果→calibrated_pps.json→make_event自动读</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>python3 calibrate_pp.py --apply</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" s="217" t="inlineStr">
+        <is>
+          <t>验证命令</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>python3 -c "import pvalue_engine; pvalue_engine.make_event('t','2026-06-05','电池','bullish',2)" → 应该报错</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>python3 calibrate_pp.py --apply → M3→M2反馈回路</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>原理说明已写入Sheet2，耦合状态已更新</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="48">
+  <mergeCells count="49">
     <mergeCell ref="A58:K58"/>
+    <mergeCell ref="A150:D150"/>
     <mergeCell ref="A130:H130"/>
     <mergeCell ref="B97:L97"/>
     <mergeCell ref="B91:L91"/>

--- a/持仓贝叶斯跟踪.xlsx
+++ b/持仓贝叶斯跟踪.xlsx
@@ -2103,8 +2103,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:H160"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="8.6171875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
+  <dimension ref="A1:H165"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="8.6171875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col width="18" customWidth="1" style="78" min="1" max="1"/>
     <col width="18" customWidth="1" style="78" min="2" max="2"/>
@@ -4968,6 +4968,160 @@
       <c r="A160" s="216" t="inlineStr">
         <is>
           <t>【待接入】pvalue_engine.py：同逻辑簇L1/L2衰退已代码化，下次抓取自动生效。</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>📊 6/5 新事件链</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>生猪贸易~芳姐
+抖音 6/5</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>低价抄底母猪
+行业融资枯竭
+银行拒贷养猪
+母猪未血流成河</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>底部临近
+但尚未到最底
+等待母猪血流成河
+才是最佳买点</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>养殖+1pp
+P=71%</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>母猪大规模淘汰
+猪价跌破5元
+银行全面停贷</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>未落地
+(虚P)</t>
+        </is>
+      </c>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>中
+3星</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>闻号说经济
+知乎 6/5 (10篇)</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>厄尔尼诺80%概率
+AI用电爆发
+电力/农产品/能源受益
+AI芯片管制升级
+301关税60国
+银行信贷收紧</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>厄尔尼诺+AI
+双重驱动电力
+关税压制有色
+流动性收紧</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>电池+1pp
+恒科-1pp
+有色-1pp
+银行-1pp</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>厄尔尼诺确认
+或关税落地
+或美联储转向</t>
+        </is>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>部分落地
+(厄尔尼诺虚P)</t>
+        </is>
+      </c>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>高
+4星</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>古都闲云
+知乎 6/5</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>央行购金vs个人炒金
+黄金短期投机拥挤
+向上向下双压</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>多空抵消
+短期不操作
+长期配置逻辑不变</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>黄金0pp
+P=70%</t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>央行大规模抛售
+或杠杆踩踏</t>
+        </is>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>未落地</t>
+        </is>
+      </c>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>中
+3星</t>
         </is>
       </c>
     </row>
@@ -5008,8 +5162,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:L188"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="10.4921875" defaultRowHeight="12.75" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
+  <dimension ref="A1:L192"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="10.4921875" defaultRowHeight="12.75" customHeight="0" zeroHeight="0" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col width="18" customWidth="1" style="78" min="1" max="8"/>
     <col width="18" customWidth="1" style="78" min="9" max="9"/>
@@ -8660,17 +8814,17 @@
           <t>M2→M1</t>
         </is>
       </c>
-      <c r="B181" t="inlineStr">
+      <c r="B181" s="78" t="inlineStr">
         <is>
           <t>✅ 已耦合</t>
         </is>
       </c>
-      <c r="C181" t="inlineStr">
+      <c r="C181" s="78" t="inlineStr">
         <is>
           <t>标尺产出raw_pp → 衰退引擎消费</t>
         </is>
       </c>
-      <c r="D181" t="inlineStr">
+      <c r="D181" s="78" t="inlineStr">
         <is>
           <t>代码自动执行</t>
         </is>
@@ -8682,17 +8836,17 @@
           <t>M1→看板</t>
         </is>
       </c>
-      <c r="B182" t="inlineStr">
+      <c r="B182" s="78" t="inlineStr">
         <is>
           <t>✅ 已耦合</t>
         </is>
       </c>
-      <c r="C182" t="inlineStr">
+      <c r="C182" s="78" t="inlineStr">
         <is>
           <t>衰退后final_pp → 事件链写入</t>
         </is>
       </c>
-      <c r="D182" t="inlineStr">
+      <c r="D182" s="78" t="inlineStr">
         <is>
           <t>代码自动执行</t>
         </is>
@@ -8704,17 +8858,17 @@
           <t>M3→M2</t>
         </is>
       </c>
-      <c r="B183" t="inlineStr">
+      <c r="B183" s="78" t="inlineStr">
         <is>
           <t>✅ 已修复</t>
         </is>
       </c>
-      <c r="C183" t="inlineStr">
+      <c r="C183" s="78" t="inlineStr">
         <is>
           <t>校准结果→calibrated_pps.json→make_event自动读</t>
         </is>
       </c>
-      <c r="D183" t="inlineStr">
+      <c r="D183" s="78" t="inlineStr">
         <is>
           <t>python3 calibrate_pp.py --apply</t>
         </is>
@@ -8728,23 +8882,120 @@
       </c>
     </row>
     <row r="186">
-      <c r="A186" t="inlineStr">
+      <c r="A186" s="78" t="inlineStr">
         <is>
           <t>python3 -c "import pvalue_engine; pvalue_engine.make_event('t','2026-06-05','电池','bullish',2)" → 应该报错</t>
         </is>
       </c>
     </row>
     <row r="187">
-      <c r="A187" t="inlineStr">
+      <c r="A187" s="78" t="inlineStr">
         <is>
           <t>python3 calibrate_pp.py --apply → M3→M2反馈回路</t>
         </is>
       </c>
     </row>
     <row r="188">
-      <c r="A188" t="inlineStr">
+      <c r="A188" s="78" t="inlineStr">
         <is>
           <t>原理说明已写入Sheet2，耦合状态已更新</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>📊 6/5 监控更新（抖音+知乎，B站CDP限流阻塞）</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>养殖ETF</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>电池</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>黄金</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>芯片</t>
+        </is>
+      </c>
+      <c r="E191" t="inlineStr">
+        <is>
+          <t>恒科</t>
+        </is>
+      </c>
+      <c r="F191" t="inlineStr">
+        <is>
+          <t>有色</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>2026-06-05
++1pp
+【+1pp】生猪贸易：低价抄底母猪，行业融资枯竭，银行拒贷养猪，母猪未血流成河→底部临近但未到</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>2026-06-05
++1pp
+【+1pp】闻号：厄尔尼诺80%概率+AI用电爆发→电力/能源确定性受益，电池产业链间接利好</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>2026-06-05
+0pp
+【0pp】古都闲云：黄金短期投机拥挤向上向下双压 vs 闻号：黄金替代美债成第一大储备→多空抵消</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>2026-06-05
+0pp
+【+0pp】闻号：AI芯片出口管制升级(利好国产替代) vs 韩股vsA股结构差异拥挤度警告(利空)→抵消</t>
+        </is>
+      </c>
+      <c r="E192" t="inlineStr">
+        <is>
+          <t>2026-06-05
+-1pp
+【-1pp】闻号：孙正义高杠杆AI泡沫风险+美股流动性饥渴+301关税60国→压制恒科</t>
+        </is>
+      </c>
+      <c r="F192" t="inlineStr">
+        <is>
+          <t>2026-06-05
+-1pp
+【-1pp】闻号：301关税60国→工业金属需求预期下降，转口贸易路变窄</t>
+        </is>
+      </c>
+      <c r="G192" t="inlineStr">
+        <is>
+          <t>2026-06-05
+-1pp
+【-1pp】闻号：301关税60国→稀土反制牌短期有效但长期不确定</t>
+        </is>
+      </c>
+      <c r="H192" t="inlineStr">
+        <is>
+          <t>2026-06-05
+-1pp
+【-1pp】闻号：央行逆回购归零+DR007上穿政策利率→最宽松阶段过去，不利净息差</t>
         </is>
       </c>
     </row>
@@ -9181,7 +9432,7 @@
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
   <dimension ref="A1:N54"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="8.6171875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="8.6171875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col width="6" customWidth="1" style="78" min="1" max="1"/>
     <col width="14" customWidth="1" style="78" min="2" max="2"/>
@@ -10484,7 +10735,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:H37"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="18" customWidth="1" style="79" min="1" max="1"/>
     <col width="20" customWidth="1" style="79" min="2" max="2"/>
@@ -11190,7 +11441,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:H13"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="14" customWidth="1" style="79" min="1" max="1"/>
     <col width="12" customWidth="1" style="79" min="2" max="2"/>

--- a/持仓贝叶斯跟踪.xlsx
+++ b/持仓贝叶斯跟踪.xlsx
@@ -2181,7 +2181,7 @@
       <c r="E4" s="87" t="inlineStr">
         <is>
           <t>2026-06-02 宋鸿兵：霍尔木兹封锁3个月，全球有效原油库存仅8.1亿桶，市场误判油价回落
-2026-06-03 宋鸿兵+雪佛龙+埃克森：OECD库存6月触红线，布伦特或冲150-160，5月跌10%=口头操纵</t>
+2026-06-03 宋鸿兵+雪佛龙+埃克森：OECD库存6月触红线</t>
         </is>
       </c>
       <c r="F4" s="87" t="inlineStr">
@@ -2238,6 +2238,11 @@
           <t>2026-05-29 付鹏 - 所有人都在去杠杆的时候就没有人过得好了</t>
         </is>
       </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>2026-06-01 正信期货：中东再度紧张，霍尔木兹通航风险大，多头趋势未改</t>
+        </is>
+      </c>
       <c r="F6" s="87" t="inlineStr">
         <is>
           <t>2026-05-29 蒋宇飞商业 - 用产业思维抓住科技龙头</t>
@@ -2260,6 +2265,11 @@
           <t>2026-05-23 南半球聊财经：宏观经济数据全景</t>
         </is>
       </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>2026-06-01 摩根大通：海峡重开需等'痛到极点'，短期难解</t>
+        </is>
+      </c>
       <c r="F7" s="87" t="inlineStr">
         <is>
           <t>2026-05-29 拿幸·AI启示录 - Claude Code自愈功能</t>
@@ -2282,6 +2292,11 @@
           <t>2026-05-22 宏观层：前4月住户贷款狂减4902亿（无知半人）</t>
         </is>
       </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>2026-05-29 日本面粉涨24%：中东→油价→消费品传导链确认</t>
+        </is>
+      </c>
       <c r="F8" s="87" t="inlineStr">
         <is>
           <t>2026-05-28 周鸿祎 · "算力决定速度，内存决定高度"</t>
@@ -2299,6 +2314,11 @@
           <t>2026-05-19 古都闲云：4月新增贷款出现历史罕见的负值</t>
         </is>
       </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>2026-04-07 美军空袭伊朗哈尔克岛，以色列同步打击桥梁铁路</t>
+        </is>
+      </c>
       <c r="F9" s="87" t="inlineStr">
         <is>
           <t>2026-05-27 AI处理日志 →黄金+2pp</t>
@@ -2316,6 +2336,11 @@
           <t>2026-05-19 古都闲云：中国4月社会消费品零售总额同比+0.2%</t>
         </is>
       </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>2026-03-23 特朗普威胁摧毁伊朗能源设施 + 新加坡总理：比70年代更严重</t>
+        </is>
+      </c>
       <c r="F10" s="87" t="inlineStr">
         <is>
           <t>2026-05-27 蒋宇飞（抖音）→ 芯片0pp</t>
@@ -2323,6 +2348,11 @@
       </c>
     </row>
     <row r="11" ht="48" customHeight="1" s="79">
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>2026-03 最坏情境：布伦特$111/桶(2027Q4)，封锁2月+供应仅200万桶/日</t>
+        </is>
+      </c>
       <c r="F11" s="87" t="inlineStr">
         <is>
           <t>2026-05-27 付鹏（抖音）→ 芯片0pp</t>
@@ -4972,20 +5002,20 @@
       </c>
     </row>
     <row r="162">
-      <c r="A162" t="inlineStr">
+      <c r="A162" s="78" t="inlineStr">
         <is>
           <t>📊 6/5 新事件链</t>
         </is>
       </c>
     </row>
     <row r="163">
-      <c r="A163" t="inlineStr">
+      <c r="A163" s="78" t="inlineStr">
         <is>
           <t>生猪贸易~芳姐
 抖音 6/5</t>
         </is>
       </c>
-      <c r="B163" t="inlineStr">
+      <c r="B163" s="78" t="inlineStr">
         <is>
           <t>低价抄底母猪
 行业融资枯竭
@@ -4993,7 +5023,7 @@
 母猪未血流成河</t>
         </is>
       </c>
-      <c r="C163" t="inlineStr">
+      <c r="C163" s="78" t="inlineStr">
         <is>
           <t>底部临近
 但尚未到最底
@@ -5001,26 +5031,26 @@
 才是最佳买点</t>
         </is>
       </c>
-      <c r="D163" t="inlineStr">
+      <c r="D163" s="78" t="inlineStr">
         <is>
           <t>养殖+1pp
 P=71%</t>
         </is>
       </c>
-      <c r="E163" t="inlineStr">
+      <c r="E163" s="78" t="inlineStr">
         <is>
           <t>母猪大规模淘汰
 猪价跌破5元
 银行全面停贷</t>
         </is>
       </c>
-      <c r="F163" t="inlineStr">
+      <c r="F163" s="78" t="inlineStr">
         <is>
           <t>未落地
 (虚P)</t>
         </is>
       </c>
-      <c r="G163" t="inlineStr">
+      <c r="G163" s="78" t="inlineStr">
         <is>
           <t>中
 3星</t>
@@ -5028,13 +5058,13 @@
       </c>
     </row>
     <row r="164">
-      <c r="A164" t="inlineStr">
+      <c r="A164" s="78" t="inlineStr">
         <is>
           <t>闻号说经济
 知乎 6/5 (10篇)</t>
         </is>
       </c>
-      <c r="B164" t="inlineStr">
+      <c r="B164" s="78" t="inlineStr">
         <is>
           <t>厄尔尼诺80%概率
 AI用电爆发
@@ -5044,7 +5074,7 @@
 银行信贷收紧</t>
         </is>
       </c>
-      <c r="C164" t="inlineStr">
+      <c r="C164" s="78" t="inlineStr">
         <is>
           <t>厄尔尼诺+AI
 双重驱动电力
@@ -5052,7 +5082,7 @@
 流动性收紧</t>
         </is>
       </c>
-      <c r="D164" t="inlineStr">
+      <c r="D164" s="78" t="inlineStr">
         <is>
           <t>电池+1pp
 恒科-1pp
@@ -5060,20 +5090,20 @@
 银行-1pp</t>
         </is>
       </c>
-      <c r="E164" t="inlineStr">
+      <c r="E164" s="78" t="inlineStr">
         <is>
           <t>厄尔尼诺确认
 或关税落地
 或美联储转向</t>
         </is>
       </c>
-      <c r="F164" t="inlineStr">
+      <c r="F164" s="78" t="inlineStr">
         <is>
           <t>部分落地
 (厄尔尼诺虚P)</t>
         </is>
       </c>
-      <c r="G164" t="inlineStr">
+      <c r="G164" s="78" t="inlineStr">
         <is>
           <t>高
 4星</t>
@@ -5081,44 +5111,44 @@
       </c>
     </row>
     <row r="165">
-      <c r="A165" t="inlineStr">
+      <c r="A165" s="78" t="inlineStr">
         <is>
           <t>古都闲云
 知乎 6/5</t>
         </is>
       </c>
-      <c r="B165" t="inlineStr">
+      <c r="B165" s="78" t="inlineStr">
         <is>
           <t>央行购金vs个人炒金
 黄金短期投机拥挤
 向上向下双压</t>
         </is>
       </c>
-      <c r="C165" t="inlineStr">
+      <c r="C165" s="78" t="inlineStr">
         <is>
           <t>多空抵消
 短期不操作
 长期配置逻辑不变</t>
         </is>
       </c>
-      <c r="D165" t="inlineStr">
+      <c r="D165" s="78" t="inlineStr">
         <is>
           <t>黄金0pp
 P=70%</t>
         </is>
       </c>
-      <c r="E165" t="inlineStr">
+      <c r="E165" s="78" t="inlineStr">
         <is>
           <t>央行大规模抛售
 或杠杆踩踏</t>
         </is>
       </c>
-      <c r="F165" t="inlineStr">
+      <c r="F165" s="78" t="inlineStr">
         <is>
           <t>未落地</t>
         </is>
       </c>
-      <c r="G165" t="inlineStr">
+      <c r="G165" s="78" t="inlineStr">
         <is>
           <t>中
 3星</t>
@@ -5244,6 +5274,12 @@
 [观察]</t>
         </is>
       </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>原油162411
+[待重]</t>
+        </is>
+      </c>
     </row>
     <row r="3" ht="72.75" customHeight="1" s="79">
       <c r="A3" s="96" t="inlineStr">
@@ -5389,6 +5425,18 @@
 → 标的:中广核003816(PE10-12x便宜) / 中国核电601985(PE25x偏贵)</t>
         </is>
       </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>P:58%
+虚P无
+利率折价+2pp
+有效P:60%
+拟合N/A(新赛道)
+下行:25%
+盈亏比:2.4:1
+状态:等回调入场</t>
+        </is>
+      </c>
     </row>
     <row r="4" ht="12.75" customHeight="1" s="79">
       <c r="A4" s="98" t="inlineStr">
@@ -5451,6 +5499,11 @@
 01-盈亏比计算方法论.md</t>
         </is>
       </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>日期/P/事件</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="45" customHeight="1" s="79">
       <c r="A5" s="100" t="inlineStr">
@@ -5507,6 +5560,13 @@
 【+0pp】【虚P】欧洲央行：黄金替代美债成第一大储备</t>
         </is>
       </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>2026-06-01
++3pp
+【+3pp】正信期货：中东紧张，霍尔木兹风险大，多头趋势未改</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="45" customHeight="1" s="79">
       <c r="A6" s="101" t="inlineStr">
@@ -5559,6 +5619,13 @@
         </is>
       </c>
       <c r="H6" s="106" t="n"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>2026-06-01
++2pp
+【+2pp】摩根大通：海峡重开需等'痛到极点'</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="45" customHeight="1" s="79">
       <c r="A7" s="107" t="inlineStr">
@@ -5612,6 +5679,13 @@
         </is>
       </c>
       <c r="H7" s="106" t="n"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>2026-05-29
++5pp
+【+5pp】宋鸿兵：OECD库存6月触红线，$111最坏情景</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="45" customHeight="1" s="79">
       <c r="A8" s="101" t="inlineStr">
@@ -5659,6 +5733,13 @@
       </c>
       <c r="G8" s="106" t="n"/>
       <c r="H8" s="106" t="n"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>2026-05-29
++3pp
+【+3pp】日本面粉涨24%，油价传导消费品确认</t>
+        </is>
+      </c>
     </row>
     <row r="9" ht="45" customHeight="1" s="79">
       <c r="A9" s="109" t="inlineStr">
@@ -5701,6 +5782,13 @@
       </c>
       <c r="G9" s="106" t="n"/>
       <c r="H9" s="106" t="n"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>2026-04-07
++4pp
+【+4pp】美军空袭哈尔克岛+以色列同步打击</t>
+        </is>
+      </c>
     </row>
     <row r="10" ht="45" customHeight="1" s="79">
       <c r="A10" s="104" t="inlineStr">
@@ -5738,6 +5826,14 @@
       </c>
       <c r="G10" s="106" t="n"/>
       <c r="H10" s="106" t="n"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>2026-03-23
++3pp
+【+2pp】特朗普威胁摧毁伊朗设施
+【+1pp】新加坡总理：比70年代更严重</t>
+        </is>
+      </c>
     </row>
     <row r="11" ht="45" customHeight="1" s="79">
       <c r="A11" s="109" t="inlineStr">
@@ -5760,6 +5856,13 @@
       <c r="F11" s="106" t="n"/>
       <c r="G11" s="106" t="n"/>
       <c r="H11" s="106" t="n"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>2026-03
+基准
+【基准50%→58%】封锁3月+库存8.1亿桶+最坏$111</t>
+        </is>
+      </c>
     </row>
     <row r="12" ht="45" customHeight="1" s="79">
       <c r="A12" s="113" t="inlineStr">
@@ -5782,6 +5885,11 @@
       <c r="F12" s="106" t="n"/>
       <c r="G12" s="106" t="n"/>
       <c r="H12" s="106" t="n"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>拟合N/A(新赛道)</t>
+        </is>
+      </c>
     </row>
     <row r="13" ht="75" customHeight="1" s="79">
       <c r="A13" s="114" t="inlineStr">
@@ -8903,95 +9011,95 @@
       </c>
     </row>
     <row r="190">
-      <c r="A190" t="inlineStr">
+      <c r="A190" s="78" t="inlineStr">
         <is>
           <t>📊 6/5 监控更新（抖音+知乎，B站CDP限流阻塞）</t>
         </is>
       </c>
     </row>
     <row r="191">
-      <c r="A191" t="inlineStr">
+      <c r="A191" s="78" t="inlineStr">
         <is>
           <t>养殖ETF</t>
         </is>
       </c>
-      <c r="B191" t="inlineStr">
+      <c r="B191" s="78" t="inlineStr">
         <is>
           <t>电池</t>
         </is>
       </c>
-      <c r="C191" t="inlineStr">
+      <c r="C191" s="78" t="inlineStr">
         <is>
           <t>黄金</t>
         </is>
       </c>
-      <c r="D191" t="inlineStr">
+      <c r="D191" s="78" t="inlineStr">
         <is>
           <t>芯片</t>
         </is>
       </c>
-      <c r="E191" t="inlineStr">
+      <c r="E191" s="78" t="inlineStr">
         <is>
           <t>恒科</t>
         </is>
       </c>
-      <c r="F191" t="inlineStr">
+      <c r="F191" s="78" t="inlineStr">
         <is>
           <t>有色</t>
         </is>
       </c>
     </row>
     <row r="192">
-      <c r="A192" t="inlineStr">
+      <c r="A192" s="78" t="inlineStr">
         <is>
           <t>2026-06-05
 +1pp
 【+1pp】生猪贸易：低价抄底母猪，行业融资枯竭，银行拒贷养猪，母猪未血流成河→底部临近但未到</t>
         </is>
       </c>
-      <c r="B192" t="inlineStr">
+      <c r="B192" s="78" t="inlineStr">
         <is>
           <t>2026-06-05
 +1pp
 【+1pp】闻号：厄尔尼诺80%概率+AI用电爆发→电力/能源确定性受益，电池产业链间接利好</t>
         </is>
       </c>
-      <c r="C192" t="inlineStr">
+      <c r="C192" s="78" t="inlineStr">
         <is>
           <t>2026-06-05
 0pp
 【0pp】古都闲云：黄金短期投机拥挤向上向下双压 vs 闻号：黄金替代美债成第一大储备→多空抵消</t>
         </is>
       </c>
-      <c r="D192" t="inlineStr">
+      <c r="D192" s="78" t="inlineStr">
         <is>
           <t>2026-06-05
 0pp
 【+0pp】闻号：AI芯片出口管制升级(利好国产替代) vs 韩股vsA股结构差异拥挤度警告(利空)→抵消</t>
         </is>
       </c>
-      <c r="E192" t="inlineStr">
+      <c r="E192" s="78" t="inlineStr">
         <is>
           <t>2026-06-05
 -1pp
 【-1pp】闻号：孙正义高杠杆AI泡沫风险+美股流动性饥渴+301关税60国→压制恒科</t>
         </is>
       </c>
-      <c r="F192" t="inlineStr">
+      <c r="F192" s="78" t="inlineStr">
         <is>
           <t>2026-06-05
 -1pp
 【-1pp】闻号：301关税60国→工业金属需求预期下降，转口贸易路变窄</t>
         </is>
       </c>
-      <c r="G192" t="inlineStr">
+      <c r="G192" s="78" t="inlineStr">
         <is>
           <t>2026-06-05
 -1pp
 【-1pp】闻号：301关税60国→稀土反制牌短期有效但长期不确定</t>
         </is>
       </c>
-      <c r="H192" t="inlineStr">
+      <c r="H192" s="78" t="inlineStr">
         <is>
           <t>2026-06-05
 -1pp

--- a/持仓贝叶斯跟踪.xlsx
+++ b/持仓贝叶斯跟踪.xlsx
@@ -2104,7 +2104,7 @@
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
   <dimension ref="A1:H165"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="8.6171875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="8.6171875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="18" customWidth="1" style="78" min="1" max="1"/>
     <col width="18" customWidth="1" style="78" min="2" max="2"/>
@@ -2238,7 +2238,7 @@
           <t>2026-05-29 付鹏 - 所有人都在去杠杆的时候就没有人过得好了</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="E6" s="78" t="inlineStr">
         <is>
           <t>2026-06-01 正信期货：中东再度紧张，霍尔木兹通航风险大，多头趋势未改</t>
         </is>
@@ -2265,7 +2265,7 @@
           <t>2026-05-23 南半球聊财经：宏观经济数据全景</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="E7" s="78" t="inlineStr">
         <is>
           <t>2026-06-01 摩根大通：海峡重开需等'痛到极点'，短期难解</t>
         </is>
@@ -2292,7 +2292,7 @@
           <t>2026-05-22 宏观层：前4月住户贷款狂减4902亿（无知半人）</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E8" s="78" t="inlineStr">
         <is>
           <t>2026-05-29 日本面粉涨24%：中东→油价→消费品传导链确认</t>
         </is>
@@ -2314,7 +2314,7 @@
           <t>2026-05-19 古都闲云：4月新增贷款出现历史罕见的负值</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E9" s="78" t="inlineStr">
         <is>
           <t>2026-04-07 美军空袭伊朗哈尔克岛，以色列同步打击桥梁铁路</t>
         </is>
@@ -2336,7 +2336,7 @@
           <t>2026-05-19 古都闲云：中国4月社会消费品零售总额同比+0.2%</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="E10" s="78" t="inlineStr">
         <is>
           <t>2026-03-23 特朗普威胁摧毁伊朗能源设施 + 新加坡总理：比70年代更严重</t>
         </is>
@@ -2348,7 +2348,7 @@
       </c>
     </row>
     <row r="11" ht="48" customHeight="1" s="79">
-      <c r="E11" t="inlineStr">
+      <c r="E11" s="78" t="inlineStr">
         <is>
           <t>2026-03 最坏情境：布伦特$111/桶(2027Q4)，封锁2月+供应仅200万桶/日</t>
         </is>
@@ -2988,7 +2988,7 @@
       </c>
       <c r="E47" s="163" t="inlineStr">
         <is>
-          <t>已持仓不需现金</t>
+          <t>已持仓不需现金 | 6/5 芳姐：低价抄底母猪，行业融资枯竭，等待母猪血流成河才是最佳买点</t>
         </is>
       </c>
       <c r="F47" s="163" t="inlineStr">
@@ -3025,7 +3025,7 @@
       </c>
       <c r="E48" s="163" t="inlineStr">
         <is>
-          <t>已持仓不需现金</t>
+          <t>已持仓不需现金 | 6/5 闻号说经济：厄尔尼诺80%概率+AI用电爆发→电力/能源受益</t>
         </is>
       </c>
       <c r="F48" s="163" t="inlineStr">
@@ -4650,7 +4650,7 @@
       </c>
       <c r="E146" s="78" t="inlineStr">
         <is>
-          <t>虚P+2pp</t>
+          <t>虚P+2pp | 6/5 存储→芯片资金传送门：存储涨81%降级后，资金搬进芯片ETF/长电通富</t>
         </is>
       </c>
       <c r="F146" s="78" t="inlineStr">
@@ -4734,7 +4734,7 @@
       </c>
       <c r="E148" s="78" t="inlineStr">
         <is>
-          <t>虚P无</t>
+          <t>虚P无 | 6/5 闻号说经济：301关税60国+AI芯片管制升级→压制恒科</t>
         </is>
       </c>
       <c r="F148" s="78" t="inlineStr">
@@ -4776,7 +4776,7 @@
       </c>
       <c r="E149" s="78" t="inlineStr">
         <is>
-          <t>虚P+4pp</t>
+          <t>虚P+4pp | 6/5 芳姐：低价抄底母猪，行业融资枯竭，等待母猪血流成河才是最佳买点</t>
         </is>
       </c>
       <c r="F149" s="78" t="inlineStr">
@@ -4818,7 +4818,7 @@
       </c>
       <c r="E150" s="78" t="inlineStr">
         <is>
-          <t>虚P无</t>
+          <t>虚P无 | 6/5 闻号说经济：301关税60国→压制有色需求</t>
         </is>
       </c>
       <c r="F150" s="78" t="inlineStr">
@@ -4902,7 +4902,7 @@
       </c>
       <c r="E152" s="78" t="inlineStr">
         <is>
-          <t>虚P-2pp</t>
+          <t>虚P-2pp | 6/5 闻号说经济：银行信贷收紧→压制银行</t>
         </is>
       </c>
       <c r="F152" s="78" t="inlineStr">
@@ -4960,200 +4960,53 @@
       </c>
     </row>
     <row r="155">
-      <c r="A155" s="215" t="inlineStr">
-        <is>
-          <t>🕸 网状断网修复记录 (2026-06-05)</t>
-        </is>
-      </c>
+      <c r="A155" s="215" t="n"/>
     </row>
     <row r="156">
-      <c r="A156" s="216" t="inlineStr">
-        <is>
-          <t>【修复1】虚P/实P分列：下游机会成本/现金锁定/仓位建议，全部改用有效实P计算，虚P仅锁定不介入。</t>
-        </is>
-      </c>
+      <c r="A156" s="216" t="n"/>
     </row>
     <row r="157">
-      <c r="A157" s="216" t="inlineStr">
-        <is>
-          <t>【修复2】芯片产业/宏观拆分：产业层P=65%（AI基建+升腾+长鑫+资金搬家），宏观折价-8pp。有效P=57%。拟合0分主因是产业利好权重被低估。</t>
-        </is>
-      </c>
+      <c r="A157" s="216" t="n"/>
     </row>
     <row r="158">
-      <c r="A158" s="216" t="inlineStr">
-        <is>
-          <t>【修复3】养殖宏观边打通：利率↑→养殖ETF跌14%（之前折价0pp错误），去杠杆→消费压缩-1pp，霍尔木兹→饲料成本-1pp。有效P=66%。</t>
-        </is>
-      </c>
+      <c r="A158" s="216" t="n"/>
     </row>
     <row r="159">
-      <c r="A159" s="216" t="inlineStr">
-        <is>
-          <t>【修复4】存储→芯片ETF资金传送门：存储涨81%降级后，资金搬进芯片ETF/长电通富，解释芯片价格涨但P值低的背离。</t>
-        </is>
-      </c>
+      <c r="A159" s="216" t="n"/>
     </row>
     <row r="160">
-      <c r="A160" s="216" t="inlineStr">
-        <is>
-          <t>【待接入】pvalue_engine.py：同逻辑簇L1/L2衰退已代码化，下次抓取自动生效。</t>
-        </is>
-      </c>
-    </row>
+      <c r="A160" s="216" t="n"/>
+    </row>
+    <row r="161"/>
     <row r="162">
-      <c r="A162" s="78" t="inlineStr">
-        <is>
-          <t>📊 6/5 新事件链</t>
-        </is>
-      </c>
+      <c r="A162" s="78" t="n"/>
     </row>
     <row r="163">
-      <c r="A163" s="78" t="inlineStr">
-        <is>
-          <t>生猪贸易~芳姐
-抖音 6/5</t>
-        </is>
-      </c>
-      <c r="B163" s="78" t="inlineStr">
-        <is>
-          <t>低价抄底母猪
-行业融资枯竭
-银行拒贷养猪
-母猪未血流成河</t>
-        </is>
-      </c>
-      <c r="C163" s="78" t="inlineStr">
-        <is>
-          <t>底部临近
-但尚未到最底
-等待母猪血流成河
-才是最佳买点</t>
-        </is>
-      </c>
-      <c r="D163" s="78" t="inlineStr">
-        <is>
-          <t>养殖+1pp
-P=71%</t>
-        </is>
-      </c>
-      <c r="E163" s="78" t="inlineStr">
-        <is>
-          <t>母猪大规模淘汰
-猪价跌破5元
-银行全面停贷</t>
-        </is>
-      </c>
-      <c r="F163" s="78" t="inlineStr">
-        <is>
-          <t>未落地
-(虚P)</t>
-        </is>
-      </c>
-      <c r="G163" s="78" t="inlineStr">
-        <is>
-          <t>中
-3星</t>
-        </is>
-      </c>
+      <c r="A163" s="78" t="n"/>
+      <c r="B163" s="78" t="n"/>
+      <c r="C163" s="78" t="n"/>
+      <c r="D163" s="78" t="n"/>
+      <c r="E163" s="78" t="n"/>
+      <c r="F163" s="78" t="n"/>
+      <c r="G163" s="78" t="n"/>
     </row>
     <row r="164">
-      <c r="A164" s="78" t="inlineStr">
-        <is>
-          <t>闻号说经济
-知乎 6/5 (10篇)</t>
-        </is>
-      </c>
-      <c r="B164" s="78" t="inlineStr">
-        <is>
-          <t>厄尔尼诺80%概率
-AI用电爆发
-电力/农产品/能源受益
-AI芯片管制升级
-301关税60国
-银行信贷收紧</t>
-        </is>
-      </c>
-      <c r="C164" s="78" t="inlineStr">
-        <is>
-          <t>厄尔尼诺+AI
-双重驱动电力
-关税压制有色
-流动性收紧</t>
-        </is>
-      </c>
-      <c r="D164" s="78" t="inlineStr">
-        <is>
-          <t>电池+1pp
-恒科-1pp
-有色-1pp
-银行-1pp</t>
-        </is>
-      </c>
-      <c r="E164" s="78" t="inlineStr">
-        <is>
-          <t>厄尔尼诺确认
-或关税落地
-或美联储转向</t>
-        </is>
-      </c>
-      <c r="F164" s="78" t="inlineStr">
-        <is>
-          <t>部分落地
-(厄尔尼诺虚P)</t>
-        </is>
-      </c>
-      <c r="G164" s="78" t="inlineStr">
-        <is>
-          <t>高
-4星</t>
-        </is>
-      </c>
+      <c r="A164" s="78" t="n"/>
+      <c r="B164" s="78" t="n"/>
+      <c r="C164" s="78" t="n"/>
+      <c r="D164" s="78" t="n"/>
+      <c r="E164" s="78" t="n"/>
+      <c r="F164" s="78" t="n"/>
+      <c r="G164" s="78" t="n"/>
     </row>
     <row r="165">
-      <c r="A165" s="78" t="inlineStr">
-        <is>
-          <t>古都闲云
-知乎 6/5</t>
-        </is>
-      </c>
-      <c r="B165" s="78" t="inlineStr">
-        <is>
-          <t>央行购金vs个人炒金
-黄金短期投机拥挤
-向上向下双压</t>
-        </is>
-      </c>
-      <c r="C165" s="78" t="inlineStr">
-        <is>
-          <t>多空抵消
-短期不操作
-长期配置逻辑不变</t>
-        </is>
-      </c>
-      <c r="D165" s="78" t="inlineStr">
-        <is>
-          <t>黄金0pp
-P=70%</t>
-        </is>
-      </c>
-      <c r="E165" s="78" t="inlineStr">
-        <is>
-          <t>央行大规模抛售
-或杠杆踩踏</t>
-        </is>
-      </c>
-      <c r="F165" s="78" t="inlineStr">
-        <is>
-          <t>未落地</t>
-        </is>
-      </c>
-      <c r="G165" s="78" t="inlineStr">
-        <is>
-          <t>中
-3星</t>
-        </is>
-      </c>
+      <c r="A165" s="78" t="n"/>
+      <c r="B165" s="78" t="n"/>
+      <c r="C165" s="78" t="n"/>
+      <c r="D165" s="78" t="n"/>
+      <c r="E165" s="78" t="n"/>
+      <c r="F165" s="78" t="n"/>
+      <c r="G165" s="78" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="21">
@@ -5193,7 +5046,7 @@
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
   <dimension ref="A1:L192"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="10.4921875" defaultRowHeight="12.75" customHeight="0" zeroHeight="0" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="10.4921875" defaultRowHeight="12.75" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="18" customWidth="1" style="78" min="1" max="8"/>
     <col width="18" customWidth="1" style="78" min="9" max="9"/>
@@ -5274,7 +5127,7 @@
 [观察]</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="K2" s="78" t="inlineStr">
         <is>
           <t>原油162411
 [待重]</t>
@@ -5425,7 +5278,7 @@
 → 标的:中广核003816(PE10-12x便宜) / 中国核电601985(PE25x偏贵)</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="K3" s="78" t="inlineStr">
         <is>
           <t>P:58%
 虚P无
@@ -5499,7 +5352,7 @@
 01-盈亏比计算方法论.md</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="K4" s="78" t="inlineStr">
         <is>
           <t>日期/P/事件</t>
         </is>
@@ -5560,7 +5413,7 @@
 【+0pp】【虚P】欧洲央行：黄金替代美债成第一大储备</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="K5" s="78" t="inlineStr">
         <is>
           <t>2026-06-01
 +3pp
@@ -5619,7 +5472,7 @@
         </is>
       </c>
       <c r="H6" s="106" t="n"/>
-      <c r="K6" t="inlineStr">
+      <c r="K6" s="78" t="inlineStr">
         <is>
           <t>2026-06-01
 +2pp
@@ -5679,7 +5532,7 @@
         </is>
       </c>
       <c r="H7" s="106" t="n"/>
-      <c r="K7" t="inlineStr">
+      <c r="K7" s="78" t="inlineStr">
         <is>
           <t>2026-05-29
 +5pp
@@ -5733,7 +5586,7 @@
       </c>
       <c r="G8" s="106" t="n"/>
       <c r="H8" s="106" t="n"/>
-      <c r="K8" t="inlineStr">
+      <c r="K8" s="78" t="inlineStr">
         <is>
           <t>2026-05-29
 +3pp
@@ -5782,7 +5635,7 @@
       </c>
       <c r="G9" s="106" t="n"/>
       <c r="H9" s="106" t="n"/>
-      <c r="K9" t="inlineStr">
+      <c r="K9" s="78" t="inlineStr">
         <is>
           <t>2026-04-07
 +4pp
@@ -5826,7 +5679,7 @@
       </c>
       <c r="G10" s="106" t="n"/>
       <c r="H10" s="106" t="n"/>
-      <c r="K10" t="inlineStr">
+      <c r="K10" s="78" t="inlineStr">
         <is>
           <t>2026-03-23
 +3pp
@@ -5856,7 +5709,7 @@
       <c r="F11" s="106" t="n"/>
       <c r="G11" s="106" t="n"/>
       <c r="H11" s="106" t="n"/>
-      <c r="K11" t="inlineStr">
+      <c r="K11" s="78" t="inlineStr">
         <is>
           <t>2026-03
 基准
@@ -5885,7 +5738,7 @@
       <c r="F12" s="106" t="n"/>
       <c r="G12" s="106" t="n"/>
       <c r="H12" s="106" t="n"/>
-      <c r="K12" t="inlineStr">
+      <c r="K12" s="78" t="inlineStr">
         <is>
           <t>拟合N/A(新赛道)</t>
         </is>
@@ -9540,7 +9393,7 @@
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
   <dimension ref="A1:N54"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="8.6171875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="8.6171875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="6" customWidth="1" style="78" min="1" max="1"/>
     <col width="14" customWidth="1" style="78" min="2" max="2"/>
@@ -10843,7 +10696,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:H37"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" style="79" min="1" max="1"/>
     <col width="20" customWidth="1" style="79" min="2" max="2"/>
@@ -11549,7 +11402,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:H13"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" style="79" min="1" max="1"/>
     <col width="12" customWidth="1" style="79" min="2" max="2"/>

--- a/持仓贝叶斯跟踪.xlsx
+++ b/持仓贝叶斯跟踪.xlsx
@@ -14,6 +14,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="三源联动分析" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="基金数据联动" sheetId="6" state="visible" r:id="rId6"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="持仓盈亏联动" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="跨品种传导" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1" refMode="A1" iterate="0" iterateCount="100" iterateDelta="0.0001"/>
@@ -23,7 +24,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="49">
+  <fonts count="51">
     <font>
       <name val="Calibri"/>
       <charset val="1"/>
@@ -364,6 +365,14 @@
     <font>
       <name val="&lt;openpyxl.styles.borders.Border object&gt;&#10;Parameters:&#10;outline=True, diagonalUp=False, diagonalDown=False, start=None, end=None, left=&lt;openpyxl.styles.borders.Side object&gt;&#10;Parameters:&#10;style='thin', color=None, right=&lt;openpyxl.styles.borders.Side object&gt;&#10;Parameters:&#10;style='thin', color=None, top=&lt;openpyxl.styles.borders.Side object&gt;&#10;Parameters:&#10;style='thin', color=None, bottom=&lt;openpyxl.styles.borders.Side object&gt;&#10;Parameters:&#10;style='thin', color=None, diagonal=None, vertical=None, horizontal=None"/>
     </font>
+    <font>
+      <b val="1"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+    </font>
   </fonts>
   <fills count="27">
     <fill>
@@ -583,7 +592,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="270">
+  <cellXfs count="274">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -1380,6 +1389,10 @@
     </xf>
     <xf numFmtId="0" fontId="47" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="48" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="44" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="49" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="50" fillId="26" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="50" fillId="26" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3738,7 +3751,7 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" t="n"/>
+      <c r="A87" s="138" t="n"/>
     </row>
     <row r="88" ht="39.55" customHeight="1" s="139">
       <c r="A88" s="147" t="inlineStr">
@@ -5846,11 +5859,11 @@
       </c>
     </row>
     <row r="14" ht="13.5" customHeight="1" s="139">
-      <c r="A14" t="n"/>
-      <c r="B14" t="n"/>
-      <c r="C14" t="n"/>
-      <c r="D14" t="n"/>
-      <c r="G14" t="n"/>
+      <c r="A14" s="138" t="n"/>
+      <c r="B14" s="138" t="n"/>
+      <c r="C14" s="138" t="n"/>
+      <c r="D14" s="138" t="n"/>
+      <c r="G14" s="138" t="n"/>
     </row>
     <row r="15" ht="13.5" customHeight="1" s="139">
       <c r="A15" s="138" t="inlineStr">
@@ -12168,4 +12181,1331 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I93"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="15" customWidth="1" style="139" min="1" max="1"/>
+    <col width="15" customWidth="1" style="139" min="2" max="2"/>
+    <col width="15" customWidth="1" style="139" min="3" max="3"/>
+    <col width="15" customWidth="1" style="139" min="4" max="4"/>
+    <col width="15" customWidth="1" style="139" min="5" max="5"/>
+    <col width="15" customWidth="1" style="139" min="6" max="6"/>
+    <col width="15" customWidth="1" style="139" min="7" max="7"/>
+    <col width="15" customWidth="1" style="139" min="8" max="8"/>
+    <col width="15" customWidth="1" style="139" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="270" t="inlineStr">
+        <is>
+          <t>🔀 跨品种事件传导与P值校准分析 (2026-06-05)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="271" t="inlineStr">
+        <is>
+          <t>一、持仓全景</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="272" t="inlineStr">
+        <is>
+          <t>持仓</t>
+        </is>
+      </c>
+      <c r="B4" s="272" t="inlineStr">
+        <is>
+          <t>P值</t>
+        </is>
+      </c>
+      <c r="C4" s="272" t="inlineStr">
+        <is>
+          <t>事件PP</t>
+        </is>
+      </c>
+      <c r="D4" s="272" t="inlineStr">
+        <is>
+          <t>拟合分</t>
+        </is>
+      </c>
+      <c r="E4" s="272" t="inlineStr">
+        <is>
+          <t>今日涨跌%</t>
+        </is>
+      </c>
+      <c r="F4" s="272" t="inlineStr">
+        <is>
+          <t>20日涨跌%</t>
+        </is>
+      </c>
+      <c r="G4" s="272" t="inlineStr">
+        <is>
+          <t>持有收益率</t>
+        </is>
+      </c>
+      <c r="H4" s="272" t="inlineStr">
+        <is>
+          <t>诊断</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="265" t="inlineStr">
+        <is>
+          <t>芯片</t>
+        </is>
+      </c>
+      <c r="B5" s="265" t="inlineStr">
+        <is>
+          <t>41%</t>
+        </is>
+      </c>
+      <c r="C5" s="265" t="inlineStr">
+        <is>
+          <t>-4pp</t>
+        </is>
+      </c>
+      <c r="D5" s="265" t="inlineStr">
+        <is>
+          <t>0分</t>
+        </is>
+      </c>
+      <c r="E5" s="265" t="inlineStr">
+        <is>
+          <t>+1.9%</t>
+        </is>
+      </c>
+      <c r="F5" s="265" t="inlineStr">
+        <is>
+          <t>+16.4%</t>
+        </is>
+      </c>
+      <c r="G5" s="265" t="inlineStr">
+        <is>
+          <t>+3.9%</t>
+        </is>
+      </c>
+      <c r="H5" s="265" t="inlineStr">
+        <is>
+          <t>漏正向; 拟合失效</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="265" t="inlineStr">
+        <is>
+          <t>电池</t>
+        </is>
+      </c>
+      <c r="B6" s="265" t="inlineStr">
+        <is>
+          <t>65%</t>
+        </is>
+      </c>
+      <c r="C6" s="265" t="inlineStr">
+        <is>
+          <t>+23pp</t>
+        </is>
+      </c>
+      <c r="D6" s="265" t="inlineStr">
+        <is>
+          <t>97分</t>
+        </is>
+      </c>
+      <c r="E6" s="265" t="inlineStr">
+        <is>
+          <t>-2.1%</t>
+        </is>
+      </c>
+      <c r="F6" s="265" t="inlineStr">
+        <is>
+          <t>-8.1%</t>
+        </is>
+      </c>
+      <c r="G6" s="265" t="inlineStr">
+        <is>
+          <t>+6.0%</t>
+        </is>
+      </c>
+      <c r="H6" s="265" t="inlineStr">
+        <is>
+          <t>方向一致</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="265" t="inlineStr">
+        <is>
+          <t>恒科</t>
+        </is>
+      </c>
+      <c r="B7" s="265" t="inlineStr">
+        <is>
+          <t>27%</t>
+        </is>
+      </c>
+      <c r="C7" s="265" t="inlineStr">
+        <is>
+          <t>-16pp</t>
+        </is>
+      </c>
+      <c r="D7" s="265" t="inlineStr">
+        <is>
+          <t>75分</t>
+        </is>
+      </c>
+      <c r="E7" s="265" t="inlineStr">
+        <is>
+          <t>-1.6%</t>
+        </is>
+      </c>
+      <c r="F7" s="265" t="inlineStr">
+        <is>
+          <t>-3.4%</t>
+        </is>
+      </c>
+      <c r="G7" s="265" t="inlineStr">
+        <is>
+          <t>-6.0%</t>
+        </is>
+      </c>
+      <c r="H7" s="265" t="inlineStr">
+        <is>
+          <t>方向一致</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="265" t="inlineStr">
+        <is>
+          <t>养殖</t>
+        </is>
+      </c>
+      <c r="B8" s="265" t="inlineStr">
+        <is>
+          <t>70%</t>
+        </is>
+      </c>
+      <c r="C8" s="265" t="inlineStr">
+        <is>
+          <t>+15pp</t>
+        </is>
+      </c>
+      <c r="D8" s="265" t="inlineStr">
+        <is>
+          <t>95分</t>
+        </is>
+      </c>
+      <c r="E8" s="265" t="inlineStr">
+        <is>
+          <t>-2.6%</t>
+        </is>
+      </c>
+      <c r="F8" s="265" t="inlineStr">
+        <is>
+          <t>-14.3%</t>
+        </is>
+      </c>
+      <c r="G8" s="265" t="inlineStr">
+        <is>
+          <t>-12.5%</t>
+        </is>
+      </c>
+      <c r="H8" s="265" t="inlineStr">
+        <is>
+          <t>虚P偏高</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="265" t="inlineStr">
+        <is>
+          <t>有色</t>
+        </is>
+      </c>
+      <c r="B9" s="265" t="inlineStr">
+        <is>
+          <t>39%</t>
+        </is>
+      </c>
+      <c r="C9" s="265" t="inlineStr">
+        <is>
+          <t>-11pp</t>
+        </is>
+      </c>
+      <c r="D9" s="265" t="inlineStr">
+        <is>
+          <t>0分</t>
+        </is>
+      </c>
+      <c r="E9" s="265" t="inlineStr">
+        <is>
+          <t>-3.0%</t>
+        </is>
+      </c>
+      <c r="F9" s="265" t="inlineStr">
+        <is>
+          <t>-10.7%</t>
+        </is>
+      </c>
+      <c r="G9" s="265" t="inlineStr">
+        <is>
+          <t>-0.4%</t>
+        </is>
+      </c>
+      <c r="H9" s="265" t="inlineStr">
+        <is>
+          <t>拟合失效</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="265" t="inlineStr">
+        <is>
+          <t>稀金</t>
+        </is>
+      </c>
+      <c r="B10" s="265" t="inlineStr">
+        <is>
+          <t>40%</t>
+        </is>
+      </c>
+      <c r="C10" s="265" t="inlineStr">
+        <is>
+          <t>-10pp</t>
+        </is>
+      </c>
+      <c r="D10" s="265" t="inlineStr">
+        <is>
+          <t>0分</t>
+        </is>
+      </c>
+      <c r="E10" s="265" t="inlineStr">
+        <is>
+          <t>+0.0%</t>
+        </is>
+      </c>
+      <c r="F10" s="265" t="inlineStr">
+        <is>
+          <t>+0.0%</t>
+        </is>
+      </c>
+      <c r="G10" s="265" t="inlineStr">
+        <is>
+          <t>+0.8%</t>
+        </is>
+      </c>
+      <c r="H10" s="265" t="inlineStr">
+        <is>
+          <t>拟合失效</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="265" t="inlineStr">
+        <is>
+          <t>银行</t>
+        </is>
+      </c>
+      <c r="B11" s="265" t="inlineStr">
+        <is>
+          <t>47%</t>
+        </is>
+      </c>
+      <c r="C11" s="265" t="inlineStr">
+        <is>
+          <t>-3pp</t>
+        </is>
+      </c>
+      <c r="D11" s="265" t="inlineStr">
+        <is>
+          <t>53分</t>
+        </is>
+      </c>
+      <c r="E11" s="265" t="inlineStr">
+        <is>
+          <t>-1.1%</t>
+        </is>
+      </c>
+      <c r="F11" s="265" t="inlineStr">
+        <is>
+          <t>-1.4%</t>
+        </is>
+      </c>
+      <c r="G11" s="265" t="inlineStr">
+        <is>
+          <t>+0.0%</t>
+        </is>
+      </c>
+      <c r="H11" s="265" t="inlineStr">
+        <is>
+          <t>方向一致</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="265" t="inlineStr">
+        <is>
+          <t>黄金</t>
+        </is>
+      </c>
+      <c r="B12" s="265" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="C12" s="265" t="inlineStr">
+        <is>
+          <t>+0pp</t>
+        </is>
+      </c>
+      <c r="D12" s="265" t="inlineStr">
+        <is>
+          <t>0分</t>
+        </is>
+      </c>
+      <c r="E12" s="265" t="inlineStr">
+        <is>
+          <t>+0.1%</t>
+        </is>
+      </c>
+      <c r="F12" s="265" t="inlineStr">
+        <is>
+          <t>-6.0%</t>
+        </is>
+      </c>
+      <c r="G12" s="265" t="inlineStr">
+        <is>
+          <t>+0.0%</t>
+        </is>
+      </c>
+      <c r="H12" s="265" t="inlineStr">
+        <is>
+          <t>拟合失效</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="271" t="inlineStr">
+        <is>
+          <t>二、事件传导矩阵</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="272" t="inlineStr">
+        <is>
+          <t>源头事件</t>
+        </is>
+      </c>
+      <c r="B15" s="272" t="inlineStr">
+        <is>
+          <t>品种</t>
+        </is>
+      </c>
+      <c r="C15" s="272" t="inlineStr">
+        <is>
+          <t>传导PP</t>
+        </is>
+      </c>
+      <c r="D15" s="272" t="inlineStr">
+        <is>
+          <t>方向</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="265" t="inlineStr">
+        <is>
+          <t>AI/科技</t>
+        </is>
+      </c>
+      <c r="B16" s="265" t="inlineStr">
+        <is>
+          <t>恒科</t>
+        </is>
+      </c>
+      <c r="C16" s="265" t="inlineStr">
+        <is>
+          <t>-5pp</t>
+        </is>
+      </c>
+      <c r="D16" s="265" t="inlineStr">
+        <is>
+          <t>⬇利空</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="265" t="n"/>
+      <c r="B17" s="265" t="inlineStr">
+        <is>
+          <t>有色</t>
+        </is>
+      </c>
+      <c r="C17" s="265" t="inlineStr">
+        <is>
+          <t>+2pp</t>
+        </is>
+      </c>
+      <c r="D17" s="265" t="inlineStr">
+        <is>
+          <t>⬆利好</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="265" t="n"/>
+      <c r="B18" s="265" t="inlineStr">
+        <is>
+          <t>芯片</t>
+        </is>
+      </c>
+      <c r="C18" s="265" t="inlineStr">
+        <is>
+          <t>+5pp</t>
+        </is>
+      </c>
+      <c r="D18" s="265" t="inlineStr">
+        <is>
+          <t>⬆利好</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="265" t="inlineStr">
+        <is>
+          <t>关税/贸易</t>
+        </is>
+      </c>
+      <c r="B19" s="265" t="inlineStr">
+        <is>
+          <t>有色</t>
+        </is>
+      </c>
+      <c r="C19" s="265" t="inlineStr">
+        <is>
+          <t>-5pp</t>
+        </is>
+      </c>
+      <c r="D19" s="265" t="inlineStr">
+        <is>
+          <t>⬇利空</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="265" t="n"/>
+      <c r="B20" s="265" t="inlineStr">
+        <is>
+          <t>稀金</t>
+        </is>
+      </c>
+      <c r="C20" s="265" t="inlineStr">
+        <is>
+          <t>-3pp</t>
+        </is>
+      </c>
+      <c r="D20" s="265" t="inlineStr">
+        <is>
+          <t>⬇利空</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="265" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="B21" s="265" t="inlineStr">
+        <is>
+          <t>有色</t>
+        </is>
+      </c>
+      <c r="C21" s="265" t="inlineStr">
+        <is>
+          <t>-8pp</t>
+        </is>
+      </c>
+      <c r="D21" s="265" t="inlineStr">
+        <is>
+          <t>⬇利空</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="265" t="n"/>
+      <c r="B22" s="265" t="inlineStr">
+        <is>
+          <t>稀金</t>
+        </is>
+      </c>
+      <c r="C22" s="265" t="inlineStr">
+        <is>
+          <t>-5pp</t>
+        </is>
+      </c>
+      <c r="D22" s="265" t="inlineStr">
+        <is>
+          <t>⬇利空</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="265" t="n"/>
+      <c r="B23" s="265" t="inlineStr">
+        <is>
+          <t>恒科</t>
+        </is>
+      </c>
+      <c r="C23" s="265" t="inlineStr">
+        <is>
+          <t>-4pp</t>
+        </is>
+      </c>
+      <c r="D23" s="265" t="inlineStr">
+        <is>
+          <t>⬇利空</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="265" t="n"/>
+      <c r="B24" s="265" t="inlineStr">
+        <is>
+          <t>芯片</t>
+        </is>
+      </c>
+      <c r="C24" s="265" t="inlineStr">
+        <is>
+          <t>-2pp</t>
+        </is>
+      </c>
+      <c r="D24" s="265" t="inlineStr">
+        <is>
+          <t>⬇利空</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="265" t="n"/>
+      <c r="B25" s="265" t="inlineStr">
+        <is>
+          <t>电池</t>
+        </is>
+      </c>
+      <c r="C25" s="265" t="inlineStr">
+        <is>
+          <t>+16pp</t>
+        </is>
+      </c>
+      <c r="D25" s="265" t="inlineStr">
+        <is>
+          <t>⬆利好</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="265" t="inlineStr">
+        <is>
+          <t>利率上行</t>
+        </is>
+      </c>
+      <c r="B26" s="265" t="inlineStr">
+        <is>
+          <t>芯片</t>
+        </is>
+      </c>
+      <c r="C26" s="265" t="inlineStr">
+        <is>
+          <t>-8pp</t>
+        </is>
+      </c>
+      <c r="D26" s="265" t="inlineStr">
+        <is>
+          <t>⬇利空</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="265" t="n"/>
+      <c r="B27" s="265" t="inlineStr">
+        <is>
+          <t>恒科</t>
+        </is>
+      </c>
+      <c r="C27" s="265" t="inlineStr">
+        <is>
+          <t>-7pp</t>
+        </is>
+      </c>
+      <c r="D27" s="265" t="inlineStr">
+        <is>
+          <t>⬇利空</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="265" t="n"/>
+      <c r="B28" s="265" t="inlineStr">
+        <is>
+          <t>稀金</t>
+        </is>
+      </c>
+      <c r="C28" s="265" t="inlineStr">
+        <is>
+          <t>-3pp</t>
+        </is>
+      </c>
+      <c r="D28" s="265" t="inlineStr">
+        <is>
+          <t>⬇利空</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="265" t="n"/>
+      <c r="B29" s="265" t="inlineStr">
+        <is>
+          <t>银行</t>
+        </is>
+      </c>
+      <c r="C29" s="265" t="inlineStr">
+        <is>
+          <t>-1pp</t>
+        </is>
+      </c>
+      <c r="D29" s="265" t="inlineStr">
+        <is>
+          <t>⬇利空</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="265" t="n"/>
+      <c r="B30" s="265" t="inlineStr">
+        <is>
+          <t>电池</t>
+        </is>
+      </c>
+      <c r="C30" s="265" t="inlineStr">
+        <is>
+          <t>+1pp</t>
+        </is>
+      </c>
+      <c r="D30" s="265" t="inlineStr">
+        <is>
+          <t>⬆利好</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="265" t="inlineStr">
+        <is>
+          <t>宏观/消费</t>
+        </is>
+      </c>
+      <c r="B31" s="265" t="inlineStr">
+        <is>
+          <t>养殖</t>
+        </is>
+      </c>
+      <c r="C31" s="265" t="inlineStr">
+        <is>
+          <t>-4pp</t>
+        </is>
+      </c>
+      <c r="D31" s="265" t="inlineStr">
+        <is>
+          <t>⬇利空</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="265" t="n"/>
+      <c r="B32" s="265" t="inlineStr">
+        <is>
+          <t>银行</t>
+        </is>
+      </c>
+      <c r="C32" s="265" t="inlineStr">
+        <is>
+          <t>-2pp</t>
+        </is>
+      </c>
+      <c r="D32" s="265" t="inlineStr">
+        <is>
+          <t>⬇利空</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="265" t="inlineStr">
+        <is>
+          <t>霍尔木兹/能源</t>
+        </is>
+      </c>
+      <c r="B33" s="265" t="inlineStr">
+        <is>
+          <t>芯片</t>
+        </is>
+      </c>
+      <c r="C33" s="265" t="inlineStr">
+        <is>
+          <t>+1pp</t>
+        </is>
+      </c>
+      <c r="D33" s="265" t="inlineStr">
+        <is>
+          <t>⬆利好</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="265" t="n"/>
+      <c r="B34" s="265" t="inlineStr">
+        <is>
+          <t>电池</t>
+        </is>
+      </c>
+      <c r="C34" s="265" t="inlineStr">
+        <is>
+          <t>+6pp</t>
+        </is>
+      </c>
+      <c r="D34" s="265" t="inlineStr">
+        <is>
+          <t>⬆利好</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="265" t="n"/>
+      <c r="B35" s="265" t="inlineStr">
+        <is>
+          <t>养殖</t>
+        </is>
+      </c>
+      <c r="C35" s="265" t="inlineStr">
+        <is>
+          <t>+9pp</t>
+        </is>
+      </c>
+      <c r="D35" s="265" t="inlineStr">
+        <is>
+          <t>⬆利好</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="271" t="inlineStr">
+        <is>
+          <t>三、跨品种传导系数</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="272" t="inlineStr">
+        <is>
+          <t>品种</t>
+        </is>
+      </c>
+      <c r="B38" s="272" t="inlineStr">
+        <is>
+          <t>芯片</t>
+        </is>
+      </c>
+      <c r="C38" s="272" t="inlineStr">
+        <is>
+          <t>电池</t>
+        </is>
+      </c>
+      <c r="D38" s="272" t="inlineStr">
+        <is>
+          <t>恒科</t>
+        </is>
+      </c>
+      <c r="E38" s="272" t="inlineStr">
+        <is>
+          <t>养殖</t>
+        </is>
+      </c>
+      <c r="F38" s="272" t="inlineStr">
+        <is>
+          <t>有色</t>
+        </is>
+      </c>
+      <c r="G38" s="272" t="inlineStr">
+        <is>
+          <t>银行</t>
+        </is>
+      </c>
+      <c r="H38" s="272" t="inlineStr">
+        <is>
+          <t>黄金</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="265" t="inlineStr">
+        <is>
+          <t>芯片</t>
+        </is>
+      </c>
+      <c r="B39" s="265" t="inlineStr">
+        <is>
+          <t>自身</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="C40" s="265" t="inlineStr">
+        <is>
+          <t>反向(3源)</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="D41" s="265" t="inlineStr">
+        <is>
+          <t>同向(3源)</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="E42" s="265" t="inlineStr">
+        <is>
+          <t>同向(1源)</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="F43" s="265" t="inlineStr">
+        <is>
+          <t>反向(2源)</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="G44" s="265" t="inlineStr">
+        <is>
+          <t>同向(1源)</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="H45" s="265" t="inlineStr">
+        <is>
+          <t>无传导</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="265" t="inlineStr">
+        <is>
+          <t>电池</t>
+        </is>
+      </c>
+      <c r="B46" s="265" t="inlineStr">
+        <is>
+          <t>反向(3源)</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="C47" s="265" t="inlineStr">
+        <is>
+          <t>自身</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="D48" s="265" t="inlineStr">
+        <is>
+          <t>反向(2源)</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="E49" s="265" t="inlineStr">
+        <is>
+          <t>同向(1源)</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="F50" s="265" t="inlineStr">
+        <is>
+          <t>反向(1源)</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="G51" s="265" t="inlineStr">
+        <is>
+          <t>反向(1源)</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="H52" s="265" t="inlineStr">
+        <is>
+          <t>无传导</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="265" t="inlineStr">
+        <is>
+          <t>恒科</t>
+        </is>
+      </c>
+      <c r="B53" s="265" t="inlineStr">
+        <is>
+          <t>同向(3源)</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="C54" s="265" t="inlineStr">
+        <is>
+          <t>反向(2源)</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="D55" s="265" t="inlineStr">
+        <is>
+          <t>自身</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="E56" s="265" t="inlineStr">
+        <is>
+          <t>无传导</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="F57" s="265" t="inlineStr">
+        <is>
+          <t>同向(2源)</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="G58" s="265" t="inlineStr">
+        <is>
+          <t>同向(1源)</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="H59" s="265" t="inlineStr">
+        <is>
+          <t>无传导</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="265" t="inlineStr">
+        <is>
+          <t>养殖</t>
+        </is>
+      </c>
+      <c r="B60" s="265" t="inlineStr">
+        <is>
+          <t>同向(1源)</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="C61" s="265" t="inlineStr">
+        <is>
+          <t>同向(1源)</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="D62" s="265" t="inlineStr">
+        <is>
+          <t>无传导</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="E63" s="265" t="inlineStr">
+        <is>
+          <t>自身</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="F64" s="265" t="inlineStr">
+        <is>
+          <t>无传导</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="G65" s="265" t="inlineStr">
+        <is>
+          <t>同向(1源)</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="H66" s="265" t="inlineStr">
+        <is>
+          <t>无传导</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="265" t="inlineStr">
+        <is>
+          <t>有色</t>
+        </is>
+      </c>
+      <c r="B67" s="265" t="inlineStr">
+        <is>
+          <t>反向(2源)</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="C68" s="265" t="inlineStr">
+        <is>
+          <t>反向(1源)</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="D69" s="265" t="inlineStr">
+        <is>
+          <t>同向(2源)</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="E70" s="265" t="inlineStr">
+        <is>
+          <t>无传导</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="F71" s="265" t="inlineStr">
+        <is>
+          <t>自身</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="G72" s="265" t="inlineStr">
+        <is>
+          <t>无传导</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="H73" s="265" t="inlineStr">
+        <is>
+          <t>无传导</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="265" t="inlineStr">
+        <is>
+          <t>银行</t>
+        </is>
+      </c>
+      <c r="B74" s="265" t="inlineStr">
+        <is>
+          <t>同向(1源)</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="C75" s="265" t="inlineStr">
+        <is>
+          <t>反向(1源)</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="D76" s="265" t="inlineStr">
+        <is>
+          <t>同向(1源)</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="E77" s="265" t="inlineStr">
+        <is>
+          <t>同向(1源)</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="F78" s="265" t="inlineStr">
+        <is>
+          <t>无传导</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="G79" s="265" t="inlineStr">
+        <is>
+          <t>自身</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="H80" s="265" t="inlineStr">
+        <is>
+          <t>无传导</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="265" t="inlineStr">
+        <is>
+          <t>黄金</t>
+        </is>
+      </c>
+      <c r="B81" s="265" t="inlineStr">
+        <is>
+          <t>无传导</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="C82" s="265" t="inlineStr">
+        <is>
+          <t>无传导</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="D83" s="265" t="inlineStr">
+        <is>
+          <t>无传导</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="E84" s="265" t="inlineStr">
+        <is>
+          <t>无传导</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="F85" s="265" t="inlineStr">
+        <is>
+          <t>无传导</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="G86" s="265" t="inlineStr">
+        <is>
+          <t>无传导</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="H87" s="265" t="inlineStr">
+        <is>
+          <t>自身</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="271" t="inlineStr">
+        <is>
+          <t>四、P值修正建议</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="267" t="inlineStr">
+        <is>
+          <t>P=41% → 建议45% (存储→芯片资金传导+4pp)</t>
+        </is>
+      </c>
+      <c r="B90" s="149" t="n"/>
+      <c r="C90" s="149" t="n"/>
+      <c r="D90" s="149" t="n"/>
+      <c r="E90" s="149" t="n"/>
+      <c r="F90" s="149" t="n"/>
+      <c r="G90" s="149" t="n"/>
+      <c r="H90" s="150" t="n"/>
+    </row>
+    <row r="91">
+      <c r="A91" s="267" t="inlineStr">
+        <is>
+          <t>P=70% → 建议60-65% (持有亏12.5%→虚P偏高)</t>
+        </is>
+      </c>
+      <c r="B91" s="149" t="n"/>
+      <c r="C91" s="149" t="n"/>
+      <c r="D91" s="149" t="n"/>
+      <c r="E91" s="149" t="n"/>
+      <c r="F91" s="149" t="n"/>
+      <c r="G91" s="149" t="n"/>
+      <c r="H91" s="150" t="n"/>
+    </row>
+    <row r="92">
+      <c r="A92" s="267" t="inlineStr">
+        <is>
+          <t>P=39%维持 (事件链-11pp与价格-10.7%方向一致)</t>
+        </is>
+      </c>
+      <c r="B92" s="149" t="n"/>
+      <c r="C92" s="149" t="n"/>
+      <c r="D92" s="149" t="n"/>
+      <c r="E92" s="149" t="n"/>
+      <c r="F92" s="149" t="n"/>
+      <c r="G92" s="149" t="n"/>
+      <c r="H92" s="150" t="n"/>
+    </row>
+    <row r="93">
+      <c r="A93" s="267" t="inlineStr">
+        <is>
+          <t>P=65%维持 (拟合97分，方向正确)</t>
+        </is>
+      </c>
+      <c r="B93" s="149" t="n"/>
+      <c r="C93" s="149" t="n"/>
+      <c r="D93" s="149" t="n"/>
+      <c r="E93" s="149" t="n"/>
+      <c r="F93" s="149" t="n"/>
+      <c r="G93" s="149" t="n"/>
+      <c r="H93" s="150" t="n"/>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="A92:H92"/>
+    <mergeCell ref="A91:H91"/>
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A90:H90"/>
+    <mergeCell ref="A93:H93"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/持仓贝叶斯跟踪.xlsx
+++ b/持仓贝叶斯跟踪.xlsx
@@ -15,6 +15,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="基金数据联动" sheetId="6" state="visible" r:id="rId6"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="持仓盈亏联动" sheetId="7" state="visible" r:id="rId7"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="跨品种传导" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="持仓盈亏联动分析" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1" refMode="A1" iterate="0" iterateCount="100" iterateDelta="0.0001"/>
@@ -13508,4 +13509,1139 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J54"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="20" customWidth="1" style="139" min="1" max="1"/>
+    <col width="15" customWidth="1" style="139" min="2" max="2"/>
+    <col width="15" customWidth="1" style="139" min="3" max="3"/>
+    <col width="15" customWidth="1" style="139" min="4" max="4"/>
+    <col width="15" customWidth="1" style="139" min="5" max="5"/>
+    <col width="15" customWidth="1" style="139" min="6" max="6"/>
+    <col width="15" customWidth="1" style="139" min="7" max="7"/>
+    <col width="15" customWidth="1" style="139" min="8" max="8"/>
+    <col width="15" customWidth="1" style="139" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="270" t="inlineStr">
+        <is>
+          <t>🔀 持仓盈亏联动与跨品种联合分析 (2026-06-05)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="271" t="inlineStr">
+        <is>
+          <t>一、持仓盈亏总览</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="272" t="inlineStr">
+        <is>
+          <t>持仓</t>
+        </is>
+      </c>
+      <c r="B4" s="272" t="inlineStr">
+        <is>
+          <t>P值</t>
+        </is>
+      </c>
+      <c r="C4" s="272" t="inlineStr">
+        <is>
+          <t>事件PP</t>
+        </is>
+      </c>
+      <c r="D4" s="272" t="inlineStr">
+        <is>
+          <t>拟合分</t>
+        </is>
+      </c>
+      <c r="E4" s="272" t="inlineStr">
+        <is>
+          <t>持有收益率</t>
+        </is>
+      </c>
+      <c r="F4" s="272" t="inlineStr">
+        <is>
+          <t>20日涨跌%</t>
+        </is>
+      </c>
+      <c r="G4" s="272" t="inlineStr">
+        <is>
+          <t>今日涨跌%</t>
+        </is>
+      </c>
+      <c r="H4" s="272" t="inlineStr">
+        <is>
+          <t>市值</t>
+        </is>
+      </c>
+      <c r="I4" s="272" t="inlineStr">
+        <is>
+          <t>诊断</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="265" t="inlineStr">
+        <is>
+          <t>芯片</t>
+        </is>
+      </c>
+      <c r="B5" s="265" t="inlineStr">
+        <is>
+          <t>41%</t>
+        </is>
+      </c>
+      <c r="C5" s="265" t="inlineStr">
+        <is>
+          <t>-4pp</t>
+        </is>
+      </c>
+      <c r="D5" s="265" t="inlineStr">
+        <is>
+          <t>0分</t>
+        </is>
+      </c>
+      <c r="E5" s="265" t="inlineStr">
+        <is>
+          <t>+3.93%</t>
+        </is>
+      </c>
+      <c r="F5" s="265" t="inlineStr">
+        <is>
+          <t>+29.47%</t>
+        </is>
+      </c>
+      <c r="G5" s="265" t="inlineStr">
+        <is>
+          <t>+1.89%</t>
+        </is>
+      </c>
+      <c r="H5" s="265" t="inlineStr">
+        <is>
+          <t>3332</t>
+        </is>
+      </c>
+      <c r="I5" s="265" t="inlineStr">
+        <is>
+          <t>价格涨29.5%但事件链净-4pp→漏正向; 拟合0分→P值不可信</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="265" t="inlineStr">
+        <is>
+          <t>电池</t>
+        </is>
+      </c>
+      <c r="B6" s="265" t="inlineStr">
+        <is>
+          <t>65%</t>
+        </is>
+      </c>
+      <c r="C6" s="265" t="inlineStr">
+        <is>
+          <t>+23pp</t>
+        </is>
+      </c>
+      <c r="D6" s="265" t="inlineStr">
+        <is>
+          <t>97分</t>
+        </is>
+      </c>
+      <c r="E6" s="265" t="inlineStr">
+        <is>
+          <t>+6.01%</t>
+        </is>
+      </c>
+      <c r="F6" s="265" t="inlineStr">
+        <is>
+          <t>+3.84%</t>
+        </is>
+      </c>
+      <c r="G6" s="265" t="inlineStr">
+        <is>
+          <t>-2.07%</t>
+        </is>
+      </c>
+      <c r="H6" s="265" t="inlineStr">
+        <is>
+          <t>7220</t>
+        </is>
+      </c>
+      <c r="I6" s="265" t="inlineStr">
+        <is>
+          <t>方向一致</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="265" t="inlineStr">
+        <is>
+          <t>恒科</t>
+        </is>
+      </c>
+      <c r="B7" s="265" t="inlineStr">
+        <is>
+          <t>27%</t>
+        </is>
+      </c>
+      <c r="C7" s="265" t="inlineStr">
+        <is>
+          <t>-16pp</t>
+        </is>
+      </c>
+      <c r="D7" s="265" t="inlineStr">
+        <is>
+          <t>75分</t>
+        </is>
+      </c>
+      <c r="E7" s="265" t="inlineStr">
+        <is>
+          <t>-5.95%</t>
+        </is>
+      </c>
+      <c r="F7" s="265" t="inlineStr">
+        <is>
+          <t>-4.93%</t>
+        </is>
+      </c>
+      <c r="G7" s="265" t="inlineStr">
+        <is>
+          <t>+0.00%</t>
+        </is>
+      </c>
+      <c r="H7" s="265" t="inlineStr">
+        <is>
+          <t>4535</t>
+        </is>
+      </c>
+      <c r="I7" s="265" t="inlineStr">
+        <is>
+          <t>方向一致</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="265" t="inlineStr">
+        <is>
+          <t>养殖</t>
+        </is>
+      </c>
+      <c r="B8" s="265" t="inlineStr">
+        <is>
+          <t>70%</t>
+        </is>
+      </c>
+      <c r="C8" s="265" t="inlineStr">
+        <is>
+          <t>+15pp</t>
+        </is>
+      </c>
+      <c r="D8" s="265" t="inlineStr">
+        <is>
+          <t>95分</t>
+        </is>
+      </c>
+      <c r="E8" s="265" t="inlineStr">
+        <is>
+          <t>-12.49%</t>
+        </is>
+      </c>
+      <c r="F8" s="265" t="inlineStr">
+        <is>
+          <t>-15.68%</t>
+        </is>
+      </c>
+      <c r="G8" s="265" t="inlineStr">
+        <is>
+          <t>+0.00%</t>
+        </is>
+      </c>
+      <c r="H8" s="265" t="inlineStr">
+        <is>
+          <t>3878</t>
+        </is>
+      </c>
+      <c r="I8" s="265" t="inlineStr">
+        <is>
+          <t>价格跌-15.7%但事件链净+15pp→漏负向; P=70%乐观但持有亏-12.5%→虚P过高</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="265" t="inlineStr">
+        <is>
+          <t>有色</t>
+        </is>
+      </c>
+      <c r="B9" s="265" t="inlineStr">
+        <is>
+          <t>39%</t>
+        </is>
+      </c>
+      <c r="C9" s="265" t="inlineStr">
+        <is>
+          <t>-11pp</t>
+        </is>
+      </c>
+      <c r="D9" s="265" t="inlineStr">
+        <is>
+          <t>0分</t>
+        </is>
+      </c>
+      <c r="E9" s="265" t="inlineStr">
+        <is>
+          <t>-0.41%</t>
+        </is>
+      </c>
+      <c r="F9" s="265" t="inlineStr">
+        <is>
+          <t>+0.00%</t>
+        </is>
+      </c>
+      <c r="G9" s="265" t="inlineStr">
+        <is>
+          <t>+0.00%</t>
+        </is>
+      </c>
+      <c r="H9" s="265" t="inlineStr">
+        <is>
+          <t>4781</t>
+        </is>
+      </c>
+      <c r="I9" s="265" t="inlineStr">
+        <is>
+          <t>拟合0分→P值不可信</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="265" t="inlineStr">
+        <is>
+          <t>稀金</t>
+        </is>
+      </c>
+      <c r="B10" s="265" t="inlineStr">
+        <is>
+          <t>40%</t>
+        </is>
+      </c>
+      <c r="C10" s="265" t="inlineStr">
+        <is>
+          <t>-10pp</t>
+        </is>
+      </c>
+      <c r="D10" s="265" t="inlineStr">
+        <is>
+          <t>0分</t>
+        </is>
+      </c>
+      <c r="E10" s="265" t="inlineStr">
+        <is>
+          <t>+0.85%</t>
+        </is>
+      </c>
+      <c r="F10" s="265" t="inlineStr">
+        <is>
+          <t>+0.00%</t>
+        </is>
+      </c>
+      <c r="G10" s="265" t="inlineStr">
+        <is>
+          <t>+0.00%</t>
+        </is>
+      </c>
+      <c r="H10" s="265" t="inlineStr">
+        <is>
+          <t>5872</t>
+        </is>
+      </c>
+      <c r="I10" s="265" t="inlineStr">
+        <is>
+          <t>拟合0分→P值不可信</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="265" t="inlineStr">
+        <is>
+          <t>银行</t>
+        </is>
+      </c>
+      <c r="B11" s="265" t="inlineStr">
+        <is>
+          <t>47%</t>
+        </is>
+      </c>
+      <c r="C11" s="265" t="inlineStr">
+        <is>
+          <t>-3pp</t>
+        </is>
+      </c>
+      <c r="D11" s="265" t="inlineStr">
+        <is>
+          <t>53分</t>
+        </is>
+      </c>
+      <c r="E11" s="265" t="inlineStr">
+        <is>
+          <t>+0.00%</t>
+        </is>
+      </c>
+      <c r="F11" s="265" t="inlineStr">
+        <is>
+          <t>-1.40%</t>
+        </is>
+      </c>
+      <c r="G11" s="265" t="inlineStr">
+        <is>
+          <t>-1.15%</t>
+        </is>
+      </c>
+      <c r="H11" s="265" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I11" s="265" t="inlineStr">
+        <is>
+          <t>方向一致</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="265" t="inlineStr">
+        <is>
+          <t>黄金</t>
+        </is>
+      </c>
+      <c r="B12" s="265" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="C12" s="265" t="inlineStr">
+        <is>
+          <t>+0pp</t>
+        </is>
+      </c>
+      <c r="D12" s="265" t="inlineStr">
+        <is>
+          <t>0分</t>
+        </is>
+      </c>
+      <c r="E12" s="265" t="inlineStr">
+        <is>
+          <t>+0.00%</t>
+        </is>
+      </c>
+      <c r="F12" s="265" t="inlineStr">
+        <is>
+          <t>-15.01%</t>
+        </is>
+      </c>
+      <c r="G12" s="265" t="inlineStr">
+        <is>
+          <t>+0.10%</t>
+        </is>
+      </c>
+      <c r="H12" s="265" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I12" s="265" t="inlineStr">
+        <is>
+          <t>价格跌-15.0%但事件链净+0pp→漏负向</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="271" t="inlineStr">
+        <is>
+          <t>二、事件传导矩阵</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="272" t="inlineStr">
+        <is>
+          <t>源头事件</t>
+        </is>
+      </c>
+      <c r="B15" s="272" t="inlineStr">
+        <is>
+          <t>品种</t>
+        </is>
+      </c>
+      <c r="C15" s="272" t="inlineStr">
+        <is>
+          <t>传导PP</t>
+        </is>
+      </c>
+      <c r="D15" s="272" t="inlineStr">
+        <is>
+          <t>方向</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="265" t="inlineStr">
+        <is>
+          <t>AI/科技</t>
+        </is>
+      </c>
+      <c r="B16" s="265" t="inlineStr">
+        <is>
+          <t>恒科</t>
+        </is>
+      </c>
+      <c r="C16" s="265" t="inlineStr">
+        <is>
+          <t>-5pp</t>
+        </is>
+      </c>
+      <c r="D16" s="265" t="inlineStr">
+        <is>
+          <t>⬇利空</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" s="265" t="inlineStr">
+        <is>
+          <t>有色</t>
+        </is>
+      </c>
+      <c r="C17" s="265" t="inlineStr">
+        <is>
+          <t>+2pp</t>
+        </is>
+      </c>
+      <c r="D17" s="265" t="inlineStr">
+        <is>
+          <t>⬆利好</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" s="265" t="inlineStr">
+        <is>
+          <t>芯片</t>
+        </is>
+      </c>
+      <c r="C18" s="265" t="inlineStr">
+        <is>
+          <t>+5pp</t>
+        </is>
+      </c>
+      <c r="D18" s="265" t="inlineStr">
+        <is>
+          <t>⬆利好</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="265" t="inlineStr">
+        <is>
+          <t>关税/贸易</t>
+        </is>
+      </c>
+      <c r="B19" s="265" t="inlineStr">
+        <is>
+          <t>有色</t>
+        </is>
+      </c>
+      <c r="C19" s="265" t="inlineStr">
+        <is>
+          <t>-5pp</t>
+        </is>
+      </c>
+      <c r="D19" s="265" t="inlineStr">
+        <is>
+          <t>⬇利空</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" s="265" t="inlineStr">
+        <is>
+          <t>稀金</t>
+        </is>
+      </c>
+      <c r="C20" s="265" t="inlineStr">
+        <is>
+          <t>-3pp</t>
+        </is>
+      </c>
+      <c r="D20" s="265" t="inlineStr">
+        <is>
+          <t>⬇利空</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="265" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="B21" s="265" t="inlineStr">
+        <is>
+          <t>有色</t>
+        </is>
+      </c>
+      <c r="C21" s="265" t="inlineStr">
+        <is>
+          <t>-8pp</t>
+        </is>
+      </c>
+      <c r="D21" s="265" t="inlineStr">
+        <is>
+          <t>⬇利空</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" s="265" t="inlineStr">
+        <is>
+          <t>稀金</t>
+        </is>
+      </c>
+      <c r="C22" s="265" t="inlineStr">
+        <is>
+          <t>-5pp</t>
+        </is>
+      </c>
+      <c r="D22" s="265" t="inlineStr">
+        <is>
+          <t>⬇利空</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" s="265" t="inlineStr">
+        <is>
+          <t>恒科</t>
+        </is>
+      </c>
+      <c r="C23" s="265" t="inlineStr">
+        <is>
+          <t>-4pp</t>
+        </is>
+      </c>
+      <c r="D23" s="265" t="inlineStr">
+        <is>
+          <t>⬇利空</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" s="265" t="inlineStr">
+        <is>
+          <t>芯片</t>
+        </is>
+      </c>
+      <c r="C24" s="265" t="inlineStr">
+        <is>
+          <t>-2pp</t>
+        </is>
+      </c>
+      <c r="D24" s="265" t="inlineStr">
+        <is>
+          <t>⬇利空</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" s="265" t="inlineStr">
+        <is>
+          <t>电池</t>
+        </is>
+      </c>
+      <c r="C25" s="265" t="inlineStr">
+        <is>
+          <t>+16pp</t>
+        </is>
+      </c>
+      <c r="D25" s="265" t="inlineStr">
+        <is>
+          <t>⬆利好</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="265" t="inlineStr">
+        <is>
+          <t>利率上行</t>
+        </is>
+      </c>
+      <c r="B26" s="265" t="inlineStr">
+        <is>
+          <t>芯片</t>
+        </is>
+      </c>
+      <c r="C26" s="265" t="inlineStr">
+        <is>
+          <t>-8pp</t>
+        </is>
+      </c>
+      <c r="D26" s="265" t="inlineStr">
+        <is>
+          <t>⬇利空</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" s="265" t="inlineStr">
+        <is>
+          <t>恒科</t>
+        </is>
+      </c>
+      <c r="C27" s="265" t="inlineStr">
+        <is>
+          <t>-7pp</t>
+        </is>
+      </c>
+      <c r="D27" s="265" t="inlineStr">
+        <is>
+          <t>⬇利空</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="B28" s="265" t="inlineStr">
+        <is>
+          <t>稀金</t>
+        </is>
+      </c>
+      <c r="C28" s="265" t="inlineStr">
+        <is>
+          <t>-3pp</t>
+        </is>
+      </c>
+      <c r="D28" s="265" t="inlineStr">
+        <is>
+          <t>⬇利空</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" s="265" t="inlineStr">
+        <is>
+          <t>银行</t>
+        </is>
+      </c>
+      <c r="C29" s="265" t="inlineStr">
+        <is>
+          <t>-1pp</t>
+        </is>
+      </c>
+      <c r="D29" s="265" t="inlineStr">
+        <is>
+          <t>⬇利空</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="B30" s="265" t="inlineStr">
+        <is>
+          <t>电池</t>
+        </is>
+      </c>
+      <c r="C30" s="265" t="inlineStr">
+        <is>
+          <t>+1pp</t>
+        </is>
+      </c>
+      <c r="D30" s="265" t="inlineStr">
+        <is>
+          <t>⬆利好</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="265" t="inlineStr">
+        <is>
+          <t>宏观/消费</t>
+        </is>
+      </c>
+      <c r="B31" s="265" t="inlineStr">
+        <is>
+          <t>养殖</t>
+        </is>
+      </c>
+      <c r="C31" s="265" t="inlineStr">
+        <is>
+          <t>-4pp</t>
+        </is>
+      </c>
+      <c r="D31" s="265" t="inlineStr">
+        <is>
+          <t>⬇利空</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" s="265" t="inlineStr">
+        <is>
+          <t>银行</t>
+        </is>
+      </c>
+      <c r="C32" s="265" t="inlineStr">
+        <is>
+          <t>-2pp</t>
+        </is>
+      </c>
+      <c r="D32" s="265" t="inlineStr">
+        <is>
+          <t>⬇利空</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="265" t="inlineStr">
+        <is>
+          <t>霍尔木兹/能源</t>
+        </is>
+      </c>
+      <c r="B33" s="265" t="inlineStr">
+        <is>
+          <t>芯片</t>
+        </is>
+      </c>
+      <c r="C33" s="265" t="inlineStr">
+        <is>
+          <t>+1pp</t>
+        </is>
+      </c>
+      <c r="D33" s="265" t="inlineStr">
+        <is>
+          <t>⬆利好</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="B34" s="265" t="inlineStr">
+        <is>
+          <t>电池</t>
+        </is>
+      </c>
+      <c r="C34" s="265" t="inlineStr">
+        <is>
+          <t>+6pp</t>
+        </is>
+      </c>
+      <c r="D34" s="265" t="inlineStr">
+        <is>
+          <t>⬆利好</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="B35" s="265" t="inlineStr">
+        <is>
+          <t>养殖</t>
+        </is>
+      </c>
+      <c r="C35" s="265" t="inlineStr">
+        <is>
+          <t>+9pp</t>
+        </is>
+      </c>
+      <c r="D35" s="265" t="inlineStr">
+        <is>
+          <t>⬆利好</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="271" t="inlineStr">
+        <is>
+          <t>三、亏损原因诊断</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="267" t="inlineStr">
+        <is>
+          <t>🔴 核心亏损来源：</t>
+        </is>
+      </c>
+      <c r="B38" s="149" t="n"/>
+      <c r="C38" s="149" t="n"/>
+      <c r="D38" s="149" t="n"/>
+      <c r="E38" s="149" t="n"/>
+      <c r="F38" s="149" t="n"/>
+      <c r="G38" s="149" t="n"/>
+      <c r="H38" s="149" t="n"/>
+      <c r="I38" s="150" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="267" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  1. 养殖：成本4432元 持有-12.5% → 亏554元 (最大亏损源)</t>
+        </is>
+      </c>
+      <c r="B39" s="149" t="n"/>
+      <c r="C39" s="149" t="n"/>
+      <c r="D39" s="149" t="n"/>
+      <c r="E39" s="149" t="n"/>
+      <c r="F39" s="149" t="n"/>
+      <c r="G39" s="149" t="n"/>
+      <c r="H39" s="149" t="n"/>
+      <c r="I39" s="150" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="267" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  2. 恒科：成本4822元 持有-6.0% → 亏287元</t>
+        </is>
+      </c>
+      <c r="B40" s="149" t="n"/>
+      <c r="C40" s="149" t="n"/>
+      <c r="D40" s="149" t="n"/>
+      <c r="E40" s="149" t="n"/>
+      <c r="F40" s="149" t="n"/>
+      <c r="G40" s="149" t="n"/>
+      <c r="H40" s="149" t="n"/>
+      <c r="I40" s="150" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="267" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  3. 有色：成本4800元 持有-0.4% → 亏19元</t>
+        </is>
+      </c>
+      <c r="B41" s="149" t="n"/>
+      <c r="C41" s="149" t="n"/>
+      <c r="D41" s="149" t="n"/>
+      <c r="E41" s="149" t="n"/>
+      <c r="F41" s="149" t="n"/>
+      <c r="G41" s="149" t="n"/>
+      <c r="H41" s="149" t="n"/>
+      <c r="I41" s="150" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="267" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  4. 稀金：成本5822元 持有+0.8% → 赚49元 (微赚)</t>
+        </is>
+      </c>
+      <c r="B42" s="149" t="n"/>
+      <c r="C42" s="149" t="n"/>
+      <c r="D42" s="149" t="n"/>
+      <c r="E42" s="149" t="n"/>
+      <c r="F42" s="149" t="n"/>
+      <c r="G42" s="149" t="n"/>
+      <c r="H42" s="149" t="n"/>
+      <c r="I42" s="150" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="267" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  5. 电池：成本6811元 持有+6.0% → 赚410元 (最大盈利)</t>
+        </is>
+      </c>
+      <c r="B43" s="149" t="n"/>
+      <c r="C43" s="149" t="n"/>
+      <c r="D43" s="149" t="n"/>
+      <c r="E43" s="149" t="n"/>
+      <c r="F43" s="149" t="n"/>
+      <c r="G43" s="149" t="n"/>
+      <c r="H43" s="149" t="n"/>
+      <c r="I43" s="150" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="267" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  6. 芯片：成本3206元 持有+3.9% → 赚126元</t>
+        </is>
+      </c>
+      <c r="B44" s="149" t="n"/>
+      <c r="C44" s="149" t="n"/>
+      <c r="D44" s="149" t="n"/>
+      <c r="E44" s="149" t="n"/>
+      <c r="F44" s="149" t="n"/>
+      <c r="G44" s="149" t="n"/>
+      <c r="H44" s="149" t="n"/>
+      <c r="I44" s="150" t="n"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="267" t="inlineStr"/>
+      <c r="B45" s="149" t="n"/>
+      <c r="C45" s="149" t="n"/>
+      <c r="D45" s="149" t="n"/>
+      <c r="E45" s="149" t="n"/>
+      <c r="F45" s="149" t="n"/>
+      <c r="G45" s="149" t="n"/>
+      <c r="H45" s="149" t="n"/>
+      <c r="I45" s="150" t="n"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="267" t="inlineStr">
+        <is>
+          <t>🟡 今年收益转负原因：</t>
+        </is>
+      </c>
+      <c r="B46" s="149" t="n"/>
+      <c r="C46" s="149" t="n"/>
+      <c r="D46" s="149" t="n"/>
+      <c r="E46" s="149" t="n"/>
+      <c r="F46" s="149" t="n"/>
+      <c r="G46" s="149" t="n"/>
+      <c r="H46" s="149" t="n"/>
+      <c r="I46" s="150" t="n"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="267" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  - 霍尔木兹危机：油价上涨→利率上行→压制成长股(恒科-7pp、芯片-8pp)</t>
+        </is>
+      </c>
+      <c r="B47" s="149" t="n"/>
+      <c r="C47" s="149" t="n"/>
+      <c r="D47" s="149" t="n"/>
+      <c r="E47" s="149" t="n"/>
+      <c r="F47" s="149" t="n"/>
+      <c r="G47" s="149" t="n"/>
+      <c r="H47" s="149" t="n"/>
+      <c r="I47" s="150" t="n"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="267" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  - 关税升级：301+欧盟钢铁关税→有色-5pp、稀金-3pp</t>
+        </is>
+      </c>
+      <c r="B48" s="149" t="n"/>
+      <c r="C48" s="149" t="n"/>
+      <c r="D48" s="149" t="n"/>
+      <c r="E48" s="149" t="n"/>
+      <c r="F48" s="149" t="n"/>
+      <c r="G48" s="149" t="n"/>
+      <c r="H48" s="149" t="n"/>
+      <c r="I48" s="150" t="n"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="267" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  - 宏观偏弱：贷款-4902亿→养殖-4pp、银行-2pp</t>
+        </is>
+      </c>
+      <c r="B49" s="149" t="n"/>
+      <c r="C49" s="149" t="n"/>
+      <c r="D49" s="149" t="n"/>
+      <c r="E49" s="149" t="n"/>
+      <c r="F49" s="149" t="n"/>
+      <c r="G49" s="149" t="n"/>
+      <c r="H49" s="149" t="n"/>
+      <c r="I49" s="150" t="n"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="267" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  - 虚P问题：养殖P=70%但持有-12.5%，事件链过于乐观</t>
+        </is>
+      </c>
+      <c r="B50" s="149" t="n"/>
+      <c r="C50" s="149" t="n"/>
+      <c r="D50" s="149" t="n"/>
+      <c r="E50" s="149" t="n"/>
+      <c r="F50" s="149" t="n"/>
+      <c r="G50" s="149" t="n"/>
+      <c r="H50" s="149" t="n"/>
+      <c r="I50" s="150" t="n"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="267" t="inlineStr"/>
+      <c r="B51" s="149" t="n"/>
+      <c r="C51" s="149" t="n"/>
+      <c r="D51" s="149" t="n"/>
+      <c r="E51" s="149" t="n"/>
+      <c r="F51" s="149" t="n"/>
+      <c r="G51" s="149" t="n"/>
+      <c r="H51" s="149" t="n"/>
+      <c r="I51" s="150" t="n"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="267" t="inlineStr">
+        <is>
+          <t>🟢 机会点：</t>
+        </is>
+      </c>
+      <c r="B52" s="149" t="n"/>
+      <c r="C52" s="149" t="n"/>
+      <c r="D52" s="149" t="n"/>
+      <c r="E52" s="149" t="n"/>
+      <c r="F52" s="149" t="n"/>
+      <c r="G52" s="149" t="n"/>
+      <c r="H52" s="149" t="n"/>
+      <c r="I52" s="150" t="n"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="267" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  - 芯片：20日涨16.4%但事件链漏正向，P值应上调</t>
+        </is>
+      </c>
+      <c r="B53" s="149" t="n"/>
+      <c r="C53" s="149" t="n"/>
+      <c r="D53" s="149" t="n"/>
+      <c r="E53" s="149" t="n"/>
+      <c r="F53" s="149" t="n"/>
+      <c r="G53" s="149" t="n"/>
+      <c r="H53" s="149" t="n"/>
+      <c r="I53" s="150" t="n"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="267" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  - 电池：拟合97分可靠，持有+6%方向正确</t>
+        </is>
+      </c>
+      <c r="B54" s="149" t="n"/>
+      <c r="C54" s="149" t="n"/>
+      <c r="D54" s="149" t="n"/>
+      <c r="E54" s="149" t="n"/>
+      <c r="F54" s="149" t="n"/>
+      <c r="G54" s="149" t="n"/>
+      <c r="H54" s="149" t="n"/>
+      <c r="I54" s="150" t="n"/>
+    </row>
+  </sheetData>
+  <mergeCells count="18">
+    <mergeCell ref="A52:I52"/>
+    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A43:I43"/>
+    <mergeCell ref="A41:I41"/>
+    <mergeCell ref="A49:I49"/>
+    <mergeCell ref="A51:I51"/>
+    <mergeCell ref="A47:I47"/>
+    <mergeCell ref="A42:I42"/>
+    <mergeCell ref="A46:I46"/>
+    <mergeCell ref="A44:I44"/>
+    <mergeCell ref="A45:I45"/>
+    <mergeCell ref="A40:I40"/>
+    <mergeCell ref="A53:I53"/>
+    <mergeCell ref="A39:I39"/>
+    <mergeCell ref="A50:I50"/>
+    <mergeCell ref="A48:I48"/>
+    <mergeCell ref="A38:I38"/>
+    <mergeCell ref="A54:I54"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/持仓贝叶斯跟踪.xlsx
+++ b/持仓贝叶斯跟踪.xlsx
@@ -593,7 +593,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="274">
+  <cellXfs count="275">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -1394,6 +1394,9 @@
     <xf numFmtId="0" fontId="49" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="50" fillId="26" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="50" fillId="26" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -13517,24 +13520,24 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J54"/>
+  <dimension ref="A1:J43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="20" customWidth="1" style="139" min="1" max="1"/>
-    <col width="15" customWidth="1" style="139" min="2" max="2"/>
-    <col width="15" customWidth="1" style="139" min="3" max="3"/>
-    <col width="15" customWidth="1" style="139" min="4" max="4"/>
-    <col width="15" customWidth="1" style="139" min="5" max="5"/>
-    <col width="15" customWidth="1" style="139" min="6" max="6"/>
-    <col width="15" customWidth="1" style="139" min="7" max="7"/>
-    <col width="15" customWidth="1" style="139" min="8" max="8"/>
-    <col width="15" customWidth="1" style="139" min="9" max="9"/>
+    <col width="18" customWidth="1" style="139" min="1" max="1"/>
+    <col width="18" customWidth="1" style="139" min="2" max="2"/>
+    <col width="18" customWidth="1" style="139" min="3" max="3"/>
+    <col width="18" customWidth="1" style="139" min="4" max="4"/>
+    <col width="18" customWidth="1" style="139" min="5" max="5"/>
+    <col width="18" customWidth="1" style="139" min="6" max="6"/>
+    <col width="18" customWidth="1" style="139" min="7" max="7"/>
+    <col width="18" customWidth="1" style="139" min="8" max="8"/>
+    <col width="18" customWidth="1" style="139" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="270" t="inlineStr">
         <is>
-          <t>🔀 持仓盈亏联动与跨品种联合分析 (2026-06-05)</t>
+          <t>持仓盈亏联动分析 (2026-06-05)</t>
         </is>
       </c>
     </row>
@@ -13548,45 +13551,50 @@
     <row r="4">
       <c r="A4" s="272" t="inlineStr">
         <is>
-          <t>持仓</t>
+          <t>基金名称</t>
         </is>
       </c>
       <c r="B4" s="272" t="inlineStr">
         <is>
+          <t>代码</t>
+        </is>
+      </c>
+      <c r="C4" s="272" t="inlineStr">
+        <is>
+          <t>成本</t>
+        </is>
+      </c>
+      <c r="D4" s="272" t="inlineStr">
+        <is>
+          <t>支付宝市值</t>
+        </is>
+      </c>
+      <c r="E4" s="272" t="inlineStr">
+        <is>
+          <t>持有盈亏%</t>
+        </is>
+      </c>
+      <c r="F4" s="272" t="inlineStr">
+        <is>
+          <t>API今日涨跌%</t>
+        </is>
+      </c>
+      <c r="G4" s="272" t="inlineStr">
+        <is>
+          <t>API净值</t>
+        </is>
+      </c>
+      <c r="H4" s="272" t="inlineStr">
+        <is>
           <t>P值</t>
         </is>
       </c>
-      <c r="C4" s="272" t="inlineStr">
-        <is>
-          <t>事件PP</t>
-        </is>
-      </c>
-      <c r="D4" s="272" t="inlineStr">
-        <is>
-          <t>拟合分</t>
-        </is>
-      </c>
-      <c r="E4" s="272" t="inlineStr">
-        <is>
-          <t>持有收益率</t>
-        </is>
-      </c>
-      <c r="F4" s="272" t="inlineStr">
-        <is>
-          <t>20日涨跌%</t>
-        </is>
-      </c>
-      <c r="G4" s="272" t="inlineStr">
-        <is>
-          <t>今日涨跌%</t>
-        </is>
-      </c>
-      <c r="H4" s="272" t="inlineStr">
-        <is>
-          <t>市值</t>
-        </is>
-      </c>
       <c r="I4" s="272" t="inlineStr">
+        <is>
+          <t>拟合</t>
+        </is>
+      </c>
+      <c r="J4" s="272" t="inlineStr">
         <is>
           <t>诊断</t>
         </is>
@@ -13595,1052 +13603,1066 @@
     <row r="5">
       <c r="A5" s="265" t="inlineStr">
         <is>
-          <t>芯片</t>
+          <t>汇添富上证科创板芯片ETF联接A</t>
         </is>
       </c>
       <c r="B5" s="265" t="inlineStr">
         <is>
+          <t>020628</t>
+        </is>
+      </c>
+      <c r="C5" s="265" t="inlineStr">
+        <is>
+          <t>3206</t>
+        </is>
+      </c>
+      <c r="D5" s="265" t="inlineStr">
+        <is>
+          <t>3332</t>
+        </is>
+      </c>
+      <c r="E5" s="265" t="inlineStr">
+        <is>
+          <t>+3.93%</t>
+        </is>
+      </c>
+      <c r="F5" s="265" t="inlineStr">
+        <is>
+          <t>-4.87%</t>
+        </is>
+      </c>
+      <c r="G5" s="265" t="inlineStr">
+        <is>
+          <t>3.5305</t>
+        </is>
+      </c>
+      <c r="H5" s="265" t="inlineStr">
+        <is>
           <t>41%</t>
         </is>
       </c>
-      <c r="C5" s="265" t="inlineStr">
-        <is>
-          <t>-4pp</t>
-        </is>
-      </c>
-      <c r="D5" s="265" t="inlineStr">
+      <c r="I5" s="265" t="inlineStr">
         <is>
           <t>0分</t>
         </is>
       </c>
-      <c r="E5" s="265" t="inlineStr">
-        <is>
-          <t>+3.93%</t>
-        </is>
-      </c>
-      <c r="F5" s="265" t="inlineStr">
-        <is>
-          <t>+29.47%</t>
-        </is>
-      </c>
-      <c r="G5" s="265" t="inlineStr">
-        <is>
-          <t>+1.89%</t>
-        </is>
-      </c>
-      <c r="H5" s="265" t="inlineStr">
-        <is>
-          <t>3332</t>
-        </is>
-      </c>
-      <c r="I5" s="265" t="inlineStr">
-        <is>
-          <t>价格涨29.5%但事件链净-4pp→漏正向; 拟合0分→P值不可信</t>
+      <c r="J5" s="265" t="inlineStr">
+        <is>
+          <t>拟合失效; 短期下跌</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="265" t="inlineStr">
         <is>
-          <t>电池</t>
+          <t>南方中证电池主题ETF联接A</t>
         </is>
       </c>
       <c r="B6" s="265" t="inlineStr">
         <is>
+          <t>018926</t>
+        </is>
+      </c>
+      <c r="C6" s="265" t="inlineStr">
+        <is>
+          <t>6811</t>
+        </is>
+      </c>
+      <c r="D6" s="265" t="inlineStr">
+        <is>
+          <t>7220</t>
+        </is>
+      </c>
+      <c r="E6" s="265" t="inlineStr">
+        <is>
+          <t>+6.01%</t>
+        </is>
+      </c>
+      <c r="F6" s="265" t="inlineStr">
+        <is>
+          <t>-1.88%</t>
+        </is>
+      </c>
+      <c r="G6" s="265" t="inlineStr">
+        <is>
+          <t>1.7183</t>
+        </is>
+      </c>
+      <c r="H6" s="265" t="inlineStr">
+        <is>
           <t>65%</t>
         </is>
       </c>
-      <c r="C6" s="265" t="inlineStr">
-        <is>
-          <t>+23pp</t>
-        </is>
-      </c>
-      <c r="D6" s="265" t="inlineStr">
+      <c r="I6" s="265" t="inlineStr">
         <is>
           <t>97分</t>
         </is>
       </c>
-      <c r="E6" s="265" t="inlineStr">
-        <is>
-          <t>+6.01%</t>
-        </is>
-      </c>
-      <c r="F6" s="265" t="inlineStr">
-        <is>
-          <t>+3.84%</t>
-        </is>
-      </c>
-      <c r="G6" s="265" t="inlineStr">
-        <is>
-          <t>-2.07%</t>
-        </is>
-      </c>
-      <c r="H6" s="265" t="inlineStr">
-        <is>
-          <t>7220</t>
-        </is>
-      </c>
-      <c r="I6" s="265" t="inlineStr">
-        <is>
-          <t>方向一致</t>
+      <c r="J6" s="265" t="inlineStr">
+        <is>
+          <t>正常</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="265" t="inlineStr">
         <is>
-          <t>恒科</t>
+          <t>天弘恒生科技ETF联接C</t>
         </is>
       </c>
       <c r="B7" s="265" t="inlineStr">
         <is>
+          <t>012349</t>
+        </is>
+      </c>
+      <c r="C7" s="265" t="inlineStr">
+        <is>
+          <t>4822</t>
+        </is>
+      </c>
+      <c r="D7" s="265" t="inlineStr">
+        <is>
+          <t>4535</t>
+        </is>
+      </c>
+      <c r="E7" s="265" t="inlineStr">
+        <is>
+          <t>-5.95%</t>
+        </is>
+      </c>
+      <c r="F7" s="265" t="inlineStr">
+        <is>
+          <t>-1.66%</t>
+        </is>
+      </c>
+      <c r="G7" s="265" t="inlineStr">
+        <is>
+          <t>0.6725</t>
+        </is>
+      </c>
+      <c r="H7" s="265" t="inlineStr">
+        <is>
           <t>27%</t>
         </is>
       </c>
-      <c r="C7" s="265" t="inlineStr">
-        <is>
-          <t>-16pp</t>
-        </is>
-      </c>
-      <c r="D7" s="265" t="inlineStr">
+      <c r="I7" s="265" t="inlineStr">
         <is>
           <t>75分</t>
         </is>
       </c>
-      <c r="E7" s="265" t="inlineStr">
-        <is>
-          <t>-5.95%</t>
-        </is>
-      </c>
-      <c r="F7" s="265" t="inlineStr">
-        <is>
-          <t>-4.93%</t>
-        </is>
-      </c>
-      <c r="G7" s="265" t="inlineStr">
-        <is>
-          <t>+0.00%</t>
-        </is>
-      </c>
-      <c r="H7" s="265" t="inlineStr">
-        <is>
-          <t>4535</t>
-        </is>
-      </c>
-      <c r="I7" s="265" t="inlineStr">
-        <is>
-          <t>方向一致</t>
+      <c r="J7" s="265" t="inlineStr">
+        <is>
+          <t>正常</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="265" t="inlineStr">
         <is>
-          <t>养殖</t>
+          <t>招商中证畜牧养殖ETF联接C</t>
         </is>
       </c>
       <c r="B8" s="265" t="inlineStr">
         <is>
+          <t>014415</t>
+        </is>
+      </c>
+      <c r="C8" s="265" t="inlineStr">
+        <is>
+          <t>4432</t>
+        </is>
+      </c>
+      <c r="D8" s="265" t="inlineStr">
+        <is>
+          <t>3878</t>
+        </is>
+      </c>
+      <c r="E8" s="265" t="inlineStr">
+        <is>
+          <t>-12.49%</t>
+        </is>
+      </c>
+      <c r="F8" s="265" t="inlineStr">
+        <is>
+          <t>-0.48%</t>
+        </is>
+      </c>
+      <c r="G8" s="265" t="inlineStr">
+        <is>
+          <t>0.7249</t>
+        </is>
+      </c>
+      <c r="H8" s="265" t="inlineStr">
+        <is>
           <t>70%</t>
         </is>
       </c>
-      <c r="C8" s="265" t="inlineStr">
-        <is>
-          <t>+15pp</t>
-        </is>
-      </c>
-      <c r="D8" s="265" t="inlineStr">
+      <c r="I8" s="265" t="inlineStr">
         <is>
           <t>95分</t>
         </is>
       </c>
-      <c r="E8" s="265" t="inlineStr">
-        <is>
-          <t>-12.49%</t>
-        </is>
-      </c>
-      <c r="F8" s="265" t="inlineStr">
-        <is>
-          <t>-15.68%</t>
-        </is>
-      </c>
-      <c r="G8" s="265" t="inlineStr">
-        <is>
-          <t>+0.00%</t>
-        </is>
-      </c>
-      <c r="H8" s="265" t="inlineStr">
-        <is>
-          <t>3878</t>
-        </is>
-      </c>
-      <c r="I8" s="265" t="inlineStr">
-        <is>
-          <t>价格跌-15.7%但事件链净+15pp→漏负向; P=70%乐观但持有亏-12.5%→虚P过高</t>
+      <c r="J8" s="265" t="inlineStr">
+        <is>
+          <t>虚P过高; 亏损&gt;10%</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="265" t="inlineStr">
         <is>
-          <t>有色</t>
+          <t>南方有色金属ETF联接C</t>
         </is>
       </c>
       <c r="B9" s="265" t="inlineStr">
         <is>
+          <t>004433</t>
+        </is>
+      </c>
+      <c r="C9" s="265" t="inlineStr">
+        <is>
+          <t>4800</t>
+        </is>
+      </c>
+      <c r="D9" s="265" t="inlineStr">
+        <is>
+          <t>4781</t>
+        </is>
+      </c>
+      <c r="E9" s="265" t="inlineStr">
+        <is>
+          <t>-0.41%</t>
+        </is>
+      </c>
+      <c r="F9" s="265" t="inlineStr">
+        <is>
+          <t>-2.12%</t>
+        </is>
+      </c>
+      <c r="G9" s="265" t="inlineStr">
+        <is>
+          <t>1.8756</t>
+        </is>
+      </c>
+      <c r="H9" s="265" t="inlineStr">
+        <is>
           <t>39%</t>
         </is>
       </c>
-      <c r="C9" s="265" t="inlineStr">
-        <is>
-          <t>-11pp</t>
-        </is>
-      </c>
-      <c r="D9" s="265" t="inlineStr">
+      <c r="I9" s="265" t="inlineStr">
         <is>
           <t>0分</t>
         </is>
       </c>
-      <c r="E9" s="265" t="inlineStr">
-        <is>
-          <t>-0.41%</t>
-        </is>
-      </c>
-      <c r="F9" s="265" t="inlineStr">
-        <is>
-          <t>+0.00%</t>
-        </is>
-      </c>
-      <c r="G9" s="265" t="inlineStr">
-        <is>
-          <t>+0.00%</t>
-        </is>
-      </c>
-      <c r="H9" s="265" t="inlineStr">
-        <is>
-          <t>4781</t>
-        </is>
-      </c>
-      <c r="I9" s="265" t="inlineStr">
-        <is>
-          <t>拟合0分→P值不可信</t>
+      <c r="J9" s="265" t="inlineStr">
+        <is>
+          <t>拟合失效</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="265" t="inlineStr">
         <is>
-          <t>稀金</t>
+          <t>嘉实中证稀有金属主题ETF联接C</t>
         </is>
       </c>
       <c r="B10" s="265" t="inlineStr">
         <is>
+          <t>014111</t>
+        </is>
+      </c>
+      <c r="C10" s="265" t="inlineStr">
+        <is>
+          <t>5822</t>
+        </is>
+      </c>
+      <c r="D10" s="265" t="inlineStr">
+        <is>
+          <t>5872</t>
+        </is>
+      </c>
+      <c r="E10" s="265" t="inlineStr">
+        <is>
+          <t>+0.85%</t>
+        </is>
+      </c>
+      <c r="F10" s="265" t="inlineStr">
+        <is>
+          <t>-1.24%</t>
+        </is>
+      </c>
+      <c r="G10" s="265" t="inlineStr">
+        <is>
+          <t>1.0594</t>
+        </is>
+      </c>
+      <c r="H10" s="265" t="inlineStr">
+        <is>
           <t>40%</t>
         </is>
       </c>
-      <c r="C10" s="265" t="inlineStr">
-        <is>
-          <t>-10pp</t>
-        </is>
-      </c>
-      <c r="D10" s="265" t="inlineStr">
+      <c r="I10" s="265" t="inlineStr">
         <is>
           <t>0分</t>
         </is>
       </c>
-      <c r="E10" s="265" t="inlineStr">
-        <is>
-          <t>+0.85%</t>
-        </is>
-      </c>
-      <c r="F10" s="265" t="inlineStr">
-        <is>
-          <t>+0.00%</t>
-        </is>
-      </c>
-      <c r="G10" s="265" t="inlineStr">
-        <is>
-          <t>+0.00%</t>
-        </is>
-      </c>
-      <c r="H10" s="265" t="inlineStr">
-        <is>
-          <t>5872</t>
-        </is>
-      </c>
-      <c r="I10" s="265" t="inlineStr">
-        <is>
-          <t>拟合0分→P值不可信</t>
+      <c r="J10" s="265" t="inlineStr">
+        <is>
+          <t>拟合失效</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="265" t="inlineStr">
         <is>
-          <t>银行</t>
+          <t>银行ETF联接C</t>
         </is>
       </c>
       <c r="B11" s="265" t="inlineStr">
         <is>
+          <t>001595</t>
+        </is>
+      </c>
+      <c r="C11" s="265" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D11" s="265" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E11" s="265" t="inlineStr">
+        <is>
+          <t>+0.00%</t>
+        </is>
+      </c>
+      <c r="F11" s="265" t="inlineStr">
+        <is>
+          <t>+1.32%</t>
+        </is>
+      </c>
+      <c r="G11" s="265" t="inlineStr">
+        <is>
+          <t>1.6526</t>
+        </is>
+      </c>
+      <c r="H11" s="265" t="inlineStr">
+        <is>
           <t>47%</t>
         </is>
       </c>
-      <c r="C11" s="265" t="inlineStr">
-        <is>
-          <t>-3pp</t>
-        </is>
-      </c>
-      <c r="D11" s="265" t="inlineStr">
+      <c r="I11" s="265" t="inlineStr">
         <is>
           <t>53分</t>
         </is>
       </c>
-      <c r="E11" s="265" t="inlineStr">
-        <is>
-          <t>+0.00%</t>
-        </is>
-      </c>
-      <c r="F11" s="265" t="inlineStr">
-        <is>
-          <t>-1.40%</t>
-        </is>
-      </c>
-      <c r="G11" s="265" t="inlineStr">
-        <is>
-          <t>-1.15%</t>
-        </is>
-      </c>
-      <c r="H11" s="265" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I11" s="265" t="inlineStr">
-        <is>
-          <t>方向一致</t>
+      <c r="J11" s="265" t="inlineStr">
+        <is>
+          <t>正常</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="265" t="inlineStr">
         <is>
-          <t>黄金</t>
+          <t>景顺长城中证科创创业人工智能ETF</t>
         </is>
       </c>
       <c r="B12" s="265" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>027048</t>
         </is>
       </c>
       <c r="C12" s="265" t="inlineStr">
         <is>
-          <t>+0pp</t>
+          <t>101</t>
         </is>
       </c>
       <c r="D12" s="265" t="inlineStr">
         <is>
-          <t>0分</t>
+          <t>99</t>
         </is>
       </c>
       <c r="E12" s="265" t="inlineStr">
         <is>
+          <t>-2.23%</t>
+        </is>
+      </c>
+      <c r="F12" s="265" t="inlineStr">
+        <is>
+          <t>-4.08%</t>
+        </is>
+      </c>
+      <c r="G12" s="265" t="inlineStr">
+        <is>
+          <t>1.109</t>
+        </is>
+      </c>
+      <c r="H12" s="265" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I12" s="265" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J12" s="265" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="265" t="inlineStr">
+        <is>
+          <t>国泰黄金ETF联接A</t>
+        </is>
+      </c>
+      <c r="B13" s="265" t="inlineStr">
+        <is>
+          <t>000218</t>
+        </is>
+      </c>
+      <c r="C13" s="265" t="inlineStr">
+        <is>
+          <t>2787</t>
+        </is>
+      </c>
+      <c r="D13" s="265" t="inlineStr">
+        <is>
+          <t>2594</t>
+        </is>
+      </c>
+      <c r="E13" s="265" t="inlineStr">
+        <is>
+          <t>-6.92%</t>
+        </is>
+      </c>
+      <c r="F13" s="265" t="inlineStr">
+        <is>
+          <t>-0.01%</t>
+        </is>
+      </c>
+      <c r="G13" s="265" t="inlineStr">
+        <is>
+          <t>3.5234</t>
+        </is>
+      </c>
+      <c r="H13" s="265" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I13" s="265" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J13" s="265" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="265" t="inlineStr">
+        <is>
+          <t>博时黄金ETF联接C</t>
+        </is>
+      </c>
+      <c r="B14" s="265" t="inlineStr">
+        <is>
+          <t>002611</t>
+        </is>
+      </c>
+      <c r="C14" s="265" t="inlineStr">
+        <is>
+          <t>3267</t>
+        </is>
+      </c>
+      <c r="D14" s="265" t="inlineStr">
+        <is>
+          <t>3082</t>
+        </is>
+      </c>
+      <c r="E14" s="265" t="inlineStr">
+        <is>
+          <t>-5.66%</t>
+        </is>
+      </c>
+      <c r="F14" s="265" t="inlineStr">
+        <is>
+          <t>-0.01%</t>
+        </is>
+      </c>
+      <c r="G14" s="265" t="inlineStr">
+        <is>
+          <t>3.0625</t>
+        </is>
+      </c>
+      <c r="H14" s="265" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I14" s="265" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J14" s="265" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="265" t="inlineStr">
+        <is>
+          <t>建信上海金ETF联接C</t>
+        </is>
+      </c>
+      <c r="B15" s="265" t="inlineStr">
+        <is>
+          <t>009034</t>
+        </is>
+      </c>
+      <c r="C15" s="265" t="inlineStr">
+        <is>
+          <t>2939</t>
+        </is>
+      </c>
+      <c r="D15" s="265" t="inlineStr">
+        <is>
+          <t>2828</t>
+        </is>
+      </c>
+      <c r="E15" s="265" t="inlineStr">
+        <is>
+          <t>-3.83%</t>
+        </is>
+      </c>
+      <c r="F15" s="265" t="inlineStr">
+        <is>
           <t>+0.00%</t>
         </is>
       </c>
-      <c r="F12" s="265" t="inlineStr">
-        <is>
-          <t>-15.01%</t>
-        </is>
-      </c>
-      <c r="G12" s="265" t="inlineStr">
-        <is>
-          <t>+0.10%</t>
-        </is>
-      </c>
-      <c r="H12" s="265" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I12" s="265" t="inlineStr">
-        <is>
-          <t>价格跌-15.0%但事件链净+0pp→漏负向</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="271" t="inlineStr">
-        <is>
-          <t>二、事件传导矩阵</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="272" t="inlineStr">
-        <is>
-          <t>源头事件</t>
-        </is>
-      </c>
-      <c r="B15" s="272" t="inlineStr">
-        <is>
-          <t>品种</t>
-        </is>
-      </c>
-      <c r="C15" s="272" t="inlineStr">
-        <is>
-          <t>传导PP</t>
-        </is>
-      </c>
-      <c r="D15" s="272" t="inlineStr">
-        <is>
-          <t>方向</t>
+      <c r="G15" s="265" t="inlineStr">
+        <is>
+          <t>2.2511</t>
+        </is>
+      </c>
+      <c r="H15" s="265" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I15" s="265" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J15" s="265" t="inlineStr">
+        <is>
+          <t>正常</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="265" t="inlineStr">
         <is>
+          <t>前海开源金银珠宝混合C</t>
+        </is>
+      </c>
+      <c r="B16" s="265" t="inlineStr">
+        <is>
+          <t>002207</t>
+        </is>
+      </c>
+      <c r="C16" s="265" t="inlineStr">
+        <is>
+          <t>8839</t>
+        </is>
+      </c>
+      <c r="D16" s="265" t="inlineStr">
+        <is>
+          <t>7311</t>
+        </is>
+      </c>
+      <c r="E16" s="265" t="inlineStr">
+        <is>
+          <t>-17.29%</t>
+        </is>
+      </c>
+      <c r="F16" s="265" t="inlineStr">
+        <is>
+          <t>-1.15%</t>
+        </is>
+      </c>
+      <c r="G16" s="265" t="inlineStr">
+        <is>
+          <t>2.534</t>
+        </is>
+      </c>
+      <c r="H16" s="265" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I16" s="265" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J16" s="265" t="inlineStr">
+        <is>
+          <t>亏损&gt;10%</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="271" t="inlineStr">
+        <is>
+          <t>二、事件传导矩阵</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="272" t="inlineStr">
+        <is>
+          <t>源头事件</t>
+        </is>
+      </c>
+      <c r="B19" s="272" t="inlineStr">
+        <is>
+          <t>品种</t>
+        </is>
+      </c>
+      <c r="C19" s="272" t="inlineStr">
+        <is>
+          <t>PP</t>
+        </is>
+      </c>
+      <c r="D19" s="272" t="inlineStr">
+        <is>
+          <t>方向</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="265" t="inlineStr">
+        <is>
           <t>AI/科技</t>
         </is>
       </c>
-      <c r="B16" s="265" t="inlineStr">
+      <c r="B20" s="265" t="inlineStr">
         <is>
           <t>恒科</t>
         </is>
       </c>
-      <c r="C16" s="265" t="inlineStr">
+      <c r="C20" s="265" t="inlineStr">
         <is>
           <t>-5pp</t>
         </is>
       </c>
-      <c r="D16" s="265" t="inlineStr">
-        <is>
-          <t>⬇利空</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="B17" s="265" t="inlineStr">
+      <c r="D20" s="265" t="inlineStr">
+        <is>
+          <t>利空</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="265" t="inlineStr"/>
+      <c r="B21" s="265" t="inlineStr">
         <is>
           <t>有色</t>
         </is>
       </c>
-      <c r="C17" s="265" t="inlineStr">
+      <c r="C21" s="265" t="inlineStr">
         <is>
           <t>+2pp</t>
         </is>
       </c>
-      <c r="D17" s="265" t="inlineStr">
-        <is>
-          <t>⬆利好</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="B18" s="265" t="inlineStr">
+      <c r="D21" s="265" t="inlineStr">
+        <is>
+          <t>利好</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="265" t="inlineStr"/>
+      <c r="B22" s="265" t="inlineStr">
         <is>
           <t>芯片</t>
         </is>
       </c>
-      <c r="C18" s="265" t="inlineStr">
+      <c r="C22" s="265" t="inlineStr">
         <is>
           <t>+5pp</t>
         </is>
       </c>
-      <c r="D18" s="265" t="inlineStr">
-        <is>
-          <t>⬆利好</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="265" t="inlineStr">
+      <c r="D22" s="265" t="inlineStr">
+        <is>
+          <t>利好</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="265" t="inlineStr">
         <is>
           <t>关税/贸易</t>
         </is>
       </c>
-      <c r="B19" s="265" t="inlineStr">
+      <c r="B23" s="265" t="inlineStr">
         <is>
           <t>有色</t>
         </is>
       </c>
-      <c r="C19" s="265" t="inlineStr">
+      <c r="C23" s="265" t="inlineStr">
         <is>
           <t>-5pp</t>
         </is>
       </c>
-      <c r="D19" s="265" t="inlineStr">
-        <is>
-          <t>⬇利空</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="B20" s="265" t="inlineStr">
+      <c r="D23" s="265" t="inlineStr">
+        <is>
+          <t>利空</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="265" t="inlineStr"/>
+      <c r="B24" s="265" t="inlineStr">
         <is>
           <t>稀金</t>
         </is>
       </c>
-      <c r="C20" s="265" t="inlineStr">
+      <c r="C24" s="265" t="inlineStr">
         <is>
           <t>-3pp</t>
         </is>
       </c>
-      <c r="D20" s="265" t="inlineStr">
-        <is>
-          <t>⬇利空</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="265" t="inlineStr">
+      <c r="D24" s="265" t="inlineStr">
+        <is>
+          <t>利空</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="265" t="inlineStr">
         <is>
           <t>其他</t>
         </is>
       </c>
-      <c r="B21" s="265" t="inlineStr">
+      <c r="B25" s="265" t="inlineStr">
         <is>
           <t>有色</t>
         </is>
       </c>
-      <c r="C21" s="265" t="inlineStr">
+      <c r="C25" s="265" t="inlineStr">
         <is>
           <t>-8pp</t>
         </is>
       </c>
-      <c r="D21" s="265" t="inlineStr">
-        <is>
-          <t>⬇利空</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="B22" s="265" t="inlineStr">
+      <c r="D25" s="265" t="inlineStr">
+        <is>
+          <t>利空</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="265" t="inlineStr"/>
+      <c r="B26" s="265" t="inlineStr">
         <is>
           <t>稀金</t>
         </is>
       </c>
-      <c r="C22" s="265" t="inlineStr">
+      <c r="C26" s="265" t="inlineStr">
         <is>
           <t>-5pp</t>
         </is>
       </c>
-      <c r="D22" s="265" t="inlineStr">
-        <is>
-          <t>⬇利空</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="B23" s="265" t="inlineStr">
+      <c r="D26" s="265" t="inlineStr">
+        <is>
+          <t>利空</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="265" t="inlineStr"/>
+      <c r="B27" s="265" t="inlineStr">
         <is>
           <t>恒科</t>
         </is>
       </c>
-      <c r="C23" s="265" t="inlineStr">
+      <c r="C27" s="265" t="inlineStr">
         <is>
           <t>-4pp</t>
         </is>
       </c>
-      <c r="D23" s="265" t="inlineStr">
-        <is>
-          <t>⬇利空</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="B24" s="265" t="inlineStr">
+      <c r="D27" s="265" t="inlineStr">
+        <is>
+          <t>利空</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="265" t="inlineStr"/>
+      <c r="B28" s="265" t="inlineStr">
         <is>
           <t>芯片</t>
         </is>
       </c>
-      <c r="C24" s="265" t="inlineStr">
+      <c r="C28" s="265" t="inlineStr">
         <is>
           <t>-2pp</t>
         </is>
       </c>
-      <c r="D24" s="265" t="inlineStr">
-        <is>
-          <t>⬇利空</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="B25" s="265" t="inlineStr">
+      <c r="D28" s="265" t="inlineStr">
+        <is>
+          <t>利空</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="265" t="inlineStr"/>
+      <c r="B29" s="265" t="inlineStr">
         <is>
           <t>电池</t>
         </is>
       </c>
-      <c r="C25" s="265" t="inlineStr">
+      <c r="C29" s="265" t="inlineStr">
         <is>
           <t>+16pp</t>
         </is>
       </c>
-      <c r="D25" s="265" t="inlineStr">
-        <is>
-          <t>⬆利好</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="265" t="inlineStr">
+      <c r="D29" s="265" t="inlineStr">
+        <is>
+          <t>利好</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="265" t="inlineStr">
         <is>
           <t>利率上行</t>
         </is>
       </c>
-      <c r="B26" s="265" t="inlineStr">
+      <c r="B30" s="265" t="inlineStr">
         <is>
           <t>芯片</t>
         </is>
       </c>
-      <c r="C26" s="265" t="inlineStr">
+      <c r="C30" s="265" t="inlineStr">
         <is>
           <t>-8pp</t>
         </is>
       </c>
-      <c r="D26" s="265" t="inlineStr">
-        <is>
-          <t>⬇利空</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="B27" s="265" t="inlineStr">
+      <c r="D30" s="265" t="inlineStr">
+        <is>
+          <t>利空</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="265" t="inlineStr"/>
+      <c r="B31" s="265" t="inlineStr">
         <is>
           <t>恒科</t>
         </is>
       </c>
-      <c r="C27" s="265" t="inlineStr">
+      <c r="C31" s="265" t="inlineStr">
         <is>
           <t>-7pp</t>
         </is>
       </c>
-      <c r="D27" s="265" t="inlineStr">
-        <is>
-          <t>⬇利空</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="B28" s="265" t="inlineStr">
+      <c r="D31" s="265" t="inlineStr">
+        <is>
+          <t>利空</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="265" t="inlineStr"/>
+      <c r="B32" s="265" t="inlineStr">
         <is>
           <t>稀金</t>
         </is>
       </c>
-      <c r="C28" s="265" t="inlineStr">
+      <c r="C32" s="265" t="inlineStr">
         <is>
           <t>-3pp</t>
         </is>
       </c>
-      <c r="D28" s="265" t="inlineStr">
-        <is>
-          <t>⬇利空</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="B29" s="265" t="inlineStr">
+      <c r="D32" s="265" t="inlineStr">
+        <is>
+          <t>利空</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="265" t="inlineStr"/>
+      <c r="B33" s="265" t="inlineStr">
         <is>
           <t>银行</t>
         </is>
       </c>
-      <c r="C29" s="265" t="inlineStr">
+      <c r="C33" s="265" t="inlineStr">
         <is>
           <t>-1pp</t>
         </is>
       </c>
-      <c r="D29" s="265" t="inlineStr">
-        <is>
-          <t>⬇利空</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="B30" s="265" t="inlineStr">
+      <c r="D33" s="265" t="inlineStr">
+        <is>
+          <t>利空</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="265" t="inlineStr"/>
+      <c r="B34" s="265" t="inlineStr">
         <is>
           <t>电池</t>
         </is>
       </c>
-      <c r="C30" s="265" t="inlineStr">
+      <c r="C34" s="265" t="inlineStr">
         <is>
           <t>+1pp</t>
         </is>
       </c>
-      <c r="D30" s="265" t="inlineStr">
-        <is>
-          <t>⬆利好</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="265" t="inlineStr">
+      <c r="D34" s="265" t="inlineStr">
+        <is>
+          <t>利好</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="265" t="inlineStr">
         <is>
           <t>宏观/消费</t>
         </is>
       </c>
-      <c r="B31" s="265" t="inlineStr">
+      <c r="B35" s="265" t="inlineStr">
         <is>
           <t>养殖</t>
         </is>
       </c>
-      <c r="C31" s="265" t="inlineStr">
+      <c r="C35" s="265" t="inlineStr">
         <is>
           <t>-4pp</t>
         </is>
       </c>
-      <c r="D31" s="265" t="inlineStr">
-        <is>
-          <t>⬇利空</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="B32" s="265" t="inlineStr">
+      <c r="D35" s="265" t="inlineStr">
+        <is>
+          <t>利空</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="265" t="inlineStr"/>
+      <c r="B36" s="265" t="inlineStr">
         <is>
           <t>银行</t>
         </is>
       </c>
-      <c r="C32" s="265" t="inlineStr">
+      <c r="C36" s="265" t="inlineStr">
         <is>
           <t>-2pp</t>
         </is>
       </c>
-      <c r="D32" s="265" t="inlineStr">
-        <is>
-          <t>⬇利空</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="265" t="inlineStr">
+      <c r="D36" s="265" t="inlineStr">
+        <is>
+          <t>利空</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="265" t="inlineStr">
         <is>
           <t>霍尔木兹/能源</t>
         </is>
       </c>
-      <c r="B33" s="265" t="inlineStr">
+      <c r="B37" s="265" t="inlineStr">
         <is>
           <t>芯片</t>
         </is>
       </c>
-      <c r="C33" s="265" t="inlineStr">
+      <c r="C37" s="265" t="inlineStr">
         <is>
           <t>+1pp</t>
         </is>
       </c>
-      <c r="D33" s="265" t="inlineStr">
-        <is>
-          <t>⬆利好</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="B34" s="265" t="inlineStr">
+      <c r="D37" s="265" t="inlineStr">
+        <is>
+          <t>利好</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="265" t="inlineStr"/>
+      <c r="B38" s="265" t="inlineStr">
         <is>
           <t>电池</t>
         </is>
       </c>
-      <c r="C34" s="265" t="inlineStr">
+      <c r="C38" s="265" t="inlineStr">
         <is>
           <t>+6pp</t>
         </is>
       </c>
-      <c r="D34" s="265" t="inlineStr">
-        <is>
-          <t>⬆利好</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="B35" s="265" t="inlineStr">
+      <c r="D38" s="265" t="inlineStr">
+        <is>
+          <t>利好</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="265" t="inlineStr"/>
+      <c r="B39" s="265" t="inlineStr">
         <is>
           <t>养殖</t>
         </is>
       </c>
-      <c r="C35" s="265" t="inlineStr">
+      <c r="C39" s="265" t="inlineStr">
         <is>
           <t>+9pp</t>
         </is>
       </c>
-      <c r="D35" s="265" t="inlineStr">
-        <is>
-          <t>⬆利好</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="271" t="inlineStr">
-        <is>
-          <t>三、亏损原因诊断</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="267" t="inlineStr">
-        <is>
-          <t>🔴 核心亏损来源：</t>
-        </is>
-      </c>
-      <c r="B38" s="149" t="n"/>
-      <c r="C38" s="149" t="n"/>
-      <c r="D38" s="149" t="n"/>
-      <c r="E38" s="149" t="n"/>
-      <c r="F38" s="149" t="n"/>
-      <c r="G38" s="149" t="n"/>
-      <c r="H38" s="149" t="n"/>
-      <c r="I38" s="150" t="n"/>
-    </row>
-    <row r="39">
-      <c r="A39" s="267" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  1. 养殖：成本4432元 持有-12.5% → 亏554元 (最大亏损源)</t>
-        </is>
-      </c>
-      <c r="B39" s="149" t="n"/>
-      <c r="C39" s="149" t="n"/>
-      <c r="D39" s="149" t="n"/>
-      <c r="E39" s="149" t="n"/>
-      <c r="F39" s="149" t="n"/>
-      <c r="G39" s="149" t="n"/>
-      <c r="H39" s="149" t="n"/>
-      <c r="I39" s="150" t="n"/>
-    </row>
-    <row r="40">
-      <c r="A40" s="267" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  2. 恒科：成本4822元 持有-6.0% → 亏287元</t>
-        </is>
-      </c>
-      <c r="B40" s="149" t="n"/>
-      <c r="C40" s="149" t="n"/>
-      <c r="D40" s="149" t="n"/>
-      <c r="E40" s="149" t="n"/>
-      <c r="F40" s="149" t="n"/>
-      <c r="G40" s="149" t="n"/>
-      <c r="H40" s="149" t="n"/>
-      <c r="I40" s="150" t="n"/>
+      <c r="D39" s="265" t="inlineStr">
+        <is>
+          <t>利好</t>
+        </is>
+      </c>
     </row>
     <row r="41">
-      <c r="A41" s="267" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  3. 有色：成本4800元 持有-0.4% → 亏19元</t>
-        </is>
-      </c>
-      <c r="B41" s="149" t="n"/>
-      <c r="C41" s="149" t="n"/>
-      <c r="D41" s="149" t="n"/>
-      <c r="E41" s="149" t="n"/>
-      <c r="F41" s="149" t="n"/>
-      <c r="G41" s="149" t="n"/>
-      <c r="H41" s="149" t="n"/>
-      <c r="I41" s="150" t="n"/>
+      <c r="A41" s="271" t="inlineStr">
+        <is>
+          <t>三、贝叶斯回归诊断</t>
+        </is>
+      </c>
     </row>
     <row r="42">
-      <c r="A42" s="267" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  4. 稀金：成本5822元 持有+0.8% → 赚49元 (微赚)</t>
-        </is>
-      </c>
-      <c r="B42" s="149" t="n"/>
-      <c r="C42" s="149" t="n"/>
-      <c r="D42" s="149" t="n"/>
-      <c r="E42" s="149" t="n"/>
-      <c r="F42" s="149" t="n"/>
-      <c r="G42" s="149" t="n"/>
-      <c r="H42" s="149" t="n"/>
-      <c r="I42" s="150" t="n"/>
+      <c r="A42" s="274" t="inlineStr">
+        <is>
+          <t>P值合理性: 电池65%(97分)✅ 养殖70%(95分但虚高)⚠️ 恒科27%(75分)✅ 芯片41%(0分需修正)❌ 有色39%(0分)❌</t>
+        </is>
+      </c>
     </row>
     <row r="43">
-      <c r="A43" s="267" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  5. 电池：成本6811元 持有+6.0% → 赚410元 (最大盈利)</t>
-        </is>
-      </c>
-      <c r="B43" s="149" t="n"/>
-      <c r="C43" s="149" t="n"/>
-      <c r="D43" s="149" t="n"/>
-      <c r="E43" s="149" t="n"/>
-      <c r="F43" s="149" t="n"/>
-      <c r="G43" s="149" t="n"/>
-      <c r="H43" s="149" t="n"/>
-      <c r="I43" s="150" t="n"/>
-    </row>
-    <row r="44">
-      <c r="A44" s="267" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  6. 芯片：成本3206元 持有+3.9% → 赚126元</t>
-        </is>
-      </c>
-      <c r="B44" s="149" t="n"/>
-      <c r="C44" s="149" t="n"/>
-      <c r="D44" s="149" t="n"/>
-      <c r="E44" s="149" t="n"/>
-      <c r="F44" s="149" t="n"/>
-      <c r="G44" s="149" t="n"/>
-      <c r="H44" s="149" t="n"/>
-      <c r="I44" s="150" t="n"/>
-    </row>
-    <row r="45">
-      <c r="A45" s="267" t="inlineStr"/>
-      <c r="B45" s="149" t="n"/>
-      <c r="C45" s="149" t="n"/>
-      <c r="D45" s="149" t="n"/>
-      <c r="E45" s="149" t="n"/>
-      <c r="F45" s="149" t="n"/>
-      <c r="G45" s="149" t="n"/>
-      <c r="H45" s="149" t="n"/>
-      <c r="I45" s="150" t="n"/>
-    </row>
-    <row r="46">
-      <c r="A46" s="267" t="inlineStr">
-        <is>
-          <t>🟡 今年收益转负原因：</t>
-        </is>
-      </c>
-      <c r="B46" s="149" t="n"/>
-      <c r="C46" s="149" t="n"/>
-      <c r="D46" s="149" t="n"/>
-      <c r="E46" s="149" t="n"/>
-      <c r="F46" s="149" t="n"/>
-      <c r="G46" s="149" t="n"/>
-      <c r="H46" s="149" t="n"/>
-      <c r="I46" s="150" t="n"/>
-    </row>
-    <row r="47">
-      <c r="A47" s="267" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  - 霍尔木兹危机：油价上涨→利率上行→压制成长股(恒科-7pp、芯片-8pp)</t>
-        </is>
-      </c>
-      <c r="B47" s="149" t="n"/>
-      <c r="C47" s="149" t="n"/>
-      <c r="D47" s="149" t="n"/>
-      <c r="E47" s="149" t="n"/>
-      <c r="F47" s="149" t="n"/>
-      <c r="G47" s="149" t="n"/>
-      <c r="H47" s="149" t="n"/>
-      <c r="I47" s="150" t="n"/>
-    </row>
-    <row r="48">
-      <c r="A48" s="267" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  - 关税升级：301+欧盟钢铁关税→有色-5pp、稀金-3pp</t>
-        </is>
-      </c>
-      <c r="B48" s="149" t="n"/>
-      <c r="C48" s="149" t="n"/>
-      <c r="D48" s="149" t="n"/>
-      <c r="E48" s="149" t="n"/>
-      <c r="F48" s="149" t="n"/>
-      <c r="G48" s="149" t="n"/>
-      <c r="H48" s="149" t="n"/>
-      <c r="I48" s="150" t="n"/>
-    </row>
-    <row r="49">
-      <c r="A49" s="267" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  - 宏观偏弱：贷款-4902亿→养殖-4pp、银行-2pp</t>
-        </is>
-      </c>
-      <c r="B49" s="149" t="n"/>
-      <c r="C49" s="149" t="n"/>
-      <c r="D49" s="149" t="n"/>
-      <c r="E49" s="149" t="n"/>
-      <c r="F49" s="149" t="n"/>
-      <c r="G49" s="149" t="n"/>
-      <c r="H49" s="149" t="n"/>
-      <c r="I49" s="150" t="n"/>
-    </row>
-    <row r="50">
-      <c r="A50" s="267" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  - 虚P问题：养殖P=70%但持有-12.5%，事件链过于乐观</t>
-        </is>
-      </c>
-      <c r="B50" s="149" t="n"/>
-      <c r="C50" s="149" t="n"/>
-      <c r="D50" s="149" t="n"/>
-      <c r="E50" s="149" t="n"/>
-      <c r="F50" s="149" t="n"/>
-      <c r="G50" s="149" t="n"/>
-      <c r="H50" s="149" t="n"/>
-      <c r="I50" s="150" t="n"/>
-    </row>
-    <row r="51">
-      <c r="A51" s="267" t="inlineStr"/>
-      <c r="B51" s="149" t="n"/>
-      <c r="C51" s="149" t="n"/>
-      <c r="D51" s="149" t="n"/>
-      <c r="E51" s="149" t="n"/>
-      <c r="F51" s="149" t="n"/>
-      <c r="G51" s="149" t="n"/>
-      <c r="H51" s="149" t="n"/>
-      <c r="I51" s="150" t="n"/>
-    </row>
-    <row r="52">
-      <c r="A52" s="267" t="inlineStr">
-        <is>
-          <t>🟢 机会点：</t>
-        </is>
-      </c>
-      <c r="B52" s="149" t="n"/>
-      <c r="C52" s="149" t="n"/>
-      <c r="D52" s="149" t="n"/>
-      <c r="E52" s="149" t="n"/>
-      <c r="F52" s="149" t="n"/>
-      <c r="G52" s="149" t="n"/>
-      <c r="H52" s="149" t="n"/>
-      <c r="I52" s="150" t="n"/>
-    </row>
-    <row r="53">
-      <c r="A53" s="267" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  - 芯片：20日涨16.4%但事件链漏正向，P值应上调</t>
-        </is>
-      </c>
-      <c r="B53" s="149" t="n"/>
-      <c r="C53" s="149" t="n"/>
-      <c r="D53" s="149" t="n"/>
-      <c r="E53" s="149" t="n"/>
-      <c r="F53" s="149" t="n"/>
-      <c r="G53" s="149" t="n"/>
-      <c r="H53" s="149" t="n"/>
-      <c r="I53" s="150" t="n"/>
-    </row>
-    <row r="54">
-      <c r="A54" s="267" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  - 电池：拟合97分可靠，持有+6%方向正确</t>
-        </is>
-      </c>
-      <c r="B54" s="149" t="n"/>
-      <c r="C54" s="149" t="n"/>
-      <c r="D54" s="149" t="n"/>
-      <c r="E54" s="149" t="n"/>
-      <c r="F54" s="149" t="n"/>
-      <c r="G54" s="149" t="n"/>
-      <c r="H54" s="149" t="n"/>
-      <c r="I54" s="150" t="n"/>
+      <c r="A43" s="274" t="inlineStr">
+        <is>
+          <t>建议: 养殖P值下调至60-65% 芯片P值上调至45% 其他维持</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="18">
-    <mergeCell ref="A52:I52"/>
+  <mergeCells count="3">
+    <mergeCell ref="A42:I42"/>
     <mergeCell ref="A1:J1"/>
     <mergeCell ref="A43:I43"/>
-    <mergeCell ref="A41:I41"/>
-    <mergeCell ref="A49:I49"/>
-    <mergeCell ref="A51:I51"/>
-    <mergeCell ref="A47:I47"/>
-    <mergeCell ref="A42:I42"/>
-    <mergeCell ref="A46:I46"/>
-    <mergeCell ref="A44:I44"/>
-    <mergeCell ref="A45:I45"/>
-    <mergeCell ref="A40:I40"/>
-    <mergeCell ref="A53:I53"/>
-    <mergeCell ref="A39:I39"/>
-    <mergeCell ref="A50:I50"/>
-    <mergeCell ref="A48:I48"/>
-    <mergeCell ref="A38:I38"/>
-    <mergeCell ref="A54:I54"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/持仓贝叶斯跟踪.xlsx
+++ b/持仓贝叶斯跟踪.xlsx
@@ -16,6 +16,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="持仓盈亏联动" sheetId="7" state="visible" r:id="rId7"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="跨品种传导" sheetId="8" state="visible" r:id="rId8"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="持仓盈亏联动分析" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="信源校准分析" sheetId="10" state="visible" r:id="rId10"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1" refMode="A1" iterate="0" iterateCount="100" iterateDelta="0.0001"/>
@@ -25,7 +26,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="51">
+  <fonts count="52">
     <font>
       <name val="Calibri"/>
       <charset val="1"/>
@@ -374,6 +375,10 @@
       <b val="1"/>
       <color rgb="00FFFFFF"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00C00000"/>
+    </font>
   </fonts>
   <fills count="27">
     <fill>
@@ -593,7 +598,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="275">
+  <cellXfs count="276">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -1397,6 +1402,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="51" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -5118,6 +5124,851 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J42"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" style="139" min="1" max="1"/>
+    <col width="22" customWidth="1" style="139" min="2" max="2"/>
+    <col width="22" customWidth="1" style="139" min="3" max="3"/>
+    <col width="22" customWidth="1" style="139" min="4" max="4"/>
+    <col width="22" customWidth="1" style="139" min="5" max="5"/>
+    <col width="22" customWidth="1" style="139" min="6" max="6"/>
+    <col width="22" customWidth="1" style="139" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="270" t="inlineStr">
+        <is>
+          <t>🔬 贝叶斯信源校准分析 (2026-06-06)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="271" t="inlineStr">
+        <is>
+          <t>一、方法论</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="274" t="inlineStr">
+        <is>
+          <t>1. 虚P事件不参与P值计算（传导机制问题，不是信源准确率问题）</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="274" t="inlineStr">
+        <is>
+          <t>2. 虚P事件不参与信源准确率评估（V4 Pro审核确认）</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="274" t="inlineStr">
+        <is>
+          <t>3. 信源权重用Beta(5,5)贝叶斯后验：weight = (correct+5)/(total+10)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="274" t="inlineStr">
+        <is>
+          <t>4. 最小样本3条才开始校准，&lt;3条权重=1.0（不衰减）</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="274" t="inlineStr">
+        <is>
+          <t>5. 乘子 = 2×weight-1：&gt;0正向，&lt;0反向，=0忽略</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="274" t="inlineStr">
+        <is>
+          <t>6. 校准后P = 50% + Σ(pp_i × weight_i)（仅实P事件）</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="274" t="inlineStr">
+        <is>
+          <t>7. 当前状态：所有信源实P事件&lt;3条，权重校准暂未生效</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="274" t="inlineStr">
+        <is>
+          <t>8. 但当务之急：剔除虚P事件→P值立刻修正</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="271" t="inlineStr">
+        <is>
+          <t>二、虚P剔除对P值的直接影响</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="272" t="inlineStr">
+        <is>
+          <t>持仓</t>
+        </is>
+      </c>
+      <c r="B14" s="272" t="inlineStr">
+        <is>
+          <t>原P值</t>
+        </is>
+      </c>
+      <c r="C14" s="272" t="inlineStr">
+        <is>
+          <t>虚P贡献</t>
+        </is>
+      </c>
+      <c r="D14" s="272" t="inlineStr">
+        <is>
+          <t>剔除后P</t>
+        </is>
+      </c>
+      <c r="E14" s="272" t="inlineStr">
+        <is>
+          <t>调整</t>
+        </is>
+      </c>
+      <c r="F14" s="272" t="inlineStr">
+        <is>
+          <t>持有收益率</t>
+        </is>
+      </c>
+      <c r="G14" s="272" t="inlineStr">
+        <is>
+          <t>方向是否一致</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="265" t="inlineStr">
+        <is>
+          <t>芯片</t>
+        </is>
+      </c>
+      <c r="B15" s="265" t="inlineStr">
+        <is>
+          <t>41%</t>
+        </is>
+      </c>
+      <c r="C15" s="265" t="inlineStr">
+        <is>
+          <t>+2pp</t>
+        </is>
+      </c>
+      <c r="D15" s="265" t="inlineStr">
+        <is>
+          <t>39%</t>
+        </is>
+      </c>
+      <c r="E15" s="265" t="inlineStr">
+        <is>
+          <t>-2pp</t>
+        </is>
+      </c>
+      <c r="F15" s="265" t="inlineStr">
+        <is>
+          <t>+3.93%</t>
+        </is>
+      </c>
+      <c r="G15" s="265" t="inlineStr">
+        <is>
+          <t>拟合0分需更多数据</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="265" t="inlineStr">
+        <is>
+          <t>电池</t>
+        </is>
+      </c>
+      <c r="B16" s="265" t="inlineStr">
+        <is>
+          <t>65%</t>
+        </is>
+      </c>
+      <c r="C16" s="265" t="inlineStr">
+        <is>
+          <t>+0pp</t>
+        </is>
+      </c>
+      <c r="D16" s="265" t="inlineStr">
+        <is>
+          <t>65%</t>
+        </is>
+      </c>
+      <c r="E16" s="265" t="inlineStr">
+        <is>
+          <t>+0pp</t>
+        </is>
+      </c>
+      <c r="F16" s="265" t="inlineStr">
+        <is>
+          <t>+6.01%</t>
+        </is>
+      </c>
+      <c r="G16" s="265" t="inlineStr">
+        <is>
+          <t>✅ 方向一致</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="265" t="inlineStr">
+        <is>
+          <t>恒科</t>
+        </is>
+      </c>
+      <c r="B17" s="265" t="inlineStr">
+        <is>
+          <t>27%</t>
+        </is>
+      </c>
+      <c r="C17" s="265" t="inlineStr">
+        <is>
+          <t>+0pp</t>
+        </is>
+      </c>
+      <c r="D17" s="265" t="inlineStr">
+        <is>
+          <t>27%</t>
+        </is>
+      </c>
+      <c r="E17" s="265" t="inlineStr">
+        <is>
+          <t>+0pp</t>
+        </is>
+      </c>
+      <c r="F17" s="265" t="inlineStr">
+        <is>
+          <t>-5.95%</t>
+        </is>
+      </c>
+      <c r="G17" s="265" t="inlineStr">
+        <is>
+          <t>✅ 方向一致</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="265" t="inlineStr">
+        <is>
+          <t>养殖</t>
+        </is>
+      </c>
+      <c r="B18" s="265" t="inlineStr">
+        <is>
+          <t>70%</t>
+        </is>
+      </c>
+      <c r="C18" s="265" t="inlineStr">
+        <is>
+          <t>+4pp</t>
+        </is>
+      </c>
+      <c r="D18" s="265" t="inlineStr">
+        <is>
+          <t>66%</t>
+        </is>
+      </c>
+      <c r="E18" s="265" t="inlineStr">
+        <is>
+          <t>-4pp</t>
+        </is>
+      </c>
+      <c r="F18" s="265" t="inlineStr">
+        <is>
+          <t>-12.49%</t>
+        </is>
+      </c>
+      <c r="G18" s="275" t="inlineStr">
+        <is>
+          <t>❌ P=66%仍远高于实际→虚P外还有其他问题</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="265" t="inlineStr">
+        <is>
+          <t>有色</t>
+        </is>
+      </c>
+      <c r="B19" s="265" t="inlineStr">
+        <is>
+          <t>39%</t>
+        </is>
+      </c>
+      <c r="C19" s="265" t="inlineStr">
+        <is>
+          <t>+0pp</t>
+        </is>
+      </c>
+      <c r="D19" s="265" t="inlineStr">
+        <is>
+          <t>39%</t>
+        </is>
+      </c>
+      <c r="E19" s="265" t="inlineStr">
+        <is>
+          <t>+0pp</t>
+        </is>
+      </c>
+      <c r="F19" s="265" t="inlineStr">
+        <is>
+          <t>-0.41%</t>
+        </is>
+      </c>
+      <c r="G19" s="265" t="inlineStr">
+        <is>
+          <t>拟合不足</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="265" t="inlineStr">
+        <is>
+          <t>稀金</t>
+        </is>
+      </c>
+      <c r="B20" s="265" t="inlineStr">
+        <is>
+          <t>40%</t>
+        </is>
+      </c>
+      <c r="C20" s="265" t="inlineStr">
+        <is>
+          <t>+0pp</t>
+        </is>
+      </c>
+      <c r="D20" s="265" t="inlineStr">
+        <is>
+          <t>40%</t>
+        </is>
+      </c>
+      <c r="E20" s="265" t="inlineStr">
+        <is>
+          <t>+0pp</t>
+        </is>
+      </c>
+      <c r="F20" s="265" t="inlineStr">
+        <is>
+          <t>+0.85%</t>
+        </is>
+      </c>
+      <c r="G20" s="265" t="inlineStr">
+        <is>
+          <t>拟合不足</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="265" t="inlineStr">
+        <is>
+          <t>银行</t>
+        </is>
+      </c>
+      <c r="B21" s="265" t="inlineStr">
+        <is>
+          <t>47%</t>
+        </is>
+      </c>
+      <c r="C21" s="265" t="inlineStr">
+        <is>
+          <t>+2pp</t>
+        </is>
+      </c>
+      <c r="D21" s="265" t="inlineStr">
+        <is>
+          <t>45%</t>
+        </is>
+      </c>
+      <c r="E21" s="265" t="inlineStr">
+        <is>
+          <t>-2pp</t>
+        </is>
+      </c>
+      <c r="F21" s="265" t="inlineStr">
+        <is>
+          <t>+0.00%</t>
+        </is>
+      </c>
+      <c r="G21" s="265" t="inlineStr">
+        <is>
+          <t>监控仓</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="271" t="inlineStr">
+        <is>
+          <t>三、信源准确率统计（仅实P事件，待样本积累后校准）</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="272" t="inlineStr">
+        <is>
+          <t>信源</t>
+        </is>
+      </c>
+      <c r="B24" s="272" t="inlineStr">
+        <is>
+          <t>实P事件数</t>
+        </is>
+      </c>
+      <c r="C24" s="272" t="inlineStr">
+        <is>
+          <t>正确/总数</t>
+        </is>
+      </c>
+      <c r="D24" s="272" t="inlineStr">
+        <is>
+          <t>后验均值(Beta5,5)</t>
+        </is>
+      </c>
+      <c r="E24" s="272" t="inlineStr">
+        <is>
+          <t>校准状态</t>
+        </is>
+      </c>
+      <c r="F24" s="272" t="inlineStr">
+        <is>
+          <t>备注</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="265" t="inlineStr">
+        <is>
+          <t>付鹏</t>
+        </is>
+      </c>
+      <c r="B25" s="265" t="inlineStr">
+        <is>
+          <t>2条</t>
+        </is>
+      </c>
+      <c r="C25" s="265" t="inlineStr">
+        <is>
+          <t>2/2</t>
+        </is>
+      </c>
+      <c r="D25" s="265" t="inlineStr">
+        <is>
+          <t>0.58</t>
+        </is>
+      </c>
+      <c r="E25" s="265" t="inlineStr">
+        <is>
+          <t>样本不足</t>
+        </is>
+      </c>
+      <c r="F25" s="265" t="inlineStr">
+        <is>
+          <t>看多芯片/看空恒科都对了</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="265" t="inlineStr">
+        <is>
+          <t>伊娃</t>
+        </is>
+      </c>
+      <c r="B26" s="265" t="inlineStr">
+        <is>
+          <t>2条</t>
+        </is>
+      </c>
+      <c r="C26" s="275" t="inlineStr">
+        <is>
+          <t>0/2</t>
+        </is>
+      </c>
+      <c r="D26" s="265" t="inlineStr">
+        <is>
+          <t>0.42</t>
+        </is>
+      </c>
+      <c r="E26" s="265" t="inlineStr">
+        <is>
+          <t>样本不足</t>
+        </is>
+      </c>
+      <c r="F26" s="265" t="inlineStr">
+        <is>
+          <t>⚠️ 2/2全错，养殖跌15%</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="265" t="inlineStr">
+        <is>
+          <t>无知半人</t>
+        </is>
+      </c>
+      <c r="B27" s="265" t="inlineStr">
+        <is>
+          <t>2条</t>
+        </is>
+      </c>
+      <c r="C27" s="265" t="inlineStr">
+        <is>
+          <t>2/2</t>
+        </is>
+      </c>
+      <c r="D27" s="265" t="inlineStr">
+        <is>
+          <t>0.58</t>
+        </is>
+      </c>
+      <c r="E27" s="265" t="inlineStr">
+        <is>
+          <t>样本不足</t>
+        </is>
+      </c>
+      <c r="F27" s="265" t="inlineStr">
+        <is>
+          <t>看空养殖/银行都对了</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="265" t="inlineStr">
+        <is>
+          <t>知乎</t>
+        </is>
+      </c>
+      <c r="B28" s="265" t="inlineStr">
+        <is>
+          <t>2条</t>
+        </is>
+      </c>
+      <c r="C28" s="265" t="inlineStr">
+        <is>
+          <t>2/2</t>
+        </is>
+      </c>
+      <c r="D28" s="265" t="inlineStr">
+        <is>
+          <t>0.58</t>
+        </is>
+      </c>
+      <c r="E28" s="265" t="inlineStr">
+        <is>
+          <t>样本不足</t>
+        </is>
+      </c>
+      <c r="F28" s="265" t="inlineStr">
+        <is>
+          <t>看空有色/稀金都对了</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="265" t="inlineStr">
+        <is>
+          <t>岩松</t>
+        </is>
+      </c>
+      <c r="B29" s="265" t="inlineStr">
+        <is>
+          <t>2条</t>
+        </is>
+      </c>
+      <c r="C29" s="265" t="inlineStr">
+        <is>
+          <t>2/2</t>
+        </is>
+      </c>
+      <c r="D29" s="265" t="inlineStr">
+        <is>
+          <t>0.58</t>
+        </is>
+      </c>
+      <c r="E29" s="265" t="inlineStr">
+        <is>
+          <t>样本不足</t>
+        </is>
+      </c>
+      <c r="F29" s="265" t="inlineStr">
+        <is>
+          <t>看空有色/稀金都对了</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="265" t="inlineStr">
+        <is>
+          <t>凯文·沃什</t>
+        </is>
+      </c>
+      <c r="B30" s="265" t="inlineStr">
+        <is>
+          <t>1条</t>
+        </is>
+      </c>
+      <c r="C30" s="275" t="inlineStr">
+        <is>
+          <t>0/1</t>
+        </is>
+      </c>
+      <c r="D30" s="265" t="inlineStr">
+        <is>
+          <t>0.45</t>
+        </is>
+      </c>
+      <c r="E30" s="265" t="inlineStr">
+        <is>
+          <t>样本不足</t>
+        </is>
+      </c>
+      <c r="F30" s="265" t="inlineStr">
+        <is>
+          <t>❌ 看空芯片-8pp但芯片涨了16%</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="265" t="inlineStr">
+        <is>
+          <t>巴克莱</t>
+        </is>
+      </c>
+      <c r="B31" s="265" t="inlineStr">
+        <is>
+          <t>1条</t>
+        </is>
+      </c>
+      <c r="C31" s="275" t="inlineStr">
+        <is>
+          <t>0/1</t>
+        </is>
+      </c>
+      <c r="D31" s="265" t="inlineStr">
+        <is>
+          <t>0.45</t>
+        </is>
+      </c>
+      <c r="E31" s="265" t="inlineStr">
+        <is>
+          <t>样本不足</t>
+        </is>
+      </c>
+      <c r="F31" s="265" t="inlineStr">
+        <is>
+          <t>❌ 看多电池但电池跌了8%</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="265" t="inlineStr">
+        <is>
+          <t>AI铜需求</t>
+        </is>
+      </c>
+      <c r="B32" s="265" t="inlineStr">
+        <is>
+          <t>1条</t>
+        </is>
+      </c>
+      <c r="C32" s="275" t="inlineStr">
+        <is>
+          <t>0/1</t>
+        </is>
+      </c>
+      <c r="D32" s="265" t="inlineStr">
+        <is>
+          <t>0.45</t>
+        </is>
+      </c>
+      <c r="E32" s="265" t="inlineStr">
+        <is>
+          <t>样本不足</t>
+        </is>
+      </c>
+      <c r="F32" s="265" t="inlineStr">
+        <is>
+          <t>❌ 看多有色但有色跌了10%</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="265" t="inlineStr">
+        <is>
+          <t>宋鸿兵</t>
+        </is>
+      </c>
+      <c r="B33" s="265" t="inlineStr">
+        <is>
+          <t>1条</t>
+        </is>
+      </c>
+      <c r="C33" s="265" t="inlineStr">
+        <is>
+          <t>1/1</t>
+        </is>
+      </c>
+      <c r="D33" s="265" t="inlineStr">
+        <is>
+          <t>0.55</t>
+        </is>
+      </c>
+      <c r="E33" s="265" t="inlineStr">
+        <is>
+          <t>样本不足</t>
+        </is>
+      </c>
+      <c r="F33" s="265" t="inlineStr">
+        <is>
+          <t>看多芯片对了</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="265" t="inlineStr">
+        <is>
+          <t>蒋宇飞</t>
+        </is>
+      </c>
+      <c r="B34" s="265" t="inlineStr">
+        <is>
+          <t>0条</t>
+        </is>
+      </c>
+      <c r="C34" s="265" t="inlineStr">
+        <is>
+          <t>0/0</t>
+        </is>
+      </c>
+      <c r="D34" s="265" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E34" s="265" t="inlineStr">
+        <is>
+          <t>全虚P</t>
+        </is>
+      </c>
+      <c r="F34" s="265" t="inlineStr">
+        <is>
+          <t>所有事件都是虚P</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="265" t="inlineStr">
+        <is>
+          <t>霍尔木兹→养殖</t>
+        </is>
+      </c>
+      <c r="B35" s="265" t="inlineStr">
+        <is>
+          <t>0条</t>
+        </is>
+      </c>
+      <c r="C35" s="265" t="inlineStr">
+        <is>
+          <t>0/0</t>
+        </is>
+      </c>
+      <c r="D35" s="265" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E35" s="265" t="inlineStr">
+        <is>
+          <t>全虚P</t>
+        </is>
+      </c>
+      <c r="F35" s="265" t="inlineStr">
+        <is>
+          <t>传导断了三层</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="271" t="inlineStr">
+        <is>
+          <t>四、下一步行动</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="274" t="inlineStr">
+        <is>
+          <t>1. 【立即】养殖P值从70%下调：虚P剔除→66%，再考虑伊娃2/2全错→建议调至55-60%</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="274" t="inlineStr">
+        <is>
+          <t>2. 【立即】芯片P值从41%上调：虚P剔除→39%，但漏了存储→芯片资金传导(+5pp)→建议44-48%</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="274" t="inlineStr">
+        <is>
+          <t>3. 【持续】每次抓取新事件时，自动分类实P/虚P，虚P不进P值计算</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="274" t="inlineStr">
+        <is>
+          <t>4. 【持续】积累信源实P事件，达到3条后自动触发贝叶斯权重校准</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="274" t="inlineStr">
+        <is>
+          <t>5. 【后续】按宏观/产业/情绪拆分先验，扣除市场β偏倚</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="14">
+    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A5:J5"/>
+    <mergeCell ref="A8:J8"/>
+    <mergeCell ref="A6:J6"/>
+    <mergeCell ref="A40:J40"/>
+    <mergeCell ref="A9:J9"/>
+    <mergeCell ref="A39:J39"/>
+    <mergeCell ref="A4:J4"/>
+    <mergeCell ref="A7:J7"/>
+    <mergeCell ref="A38:J38"/>
+    <mergeCell ref="A10:J10"/>
+    <mergeCell ref="A42:J42"/>
+    <mergeCell ref="A41:J41"/>
+    <mergeCell ref="A11:J11"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr filterMode="0">

--- a/持仓贝叶斯跟踪.xlsx
+++ b/持仓贝叶斯跟踪.xlsx
@@ -17,6 +17,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="跨品种传导" sheetId="8" state="visible" r:id="rId8"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="持仓盈亏联动分析" sheetId="9" state="visible" r:id="rId9"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="信源校准分析" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="深度分析报告" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1" refMode="A1" iterate="0" iterateCount="100" iterateDelta="0.0001"/>
@@ -5969,6 +5970,1213 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:Z144"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="120" customWidth="1" style="139" min="1" max="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="270" t="inlineStr">
+        <is>
+          <t>🔬 深度分析报告 (2026-06-06)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="274">
+        <f>===============================================================================</f>
+        <v/>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="274" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  持仓贝叶斯P值+赔率 深度分析报告</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="274" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  生成时间: 2026-06-06 00:43</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="274">
+        <f>===============================================================================</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="274" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+【一】持仓全景（全部27只基金）</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="274" t="inlineStr">
+        <is>
+          <t>--------------------------------------------------------------------------------</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="274" t="inlineStr">
+        <is>
+          <t>基金名称                         代码       成本     今日涨跌       净值</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="274" t="inlineStr">
+        <is>
+          <t>--------------------------------------------------------------------------------</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="274" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  汇添富上证科创板芯片ETF联接A         020628     3206   -4.87%   3.5305</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="274" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  南方中证电池主题ETF联接A           018926     6811   -1.88%   1.7183</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="274" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  天弘恒生科技ETF联接C             012349     4822   -1.66%   0.6725</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="274" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  招商中证畜牧养殖ETF联接C           014415     4432   -0.48%   0.7249</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="274" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  南方有色金属ETF联接C             004433     4800   -2.12%   1.8756</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="274" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  嘉实中证稀有金属主题ETF联接C         014111     5822   -1.24%   1.0594</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="274" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  银行ETF联接C                 001595        -   +1.32%   1.6526</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="274" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  景顺长城中证科创创业人工智能ETF        027048      101   -4.08%   1.1090</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="274" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  国泰黄金ETF联接A               000218     2787   -0.01%   3.5234</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="274" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  博时黄金ETF联接C               002611     3267   -0.01%   3.0625</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="274" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  建信上海金ETF联接C              009034     2939   +0.00%   2.2511</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="274" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  前海开源金银珠宝混合C              002207     8839   -1.15%   2.5340</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="274" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  永赢先进制造智选A                018124        -   +0.74%   2.4177</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="274" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  嘉实自由现金流联接C               024575        -   -0.62%   1.1112</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="274" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  华宝纳斯达克精选QA               017436        -   -0.28%   2.5059</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="274" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  华宝有色联接C                  017141        -   -2.14%   1.6717</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="274" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  景顺招利6月债券A                010011        -   -0.20%   1.3247</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="274" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  汇添富鑫享添利6月A               012951        -   -0.13%   1.1815</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="274" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  永赢医药创新A                  015915        -   -1.17%   1.4207</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="274" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  广发碳中和混合C                 018419        -   -2.25%   1.9262</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="274" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  天弘绿色电力C                  017175        -   -3.68%   1.2385</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="274" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  摩根日本精选QC                 019449        -        -        -</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="274" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  华宝海外科技QA                 501312        -   +0.00%   2.4162</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="274" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  摩根日本精选QA                 007280        -        -        -</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="274" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  港股通互联网联接A                027127        -   -0.32%   1.0106</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="274" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  广发全球精选QDIIC              021277        -   -0.17%   6.7843</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="274" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  平安先进制造C                  019458        -   +1.66%   1.8590</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="274" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  大成有色期货联接C                007911        -        -        -</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="274" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+  追踪持仓总市值: 45531元  总盈亏: -2296元</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="274" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+【二】信源深度分析（事实核查+传导评估）</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="274">
+        <f>===============================================================================</f>
+        <v/>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="274" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+  伊娃 → 养殖</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="274" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  ────────────────────────────────────────────────────────────</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="274" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  事件:</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="274" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    06-03: 仔猪价格硬挺420元→供给收缩有序 (+1pp, 事实)</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="274" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    05-26: 17/18猪企亏损→加速去产能确认 (+5pp, 事实)</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="274" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  事实核查:</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="274" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    - 仔猪价格420元：需查牧原股份/温氏股份财报验证</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="274" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    - 17/18猪企亏损：可查2026年中报，牧原/温氏/新希望等利润数据</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="274" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    - 供给收缩：查能繁母猪存栏量（农业农村部月度数据）</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="274" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  传导分析:</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="274" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    传导链：亏损→减产→供给减少→猪价上涨→ETF涨</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="274" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    传导周期：能繁母猪→仔猪→出栏→猪价，约6-12个月</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="274" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    当前状态：ETF跌15.7%，但传导可能还没到价格层</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="274" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    宏观干扰：利率上行可能压制整个市场估值</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="274" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  结论: 事实层待核查，传导层待观察（周期长），暂不调整权重</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="274" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+  付鹏 → 芯片, 恒科, 银行</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="274" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  ────────────────────────────────────────────────────────────</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="274" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  事件:</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="274" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    05-16: 存储=AI基建 (+2pp, 虚P)</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="274" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    06-02: 恒科套利闭环不可持续 (-3pp, 事实)</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="274" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    05-19: 港股结构性偏弱 (-2pp, 事实)</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="274" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    06-02: 去杠杆周期不利 (-2pp, 虚P)</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="274" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  事实核查:</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="274" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    - 存储=AI基建：可查DRAM/NAND价格趋势（TrendForce数据）</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="274" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    - 恒科套利：可查南向资金流量、恒科溢价率</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="274" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    - 港股偏弱：可查恒生指数估值PE/PB分位数</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="274" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  传导分析:</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="274" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    芯片：存储涨价→芯片ETF涨16.4% → 传导快（资金直接买）</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="274" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    恒科：套利闭环破裂→恒科跌5% → 传导快（估值调整）</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="274" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    银行：去杠杆→银行跌1.4% → 传导中（净息差影响）</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="274" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  结论: 事实层部分可查，传导层高效（2/2实P方向对），样本不足暂不调整</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="274" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+  宋鸿兵 → 芯片, 电池</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="274" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  ────────────────────────────────────────────────────────────</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="274" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  事件:</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="274" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    06-03: 摩尔定律物理+经济双重极限 (+3pp, 事实)</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="274" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    06-03: 油价危机OECD红线 (+4pp, 虚P)</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="274" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  事实核查:</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="274" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    - 摩尔定律极限：可查Intel/TSMC制程进展、AI芯片功耗数据</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="274" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    - 油价危机：可查OECD商业库存、布伦特原油价格</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="274" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  传导分析:</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="274" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    芯片：摩尔极限→技术突破需求→芯片涨16.4% → 传导成立</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="274" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    电池：油价高→新能源需求→但电池跌8% → 传导被宏观覆盖？</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="274" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  结论: 芯片方向对，电池方向矛盾（油价高但电池跌），需区分宏观vs产业</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="274" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+  凯文·沃什（美联储） → 芯片</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="274" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  ────────────────────────────────────────────────────────────</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="274" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  事件:</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="274" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    05-22: 就任美联储主席→利率风暴 (-8pp, 宏观)</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="274" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  事实核查:</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="274" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    - 利率上行：可查10年期美债收益率（从4.x%升到5.x%）</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="274" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    - 美联储态度：点阵图、鲍威尔讲话</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="274" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  传导分析:</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="274" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    理论：利率↑→成长股估值↓→芯片应跌</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="274" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    实际：芯片涨16.4% → 产业利好（AI存储）&gt; 宏观利空（利率）</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="274" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    结论：利率对芯片的传导被AI产业需求覆盖了</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="274" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  结论: 宏观事实对，但传导被产业覆盖→权重应区分"纯宏观影响"vs"宏观+产业"场景</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="274" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+  霍尔木兹通航 → 养殖</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="274" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  ────────────────────────────────────────────────────────────</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="274" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  事件:</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="274" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    05-24: 霍尔木兹通航→利好养殖 (+9pp, 虚P)</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="274" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  事实核查:</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="274" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    - 霍尔木兹通航状态：可查原油价格、航运费率</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="274" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    - 传导链：通航→油价跌→饲料成本跌→养殖利润改善</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="274" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  传导分析:</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="274" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    传导链断了三层：</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="274" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      1. 油价→国内饲料价格（关税/自给率缓冲）</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="274" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      2. 饲料成本→养殖利润（存栏周期延迟）</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="274" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      3. 利润改善→ETF价格（市场情绪配合）</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="274" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    结论：+9pp强度严重过高，间接传导不应给这么大权重</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="274" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  结论: 虚P，传导链过长，强度定得不合理→事件强度本身需校准</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="274" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+【三】P值校准（基于深度分析）</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="274">
+        <f>===============================================================================</f>
+        <v/>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="274" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+持仓        原P    原PP    拟合     20日      持有 问题诊断                          </t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="274" t="inlineStr">
+        <is>
+          <t>--------------------------------------------------------------------------------</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="274" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  芯片      41%    -4pp    0分  +16.4%   +3.9% 拟合0分:漏了存储→资金传导事件;P偏低</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="274" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  电池      65%   +23pp   97分   -8.1%   +6.0% 拟合97分:可靠;短期回调中</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="274" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  恒科      27%   -16pp   75分   -3.4%   -6.0% 拟合75分:方向对;悲观但合理</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="274" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  养殖      70%   +15pp   95分  -14.3%  -12.5% 拟合95分但P虚高:伊娃+霍尔木兹权重问题</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="274" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  有色      39%   -11pp    0分  -10.7%   -0.4% 拟合0分:样本少;方向对但需验证</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="274" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  稀金      40%   -10pp    0分   +0.0%   +0.8% 拟合0分:样本少;关税传导需更多数据</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="274" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  银行      47%    -3pp   53分   -1.4%   +0.0% 拟合53分:一般;利率传导-1pp合理</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="274" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+  校准建议:</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="274" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  1. 芯片: 41%→48% (补存储→资金传导+5pp, 存储涨81%后资金搬入芯片)</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="274" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  2. 养殖: 70%→55% (伊娃传导待验证-5pp, 霍尔木兹强度过高-10pp调为-5pp)</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="274" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  3. 电池: 65%维持 (拟合97分可靠)</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="274" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  4. 恒科: 27%维持 (拟合75分方向对)</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="274" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  5. 有色/稀金: 维持 (样本不足，等更多数据)</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="274" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+【四】赔率计算</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="274">
+        <f>===============================================================================</f>
+        <v/>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="274" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+持仓        P值    波动率     下行风险    确定性    溢价     赔率    正期望 操作</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="274" t="inlineStr">
+        <is>
+          <t>--------------------------------------------------------------------------------</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="274" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  芯片      41%  46.0%     9.4%   0.8  1.5x   5.4:1  2.20 观望</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="274" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  电池      65%  32.7%     3.9%   0.7  1.1x  12.6:1  8.16 持有</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="274" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  恒科      27%  27.5%     6.9%   0.6  0.9x   2.1:1  0.58 不干</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="274" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  养殖      70%  21.5%     2.2%   0.5  0.7x  11.3:1  7.89 持有</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="274" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  有色      39%  39.2%     8.3%   0.4  1.3x   2.5:1  0.96 观望</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="274" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  稀金      40%  39.2%     8.1%   0.4  1.3x   2.6:1  1.03 观望</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="274" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  银行      47%  13.3%     2.4%   0.3  0.4x   2.6:1  1.21 观望</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="274" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+【五】跨品种传导矩阵（隐藏信息）</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="274">
+        <f>===============================================================================</f>
+        <v/>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="274" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+  利率上行传导:
+    理论: 利率↑→成长股↓→芯片/恒科应跌
+    实际: 芯片涨16.4%! 恒科跌5%
+    发现: AI产业需求覆盖了利率利空→利率对"有产业支撑的科技股"传导失效
+    含义: 以后利率事件对芯片的权重应降低（产业&gt;宏观）
+  霍尔木兹传导:
+    理论: 通航→油价↓→饲料成本↓→养殖利润↑
+    实际: 养殖跌15.7%
+    发现: 传导链3层断裂→间接传导效率极低
+    含义: 霍尔木兹对养殖的+9pp强度严重过高，应降至+2pp或直接标记虚P
+  AI/科技传导:
+    理论: AI基建利好芯片
+    实际: 芯片涨16.4%，但恒科跌5%
+    发现: 同是科技，芯片（硬科技/存储）vs恒科（互联网/估值）分化
+    含义: "科技"不是单一品类，需拆分为"硬科技"和"互联网"分别建模
+  关税传导:
+    理论: 301+欧盟关税→资源品需求↓
+    实际: 有色跌10.7%，稀金变化不大
+    发现: 有色（铜铝）对关税敏感，稀金（稀土）有反制溢价缓冲
+    含义: 同为资源，传导效率不同，需分品种建模
+</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="274" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+【六】操作建议（基于P值×赔率正期望）</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="274">
+        <f>===============================================================================</f>
+        <v/>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="274" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+  持仓              P值   赔率    正期望  持有盈亏  建议
+  ─────────────────────────────────────────────────────────
+  南方电池主题ETF联接A  65%  2.0:1   1.30  +6.01%  ✅ 持有（两条腿都稳）
+  汇添富芯片ETF联接A   48%  1.5:1   0.72  +3.93%  ⚠️ 等回调加仓（P偏低但产业强）
+  天弘恒生科技ETF联接C  27%  0.4:1   0.11  -5.95%  ❌ 不干（P+赔率都低）
+  招商畜牧养殖ETF联接C  55%  1.2:1   0.66 -12.49%  ⚠️ 谨慎持有（P校准后下降，等右侧信号）
+  南方有色金属ETF联接C  39%  1.7:1   0.66  -0.41%  ⏸ 观望（样本少）
+  嘉实稀有金属ETF联接C  40%  1.6:1   0.64  +0.85%  ⏸ 观望（样本少）
+  黄金组4只合计: -2018元 → 避险配置，维持
+  核心结论:
+  1. 只有电池满足"高P+高赔率"→正期望&gt;1→持有
+  2. 芯片产业逻辑强但P值偏低→等回调（如-10%）加仓
+  3. 养殖P值从70%校准到55%→正期望下降→不再激进
+  4. 恒科P+赔率双低→不操作
+</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="143">
+    <mergeCell ref="A115:Z115"/>
+    <mergeCell ref="A93:Z93"/>
+    <mergeCell ref="A102:Z102"/>
+    <mergeCell ref="A77:Z77"/>
+    <mergeCell ref="A34:Z34"/>
+    <mergeCell ref="A83:Z83"/>
+    <mergeCell ref="A92:Z92"/>
+    <mergeCell ref="A49:Z49"/>
+    <mergeCell ref="A138:Z138"/>
+    <mergeCell ref="A36:Z36"/>
+    <mergeCell ref="A119:Z119"/>
+    <mergeCell ref="A1:Z1"/>
+    <mergeCell ref="A94:Z94"/>
+    <mergeCell ref="A69:Z69"/>
+    <mergeCell ref="A78:Z78"/>
+    <mergeCell ref="A65:Z65"/>
+    <mergeCell ref="A75:Z75"/>
+    <mergeCell ref="A133:Z133"/>
+    <mergeCell ref="A80:Z80"/>
+    <mergeCell ref="A120:Z120"/>
+    <mergeCell ref="A3:Z3"/>
+    <mergeCell ref="A55:Z55"/>
+    <mergeCell ref="A12:Z12"/>
+    <mergeCell ref="A95:Z95"/>
+    <mergeCell ref="A104:Z104"/>
+    <mergeCell ref="A113:Z113"/>
+    <mergeCell ref="A5:Z5"/>
+    <mergeCell ref="A32:Z32"/>
+    <mergeCell ref="A14:Z14"/>
+    <mergeCell ref="A97:Z97"/>
+    <mergeCell ref="A106:Z106"/>
+    <mergeCell ref="A4:Z4"/>
+    <mergeCell ref="A38:Z38"/>
+    <mergeCell ref="A96:Z96"/>
+    <mergeCell ref="A43:Z43"/>
+    <mergeCell ref="A58:Z58"/>
+    <mergeCell ref="A40:Z40"/>
+    <mergeCell ref="A67:Z67"/>
+    <mergeCell ref="A130:Z130"/>
+    <mergeCell ref="A24:Z24"/>
+    <mergeCell ref="A73:Z73"/>
+    <mergeCell ref="A82:Z82"/>
+    <mergeCell ref="A60:Z60"/>
+    <mergeCell ref="A123:Z123"/>
+    <mergeCell ref="A132:Z132"/>
+    <mergeCell ref="A110:Z110"/>
+    <mergeCell ref="A124:Z124"/>
+    <mergeCell ref="A6:Z6"/>
+    <mergeCell ref="A16:Z16"/>
+    <mergeCell ref="A25:Z25"/>
+    <mergeCell ref="A108:Z108"/>
+    <mergeCell ref="A84:Z84"/>
+    <mergeCell ref="A66:Z66"/>
+    <mergeCell ref="A118:Z118"/>
+    <mergeCell ref="A18:Z18"/>
+    <mergeCell ref="A50:Z50"/>
+    <mergeCell ref="A86:Z86"/>
+    <mergeCell ref="A47:Z47"/>
+    <mergeCell ref="A141:Z141"/>
+    <mergeCell ref="A135:Z135"/>
+    <mergeCell ref="A144:Z144"/>
+    <mergeCell ref="A122:Z122"/>
+    <mergeCell ref="A20:Z20"/>
+    <mergeCell ref="A125:Z125"/>
+    <mergeCell ref="A72:Z72"/>
+    <mergeCell ref="A29:Z29"/>
+    <mergeCell ref="A134:Z134"/>
+    <mergeCell ref="A81:Z81"/>
+    <mergeCell ref="A112:Z112"/>
+    <mergeCell ref="A121:Z121"/>
+    <mergeCell ref="A13:Z13"/>
+    <mergeCell ref="A44:Z44"/>
+    <mergeCell ref="A127:Z127"/>
+    <mergeCell ref="A31:Z31"/>
+    <mergeCell ref="A114:Z114"/>
+    <mergeCell ref="A59:Z59"/>
+    <mergeCell ref="A15:Z15"/>
+    <mergeCell ref="A64:Z64"/>
+    <mergeCell ref="A98:Z98"/>
+    <mergeCell ref="A51:Z51"/>
+    <mergeCell ref="A107:Z107"/>
+    <mergeCell ref="A61:Z61"/>
+    <mergeCell ref="A88:Z88"/>
+    <mergeCell ref="A70:Z70"/>
+    <mergeCell ref="A54:Z54"/>
+    <mergeCell ref="A7:Z7"/>
+    <mergeCell ref="A41:Z41"/>
+    <mergeCell ref="A90:Z90"/>
+    <mergeCell ref="A99:Z99"/>
+    <mergeCell ref="A74:Z74"/>
+    <mergeCell ref="A56:Z56"/>
+    <mergeCell ref="A27:Z27"/>
+    <mergeCell ref="A101:Z101"/>
+    <mergeCell ref="A76:Z76"/>
+    <mergeCell ref="A33:Z33"/>
+    <mergeCell ref="A85:Z85"/>
+    <mergeCell ref="A42:Z42"/>
+    <mergeCell ref="A17:Z17"/>
+    <mergeCell ref="A126:Z126"/>
+    <mergeCell ref="A140:Z140"/>
+    <mergeCell ref="A22:Z22"/>
+    <mergeCell ref="A53:Z53"/>
+    <mergeCell ref="A35:Z35"/>
+    <mergeCell ref="A109:Z109"/>
+    <mergeCell ref="A62:Z62"/>
+    <mergeCell ref="A10:Z10"/>
+    <mergeCell ref="A68:Z68"/>
+    <mergeCell ref="A19:Z19"/>
+    <mergeCell ref="A28:Z28"/>
+    <mergeCell ref="A117:Z117"/>
+    <mergeCell ref="A111:Z111"/>
+    <mergeCell ref="A9:Z9"/>
+    <mergeCell ref="A143:Z143"/>
+    <mergeCell ref="A39:Z39"/>
+    <mergeCell ref="A48:Z48"/>
+    <mergeCell ref="A30:Z30"/>
+    <mergeCell ref="A142:Z142"/>
+    <mergeCell ref="A11:Z11"/>
+    <mergeCell ref="A45:Z45"/>
+    <mergeCell ref="A103:Z103"/>
+    <mergeCell ref="A79:Z79"/>
+    <mergeCell ref="A87:Z87"/>
+    <mergeCell ref="A128:Z128"/>
+    <mergeCell ref="A137:Z137"/>
+    <mergeCell ref="A37:Z37"/>
+    <mergeCell ref="A46:Z46"/>
+    <mergeCell ref="A89:Z89"/>
+    <mergeCell ref="A136:Z136"/>
+    <mergeCell ref="A21:Z21"/>
+    <mergeCell ref="A105:Z105"/>
+    <mergeCell ref="A26:Z26"/>
+    <mergeCell ref="A57:Z57"/>
+    <mergeCell ref="A139:Z139"/>
+    <mergeCell ref="A71:Z71"/>
+    <mergeCell ref="A129:Z129"/>
+    <mergeCell ref="A23:Z23"/>
+    <mergeCell ref="A116:Z116"/>
+    <mergeCell ref="A8:Z8"/>
+    <mergeCell ref="A91:Z91"/>
+    <mergeCell ref="A131:Z131"/>
+    <mergeCell ref="A100:Z100"/>
+    <mergeCell ref="A52:Z52"/>
+    <mergeCell ref="A63:Z63"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr filterMode="0">

--- a/持仓贝叶斯跟踪.xlsx
+++ b/持仓贝叶斯跟踪.xlsx
@@ -5976,16 +5976,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z144"/>
+  <dimension ref="A1:Z120"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="120" customWidth="1" style="139" min="1" max="1"/>
+    <col width="140" customWidth="1" style="139" min="1" max="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="270" t="inlineStr">
         <is>
-          <t>🔬 深度分析报告 (2026-06-06)</t>
+          <t>🔬 深度分析报告 (2026-06-06 01:00)</t>
         </is>
       </c>
     </row>
@@ -5998,253 +5998,252 @@
     <row r="4">
       <c r="A4" s="274" t="inlineStr">
         <is>
-          <t xml:space="preserve">  持仓贝叶斯P值+赔率 深度分析报告</t>
+          <t xml:space="preserve">  持仓贝叶斯P值+赔率 深度分析报告（完整版）</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="274" t="inlineStr">
         <is>
-          <t xml:space="preserve">  生成时间: 2026-06-06 00:43</t>
+          <t xml:space="preserve">  生成时间: 2026-06-06 01:00</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="274">
+      <c r="A6" s="274" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  数据源: 天天基金fundgz估值API + 历史净值API + 支付宝基准</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="274">
         <f>===============================================================================</f>
         <v/>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="274" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-【一】持仓全景（全部27只基金）</t>
-        </is>
-      </c>
-    </row>
     <row r="8">
       <c r="A8" s="274" t="inlineStr">
         <is>
-          <t>--------------------------------------------------------------------------------</t>
+          <t xml:space="preserve">
+【一】持仓全景（全部28只基金）</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="274" t="inlineStr">
         <is>
-          <t>基金名称                         代码       成本     今日涨跌       净值</t>
+          <t>--------------------------------------------------------------------------------</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="274" t="inlineStr">
         <is>
-          <t>--------------------------------------------------------------------------------</t>
+          <t>基金名称                         代码       成本     今日涨跌       净值</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="274" t="inlineStr">
         <is>
-          <t xml:space="preserve">  汇添富上证科创板芯片ETF联接A         020628     3206   -4.87%   3.5305</t>
+          <t>--------------------------------------------------------------------------------</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="274" t="inlineStr">
         <is>
-          <t xml:space="preserve">  南方中证电池主题ETF联接A           018926     6811   -1.88%   1.7183</t>
+          <t xml:space="preserve">  汇添富上证科创板芯片ETF联接A         020628     3206   -4.87%   3.5305</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="274" t="inlineStr">
         <is>
-          <t xml:space="preserve">  天弘恒生科技ETF联接C             012349     4822   -1.66%   0.6725</t>
+          <t xml:space="preserve">  南方中证电池主题ETF联接A           018926     6811   -1.88%   1.7183</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="274" t="inlineStr">
         <is>
-          <t xml:space="preserve">  招商中证畜牧养殖ETF联接C           014415     4432   -0.48%   0.7249</t>
+          <t xml:space="preserve">  天弘恒生科技ETF联接C             012349     4822   -1.66%   0.6725</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="274" t="inlineStr">
         <is>
-          <t xml:space="preserve">  南方有色金属ETF联接C             004433     4800   -2.12%   1.8756</t>
+          <t xml:space="preserve">  招商中证畜牧养殖ETF联接C           014415     4432   -0.48%   0.7249</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="274" t="inlineStr">
         <is>
-          <t xml:space="preserve">  嘉实中证稀有金属主题ETF联接C         014111     5822   -1.24%   1.0594</t>
+          <t xml:space="preserve">  南方有色金属ETF联接C             004433     4800   -2.12%   1.8756</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="274" t="inlineStr">
         <is>
-          <t xml:space="preserve">  银行ETF联接C                 001595        -   +1.32%   1.6526</t>
+          <t xml:space="preserve">  嘉实中证稀有金属主题ETF联接C         014111     5822   -1.24%   1.0594</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="274" t="inlineStr">
         <is>
-          <t xml:space="preserve">  景顺长城中证科创创业人工智能ETF        027048      101   -4.08%   1.1090</t>
+          <t xml:space="preserve">  银行ETF联接C                 001595        -   +1.32%   1.6526</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="274" t="inlineStr">
         <is>
-          <t xml:space="preserve">  国泰黄金ETF联接A               000218     2787   -0.01%   3.5234</t>
+          <t xml:space="preserve">  景顺长城中证科创创业人工智能ETF        027048      101   -4.08%   1.1090</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="274" t="inlineStr">
         <is>
-          <t xml:space="preserve">  博时黄金ETF联接C               002611     3267   -0.01%   3.0625</t>
+          <t xml:space="preserve">  国泰黄金ETF联接A               000218     2787   -0.01%   3.5234</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="274" t="inlineStr">
         <is>
-          <t xml:space="preserve">  建信上海金ETF联接C              009034     2939   +0.00%   2.2511</t>
+          <t xml:space="preserve">  博时黄金ETF联接C               002611     3267   -0.01%   3.0625</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="274" t="inlineStr">
         <is>
-          <t xml:space="preserve">  前海开源金银珠宝混合C              002207     8839   -1.15%   2.5340</t>
+          <t xml:space="preserve">  建信上海金ETF联接C              009034     2939   +0.00%   2.2511</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="274" t="inlineStr">
         <is>
-          <t xml:space="preserve">  永赢先进制造智选A                018124        -   +0.74%   2.4177</t>
+          <t xml:space="preserve">  前海开源金银珠宝混合C              002207     8839   -1.15%   2.5340</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="274" t="inlineStr">
         <is>
-          <t xml:space="preserve">  嘉实自由现金流联接C               024575        -   -0.62%   1.1112</t>
+          <t xml:space="preserve">  永赢先进制造智选A                018124        -   +0.74%   2.4177</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="274" t="inlineStr">
         <is>
-          <t xml:space="preserve">  华宝纳斯达克精选QA               017436        -   -0.28%   2.5059</t>
+          <t xml:space="preserve">  嘉实自由现金流联接C               024575        -   -0.62%   1.1112</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="274" t="inlineStr">
         <is>
-          <t xml:space="preserve">  华宝有色联接C                  017141        -   -2.14%   1.6717</t>
+          <t xml:space="preserve">  华宝纳斯达克精选QA               017436        -   -0.28%   2.5059</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="274" t="inlineStr">
         <is>
-          <t xml:space="preserve">  景顺招利6月债券A                010011        -   -0.20%   1.3247</t>
+          <t xml:space="preserve">  华宝有色联接C                  017141        -   -2.14%   1.6717</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="274" t="inlineStr">
         <is>
-          <t xml:space="preserve">  汇添富鑫享添利6月A               012951        -   -0.13%   1.1815</t>
+          <t xml:space="preserve">  景顺招利6月债券A                010011        -   -0.20%   1.3247</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="274" t="inlineStr">
         <is>
-          <t xml:space="preserve">  永赢医药创新A                  015915        -   -1.17%   1.4207</t>
+          <t xml:space="preserve">  汇添富鑫享添利6月A               012951        -   -0.13%   1.1815</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="274" t="inlineStr">
         <is>
-          <t xml:space="preserve">  广发碳中和混合C                 018419        -   -2.25%   1.9262</t>
+          <t xml:space="preserve">  永赢医药创新A                  015915        -   -1.17%   1.4207</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="274" t="inlineStr">
         <is>
-          <t xml:space="preserve">  天弘绿色电力C                  017175        -   -3.68%   1.2385</t>
+          <t xml:space="preserve">  广发碳中和混合C                 018419        -   -2.25%   1.9262</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="274" t="inlineStr">
         <is>
-          <t xml:space="preserve">  摩根日本精选QC                 019449        -        -        -</t>
+          <t xml:space="preserve">  天弘绿色电力C                  017175        -   -3.68%   1.2385</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="274" t="inlineStr">
         <is>
-          <t xml:space="preserve">  华宝海外科技QA                 501312        -   +0.00%   2.4162</t>
+          <t xml:space="preserve">  摩根日本精选QC                 019449        -      N/A      N/A</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="274" t="inlineStr">
         <is>
-          <t xml:space="preserve">  摩根日本精选QA                 007280        -        -        -</t>
+          <t xml:space="preserve">  华宝海外科技QA                 501312        -   +0.00%   2.4162</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="274" t="inlineStr">
         <is>
-          <t xml:space="preserve">  港股通互联网联接A                027127        -   -0.32%   1.0106</t>
+          <t xml:space="preserve">  摩根日本精选QA                 007280        -      N/A      N/A</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="274" t="inlineStr">
         <is>
-          <t xml:space="preserve">  广发全球精选QDIIC              021277        -   -0.17%   6.7843</t>
+          <t xml:space="preserve">  港股通互联网联接A                027127        -   -0.32%   1.0106</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="274" t="inlineStr">
         <is>
-          <t xml:space="preserve">  平安先进制造C                  019458        -   +1.66%   1.8590</t>
+          <t xml:space="preserve">  广发全球精选QDIIC              021277        -   -0.17%   6.7843</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="274" t="inlineStr">
         <is>
-          <t xml:space="preserve">  大成有色期货联接C                007911        -        -        -</t>
+          <t xml:space="preserve">  平安先进制造C                  019458        -   +1.66%   1.8590</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="274" t="inlineStr">
         <is>
-          <t xml:space="preserve">
-  追踪持仓总市值: 45531元  总盈亏: -2296元</t>
+          <t xml:space="preserve">  大成有色期货联接C                007911        -      N/A      N/A</t>
         </is>
       </c>
     </row>
@@ -6252,783 +6251,623 @@
       <c r="A40" s="274" t="inlineStr">
         <is>
           <t xml:space="preserve">
-【二】信源深度分析（事实核查+传导评估）</t>
+  追踪持仓总市值: 29716元  总盈亏: -278元</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="274">
+      <c r="A41" s="274" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+【二】信源深度核查（25条事件×价格传导验证）</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="274">
         <f>===============================================================================</f>
         <v/>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" s="274" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-  伊娃 → 养殖</t>
-        </is>
-      </c>
-    </row>
     <row r="43">
       <c r="A43" s="274" t="inlineStr">
         <is>
-          <t xml:space="preserve">  ────────────────────────────────────────────────────────────</t>
+          <t xml:space="preserve">
+信源             持仓     PP 事件                     1天     3天     5天    10天   最优lag 方向</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="274" t="inlineStr">
         <is>
-          <t xml:space="preserve">  事件:</t>
+          <t>------------------------------------------------------------------------------------------</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="274" t="inlineStr">
         <is>
-          <t xml:space="preserve">    06-03: 仔猪价格硬挺420元→供给收缩有序 (+1pp, 事实)</t>
+          <t xml:space="preserve">  宋鸿兵            芯片    +3pp 摩尔定律极限+堆叠崛起         -3.3%  +0.4%  +3.6%  +4.9%      7天 ✅</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="274" t="inlineStr">
         <is>
-          <t xml:space="preserve">    05-26: 17/18猪企亏损→加速去产能确认 (+5pp, 事实)</t>
+          <t xml:space="preserve">  蒋宇飞            芯片    +2pp AI基建10年+国产算力        -2.2%  +9.6%  +9.9%  +3.8%      6天 ✅</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="274" t="inlineStr">
         <is>
-          <t xml:space="preserve">  事实核查:</t>
+          <t xml:space="preserve">  蒋宇飞            芯片    +1pp 玻璃基板万亿机遇            -6.2%  -3.3% -10.8% -11.5%     N/A ?</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="274" t="inlineStr">
         <is>
-          <t xml:space="preserve">    - 仔猪价格420元：需查牧原股份/温氏股份财报验证</t>
+          <t xml:space="preserve">  付鹏             芯片    +2pp 存储=AI基建               N/A    N/A    N/A    N/A     N/A ?</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="274" t="inlineStr">
         <is>
-          <t xml:space="preserve">    - 17/18猪企亏损：可查2026年中报，牧原/温氏/新希望等利润数据</t>
+          <t xml:space="preserve">  Schiff+周鸿祎     芯片    +1pp 美债熊市+内存决定高度         -2.3%  +2.3%  -5.8%  -7.8%      3天 ✅</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="274" t="inlineStr">
         <is>
-          <t xml:space="preserve">    - 供给收缩：查能繁母猪存栏量（农业农村部月度数据）</t>
+          <t xml:space="preserve">  凯文·沃什          芯片    -8pp 就任美联储→利率风暴          -1.8%  -1.3%  -5.5% -10.4%     20天 ✅</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="274" t="inlineStr">
         <is>
-          <t xml:space="preserve">  传导分析:</t>
+          <t xml:space="preserve">  韩国闪崩           芯片    -2pp 韩国股市闪崩情绪            -3.6%  -2.7%  -3.2% -13.5%     20天 ✅</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="274" t="inlineStr">
         <is>
-          <t xml:space="preserve">    传导链：亏损→减产→供给减少→猪价上涨→ETF涨</t>
+          <t xml:space="preserve">  雪佛龙            电池    +6pp 油价危机OECD红线          +1.1%  +2.1%  +5.4%  +7.7%     20天 ✅</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="274" t="inlineStr">
         <is>
-          <t xml:space="preserve">    传导周期：能繁母猪→仔猪→出栏→猪价，约6-12个月</t>
+          <t xml:space="preserve">  巴克莱            电池    +5pp 碳酸锂跌价+巴克莱看多         -0.1%  -1.9%  +0.8%  +0.2%      9天 ✅</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="274" t="inlineStr">
         <is>
-          <t xml:space="preserve">    当前状态：ETF跌15.7%，但传导可能还没到价格层</t>
+          <t xml:space="preserve">  恩捷+特朗普         电池    +5pp 特朗普访华+恩捷40亿扩产       -0.6%  -0.2%  +2.4%  -4.1%      5天 ✅</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="274" t="inlineStr">
         <is>
-          <t xml:space="preserve">    宏观干扰：利率上行可能压制整个市场估值</t>
+          <t xml:space="preserve">  维力能            电池    +2pp 储能全球第二              +0.3%  +4.1%  +3.7%  +3.8%     19天 ✅</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="274" t="inlineStr">
         <is>
-          <t xml:space="preserve">  结论: 事实层待核查，传导层待观察（周期长），暂不调整权重</t>
+          <t xml:space="preserve">  付鹏             恒科    -3pp 恒科套利闭环不可持续          -4.3%  -5.5%  -4.4%  -5.9%      8天 ✅</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="274" t="inlineStr">
         <is>
-          <t xml:space="preserve">
-  付鹏 → 芯片, 恒科, 银行</t>
+          <t xml:space="preserve">  付鹏+古都闲云        恒科    -4pp 港股偏弱+社消疲弱           -0.2%  +4.3%  +4.2%  +0.6%     12天 ✅</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="274" t="inlineStr">
         <is>
-          <t xml:space="preserve">  ────────────────────────────────────────────────────────────</t>
+          <t xml:space="preserve">  伊娃             养殖    +1pp 仔猪价格硬挺420元          +1.1%  +1.7%  +2.6%  +6.8%     20天 ✅</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="274" t="inlineStr">
         <is>
-          <t xml:space="preserve">  事件:</t>
+          <t xml:space="preserve">  伊娃             养殖    +5pp 17/18猪企亏损→去产能       -0.6%  +0.6%  +3.3%  +6.2%     14天 ✅</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="274" t="inlineStr">
         <is>
-          <t xml:space="preserve">    05-16: 存储=AI基建 (+2pp, 虚P)</t>
+          <t xml:space="preserve">  霍尔木兹           养殖    +9pp 霍尔木兹通航→利好养殖           N/A    N/A    N/A    N/A     N/A ?</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="274" t="inlineStr">
         <is>
-          <t xml:space="preserve">    06-02: 恒科套利闭环不可持续 (-3pp, 事实)</t>
+          <t xml:space="preserve">  无知半人           养殖    -2pp 住户贷款-4902亿          +0.6%  +3.3%  +5.6%  +7.5%     N/A ?</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="274" t="inlineStr">
         <is>
-          <t xml:space="preserve">    05-19: 港股结构性偏弱 (-2pp, 事实)</t>
+          <t xml:space="preserve">  古都闲云           养殖    -2pp 社消数据疲弱              -0.1%  +3.0%  +2.8%  +5.8%      1天 ✅</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="274" t="inlineStr">
         <is>
-          <t xml:space="preserve">    06-02: 去杠杆周期不利 (-2pp, 虚P)</t>
+          <t xml:space="preserve">  知乎             有色    -5pp 301关税+欧盟钢铁关税        -0.8%  -3.2%  -1.2%  -2.2%      9天 ✅</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="274" t="inlineStr">
         <is>
-          <t xml:space="preserve">  事实核查:</t>
+          <t xml:space="preserve">  岩松             有色    -2pp 资源非长期抗通胀            +1.3%  +7.1% +10.0%  +6.5%     N/A ?</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="274" t="inlineStr">
         <is>
-          <t xml:space="preserve">    - 存储=AI基建：可查DRAM/NAND价格趋势（TrendForce数据）</t>
+          <t xml:space="preserve">  AI铜需求          有色    +4pp AI铜需求爆发             -3.4%  -1.6%  +1.1%  +9.0%      7天 ✅</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="274" t="inlineStr">
         <is>
-          <t xml:space="preserve">    - 恒科套利：可查南向资金流量、恒科溢价率</t>
+          <t xml:space="preserve">  知乎             稀金    -3pp 贸易利空稀土              -1.7%  -1.6%  -0.0%  +0.5%      2天 ✅</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="274" t="inlineStr">
         <is>
-          <t xml:space="preserve">    - 港股偏弱：可查恒生指数估值PE/PB分位数</t>
+          <t xml:space="preserve">  岩松             稀金    -5pp 资源非长期抗通胀            +2.7%  +6.0% +10.0%  +8.6%     N/A ?</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="274" t="inlineStr">
         <is>
-          <t xml:space="preserve">  传导分析:</t>
+          <t xml:space="preserve">  付鹏             银行    -2pp 去杠杆周期不利             -0.6%  -3.3%  -2.4%  -1.8%      3天 ✅</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="274" t="inlineStr">
         <is>
-          <t xml:space="preserve">    芯片：存储涨价→芯片ETF涨16.4% → 传导快（资金直接买）</t>
+          <t xml:space="preserve">  无知半人           银行    -3pp 住户贷款-4902亿          +0.2%  +0.9%  +1.4%  +2.0%      2天 ✅</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="274" t="inlineStr">
         <is>
-          <t xml:space="preserve">    恒科：套利闭环破裂→恒科跌5% → 传导快（估值调整）</t>
+          <t xml:space="preserve">
+【三】信源权重校准（Spearman秩相关）</t>
         </is>
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="274" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    银行：去杠杆→银行跌1.4% → 传导中（净息差影响）</t>
-        </is>
+      <c r="A71" s="274">
+        <f>===============================================================================</f>
+        <v/>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="274" t="inlineStr">
         <is>
-          <t xml:space="preserve">  结论: 事实层部分可查，传导层高效（2/2实P方向对），样本不足暂不调整</t>
+          <t xml:space="preserve">  AI铜需求→有色: n=1 方向100% 样本不足→权重=1.0 lag=['7天']</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="274" t="inlineStr">
         <is>
-          <t xml:space="preserve">
-  宋鸿兵 → 芯片, 电池</t>
+          <t xml:space="preserve">  Schiff+周鸿祎→芯片: n=1 方向100% 样本不足→权重=1.0 lag=['3天']</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="274" t="inlineStr">
         <is>
-          <t xml:space="preserve">  ────────────────────────────────────────────────────────────</t>
+          <t xml:space="preserve">  付鹏+古都闲云→恒科: n=1 方向100% 样本不足→权重=1.0 lag=['12天']</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="274" t="inlineStr">
         <is>
-          <t xml:space="preserve">  事件:</t>
+          <t xml:space="preserve">  付鹏→恒科: n=1 方向100% 样本不足→权重=1.0 lag=['8天']</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="274" t="inlineStr">
         <is>
-          <t xml:space="preserve">    06-03: 摩尔定律物理+经济双重极限 (+3pp, 事实)</t>
+          <t xml:space="preserve">  付鹏→银行: n=1 方向100% 样本不足→权重=1.0 lag=['3天']</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="274" t="inlineStr">
         <is>
-          <t xml:space="preserve">    06-03: 油价危机OECD红线 (+4pp, 虚P)</t>
+          <t xml:space="preserve">  伊娃→养殖: n=2 方向100% ρ=-1.000 权重=-0.50 lag=['20天', '14天']</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="274" t="inlineStr">
         <is>
-          <t xml:space="preserve">  事实核查:</t>
+          <t xml:space="preserve">  凯文·沃什→芯片: n=1 方向100% 样本不足→权重=1.0 lag=['20天']</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="274" t="inlineStr">
         <is>
-          <t xml:space="preserve">    - 摩尔定律极限：可查Intel/TSMC制程进展、AI芯片功耗数据</t>
+          <t xml:space="preserve">  古都闲云→养殖: n=1 方向100% 样本不足→权重=1.0 lag=['1天']</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="274" t="inlineStr">
         <is>
-          <t xml:space="preserve">    - 油价危机：可查OECD商业库存、布伦特原油价格</t>
+          <t xml:space="preserve">  宋鸿兵→芯片: n=1 方向100% 样本不足→权重=1.0 lag=['7天']</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="274" t="inlineStr">
         <is>
-          <t xml:space="preserve">  传导分析:</t>
+          <t xml:space="preserve">  巴克莱→电池: n=1 方向100% 样本不足→权重=1.0 lag=['9天']</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="274" t="inlineStr">
         <is>
-          <t xml:space="preserve">    芯片：摩尔极限→技术突破需求→芯片涨16.4% → 传导成立</t>
+          <t xml:space="preserve">  恩捷+特朗普→电池: n=1 方向100% 样本不足→权重=1.0 lag=['5天']</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="274" t="inlineStr">
         <is>
-          <t xml:space="preserve">    电池：油价高→新能源需求→但电池跌8% → 传导被宏观覆盖？</t>
+          <t xml:space="preserve">  无知半人→银行: n=1 方向100% 样本不足→权重=1.0 lag=['2天']</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="274" t="inlineStr">
         <is>
-          <t xml:space="preserve">  结论: 芯片方向对，电池方向矛盾（油价高但电池跌），需区分宏观vs产业</t>
+          <t xml:space="preserve">  知乎→有色: n=1 方向100% 样本不足→权重=1.0 lag=['9天']</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="274" t="inlineStr">
         <is>
-          <t xml:space="preserve">
-  凯文·沃什（美联储） → 芯片</t>
+          <t xml:space="preserve">  知乎→稀金: n=1 方向100% 样本不足→权重=1.0 lag=['2天']</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="274" t="inlineStr">
         <is>
-          <t xml:space="preserve">  ────────────────────────────────────────────────────────────</t>
+          <t xml:space="preserve">  维力能→电池: n=1 方向100% 样本不足→权重=1.0 lag=['19天']</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="274" t="inlineStr">
         <is>
-          <t xml:space="preserve">  事件:</t>
+          <t xml:space="preserve">  蒋宇飞→芯片: n=1 方向100% 样本不足→权重=1.0 lag=['6天']</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="274" t="inlineStr">
         <is>
-          <t xml:space="preserve">    05-22: 就任美联储主席→利率风暴 (-8pp, 宏观)</t>
+          <t xml:space="preserve">  雪佛龙→电池: n=1 方向100% 样本不足→权重=1.0 lag=['20天']</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="274" t="inlineStr">
         <is>
-          <t xml:space="preserve">  事实核查:</t>
+          <t xml:space="preserve">  韩国闪崩→芯片: n=1 方向100% 样本不足→权重=1.0 lag=['20天']</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="274" t="inlineStr">
         <is>
-          <t xml:space="preserve">    - 利率上行：可查10年期美债收益率（从4.x%升到5.x%）</t>
+          <t xml:space="preserve">
+【四】P值校准结果</t>
         </is>
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="274" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    - 美联储态度：点阵图、鲍威尔讲话</t>
-        </is>
+      <c r="A91" s="274">
+        <f>===============================================================================</f>
+        <v/>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="274" t="inlineStr">
         <is>
-          <t xml:space="preserve">  传导分析:</t>
+          <t xml:space="preserve">
+持仓        原P    校准PP    校准P    拟合     20日      持有 诊断</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="274" t="inlineStr">
         <is>
-          <t xml:space="preserve">    理论：利率↑→成长股估值↓→芯片应跌</t>
+          <t>--------------------------------------------------------------------------------</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="274" t="inlineStr">
         <is>
-          <t xml:space="preserve">    实际：芯片涨16.4% → 产业利好（AI存储）&gt; 宏观利空（利率）</t>
+          <t xml:space="preserve">  芯片      41%   -1.0pp  49.0%   97分  -14.3%   +3.9% 利率-8pp被AI覆盖;漏存储→资金传导事件</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="274" t="inlineStr">
         <is>
-          <t xml:space="preserve">    结论：利率对芯片的传导被AI产业需求覆盖了</t>
+          <t xml:space="preserve">  电池      65%  +18.0pp  68.0%   97分   -8.1%   +6.0% 拟合97分可靠;短期回调中</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="274" t="inlineStr">
         <is>
-          <t xml:space="preserve">  结论: 宏观事实对，但传导被产业覆盖→权重应区分"纯宏观影响"vs"宏观+产业"场景</t>
+          <t xml:space="preserve">  恒科      27%   -7.0pp  43.0%   75分   -3.4%   -6.0% 拟合75分方向对;悲观但合理</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="274" t="inlineStr">
         <is>
-          <t xml:space="preserve">
-  霍尔木兹通航 → 养殖</t>
+          <t xml:space="preserve">  养殖      70%   +2.0pp  52.0%   95分  -14.3%  -12.5% 拟合95分但霍尔木兹+9pp强度过高</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="274" t="inlineStr">
         <is>
-          <t xml:space="preserve">  ────────────────────────────────────────────────────────────</t>
+          <t xml:space="preserve">  有色      39%   -3.0pp  47.0%    0分  -10.7%   -0.4% 拟合0分样本少</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="274" t="inlineStr">
         <is>
-          <t xml:space="preserve">  事件:</t>
+          <t xml:space="preserve">  稀金      40%   -8.0pp  42.0%    0分   +0.0%   +0.8% 拟合0分样本少</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="274" t="inlineStr">
         <is>
-          <t xml:space="preserve">    05-24: 霍尔木兹通航→利好养殖 (+9pp, 虚P)</t>
+          <t xml:space="preserve">  银行      47%   -5.0pp  45.0%   53分   -1.4%   +0.0% 拟合53分一般</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="274" t="inlineStr">
         <is>
-          <t xml:space="preserve">  事实核查:</t>
+          <t xml:space="preserve">
+【五】赔率 + 正期望（核心决策指标）</t>
         </is>
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="274" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    - 霍尔木兹通航状态：可查原油价格、航运费率</t>
-        </is>
+      <c r="A102" s="274">
+        <f>===============================================================================</f>
+        <v/>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="274" t="inlineStr">
         <is>
-          <t xml:space="preserve">    - 传导链：通航→油价跌→饲料成本跌→养殖利润改善</t>
+          <t xml:space="preserve">
+持仓        P值     赔率    正期望     下行风险     上行空间 操作</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="274" t="inlineStr">
         <is>
-          <t xml:space="preserve">  传导分析:</t>
+          <t>--------------------------------------------------------------------------------</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="274" t="inlineStr">
         <is>
-          <t xml:space="preserve">    传导链断了三层：</t>
+          <t xml:space="preserve">  芯片    49.0%   7.4:1  3.64     8.1%    60.1% ✅持有</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="274" t="inlineStr">
         <is>
-          <t xml:space="preserve">      1. 油价→国内饲料价格（关税/自给率缓冲）</t>
+          <t xml:space="preserve">  电池    68.0%  14.4:1  9.77     3.6%    51.9% ✅持有</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="274" t="inlineStr">
         <is>
-          <t xml:space="preserve">      2. 饲料成本→养殖利润（存栏周期延迟）</t>
+          <t xml:space="preserve">  恒科    43.0%   4.4:1  1.88     5.4%    23.6% ✅持有</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="274" t="inlineStr">
         <is>
-          <t xml:space="preserve">      3. 利润改善→ETF价格（市场情绪配合）</t>
+          <t xml:space="preserve">  养殖    52.0%   5.2:1  2.72     3.6%    18.6% ✅持有</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="274" t="inlineStr">
         <is>
-          <t xml:space="preserve">    结论：+9pp强度严重过高，间接传导不应给这么大权重</t>
+          <t xml:space="preserve">  有色    47.0%   3.4:1  1.61     7.2%    24.6% ✅持有</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="274" t="inlineStr">
         <is>
-          <t xml:space="preserve">  结论: 虚P，传导链过长，强度定得不合理→事件强度本身需校准</t>
+          <t xml:space="preserve">  稀金    42.0%   2.8:1  1.18     7.8%    22.0% ⚠️观察</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="274" t="inlineStr">
         <is>
+          <t xml:space="preserve">  银行    45.0%   2.4:1  1.07     2.5%     6.0% ⚠️观察</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="274" t="inlineStr">
+        <is>
           <t xml:space="preserve">
-【三】P值校准（基于深度分析）</t>
-        </is>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" s="274">
+【六】跨品种传导矩阵（AI发现的隐藏信息）</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="274">
         <f>===============================================================================</f>
         <v/>
       </c>
     </row>
-    <row r="113">
-      <c r="A113" s="274" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-持仓        原P    原PP    拟合     20日      持有 问题诊断                          </t>
-        </is>
-      </c>
-    </row>
     <row r="114">
       <c r="A114" s="274" t="inlineStr">
         <is>
-          <t>--------------------------------------------------------------------------------</t>
+          <t xml:space="preserve">
+  发现1: 利率传导被AI产业覆盖
+    凯文·沃什-8pp利率风暴→芯片理论应跌
+    实际: 芯片涨16.4%（AI存储需求覆盖利率利空）
+    含义: 利率对"有产业支撑的科技股"传导效率极低
+    建议: 以后利率事件对芯片的权重应打折
+  发现2: 霍尔木兹→养殖传导链断裂
+    霍尔木兹+9pp→油价跌→饲料成本跌→养殖利润改善
+    实际: 养殖跌15.7%
+    传导链3层断裂（国内饲料不一定同步/存栏周期/市场情绪）
+    建议: 霍尔木兹对养殖的+9pp强度严重过高，应降至+2~3pp
+  发现3: 科技股内部严重分化
+    同是科技：芯片（硬科技/存储）涨16.4% vs 恒科（互联网/估值）跌5%
+    含义: "科技"不是单一品类，需拆分为"硬科技"和"互联网"分别建模
+  发现4: 资源品传导效率不同
+    有色（铜铝）对关税敏感→跌10.7%
+    稀金（稀土）有反制溢价缓冲→变化不大
+    含义: 同为资源，传导效率不同，需分品种建模
+  发现5: 伊娃方向全对但传导窗口长
+    2条事件方向准确率100%，但最优lag=14~20天
+    养殖是长周期产业（能繁母猪→出栏→猪价约6-12个月）
+    短期价格不反应≠信源错，是传导还没到价格层
+</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="274" t="inlineStr">
         <is>
-          <t xml:space="preserve">  芯片      41%    -4pp    0分  +16.4%   +3.9% 拟合0分:漏了存储→资金传导事件;P偏低</t>
+          <t xml:space="preserve">
+【七】操作建议（基于P值×赔率正期望）</t>
         </is>
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="274" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  电池      65%   +23pp   97分   -8.1%   +6.0% 拟合97分:可靠;短期回调中</t>
-        </is>
+      <c r="A116" s="274">
+        <f>===============================================================================</f>
+        <v/>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="274" t="inlineStr">
         <is>
-          <t xml:space="preserve">  恒科      27%   -16pp   75分   -3.4%   -6.0% 拟合75分:方向对;悲观但合理</t>
-        </is>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" s="274" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  养殖      70%   +15pp   95分  -14.3%  -12.5% 拟合95分但P虚高:伊娃+霍尔木兹权重问题</t>
-        </is>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" s="274" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  有色      39%   -11pp    0分  -10.7%   -0.4% 拟合0分:样本少;方向对但需验证</t>
-        </is>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" s="274" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  稀金      40%   -10pp    0分   +0.0%   +0.8% 拟合0分:样本少;关税传导需更多数据</t>
-        </is>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" s="274" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  银行      47%    -3pp   53分   -1.4%   +0.0% 拟合53分:一般;利率传导-1pp合理</t>
-        </is>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" s="274" t="inlineStr">
-        <is>
           <t xml:space="preserve">
-  校准建议:</t>
-        </is>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" s="274" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  1. 芯片: 41%→48% (补存储→资金传导+5pp, 存储涨81%后资金搬入芯片)</t>
-        </is>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" s="274" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  2. 养殖: 70%→55% (伊娃传导待验证-5pp, 霍尔木兹强度过高-10pp调为-5pp)</t>
-        </is>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" s="274" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  3. 电池: 65%维持 (拟合97分可靠)</t>
-        </is>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" s="274" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  4. 恒科: 27%维持 (拟合75分方向对)</t>
-        </is>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" s="274" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  5. 有色/稀金: 维持 (样本不足，等更多数据)</t>
-        </is>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" s="274" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-【四】赔率计算</t>
-        </is>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" s="274">
-        <f>===============================================================================</f>
-        <v/>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" s="274" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-持仓        P值    波动率     下行风险    确定性    溢价     赔率    正期望 操作</t>
-        </is>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" s="274" t="inlineStr">
-        <is>
-          <t>--------------------------------------------------------------------------------</t>
-        </is>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" s="274" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  芯片      41%  46.0%     9.4%   0.8  1.5x   5.4:1  2.20 观望</t>
-        </is>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" s="274" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  电池      65%  32.7%     3.9%   0.7  1.1x  12.6:1  8.16 持有</t>
-        </is>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" s="274" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  恒科      27%  27.5%     6.9%   0.6  0.9x   2.1:1  0.58 不干</t>
-        </is>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" s="274" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  养殖      70%  21.5%     2.2%   0.5  0.7x  11.3:1  7.89 持有</t>
-        </is>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" s="274" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  有色      39%  39.2%     8.3%   0.4  1.3x   2.5:1  0.96 观望</t>
-        </is>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" s="274" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  稀金      40%  39.2%     8.1%   0.4  1.3x   2.6:1  1.03 观望</t>
-        </is>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" s="274" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  银行      47%  13.3%     2.4%   0.3  0.4x   2.6:1  1.21 观望</t>
-        </is>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" s="274" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-【五】跨品种传导矩阵（隐藏信息）</t>
-        </is>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" s="274">
-        <f>===============================================================================</f>
-        <v/>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" s="274" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-  利率上行传导:
-    理论: 利率↑→成长股↓→芯片/恒科应跌
-    实际: 芯片涨16.4%! 恒科跌5%
-    发现: AI产业需求覆盖了利率利空→利率对"有产业支撑的科技股"传导失效
-    含义: 以后利率事件对芯片的权重应降低（产业&gt;宏观）
-  霍尔木兹传导:
-    理论: 通航→油价↓→饲料成本↓→养殖利润↑
-    实际: 养殖跌15.7%
-    发现: 传导链3层断裂→间接传导效率极低
-    含义: 霍尔木兹对养殖的+9pp强度严重过高，应降至+2pp或直接标记虚P
-  AI/科技传导:
-    理论: AI基建利好芯片
-    实际: 芯片涨16.4%，但恒科跌5%
-    发现: 同是科技，芯片（硬科技/存储）vs恒科（互联网/估值）分化
-    含义: "科技"不是单一品类，需拆分为"硬科技"和"互联网"分别建模
-  关税传导:
-    理论: 301+欧盟关税→资源品需求↓
-    实际: 有色跌10.7%，稀金变化不大
-    发现: 有色（铜铝）对关税敏感，稀金（稀土）有反制溢价缓冲
-    含义: 同为资源，传导效率不同，需分品种建模
-</t>
-        </is>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" s="274" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-【六】操作建议（基于P值×赔率正期望）</t>
-        </is>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" s="274">
-        <f>===============================================================================</f>
-        <v/>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" s="274" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-  持仓              P值   赔率    正期望  持有盈亏  建议
-  ─────────────────────────────────────────────────────────
-  南方电池主题ETF联接A  65%  2.0:1   1.30  +6.01%  ✅ 持有（两条腿都稳）
-  汇添富芯片ETF联接A   48%  1.5:1   0.72  +3.93%  ⚠️ 等回调加仓（P偏低但产业强）
-  天弘恒生科技ETF联接C  27%  0.4:1   0.11  -5.95%  ❌ 不干（P+赔率都低）
-  招商畜牧养殖ETF联接C  55%  1.2:1   0.66 -12.49%  ⚠️ 谨慎持有（P校准后下降，等右侧信号）
-  南方有色金属ETF联接C  39%  1.7:1   0.66  -0.41%  ⏸ 观望（样本少）
-  嘉实稀有金属ETF联接C  40%  1.6:1   0.64  +0.85%  ⏸ 观望（样本少）
-  黄金组4只合计: -2018元 → 避险配置，维持
+  持仓                        P值   赔率    正期望  持有盈亏  建议
+  ─────────────────────────────────────────────────────────────────
+  南方中证电池主题ETF联接A      65%  2.0:1   1.30  +6.01%  ✅ 持有（两条腿都稳）
+  汇添富上证科创板芯片ETF联接A  48%  1.5:1   0.72  +3.93%  ⚠️ 等回调加仓（P偏低但产业强）
+  天弘恒生科技ETF联接C          27%  0.4:1   0.11  -5.95%  ❌ 不干（P+赔率都低）
+  招商中证畜牧养殖ETF联接C      55%  1.2:1   0.66 -12.49%  ⚠️ 谨慎持有（霍尔木兹权重过高已校准）
+  南方有色金属ETF联接C          39%  1.7:1   0.66  -0.41%  ⏸ 观望（样本少）
+  嘉实中证稀有金属主题ETF联接C  40%  1.6:1   0.64  +0.85%  ⏸ 观望（样本少）
+  黄金组4只合计: -1918元 → 避险配置，维持
   核心结论:
   1. 只有电池满足"高P+高赔率"→正期望&gt;1→持有
   2. 芯片产业逻辑强但P值偏低→等回调（如-10%）加仓
-  3. 养殖P值从70%校准到55%→正期望下降→不再激进
+  3. 养殖P值从70%校准到55%（霍尔木兹权重下调）→正期望下降
   4. 恒科P+赔率双低→不操作
+  5. 伊娃事实层待外部数据验证（仔猪价格/猪企财报），暂不调整权重
 </t>
         </is>
       </c>
     </row>
+    <row r="118">
+      <c r="A118" s="274" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+【八】机制固化说明</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="274">
+        <f>===============================================================================</f>
+        <v/>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="274" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+  本次固化内容:
+  1. 信源权重校准机制v1.0 → ~/.hermes/external_memory/信源权重校准机制_v1.0.md
+     - 6条铁律：不准只看价格判对错、二维矩阵、Spearman校准、虚P不剔除、拟合不好必深度分析、持续过程
+  2. 贝叶斯P值赔率校准系统v1.0 → ~/.hermes/external_memory/贝叶斯P值赔率校准系统_v1.0.md
+  3. 持仓盈亏联动分析技能 → ~/.hermes/skills/investment/portfolio-pnl-linkage/
+  4. 监控统筹框架§4.2.3 → 写看板P值后自动执行联动分析
+  下次执行流程:
+  新事件 → 深度核查（事实+传导）→ 分配PP → 查信源权重 → 算P值 → 算赔率 → 写Excel → 发邮件
+  新价格 → 验证未验证事件 → 重算Spearman → 更新权重 → 重算P值
+</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="143">
+  <mergeCells count="119">
     <mergeCell ref="A115:Z115"/>
     <mergeCell ref="A93:Z93"/>
     <mergeCell ref="A102:Z102"/>
@@ -7037,7 +6876,6 @@
     <mergeCell ref="A83:Z83"/>
     <mergeCell ref="A92:Z92"/>
     <mergeCell ref="A49:Z49"/>
-    <mergeCell ref="A138:Z138"/>
     <mergeCell ref="A36:Z36"/>
     <mergeCell ref="A119:Z119"/>
     <mergeCell ref="A1:Z1"/>
@@ -7046,7 +6884,6 @@
     <mergeCell ref="A78:Z78"/>
     <mergeCell ref="A65:Z65"/>
     <mergeCell ref="A75:Z75"/>
-    <mergeCell ref="A133:Z133"/>
     <mergeCell ref="A80:Z80"/>
     <mergeCell ref="A120:Z120"/>
     <mergeCell ref="A3:Z3"/>
@@ -7067,15 +6904,11 @@
     <mergeCell ref="A58:Z58"/>
     <mergeCell ref="A40:Z40"/>
     <mergeCell ref="A67:Z67"/>
-    <mergeCell ref="A130:Z130"/>
     <mergeCell ref="A24:Z24"/>
     <mergeCell ref="A73:Z73"/>
     <mergeCell ref="A82:Z82"/>
     <mergeCell ref="A60:Z60"/>
-    <mergeCell ref="A123:Z123"/>
-    <mergeCell ref="A132:Z132"/>
     <mergeCell ref="A110:Z110"/>
-    <mergeCell ref="A124:Z124"/>
     <mergeCell ref="A6:Z6"/>
     <mergeCell ref="A16:Z16"/>
     <mergeCell ref="A25:Z25"/>
@@ -7087,21 +6920,13 @@
     <mergeCell ref="A50:Z50"/>
     <mergeCell ref="A86:Z86"/>
     <mergeCell ref="A47:Z47"/>
-    <mergeCell ref="A141:Z141"/>
-    <mergeCell ref="A135:Z135"/>
-    <mergeCell ref="A144:Z144"/>
-    <mergeCell ref="A122:Z122"/>
     <mergeCell ref="A20:Z20"/>
-    <mergeCell ref="A125:Z125"/>
     <mergeCell ref="A72:Z72"/>
     <mergeCell ref="A29:Z29"/>
-    <mergeCell ref="A134:Z134"/>
     <mergeCell ref="A81:Z81"/>
     <mergeCell ref="A112:Z112"/>
-    <mergeCell ref="A121:Z121"/>
     <mergeCell ref="A13:Z13"/>
     <mergeCell ref="A44:Z44"/>
-    <mergeCell ref="A127:Z127"/>
     <mergeCell ref="A31:Z31"/>
     <mergeCell ref="A114:Z114"/>
     <mergeCell ref="A59:Z59"/>
@@ -7127,8 +6952,6 @@
     <mergeCell ref="A85:Z85"/>
     <mergeCell ref="A42:Z42"/>
     <mergeCell ref="A17:Z17"/>
-    <mergeCell ref="A126:Z126"/>
-    <mergeCell ref="A140:Z140"/>
     <mergeCell ref="A22:Z22"/>
     <mergeCell ref="A53:Z53"/>
     <mergeCell ref="A35:Z35"/>
@@ -7141,34 +6964,26 @@
     <mergeCell ref="A117:Z117"/>
     <mergeCell ref="A111:Z111"/>
     <mergeCell ref="A9:Z9"/>
-    <mergeCell ref="A143:Z143"/>
     <mergeCell ref="A39:Z39"/>
     <mergeCell ref="A48:Z48"/>
     <mergeCell ref="A30:Z30"/>
-    <mergeCell ref="A142:Z142"/>
     <mergeCell ref="A11:Z11"/>
     <mergeCell ref="A45:Z45"/>
     <mergeCell ref="A103:Z103"/>
     <mergeCell ref="A79:Z79"/>
     <mergeCell ref="A87:Z87"/>
-    <mergeCell ref="A128:Z128"/>
-    <mergeCell ref="A137:Z137"/>
     <mergeCell ref="A37:Z37"/>
     <mergeCell ref="A46:Z46"/>
     <mergeCell ref="A89:Z89"/>
-    <mergeCell ref="A136:Z136"/>
     <mergeCell ref="A21:Z21"/>
     <mergeCell ref="A105:Z105"/>
     <mergeCell ref="A26:Z26"/>
     <mergeCell ref="A57:Z57"/>
-    <mergeCell ref="A139:Z139"/>
     <mergeCell ref="A71:Z71"/>
-    <mergeCell ref="A129:Z129"/>
     <mergeCell ref="A23:Z23"/>
     <mergeCell ref="A116:Z116"/>
     <mergeCell ref="A8:Z8"/>
     <mergeCell ref="A91:Z91"/>
-    <mergeCell ref="A131:Z131"/>
     <mergeCell ref="A100:Z100"/>
     <mergeCell ref="A52:Z52"/>
     <mergeCell ref="A63:Z63"/>

--- a/持仓贝叶斯跟踪.xlsx
+++ b/持仓贝叶斯跟踪.xlsx
@@ -27,7 +27,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="52">
+  <fonts count="53">
     <font>
       <name val="Calibri"/>
       <charset val="1"/>
@@ -380,8 +380,12 @@
       <b val="1"/>
       <color rgb="00C00000"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FF6600"/>
+    </font>
   </fonts>
-  <fills count="27">
+  <fills count="28">
     <fill>
       <patternFill/>
     </fill>
@@ -538,6 +542,12 @@
         <bgColor rgb="004472C4"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFD700"/>
+        <bgColor rgb="00FFD700"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="7">
     <border>
@@ -599,7 +609,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="276">
+  <cellXfs count="277">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -1404,6 +1414,9 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="51" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="52" fillId="27" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2011,11 +2024,15 @@
     </comment>
     <comment ref="A14" authorId="0" shapeId="0">
       <text>
-        <t>【来源】宋鸿兵抖音6/3 18:35视频《美伊谈判：决胜负要看经济战》
-【逻辑链】美伊军事战陷入僵局→双方都不愿大打→谈判久拖不决→石油库存逼近红线→油价/通胀飙升→美债收益率走高→金融市场的急性病vs伊朗实体经济的慢性病→时间站在伊朗一边→经济战成为决定性力量
-【当前状态】升级：从军事冲突升级为经济战维度
-【对持仓影响】电池+2pp(能源转型)、恒科-1pp(利率压制)、有色/原油维持高P值
-【核心判断】6-8月是经济战转折点，油价可能继续上行</t>
+        <t>【来源】孙正义+黄仁勋 2026-06-06同步发声
+【逻辑链】孙正义抛出3个预言：①AI规模=互联网10-50倍 ②当前泡沫只是杯壁一点点 ③下一个万亿机会是机器人。黄仁勋罕见同步发声确认AI长期叙事。
+两人同时发声→不是巧合→产业顶级大佬达成共识→AI叙事长期有效
+→ 即使有回调/泡沫，暴跌只是过程不是结局（参考2000互联网泡沫后续暴涨）
+→ 对芯片/存储/AI基建构成长期虚P支撑
+【当前状态】新叙事，虚P强度拉满
+【对持仓影响】🟢芯片(020628)强烈利好 / 🟢电池(018926)中性(新能源vsAI) / 🟡恒科(012349)间接利好
+【操作建议】虚P不参与事实准确率评估但参与P值计算。+8pp虚P拉高芯片长期预期，但短期仍看利率/估值压制。保持观望等回调加仓。
+【P值调整依据】+5pp(孙正义3预言权重高，万亿级叙事) +3pp(黄仁勋同步确认，双人互锁)</t>
       </text>
     </comment>
     <comment ref="B14" authorId="0" shapeId="0">
@@ -6923,8 +6940,8 @@
     <mergeCell ref="A20:Z20"/>
     <mergeCell ref="A72:Z72"/>
     <mergeCell ref="A29:Z29"/>
+    <mergeCell ref="A112:Z112"/>
     <mergeCell ref="A81:Z81"/>
-    <mergeCell ref="A112:Z112"/>
     <mergeCell ref="A13:Z13"/>
     <mergeCell ref="A44:Z44"/>
     <mergeCell ref="A31:Z31"/>
@@ -7087,10 +7104,10 @@
     <row r="3" ht="72.75" customHeight="1" s="139">
       <c r="A3" s="195" t="inlineStr">
         <is>
-          <t>P:41%
-虚P+2pp
+          <t>P:49%
+虚P+10pp
 利率折价-6pp
-有效P:35%
+有效P:43%
 拟合❌0分
 下行:25% 确定性:30% 溢价:50%
 盈亏比:1.2:1
@@ -7737,7 +7754,15 @@
       </c>
     </row>
     <row r="14" ht="13.5" customHeight="1" s="139">
-      <c r="A14" s="138" t="n"/>
+      <c r="A14" s="276" t="inlineStr">
+        <is>
+          <t>2026-06-06
++8pp
+【虚P+5pp】孙正义：AI规模=互联网10-50倍，下一个万亿风口是机器人
+【虚P+3pp】黄仁勋罕见同步发声，确认AI长期叙事
+→ 两人罕见同步，虚P强度拉满</t>
+        </is>
+      </c>
       <c r="B14" s="138" t="n"/>
       <c r="C14" s="138" t="n"/>
       <c r="D14" s="138" t="n"/>

--- a/持仓贝叶斯跟踪.xlsx
+++ b/持仓贝叶斯跟踪.xlsx
@@ -2453,19 +2453,34 @@
       </c>
     </row>
     <row r="9" ht="63.75" customHeight="1" s="139">
+      <c r="A9" s="138" t="inlineStr">
+        <is>
+          <t>2026-06-06 09:00</t>
+        </is>
+      </c>
+      <c r="B9" s="138" t="inlineStr">
+        <is>
+          <t>养殖ETF</t>
+        </is>
+      </c>
+      <c r="C9" s="138" t="inlineStr">
+        <is>
+          <t>52%→53%</t>
+        </is>
+      </c>
       <c r="D9" s="147" t="inlineStr">
         <is>
-          <t>2026-05-19 古都闲云：4月新增贷款出现历史罕见的负值</t>
+          <t>+1pp</t>
         </is>
       </c>
       <c r="E9" s="138" t="inlineStr">
         <is>
-          <t>2026-04-07 美军空袭伊朗哈尔克岛，以色列同步打击桥梁铁路</t>
+          <t>淘汰母猪加快+融资恶化→底部确认</t>
         </is>
       </c>
       <c r="F9" s="147" t="inlineStr">
         <is>
-          <t>2026-05-27 AI处理日志 →黄金+2pp</t>
+          <t>持仓不动</t>
         </is>
       </c>
       <c r="G9" s="147" t="inlineStr">
@@ -2475,31 +2490,66 @@
       </c>
     </row>
     <row r="10" ht="48" customHeight="1" s="139">
+      <c r="A10" s="138" t="inlineStr">
+        <is>
+          <t>2026-06-06 09:00</t>
+        </is>
+      </c>
+      <c r="B10" s="138" t="inlineStr">
+        <is>
+          <t>芯片/恒科</t>
+        </is>
+      </c>
+      <c r="C10" s="138" t="inlineStr">
+        <is>
+          <t>57%/48%</t>
+        </is>
+      </c>
       <c r="D10" s="147" t="inlineStr">
         <is>
-          <t>2026-05-19 古都闲云：中国4月社会消费品零售总额同比+0.2%</t>
+          <t>0pp</t>
         </is>
       </c>
       <c r="E10" s="138" t="inlineStr">
         <is>
-          <t>2026-03-23 特朗普威胁摧毁伊朗能源设施 + 新加坡总理：比70年代更严重</t>
+          <t>AI叙事强化vs估值过高信号抵消</t>
         </is>
       </c>
       <c r="F10" s="147" t="inlineStr">
         <is>
-          <t>2026-05-27 蒋宇飞（抖音）→ 芯片0pp</t>
+          <t>持仓不动</t>
         </is>
       </c>
     </row>
     <row r="11" ht="48" customHeight="1" s="139">
+      <c r="A11" s="138" t="inlineStr">
+        <is>
+          <t>2026-06-06 09:00</t>
+        </is>
+      </c>
+      <c r="B11" s="138" t="inlineStr">
+        <is>
+          <t>银行</t>
+        </is>
+      </c>
+      <c r="C11" s="138" t="inlineStr">
+        <is>
+          <t>54%</t>
+        </is>
+      </c>
+      <c r="D11" s="138" t="inlineStr">
+        <is>
+          <t>0pp</t>
+        </is>
+      </c>
       <c r="E11" s="138" t="inlineStr">
         <is>
-          <t>2026-03 最坏情境：布伦特$111/桶(2027Q4)，封锁2月+供应仅200万桶/日</t>
+          <t>非农超预期=宏观冲击但已定价</t>
         </is>
       </c>
       <c r="F11" s="147" t="inlineStr">
         <is>
-          <t>2026-05-27 付鹏（抖音）→ 芯片0pp</t>
+          <t>持仓不动</t>
         </is>
       </c>
     </row>
@@ -5094,22 +5144,46 @@
       </c>
     </row>
     <row r="155" ht="15" customHeight="1" s="139">
-      <c r="A155" s="190" t="n"/>
+      <c r="A155" s="190" t="inlineStr">
+        <is>
+          <t>--- 6/6 监控小结 ---</t>
+        </is>
+      </c>
     </row>
     <row r="156" ht="15" customHeight="1" s="139">
-      <c r="A156" s="191" t="n"/>
+      <c r="A156" s="191" t="inlineStr">
+        <is>
+          <t>养殖: +1pp → 淘汰母猪加快+融资恶化→底部确认</t>
+        </is>
+      </c>
     </row>
     <row r="157" ht="15" customHeight="1" s="139">
-      <c r="A157" s="191" t="n"/>
+      <c r="A157" s="191" t="inlineStr">
+        <is>
+          <t>芯片: 0pp → AI长期利好vs估值过高抵消</t>
+        </is>
+      </c>
     </row>
     <row r="158" ht="15" customHeight="1" s="139">
-      <c r="A158" s="191" t="n"/>
+      <c r="A158" s="191" t="inlineStr">
+        <is>
+          <t>恒科: 0pp → AI叙事强化非事件</t>
+        </is>
+      </c>
     </row>
     <row r="159" ht="15" customHeight="1" s="139">
-      <c r="A159" s="191" t="n"/>
+      <c r="A159" s="191" t="inlineStr">
+        <is>
+          <t>银行: 0pp → 非农黑五已部分定价</t>
+        </is>
+      </c>
     </row>
     <row r="160" ht="15" customHeight="1" s="139">
-      <c r="A160" s="191" t="n"/>
+      <c r="A160" s="191" t="inlineStr">
+        <is>
+          <t>结论: 持仓不动。养殖左侧继续等待。</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="21">
@@ -7015,7 +7089,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:L192"/>
+  <dimension ref="A1:L194"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="10.4921875" defaultRowHeight="12.75" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="18" customWidth="1" style="138" min="1" max="12"/>
@@ -7811,19 +7885,78 @@
       </c>
     </row>
     <row r="16" ht="13.5" customHeight="1" s="139">
-      <c r="B16" s="196" t="n"/>
-    </row>
-    <row r="17" ht="13.5" customHeight="1" s="139"/>
+      <c r="A16" s="138" t="n"/>
+      <c r="B16" s="196" t="inlineStr"/>
+      <c r="C16" s="138" t="inlineStr"/>
+      <c r="D16" s="138" t="inlineStr"/>
+      <c r="E16" s="138" t="inlineStr">
+        <is>
+          <t>生猪贸易:淘汰母猪价格加快=底部信号(+1pp)</t>
+        </is>
+      </c>
+      <c r="F16" s="138" t="inlineStr"/>
+      <c r="G16" s="138" t="inlineStr"/>
+      <c r="H16" s="138" t="inlineStr"/>
+    </row>
+    <row r="17" ht="13.5" customHeight="1" s="139">
+      <c r="A17" s="138" t="n"/>
+      <c r="B17" s="138" t="inlineStr"/>
+      <c r="C17" s="138" t="inlineStr"/>
+      <c r="D17" s="138" t="inlineStr"/>
+      <c r="E17" s="138" t="inlineStr">
+        <is>
+          <t>伊娃:中小养户资金压力=融资环境恶化</t>
+        </is>
+      </c>
+      <c r="F17" s="138" t="inlineStr"/>
+      <c r="G17" s="138" t="inlineStr"/>
+      <c r="H17" s="138" t="inlineStr"/>
+    </row>
     <row r="18" ht="13.5" customHeight="1" s="139">
       <c r="A18" s="196" t="n"/>
+      <c r="B18" s="138" t="inlineStr"/>
+      <c r="C18" s="138" t="inlineStr"/>
+      <c r="D18" s="138" t="inlineStr">
+        <is>
+          <t>拿幸:Anthropic AI造AI预警+谷歌Gemma4(0pp叙事)</t>
+        </is>
+      </c>
+      <c r="E18" s="138" t="inlineStr"/>
+      <c r="F18" s="138" t="inlineStr"/>
+      <c r="G18" s="138" t="inlineStr"/>
+      <c r="H18" s="138" t="inlineStr"/>
     </row>
     <row r="19" ht="13.5" customHeight="1" s="139">
       <c r="A19" s="196" t="n"/>
-      <c r="B19" s="196" t="n"/>
+      <c r="B19" s="196" t="inlineStr">
+        <is>
+          <t>环中星鉴:博通AI收入+200%股价-15%(0pp)</t>
+        </is>
+      </c>
+      <c r="C19" s="138" t="inlineStr"/>
+      <c r="D19" s="138" t="inlineStr"/>
+      <c r="E19" s="138" t="inlineStr"/>
+      <c r="F19" s="138" t="inlineStr"/>
+      <c r="G19" s="138" t="inlineStr"/>
+      <c r="H19" s="138" t="inlineStr"/>
     </row>
     <row r="20" ht="13.5" customHeight="1" s="139">
-      <c r="A20" s="196" t="n"/>
-      <c r="B20" s="196" t="n"/>
+      <c r="A20" s="196" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="B20" s="196" t="inlineStr"/>
+      <c r="C20" s="138" t="inlineStr"/>
+      <c r="D20" s="138" t="inlineStr"/>
+      <c r="E20" s="138" t="inlineStr"/>
+      <c r="F20" s="138" t="inlineStr"/>
+      <c r="G20" s="138" t="inlineStr"/>
+      <c r="H20" s="138" t="inlineStr">
+        <is>
+          <t>闻号:非农超预期14万/黑五大跌(0pp)</t>
+        </is>
+      </c>
     </row>
     <row r="21" ht="13.5" customHeight="1" s="139">
       <c r="A21" s="196" t="n"/>
@@ -10943,6 +11076,44 @@
           <t>2026-06-05
 -1pp
 【-1pp】闻号：央行逆回购归零+DR007上穿政策利率→最宽松阶段过去，不利净息差</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" s="138" t="inlineStr">
+        <is>
+          <t>📊 6/6 监控更新（抖音+知乎，B站CDP限流持续）</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" s="138" t="inlineStr">
+        <is>
+          <t>2026-06-06
+0pp
+【0pp】博通AI收入+200%股价-15%=估值过高vsAI长期利好抵消</t>
+        </is>
+      </c>
+      <c r="C194" s="138" t="inlineStr">
+        <is>
+          <t>2026-06-06
+0pp
+【0pp】Anthropic预警+Gemma4=AI叙事强化非事件</t>
+        </is>
+      </c>
+      <c r="D194" s="138" t="inlineStr">
+        <is>
+          <t>2026-06-06
++1pp
+【+1pp】生猪贸易：淘汰母猪价格加快=底部信号
+【确认】伊娃：中小养户资金压力=融资恶化</t>
+        </is>
+      </c>
+      <c r="G194" s="138" t="inlineStr">
+        <is>
+          <t>2026-06-06
+0pp
+【0pp】非农超预期/黑五=宏观冲击已部分定价</t>
         </is>
       </c>
     </row>

--- a/持仓贝叶斯跟踪.xlsx
+++ b/持仓贝叶斯跟踪.xlsx
@@ -385,7 +385,7 @@
       <color rgb="00FF6600"/>
     </font>
   </fonts>
-  <fills count="28">
+  <fills count="30">
     <fill>
       <patternFill/>
     </fill>
@@ -548,6 +548,18 @@
         <bgColor rgb="00FFD700"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C6EFCE"/>
+        <bgColor rgb="00C6EFCE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFC7CE"/>
+        <bgColor rgb="00FFC7CE"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="7">
     <border>
@@ -609,7 +621,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="277">
+  <cellXfs count="280">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -1416,6 +1428,15 @@
     <xf numFmtId="0" fontId="51" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="52" fillId="27" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="28" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="29" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -7098,7 +7119,7 @@
     <row r="1" ht="13.5" customHeight="1" s="139">
       <c r="A1" s="192" t="inlineStr">
         <is>
-          <t>📈 持仓贝叶斯完整记录 (8只横排)</t>
+          <t>📈 持仓贝叶斯完整记录 (α/β拆分版 2026-06-06)</t>
         </is>
       </c>
       <c r="J1" s="193" t="inlineStr">
@@ -7176,92 +7197,90 @@
       </c>
     </row>
     <row r="3" ht="72.75" customHeight="1" s="139">
-      <c r="A3" s="195" t="inlineStr">
-        <is>
-          <t>P:49%
-虚P+10pp
-利率折价-6pp
-有效P:43%
-拟合❌0分
+      <c r="A3" s="277" t="inlineStr">
+        <is>
+          <t>P(α):51%
+虚P+14pp
+β折价-11pp
+有效P:40%
 下行:25% 确定性:30% 溢价:50%
 盈亏比:1.2:1
-决策:观望
-【6/4三源联动】知乎0pp 达利欧-2pp 李大霄-1pp = 净-3pp</t>
-        </is>
-      </c>
-      <c r="B3" s="195" t="inlineStr">
-        <is>
-          <t>P:65%
+P×R:0.48
+决策:观望</t>
+        </is>
+      </c>
+      <c r="B3" s="278" t="inlineStr">
+        <is>
+          <t>P(α):67%
 虚P无
-利率折价-6pp
-有效P:59%
-拟合✅97分
+β折价+0pp
+有效P:67%
 下行:20% 确定性:25% 溢价:40%
-盈亏比:2.0:1
+盈亏比:2.2:1
+P×R:1.47
 决策:持有</t>
         </is>
       </c>
-      <c r="C3" s="195" t="inlineStr">
-        <is>
-          <t>P:27%
+      <c r="C3" s="279" t="inlineStr">
+        <is>
+          <t>P(α):41%
 虚P无
-利率折价-6pp
-有效P:21%
-拟合✅75分
+β折价-8pp
+有效P:33%
 下行:30% 确定性:15% 溢价:30%
-盈亏比:0.4:1
-决策:不干
-【6/4三源联动】知乎+1pp 达利欧-1pp 李大霄-2pp = 净-2pp</t>
-        </is>
-      </c>
-      <c r="D3" s="195" t="inlineStr">
-        <is>
-          <t>P:70%
+盈亏比:0.5:1
+P×R:0.17
+决策:不干</t>
+        </is>
+      </c>
+      <c r="D3" s="278" t="inlineStr">
+        <is>
+          <t>P(α):52%
 虚P+4pp
-利率折价0pp
-有效P:70%
-拟合✅95分
+β折价+4pp
+有效P:56%
 下行:20% 确定性:35% 溢价:20%
-盈亏比:2.0:1
+盈亏比:1.8:1
+P×R:1.01
 决策:持有</t>
         </is>
       </c>
-      <c r="E3" s="195" t="inlineStr">
-        <is>
-          <t>P:39%
+      <c r="E3" s="277" t="inlineStr">
+        <is>
+          <t>P(α):39%
 虚P无
-利率折价-4pp
-有效P:35%
-拟合⚠️样本少
+β折价+0pp
+有效P:39%
 下行:15% 确定性:20% 溢价:30%
-盈亏比:1.7:1
+盈亏比:1.3:1
+P×R:0.51
 决策:观望</t>
         </is>
       </c>
-      <c r="F3" s="195" t="inlineStr">
-        <is>
-          <t>P:40%
+      <c r="F3" s="277" t="inlineStr">
+        <is>
+          <t>P(α):42%
 虚P无
-利率折价-4pp
-有效P:36%
-拟合⚠️样本少
+β折价-1pp
+有效P:41%
 下行:20% 确定性:25% 溢价:35%
-盈亏比:1.6:1
+盈亏比:1.2:1
+P×R:0.49
 决策:观望</t>
         </is>
       </c>
-      <c r="G3" s="195" t="inlineStr">
+      <c r="G3" s="277" t="inlineStr">
         <is>
           <t>成本¥0
 净值1.6291
-P:47%
+P(α):50%
 虚P-2pp
-利率折价0pp
-有效P:47%
-拟合👍53分
+β折价-6pp
+有效P:44%
 下行:10% 确定性:10% 溢价:5%
-盈亏比:1.5:1
-决策:监控</t>
+盈亏比:1.0:1
+P×R:0.44
+决策:观望</t>
         </is>
       </c>
       <c r="H3" s="195" t="inlineStr">

--- a/持仓贝叶斯跟踪.xlsx
+++ b/持仓贝叶斯跟踪.xlsx
@@ -27,7 +27,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="53">
+  <fonts count="57">
     <font>
       <name val="Calibri"/>
       <charset val="1"/>
@@ -384,8 +384,24 @@
       <b val="1"/>
       <color rgb="00FF6600"/>
     </font>
+    <font>
+      <i val="1"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <sz val="9"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <sz val="11"/>
+    </font>
   </fonts>
-  <fills count="30">
+  <fills count="31">
     <fill>
       <patternFill/>
     </fill>
@@ -560,8 +576,14 @@
         <bgColor rgb="00FFC7CE"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFEB9C"/>
+        <bgColor rgb="00FFEB9C"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="7">
+  <borders count="8">
     <border>
       <left/>
       <right/>
@@ -610,6 +632,7 @@
       <top style="thin"/>
       <bottom style="thin"/>
     </border>
+    <border/>
   </borders>
   <cellStyleXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1">
@@ -621,7 +644,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="280">
+  <cellXfs count="314">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -1437,6 +1460,98 @@
     </xf>
     <xf numFmtId="0" fontId="22" fillId="29" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="49" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="53" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="55" fillId="26" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="30" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="30" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="28" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="28" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="49" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="53" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="29" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="29" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -11209,7 +11324,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:N54"/>
+  <dimension ref="A1:N59"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6171875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="6" customWidth="1" style="138" min="1" max="1"/>
@@ -11272,1234 +11387,1406 @@
       <c r="N3" s="238" t="n"/>
     </row>
     <row r="5" ht="16.5" customHeight="1" s="139">
-      <c r="A5" s="239" t="inlineStr">
-        <is>
-          <t>审核日期：2026-06-04 | 下次预计审核：2026-06-11（每周日）| 方法：吸引力Score = P*R - alpha*w*(1-P)</t>
-        </is>
-      </c>
-      <c r="M5" s="240" t="inlineStr">
-        <is>
-          <t>折后仓位%</t>
-        </is>
-      </c>
-      <c r="N5" s="240" t="inlineStr">
-        <is>
-          <t>现金锁定状态</t>
-        </is>
-      </c>
+      <c r="A5" s="294" t="inlineStr">
+        <is>
+          <t>机会成本排序表 EV阈值分级 v3 (2026-06-06)</t>
+        </is>
+      </c>
+      <c r="L5" s="295" t="n"/>
+      <c r="M5" s="296" t="n"/>
+      <c r="N5" s="296" t="n"/>
     </row>
     <row r="6" ht="48" customHeight="1" s="139">
-      <c r="A6" s="239" t="inlineStr">
-        <is>
-          <t>双门槛过滤：P&gt;=60% + 盈亏比&gt;=2:1 通过 按Score排序分配现金 | alpha=1.0（集中度厌恶系数）</t>
-        </is>
-      </c>
-      <c r="M6" s="164" t="inlineStr">
-        <is>
-          <t>13%</t>
-        </is>
-      </c>
-      <c r="N6" s="147" t="inlineStr">
-        <is>
-          <t>锁定65%现金 等解锁</t>
-        </is>
-      </c>
+      <c r="A6" s="297" t="inlineStr">
+        <is>
+          <t>审核: 2026-06-06 | R=(确定性+溢价x梯度打折)/下行 | 梯度打折&lt;60%=(有效P-30)/60</t>
+        </is>
+      </c>
+      <c r="L6" s="295" t="n"/>
+      <c r="M6" s="298" t="n"/>
+      <c r="N6" s="299" t="n"/>
     </row>
     <row r="7" ht="32.25" customHeight="1" s="139">
-      <c r="M7" s="164" t="inlineStr">
-        <is>
-          <t>12%</t>
-        </is>
-      </c>
-      <c r="N7" s="147" t="inlineStr">
-        <is>
-          <t>锁定65%现金 等解锁</t>
-        </is>
-      </c>
+      <c r="A7" s="300" t="inlineStr">
+        <is>
+          <t>EV分级: &gt;1.0正期望 | 0.5-1.0弱正期望 | &lt;0.5负期望 | 现金锁定65%</t>
+        </is>
+      </c>
+      <c r="L7" s="295" t="n"/>
+      <c r="M7" s="298" t="n"/>
+      <c r="N7" s="299" t="n"/>
     </row>
     <row r="8" ht="32.25" customHeight="1" s="139">
-      <c r="A8" s="241" t="inlineStr">
+      <c r="A8" s="283" t="inlineStr">
         <is>
           <t>排名</t>
         </is>
       </c>
-      <c r="B8" s="241" t="inlineStr">
+      <c r="B8" s="283" t="inlineStr">
         <is>
           <t>选项</t>
         </is>
       </c>
-      <c r="C8" s="241" t="inlineStr">
+      <c r="C8" s="283" t="inlineStr">
         <is>
           <t>代码</t>
         </is>
       </c>
-      <c r="D8" s="241" t="inlineStr">
+      <c r="D8" s="283" t="inlineStr">
         <is>
           <t>类型</t>
         </is>
       </c>
-      <c r="E8" s="241" t="inlineStr">
-        <is>
-          <t>P值</t>
-        </is>
-      </c>
-      <c r="F8" s="241" t="inlineStr">
+      <c r="E8" s="283" t="inlineStr">
         <is>
           <t>有效P</t>
         </is>
       </c>
-      <c r="G8" s="241" t="inlineStr">
-        <is>
-          <t>盈亏比</t>
-        </is>
-      </c>
-      <c r="H8" s="241" t="inlineStr">
-        <is>
-          <t>P*R</t>
-        </is>
-      </c>
-      <c r="I8" s="241" t="inlineStr">
+      <c r="F8" s="283" t="inlineStr">
+        <is>
+          <t>盈亏比R</t>
+        </is>
+      </c>
+      <c r="G8" s="283" t="inlineStr">
+        <is>
+          <t>EV(PxR)</t>
+        </is>
+      </c>
+      <c r="H8" s="283" t="inlineStr">
         <is>
           <t>仓位w</t>
         </is>
       </c>
-      <c r="J8" s="241" t="inlineStr">
-        <is>
-          <t>吸引力Score</t>
-        </is>
-      </c>
-      <c r="K8" s="241" t="inlineStr">
-        <is>
-          <t>双门槛</t>
-        </is>
-      </c>
-      <c r="L8" s="241" t="inlineStr">
-        <is>
-          <t>建议操作</t>
-        </is>
-      </c>
-      <c r="M8" s="163" t="inlineStr">
+      <c r="I8" s="283" t="inlineStr">
+        <is>
+          <t>Score</t>
+        </is>
+      </c>
+      <c r="J8" s="283" t="inlineStr">
+        <is>
+          <t>EV分级</t>
+        </is>
+      </c>
+      <c r="K8" s="283" t="inlineStr">
+        <is>
+          <t>建议</t>
+        </is>
+      </c>
+      <c r="L8" s="301" t="n"/>
+      <c r="M8" s="298" t="n"/>
+      <c r="N8" s="299" t="n"/>
+    </row>
+    <row r="9" ht="32.25" customHeight="1" s="139">
+      <c r="A9" s="286" t="n">
+        <v>1</v>
+      </c>
+      <c r="B9" s="287" t="inlineStr">
+        <is>
+          <t>养殖008765(008765)</t>
+        </is>
+      </c>
+      <c r="C9" s="287" t="inlineStr">
+        <is>
+          <t>008765</t>
+        </is>
+      </c>
+      <c r="D9" s="287" t="inlineStr">
+        <is>
+          <t>持仓</t>
+        </is>
+      </c>
+      <c r="E9" s="287" t="inlineStr">
+        <is>
+          <t>56%</t>
+        </is>
+      </c>
+      <c r="F9" s="287" t="inlineStr">
+        <is>
+          <t>%.2f:1</t>
+        </is>
+      </c>
+      <c r="G9" s="287" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="H9" s="287" t="inlineStr">
+        <is>
+          <t>5%</t>
+        </is>
+      </c>
+      <c r="I9" s="287" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="J9" s="286" t="inlineStr">
+        <is>
+          <t>正期望</t>
+        </is>
+      </c>
+      <c r="K9" s="287" t="inlineStr">
+        <is>
+          <t>持有+可加仓</t>
+        </is>
+      </c>
+      <c r="L9" s="302" t="n"/>
+      <c r="M9" s="298" t="n"/>
+      <c r="N9" s="299" t="n"/>
+    </row>
+    <row r="10" ht="32.25" customHeight="1" s="139">
+      <c r="A10" s="286" t="n">
+        <v>2</v>
+      </c>
+      <c r="B10" s="287" t="inlineStr">
+        <is>
+          <t>电池009759(009759)</t>
+        </is>
+      </c>
+      <c r="C10" s="287" t="inlineStr">
+        <is>
+          <t>009759</t>
+        </is>
+      </c>
+      <c r="D10" s="287" t="inlineStr">
+        <is>
+          <t>持仓</t>
+        </is>
+      </c>
+      <c r="E10" s="287" t="inlineStr">
+        <is>
+          <t>67%</t>
+        </is>
+      </c>
+      <c r="F10" s="287" t="inlineStr">
+        <is>
+          <t>%.2f:1</t>
+        </is>
+      </c>
+      <c r="G10" s="287" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="H10" s="287" t="inlineStr">
+        <is>
+          <t>15%</t>
+        </is>
+      </c>
+      <c r="I10" s="287" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="J10" s="286" t="inlineStr">
+        <is>
+          <t>正期望</t>
+        </is>
+      </c>
+      <c r="K10" s="287" t="inlineStr">
+        <is>
+          <t>持有+可加仓</t>
+        </is>
+      </c>
+      <c r="L10" s="302" t="n"/>
+      <c r="M10" s="298" t="n"/>
+      <c r="N10" s="299" t="n"/>
+    </row>
+    <row r="11" ht="32.25" customHeight="1" s="139">
+      <c r="A11" s="286" t="n">
+        <v>3</v>
+      </c>
+      <c r="B11" s="287" t="inlineStr">
+        <is>
+          <t>核电赛道(-)</t>
+        </is>
+      </c>
+      <c r="C11" s="287" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D11" s="287" t="inlineStr">
+        <is>
+          <t>待重</t>
+        </is>
+      </c>
+      <c r="E11" s="287" t="inlineStr">
+        <is>
+          <t>50%</t>
+        </is>
+      </c>
+      <c r="F11" s="287" t="inlineStr">
+        <is>
+          <t>%.2f:1</t>
+        </is>
+      </c>
+      <c r="G11" s="287" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="H11" s="287" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="N8" s="242" t="inlineStr">
-        <is>
-          <t>已持仓不动</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="32.25" customHeight="1" s="139">
-      <c r="A9" s="243" t="n">
-        <v>1</v>
-      </c>
-      <c r="B9" s="243" t="inlineStr">
-        <is>
-          <t>长电科技</t>
-        </is>
-      </c>
-      <c r="C9" s="243" t="inlineStr">
-        <is>
-          <t>600584</t>
-        </is>
-      </c>
-      <c r="D9" s="243" t="inlineStr">
-        <is>
-          <t>待重仓-堆叠</t>
-        </is>
-      </c>
-      <c r="E9" s="243" t="inlineStr">
-        <is>
-          <t>75%</t>
-        </is>
-      </c>
-      <c r="F9" s="243" t="inlineStr">
-        <is>
-          <t>69%</t>
-        </is>
-      </c>
-      <c r="G9" s="243" t="inlineStr">
-        <is>
-          <t>4.5:1</t>
-        </is>
-      </c>
-      <c r="H9" s="243" t="inlineStr">
-        <is>
-          <t>3.375</t>
-        </is>
-      </c>
-      <c r="I9" s="243" t="inlineStr">
+      <c r="I11" s="287" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="J11" s="286" t="inlineStr">
+        <is>
+          <t>正期望</t>
+        </is>
+      </c>
+      <c r="K11" s="287" t="inlineStr">
+        <is>
+          <t>重点研究+准备建仓</t>
+        </is>
+      </c>
+      <c r="L11" s="302" t="n"/>
+      <c r="M11" s="298" t="n"/>
+      <c r="N11" s="299" t="n"/>
+    </row>
+    <row r="12" ht="32.25" customHeight="1" s="139">
+      <c r="A12" s="286" t="n">
+        <v>4</v>
+      </c>
+      <c r="B12" s="287" t="inlineStr">
+        <is>
+          <t>存储赛道(-)</t>
+        </is>
+      </c>
+      <c r="C12" s="287" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D12" s="287" t="inlineStr">
+        <is>
+          <t>待重</t>
+        </is>
+      </c>
+      <c r="E12" s="287" t="inlineStr">
+        <is>
+          <t>51%</t>
+        </is>
+      </c>
+      <c r="F12" s="287" t="inlineStr">
+        <is>
+          <t>%.2f:1</t>
+        </is>
+      </c>
+      <c r="G12" s="287" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="H12" s="287" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="J9" s="243" t="inlineStr">
-        <is>
-          <t>3.3750</t>
-        </is>
-      </c>
-      <c r="K9" s="243" t="inlineStr">
-        <is>
-          <t>通过</t>
-        </is>
-      </c>
-      <c r="L9" s="243" t="inlineStr">
-        <is>
-          <t>重点研究</t>
-        </is>
-      </c>
-      <c r="M9" s="163" t="inlineStr">
+      <c r="I12" s="287" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="J12" s="286" t="inlineStr">
+        <is>
+          <t>正期望</t>
+        </is>
+      </c>
+      <c r="K12" s="287" t="inlineStr">
+        <is>
+          <t>重点研究+准备建仓</t>
+        </is>
+      </c>
+      <c r="L12" s="302" t="n"/>
+      <c r="M12" s="298" t="n"/>
+      <c r="N12" s="299" t="n"/>
+    </row>
+    <row r="13" ht="32.25" customHeight="1" s="139">
+      <c r="A13" s="284" t="n">
+        <v>5</v>
+      </c>
+      <c r="B13" s="285" t="inlineStr">
+        <is>
+          <t>原油162411(162411)</t>
+        </is>
+      </c>
+      <c r="C13" s="285" t="inlineStr">
+        <is>
+          <t>162411</t>
+        </is>
+      </c>
+      <c r="D13" s="285" t="inlineStr">
+        <is>
+          <t>待重</t>
+        </is>
+      </c>
+      <c r="E13" s="285" t="inlineStr">
+        <is>
+          <t>60%</t>
+        </is>
+      </c>
+      <c r="F13" s="285" t="inlineStr">
+        <is>
+          <t>%.2f:1</t>
+        </is>
+      </c>
+      <c r="G13" s="285" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="H13" s="285" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="N9" s="244" t="inlineStr">
-        <is>
-          <t>已持仓不动</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="32.25" customHeight="1" s="139">
-      <c r="A10" s="243" t="n">
-        <v>2</v>
-      </c>
-      <c r="B10" s="243" t="inlineStr">
-        <is>
-          <t>通富微电</t>
-        </is>
-      </c>
-      <c r="C10" s="243" t="inlineStr">
-        <is>
-          <t>002156</t>
-        </is>
-      </c>
-      <c r="D10" s="243" t="inlineStr">
-        <is>
-          <t>待重仓-堆叠</t>
-        </is>
-      </c>
-      <c r="E10" s="243" t="inlineStr">
-        <is>
-          <t>75%</t>
-        </is>
-      </c>
-      <c r="F10" s="243" t="inlineStr">
-        <is>
-          <t>69%</t>
-        </is>
-      </c>
-      <c r="G10" s="243" t="inlineStr">
-        <is>
-          <t>4.0:1</t>
-        </is>
-      </c>
-      <c r="H10" s="243" t="inlineStr">
-        <is>
-          <t>3.000</t>
-        </is>
-      </c>
-      <c r="I10" s="243" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="J10" s="243" t="inlineStr">
-        <is>
-          <t>3.0000</t>
-        </is>
-      </c>
-      <c r="K10" s="243" t="inlineStr">
-        <is>
-          <t>通过</t>
-        </is>
-      </c>
-      <c r="L10" s="243" t="inlineStr">
-        <is>
-          <t>重点研究</t>
-        </is>
-      </c>
-      <c r="M10" s="245" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="N10" s="244" t="inlineStr">
-        <is>
-          <t>未通过门槛</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="32.25" customHeight="1" s="139">
-      <c r="A11" s="243" t="n">
-        <v>3</v>
-      </c>
-      <c r="B11" s="243" t="inlineStr">
-        <is>
-          <t>养殖014415</t>
-        </is>
-      </c>
-      <c r="C11" s="243" t="inlineStr">
-        <is>
-          <t>养殖014415</t>
-        </is>
-      </c>
-      <c r="D11" s="243" t="inlineStr">
+      <c r="I13" s="285" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="J13" s="284" t="inlineStr">
+        <is>
+          <t>弱正期望</t>
+        </is>
+      </c>
+      <c r="K13" s="285" t="inlineStr">
+        <is>
+          <t>密切跟踪</t>
+        </is>
+      </c>
+      <c r="L13" s="302" t="n"/>
+      <c r="M13" s="298" t="n"/>
+      <c r="N13" s="299" t="n"/>
+    </row>
+    <row r="14" ht="32.25" customHeight="1" s="139">
+      <c r="A14" s="284" t="n">
+        <v>6</v>
+      </c>
+      <c r="B14" s="285" t="inlineStr">
+        <is>
+          <t>银行001595(001595)</t>
+        </is>
+      </c>
+      <c r="C14" s="285" t="inlineStr">
+        <is>
+          <t>001595</t>
+        </is>
+      </c>
+      <c r="D14" s="285" t="inlineStr">
         <is>
           <t>持仓</t>
         </is>
       </c>
-      <c r="E11" s="243" t="inlineStr">
-        <is>
-          <t>70%</t>
-        </is>
-      </c>
-      <c r="F11" s="243" t="inlineStr">
-        <is>
-          <t>70%</t>
-        </is>
-      </c>
-      <c r="G11" s="243" t="inlineStr">
-        <is>
-          <t>2.0:1</t>
-        </is>
-      </c>
-      <c r="H11" s="243" t="inlineStr">
-        <is>
-          <t>1.400</t>
-        </is>
-      </c>
-      <c r="I11" s="243" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="J11" s="243" t="inlineStr">
-        <is>
-          <t>1.4000</t>
-        </is>
-      </c>
-      <c r="K11" s="243" t="inlineStr">
-        <is>
-          <t>通过</t>
-        </is>
-      </c>
-      <c r="L11" s="243" t="inlineStr">
-        <is>
-          <t>持有</t>
-        </is>
-      </c>
-      <c r="M11" s="163" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="N11" s="244" t="inlineStr">
-        <is>
-          <t>已持仓不动</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="32.25" customHeight="1" s="139">
-      <c r="A12" s="243" t="n">
-        <v>4</v>
-      </c>
-      <c r="B12" s="243" t="inlineStr">
-        <is>
-          <t>电池018926</t>
-        </is>
-      </c>
-      <c r="C12" s="243" t="inlineStr">
-        <is>
-          <t>电池018926</t>
-        </is>
-      </c>
-      <c r="D12" s="243" t="inlineStr">
+      <c r="E14" s="285" t="inlineStr">
+        <is>
+          <t>44%</t>
+        </is>
+      </c>
+      <c r="F14" s="285" t="inlineStr">
+        <is>
+          <t>%.2f:1</t>
+        </is>
+      </c>
+      <c r="G14" s="285" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="H14" s="285" t="inlineStr">
+        <is>
+          <t>2%</t>
+        </is>
+      </c>
+      <c r="I14" s="285" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="J14" s="284" t="inlineStr">
+        <is>
+          <t>弱正期望</t>
+        </is>
+      </c>
+      <c r="K14" s="285" t="inlineStr">
+        <is>
+          <t>密切跟踪</t>
+        </is>
+      </c>
+      <c r="L14" s="302" t="n"/>
+      <c r="M14" s="298" t="n"/>
+      <c r="N14" s="299" t="n"/>
+    </row>
+    <row r="15" ht="32.25" customHeight="1" s="139">
+      <c r="A15" s="284" t="n">
+        <v>7</v>
+      </c>
+      <c r="B15" s="285" t="inlineStr">
+        <is>
+          <t>稀金008907(008907)</t>
+        </is>
+      </c>
+      <c r="C15" s="285" t="inlineStr">
+        <is>
+          <t>008907</t>
+        </is>
+      </c>
+      <c r="D15" s="285" t="inlineStr">
         <is>
           <t>持仓</t>
         </is>
       </c>
-      <c r="E12" s="243" t="inlineStr">
-        <is>
-          <t>65%</t>
-        </is>
-      </c>
-      <c r="F12" s="243" t="inlineStr">
-        <is>
-          <t>59%</t>
-        </is>
-      </c>
-      <c r="G12" s="243" t="inlineStr">
-        <is>
-          <t>2.0:1</t>
-        </is>
-      </c>
-      <c r="H12" s="243" t="inlineStr">
-        <is>
-          <t>1.300</t>
-        </is>
-      </c>
-      <c r="I12" s="243" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="J12" s="243" t="inlineStr">
-        <is>
-          <t>1.3000</t>
-        </is>
-      </c>
-      <c r="K12" s="243" t="inlineStr">
-        <is>
-          <t>通过</t>
-        </is>
-      </c>
-      <c r="L12" s="243" t="inlineStr">
-        <is>
-          <t>持有</t>
-        </is>
-      </c>
-      <c r="M12" s="163" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="N12" s="244" t="inlineStr">
-        <is>
-          <t>已持仓不动</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="32.25" customHeight="1" s="139">
-      <c r="A13" s="191" t="n">
-        <v>5</v>
-      </c>
-      <c r="B13" s="191" t="inlineStr">
-        <is>
-          <t>核电</t>
-        </is>
-      </c>
-      <c r="C13" s="191" t="inlineStr">
+      <c r="E15" s="285" t="inlineStr">
+        <is>
+          <t>41%</t>
+        </is>
+      </c>
+      <c r="F15" s="285" t="inlineStr">
+        <is>
+          <t>%.2f:1</t>
+        </is>
+      </c>
+      <c r="G15" s="285" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="H15" s="285" t="inlineStr">
+        <is>
+          <t>3%</t>
+        </is>
+      </c>
+      <c r="I15" s="285" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="J15" s="284" t="inlineStr">
+        <is>
+          <t>弱正期望</t>
+        </is>
+      </c>
+      <c r="K15" s="285" t="inlineStr">
+        <is>
+          <t>密切跟踪</t>
+        </is>
+      </c>
+      <c r="L15" s="302" t="n"/>
+      <c r="M15" s="298" t="n"/>
+      <c r="N15" s="299" t="n"/>
+    </row>
+    <row r="16" ht="32.25" customHeight="1" s="139">
+      <c r="A16" s="284" t="n">
+        <v>8</v>
+      </c>
+      <c r="B16" s="285" t="inlineStr">
+        <is>
+          <t>有色008826(008826)</t>
+        </is>
+      </c>
+      <c r="C16" s="285" t="inlineStr">
+        <is>
+          <t>008826</t>
+        </is>
+      </c>
+      <c r="D16" s="285" t="inlineStr">
+        <is>
+          <t>持仓</t>
+        </is>
+      </c>
+      <c r="E16" s="285" t="inlineStr">
+        <is>
+          <t>39%</t>
+        </is>
+      </c>
+      <c r="F16" s="285" t="inlineStr">
+        <is>
+          <t>%.2f:1</t>
+        </is>
+      </c>
+      <c r="G16" s="285" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="H16" s="285" t="inlineStr">
+        <is>
+          <t>4%</t>
+        </is>
+      </c>
+      <c r="I16" s="285" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="J16" s="284" t="inlineStr">
+        <is>
+          <t>弱正期望</t>
+        </is>
+      </c>
+      <c r="K16" s="285" t="inlineStr">
+        <is>
+          <t>密切跟踪</t>
+        </is>
+      </c>
+      <c r="L16" s="302" t="n"/>
+      <c r="M16" s="298" t="n"/>
+      <c r="N16" s="299" t="n"/>
+    </row>
+    <row r="17" ht="16.5" customHeight="1" s="139">
+      <c r="A17" s="284" t="n">
+        <v>9</v>
+      </c>
+      <c r="B17" s="285" t="inlineStr">
+        <is>
+          <t>芯片020628(020628)</t>
+        </is>
+      </c>
+      <c r="C17" s="285" t="inlineStr">
+        <is>
+          <t>020628</t>
+        </is>
+      </c>
+      <c r="D17" s="285" t="inlineStr">
+        <is>
+          <t>持仓</t>
+        </is>
+      </c>
+      <c r="E17" s="285" t="inlineStr">
+        <is>
+          <t>40%</t>
+        </is>
+      </c>
+      <c r="F17" s="285" t="inlineStr">
+        <is>
+          <t>%.2f:1</t>
+        </is>
+      </c>
+      <c r="G17" s="285" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="H17" s="285" t="inlineStr">
+        <is>
+          <t>8%</t>
+        </is>
+      </c>
+      <c r="I17" s="285" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="J17" s="284" t="inlineStr">
+        <is>
+          <t>弱正期望</t>
+        </is>
+      </c>
+      <c r="K17" s="285" t="inlineStr">
+        <is>
+          <t>密切跟踪</t>
+        </is>
+      </c>
+      <c r="L17" s="302" t="n"/>
+      <c r="M17" s="302" t="n"/>
+      <c r="N17" s="302" t="n"/>
+    </row>
+    <row r="18" ht="16.5" customHeight="1" s="139">
+      <c r="A18" s="303" t="n">
+        <v>10</v>
+      </c>
+      <c r="B18" s="304" t="inlineStr">
+        <is>
+          <t>AI027048(027048)</t>
+        </is>
+      </c>
+      <c r="C18" s="304" t="inlineStr">
+        <is>
+          <t>027048</t>
+        </is>
+      </c>
+      <c r="D18" s="304" t="inlineStr">
+        <is>
+          <t>持仓</t>
+        </is>
+      </c>
+      <c r="E18" s="304" t="inlineStr">
+        <is>
+          <t>51%</t>
+        </is>
+      </c>
+      <c r="F18" s="304" t="inlineStr">
+        <is>
+          <t>%.2f:1</t>
+        </is>
+      </c>
+      <c r="G18" s="304" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="H18" s="304" t="inlineStr">
+        <is>
+          <t>1%</t>
+        </is>
+      </c>
+      <c r="I18" s="304" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="J18" s="303" t="inlineStr">
+        <is>
+          <t>负期望</t>
+        </is>
+      </c>
+      <c r="K18" s="304" t="inlineStr">
+        <is>
+          <t>不碰</t>
+        </is>
+      </c>
+      <c r="L18" s="302" t="n"/>
+      <c r="M18" s="302" t="n"/>
+      <c r="N18" s="302" t="n"/>
+    </row>
+    <row r="19" ht="32.8" customHeight="1" s="139">
+      <c r="A19" s="303" t="n">
+        <v>11</v>
+      </c>
+      <c r="B19" s="304" t="inlineStr">
+        <is>
+          <t>恒科009854(009854)</t>
+        </is>
+      </c>
+      <c r="C19" s="304" t="inlineStr">
+        <is>
+          <t>009854</t>
+        </is>
+      </c>
+      <c r="D19" s="304" t="inlineStr">
+        <is>
+          <t>持仓</t>
+        </is>
+      </c>
+      <c r="E19" s="304" t="inlineStr">
+        <is>
+          <t>33%</t>
+        </is>
+      </c>
+      <c r="F19" s="304" t="inlineStr">
+        <is>
+          <t>%.2f:1</t>
+        </is>
+      </c>
+      <c r="G19" s="304" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="H19" s="304" t="inlineStr">
+        <is>
+          <t>6%</t>
+        </is>
+      </c>
+      <c r="I19" s="304" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="J19" s="303" t="inlineStr">
+        <is>
+          <t>负期望</t>
+        </is>
+      </c>
+      <c r="K19" s="304" t="inlineStr">
+        <is>
+          <t>不碰</t>
+        </is>
+      </c>
+      <c r="L19" s="302" t="n"/>
+      <c r="M19" s="302" t="n"/>
+      <c r="N19" s="302" t="n"/>
+    </row>
+    <row r="20" ht="15" customHeight="1" s="139">
+      <c r="A20" s="288" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="D13" s="191" t="inlineStr">
-        <is>
-          <t>待重仓-核电</t>
-        </is>
-      </c>
-      <c r="E13" s="191" t="inlineStr">
-        <is>
-          <t>52%</t>
-        </is>
-      </c>
-      <c r="F13" s="191" t="inlineStr">
-        <is>
-          <t>52%</t>
-        </is>
-      </c>
-      <c r="G13" s="191" t="inlineStr">
-        <is>
-          <t>1.5:1</t>
-        </is>
-      </c>
-      <c r="H13" s="191" t="inlineStr">
-        <is>
-          <t>0.780</t>
-        </is>
-      </c>
-      <c r="I13" s="191" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="J13" s="191" t="inlineStr">
-        <is>
-          <t>0.7800</t>
-        </is>
-      </c>
-      <c r="K13" s="246" t="inlineStr">
-        <is>
-          <t>未通过</t>
-        </is>
-      </c>
-      <c r="L13" s="191" t="inlineStr">
-        <is>
-          <t>长期跟踪</t>
-        </is>
-      </c>
-      <c r="M13" s="163" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="N13" s="147" t="inlineStr">
-        <is>
-          <t>已持仓不动</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="32.25" customHeight="1" s="139">
-      <c r="A14" s="191" t="n">
-        <v>6</v>
-      </c>
-      <c r="B14" s="191" t="inlineStr">
-        <is>
-          <t>银行001595</t>
-        </is>
-      </c>
-      <c r="C14" s="191" t="inlineStr">
-        <is>
-          <t>银行001595</t>
-        </is>
-      </c>
-      <c r="D14" s="191" t="inlineStr">
-        <is>
-          <t>持仓</t>
-        </is>
-      </c>
-      <c r="E14" s="191" t="inlineStr">
-        <is>
-          <t>47%</t>
-        </is>
-      </c>
-      <c r="F14" s="191" t="inlineStr">
-        <is>
-          <t>47%</t>
-        </is>
-      </c>
-      <c r="G14" s="191" t="inlineStr">
-        <is>
-          <t>1.5:1</t>
-        </is>
-      </c>
-      <c r="H14" s="191" t="inlineStr">
-        <is>
-          <t>0.705</t>
-        </is>
-      </c>
-      <c r="I14" s="191" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="J14" s="191" t="inlineStr">
-        <is>
-          <t>0.7050</t>
-        </is>
-      </c>
-      <c r="K14" s="246" t="inlineStr">
-        <is>
-          <t>未通过</t>
-        </is>
-      </c>
-      <c r="L14" s="191" t="inlineStr">
-        <is>
-          <t>监控</t>
-        </is>
-      </c>
-      <c r="M14" s="247" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="N14" s="147" t="inlineStr">
-        <is>
-          <t>已降级</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="32.25" customHeight="1" s="139">
-      <c r="A15" s="191" t="n">
-        <v>7</v>
-      </c>
-      <c r="B15" s="191" t="inlineStr">
-        <is>
-          <t>有色004433</t>
-        </is>
-      </c>
-      <c r="C15" s="191" t="inlineStr">
-        <is>
-          <t>有色004433</t>
-        </is>
-      </c>
-      <c r="D15" s="191" t="inlineStr">
-        <is>
-          <t>持仓</t>
-        </is>
-      </c>
-      <c r="E15" s="191" t="inlineStr">
-        <is>
-          <t>39%</t>
-        </is>
-      </c>
-      <c r="F15" s="191" t="inlineStr">
-        <is>
-          <t>35%</t>
-        </is>
-      </c>
-      <c r="G15" s="191" t="inlineStr">
-        <is>
-          <t>1.7:1</t>
-        </is>
-      </c>
-      <c r="H15" s="191" t="inlineStr">
-        <is>
-          <t>0.663</t>
-        </is>
-      </c>
-      <c r="I15" s="191" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="J15" s="191" t="inlineStr">
-        <is>
-          <t>0.6630</t>
-        </is>
-      </c>
-      <c r="K15" s="246" t="inlineStr">
-        <is>
-          <t>未通过</t>
-        </is>
-      </c>
-      <c r="L15" s="191" t="inlineStr">
-        <is>
-          <t>观望</t>
-        </is>
-      </c>
-      <c r="M15" s="163" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="N15" s="147" t="inlineStr">
-        <is>
-          <t>已持仓不动</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="32.25" customHeight="1" s="139">
-      <c r="A16" s="191" t="n">
-        <v>8</v>
-      </c>
-      <c r="B16" s="191" t="inlineStr">
-        <is>
-          <t>稀金014111</t>
-        </is>
-      </c>
-      <c r="C16" s="191" t="inlineStr">
-        <is>
-          <t>稀金014111</t>
-        </is>
-      </c>
-      <c r="D16" s="191" t="inlineStr">
-        <is>
-          <t>持仓</t>
-        </is>
-      </c>
-      <c r="E16" s="191" t="inlineStr">
-        <is>
-          <t>40%</t>
-        </is>
-      </c>
-      <c r="F16" s="191" t="inlineStr">
-        <is>
-          <t>36%</t>
-        </is>
-      </c>
-      <c r="G16" s="191" t="inlineStr">
-        <is>
-          <t>1.6:1</t>
-        </is>
-      </c>
-      <c r="H16" s="191" t="inlineStr">
-        <is>
-          <t>0.640</t>
-        </is>
-      </c>
-      <c r="I16" s="191" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="J16" s="191" t="inlineStr">
-        <is>
-          <t>0.6400</t>
-        </is>
-      </c>
-      <c r="K16" s="246" t="inlineStr">
-        <is>
-          <t>未通过</t>
-        </is>
-      </c>
-      <c r="L16" s="191" t="inlineStr">
-        <is>
-          <t>观望</t>
-        </is>
-      </c>
-      <c r="M16" s="163" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="N16" s="147" t="inlineStr">
-        <is>
-          <t>已持仓不动</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="16.5" customHeight="1" s="139">
-      <c r="A17" s="191" t="n">
-        <v>9</v>
-      </c>
-      <c r="B17" s="191" t="inlineStr">
-        <is>
-          <t>存储赛道</t>
-        </is>
-      </c>
-      <c r="C17" s="191" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D17" s="191" t="inlineStr">
-        <is>
-          <t>待重仓-存储</t>
-        </is>
-      </c>
-      <c r="E17" s="191" t="inlineStr">
-        <is>
-          <t>55%</t>
-        </is>
-      </c>
-      <c r="F17" s="191" t="inlineStr">
-        <is>
-          <t>49%</t>
-        </is>
-      </c>
-      <c r="G17" s="191" t="inlineStr">
-        <is>
-          <t>1.0:1</t>
-        </is>
-      </c>
-      <c r="H17" s="191" t="inlineStr">
-        <is>
-          <t>0.550</t>
-        </is>
-      </c>
-      <c r="I17" s="191" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="J17" s="191" t="inlineStr">
-        <is>
-          <t>0.5500</t>
-        </is>
-      </c>
-      <c r="K17" s="246" t="inlineStr">
-        <is>
-          <t>未通过</t>
-        </is>
-      </c>
-      <c r="L17" s="191" t="inlineStr">
-        <is>
-          <t>降级观察</t>
-        </is>
-      </c>
-      <c r="M17" s="191" t="inlineStr">
-        <is>
-          <t>兆易525元涨81% PE天际线，安全边际不足</t>
-        </is>
-      </c>
-      <c r="N17" s="191" t="inlineStr">
-        <is>
-          <t>安全边际不足，PE天际线，向上小于向下</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="16.5" customHeight="1" s="139">
-      <c r="A18" s="191" t="n">
-        <v>10</v>
-      </c>
-      <c r="B18" s="191" t="inlineStr">
-        <is>
-          <t>芯片020628</t>
-        </is>
-      </c>
-      <c r="C18" s="191" t="inlineStr">
-        <is>
-          <t>芯片020628</t>
-        </is>
-      </c>
-      <c r="D18" s="191" t="inlineStr">
-        <is>
-          <t>持仓</t>
-        </is>
-      </c>
-      <c r="E18" s="191" t="inlineStr">
-        <is>
-          <t>44%</t>
-        </is>
-      </c>
-      <c r="F18" s="191" t="inlineStr">
-        <is>
-          <t>38%</t>
-        </is>
-      </c>
-      <c r="G18" s="191" t="inlineStr">
-        <is>
-          <t>1.2:1</t>
-        </is>
-      </c>
-      <c r="H18" s="191" t="inlineStr">
-        <is>
-          <t>0.528</t>
-        </is>
-      </c>
-      <c r="I18" s="191" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="J18" s="191" t="inlineStr">
-        <is>
-          <t>0.5280</t>
-        </is>
-      </c>
-      <c r="K18" s="246" t="inlineStr">
-        <is>
-          <t>未通过</t>
-        </is>
-      </c>
-      <c r="L18" s="191" t="inlineStr">
-        <is>
-          <t>观望</t>
-        </is>
-      </c>
-      <c r="M18" s="191" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N18" s="191" t="inlineStr">
-        <is>
-          <t>已持仓观望，利率折价6pp</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="32.8" customHeight="1" s="139">
-      <c r="A19" s="191" t="n">
-        <v>11</v>
-      </c>
-      <c r="B19" s="191" t="inlineStr">
-        <is>
-          <t>恒科012349</t>
-        </is>
-      </c>
-      <c r="C19" s="191" t="inlineStr">
-        <is>
-          <t>恒科012349</t>
-        </is>
-      </c>
-      <c r="D19" s="191" t="inlineStr">
-        <is>
-          <t>持仓</t>
-        </is>
-      </c>
-      <c r="E19" s="191" t="inlineStr">
-        <is>
-          <t>29%</t>
-        </is>
-      </c>
-      <c r="F19" s="191" t="inlineStr">
-        <is>
-          <t>23%</t>
-        </is>
-      </c>
-      <c r="G19" s="191" t="inlineStr">
-        <is>
-          <t>0.4:1</t>
-        </is>
-      </c>
-      <c r="H19" s="191" t="inlineStr">
-        <is>
-          <t>0.116</t>
-        </is>
-      </c>
-      <c r="I19" s="191" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="J19" s="191" t="inlineStr">
-        <is>
-          <t>0.1160</t>
-        </is>
-      </c>
-      <c r="K19" s="246" t="inlineStr">
-        <is>
-          <t>未通过</t>
-        </is>
-      </c>
-      <c r="L19" s="191" t="inlineStr">
-        <is>
-          <t>不干</t>
-        </is>
-      </c>
-      <c r="M19" s="191" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N19" s="191" t="inlineStr">
-        <is>
-          <t>已持仓不干，利率折价5pp</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="15" customHeight="1" s="139">
-      <c r="A20" s="248" t="n">
-        <v>12</v>
-      </c>
-      <c r="B20" s="248" t="inlineStr">
+      <c r="B20" s="289" t="inlineStr">
         <is>
           <t>现金</t>
         </is>
       </c>
-      <c r="C20" s="248" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D20" s="248" t="inlineStr">
-        <is>
-          <t>现金</t>
-        </is>
-      </c>
-      <c r="E20" s="248" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F20" s="248" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G20" s="248" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H20" s="248" t="inlineStr">
-        <is>
-          <t>0.000</t>
-        </is>
-      </c>
-      <c r="I20" s="248" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="J20" s="248" t="inlineStr">
-        <is>
-          <t>0.0000</t>
-        </is>
-      </c>
-      <c r="K20" s="248" t="inlineStr">
+      <c r="C20" s="289" t="inlineStr"/>
+      <c r="D20" s="289" t="inlineStr"/>
+      <c r="E20" s="289" t="inlineStr"/>
+      <c r="F20" s="289" t="inlineStr"/>
+      <c r="G20" s="289" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" s="289" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I20" s="289" t="n">
+        <v>0</v>
+      </c>
+      <c r="J20" s="288" t="inlineStr">
         <is>
           <t>基准</t>
         </is>
       </c>
-      <c r="L20" s="248" t="inlineStr">
-        <is>
-          <t>Score=0基准线</t>
-        </is>
-      </c>
-      <c r="M20" s="248" t="inlineStr">
-        <is>
-          <t>Score=0，所有选项都要跟现金比</t>
-        </is>
-      </c>
-      <c r="N20" s="248" t="inlineStr">
-        <is>
-          <t>无风险，但通胀侵蚀购买力</t>
-        </is>
-      </c>
+      <c r="K20" s="289" t="inlineStr">
+        <is>
+          <t>Score=0</t>
+        </is>
+      </c>
+      <c r="L20" s="302" t="n"/>
+      <c r="M20" s="302" t="n"/>
+      <c r="N20" s="302" t="n"/>
     </row>
     <row r="21" ht="16.5" customHeight="1" s="139">
-      <c r="A21" s="191" t="n">
-        <v>13</v>
-      </c>
-      <c r="B21" s="191" t="inlineStr">
-        <is>
-          <t>AI027048</t>
-        </is>
-      </c>
-      <c r="C21" s="191" t="inlineStr">
-        <is>
-          <t>AI027048</t>
-        </is>
-      </c>
-      <c r="D21" s="191" t="inlineStr">
-        <is>
-          <t>持仓</t>
-        </is>
-      </c>
-      <c r="E21" s="191" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F21" s="191" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G21" s="191" t="inlineStr">
-        <is>
-          <t>0.7:1</t>
-        </is>
-      </c>
-      <c r="H21" s="191" t="inlineStr">
-        <is>
-          <t>0.000</t>
-        </is>
-      </c>
-      <c r="I21" s="191" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
-      <c r="J21" s="191" t="inlineStr">
-        <is>
-          <t>-1.0000</t>
-        </is>
-      </c>
-      <c r="K21" s="246" t="inlineStr">
-        <is>
-          <t>未通过</t>
-        </is>
-      </c>
-      <c r="L21" s="191" t="inlineStr">
-        <is>
-          <t>不干</t>
-        </is>
-      </c>
-      <c r="M21" s="191" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N21" s="191" t="inlineStr">
-        <is>
-          <t>已持仓不干，利率折价0pp</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="16.5" customHeight="1" s="139"/>
+      <c r="A21" s="302" t="n"/>
+      <c r="B21" s="302" t="n"/>
+      <c r="C21" s="302" t="n"/>
+      <c r="D21" s="302" t="n"/>
+      <c r="E21" s="302" t="n"/>
+      <c r="F21" s="302" t="n"/>
+      <c r="G21" s="302" t="n"/>
+      <c r="H21" s="302" t="n"/>
+      <c r="I21" s="302" t="n"/>
+      <c r="J21" s="302" t="n"/>
+      <c r="K21" s="302" t="n"/>
+      <c r="L21" s="302" t="n"/>
+      <c r="M21" s="302" t="n"/>
+      <c r="N21" s="302" t="n"/>
+    </row>
+    <row r="22" ht="16.5" customHeight="1" s="139">
+      <c r="A22" s="305" t="inlineStr">
+        <is>
+          <t>结论：现金分配建议</t>
+        </is>
+      </c>
+      <c r="L22" s="295" t="n"/>
+      <c r="M22" s="295" t="n"/>
+      <c r="N22" s="295" t="n"/>
+    </row>
     <row r="23" ht="16.5" customHeight="1" s="139">
-      <c r="A23" s="249" t="inlineStr">
-        <is>
-          <t>结论：现金该往哪分配</t>
-        </is>
-      </c>
+      <c r="A23" s="306" t="inlineStr">
+        <is>
+          <t>正期望EV&gt;1.0 (4个):</t>
+        </is>
+      </c>
+      <c r="B23" s="295" t="n"/>
+      <c r="C23" s="295" t="n"/>
+      <c r="D23" s="295" t="n"/>
+      <c r="E23" s="295" t="n"/>
+      <c r="F23" s="295" t="n"/>
+      <c r="G23" s="295" t="n"/>
+      <c r="H23" s="295" t="n"/>
+      <c r="I23" s="295" t="n"/>
+      <c r="J23" s="295" t="n"/>
+      <c r="K23" s="295" t="n"/>
+      <c r="L23" s="295" t="n"/>
+      <c r="M23" s="295" t="n"/>
+      <c r="N23" s="295" t="n"/>
     </row>
     <row r="24" ht="16.5" customHeight="1" s="139">
-      <c r="A24" s="214" t="inlineStr">
-        <is>
-          <t>1. 长电科技(600584) - P=75% R=4.5:1 Score=3.3750 目标仓位占比=37%的可投资金</t>
-        </is>
-      </c>
+      <c r="A24" s="307" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  养殖008765 P=56% R=2.73:1 EV=1.53 仓位5%</t>
+        </is>
+      </c>
+      <c r="B24" s="295" t="n"/>
+      <c r="C24" s="295" t="n"/>
+      <c r="D24" s="295" t="n"/>
+      <c r="E24" s="295" t="n"/>
+      <c r="F24" s="295" t="n"/>
+      <c r="G24" s="295" t="n"/>
+      <c r="H24" s="295" t="n"/>
+      <c r="I24" s="295" t="n"/>
+      <c r="J24" s="295" t="n"/>
+      <c r="K24" s="295" t="n"/>
+      <c r="L24" s="295" t="n"/>
+      <c r="M24" s="295" t="n"/>
+      <c r="N24" s="295" t="n"/>
     </row>
     <row r="25" ht="17.15" customHeight="1" s="139">
-      <c r="A25" s="214" t="inlineStr">
-        <is>
-          <t>2. 通富微电(002156) - P=75% R=4.0:1 Score=3.0000 目标仓位占比=33%的可投资金</t>
-        </is>
-      </c>
+      <c r="A25" s="307" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  电池009759 P=67% R=2.25:1 EV=1.51 仓位15%</t>
+        </is>
+      </c>
+      <c r="B25" s="295" t="n"/>
+      <c r="C25" s="295" t="n"/>
+      <c r="D25" s="295" t="n"/>
+      <c r="E25" s="295" t="n"/>
+      <c r="F25" s="295" t="n"/>
+      <c r="G25" s="295" t="n"/>
+      <c r="H25" s="295" t="n"/>
+      <c r="I25" s="295" t="n"/>
+      <c r="J25" s="295" t="n"/>
+      <c r="K25" s="295" t="n"/>
+      <c r="L25" s="295" t="n"/>
+      <c r="M25" s="295" t="n"/>
+      <c r="N25" s="295" t="n"/>
     </row>
     <row r="26" ht="15" customHeight="1" s="139">
-      <c r="A26" s="214" t="inlineStr">
-        <is>
-          <t>3. 养殖014415(养殖014415) - P=70% R=2.0:1 Score=1.4000 目标仓位占比=15%的可投资金</t>
-        </is>
-      </c>
+      <c r="A26" s="307" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  核电赛道 P=50% R=2.44:1 EV=1.22 仓位0%</t>
+        </is>
+      </c>
+      <c r="B26" s="295" t="n"/>
+      <c r="C26" s="295" t="n"/>
+      <c r="D26" s="295" t="n"/>
+      <c r="E26" s="295" t="n"/>
+      <c r="F26" s="295" t="n"/>
+      <c r="G26" s="295" t="n"/>
+      <c r="H26" s="295" t="n"/>
+      <c r="I26" s="295" t="n"/>
+      <c r="J26" s="295" t="n"/>
+      <c r="K26" s="295" t="n"/>
+      <c r="L26" s="295" t="n"/>
+      <c r="M26" s="295" t="n"/>
+      <c r="N26" s="295" t="n"/>
     </row>
     <row r="27" ht="16.5" customHeight="1" s="139">
-      <c r="A27" s="214" t="inlineStr">
-        <is>
-          <t>4. 电池018926(电池018926) - P=65% R=2.0:1 Score=1.3000 目标仓位占比=14%的可投资金</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="16.5" customHeight="1" s="139"/>
+      <c r="A27" s="307" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  存储赛道 P=51% R=2.03:1 EV=1.04 仓位0%</t>
+        </is>
+      </c>
+      <c r="B27" s="295" t="n"/>
+      <c r="C27" s="295" t="n"/>
+      <c r="D27" s="295" t="n"/>
+      <c r="E27" s="295" t="n"/>
+      <c r="F27" s="295" t="n"/>
+      <c r="G27" s="295" t="n"/>
+      <c r="H27" s="295" t="n"/>
+      <c r="I27" s="295" t="n"/>
+      <c r="J27" s="295" t="n"/>
+      <c r="K27" s="295" t="n"/>
+      <c r="L27" s="295" t="n"/>
+      <c r="M27" s="295" t="n"/>
+      <c r="N27" s="295" t="n"/>
+    </row>
+    <row r="28" ht="16.5" customHeight="1" s="139">
+      <c r="A28" s="308" t="inlineStr">
+        <is>
+          <t>弱正期望0.5&lt;EV&lt;=1.0 (5个):</t>
+        </is>
+      </c>
+      <c r="B28" s="295" t="n"/>
+      <c r="C28" s="295" t="n"/>
+      <c r="D28" s="295" t="n"/>
+      <c r="E28" s="295" t="n"/>
+      <c r="F28" s="295" t="n"/>
+      <c r="G28" s="295" t="n"/>
+      <c r="H28" s="295" t="n"/>
+      <c r="I28" s="295" t="n"/>
+      <c r="J28" s="295" t="n"/>
+      <c r="K28" s="295" t="n"/>
+      <c r="L28" s="295" t="n"/>
+      <c r="M28" s="295" t="n"/>
+      <c r="N28" s="295" t="n"/>
+    </row>
     <row r="29" ht="15" customHeight="1" s="139">
-      <c r="A29" s="214" t="inlineStr">
-        <is>
-          <t>未通过但接近的选项：</t>
-        </is>
-      </c>
+      <c r="A29" s="307" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  原油162411 P=60% R=1.60:1 EV=0.96</t>
+        </is>
+      </c>
+      <c r="B29" s="295" t="n"/>
+      <c r="C29" s="295" t="n"/>
+      <c r="D29" s="295" t="n"/>
+      <c r="E29" s="295" t="n"/>
+      <c r="F29" s="295" t="n"/>
+      <c r="G29" s="295" t="n"/>
+      <c r="H29" s="295" t="n"/>
+      <c r="I29" s="295" t="n"/>
+      <c r="J29" s="295" t="n"/>
+      <c r="K29" s="295" t="n"/>
+      <c r="L29" s="295" t="n"/>
+      <c r="M29" s="295" t="n"/>
+      <c r="N29" s="295" t="n"/>
     </row>
     <row r="30" ht="16.5" customHeight="1" s="139">
-      <c r="A30" s="138" t="inlineStr">
-        <is>
-          <t>- 核电(-) - P=52% R=1.5:1 - P差8pp到门槛, R差0.5到门槛</t>
-        </is>
-      </c>
+      <c r="A30" s="308" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  银行001595 P=44% R=1.80:1 EV=0.79</t>
+        </is>
+      </c>
+      <c r="B30" s="295" t="n"/>
+      <c r="C30" s="295" t="n"/>
+      <c r="D30" s="295" t="n"/>
+      <c r="E30" s="295" t="n"/>
+      <c r="F30" s="295" t="n"/>
+      <c r="G30" s="295" t="n"/>
+      <c r="H30" s="295" t="n"/>
+      <c r="I30" s="295" t="n"/>
+      <c r="J30" s="295" t="n"/>
+      <c r="K30" s="295" t="n"/>
+      <c r="L30" s="295" t="n"/>
+      <c r="M30" s="295" t="n"/>
+      <c r="N30" s="295" t="n"/>
     </row>
     <row r="31" ht="17.15" customHeight="1" s="139">
-      <c r="A31" s="138" t="inlineStr">
-        <is>
-          <t>- 存储赛道(-) - P=55% R=1.0:1 - P差5pp到门槛, R差1.0到门槛</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="15" customHeight="1" s="139"/>
+      <c r="A31" s="308" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  稀金008907 P=41% R=1.57:1 EV=0.64</t>
+        </is>
+      </c>
+      <c r="B31" s="295" t="n"/>
+      <c r="C31" s="295" t="n"/>
+      <c r="D31" s="295" t="n"/>
+      <c r="E31" s="295" t="n"/>
+      <c r="F31" s="295" t="n"/>
+      <c r="G31" s="295" t="n"/>
+      <c r="H31" s="295" t="n"/>
+      <c r="I31" s="295" t="n"/>
+      <c r="J31" s="295" t="n"/>
+      <c r="K31" s="295" t="n"/>
+      <c r="L31" s="295" t="n"/>
+      <c r="M31" s="295" t="n"/>
+      <c r="N31" s="295" t="n"/>
+    </row>
+    <row r="32" ht="15" customHeight="1" s="139">
+      <c r="A32" s="295" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  有色008826 P=39% R=1.63:1 EV=0.64</t>
+        </is>
+      </c>
+      <c r="B32" s="295" t="n"/>
+      <c r="C32" s="295" t="n"/>
+      <c r="D32" s="295" t="n"/>
+      <c r="E32" s="295" t="n"/>
+      <c r="F32" s="295" t="n"/>
+      <c r="G32" s="295" t="n"/>
+      <c r="H32" s="295" t="n"/>
+      <c r="I32" s="295" t="n"/>
+      <c r="J32" s="295" t="n"/>
+      <c r="K32" s="295" t="n"/>
+      <c r="L32" s="295" t="n"/>
+      <c r="M32" s="295" t="n"/>
+      <c r="N32" s="295" t="n"/>
+    </row>
     <row r="33" ht="15" customHeight="1" s="139">
-      <c r="A33" s="214" t="inlineStr">
-        <is>
-          <t>现金：按Score排序，优先分配给最高Score选项</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="15" customHeight="1" s="139"/>
+      <c r="A33" s="307" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  芯片020628 P=40% R=1.47:1 EV=0.59</t>
+        </is>
+      </c>
+      <c r="B33" s="295" t="n"/>
+      <c r="C33" s="295" t="n"/>
+      <c r="D33" s="295" t="n"/>
+      <c r="E33" s="295" t="n"/>
+      <c r="F33" s="295" t="n"/>
+      <c r="G33" s="295" t="n"/>
+      <c r="H33" s="295" t="n"/>
+      <c r="I33" s="295" t="n"/>
+      <c r="J33" s="295" t="n"/>
+      <c r="K33" s="295" t="n"/>
+      <c r="L33" s="295" t="n"/>
+      <c r="M33" s="295" t="n"/>
+      <c r="N33" s="295" t="n"/>
+    </row>
+    <row r="34" ht="15" customHeight="1" s="139">
+      <c r="A34" s="295" t="n"/>
+      <c r="B34" s="295" t="n"/>
+      <c r="C34" s="295" t="n"/>
+      <c r="D34" s="295" t="n"/>
+      <c r="E34" s="295" t="n"/>
+      <c r="F34" s="295" t="n"/>
+      <c r="G34" s="295" t="n"/>
+      <c r="H34" s="295" t="n"/>
+      <c r="I34" s="295" t="n"/>
+      <c r="J34" s="295" t="n"/>
+      <c r="K34" s="295" t="n"/>
+      <c r="L34" s="295" t="n"/>
+      <c r="M34" s="295" t="n"/>
+      <c r="N34" s="295" t="n"/>
+    </row>
     <row r="35" ht="15" customHeight="1" s="139">
-      <c r="A35" s="214" t="inlineStr">
-        <is>
-          <t>方法说明</t>
-        </is>
-      </c>
+      <c r="A35" s="307" t="inlineStr">
+        <is>
+          <t>现金65%锁定 | 35%可配: 养殖(15%) 电池(10%) 核电/存储(各5%待建仓)</t>
+        </is>
+      </c>
+      <c r="B35" s="295" t="n"/>
+      <c r="C35" s="295" t="n"/>
+      <c r="D35" s="295" t="n"/>
+      <c r="E35" s="295" t="n"/>
+      <c r="F35" s="295" t="n"/>
+      <c r="G35" s="295" t="n"/>
+      <c r="H35" s="295" t="n"/>
+      <c r="I35" s="295" t="n"/>
+      <c r="J35" s="295" t="n"/>
+      <c r="K35" s="295" t="n"/>
+      <c r="L35" s="295" t="n"/>
+      <c r="M35" s="295" t="n"/>
+      <c r="N35" s="295" t="n"/>
     </row>
     <row r="36" ht="15" customHeight="1" s="139">
-      <c r="A36" s="250" t="inlineStr">
-        <is>
-          <t>1. 吸引力Score = P*R - alpha*w*(1-P) | P=胜率 R=盈亏比 w=当前仓位占比 alpha=1.0</t>
-        </is>
-      </c>
+      <c r="A36" s="309" t="inlineStr">
+        <is>
+          <t>注意: 芯片信源Spearman=-0.676需替换，当前P值可靠性存疑</t>
+        </is>
+      </c>
+      <c r="B36" s="295" t="n"/>
+      <c r="C36" s="295" t="n"/>
+      <c r="D36" s="295" t="n"/>
+      <c r="E36" s="295" t="n"/>
+      <c r="F36" s="295" t="n"/>
+      <c r="G36" s="295" t="n"/>
+      <c r="H36" s="295" t="n"/>
+      <c r="I36" s="295" t="n"/>
+      <c r="J36" s="295" t="n"/>
+      <c r="K36" s="295" t="n"/>
+      <c r="L36" s="295" t="n"/>
+      <c r="M36" s="295" t="n"/>
+      <c r="N36" s="295" t="n"/>
     </row>
     <row r="37" ht="15" customHeight="1" s="139">
-      <c r="A37" s="250" t="inlineStr">
-        <is>
-          <t>2. 大白话：吸引力 = 机会多好(P*R) 减去 风险多重(仓位乘不确定性)</t>
-        </is>
-      </c>
+      <c r="A37" s="309" t="n"/>
+      <c r="B37" s="295" t="n"/>
+      <c r="C37" s="295" t="n"/>
+      <c r="D37" s="295" t="n"/>
+      <c r="E37" s="295" t="n"/>
+      <c r="F37" s="295" t="n"/>
+      <c r="G37" s="295" t="n"/>
+      <c r="H37" s="295" t="n"/>
+      <c r="I37" s="295" t="n"/>
+      <c r="J37" s="295" t="n"/>
+      <c r="K37" s="295" t="n"/>
+      <c r="L37" s="295" t="n"/>
+      <c r="M37" s="295" t="n"/>
+      <c r="N37" s="295" t="n"/>
     </row>
     <row r="38" ht="15" customHeight="1" s="139">
-      <c r="A38" s="250" t="inlineStr">
-        <is>
-          <t>3. 双门槛：P&gt;=60% + 盈亏比&gt;=2:1 通过 按Score排序分配现金</t>
-        </is>
-      </c>
+      <c r="A38" s="309" t="n"/>
+      <c r="B38" s="295" t="n"/>
+      <c r="C38" s="295" t="n"/>
+      <c r="D38" s="295" t="n"/>
+      <c r="E38" s="295" t="n"/>
+      <c r="F38" s="295" t="n"/>
+      <c r="G38" s="295" t="n"/>
+      <c r="H38" s="295" t="n"/>
+      <c r="I38" s="295" t="n"/>
+      <c r="J38" s="295" t="n"/>
+      <c r="K38" s="295" t="n"/>
+      <c r="L38" s="295" t="n"/>
+      <c r="M38" s="295" t="n"/>
+      <c r="N38" s="295" t="n"/>
     </row>
     <row r="39" ht="15" customHeight="1" s="139">
-      <c r="A39" s="250" t="inlineStr">
-        <is>
-          <t>4. 目标仓位分配：按P*R比例分配可投资金（通过门槛的选项）</t>
-        </is>
-      </c>
+      <c r="A39" s="309" t="n"/>
+      <c r="B39" s="295" t="n"/>
+      <c r="C39" s="295" t="n"/>
+      <c r="D39" s="295" t="n"/>
+      <c r="E39" s="295" t="n"/>
+      <c r="F39" s="295" t="n"/>
+      <c r="G39" s="295" t="n"/>
+      <c r="H39" s="295" t="n"/>
+      <c r="I39" s="295" t="n"/>
+      <c r="J39" s="295" t="n"/>
+      <c r="K39" s="295" t="n"/>
+      <c r="L39" s="295" t="n"/>
+      <c r="M39" s="295" t="n"/>
+      <c r="N39" s="295" t="n"/>
     </row>
     <row r="40" ht="15" customHeight="1" s="139">
-      <c r="A40" s="250" t="inlineStr">
-        <is>
-          <t>5. 饱和度检查：当前仓位/目标仓位 小于50%加仓，大于100%减仓</t>
-        </is>
-      </c>
+      <c r="A40" s="309" t="n"/>
+      <c r="B40" s="295" t="n"/>
+      <c r="C40" s="295" t="n"/>
+      <c r="D40" s="295" t="n"/>
+      <c r="E40" s="295" t="n"/>
+      <c r="F40" s="295" t="n"/>
+      <c r="G40" s="295" t="n"/>
+      <c r="H40" s="295" t="n"/>
+      <c r="I40" s="295" t="n"/>
+      <c r="J40" s="295" t="n"/>
+      <c r="K40" s="295" t="n"/>
+      <c r="L40" s="295" t="n"/>
+      <c r="M40" s="295" t="n"/>
+      <c r="N40" s="295" t="n"/>
     </row>
     <row r="41" ht="15" customHeight="1" s="139">
-      <c r="A41" s="250" t="inlineStr">
-        <is>
-          <t>6. 有效P = P + 利率折价（成长股-6pp/周期股-4pp/防御股0pp）</t>
-        </is>
-      </c>
+      <c r="A41" s="309" t="n"/>
+      <c r="B41" s="295" t="n"/>
+      <c r="C41" s="295" t="n"/>
+      <c r="D41" s="295" t="n"/>
+      <c r="E41" s="295" t="n"/>
+      <c r="F41" s="295" t="n"/>
+      <c r="G41" s="295" t="n"/>
+      <c r="H41" s="295" t="n"/>
+      <c r="I41" s="295" t="n"/>
+      <c r="J41" s="295" t="n"/>
+      <c r="K41" s="295" t="n"/>
+      <c r="L41" s="295" t="n"/>
+      <c r="M41" s="295" t="n"/>
+      <c r="N41" s="295" t="n"/>
     </row>
     <row r="42" ht="15" customHeight="1" s="139">
-      <c r="A42" s="250" t="inlineStr">
-        <is>
-          <t>7. 审核频率：每周日一次 + P值跨越60%阈值时 + 新机会加入时</t>
-        </is>
-      </c>
+      <c r="A42" s="309" t="n"/>
+      <c r="B42" s="295" t="n"/>
+      <c r="C42" s="295" t="n"/>
+      <c r="D42" s="295" t="n"/>
+      <c r="E42" s="295" t="n"/>
+      <c r="F42" s="295" t="n"/>
+      <c r="G42" s="295" t="n"/>
+      <c r="H42" s="295" t="n"/>
+      <c r="I42" s="295" t="n"/>
+      <c r="J42" s="295" t="n"/>
+      <c r="K42" s="295" t="n"/>
+      <c r="L42" s="295" t="n"/>
+      <c r="M42" s="295" t="n"/>
+      <c r="N42" s="295" t="n"/>
     </row>
     <row r="43" ht="15" customHeight="1" s="139">
-      <c r="A43" s="250" t="inlineStr">
-        <is>
-          <t>8. 本次审核：2026-06-04 | 下次预计：2026-06-11</t>
-        </is>
-      </c>
+      <c r="A43" s="309" t="n"/>
+      <c r="B43" s="295" t="n"/>
+      <c r="C43" s="295" t="n"/>
+      <c r="D43" s="295" t="n"/>
+      <c r="E43" s="295" t="n"/>
+      <c r="F43" s="295" t="n"/>
+      <c r="G43" s="295" t="n"/>
+      <c r="H43" s="295" t="n"/>
+      <c r="I43" s="295" t="n"/>
+      <c r="J43" s="295" t="n"/>
+      <c r="K43" s="295" t="n"/>
+      <c r="L43" s="295" t="n"/>
+      <c r="M43" s="295" t="n"/>
+      <c r="N43" s="295" t="n"/>
     </row>
     <row r="44" ht="15" customHeight="1" s="139">
-      <c r="A44" s="250" t="inlineStr">
-        <is>
-          <t>9. 数据来源：Sheet2持仓数据 + 待重仓监控.md + 6/4盘中价格</t>
-        </is>
-      </c>
+      <c r="A44" s="309" t="n"/>
+      <c r="B44" s="295" t="n"/>
+      <c r="C44" s="295" t="n"/>
+      <c r="D44" s="295" t="n"/>
+      <c r="E44" s="295" t="n"/>
+      <c r="F44" s="295" t="n"/>
+      <c r="G44" s="295" t="n"/>
+      <c r="H44" s="295" t="n"/>
+      <c r="I44" s="295" t="n"/>
+      <c r="J44" s="295" t="n"/>
+      <c r="K44" s="295" t="n"/>
+      <c r="L44" s="295" t="n"/>
+      <c r="M44" s="295" t="n"/>
+      <c r="N44" s="295" t="n"/>
     </row>
     <row r="45" ht="15" customHeight="1" s="139">
-      <c r="A45" s="250" t="inlineStr">
-        <is>
-          <t>10. 小龙虾技术分析：长电科技(先进封装广度最强) + 通富微电(AMD封测不可替代)</t>
-        </is>
-      </c>
+      <c r="A45" s="309" t="n"/>
+      <c r="B45" s="295" t="n"/>
+      <c r="C45" s="295" t="n"/>
+      <c r="D45" s="295" t="n"/>
+      <c r="E45" s="295" t="n"/>
+      <c r="F45" s="295" t="n"/>
+      <c r="G45" s="295" t="n"/>
+      <c r="H45" s="295" t="n"/>
+      <c r="I45" s="295" t="n"/>
+      <c r="J45" s="295" t="n"/>
+      <c r="K45" s="295" t="n"/>
+      <c r="L45" s="295" t="n"/>
+      <c r="M45" s="295" t="n"/>
+      <c r="N45" s="295" t="n"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="295" t="n"/>
+      <c r="B46" s="295" t="n"/>
+      <c r="C46" s="295" t="n"/>
+      <c r="D46" s="295" t="n"/>
+      <c r="E46" s="295" t="n"/>
+      <c r="F46" s="295" t="n"/>
+      <c r="G46" s="295" t="n"/>
+      <c r="H46" s="295" t="n"/>
+      <c r="I46" s="295" t="n"/>
+      <c r="J46" s="295" t="n"/>
+      <c r="K46" s="295" t="n"/>
+      <c r="L46" s="295" t="n"/>
+      <c r="M46" s="295" t="n"/>
+      <c r="N46" s="295" t="n"/>
     </row>
     <row r="47" ht="17.15" customHeight="1" s="139">
-      <c r="A47" s="219" t="inlineStr">
-        <is>
-          <t>📖 现金锁定机制说明（机制v2）</t>
-        </is>
-      </c>
+      <c r="A47" s="310" t="n"/>
+      <c r="B47" s="295" t="n"/>
+      <c r="C47" s="295" t="n"/>
+      <c r="D47" s="295" t="n"/>
+      <c r="E47" s="295" t="n"/>
+      <c r="F47" s="295" t="n"/>
+      <c r="G47" s="295" t="n"/>
+      <c r="H47" s="295" t="n"/>
+      <c r="I47" s="295" t="n"/>
+      <c r="J47" s="295" t="n"/>
+      <c r="K47" s="295" t="n"/>
+      <c r="L47" s="295" t="n"/>
+      <c r="M47" s="295" t="n"/>
+      <c r="N47" s="295" t="n"/>
     </row>
     <row r="48" ht="15" customHeight="1" s="139">
-      <c r="A48" s="182" t="inlineStr">
-        <is>
-          <t>公式：折后仓位% = 原目标仓位% × (1 - 现金锁定系数)</t>
-        </is>
-      </c>
+      <c r="A48" s="311" t="n"/>
+      <c r="B48" s="295" t="n"/>
+      <c r="C48" s="295" t="n"/>
+      <c r="D48" s="295" t="n"/>
+      <c r="E48" s="295" t="n"/>
+      <c r="F48" s="295" t="n"/>
+      <c r="G48" s="295" t="n"/>
+      <c r="H48" s="295" t="n"/>
+      <c r="I48" s="295" t="n"/>
+      <c r="J48" s="295" t="n"/>
+      <c r="K48" s="295" t="n"/>
+      <c r="L48" s="295" t="n"/>
+      <c r="M48" s="295" t="n"/>
+      <c r="N48" s="295" t="n"/>
     </row>
     <row r="49" ht="15" customHeight="1" s="139">
-      <c r="A49" s="230" t="inlineStr">
-        <is>
-          <t>现金锁定系数 = 达利欧泡沫概率(70%) × 三源互锁强度(1.0=强印证) × 时间衰减(剩余月数/12)</t>
-        </is>
-      </c>
+      <c r="A49" s="312" t="n"/>
+      <c r="B49" s="295" t="n"/>
+      <c r="C49" s="295" t="n"/>
+      <c r="D49" s="295" t="n"/>
+      <c r="E49" s="295" t="n"/>
+      <c r="F49" s="295" t="n"/>
+      <c r="G49" s="295" t="n"/>
+      <c r="H49" s="295" t="n"/>
+      <c r="I49" s="295" t="n"/>
+      <c r="J49" s="295" t="n"/>
+      <c r="K49" s="295" t="n"/>
+      <c r="L49" s="295" t="n"/>
+      <c r="M49" s="295" t="n"/>
+      <c r="N49" s="295" t="n"/>
     </row>
     <row r="50" ht="15" customHeight="1" s="139">
-      <c r="A50" s="230" t="inlineStr">
-        <is>
-          <t>当前计算：0.70 × 1.0 × (5/12≈0.42) ≈ 0.65 → 65%现金锁定</t>
-        </is>
-      </c>
+      <c r="A50" s="312" t="n"/>
+      <c r="B50" s="295" t="n"/>
+      <c r="C50" s="295" t="n"/>
+      <c r="D50" s="295" t="n"/>
+      <c r="E50" s="295" t="n"/>
+      <c r="F50" s="295" t="n"/>
+      <c r="G50" s="295" t="n"/>
+      <c r="H50" s="295" t="n"/>
+      <c r="I50" s="295" t="n"/>
+      <c r="J50" s="295" t="n"/>
+      <c r="K50" s="295" t="n"/>
+      <c r="L50" s="295" t="n"/>
+      <c r="M50" s="295" t="n"/>
+      <c r="N50" s="295" t="n"/>
     </row>
     <row r="51" ht="15" customHeight="1" s="139">
-      <c r="A51" s="230" t="inlineStr">
-        <is>
-          <t>解锁条件：三源信号任一落地（达利欧：七姐妹&gt;15%回调；李大霄：多数成分股下跌；中期选举：11月美股跌）</t>
-        </is>
-      </c>
+      <c r="A51" s="312" t="n"/>
+      <c r="B51" s="295" t="n"/>
+      <c r="C51" s="295" t="n"/>
+      <c r="D51" s="295" t="n"/>
+      <c r="E51" s="295" t="n"/>
+      <c r="F51" s="295" t="n"/>
+      <c r="G51" s="295" t="n"/>
+      <c r="H51" s="295" t="n"/>
+      <c r="I51" s="295" t="n"/>
+      <c r="J51" s="295" t="n"/>
+      <c r="K51" s="295" t="n"/>
+      <c r="L51" s="295" t="n"/>
+      <c r="M51" s="295" t="n"/>
+      <c r="N51" s="295" t="n"/>
     </row>
     <row r="52" ht="15" customHeight="1" s="139">
-      <c r="A52" s="230" t="inlineStr">
-        <is>
-          <t>已持仓不受影响（养殖/电池/有色等），仅影响待重仓的新现金分配</t>
-        </is>
-      </c>
+      <c r="A52" s="312" t="n"/>
+      <c r="B52" s="295" t="n"/>
+      <c r="C52" s="295" t="n"/>
+      <c r="D52" s="295" t="n"/>
+      <c r="E52" s="295" t="n"/>
+      <c r="F52" s="295" t="n"/>
+      <c r="G52" s="295" t="n"/>
+      <c r="H52" s="295" t="n"/>
+      <c r="I52" s="295" t="n"/>
+      <c r="J52" s="295" t="n"/>
+      <c r="K52" s="295" t="n"/>
+      <c r="L52" s="295" t="n"/>
+      <c r="M52" s="295" t="n"/>
+      <c r="N52" s="295" t="n"/>
     </row>
     <row r="53" ht="15" customHeight="1" s="139">
-      <c r="A53" s="251" t="inlineStr">
-        <is>
-          <t>每月重算：时间衰减系数随11月临近而增大→现金锁定系数下降→折后仓位上升</t>
-        </is>
-      </c>
+      <c r="A53" s="313" t="n"/>
+      <c r="B53" s="295" t="n"/>
+      <c r="C53" s="295" t="n"/>
+      <c r="D53" s="295" t="n"/>
+      <c r="E53" s="295" t="n"/>
+      <c r="F53" s="295" t="n"/>
+      <c r="G53" s="295" t="n"/>
+      <c r="H53" s="295" t="n"/>
+      <c r="I53" s="295" t="n"/>
+      <c r="J53" s="295" t="n"/>
+      <c r="K53" s="295" t="n"/>
+      <c r="L53" s="295" t="n"/>
+      <c r="M53" s="295" t="n"/>
+      <c r="N53" s="295" t="n"/>
     </row>
     <row r="54" ht="15" customHeight="1" s="139">
-      <c r="A54" s="230" t="inlineStr">
-        <is>
-          <t>更新日志：2026-06-04 首次加入现金锁定机制 v2 | 下次审核：2026-06-11</t>
-        </is>
-      </c>
+      <c r="A54" s="312" t="n"/>
+      <c r="B54" s="295" t="n"/>
+      <c r="C54" s="295" t="n"/>
+      <c r="D54" s="295" t="n"/>
+      <c r="E54" s="295" t="n"/>
+      <c r="F54" s="295" t="n"/>
+      <c r="G54" s="295" t="n"/>
+      <c r="H54" s="295" t="n"/>
+      <c r="I54" s="295" t="n"/>
+      <c r="J54" s="295" t="n"/>
+      <c r="K54" s="295" t="n"/>
+      <c r="L54" s="295" t="n"/>
+      <c r="M54" s="295" t="n"/>
+      <c r="N54" s="295" t="n"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="295" t="n"/>
+      <c r="B55" s="295" t="n"/>
+      <c r="C55" s="295" t="n"/>
+      <c r="D55" s="295" t="n"/>
+      <c r="E55" s="295" t="n"/>
+      <c r="F55" s="295" t="n"/>
+      <c r="G55" s="295" t="n"/>
+      <c r="H55" s="295" t="n"/>
+      <c r="I55" s="295" t="n"/>
+      <c r="J55" s="295" t="n"/>
+      <c r="K55" s="295" t="n"/>
+      <c r="L55" s="295" t="n"/>
+      <c r="M55" s="295" t="n"/>
+      <c r="N55" s="295" t="n"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="295" t="n"/>
+      <c r="B56" s="295" t="n"/>
+      <c r="C56" s="295" t="n"/>
+      <c r="D56" s="295" t="n"/>
+      <c r="E56" s="295" t="n"/>
+      <c r="F56" s="295" t="n"/>
+      <c r="G56" s="295" t="n"/>
+      <c r="H56" s="295" t="n"/>
+      <c r="I56" s="295" t="n"/>
+      <c r="J56" s="295" t="n"/>
+      <c r="K56" s="295" t="n"/>
+      <c r="L56" s="295" t="n"/>
+      <c r="M56" s="295" t="n"/>
+      <c r="N56" s="295" t="n"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="295" t="n"/>
+      <c r="B57" s="295" t="n"/>
+      <c r="C57" s="295" t="n"/>
+      <c r="D57" s="295" t="n"/>
+      <c r="E57" s="295" t="n"/>
+      <c r="F57" s="295" t="n"/>
+      <c r="G57" s="295" t="n"/>
+      <c r="H57" s="295" t="n"/>
+      <c r="I57" s="295" t="n"/>
+      <c r="J57" s="295" t="n"/>
+      <c r="K57" s="295" t="n"/>
+      <c r="L57" s="295" t="n"/>
+      <c r="M57" s="295" t="n"/>
+      <c r="N57" s="295" t="n"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="295" t="n"/>
+      <c r="B58" s="295" t="n"/>
+      <c r="C58" s="295" t="n"/>
+      <c r="D58" s="295" t="n"/>
+      <c r="E58" s="295" t="n"/>
+      <c r="F58" s="295" t="n"/>
+      <c r="G58" s="295" t="n"/>
+      <c r="H58" s="295" t="n"/>
+      <c r="I58" s="295" t="n"/>
+      <c r="J58" s="295" t="n"/>
+      <c r="K58" s="295" t="n"/>
+      <c r="L58" s="295" t="n"/>
+      <c r="M58" s="295" t="n"/>
+      <c r="N58" s="295" t="n"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="295" t="n"/>
+      <c r="B59" s="295" t="n"/>
+      <c r="C59" s="295" t="n"/>
+      <c r="D59" s="295" t="n"/>
+      <c r="E59" s="295" t="n"/>
+      <c r="F59" s="295" t="n"/>
+      <c r="G59" s="295" t="n"/>
+      <c r="H59" s="295" t="n"/>
+      <c r="I59" s="295" t="n"/>
+      <c r="J59" s="295" t="n"/>
+      <c r="K59" s="295" t="n"/>
+      <c r="L59" s="295" t="n"/>
+      <c r="M59" s="295" t="n"/>
+      <c r="N59" s="295" t="n"/>
     </row>
   </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="A6:K6"/>
+    <mergeCell ref="A22:K22"/>
+    <mergeCell ref="A5:K5"/>
+    <mergeCell ref="A7:K7"/>
+  </mergeCells>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>

--- a/持仓贝叶斯跟踪.xlsx
+++ b/持仓贝叶斯跟踪.xlsx
@@ -27,7 +27,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="57">
+  <fonts count="58">
     <font>
       <name val="Calibri"/>
       <charset val="1"/>
@@ -400,6 +400,9 @@
       <b val="1"/>
       <sz val="11"/>
     </font>
+    <font>
+      <b val="1"/>
+    </font>
   </fonts>
   <fills count="31">
     <fill>
@@ -644,7 +647,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="314">
+  <cellXfs count="319">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -1551,6 +1554,19 @@
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
     <xf numFmtId="0" fontId="41" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="57" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="57" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="57" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
   </cellXfs>
@@ -7225,7 +7241,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:L194"/>
+  <dimension ref="A1:L211"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="10.4921875" defaultRowHeight="12.75" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="18" customWidth="1" style="138" min="1" max="12"/>
@@ -7315,86 +7331,70 @@
       <c r="A3" s="277" t="inlineStr">
         <is>
           <t>P(α):51%
-虚P+14pp
-β折价-11pp
-有效P:40%
-下行:25% 确定性:30% 溢价:50%
-盈亏比:1.2:1
-P×R:0.48
+β折价-3pp（↓从-11降：宏观对芯片价格影响≈0）
+有效P:48%
+R=P/(1-P)=0.9:1
+P×R:0.44
 决策:观望</t>
         </is>
       </c>
       <c r="B3" s="278" t="inlineStr">
         <is>
           <t>P(α):67%
-虚P无
 β折价+0pp
 有效P:67%
-下行:20% 确定性:25% 溢价:40%
-盈亏比:2.2:1
-P×R:1.47
+R=P/(1-P)=2.0:1
+P×R:1.36
 决策:持有</t>
         </is>
       </c>
       <c r="C3" s="279" t="inlineStr">
         <is>
           <t>P(α):41%
-虚P无
 β折价-8pp
 有效P:33%
-下行:30% 确定性:15% 溢价:30%
-盈亏比:0.5:1
-P×R:0.17
+R=P/(1-P)=0.5:1
+P×R:0.16
 决策:不干</t>
         </is>
       </c>
       <c r="D3" s="278" t="inlineStr">
         <is>
           <t>P(α):52%
-虚P+4pp
 β折价+4pp
 有效P:56%
-下行:20% 确定性:35% 溢价:20%
-盈亏比:1.8:1
-P×R:1.01
+R=P/(1-P)=1.3:1
+P×R:0.71
 决策:持有</t>
         </is>
       </c>
       <c r="E3" s="277" t="inlineStr">
         <is>
           <t>P(α):39%
-虚P无
 β折价+0pp
 有效P:39%
-下行:15% 确定性:20% 溢价:30%
-盈亏比:1.3:1
-P×R:0.51
-决策:观望</t>
+R=P/(1-P)=0.6:1
+P×R:0.25
+决策:不干</t>
         </is>
       </c>
       <c r="F3" s="277" t="inlineStr">
         <is>
           <t>P(α):42%
-虚P无
 β折价-1pp
 有效P:41%
-下行:20% 确定性:25% 溢价:35%
-盈亏比:1.2:1
-P×R:0.49
+R=P/(1-P)=0.7:1
+P×R:0.28
 决策:观望</t>
         </is>
       </c>
       <c r="G3" s="277" t="inlineStr">
         <is>
-          <t>成本¥0
-净值1.6291
-P(α):50%
-虚P-2pp
+          <t>P(α):50%
 β折价-6pp
 有效P:44%
-下行:10% 确定性:10% 溢价:5%
-盈亏比:1.0:1
-P×R:0.44
+R=P/(1-P)=0.8:1
+P×R:0.35
 决策:观望</t>
         </is>
       </c>
@@ -7411,58 +7411,34 @@
 决策:不干</t>
         </is>
       </c>
-      <c r="I3" s="175" t="inlineStr">
-        <is>
-          <t>P:55%
-虚P-15pp(6/3→6/4认知升级)
-利率折价-4pp
+      <c r="I3" s="314" t="inlineStr">
+        <is>
+          <t>P(α):55%
+β折价-4pp
 有效P:51%
-拟合✅(6/3分析)
-下行:25% 确定性:40% 溢价:80%
-盈亏比:5.0:1(保守2:1)
-决策:降级观察(安全边际不足)
----
-事件链:
-2026-06-03 +15pp 群联潘健成:Flash供应仍严重不足,明年更紧张(产业一线⭐⭐⭐⭐)
-2026-06-03 +10pp 蒋宇飞:两长存储=国产存储双雄,三级火箭Flash→DRAM→CoWoS→3D堆叠
-2026-06-03 +10pp 蒋宇飞框架:"越靠近GPU越值钱",存储&gt;光模块10倍
-2026-06-03 +5pp 周鸿祎:"内存决定AI高度"
-2026-06-03 +10pp 宋鸿兵:摩尔定律终结→堆叠/存储崛起
-2026-06-04 -15pp 用户认知升级:存储机会尾声→堆叠才是主线,兆易创新2月涨81%安全边际不足
-→ 净P:55%(极高确定性但估值已透支)</t>
-        </is>
-      </c>
-      <c r="J3" s="175" t="inlineStr">
-        <is>
-          <t>P:52%
-虚P无
-利率折价-2pp
+R=P/(1-P)=1.0:1
+P×R:0.53
+决策:观望</t>
+        </is>
+      </c>
+      <c r="J3" s="314" t="inlineStr">
+        <is>
+          <t>P(α):52%
+β折价-2pp
 有效P:50%
-拟合N/A(新赛道)
-下行:15% 确定性:25% 溢价:40%
-盈亏比:1.5:1(长期3:1)
-决策:观察(10年维度)
----
-事件链:
-2026-06-04 +10pp 孙宇晨:"未来10年看核电",10亿美元押注物理AI→电力是核心瓶颈
-2026-06-04 +10pp Sereneity/Leopold:AI物理瓶颈=材料+电力/土地,盯电力基础设施
-2026-06-04 +12pp 行业数据:美国数据中心规划245GW,2028年占全美电力6.7%-12%
-2026-06-04 +10pp 国内政策:2025年核准10台机组(审批加速),金七门2号2026年4月FCD
-2026-06-04 -10pp 短期风险:中国核电2026Q1净利-34.19%,电价下行压力
-→ 净P:52%(4条独立信源同向,短期业绩承压)
-→ 标的:中广核003816(PE10-12x便宜) / 中国核电601985(PE25x偏贵)</t>
-        </is>
-      </c>
-      <c r="K3" s="196" t="inlineStr">
-        <is>
-          <t>P:58%
-虚P无
-利率折价+2pp
+R=P/(1-P)=1.0:1
+P×R:0.50
+决策:观望</t>
+        </is>
+      </c>
+      <c r="K3" s="314" t="inlineStr">
+        <is>
+          <t>P(α):58%
+β折价+2pp
 有效P:60%
-拟合N/A(新赛道)
-下行:25%
-盈亏比:2.4:1
-状态:等回调入场</t>
+R=P/(1-P)=1.5:1
+P×R:0.90
+决策:持有</t>
         </is>
       </c>
     </row>
@@ -7819,12 +7795,12 @@
       </c>
     </row>
     <row r="10" ht="45" customHeight="1" s="139">
-      <c r="A10" s="202" t="inlineStr">
+      <c r="A10" s="315" t="inlineStr">
         <is>
           <t>2026-05-22
--9pp
-【-3pp】宋鸿兵利率风暴
-【-6pp】凯文·沃什就任美联储主席</t>
+-3pp
+【-1pp】宋鸿兵利率风暴（↓从-3pp降级：实际对芯片价格影响≈0）
+【-2pp】凯文·沃什就任美联储主席（↓从-6pp降级：宏观β被产业α碾过）</t>
         </is>
       </c>
       <c r="B10" s="200" t="inlineStr">
@@ -11248,6 +11224,594 @@
           <t>2026-06-06
 0pp
 【0pp】非农超预期/黑五=宏观冲击已部分定价</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" s="138" t="inlineStr">
+        <is>
+          <t>📊 机会成本排序表（2026-06-06 更新）</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" s="316" t="inlineStr">
+        <is>
+          <t>排名</t>
+        </is>
+      </c>
+      <c r="B198" s="316" t="inlineStr">
+        <is>
+          <t>选项</t>
+        </is>
+      </c>
+      <c r="C198" s="316" t="inlineStr">
+        <is>
+          <t>类型</t>
+        </is>
+      </c>
+      <c r="D198" s="316" t="inlineStr">
+        <is>
+          <t>P值</t>
+        </is>
+      </c>
+      <c r="E198" s="316" t="inlineStr">
+        <is>
+          <t>R=P/(1-P)</t>
+        </is>
+      </c>
+      <c r="F198" s="316" t="inlineStr">
+        <is>
+          <t>P×R</t>
+        </is>
+      </c>
+      <c r="G198" s="316" t="inlineStr">
+        <is>
+          <t>仓位w</t>
+        </is>
+      </c>
+      <c r="H198" s="316" t="inlineStr">
+        <is>
+          <t>风险惩罚</t>
+        </is>
+      </c>
+      <c r="I198" s="316" t="inlineStr">
+        <is>
+          <t>Score</t>
+        </is>
+      </c>
+      <c r="J198" s="316" t="inlineStr">
+        <is>
+          <t>信号</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" s="138" t="n">
+        <v>1</v>
+      </c>
+      <c r="B199" s="138" t="inlineStr">
+        <is>
+          <t>电池018926</t>
+        </is>
+      </c>
+      <c r="C199" s="138" t="inlineStr">
+        <is>
+          <t>持仓</t>
+        </is>
+      </c>
+      <c r="D199" s="138" t="inlineStr">
+        <is>
+          <t>67%</t>
+        </is>
+      </c>
+      <c r="E199" s="138" t="inlineStr">
+        <is>
+          <t>2.03:1</t>
+        </is>
+      </c>
+      <c r="F199" s="138" t="inlineStr">
+        <is>
+          <t>1.360</t>
+        </is>
+      </c>
+      <c r="G199" s="138" t="inlineStr">
+        <is>
+          <t>12%</t>
+        </is>
+      </c>
+      <c r="H199" s="138" t="inlineStr">
+        <is>
+          <t>-0.0396</t>
+        </is>
+      </c>
+      <c r="I199" s="138" t="inlineStr">
+        <is>
+          <t>1.3207</t>
+        </is>
+      </c>
+      <c r="J199" s="138" t="inlineStr">
+        <is>
+          <t>🟢优先</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" s="138" t="n">
+        <v>2</v>
+      </c>
+      <c r="B200" s="138" t="inlineStr">
+        <is>
+          <t>原油162411</t>
+        </is>
+      </c>
+      <c r="C200" s="138" t="inlineStr">
+        <is>
+          <t>待重</t>
+        </is>
+      </c>
+      <c r="D200" s="138" t="inlineStr">
+        <is>
+          <t>60%</t>
+        </is>
+      </c>
+      <c r="E200" s="138" t="inlineStr">
+        <is>
+          <t>1.50:1</t>
+        </is>
+      </c>
+      <c r="F200" s="138" t="inlineStr">
+        <is>
+          <t>0.900</t>
+        </is>
+      </c>
+      <c r="G200" s="138" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="H200" s="138" t="inlineStr">
+        <is>
+          <t>-0.0000</t>
+        </is>
+      </c>
+      <c r="I200" s="138" t="inlineStr">
+        <is>
+          <t>0.9000</t>
+        </is>
+      </c>
+      <c r="J200" s="138" t="inlineStr">
+        <is>
+          <t>🟡观察</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" s="138" t="n">
+        <v>3</v>
+      </c>
+      <c r="B201" s="138" t="inlineStr">
+        <is>
+          <t>养殖014415</t>
+        </is>
+      </c>
+      <c r="C201" s="138" t="inlineStr">
+        <is>
+          <t>持仓</t>
+        </is>
+      </c>
+      <c r="D201" s="138" t="inlineStr">
+        <is>
+          <t>56%</t>
+        </is>
+      </c>
+      <c r="E201" s="138" t="inlineStr">
+        <is>
+          <t>1.27:1</t>
+        </is>
+      </c>
+      <c r="F201" s="138" t="inlineStr">
+        <is>
+          <t>0.713</t>
+        </is>
+      </c>
+      <c r="G201" s="138" t="inlineStr">
+        <is>
+          <t>10%</t>
+        </is>
+      </c>
+      <c r="H201" s="138" t="inlineStr">
+        <is>
+          <t>-0.0440</t>
+        </is>
+      </c>
+      <c r="I201" s="138" t="inlineStr">
+        <is>
+          <t>0.6687</t>
+        </is>
+      </c>
+      <c r="J201" s="138" t="inlineStr">
+        <is>
+          <t>🟡观察</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" s="138" t="n">
+        <v>4</v>
+      </c>
+      <c r="B202" s="138" t="inlineStr">
+        <is>
+          <t>存储</t>
+        </is>
+      </c>
+      <c r="C202" s="138" t="inlineStr">
+        <is>
+          <t>待重</t>
+        </is>
+      </c>
+      <c r="D202" s="138" t="inlineStr">
+        <is>
+          <t>51%</t>
+        </is>
+      </c>
+      <c r="E202" s="138" t="inlineStr">
+        <is>
+          <t>1.04:1</t>
+        </is>
+      </c>
+      <c r="F202" s="138" t="inlineStr">
+        <is>
+          <t>0.531</t>
+        </is>
+      </c>
+      <c r="G202" s="138" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="H202" s="138" t="inlineStr">
+        <is>
+          <t>-0.0000</t>
+        </is>
+      </c>
+      <c r="I202" s="138" t="inlineStr">
+        <is>
+          <t>0.5308</t>
+        </is>
+      </c>
+      <c r="J202" s="138" t="inlineStr">
+        <is>
+          <t>🟡观察</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" s="138" t="n">
+        <v>5</v>
+      </c>
+      <c r="B203" s="138" t="inlineStr">
+        <is>
+          <t>核电</t>
+        </is>
+      </c>
+      <c r="C203" s="138" t="inlineStr">
+        <is>
+          <t>待重</t>
+        </is>
+      </c>
+      <c r="D203" s="138" t="inlineStr">
+        <is>
+          <t>50%</t>
+        </is>
+      </c>
+      <c r="E203" s="138" t="inlineStr">
+        <is>
+          <t>1.00:1</t>
+        </is>
+      </c>
+      <c r="F203" s="138" t="inlineStr">
+        <is>
+          <t>0.500</t>
+        </is>
+      </c>
+      <c r="G203" s="138" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="H203" s="138" t="inlineStr">
+        <is>
+          <t>-0.0000</t>
+        </is>
+      </c>
+      <c r="I203" s="138" t="inlineStr">
+        <is>
+          <t>0.5000</t>
+        </is>
+      </c>
+      <c r="J203" s="138" t="inlineStr">
+        <is>
+          <t>🟡观察</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" s="138" t="n">
+        <v>6</v>
+      </c>
+      <c r="B204" s="138" t="inlineStr">
+        <is>
+          <t>芯片020628</t>
+        </is>
+      </c>
+      <c r="C204" s="138" t="inlineStr">
+        <is>
+          <t>持仓</t>
+        </is>
+      </c>
+      <c r="D204" s="138" t="inlineStr">
+        <is>
+          <t>48%</t>
+        </is>
+      </c>
+      <c r="E204" s="138" t="inlineStr">
+        <is>
+          <t>0.92:1</t>
+        </is>
+      </c>
+      <c r="F204" s="138" t="inlineStr">
+        <is>
+          <t>0.443</t>
+        </is>
+      </c>
+      <c r="G204" s="138" t="inlineStr">
+        <is>
+          <t>15%</t>
+        </is>
+      </c>
+      <c r="H204" s="138" t="inlineStr">
+        <is>
+          <t>-0.0780</t>
+        </is>
+      </c>
+      <c r="I204" s="138" t="inlineStr">
+        <is>
+          <t>0.3651</t>
+        </is>
+      </c>
+      <c r="J204" s="138" t="inlineStr">
+        <is>
+          <t>🟡观察</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" s="138" t="n">
+        <v>7</v>
+      </c>
+      <c r="B205" s="138" t="inlineStr">
+        <is>
+          <t>银行001595</t>
+        </is>
+      </c>
+      <c r="C205" s="138" t="inlineStr">
+        <is>
+          <t>持仓</t>
+        </is>
+      </c>
+      <c r="D205" s="138" t="inlineStr">
+        <is>
+          <t>44%</t>
+        </is>
+      </c>
+      <c r="E205" s="138" t="inlineStr">
+        <is>
+          <t>0.79:1</t>
+        </is>
+      </c>
+      <c r="F205" s="138" t="inlineStr">
+        <is>
+          <t>0.346</t>
+        </is>
+      </c>
+      <c r="G205" s="138" t="inlineStr">
+        <is>
+          <t>5%</t>
+        </is>
+      </c>
+      <c r="H205" s="138" t="inlineStr">
+        <is>
+          <t>-0.0280</t>
+        </is>
+      </c>
+      <c r="I205" s="138" t="inlineStr">
+        <is>
+          <t>0.3177</t>
+        </is>
+      </c>
+      <c r="J205" s="138" t="inlineStr">
+        <is>
+          <t>🟡观察</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" s="138" t="n">
+        <v>8</v>
+      </c>
+      <c r="B206" s="138" t="inlineStr">
+        <is>
+          <t>稀金014111</t>
+        </is>
+      </c>
+      <c r="C206" s="138" t="inlineStr">
+        <is>
+          <t>持仓</t>
+        </is>
+      </c>
+      <c r="D206" s="138" t="inlineStr">
+        <is>
+          <t>41%</t>
+        </is>
+      </c>
+      <c r="E206" s="138" t="inlineStr">
+        <is>
+          <t>0.69:1</t>
+        </is>
+      </c>
+      <c r="F206" s="138" t="inlineStr">
+        <is>
+          <t>0.285</t>
+        </is>
+      </c>
+      <c r="G206" s="138" t="inlineStr">
+        <is>
+          <t>7%</t>
+        </is>
+      </c>
+      <c r="H206" s="138" t="inlineStr">
+        <is>
+          <t>-0.0413</t>
+        </is>
+      </c>
+      <c r="I206" s="138" t="inlineStr">
+        <is>
+          <t>0.2436</t>
+        </is>
+      </c>
+      <c r="J206" s="138" t="inlineStr">
+        <is>
+          <t>🔴不动</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" s="138" t="n">
+        <v>9</v>
+      </c>
+      <c r="B207" s="138" t="inlineStr">
+        <is>
+          <t>有色004433</t>
+        </is>
+      </c>
+      <c r="C207" s="138" t="inlineStr">
+        <is>
+          <t>持仓</t>
+        </is>
+      </c>
+      <c r="D207" s="138" t="inlineStr">
+        <is>
+          <t>39%</t>
+        </is>
+      </c>
+      <c r="E207" s="138" t="inlineStr">
+        <is>
+          <t>0.64:1</t>
+        </is>
+      </c>
+      <c r="F207" s="138" t="inlineStr">
+        <is>
+          <t>0.249</t>
+        </is>
+      </c>
+      <c r="G207" s="138" t="inlineStr">
+        <is>
+          <t>8%</t>
+        </is>
+      </c>
+      <c r="H207" s="138" t="inlineStr">
+        <is>
+          <t>-0.0488</t>
+        </is>
+      </c>
+      <c r="I207" s="138" t="inlineStr">
+        <is>
+          <t>0.2005</t>
+        </is>
+      </c>
+      <c r="J207" s="138" t="inlineStr">
+        <is>
+          <t>🔴不动</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" s="138" t="n">
+        <v>10</v>
+      </c>
+      <c r="B208" s="138" t="inlineStr">
+        <is>
+          <t>恒科012349</t>
+        </is>
+      </c>
+      <c r="C208" s="138" t="inlineStr">
+        <is>
+          <t>持仓</t>
+        </is>
+      </c>
+      <c r="D208" s="138" t="inlineStr">
+        <is>
+          <t>33%</t>
+        </is>
+      </c>
+      <c r="E208" s="138" t="inlineStr">
+        <is>
+          <t>0.49:1</t>
+        </is>
+      </c>
+      <c r="F208" s="138" t="inlineStr">
+        <is>
+          <t>0.163</t>
+        </is>
+      </c>
+      <c r="G208" s="138" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="H208" s="138" t="inlineStr">
+        <is>
+          <t>-0.0000</t>
+        </is>
+      </c>
+      <c r="I208" s="138" t="inlineStr">
+        <is>
+          <t>0.1625</t>
+        </is>
+      </c>
+      <c r="J208" s="138" t="inlineStr">
+        <is>
+          <t>🔴不动</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" s="138" t="inlineStr">
+        <is>
+          <t>公式说明</t>
+        </is>
+      </c>
+      <c r="B210" s="138" t="inlineStr">
+        <is>
+          <t>R = P/(1-P) — 纯P值转换，无拍脑袋参数。PE百分位数据补齐后可加PE修正乘子</t>
+        </is>
+      </c>
+      <c r="C210" s="138" t="inlineStr">
+        <is>
+          <t>Score = P×R - α×w×(1-P)，α=1.0。Score&gt;0表示比持有现金好</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" s="138" t="inlineStr">
+        <is>
+          <t>R值校准说明（2026-06-06 小龙虾审核通过）</t>
+        </is>
+      </c>
+      <c r="B211" s="138" t="inlineStr">
+        <is>
+          <t>用电池P=67%→R≈2.0校准k=1.0。当前无PE百分位数据，R完全由P驱动。未来加PE折扣=min(1,中位PE/当前PE)</t>
         </is>
       </c>
     </row>
@@ -11340,16 +11904,16 @@
   </cols>
   <sheetData>
     <row r="1" ht="17.25" customHeight="1" s="139">
-      <c r="A1" s="214" t="inlineStr">
-        <is>
-          <t>机会成本比较 边际量排序（含现金锁定机制 v2）</t>
+      <c r="A1" s="280" t="inlineStr">
+        <is>
+          <t>📊 机会成本排序表 R=P/(1-P) 2026-06-06</t>
         </is>
       </c>
     </row>
     <row r="2" ht="15" customHeight="1" s="139">
       <c r="A2" s="154" t="inlineStr">
         <is>
-          <t>🔒 现金锁定系数 = 达利欧概率(70%) × 三源互锁确认(强) × 时间权重(5/12月) ≈ 0.65 → 65%现金锁定等11月，仅35%可投资金可用</t>
+          <t>审核: 2026-06-06 小龙虾多轮审核 | R=P/(1-P) 纯P值转换 | 芯片宏观降权 | 信源门控已嵌入</t>
         </is>
       </c>
       <c r="B2" s="236" t="n"/>
@@ -11367,29 +11931,164 @@
       <c r="N2" s="236" t="n"/>
     </row>
     <row r="3" ht="15" customHeight="1" s="139">
-      <c r="A3" s="237" t="inlineStr">
-        <is>
-          <t>折后仓位 = 原目标仓位 × (1-现金锁定系数) | 例：长电原37%×35%=13% | 已持仓不受影响 | 解锁条件：三源信号任一落地</t>
-        </is>
-      </c>
-      <c r="B3" s="238" t="n"/>
-      <c r="C3" s="238" t="n"/>
-      <c r="D3" s="238" t="n"/>
-      <c r="E3" s="238" t="n"/>
-      <c r="F3" s="238" t="n"/>
-      <c r="G3" s="238" t="n"/>
-      <c r="H3" s="238" t="n"/>
-      <c r="I3" s="238" t="n"/>
-      <c r="J3" s="238" t="n"/>
-      <c r="K3" s="238" t="n"/>
+      <c r="A3" s="317" t="inlineStr">
+        <is>
+          <t>排名</t>
+        </is>
+      </c>
+      <c r="B3" s="318" t="inlineStr">
+        <is>
+          <t>选项</t>
+        </is>
+      </c>
+      <c r="C3" s="318" t="inlineStr">
+        <is>
+          <t>代码</t>
+        </is>
+      </c>
+      <c r="D3" s="318" t="inlineStr">
+        <is>
+          <t>类型</t>
+        </is>
+      </c>
+      <c r="E3" s="318" t="inlineStr">
+        <is>
+          <t>有效P</t>
+        </is>
+      </c>
+      <c r="F3" s="318" t="inlineStr">
+        <is>
+          <t>R=P/(1-P)</t>
+        </is>
+      </c>
+      <c r="G3" s="318" t="inlineStr">
+        <is>
+          <t>EV(P×R)</t>
+        </is>
+      </c>
+      <c r="H3" s="318" t="inlineStr">
+        <is>
+          <t>仓位w</t>
+        </is>
+      </c>
+      <c r="I3" s="318" t="inlineStr">
+        <is>
+          <t>Score</t>
+        </is>
+      </c>
+      <c r="J3" s="318" t="inlineStr">
+        <is>
+          <t>EV分级</t>
+        </is>
+      </c>
+      <c r="K3" s="318" t="inlineStr">
+        <is>
+          <t>信号</t>
+        </is>
+      </c>
       <c r="L3" s="238" t="n"/>
       <c r="M3" s="238" t="n"/>
       <c r="N3" s="238" t="n"/>
     </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>1</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>电池009759</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>009759</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>持仓</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>67%</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>2.03:1</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>15%</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>正期望</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>🟢优先</t>
+        </is>
+      </c>
+    </row>
     <row r="5" ht="16.5" customHeight="1" s="139">
-      <c r="A5" s="294" t="inlineStr">
-        <is>
-          <t>机会成本排序表 EV阈值分级 v3 (2026-06-06)</t>
+      <c r="A5" s="294" t="n">
+        <v>2</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>原油162411</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>162411</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>待重</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>60%</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>1.50:1</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>弱正期望</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>🟡观察</t>
         </is>
       </c>
       <c r="L5" s="295" t="n"/>
@@ -11397,9 +12096,53 @@
       <c r="N5" s="296" t="n"/>
     </row>
     <row r="6" ht="48" customHeight="1" s="139">
-      <c r="A6" s="297" t="inlineStr">
-        <is>
-          <t>审核: 2026-06-06 | R=(确定性+溢价x梯度打折)/下行 | 梯度打折&lt;60%=(有效P-30)/60</t>
+      <c r="A6" s="297" t="n">
+        <v>3</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>养殖008765</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>008765</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>持仓</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>56%</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>1.27:1</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>5%</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>弱正期望</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>🟡观察</t>
         </is>
       </c>
       <c r="L6" s="295" t="n"/>
@@ -11407,9 +12150,53 @@
       <c r="N6" s="299" t="n"/>
     </row>
     <row r="7" ht="32.25" customHeight="1" s="139">
-      <c r="A7" s="300" t="inlineStr">
-        <is>
-          <t>EV分级: &gt;1.0正期望 | 0.5-1.0弱正期望 | &lt;0.5负期望 | 现金锁定65%</t>
+      <c r="A7" s="300" t="n">
+        <v>4</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>存储赛道</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>待重</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>51%</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>1.04:1</t>
+        </is>
+      </c>
+      <c r="G7" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>弱正期望</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>🟡观察</t>
         </is>
       </c>
       <c r="L7" s="295" t="n"/>
@@ -11417,59 +12204,53 @@
       <c r="N7" s="299" t="n"/>
     </row>
     <row r="8" ht="32.25" customHeight="1" s="139">
-      <c r="A8" s="283" t="inlineStr">
-        <is>
-          <t>排名</t>
-        </is>
+      <c r="A8" s="283" t="n">
+        <v>5</v>
       </c>
       <c r="B8" s="283" t="inlineStr">
         <is>
-          <t>选项</t>
+          <t>核电赛道</t>
         </is>
       </c>
       <c r="C8" s="283" t="inlineStr">
         <is>
-          <t>代码</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D8" s="283" t="inlineStr">
         <is>
-          <t>类型</t>
+          <t>待重</t>
         </is>
       </c>
       <c r="E8" s="283" t="inlineStr">
         <is>
-          <t>有效P</t>
+          <t>50%</t>
         </is>
       </c>
       <c r="F8" s="283" t="inlineStr">
         <is>
-          <t>盈亏比R</t>
-        </is>
-      </c>
-      <c r="G8" s="283" t="inlineStr">
-        <is>
-          <t>EV(PxR)</t>
-        </is>
+          <t>1.00:1</t>
+        </is>
+      </c>
+      <c r="G8" s="283" t="n">
+        <v>0.5</v>
       </c>
       <c r="H8" s="283" t="inlineStr">
         <is>
-          <t>仓位w</t>
-        </is>
-      </c>
-      <c r="I8" s="283" t="inlineStr">
-        <is>
-          <t>Score</t>
-        </is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="I8" s="283" t="n">
+        <v>0.5</v>
       </c>
       <c r="J8" s="283" t="inlineStr">
         <is>
-          <t>EV分级</t>
+          <t>负期望</t>
         </is>
       </c>
       <c r="K8" s="283" t="inlineStr">
         <is>
-          <t>建议</t>
+          <t>🔴不动</t>
         </is>
       </c>
       <c r="L8" s="301" t="n"/>
@@ -11478,16 +12259,16 @@
     </row>
     <row r="9" ht="32.25" customHeight="1" s="139">
       <c r="A9" s="286" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="B9" s="287" t="inlineStr">
         <is>
-          <t>养殖008765(008765)</t>
+          <t>芯片020628</t>
         </is>
       </c>
       <c r="C9" s="287" t="inlineStr">
         <is>
-          <t>008765</t>
+          <t>020628</t>
         </is>
       </c>
       <c r="D9" s="287" t="inlineStr">
@@ -11497,33 +12278,33 @@
       </c>
       <c r="E9" s="287" t="inlineStr">
         <is>
-          <t>56%</t>
+          <t>48%</t>
         </is>
       </c>
       <c r="F9" s="287" t="inlineStr">
         <is>
-          <t>%.2f:1</t>
+          <t>0.92:1</t>
         </is>
       </c>
       <c r="G9" s="287" t="n">
-        <v>1.53</v>
+        <v>0.44</v>
       </c>
       <c r="H9" s="287" t="inlineStr">
         <is>
-          <t>5%</t>
+          <t>8%</t>
         </is>
       </c>
       <c r="I9" s="287" t="n">
-        <v>1.51</v>
+        <v>0.4</v>
       </c>
       <c r="J9" s="286" t="inlineStr">
         <is>
-          <t>正期望</t>
+          <t>负期望</t>
         </is>
       </c>
       <c r="K9" s="287" t="inlineStr">
         <is>
-          <t>持有+可加仓</t>
+          <t>🔴不动</t>
         </is>
       </c>
       <c r="L9" s="302" t="n"/>
@@ -11532,16 +12313,16 @@
     </row>
     <row r="10" ht="32.25" customHeight="1" s="139">
       <c r="A10" s="286" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="B10" s="287" t="inlineStr">
         <is>
-          <t>电池009759(009759)</t>
+          <t>银行001595</t>
         </is>
       </c>
       <c r="C10" s="287" t="inlineStr">
         <is>
-          <t>009759</t>
+          <t>001595</t>
         </is>
       </c>
       <c r="D10" s="287" t="inlineStr">
@@ -11551,33 +12332,33 @@
       </c>
       <c r="E10" s="287" t="inlineStr">
         <is>
-          <t>67%</t>
+          <t>44%</t>
         </is>
       </c>
       <c r="F10" s="287" t="inlineStr">
         <is>
-          <t>%.2f:1</t>
+          <t>0.79:1</t>
         </is>
       </c>
       <c r="G10" s="287" t="n">
-        <v>1.51</v>
+        <v>0.35</v>
       </c>
       <c r="H10" s="287" t="inlineStr">
         <is>
-          <t>15%</t>
+          <t>2%</t>
         </is>
       </c>
       <c r="I10" s="287" t="n">
-        <v>1.46</v>
+        <v>0.33</v>
       </c>
       <c r="J10" s="286" t="inlineStr">
         <is>
-          <t>正期望</t>
+          <t>负期望</t>
         </is>
       </c>
       <c r="K10" s="287" t="inlineStr">
         <is>
-          <t>持有+可加仓</t>
+          <t>🔴不动</t>
         </is>
       </c>
       <c r="L10" s="302" t="n"/>
@@ -11586,52 +12367,52 @@
     </row>
     <row r="11" ht="32.25" customHeight="1" s="139">
       <c r="A11" s="286" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="B11" s="287" t="inlineStr">
         <is>
-          <t>核电赛道(-)</t>
+          <t>稀金008907</t>
         </is>
       </c>
       <c r="C11" s="287" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>008907</t>
         </is>
       </c>
       <c r="D11" s="287" t="inlineStr">
         <is>
-          <t>待重</t>
+          <t>持仓</t>
         </is>
       </c>
       <c r="E11" s="287" t="inlineStr">
         <is>
-          <t>50%</t>
+          <t>41%</t>
         </is>
       </c>
       <c r="F11" s="287" t="inlineStr">
         <is>
-          <t>%.2f:1</t>
+          <t>0.69:1</t>
         </is>
       </c>
       <c r="G11" s="287" t="n">
-        <v>1.22</v>
+        <v>0.28</v>
       </c>
       <c r="H11" s="287" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>3%</t>
         </is>
       </c>
       <c r="I11" s="287" t="n">
-        <v>1.22</v>
+        <v>0.27</v>
       </c>
       <c r="J11" s="286" t="inlineStr">
         <is>
-          <t>正期望</t>
+          <t>负期望</t>
         </is>
       </c>
       <c r="K11" s="287" t="inlineStr">
         <is>
-          <t>重点研究+准备建仓</t>
+          <t>🔴不动</t>
         </is>
       </c>
       <c r="L11" s="302" t="n"/>
@@ -11640,52 +12421,52 @@
     </row>
     <row r="12" ht="32.25" customHeight="1" s="139">
       <c r="A12" s="286" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="B12" s="287" t="inlineStr">
         <is>
-          <t>存储赛道(-)</t>
+          <t>有色008826</t>
         </is>
       </c>
       <c r="C12" s="287" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>008826</t>
         </is>
       </c>
       <c r="D12" s="287" t="inlineStr">
         <is>
-          <t>待重</t>
+          <t>持仓</t>
         </is>
       </c>
       <c r="E12" s="287" t="inlineStr">
         <is>
-          <t>51%</t>
+          <t>39%</t>
         </is>
       </c>
       <c r="F12" s="287" t="inlineStr">
         <is>
-          <t>%.2f:1</t>
+          <t>0.64:1</t>
         </is>
       </c>
       <c r="G12" s="287" t="n">
-        <v>1.04</v>
+        <v>0.25</v>
       </c>
       <c r="H12" s="287" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="I12" s="287" t="n">
-        <v>1.04</v>
+        <v>0.22</v>
       </c>
       <c r="J12" s="286" t="inlineStr">
         <is>
-          <t>正期望</t>
+          <t>负期望</t>
         </is>
       </c>
       <c r="K12" s="287" t="inlineStr">
         <is>
-          <t>重点研究+准备建仓</t>
+          <t>🔴不动</t>
         </is>
       </c>
       <c r="L12" s="302" t="n"/>
@@ -11694,52 +12475,52 @@
     </row>
     <row r="13" ht="32.25" customHeight="1" s="139">
       <c r="A13" s="284" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="B13" s="285" t="inlineStr">
         <is>
-          <t>原油162411(162411)</t>
+          <t>恒科009854</t>
         </is>
       </c>
       <c r="C13" s="285" t="inlineStr">
         <is>
-          <t>162411</t>
+          <t>009854</t>
         </is>
       </c>
       <c r="D13" s="285" t="inlineStr">
         <is>
-          <t>待重</t>
+          <t>持仓</t>
         </is>
       </c>
       <c r="E13" s="285" t="inlineStr">
         <is>
-          <t>60%</t>
+          <t>33%</t>
         </is>
       </c>
       <c r="F13" s="285" t="inlineStr">
         <is>
-          <t>%.2f:1</t>
+          <t>0.49:1</t>
         </is>
       </c>
       <c r="G13" s="285" t="n">
-        <v>0.96</v>
+        <v>0.16</v>
       </c>
       <c r="H13" s="285" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>6%</t>
         </is>
       </c>
       <c r="I13" s="285" t="n">
-        <v>0.96</v>
+        <v>0.12</v>
       </c>
       <c r="J13" s="284" t="inlineStr">
         <is>
-          <t>弱正期望</t>
+          <t>负期望</t>
         </is>
       </c>
       <c r="K13" s="285" t="inlineStr">
         <is>
-          <t>密切跟踪</t>
+          <t>🔴不动</t>
         </is>
       </c>
       <c r="L13" s="302" t="n"/>
@@ -11747,325 +12528,121 @@
       <c r="N13" s="299" t="n"/>
     </row>
     <row r="14" ht="32.25" customHeight="1" s="139">
-      <c r="A14" s="284" t="n">
-        <v>6</v>
-      </c>
-      <c r="B14" s="285" t="inlineStr">
-        <is>
-          <t>银行001595(001595)</t>
-        </is>
-      </c>
-      <c r="C14" s="285" t="inlineStr">
-        <is>
-          <t>001595</t>
-        </is>
-      </c>
-      <c r="D14" s="285" t="inlineStr">
-        <is>
-          <t>持仓</t>
-        </is>
-      </c>
-      <c r="E14" s="285" t="inlineStr">
-        <is>
-          <t>44%</t>
-        </is>
-      </c>
-      <c r="F14" s="285" t="inlineStr">
-        <is>
-          <t>%.2f:1</t>
-        </is>
-      </c>
-      <c r="G14" s="285" t="n">
-        <v>0.79</v>
-      </c>
-      <c r="H14" s="285" t="inlineStr">
-        <is>
-          <t>2%</t>
-        </is>
-      </c>
-      <c r="I14" s="285" t="n">
-        <v>0.78</v>
-      </c>
-      <c r="J14" s="284" t="inlineStr">
-        <is>
-          <t>弱正期望</t>
-        </is>
-      </c>
-      <c r="K14" s="285" t="inlineStr">
-        <is>
-          <t>密切跟踪</t>
-        </is>
-      </c>
+      <c r="A14" s="284" t="n"/>
+      <c r="B14" s="285" t="n"/>
+      <c r="C14" s="285" t="n"/>
+      <c r="D14" s="285" t="n"/>
+      <c r="E14" s="285" t="n"/>
+      <c r="F14" s="285" t="n"/>
+      <c r="G14" s="285" t="n"/>
+      <c r="H14" s="285" t="n"/>
+      <c r="I14" s="285" t="n"/>
+      <c r="J14" s="284" t="n"/>
+      <c r="K14" s="285" t="n"/>
       <c r="L14" s="302" t="n"/>
       <c r="M14" s="298" t="n"/>
       <c r="N14" s="299" t="n"/>
     </row>
     <row r="15" ht="32.25" customHeight="1" s="139">
-      <c r="A15" s="284" t="n">
-        <v>7</v>
-      </c>
+      <c r="A15" s="284" t="n"/>
       <c r="B15" s="285" t="inlineStr">
         <is>
-          <t>稀金008907(008907)</t>
-        </is>
-      </c>
-      <c r="C15" s="285" t="inlineStr">
-        <is>
-          <t>008907</t>
-        </is>
-      </c>
-      <c r="D15" s="285" t="inlineStr">
-        <is>
-          <t>持仓</t>
-        </is>
-      </c>
-      <c r="E15" s="285" t="inlineStr">
-        <is>
-          <t>41%</t>
-        </is>
-      </c>
-      <c r="F15" s="285" t="inlineStr">
-        <is>
-          <t>%.2f:1</t>
-        </is>
-      </c>
+          <t>现金（基准）</t>
+        </is>
+      </c>
+      <c r="C15" s="285" t="n"/>
+      <c r="D15" s="285" t="n"/>
+      <c r="E15" s="285" t="n"/>
+      <c r="F15" s="285" t="n"/>
       <c r="G15" s="285" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="H15" s="285" t="inlineStr">
-        <is>
-          <t>3%</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="H15" s="285" t="n"/>
       <c r="I15" s="285" t="n">
-        <v>0.62</v>
+        <v>0</v>
       </c>
       <c r="J15" s="284" t="inlineStr">
         <is>
-          <t>弱正期望</t>
-        </is>
-      </c>
-      <c r="K15" s="285" t="inlineStr">
-        <is>
-          <t>密切跟踪</t>
-        </is>
-      </c>
+          <t>基准</t>
+        </is>
+      </c>
+      <c r="K15" s="285" t="n"/>
       <c r="L15" s="302" t="n"/>
       <c r="M15" s="298" t="n"/>
       <c r="N15" s="299" t="n"/>
     </row>
     <row r="16" ht="32.25" customHeight="1" s="139">
-      <c r="A16" s="284" t="n">
-        <v>8</v>
-      </c>
-      <c r="B16" s="285" t="inlineStr">
-        <is>
-          <t>有色008826(008826)</t>
-        </is>
-      </c>
-      <c r="C16" s="285" t="inlineStr">
-        <is>
-          <t>008826</t>
-        </is>
-      </c>
-      <c r="D16" s="285" t="inlineStr">
-        <is>
-          <t>持仓</t>
-        </is>
-      </c>
-      <c r="E16" s="285" t="inlineStr">
-        <is>
-          <t>39%</t>
-        </is>
-      </c>
-      <c r="F16" s="285" t="inlineStr">
-        <is>
-          <t>%.2f:1</t>
-        </is>
-      </c>
-      <c r="G16" s="285" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="H16" s="285" t="inlineStr">
-        <is>
-          <t>4%</t>
-        </is>
-      </c>
-      <c r="I16" s="285" t="n">
-        <v>0.62</v>
-      </c>
-      <c r="J16" s="284" t="inlineStr">
-        <is>
-          <t>弱正期望</t>
-        </is>
-      </c>
-      <c r="K16" s="285" t="inlineStr">
-        <is>
-          <t>密切跟踪</t>
-        </is>
-      </c>
+      <c r="A16" s="284" t="n"/>
+      <c r="B16" s="285" t="n"/>
+      <c r="C16" s="285" t="n"/>
+      <c r="D16" s="285" t="n"/>
+      <c r="E16" s="285" t="n"/>
+      <c r="F16" s="285" t="n"/>
+      <c r="G16" s="285" t="n"/>
+      <c r="H16" s="285" t="n"/>
+      <c r="I16" s="285" t="n"/>
+      <c r="J16" s="284" t="n"/>
+      <c r="K16" s="285" t="n"/>
       <c r="L16" s="302" t="n"/>
       <c r="M16" s="298" t="n"/>
       <c r="N16" s="299" t="n"/>
     </row>
     <row r="17" ht="16.5" customHeight="1" s="139">
-      <c r="A17" s="284" t="n">
-        <v>9</v>
-      </c>
-      <c r="B17" s="285" t="inlineStr">
-        <is>
-          <t>芯片020628(020628)</t>
-        </is>
-      </c>
-      <c r="C17" s="285" t="inlineStr">
-        <is>
-          <t>020628</t>
-        </is>
-      </c>
-      <c r="D17" s="285" t="inlineStr">
-        <is>
-          <t>持仓</t>
-        </is>
-      </c>
-      <c r="E17" s="285" t="inlineStr">
-        <is>
-          <t>40%</t>
-        </is>
-      </c>
-      <c r="F17" s="285" t="inlineStr">
-        <is>
-          <t>%.2f:1</t>
-        </is>
-      </c>
-      <c r="G17" s="285" t="n">
-        <v>0.59</v>
-      </c>
-      <c r="H17" s="285" t="inlineStr">
-        <is>
-          <t>8%</t>
-        </is>
-      </c>
-      <c r="I17" s="285" t="n">
-        <v>0.54</v>
-      </c>
-      <c r="J17" s="284" t="inlineStr">
-        <is>
-          <t>弱正期望</t>
-        </is>
-      </c>
-      <c r="K17" s="285" t="inlineStr">
-        <is>
-          <t>密切跟踪</t>
-        </is>
-      </c>
+      <c r="A17" s="284" t="inlineStr">
+        <is>
+          <t>结论：R=P/(1-P) 纯P值转换，无拍脑袋参数</t>
+        </is>
+      </c>
+      <c r="B17" s="285" t="n"/>
+      <c r="C17" s="285" t="n"/>
+      <c r="D17" s="285" t="n"/>
+      <c r="E17" s="285" t="n"/>
+      <c r="F17" s="285" t="n"/>
+      <c r="G17" s="285" t="n"/>
+      <c r="H17" s="285" t="n"/>
+      <c r="I17" s="285" t="n"/>
+      <c r="J17" s="284" t="n"/>
+      <c r="K17" s="285" t="n"/>
       <c r="L17" s="302" t="n"/>
       <c r="M17" s="302" t="n"/>
       <c r="N17" s="302" t="n"/>
     </row>
     <row r="18" ht="16.5" customHeight="1" s="139">
-      <c r="A18" s="303" t="n">
-        <v>10</v>
-      </c>
-      <c r="B18" s="304" t="inlineStr">
-        <is>
-          <t>AI027048(027048)</t>
-        </is>
-      </c>
-      <c r="C18" s="304" t="inlineStr">
-        <is>
-          <t>027048</t>
-        </is>
-      </c>
-      <c r="D18" s="304" t="inlineStr">
-        <is>
-          <t>持仓</t>
-        </is>
-      </c>
-      <c r="E18" s="304" t="inlineStr">
-        <is>
-          <t>51%</t>
-        </is>
-      </c>
-      <c r="F18" s="304" t="inlineStr">
-        <is>
-          <t>%.2f:1</t>
-        </is>
-      </c>
-      <c r="G18" s="304" t="n">
-        <v>0.37</v>
-      </c>
-      <c r="H18" s="304" t="inlineStr">
-        <is>
-          <t>1%</t>
-        </is>
-      </c>
-      <c r="I18" s="304" t="n">
-        <v>0.37</v>
-      </c>
-      <c r="J18" s="303" t="inlineStr">
-        <is>
-          <t>负期望</t>
-        </is>
-      </c>
-      <c r="K18" s="304" t="inlineStr">
-        <is>
-          <t>不碰</t>
-        </is>
-      </c>
+      <c r="A18" s="303" t="inlineStr">
+        <is>
+          <t>正期望: 电池(67%,R=2.03) &gt; 养殖(56%,R=1.27) &gt; 存储(51%,R=1.04) &gt; 核电(50%,R=1.00)</t>
+        </is>
+      </c>
+      <c r="B18" s="304" t="n"/>
+      <c r="C18" s="304" t="n"/>
+      <c r="D18" s="304" t="n"/>
+      <c r="E18" s="304" t="n"/>
+      <c r="F18" s="304" t="n"/>
+      <c r="G18" s="304" t="n"/>
+      <c r="H18" s="304" t="n"/>
+      <c r="I18" s="304" t="n"/>
+      <c r="J18" s="303" t="n"/>
+      <c r="K18" s="304" t="n"/>
       <c r="L18" s="302" t="n"/>
       <c r="M18" s="302" t="n"/>
       <c r="N18" s="302" t="n"/>
     </row>
     <row r="19" ht="32.8" customHeight="1" s="139">
-      <c r="A19" s="303" t="n">
-        <v>11</v>
-      </c>
-      <c r="B19" s="304" t="inlineStr">
-        <is>
-          <t>恒科009854(009854)</t>
-        </is>
-      </c>
-      <c r="C19" s="304" t="inlineStr">
-        <is>
-          <t>009854</t>
-        </is>
-      </c>
-      <c r="D19" s="304" t="inlineStr">
-        <is>
-          <t>持仓</t>
-        </is>
-      </c>
-      <c r="E19" s="304" t="inlineStr">
-        <is>
-          <t>33%</t>
-        </is>
-      </c>
-      <c r="F19" s="304" t="inlineStr">
-        <is>
-          <t>%.2f:1</t>
-        </is>
-      </c>
-      <c r="G19" s="304" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="H19" s="304" t="inlineStr">
-        <is>
-          <t>6%</t>
-        </is>
-      </c>
-      <c r="I19" s="304" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="J19" s="303" t="inlineStr">
-        <is>
-          <t>负期望</t>
-        </is>
-      </c>
-      <c r="K19" s="304" t="inlineStr">
-        <is>
-          <t>不碰</t>
-        </is>
-      </c>
+      <c r="A19" s="303" t="inlineStr">
+        <is>
+          <t>弱正期望: 原油(60%,R=1.50) &gt; 银行(44%,R=0.79) &gt; 稀金(41%,R=0.69) &gt; 有色(39%,R=0.64)</t>
+        </is>
+      </c>
+      <c r="B19" s="304" t="n"/>
+      <c r="C19" s="304" t="n"/>
+      <c r="D19" s="304" t="n"/>
+      <c r="E19" s="304" t="n"/>
+      <c r="F19" s="304" t="n"/>
+      <c r="G19" s="304" t="n"/>
+      <c r="H19" s="304" t="n"/>
+      <c r="I19" s="304" t="n"/>
+      <c r="J19" s="303" t="n"/>
+      <c r="K19" s="304" t="n"/>
       <c r="L19" s="302" t="n"/>
       <c r="M19" s="302" t="n"/>
       <c r="N19" s="302" t="n"/>
@@ -12073,45 +12650,29 @@
     <row r="20" ht="15" customHeight="1" s="139">
       <c r="A20" s="288" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="B20" s="289" t="inlineStr">
-        <is>
-          <t>现金</t>
-        </is>
-      </c>
-      <c r="C20" s="289" t="inlineStr"/>
-      <c r="D20" s="289" t="inlineStr"/>
-      <c r="E20" s="289" t="inlineStr"/>
-      <c r="F20" s="289" t="inlineStr"/>
-      <c r="G20" s="289" t="n">
-        <v>0</v>
-      </c>
-      <c r="H20" s="289" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I20" s="289" t="n">
-        <v>0</v>
-      </c>
-      <c r="J20" s="288" t="inlineStr">
-        <is>
-          <t>基准</t>
-        </is>
-      </c>
-      <c r="K20" s="289" t="inlineStr">
-        <is>
-          <t>Score=0</t>
-        </is>
-      </c>
+          <t>芯片从40%→48%（宏观降权），R从0.67→0.92，接近盈亏平衡</t>
+        </is>
+      </c>
+      <c r="B20" s="289" t="n"/>
+      <c r="C20" s="289" t="n"/>
+      <c r="D20" s="289" t="n"/>
+      <c r="E20" s="289" t="n"/>
+      <c r="F20" s="289" t="n"/>
+      <c r="G20" s="289" t="n"/>
+      <c r="H20" s="289" t="n"/>
+      <c r="I20" s="289" t="n"/>
+      <c r="J20" s="288" t="n"/>
+      <c r="K20" s="289" t="n"/>
       <c r="L20" s="302" t="n"/>
       <c r="M20" s="302" t="n"/>
       <c r="N20" s="302" t="n"/>
     </row>
     <row r="21" ht="16.5" customHeight="1" s="139">
-      <c r="A21" s="302" t="n"/>
+      <c r="A21" s="302" t="inlineStr">
+        <is>
+          <t>恒科33% R=0.49 负期望，不碰</t>
+        </is>
+      </c>
       <c r="B21" s="302" t="n"/>
       <c r="C21" s="302" t="n"/>
       <c r="D21" s="302" t="n"/>
@@ -12127,21 +12688,13 @@
       <c r="N21" s="302" t="n"/>
     </row>
     <row r="22" ht="16.5" customHeight="1" s="139">
-      <c r="A22" s="305" t="inlineStr">
-        <is>
-          <t>结论：现金分配建议</t>
-        </is>
-      </c>
+      <c r="A22" s="305" t="n"/>
       <c r="L22" s="295" t="n"/>
       <c r="M22" s="295" t="n"/>
       <c r="N22" s="295" t="n"/>
     </row>
     <row r="23" ht="16.5" customHeight="1" s="139">
-      <c r="A23" s="306" t="inlineStr">
-        <is>
-          <t>正期望EV&gt;1.0 (4个):</t>
-        </is>
-      </c>
+      <c r="A23" s="306" t="n"/>
       <c r="B23" s="295" t="n"/>
       <c r="C23" s="295" t="n"/>
       <c r="D23" s="295" t="n"/>
@@ -12157,11 +12710,7 @@
       <c r="N23" s="295" t="n"/>
     </row>
     <row r="24" ht="16.5" customHeight="1" s="139">
-      <c r="A24" s="307" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  养殖008765 P=56% R=2.73:1 EV=1.53 仓位5%</t>
-        </is>
-      </c>
+      <c r="A24" s="307" t="n"/>
       <c r="B24" s="295" t="n"/>
       <c r="C24" s="295" t="n"/>
       <c r="D24" s="295" t="n"/>
@@ -12177,11 +12726,7 @@
       <c r="N24" s="295" t="n"/>
     </row>
     <row r="25" ht="17.15" customHeight="1" s="139">
-      <c r="A25" s="307" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  电池009759 P=67% R=2.25:1 EV=1.51 仓位15%</t>
-        </is>
-      </c>
+      <c r="A25" s="307" t="n"/>
       <c r="B25" s="295" t="n"/>
       <c r="C25" s="295" t="n"/>
       <c r="D25" s="295" t="n"/>
@@ -12197,11 +12742,7 @@
       <c r="N25" s="295" t="n"/>
     </row>
     <row r="26" ht="15" customHeight="1" s="139">
-      <c r="A26" s="307" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  核电赛道 P=50% R=2.44:1 EV=1.22 仓位0%</t>
-        </is>
-      </c>
+      <c r="A26" s="307" t="n"/>
       <c r="B26" s="295" t="n"/>
       <c r="C26" s="295" t="n"/>
       <c r="D26" s="295" t="n"/>
@@ -12217,11 +12758,7 @@
       <c r="N26" s="295" t="n"/>
     </row>
     <row r="27" ht="16.5" customHeight="1" s="139">
-      <c r="A27" s="307" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  存储赛道 P=51% R=2.03:1 EV=1.04 仓位0%</t>
-        </is>
-      </c>
+      <c r="A27" s="307" t="n"/>
       <c r="B27" s="295" t="n"/>
       <c r="C27" s="295" t="n"/>
       <c r="D27" s="295" t="n"/>
@@ -12237,11 +12774,7 @@
       <c r="N27" s="295" t="n"/>
     </row>
     <row r="28" ht="16.5" customHeight="1" s="139">
-      <c r="A28" s="308" t="inlineStr">
-        <is>
-          <t>弱正期望0.5&lt;EV&lt;=1.0 (5个):</t>
-        </is>
-      </c>
+      <c r="A28" s="308" t="n"/>
       <c r="B28" s="295" t="n"/>
       <c r="C28" s="295" t="n"/>
       <c r="D28" s="295" t="n"/>
@@ -12257,11 +12790,7 @@
       <c r="N28" s="295" t="n"/>
     </row>
     <row r="29" ht="15" customHeight="1" s="139">
-      <c r="A29" s="307" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  原油162411 P=60% R=1.60:1 EV=0.96</t>
-        </is>
-      </c>
+      <c r="A29" s="307" t="n"/>
       <c r="B29" s="295" t="n"/>
       <c r="C29" s="295" t="n"/>
       <c r="D29" s="295" t="n"/>
@@ -12277,11 +12806,7 @@
       <c r="N29" s="295" t="n"/>
     </row>
     <row r="30" ht="16.5" customHeight="1" s="139">
-      <c r="A30" s="308" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  银行001595 P=44% R=1.80:1 EV=0.79</t>
-        </is>
-      </c>
+      <c r="A30" s="308" t="n"/>
       <c r="B30" s="295" t="n"/>
       <c r="C30" s="295" t="n"/>
       <c r="D30" s="295" t="n"/>
@@ -12297,11 +12822,7 @@
       <c r="N30" s="295" t="n"/>
     </row>
     <row r="31" ht="17.15" customHeight="1" s="139">
-      <c r="A31" s="308" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  稀金008907 P=41% R=1.57:1 EV=0.64</t>
-        </is>
-      </c>
+      <c r="A31" s="308" t="n"/>
       <c r="B31" s="295" t="n"/>
       <c r="C31" s="295" t="n"/>
       <c r="D31" s="295" t="n"/>
@@ -12317,11 +12838,7 @@
       <c r="N31" s="295" t="n"/>
     </row>
     <row r="32" ht="15" customHeight="1" s="139">
-      <c r="A32" s="295" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  有色008826 P=39% R=1.63:1 EV=0.64</t>
-        </is>
-      </c>
+      <c r="A32" s="295" t="n"/>
       <c r="B32" s="295" t="n"/>
       <c r="C32" s="295" t="n"/>
       <c r="D32" s="295" t="n"/>
@@ -12337,11 +12854,7 @@
       <c r="N32" s="295" t="n"/>
     </row>
     <row r="33" ht="15" customHeight="1" s="139">
-      <c r="A33" s="307" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  芯片020628 P=40% R=1.47:1 EV=0.59</t>
-        </is>
-      </c>
+      <c r="A33" s="307" t="n"/>
       <c r="B33" s="295" t="n"/>
       <c r="C33" s="295" t="n"/>
       <c r="D33" s="295" t="n"/>
@@ -12373,11 +12886,7 @@
       <c r="N34" s="295" t="n"/>
     </row>
     <row r="35" ht="15" customHeight="1" s="139">
-      <c r="A35" s="307" t="inlineStr">
-        <is>
-          <t>现金65%锁定 | 35%可配: 养殖(15%) 电池(10%) 核电/存储(各5%待建仓)</t>
-        </is>
-      </c>
+      <c r="A35" s="307" t="n"/>
       <c r="B35" s="295" t="n"/>
       <c r="C35" s="295" t="n"/>
       <c r="D35" s="295" t="n"/>
@@ -12393,11 +12902,7 @@
       <c r="N35" s="295" t="n"/>
     </row>
     <row r="36" ht="15" customHeight="1" s="139">
-      <c r="A36" s="309" t="inlineStr">
-        <is>
-          <t>注意: 芯片信源Spearman=-0.676需替换，当前P值可靠性存疑</t>
-        </is>
-      </c>
+      <c r="A36" s="309" t="n"/>
       <c r="B36" s="295" t="n"/>
       <c r="C36" s="295" t="n"/>
       <c r="D36" s="295" t="n"/>
@@ -12781,12 +13286,6 @@
       <c r="N59" s="295" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="4">
-    <mergeCell ref="A6:K6"/>
-    <mergeCell ref="A22:K22"/>
-    <mergeCell ref="A5:K5"/>
-    <mergeCell ref="A7:K7"/>
-  </mergeCells>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>

--- a/持仓贝叶斯跟踪.xlsx
+++ b/持仓贝叶斯跟踪.xlsx
@@ -27,7 +27,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="58">
+  <fonts count="59">
     <font>
       <name val="Calibri"/>
       <charset val="1"/>
@@ -403,8 +403,9 @@
     <font>
       <b val="1"/>
     </font>
+    <font/>
   </fonts>
-  <fills count="31">
+  <fills count="32">
     <fill>
       <patternFill/>
     </fill>
@@ -585,6 +586,12 @@
         <bgColor rgb="00FFEB9C"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D9E2F3"/>
+        <bgColor rgb="00D9E2F3"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="8">
     <border>
@@ -647,7 +654,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="319">
+  <cellXfs count="324">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -1569,6 +1576,17 @@
     <xf numFmtId="0" fontId="57" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
+    <xf numFmtId="0" fontId="56" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="57" fillId="31" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="31" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="58" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="58" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -7241,7 +7259,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:L211"/>
+  <dimension ref="A1:L219"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="10.4921875" defaultRowHeight="12.75" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="18" customWidth="1" style="138" min="1" max="12"/>
@@ -11812,6 +11830,48 @@
       <c r="B211" s="138" t="inlineStr">
         <is>
           <t>用电池P=67%→R≈2.0校准k=1.0。当前无PE百分位数据，R完全由P驱动。未来加PE折扣=min(1,中位PE/当前PE)</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" s="293" t="inlineStr">
+        <is>
+          <t>📌 MLCC机会评估（2026-06-06）</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>结论：MLCC &lt; 芯片堆叠，差距不在一个量级</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>MLCC是被动元件，标准化高、竞争分散、毛利率一般。AI服务器用量×3-5倍是利好，但属于被动受益。</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>芯片堆叠是AI核心瓶颈，不可替代性极高，全球就长电/通富/台积电几家能做。</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>现金有限→优先堆叠。MLCC可关注（风华高科/三环集团），但不值得重仓。</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>P值预估：MLCC约45-50%（逻辑偏泛），芯片堆叠75%（逻辑硬）。差距明显。</t>
         </is>
       </c>
     </row>
@@ -11991,51 +12051,51 @@
       <c r="N3" s="238" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" t="n">
+      <c r="A4" s="138" t="n">
         <v>1</v>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B4" s="138" t="inlineStr">
         <is>
           <t>电池009759</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C4" s="138" t="inlineStr">
         <is>
           <t>009759</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="D4" s="138" t="inlineStr">
         <is>
           <t>持仓</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="E4" s="138" t="inlineStr">
         <is>
           <t>67%</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="F4" s="138" t="inlineStr">
         <is>
           <t>2.03:1</t>
         </is>
       </c>
-      <c r="G4" t="n">
+      <c r="G4" s="138" t="n">
         <v>1.36</v>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="H4" s="138" t="inlineStr">
         <is>
           <t>15%</t>
         </is>
       </c>
-      <c r="I4" t="n">
+      <c r="I4" s="138" t="n">
         <v>1.31</v>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="J4" s="138" t="inlineStr">
         <is>
           <t>正期望</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="K4" s="138" t="inlineStr">
         <is>
           <t>🟢优先</t>
         </is>
@@ -12045,48 +12105,48 @@
       <c r="A5" s="294" t="n">
         <v>2</v>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B5" s="138" t="inlineStr">
         <is>
           <t>原油162411</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C5" s="138" t="inlineStr">
         <is>
           <t>162411</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D5" s="138" t="inlineStr">
         <is>
           <t>待重</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E5" s="138" t="inlineStr">
         <is>
           <t>60%</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="F5" s="138" t="inlineStr">
         <is>
           <t>1.50:1</t>
         </is>
       </c>
-      <c r="G5" t="n">
+      <c r="G5" s="138" t="n">
         <v>0.9</v>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="H5" s="138" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="I5" t="n">
+      <c r="I5" s="138" t="n">
         <v>0.9</v>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="J5" s="138" t="inlineStr">
         <is>
           <t>弱正期望</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="K5" s="138" t="inlineStr">
         <is>
           <t>🟡观察</t>
         </is>
@@ -12099,48 +12159,48 @@
       <c r="A6" s="297" t="n">
         <v>3</v>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B6" s="138" t="inlineStr">
         <is>
           <t>养殖008765</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C6" s="138" t="inlineStr">
         <is>
           <t>008765</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="D6" s="138" t="inlineStr">
         <is>
           <t>持仓</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="E6" s="138" t="inlineStr">
         <is>
           <t>56%</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="F6" s="138" t="inlineStr">
         <is>
           <t>1.27:1</t>
         </is>
       </c>
-      <c r="G6" t="n">
+      <c r="G6" s="138" t="n">
         <v>0.71</v>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="H6" s="138" t="inlineStr">
         <is>
           <t>5%</t>
         </is>
       </c>
-      <c r="I6" t="n">
+      <c r="I6" s="138" t="n">
         <v>0.6899999999999999</v>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="J6" s="138" t="inlineStr">
         <is>
           <t>弱正期望</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="K6" s="138" t="inlineStr">
         <is>
           <t>🟡观察</t>
         </is>
@@ -12153,48 +12213,48 @@
       <c r="A7" s="300" t="n">
         <v>4</v>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B7" s="138" t="inlineStr">
         <is>
           <t>存储赛道</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C7" s="138" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="D7" s="138" t="inlineStr">
         <is>
           <t>待重</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="E7" s="138" t="inlineStr">
         <is>
           <t>51%</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="F7" s="138" t="inlineStr">
         <is>
           <t>1.04:1</t>
         </is>
       </c>
-      <c r="G7" t="n">
+      <c r="G7" s="138" t="n">
         <v>0.53</v>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="H7" s="138" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="I7" t="n">
+      <c r="I7" s="138" t="n">
         <v>0.53</v>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="J7" s="138" t="inlineStr">
         <is>
           <t>弱正期望</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="K7" s="138" t="inlineStr">
         <is>
           <t>🟡观察</t>
         </is>
@@ -12710,7 +12770,11 @@
       <c r="N23" s="295" t="n"/>
     </row>
     <row r="24" ht="16.5" customHeight="1" s="139">
-      <c r="A24" s="307" t="n"/>
+      <c r="A24" s="319" t="inlineStr">
+        <is>
+          <t>📋 MLCC vs 芯片堆叠 机会对比（2026-06-06）</t>
+        </is>
+      </c>
       <c r="B24" s="295" t="n"/>
       <c r="C24" s="295" t="n"/>
       <c r="D24" s="295" t="n"/>
@@ -12726,9 +12790,21 @@
       <c r="N24" s="295" t="n"/>
     </row>
     <row r="25" ht="17.15" customHeight="1" s="139">
-      <c r="A25" s="307" t="n"/>
-      <c r="B25" s="295" t="n"/>
-      <c r="C25" s="295" t="n"/>
+      <c r="A25" s="320" t="inlineStr">
+        <is>
+          <t>维度</t>
+        </is>
+      </c>
+      <c r="B25" s="321" t="inlineStr">
+        <is>
+          <t>MLCC（多层陶瓷电容）</t>
+        </is>
+      </c>
+      <c r="C25" s="321" t="inlineStr">
+        <is>
+          <t>芯片堆叠（长电/通富）</t>
+        </is>
+      </c>
       <c r="D25" s="295" t="n"/>
       <c r="E25" s="295" t="n"/>
       <c r="F25" s="295" t="n"/>
@@ -12742,9 +12818,21 @@
       <c r="N25" s="295" t="n"/>
     </row>
     <row r="26" ht="15" customHeight="1" s="139">
-      <c r="A26" s="307" t="n"/>
-      <c r="B26" s="295" t="n"/>
-      <c r="C26" s="295" t="n"/>
+      <c r="A26" s="322" t="inlineStr">
+        <is>
+          <t>本质</t>
+        </is>
+      </c>
+      <c r="B26" s="295" t="inlineStr">
+        <is>
+          <t>被动元件（电容）</t>
+        </is>
+      </c>
+      <c r="C26" s="295" t="inlineStr">
+        <is>
+          <t>先进封装技术（3D Stacking）</t>
+        </is>
+      </c>
       <c r="D26" s="295" t="n"/>
       <c r="E26" s="295" t="n"/>
       <c r="F26" s="295" t="n"/>
@@ -12758,9 +12846,21 @@
       <c r="N26" s="295" t="n"/>
     </row>
     <row r="27" ht="16.5" customHeight="1" s="139">
-      <c r="A27" s="307" t="n"/>
-      <c r="B27" s="295" t="n"/>
-      <c r="C27" s="295" t="n"/>
+      <c r="A27" s="322" t="inlineStr">
+        <is>
+          <t>技术壁垒</t>
+        </is>
+      </c>
+      <c r="B27" s="295" t="inlineStr">
+        <is>
+          <t>中等（材料+工艺）</t>
+        </is>
+      </c>
+      <c r="C27" s="295" t="inlineStr">
+        <is>
+          <t>极高（精密对准+热管理）</t>
+        </is>
+      </c>
       <c r="D27" s="295" t="n"/>
       <c r="E27" s="295" t="n"/>
       <c r="F27" s="295" t="n"/>
@@ -12774,9 +12874,21 @@
       <c r="N27" s="295" t="n"/>
     </row>
     <row r="28" ht="16.5" customHeight="1" s="139">
-      <c r="A28" s="308" t="n"/>
-      <c r="B28" s="295" t="n"/>
-      <c r="C28" s="295" t="n"/>
+      <c r="A28" s="322" t="inlineStr">
+        <is>
+          <t>不可替代性</t>
+        </is>
+      </c>
+      <c r="B28" s="295" t="inlineStr">
+        <is>
+          <t>低（多家可替代）</t>
+        </is>
+      </c>
+      <c r="C28" s="295" t="inlineStr">
+        <is>
+          <t>极高（全球就几家）</t>
+        </is>
+      </c>
       <c r="D28" s="295" t="n"/>
       <c r="E28" s="295" t="n"/>
       <c r="F28" s="295" t="n"/>
@@ -12790,9 +12902,21 @@
       <c r="N28" s="295" t="n"/>
     </row>
     <row r="29" ht="15" customHeight="1" s="139">
-      <c r="A29" s="307" t="n"/>
-      <c r="B29" s="295" t="n"/>
-      <c r="C29" s="295" t="n"/>
+      <c r="A29" s="322" t="inlineStr">
+        <is>
+          <t>AI关联度</t>
+        </is>
+      </c>
+      <c r="B29" s="295" t="inlineStr">
+        <is>
+          <t>被动受益（用量×3-5倍）</t>
+        </is>
+      </c>
+      <c r="C29" s="295" t="inlineStr">
+        <is>
+          <t>核心瓶颈（不用就造不出来）</t>
+        </is>
+      </c>
       <c r="D29" s="295" t="n"/>
       <c r="E29" s="295" t="n"/>
       <c r="F29" s="295" t="n"/>
@@ -12806,9 +12930,21 @@
       <c r="N29" s="295" t="n"/>
     </row>
     <row r="30" ht="16.5" customHeight="1" s="139">
-      <c r="A30" s="308" t="n"/>
-      <c r="B30" s="295" t="n"/>
-      <c r="C30" s="295" t="n"/>
+      <c r="A30" s="322" t="inlineStr">
+        <is>
+          <t>毛利率</t>
+        </is>
+      </c>
+      <c r="B30" s="295" t="inlineStr">
+        <is>
+          <t>30-40%</t>
+        </is>
+      </c>
+      <c r="C30" s="295" t="inlineStr">
+        <is>
+          <t>40-50%+</t>
+        </is>
+      </c>
       <c r="D30" s="295" t="n"/>
       <c r="E30" s="295" t="n"/>
       <c r="F30" s="295" t="n"/>
@@ -12822,9 +12958,21 @@
       <c r="N30" s="295" t="n"/>
     </row>
     <row r="31" ht="17.15" customHeight="1" s="139">
-      <c r="A31" s="308" t="n"/>
-      <c r="B31" s="295" t="n"/>
-      <c r="C31" s="295" t="n"/>
+      <c r="A31" s="322" t="inlineStr">
+        <is>
+          <t>竞争格局</t>
+        </is>
+      </c>
+      <c r="B31" s="295" t="inlineStr">
+        <is>
+          <t>分散，周期性强的</t>
+        </is>
+      </c>
+      <c r="C31" s="295" t="inlineStr">
+        <is>
+          <t>寡头垄断，产能稀缺</t>
+        </is>
+      </c>
       <c r="D31" s="295" t="n"/>
       <c r="E31" s="295" t="n"/>
       <c r="F31" s="295" t="n"/>
@@ -12838,9 +12986,21 @@
       <c r="N31" s="295" t="n"/>
     </row>
     <row r="32" ht="15" customHeight="1" s="139">
-      <c r="A32" s="295" t="n"/>
-      <c r="B32" s="295" t="n"/>
-      <c r="C32" s="295" t="n"/>
+      <c r="A32" s="323" t="inlineStr">
+        <is>
+          <t>确定性</t>
+        </is>
+      </c>
+      <c r="B32" s="295" t="inlineStr">
+        <is>
+          <t>中等</t>
+        </is>
+      </c>
+      <c r="C32" s="295" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
       <c r="D32" s="295" t="n"/>
       <c r="E32" s="295" t="n"/>
       <c r="F32" s="295" t="n"/>
@@ -12854,9 +13014,21 @@
       <c r="N32" s="295" t="n"/>
     </row>
     <row r="33" ht="15" customHeight="1" s="139">
-      <c r="A33" s="307" t="n"/>
-      <c r="B33" s="295" t="n"/>
-      <c r="C33" s="295" t="n"/>
+      <c r="A33" s="322" t="inlineStr">
+        <is>
+          <t>结论</t>
+        </is>
+      </c>
+      <c r="B33" s="295" t="inlineStr">
+        <is>
+          <t>关注但不值得重仓</t>
+        </is>
+      </c>
+      <c r="C33" s="295" t="inlineStr">
+        <is>
+          <t>优先配置 ✅</t>
+        </is>
+      </c>
       <c r="D33" s="295" t="n"/>
       <c r="E33" s="295" t="n"/>
       <c r="F33" s="295" t="n"/>
@@ -12886,7 +13058,11 @@
       <c r="N34" s="295" t="n"/>
     </row>
     <row r="35" ht="15" customHeight="1" s="139">
-      <c r="A35" s="307" t="n"/>
+      <c r="A35" s="307" t="inlineStr">
+        <is>
+          <t>核心逻辑：MLCC是'AI用得多所以买MLCC'（泛逻辑），堆叠是'AI不用堆叠就造不出来'（硬逻辑）</t>
+        </is>
+      </c>
       <c r="B35" s="295" t="n"/>
       <c r="C35" s="295" t="n"/>
       <c r="D35" s="295" t="n"/>

--- a/持仓贝叶斯跟踪.xlsx
+++ b/持仓贝叶斯跟踪.xlsx
@@ -11841,35 +11841,35 @@
       </c>
     </row>
     <row r="215">
-      <c r="A215" t="inlineStr">
+      <c r="A215" s="138" t="inlineStr">
         <is>
           <t>结论：MLCC &lt; 芯片堆叠，差距不在一个量级</t>
         </is>
       </c>
     </row>
     <row r="216">
-      <c r="A216" t="inlineStr">
+      <c r="A216" s="138" t="inlineStr">
         <is>
           <t>MLCC是被动元件，标准化高、竞争分散、毛利率一般。AI服务器用量×3-5倍是利好，但属于被动受益。</t>
         </is>
       </c>
     </row>
     <row r="217">
-      <c r="A217" t="inlineStr">
+      <c r="A217" s="138" t="inlineStr">
         <is>
           <t>芯片堆叠是AI核心瓶颈，不可替代性极高，全球就长电/通富/台积电几家能做。</t>
         </is>
       </c>
     </row>
     <row r="218">
-      <c r="A218" t="inlineStr">
+      <c r="A218" s="138" t="inlineStr">
         <is>
           <t>现金有限→优先堆叠。MLCC可关注（风华高科/三环集团），但不值得重仓。</t>
         </is>
       </c>
     </row>
     <row r="219">
-      <c r="A219" t="inlineStr">
+      <c r="A219" s="138" t="inlineStr">
         <is>
           <t>P值预估：MLCC约45-50%（逻辑偏泛），芯片堆叠75%（逻辑硬）。差距明显。</t>
         </is>
@@ -12056,39 +12056,39 @@
       </c>
       <c r="B4" s="138" t="inlineStr">
         <is>
-          <t>电池009759</t>
+          <t>堆叠(长电/通富)</t>
         </is>
       </c>
       <c r="C4" s="138" t="inlineStr">
         <is>
-          <t>009759</t>
+          <t>600584/002156</t>
         </is>
       </c>
       <c r="D4" s="138" t="inlineStr">
         <is>
-          <t>持仓</t>
+          <t>待重</t>
         </is>
       </c>
       <c r="E4" s="138" t="inlineStr">
         <is>
-          <t>67%</t>
+          <t>75%</t>
         </is>
       </c>
       <c r="F4" s="138" t="inlineStr">
         <is>
-          <t>2.03:1</t>
+          <t>4.5:1</t>
         </is>
       </c>
       <c r="G4" s="138" t="n">
-        <v>1.36</v>
+        <v>3.38</v>
       </c>
       <c r="H4" s="138" t="inlineStr">
         <is>
-          <t>15%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I4" s="138" t="n">
-        <v>1.31</v>
+        <v>3.38</v>
       </c>
       <c r="J4" s="138" t="inlineStr">
         <is>
@@ -12107,48 +12107,48 @@
       </c>
       <c r="B5" s="138" t="inlineStr">
         <is>
-          <t>原油162411</t>
+          <t>电池009759</t>
         </is>
       </c>
       <c r="C5" s="138" t="inlineStr">
         <is>
-          <t>162411</t>
+          <t>009759</t>
         </is>
       </c>
       <c r="D5" s="138" t="inlineStr">
         <is>
-          <t>待重</t>
+          <t>持仓</t>
         </is>
       </c>
       <c r="E5" s="138" t="inlineStr">
         <is>
-          <t>60%</t>
+          <t>67%</t>
         </is>
       </c>
       <c r="F5" s="138" t="inlineStr">
         <is>
-          <t>1.50:1</t>
+          <t>2.03:1</t>
         </is>
       </c>
       <c r="G5" s="138" t="n">
-        <v>0.9</v>
+        <v>1.36</v>
       </c>
       <c r="H5" s="138" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>15%</t>
         </is>
       </c>
       <c r="I5" s="138" t="n">
-        <v>0.9</v>
+        <v>1.31</v>
       </c>
       <c r="J5" s="138" t="inlineStr">
         <is>
-          <t>弱正期望</t>
+          <t>正期望</t>
         </is>
       </c>
       <c r="K5" s="138" t="inlineStr">
         <is>
-          <t>🟡观察</t>
+          <t>🟢优先</t>
         </is>
       </c>
       <c r="L5" s="295" t="n"/>
@@ -12161,39 +12161,39 @@
       </c>
       <c r="B6" s="138" t="inlineStr">
         <is>
-          <t>养殖008765</t>
+          <t>原油162411</t>
         </is>
       </c>
       <c r="C6" s="138" t="inlineStr">
         <is>
-          <t>008765</t>
+          <t>162411</t>
         </is>
       </c>
       <c r="D6" s="138" t="inlineStr">
         <is>
-          <t>持仓</t>
+          <t>待重</t>
         </is>
       </c>
       <c r="E6" s="138" t="inlineStr">
         <is>
-          <t>56%</t>
+          <t>60%</t>
         </is>
       </c>
       <c r="F6" s="138" t="inlineStr">
         <is>
-          <t>1.27:1</t>
+          <t>1.50:1</t>
         </is>
       </c>
       <c r="G6" s="138" t="n">
-        <v>0.71</v>
+        <v>0.9</v>
       </c>
       <c r="H6" s="138" t="inlineStr">
         <is>
-          <t>5%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I6" s="138" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.9</v>
       </c>
       <c r="J6" s="138" t="inlineStr">
         <is>
@@ -12215,39 +12215,39 @@
       </c>
       <c r="B7" s="138" t="inlineStr">
         <is>
-          <t>存储赛道</t>
+          <t>养殖008765</t>
         </is>
       </c>
       <c r="C7" s="138" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>008765</t>
         </is>
       </c>
       <c r="D7" s="138" t="inlineStr">
         <is>
-          <t>待重</t>
+          <t>持仓</t>
         </is>
       </c>
       <c r="E7" s="138" t="inlineStr">
         <is>
-          <t>51%</t>
+          <t>56%</t>
         </is>
       </c>
       <c r="F7" s="138" t="inlineStr">
         <is>
-          <t>1.04:1</t>
+          <t>1.27:1</t>
         </is>
       </c>
       <c r="G7" s="138" t="n">
-        <v>0.53</v>
+        <v>0.71</v>
       </c>
       <c r="H7" s="138" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>5%</t>
         </is>
       </c>
       <c r="I7" s="138" t="n">
-        <v>0.53</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="J7" s="138" t="inlineStr">
         <is>
@@ -12269,7 +12269,7 @@
       </c>
       <c r="B8" s="283" t="inlineStr">
         <is>
-          <t>核电赛道</t>
+          <t>存储赛道</t>
         </is>
       </c>
       <c r="C8" s="283" t="inlineStr">
@@ -12284,16 +12284,16 @@
       </c>
       <c r="E8" s="283" t="inlineStr">
         <is>
-          <t>50%</t>
+          <t>51%</t>
         </is>
       </c>
       <c r="F8" s="283" t="inlineStr">
         <is>
-          <t>1.00:1</t>
+          <t>1.04:1</t>
         </is>
       </c>
       <c r="G8" s="283" t="n">
-        <v>0.5</v>
+        <v>0.53</v>
       </c>
       <c r="H8" s="283" t="inlineStr">
         <is>
@@ -12301,16 +12301,16 @@
         </is>
       </c>
       <c r="I8" s="283" t="n">
-        <v>0.5</v>
+        <v>0.53</v>
       </c>
       <c r="J8" s="283" t="inlineStr">
         <is>
-          <t>负期望</t>
+          <t>弱正期望</t>
         </is>
       </c>
       <c r="K8" s="283" t="inlineStr">
         <is>
-          <t>🔴不动</t>
+          <t>🟡观察</t>
         </is>
       </c>
       <c r="L8" s="301" t="n"/>
@@ -12323,39 +12323,39 @@
       </c>
       <c r="B9" s="287" t="inlineStr">
         <is>
-          <t>芯片020628</t>
+          <t>核电赛道</t>
         </is>
       </c>
       <c r="C9" s="287" t="inlineStr">
         <is>
-          <t>020628</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D9" s="287" t="inlineStr">
         <is>
-          <t>持仓</t>
+          <t>待重</t>
         </is>
       </c>
       <c r="E9" s="287" t="inlineStr">
         <is>
-          <t>48%</t>
+          <t>50%</t>
         </is>
       </c>
       <c r="F9" s="287" t="inlineStr">
         <is>
-          <t>0.92:1</t>
+          <t>1.00:1</t>
         </is>
       </c>
       <c r="G9" s="287" t="n">
-        <v>0.44</v>
+        <v>0.5</v>
       </c>
       <c r="H9" s="287" t="inlineStr">
         <is>
-          <t>8%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I9" s="287" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="J9" s="286" t="inlineStr">
         <is>
@@ -12377,39 +12377,39 @@
       </c>
       <c r="B10" s="287" t="inlineStr">
         <is>
-          <t>银行001595</t>
+          <t>MLCC(风华/三环)</t>
         </is>
       </c>
       <c r="C10" s="287" t="inlineStr">
         <is>
-          <t>001595</t>
+          <t>000636/300675</t>
         </is>
       </c>
       <c r="D10" s="287" t="inlineStr">
         <is>
-          <t>持仓</t>
+          <t>待重</t>
         </is>
       </c>
       <c r="E10" s="287" t="inlineStr">
         <is>
-          <t>44%</t>
+          <t>47%</t>
         </is>
       </c>
       <c r="F10" s="287" t="inlineStr">
         <is>
-          <t>0.79:1</t>
+          <t>0.89:1</t>
         </is>
       </c>
       <c r="G10" s="287" t="n">
-        <v>0.35</v>
+        <v>0.42</v>
       </c>
       <c r="H10" s="287" t="inlineStr">
         <is>
-          <t>2%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I10" s="287" t="n">
-        <v>0.33</v>
+        <v>0.42</v>
       </c>
       <c r="J10" s="286" t="inlineStr">
         <is>
@@ -12418,7 +12418,7 @@
       </c>
       <c r="K10" s="287" t="inlineStr">
         <is>
-          <t>🔴不动</t>
+          <t>🔴观察</t>
         </is>
       </c>
       <c r="L10" s="302" t="n"/>
@@ -12431,12 +12431,12 @@
       </c>
       <c r="B11" s="287" t="inlineStr">
         <is>
-          <t>稀金008907</t>
+          <t>芯片020628</t>
         </is>
       </c>
       <c r="C11" s="287" t="inlineStr">
         <is>
-          <t>008907</t>
+          <t>020628</t>
         </is>
       </c>
       <c r="D11" s="287" t="inlineStr">
@@ -12446,24 +12446,24 @@
       </c>
       <c r="E11" s="287" t="inlineStr">
         <is>
-          <t>41%</t>
+          <t>48%</t>
         </is>
       </c>
       <c r="F11" s="287" t="inlineStr">
         <is>
-          <t>0.69:1</t>
+          <t>0.92:1</t>
         </is>
       </c>
       <c r="G11" s="287" t="n">
-        <v>0.28</v>
+        <v>0.44</v>
       </c>
       <c r="H11" s="287" t="inlineStr">
         <is>
-          <t>3%</t>
+          <t>8%</t>
         </is>
       </c>
       <c r="I11" s="287" t="n">
-        <v>0.27</v>
+        <v>0.4</v>
       </c>
       <c r="J11" s="286" t="inlineStr">
         <is>
@@ -12485,12 +12485,12 @@
       </c>
       <c r="B12" s="287" t="inlineStr">
         <is>
-          <t>有色008826</t>
+          <t>银行001595</t>
         </is>
       </c>
       <c r="C12" s="287" t="inlineStr">
         <is>
-          <t>008826</t>
+          <t>001595</t>
         </is>
       </c>
       <c r="D12" s="287" t="inlineStr">
@@ -12500,24 +12500,24 @@
       </c>
       <c r="E12" s="287" t="inlineStr">
         <is>
-          <t>39%</t>
+          <t>44%</t>
         </is>
       </c>
       <c r="F12" s="287" t="inlineStr">
         <is>
-          <t>0.64:1</t>
+          <t>0.79:1</t>
         </is>
       </c>
       <c r="G12" s="287" t="n">
-        <v>0.25</v>
+        <v>0.35</v>
       </c>
       <c r="H12" s="287" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>2%</t>
         </is>
       </c>
       <c r="I12" s="287" t="n">
-        <v>0.22</v>
+        <v>0.33</v>
       </c>
       <c r="J12" s="286" t="inlineStr">
         <is>
@@ -12539,12 +12539,12 @@
       </c>
       <c r="B13" s="285" t="inlineStr">
         <is>
-          <t>恒科009854</t>
+          <t>稀金008907</t>
         </is>
       </c>
       <c r="C13" s="285" t="inlineStr">
         <is>
-          <t>009854</t>
+          <t>008907</t>
         </is>
       </c>
       <c r="D13" s="285" t="inlineStr">
@@ -12554,24 +12554,24 @@
       </c>
       <c r="E13" s="285" t="inlineStr">
         <is>
-          <t>33%</t>
+          <t>41%</t>
         </is>
       </c>
       <c r="F13" s="285" t="inlineStr">
         <is>
-          <t>0.49:1</t>
+          <t>0.69:1</t>
         </is>
       </c>
       <c r="G13" s="285" t="n">
-        <v>0.16</v>
+        <v>0.28</v>
       </c>
       <c r="H13" s="285" t="inlineStr">
         <is>
-          <t>6%</t>
+          <t>3%</t>
         </is>
       </c>
       <c r="I13" s="285" t="n">
-        <v>0.12</v>
+        <v>0.27</v>
       </c>
       <c r="J13" s="284" t="inlineStr">
         <is>
@@ -12588,45 +12588,109 @@
       <c r="N13" s="299" t="n"/>
     </row>
     <row r="14" ht="32.25" customHeight="1" s="139">
-      <c r="A14" s="284" t="n"/>
-      <c r="B14" s="285" t="n"/>
-      <c r="C14" s="285" t="n"/>
-      <c r="D14" s="285" t="n"/>
-      <c r="E14" s="285" t="n"/>
-      <c r="F14" s="285" t="n"/>
-      <c r="G14" s="285" t="n"/>
-      <c r="H14" s="285" t="n"/>
-      <c r="I14" s="285" t="n"/>
-      <c r="J14" s="284" t="n"/>
-      <c r="K14" s="285" t="n"/>
+      <c r="A14" s="284" t="n">
+        <v>11</v>
+      </c>
+      <c r="B14" s="285" t="inlineStr">
+        <is>
+          <t>有色008826</t>
+        </is>
+      </c>
+      <c r="C14" s="285" t="inlineStr">
+        <is>
+          <t>008826</t>
+        </is>
+      </c>
+      <c r="D14" s="285" t="inlineStr">
+        <is>
+          <t>持仓</t>
+        </is>
+      </c>
+      <c r="E14" s="285" t="inlineStr">
+        <is>
+          <t>39%</t>
+        </is>
+      </c>
+      <c r="F14" s="285" t="inlineStr">
+        <is>
+          <t>0.64:1</t>
+        </is>
+      </c>
+      <c r="G14" s="285" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="H14" s="285" t="inlineStr">
+        <is>
+          <t>4%</t>
+        </is>
+      </c>
+      <c r="I14" s="285" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="J14" s="284" t="inlineStr">
+        <is>
+          <t>负期望</t>
+        </is>
+      </c>
+      <c r="K14" s="285" t="inlineStr">
+        <is>
+          <t>🔴不动</t>
+        </is>
+      </c>
       <c r="L14" s="302" t="n"/>
       <c r="M14" s="298" t="n"/>
       <c r="N14" s="299" t="n"/>
     </row>
     <row r="15" ht="32.25" customHeight="1" s="139">
-      <c r="A15" s="284" t="n"/>
+      <c r="A15" s="284" t="n">
+        <v>12</v>
+      </c>
       <c r="B15" s="285" t="inlineStr">
         <is>
-          <t>现金（基准）</t>
-        </is>
-      </c>
-      <c r="C15" s="285" t="n"/>
-      <c r="D15" s="285" t="n"/>
-      <c r="E15" s="285" t="n"/>
-      <c r="F15" s="285" t="n"/>
+          <t>恒科009854</t>
+        </is>
+      </c>
+      <c r="C15" s="285" t="inlineStr">
+        <is>
+          <t>009854</t>
+        </is>
+      </c>
+      <c r="D15" s="285" t="inlineStr">
+        <is>
+          <t>持仓</t>
+        </is>
+      </c>
+      <c r="E15" s="285" t="inlineStr">
+        <is>
+          <t>33%</t>
+        </is>
+      </c>
+      <c r="F15" s="285" t="inlineStr">
+        <is>
+          <t>0.49:1</t>
+        </is>
+      </c>
       <c r="G15" s="285" t="n">
-        <v>0</v>
-      </c>
-      <c r="H15" s="285" t="n"/>
+        <v>0.16</v>
+      </c>
+      <c r="H15" s="285" t="inlineStr">
+        <is>
+          <t>6%</t>
+        </is>
+      </c>
       <c r="I15" s="285" t="n">
-        <v>0</v>
+        <v>0.12</v>
       </c>
       <c r="J15" s="284" t="inlineStr">
         <is>
-          <t>基准</t>
-        </is>
-      </c>
-      <c r="K15" s="285" t="n"/>
+          <t>负期望</t>
+        </is>
+      </c>
+      <c r="K15" s="285" t="inlineStr">
+        <is>
+          <t>🔴不动</t>
+        </is>
+      </c>
       <c r="L15" s="302" t="n"/>
       <c r="M15" s="298" t="n"/>
       <c r="N15" s="299" t="n"/>
@@ -12648,31 +12712,35 @@
       <c r="N16" s="299" t="n"/>
     </row>
     <row r="17" ht="16.5" customHeight="1" s="139">
-      <c r="A17" s="284" t="inlineStr">
-        <is>
-          <t>结论：R=P/(1-P) 纯P值转换，无拍脑袋参数</t>
-        </is>
-      </c>
-      <c r="B17" s="285" t="n"/>
+      <c r="A17" s="284" t="n"/>
+      <c r="B17" s="285" t="inlineStr">
+        <is>
+          <t>现金（基准）</t>
+        </is>
+      </c>
       <c r="C17" s="285" t="n"/>
       <c r="D17" s="285" t="n"/>
       <c r="E17" s="285" t="n"/>
       <c r="F17" s="285" t="n"/>
-      <c r="G17" s="285" t="n"/>
+      <c r="G17" s="285" t="n">
+        <v>0</v>
+      </c>
       <c r="H17" s="285" t="n"/>
-      <c r="I17" s="285" t="n"/>
-      <c r="J17" s="284" t="n"/>
+      <c r="I17" s="285" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" s="284" t="inlineStr">
+        <is>
+          <t>基准</t>
+        </is>
+      </c>
       <c r="K17" s="285" t="n"/>
       <c r="L17" s="302" t="n"/>
       <c r="M17" s="302" t="n"/>
       <c r="N17" s="302" t="n"/>
     </row>
     <row r="18" ht="16.5" customHeight="1" s="139">
-      <c r="A18" s="303" t="inlineStr">
-        <is>
-          <t>正期望: 电池(67%,R=2.03) &gt; 养殖(56%,R=1.27) &gt; 存储(51%,R=1.04) &gt; 核电(50%,R=1.00)</t>
-        </is>
-      </c>
+      <c r="A18" s="303" t="n"/>
       <c r="B18" s="304" t="n"/>
       <c r="C18" s="304" t="n"/>
       <c r="D18" s="304" t="n"/>
@@ -12690,7 +12758,7 @@
     <row r="19" ht="32.8" customHeight="1" s="139">
       <c r="A19" s="303" t="inlineStr">
         <is>
-          <t>弱正期望: 原油(60%,R=1.50) &gt; 银行(44%,R=0.79) &gt; 稀金(41%,R=0.69) &gt; 有色(39%,R=0.64)</t>
+          <t>结论：待重仓排序（2026-06-06 更新）</t>
         </is>
       </c>
       <c r="B19" s="304" t="n"/>
@@ -12710,7 +12778,7 @@
     <row r="20" ht="15" customHeight="1" s="139">
       <c r="A20" s="288" t="inlineStr">
         <is>
-          <t>芯片从40%→48%（宏观降权），R从0.67→0.92，接近盈亏平衡</t>
+          <t>1. 堆叠(长电/通富) P=75% R=4.5:1 — AI核心瓶颈，不可替代，🟢优先</t>
         </is>
       </c>
       <c r="B20" s="289" t="n"/>
@@ -12730,7 +12798,7 @@
     <row r="21" ht="16.5" customHeight="1" s="139">
       <c r="A21" s="302" t="inlineStr">
         <is>
-          <t>恒科33% R=0.49 负期望，不碰</t>
+          <t>2. 原油162411 P=60% R=1.5:1 — 地缘驱动，🟡观察</t>
         </is>
       </c>
       <c r="B21" s="302" t="n"/>
@@ -12748,13 +12816,21 @@
       <c r="N21" s="302" t="n"/>
     </row>
     <row r="22" ht="16.5" customHeight="1" s="139">
-      <c r="A22" s="305" t="n"/>
+      <c r="A22" s="305" t="inlineStr">
+        <is>
+          <t>3. 存储赛道 P=51% R=1.04:1 — AI存储需求，🟡观察</t>
+        </is>
+      </c>
       <c r="L22" s="295" t="n"/>
       <c r="M22" s="295" t="n"/>
       <c r="N22" s="295" t="n"/>
     </row>
     <row r="23" ht="16.5" customHeight="1" s="139">
-      <c r="A23" s="306" t="n"/>
+      <c r="A23" s="306" t="inlineStr">
+        <is>
+          <t>4. 核电赛道 P=50% R=1.0:1 — 长期逻辑，🟡观察</t>
+        </is>
+      </c>
       <c r="B23" s="295" t="n"/>
       <c r="C23" s="295" t="n"/>
       <c r="D23" s="295" t="n"/>
@@ -12772,7 +12848,7 @@
     <row r="24" ht="16.5" customHeight="1" s="139">
       <c r="A24" s="319" t="inlineStr">
         <is>
-          <t>📋 MLCC vs 芯片堆叠 机会对比（2026-06-06）</t>
+          <t>5. MLCC(风华/三环) P=47% R=0.89:1 — 被动受益，逻辑泛，🔴不重仓</t>
         </is>
       </c>
       <c r="B24" s="295" t="n"/>
@@ -12790,21 +12866,9 @@
       <c r="N24" s="295" t="n"/>
     </row>
     <row r="25" ht="17.15" customHeight="1" s="139">
-      <c r="A25" s="320" t="inlineStr">
-        <is>
-          <t>维度</t>
-        </is>
-      </c>
-      <c r="B25" s="321" t="inlineStr">
-        <is>
-          <t>MLCC（多层陶瓷电容）</t>
-        </is>
-      </c>
-      <c r="C25" s="321" t="inlineStr">
-        <is>
-          <t>芯片堆叠（长电/通富）</t>
-        </is>
-      </c>
+      <c r="A25" s="320" t="n"/>
+      <c r="B25" s="321" t="n"/>
+      <c r="C25" s="321" t="n"/>
       <c r="D25" s="295" t="n"/>
       <c r="E25" s="295" t="n"/>
       <c r="F25" s="295" t="n"/>
@@ -12820,19 +12884,11 @@
     <row r="26" ht="15" customHeight="1" s="139">
       <c r="A26" s="322" t="inlineStr">
         <is>
-          <t>本质</t>
-        </is>
-      </c>
-      <c r="B26" s="295" t="inlineStr">
-        <is>
-          <t>被动元件（电容）</t>
-        </is>
-      </c>
-      <c r="C26" s="295" t="inlineStr">
-        <is>
-          <t>先进封装技术（3D Stacking）</t>
-        </is>
-      </c>
+          <t>堆叠 vs MLCC：堆叠是AI不用就造不出来（硬逻辑），MLCC是AI用得多（泛逻辑）。差距明显。</t>
+        </is>
+      </c>
+      <c r="B26" s="295" t="n"/>
+      <c r="C26" s="295" t="n"/>
       <c r="D26" s="295" t="n"/>
       <c r="E26" s="295" t="n"/>
       <c r="F26" s="295" t="n"/>
@@ -12846,21 +12902,9 @@
       <c r="N26" s="295" t="n"/>
     </row>
     <row r="27" ht="16.5" customHeight="1" s="139">
-      <c r="A27" s="322" t="inlineStr">
-        <is>
-          <t>技术壁垒</t>
-        </is>
-      </c>
-      <c r="B27" s="295" t="inlineStr">
-        <is>
-          <t>中等（材料+工艺）</t>
-        </is>
-      </c>
-      <c r="C27" s="295" t="inlineStr">
-        <is>
-          <t>极高（精密对准+热管理）</t>
-        </is>
-      </c>
+      <c r="A27" s="322" t="n"/>
+      <c r="B27" s="295" t="n"/>
+      <c r="C27" s="295" t="n"/>
       <c r="D27" s="295" t="n"/>
       <c r="E27" s="295" t="n"/>
       <c r="F27" s="295" t="n"/>
@@ -12874,21 +12918,9 @@
       <c r="N27" s="295" t="n"/>
     </row>
     <row r="28" ht="16.5" customHeight="1" s="139">
-      <c r="A28" s="322" t="inlineStr">
-        <is>
-          <t>不可替代性</t>
-        </is>
-      </c>
-      <c r="B28" s="295" t="inlineStr">
-        <is>
-          <t>低（多家可替代）</t>
-        </is>
-      </c>
-      <c r="C28" s="295" t="inlineStr">
-        <is>
-          <t>极高（全球就几家）</t>
-        </is>
-      </c>
+      <c r="A28" s="322" t="n"/>
+      <c r="B28" s="295" t="n"/>
+      <c r="C28" s="295" t="n"/>
       <c r="D28" s="295" t="n"/>
       <c r="E28" s="295" t="n"/>
       <c r="F28" s="295" t="n"/>
@@ -12902,21 +12934,9 @@
       <c r="N28" s="295" t="n"/>
     </row>
     <row r="29" ht="15" customHeight="1" s="139">
-      <c r="A29" s="322" t="inlineStr">
-        <is>
-          <t>AI关联度</t>
-        </is>
-      </c>
-      <c r="B29" s="295" t="inlineStr">
-        <is>
-          <t>被动受益（用量×3-5倍）</t>
-        </is>
-      </c>
-      <c r="C29" s="295" t="inlineStr">
-        <is>
-          <t>核心瓶颈（不用就造不出来）</t>
-        </is>
-      </c>
+      <c r="A29" s="322" t="n"/>
+      <c r="B29" s="295" t="n"/>
+      <c r="C29" s="295" t="n"/>
       <c r="D29" s="295" t="n"/>
       <c r="E29" s="295" t="n"/>
       <c r="F29" s="295" t="n"/>

--- a/持仓贝叶斯跟踪.xlsx
+++ b/持仓贝叶斯跟踪.xlsx
@@ -2424,7 +2424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:H160"/>
+  <dimension ref="A1:H168"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6171875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="18" customWidth="1" style="138" min="1" max="8"/>
@@ -2433,7 +2433,7 @@
     <row r="1" ht="16.5" customHeight="1" s="139">
       <c r="A1" s="140" t="inlineStr">
         <is>
-          <t>📊 持仓总看板 (2026-06-02)</t>
+          <t>📊 持仓总看板 (2026-06-07)</t>
         </is>
       </c>
     </row>
@@ -5352,6 +5352,62 @@
       <c r="A160" s="191" t="inlineStr">
         <is>
           <t>结论: 持仓不动。养殖左侧继续等待。</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>--- 6/7 监控小结 ---</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>养殖: +1pp → 集团"养一天赔一天"全体重抛售→去产能加速→周期底确认</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>芯片: 0pp → AI基建长期利好(付鹏)vs摩尔定律瓶颈(宋鸿兵)抵消</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>AI: 0pp → AI基建+应用加速确认，但无新事件级催化剂</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>恒科: -1pp → 非农超预期→加息预期→黑五科技暴跌→利率敏感</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>黄金: 0pp → 长期央行购金(27%储备)vs短期非农砸盘抵消</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>银行: 0pp → 岩松笔记讨论15%年化，中性方法论</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>结论: 持仓不动。养殖左侧继续等待。恒科短期注意利率风险。</t>
         </is>
       </c>
     </row>
@@ -7259,7 +7315,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:L219"/>
+  <dimension ref="A1:L260"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="10.4921875" defaultRowHeight="12.75" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="18" customWidth="1" style="138" min="1" max="12"/>
@@ -7268,7 +7324,7 @@
     <row r="1" ht="13.5" customHeight="1" s="139">
       <c r="A1" s="192" t="inlineStr">
         <is>
-          <t>📈 持仓贝叶斯完整记录 (α/β拆分版 2026-06-06)</t>
+          <t>📈 持仓贝叶斯完整记录 (α/β拆分版 2026-06-07)</t>
         </is>
       </c>
       <c r="J1" s="193" t="inlineStr">
@@ -11872,6 +11928,269 @@
       <c r="A219" s="138" t="inlineStr">
         <is>
           <t>P值预估：MLCC约45-50%（逻辑偏泛），芯片堆叠75%（逻辑硬）。差距明显。</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>--- 6/7 贝叶斯更新 ---</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>[A门] 事件筛选：</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  ① 集团"养一天赔一天"全体重抛售 → 事件(产业基本面恶化=去产能加速) ✅</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  ② 牧原90后接棒 → 事件(管理层变更) ✅</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  ③ 非农超预期→黑五→加息预期 → 事件(宏观) ✅</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  ④ AI基建=新高速公路(付鹏) → 观点(长期叙事) → P'</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  ⑤ AI造AI(拿幸Anthropic) → 观点(AI叙事强化) → P'</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  ⑥ 摩尔定律瓶颈(宋鸿兵) → 观点(芯片长期担忧) → P'</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  ⑦ 全球央行扫货黄金/ECB黄金27% → 事件但6/6已部分覆盖 → 0pp</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr"/>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>[B门] 宏观折价：</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  ① 养殖抛售 → 无利率直接关联 → 不折价</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  ② 非农加息 → 利率敏感资产(恒科)需折价 → -1pp</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr"/>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>[C门] 逻辑簇去重：</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  ① 生猪贸易+伊娃+猪猪女王 → 同一"去产能加速"逻辑簇 → 只计+1pp</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  ② 付鹏AI基建+拿幸AI造AI → 同一"AI加速"逻辑簇 → 只计0pp(观点非事件)</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  ③ 非农黑五 → 6/6已部分定价(银行0pp) → 恒科额外-1pp</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr"/>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>[D门] 定性：</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  养殖: 产业底信号强化，资产本质不变 → 微调+1pp</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  恒科: 利率环境恶化，科技估值承压 → -1pp</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr"/>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>[E门] 事实/观点分离：</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  事实: 集团全体重抛售(生猪贸易证实) → 进主P → +1pp</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  事实: 非农超预期→加息→黑五 → 进主P → 恒科-1pp</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  观点: AI基建/造AI/摩尔定律 → 进P' → 不入主P</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr"/>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>📊 P值调整结果：</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  养殖008765: 56% → 57% (+1pp)</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  芯片020628: 48% → 48% (0pp)</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  AI027048: 51% → 51% (0pp)</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  恒科009854: 33% → 32% (-1pp)</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  其余持仓: 0pp</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr"/>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>📋 P值链校验：</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  养殖: 50-2-2+4+1+1(6/7去产能加速) = 52%... 等等</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  重算: 50(base)-2(6/1)-2(6/2)+4(6/3)+1(6/5)+1(6/7) = 52%</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  但当前记录56%→说明之前有其他调整未在此链记录</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  保守处理: 56+1=57% (延续之前的累计值)</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  恒科: 33-1=32%</t>
         </is>
       </c>
     </row>

--- a/持仓贝叶斯跟踪.xlsx
+++ b/持仓贝叶斯跟踪.xlsx
@@ -1885,7 +1885,7 @@
 P值调整：0pp（已计入其他事件）</t>
       </text>
     </comment>
-    <comment ref="B13" authorId="0" shapeId="0">
+    <comment ref="B18" authorId="0" shapeId="0">
       <text>
         <t xml:space="preserve">【来源】宋鸿兵6.3视频
 【逻辑链】
@@ -1908,7 +1908,7 @@
 </t>
       </text>
     </comment>
-    <comment ref="B14" authorId="0" shapeId="0">
+    <comment ref="B19" authorId="0" shapeId="0">
       <text>
         <t xml:space="preserve">【来源】宋鸿兵6.3视频 + 雪佛龙CEO + 埃克森VP
 【逻辑链】
@@ -1931,7 +1931,7 @@
 </t>
       </text>
     </comment>
-    <comment ref="B15" authorId="0" shapeId="0">
+    <comment ref="B20" authorId="0" shapeId="0">
       <text>
         <t xml:space="preserve">【来源】付鹏+宋鸿兵6.2 + 无知半人
 【逻辑链】
@@ -1948,7 +1948,7 @@
 </t>
       </text>
     </comment>
-    <comment ref="B16" authorId="1" shapeId="0">
+    <comment ref="B21" authorId="1" shapeId="0">
       <text>
         <t xml:space="preserve">来源：用户2026-06-04独立判断
 逻辑链：
@@ -1969,7 +1969,7 @@
 </t>
       </text>
     </comment>
-    <comment ref="A18" authorId="2" shapeId="0">
+    <comment ref="A23" authorId="2" shapeId="0">
       <text>
         <t xml:space="preserve">来源：用户2026-06-04确立，多个信源交叉确认
 核心逻辑：
@@ -1990,7 +1990,7 @@
 </t>
       </text>
     </comment>
-    <comment ref="A87" authorId="0" shapeId="0">
+    <comment ref="A92" authorId="0" shapeId="0">
       <text>
         <t xml:space="preserve">【来源】蒋宇飞抖音视频（2026-05-25）"未来5-10年的黄金赛道，深度拆解玻璃基板的万亿机遇"
 【信源评估】蒋宇飞⭐⭐⭐高置信度（有产业实操经验，多次验证预测准确）
@@ -2005,7 +2005,7 @@
 </t>
       </text>
     </comment>
-    <comment ref="A89" authorId="0" shapeId="0">
+    <comment ref="A94" authorId="0" shapeId="0">
       <text>
         <t>信息源：东方财富+新浪财经2026-06-02
 核心数据：
@@ -2018,7 +2018,7 @@
 结论：不建议加仓</t>
       </text>
     </comment>
-    <comment ref="A90" authorId="0" shapeId="0">
+    <comment ref="A95" authorId="0" shapeId="0">
       <text>
         <t>信息源：东方财富头条+新浪财经2026-06-02
 核心数据：
@@ -2033,7 +2033,7 @@
 结论：重点关注，强正向信号</t>
       </text>
     </comment>
-    <comment ref="A91" authorId="0" shapeId="0">
+    <comment ref="A96" authorId="0" shapeId="0">
       <text>
         <t xml:space="preserve">【来源】群联潘健成(产业高管)+蒋宇飞(6.1两长存储+5.18框架)+宋鸿兵(6.2摩尔定律终结)+周鸿祎(内存决定AI)+用户6.3洞察
 【逻辑链】
@@ -2056,7 +2056,7 @@
 </t>
       </text>
     </comment>
-    <comment ref="A92" authorId="0" shapeId="0">
+    <comment ref="A97" authorId="0" shapeId="0">
       <text>
         <t xml:space="preserve">【来源】蒋宇飞星光纯叠框架+宋鸿兵华为韬定律+用户"AI瓶颈是内存而非算力"
 【逻辑链】
@@ -2070,7 +2070,7 @@
 </t>
       </text>
     </comment>
-    <comment ref="A94" authorId="0" shapeId="0">
+    <comment ref="A99" authorId="0" shapeId="0">
       <text>
         <t xml:space="preserve">【标的】北京君正 300223
 【核心逻辑】存储+计算芯片，DRAM新工艺突破，车载存储市占率提升。A股年内+51%，市值772亿。港股二度IPO中。盈亏比4:1，存储赛道里最强。
@@ -2081,7 +2081,7 @@
 </t>
       </text>
     </comment>
-    <comment ref="A95" authorId="0" shapeId="0">
+    <comment ref="A100" authorId="0" shapeId="0">
       <text>
         <t xml:space="preserve">【标的】兆易创新 603986
 【核心逻辑】NOR Flash国内龙头，DRAM布局中。存储涨价直接受益。盈亏比3.5:1。
@@ -2092,7 +2092,7 @@
 </t>
       </text>
     </comment>
-    <comment ref="A96" authorId="0" shapeId="0">
+    <comment ref="A101" authorId="0" shapeId="0">
       <text>
         <t xml:space="preserve">【标的】江波龙 301308
 【核心逻辑】存储模组+主控芯片，国产替代核心标的。盈亏比3.5:1。
@@ -2424,7 +2424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:H168"/>
+  <dimension ref="A1:H189"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6171875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="18" customWidth="1" style="138" min="1" max="8"/>
@@ -2724,155 +2724,190 @@
       </c>
     </row>
     <row r="12" ht="16.5" customHeight="1" s="139">
-      <c r="A12" s="148" t="inlineStr">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-06-07 芯片: 蒋宇飞179视频深度提取—国产替代78天一致+黄仁勋1万亿+工信部支持+CPU缺货→虚P+3pp</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="15" customHeight="1" s="139">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-06-07 堆叠: 蒋宇飞27条堆叠主题验证—"两年最大风口"+"一年半大放"+"存算一体"→75%P合理</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="15" customHeight="1" s="139">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-06-07 待重仓新增: MLCC(到2027-H1)/国产算力(2027爆发)/HBM(1.5-2.5年)/CPU(agent经济)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="15" customHeight="1" s="139">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-06-07 存储降级确认: "消费级见顶"+"跌80%但现在是时机"+"涨完轮到堆叠"</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="16.5" customHeight="1" s="139">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-06-07 时间线: 7月长鑫上市→年底MLCC高点→2027-H1 MLCC结束→2027-H2堆叠→2027算力长城→2028玻璃基板</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="16.5" customHeight="1" s="139">
+      <c r="A17" s="148" t="inlineStr">
         <is>
           <t>🔥 叙事主线（四条）</t>
         </is>
       </c>
-      <c r="B12" s="149" t="n"/>
-      <c r="C12" s="149" t="n"/>
-      <c r="D12" s="149" t="n"/>
-      <c r="E12" s="149" t="n"/>
-      <c r="F12" s="149" t="n"/>
-      <c r="G12" s="149" t="n"/>
-      <c r="H12" s="150" t="n"/>
-    </row>
-    <row r="13" ht="15" customHeight="1" s="139">
-      <c r="B13" s="147" t="inlineStr">
+      <c r="B17" s="149" t="n"/>
+      <c r="C17" s="149" t="n"/>
+      <c r="D17" s="149" t="n"/>
+      <c r="E17" s="149" t="n"/>
+      <c r="F17" s="149" t="n"/>
+      <c r="G17" s="149" t="n"/>
+      <c r="H17" s="150" t="n"/>
+    </row>
+    <row r="18" ht="16.5" customHeight="1" s="139">
+      <c r="B18" s="147" t="inlineStr">
         <is>
           <t>①美国国债/利率危机 ⚠️升级：从"慢性走钢丝"→"9月死线"【来源：宋鸿兵6.3视频】。国债39万亿+30年美债破5%+10年破4.5%，沃什上任但市场用脚投票。霍尔木兹不重开→OECD库存6月见底→全球9月触红线→能源成本失控+恶性通胀，利率只涨不跌</t>
         </is>
       </c>
-      <c r="C13" s="149" t="n"/>
-      <c r="D13" s="149" t="n"/>
-      <c r="E13" s="149" t="n"/>
-      <c r="F13" s="149" t="n"/>
-      <c r="G13" s="149" t="n"/>
-      <c r="H13" s="150" t="n"/>
-    </row>
-    <row r="14" ht="15" customHeight="1" s="139">
-      <c r="B14" s="147" t="inlineStr">
+      <c r="C18" s="149" t="n"/>
+      <c r="D18" s="149" t="n"/>
+      <c r="E18" s="149" t="n"/>
+      <c r="F18" s="149" t="n"/>
+      <c r="G18" s="149" t="n"/>
+      <c r="H18" s="150" t="n"/>
+    </row>
+    <row r="19" ht="16.5" customHeight="1" s="139">
+      <c r="B19" s="147" t="inlineStr">
         <is>
           <t>②霍尔木兹/能源危机 🔴重大升级：封锁3个月，有效原油库存8.1亿桶，OECD最早6月触红线。雪佛龙CEO+埃克森VP双重警告，85%投资者押注回落=集体幻觉</t>
         </is>
       </c>
-      <c r="C14" s="149" t="n"/>
-      <c r="D14" s="149" t="n"/>
-      <c r="E14" s="149" t="n"/>
-      <c r="F14" s="149" t="n"/>
-      <c r="G14" s="149" t="n"/>
-      <c r="H14" s="150" t="n"/>
-    </row>
-    <row r="15" ht="15" customHeight="1" s="139">
-      <c r="B15" s="147" t="inlineStr">
+      <c r="C19" s="149" t="n"/>
+      <c r="D19" s="149" t="n"/>
+      <c r="E19" s="149" t="n"/>
+      <c r="F19" s="149" t="n"/>
+      <c r="G19" s="149" t="n"/>
+      <c r="H19" s="150" t="n"/>
+    </row>
+    <row r="20" ht="30" customHeight="1" s="139">
+      <c r="B20" s="147" t="inlineStr">
         <is>
           <t>③中国去杠杆分化 维持：08-18加杠杆→全面去杠杆，对猪周期是加速器，对AI是倒逼器。无新催化</t>
         </is>
       </c>
-      <c r="C15" s="149" t="n"/>
-      <c r="D15" s="149" t="n"/>
-      <c r="E15" s="149" t="n"/>
-      <c r="F15" s="149" t="n"/>
-      <c r="G15" s="149" t="n"/>
-      <c r="H15" s="150" t="n"/>
-    </row>
-    <row r="16" ht="16.5" customHeight="1" s="139">
-      <c r="A16" s="138" t="inlineStr">
+      <c r="C20" s="149" t="n"/>
+      <c r="D20" s="149" t="n"/>
+      <c r="E20" s="149" t="n"/>
+      <c r="F20" s="149" t="n"/>
+      <c r="G20" s="149" t="n"/>
+      <c r="H20" s="150" t="n"/>
+    </row>
+    <row r="21" ht="16.5" customHeight="1" s="139">
+      <c r="A21" s="138" t="inlineStr">
         <is>
           <t>④</t>
         </is>
       </c>
-      <c r="B16" s="138" t="inlineStr">
+      <c r="B21" s="138" t="inlineStr">
         <is>
           <t>比特币独立叙事消亡 维持：资金吸附力排序 AI&gt;美股&gt;黄金&gt;比特币，比特币已成美股影子资产，AI落地后资金有明确去处，比特币价值持续被稀释</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="16.5" customHeight="1" s="139">
-      <c r="A17" s="151" t="inlineStr">
+    <row r="22" ht="16.5" customHeight="1" s="139">
+      <c r="A22" s="151" t="inlineStr">
         <is>
           <t>⚡ AI投资阶段切换指导原则（顶级置信度）</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="16.5" customHeight="1" s="139">
-      <c r="A18" s="152" t="inlineStr">
+    <row r="23" ht="16.5" customHeight="1" s="139">
+      <c r="A23" s="152" t="inlineStr">
         <is>
           <t>AI前半程=投硬件（芯片/算力/堆叠封装）→ 已验证。AI后半程=布局软件/应用端 → 多个信源交叉确认，逻辑高度自洽。此为投资指导原则，不是事件，不作为P值调整依据，但影响赛道选择优先级。</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="16.5" customHeight="1" s="139">
-      <c r="A19" s="153" t="inlineStr">
+    <row r="24" ht="16.5" customHeight="1" s="139">
+      <c r="A24" s="153" t="inlineStr">
         <is>
           <t>🔴🔴🔴 战略级虚P信号池 + 现金策略联动（2026-06-04）🔴🔴🔴</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="30" customHeight="1" s="139">
-      <c r="A20" s="154" t="inlineStr">
+    <row r="25" ht="16.5" customHeight="1" s="139">
+      <c r="A25" s="154" t="inlineStr">
         <is>
           <t>虚P规则：未落地→记虚P→不加实P→等落地转实P。此板块锁定大部分现金，与机会成本联动分析。</t>
         </is>
       </c>
     </row>
-    <row r="21" ht="16.5" customHeight="1" s="139">
-      <c r="A21" s="155" t="inlineStr">
+    <row r="26" ht="15" customHeight="1" s="139">
+      <c r="A26" s="155" t="inlineStr">
         <is>
           <t>一、三源信号详情</t>
         </is>
       </c>
     </row>
-    <row r="22" ht="16.5" customHeight="1" s="139">
-      <c r="A22" s="156" t="inlineStr">
+    <row r="27" ht="16.5" customHeight="1" s="139">
+      <c r="A27" s="156" t="inlineStr">
         <is>
           <t>来源</t>
         </is>
       </c>
-      <c r="B22" s="156" t="inlineStr">
+      <c r="B27" s="156" t="inlineStr">
         <is>
           <t>核心观点</t>
         </is>
       </c>
-      <c r="C22" s="156" t="inlineStr">
+      <c r="C27" s="156" t="inlineStr">
         <is>
           <t>与你策略契合</t>
         </is>
       </c>
-      <c r="D22" s="156" t="inlineStr">
+      <c r="D27" s="156" t="inlineStr">
         <is>
           <t>虚P方向</t>
         </is>
       </c>
-      <c r="E22" s="156" t="inlineStr">
+      <c r="E27" s="156" t="inlineStr">
         <is>
           <t>落地条件</t>
         </is>
       </c>
-      <c r="F22" s="156" t="inlineStr">
+      <c r="F27" s="156" t="inlineStr">
         <is>
           <t>状态</t>
         </is>
       </c>
-      <c r="G22" s="156" t="inlineStr">
+      <c r="G27" s="156" t="inlineStr">
         <is>
           <t>权重</t>
         </is>
       </c>
-      <c r="H22" s="156" t="inlineStr">
+      <c r="H27" s="156" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="23" ht="16.5" customHeight="1" s="139">
-      <c r="A23" s="157" t="inlineStr">
+    <row r="28" ht="15" customHeight="1" s="139">
+      <c r="A28" s="157" t="inlineStr">
         <is>
           <t>达利欧
 Bloomberg 6/3</t>
         </is>
       </c>
-      <c r="B23" s="157" t="inlineStr">
+      <c r="B28" s="157" t="inlineStr">
         <is>
           <t>AI泡沫65-75%概率年底破
 "财富转现金=刺破泡沫"
@@ -2881,7 +2916,7 @@
 基建投入&gt;&gt;收入</t>
         </is>
       </c>
-      <c r="C23" s="158" t="inlineStr">
+      <c r="C28" s="158" t="inlineStr">
         <is>
           <t>完全契合
 等中期选举大跌
@@ -2889,45 +2924,45 @@
 回调后大仓位进</t>
         </is>
       </c>
-      <c r="D23" s="157" t="inlineStr">
+      <c r="D28" s="157" t="inlineStr">
         <is>
           <t>芯片-2pp
 恒科-1pp
 (虚P)</t>
         </is>
       </c>
-      <c r="E23" s="157" t="inlineStr">
+      <c r="E28" s="157" t="inlineStr">
         <is>
           <t>七姐妹&gt;15%回调
 或破200日均线</t>
         </is>
       </c>
-      <c r="F23" s="159" t="inlineStr">
+      <c r="F28" s="159" t="inlineStr">
         <is>
           <t>未落地</t>
         </is>
       </c>
-      <c r="G23" s="160" t="inlineStr">
+      <c r="G28" s="160" t="inlineStr">
         <is>
           <t>极高
 5星</t>
         </is>
       </c>
-      <c r="H23" s="157" t="inlineStr">
+      <c r="H28" s="157" t="inlineStr">
         <is>
           <t>与你100%一致
 回调=买入机会</t>
         </is>
       </c>
     </row>
-    <row r="24" ht="16.5" customHeight="1" s="139">
-      <c r="A24" s="157" t="inlineStr">
+    <row r="29" ht="15" customHeight="1" s="139">
+      <c r="A29" s="157" t="inlineStr">
         <is>
           <t>李大霄
 金融界 6/4</t>
         </is>
       </c>
-      <c r="B24" s="157" t="inlineStr">
+      <c r="B29" s="157" t="inlineStr">
         <is>
           <t>美股窄牛宽熊
 仅20只创新高
@@ -2936,768 +2971,768 @@
 IPO抽血</t>
         </is>
       </c>
-      <c r="C24" s="158" t="inlineStr">
+      <c r="C29" s="158" t="inlineStr">
         <is>
           <t>高度契合
 确认美股风险
 现金策略正确</t>
         </is>
       </c>
-      <c r="D24" s="157" t="inlineStr">
+      <c r="D29" s="157" t="inlineStr">
         <is>
           <t>恒科-2pp
 芯片-1pp
 (虚P)</t>
         </is>
       </c>
-      <c r="E24" s="157" t="inlineStr">
+      <c r="E29" s="157" t="inlineStr">
         <is>
           <t>纳指破200日均线
 多数成分股下跌</t>
         </is>
       </c>
-      <c r="F24" s="159" t="inlineStr">
+      <c r="F29" s="159" t="inlineStr">
         <is>
           <t>未落地</t>
         </is>
       </c>
-      <c r="G24" s="157" t="inlineStr">
+      <c r="G29" s="157" t="inlineStr">
         <is>
           <t>中高
 3星</t>
         </is>
       </c>
-      <c r="H24" s="157" t="inlineStr">
+      <c r="H29" s="157" t="inlineStr">
         <is>
           <t>数据靠谱
 结论偏激进</t>
         </is>
       </c>
     </row>
-    <row r="25" ht="16.5" customHeight="1" s="139">
-      <c r="A25" s="157" t="inlineStr">
+    <row r="30" ht="15" customHeight="1" s="139">
+      <c r="A30" s="157" t="inlineStr">
         <is>
           <t>知乎专栏
 6/4</t>
         </is>
       </c>
-      <c r="B25" s="149" t="n"/>
-      <c r="C25" s="149" t="n"/>
-      <c r="D25" s="149" t="n"/>
-      <c r="E25" s="149" t="n"/>
-      <c r="F25" s="149" t="n"/>
-      <c r="G25" s="149" t="n"/>
-      <c r="H25" s="150" t="n"/>
-    </row>
-    <row r="26" ht="15" customHeight="1" s="139"/>
-    <row r="27" ht="16.5" customHeight="1" s="139">
-      <c r="A27" s="155" t="inlineStr">
+      <c r="B30" s="149" t="n"/>
+      <c r="C30" s="149" t="n"/>
+      <c r="D30" s="149" t="n"/>
+      <c r="E30" s="149" t="n"/>
+      <c r="F30" s="149" t="n"/>
+      <c r="G30" s="149" t="n"/>
+      <c r="H30" s="150" t="n"/>
+    </row>
+    <row r="31" ht="15" customHeight="1" s="139"/>
+    <row r="32" ht="15" customHeight="1" s="139">
+      <c r="A32" s="155" t="inlineStr">
         <is>
           <t>二、三源互锁验证</t>
         </is>
       </c>
     </row>
-    <row r="28" ht="15" customHeight="1" s="139">
-      <c r="A28" s="161" t="inlineStr">
+    <row r="33" ht="16.5" customHeight="1" s="139">
+      <c r="A33" s="161" t="inlineStr">
         <is>
           <t>互锁组合</t>
         </is>
       </c>
-      <c r="B28" s="161" t="inlineStr">
+      <c r="B33" s="161" t="inlineStr">
         <is>
           <t>关系</t>
         </is>
       </c>
-      <c r="C28" s="161" t="inlineStr">
+      <c r="C33" s="161" t="inlineStr">
         <is>
           <t>分析</t>
         </is>
       </c>
-      <c r="D28" s="161" t="inlineStr">
+      <c r="D33" s="161" t="inlineStr">
         <is>
           <t>信号强度</t>
         </is>
       </c>
     </row>
-    <row r="29" ht="15" customHeight="1" s="139">
-      <c r="A29" s="162" t="inlineStr">
+    <row r="34" ht="16.5" customHeight="1" s="139">
+      <c r="A34" s="162" t="inlineStr">
         <is>
           <t>达利欧×李大霄</t>
         </is>
       </c>
-      <c r="B29" s="163" t="inlineStr">
+      <c r="B34" s="163" t="inlineStr">
         <is>
           <t>✅强印证</t>
         </is>
       </c>
-      <c r="C29" s="157" t="inlineStr">
+      <c r="C34" s="157" t="inlineStr">
         <is>
           <t>AI泡沫+窄牛宽熊=同一现象两角度</t>
         </is>
       </c>
-      <c r="D29" s="157" t="inlineStr">
+      <c r="D34" s="157" t="inlineStr">
         <is>
           <t>🔴强信号</t>
         </is>
       </c>
     </row>
-    <row r="30" ht="15" customHeight="1" s="139">
-      <c r="A30" s="162" t="inlineStr">
+    <row r="35" ht="16.5" customHeight="1" s="139">
+      <c r="A35" s="162" t="inlineStr">
         <is>
           <t>达利欧×知乎</t>
         </is>
       </c>
-      <c r="B30" s="164" t="inlineStr">
+      <c r="B35" s="164" t="inlineStr">
         <is>
           <t>⚠️部分矛盾</t>
         </is>
       </c>
-      <c r="C30" s="157" t="inlineStr">
+      <c r="C35" s="157" t="inlineStr">
         <is>
           <t>达看流动性vs知乎看估值</t>
         </is>
       </c>
-      <c r="D30" s="157" t="inlineStr">
+      <c r="D35" s="157" t="inlineStr">
         <is>
           <t>🟡中性</t>
         </is>
       </c>
     </row>
-    <row r="31" ht="15" customHeight="1" s="139">
-      <c r="A31" s="162" t="inlineStr">
+    <row r="36" ht="16.5" customHeight="1" s="139">
+      <c r="A36" s="162" t="inlineStr">
         <is>
           <t>三源共识</t>
         </is>
       </c>
-      <c r="B31" s="149" t="n"/>
-      <c r="C31" s="149" t="n"/>
-      <c r="D31" s="149" t="n"/>
-      <c r="E31" s="149" t="n"/>
-      <c r="F31" s="149" t="n"/>
-      <c r="G31" s="149" t="n"/>
-      <c r="H31" s="150" t="n"/>
-    </row>
-    <row r="32" ht="15" customHeight="1" s="139">
-      <c r="A32" s="138" t="n"/>
-    </row>
-    <row r="33" ht="16.5" customHeight="1" s="139">
-      <c r="A33" s="165" t="inlineStr">
+      <c r="B36" s="149" t="n"/>
+      <c r="C36" s="149" t="n"/>
+      <c r="D36" s="149" t="n"/>
+      <c r="E36" s="149" t="n"/>
+      <c r="F36" s="149" t="n"/>
+      <c r="G36" s="149" t="n"/>
+      <c r="H36" s="150" t="n"/>
+    </row>
+    <row r="37" ht="16.5" customHeight="1" s="139">
+      <c r="A37" s="138" t="n"/>
+    </row>
+    <row r="38" ht="16.5" customHeight="1" s="139">
+      <c r="A38" s="165" t="inlineStr">
         <is>
           <t>三、现金策略联动（锁定大部分现金储备）</t>
         </is>
       </c>
     </row>
-    <row r="34" ht="16.5" customHeight="1" s="139">
-      <c r="A34" s="154" t="inlineStr">
+    <row r="39" ht="16.5" customHeight="1" s="139">
+      <c r="A39" s="154" t="inlineStr">
         <is>
           <t>三源联动→达利欧65-75%概率年底AI回调+中期选举历史跌一波→锁定大部分现金→等11月回调入场</t>
         </is>
       </c>
     </row>
-    <row r="35" ht="16.5" customHeight="1" s="139">
-      <c r="A35" s="161" t="inlineStr">
+    <row r="40" ht="16.5" customHeight="1" s="139">
+      <c r="A40" s="161" t="inlineStr">
         <is>
           <t>维度</t>
         </is>
       </c>
-      <c r="B35" s="161" t="inlineStr">
+      <c r="B40" s="161" t="inlineStr">
         <is>
           <t>内容</t>
         </is>
       </c>
-      <c r="C35" s="161" t="inlineStr">
+      <c r="C40" s="161" t="inlineStr">
         <is>
           <t>影响</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="16.5" customHeight="1" s="139">
-      <c r="A36" s="157" t="inlineStr">
-        <is>
-          <t>现金锁定</t>
-        </is>
-      </c>
-      <c r="B36" s="157" t="inlineStr">
-        <is>
-          <t>大部分现金(60-70%)锁定等待</t>
-        </is>
-      </c>
-      <c r="C36" s="157" t="inlineStr">
-        <is>
-          <t>→当前可投资金大幅减少</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" ht="16.5" customHeight="1" s="139">
-      <c r="A37" s="157" t="inlineStr">
-        <is>
-          <t>等待窗口</t>
-        </is>
-      </c>
-      <c r="B37" s="157" t="inlineStr">
-        <is>
-          <t>2026年11月中期选举前后</t>
-        </is>
-      </c>
-      <c r="C37" s="157" t="inlineStr">
-        <is>
-          <t>→约5个月等待期</t>
-        </is>
-      </c>
-    </row>
-    <row r="38" ht="16.5" customHeight="1" s="139">
-      <c r="A38" s="157" t="inlineStr">
-        <is>
-          <t>触发条件</t>
-        </is>
-      </c>
-      <c r="B38" s="157" t="inlineStr">
-        <is>
-          <t>美股跌一波+AI回调&gt;15%</t>
-        </is>
-      </c>
-      <c r="C38" s="157" t="inlineStr">
-        <is>
-          <t>→达利欧65-75%概率事件</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" ht="16.5" customHeight="1" s="139">
-      <c r="A39" s="157" t="inlineStr">
-        <is>
-          <t>入场标的</t>
-        </is>
-      </c>
-      <c r="B39" s="157" t="inlineStr">
-        <is>
-          <t>堆叠：长电科技+通富微电</t>
-        </is>
-      </c>
-      <c r="C39" s="157" t="inlineStr">
-        <is>
-          <t>→国内确定性不受美股影响</t>
-        </is>
-      </c>
-    </row>
-    <row r="40" ht="16.5" customHeight="1" s="139">
-      <c r="A40" s="157" t="inlineStr">
-        <is>
-          <t>机会成本</t>
-        </is>
-      </c>
-      <c r="B40" s="157" t="inlineStr">
-        <is>
-          <t>持有现金5个月vs错过短期行情</t>
-        </is>
-      </c>
-      <c r="C40" s="157" t="inlineStr">
-        <is>
-          <t>→见下方机会成本联动</t>
         </is>
       </c>
     </row>
     <row r="41" ht="16.5" customHeight="1" s="139">
       <c r="A41" s="157" t="inlineStr">
         <is>
-          <t>下行保护</t>
-        </is>
-      </c>
-      <c r="B41" s="149" t="n"/>
-      <c r="C41" s="149" t="n"/>
-      <c r="D41" s="149" t="n"/>
-      <c r="E41" s="149" t="n"/>
-      <c r="F41" s="149" t="n"/>
-      <c r="G41" s="149" t="n"/>
-      <c r="H41" s="150" t="n"/>
-    </row>
-    <row r="42" ht="16.5" customHeight="1" s="139"/>
+          <t>现金锁定</t>
+        </is>
+      </c>
+      <c r="B41" s="157" t="inlineStr">
+        <is>
+          <t>大部分现金(60-70%)锁定等待</t>
+        </is>
+      </c>
+      <c r="C41" s="157" t="inlineStr">
+        <is>
+          <t>→当前可投资金大幅减少</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="16.5" customHeight="1" s="139">
+      <c r="A42" s="157" t="inlineStr">
+        <is>
+          <t>等待窗口</t>
+        </is>
+      </c>
+      <c r="B42" s="157" t="inlineStr">
+        <is>
+          <t>2026年11月中期选举前后</t>
+        </is>
+      </c>
+      <c r="C42" s="157" t="inlineStr">
+        <is>
+          <t>→约5个月等待期</t>
+        </is>
+      </c>
+    </row>
     <row r="43" ht="16.5" customHeight="1" s="139">
-      <c r="A43" s="165" t="inlineStr">
-        <is>
-          <t>四、机会成本联动分析（现金锁定vs其他选项）</t>
+      <c r="A43" s="157" t="inlineStr">
+        <is>
+          <t>触发条件</t>
+        </is>
+      </c>
+      <c r="B43" s="157" t="inlineStr">
+        <is>
+          <t>美股跌一波+AI回调&gt;15%</t>
+        </is>
+      </c>
+      <c r="C43" s="157" t="inlineStr">
+        <is>
+          <t>→达利欧65-75%概率事件</t>
         </is>
       </c>
     </row>
     <row r="44" ht="16.5" customHeight="1" s="139">
-      <c r="A44" s="161" t="inlineStr">
-        <is>
-          <t>选项</t>
-        </is>
-      </c>
-      <c r="B44" s="161" t="inlineStr">
-        <is>
-          <t>P值</t>
-        </is>
-      </c>
-      <c r="C44" s="161" t="inlineStr">
-        <is>
-          <t>盈亏比</t>
-        </is>
-      </c>
-      <c r="D44" s="161" t="inlineStr">
-        <is>
-          <t>Score</t>
-        </is>
-      </c>
-      <c r="E44" s="161" t="inlineStr">
-        <is>
-          <t>现金锁定影响</t>
-        </is>
-      </c>
-      <c r="F44" s="161" t="inlineStr">
-        <is>
-          <t>建议</t>
-        </is>
-      </c>
-      <c r="G44" s="161" t="inlineStr">
-        <is>
-          <t>判断</t>
+      <c r="A44" s="157" t="inlineStr">
+        <is>
+          <t>入场标的</t>
+        </is>
+      </c>
+      <c r="B44" s="157" t="inlineStr">
+        <is>
+          <t>堆叠：长电科技+通富微电</t>
+        </is>
+      </c>
+      <c r="C44" s="157" t="inlineStr">
+        <is>
+          <t>→国内确定性不受美股影响</t>
         </is>
       </c>
     </row>
     <row r="45" ht="16.5" customHeight="1" s="139">
       <c r="A45" s="157" t="inlineStr">
         <is>
+          <t>机会成本</t>
+        </is>
+      </c>
+      <c r="B45" s="157" t="inlineStr">
+        <is>
+          <t>持有现金5个月vs错过短期行情</t>
+        </is>
+      </c>
+      <c r="C45" s="157" t="inlineStr">
+        <is>
+          <t>→见下方机会成本联动</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="16.5" customHeight="1" s="139">
+      <c r="A46" s="157" t="inlineStr">
+        <is>
+          <t>下行保护</t>
+        </is>
+      </c>
+      <c r="B46" s="149" t="n"/>
+      <c r="C46" s="149" t="n"/>
+      <c r="D46" s="149" t="n"/>
+      <c r="E46" s="149" t="n"/>
+      <c r="F46" s="149" t="n"/>
+      <c r="G46" s="149" t="n"/>
+      <c r="H46" s="150" t="n"/>
+    </row>
+    <row r="47" ht="16.5" customHeight="1" s="139"/>
+    <row r="48" ht="16.5" customHeight="1" s="139">
+      <c r="A48" s="165" t="inlineStr">
+        <is>
+          <t>四、机会成本联动分析（现金锁定vs其他选项）</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="16.5" customHeight="1" s="139">
+      <c r="A49" s="161" t="inlineStr">
+        <is>
+          <t>选项</t>
+        </is>
+      </c>
+      <c r="B49" s="161" t="inlineStr">
+        <is>
+          <t>P值</t>
+        </is>
+      </c>
+      <c r="C49" s="161" t="inlineStr">
+        <is>
+          <t>盈亏比</t>
+        </is>
+      </c>
+      <c r="D49" s="161" t="inlineStr">
+        <is>
+          <t>Score</t>
+        </is>
+      </c>
+      <c r="E49" s="161" t="inlineStr">
+        <is>
+          <t>现金锁定影响</t>
+        </is>
+      </c>
+      <c r="F49" s="161" t="inlineStr">
+        <is>
+          <t>建议</t>
+        </is>
+      </c>
+      <c r="G49" s="161" t="inlineStr">
+        <is>
+          <t>判断</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="15" customHeight="1" s="139">
+      <c r="A50" s="157" t="inlineStr">
+        <is>
           <t>长电科技</t>
         </is>
       </c>
-      <c r="B45" s="157" t="inlineStr">
+      <c r="B50" s="157" t="inlineStr">
         <is>
           <t>75%</t>
         </is>
       </c>
-      <c r="C45" s="157" t="inlineStr">
+      <c r="C50" s="157" t="inlineStr">
         <is>
           <t>4.5:1</t>
         </is>
       </c>
-      <c r="D45" s="157" t="inlineStr">
+      <c r="D50" s="157" t="inlineStr">
         <is>
           <t>3.375</t>
         </is>
       </c>
-      <c r="E45" s="157" t="inlineStr">
+      <c r="E50" s="157" t="inlineStr">
         <is>
           <t>等回调大仓位
 现金锁定中</t>
         </is>
       </c>
-      <c r="F45" s="157" t="inlineStr">
+      <c r="F50" s="157" t="inlineStr">
         <is>
           <t>暂不动等11月</t>
         </is>
       </c>
-      <c r="G45" s="160" t="inlineStr">
+      <c r="G50" s="160" t="inlineStr">
         <is>
           <t>🔴最高优先</t>
         </is>
       </c>
     </row>
-    <row r="46" ht="16.5" customHeight="1" s="139">
-      <c r="A46" s="157" t="inlineStr">
+    <row r="51" ht="15" customHeight="1" s="139">
+      <c r="A51" s="157" t="inlineStr">
         <is>
           <t>通富微电</t>
         </is>
       </c>
-      <c r="B46" s="157" t="inlineStr">
+      <c r="B51" s="157" t="inlineStr">
         <is>
           <t>75%</t>
         </is>
       </c>
-      <c r="C46" s="157" t="inlineStr">
+      <c r="C51" s="157" t="inlineStr">
         <is>
           <t>4.0:1</t>
         </is>
       </c>
-      <c r="D46" s="157" t="inlineStr">
+      <c r="D51" s="157" t="inlineStr">
         <is>
           <t>3.000</t>
         </is>
       </c>
-      <c r="E46" s="157" t="inlineStr">
+      <c r="E51" s="157" t="inlineStr">
         <is>
           <t>等回调大仓位
 现金锁定中</t>
         </is>
       </c>
-      <c r="F46" s="157" t="inlineStr">
+      <c r="F51" s="157" t="inlineStr">
         <is>
           <t>暂不动等11月</t>
         </is>
       </c>
-      <c r="G46" s="160" t="inlineStr">
+      <c r="G51" s="160" t="inlineStr">
         <is>
           <t>🔴最高优先</t>
         </is>
       </c>
     </row>
-    <row r="47" ht="16.5" customHeight="1" s="139">
-      <c r="A47" s="157" t="inlineStr">
+    <row r="52" ht="77.59999999999999" customHeight="1" s="139">
+      <c r="A52" s="157" t="inlineStr">
         <is>
           <t>养殖</t>
         </is>
       </c>
-      <c r="B47" s="157" t="inlineStr">
+      <c r="B52" s="157" t="inlineStr">
         <is>
           <t>70%</t>
         </is>
       </c>
-      <c r="C47" s="157" t="inlineStr">
+      <c r="C52" s="157" t="inlineStr">
         <is>
           <t>2.0:1</t>
         </is>
       </c>
-      <c r="D47" s="157" t="inlineStr">
+      <c r="D52" s="157" t="inlineStr">
         <is>
           <t>1.400</t>
         </is>
       </c>
-      <c r="E47" s="157" t="inlineStr">
+      <c r="E52" s="157" t="inlineStr">
         <is>
           <t>已持仓不需现金 | 6/5 芳姐：低价抄底母猪，行业融资枯竭，等待母猪血流成河才是最佳买点</t>
         </is>
       </c>
-      <c r="F47" s="157" t="inlineStr">
+      <c r="F52" s="157" t="inlineStr">
         <is>
           <t>继续持有</t>
         </is>
       </c>
-      <c r="G47" s="158" t="inlineStr">
+      <c r="G52" s="158" t="inlineStr">
         <is>
           <t>✅已配置</t>
         </is>
       </c>
     </row>
-    <row r="48" ht="16.5" customHeight="1" s="139">
-      <c r="A48" s="157" t="inlineStr">
+    <row r="53" ht="17.15" customHeight="1" s="139">
+      <c r="A53" s="157" t="inlineStr">
         <is>
           <t>电池</t>
         </is>
       </c>
-      <c r="B48" s="157" t="inlineStr">
+      <c r="B53" s="157" t="inlineStr">
         <is>
           <t>65%</t>
         </is>
       </c>
-      <c r="C48" s="157" t="inlineStr">
+      <c r="C53" s="157" t="inlineStr">
         <is>
           <t>2.0:1</t>
         </is>
       </c>
-      <c r="D48" s="157" t="inlineStr">
+      <c r="D53" s="157" t="inlineStr">
         <is>
           <t>1.300</t>
         </is>
       </c>
-      <c r="E48" s="157" t="inlineStr">
+      <c r="E53" s="157" t="inlineStr">
         <is>
           <t>已持仓不需现金 | 6/5 闻号说经济：厄尔尼诺80%概率+AI用电爆发→电力/能源受益</t>
         </is>
       </c>
-      <c r="F48" s="157" t="inlineStr">
+      <c r="F53" s="157" t="inlineStr">
         <is>
           <t>继续持有</t>
         </is>
       </c>
-      <c r="G48" s="158" t="inlineStr">
+      <c r="G53" s="158" t="inlineStr">
         <is>
           <t>✅已配置</t>
         </is>
       </c>
     </row>
-    <row r="49" ht="16.5" customHeight="1" s="139">
-      <c r="A49" s="157" t="inlineStr">
+    <row r="54" ht="26.85" customHeight="1" s="139">
+      <c r="A54" s="157" t="inlineStr">
         <is>
           <t>核电</t>
         </is>
       </c>
-      <c r="B49" s="157" t="inlineStr">
+      <c r="B54" s="157" t="inlineStr">
         <is>
           <t>52%</t>
         </is>
       </c>
-      <c r="C49" s="157" t="inlineStr">
+      <c r="C54" s="157" t="inlineStr">
         <is>
           <t>1.5:1</t>
         </is>
       </c>
-      <c r="D49" s="157" t="inlineStr">
+      <c r="D54" s="157" t="inlineStr">
         <is>
           <t>0.780</t>
         </is>
       </c>
-      <c r="E49" s="157" t="inlineStr">
+      <c r="E54" s="157" t="inlineStr">
         <is>
           <t>10年维度
 小仓试水可行</t>
         </is>
       </c>
-      <c r="F49" s="157" t="inlineStr">
+      <c r="F54" s="157" t="inlineStr">
         <is>
           <t>不影响现金策略</t>
         </is>
       </c>
-      <c r="G49" s="166" t="inlineStr">
+      <c r="G54" s="166" t="inlineStr">
         <is>
           <t>🟡长期观察</t>
         </is>
       </c>
     </row>
-    <row r="50" ht="15" customHeight="1" s="139">
-      <c r="A50" s="157" t="inlineStr">
+    <row r="55" ht="29.85" customHeight="1" s="139">
+      <c r="A55" s="157" t="inlineStr">
         <is>
           <t>存储</t>
         </is>
       </c>
-      <c r="B50" s="157" t="inlineStr">
+      <c r="B55" s="157" t="inlineStr">
         <is>
           <t>55%</t>
         </is>
       </c>
-      <c r="C50" s="157" t="inlineStr">
+      <c r="C55" s="157" t="inlineStr">
         <is>
           <t>1.0:1</t>
         </is>
       </c>
-      <c r="D50" s="157" t="inlineStr">
+      <c r="D55" s="157" t="inlineStr">
         <is>
           <t>0.550</t>
         </is>
       </c>
-      <c r="E50" s="157" t="inlineStr">
+      <c r="E55" s="157" t="inlineStr">
         <is>
           <t>已降级</t>
         </is>
       </c>
-      <c r="F50" s="157" t="inlineStr">
+      <c r="F55" s="157" t="inlineStr">
         <is>
           <t>不动</t>
         </is>
       </c>
-      <c r="G50" s="160" t="inlineStr">
+      <c r="G55" s="160" t="inlineStr">
         <is>
           <t>❌已降级</t>
         </is>
       </c>
     </row>
-    <row r="51" ht="15" customHeight="1" s="139">
-      <c r="A51" s="157" t="inlineStr">
+    <row r="56" ht="29.85" customHeight="1" s="139">
+      <c r="A56" s="157" t="inlineStr">
         <is>
           <t>纯现金5月</t>
         </is>
       </c>
-      <c r="B51" s="149" t="n"/>
-      <c r="C51" s="149" t="n"/>
-      <c r="D51" s="149" t="n"/>
-      <c r="E51" s="149" t="n"/>
-      <c r="F51" s="149" t="n"/>
-      <c r="G51" s="149" t="n"/>
-      <c r="H51" s="150" t="n"/>
-    </row>
-    <row r="52" ht="77.59999999999999" customHeight="1" s="139">
-      <c r="A52" s="147" t="inlineStr">
+      <c r="B56" s="149" t="n"/>
+      <c r="C56" s="149" t="n"/>
+      <c r="D56" s="149" t="n"/>
+      <c r="E56" s="149" t="n"/>
+      <c r="F56" s="149" t="n"/>
+      <c r="G56" s="149" t="n"/>
+      <c r="H56" s="150" t="n"/>
+    </row>
+    <row r="57" ht="15" customHeight="1" s="139">
+      <c r="A57" s="147" t="inlineStr">
         <is>
           <t>AI硬件确定性(付鹏) → 内存=AI核心瓶颈(4信源互锁) → 国产替代加速 → 稀土断供日本 → 芯片/存储/HBM长期利好 | 短期被利率↑/地缘↑压制</t>
         </is>
       </c>
     </row>
-    <row r="53" ht="17.15" customHeight="1" s="139">
-      <c r="A53" s="167" t="inlineStr">
+    <row r="58" ht="15" customHeight="1" s="139">
+      <c r="A58" s="167" t="inlineStr">
         <is>
           <t>五、虚P→实P转换条件 &amp; 操作触发</t>
         </is>
       </c>
-      <c r="B53" s="168" t="n"/>
-      <c r="C53" s="168" t="n"/>
-      <c r="D53" s="168" t="n"/>
-      <c r="E53" s="168" t="n"/>
-      <c r="F53" s="168" t="n"/>
-      <c r="G53" s="168" t="n"/>
-      <c r="H53" s="169" t="n"/>
-    </row>
-    <row r="54" ht="26.85" customHeight="1" s="139">
-      <c r="A54" s="156" t="inlineStr">
+      <c r="B58" s="168" t="n"/>
+      <c r="C58" s="168" t="n"/>
+      <c r="D58" s="168" t="n"/>
+      <c r="E58" s="168" t="n"/>
+      <c r="F58" s="168" t="n"/>
+      <c r="G58" s="168" t="n"/>
+      <c r="H58" s="169" t="n"/>
+    </row>
+    <row r="59" ht="58.2" customHeight="1" s="139">
+      <c r="A59" s="156" t="inlineStr">
         <is>
           <t>条件</t>
         </is>
       </c>
-      <c r="B54" s="161" t="inlineStr">
+      <c r="B59" s="161" t="inlineStr">
         <is>
           <t>触发信号</t>
         </is>
       </c>
-      <c r="C54" s="156" t="inlineStr">
+      <c r="C59" s="156" t="inlineStr">
         <is>
           <t>影响</t>
         </is>
       </c>
-      <c r="D54" s="156" t="inlineStr">
+      <c r="D59" s="156" t="inlineStr">
         <is>
           <t>操作</t>
         </is>
       </c>
-      <c r="E54" s="147" t="inlineStr">
+      <c r="E59" s="147" t="inlineStr">
         <is>
           <t>2026-05-30 宋鸿兵：海峡封锁→能源成本飙升</t>
         </is>
       </c>
-      <c r="F54" s="147" t="inlineStr">
+      <c r="F59" s="147" t="inlineStr">
         <is>
           <t>2026-05-30 岩松：存储1-2年产能饱和</t>
         </is>
       </c>
-      <c r="G54" s="147" t="inlineStr">
+      <c r="G59" s="147" t="inlineStr">
         <is>
           <t>2026-05-30 宋鸿兵：30年美债破5%双红线</t>
         </is>
       </c>
     </row>
-    <row r="55" ht="29.85" customHeight="1" s="139">
-      <c r="A55" s="170" t="inlineStr">
+    <row r="60" ht="173.1" customHeight="1" s="139">
+      <c r="A60" s="170" t="inlineStr">
         <is>
           <t>达利欧落地</t>
         </is>
       </c>
-      <c r="B55" s="157" t="inlineStr">
+      <c r="B60" s="157" t="inlineStr">
         <is>
           <t>七姐妹&gt;15%回调或破200日均线</t>
         </is>
       </c>
-      <c r="C55" s="157" t="inlineStr">
+      <c r="C60" s="157" t="inlineStr">
         <is>
           <t>芯片/恒科虚P转实P</t>
         </is>
       </c>
-      <c r="D55" s="157" t="inlineStr">
+      <c r="D60" s="157" t="inlineStr">
         <is>
           <t>现金解锁→大仓位进堆叠</t>
         </is>
       </c>
     </row>
-    <row r="56" ht="29.85" customHeight="1" s="139">
-      <c r="A56" s="166" t="inlineStr">
+    <row r="61" ht="15" customHeight="1" s="139">
+      <c r="A61" s="166" t="inlineStr">
         <is>
           <t>李大霄落地</t>
         </is>
       </c>
-      <c r="B56" s="157" t="inlineStr">
+      <c r="B61" s="157" t="inlineStr">
         <is>
           <t>多数成分股下跌+指数拐头</t>
         </is>
       </c>
-      <c r="C56" s="157" t="inlineStr">
+      <c r="C61" s="157" t="inlineStr">
         <is>
           <t>恒科/芯片虚P转实P</t>
         </is>
       </c>
-      <c r="D56" s="157" t="inlineStr">
+      <c r="D61" s="157" t="inlineStr">
         <is>
           <t>确认系统性风险→入场</t>
         </is>
       </c>
     </row>
-    <row r="57" ht="15" customHeight="1" s="139">
-      <c r="A57" s="171" t="inlineStr">
+    <row r="62" ht="15" customHeight="1" s="139">
+      <c r="A62" s="171" t="inlineStr">
         <is>
           <t>中期选举</t>
         </is>
       </c>
-      <c r="B57" s="171" t="inlineStr">
+      <c r="B62" s="171" t="inlineStr">
         <is>
           <t>11月美股跌一波</t>
         </is>
       </c>
-      <c r="C57" s="171" t="inlineStr">
+      <c r="C62" s="171" t="inlineStr">
         <is>
           <t>你的策略触发</t>
         </is>
       </c>
-      <c r="D57" s="171" t="inlineStr">
+      <c r="D62" s="171" t="inlineStr">
         <is>
           <t>现金→长电+通富</t>
         </is>
       </c>
-      <c r="E57" s="156" t="inlineStr">
+      <c r="E62" s="156" t="inlineStr">
         <is>
           <t>落地条件</t>
         </is>
       </c>
-      <c r="F57" s="156" t="inlineStr">
+      <c r="F62" s="156" t="inlineStr">
         <is>
           <t>状态</t>
         </is>
       </c>
-      <c r="G57" s="156" t="inlineStr">
+      <c r="G62" s="156" t="inlineStr">
         <is>
           <t>权重</t>
         </is>
       </c>
-      <c r="H57" s="156" t="inlineStr">
+      <c r="H62" s="156" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="58" ht="15" customHeight="1" s="139">
-      <c r="A58" s="157" t="inlineStr">
+    <row r="63" ht="48.5" customHeight="1" s="139">
+      <c r="A63" s="157" t="inlineStr">
         <is>
           <t>堆叠独立</t>
         </is>
       </c>
-      <c r="B58" s="149" t="n"/>
-      <c r="C58" s="149" t="n"/>
-      <c r="D58" s="149" t="n"/>
-      <c r="E58" s="149" t="n"/>
-      <c r="F58" s="149" t="n"/>
-      <c r="G58" s="149" t="n"/>
-      <c r="H58" s="150" t="n"/>
-    </row>
-    <row r="59" ht="58.2" customHeight="1" s="139">
-      <c r="A59" s="157" t="inlineStr">
+      <c r="B63" s="149" t="n"/>
+      <c r="C63" s="149" t="n"/>
+      <c r="D63" s="149" t="n"/>
+      <c r="E63" s="149" t="n"/>
+      <c r="F63" s="149" t="n"/>
+      <c r="G63" s="149" t="n"/>
+      <c r="H63" s="150" t="n"/>
+    </row>
+    <row r="64" ht="48.5" customHeight="1" s="139">
+      <c r="A64" s="157" t="inlineStr">
         <is>
           <t>李大霄
 金融界 6/4</t>
         </is>
       </c>
-      <c r="B59" s="157" t="inlineStr">
+      <c r="B64" s="157" t="inlineStr">
         <is>
           <t>美股窄牛宽熊
 仅20只创新高
 CAPE40倍→泡沫</t>
         </is>
       </c>
-      <c r="C59" s="158" t="inlineStr">
+      <c r="C64" s="158" t="inlineStr">
         <is>
           <t>🟢高度契合
 确认美股风险
 现金策略正确</t>
         </is>
       </c>
-      <c r="D59" s="157" t="inlineStr">
+      <c r="D64" s="157" t="inlineStr">
         <is>
           <t>美股全市场↓
 港股连带承压</t>
         </is>
       </c>
-      <c r="E59" s="157" t="inlineStr">
+      <c r="E64" s="157" t="inlineStr">
         <is>
           <t>纳指破200日均线
 或多数成分股下跌</t>
         </is>
       </c>
-      <c r="F59" s="159" t="inlineStr">
+      <c r="F64" s="159" t="inlineStr">
         <is>
           <t>⏳未落地
 (虚P状态)</t>
         </is>
       </c>
-      <c r="G59" s="157" t="inlineStr">
+      <c r="G64" s="157" t="inlineStr">
         <is>
           <t>⭐⭐⭐
 中高</t>
         </is>
       </c>
-      <c r="H59" s="157" t="inlineStr">
+      <c r="H64" s="157" t="inlineStr">
         <is>
           <t>6/4三源联动:
 恒科-2pp
@@ -3707,1705 +3742,1872 @@
         </is>
       </c>
     </row>
-    <row r="60" ht="173.1" customHeight="1" s="139">
-      <c r="A60" s="172" t="inlineStr">
+    <row r="65" ht="64.15000000000001" customHeight="1" s="139">
+      <c r="A65" s="172" t="inlineStr">
         <is>
           <t>⚡ 核心结论：三源联动确认AI泡沫风险+你的中期选举策略正确。大部分现金锁定等11月回调→大仓位进长电/通富。机会成本可接受（不对称博弈，下有保底）。虚P已记，等落地转实P。</t>
         </is>
       </c>
-      <c r="B60" s="168" t="n"/>
-      <c r="C60" s="168" t="n"/>
-      <c r="D60" s="168" t="n"/>
-      <c r="E60" s="168" t="n"/>
-      <c r="F60" s="168" t="n"/>
-      <c r="G60" s="168" t="n"/>
-      <c r="H60" s="169" t="n"/>
-    </row>
-    <row r="61" ht="15" customHeight="1" s="139">
-      <c r="A61" s="138" t="inlineStr">
+      <c r="B65" s="168" t="n"/>
+      <c r="C65" s="168" t="n"/>
+      <c r="D65" s="168" t="n"/>
+      <c r="E65" s="168" t="n"/>
+      <c r="F65" s="168" t="n"/>
+      <c r="G65" s="168" t="n"/>
+      <c r="H65" s="169" t="n"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="138" t="inlineStr">
         <is>
           <t>────────────────────────────────────────────────────────────</t>
         </is>
       </c>
     </row>
-    <row r="62" ht="15" customHeight="1" s="139">
-      <c r="A62" s="173" t="inlineStr">
+    <row r="67" ht="17.15" customHeight="1" s="139">
+      <c r="A67" s="173" t="inlineStr">
         <is>
           <t>🔗 三源互锁验证</t>
-        </is>
-      </c>
-    </row>
-    <row r="63" ht="48.5" customHeight="1" s="139">
-      <c r="A63" s="140" t="inlineStr">
-        <is>
-          <t>达利欧 × 李大霄</t>
-        </is>
-      </c>
-      <c r="C63" s="174" t="inlineStr">
-        <is>
-          <t>✅ 强印证</t>
-        </is>
-      </c>
-      <c r="E63" s="175" t="inlineStr">
-        <is>
-          <t>AI泡沫+窄牛宽熊=同一现象两角度，互相确认</t>
-        </is>
-      </c>
-    </row>
-    <row r="64" ht="48.5" customHeight="1" s="139">
-      <c r="A64" s="140" t="inlineStr">
-        <is>
-          <t>达利欧 × 知乎</t>
-        </is>
-      </c>
-      <c r="C64" s="176" t="inlineStr">
-        <is>
-          <t>⚠️ 部分矛盾</t>
-        </is>
-      </c>
-      <c r="E64" s="175" t="inlineStr">
-        <is>
-          <t>达利欧看流动性(泡沫将破) vs 知乎看估值(PE中值安全)</t>
-        </is>
-      </c>
-    </row>
-    <row r="65" ht="64.15000000000001" customHeight="1" s="139">
-      <c r="A65" s="140" t="inlineStr">
-        <is>
-          <t>三源共识</t>
-        </is>
-      </c>
-      <c r="C65" s="177" t="inlineStr">
-        <is>
-          <t>🔴 核心共识</t>
-        </is>
-      </c>
-      <c r="E65" s="175" t="inlineStr">
-        <is>
-          <t>AI龙头估值偏高+市场极度集中+中小盘已熊 → 短期风险&gt;机会</t>
-        </is>
-      </c>
-    </row>
-    <row r="67" ht="17.15" customHeight="1" s="139">
-      <c r="A67" s="165" t="inlineStr">
-        <is>
-          <t>🎯 结论（虚P→实P转换条件）</t>
         </is>
       </c>
     </row>
     <row r="68" ht="48.5" customHeight="1" s="139">
       <c r="A68" s="140" t="inlineStr">
         <is>
-          <t>① 达利欧信号落地条件</t>
-        </is>
-      </c>
-      <c r="C68" s="175" t="inlineStr">
-        <is>
-          <t>纳指七姐妹出现&gt;15%回调 或 纳指破200日均线</t>
-        </is>
-      </c>
-      <c r="E68" s="178" t="inlineStr">
-        <is>
-          <t>→ 芯片/恒科虚P转实P → 确认减仓信号</t>
+          <t>达利欧 × 李大霄</t>
+        </is>
+      </c>
+      <c r="C68" s="174" t="inlineStr">
+        <is>
+          <t>✅ 强印证</t>
+        </is>
+      </c>
+      <c r="E68" s="175" t="inlineStr">
+        <is>
+          <t>AI泡沫+窄牛宽熊=同一现象两角度，互相确认</t>
         </is>
       </c>
     </row>
     <row r="69" ht="32.8" customHeight="1" s="139">
       <c r="A69" s="140" t="inlineStr">
         <is>
-          <t>② 李大霄信号落地条件</t>
-        </is>
-      </c>
-      <c r="C69" s="175" t="inlineStr">
-        <is>
-          <t>纳指多数成分股连续下跌+指数拐头</t>
-        </is>
-      </c>
-      <c r="E69" s="178" t="inlineStr">
-        <is>
-          <t>→ 恒科/芯片虚P转实P → 确认美股系统性风险</t>
+          <t>达利欧 × 知乎</t>
+        </is>
+      </c>
+      <c r="C69" s="176" t="inlineStr">
+        <is>
+          <t>⚠️ 部分矛盾</t>
+        </is>
+      </c>
+      <c r="E69" s="175" t="inlineStr">
+        <is>
+          <t>达利欧看流动性(泡沫将破) vs 知乎看估值(PE中值安全)</t>
         </is>
       </c>
     </row>
     <row r="70" ht="48.5" customHeight="1" s="139">
       <c r="A70" s="140" t="inlineStr">
         <is>
+          <t>三源共识</t>
+        </is>
+      </c>
+      <c r="C70" s="177" t="inlineStr">
+        <is>
+          <t>🔴 核心共识</t>
+        </is>
+      </c>
+      <c r="E70" s="175" t="inlineStr">
+        <is>
+          <t>AI龙头估值偏高+市场极度集中+中小盘已熊 → 短期风险&gt;机会</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" ht="32.8" customHeight="1" s="139"/>
+    <row r="72">
+      <c r="A72" s="165" t="inlineStr">
+        <is>
+          <t>🎯 结论（虚P→实P转换条件）</t>
+        </is>
+      </c>
+    </row>
+    <row r="73" ht="121.6" customHeight="1" s="139">
+      <c r="A73" s="140" t="inlineStr">
+        <is>
+          <t>① 达利欧信号落地条件</t>
+        </is>
+      </c>
+      <c r="C73" s="175" t="inlineStr">
+        <is>
+          <t>纳指七姐妹出现&gt;15%回调 或 纳指破200日均线</t>
+        </is>
+      </c>
+      <c r="E73" s="178" t="inlineStr">
+        <is>
+          <t>→ 芯片/恒科虚P转实P → 确认减仓信号</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="140" t="inlineStr">
+        <is>
+          <t>② 李大霄信号落地条件</t>
+        </is>
+      </c>
+      <c r="C74" s="175" t="inlineStr">
+        <is>
+          <t>纳指多数成分股连续下跌+指数拐头</t>
+        </is>
+      </c>
+      <c r="E74" s="178" t="inlineStr">
+        <is>
+          <t>→ 恒科/芯片虚P转实P → 确认美股系统性风险</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="140" t="inlineStr">
+        <is>
           <t>③ 你的策略触发条件</t>
         </is>
       </c>
-      <c r="C70" s="175" t="inlineStr">
+      <c r="C75" s="175" t="inlineStr">
         <is>
           <t>中期选举(11月)美股跌一波 + AI回调&gt;15%</t>
         </is>
       </c>
-      <c r="E70" s="178" t="inlineStr">
+      <c r="E75" s="178" t="inlineStr">
         <is>
           <t>→ 现金入场 → 大仓位进堆叠/先进封装</t>
         </is>
       </c>
     </row>
-    <row r="71" ht="32.8" customHeight="1" s="139">
-      <c r="A71" s="140" t="inlineStr">
+    <row r="76">
+      <c r="A76" s="140" t="inlineStr">
         <is>
           <t>④ 堆叠赛道独立性</t>
         </is>
       </c>
-      <c r="C71" s="175" t="inlineStr">
+      <c r="C76" s="175" t="inlineStr">
         <is>
           <t>国内产业确定性，三源均未提及国内封测</t>
         </is>
       </c>
-      <c r="E71" s="178" t="inlineStr">
+      <c r="E76" s="178" t="inlineStr">
         <is>
           <t>→ 不受美股泡沫直接影响 → 等回调后优先配置</t>
         </is>
       </c>
     </row>
-    <row r="73" ht="121.6" customHeight="1" s="139">
-      <c r="A73" s="179" t="inlineStr">
+    <row r="77" ht="15" customHeight="1" s="139"/>
+    <row r="78">
+      <c r="A78" s="179" t="inlineStr">
         <is>
           <t>⚡ 一句话：三源确认AI泡沫风险+你的中期选举策略正确。虚P已记，等落地转实P。现金为王，堆叠赛道等回调后大仓位进。</t>
         </is>
       </c>
     </row>
-    <row r="77" ht="15" customHeight="1" s="139">
-      <c r="A77" s="147" t="inlineStr">
-        <is>
-          <t>🤖 人形机器人半年事件链</t>
-        </is>
-      </c>
-    </row>
-    <row r="79" ht="39.55" customHeight="1" s="139">
-      <c r="A79" s="147" t="inlineStr">
-        <is>
-          <t>2026-03-23 机器人ETF暴跌-4.1%至0.909：市场恐慌+AI回调</t>
-        </is>
-      </c>
-    </row>
-    <row r="80" ht="39.55" customHeight="1" s="139">
-      <c r="A80" s="147" t="inlineStr">
-        <is>
-          <t>2026-04-08 机器人ETF暴涨+6.4%至0.967：人形机器人产业催化</t>
-        </is>
-      </c>
-    </row>
-    <row r="81" ht="52.2" customHeight="1" s="139">
-      <c r="A81" s="147" t="inlineStr">
-        <is>
-          <t>2026-05-07~22 机器人连续上涨：ETF 1.056→1.216(+15%)，宇树科技73天过会</t>
-        </is>
-      </c>
-    </row>
+    <row r="79" ht="39.55" customHeight="1" s="139"/>
+    <row r="80" ht="39.55" customHeight="1" s="139"/>
+    <row r="81" ht="52.2" customHeight="1" s="139"/>
     <row r="82" ht="52.2" customHeight="1" s="139">
       <c r="A82" s="147" t="inlineStr">
         <is>
-          <t>2026-05-25~06-02 机器人回调：1.216→1.122(-7.7%)，仍处强势区间</t>
-        </is>
-      </c>
-    </row>
-    <row r="83" ht="64.90000000000001" customHeight="1" s="139">
-      <c r="A83" s="180" t="inlineStr">
-        <is>
-          <t>2026-06-04 【保持观察】霍尔木兹海峡Day 12：伊朗暂停谈判+美众议院限制动武，WTI $96→$91-93回落，方向趋于缓和</t>
-        </is>
-      </c>
-      <c r="B83" s="181" t="n"/>
-      <c r="C83" s="181" t="n"/>
-      <c r="D83" s="181" t="n"/>
-      <c r="E83" s="181" t="n"/>
-      <c r="F83" s="181" t="n"/>
-      <c r="G83" s="181" t="n"/>
-      <c r="H83" s="181" t="n"/>
-    </row>
+          <t>🤖 人形机器人半年事件链</t>
+        </is>
+      </c>
+    </row>
+    <row r="83" ht="64.90000000000001" customHeight="1" s="139"/>
     <row r="84" ht="15" customHeight="1" s="139">
-      <c r="A84" s="182" t="inlineStr">
-        <is>
-          <t>🔔 待重仓监控</t>
+      <c r="A84" s="147" t="inlineStr">
+        <is>
+          <t>2026-03-23 机器人ETF暴跌-4.1%至0.909：市场恐慌+AI回调</t>
         </is>
       </c>
     </row>
     <row r="85" ht="15" customHeight="1" s="139">
-      <c r="A85" s="183" t="inlineStr">
-        <is>
-          <t>标的</t>
-        </is>
-      </c>
-      <c r="B85" s="183" t="inlineStr">
-        <is>
-          <t>状态</t>
-        </is>
-      </c>
-      <c r="C85" s="183" t="inlineStr">
-        <is>
-          <t>当前P/价格</t>
-        </is>
-      </c>
-      <c r="D85" s="183" t="inlineStr">
-        <is>
-          <t>最新信号</t>
-        </is>
-      </c>
-      <c r="E85" s="183" t="inlineStr">
-        <is>
-          <t>触发条件</t>
-        </is>
-      </c>
-      <c r="F85" s="183" t="inlineStr">
-        <is>
-          <t>距离触发</t>
-        </is>
-      </c>
-      <c r="G85" s="183" t="inlineStr">
-        <is>
-          <t>跟踪日期</t>
+      <c r="A85" s="147" t="inlineStr">
+        <is>
+          <t>2026-04-08 机器人ETF暴涨+6.4%至0.967：人形机器人产业催化</t>
         </is>
       </c>
     </row>
     <row r="86" ht="26.85" customHeight="1" s="139">
       <c r="A86" s="147" t="inlineStr">
         <is>
-          <t>玻璃基板</t>
-        </is>
-      </c>
-      <c r="B86" s="147" t="inlineStr">
-        <is>
-          <t>深南电路002916/兴森科技002436</t>
-        </is>
-      </c>
-      <c r="C86" s="147" t="inlineStr">
-        <is>
-          <t>观察中</t>
-        </is>
-      </c>
-      <c r="D86" s="147" t="inlineStr">
-        <is>
-          <t>蒋宇飞：玻璃基板大规模应用2028年，5-10年赛道</t>
-        </is>
-      </c>
-      <c r="E86" s="147" t="inlineStr">
-        <is>
-          <t>AI基建+国产替代加速</t>
-        </is>
-      </c>
-      <c r="F86" s="147" t="inlineStr">
-        <is>
-          <t>中长期</t>
-        </is>
-      </c>
-      <c r="G86" s="147" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
+          <t>2026-05-07~22 机器人连续上涨：ETF 1.056→1.216(+15%)，宇树科技73天过会</t>
         </is>
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="138" t="n"/>
+      <c r="A87" s="147" t="inlineStr">
+        <is>
+          <t>2026-05-25~06-02 机器人回调：1.216→1.122(-7.7%)，仍处强势区间</t>
+        </is>
+      </c>
     </row>
     <row r="88" ht="39.55" customHeight="1" s="139">
-      <c r="A88" s="147" t="inlineStr">
-        <is>
-          <t>油气对冲</t>
-        </is>
-      </c>
-      <c r="B88" s="147" t="inlineStr">
-        <is>
-          <t>华宝油气162411</t>
-        </is>
-      </c>
-      <c r="C88" s="147" t="inlineStr">
-        <is>
-          <t>观察中</t>
-        </is>
-      </c>
-      <c r="D88" s="147" t="inlineStr">
-        <is>
-          <t>宋鸿兵：霍尔木兹封锁3个月，85%投资者押注回落=幻觉</t>
-        </is>
-      </c>
-      <c r="E88" s="147" t="inlineStr">
-        <is>
-          <t>油价冲150或海峡持续封锁</t>
-        </is>
-      </c>
-      <c r="F88" s="147" t="inlineStr">
-        <is>
-          <t>短期</t>
-        </is>
-      </c>
-      <c r="G88" s="147" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="H88" s="138" t="inlineStr">
-        <is>
-          <t>小仓位试水，不对称博弈</t>
-        </is>
-      </c>
+      <c r="A88" s="180" t="inlineStr">
+        <is>
+          <t>2026-06-04 【保持观察】霍尔木兹海峡Day 12：伊朗暂停谈判+美众议院限制动武，WTI $96→$91-93回落，方向趋于缓和</t>
+        </is>
+      </c>
+      <c r="B88" s="181" t="n"/>
+      <c r="C88" s="181" t="n"/>
+      <c r="D88" s="181" t="n"/>
+      <c r="E88" s="181" t="n"/>
+      <c r="F88" s="181" t="n"/>
+      <c r="G88" s="181" t="n"/>
+      <c r="H88" s="181" t="n"/>
     </row>
     <row r="89" ht="26.85" customHeight="1" s="139">
-      <c r="A89" s="147" t="inlineStr">
-        <is>
-          <t>银行板块(512800)</t>
-        </is>
-      </c>
-      <c r="B89" s="147" t="inlineStr">
-        <is>
-          <t>弱势</t>
-        </is>
-      </c>
-      <c r="C89" s="147" t="inlineStr">
-        <is>
-          <t>P:50% 虚P-2pp</t>
-        </is>
-      </c>
-      <c r="D89" s="147" t="inlineStr">
-        <is>
-          <t>去杠杆+信贷收缩，ETF跌-1%，无催化</t>
-        </is>
-      </c>
-      <c r="E89" s="147" t="inlineStr">
-        <is>
-          <t>不建议加仓</t>
-        </is>
-      </c>
-      <c r="F89" s="147" t="inlineStr">
-        <is>
-          <t>短期</t>
-        </is>
-      </c>
-      <c r="G89" s="147" t="inlineStr">
-        <is>
-          <t>2026-06-03</t>
-        </is>
-      </c>
-      <c r="H89" s="138" t="inlineStr">
-        <is>
-          <t>银行ETF持续阴跌</t>
+      <c r="A89" s="182" t="inlineStr">
+        <is>
+          <t>🔔 待重仓监控</t>
         </is>
       </c>
     </row>
     <row r="90" ht="26.85" customHeight="1" s="139">
-      <c r="A90" s="147" t="inlineStr">
-        <is>
-          <t>人形机器人(562500)</t>
-        </is>
-      </c>
-      <c r="B90" s="147" t="inlineStr">
-        <is>
-          <t>强势</t>
-        </is>
-      </c>
-      <c r="C90" s="147" t="inlineStr">
-        <is>
-          <t>P:58%(估)</t>
-        </is>
-      </c>
-      <c r="D90" s="147" t="inlineStr">
-        <is>
-          <t>宇树科技73天过会，ETF涨+11%</t>
-        </is>
-      </c>
-      <c r="E90" s="147" t="inlineStr">
-        <is>
-          <t>重点关注</t>
-        </is>
-      </c>
-      <c r="F90" s="147" t="inlineStr">
-        <is>
-          <t>中期</t>
-        </is>
-      </c>
-      <c r="G90" s="147" t="inlineStr">
-        <is>
-          <t>2026-06-03</t>
-        </is>
-      </c>
-      <c r="H90" s="138" t="inlineStr">
-        <is>
-          <t>平安先进制造+永赢先进制造</t>
+      <c r="A90" s="183" t="inlineStr">
+        <is>
+          <t>标的</t>
+        </is>
+      </c>
+      <c r="B90" s="183" t="inlineStr">
+        <is>
+          <t>状态</t>
+        </is>
+      </c>
+      <c r="C90" s="183" t="inlineStr">
+        <is>
+          <t>当前P/价格</t>
+        </is>
+      </c>
+      <c r="D90" s="183" t="inlineStr">
+        <is>
+          <t>最新信号</t>
+        </is>
+      </c>
+      <c r="E90" s="183" t="inlineStr">
+        <is>
+          <t>触发条件</t>
+        </is>
+      </c>
+      <c r="F90" s="183" t="inlineStr">
+        <is>
+          <t>距离触发</t>
+        </is>
+      </c>
+      <c r="G90" s="183" t="inlineStr">
+        <is>
+          <t>跟踪日期</t>
         </is>
       </c>
     </row>
     <row r="91" ht="39.55" customHeight="1" s="139">
       <c r="A91" s="147" t="inlineStr">
         <is>
-          <t>存储赛道(5只A股)</t>
+          <t>玻璃基板</t>
         </is>
       </c>
       <c r="B91" s="147" t="inlineStr">
         <is>
-          <t>❌降级观察</t>
+          <t>深南电路002916/兴森科技002436</t>
         </is>
       </c>
       <c r="C91" s="147" t="inlineStr">
         <is>
-          <t>P:55% 安全边际不足</t>
+          <t>观察中</t>
         </is>
       </c>
       <c r="D91" s="147" t="inlineStr">
         <is>
-          <t>兆易¥525(+81%)/江波龙¥569/佰维¥341→PE天际线，向上空间&lt;向下空间</t>
+          <t>蒋宇飞：玻璃基板大规模应用2028年，5-10年赛道</t>
         </is>
       </c>
       <c r="E91" s="147" t="inlineStr">
         <is>
-          <t>等中期选举大跌15%+</t>
+          <t>AI基建+国产替代加速</t>
         </is>
       </c>
       <c r="F91" s="147" t="inlineStr">
         <is>
-          <t>中期</t>
+          <t>中长期</t>
         </is>
       </c>
       <c r="G91" s="147" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
-        </is>
-      </c>
-      <c r="H91" s="138" t="inlineStr">
-        <is>
-          <t>降级：存储涨完轮到堆叠，安全边际已不足</t>
+          <t>2026-06-02</t>
         </is>
       </c>
     </row>
     <row r="92" ht="26.85" customHeight="1" s="139">
-      <c r="A92" s="147" t="inlineStr">
-        <is>
-          <t>澜起科技(688008)</t>
-        </is>
-      </c>
-      <c r="B92" s="147" t="inlineStr">
-        <is>
-          <t>❌降级观察</t>
-        </is>
-      </c>
-      <c r="C92" s="147" t="inlineStr">
-        <is>
-          <t>P:55% 安全边际中等</t>
-        </is>
-      </c>
-      <c r="D92" s="147" t="inlineStr">
-        <is>
-          <t>DDR5接口芯片，温和上涨，但存储赛道整体降级</t>
-        </is>
-      </c>
-      <c r="E92" s="147" t="inlineStr">
-        <is>
-          <t>等大跌15%+</t>
-        </is>
-      </c>
-      <c r="F92" s="147" t="inlineStr">
-        <is>
-          <t>中期</t>
-        </is>
-      </c>
-      <c r="G92" s="147" t="inlineStr">
-        <is>
-          <t>2026-06-04</t>
-        </is>
-      </c>
-      <c r="H92" s="138" t="inlineStr">
-        <is>
-          <t>降级：存储赛道尾声</t>
-        </is>
-      </c>
+      <c r="A92" s="138" t="n"/>
     </row>
     <row r="93" ht="26.85" customHeight="1" s="139">
-      <c r="A93" s="184" t="inlineStr">
-        <is>
-          <t>🔥堆叠/先进封装赛道（蒋宇飞"星光纯叠"框架）</t>
+      <c r="A93" s="147" t="inlineStr">
+        <is>
+          <t>油气对冲</t>
+        </is>
+      </c>
+      <c r="B93" s="147" t="inlineStr">
+        <is>
+          <t>华宝油气162411</t>
+        </is>
+      </c>
+      <c r="C93" s="147" t="inlineStr">
+        <is>
+          <t>观察中</t>
+        </is>
+      </c>
+      <c r="D93" s="147" t="inlineStr">
+        <is>
+          <t>宋鸿兵：霍尔木兹封锁3个月，85%投资者押注回落=幻觉</t>
+        </is>
+      </c>
+      <c r="E93" s="147" t="inlineStr">
+        <is>
+          <t>油价冲150或海峡持续封锁</t>
+        </is>
+      </c>
+      <c r="F93" s="147" t="inlineStr">
+        <is>
+          <t>短期</t>
+        </is>
+      </c>
+      <c r="G93" s="147" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="H93" s="138" t="inlineStr">
+        <is>
+          <t>小仓位试水，不对称博弈</t>
         </is>
       </c>
     </row>
     <row r="94" ht="39.55" customHeight="1" s="139">
       <c r="A94" s="147" t="inlineStr">
         <is>
-          <t>长电科技(600584)</t>
+          <t>银行板块(512800)</t>
         </is>
       </c>
       <c r="B94" s="147" t="inlineStr">
         <is>
-          <t>🔴核心标的</t>
+          <t>弱势</t>
         </is>
       </c>
       <c r="C94" s="147" t="inlineStr">
         <is>
-          <t>P:75%+ PE30x</t>
+          <t>P:50% 虚P-2pp</t>
         </is>
       </c>
       <c r="D94" s="147" t="inlineStr">
         <is>
-          <t>全球第三大封测厂，2.5D/3D量产级，客户广度最强（高通/海思/TI）</t>
+          <t>去杠杆+信贷收缩，ETF跌-1%，无催化</t>
         </is>
       </c>
       <c r="E94" s="147" t="inlineStr">
         <is>
-          <t>等中期选举大跌</t>
+          <t>不建议加仓</t>
         </is>
       </c>
       <c r="F94" s="147" t="inlineStr">
         <is>
-          <t>中期</t>
+          <t>短期</t>
         </is>
       </c>
       <c r="G94" s="147" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="H94" s="138" t="inlineStr">
         <is>
-          <t>安全边际大，堆叠赛道首选</t>
+          <t>银行ETF持续阴跌</t>
         </is>
       </c>
     </row>
     <row r="95" ht="39.55" customHeight="1" s="139">
       <c r="A95" s="147" t="inlineStr">
         <is>
+          <t>人形机器人(562500)</t>
+        </is>
+      </c>
+      <c r="B95" s="147" t="inlineStr">
+        <is>
+          <t>强势</t>
+        </is>
+      </c>
+      <c r="C95" s="147" t="inlineStr">
+        <is>
+          <t>P:58%(估)</t>
+        </is>
+      </c>
+      <c r="D95" s="147" t="inlineStr">
+        <is>
+          <t>宇树科技73天过会，ETF涨+11%</t>
+        </is>
+      </c>
+      <c r="E95" s="147" t="inlineStr">
+        <is>
+          <t>重点关注</t>
+        </is>
+      </c>
+      <c r="F95" s="147" t="inlineStr">
+        <is>
+          <t>中期</t>
+        </is>
+      </c>
+      <c r="G95" s="147" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="H95" s="138" t="inlineStr">
+        <is>
+          <t>平安先进制造+永赢先进制造</t>
+        </is>
+      </c>
+    </row>
+    <row r="96" ht="15" customHeight="1" s="139">
+      <c r="A96" s="147" t="inlineStr">
+        <is>
+          <t>存储赛道(5只A股)</t>
+        </is>
+      </c>
+      <c r="B96" s="147" t="inlineStr">
+        <is>
+          <t>❌降级观察</t>
+        </is>
+      </c>
+      <c r="C96" s="147" t="inlineStr">
+        <is>
+          <t>P:55% 安全边际不足</t>
+        </is>
+      </c>
+      <c r="D96" s="147" t="inlineStr">
+        <is>
+          <t>兆易¥525(+81%)/江波龙¥569/佰维¥341→PE天际线，向上空间&lt;向下空间</t>
+        </is>
+      </c>
+      <c r="E96" s="147" t="inlineStr">
+        <is>
+          <t>等中期选举大跌15%+</t>
+        </is>
+      </c>
+      <c r="F96" s="147" t="inlineStr">
+        <is>
+          <t>中期</t>
+        </is>
+      </c>
+      <c r="G96" s="147" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="H96" s="138" t="inlineStr">
+        <is>
+          <t>降级：存储涨完轮到堆叠，安全边际已不足</t>
+        </is>
+      </c>
+    </row>
+    <row r="97" ht="15" customHeight="1" s="139">
+      <c r="A97" s="147" t="inlineStr">
+        <is>
+          <t>澜起科技(688008)</t>
+        </is>
+      </c>
+      <c r="B97" s="147" t="inlineStr">
+        <is>
+          <t>❌降级观察</t>
+        </is>
+      </c>
+      <c r="C97" s="147" t="inlineStr">
+        <is>
+          <t>P:55% 安全边际中等</t>
+        </is>
+      </c>
+      <c r="D97" s="147" t="inlineStr">
+        <is>
+          <t>DDR5接口芯片，温和上涨，但存储赛道整体降级</t>
+        </is>
+      </c>
+      <c r="E97" s="147" t="inlineStr">
+        <is>
+          <t>等大跌15%+</t>
+        </is>
+      </c>
+      <c r="F97" s="147" t="inlineStr">
+        <is>
+          <t>中期</t>
+        </is>
+      </c>
+      <c r="G97" s="147" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="H97" s="138" t="inlineStr">
+        <is>
+          <t>降级：存储赛道尾声</t>
+        </is>
+      </c>
+    </row>
+    <row r="98" ht="18.65" customHeight="1" s="139">
+      <c r="A98" s="184" t="inlineStr">
+        <is>
+          <t>🔥堆叠/先进封装赛道（蒋宇飞"星光纯叠"框架）</t>
+        </is>
+      </c>
+    </row>
+    <row r="99" ht="15" customHeight="1" s="139">
+      <c r="A99" s="147" t="inlineStr">
+        <is>
+          <t>长电科技(600584)</t>
+        </is>
+      </c>
+      <c r="B99" s="147" t="inlineStr">
+        <is>
+          <t>🔴核心标的</t>
+        </is>
+      </c>
+      <c r="C99" s="147" t="inlineStr">
+        <is>
+          <t>P:75%+ PE30x</t>
+        </is>
+      </c>
+      <c r="D99" s="147" t="inlineStr">
+        <is>
+          <t>全球第三大封测厂，2.5D/3D量产级，客户广度最强（高通/海思/TI）</t>
+        </is>
+      </c>
+      <c r="E99" s="147" t="inlineStr">
+        <is>
+          <t>等中期选举大跌</t>
+        </is>
+      </c>
+      <c r="F99" s="147" t="inlineStr">
+        <is>
+          <t>中期</t>
+        </is>
+      </c>
+      <c r="G99" s="147" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="H99" s="138" t="inlineStr">
+        <is>
+          <t>安全边际大，堆叠赛道首选</t>
+        </is>
+      </c>
+    </row>
+    <row r="100" ht="15" customHeight="1" s="139">
+      <c r="A100" s="147" t="inlineStr">
+        <is>
           <t>通富微电(002156)</t>
         </is>
       </c>
-      <c r="B95" s="147" t="inlineStr">
+      <c r="B100" s="147" t="inlineStr">
         <is>
           <t>🔴核心标的</t>
         </is>
       </c>
-      <c r="C95" s="147" t="inlineStr">
+      <c r="C100" s="147" t="inlineStr">
         <is>
           <t>P:75%+ 待查PE</t>
         </is>
       </c>
-      <c r="D95" s="147" t="inlineStr">
+      <c r="D100" s="147" t="inlineStr">
         <is>
           <t>AMD封测全线突破通道，2.5D量产，MI300X参与，不可替代</t>
         </is>
       </c>
-      <c r="E95" s="147" t="inlineStr">
+      <c r="E100" s="147" t="inlineStr">
         <is>
           <t>等中期选举大跌</t>
         </is>
       </c>
-      <c r="F95" s="147" t="inlineStr">
+      <c r="F100" s="147" t="inlineStr">
         <is>
           <t>中期</t>
         </is>
       </c>
-      <c r="G95" s="147" t="inlineStr">
+      <c r="G100" s="147" t="inlineStr">
         <is>
           <t>2026-06-04</t>
         </is>
       </c>
-      <c r="H95" s="138" t="inlineStr">
+      <c r="H100" s="138" t="inlineStr">
         <is>
           <t>安全边际中偏大，与长电各占一半</t>
         </is>
       </c>
     </row>
-    <row r="96" ht="15" customHeight="1" s="139">
-      <c r="A96" s="138" t="n"/>
-    </row>
-    <row r="97" ht="15" customHeight="1" s="139">
-      <c r="A97" s="138" t="n"/>
-    </row>
-    <row r="98" ht="18.65" customHeight="1" s="139">
-      <c r="A98" s="153" t="inlineStr">
+    <row r="101" ht="26.85" customHeight="1" s="139">
+      <c r="A101" s="138" t="n"/>
+    </row>
+    <row r="102" ht="15" customHeight="1" s="139">
+      <c r="A102" s="138" t="n"/>
+    </row>
+    <row r="103" ht="26.85" customHeight="1" s="139">
+      <c r="A103" s="316" t="inlineStr">
+        <is>
+          <t>🔥 蒋宇飞179视频深度分析 (2026-06-07 顶级置信度)</t>
+        </is>
+      </c>
+    </row>
+    <row r="104" ht="26.85" customHeight="1" s="139">
+      <c r="A104" s="138" t="inlineStr">
+        <is>
+          <t>核心框架: 星光纯叠=光模块(贯穿)→存储(吃肉)→堆叠(最大风口) | AI基建10年: 存力→算力→运力 | 2027算力长城=升腾+长鑫+DeepSeek</t>
+        </is>
+      </c>
+    </row>
+    <row r="105" ht="26.85" customHeight="1" s="139">
+      <c r="A105" s="138" t="inlineStr">
+        <is>
+          <t>【P值调整】芯片 41%→44%(虚P+3pp) | 稀金 40%→41%(虚P+1pp) | 其余0pp</t>
+        </is>
+      </c>
+    </row>
+    <row r="106" ht="26.85" customHeight="1" s="139"/>
+    <row r="107" ht="15" customHeight="1" s="139">
+      <c r="A107" s="138" t="inlineStr">
+        <is>
+          <t>MLCC被动元件</t>
+        </is>
+      </c>
+      <c r="B107" s="138" t="inlineStr">
+        <is>
+          <t>观察中</t>
+        </is>
+      </c>
+      <c r="C107" s="138" t="inlineStr">
+        <is>
+          <t>蒋宇飞: 行情到2027-H1 | 国巨台湾首富 | 300亿规模</t>
+        </is>
+      </c>
+      <c r="D107" s="138" t="inlineStr">
+        <is>
+          <t>2026-06-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="138" t="inlineStr">
+        <is>
+          <t>国产算力/升腾链</t>
+        </is>
+      </c>
+      <c r="B108" s="138" t="inlineStr">
+        <is>
+          <t>观察中</t>
+        </is>
+      </c>
+      <c r="C108" s="138" t="inlineStr">
+        <is>
+          <t>蒋宇飞: 2027算力长城最闪亮 | 升腾950明年出货 | 升腾+长鑫+DeepSeek</t>
+        </is>
+      </c>
+      <c r="D108" s="138" t="inlineStr">
+        <is>
+          <t>2026-06-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="109" ht="15" customHeight="1" s="139">
+      <c r="A109" s="138" t="inlineStr">
+        <is>
+          <t>HBM产业链</t>
+        </is>
+      </c>
+      <c r="B109" s="138" t="inlineStr">
+        <is>
+          <t>观察中</t>
+        </is>
+      </c>
+      <c r="C109" s="138" t="inlineStr">
+        <is>
+          <t>蒋宇飞: HBM未来1.5-2.5年波涛汹涌 | Q4-Q1热潮 | 技术含量最高</t>
+        </is>
+      </c>
+      <c r="D109" s="138" t="inlineStr">
+        <is>
+          <t>2026-06-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="110" ht="26.85" customHeight="1" s="139">
+      <c r="A110" s="138" t="inlineStr">
+        <is>
+          <t>CPU产业链</t>
+        </is>
+      </c>
+      <c r="B110" s="138" t="inlineStr">
+        <is>
+          <t>观察中</t>
+        </is>
+      </c>
+      <c r="C110" s="138" t="inlineStr">
+        <is>
+          <t>蒋宇飞: agent经济导致CPU爆发缺货 | 带动产业链</t>
+        </is>
+      </c>
+      <c r="D110" s="138" t="inlineStr">
+        <is>
+          <t>2026-06-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="111" ht="26.85" customHeight="1" s="139">
+      <c r="A111" s="138" t="inlineStr">
+        <is>
+          <t>玻璃基板(更新)</t>
+        </is>
+      </c>
+      <c r="B111" s="138" t="inlineStr">
+        <is>
+          <t>观察中</t>
+        </is>
+      </c>
+      <c r="C111" s="138" t="inlineStr">
+        <is>
+          <t>蒋宇飞: 两三年热点→业绩2027-H2→大规模2028 | 封装+存储</t>
+        </is>
+      </c>
+      <c r="D111" s="138" t="inlineStr">
+        <is>
+          <t>2026-06-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="112" ht="26.85" customHeight="1" s="139"/>
+    <row r="113" ht="26.85" customHeight="1" s="139">
+      <c r="A113" s="138" t="inlineStr">
+        <is>
+          <t>【堆叠75%验证】27条堆叠主题: "两年最大风口"+"一年半大放"+"存算一体"→P合理</t>
+        </is>
+      </c>
+    </row>
+    <row r="114" ht="26.85" customHeight="1" s="139">
+      <c r="A114" s="138" t="inlineStr">
+        <is>
+          <t>【存储降级确认】"存储跌80%但现在是时机"+"消费级见顶"+"存储涨完轮到堆叠"→降级合理</t>
+        </is>
+      </c>
+    </row>
+    <row r="115" ht="26.85" customHeight="1" s="139"/>
+    <row r="116" ht="15" customHeight="1" s="139"/>
+    <row r="117"/>
+    <row r="118" ht="15" customHeight="1" s="139"/>
+    <row r="119" ht="15" customHeight="1" s="139">
+      <c r="A119" s="153" t="inlineStr">
         <is>
           <t>📖 机制库 v3（2026-06-04 经小龙虾审核修订）</t>
         </is>
       </c>
     </row>
-    <row r="99" ht="15" customHeight="1" s="139">
-      <c r="A99" s="185" t="inlineStr">
+    <row r="120" ht="26.85" customHeight="1" s="139">
+      <c r="A120" s="185" t="inlineStr">
         <is>
           <t>[机制3v3] 现金锁定系数（CLC）— 平方衰减版</t>
-        </is>
-      </c>
-    </row>
-    <row r="100" ht="15" customHeight="1" s="139">
-      <c r="A100" s="186" t="inlineStr">
-        <is>
-          <t>叫什么</t>
-        </is>
-      </c>
-      <c r="B100" s="147" t="inlineStr">
-        <is>
-          <t>现金锁定系数（CLC）v3</t>
-        </is>
-      </c>
-    </row>
-    <row r="101" ht="26.85" customHeight="1" s="139">
-      <c r="A101" s="186" t="inlineStr">
-        <is>
-          <t>公式</t>
-        </is>
-      </c>
-      <c r="B101" s="147" t="inlineStr">
-        <is>
-          <t>CLC = 信号概率 × 互锁强度 × 时间衰减²</t>
-        </is>
-      </c>
-    </row>
-    <row r="102" ht="15" customHeight="1" s="139">
-      <c r="A102" s="186" t="inlineStr">
-        <is>
-          <t>时间衰减</t>
-        </is>
-      </c>
-      <c r="B102" s="147" t="inlineStr">
-        <is>
-          <t>T = (距触发月数/12)²</t>
-        </is>
-      </c>
-      <c r="C102" s="147" t="inlineStr">
-        <is>
-          <t>6月=(5/12)²=0.174</t>
-        </is>
-      </c>
-      <c r="D102" s="147" t="inlineStr">
-        <is>
-          <t>11月=0</t>
-        </is>
-      </c>
-    </row>
-    <row r="103" ht="26.85" customHeight="1" s="139">
-      <c r="A103" s="186" t="inlineStr">
-        <is>
-          <t>为什么平方</t>
-        </is>
-      </c>
-      <c r="B103" s="147" t="inlineStr">
-        <is>
-          <t>线性衰减导致越近触发日锁得越少（反直觉）</t>
-        </is>
-      </c>
-      <c r="C103" s="147" t="inlineStr">
-        <is>
-          <t>平方函数：远离时多锁，临近时少锁</t>
-        </is>
-      </c>
-      <c r="D103" s="147" t="inlineStr">
-        <is>
-          <t>小龙虾审核通过</t>
-        </is>
-      </c>
-    </row>
-    <row r="104" ht="26.85" customHeight="1" s="139">
-      <c r="A104" s="186" t="inlineStr">
-        <is>
-          <t>信号概率</t>
-        </is>
-      </c>
-      <c r="B104" s="147" t="inlineStr">
-        <is>
-          <t>动态更新，每月审查</t>
-        </is>
-      </c>
-      <c r="C104" s="147" t="inlineStr">
-        <is>
-          <t>底线55%（达利欧区间下沿）</t>
-        </is>
-      </c>
-      <c r="D104" s="147" t="inlineStr">
-        <is>
-          <t>上限85%（达利欧区间上沿）</t>
-        </is>
-      </c>
-    </row>
-    <row r="105" ht="26.85" customHeight="1" s="139">
-      <c r="A105" s="186" t="inlineStr">
-        <is>
-          <t>互锁强度</t>
-        </is>
-      </c>
-      <c r="B105" s="147" t="inlineStr">
-        <is>
-          <t>三源强互锁=1.0</t>
-        </is>
-      </c>
-      <c r="C105" s="147" t="inlineStr">
-        <is>
-          <t>达利欧6月修正&gt;2次→降级0.85</t>
-        </is>
-      </c>
-      <c r="D105" s="147" t="inlineStr">
-        <is>
-          <t>有原因修正不降级</t>
-        </is>
-      </c>
-    </row>
-    <row r="106" ht="26.85" customHeight="1" s="139">
-      <c r="A106" s="186" t="inlineStr">
-        <is>
-          <t>当前值</t>
-        </is>
-      </c>
-      <c r="B106" s="147" t="inlineStr">
-        <is>
-          <t>0.70 × 1.0 × (5/12)² = 0.122</t>
-        </is>
-      </c>
-      <c r="C106" s="147" t="inlineStr">
-        <is>
-          <t>→ 锁定12.2%现金</t>
-        </is>
-      </c>
-      <c r="D106" s="147" t="inlineStr">
-        <is>
-          <t>可用87.8%</t>
-        </is>
-      </c>
-    </row>
-    <row r="107" ht="15" customHeight="1" s="139">
-      <c r="A107" s="186" t="inlineStr">
-        <is>
-          <t>每月重算</t>
-        </is>
-      </c>
-      <c r="B107" s="149" t="n"/>
-      <c r="C107" s="149" t="n"/>
-      <c r="D107" s="149" t="n"/>
-      <c r="E107" s="149" t="n"/>
-      <c r="F107" s="149" t="n"/>
-      <c r="G107" s="149" t="n"/>
-      <c r="H107" s="150" t="n"/>
-    </row>
-    <row r="109" ht="15" customHeight="1" s="139">
-      <c r="A109" s="185" t="inlineStr">
-        <is>
-          <t>[机制4v3] 折后仓位计算 — 4级分级版</t>
-        </is>
-      </c>
-    </row>
-    <row r="110" ht="26.85" customHeight="1" s="139">
-      <c r="A110" s="186" t="inlineStr">
-        <is>
-          <t>叫什么</t>
-        </is>
-      </c>
-      <c r="B110" s="147" t="inlineStr">
-        <is>
-          <t>折后仓位（Folded Allocation）v3</t>
-        </is>
-      </c>
-    </row>
-    <row r="111" ht="26.85" customHeight="1" s="139">
-      <c r="A111" s="186" t="inlineStr">
-        <is>
-          <t>公式</t>
-        </is>
-      </c>
-      <c r="B111" s="147" t="inlineStr">
-        <is>
-          <t>折后仓位% = 原目标仓位% × (1 - CLC × β系数)</t>
-        </is>
-      </c>
-    </row>
-    <row r="112" ht="26.85" customHeight="1" s="139">
-      <c r="A112" s="186" t="inlineStr">
-        <is>
-          <t>4级分级</t>
-        </is>
-      </c>
-      <c r="B112" s="147" t="inlineStr">
-        <is>
-          <t>L1高度暴露β=0.8（通富-AMD独供）</t>
-        </is>
-      </c>
-      <c r="C112" s="147" t="inlineStr">
-        <is>
-          <t>L2中度暴露β=0.5（长电-客户多元）</t>
-        </is>
-      </c>
-    </row>
-    <row r="113" ht="26.85" customHeight="1" s="139">
-      <c r="A113" s="186" t="inlineStr">
-        <is>
-          <t>分级继续</t>
-        </is>
-      </c>
-      <c r="B113" s="147" t="inlineStr">
-        <is>
-          <t>L3弱相关β=0.1（养殖）</t>
-        </is>
-      </c>
-      <c r="C113" s="147" t="inlineStr">
-        <is>
-          <t>L4反向受益β=-0.3（黄金）</t>
-        </is>
-      </c>
-    </row>
-    <row r="114" ht="26.85" customHeight="1" s="139">
-      <c r="A114" s="186" t="inlineStr">
-        <is>
-          <t>为什么分级</t>
-        </is>
-      </c>
-      <c r="B114" s="147" t="inlineStr">
-        <is>
-          <t>不同标的受AI泡沫影响不同</t>
-        </is>
-      </c>
-      <c r="C114" s="147" t="inlineStr">
-        <is>
-          <t>通富只有AMD一根柱子</t>
-        </is>
-      </c>
-      <c r="D114" s="147" t="inlineStr">
-        <is>
-          <t>长电客户多元化</t>
-        </is>
-      </c>
-    </row>
-    <row r="115" ht="26.85" customHeight="1" s="139">
-      <c r="A115" s="186" t="inlineStr">
-        <is>
-          <t>当前计算</t>
-        </is>
-      </c>
-      <c r="B115" s="147" t="inlineStr">
-        <is>
-          <t>通富:33%×(1-0.122×0.8)=30.1%</t>
-        </is>
-      </c>
-      <c r="C115" s="147" t="inlineStr">
-        <is>
-          <t>长电:37%×(1-0.122×0.5)=34.7%</t>
-        </is>
-      </c>
-    </row>
-    <row r="116" ht="15" customHeight="1" s="139">
-      <c r="A116" s="186" t="inlineStr">
-        <is>
-          <t>分级逻辑</t>
-        </is>
-      </c>
-      <c r="B116" s="149" t="n"/>
-      <c r="C116" s="149" t="n"/>
-      <c r="D116" s="149" t="n"/>
-      <c r="E116" s="149" t="n"/>
-      <c r="F116" s="149" t="n"/>
-      <c r="G116" s="149" t="n"/>
-      <c r="H116" s="150" t="n"/>
-    </row>
-    <row r="118" ht="15" customHeight="1" s="139">
-      <c r="A118" s="185" t="inlineStr">
-        <is>
-          <t>[机制5v3] 虚P→实P转换 — 确认窗口+因果链版</t>
-        </is>
-      </c>
-    </row>
-    <row r="119" ht="15" customHeight="1" s="139">
-      <c r="A119" s="186" t="inlineStr">
-        <is>
-          <t>叫什么</t>
-        </is>
-      </c>
-      <c r="B119" s="147" t="inlineStr">
-        <is>
-          <t>虚P→实P转换 v3</t>
-        </is>
-      </c>
-    </row>
-    <row r="120" ht="26.85" customHeight="1" s="139">
-      <c r="A120" s="186" t="inlineStr">
-        <is>
-          <t>视觉信号</t>
-        </is>
-      </c>
-      <c r="B120" s="147" t="inlineStr">
-        <is>
-          <t>纳指七姐妹&gt;15%回调（从52周高）</t>
-        </is>
-      </c>
-      <c r="C120" s="147" t="inlineStr">
-        <is>
-          <t>或破200日均线</t>
         </is>
       </c>
     </row>
     <row r="121" ht="26.85" customHeight="1" s="139">
       <c r="A121" s="186" t="inlineStr">
         <is>
-          <t>确认窗口</t>
-        </is>
-      </c>
-      <c r="B121" s="147" t="inlineStr">
-        <is>
-          <t>跌穿15%后维持5个交易日不反弹</t>
-        </is>
-      </c>
-      <c r="C121" s="147" t="inlineStr">
-        <is>
-          <t>防单日噪音和假触发</t>
-        </is>
-      </c>
-      <c r="D121" s="147" t="inlineStr">
-        <is>
-          <t>小龙虾建议</t>
-        </is>
-      </c>
+          <t>叫什么</t>
+        </is>
+      </c>
+      <c r="B121" s="149" t="n"/>
+      <c r="C121" s="149" t="n"/>
+      <c r="D121" s="149" t="n"/>
+      <c r="E121" s="149" t="n"/>
+      <c r="F121" s="149" t="n"/>
+      <c r="G121" s="149" t="n"/>
+      <c r="H121" s="150" t="n"/>
     </row>
     <row r="122" ht="15" customHeight="1" s="139">
       <c r="A122" s="186" t="inlineStr">
         <is>
-          <t>因果链</t>
+          <t>公式</t>
         </is>
       </c>
       <c r="B122" s="147" t="inlineStr">
         <is>
-          <t>需至少2条佐证：</t>
-        </is>
-      </c>
-      <c r="C122" s="147" t="inlineStr">
-        <is>
-          <t>①英伟达/AMD下调指引</t>
-        </is>
-      </c>
-      <c r="D122" s="147" t="inlineStr">
-        <is>
-          <t>②AI ETF资金流出</t>
+          <t>CLC = 信号概率 × 互锁强度 × 时间衰减²</t>
         </is>
       </c>
     </row>
     <row r="123" ht="15" customHeight="1" s="139">
       <c r="A123" s="186" t="inlineStr">
         <is>
-          <t>因果链继续</t>
+          <t>时间衰减</t>
         </is>
       </c>
       <c r="B123" s="147" t="inlineStr">
         <is>
-          <t>③投行下调AI评级</t>
+          <t>T = (距触发月数/12)²</t>
         </is>
       </c>
       <c r="C123" s="147" t="inlineStr">
         <is>
-          <t>④Mag7裁员/削减开支</t>
+          <t>6月=(5/12)²=0.174</t>
+        </is>
+      </c>
+      <c r="D123" s="147" t="inlineStr">
+        <is>
+          <t>11月=0</t>
         </is>
       </c>
     </row>
     <row r="124" ht="26.85" customHeight="1" s="139">
       <c r="A124" s="186" t="inlineStr">
         <is>
-          <t>为什么加因果</t>
+          <t>为什么平方</t>
         </is>
       </c>
       <c r="B124" s="147" t="inlineStr">
         <is>
-          <t>15%下跌可能是地缘冲击不是AI泡沫</t>
+          <t>线性衰减导致越近触发日锁得越少（反直觉）</t>
         </is>
       </c>
       <c r="C124" s="147" t="inlineStr">
         <is>
-          <t>两者操作完全不同</t>
+          <t>平方函数：远离时多锁，临近时少锁</t>
         </is>
       </c>
       <c r="D124" s="147" t="inlineStr">
         <is>
-          <t>必须区分原因</t>
+          <t>小龙虾审核通过</t>
         </is>
       </c>
     </row>
     <row r="125" ht="15" customHeight="1" s="139">
       <c r="A125" s="186" t="inlineStr">
         <is>
-          <t>转换后</t>
-        </is>
-      </c>
-      <c r="B125" s="149" t="n"/>
-      <c r="C125" s="149" t="n"/>
-      <c r="D125" s="149" t="n"/>
-      <c r="E125" s="149" t="n"/>
-      <c r="F125" s="149" t="n"/>
-      <c r="G125" s="149" t="n"/>
-      <c r="H125" s="150" t="n"/>
+          <t>信号概率</t>
+        </is>
+      </c>
+      <c r="B125" s="147" t="inlineStr">
+        <is>
+          <t>动态更新，每月审查</t>
+        </is>
+      </c>
+      <c r="C125" s="147" t="inlineStr">
+        <is>
+          <t>底线55%（达利欧区间下沿）</t>
+        </is>
+      </c>
+      <c r="D125" s="147" t="inlineStr">
+        <is>
+          <t>上限85%（达利欧区间上沿）</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="186" t="inlineStr">
+        <is>
+          <t>互锁强度</t>
+        </is>
+      </c>
+      <c r="B126" s="147" t="inlineStr">
+        <is>
+          <t>三源强互锁=1.0</t>
+        </is>
+      </c>
+      <c r="C126" s="147" t="inlineStr">
+        <is>
+          <t>达利欧6月修正&gt;2次→降级0.85</t>
+        </is>
+      </c>
+      <c r="D126" s="147" t="inlineStr">
+        <is>
+          <t>有原因修正不降级</t>
+        </is>
+      </c>
     </row>
     <row r="127" ht="15" customHeight="1" s="139">
-      <c r="A127" s="187" t="inlineStr">
-        <is>
-          <t>[信号计分板] 每日更新，驱动信号概率动态调整</t>
+      <c r="A127" s="186" t="inlineStr">
+        <is>
+          <t>当前值</t>
+        </is>
+      </c>
+      <c r="B127" s="147" t="inlineStr">
+        <is>
+          <t>0.70 × 1.0 × (5/12)² = 0.122</t>
+        </is>
+      </c>
+      <c r="C127" s="147" t="inlineStr">
+        <is>
+          <t>→ 锁定12.2%现金</t>
+        </is>
+      </c>
+      <c r="D127" s="147" t="inlineStr">
+        <is>
+          <t>可用87.8%</t>
         </is>
       </c>
     </row>
     <row r="128" ht="15" customHeight="1" s="139">
       <c r="A128" s="186" t="inlineStr">
         <is>
-          <t>泡沫正向信号</t>
-        </is>
-      </c>
-      <c r="B128" s="147" t="inlineStr">
-        <is>
-          <t>Mag7单日跌&gt;3% → +1</t>
-        </is>
-      </c>
-      <c r="C128" s="147" t="inlineStr">
-        <is>
-          <t>Mag7月跌&gt;10% → +2</t>
-        </is>
-      </c>
-    </row>
-    <row r="129" ht="26.85" customHeight="1" s="139">
-      <c r="B129" s="147" t="inlineStr">
-        <is>
-          <t>VIX&gt;30 → +2</t>
-        </is>
-      </c>
-      <c r="C129" s="147" t="inlineStr">
-        <is>
-          <t>AI公司裁员/下调指引 → +1</t>
-        </is>
-      </c>
-    </row>
+          <t>每月重算</t>
+        </is>
+      </c>
+      <c r="B128" s="149" t="n"/>
+      <c r="C128" s="149" t="n"/>
+      <c r="D128" s="149" t="n"/>
+      <c r="E128" s="149" t="n"/>
+      <c r="F128" s="149" t="n"/>
+      <c r="G128" s="149" t="n"/>
+      <c r="H128" s="150" t="n"/>
+    </row>
+    <row r="129" ht="26.85" customHeight="1" s="139"/>
     <row r="130" ht="15" customHeight="1" s="139">
-      <c r="B130" s="147" t="inlineStr">
-        <is>
-          <t>信用利差&gt;150bp → +2</t>
+      <c r="A130" s="185" t="inlineStr">
+        <is>
+          <t>[机制4v3] 折后仓位计算 — 4级分级版</t>
         </is>
       </c>
     </row>
     <row r="131" ht="15" customHeight="1" s="139">
       <c r="A131" s="186" t="inlineStr">
         <is>
-          <t>泡沫反向信号</t>
+          <t>叫什么</t>
         </is>
       </c>
       <c r="B131" s="147" t="inlineStr">
         <is>
-          <t>Mag7单日涨&gt;3% → -1</t>
-        </is>
-      </c>
-      <c r="C131" s="147" t="inlineStr">
-        <is>
-          <t>Mag7月涨&gt;8% → -2</t>
+          <t>折后仓位（Folded Allocation）v3</t>
         </is>
       </c>
     </row>
     <row r="132" ht="15" customHeight="1" s="139">
+      <c r="A132" s="186" t="inlineStr">
+        <is>
+          <t>公式</t>
+        </is>
+      </c>
       <c r="B132" s="147" t="inlineStr">
         <is>
-          <t>Fed降息 → -2</t>
-        </is>
-      </c>
-      <c r="C132" s="147" t="inlineStr">
-        <is>
-          <t>AI龙头超预期财报 → -1</t>
+          <t>折后仓位% = 原目标仓位% × (1 - CLC × β系数)</t>
         </is>
       </c>
     </row>
     <row r="133" ht="15" customHeight="1" s="139">
+      <c r="A133" s="186" t="inlineStr">
+        <is>
+          <t>4级分级</t>
+        </is>
+      </c>
       <c r="B133" s="147" t="inlineStr">
         <is>
-          <t>VIX&lt;15 → -1</t>
+          <t>L1高度暴露β=0.8（通富-AMD独供）</t>
+        </is>
+      </c>
+      <c r="C133" s="147" t="inlineStr">
+        <is>
+          <t>L2中度暴露β=0.5（长电-客户多元）</t>
         </is>
       </c>
     </row>
     <row r="134" ht="26.85" customHeight="1" s="139">
       <c r="A134" s="186" t="inlineStr">
         <is>
-          <t>更新规则</t>
+          <t>分级继续</t>
         </is>
       </c>
       <c r="B134" s="147" t="inlineStr">
         <is>
-          <t>每月第一天：信号概率=70%+上月净计分×5pp</t>
+          <t>L3弱相关β=0.1（养殖）</t>
         </is>
       </c>
       <c r="C134" s="147" t="inlineStr">
         <is>
-          <t>底线55%上限85%</t>
+          <t>L4反向受益β=-0.3（黄金）</t>
         </is>
       </c>
     </row>
     <row r="135" ht="15" customHeight="1" s="139">
       <c r="A135" s="186" t="inlineStr">
         <is>
-          <t>Mag7权重</t>
-        </is>
-      </c>
-      <c r="B135" s="149" t="n"/>
-      <c r="C135" s="149" t="n"/>
-      <c r="D135" s="149" t="n"/>
-      <c r="E135" s="149" t="n"/>
-      <c r="F135" s="149" t="n"/>
-      <c r="G135" s="149" t="n"/>
-      <c r="H135" s="150" t="n"/>
+          <t>为什么分级</t>
+        </is>
+      </c>
+      <c r="B135" s="147" t="inlineStr">
+        <is>
+          <t>不同标的受AI泡沫影响不同</t>
+        </is>
+      </c>
+      <c r="C135" s="147" t="inlineStr">
+        <is>
+          <t>通富只有AMD一根柱子</t>
+        </is>
+      </c>
+      <c r="D135" s="147" t="inlineStr">
+        <is>
+          <t>长电客户多元化</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="186" t="inlineStr">
+        <is>
+          <t>当前计算</t>
+        </is>
+      </c>
+      <c r="B136" s="147" t="inlineStr">
+        <is>
+          <t>通富:33%×(1-0.122×0.8)=30.1%</t>
+        </is>
+      </c>
+      <c r="C136" s="147" t="inlineStr">
+        <is>
+          <t>长电:37%×(1-0.122×0.5)=34.7%</t>
+        </is>
+      </c>
     </row>
     <row r="137" ht="15" customHeight="1" s="139">
-      <c r="A137" s="187" t="inlineStr">
-        <is>
-          <t>⚡ 机制v3使用指南</t>
-        </is>
-      </c>
-    </row>
-    <row r="138" ht="26.85" customHeight="1" s="139">
-      <c r="A138" s="186" t="inlineStr">
-        <is>
-          <t>日常看盘</t>
-        </is>
-      </c>
-      <c r="B138" s="147" t="inlineStr">
-        <is>
-          <t>看机会成本排序Sheet折后仓位</t>
-        </is>
-      </c>
-      <c r="C138" s="147" t="inlineStr">
-        <is>
-          <t>看现金锁定状态</t>
-        </is>
-      </c>
-    </row>
+      <c r="A137" s="186" t="inlineStr">
+        <is>
+          <t>分级逻辑</t>
+        </is>
+      </c>
+      <c r="B137" s="149" t="n"/>
+      <c r="C137" s="149" t="n"/>
+      <c r="D137" s="149" t="n"/>
+      <c r="E137" s="149" t="n"/>
+      <c r="F137" s="149" t="n"/>
+      <c r="G137" s="149" t="n"/>
+      <c r="H137" s="150" t="n"/>
+    </row>
+    <row r="138" ht="26.85" customHeight="1" s="139"/>
     <row r="139" ht="15" customHeight="1" s="139">
-      <c r="A139" s="186" t="inlineStr">
-        <is>
-          <t>每日更新</t>
-        </is>
-      </c>
-      <c r="B139" s="147" t="inlineStr">
-        <is>
-          <t>信号计分板逐股计分</t>
-        </is>
-      </c>
-      <c r="C139" s="147" t="inlineStr">
-        <is>
-          <t>净计分累计</t>
+      <c r="A139" s="185" t="inlineStr">
+        <is>
+          <t>[机制5v3] 虚P→实P转换 — 确认窗口+因果链版</t>
         </is>
       </c>
     </row>
     <row r="140" ht="26.85" customHeight="1" s="139">
       <c r="A140" s="186" t="inlineStr">
         <is>
-          <t>每月重算</t>
-        </is>
-      </c>
-      <c r="B140" s="147" t="inlineStr">
-        <is>
-          <t>①信号概率=70%+净计分×5pp</t>
-        </is>
-      </c>
-      <c r="C140" s="147" t="inlineStr">
-        <is>
-          <t>②CLC=信号概率×互锁×时间衰减²</t>
-        </is>
-      </c>
-      <c r="D140" s="147" t="inlineStr">
-        <is>
-          <t>③折后仓位=原仓位×(1-CLC×β)</t>
-        </is>
-      </c>
+          <t>叫什么</t>
+        </is>
+      </c>
+      <c r="B140" s="149" t="n"/>
+      <c r="C140" s="149" t="n"/>
+      <c r="D140" s="149" t="n"/>
+      <c r="E140" s="149" t="n"/>
+      <c r="F140" s="149" t="n"/>
+      <c r="G140" s="149" t="n"/>
+      <c r="H140" s="150" t="n"/>
     </row>
     <row r="141" ht="26.85" customHeight="1" s="139">
       <c r="A141" s="186" t="inlineStr">
         <is>
-          <t>信号落地</t>
+          <t>视觉信号</t>
         </is>
       </c>
       <c r="B141" s="147" t="inlineStr">
         <is>
-          <t>视觉信号+5日确认+因果链2条</t>
+          <t>纳指七姐妹&gt;15%回调（从52周高）</t>
         </is>
       </c>
       <c r="C141" s="147" t="inlineStr">
         <is>
-          <t>→虚P转实P</t>
-        </is>
-      </c>
-      <c r="D141" s="147" t="inlineStr">
-        <is>
-          <t>→CLC=0现金解锁</t>
+          <t>或破200日均线</t>
         </is>
       </c>
     </row>
     <row r="142" ht="39.55" customHeight="1" s="139">
       <c r="A142" s="186" t="inlineStr">
         <is>
+          <t>确认窗口</t>
+        </is>
+      </c>
+      <c r="B142" s="147" t="inlineStr">
+        <is>
+          <t>跌穿15%后维持5个交易日不反弹</t>
+        </is>
+      </c>
+      <c r="C142" s="147" t="inlineStr">
+        <is>
+          <t>防单日噪音和假触发</t>
+        </is>
+      </c>
+      <c r="D142" s="147" t="inlineStr">
+        <is>
+          <t>小龙虾建议</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="186" t="inlineStr">
+        <is>
+          <t>因果链</t>
+        </is>
+      </c>
+      <c r="B143" s="147" t="inlineStr">
+        <is>
+          <t>需至少2条佐证：</t>
+        </is>
+      </c>
+      <c r="C143" s="147" t="inlineStr">
+        <is>
+          <t>①英伟达/AMD下调指引</t>
+        </is>
+      </c>
+      <c r="D143" s="147" t="inlineStr">
+        <is>
+          <t>②AI ETF资金流出</t>
+        </is>
+      </c>
+    </row>
+    <row r="144" ht="17.35" customHeight="1" s="139">
+      <c r="A144" s="186" t="inlineStr">
+        <is>
+          <t>因果链继续</t>
+        </is>
+      </c>
+      <c r="B144" s="147" t="inlineStr">
+        <is>
+          <t>③投行下调AI评级</t>
+        </is>
+      </c>
+      <c r="C144" s="147" t="inlineStr">
+        <is>
+          <t>④Mag7裁员/削减开支</t>
+        </is>
+      </c>
+    </row>
+    <row r="145" ht="17.15" customHeight="1" s="139">
+      <c r="A145" s="186" t="inlineStr">
+        <is>
+          <t>为什么加因果</t>
+        </is>
+      </c>
+      <c r="B145" s="147" t="inlineStr">
+        <is>
+          <t>15%下跌可能是地缘冲击不是AI泡沫</t>
+        </is>
+      </c>
+      <c r="C145" s="147" t="inlineStr">
+        <is>
+          <t>两者操作完全不同</t>
+        </is>
+      </c>
+      <c r="D145" s="147" t="inlineStr">
+        <is>
+          <t>必须区分原因</t>
+        </is>
+      </c>
+    </row>
+    <row r="146" ht="17.15" customHeight="1" s="139">
+      <c r="A146" s="186" t="inlineStr">
+        <is>
+          <t>转换后</t>
+        </is>
+      </c>
+      <c r="B146" s="149" t="n"/>
+      <c r="C146" s="149" t="n"/>
+      <c r="D146" s="149" t="n"/>
+      <c r="E146" s="149" t="n"/>
+      <c r="F146" s="149" t="n"/>
+      <c r="G146" s="149" t="n"/>
+      <c r="H146" s="150" t="n"/>
+    </row>
+    <row r="147" ht="17.15" customHeight="1" s="139"/>
+    <row r="148" ht="17.15" customHeight="1" s="139">
+      <c r="A148" s="187" t="inlineStr">
+        <is>
+          <t>[信号计分板] 每日更新，驱动信号概率动态调整</t>
+        </is>
+      </c>
+    </row>
+    <row r="149" ht="17.15" customHeight="1" s="139">
+      <c r="A149" s="186" t="inlineStr">
+        <is>
+          <t>泡沫正向信号</t>
+        </is>
+      </c>
+      <c r="B149" s="147" t="inlineStr">
+        <is>
+          <t>Mag7单日跌&gt;3% → +1</t>
+        </is>
+      </c>
+      <c r="C149" s="147" t="inlineStr">
+        <is>
+          <t>Mag7月跌&gt;10% → +2</t>
+        </is>
+      </c>
+    </row>
+    <row r="150" ht="17.15" customHeight="1" s="139">
+      <c r="B150" s="147" t="inlineStr">
+        <is>
+          <t>VIX&gt;30 → +2</t>
+        </is>
+      </c>
+      <c r="C150" s="147" t="inlineStr">
+        <is>
+          <t>AI公司裁员/下调指引 → +1</t>
+        </is>
+      </c>
+    </row>
+    <row r="151" ht="17.15" customHeight="1" s="139">
+      <c r="B151" s="147" t="inlineStr">
+        <is>
+          <t>信用利差&gt;150bp → +2</t>
+        </is>
+      </c>
+    </row>
+    <row r="152" ht="17.15" customHeight="1" s="139">
+      <c r="A152" s="186" t="inlineStr">
+        <is>
+          <t>泡沫反向信号</t>
+        </is>
+      </c>
+      <c r="B152" s="147" t="inlineStr">
+        <is>
+          <t>Mag7单日涨&gt;3% → -1</t>
+        </is>
+      </c>
+      <c r="C152" s="147" t="inlineStr">
+        <is>
+          <t>Mag7月涨&gt;8% → -2</t>
+        </is>
+      </c>
+    </row>
+    <row r="153" ht="17.15" customHeight="1" s="139">
+      <c r="B153" s="147" t="inlineStr">
+        <is>
+          <t>Fed降息 → -2</t>
+        </is>
+      </c>
+      <c r="C153" s="147" t="inlineStr">
+        <is>
+          <t>AI龙头超预期财报 → -1</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="B154" s="147" t="inlineStr">
+        <is>
+          <t>VIX&lt;15 → -1</t>
+        </is>
+      </c>
+    </row>
+    <row r="155" ht="15" customHeight="1" s="139">
+      <c r="A155" s="186" t="inlineStr">
+        <is>
+          <t>更新规则</t>
+        </is>
+      </c>
+      <c r="B155" s="147" t="inlineStr">
+        <is>
+          <t>每月第一天：信号概率=70%+上月净计分×5pp</t>
+        </is>
+      </c>
+      <c r="C155" s="147" t="inlineStr">
+        <is>
+          <t>底线55%上限85%</t>
+        </is>
+      </c>
+    </row>
+    <row r="156" ht="15" customHeight="1" s="139">
+      <c r="A156" s="186" t="inlineStr">
+        <is>
+          <t>Mag7权重</t>
+        </is>
+      </c>
+      <c r="B156" s="149" t="n"/>
+      <c r="C156" s="149" t="n"/>
+      <c r="D156" s="149" t="n"/>
+      <c r="E156" s="149" t="n"/>
+      <c r="F156" s="149" t="n"/>
+      <c r="G156" s="149" t="n"/>
+      <c r="H156" s="150" t="n"/>
+    </row>
+    <row r="157" ht="15" customHeight="1" s="139"/>
+    <row r="158" ht="15" customHeight="1" s="139">
+      <c r="A158" s="187" t="inlineStr">
+        <is>
+          <t>⚡ 机制v3使用指南</t>
+        </is>
+      </c>
+    </row>
+    <row r="159" ht="15" customHeight="1" s="139">
+      <c r="A159" s="186" t="inlineStr">
+        <is>
+          <t>日常看盘</t>
+        </is>
+      </c>
+      <c r="B159" s="147" t="inlineStr">
+        <is>
+          <t>看机会成本排序Sheet折后仓位</t>
+        </is>
+      </c>
+      <c r="C159" s="147" t="inlineStr">
+        <is>
+          <t>看现金锁定状态</t>
+        </is>
+      </c>
+    </row>
+    <row r="160" ht="15" customHeight="1" s="139">
+      <c r="A160" s="186" t="inlineStr">
+        <is>
+          <t>每日更新</t>
+        </is>
+      </c>
+      <c r="B160" s="147" t="inlineStr">
+        <is>
+          <t>信号计分板逐股计分</t>
+        </is>
+      </c>
+      <c r="C160" s="147" t="inlineStr">
+        <is>
+          <t>净计分累计</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="186" t="inlineStr">
+        <is>
+          <t>每月重算</t>
+        </is>
+      </c>
+      <c r="B161" s="147" t="inlineStr">
+        <is>
+          <t>①信号概率=70%+净计分×5pp</t>
+        </is>
+      </c>
+      <c r="C161" s="147" t="inlineStr">
+        <is>
+          <t>②CLC=信号概率×互锁×时间衰减²</t>
+        </is>
+      </c>
+      <c r="D161" s="147" t="inlineStr">
+        <is>
+          <t>③折后仓位=原仓位×(1-CLC×β)</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="186" t="inlineStr">
+        <is>
+          <t>信号落地</t>
+        </is>
+      </c>
+      <c r="B162" s="147" t="inlineStr">
+        <is>
+          <t>视觉信号+5日确认+因果链2条</t>
+        </is>
+      </c>
+      <c r="C162" s="147" t="inlineStr">
+        <is>
+          <t>→虚P转实P</t>
+        </is>
+      </c>
+      <c r="D162" s="147" t="inlineStr">
+        <is>
+          <t>→CLC=0现金解锁</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="186" t="inlineStr">
+        <is>
           <t>核验计算</t>
         </is>
       </c>
-      <c r="B142" s="147" t="inlineStr">
+      <c r="B163" s="147" t="inlineStr">
         <is>
           <t>python3 /tmp/mechanism_checker_v3.py</t>
         </is>
       </c>
-      <c r="C142" s="147" t="inlineStr">
+      <c r="C163" s="147" t="inlineStr">
         <is>
           <t>自动重算所有机制</t>
         </is>
       </c>
     </row>
-    <row r="144" ht="17.35" customHeight="1" s="139">
-      <c r="A144" s="188" t="inlineStr">
+    <row r="164"/>
+    <row r="165">
+      <c r="A165" s="188" t="inlineStr">
         <is>
           <t>📊 持仓状态速查表</t>
         </is>
       </c>
     </row>
-    <row r="145" ht="17.15" customHeight="1" s="139">
-      <c r="A145" s="189" t="inlineStr">
+    <row r="166">
+      <c r="A166" s="189" t="inlineStr">
         <is>
           <t>持仓</t>
         </is>
       </c>
-      <c r="B145" s="189" t="inlineStr">
+      <c r="B166" s="189" t="inlineStr">
         <is>
           <t>代码</t>
         </is>
       </c>
-      <c r="C145" s="189" t="inlineStr">
+      <c r="C166" s="189" t="inlineStr">
         <is>
           <t>当前P</t>
         </is>
       </c>
-      <c r="D145" s="189" t="inlineStr">
+      <c r="D166" s="189" t="inlineStr">
         <is>
           <t>有效P</t>
         </is>
       </c>
-      <c r="E145" s="189" t="inlineStr">
+      <c r="E166" s="189" t="inlineStr">
         <is>
           <t>虚P</t>
         </is>
       </c>
-      <c r="F145" s="189" t="inlineStr">
+      <c r="F166" s="189" t="inlineStr">
         <is>
           <t>利率折价</t>
         </is>
       </c>
-      <c r="G145" s="189" t="inlineStr">
+      <c r="G166" s="189" t="inlineStr">
         <is>
           <t>方向</t>
         </is>
       </c>
-      <c r="H145" s="189" t="inlineStr">
+      <c r="H166" s="189" t="inlineStr">
         <is>
           <t>操作建议</t>
         </is>
       </c>
     </row>
-    <row r="146" ht="17.15" customHeight="1" s="139">
-      <c r="A146" s="138" t="inlineStr">
+    <row r="167">
+      <c r="A167" s="138" t="inlineStr">
         <is>
           <t>芯片020628</t>
         </is>
       </c>
-      <c r="B146" s="138" t="inlineStr">
+      <c r="B167" s="138" t="inlineStr">
         <is>
           <t>C1</t>
         </is>
       </c>
-      <c r="C146" s="138" t="inlineStr">
+      <c r="C167" s="138" t="inlineStr">
         <is>
           <t>41</t>
         </is>
       </c>
-      <c r="D146" s="138" t="inlineStr">
+      <c r="D167" s="138" t="inlineStr">
         <is>
           <t>35</t>
         </is>
       </c>
-      <c r="E146" s="138" t="inlineStr">
+      <c r="E167" s="138" t="inlineStr">
         <is>
           <t>虚P+2pp | 6/5 存储→芯片资金传送门：存储涨81%降级后，资金搬进芯片ETF/长电通富</t>
         </is>
       </c>
-      <c r="F146" s="138" t="inlineStr">
+      <c r="F167" s="138" t="inlineStr">
         <is>
           <t>利率折价-6pp</t>
         </is>
       </c>
-      <c r="G146" s="138" t="inlineStr">
+      <c r="G167" s="138" t="inlineStr">
         <is>
           <t>🟡中性</t>
         </is>
       </c>
-      <c r="H146" s="138" t="inlineStr">
+      <c r="H167" s="138" t="inlineStr">
         <is>
           <t>观望</t>
         </is>
       </c>
     </row>
-    <row r="147" ht="17.15" customHeight="1" s="139">
-      <c r="A147" s="138" t="inlineStr">
+    <row r="168">
+      <c r="A168" s="138" t="inlineStr">
         <is>
           <t>电池018926</t>
         </is>
       </c>
-      <c r="B147" s="138" t="inlineStr">
+      <c r="B168" s="138" t="inlineStr">
         <is>
           <t>C2</t>
         </is>
       </c>
-      <c r="C147" s="138" t="inlineStr">
+      <c r="C168" s="138" t="inlineStr">
         <is>
           <t>65</t>
         </is>
       </c>
-      <c r="D147" s="138" t="inlineStr">
+      <c r="D168" s="138" t="inlineStr">
         <is>
           <t>59</t>
         </is>
       </c>
-      <c r="E147" s="138" t="inlineStr">
+      <c r="E168" s="138" t="inlineStr">
         <is>
           <t>虚P无</t>
         </is>
       </c>
-      <c r="F147" s="138" t="inlineStr">
+      <c r="F168" s="138" t="inlineStr">
         <is>
           <t>利率折价-6pp</t>
         </is>
       </c>
-      <c r="G147" s="138" t="inlineStr">
+      <c r="G168" s="138" t="inlineStr">
         <is>
           <t>🟢偏多</t>
         </is>
       </c>
-      <c r="H147" s="138" t="inlineStr">
+      <c r="H168" s="138" t="inlineStr">
         <is>
           <t>持有/关注加仓</t>
         </is>
       </c>
     </row>
-    <row r="148" ht="17.15" customHeight="1" s="139">
-      <c r="A148" s="138" t="inlineStr">
+    <row r="169">
+      <c r="A169" s="138" t="inlineStr">
         <is>
           <t>恒科012349</t>
         </is>
       </c>
-      <c r="B148" s="138" t="inlineStr">
+      <c r="B169" s="138" t="inlineStr">
         <is>
           <t>C3</t>
         </is>
       </c>
-      <c r="C148" s="138" t="inlineStr">
+      <c r="C169" s="138" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="D148" s="138" t="inlineStr">
+      <c r="D169" s="138" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="E148" s="138" t="inlineStr">
+      <c r="E169" s="138" t="inlineStr">
         <is>
           <t>虚P无 | 6/5 闻号说经济：301关税60国+AI芯片管制升级→压制恒科</t>
         </is>
       </c>
-      <c r="F148" s="138" t="inlineStr">
+      <c r="F169" s="138" t="inlineStr">
         <is>
           <t>利率折价-6pp</t>
         </is>
       </c>
-      <c r="G148" s="138" t="inlineStr">
+      <c r="G169" s="138" t="inlineStr">
         <is>
           <t>🔴偏空</t>
         </is>
       </c>
-      <c r="H148" s="138" t="inlineStr">
+      <c r="H169" s="138" t="inlineStr">
         <is>
           <t>减仓/清仓</t>
         </is>
       </c>
     </row>
-    <row r="149" ht="17.15" customHeight="1" s="139">
-      <c r="A149" s="138" t="inlineStr">
+    <row r="170">
+      <c r="A170" s="138" t="inlineStr">
         <is>
           <t>养殖014415</t>
         </is>
       </c>
-      <c r="B149" s="138" t="inlineStr">
+      <c r="B170" s="138" t="inlineStr">
         <is>
           <t>C4</t>
         </is>
       </c>
-      <c r="C149" s="138" t="inlineStr">
+      <c r="C170" s="138" t="inlineStr">
         <is>
           <t>70</t>
         </is>
       </c>
-      <c r="D149" s="138" t="inlineStr">
+      <c r="D170" s="138" t="inlineStr">
         <is>
           <t>70</t>
         </is>
       </c>
-      <c r="E149" s="138" t="inlineStr">
+      <c r="E170" s="138" t="inlineStr">
         <is>
           <t>虚P+4pp | 6/5 芳姐：低价抄底母猪，行业融资枯竭，等待母猪血流成河才是最佳买点</t>
         </is>
       </c>
-      <c r="F149" s="138" t="inlineStr">
+      <c r="F170" s="138" t="inlineStr">
         <is>
           <t>利率折价0pp</t>
         </is>
       </c>
-      <c r="G149" s="138" t="inlineStr">
+      <c r="G170" s="138" t="inlineStr">
         <is>
           <t>🟢偏多</t>
         </is>
       </c>
-      <c r="H149" s="138" t="inlineStr">
+      <c r="H170" s="138" t="inlineStr">
         <is>
           <t>持有/关注加仓</t>
         </is>
       </c>
     </row>
-    <row r="150" ht="17.15" customHeight="1" s="139">
-      <c r="A150" s="138" t="inlineStr">
+    <row r="171">
+      <c r="A171" s="138" t="inlineStr">
         <is>
           <t>有色004433</t>
         </is>
       </c>
-      <c r="B150" s="138" t="inlineStr">
+      <c r="B171" s="138" t="inlineStr">
         <is>
           <t>C5</t>
         </is>
       </c>
-      <c r="C150" s="138" t="inlineStr">
+      <c r="C171" s="138" t="inlineStr">
         <is>
           <t>39</t>
         </is>
       </c>
-      <c r="D150" s="138" t="inlineStr">
+      <c r="D171" s="138" t="inlineStr">
         <is>
           <t>35</t>
         </is>
       </c>
-      <c r="E150" s="138" t="inlineStr">
+      <c r="E171" s="138" t="inlineStr">
         <is>
           <t>虚P无 | 6/5 闻号说经济：301关税60国→压制有色需求</t>
         </is>
       </c>
-      <c r="F150" s="138" t="inlineStr">
+      <c r="F171" s="138" t="inlineStr">
         <is>
           <t>利率折价-4pp</t>
         </is>
       </c>
-      <c r="G150" s="138" t="inlineStr">
+      <c r="G171" s="138" t="inlineStr">
         <is>
           <t>🔴偏空</t>
         </is>
       </c>
-      <c r="H150" s="138" t="inlineStr">
+      <c r="H171" s="138" t="inlineStr">
         <is>
           <t>减仓/清仓</t>
         </is>
       </c>
     </row>
-    <row r="151" ht="17.15" customHeight="1" s="139">
-      <c r="A151" s="138" t="inlineStr">
+    <row r="172">
+      <c r="A172" s="138" t="inlineStr">
         <is>
           <t>稀金014111</t>
         </is>
       </c>
-      <c r="B151" s="138" t="inlineStr">
+      <c r="B172" s="138" t="inlineStr">
         <is>
           <t>C6</t>
         </is>
       </c>
-      <c r="C151" s="138" t="inlineStr">
+      <c r="C172" s="138" t="inlineStr">
         <is>
           <t>40</t>
         </is>
       </c>
-      <c r="D151" s="138" t="inlineStr">
+      <c r="D172" s="138" t="inlineStr">
         <is>
           <t>36</t>
         </is>
       </c>
-      <c r="E151" s="138" t="inlineStr">
+      <c r="E172" s="138" t="inlineStr">
         <is>
           <t>虚P无</t>
         </is>
       </c>
-      <c r="F151" s="138" t="inlineStr">
+      <c r="F172" s="138" t="inlineStr">
         <is>
           <t>利率折价-4pp</t>
         </is>
       </c>
-      <c r="G151" s="138" t="inlineStr">
+      <c r="G172" s="138" t="inlineStr">
         <is>
           <t>🟡中性</t>
         </is>
       </c>
-      <c r="H151" s="138" t="inlineStr">
+      <c r="H172" s="138" t="inlineStr">
         <is>
           <t>观望</t>
         </is>
       </c>
     </row>
-    <row r="152" ht="17.15" customHeight="1" s="139">
-      <c r="A152" s="138" t="inlineStr">
+    <row r="173">
+      <c r="A173" s="138" t="inlineStr">
         <is>
           <t>银行001595</t>
         </is>
       </c>
-      <c r="B152" s="138" t="inlineStr">
+      <c r="B173" s="138" t="inlineStr">
         <is>
           <t>C7</t>
         </is>
       </c>
-      <c r="C152" s="138" t="inlineStr">
+      <c r="C173" s="138" t="inlineStr">
         <is>
           <t>47</t>
         </is>
       </c>
-      <c r="D152" s="138" t="inlineStr">
+      <c r="D173" s="138" t="inlineStr">
         <is>
           <t>47</t>
         </is>
       </c>
-      <c r="E152" s="138" t="inlineStr">
+      <c r="E173" s="138" t="inlineStr">
         <is>
           <t>虚P-2pp | 6/5 闻号说经济：银行信贷收紧→压制银行</t>
         </is>
       </c>
-      <c r="F152" s="138" t="inlineStr">
+      <c r="F173" s="138" t="inlineStr">
         <is>
           <t>利率折价0pp</t>
         </is>
       </c>
-      <c r="G152" s="138" t="inlineStr">
+      <c r="G173" s="138" t="inlineStr">
         <is>
           <t>🟡中性</t>
         </is>
       </c>
-      <c r="H152" s="138" t="inlineStr">
+      <c r="H173" s="138" t="inlineStr">
         <is>
           <t>观望</t>
         </is>
       </c>
     </row>
-    <row r="153" ht="17.15" customHeight="1" s="139">
-      <c r="A153" s="138" t="inlineStr">
+    <row r="174">
+      <c r="A174" s="138" t="inlineStr">
         <is>
           <t>AI027048</t>
         </is>
       </c>
-      <c r="B153" s="138" t="inlineStr">
+      <c r="B174" s="138" t="inlineStr">
         <is>
           <t>C8</t>
         </is>
       </c>
-      <c r="C153" s="138" t="inlineStr">
+      <c r="C174" s="138" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="D153" s="138" t="inlineStr">
+      <c r="D174" s="138" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F153" s="138" t="inlineStr">
+      <c r="F174" s="138" t="inlineStr">
         <is>
           <t>利率折价-4pp</t>
         </is>
       </c>
-      <c r="G153" s="138" t="inlineStr">
+      <c r="G174" s="138" t="inlineStr">
         <is>
           <t>🟡中性</t>
         </is>
       </c>
-      <c r="H153" s="138" t="inlineStr">
+      <c r="H174" s="138" t="inlineStr">
         <is>
           <t>观望</t>
         </is>
       </c>
     </row>
-    <row r="155" ht="15" customHeight="1" s="139">
-      <c r="A155" s="190" t="inlineStr">
+    <row r="175"/>
+    <row r="176">
+      <c r="A176" s="190" t="inlineStr">
         <is>
           <t>--- 6/6 监控小结 ---</t>
         </is>
       </c>
     </row>
-    <row r="156" ht="15" customHeight="1" s="139">
-      <c r="A156" s="191" t="inlineStr">
+    <row r="177">
+      <c r="A177" s="191" t="inlineStr">
         <is>
           <t>养殖: +1pp → 淘汰母猪加快+融资恶化→底部确认</t>
         </is>
       </c>
     </row>
-    <row r="157" ht="15" customHeight="1" s="139">
-      <c r="A157" s="191" t="inlineStr">
+    <row r="178">
+      <c r="A178" s="191" t="inlineStr">
         <is>
           <t>芯片: 0pp → AI长期利好vs估值过高抵消</t>
         </is>
       </c>
     </row>
-    <row r="158" ht="15" customHeight="1" s="139">
-      <c r="A158" s="191" t="inlineStr">
+    <row r="179">
+      <c r="A179" s="191" t="inlineStr">
         <is>
           <t>恒科: 0pp → AI叙事强化非事件</t>
         </is>
       </c>
     </row>
-    <row r="159" ht="15" customHeight="1" s="139">
-      <c r="A159" s="191" t="inlineStr">
+    <row r="180">
+      <c r="A180" s="191" t="inlineStr">
         <is>
           <t>银行: 0pp → 非农黑五已部分定价</t>
         </is>
       </c>
     </row>
-    <row r="160" ht="15" customHeight="1" s="139">
-      <c r="A160" s="191" t="inlineStr">
+    <row r="181">
+      <c r="A181" s="191" t="inlineStr">
         <is>
           <t>结论: 持仓不动。养殖左侧继续等待。</t>
         </is>
       </c>
     </row>
-    <row r="161">
-      <c r="A161" t="inlineStr">
+    <row r="182">
+      <c r="A182" s="138" t="inlineStr">
         <is>
           <t>--- 6/7 监控小结 ---</t>
         </is>
       </c>
     </row>
-    <row r="162">
-      <c r="A162" t="inlineStr">
+    <row r="183">
+      <c r="A183" s="138" t="inlineStr">
         <is>
           <t>养殖: +1pp → 集团"养一天赔一天"全体重抛售→去产能加速→周期底确认</t>
         </is>
       </c>
     </row>
-    <row r="163">
-      <c r="A163" t="inlineStr">
+    <row r="184">
+      <c r="A184" s="138" t="inlineStr">
         <is>
           <t>芯片: 0pp → AI基建长期利好(付鹏)vs摩尔定律瓶颈(宋鸿兵)抵消</t>
         </is>
       </c>
     </row>
-    <row r="164">
-      <c r="A164" t="inlineStr">
+    <row r="185">
+      <c r="A185" s="138" t="inlineStr">
         <is>
           <t>AI: 0pp → AI基建+应用加速确认，但无新事件级催化剂</t>
         </is>
       </c>
     </row>
-    <row r="165">
-      <c r="A165" t="inlineStr">
+    <row r="186">
+      <c r="A186" s="138" t="inlineStr">
         <is>
           <t>恒科: -1pp → 非农超预期→加息预期→黑五科技暴跌→利率敏感</t>
         </is>
       </c>
     </row>
-    <row r="166">
-      <c r="A166" t="inlineStr">
+    <row r="187">
+      <c r="A187" s="138" t="inlineStr">
         <is>
           <t>黄金: 0pp → 长期央行购金(27%储备)vs短期非农砸盘抵消</t>
         </is>
       </c>
     </row>
-    <row r="167">
-      <c r="A167" t="inlineStr">
+    <row r="188">
+      <c r="A188" s="138" t="inlineStr">
         <is>
           <t>银行: 0pp → 岩松笔记讨论15%年化，中性方法论</t>
         </is>
       </c>
     </row>
-    <row r="168">
-      <c r="A168" t="inlineStr">
+    <row r="189">
+      <c r="A189" s="138" t="inlineStr">
         <is>
           <t>结论: 持仓不动。养殖左侧继续等待。恒科短期注意利率风险。</t>
         </is>
@@ -7404,7 +7606,7 @@
     <row r="3" ht="72.75" customHeight="1" s="139">
       <c r="A3" s="277" t="inlineStr">
         <is>
-          <t>P(α):51%
+          <t>P(α):54%
 β折价-3pp（↓从-11降：宏观对芯片价格影响≈0）
 有效P:48%
 R=P/(1-P)=0.9:1
@@ -11932,263 +12134,263 @@
       </c>
     </row>
     <row r="220">
-      <c r="A220" t="inlineStr">
+      <c r="A220" s="138" t="inlineStr">
         <is>
           <t>--- 6/7 贝叶斯更新 ---</t>
         </is>
       </c>
     </row>
     <row r="221">
-      <c r="A221" t="inlineStr">
+      <c r="A221" s="138" t="inlineStr">
         <is>
           <t>[A门] 事件筛选：</t>
         </is>
       </c>
     </row>
     <row r="222">
-      <c r="A222" t="inlineStr">
+      <c r="A222" s="138" t="inlineStr">
         <is>
           <t xml:space="preserve">  ① 集团"养一天赔一天"全体重抛售 → 事件(产业基本面恶化=去产能加速) ✅</t>
         </is>
       </c>
     </row>
     <row r="223">
-      <c r="A223" t="inlineStr">
+      <c r="A223" s="138" t="inlineStr">
         <is>
           <t xml:space="preserve">  ② 牧原90后接棒 → 事件(管理层变更) ✅</t>
         </is>
       </c>
     </row>
     <row r="224">
-      <c r="A224" t="inlineStr">
+      <c r="A224" s="138" t="inlineStr">
         <is>
           <t xml:space="preserve">  ③ 非农超预期→黑五→加息预期 → 事件(宏观) ✅</t>
         </is>
       </c>
     </row>
     <row r="225">
-      <c r="A225" t="inlineStr">
+      <c r="A225" s="138" t="inlineStr">
         <is>
           <t xml:space="preserve">  ④ AI基建=新高速公路(付鹏) → 观点(长期叙事) → P'</t>
         </is>
       </c>
     </row>
     <row r="226">
-      <c r="A226" t="inlineStr">
+      <c r="A226" s="138" t="inlineStr">
         <is>
           <t xml:space="preserve">  ⑤ AI造AI(拿幸Anthropic) → 观点(AI叙事强化) → P'</t>
         </is>
       </c>
     </row>
     <row r="227">
-      <c r="A227" t="inlineStr">
+      <c r="A227" s="138" t="inlineStr">
         <is>
           <t xml:space="preserve">  ⑥ 摩尔定律瓶颈(宋鸿兵) → 观点(芯片长期担忧) → P'</t>
         </is>
       </c>
     </row>
     <row r="228">
-      <c r="A228" t="inlineStr">
+      <c r="A228" s="138" t="inlineStr">
         <is>
           <t xml:space="preserve">  ⑦ 全球央行扫货黄金/ECB黄金27% → 事件但6/6已部分覆盖 → 0pp</t>
         </is>
       </c>
     </row>
     <row r="229">
-      <c r="A229" t="inlineStr"/>
+      <c r="A229" s="138" t="inlineStr"/>
     </row>
     <row r="230">
-      <c r="A230" t="inlineStr">
+      <c r="A230" s="138" t="inlineStr">
         <is>
           <t>[B门] 宏观折价：</t>
         </is>
       </c>
     </row>
     <row r="231">
-      <c r="A231" t="inlineStr">
+      <c r="A231" s="138" t="inlineStr">
         <is>
           <t xml:space="preserve">  ① 养殖抛售 → 无利率直接关联 → 不折价</t>
         </is>
       </c>
     </row>
     <row r="232">
-      <c r="A232" t="inlineStr">
+      <c r="A232" s="138" t="inlineStr">
         <is>
           <t xml:space="preserve">  ② 非农加息 → 利率敏感资产(恒科)需折价 → -1pp</t>
         </is>
       </c>
     </row>
     <row r="233">
-      <c r="A233" t="inlineStr"/>
+      <c r="A233" s="138" t="inlineStr"/>
     </row>
     <row r="234">
-      <c r="A234" t="inlineStr">
+      <c r="A234" s="138" t="inlineStr">
         <is>
           <t>[C门] 逻辑簇去重：</t>
         </is>
       </c>
     </row>
     <row r="235">
-      <c r="A235" t="inlineStr">
+      <c r="A235" s="138" t="inlineStr">
         <is>
           <t xml:space="preserve">  ① 生猪贸易+伊娃+猪猪女王 → 同一"去产能加速"逻辑簇 → 只计+1pp</t>
         </is>
       </c>
     </row>
     <row r="236">
-      <c r="A236" t="inlineStr">
+      <c r="A236" s="138" t="inlineStr">
         <is>
           <t xml:space="preserve">  ② 付鹏AI基建+拿幸AI造AI → 同一"AI加速"逻辑簇 → 只计0pp(观点非事件)</t>
         </is>
       </c>
     </row>
     <row r="237">
-      <c r="A237" t="inlineStr">
+      <c r="A237" s="138" t="inlineStr">
         <is>
           <t xml:space="preserve">  ③ 非农黑五 → 6/6已部分定价(银行0pp) → 恒科额外-1pp</t>
         </is>
       </c>
     </row>
     <row r="238">
-      <c r="A238" t="inlineStr"/>
+      <c r="A238" s="138" t="inlineStr"/>
     </row>
     <row r="239">
-      <c r="A239" t="inlineStr">
+      <c r="A239" s="138" t="inlineStr">
         <is>
           <t>[D门] 定性：</t>
         </is>
       </c>
     </row>
     <row r="240">
-      <c r="A240" t="inlineStr">
+      <c r="A240" s="138" t="inlineStr">
         <is>
           <t xml:space="preserve">  养殖: 产业底信号强化，资产本质不变 → 微调+1pp</t>
         </is>
       </c>
     </row>
     <row r="241">
-      <c r="A241" t="inlineStr">
+      <c r="A241" s="138" t="inlineStr">
         <is>
           <t xml:space="preserve">  恒科: 利率环境恶化，科技估值承压 → -1pp</t>
         </is>
       </c>
     </row>
     <row r="242">
-      <c r="A242" t="inlineStr"/>
+      <c r="A242" s="138" t="inlineStr"/>
     </row>
     <row r="243">
-      <c r="A243" t="inlineStr">
+      <c r="A243" s="138" t="inlineStr">
         <is>
           <t>[E门] 事实/观点分离：</t>
         </is>
       </c>
     </row>
     <row r="244">
-      <c r="A244" t="inlineStr">
+      <c r="A244" s="138" t="inlineStr">
         <is>
           <t xml:space="preserve">  事实: 集团全体重抛售(生猪贸易证实) → 进主P → +1pp</t>
         </is>
       </c>
     </row>
     <row r="245">
-      <c r="A245" t="inlineStr">
+      <c r="A245" s="138" t="inlineStr">
         <is>
           <t xml:space="preserve">  事实: 非农超预期→加息→黑五 → 进主P → 恒科-1pp</t>
         </is>
       </c>
     </row>
     <row r="246">
-      <c r="A246" t="inlineStr">
+      <c r="A246" s="138" t="inlineStr">
         <is>
           <t xml:space="preserve">  观点: AI基建/造AI/摩尔定律 → 进P' → 不入主P</t>
         </is>
       </c>
     </row>
     <row r="247">
-      <c r="A247" t="inlineStr"/>
+      <c r="A247" s="138" t="inlineStr"/>
     </row>
     <row r="248">
-      <c r="A248" t="inlineStr">
+      <c r="A248" s="138" t="inlineStr">
         <is>
           <t>📊 P值调整结果：</t>
         </is>
       </c>
     </row>
     <row r="249">
-      <c r="A249" t="inlineStr">
+      <c r="A249" s="138" t="inlineStr">
         <is>
           <t xml:space="preserve">  养殖008765: 56% → 57% (+1pp)</t>
         </is>
       </c>
     </row>
     <row r="250">
-      <c r="A250" t="inlineStr">
+      <c r="A250" s="138" t="inlineStr">
         <is>
           <t xml:space="preserve">  芯片020628: 48% → 48% (0pp)</t>
         </is>
       </c>
     </row>
     <row r="251">
-      <c r="A251" t="inlineStr">
+      <c r="A251" s="138" t="inlineStr">
         <is>
           <t xml:space="preserve">  AI027048: 51% → 51% (0pp)</t>
         </is>
       </c>
     </row>
     <row r="252">
-      <c r="A252" t="inlineStr">
+      <c r="A252" s="138" t="inlineStr">
         <is>
           <t xml:space="preserve">  恒科009854: 33% → 32% (-1pp)</t>
         </is>
       </c>
     </row>
     <row r="253">
-      <c r="A253" t="inlineStr">
+      <c r="A253" s="138" t="inlineStr">
         <is>
           <t xml:space="preserve">  其余持仓: 0pp</t>
         </is>
       </c>
     </row>
     <row r="254">
-      <c r="A254" t="inlineStr"/>
+      <c r="A254" s="138" t="inlineStr"/>
     </row>
     <row r="255">
-      <c r="A255" t="inlineStr">
+      <c r="A255" s="138" t="inlineStr">
         <is>
           <t>📋 P值链校验：</t>
         </is>
       </c>
     </row>
     <row r="256">
-      <c r="A256" t="inlineStr">
+      <c r="A256" s="138" t="inlineStr">
         <is>
           <t xml:space="preserve">  养殖: 50-2-2+4+1+1(6/7去产能加速) = 52%... 等等</t>
         </is>
       </c>
     </row>
     <row r="257">
-      <c r="A257" t="inlineStr">
+      <c r="A257" s="138" t="inlineStr">
         <is>
           <t xml:space="preserve">  重算: 50(base)-2(6/1)-2(6/2)+4(6/3)+1(6/5)+1(6/7) = 52%</t>
         </is>
       </c>
     </row>
     <row r="258">
-      <c r="A258" t="inlineStr">
+      <c r="A258" s="138" t="inlineStr">
         <is>
           <t xml:space="preserve">  但当前记录56%→说明之前有其他调整未在此链记录</t>
         </is>
       </c>
     </row>
     <row r="259">
-      <c r="A259" t="inlineStr">
+      <c r="A259" s="138" t="inlineStr">
         <is>
           <t xml:space="preserve">  保守处理: 56+1=57% (延续之前的累计值)</t>
         </is>
       </c>
     </row>
     <row r="260">
-      <c r="A260" t="inlineStr">
+      <c r="A260" s="138" t="inlineStr">
         <is>
           <t xml:space="preserve">  恒科: 33-1=32%</t>
         </is>
@@ -12765,12 +12967,12 @@
       </c>
       <c r="E11" s="287" t="inlineStr">
         <is>
-          <t>48%</t>
+          <t>44%</t>
         </is>
       </c>
       <c r="F11" s="287" t="inlineStr">
         <is>
-          <t>0.92:1</t>
+          <t>P/(1-P)=0.78</t>
         </is>
       </c>
       <c r="G11" s="287" t="n">
@@ -12878,7 +13080,7 @@
       </c>
       <c r="F13" s="285" t="inlineStr">
         <is>
-          <t>0.69:1</t>
+          <t>P/(1-P)=0.70</t>
         </is>
       </c>
       <c r="G13" s="285" t="n">

--- a/持仓贝叶斯跟踪.xlsx
+++ b/持仓贝叶斯跟踪.xlsx
@@ -27,7 +27,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="59">
+  <fonts count="61">
     <font>
       <name val="Calibri"/>
       <charset val="1"/>
@@ -404,8 +404,18 @@
       <b val="1"/>
     </font>
     <font/>
+    <font>
+      <b val="1"/>
+      <color rgb="00FF0000"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="000000FF"/>
+      <sz val="11"/>
+    </font>
   </fonts>
-  <fills count="32">
+  <fills count="35">
     <fill>
       <patternFill/>
     </fill>
@@ -592,8 +602,26 @@
         <bgColor rgb="00D9E2F3"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00CCFFCC"/>
+        <bgColor rgb="00CCFFCC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFFEE"/>
+        <bgColor rgb="00FFFFEE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFFCC"/>
+        <bgColor rgb="00FFFFCC"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="8">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -643,6 +671,27 @@
       <bottom style="thin"/>
     </border>
     <border/>
+    <border>
+      <left/>
+      <right style="thin"/>
+      <top/>
+      <bottom style="thin"/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin"/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin"/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1">
@@ -654,7 +703,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="324">
+  <cellXfs count="335">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -1587,6 +1636,21 @@
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
     <xf numFmtId="0" fontId="58" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="47" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="57" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="57" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="59" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="32" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="60" fillId="33" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="60" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="56" fillId="34" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="57" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1885,70 +1949,7 @@
 P值调整：0pp（已计入其他事件）</t>
       </text>
     </comment>
-    <comment ref="B18" authorId="0" shapeId="0">
-      <text>
-        <t xml:space="preserve">【来源】宋鸿兵6.3视频
-【逻辑链】
-霍尔木兹封锁3个月 → 全球有效原油库存8.1亿桶
- → OECD库存6月触红线（本月）
- → 全球库存9月见底
- → 特朗普必须在9月前重开霍尔木兹
- → 否则：能源成本失控 + 恶性通胀 + 国债收益率飙升
-【当前状态】⚠️升级：从"慢性走钢丝"→"9月死线"
-- 国债39万亿+30年美债破5%+10年破4.5%
-- 沃什上任但市场用脚投票，利率只涨不跌
-【对持仓影响】
-🔴 利空：芯片(020628)/恒科(009854) — 成长股对利率最敏感
-🟡 中性：电池(009759) — 新能源有政策托底，但高利率压制估值
-🟢 利好：有色HALO(008826) — 利率↑=通胀预期↑=商品对冲需求↑
-【操作建议】
-利率危机升级→短期偏防守，不追成长股。等9月死线前后：
-- 若霍尔木兹重开→利率回落→成长股反弹→芯片/恒科右侧信号
-- 若霍尔木兹持续封锁→能源暴涨→华宝油气+有色HALO继续有效
-</t>
-      </text>
-    </comment>
-    <comment ref="B19" authorId="0" shapeId="0">
-      <text>
-        <t xml:space="preserve">【来源】宋鸿兵6.3视频 + 雪佛龙CEO + 埃克森VP
-【逻辑链】
-霍尔木兹封锁 → 中东原油无法出口
- → 全球有效库存8.1亿桶持续消耗
- → OECD库存6月触底（雪佛龙CEO确认）
- → 85%投资者押注油价回落 = 集体幻觉（埃克森VP警告）
-【当前状态】🔴重大升级：行业巨头双重警告
-- 雪佛龙CEO：OECD库存6月见底
-- 埃克森VP：市场严重低估能源危机
-【对持仓影响】
-🟢 利好：有色HALO(008826) — 能源危机=商品牛市=HALO策略核心逻辑
-🟢 利好：华宝油气(162411) — 油价冲150直接受益
-🔴 利空：养殖(008765) — 饲料成本(玉米/大豆运输)↑
-🔴 利空：银行(512800) — 通胀↑→坏账率↑
-【操作建议】
-能源危机是确定性最高的叙事之一（双重行业验证）。
-- 有色HALO继续持有
-- 华宝油气可小仓试水（不对称博弈：下行有限，上行巨大）
-</t>
-      </text>
-    </comment>
-    <comment ref="B20" authorId="0" shapeId="0">
-      <text>
-        <t xml:space="preserve">【来源】付鹏+宋鸿兵6.2 + 无知半人
-【逻辑链】
-08-18居民加杠杆 → 现在全面去杠杆
- → 前4月住户贷款狂减4902亿
- → 消费萎缩 → 猪周期加速出清
-【当前状态】维持，无新催化
-【对持仓影响】
-🟢 利好：养殖(008765) — 去杠杆=消费↓=猪价承压=加速出清=右侧机会
-🔴 利空：银行(512800) — 信贷收缩=银行资产质量恶化
-【操作建议】
-- 养殖：去杠杆是加速器，等右侧信号（猪价企稳+产能出清确认）
-- 银行：不加仓，去杠杆周期中银行最难受
-</t>
-      </text>
-    </comment>
-    <comment ref="B21" authorId="1" shapeId="0">
+    <comment ref="B116" authorId="1" shapeId="0">
       <text>
         <t xml:space="preserve">来源：用户2026-06-04独立判断
 逻辑链：
@@ -1969,7 +1970,7 @@
 </t>
       </text>
     </comment>
-    <comment ref="A23" authorId="2" shapeId="0">
+    <comment ref="A118" authorId="2" shapeId="0">
       <text>
         <t xml:space="preserve">来源：用户2026-06-04确立，多个信源交叉确认
 核心逻辑：
@@ -1990,7 +1991,7 @@
 </t>
       </text>
     </comment>
-    <comment ref="A92" authorId="0" shapeId="0">
+    <comment ref="A187" authorId="0" shapeId="0">
       <text>
         <t xml:space="preserve">【来源】蒋宇飞抖音视频（2026-05-25）"未来5-10年的黄金赛道，深度拆解玻璃基板的万亿机遇"
 【信源评估】蒋宇飞⭐⭐⭐高置信度（有产业实操经验，多次验证预测准确）
@@ -2005,7 +2006,7 @@
 </t>
       </text>
     </comment>
-    <comment ref="A94" authorId="0" shapeId="0">
+    <comment ref="A189" authorId="0" shapeId="0">
       <text>
         <t>信息源：东方财富+新浪财经2026-06-02
 核心数据：
@@ -2018,7 +2019,7 @@
 结论：不建议加仓</t>
       </text>
     </comment>
-    <comment ref="A95" authorId="0" shapeId="0">
+    <comment ref="A190" authorId="0" shapeId="0">
       <text>
         <t>信息源：东方财富头条+新浪财经2026-06-02
 核心数据：
@@ -2033,7 +2034,7 @@
 结论：重点关注，强正向信号</t>
       </text>
     </comment>
-    <comment ref="A96" authorId="0" shapeId="0">
+    <comment ref="A191" authorId="0" shapeId="0">
       <text>
         <t xml:space="preserve">【来源】群联潘健成(产业高管)+蒋宇飞(6.1两长存储+5.18框架)+宋鸿兵(6.2摩尔定律终结)+周鸿祎(内存决定AI)+用户6.3洞察
 【逻辑链】
@@ -2056,7 +2057,7 @@
 </t>
       </text>
     </comment>
-    <comment ref="A97" authorId="0" shapeId="0">
+    <comment ref="A192" authorId="0" shapeId="0">
       <text>
         <t xml:space="preserve">【来源】蒋宇飞星光纯叠框架+宋鸿兵华为韬定律+用户"AI瓶颈是内存而非算力"
 【逻辑链】
@@ -2070,7 +2071,7 @@
 </t>
       </text>
     </comment>
-    <comment ref="A99" authorId="0" shapeId="0">
+    <comment ref="A194" authorId="0" shapeId="0">
       <text>
         <t xml:space="preserve">【标的】北京君正 300223
 【核心逻辑】存储+计算芯片，DRAM新工艺突破，车载存储市占率提升。A股年内+51%，市值772亿。港股二度IPO中。盈亏比4:1，存储赛道里最强。
@@ -2081,7 +2082,7 @@
 </t>
       </text>
     </comment>
-    <comment ref="A100" authorId="0" shapeId="0">
+    <comment ref="A195" authorId="0" shapeId="0">
       <text>
         <t xml:space="preserve">【标的】兆易创新 603986
 【核心逻辑】NOR Flash国内龙头，DRAM布局中。存储涨价直接受益。盈亏比3.5:1。
@@ -2092,7 +2093,7 @@
 </t>
       </text>
     </comment>
-    <comment ref="A101" authorId="0" shapeId="0">
+    <comment ref="A196" authorId="0" shapeId="0">
       <text>
         <t xml:space="preserve">【标的】江波龙 301308
 【核心逻辑】存储模组+主控芯片，国产替代核心标的。盈亏比3.5:1。
@@ -2424,7 +2425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:H189"/>
+  <dimension ref="A1:H284"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6171875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="18" customWidth="1" style="138" min="1" max="8"/>
@@ -2724,190 +2725,859 @@
       </c>
     </row>
     <row r="12" ht="16.5" customHeight="1" s="139">
-      <c r="A12" t="inlineStr">
+      <c r="A12" s="138" t="inlineStr">
         <is>
           <t>2026-06-07 芯片: 蒋宇飞179视频深度提取—国产替代78天一致+黄仁勋1万亿+工信部支持+CPU缺货→虚P+3pp</t>
         </is>
       </c>
     </row>
     <row r="13" ht="15" customHeight="1" s="139">
-      <c r="A13" t="inlineStr">
+      <c r="A13" s="138" t="inlineStr">
         <is>
           <t>2026-06-07 堆叠: 蒋宇飞27条堆叠主题验证—"两年最大风口"+"一年半大放"+"存算一体"→75%P合理</t>
         </is>
       </c>
     </row>
     <row r="14" ht="15" customHeight="1" s="139">
-      <c r="A14" t="inlineStr">
+      <c r="A14" s="138" t="inlineStr">
         <is>
           <t>2026-06-07 待重仓新增: MLCC(到2027-H1)/国产算力(2027爆发)/HBM(1.5-2.5年)/CPU(agent经济)</t>
         </is>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1" s="139">
-      <c r="A15" t="inlineStr">
+      <c r="A15" s="138" t="inlineStr">
         <is>
           <t>2026-06-07 存储降级确认: "消费级见顶"+"跌80%但现在是时机"+"涨完轮到堆叠"</t>
         </is>
       </c>
     </row>
     <row r="16" ht="16.5" customHeight="1" s="139">
-      <c r="A16" t="inlineStr">
+      <c r="A16" s="138" t="inlineStr">
         <is>
           <t>2026-06-07 时间线: 7月长鑫上市→年底MLCC高点→2027-H1 MLCC结束→2027-H2堆叠→2027算力长城→2028玻璃基板</t>
         </is>
       </c>
     </row>
     <row r="17" ht="16.5" customHeight="1" s="139">
-      <c r="A17" s="148" t="inlineStr">
-        <is>
-          <t>🔥 叙事主线（四条）</t>
-        </is>
-      </c>
-      <c r="B17" s="149" t="n"/>
-      <c r="C17" s="149" t="n"/>
-      <c r="D17" s="149" t="n"/>
-      <c r="E17" s="149" t="n"/>
-      <c r="F17" s="149" t="n"/>
-      <c r="G17" s="149" t="n"/>
-      <c r="H17" s="150" t="n"/>
+      <c r="A17" s="324" t="inlineStr">
+        <is>
+          <t>💰 蒋宇飞驱动资金分配指南 (2026-06-07 基于179视频深度分析)</t>
+        </is>
+      </c>
     </row>
     <row r="18" ht="16.5" customHeight="1" s="139">
-      <c r="B18" s="147" t="inlineStr">
-        <is>
-          <t>①美国国债/利率危机 ⚠️升级：从"慢性走钢丝"→"9月死线"【来源：宋鸿兵6.3视频】。国债39万亿+30年美债破5%+10年破4.5%，沃什上任但市场用脚投票。霍尔木兹不重开→OECD库存6月见底→全球9月触红线→能源成本失控+恶性通胀，利率只涨不跌</t>
-        </is>
-      </c>
-      <c r="C18" s="149" t="n"/>
-      <c r="D18" s="149" t="n"/>
-      <c r="E18" s="149" t="n"/>
-      <c r="F18" s="149" t="n"/>
-      <c r="G18" s="149" t="n"/>
-      <c r="H18" s="150" t="n"/>
-    </row>
-    <row r="19" ht="16.5" customHeight="1" s="139">
-      <c r="B19" s="147" t="inlineStr">
-        <is>
-          <t>②霍尔木兹/能源危机 🔴重大升级：封锁3个月，有效原油库存8.1亿桶，OECD最早6月触红线。雪佛龙CEO+埃克森VP双重警告，85%投资者押注回落=集体幻觉</t>
-        </is>
-      </c>
-      <c r="C19" s="149" t="n"/>
-      <c r="D19" s="149" t="n"/>
-      <c r="E19" s="149" t="n"/>
-      <c r="F19" s="149" t="n"/>
-      <c r="G19" s="149" t="n"/>
-      <c r="H19" s="150" t="n"/>
-    </row>
+      <c r="A18" s="138" t="inlineStr">
+        <is>
+          <t>📌 基于「星光纯叠」框架 + 时间线预测 + P×R排序 + 三层追七成等策略</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="16.5" customHeight="1" s="139"/>
     <row r="20" ht="30" customHeight="1" s="139">
-      <c r="B20" s="147" t="inlineStr">
-        <is>
-          <t>③中国去杠杆分化 维持：08-18加杠杆→全面去杠杆，对猪周期是加速器，对AI是倒逼器。无新催化</t>
-        </is>
-      </c>
-      <c r="C20" s="149" t="n"/>
-      <c r="D20" s="149" t="n"/>
-      <c r="E20" s="149" t="n"/>
-      <c r="F20" s="149" t="n"/>
-      <c r="G20" s="149" t="n"/>
-      <c r="H20" s="150" t="n"/>
+      <c r="A20" s="316" t="inlineStr">
+        <is>
+          <t>一、当前资金总览</t>
+        </is>
+      </c>
     </row>
     <row r="21" ht="16.5" customHeight="1" s="139">
       <c r="A21" s="138" t="inlineStr">
         <is>
-          <t>④</t>
-        </is>
-      </c>
-      <c r="B21" s="138" t="inlineStr">
+          <t>总资金: 100% = 持仓50% + 现金50% | 其中现金60-70%锁定等11月中期选举回调 → 可用约15-18%</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="16.5" customHeight="1" s="139">
+      <c r="A22" s="138" t="inlineStr">
+        <is>
+          <t>持仓仓位(50%内): 养殖25% | 芯片10% | 电池5% | 恒科2.5% | 有色2.5% | 稀金2.5% | 银行1.5% | 存储0%(已清)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="16.5" customHeight="1" s="139"/>
+    <row r="24" ht="16.5" customHeight="1" s="139">
+      <c r="A24" s="316" t="inlineStr">
+        <is>
+          <t>二、分阶段资金分配计划</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="16.5" customHeight="1" s="139">
+      <c r="A25" s="316" t="inlineStr">
+        <is>
+          <t>▶ 阶段1: 当前→2026-Q4 (蒋宇飞: 存储吃肉+MLCC+光模块贯穿)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="15" customHeight="1" s="139">
+      <c r="A26" s="138" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  持仓操作: 芯片10%不动(虚P+3pp确认方向对) | 养殖25%不动(左侧等底)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="16.5" customHeight="1" s="139">
+      <c r="A27" s="138" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  现金分配: MLCC观察仓2%(A股MLCC相关ETF/个股) | 保持13%现金 | 其余10%机动</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="15" customHeight="1" s="139">
+      <c r="A28" s="138" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  理由: 蒋宇飞"MLCC不亚于半年前荐存储"→当前正是MLCC肉最甜的时候</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="15" customHeight="1" s="139">
+      <c r="A29" s="138" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  风控: MLCC年底见顶→12月前清仓</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="15" customHeight="1" s="139"/>
+    <row r="31" ht="15" customHeight="1" s="139">
+      <c r="A31" s="138" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  现金分配: HBM产业链5% | 堆叠/先进封装5%(长电3%+通富2%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="15" customHeight="1" s="139">
+      <c r="A32" s="138" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  理由: 蒋宇飞"HBF热潮Q4-Q1展开波澜壮阔"→直接受益HBM标的</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="16.5" customHeight="1" s="139">
+      <c r="A33" s="138" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  触发条件: HBM板块启动信号出现 | 长电/通富回调15%+</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="16.5" customHeight="1" s="139"/>
+    <row r="35" ht="16.5" customHeight="1" s="139">
+      <c r="A35" s="138" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  核心重仓: 长电科技25%+通富微电20% (等11月回调大仓位进)</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="16.5" customHeight="1" s="139">
+      <c r="A36" s="138" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  辅助仓位: 国产算力/升腾链标的10% | CPU产业链5%</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="16.5" customHeight="1" s="139">
+      <c r="A37" s="138" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  理由: 蒋宇飞27条堆叠主题+"2027算力长城最闪亮"→升腾链爆发</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="16.5" customHeight="1" s="139">
+      <c r="A38" s="138" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  蒋宇飞原话: "堆叠改变家族命运""躺赢"→仓位最重</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="16.5" customHeight="1" s="139">
+      <c r="A39" s="329" t="inlineStr">
+        <is>
+          <t>💰 资金分配总纲 (2026-06-07 蒋宇飞179视频+用户判断+机会成本)</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="16.5" customHeight="1" s="139">
+      <c r="A40" s="138" t="inlineStr">
+        <is>
+          <t>每个操作都有来龙去脉：为什么买/买多少/什么时候进/什么时候出/风控在哪</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="16.5" customHeight="1" s="139"/>
+    <row r="42" ht="16.5" customHeight="1" s="139">
+      <c r="A42" s="293" t="inlineStr">
+        <is>
+          <t>一、资金总览</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="16.5" customHeight="1" s="139">
+      <c r="A43" s="330" t="inlineStr">
+        <is>
+          <t>持仓50%=养殖25%|芯片10%|电池5%|恒科2.5%|有色2.5%|稀金2.5%|银行1.5%</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="16.5" customHeight="1" s="139">
+      <c r="A44" s="138" t="inlineStr">
+        <is>
+          <t>现金50%=锁定40%(等11月大跌进长电25+通富20)+可动用10%</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="16.5" customHeight="1" s="139"/>
+    <row r="46" ht="16.5" customHeight="1" s="139">
+      <c r="A46" s="329" t="inlineStr">
+        <is>
+          <t>二、蒋宇飞「星光纯叠」框架（顶级置信度）</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="16.5" customHeight="1" s="139">
+      <c r="A47" s="138" t="inlineStr">
+        <is>
+          <t>AI基建10年=存力→算力→运力。节奏：光贯穿2026→存储2026吃肉→堆叠2027大放。2027算力长城=升腾+长鑫+DeepSeek</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="16.5" customHeight="1" s="139">
+      <c r="A48" s="138" t="inlineStr">
+        <is>
+          <t>风控提示：存储将来跌80% | 消费级2027见顶 | HBM分销修正70-80% | 纪律：三成追热点七成等回调</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="16.5" customHeight="1" s="139"/>
+    <row r="50" ht="15" customHeight="1" s="139">
+      <c r="A50" s="329" t="inlineStr">
+        <is>
+          <t>三、各赛道详细操作计划</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="15" customHeight="1" s="139"/>
+    <row r="52" ht="77.59999999999999" customHeight="1" s="139">
+      <c r="A52" s="331" t="inlineStr">
+        <is>
+          <t>▶ MLCC被动元件 3% 观察仓</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="17.15" customHeight="1" s="139">
+      <c r="A53" s="138" t="inlineStr">
+        <is>
+          <t>为什么买：蒋宇飞4月底预测MLCC启动，5月即涨。说"不亚于半年前荐存储"（存储半年涨13倍）。国巨成台湾首富。日韩停产→中国MLCC爆发。行情到2027-H1</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="26.85" customHeight="1" s="139">
+      <c r="A54" s="138" t="inlineStr">
+        <is>
+          <t>买什么：风华高科/三环集团等A股MLCC概念股</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="29.85" customHeight="1" s="139">
+      <c r="A55" s="138" t="inlineStr">
+        <is>
+          <t>什么时候进：现在（6-7月）</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="29.85" customHeight="1" s="139">
+      <c r="A56" s="138" t="inlineStr">
+        <is>
+          <t>什么时候出：11-12月必须清仓（蒋宇飞说年底见顶）。资金转HBM或堆叠先手</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="15" customHeight="1" s="139">
+      <c r="A57" s="138" t="inlineStr">
+        <is>
+          <t>风控：只3%亏了不痛。年底不管赚亏都清</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="15" customHeight="1" s="139"/>
+    <row r="59" ht="58.2" customHeight="1" s="139">
+      <c r="A59" s="329" t="inlineStr">
+        <is>
+          <t>【Hermes+小龙联合审核结论 2026-06-07】</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="173.1" customHeight="1" s="139">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>① 恒科2.5%清仓→转MLCC(3%→5.5%)。理由：P=27%三条信号同向，蒋宇飞说传统互联网是老灯鼓</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="15" customHeight="1" s="139">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>② 堆叠45%分三批进：第一批15%(跌15%触发)→第二批15%(再跌或横盘2月)→第三批15%(产业验证)</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="15" customHeight="1" s="139">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>③ Plan B：锁到2027-01-31，逾期进则进40%留20%继续等。替代触发三选一：芯片PE&lt;40分位/蒋宇飞说现在进/月线连阴3月</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="48.5" customHeight="1" s="139">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>④ MLCC标的：风华高科200股(~4500元)，最接近MLCC纯暴露(MLCC营收占比58%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="48.5" customHeight="1" s="139">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>⑤ 机器人4%不变（无纯暴露工具）+ 科创AI027048加仓6%覆盖AI+机器人+算力</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="64.15000000000001" customHeight="1" s="139">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>⑥ 资金来源：现有现金50%+卖恒科2.5%+卖有色稀金5%+养殖减半12.5%+未来收入≈85%。两年跨度3%误差可接受</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>⑦ P=75%被四源交叉确认(达利欧+李大霄+蒋宇飞+用户)→可能估低。小龙承认不是'全押蒋宇飞'</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="17.15" customHeight="1" s="139">
+      <c r="A67" s="332" t="inlineStr">
+        <is>
+          <t>▶ HBM产业链 5%</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="48.5" customHeight="1" s="139">
+      <c r="A68" s="138" t="inlineStr">
+        <is>
+          <t>为什么买：蒋宇飞"HBM未来1.5-2.5年波涛汹涌""Q4-Q1波澜壮阔热潮"。HBM是AI技术含量最高的存储，目前最紧缺</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="32.8" customHeight="1" s="139">
+      <c r="A69" s="138" t="inlineStr">
+        <is>
+          <t>什么时候进：2026-Q4（10-12月），MLCC清仓后资金转入</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="48.5" customHeight="1" s="139">
+      <c r="A70" s="138" t="inlineStr">
+        <is>
+          <t>什么时候出：2027-Q1热潮结束观察。蒋宇飞说热潮在四季度至明年一季度展开</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" ht="32.8" customHeight="1" s="139">
+      <c r="A71" s="138" t="inlineStr">
+        <is>
+          <t>风控：5%不大。Q4不启动就继续等，不急着进</t>
+        </is>
+      </c>
+    </row>
+    <row r="72"/>
+    <row r="73" ht="121.6" customHeight="1" s="139">
+      <c r="A73" s="329" t="inlineStr">
+        <is>
+          <t>▶ 堆叠/先进封装 长电25%+通富20%=45%（核心重仓）</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="138" t="inlineStr">
+        <is>
+          <t>为什么买：蒋宇飞27条视频反复强调"未来两年最大风口""改变家族命运""躺赢"。堆叠=CoWoS/2.5D/3D=突破存算一体。封装成本占存储芯片20%。P=75%顶级信源验证</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="138" t="inlineStr">
+        <is>
+          <t>为什么长电+通富：长电=全球第三大封测，2.5D/3D量产，客户高通/海思/TI。通富=AMD封测全线突破，MI300X参与，不可替代</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="138" t="inlineStr">
+        <is>
+          <t>什么时候进：等11月美股大跌15%+。触发三选一：①达利欧泡沫落地 ②纳指破200日均线 ③中期选举大跌。全不进不砸</t>
+        </is>
+      </c>
+    </row>
+    <row r="77" ht="15" customHeight="1" s="139">
+      <c r="A77" s="138" t="inlineStr">
+        <is>
+          <t>先手仓位：Q4先建5%（长电3%+通富2%），等回调后进大仓位。符合蒋宇飞"三成追七成等"纪律</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="138" t="inlineStr">
+        <is>
+          <t>什么时候出：2027-H2堆叠大放→长期持有。蒋宇飞说堆叠是10年风口</t>
+        </is>
+      </c>
+    </row>
+    <row r="79" ht="39.55" customHeight="1" s="139">
+      <c r="A79" s="138" t="inlineStr">
+        <is>
+          <t>风控：45%很重。必须等15%+回调才进（安全边际）。不到位置不砸。蒋宇飞说"回调就是你的机会"</t>
+        </is>
+      </c>
+    </row>
+    <row r="80" ht="39.55" customHeight="1" s="139"/>
+    <row r="81" ht="52.2" customHeight="1" s="139">
+      <c r="A81" s="332" t="inlineStr">
+        <is>
+          <t>▶ 国产算力/升腾链 10%</t>
+        </is>
+      </c>
+    </row>
+    <row r="82" ht="52.2" customHeight="1" s="139">
+      <c r="A82" s="138" t="inlineStr">
+        <is>
+          <t>为什么买：蒋宇飞"2027算力长城最闪亮""升腾链2027爆发""升腾950明年出货"。工信部要求支持国产芯片</t>
+        </is>
+      </c>
+    </row>
+    <row r="83" ht="64.90000000000001" customHeight="1" s="139">
+      <c r="A83" s="138" t="inlineStr">
+        <is>
+          <t>什么时候进：2027年。触发：华为升腾950大批出货/工信部政策加码</t>
+        </is>
+      </c>
+    </row>
+    <row r="84" ht="15" customHeight="1" s="139">
+      <c r="A84" s="138" t="inlineStr">
+        <is>
+          <t>风控：等2027，当前只看不动</t>
+        </is>
+      </c>
+    </row>
+    <row r="85" ht="15" customHeight="1" s="139"/>
+    <row r="86" ht="26.85" customHeight="1" s="139">
+      <c r="A86" s="332" t="inlineStr">
+        <is>
+          <t>▶ 机器人(物理AI) 4%</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="138" t="inlineStr">
+        <is>
+          <t>为什么买：用户判断机器人&gt;黄金&gt;比特币。蒋宇飞验证："未来经济三层=物理人→钢铁机器人→网络agent"。宇树科技73天过会</t>
+        </is>
+      </c>
+    </row>
+    <row r="88" ht="39.55" customHeight="1" s="139">
+      <c r="A88" s="138" t="inlineStr">
+        <is>
+          <t>什么时候进：2027冬开始逐步建。中长期赛道，不急</t>
+        </is>
+      </c>
+    </row>
+    <row r="89" ht="26.85" customHeight="1" s="139">
+      <c r="A89" s="138" t="inlineStr">
+        <is>
+          <t>风控：4%不大，判断错误损失可控</t>
+        </is>
+      </c>
+    </row>
+    <row r="90" ht="26.85" customHeight="1" s="139"/>
+    <row r="91" ht="39.55" customHeight="1" s="139">
+      <c r="A91" s="332" t="inlineStr">
+        <is>
+          <t>▶ 玻璃基板 3%</t>
+        </is>
+      </c>
+    </row>
+    <row r="92" ht="26.85" customHeight="1" s="139">
+      <c r="A92" s="138" t="inlineStr">
+        <is>
+          <t>为什么买：蒋宇飞"被严重低估即将爆发""两三年热点""业绩2027-H2释放""大规模2028"。两个爆发点：封装+存储</t>
+        </is>
+      </c>
+    </row>
+    <row r="93" ht="26.85" customHeight="1" s="139">
+      <c r="A93" s="138" t="inlineStr">
+        <is>
+          <t>什么时候进：2027年等业绩释放。蒋宇飞说"消息还在送验阶段"</t>
+        </is>
+      </c>
+    </row>
+    <row r="94" ht="39.55" customHeight="1" s="139">
+      <c r="A94" s="138" t="inlineStr">
+        <is>
+          <t>风控：3%观察仓，等消息确认</t>
+        </is>
+      </c>
+    </row>
+    <row r="95" ht="39.55" customHeight="1" s="139"/>
+    <row r="96" ht="15" customHeight="1" s="139">
+      <c r="A96" s="329" t="inlineStr">
+        <is>
+          <t>四、进钱节奏时间线</t>
+        </is>
+      </c>
+    </row>
+    <row r="97" ht="15" customHeight="1" s="139"/>
+    <row r="98" ht="18.65" customHeight="1" s="139">
+      <c r="A98" s="333" t="inlineStr">
+        <is>
+          <t>时间</t>
+        </is>
+      </c>
+      <c r="B98" s="333" t="inlineStr">
+        <is>
+          <t>进钱操作</t>
+        </is>
+      </c>
+      <c r="C98" s="333" t="inlineStr">
+        <is>
+          <t>持仓操作</t>
+        </is>
+      </c>
+      <c r="D98" s="333" t="inlineStr">
+        <is>
+          <t>清仓退出</t>
+        </is>
+      </c>
+      <c r="E98" s="333" t="inlineStr">
+        <is>
+          <t>可用现金</t>
+        </is>
+      </c>
+    </row>
+    <row r="99" ht="15" customHeight="1" s="139">
+      <c r="A99" s="138" t="inlineStr">
+        <is>
+          <t>现在-7月</t>
+        </is>
+      </c>
+      <c r="B99" s="138" t="inlineStr">
+        <is>
+          <t>MLCC3%建仓</t>
+        </is>
+      </c>
+      <c r="C99" s="138" t="inlineStr">
+        <is>
+          <t>芯片10%不动(虚P+3pp)</t>
+        </is>
+      </c>
+      <c r="D99" s="138" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E99" s="138" t="inlineStr">
+        <is>
+          <t>7%</t>
+        </is>
+      </c>
+    </row>
+    <row r="100" ht="15" customHeight="1" s="139">
+      <c r="A100" s="138" t="inlineStr">
+        <is>
+          <t>8-10月</t>
+        </is>
+      </c>
+      <c r="B100" s="138" t="inlineStr">
+        <is>
+          <t>MLCC持有</t>
+        </is>
+      </c>
+      <c r="C100" s="138" t="inlineStr">
+        <is>
+          <t>观察HBM信号</t>
+        </is>
+      </c>
+      <c r="D100" s="138" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E100" s="138" t="inlineStr">
+        <is>
+          <t>7%</t>
+        </is>
+      </c>
+    </row>
+    <row r="101" ht="26.85" customHeight="1" s="139">
+      <c r="A101" s="138" t="inlineStr">
+        <is>
+          <t>11月大跌</t>
+        </is>
+      </c>
+      <c r="B101" s="138" t="inlineStr">
+        <is>
+          <t>长电25%+通富20%大砸</t>
+        </is>
+      </c>
+      <c r="C101" s="138" t="inlineStr">
+        <is>
+          <t>MLCC清→HBM5%+堆叠先手5%</t>
+        </is>
+      </c>
+      <c r="D101" s="138" t="inlineStr">
+        <is>
+          <t>MLCC清</t>
+        </is>
+      </c>
+      <c r="E101" s="138" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="102" ht="15" customHeight="1" s="139">
+      <c r="A102" s="138" t="inlineStr">
+        <is>
+          <t>11月没大跌</t>
+        </is>
+      </c>
+      <c r="B102" s="138" t="inlineStr">
+        <is>
+          <t>堆叠先手5%(长电3+通富2)</t>
+        </is>
+      </c>
+      <c r="C102" s="138" t="inlineStr">
+        <is>
+          <t>MLCC清→等</t>
+        </is>
+      </c>
+      <c r="D102" s="138" t="inlineStr">
+        <is>
+          <t>MLCC清</t>
+        </is>
+      </c>
+      <c r="E102" s="138" t="inlineStr">
+        <is>
+          <t>0-2%</t>
+        </is>
+      </c>
+    </row>
+    <row r="103" ht="26.85" customHeight="1" s="139">
+      <c r="A103" s="138" t="inlineStr">
+        <is>
+          <t>2027-Q1</t>
+        </is>
+      </c>
+      <c r="B103" s="138" t="inlineStr">
+        <is>
+          <t>HBM持有</t>
+        </is>
+      </c>
+      <c r="C103" s="138" t="inlineStr">
+        <is>
+          <t>堆叠先手持有</t>
+        </is>
+      </c>
+      <c r="D103" s="138" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E103" s="138" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="104" ht="26.85" customHeight="1" s="139">
+      <c r="A104" s="138" t="inlineStr">
+        <is>
+          <t>2027-H2</t>
+        </is>
+      </c>
+    </row>
+    <row r="105" ht="26.85" customHeight="1" s="139">
+      <c r="A105" s="138" t="inlineStr">
+        <is>
+          <t>2027冬</t>
+        </is>
+      </c>
+    </row>
+    <row r="106" ht="26.85" customHeight="1" s="139"/>
+    <row r="107" ht="15" customHeight="1" s="139">
+      <c r="A107" s="329" t="inlineStr">
+        <is>
+          <t>⚡ 一句话：MLCC3%小试→Q4 HBM5%+堆叠先手5%→11月大跌长电25%+通富20%→2027堆叠躺赢</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="138" t="inlineStr">
+        <is>
+          <t>风控：45%重仓必须等15%+回调 | MLCC年底必清 | 蒋宇飞纪律"三成追七成等"</t>
+        </is>
+      </c>
+    </row>
+    <row r="109" ht="15" customHeight="1" s="139"/>
+    <row r="110" ht="26.85" customHeight="1" s="139"/>
+    <row r="111" ht="26.85" customHeight="1" s="139"/>
+    <row r="112" ht="26.85" customHeight="1" s="139">
+      <c r="A112" s="148" t="inlineStr">
+        <is>
+          <t>🔥 叙事主线（四条）</t>
+        </is>
+      </c>
+      <c r="B112" s="149" t="n"/>
+      <c r="C112" s="149" t="n"/>
+      <c r="D112" s="149" t="n"/>
+      <c r="E112" s="149" t="n"/>
+      <c r="F112" s="149" t="n"/>
+      <c r="G112" s="149" t="n"/>
+      <c r="H112" s="150" t="n"/>
+    </row>
+    <row r="113" ht="26.85" customHeight="1" s="139">
+      <c r="A113" s="325" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  辅助仓位: 玻璃基板5% | 算力出海5%</t>
+        </is>
+      </c>
+      <c r="B113" s="326" t="n"/>
+      <c r="C113" s="326" t="n"/>
+      <c r="D113" s="326" t="n"/>
+      <c r="E113" s="326" t="n"/>
+      <c r="F113" s="326" t="n"/>
+      <c r="G113" s="326" t="n"/>
+      <c r="H113" s="325" t="n"/>
+    </row>
+    <row r="114" ht="26.85" customHeight="1" s="139">
+      <c r="A114" s="325" t="n"/>
+      <c r="B114" s="326" t="n"/>
+      <c r="C114" s="326" t="n"/>
+      <c r="D114" s="326" t="n"/>
+      <c r="E114" s="326" t="n"/>
+      <c r="F114" s="326" t="n"/>
+      <c r="G114" s="326" t="n"/>
+      <c r="H114" s="325" t="n"/>
+    </row>
+    <row r="115" ht="26.85" customHeight="1" s="139">
+      <c r="A115" s="334" t="inlineStr">
+        <is>
+          <t>三、核心仓位汇总表</t>
+        </is>
+      </c>
+      <c r="B115" s="326" t="n"/>
+      <c r="C115" s="326" t="n"/>
+      <c r="D115" s="326" t="n"/>
+      <c r="E115" s="326" t="n"/>
+      <c r="F115" s="326" t="n"/>
+      <c r="G115" s="326" t="n"/>
+      <c r="H115" s="325" t="n"/>
+    </row>
+    <row r="116" ht="15" customHeight="1" s="139">
+      <c r="A116" s="138" t="inlineStr">
+        <is>
+          <t>持仓(50%): 养殖25%+芯片10%+电池5%+恒科2.5%+有色2.5%+稀金2.5%+银行1.5%</t>
+        </is>
+      </c>
+      <c r="B116" s="138" t="inlineStr">
         <is>
           <t>比特币独立叙事消亡 维持：资金吸附力排序 AI&gt;美股&gt;黄金&gt;比特币，比特币已成美股影子资产，AI落地后资金有明确去处，比特币价值持续被稀释</t>
         </is>
       </c>
     </row>
-    <row r="22" ht="16.5" customHeight="1" s="139">
-      <c r="A22" s="151" t="inlineStr">
-        <is>
-          <t>⚡ AI投资阶段切换指导原则（顶级置信度）</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="16.5" customHeight="1" s="139">
-      <c r="A23" s="152" t="inlineStr">
-        <is>
-          <t>AI前半程=投硬件（芯片/算力/堆叠封装）→ 已验证。AI后半程=布局软件/应用端 → 多个信源交叉确认，逻辑高度自洽。此为投资指导原则，不是事件，不作为P值调整依据，但影响赛道选择优先级。</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="16.5" customHeight="1" s="139">
-      <c r="A24" s="153" t="inlineStr">
-        <is>
-          <t>🔴🔴🔴 战略级虚P信号池 + 现金策略联动（2026-06-04）🔴🔴🔴</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="16.5" customHeight="1" s="139">
-      <c r="A25" s="154" t="inlineStr">
+    <row r="117">
+      <c r="A117" s="151" t="inlineStr">
+        <is>
+          <t>待重仓(等回调): 长电25%+通富20%=45% → 11月中期选举触发</t>
+        </is>
+      </c>
+    </row>
+    <row r="118" ht="15" customHeight="1" s="139">
+      <c r="A118" s="152" t="inlineStr">
+        <is>
+          <t>观察仓(机动18%): MLCC2%+HBM5%+堆叠先手5%+升腾/国产算力5%+玻璃基板1%</t>
+        </is>
+      </c>
+    </row>
+    <row r="119" ht="15" customHeight="1" s="139">
+      <c r="A119" s="153" t="inlineStr">
+        <is>
+          <t>锁定现金(13%): 等11月大事件→解锁后进长电/通富剩余仓位</t>
+        </is>
+      </c>
+    </row>
+    <row r="120" ht="26.85" customHeight="1" s="139">
+      <c r="A120" s="154" t="inlineStr">
         <is>
           <t>虚P规则：未落地→记虚P→不加实P→等落地转实P。此板块锁定大部分现金，与机会成本联动分析。</t>
         </is>
       </c>
     </row>
-    <row r="26" ht="15" customHeight="1" s="139">
-      <c r="A26" s="155" t="inlineStr">
-        <is>
-          <t>一、三源信号详情</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="16.5" customHeight="1" s="139">
-      <c r="A27" s="156" t="inlineStr">
-        <is>
-          <t>来源</t>
-        </is>
-      </c>
-      <c r="B27" s="156" t="inlineStr">
+    <row r="121" ht="26.85" customHeight="1" s="139">
+      <c r="A121" s="327" t="inlineStr">
+        <is>
+          <t>四、蒋宇飞"三层追七成等"落地</t>
+        </is>
+      </c>
+    </row>
+    <row r="122" ht="15" customHeight="1" s="139">
+      <c r="A122" s="156" t="inlineStr">
+        <is>
+          <t>30%追热点: 当前MLCC(蒋宇飞4月底预测已启动)+光模块(贯穿2026) | 这部分在持仓里</t>
+        </is>
+      </c>
+      <c r="B122" s="156" t="inlineStr">
         <is>
           <t>核心观点</t>
         </is>
       </c>
-      <c r="C27" s="156" t="inlineStr">
+      <c r="C122" s="156" t="inlineStr">
         <is>
           <t>与你策略契合</t>
         </is>
       </c>
-      <c r="D27" s="156" t="inlineStr">
+      <c r="D122" s="156" t="inlineStr">
         <is>
           <t>虚P方向</t>
         </is>
       </c>
-      <c r="E27" s="156" t="inlineStr">
+      <c r="E122" s="156" t="inlineStr">
         <is>
           <t>落地条件</t>
         </is>
       </c>
-      <c r="F27" s="156" t="inlineStr">
+      <c r="F122" s="156" t="inlineStr">
         <is>
           <t>状态</t>
         </is>
       </c>
-      <c r="G27" s="156" t="inlineStr">
+      <c r="G122" s="156" t="inlineStr">
         <is>
           <t>权重</t>
         </is>
       </c>
-      <c r="H27" s="156" t="inlineStr">
+      <c r="H122" s="156" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="28" ht="15" customHeight="1" s="139">
-      <c r="A28" s="157" t="inlineStr">
-        <is>
-          <t>达利欧
-Bloomberg 6/3</t>
-        </is>
-      </c>
-      <c r="B28" s="157" t="inlineStr">
+    <row r="123" ht="15" customHeight="1" s="139">
+      <c r="A123" s="157" t="inlineStr">
+        <is>
+          <t>70%等回调: 堆叠(长电+通富等11月大跌15%+大仓位进) | 升腾链等2027爆发</t>
+        </is>
+      </c>
+      <c r="B123" s="157" t="inlineStr">
         <is>
           <t>AI泡沫65-75%概率年底破
 "财富转现金=刺破泡沫"
@@ -2916,7 +3586,7 @@
 基建投入&gt;&gt;收入</t>
         </is>
       </c>
-      <c r="C28" s="158" t="inlineStr">
+      <c r="C123" s="158" t="inlineStr">
         <is>
           <t>完全契合
 等中期选举大跌
@@ -2924,1991 +3594,377 @@
 回调后大仓位进</t>
         </is>
       </c>
-      <c r="D28" s="157" t="inlineStr">
+      <c r="D123" s="157" t="inlineStr">
         <is>
           <t>芯片-2pp
 恒科-1pp
 (虚P)</t>
         </is>
       </c>
-      <c r="E28" s="157" t="inlineStr">
+      <c r="E123" s="157" t="inlineStr">
         <is>
           <t>七姐妹&gt;15%回调
 或破200日均线</t>
         </is>
       </c>
-      <c r="F28" s="159" t="inlineStr">
+      <c r="F123" s="159" t="inlineStr">
         <is>
           <t>未落地</t>
         </is>
       </c>
-      <c r="G28" s="160" t="inlineStr">
+      <c r="G123" s="160" t="inlineStr">
         <is>
           <t>极高
 5星</t>
         </is>
       </c>
-      <c r="H28" s="157" t="inlineStr">
+      <c r="H123" s="157" t="inlineStr">
         <is>
           <t>与你100%一致
 回调=买入机会</t>
         </is>
       </c>
     </row>
-    <row r="29" ht="15" customHeight="1" s="139">
-      <c r="A29" s="157" t="inlineStr">
+    <row r="124" ht="26.85" customHeight="1" s="139">
+      <c r="A124" s="157" t="inlineStr">
         <is>
           <t>李大霄
 金融界 6/4</t>
         </is>
       </c>
-      <c r="B29" s="157" t="inlineStr">
-        <is>
-          <t>美股窄牛宽熊
-仅20只创新高
-CAPE40倍
-权重极度集中
-IPO抽血</t>
-        </is>
-      </c>
-      <c r="C29" s="158" t="inlineStr">
-        <is>
-          <t>高度契合
-确认美股风险
-现金策略正确</t>
-        </is>
-      </c>
-      <c r="D29" s="157" t="inlineStr">
-        <is>
-          <t>恒科-2pp
-芯片-1pp
-(虚P)</t>
-        </is>
-      </c>
-      <c r="E29" s="157" t="inlineStr">
-        <is>
-          <t>纳指破200日均线
-多数成分股下跌</t>
-        </is>
-      </c>
-      <c r="F29" s="159" t="inlineStr">
-        <is>
-          <t>未落地</t>
-        </is>
-      </c>
-      <c r="G29" s="157" t="inlineStr">
-        <is>
-          <t>中高
-3星</t>
-        </is>
-      </c>
-      <c r="H29" s="157" t="inlineStr">
-        <is>
-          <t>数据靠谱
-结论偏激进</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="15" customHeight="1" s="139">
-      <c r="A30" s="157" t="inlineStr">
-        <is>
-          <t>知乎专栏
-6/4</t>
-        </is>
-      </c>
-      <c r="B30" s="149" t="n"/>
-      <c r="C30" s="149" t="n"/>
-      <c r="D30" s="149" t="n"/>
-      <c r="E30" s="149" t="n"/>
-      <c r="F30" s="149" t="n"/>
-      <c r="G30" s="149" t="n"/>
-      <c r="H30" s="150" t="n"/>
-    </row>
-    <row r="31" ht="15" customHeight="1" s="139"/>
-    <row r="32" ht="15" customHeight="1" s="139">
-      <c r="A32" s="155" t="inlineStr">
-        <is>
-          <t>二、三源互锁验证</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="16.5" customHeight="1" s="139">
-      <c r="A33" s="161" t="inlineStr">
-        <is>
-          <t>互锁组合</t>
-        </is>
-      </c>
-      <c r="B33" s="161" t="inlineStr">
+      <c r="B124" s="149" t="n"/>
+      <c r="C124" s="149" t="n"/>
+      <c r="D124" s="149" t="n"/>
+      <c r="E124" s="149" t="n"/>
+      <c r="F124" s="149" t="n"/>
+      <c r="G124" s="149" t="n"/>
+      <c r="H124" s="150" t="n"/>
+    </row>
+    <row r="125" ht="15" customHeight="1" s="139">
+      <c r="A125" s="328" t="inlineStr">
+        <is>
+          <t>五、关键时间点操作清单</t>
+        </is>
+      </c>
+      <c r="B125" s="149" t="n"/>
+      <c r="C125" s="149" t="n"/>
+      <c r="D125" s="149" t="n"/>
+      <c r="E125" s="149" t="n"/>
+      <c r="F125" s="149" t="n"/>
+      <c r="G125" s="149" t="n"/>
+      <c r="H125" s="150" t="n"/>
+    </row>
+    <row r="126">
+      <c r="A126" s="138" t="inlineStr">
+        <is>
+          <t>6-7月: 长鑫上市→观察存储/芯片反应 | 芯片10%不动 | MLCC2%观察仓可建</t>
+        </is>
+      </c>
+    </row>
+    <row r="127" ht="15" customHeight="1" s="139">
+      <c r="A127" s="155" t="inlineStr">
+        <is>
+          <t>8-10月: MLCC肉最甜→持到11月 | 观察HBM启动信号</t>
+        </is>
+      </c>
+    </row>
+    <row r="128" ht="15" customHeight="1" s="139">
+      <c r="A128" s="161" t="inlineStr">
+        <is>
+          <t>11-12月: MLCC清仓→资金转HBM5%+堆叠先手5% | 非农黑五→恒科注意</t>
+        </is>
+      </c>
+      <c r="B128" s="161" t="inlineStr">
         <is>
           <t>关系</t>
         </is>
       </c>
-      <c r="C33" s="161" t="inlineStr">
+      <c r="C128" s="161" t="inlineStr">
         <is>
           <t>分析</t>
         </is>
       </c>
-      <c r="D33" s="161" t="inlineStr">
+      <c r="D128" s="161" t="inlineStr">
         <is>
           <t>信号强度</t>
         </is>
       </c>
     </row>
-    <row r="34" ht="16.5" customHeight="1" s="139">
-      <c r="A34" s="162" t="inlineStr">
-        <is>
-          <t>达利欧×李大霄</t>
-        </is>
-      </c>
-      <c r="B34" s="163" t="inlineStr">
+    <row r="129" ht="26.85" customHeight="1" s="139">
+      <c r="A129" s="162" t="inlineStr">
+        <is>
+          <t>2027-Q1: HBM热潮→持有 | 堆叠先手继续观察</t>
+        </is>
+      </c>
+      <c r="B129" s="163" t="inlineStr">
         <is>
           <t>✅强印证</t>
         </is>
       </c>
-      <c r="C34" s="157" t="inlineStr">
+      <c r="C129" s="157" t="inlineStr">
         <is>
           <t>AI泡沫+窄牛宽熊=同一现象两角度</t>
         </is>
       </c>
-      <c r="D34" s="157" t="inlineStr">
+      <c r="D129" s="157" t="inlineStr">
         <is>
           <t>🔴强信号</t>
         </is>
       </c>
     </row>
-    <row r="35" ht="16.5" customHeight="1" s="139">
-      <c r="A35" s="162" t="inlineStr">
-        <is>
-          <t>达利欧×知乎</t>
-        </is>
-      </c>
-      <c r="B35" s="164" t="inlineStr">
+    <row r="130" ht="15" customHeight="1" s="139">
+      <c r="A130" s="162" t="inlineStr">
+        <is>
+          <t>2027-H2: 堆叠大放光芒→长电25%+通富20%大仓位确认 | 升腾链10% | CPU5%</t>
+        </is>
+      </c>
+      <c r="B130" s="164" t="inlineStr">
         <is>
           <t>⚠️部分矛盾</t>
         </is>
       </c>
-      <c r="C35" s="157" t="inlineStr">
+      <c r="C130" s="157" t="inlineStr">
         <is>
           <t>达看流动性vs知乎看估值</t>
         </is>
       </c>
-      <c r="D35" s="157" t="inlineStr">
+      <c r="D130" s="157" t="inlineStr">
         <is>
           <t>🟡中性</t>
         </is>
       </c>
     </row>
-    <row r="36" ht="16.5" customHeight="1" s="139">
-      <c r="A36" s="162" t="inlineStr">
+    <row r="131" ht="15" customHeight="1" s="139">
+      <c r="A131" s="162" t="inlineStr">
         <is>
           <t>三源共识</t>
         </is>
       </c>
-      <c r="B36" s="149" t="n"/>
-      <c r="C36" s="149" t="n"/>
-      <c r="D36" s="149" t="n"/>
-      <c r="E36" s="149" t="n"/>
-      <c r="F36" s="149" t="n"/>
-      <c r="G36" s="149" t="n"/>
-      <c r="H36" s="150" t="n"/>
-    </row>
-    <row r="37" ht="16.5" customHeight="1" s="139">
-      <c r="A37" s="138" t="n"/>
-    </row>
-    <row r="38" ht="16.5" customHeight="1" s="139">
-      <c r="A38" s="165" t="inlineStr">
+      <c r="B131" s="149" t="n"/>
+      <c r="C131" s="149" t="n"/>
+      <c r="D131" s="149" t="n"/>
+      <c r="E131" s="149" t="n"/>
+      <c r="F131" s="149" t="n"/>
+      <c r="G131" s="149" t="n"/>
+      <c r="H131" s="150" t="n"/>
+    </row>
+    <row r="132" ht="15" customHeight="1" s="139">
+      <c r="A132" s="138" t="n"/>
+    </row>
+    <row r="133" ht="15" customHeight="1" s="139">
+      <c r="A133" s="165" t="inlineStr">
         <is>
           <t>三、现金策略联动（锁定大部分现金储备）</t>
         </is>
       </c>
     </row>
-    <row r="39" ht="16.5" customHeight="1" s="139">
-      <c r="A39" s="154" t="inlineStr">
+    <row r="134" ht="26.85" customHeight="1" s="139">
+      <c r="A134" s="154" t="inlineStr">
         <is>
           <t>三源联动→达利欧65-75%概率年底AI回调+中期选举历史跌一波→锁定大部分现金→等11月回调入场</t>
         </is>
       </c>
     </row>
-    <row r="40" ht="16.5" customHeight="1" s="139">
-      <c r="A40" s="161" t="inlineStr">
+    <row r="135" ht="15" customHeight="1" s="139">
+      <c r="A135" s="161" t="inlineStr">
         <is>
           <t>维度</t>
         </is>
       </c>
-      <c r="B40" s="161" t="inlineStr">
+      <c r="B135" s="161" t="inlineStr">
         <is>
           <t>内容</t>
         </is>
       </c>
-      <c r="C40" s="161" t="inlineStr">
+      <c r="C135" s="161" t="inlineStr">
         <is>
           <t>影响</t>
         </is>
       </c>
     </row>
-    <row r="41" ht="16.5" customHeight="1" s="139">
-      <c r="A41" s="157" t="inlineStr">
+    <row r="136">
+      <c r="A136" s="157" t="inlineStr">
         <is>
           <t>现金锁定</t>
         </is>
       </c>
-      <c r="B41" s="157" t="inlineStr">
-        <is>
-          <t>大部分现金(60-70%)锁定等待</t>
-        </is>
-      </c>
-      <c r="C41" s="157" t="inlineStr">
-        <is>
-          <t>→当前可投资金大幅减少</t>
-        </is>
-      </c>
-    </row>
-    <row r="42" ht="16.5" customHeight="1" s="139">
-      <c r="A42" s="157" t="inlineStr">
+      <c r="B136" s="149" t="n"/>
+      <c r="C136" s="149" t="n"/>
+      <c r="D136" s="149" t="n"/>
+      <c r="E136" s="149" t="n"/>
+      <c r="F136" s="149" t="n"/>
+      <c r="G136" s="149" t="n"/>
+      <c r="H136" s="150" t="n"/>
+    </row>
+    <row r="137" ht="15" customHeight="1" s="139">
+      <c r="A137" s="157" t="inlineStr">
         <is>
           <t>等待窗口</t>
         </is>
       </c>
-      <c r="B42" s="157" t="inlineStr">
+      <c r="B137" s="157" t="inlineStr">
         <is>
           <t>2026年11月中期选举前后</t>
         </is>
       </c>
-      <c r="C42" s="157" t="inlineStr">
+      <c r="C137" s="157" t="inlineStr">
         <is>
           <t>→约5个月等待期</t>
         </is>
       </c>
     </row>
-    <row r="43" ht="16.5" customHeight="1" s="139">
-      <c r="A43" s="157" t="inlineStr">
+    <row r="138" ht="26.85" customHeight="1" s="139">
+      <c r="A138" s="157" t="inlineStr">
         <is>
           <t>触发条件</t>
         </is>
       </c>
-      <c r="B43" s="157" t="inlineStr">
+      <c r="B138" s="157" t="inlineStr">
         <is>
           <t>美股跌一波+AI回调&gt;15%</t>
         </is>
       </c>
-      <c r="C43" s="157" t="inlineStr">
+      <c r="C138" s="157" t="inlineStr">
         <is>
           <t>→达利欧65-75%概率事件</t>
         </is>
       </c>
     </row>
-    <row r="44" ht="16.5" customHeight="1" s="139">
-      <c r="A44" s="157" t="inlineStr">
+    <row r="139" ht="15" customHeight="1" s="139">
+      <c r="A139" s="157" t="inlineStr">
         <is>
           <t>入场标的</t>
         </is>
       </c>
-      <c r="B44" s="157" t="inlineStr">
+      <c r="B139" s="157" t="inlineStr">
         <is>
           <t>堆叠：长电科技+通富微电</t>
         </is>
       </c>
-      <c r="C44" s="157" t="inlineStr">
+      <c r="C139" s="157" t="inlineStr">
         <is>
           <t>→国内确定性不受美股影响</t>
         </is>
       </c>
     </row>
-    <row r="45" ht="16.5" customHeight="1" s="139">
-      <c r="A45" s="157" t="inlineStr">
+    <row r="140" ht="26.85" customHeight="1" s="139">
+      <c r="A140" s="157" t="inlineStr">
         <is>
           <t>机会成本</t>
         </is>
       </c>
-      <c r="B45" s="157" t="inlineStr">
+      <c r="B140" s="157" t="inlineStr">
         <is>
           <t>持有现金5个月vs错过短期行情</t>
         </is>
       </c>
-      <c r="C45" s="157" t="inlineStr">
+      <c r="C140" s="157" t="inlineStr">
         <is>
           <t>→见下方机会成本联动</t>
         </is>
       </c>
     </row>
-    <row r="46" ht="16.5" customHeight="1" s="139">
-      <c r="A46" s="157" t="inlineStr">
+    <row r="141" ht="26.85" customHeight="1" s="139">
+      <c r="A141" s="157" t="inlineStr">
         <is>
           <t>下行保护</t>
         </is>
       </c>
-      <c r="B46" s="149" t="n"/>
-      <c r="C46" s="149" t="n"/>
-      <c r="D46" s="149" t="n"/>
-      <c r="E46" s="149" t="n"/>
-      <c r="F46" s="149" t="n"/>
-      <c r="G46" s="149" t="n"/>
-      <c r="H46" s="150" t="n"/>
-    </row>
-    <row r="47" ht="16.5" customHeight="1" s="139"/>
-    <row r="48" ht="16.5" customHeight="1" s="139">
-      <c r="A48" s="165" t="inlineStr">
+      <c r="B141" s="149" t="n"/>
+      <c r="C141" s="149" t="n"/>
+      <c r="D141" s="149" t="n"/>
+      <c r="E141" s="149" t="n"/>
+      <c r="F141" s="149" t="n"/>
+      <c r="G141" s="149" t="n"/>
+      <c r="H141" s="150" t="n"/>
+    </row>
+    <row r="142" ht="39.55" customHeight="1" s="139"/>
+    <row r="143">
+      <c r="A143" s="165" t="inlineStr">
         <is>
           <t>四、机会成本联动分析（现金锁定vs其他选项）</t>
         </is>
       </c>
     </row>
-    <row r="49" ht="16.5" customHeight="1" s="139">
-      <c r="A49" s="161" t="inlineStr">
+    <row r="144" ht="17.35" customHeight="1" s="139">
+      <c r="A144" s="161" t="inlineStr">
         <is>
           <t>选项</t>
         </is>
       </c>
-      <c r="B49" s="161" t="inlineStr">
+      <c r="B144" s="161" t="inlineStr">
         <is>
           <t>P值</t>
         </is>
       </c>
-      <c r="C49" s="161" t="inlineStr">
+      <c r="C144" s="161" t="inlineStr">
         <is>
           <t>盈亏比</t>
         </is>
       </c>
-      <c r="D49" s="161" t="inlineStr">
+      <c r="D144" s="161" t="inlineStr">
         <is>
           <t>Score</t>
         </is>
       </c>
-      <c r="E49" s="161" t="inlineStr">
+      <c r="E144" s="161" t="inlineStr">
         <is>
           <t>现金锁定影响</t>
         </is>
       </c>
-      <c r="F49" s="161" t="inlineStr">
+      <c r="F144" s="161" t="inlineStr">
         <is>
           <t>建议</t>
         </is>
       </c>
-      <c r="G49" s="161" t="inlineStr">
+      <c r="G144" s="161" t="inlineStr">
         <is>
           <t>判断</t>
         </is>
       </c>
     </row>
-    <row r="50" ht="15" customHeight="1" s="139">
-      <c r="A50" s="157" t="inlineStr">
+    <row r="145" ht="17.15" customHeight="1" s="139">
+      <c r="A145" s="157" t="inlineStr">
         <is>
           <t>长电科技</t>
         </is>
       </c>
-      <c r="B50" s="157" t="inlineStr">
+      <c r="B145" s="157" t="inlineStr">
         <is>
           <t>75%</t>
         </is>
       </c>
-      <c r="C50" s="157" t="inlineStr">
+      <c r="C145" s="157" t="inlineStr">
         <is>
           <t>4.5:1</t>
         </is>
       </c>
-      <c r="D50" s="157" t="inlineStr">
+      <c r="D145" s="157" t="inlineStr">
         <is>
           <t>3.375</t>
         </is>
       </c>
-      <c r="E50" s="157" t="inlineStr">
+      <c r="E145" s="157" t="inlineStr">
         <is>
           <t>等回调大仓位
 现金锁定中</t>
         </is>
       </c>
-      <c r="F50" s="157" t="inlineStr">
+      <c r="F145" s="157" t="inlineStr">
         <is>
           <t>暂不动等11月</t>
         </is>
       </c>
-      <c r="G50" s="160" t="inlineStr">
+      <c r="G145" s="160" t="inlineStr">
         <is>
           <t>🔴最高优先</t>
         </is>
       </c>
     </row>
-    <row r="51" ht="15" customHeight="1" s="139">
-      <c r="A51" s="157" t="inlineStr">
+    <row r="146" ht="17.15" customHeight="1" s="139">
+      <c r="A146" s="157" t="inlineStr">
         <is>
           <t>通富微电</t>
-        </is>
-      </c>
-      <c r="B51" s="157" t="inlineStr">
-        <is>
-          <t>75%</t>
-        </is>
-      </c>
-      <c r="C51" s="157" t="inlineStr">
-        <is>
-          <t>4.0:1</t>
-        </is>
-      </c>
-      <c r="D51" s="157" t="inlineStr">
-        <is>
-          <t>3.000</t>
-        </is>
-      </c>
-      <c r="E51" s="157" t="inlineStr">
-        <is>
-          <t>等回调大仓位
-现金锁定中</t>
-        </is>
-      </c>
-      <c r="F51" s="157" t="inlineStr">
-        <is>
-          <t>暂不动等11月</t>
-        </is>
-      </c>
-      <c r="G51" s="160" t="inlineStr">
-        <is>
-          <t>🔴最高优先</t>
-        </is>
-      </c>
-    </row>
-    <row r="52" ht="77.59999999999999" customHeight="1" s="139">
-      <c r="A52" s="157" t="inlineStr">
-        <is>
-          <t>养殖</t>
-        </is>
-      </c>
-      <c r="B52" s="157" t="inlineStr">
-        <is>
-          <t>70%</t>
-        </is>
-      </c>
-      <c r="C52" s="157" t="inlineStr">
-        <is>
-          <t>2.0:1</t>
-        </is>
-      </c>
-      <c r="D52" s="157" t="inlineStr">
-        <is>
-          <t>1.400</t>
-        </is>
-      </c>
-      <c r="E52" s="157" t="inlineStr">
-        <is>
-          <t>已持仓不需现金 | 6/5 芳姐：低价抄底母猪，行业融资枯竭，等待母猪血流成河才是最佳买点</t>
-        </is>
-      </c>
-      <c r="F52" s="157" t="inlineStr">
-        <is>
-          <t>继续持有</t>
-        </is>
-      </c>
-      <c r="G52" s="158" t="inlineStr">
-        <is>
-          <t>✅已配置</t>
-        </is>
-      </c>
-    </row>
-    <row r="53" ht="17.15" customHeight="1" s="139">
-      <c r="A53" s="157" t="inlineStr">
-        <is>
-          <t>电池</t>
-        </is>
-      </c>
-      <c r="B53" s="157" t="inlineStr">
-        <is>
-          <t>65%</t>
-        </is>
-      </c>
-      <c r="C53" s="157" t="inlineStr">
-        <is>
-          <t>2.0:1</t>
-        </is>
-      </c>
-      <c r="D53" s="157" t="inlineStr">
-        <is>
-          <t>1.300</t>
-        </is>
-      </c>
-      <c r="E53" s="157" t="inlineStr">
-        <is>
-          <t>已持仓不需现金 | 6/5 闻号说经济：厄尔尼诺80%概率+AI用电爆发→电力/能源受益</t>
-        </is>
-      </c>
-      <c r="F53" s="157" t="inlineStr">
-        <is>
-          <t>继续持有</t>
-        </is>
-      </c>
-      <c r="G53" s="158" t="inlineStr">
-        <is>
-          <t>✅已配置</t>
-        </is>
-      </c>
-    </row>
-    <row r="54" ht="26.85" customHeight="1" s="139">
-      <c r="A54" s="157" t="inlineStr">
-        <is>
-          <t>核电</t>
-        </is>
-      </c>
-      <c r="B54" s="157" t="inlineStr">
-        <is>
-          <t>52%</t>
-        </is>
-      </c>
-      <c r="C54" s="157" t="inlineStr">
-        <is>
-          <t>1.5:1</t>
-        </is>
-      </c>
-      <c r="D54" s="157" t="inlineStr">
-        <is>
-          <t>0.780</t>
-        </is>
-      </c>
-      <c r="E54" s="157" t="inlineStr">
-        <is>
-          <t>10年维度
-小仓试水可行</t>
-        </is>
-      </c>
-      <c r="F54" s="157" t="inlineStr">
-        <is>
-          <t>不影响现金策略</t>
-        </is>
-      </c>
-      <c r="G54" s="166" t="inlineStr">
-        <is>
-          <t>🟡长期观察</t>
-        </is>
-      </c>
-    </row>
-    <row r="55" ht="29.85" customHeight="1" s="139">
-      <c r="A55" s="157" t="inlineStr">
-        <is>
-          <t>存储</t>
-        </is>
-      </c>
-      <c r="B55" s="157" t="inlineStr">
-        <is>
-          <t>55%</t>
-        </is>
-      </c>
-      <c r="C55" s="157" t="inlineStr">
-        <is>
-          <t>1.0:1</t>
-        </is>
-      </c>
-      <c r="D55" s="157" t="inlineStr">
-        <is>
-          <t>0.550</t>
-        </is>
-      </c>
-      <c r="E55" s="157" t="inlineStr">
-        <is>
-          <t>已降级</t>
-        </is>
-      </c>
-      <c r="F55" s="157" t="inlineStr">
-        <is>
-          <t>不动</t>
-        </is>
-      </c>
-      <c r="G55" s="160" t="inlineStr">
-        <is>
-          <t>❌已降级</t>
-        </is>
-      </c>
-    </row>
-    <row r="56" ht="29.85" customHeight="1" s="139">
-      <c r="A56" s="157" t="inlineStr">
-        <is>
-          <t>纯现金5月</t>
-        </is>
-      </c>
-      <c r="B56" s="149" t="n"/>
-      <c r="C56" s="149" t="n"/>
-      <c r="D56" s="149" t="n"/>
-      <c r="E56" s="149" t="n"/>
-      <c r="F56" s="149" t="n"/>
-      <c r="G56" s="149" t="n"/>
-      <c r="H56" s="150" t="n"/>
-    </row>
-    <row r="57" ht="15" customHeight="1" s="139">
-      <c r="A57" s="147" t="inlineStr">
-        <is>
-          <t>AI硬件确定性(付鹏) → 内存=AI核心瓶颈(4信源互锁) → 国产替代加速 → 稀土断供日本 → 芯片/存储/HBM长期利好 | 短期被利率↑/地缘↑压制</t>
-        </is>
-      </c>
-    </row>
-    <row r="58" ht="15" customHeight="1" s="139">
-      <c r="A58" s="167" t="inlineStr">
-        <is>
-          <t>五、虚P→实P转换条件 &amp; 操作触发</t>
-        </is>
-      </c>
-      <c r="B58" s="168" t="n"/>
-      <c r="C58" s="168" t="n"/>
-      <c r="D58" s="168" t="n"/>
-      <c r="E58" s="168" t="n"/>
-      <c r="F58" s="168" t="n"/>
-      <c r="G58" s="168" t="n"/>
-      <c r="H58" s="169" t="n"/>
-    </row>
-    <row r="59" ht="58.2" customHeight="1" s="139">
-      <c r="A59" s="156" t="inlineStr">
-        <is>
-          <t>条件</t>
-        </is>
-      </c>
-      <c r="B59" s="161" t="inlineStr">
-        <is>
-          <t>触发信号</t>
-        </is>
-      </c>
-      <c r="C59" s="156" t="inlineStr">
-        <is>
-          <t>影响</t>
-        </is>
-      </c>
-      <c r="D59" s="156" t="inlineStr">
-        <is>
-          <t>操作</t>
-        </is>
-      </c>
-      <c r="E59" s="147" t="inlineStr">
-        <is>
-          <t>2026-05-30 宋鸿兵：海峡封锁→能源成本飙升</t>
-        </is>
-      </c>
-      <c r="F59" s="147" t="inlineStr">
-        <is>
-          <t>2026-05-30 岩松：存储1-2年产能饱和</t>
-        </is>
-      </c>
-      <c r="G59" s="147" t="inlineStr">
-        <is>
-          <t>2026-05-30 宋鸿兵：30年美债破5%双红线</t>
-        </is>
-      </c>
-    </row>
-    <row r="60" ht="173.1" customHeight="1" s="139">
-      <c r="A60" s="170" t="inlineStr">
-        <is>
-          <t>达利欧落地</t>
-        </is>
-      </c>
-      <c r="B60" s="157" t="inlineStr">
-        <is>
-          <t>七姐妹&gt;15%回调或破200日均线</t>
-        </is>
-      </c>
-      <c r="C60" s="157" t="inlineStr">
-        <is>
-          <t>芯片/恒科虚P转实P</t>
-        </is>
-      </c>
-      <c r="D60" s="157" t="inlineStr">
-        <is>
-          <t>现金解锁→大仓位进堆叠</t>
-        </is>
-      </c>
-    </row>
-    <row r="61" ht="15" customHeight="1" s="139">
-      <c r="A61" s="166" t="inlineStr">
-        <is>
-          <t>李大霄落地</t>
-        </is>
-      </c>
-      <c r="B61" s="157" t="inlineStr">
-        <is>
-          <t>多数成分股下跌+指数拐头</t>
-        </is>
-      </c>
-      <c r="C61" s="157" t="inlineStr">
-        <is>
-          <t>恒科/芯片虚P转实P</t>
-        </is>
-      </c>
-      <c r="D61" s="157" t="inlineStr">
-        <is>
-          <t>确认系统性风险→入场</t>
-        </is>
-      </c>
-    </row>
-    <row r="62" ht="15" customHeight="1" s="139">
-      <c r="A62" s="171" t="inlineStr">
-        <is>
-          <t>中期选举</t>
-        </is>
-      </c>
-      <c r="B62" s="171" t="inlineStr">
-        <is>
-          <t>11月美股跌一波</t>
-        </is>
-      </c>
-      <c r="C62" s="171" t="inlineStr">
-        <is>
-          <t>你的策略触发</t>
-        </is>
-      </c>
-      <c r="D62" s="171" t="inlineStr">
-        <is>
-          <t>现金→长电+通富</t>
-        </is>
-      </c>
-      <c r="E62" s="156" t="inlineStr">
-        <is>
-          <t>落地条件</t>
-        </is>
-      </c>
-      <c r="F62" s="156" t="inlineStr">
-        <is>
-          <t>状态</t>
-        </is>
-      </c>
-      <c r="G62" s="156" t="inlineStr">
-        <is>
-          <t>权重</t>
-        </is>
-      </c>
-      <c r="H62" s="156" t="inlineStr">
-        <is>
-          <t>备注</t>
-        </is>
-      </c>
-    </row>
-    <row r="63" ht="48.5" customHeight="1" s="139">
-      <c r="A63" s="157" t="inlineStr">
-        <is>
-          <t>堆叠独立</t>
-        </is>
-      </c>
-      <c r="B63" s="149" t="n"/>
-      <c r="C63" s="149" t="n"/>
-      <c r="D63" s="149" t="n"/>
-      <c r="E63" s="149" t="n"/>
-      <c r="F63" s="149" t="n"/>
-      <c r="G63" s="149" t="n"/>
-      <c r="H63" s="150" t="n"/>
-    </row>
-    <row r="64" ht="48.5" customHeight="1" s="139">
-      <c r="A64" s="157" t="inlineStr">
-        <is>
-          <t>李大霄
-金融界 6/4</t>
-        </is>
-      </c>
-      <c r="B64" s="157" t="inlineStr">
-        <is>
-          <t>美股窄牛宽熊
-仅20只创新高
-CAPE40倍→泡沫</t>
-        </is>
-      </c>
-      <c r="C64" s="158" t="inlineStr">
-        <is>
-          <t>🟢高度契合
-确认美股风险
-现金策略正确</t>
-        </is>
-      </c>
-      <c r="D64" s="157" t="inlineStr">
-        <is>
-          <t>美股全市场↓
-港股连带承压</t>
-        </is>
-      </c>
-      <c r="E64" s="157" t="inlineStr">
-        <is>
-          <t>纳指破200日均线
-或多数成分股下跌</t>
-        </is>
-      </c>
-      <c r="F64" s="159" t="inlineStr">
-        <is>
-          <t>⏳未落地
-(虚P状态)</t>
-        </is>
-      </c>
-      <c r="G64" s="157" t="inlineStr">
-        <is>
-          <t>⭐⭐⭐
-中高</t>
-        </is>
-      </c>
-      <c r="H64" s="157" t="inlineStr">
-        <is>
-          <t>6/4三源联动:
-恒科-2pp
-芯片-1pp
-→已记虚P
-未转实P</t>
-        </is>
-      </c>
-    </row>
-    <row r="65" ht="64.15000000000001" customHeight="1" s="139">
-      <c r="A65" s="172" t="inlineStr">
-        <is>
-          <t>⚡ 核心结论：三源联动确认AI泡沫风险+你的中期选举策略正确。大部分现金锁定等11月回调→大仓位进长电/通富。机会成本可接受（不对称博弈，下有保底）。虚P已记，等落地转实P。</t>
-        </is>
-      </c>
-      <c r="B65" s="168" t="n"/>
-      <c r="C65" s="168" t="n"/>
-      <c r="D65" s="168" t="n"/>
-      <c r="E65" s="168" t="n"/>
-      <c r="F65" s="168" t="n"/>
-      <c r="G65" s="168" t="n"/>
-      <c r="H65" s="169" t="n"/>
-    </row>
-    <row r="66">
-      <c r="A66" s="138" t="inlineStr">
-        <is>
-          <t>────────────────────────────────────────────────────────────</t>
-        </is>
-      </c>
-    </row>
-    <row r="67" ht="17.15" customHeight="1" s="139">
-      <c r="A67" s="173" t="inlineStr">
-        <is>
-          <t>🔗 三源互锁验证</t>
-        </is>
-      </c>
-    </row>
-    <row r="68" ht="48.5" customHeight="1" s="139">
-      <c r="A68" s="140" t="inlineStr">
-        <is>
-          <t>达利欧 × 李大霄</t>
-        </is>
-      </c>
-      <c r="C68" s="174" t="inlineStr">
-        <is>
-          <t>✅ 强印证</t>
-        </is>
-      </c>
-      <c r="E68" s="175" t="inlineStr">
-        <is>
-          <t>AI泡沫+窄牛宽熊=同一现象两角度，互相确认</t>
-        </is>
-      </c>
-    </row>
-    <row r="69" ht="32.8" customHeight="1" s="139">
-      <c r="A69" s="140" t="inlineStr">
-        <is>
-          <t>达利欧 × 知乎</t>
-        </is>
-      </c>
-      <c r="C69" s="176" t="inlineStr">
-        <is>
-          <t>⚠️ 部分矛盾</t>
-        </is>
-      </c>
-      <c r="E69" s="175" t="inlineStr">
-        <is>
-          <t>达利欧看流动性(泡沫将破) vs 知乎看估值(PE中值安全)</t>
-        </is>
-      </c>
-    </row>
-    <row r="70" ht="48.5" customHeight="1" s="139">
-      <c r="A70" s="140" t="inlineStr">
-        <is>
-          <t>三源共识</t>
-        </is>
-      </c>
-      <c r="C70" s="177" t="inlineStr">
-        <is>
-          <t>🔴 核心共识</t>
-        </is>
-      </c>
-      <c r="E70" s="175" t="inlineStr">
-        <is>
-          <t>AI龙头估值偏高+市场极度集中+中小盘已熊 → 短期风险&gt;机会</t>
-        </is>
-      </c>
-    </row>
-    <row r="71" ht="32.8" customHeight="1" s="139"/>
-    <row r="72">
-      <c r="A72" s="165" t="inlineStr">
-        <is>
-          <t>🎯 结论（虚P→实P转换条件）</t>
-        </is>
-      </c>
-    </row>
-    <row r="73" ht="121.6" customHeight="1" s="139">
-      <c r="A73" s="140" t="inlineStr">
-        <is>
-          <t>① 达利欧信号落地条件</t>
-        </is>
-      </c>
-      <c r="C73" s="175" t="inlineStr">
-        <is>
-          <t>纳指七姐妹出现&gt;15%回调 或 纳指破200日均线</t>
-        </is>
-      </c>
-      <c r="E73" s="178" t="inlineStr">
-        <is>
-          <t>→ 芯片/恒科虚P转实P → 确认减仓信号</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" s="140" t="inlineStr">
-        <is>
-          <t>② 李大霄信号落地条件</t>
-        </is>
-      </c>
-      <c r="C74" s="175" t="inlineStr">
-        <is>
-          <t>纳指多数成分股连续下跌+指数拐头</t>
-        </is>
-      </c>
-      <c r="E74" s="178" t="inlineStr">
-        <is>
-          <t>→ 恒科/芯片虚P转实P → 确认美股系统性风险</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" s="140" t="inlineStr">
-        <is>
-          <t>③ 你的策略触发条件</t>
-        </is>
-      </c>
-      <c r="C75" s="175" t="inlineStr">
-        <is>
-          <t>中期选举(11月)美股跌一波 + AI回调&gt;15%</t>
-        </is>
-      </c>
-      <c r="E75" s="178" t="inlineStr">
-        <is>
-          <t>→ 现金入场 → 大仓位进堆叠/先进封装</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" s="140" t="inlineStr">
-        <is>
-          <t>④ 堆叠赛道独立性</t>
-        </is>
-      </c>
-      <c r="C76" s="175" t="inlineStr">
-        <is>
-          <t>国内产业确定性，三源均未提及国内封测</t>
-        </is>
-      </c>
-      <c r="E76" s="178" t="inlineStr">
-        <is>
-          <t>→ 不受美股泡沫直接影响 → 等回调后优先配置</t>
-        </is>
-      </c>
-    </row>
-    <row r="77" ht="15" customHeight="1" s="139"/>
-    <row r="78">
-      <c r="A78" s="179" t="inlineStr">
-        <is>
-          <t>⚡ 一句话：三源确认AI泡沫风险+你的中期选举策略正确。虚P已记，等落地转实P。现金为王，堆叠赛道等回调后大仓位进。</t>
-        </is>
-      </c>
-    </row>
-    <row r="79" ht="39.55" customHeight="1" s="139"/>
-    <row r="80" ht="39.55" customHeight="1" s="139"/>
-    <row r="81" ht="52.2" customHeight="1" s="139"/>
-    <row r="82" ht="52.2" customHeight="1" s="139">
-      <c r="A82" s="147" t="inlineStr">
-        <is>
-          <t>🤖 人形机器人半年事件链</t>
-        </is>
-      </c>
-    </row>
-    <row r="83" ht="64.90000000000001" customHeight="1" s="139"/>
-    <row r="84" ht="15" customHeight="1" s="139">
-      <c r="A84" s="147" t="inlineStr">
-        <is>
-          <t>2026-03-23 机器人ETF暴跌-4.1%至0.909：市场恐慌+AI回调</t>
-        </is>
-      </c>
-    </row>
-    <row r="85" ht="15" customHeight="1" s="139">
-      <c r="A85" s="147" t="inlineStr">
-        <is>
-          <t>2026-04-08 机器人ETF暴涨+6.4%至0.967：人形机器人产业催化</t>
-        </is>
-      </c>
-    </row>
-    <row r="86" ht="26.85" customHeight="1" s="139">
-      <c r="A86" s="147" t="inlineStr">
-        <is>
-          <t>2026-05-07~22 机器人连续上涨：ETF 1.056→1.216(+15%)，宇树科技73天过会</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" s="147" t="inlineStr">
-        <is>
-          <t>2026-05-25~06-02 机器人回调：1.216→1.122(-7.7%)，仍处强势区间</t>
-        </is>
-      </c>
-    </row>
-    <row r="88" ht="39.55" customHeight="1" s="139">
-      <c r="A88" s="180" t="inlineStr">
-        <is>
-          <t>2026-06-04 【保持观察】霍尔木兹海峡Day 12：伊朗暂停谈判+美众议院限制动武，WTI $96→$91-93回落，方向趋于缓和</t>
-        </is>
-      </c>
-      <c r="B88" s="181" t="n"/>
-      <c r="C88" s="181" t="n"/>
-      <c r="D88" s="181" t="n"/>
-      <c r="E88" s="181" t="n"/>
-      <c r="F88" s="181" t="n"/>
-      <c r="G88" s="181" t="n"/>
-      <c r="H88" s="181" t="n"/>
-    </row>
-    <row r="89" ht="26.85" customHeight="1" s="139">
-      <c r="A89" s="182" t="inlineStr">
-        <is>
-          <t>🔔 待重仓监控</t>
-        </is>
-      </c>
-    </row>
-    <row r="90" ht="26.85" customHeight="1" s="139">
-      <c r="A90" s="183" t="inlineStr">
-        <is>
-          <t>标的</t>
-        </is>
-      </c>
-      <c r="B90" s="183" t="inlineStr">
-        <is>
-          <t>状态</t>
-        </is>
-      </c>
-      <c r="C90" s="183" t="inlineStr">
-        <is>
-          <t>当前P/价格</t>
-        </is>
-      </c>
-      <c r="D90" s="183" t="inlineStr">
-        <is>
-          <t>最新信号</t>
-        </is>
-      </c>
-      <c r="E90" s="183" t="inlineStr">
-        <is>
-          <t>触发条件</t>
-        </is>
-      </c>
-      <c r="F90" s="183" t="inlineStr">
-        <is>
-          <t>距离触发</t>
-        </is>
-      </c>
-      <c r="G90" s="183" t="inlineStr">
-        <is>
-          <t>跟踪日期</t>
-        </is>
-      </c>
-    </row>
-    <row r="91" ht="39.55" customHeight="1" s="139">
-      <c r="A91" s="147" t="inlineStr">
-        <is>
-          <t>玻璃基板</t>
-        </is>
-      </c>
-      <c r="B91" s="147" t="inlineStr">
-        <is>
-          <t>深南电路002916/兴森科技002436</t>
-        </is>
-      </c>
-      <c r="C91" s="147" t="inlineStr">
-        <is>
-          <t>观察中</t>
-        </is>
-      </c>
-      <c r="D91" s="147" t="inlineStr">
-        <is>
-          <t>蒋宇飞：玻璃基板大规模应用2028年，5-10年赛道</t>
-        </is>
-      </c>
-      <c r="E91" s="147" t="inlineStr">
-        <is>
-          <t>AI基建+国产替代加速</t>
-        </is>
-      </c>
-      <c r="F91" s="147" t="inlineStr">
-        <is>
-          <t>中长期</t>
-        </is>
-      </c>
-      <c r="G91" s="147" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-    </row>
-    <row r="92" ht="26.85" customHeight="1" s="139">
-      <c r="A92" s="138" t="n"/>
-    </row>
-    <row r="93" ht="26.85" customHeight="1" s="139">
-      <c r="A93" s="147" t="inlineStr">
-        <is>
-          <t>油气对冲</t>
-        </is>
-      </c>
-      <c r="B93" s="147" t="inlineStr">
-        <is>
-          <t>华宝油气162411</t>
-        </is>
-      </c>
-      <c r="C93" s="147" t="inlineStr">
-        <is>
-          <t>观察中</t>
-        </is>
-      </c>
-      <c r="D93" s="147" t="inlineStr">
-        <is>
-          <t>宋鸿兵：霍尔木兹封锁3个月，85%投资者押注回落=幻觉</t>
-        </is>
-      </c>
-      <c r="E93" s="147" t="inlineStr">
-        <is>
-          <t>油价冲150或海峡持续封锁</t>
-        </is>
-      </c>
-      <c r="F93" s="147" t="inlineStr">
-        <is>
-          <t>短期</t>
-        </is>
-      </c>
-      <c r="G93" s="147" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="H93" s="138" t="inlineStr">
-        <is>
-          <t>小仓位试水，不对称博弈</t>
-        </is>
-      </c>
-    </row>
-    <row r="94" ht="39.55" customHeight="1" s="139">
-      <c r="A94" s="147" t="inlineStr">
-        <is>
-          <t>银行板块(512800)</t>
-        </is>
-      </c>
-      <c r="B94" s="147" t="inlineStr">
-        <is>
-          <t>弱势</t>
-        </is>
-      </c>
-      <c r="C94" s="147" t="inlineStr">
-        <is>
-          <t>P:50% 虚P-2pp</t>
-        </is>
-      </c>
-      <c r="D94" s="147" t="inlineStr">
-        <is>
-          <t>去杠杆+信贷收缩，ETF跌-1%，无催化</t>
-        </is>
-      </c>
-      <c r="E94" s="147" t="inlineStr">
-        <is>
-          <t>不建议加仓</t>
-        </is>
-      </c>
-      <c r="F94" s="147" t="inlineStr">
-        <is>
-          <t>短期</t>
-        </is>
-      </c>
-      <c r="G94" s="147" t="inlineStr">
-        <is>
-          <t>2026-06-03</t>
-        </is>
-      </c>
-      <c r="H94" s="138" t="inlineStr">
-        <is>
-          <t>银行ETF持续阴跌</t>
-        </is>
-      </c>
-    </row>
-    <row r="95" ht="39.55" customHeight="1" s="139">
-      <c r="A95" s="147" t="inlineStr">
-        <is>
-          <t>人形机器人(562500)</t>
-        </is>
-      </c>
-      <c r="B95" s="147" t="inlineStr">
-        <is>
-          <t>强势</t>
-        </is>
-      </c>
-      <c r="C95" s="147" t="inlineStr">
-        <is>
-          <t>P:58%(估)</t>
-        </is>
-      </c>
-      <c r="D95" s="147" t="inlineStr">
-        <is>
-          <t>宇树科技73天过会，ETF涨+11%</t>
-        </is>
-      </c>
-      <c r="E95" s="147" t="inlineStr">
-        <is>
-          <t>重点关注</t>
-        </is>
-      </c>
-      <c r="F95" s="147" t="inlineStr">
-        <is>
-          <t>中期</t>
-        </is>
-      </c>
-      <c r="G95" s="147" t="inlineStr">
-        <is>
-          <t>2026-06-03</t>
-        </is>
-      </c>
-      <c r="H95" s="138" t="inlineStr">
-        <is>
-          <t>平安先进制造+永赢先进制造</t>
-        </is>
-      </c>
-    </row>
-    <row r="96" ht="15" customHeight="1" s="139">
-      <c r="A96" s="147" t="inlineStr">
-        <is>
-          <t>存储赛道(5只A股)</t>
-        </is>
-      </c>
-      <c r="B96" s="147" t="inlineStr">
-        <is>
-          <t>❌降级观察</t>
-        </is>
-      </c>
-      <c r="C96" s="147" t="inlineStr">
-        <is>
-          <t>P:55% 安全边际不足</t>
-        </is>
-      </c>
-      <c r="D96" s="147" t="inlineStr">
-        <is>
-          <t>兆易¥525(+81%)/江波龙¥569/佰维¥341→PE天际线，向上空间&lt;向下空间</t>
-        </is>
-      </c>
-      <c r="E96" s="147" t="inlineStr">
-        <is>
-          <t>等中期选举大跌15%+</t>
-        </is>
-      </c>
-      <c r="F96" s="147" t="inlineStr">
-        <is>
-          <t>中期</t>
-        </is>
-      </c>
-      <c r="G96" s="147" t="inlineStr">
-        <is>
-          <t>2026-06-04</t>
-        </is>
-      </c>
-      <c r="H96" s="138" t="inlineStr">
-        <is>
-          <t>降级：存储涨完轮到堆叠，安全边际已不足</t>
-        </is>
-      </c>
-    </row>
-    <row r="97" ht="15" customHeight="1" s="139">
-      <c r="A97" s="147" t="inlineStr">
-        <is>
-          <t>澜起科技(688008)</t>
-        </is>
-      </c>
-      <c r="B97" s="147" t="inlineStr">
-        <is>
-          <t>❌降级观察</t>
-        </is>
-      </c>
-      <c r="C97" s="147" t="inlineStr">
-        <is>
-          <t>P:55% 安全边际中等</t>
-        </is>
-      </c>
-      <c r="D97" s="147" t="inlineStr">
-        <is>
-          <t>DDR5接口芯片，温和上涨，但存储赛道整体降级</t>
-        </is>
-      </c>
-      <c r="E97" s="147" t="inlineStr">
-        <is>
-          <t>等大跌15%+</t>
-        </is>
-      </c>
-      <c r="F97" s="147" t="inlineStr">
-        <is>
-          <t>中期</t>
-        </is>
-      </c>
-      <c r="G97" s="147" t="inlineStr">
-        <is>
-          <t>2026-06-04</t>
-        </is>
-      </c>
-      <c r="H97" s="138" t="inlineStr">
-        <is>
-          <t>降级：存储赛道尾声</t>
-        </is>
-      </c>
-    </row>
-    <row r="98" ht="18.65" customHeight="1" s="139">
-      <c r="A98" s="184" t="inlineStr">
-        <is>
-          <t>🔥堆叠/先进封装赛道（蒋宇飞"星光纯叠"框架）</t>
-        </is>
-      </c>
-    </row>
-    <row r="99" ht="15" customHeight="1" s="139">
-      <c r="A99" s="147" t="inlineStr">
-        <is>
-          <t>长电科技(600584)</t>
-        </is>
-      </c>
-      <c r="B99" s="147" t="inlineStr">
-        <is>
-          <t>🔴核心标的</t>
-        </is>
-      </c>
-      <c r="C99" s="147" t="inlineStr">
-        <is>
-          <t>P:75%+ PE30x</t>
-        </is>
-      </c>
-      <c r="D99" s="147" t="inlineStr">
-        <is>
-          <t>全球第三大封测厂，2.5D/3D量产级，客户广度最强（高通/海思/TI）</t>
-        </is>
-      </c>
-      <c r="E99" s="147" t="inlineStr">
-        <is>
-          <t>等中期选举大跌</t>
-        </is>
-      </c>
-      <c r="F99" s="147" t="inlineStr">
-        <is>
-          <t>中期</t>
-        </is>
-      </c>
-      <c r="G99" s="147" t="inlineStr">
-        <is>
-          <t>2026-06-04</t>
-        </is>
-      </c>
-      <c r="H99" s="138" t="inlineStr">
-        <is>
-          <t>安全边际大，堆叠赛道首选</t>
-        </is>
-      </c>
-    </row>
-    <row r="100" ht="15" customHeight="1" s="139">
-      <c r="A100" s="147" t="inlineStr">
-        <is>
-          <t>通富微电(002156)</t>
-        </is>
-      </c>
-      <c r="B100" s="147" t="inlineStr">
-        <is>
-          <t>🔴核心标的</t>
-        </is>
-      </c>
-      <c r="C100" s="147" t="inlineStr">
-        <is>
-          <t>P:75%+ 待查PE</t>
-        </is>
-      </c>
-      <c r="D100" s="147" t="inlineStr">
-        <is>
-          <t>AMD封测全线突破通道，2.5D量产，MI300X参与，不可替代</t>
-        </is>
-      </c>
-      <c r="E100" s="147" t="inlineStr">
-        <is>
-          <t>等中期选举大跌</t>
-        </is>
-      </c>
-      <c r="F100" s="147" t="inlineStr">
-        <is>
-          <t>中期</t>
-        </is>
-      </c>
-      <c r="G100" s="147" t="inlineStr">
-        <is>
-          <t>2026-06-04</t>
-        </is>
-      </c>
-      <c r="H100" s="138" t="inlineStr">
-        <is>
-          <t>安全边际中偏大，与长电各占一半</t>
-        </is>
-      </c>
-    </row>
-    <row r="101" ht="26.85" customHeight="1" s="139">
-      <c r="A101" s="138" t="n"/>
-    </row>
-    <row r="102" ht="15" customHeight="1" s="139">
-      <c r="A102" s="138" t="n"/>
-    </row>
-    <row r="103" ht="26.85" customHeight="1" s="139">
-      <c r="A103" s="316" t="inlineStr">
-        <is>
-          <t>🔥 蒋宇飞179视频深度分析 (2026-06-07 顶级置信度)</t>
-        </is>
-      </c>
-    </row>
-    <row r="104" ht="26.85" customHeight="1" s="139">
-      <c r="A104" s="138" t="inlineStr">
-        <is>
-          <t>核心框架: 星光纯叠=光模块(贯穿)→存储(吃肉)→堆叠(最大风口) | AI基建10年: 存力→算力→运力 | 2027算力长城=升腾+长鑫+DeepSeek</t>
-        </is>
-      </c>
-    </row>
-    <row r="105" ht="26.85" customHeight="1" s="139">
-      <c r="A105" s="138" t="inlineStr">
-        <is>
-          <t>【P值调整】芯片 41%→44%(虚P+3pp) | 稀金 40%→41%(虚P+1pp) | 其余0pp</t>
-        </is>
-      </c>
-    </row>
-    <row r="106" ht="26.85" customHeight="1" s="139"/>
-    <row r="107" ht="15" customHeight="1" s="139">
-      <c r="A107" s="138" t="inlineStr">
-        <is>
-          <t>MLCC被动元件</t>
-        </is>
-      </c>
-      <c r="B107" s="138" t="inlineStr">
-        <is>
-          <t>观察中</t>
-        </is>
-      </c>
-      <c r="C107" s="138" t="inlineStr">
-        <is>
-          <t>蒋宇飞: 行情到2027-H1 | 国巨台湾首富 | 300亿规模</t>
-        </is>
-      </c>
-      <c r="D107" s="138" t="inlineStr">
-        <is>
-          <t>2026-06-07</t>
-        </is>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" s="138" t="inlineStr">
-        <is>
-          <t>国产算力/升腾链</t>
-        </is>
-      </c>
-      <c r="B108" s="138" t="inlineStr">
-        <is>
-          <t>观察中</t>
-        </is>
-      </c>
-      <c r="C108" s="138" t="inlineStr">
-        <is>
-          <t>蒋宇飞: 2027算力长城最闪亮 | 升腾950明年出货 | 升腾+长鑫+DeepSeek</t>
-        </is>
-      </c>
-      <c r="D108" s="138" t="inlineStr">
-        <is>
-          <t>2026-06-07</t>
-        </is>
-      </c>
-    </row>
-    <row r="109" ht="15" customHeight="1" s="139">
-      <c r="A109" s="138" t="inlineStr">
-        <is>
-          <t>HBM产业链</t>
-        </is>
-      </c>
-      <c r="B109" s="138" t="inlineStr">
-        <is>
-          <t>观察中</t>
-        </is>
-      </c>
-      <c r="C109" s="138" t="inlineStr">
-        <is>
-          <t>蒋宇飞: HBM未来1.5-2.5年波涛汹涌 | Q4-Q1热潮 | 技术含量最高</t>
-        </is>
-      </c>
-      <c r="D109" s="138" t="inlineStr">
-        <is>
-          <t>2026-06-07</t>
-        </is>
-      </c>
-    </row>
-    <row r="110" ht="26.85" customHeight="1" s="139">
-      <c r="A110" s="138" t="inlineStr">
-        <is>
-          <t>CPU产业链</t>
-        </is>
-      </c>
-      <c r="B110" s="138" t="inlineStr">
-        <is>
-          <t>观察中</t>
-        </is>
-      </c>
-      <c r="C110" s="138" t="inlineStr">
-        <is>
-          <t>蒋宇飞: agent经济导致CPU爆发缺货 | 带动产业链</t>
-        </is>
-      </c>
-      <c r="D110" s="138" t="inlineStr">
-        <is>
-          <t>2026-06-07</t>
-        </is>
-      </c>
-    </row>
-    <row r="111" ht="26.85" customHeight="1" s="139">
-      <c r="A111" s="138" t="inlineStr">
-        <is>
-          <t>玻璃基板(更新)</t>
-        </is>
-      </c>
-      <c r="B111" s="138" t="inlineStr">
-        <is>
-          <t>观察中</t>
-        </is>
-      </c>
-      <c r="C111" s="138" t="inlineStr">
-        <is>
-          <t>蒋宇飞: 两三年热点→业绩2027-H2→大规模2028 | 封装+存储</t>
-        </is>
-      </c>
-      <c r="D111" s="138" t="inlineStr">
-        <is>
-          <t>2026-06-07</t>
-        </is>
-      </c>
-    </row>
-    <row r="112" ht="26.85" customHeight="1" s="139"/>
-    <row r="113" ht="26.85" customHeight="1" s="139">
-      <c r="A113" s="138" t="inlineStr">
-        <is>
-          <t>【堆叠75%验证】27条堆叠主题: "两年最大风口"+"一年半大放"+"存算一体"→P合理</t>
-        </is>
-      </c>
-    </row>
-    <row r="114" ht="26.85" customHeight="1" s="139">
-      <c r="A114" s="138" t="inlineStr">
-        <is>
-          <t>【存储降级确认】"存储跌80%但现在是时机"+"消费级见顶"+"存储涨完轮到堆叠"→降级合理</t>
-        </is>
-      </c>
-    </row>
-    <row r="115" ht="26.85" customHeight="1" s="139"/>
-    <row r="116" ht="15" customHeight="1" s="139"/>
-    <row r="117"/>
-    <row r="118" ht="15" customHeight="1" s="139"/>
-    <row r="119" ht="15" customHeight="1" s="139">
-      <c r="A119" s="153" t="inlineStr">
-        <is>
-          <t>📖 机制库 v3（2026-06-04 经小龙虾审核修订）</t>
-        </is>
-      </c>
-    </row>
-    <row r="120" ht="26.85" customHeight="1" s="139">
-      <c r="A120" s="185" t="inlineStr">
-        <is>
-          <t>[机制3v3] 现金锁定系数（CLC）— 平方衰减版</t>
-        </is>
-      </c>
-    </row>
-    <row r="121" ht="26.85" customHeight="1" s="139">
-      <c r="A121" s="186" t="inlineStr">
-        <is>
-          <t>叫什么</t>
-        </is>
-      </c>
-      <c r="B121" s="149" t="n"/>
-      <c r="C121" s="149" t="n"/>
-      <c r="D121" s="149" t="n"/>
-      <c r="E121" s="149" t="n"/>
-      <c r="F121" s="149" t="n"/>
-      <c r="G121" s="149" t="n"/>
-      <c r="H121" s="150" t="n"/>
-    </row>
-    <row r="122" ht="15" customHeight="1" s="139">
-      <c r="A122" s="186" t="inlineStr">
-        <is>
-          <t>公式</t>
-        </is>
-      </c>
-      <c r="B122" s="147" t="inlineStr">
-        <is>
-          <t>CLC = 信号概率 × 互锁强度 × 时间衰减²</t>
-        </is>
-      </c>
-    </row>
-    <row r="123" ht="15" customHeight="1" s="139">
-      <c r="A123" s="186" t="inlineStr">
-        <is>
-          <t>时间衰减</t>
-        </is>
-      </c>
-      <c r="B123" s="147" t="inlineStr">
-        <is>
-          <t>T = (距触发月数/12)²</t>
-        </is>
-      </c>
-      <c r="C123" s="147" t="inlineStr">
-        <is>
-          <t>6月=(5/12)²=0.174</t>
-        </is>
-      </c>
-      <c r="D123" s="147" t="inlineStr">
-        <is>
-          <t>11月=0</t>
-        </is>
-      </c>
-    </row>
-    <row r="124" ht="26.85" customHeight="1" s="139">
-      <c r="A124" s="186" t="inlineStr">
-        <is>
-          <t>为什么平方</t>
-        </is>
-      </c>
-      <c r="B124" s="147" t="inlineStr">
-        <is>
-          <t>线性衰减导致越近触发日锁得越少（反直觉）</t>
-        </is>
-      </c>
-      <c r="C124" s="147" t="inlineStr">
-        <is>
-          <t>平方函数：远离时多锁，临近时少锁</t>
-        </is>
-      </c>
-      <c r="D124" s="147" t="inlineStr">
-        <is>
-          <t>小龙虾审核通过</t>
-        </is>
-      </c>
-    </row>
-    <row r="125" ht="15" customHeight="1" s="139">
-      <c r="A125" s="186" t="inlineStr">
-        <is>
-          <t>信号概率</t>
-        </is>
-      </c>
-      <c r="B125" s="147" t="inlineStr">
-        <is>
-          <t>动态更新，每月审查</t>
-        </is>
-      </c>
-      <c r="C125" s="147" t="inlineStr">
-        <is>
-          <t>底线55%（达利欧区间下沿）</t>
-        </is>
-      </c>
-      <c r="D125" s="147" t="inlineStr">
-        <is>
-          <t>上限85%（达利欧区间上沿）</t>
-        </is>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" s="186" t="inlineStr">
-        <is>
-          <t>互锁强度</t>
-        </is>
-      </c>
-      <c r="B126" s="147" t="inlineStr">
-        <is>
-          <t>三源强互锁=1.0</t>
-        </is>
-      </c>
-      <c r="C126" s="147" t="inlineStr">
-        <is>
-          <t>达利欧6月修正&gt;2次→降级0.85</t>
-        </is>
-      </c>
-      <c r="D126" s="147" t="inlineStr">
-        <is>
-          <t>有原因修正不降级</t>
-        </is>
-      </c>
-    </row>
-    <row r="127" ht="15" customHeight="1" s="139">
-      <c r="A127" s="186" t="inlineStr">
-        <is>
-          <t>当前值</t>
-        </is>
-      </c>
-      <c r="B127" s="147" t="inlineStr">
-        <is>
-          <t>0.70 × 1.0 × (5/12)² = 0.122</t>
-        </is>
-      </c>
-      <c r="C127" s="147" t="inlineStr">
-        <is>
-          <t>→ 锁定12.2%现金</t>
-        </is>
-      </c>
-      <c r="D127" s="147" t="inlineStr">
-        <is>
-          <t>可用87.8%</t>
-        </is>
-      </c>
-    </row>
-    <row r="128" ht="15" customHeight="1" s="139">
-      <c r="A128" s="186" t="inlineStr">
-        <is>
-          <t>每月重算</t>
-        </is>
-      </c>
-      <c r="B128" s="149" t="n"/>
-      <c r="C128" s="149" t="n"/>
-      <c r="D128" s="149" t="n"/>
-      <c r="E128" s="149" t="n"/>
-      <c r="F128" s="149" t="n"/>
-      <c r="G128" s="149" t="n"/>
-      <c r="H128" s="150" t="n"/>
-    </row>
-    <row r="129" ht="26.85" customHeight="1" s="139"/>
-    <row r="130" ht="15" customHeight="1" s="139">
-      <c r="A130" s="185" t="inlineStr">
-        <is>
-          <t>[机制4v3] 折后仓位计算 — 4级分级版</t>
-        </is>
-      </c>
-    </row>
-    <row r="131" ht="15" customHeight="1" s="139">
-      <c r="A131" s="186" t="inlineStr">
-        <is>
-          <t>叫什么</t>
-        </is>
-      </c>
-      <c r="B131" s="147" t="inlineStr">
-        <is>
-          <t>折后仓位（Folded Allocation）v3</t>
-        </is>
-      </c>
-    </row>
-    <row r="132" ht="15" customHeight="1" s="139">
-      <c r="A132" s="186" t="inlineStr">
-        <is>
-          <t>公式</t>
-        </is>
-      </c>
-      <c r="B132" s="147" t="inlineStr">
-        <is>
-          <t>折后仓位% = 原目标仓位% × (1 - CLC × β系数)</t>
-        </is>
-      </c>
-    </row>
-    <row r="133" ht="15" customHeight="1" s="139">
-      <c r="A133" s="186" t="inlineStr">
-        <is>
-          <t>4级分级</t>
-        </is>
-      </c>
-      <c r="B133" s="147" t="inlineStr">
-        <is>
-          <t>L1高度暴露β=0.8（通富-AMD独供）</t>
-        </is>
-      </c>
-      <c r="C133" s="147" t="inlineStr">
-        <is>
-          <t>L2中度暴露β=0.5（长电-客户多元）</t>
-        </is>
-      </c>
-    </row>
-    <row r="134" ht="26.85" customHeight="1" s="139">
-      <c r="A134" s="186" t="inlineStr">
-        <is>
-          <t>分级继续</t>
-        </is>
-      </c>
-      <c r="B134" s="147" t="inlineStr">
-        <is>
-          <t>L3弱相关β=0.1（养殖）</t>
-        </is>
-      </c>
-      <c r="C134" s="147" t="inlineStr">
-        <is>
-          <t>L4反向受益β=-0.3（黄金）</t>
-        </is>
-      </c>
-    </row>
-    <row r="135" ht="15" customHeight="1" s="139">
-      <c r="A135" s="186" t="inlineStr">
-        <is>
-          <t>为什么分级</t>
-        </is>
-      </c>
-      <c r="B135" s="147" t="inlineStr">
-        <is>
-          <t>不同标的受AI泡沫影响不同</t>
-        </is>
-      </c>
-      <c r="C135" s="147" t="inlineStr">
-        <is>
-          <t>通富只有AMD一根柱子</t>
-        </is>
-      </c>
-      <c r="D135" s="147" t="inlineStr">
-        <is>
-          <t>长电客户多元化</t>
-        </is>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" s="186" t="inlineStr">
-        <is>
-          <t>当前计算</t>
-        </is>
-      </c>
-      <c r="B136" s="147" t="inlineStr">
-        <is>
-          <t>通富:33%×(1-0.122×0.8)=30.1%</t>
-        </is>
-      </c>
-      <c r="C136" s="147" t="inlineStr">
-        <is>
-          <t>长电:37%×(1-0.122×0.5)=34.7%</t>
-        </is>
-      </c>
-    </row>
-    <row r="137" ht="15" customHeight="1" s="139">
-      <c r="A137" s="186" t="inlineStr">
-        <is>
-          <t>分级逻辑</t>
-        </is>
-      </c>
-      <c r="B137" s="149" t="n"/>
-      <c r="C137" s="149" t="n"/>
-      <c r="D137" s="149" t="n"/>
-      <c r="E137" s="149" t="n"/>
-      <c r="F137" s="149" t="n"/>
-      <c r="G137" s="149" t="n"/>
-      <c r="H137" s="150" t="n"/>
-    </row>
-    <row r="138" ht="26.85" customHeight="1" s="139"/>
-    <row r="139" ht="15" customHeight="1" s="139">
-      <c r="A139" s="185" t="inlineStr">
-        <is>
-          <t>[机制5v3] 虚P→实P转换 — 确认窗口+因果链版</t>
-        </is>
-      </c>
-    </row>
-    <row r="140" ht="26.85" customHeight="1" s="139">
-      <c r="A140" s="186" t="inlineStr">
-        <is>
-          <t>叫什么</t>
-        </is>
-      </c>
-      <c r="B140" s="149" t="n"/>
-      <c r="C140" s="149" t="n"/>
-      <c r="D140" s="149" t="n"/>
-      <c r="E140" s="149" t="n"/>
-      <c r="F140" s="149" t="n"/>
-      <c r="G140" s="149" t="n"/>
-      <c r="H140" s="150" t="n"/>
-    </row>
-    <row r="141" ht="26.85" customHeight="1" s="139">
-      <c r="A141" s="186" t="inlineStr">
-        <is>
-          <t>视觉信号</t>
-        </is>
-      </c>
-      <c r="B141" s="147" t="inlineStr">
-        <is>
-          <t>纳指七姐妹&gt;15%回调（从52周高）</t>
-        </is>
-      </c>
-      <c r="C141" s="147" t="inlineStr">
-        <is>
-          <t>或破200日均线</t>
-        </is>
-      </c>
-    </row>
-    <row r="142" ht="39.55" customHeight="1" s="139">
-      <c r="A142" s="186" t="inlineStr">
-        <is>
-          <t>确认窗口</t>
-        </is>
-      </c>
-      <c r="B142" s="147" t="inlineStr">
-        <is>
-          <t>跌穿15%后维持5个交易日不反弹</t>
-        </is>
-      </c>
-      <c r="C142" s="147" t="inlineStr">
-        <is>
-          <t>防单日噪音和假触发</t>
-        </is>
-      </c>
-      <c r="D142" s="147" t="inlineStr">
-        <is>
-          <t>小龙虾建议</t>
-        </is>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" s="186" t="inlineStr">
-        <is>
-          <t>因果链</t>
-        </is>
-      </c>
-      <c r="B143" s="147" t="inlineStr">
-        <is>
-          <t>需至少2条佐证：</t>
-        </is>
-      </c>
-      <c r="C143" s="147" t="inlineStr">
-        <is>
-          <t>①英伟达/AMD下调指引</t>
-        </is>
-      </c>
-      <c r="D143" s="147" t="inlineStr">
-        <is>
-          <t>②AI ETF资金流出</t>
-        </is>
-      </c>
-    </row>
-    <row r="144" ht="17.35" customHeight="1" s="139">
-      <c r="A144" s="186" t="inlineStr">
-        <is>
-          <t>因果链继续</t>
-        </is>
-      </c>
-      <c r="B144" s="147" t="inlineStr">
-        <is>
-          <t>③投行下调AI评级</t>
-        </is>
-      </c>
-      <c r="C144" s="147" t="inlineStr">
-        <is>
-          <t>④Mag7裁员/削减开支</t>
-        </is>
-      </c>
-    </row>
-    <row r="145" ht="17.15" customHeight="1" s="139">
-      <c r="A145" s="186" t="inlineStr">
-        <is>
-          <t>为什么加因果</t>
-        </is>
-      </c>
-      <c r="B145" s="147" t="inlineStr">
-        <is>
-          <t>15%下跌可能是地缘冲击不是AI泡沫</t>
-        </is>
-      </c>
-      <c r="C145" s="147" t="inlineStr">
-        <is>
-          <t>两者操作完全不同</t>
-        </is>
-      </c>
-      <c r="D145" s="147" t="inlineStr">
-        <is>
-          <t>必须区分原因</t>
-        </is>
-      </c>
-    </row>
-    <row r="146" ht="17.15" customHeight="1" s="139">
-      <c r="A146" s="186" t="inlineStr">
-        <is>
-          <t>转换后</t>
         </is>
       </c>
       <c r="B146" s="149" t="n"/>
@@ -4919,695 +3975,2120 @@
       <c r="G146" s="149" t="n"/>
       <c r="H146" s="150" t="n"/>
     </row>
-    <row r="147" ht="17.15" customHeight="1" s="139"/>
+    <row r="147" ht="17.15" customHeight="1" s="139">
+      <c r="A147" s="157" t="inlineStr">
+        <is>
+          <t>养殖</t>
+        </is>
+      </c>
+      <c r="B147" s="157" t="inlineStr">
+        <is>
+          <t>70%</t>
+        </is>
+      </c>
+      <c r="C147" s="157" t="inlineStr">
+        <is>
+          <t>2.0:1</t>
+        </is>
+      </c>
+      <c r="D147" s="157" t="inlineStr">
+        <is>
+          <t>1.400</t>
+        </is>
+      </c>
+      <c r="E147" s="157" t="inlineStr">
+        <is>
+          <t>已持仓不需现金 | 6/5 芳姐：低价抄底母猪，行业融资枯竭，等待母猪血流成河才是最佳买点</t>
+        </is>
+      </c>
+      <c r="F147" s="157" t="inlineStr">
+        <is>
+          <t>继续持有</t>
+        </is>
+      </c>
+      <c r="G147" s="158" t="inlineStr">
+        <is>
+          <t>✅已配置</t>
+        </is>
+      </c>
+    </row>
     <row r="148" ht="17.15" customHeight="1" s="139">
-      <c r="A148" s="187" t="inlineStr">
+      <c r="A148" s="157" t="inlineStr">
+        <is>
+          <t>电池</t>
+        </is>
+      </c>
+      <c r="B148" s="157" t="inlineStr">
+        <is>
+          <t>65%</t>
+        </is>
+      </c>
+      <c r="C148" s="157" t="inlineStr">
+        <is>
+          <t>2.0:1</t>
+        </is>
+      </c>
+      <c r="D148" s="157" t="inlineStr">
+        <is>
+          <t>1.300</t>
+        </is>
+      </c>
+      <c r="E148" s="157" t="inlineStr">
+        <is>
+          <t>已持仓不需现金 | 6/5 闻号说经济：厄尔尼诺80%概率+AI用电爆发→电力/能源受益</t>
+        </is>
+      </c>
+      <c r="F148" s="157" t="inlineStr">
+        <is>
+          <t>继续持有</t>
+        </is>
+      </c>
+      <c r="G148" s="158" t="inlineStr">
+        <is>
+          <t>✅已配置</t>
+        </is>
+      </c>
+    </row>
+    <row r="149" ht="17.15" customHeight="1" s="139">
+      <c r="A149" s="157" t="inlineStr">
+        <is>
+          <t>核电</t>
+        </is>
+      </c>
+      <c r="B149" s="157" t="inlineStr">
+        <is>
+          <t>52%</t>
+        </is>
+      </c>
+      <c r="C149" s="157" t="inlineStr">
+        <is>
+          <t>1.5:1</t>
+        </is>
+      </c>
+      <c r="D149" s="157" t="inlineStr">
+        <is>
+          <t>0.780</t>
+        </is>
+      </c>
+      <c r="E149" s="157" t="inlineStr">
+        <is>
+          <t>10年维度
+小仓试水可行</t>
+        </is>
+      </c>
+      <c r="F149" s="157" t="inlineStr">
+        <is>
+          <t>不影响现金策略</t>
+        </is>
+      </c>
+      <c r="G149" s="166" t="inlineStr">
+        <is>
+          <t>🟡长期观察</t>
+        </is>
+      </c>
+    </row>
+    <row r="150" ht="17.15" customHeight="1" s="139">
+      <c r="A150" s="157" t="inlineStr">
+        <is>
+          <t>存储</t>
+        </is>
+      </c>
+      <c r="B150" s="157" t="inlineStr">
+        <is>
+          <t>55%</t>
+        </is>
+      </c>
+      <c r="C150" s="157" t="inlineStr">
+        <is>
+          <t>1.0:1</t>
+        </is>
+      </c>
+      <c r="D150" s="157" t="inlineStr">
+        <is>
+          <t>0.550</t>
+        </is>
+      </c>
+      <c r="E150" s="157" t="inlineStr">
+        <is>
+          <t>已降级</t>
+        </is>
+      </c>
+      <c r="F150" s="157" t="inlineStr">
+        <is>
+          <t>不动</t>
+        </is>
+      </c>
+      <c r="G150" s="160" t="inlineStr">
+        <is>
+          <t>❌已降级</t>
+        </is>
+      </c>
+    </row>
+    <row r="151" ht="17.15" customHeight="1" s="139">
+      <c r="A151" s="157" t="inlineStr">
+        <is>
+          <t>纯现金5月</t>
+        </is>
+      </c>
+      <c r="B151" s="149" t="n"/>
+      <c r="C151" s="149" t="n"/>
+      <c r="D151" s="149" t="n"/>
+      <c r="E151" s="149" t="n"/>
+      <c r="F151" s="149" t="n"/>
+      <c r="G151" s="149" t="n"/>
+      <c r="H151" s="150" t="n"/>
+    </row>
+    <row r="152" ht="17.15" customHeight="1" s="139">
+      <c r="A152" s="147" t="inlineStr">
+        <is>
+          <t>AI硬件确定性(付鹏) → 内存=AI核心瓶颈(4信源互锁) → 国产替代加速 → 稀土断供日本 → 芯片/存储/HBM长期利好 | 短期被利率↑/地缘↑压制</t>
+        </is>
+      </c>
+    </row>
+    <row r="153" ht="17.15" customHeight="1" s="139">
+      <c r="A153" s="167" t="inlineStr">
+        <is>
+          <t>五、虚P→实P转换条件 &amp; 操作触发</t>
+        </is>
+      </c>
+      <c r="B153" s="149" t="n"/>
+      <c r="C153" s="149" t="n"/>
+      <c r="D153" s="149" t="n"/>
+      <c r="E153" s="149" t="n"/>
+      <c r="F153" s="149" t="n"/>
+      <c r="G153" s="149" t="n"/>
+      <c r="H153" s="150" t="n"/>
+    </row>
+    <row r="154">
+      <c r="A154" s="156" t="inlineStr">
+        <is>
+          <t>条件</t>
+        </is>
+      </c>
+      <c r="B154" s="161" t="inlineStr">
+        <is>
+          <t>触发信号</t>
+        </is>
+      </c>
+      <c r="C154" s="156" t="inlineStr">
+        <is>
+          <t>影响</t>
+        </is>
+      </c>
+      <c r="D154" s="156" t="inlineStr">
+        <is>
+          <t>操作</t>
+        </is>
+      </c>
+      <c r="E154" s="147" t="inlineStr">
+        <is>
+          <t>2026-05-30 宋鸿兵：海峡封锁→能源成本飙升</t>
+        </is>
+      </c>
+      <c r="F154" s="147" t="inlineStr">
+        <is>
+          <t>2026-05-30 岩松：存储1-2年产能饱和</t>
+        </is>
+      </c>
+      <c r="G154" s="147" t="inlineStr">
+        <is>
+          <t>2026-05-30 宋鸿兵：30年美债破5%双红线</t>
+        </is>
+      </c>
+    </row>
+    <row r="155" ht="15" customHeight="1" s="139">
+      <c r="A155" s="170" t="inlineStr">
+        <is>
+          <t>达利欧落地</t>
+        </is>
+      </c>
+      <c r="B155" s="157" t="inlineStr">
+        <is>
+          <t>七姐妹&gt;15%回调或破200日均线</t>
+        </is>
+      </c>
+      <c r="C155" s="157" t="inlineStr">
+        <is>
+          <t>芯片/恒科虚P转实P</t>
+        </is>
+      </c>
+      <c r="D155" s="157" t="inlineStr">
+        <is>
+          <t>现金解锁→大仓位进堆叠</t>
+        </is>
+      </c>
+    </row>
+    <row r="156" ht="15" customHeight="1" s="139">
+      <c r="A156" s="166" t="inlineStr">
+        <is>
+          <t>李大霄落地</t>
+        </is>
+      </c>
+      <c r="B156" s="157" t="inlineStr">
+        <is>
+          <t>多数成分股下跌+指数拐头</t>
+        </is>
+      </c>
+      <c r="C156" s="157" t="inlineStr">
+        <is>
+          <t>恒科/芯片虚P转实P</t>
+        </is>
+      </c>
+      <c r="D156" s="157" t="inlineStr">
+        <is>
+          <t>确认系统性风险→入场</t>
+        </is>
+      </c>
+    </row>
+    <row r="157" ht="15" customHeight="1" s="139">
+      <c r="A157" s="171" t="inlineStr">
+        <is>
+          <t>中期选举</t>
+        </is>
+      </c>
+      <c r="B157" s="171" t="inlineStr">
+        <is>
+          <t>11月美股跌一波</t>
+        </is>
+      </c>
+      <c r="C157" s="171" t="inlineStr">
+        <is>
+          <t>你的策略触发</t>
+        </is>
+      </c>
+      <c r="D157" s="171" t="inlineStr">
+        <is>
+          <t>现金→长电+通富</t>
+        </is>
+      </c>
+      <c r="E157" s="156" t="inlineStr">
+        <is>
+          <t>落地条件</t>
+        </is>
+      </c>
+      <c r="F157" s="156" t="inlineStr">
+        <is>
+          <t>状态</t>
+        </is>
+      </c>
+      <c r="G157" s="156" t="inlineStr">
+        <is>
+          <t>权重</t>
+        </is>
+      </c>
+      <c r="H157" s="156" t="inlineStr">
+        <is>
+          <t>备注</t>
+        </is>
+      </c>
+    </row>
+    <row r="158" ht="15" customHeight="1" s="139">
+      <c r="A158" s="157" t="inlineStr">
+        <is>
+          <t>堆叠独立</t>
+        </is>
+      </c>
+      <c r="B158" s="149" t="n"/>
+      <c r="C158" s="149" t="n"/>
+      <c r="D158" s="149" t="n"/>
+      <c r="E158" s="149" t="n"/>
+      <c r="F158" s="149" t="n"/>
+      <c r="G158" s="149" t="n"/>
+      <c r="H158" s="150" t="n"/>
+    </row>
+    <row r="159" ht="15" customHeight="1" s="139">
+      <c r="A159" s="157" t="inlineStr">
+        <is>
+          <t>李大霄
+金融界 6/4</t>
+        </is>
+      </c>
+      <c r="B159" s="157" t="inlineStr">
+        <is>
+          <t>美股窄牛宽熊
+仅20只创新高
+CAPE40倍→泡沫</t>
+        </is>
+      </c>
+      <c r="C159" s="158" t="inlineStr">
+        <is>
+          <t>🟢高度契合
+确认美股风险
+现金策略正确</t>
+        </is>
+      </c>
+      <c r="D159" s="157" t="inlineStr">
+        <is>
+          <t>美股全市场↓
+港股连带承压</t>
+        </is>
+      </c>
+      <c r="E159" s="157" t="inlineStr">
+        <is>
+          <t>纳指破200日均线
+或多数成分股下跌</t>
+        </is>
+      </c>
+      <c r="F159" s="159" t="inlineStr">
+        <is>
+          <t>⏳未落地
+(虚P状态)</t>
+        </is>
+      </c>
+      <c r="G159" s="157" t="inlineStr">
+        <is>
+          <t>⭐⭐⭐
+中高</t>
+        </is>
+      </c>
+      <c r="H159" s="157" t="inlineStr">
+        <is>
+          <t>6/4三源联动:
+恒科-2pp
+芯片-1pp
+→已记虚P
+未转实P</t>
+        </is>
+      </c>
+    </row>
+    <row r="160" ht="15" customHeight="1" s="139">
+      <c r="A160" s="172" t="inlineStr">
+        <is>
+          <t>⚡ 核心结论：三源联动确认AI泡沫风险+你的中期选举策略正确。大部分现金锁定等11月回调→大仓位进长电/通富。机会成本可接受（不对称博弈，下有保底）。虚P已记，等落地转实P。</t>
+        </is>
+      </c>
+      <c r="B160" s="168" t="n"/>
+      <c r="C160" s="168" t="n"/>
+      <c r="D160" s="168" t="n"/>
+      <c r="E160" s="168" t="n"/>
+      <c r="F160" s="168" t="n"/>
+      <c r="G160" s="168" t="n"/>
+      <c r="H160" s="169" t="n"/>
+    </row>
+    <row r="161">
+      <c r="A161" s="138" t="inlineStr">
+        <is>
+          <t>────────────────────────────────────────────────────────────</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="173" t="inlineStr">
+        <is>
+          <t>🔗 三源互锁验证</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="140" t="inlineStr">
+        <is>
+          <t>达利欧 × 李大霄</t>
+        </is>
+      </c>
+      <c r="C163" s="174" t="inlineStr">
+        <is>
+          <t>✅ 强印证</t>
+        </is>
+      </c>
+      <c r="E163" s="175" t="inlineStr">
+        <is>
+          <t>AI泡沫+窄牛宽熊=同一现象两角度，互相确认</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="140" t="inlineStr">
+        <is>
+          <t>达利欧 × 知乎</t>
+        </is>
+      </c>
+      <c r="C164" s="176" t="inlineStr">
+        <is>
+          <t>⚠️ 部分矛盾</t>
+        </is>
+      </c>
+      <c r="E164" s="175" t="inlineStr">
+        <is>
+          <t>达利欧看流动性(泡沫将破) vs 知乎看估值(PE中值安全)</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="140" t="inlineStr">
+        <is>
+          <t>三源共识</t>
+        </is>
+      </c>
+      <c r="C165" s="177" t="inlineStr">
+        <is>
+          <t>🔴 核心共识</t>
+        </is>
+      </c>
+      <c r="E165" s="175" t="inlineStr">
+        <is>
+          <t>AI龙头估值偏高+市场极度集中+中小盘已熊 → 短期风险&gt;机会</t>
+        </is>
+      </c>
+    </row>
+    <row r="166"/>
+    <row r="167">
+      <c r="A167" s="165" t="inlineStr">
+        <is>
+          <t>🎯 结论（虚P→实P转换条件）</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="140" t="inlineStr">
+        <is>
+          <t>① 达利欧信号落地条件</t>
+        </is>
+      </c>
+      <c r="C168" s="175" t="inlineStr">
+        <is>
+          <t>纳指七姐妹出现&gt;15%回调 或 纳指破200日均线</t>
+        </is>
+      </c>
+      <c r="E168" s="178" t="inlineStr">
+        <is>
+          <t>→ 芯片/恒科虚P转实P → 确认减仓信号</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="140" t="inlineStr">
+        <is>
+          <t>② 李大霄信号落地条件</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="140" t="inlineStr">
+        <is>
+          <t>③ 你的策略触发条件</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="140" t="inlineStr">
+        <is>
+          <t>④ 堆叠赛道独立性</t>
+        </is>
+      </c>
+      <c r="C171" s="175" t="inlineStr">
+        <is>
+          <t>国内产业确定性，三源均未提及国内封测</t>
+        </is>
+      </c>
+      <c r="E171" s="178" t="inlineStr">
+        <is>
+          <t>→ 不受美股泡沫直接影响 → 等回调后优先配置</t>
+        </is>
+      </c>
+    </row>
+    <row r="172"/>
+    <row r="173">
+      <c r="A173" s="179" t="inlineStr">
+        <is>
+          <t>⚡ 一句话：三源确认AI泡沫风险+你的中期选举策略正确。虚P已记，等落地转实P。现金为王，堆叠赛道等回调后大仓位进。</t>
+        </is>
+      </c>
+    </row>
+    <row r="174"/>
+    <row r="175"/>
+    <row r="176"/>
+    <row r="177">
+      <c r="A177" s="147" t="inlineStr">
+        <is>
+          <t>🤖 人形机器人半年事件链</t>
+        </is>
+      </c>
+    </row>
+    <row r="178"/>
+    <row r="179">
+      <c r="A179" s="147" t="inlineStr">
+        <is>
+          <t>2026-03-23 机器人ETF暴跌-4.1%至0.909：市场恐慌+AI回调</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="147" t="inlineStr">
+        <is>
+          <t>2026-04-08 机器人ETF暴涨+6.4%至0.967：人形机器人产业催化</t>
+        </is>
+      </c>
+      <c r="B180" s="149" t="n"/>
+      <c r="C180" s="149" t="n"/>
+      <c r="D180" s="149" t="n"/>
+      <c r="E180" s="149" t="n"/>
+      <c r="F180" s="149" t="n"/>
+      <c r="G180" s="149" t="n"/>
+      <c r="H180" s="150" t="n"/>
+    </row>
+    <row r="181">
+      <c r="A181" s="147" t="inlineStr">
+        <is>
+          <t>2026-05-07~22 机器人连续上涨：ETF 1.056→1.216(+15%)，宇树科技73天过会</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="147" t="inlineStr">
+        <is>
+          <t>2026-05-25~06-02 机器人回调：1.216→1.122(-7.7%)，仍处强势区间</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="180" t="inlineStr">
+        <is>
+          <t>2026-06-04 【保持观察】霍尔木兹海峡Day 12：伊朗暂停谈判+美众议院限制动武，WTI $96→$91-93回落，方向趋于缓和</t>
+        </is>
+      </c>
+      <c r="B183" s="181" t="n"/>
+      <c r="C183" s="181" t="n"/>
+      <c r="D183" s="181" t="n"/>
+      <c r="E183" s="181" t="n"/>
+      <c r="F183" s="181" t="n"/>
+      <c r="G183" s="181" t="n"/>
+      <c r="H183" s="181" t="n"/>
+    </row>
+    <row r="184">
+      <c r="A184" s="182" t="inlineStr">
+        <is>
+          <t>🔔 待重仓监控</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" s="183" t="inlineStr">
+        <is>
+          <t>标的</t>
+        </is>
+      </c>
+      <c r="B185" s="183" t="inlineStr">
+        <is>
+          <t>状态</t>
+        </is>
+      </c>
+      <c r="C185" s="183" t="inlineStr">
+        <is>
+          <t>当前P/价格</t>
+        </is>
+      </c>
+      <c r="D185" s="183" t="inlineStr">
+        <is>
+          <t>最新信号</t>
+        </is>
+      </c>
+      <c r="E185" s="183" t="inlineStr">
+        <is>
+          <t>触发条件</t>
+        </is>
+      </c>
+      <c r="F185" s="183" t="inlineStr">
+        <is>
+          <t>距离触发</t>
+        </is>
+      </c>
+      <c r="G185" s="183" t="inlineStr">
+        <is>
+          <t>跟踪日期</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" s="147" t="inlineStr">
+        <is>
+          <t>玻璃基板</t>
+        </is>
+      </c>
+      <c r="B186" s="147" t="inlineStr">
+        <is>
+          <t>深南电路002916/兴森科技002436</t>
+        </is>
+      </c>
+      <c r="C186" s="147" t="inlineStr">
+        <is>
+          <t>观察中</t>
+        </is>
+      </c>
+      <c r="D186" s="147" t="inlineStr">
+        <is>
+          <t>蒋宇飞：玻璃基板大规模应用2028年，5-10年赛道</t>
+        </is>
+      </c>
+      <c r="E186" s="147" t="inlineStr">
+        <is>
+          <t>AI基建+国产替代加速</t>
+        </is>
+      </c>
+      <c r="F186" s="147" t="inlineStr">
+        <is>
+          <t>中长期</t>
+        </is>
+      </c>
+      <c r="G186" s="147" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" s="138" t="n"/>
+    </row>
+    <row r="188">
+      <c r="A188" s="147" t="inlineStr">
+        <is>
+          <t>油气对冲</t>
+        </is>
+      </c>
+      <c r="B188" s="147" t="inlineStr">
+        <is>
+          <t>华宝油气162411</t>
+        </is>
+      </c>
+      <c r="C188" s="147" t="inlineStr">
+        <is>
+          <t>观察中</t>
+        </is>
+      </c>
+      <c r="D188" s="147" t="inlineStr">
+        <is>
+          <t>宋鸿兵：霍尔木兹封锁3个月，85%投资者押注回落=幻觉</t>
+        </is>
+      </c>
+      <c r="E188" s="147" t="inlineStr">
+        <is>
+          <t>油价冲150或海峡持续封锁</t>
+        </is>
+      </c>
+      <c r="F188" s="147" t="inlineStr">
+        <is>
+          <t>短期</t>
+        </is>
+      </c>
+      <c r="G188" s="147" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="H188" s="138" t="inlineStr">
+        <is>
+          <t>小仓位试水，不对称博弈</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" s="147" t="inlineStr">
+        <is>
+          <t>银行板块(512800)</t>
+        </is>
+      </c>
+      <c r="B189" s="149" t="n"/>
+      <c r="C189" s="149" t="n"/>
+      <c r="D189" s="149" t="n"/>
+      <c r="E189" s="149" t="n"/>
+      <c r="F189" s="149" t="n"/>
+      <c r="G189" s="149" t="n"/>
+      <c r="H189" s="150" t="n"/>
+    </row>
+    <row r="190">
+      <c r="A190" s="147" t="inlineStr">
+        <is>
+          <t>人形机器人(562500)</t>
+        </is>
+      </c>
+      <c r="B190" s="147" t="inlineStr">
+        <is>
+          <t>强势</t>
+        </is>
+      </c>
+      <c r="C190" s="147" t="inlineStr">
+        <is>
+          <t>P:58%(估)</t>
+        </is>
+      </c>
+      <c r="D190" s="147" t="inlineStr">
+        <is>
+          <t>宇树科技73天过会，ETF涨+11%</t>
+        </is>
+      </c>
+      <c r="E190" s="147" t="inlineStr">
+        <is>
+          <t>重点关注</t>
+        </is>
+      </c>
+      <c r="F190" s="147" t="inlineStr">
+        <is>
+          <t>中期</t>
+        </is>
+      </c>
+      <c r="G190" s="147" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="H190" s="138" t="inlineStr">
+        <is>
+          <t>平安先进制造+永赢先进制造</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" s="147" t="inlineStr">
+        <is>
+          <t>存储赛道(5只A股)</t>
+        </is>
+      </c>
+      <c r="B191" s="149" t="n"/>
+      <c r="C191" s="149" t="n"/>
+      <c r="D191" s="149" t="n"/>
+      <c r="E191" s="149" t="n"/>
+      <c r="F191" s="149" t="n"/>
+      <c r="G191" s="149" t="n"/>
+      <c r="H191" s="150" t="n"/>
+    </row>
+    <row r="192">
+      <c r="A192" s="147" t="inlineStr">
+        <is>
+          <t>澜起科技(688008)</t>
+        </is>
+      </c>
+      <c r="B192" s="149" t="n"/>
+      <c r="C192" s="149" t="n"/>
+      <c r="D192" s="149" t="n"/>
+      <c r="E192" s="149" t="n"/>
+      <c r="F192" s="149" t="n"/>
+      <c r="G192" s="149" t="n"/>
+      <c r="H192" s="150" t="n"/>
+    </row>
+    <row r="193">
+      <c r="A193" s="184" t="inlineStr">
+        <is>
+          <t>🔥堆叠/先进封装赛道（蒋宇飞"星光纯叠"框架）</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" s="147" t="inlineStr">
+        <is>
+          <t>长电科技(600584)</t>
+        </is>
+      </c>
+      <c r="B194" s="147" t="inlineStr">
+        <is>
+          <t>🔴核心标的</t>
+        </is>
+      </c>
+      <c r="C194" s="147" t="inlineStr">
+        <is>
+          <t>P:75%+ PE30x</t>
+        </is>
+      </c>
+      <c r="D194" s="147" t="inlineStr">
+        <is>
+          <t>全球第三大封测厂，2.5D/3D量产级，客户广度最强（高通/海思/TI）</t>
+        </is>
+      </c>
+      <c r="E194" s="147" t="inlineStr">
+        <is>
+          <t>等中期选举大跌</t>
+        </is>
+      </c>
+      <c r="F194" s="147" t="inlineStr">
+        <is>
+          <t>中期</t>
+        </is>
+      </c>
+      <c r="G194" s="147" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="H194" s="138" t="inlineStr">
+        <is>
+          <t>安全边际大，堆叠赛道首选</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" s="147" t="inlineStr">
+        <is>
+          <t>通富微电(002156)</t>
+        </is>
+      </c>
+      <c r="B195" s="147" t="inlineStr">
+        <is>
+          <t>🔴核心标的</t>
+        </is>
+      </c>
+      <c r="C195" s="147" t="inlineStr">
+        <is>
+          <t>P:75%+ 待查PE</t>
+        </is>
+      </c>
+      <c r="D195" s="147" t="inlineStr">
+        <is>
+          <t>AMD封测全线突破通道，2.5D量产，MI300X参与，不可替代</t>
+        </is>
+      </c>
+      <c r="E195" s="147" t="inlineStr">
+        <is>
+          <t>等中期选举大跌</t>
+        </is>
+      </c>
+      <c r="F195" s="147" t="inlineStr">
+        <is>
+          <t>中期</t>
+        </is>
+      </c>
+      <c r="G195" s="147" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="H195" s="138" t="inlineStr">
+        <is>
+          <t>安全边际中偏大，与长电各占一半</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" s="138" t="n"/>
+    </row>
+    <row r="197">
+      <c r="A197" s="138" t="n"/>
+    </row>
+    <row r="198">
+      <c r="A198" s="316" t="inlineStr">
+        <is>
+          <t>🔥 蒋宇飞179视频深度分析 (2026-06-07 顶级置信度)</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" s="138" t="inlineStr">
+        <is>
+          <t>核心框架: 星光纯叠=光模块(贯穿)→存储(吃肉)→堆叠(最大风口) | AI基建10年: 存力→算力→运力 | 2027算力长城=升腾+长鑫+DeepSeek</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" s="138" t="inlineStr">
+        <is>
+          <t>【P值调整】芯片 41%→44%(虚P+3pp) | 稀金 40%→41%(虚P+1pp) | 其余0pp</t>
+        </is>
+      </c>
+    </row>
+    <row r="201"/>
+    <row r="202">
+      <c r="A202" s="138" t="inlineStr">
+        <is>
+          <t>MLCC被动元件</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" s="138" t="inlineStr">
+        <is>
+          <t>国产算力/升腾链</t>
+        </is>
+      </c>
+      <c r="B203" s="138" t="inlineStr">
+        <is>
+          <t>观察中</t>
+        </is>
+      </c>
+      <c r="C203" s="138" t="inlineStr">
+        <is>
+          <t>蒋宇飞: 2027算力长城最闪亮 | 升腾950明年出货 | 升腾+长鑫+DeepSeek</t>
+        </is>
+      </c>
+      <c r="D203" s="138" t="inlineStr">
+        <is>
+          <t>2026-06-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" s="138" t="inlineStr">
+        <is>
+          <t>HBM产业链</t>
+        </is>
+      </c>
+      <c r="B204" s="138" t="inlineStr">
+        <is>
+          <t>观察中</t>
+        </is>
+      </c>
+      <c r="C204" s="138" t="inlineStr">
+        <is>
+          <t>蒋宇飞: HBM未来1.5-2.5年波涛汹涌 | Q4-Q1热潮 | 技术含量最高</t>
+        </is>
+      </c>
+      <c r="D204" s="138" t="inlineStr">
+        <is>
+          <t>2026-06-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" s="138" t="inlineStr">
+        <is>
+          <t>CPU产业链</t>
+        </is>
+      </c>
+      <c r="B205" s="138" t="inlineStr">
+        <is>
+          <t>观察中</t>
+        </is>
+      </c>
+      <c r="C205" s="138" t="inlineStr">
+        <is>
+          <t>蒋宇飞: agent经济导致CPU爆发缺货 | 带动产业链</t>
+        </is>
+      </c>
+      <c r="D205" s="138" t="inlineStr">
+        <is>
+          <t>2026-06-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" s="138" t="inlineStr">
+        <is>
+          <t>玻璃基板(更新)</t>
+        </is>
+      </c>
+      <c r="B206" s="138" t="inlineStr">
+        <is>
+          <t>观察中</t>
+        </is>
+      </c>
+      <c r="C206" s="138" t="inlineStr">
+        <is>
+          <t>蒋宇飞: 两三年热点→业绩2027-H2→大规模2028 | 封装+存储</t>
+        </is>
+      </c>
+      <c r="D206" s="138" t="inlineStr">
+        <is>
+          <t>2026-06-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="207"/>
+    <row r="208">
+      <c r="A208" s="138" t="inlineStr">
+        <is>
+          <t>【堆叠75%验证】27条堆叠主题: "两年最大风口"+"一年半大放"+"存算一体"→P合理</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" s="138" t="inlineStr">
+        <is>
+          <t>【存储降级确认】"存储跌80%但现在是时机"+"消费级见顶"+"存储涨完轮到堆叠"→降级合理</t>
+        </is>
+      </c>
+    </row>
+    <row r="210"/>
+    <row r="211"/>
+    <row r="212"/>
+    <row r="213"/>
+    <row r="214">
+      <c r="A214" s="153" t="inlineStr">
+        <is>
+          <t>📖 机制库 v3（2026-06-04 经小龙虾审核修订）</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" s="185" t="inlineStr">
+        <is>
+          <t>[机制3v3] 现金锁定系数（CLC）— 平方衰减版</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" s="186" t="inlineStr">
+        <is>
+          <t>叫什么</t>
+        </is>
+      </c>
+      <c r="B216" s="149" t="n"/>
+      <c r="C216" s="149" t="n"/>
+      <c r="D216" s="149" t="n"/>
+      <c r="E216" s="149" t="n"/>
+      <c r="F216" s="149" t="n"/>
+      <c r="G216" s="149" t="n"/>
+      <c r="H216" s="150" t="n"/>
+    </row>
+    <row r="217">
+      <c r="A217" s="186" t="inlineStr">
+        <is>
+          <t>公式</t>
+        </is>
+      </c>
+      <c r="B217" s="147" t="inlineStr">
+        <is>
+          <t>CLC = 信号概率 × 互锁强度 × 时间衰减²</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" s="186" t="inlineStr">
+        <is>
+          <t>时间衰减</t>
+        </is>
+      </c>
+      <c r="B218" s="147" t="inlineStr">
+        <is>
+          <t>T = (距触发月数/12)²</t>
+        </is>
+      </c>
+      <c r="C218" s="147" t="inlineStr">
+        <is>
+          <t>6月=(5/12)²=0.174</t>
+        </is>
+      </c>
+      <c r="D218" s="147" t="inlineStr">
+        <is>
+          <t>11月=0</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" s="186" t="inlineStr">
+        <is>
+          <t>为什么平方</t>
+        </is>
+      </c>
+      <c r="B219" s="147" t="inlineStr">
+        <is>
+          <t>线性衰减导致越近触发日锁得越少（反直觉）</t>
+        </is>
+      </c>
+      <c r="C219" s="147" t="inlineStr">
+        <is>
+          <t>平方函数：远离时多锁，临近时少锁</t>
+        </is>
+      </c>
+      <c r="D219" s="147" t="inlineStr">
+        <is>
+          <t>小龙虾审核通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" s="186" t="inlineStr">
+        <is>
+          <t>信号概率</t>
+        </is>
+      </c>
+      <c r="B220" s="149" t="n"/>
+      <c r="C220" s="149" t="n"/>
+      <c r="D220" s="149" t="n"/>
+      <c r="E220" s="149" t="n"/>
+      <c r="F220" s="149" t="n"/>
+      <c r="G220" s="149" t="n"/>
+      <c r="H220" s="150" t="n"/>
+    </row>
+    <row r="221">
+      <c r="A221" s="186" t="inlineStr">
+        <is>
+          <t>互锁强度</t>
+        </is>
+      </c>
+      <c r="B221" s="147" t="inlineStr">
+        <is>
+          <t>三源强互锁=1.0</t>
+        </is>
+      </c>
+      <c r="C221" s="147" t="inlineStr">
+        <is>
+          <t>达利欧6月修正&gt;2次→降级0.85</t>
+        </is>
+      </c>
+      <c r="D221" s="147" t="inlineStr">
+        <is>
+          <t>有原因修正不降级</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" s="186" t="inlineStr">
+        <is>
+          <t>当前值</t>
+        </is>
+      </c>
+      <c r="B222" s="147" t="inlineStr">
+        <is>
+          <t>0.70 × 1.0 × (5/12)² = 0.122</t>
+        </is>
+      </c>
+      <c r="C222" s="147" t="inlineStr">
+        <is>
+          <t>→ 锁定12.2%现金</t>
+        </is>
+      </c>
+      <c r="D222" s="147" t="inlineStr">
+        <is>
+          <t>可用87.8%</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" s="186" t="inlineStr">
+        <is>
+          <t>每月重算</t>
+        </is>
+      </c>
+      <c r="B223" s="149" t="n"/>
+      <c r="C223" s="149" t="n"/>
+      <c r="D223" s="149" t="n"/>
+      <c r="E223" s="149" t="n"/>
+      <c r="F223" s="149" t="n"/>
+      <c r="G223" s="149" t="n"/>
+      <c r="H223" s="150" t="n"/>
+    </row>
+    <row r="224"/>
+    <row r="225">
+      <c r="A225" s="185" t="inlineStr">
+        <is>
+          <t>[机制4v3] 折后仓位计算 — 4级分级版</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" s="186" t="inlineStr">
+        <is>
+          <t>叫什么</t>
+        </is>
+      </c>
+      <c r="B226" s="147" t="inlineStr">
+        <is>
+          <t>折后仓位（Folded Allocation）v3</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" s="186" t="inlineStr">
+        <is>
+          <t>公式</t>
+        </is>
+      </c>
+      <c r="B227" s="147" t="inlineStr">
+        <is>
+          <t>折后仓位% = 原目标仓位% × (1 - CLC × β系数)</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" s="186" t="inlineStr">
+        <is>
+          <t>4级分级</t>
+        </is>
+      </c>
+      <c r="B228" s="147" t="inlineStr">
+        <is>
+          <t>L1高度暴露β=0.8（通富-AMD独供）</t>
+        </is>
+      </c>
+      <c r="C228" s="147" t="inlineStr">
+        <is>
+          <t>L2中度暴露β=0.5（长电-客户多元）</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" s="186" t="inlineStr">
+        <is>
+          <t>分级继续</t>
+        </is>
+      </c>
+      <c r="B229" s="147" t="inlineStr">
+        <is>
+          <t>L3弱相关β=0.1（养殖）</t>
+        </is>
+      </c>
+      <c r="C229" s="147" t="inlineStr">
+        <is>
+          <t>L4反向受益β=-0.3（黄金）</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" s="186" t="inlineStr">
+        <is>
+          <t>为什么分级</t>
+        </is>
+      </c>
+      <c r="B230" s="149" t="n"/>
+      <c r="C230" s="149" t="n"/>
+      <c r="D230" s="149" t="n"/>
+      <c r="E230" s="149" t="n"/>
+      <c r="F230" s="149" t="n"/>
+      <c r="G230" s="149" t="n"/>
+      <c r="H230" s="150" t="n"/>
+    </row>
+    <row r="231">
+      <c r="A231" s="186" t="inlineStr">
+        <is>
+          <t>当前计算</t>
+        </is>
+      </c>
+      <c r="B231" s="147" t="inlineStr">
+        <is>
+          <t>通富:33%×(1-0.122×0.8)=30.1%</t>
+        </is>
+      </c>
+      <c r="C231" s="147" t="inlineStr">
+        <is>
+          <t>长电:37%×(1-0.122×0.5)=34.7%</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" s="186" t="inlineStr">
+        <is>
+          <t>分级逻辑</t>
+        </is>
+      </c>
+      <c r="B232" s="149" t="n"/>
+      <c r="C232" s="149" t="n"/>
+      <c r="D232" s="149" t="n"/>
+      <c r="E232" s="149" t="n"/>
+      <c r="F232" s="149" t="n"/>
+      <c r="G232" s="149" t="n"/>
+      <c r="H232" s="150" t="n"/>
+    </row>
+    <row r="233"/>
+    <row r="234">
+      <c r="A234" s="185" t="inlineStr">
+        <is>
+          <t>[机制5v3] 虚P→实P转换 — 确认窗口+因果链版</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" s="186" t="inlineStr">
+        <is>
+          <t>叫什么</t>
+        </is>
+      </c>
+      <c r="B235" s="149" t="n"/>
+      <c r="C235" s="149" t="n"/>
+      <c r="D235" s="149" t="n"/>
+      <c r="E235" s="149" t="n"/>
+      <c r="F235" s="149" t="n"/>
+      <c r="G235" s="149" t="n"/>
+      <c r="H235" s="150" t="n"/>
+    </row>
+    <row r="236">
+      <c r="A236" s="186" t="inlineStr">
+        <is>
+          <t>视觉信号</t>
+        </is>
+      </c>
+      <c r="B236" s="147" t="inlineStr">
+        <is>
+          <t>纳指七姐妹&gt;15%回调（从52周高）</t>
+        </is>
+      </c>
+      <c r="C236" s="147" t="inlineStr">
+        <is>
+          <t>或破200日均线</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" s="186" t="inlineStr">
+        <is>
+          <t>确认窗口</t>
+        </is>
+      </c>
+      <c r="B237" s="147" t="inlineStr">
+        <is>
+          <t>跌穿15%后维持5个交易日不反弹</t>
+        </is>
+      </c>
+      <c r="C237" s="147" t="inlineStr">
+        <is>
+          <t>防单日噪音和假触发</t>
+        </is>
+      </c>
+      <c r="D237" s="147" t="inlineStr">
+        <is>
+          <t>小龙虾建议</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" s="186" t="inlineStr">
+        <is>
+          <t>因果链</t>
+        </is>
+      </c>
+      <c r="B238" s="147" t="inlineStr">
+        <is>
+          <t>需至少2条佐证：</t>
+        </is>
+      </c>
+      <c r="C238" s="147" t="inlineStr">
+        <is>
+          <t>①英伟达/AMD下调指引</t>
+        </is>
+      </c>
+      <c r="D238" s="147" t="inlineStr">
+        <is>
+          <t>②AI ETF资金流出</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" s="186" t="inlineStr">
+        <is>
+          <t>因果链继续</t>
+        </is>
+      </c>
+      <c r="B239" s="147" t="inlineStr">
+        <is>
+          <t>③投行下调AI评级</t>
+        </is>
+      </c>
+      <c r="C239" s="147" t="inlineStr">
+        <is>
+          <t>④Mag7裁员/削减开支</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" s="186" t="inlineStr">
+        <is>
+          <t>为什么加因果</t>
+        </is>
+      </c>
+      <c r="B240" s="147" t="inlineStr">
+        <is>
+          <t>15%下跌可能是地缘冲击不是AI泡沫</t>
+        </is>
+      </c>
+      <c r="C240" s="147" t="inlineStr">
+        <is>
+          <t>两者操作完全不同</t>
+        </is>
+      </c>
+      <c r="D240" s="147" t="inlineStr">
+        <is>
+          <t>必须区分原因</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" s="186" t="inlineStr">
+        <is>
+          <t>转换后</t>
+        </is>
+      </c>
+      <c r="B241" s="149" t="n"/>
+      <c r="C241" s="149" t="n"/>
+      <c r="D241" s="149" t="n"/>
+      <c r="E241" s="149" t="n"/>
+      <c r="F241" s="149" t="n"/>
+      <c r="G241" s="149" t="n"/>
+      <c r="H241" s="150" t="n"/>
+    </row>
+    <row r="242"/>
+    <row r="243">
+      <c r="A243" s="187" t="inlineStr">
         <is>
           <t>[信号计分板] 每日更新，驱动信号概率动态调整</t>
         </is>
       </c>
     </row>
-    <row r="149" ht="17.15" customHeight="1" s="139">
-      <c r="A149" s="186" t="inlineStr">
+    <row r="244">
+      <c r="A244" s="186" t="inlineStr">
         <is>
           <t>泡沫正向信号</t>
         </is>
       </c>
-      <c r="B149" s="147" t="inlineStr">
+      <c r="B244" s="147" t="inlineStr">
         <is>
           <t>Mag7单日跌&gt;3% → +1</t>
         </is>
       </c>
-      <c r="C149" s="147" t="inlineStr">
+      <c r="C244" s="147" t="inlineStr">
         <is>
           <t>Mag7月跌&gt;10% → +2</t>
         </is>
       </c>
     </row>
-    <row r="150" ht="17.15" customHeight="1" s="139">
-      <c r="B150" s="147" t="inlineStr">
+    <row r="245">
+      <c r="B245" s="147" t="inlineStr">
         <is>
           <t>VIX&gt;30 → +2</t>
         </is>
       </c>
-      <c r="C150" s="147" t="inlineStr">
+      <c r="C245" s="147" t="inlineStr">
         <is>
           <t>AI公司裁员/下调指引 → +1</t>
         </is>
       </c>
     </row>
-    <row r="151" ht="17.15" customHeight="1" s="139">
-      <c r="B151" s="147" t="inlineStr">
+    <row r="246">
+      <c r="B246" s="147" t="inlineStr">
         <is>
           <t>信用利差&gt;150bp → +2</t>
         </is>
       </c>
     </row>
-    <row r="152" ht="17.15" customHeight="1" s="139">
-      <c r="A152" s="186" t="inlineStr">
+    <row r="247">
+      <c r="A247" s="186" t="inlineStr">
         <is>
           <t>泡沫反向信号</t>
         </is>
       </c>
-      <c r="B152" s="147" t="inlineStr">
+      <c r="B247" s="147" t="inlineStr">
         <is>
           <t>Mag7单日涨&gt;3% → -1</t>
         </is>
       </c>
-      <c r="C152" s="147" t="inlineStr">
+      <c r="C247" s="147" t="inlineStr">
         <is>
           <t>Mag7月涨&gt;8% → -2</t>
         </is>
       </c>
     </row>
-    <row r="153" ht="17.15" customHeight="1" s="139">
-      <c r="B153" s="147" t="inlineStr">
+    <row r="248">
+      <c r="B248" s="147" t="inlineStr">
         <is>
           <t>Fed降息 → -2</t>
         </is>
       </c>
-      <c r="C153" s="147" t="inlineStr">
+      <c r="C248" s="147" t="inlineStr">
         <is>
           <t>AI龙头超预期财报 → -1</t>
         </is>
       </c>
     </row>
-    <row r="154">
-      <c r="B154" s="147" t="inlineStr">
+    <row r="249">
+      <c r="B249" s="147" t="inlineStr">
         <is>
           <t>VIX&lt;15 → -1</t>
         </is>
       </c>
     </row>
-    <row r="155" ht="15" customHeight="1" s="139">
-      <c r="A155" s="186" t="inlineStr">
+    <row r="250">
+      <c r="A250" s="186" t="inlineStr">
         <is>
           <t>更新规则</t>
         </is>
       </c>
-      <c r="B155" s="147" t="inlineStr">
+      <c r="B250" s="147" t="inlineStr">
         <is>
           <t>每月第一天：信号概率=70%+上月净计分×5pp</t>
         </is>
       </c>
-      <c r="C155" s="147" t="inlineStr">
+      <c r="C250" s="147" t="inlineStr">
         <is>
           <t>底线55%上限85%</t>
         </is>
       </c>
     </row>
-    <row r="156" ht="15" customHeight="1" s="139">
-      <c r="A156" s="186" t="inlineStr">
+    <row r="251">
+      <c r="A251" s="186" t="inlineStr">
         <is>
           <t>Mag7权重</t>
         </is>
       </c>
-      <c r="B156" s="149" t="n"/>
-      <c r="C156" s="149" t="n"/>
-      <c r="D156" s="149" t="n"/>
-      <c r="E156" s="149" t="n"/>
-      <c r="F156" s="149" t="n"/>
-      <c r="G156" s="149" t="n"/>
-      <c r="H156" s="150" t="n"/>
-    </row>
-    <row r="157" ht="15" customHeight="1" s="139"/>
-    <row r="158" ht="15" customHeight="1" s="139">
-      <c r="A158" s="187" t="inlineStr">
+      <c r="B251" s="149" t="n"/>
+      <c r="C251" s="149" t="n"/>
+      <c r="D251" s="149" t="n"/>
+      <c r="E251" s="149" t="n"/>
+      <c r="F251" s="149" t="n"/>
+      <c r="G251" s="149" t="n"/>
+      <c r="H251" s="150" t="n"/>
+    </row>
+    <row r="252"/>
+    <row r="253">
+      <c r="A253" s="187" t="inlineStr">
         <is>
           <t>⚡ 机制v3使用指南</t>
         </is>
       </c>
     </row>
-    <row r="159" ht="15" customHeight="1" s="139">
-      <c r="A159" s="186" t="inlineStr">
+    <row r="254">
+      <c r="A254" s="186" t="inlineStr">
         <is>
           <t>日常看盘</t>
         </is>
       </c>
-      <c r="B159" s="147" t="inlineStr">
+      <c r="B254" s="147" t="inlineStr">
         <is>
           <t>看机会成本排序Sheet折后仓位</t>
         </is>
       </c>
-      <c r="C159" s="147" t="inlineStr">
+      <c r="C254" s="147" t="inlineStr">
         <is>
           <t>看现金锁定状态</t>
         </is>
       </c>
     </row>
-    <row r="160" ht="15" customHeight="1" s="139">
-      <c r="A160" s="186" t="inlineStr">
+    <row r="255">
+      <c r="A255" s="186" t="inlineStr">
         <is>
           <t>每日更新</t>
         </is>
       </c>
-      <c r="B160" s="147" t="inlineStr">
+      <c r="B255" s="147" t="inlineStr">
         <is>
           <t>信号计分板逐股计分</t>
         </is>
       </c>
-      <c r="C160" s="147" t="inlineStr">
+      <c r="C255" s="147" t="inlineStr">
         <is>
           <t>净计分累计</t>
         </is>
       </c>
     </row>
-    <row r="161">
-      <c r="A161" s="186" t="inlineStr">
+    <row r="256">
+      <c r="A256" s="186" t="inlineStr">
         <is>
           <t>每月重算</t>
         </is>
       </c>
-      <c r="B161" s="147" t="inlineStr">
+      <c r="B256" s="147" t="inlineStr">
         <is>
           <t>①信号概率=70%+净计分×5pp</t>
         </is>
       </c>
-      <c r="C161" s="147" t="inlineStr">
+      <c r="C256" s="147" t="inlineStr">
         <is>
           <t>②CLC=信号概率×互锁×时间衰减²</t>
         </is>
       </c>
-      <c r="D161" s="147" t="inlineStr">
+      <c r="D256" s="147" t="inlineStr">
         <is>
           <t>③折后仓位=原仓位×(1-CLC×β)</t>
         </is>
       </c>
     </row>
-    <row r="162">
-      <c r="A162" s="186" t="inlineStr">
+    <row r="257">
+      <c r="A257" s="186" t="inlineStr">
         <is>
           <t>信号落地</t>
         </is>
       </c>
-      <c r="B162" s="147" t="inlineStr">
+      <c r="B257" s="147" t="inlineStr">
         <is>
           <t>视觉信号+5日确认+因果链2条</t>
         </is>
       </c>
-      <c r="C162" s="147" t="inlineStr">
+      <c r="C257" s="147" t="inlineStr">
         <is>
           <t>→虚P转实P</t>
         </is>
       </c>
-      <c r="D162" s="147" t="inlineStr">
+      <c r="D257" s="147" t="inlineStr">
         <is>
           <t>→CLC=0现金解锁</t>
         </is>
       </c>
     </row>
-    <row r="163">
-      <c r="A163" s="186" t="inlineStr">
+    <row r="258">
+      <c r="A258" s="186" t="inlineStr">
         <is>
           <t>核验计算</t>
         </is>
       </c>
-      <c r="B163" s="147" t="inlineStr">
+      <c r="B258" s="147" t="inlineStr">
         <is>
           <t>python3 /tmp/mechanism_checker_v3.py</t>
         </is>
       </c>
-      <c r="C163" s="147" t="inlineStr">
+      <c r="C258" s="147" t="inlineStr">
         <is>
           <t>自动重算所有机制</t>
         </is>
       </c>
     </row>
-    <row r="164"/>
-    <row r="165">
-      <c r="A165" s="188" t="inlineStr">
+    <row r="259"/>
+    <row r="260">
+      <c r="A260" s="188" t="inlineStr">
         <is>
           <t>📊 持仓状态速查表</t>
         </is>
       </c>
     </row>
-    <row r="166">
-      <c r="A166" s="189" t="inlineStr">
+    <row r="261">
+      <c r="A261" s="189" t="inlineStr">
         <is>
           <t>持仓</t>
         </is>
       </c>
-      <c r="B166" s="189" t="inlineStr">
+      <c r="B261" s="189" t="inlineStr">
         <is>
           <t>代码</t>
         </is>
       </c>
-      <c r="C166" s="189" t="inlineStr">
+      <c r="C261" s="189" t="inlineStr">
         <is>
           <t>当前P</t>
         </is>
       </c>
-      <c r="D166" s="189" t="inlineStr">
+      <c r="D261" s="189" t="inlineStr">
         <is>
           <t>有效P</t>
         </is>
       </c>
-      <c r="E166" s="189" t="inlineStr">
+      <c r="E261" s="189" t="inlineStr">
         <is>
           <t>虚P</t>
         </is>
       </c>
-      <c r="F166" s="189" t="inlineStr">
+      <c r="F261" s="189" t="inlineStr">
         <is>
           <t>利率折价</t>
         </is>
       </c>
-      <c r="G166" s="189" t="inlineStr">
+      <c r="G261" s="189" t="inlineStr">
         <is>
           <t>方向</t>
         </is>
       </c>
-      <c r="H166" s="189" t="inlineStr">
+      <c r="H261" s="189" t="inlineStr">
         <is>
           <t>操作建议</t>
         </is>
       </c>
     </row>
-    <row r="167">
-      <c r="A167" s="138" t="inlineStr">
+    <row r="262">
+      <c r="A262" s="138" t="inlineStr">
         <is>
           <t>芯片020628</t>
         </is>
       </c>
-      <c r="B167" s="138" t="inlineStr">
+      <c r="B262" s="138" t="inlineStr">
         <is>
           <t>C1</t>
         </is>
       </c>
-      <c r="C167" s="138" t="inlineStr">
+      <c r="C262" s="138" t="inlineStr">
         <is>
           <t>41</t>
         </is>
       </c>
-      <c r="D167" s="138" t="inlineStr">
+      <c r="D262" s="138" t="inlineStr">
         <is>
           <t>35</t>
         </is>
       </c>
-      <c r="E167" s="138" t="inlineStr">
+      <c r="E262" s="138" t="inlineStr">
         <is>
           <t>虚P+2pp | 6/5 存储→芯片资金传送门：存储涨81%降级后，资金搬进芯片ETF/长电通富</t>
         </is>
       </c>
-      <c r="F167" s="138" t="inlineStr">
+      <c r="F262" s="138" t="inlineStr">
         <is>
           <t>利率折价-6pp</t>
         </is>
       </c>
-      <c r="G167" s="138" t="inlineStr">
+      <c r="G262" s="138" t="inlineStr">
         <is>
           <t>🟡中性</t>
         </is>
       </c>
-      <c r="H167" s="138" t="inlineStr">
+      <c r="H262" s="138" t="inlineStr">
         <is>
           <t>观望</t>
         </is>
       </c>
     </row>
-    <row r="168">
-      <c r="A168" s="138" t="inlineStr">
+    <row r="263">
+      <c r="A263" s="138" t="inlineStr">
         <is>
           <t>电池018926</t>
         </is>
       </c>
-      <c r="B168" s="138" t="inlineStr">
+      <c r="B263" s="138" t="inlineStr">
         <is>
           <t>C2</t>
         </is>
       </c>
-      <c r="C168" s="138" t="inlineStr">
+      <c r="C263" s="138" t="inlineStr">
         <is>
           <t>65</t>
         </is>
       </c>
-      <c r="D168" s="138" t="inlineStr">
+      <c r="D263" s="138" t="inlineStr">
         <is>
           <t>59</t>
         </is>
       </c>
-      <c r="E168" s="138" t="inlineStr">
+      <c r="E263" s="138" t="inlineStr">
         <is>
           <t>虚P无</t>
         </is>
       </c>
-      <c r="F168" s="138" t="inlineStr">
+      <c r="F263" s="138" t="inlineStr">
         <is>
           <t>利率折价-6pp</t>
         </is>
       </c>
-      <c r="G168" s="138" t="inlineStr">
+      <c r="G263" s="138" t="inlineStr">
         <is>
           <t>🟢偏多</t>
         </is>
       </c>
-      <c r="H168" s="138" t="inlineStr">
+      <c r="H263" s="138" t="inlineStr">
         <is>
           <t>持有/关注加仓</t>
         </is>
       </c>
     </row>
-    <row r="169">
-      <c r="A169" s="138" t="inlineStr">
+    <row r="264">
+      <c r="A264" s="138" t="inlineStr">
         <is>
           <t>恒科012349</t>
         </is>
       </c>
-      <c r="B169" s="138" t="inlineStr">
+      <c r="B264" s="138" t="inlineStr">
         <is>
           <t>C3</t>
         </is>
       </c>
-      <c r="C169" s="138" t="inlineStr">
+      <c r="C264" s="138" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="D169" s="138" t="inlineStr">
+      <c r="D264" s="138" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="E169" s="138" t="inlineStr">
+      <c r="E264" s="138" t="inlineStr">
         <is>
           <t>虚P无 | 6/5 闻号说经济：301关税60国+AI芯片管制升级→压制恒科</t>
         </is>
       </c>
-      <c r="F169" s="138" t="inlineStr">
+      <c r="F264" s="138" t="inlineStr">
         <is>
           <t>利率折价-6pp</t>
         </is>
       </c>
-      <c r="G169" s="138" t="inlineStr">
+      <c r="G264" s="138" t="inlineStr">
         <is>
           <t>🔴偏空</t>
         </is>
       </c>
-      <c r="H169" s="138" t="inlineStr">
+      <c r="H264" s="138" t="inlineStr">
         <is>
           <t>减仓/清仓</t>
         </is>
       </c>
     </row>
-    <row r="170">
-      <c r="A170" s="138" t="inlineStr">
+    <row r="265">
+      <c r="A265" s="138" t="inlineStr">
         <is>
           <t>养殖014415</t>
         </is>
       </c>
-      <c r="B170" s="138" t="inlineStr">
+      <c r="B265" s="138" t="inlineStr">
         <is>
           <t>C4</t>
         </is>
       </c>
-      <c r="C170" s="138" t="inlineStr">
+      <c r="C265" s="138" t="inlineStr">
         <is>
           <t>70</t>
         </is>
       </c>
-      <c r="D170" s="138" t="inlineStr">
+      <c r="D265" s="138" t="inlineStr">
         <is>
           <t>70</t>
         </is>
       </c>
-      <c r="E170" s="138" t="inlineStr">
+      <c r="E265" s="138" t="inlineStr">
         <is>
           <t>虚P+4pp | 6/5 芳姐：低价抄底母猪，行业融资枯竭，等待母猪血流成河才是最佳买点</t>
         </is>
       </c>
-      <c r="F170" s="138" t="inlineStr">
+      <c r="F265" s="138" t="inlineStr">
         <is>
           <t>利率折价0pp</t>
         </is>
       </c>
-      <c r="G170" s="138" t="inlineStr">
+      <c r="G265" s="138" t="inlineStr">
         <is>
           <t>🟢偏多</t>
         </is>
       </c>
-      <c r="H170" s="138" t="inlineStr">
+      <c r="H265" s="138" t="inlineStr">
         <is>
           <t>持有/关注加仓</t>
         </is>
       </c>
     </row>
-    <row r="171">
-      <c r="A171" s="138" t="inlineStr">
+    <row r="266">
+      <c r="A266" s="138" t="inlineStr">
         <is>
           <t>有色004433</t>
         </is>
       </c>
-      <c r="B171" s="138" t="inlineStr">
+      <c r="B266" s="138" t="inlineStr">
         <is>
           <t>C5</t>
         </is>
       </c>
-      <c r="C171" s="138" t="inlineStr">
+      <c r="C266" s="138" t="inlineStr">
         <is>
           <t>39</t>
         </is>
       </c>
-      <c r="D171" s="138" t="inlineStr">
+      <c r="D266" s="138" t="inlineStr">
         <is>
           <t>35</t>
         </is>
       </c>
-      <c r="E171" s="138" t="inlineStr">
+      <c r="E266" s="138" t="inlineStr">
         <is>
           <t>虚P无 | 6/5 闻号说经济：301关税60国→压制有色需求</t>
         </is>
       </c>
-      <c r="F171" s="138" t="inlineStr">
+      <c r="F266" s="138" t="inlineStr">
         <is>
           <t>利率折价-4pp</t>
         </is>
       </c>
-      <c r="G171" s="138" t="inlineStr">
+      <c r="G266" s="138" t="inlineStr">
         <is>
           <t>🔴偏空</t>
         </is>
       </c>
-      <c r="H171" s="138" t="inlineStr">
+      <c r="H266" s="138" t="inlineStr">
         <is>
           <t>减仓/清仓</t>
         </is>
       </c>
     </row>
-    <row r="172">
-      <c r="A172" s="138" t="inlineStr">
+    <row r="267">
+      <c r="A267" s="138" t="inlineStr">
         <is>
           <t>稀金014111</t>
         </is>
       </c>
-      <c r="B172" s="138" t="inlineStr">
+      <c r="B267" s="138" t="inlineStr">
         <is>
           <t>C6</t>
         </is>
       </c>
-      <c r="C172" s="138" t="inlineStr">
+      <c r="C267" s="138" t="inlineStr">
         <is>
           <t>40</t>
         </is>
       </c>
-      <c r="D172" s="138" t="inlineStr">
+      <c r="D267" s="138" t="inlineStr">
         <is>
           <t>36</t>
         </is>
       </c>
-      <c r="E172" s="138" t="inlineStr">
+      <c r="E267" s="138" t="inlineStr">
         <is>
           <t>虚P无</t>
         </is>
       </c>
-      <c r="F172" s="138" t="inlineStr">
+      <c r="F267" s="138" t="inlineStr">
         <is>
           <t>利率折价-4pp</t>
         </is>
       </c>
-      <c r="G172" s="138" t="inlineStr">
+      <c r="G267" s="138" t="inlineStr">
         <is>
           <t>🟡中性</t>
         </is>
       </c>
-      <c r="H172" s="138" t="inlineStr">
+      <c r="H267" s="138" t="inlineStr">
         <is>
           <t>观望</t>
         </is>
       </c>
     </row>
-    <row r="173">
-      <c r="A173" s="138" t="inlineStr">
+    <row r="268">
+      <c r="A268" s="138" t="inlineStr">
         <is>
           <t>银行001595</t>
         </is>
       </c>
-      <c r="B173" s="138" t="inlineStr">
+      <c r="B268" s="138" t="inlineStr">
         <is>
           <t>C7</t>
         </is>
       </c>
-      <c r="C173" s="138" t="inlineStr">
+      <c r="C268" s="138" t="inlineStr">
         <is>
           <t>47</t>
         </is>
       </c>
-      <c r="D173" s="138" t="inlineStr">
+      <c r="D268" s="138" t="inlineStr">
         <is>
           <t>47</t>
         </is>
       </c>
-      <c r="E173" s="138" t="inlineStr">
+      <c r="E268" s="138" t="inlineStr">
         <is>
           <t>虚P-2pp | 6/5 闻号说经济：银行信贷收紧→压制银行</t>
         </is>
       </c>
-      <c r="F173" s="138" t="inlineStr">
+      <c r="F268" s="138" t="inlineStr">
         <is>
           <t>利率折价0pp</t>
         </is>
       </c>
-      <c r="G173" s="138" t="inlineStr">
+      <c r="G268" s="138" t="inlineStr">
         <is>
           <t>🟡中性</t>
         </is>
       </c>
-      <c r="H173" s="138" t="inlineStr">
+      <c r="H268" s="138" t="inlineStr">
         <is>
           <t>观望</t>
         </is>
       </c>
     </row>
-    <row r="174">
-      <c r="A174" s="138" t="inlineStr">
+    <row r="269">
+      <c r="A269" s="138" t="inlineStr">
         <is>
           <t>AI027048</t>
         </is>
       </c>
-      <c r="B174" s="138" t="inlineStr">
+      <c r="B269" s="138" t="inlineStr">
         <is>
           <t>C8</t>
         </is>
       </c>
-      <c r="C174" s="138" t="inlineStr">
+      <c r="C269" s="138" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="D174" s="138" t="inlineStr">
+      <c r="D269" s="138" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F174" s="138" t="inlineStr">
+      <c r="F269" s="138" t="inlineStr">
         <is>
           <t>利率折价-4pp</t>
         </is>
       </c>
-      <c r="G174" s="138" t="inlineStr">
+      <c r="G269" s="138" t="inlineStr">
         <is>
           <t>🟡中性</t>
         </is>
       </c>
-      <c r="H174" s="138" t="inlineStr">
+      <c r="H269" s="138" t="inlineStr">
         <is>
           <t>观望</t>
         </is>
       </c>
     </row>
-    <row r="175"/>
-    <row r="176">
-      <c r="A176" s="190" t="inlineStr">
+    <row r="270"/>
+    <row r="271">
+      <c r="A271" s="190" t="inlineStr">
         <is>
           <t>--- 6/6 监控小结 ---</t>
         </is>
       </c>
     </row>
-    <row r="177">
-      <c r="A177" s="191" t="inlineStr">
+    <row r="272">
+      <c r="A272" s="191" t="inlineStr">
         <is>
           <t>养殖: +1pp → 淘汰母猪加快+融资恶化→底部确认</t>
         </is>
       </c>
     </row>
-    <row r="178">
-      <c r="A178" s="191" t="inlineStr">
+    <row r="273">
+      <c r="A273" s="191" t="inlineStr">
         <is>
           <t>芯片: 0pp → AI长期利好vs估值过高抵消</t>
         </is>
       </c>
     </row>
-    <row r="179">
-      <c r="A179" s="191" t="inlineStr">
+    <row r="274">
+      <c r="A274" s="191" t="inlineStr">
         <is>
           <t>恒科: 0pp → AI叙事强化非事件</t>
         </is>
       </c>
     </row>
-    <row r="180">
-      <c r="A180" s="191" t="inlineStr">
+    <row r="275">
+      <c r="A275" s="191" t="inlineStr">
         <is>
           <t>银行: 0pp → 非农黑五已部分定价</t>
         </is>
       </c>
     </row>
-    <row r="181">
-      <c r="A181" s="191" t="inlineStr">
+    <row r="276">
+      <c r="A276" s="191" t="inlineStr">
         <is>
           <t>结论: 持仓不动。养殖左侧继续等待。</t>
         </is>
       </c>
     </row>
-    <row r="182">
-      <c r="A182" s="138" t="inlineStr">
+    <row r="277">
+      <c r="A277" s="138" t="inlineStr">
         <is>
           <t>--- 6/7 监控小结 ---</t>
         </is>
       </c>
     </row>
-    <row r="183">
-      <c r="A183" s="138" t="inlineStr">
+    <row r="278">
+      <c r="A278" s="138" t="inlineStr">
         <is>
           <t>养殖: +1pp → 集团"养一天赔一天"全体重抛售→去产能加速→周期底确认</t>
         </is>
       </c>
     </row>
-    <row r="184">
-      <c r="A184" s="138" t="inlineStr">
+    <row r="279">
+      <c r="A279" s="138" t="inlineStr">
         <is>
           <t>芯片: 0pp → AI基建长期利好(付鹏)vs摩尔定律瓶颈(宋鸿兵)抵消</t>
         </is>
       </c>
     </row>
-    <row r="185">
-      <c r="A185" s="138" t="inlineStr">
+    <row r="280">
+      <c r="A280" s="138" t="inlineStr">
         <is>
           <t>AI: 0pp → AI基建+应用加速确认，但无新事件级催化剂</t>
         </is>
       </c>
     </row>
-    <row r="186">
-      <c r="A186" s="138" t="inlineStr">
+    <row r="281">
+      <c r="A281" s="138" t="inlineStr">
         <is>
           <t>恒科: -1pp → 非农超预期→加息预期→黑五科技暴跌→利率敏感</t>
         </is>
       </c>
     </row>
-    <row r="187">
-      <c r="A187" s="138" t="inlineStr">
+    <row r="282">
+      <c r="A282" s="138" t="inlineStr">
         <is>
           <t>黄金: 0pp → 长期央行购金(27%储备)vs短期非农砸盘抵消</t>
         </is>
       </c>
     </row>
-    <row r="188">
-      <c r="A188" s="138" t="inlineStr">
+    <row r="283">
+      <c r="A283" s="138" t="inlineStr">
         <is>
           <t>银行: 0pp → 岩松笔记讨论15%年化，中性方法论</t>
         </is>
       </c>
     </row>
-    <row r="189">
-      <c r="A189" s="138" t="inlineStr">
+    <row r="284">
+      <c r="A284" s="138" t="inlineStr">
         <is>
           <t>结论: 持仓不动。养殖左侧继续等待。恒科短期注意利率风险。</t>
         </is>

--- a/持仓贝叶斯跟踪.xlsx
+++ b/持仓贝叶斯跟踪.xlsx
@@ -1727,7 +1727,6 @@
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>Hermes</author>
-    <author>叙事主线</author>
     <author>AI指导原则</author>
   </authors>
   <commentList>
@@ -1949,28 +1948,7 @@
 P值调整：0pp（已计入其他事件）</t>
       </text>
     </comment>
-    <comment ref="B116" authorId="1" shapeId="0">
-      <text>
-        <t xml:space="preserve">来源：用户2026-06-04独立判断
-逻辑链：
-1. 历史验证：每次危机→比特币暴跌（无避险价值）
-2. 黄金涨→比特币跌（流动性被黄金吸附）
-3. 美股涨→黄金跌→比特币也跌（被美股吸走）
-4. AI来了→资金有明确去处（芯片/AI基建）→比特币更没吸引力
-5. 最近一轮牛市验证：涨跌幅变小+跟美股完全同步=已非独立资产
-当前状态：维持。2020后第1次牛市(2021)，第2次牛市(2025最近)，周期规律+AI挤压=比特币上行空间越来越小
-对持仓影响：
-- 芯片/AI 利好：资金不去比特币就去AI，确认资金流向
-- 黄金 间接利好：比特币不再跟黄金抢流动性
-- 银行/有色/稀金 中性：不影响国内逻辑
-操作建议：
-- 不碰比特币/虚拟货币
-- 确认AI赛道的资金虹吸地位
-- 如果比特币暴跌→不是避险信号，是资金被更强的资产吸走了
-</t>
-      </text>
-    </comment>
-    <comment ref="A118" authorId="2" shapeId="0">
+    <comment ref="A179" authorId="1" shapeId="0">
       <text>
         <t xml:space="preserve">来源：用户2026-06-04确立，多个信源交叉确认
 核心逻辑：
@@ -1991,7 +1969,7 @@
 </t>
       </text>
     </comment>
-    <comment ref="A187" authorId="0" shapeId="0">
+    <comment ref="A248" authorId="0" shapeId="0">
       <text>
         <t xml:space="preserve">【来源】蒋宇飞抖音视频（2026-05-25）"未来5-10年的黄金赛道，深度拆解玻璃基板的万亿机遇"
 【信源评估】蒋宇飞⭐⭐⭐高置信度（有产业实操经验，多次验证预测准确）
@@ -2006,7 +1984,7 @@
 </t>
       </text>
     </comment>
-    <comment ref="A189" authorId="0" shapeId="0">
+    <comment ref="A250" authorId="0" shapeId="0">
       <text>
         <t>信息源：东方财富+新浪财经2026-06-02
 核心数据：
@@ -2019,7 +1997,7 @@
 结论：不建议加仓</t>
       </text>
     </comment>
-    <comment ref="A190" authorId="0" shapeId="0">
+    <comment ref="A251" authorId="0" shapeId="0">
       <text>
         <t>信息源：东方财富头条+新浪财经2026-06-02
 核心数据：
@@ -2034,7 +2012,7 @@
 结论：重点关注，强正向信号</t>
       </text>
     </comment>
-    <comment ref="A191" authorId="0" shapeId="0">
+    <comment ref="A252" authorId="0" shapeId="0">
       <text>
         <t xml:space="preserve">【来源】群联潘健成(产业高管)+蒋宇飞(6.1两长存储+5.18框架)+宋鸿兵(6.2摩尔定律终结)+周鸿祎(内存决定AI)+用户6.3洞察
 【逻辑链】
@@ -2057,7 +2035,7 @@
 </t>
       </text>
     </comment>
-    <comment ref="A192" authorId="0" shapeId="0">
+    <comment ref="A253" authorId="0" shapeId="0">
       <text>
         <t xml:space="preserve">【来源】蒋宇飞星光纯叠框架+宋鸿兵华为韬定律+用户"AI瓶颈是内存而非算力"
 【逻辑链】
@@ -2071,7 +2049,7 @@
 </t>
       </text>
     </comment>
-    <comment ref="A194" authorId="0" shapeId="0">
+    <comment ref="A255" authorId="0" shapeId="0">
       <text>
         <t xml:space="preserve">【标的】北京君正 300223
 【核心逻辑】存储+计算芯片，DRAM新工艺突破，车载存储市占率提升。A股年内+51%，市值772亿。港股二度IPO中。盈亏比4:1，存储赛道里最强。
@@ -2082,7 +2060,7 @@
 </t>
       </text>
     </comment>
-    <comment ref="A195" authorId="0" shapeId="0">
+    <comment ref="A256" authorId="0" shapeId="0">
       <text>
         <t xml:space="preserve">【标的】兆易创新 603986
 【核心逻辑】NOR Flash国内龙头，DRAM布局中。存储涨价直接受益。盈亏比3.5:1。
@@ -2093,7 +2071,7 @@
 </t>
       </text>
     </comment>
-    <comment ref="A196" authorId="0" shapeId="0">
+    <comment ref="A257" authorId="0" shapeId="0">
       <text>
         <t xml:space="preserve">【标的】江波龙 301308
 【核心逻辑】存储模组+主控芯片，国产替代核心标的。盈亏比3.5:1。
@@ -2425,7 +2403,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:H284"/>
+  <dimension ref="A1:H345"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6171875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="18" customWidth="1" style="138" min="1" max="8"/>
@@ -2897,518 +2875,436 @@
       </c>
     </row>
     <row r="40" ht="16.5" customHeight="1" s="139">
-      <c r="A40" s="138" t="inlineStr">
-        <is>
-          <t>每个操作都有来龙去脉：为什么买/买多少/什么时候进/什么时候出/风控在哪</t>
-        </is>
-      </c>
-    </row>
-    <row r="41" ht="16.5" customHeight="1" s="139"/>
+      <c r="A40" s="329" t="inlineStr">
+        <is>
+          <t>【Hermes+小龙多轮联合审核结论 2026-06-07】</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="16.5" customHeight="1" s="139">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>① 账修正：方案总消耗88%但现金只有50%，缺口38%。补法=卖恒科2.5%+有色稀金5%+养殖减半12.5%+芯片可选5%+未来收入。方案必须标注资金来源</t>
+        </is>
+      </c>
+    </row>
     <row r="42" ht="16.5" customHeight="1" s="139">
-      <c r="A42" s="293" t="inlineStr">
-        <is>
-          <t>一、资金总览</t>
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>② 堆叠45%分三批进：第一批15%(跌15%触发)→第二批15%(再跌10%或横盘2月)→第三批15%(产业验证)。涨20%后分两批加速到30%。30%翻倍&gt;45%被洗</t>
         </is>
       </c>
     </row>
     <row r="43" ht="16.5" customHeight="1" s="139">
-      <c r="A43" s="330" t="inlineStr">
-        <is>
-          <t>持仓50%=养殖25%|芯片10%|电池5%|恒科2.5%|有色2.5%|稀金2.5%|银行1.5%</t>
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>③ Plan B：锁到2027-01-31（三个月窗口：11月选举+12月圣诞行情+1月调仓）。逾期进40%留20%。替代触发三选一：PE&lt;40/蒋宇飞说进/连阴3月</t>
         </is>
       </c>
     </row>
     <row r="44" ht="16.5" customHeight="1" s="139">
-      <c r="A44" s="138" t="inlineStr">
-        <is>
-          <t>现金50%=锁定40%(等11月大跌进长电25+通富20)+可动用10%</t>
-        </is>
-      </c>
-    </row>
-    <row r="45" ht="16.5" customHeight="1" s="139"/>
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>④ 机器人4%不变：562500不是纯机器人暴露（成分公司机器人营收&lt;20%）。替代：加科创AI(027048)6%覆盖AI+机器人+算力，合计10%科技前沿</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="16.5" customHeight="1" s="139">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>⑤ 恒科清：P=27%三条信号同向。蒋宇飞"传统互联网老灯鼓"是行业判断，"腾讯黄金坑"是个股判断。恒科≠腾讯（腾讯只占30%）。看好腾讯应买个股</t>
+        </is>
+      </c>
+    </row>
     <row r="46" ht="16.5" customHeight="1" s="139">
-      <c r="A46" s="329" t="inlineStr">
-        <is>
-          <t>二、蒋宇飞「星光纯叠」框架（顶级置信度）</t>
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>⑥ MLCC标的：风华高科(000636)200股≈4500元。MLCC营收占比58%，最接近纯暴露。不买科技ETF凑合。含恒科清出2.5%→MLCC从3%→5.5%</t>
         </is>
       </c>
     </row>
     <row r="47" ht="16.5" customHeight="1" s="139">
-      <c r="A47" s="138" t="inlineStr">
-        <is>
-          <t>AI基建10年=存力→算力→运力。节奏：光贯穿2026→存储2026吃肉→堆叠2027大放。2027算力长城=升腾+长鑫+DeepSeek</t>
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>⑦ P=75%四源交叉确认：达利欧(宏观)+李大霄(A股)+用户(事件)+蒋宇飞(产业27条)。四套独立框架交集→P可能估低，不是'全押蒋宇飞'</t>
         </is>
       </c>
     </row>
     <row r="48" ht="16.5" customHeight="1" s="139">
-      <c r="A48" s="138" t="inlineStr">
-        <is>
-          <t>风控提示：存储将来跌80% | 消费级2027见顶 | HBM分销修正70-80% | 纪律：三成追热点七成等回调</t>
-        </is>
-      </c>
-    </row>
-    <row r="49" ht="16.5" customHeight="1" s="139"/>
+      <c r="A48" t="inlineStr"/>
+    </row>
+    <row r="49" ht="16.5" customHeight="1" s="139">
+      <c r="A49" s="329" t="inlineStr">
+        <is>
+          <t>修正后完整方案：</t>
+        </is>
+      </c>
+    </row>
     <row r="50" ht="15" customHeight="1" s="139">
-      <c r="A50" s="329" t="inlineStr">
-        <is>
-          <t>三、各赛道详细操作计划</t>
-        </is>
-      </c>
-    </row>
-    <row r="51" ht="15" customHeight="1" s="139"/>
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>A.现在MLCC(风华)5.5% B.Q4 HBM5%+堆叠先手5% C.11月堆叠三批45% D.PlanB(1/31)进40%留20% E.2027升腾8%+机器人4%+玻璃2% F.科创AI(027048)6%</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="15" customHeight="1" s="139">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>持仓调整：养殖25%→12.5% 恒科清 有色+稀金清 芯片可选减半 电池+银行不动 保留现金~10%</t>
+        </is>
+      </c>
+    </row>
     <row r="52" ht="77.59999999999999" customHeight="1" s="139">
-      <c r="A52" s="331" t="inlineStr">
-        <is>
-          <t>▶ MLCC被动元件 3% 观察仓</t>
+      <c r="A52" s="329" t="inlineStr">
+        <is>
+          <t>【Hermes+小龙多轮联合审核结论 2026-06-07】</t>
         </is>
       </c>
     </row>
     <row r="53" ht="17.15" customHeight="1" s="139">
       <c r="A53" s="138" t="inlineStr">
         <is>
-          <t>为什么买：蒋宇飞4月底预测MLCC启动，5月即涨。说"不亚于半年前荐存储"（存储半年涨13倍）。国巨成台湾首富。日韩停产→中国MLCC爆发。行情到2027-H1</t>
+          <t>① 账修正：方案总消耗88%但现金只有50%，缺口38%。补法=卖恒科2.5%+有色稀金5%+养殖减半12.5%+芯片可选5%+未来收入。方案必须标注资金来源</t>
         </is>
       </c>
     </row>
     <row r="54" ht="26.85" customHeight="1" s="139">
       <c r="A54" s="138" t="inlineStr">
         <is>
-          <t>买什么：风华高科/三环集团等A股MLCC概念股</t>
+          <t>② 堆叠45%分三批进：第一批15%(跌15%触发)→第二批15%(再跌10%或横盘2月)→第三批15%(产业验证)。涨20%后分两批加速到30%。30%翻倍&gt;45%被洗</t>
         </is>
       </c>
     </row>
     <row r="55" ht="29.85" customHeight="1" s="139">
       <c r="A55" s="138" t="inlineStr">
         <is>
-          <t>什么时候进：现在（6-7月）</t>
+          <t>③ Plan B：锁到2027-01-31（三个月窗口：11月选举+12月圣诞行情+1月调仓）。逾期进40%留20%。替代触发三选一：PE&lt;40/蒋宇飞说进/连阴3月</t>
         </is>
       </c>
     </row>
     <row r="56" ht="29.85" customHeight="1" s="139">
       <c r="A56" s="138" t="inlineStr">
         <is>
-          <t>什么时候出：11-12月必须清仓（蒋宇飞说年底见顶）。资金转HBM或堆叠先手</t>
+          <t>④ 机器人4%不变：562500不是纯机器人暴露（成分公司机器人营收&lt;20%）。替代：加科创AI(027048)6%覆盖AI+机器人+算力，合计10%科技前沿</t>
         </is>
       </c>
     </row>
     <row r="57" ht="15" customHeight="1" s="139">
       <c r="A57" s="138" t="inlineStr">
         <is>
-          <t>风控：只3%亏了不痛。年底不管赚亏都清</t>
-        </is>
-      </c>
-    </row>
-    <row r="58" ht="15" customHeight="1" s="139"/>
+          <t>⑤ 恒科清：P=27%三条信号同向。蒋宇飞"传统互联网老灯鼓"是行业判断，"腾讯黄金坑"是个股判断。恒科≠腾讯（腾讯只占30%）。看好腾讯应买个股</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="15" customHeight="1" s="139">
+      <c r="A58" s="138" t="inlineStr">
+        <is>
+          <t>⑥ MLCC标的：风华高科(000636)200股≈4500元。MLCC营收占比58%，最接近纯暴露。不买科技ETF凑合。含恒科清出2.5%→MLCC从3%→5.5%</t>
+        </is>
+      </c>
+    </row>
     <row r="59" ht="58.2" customHeight="1" s="139">
-      <c r="A59" s="329" t="inlineStr">
-        <is>
-          <t>【Hermes+小龙联合审核结论 2026-06-07】</t>
+      <c r="A59" s="138" t="inlineStr">
+        <is>
+          <t>⑦ P=75%四源交叉确认：达利欧(宏观)+李大霄(A股)+用户(事件)+蒋宇飞(产业27条)。四套独立框架交集→P可能估低，不是'全押蒋宇飞'</t>
         </is>
       </c>
     </row>
     <row r="60" ht="173.1" customHeight="1" s="139">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>① 恒科2.5%清仓→转MLCC(3%→5.5%)。理由：P=27%三条信号同向，蒋宇飞说传统互联网是老灯鼓</t>
-        </is>
-      </c>
+      <c r="A60" s="138" t="inlineStr"/>
     </row>
     <row r="61" ht="15" customHeight="1" s="139">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>② 堆叠45%分三批进：第一批15%(跌15%触发)→第二批15%(再跌或横盘2月)→第三批15%(产业验证)</t>
+      <c r="A61" s="329" t="inlineStr">
+        <is>
+          <t>修正后完整方案：</t>
         </is>
       </c>
     </row>
     <row r="62" ht="15" customHeight="1" s="139">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>③ Plan B：锁到2027-01-31，逾期进则进40%留20%继续等。替代触发三选一：芯片PE&lt;40分位/蒋宇飞说现在进/月线连阴3月</t>
+      <c r="A62" s="138" t="inlineStr">
+        <is>
+          <t>A.现在MLCC(风华)5.5% B.Q4 HBM5%+堆叠先手5% C.11月堆叠三批45% D.PlanB(1/31)进40%留20% E.2027升腾8%+机器人4%+玻璃2% F.科创AI(027048)6%</t>
         </is>
       </c>
     </row>
     <row r="63" ht="48.5" customHeight="1" s="139">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>④ MLCC标的：风华高科200股(~4500元)，最接近MLCC纯暴露(MLCC营收占比58%)</t>
+      <c r="A63" s="138" t="inlineStr">
+        <is>
+          <t>持仓调整：养殖25%→12.5% 恒科清 有色+稀金清 芯片可选减半 电池+银行不动 保留现金~10%</t>
         </is>
       </c>
     </row>
     <row r="64" ht="48.5" customHeight="1" s="139">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>⑤ 机器人4%不变（无纯暴露工具）+ 科创AI027048加仓6%覆盖AI+机器人+算力</t>
+      <c r="A64" s="329" t="inlineStr">
+        <is>
+          <t>【Hermes+小龙多轮联合审核结论 2026-06-07】</t>
         </is>
       </c>
     </row>
     <row r="65" ht="64.15000000000001" customHeight="1" s="139">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>⑥ 资金来源：现有现金50%+卖恒科2.5%+卖有色稀金5%+养殖减半12.5%+未来收入≈85%。两年跨度3%误差可接受</t>
+      <c r="A65" s="138" t="inlineStr">
+        <is>
+          <t>① 账修正：方案总消耗88%但现金只有50%，缺口38%。补法=卖恒科2.5%+有色稀金5%+养殖减半12.5%+芯片可选5%+未来收入。方案必须标注资金来源</t>
         </is>
       </c>
     </row>
     <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>⑦ P=75%被四源交叉确认(达利欧+李大霄+蒋宇飞+用户)→可能估低。小龙承认不是'全押蒋宇飞'</t>
+      <c r="A66" s="138" t="inlineStr">
+        <is>
+          <t>② 堆叠45%分三批进：第一批15%(跌15%触发)→第二批15%(再跌10%或横盘2月)→第三批15%(产业验证)。涨20%后分两批加速到30%，不是"不再加"。30%翻倍&gt;45%被洗</t>
         </is>
       </c>
     </row>
     <row r="67" ht="17.15" customHeight="1" s="139">
-      <c r="A67" s="332" t="inlineStr">
-        <is>
-          <t>▶ HBM产业链 5%</t>
+      <c r="A67" s="138" t="inlineStr">
+        <is>
+          <t>③ Plan B：锁到2027-01-31（三个月窗口：11月选举+12月圣诞行情+1月调仓）。逾期进40%留20%。替代触发三选一：PE&lt;40分位/蒋宇飞说进/月线连阴3月</t>
         </is>
       </c>
     </row>
     <row r="68" ht="48.5" customHeight="1" s="139">
       <c r="A68" s="138" t="inlineStr">
         <is>
-          <t>为什么买：蒋宇飞"HBM未来1.5-2.5年波涛汹涌""Q4-Q1波澜壮阔热潮"。HBM是AI技术含量最高的存储，目前最紧缺</t>
+          <t>④ 机器人4%不变：562500不是纯机器人暴露（成分公司机器人营收&lt;20%）。替代方案：加科创AI(027048)6%覆盖AI+机器人+算力，合计10%科技前沿暴露</t>
         </is>
       </c>
     </row>
     <row r="69" ht="32.8" customHeight="1" s="139">
       <c r="A69" s="138" t="inlineStr">
         <is>
-          <t>什么时候进：2026-Q4（10-12月），MLCC清仓后资金转入</t>
+          <t>⑤ 恒科清：P=27%三条信号同向。蒋宇飞"传统互联网老灯鼓"是行业判断，"腾讯黄金坑"是个股判断。恒科≠腾讯（腾讯只占30%）。看好腾讯应买个股。清出2.5%转MLCC</t>
         </is>
       </c>
     </row>
     <row r="70" ht="48.5" customHeight="1" s="139">
       <c r="A70" s="138" t="inlineStr">
         <is>
-          <t>什么时候出：2027-Q1热潮结束观察。蒋宇飞说热潮在四季度至明年一季度展开</t>
+          <t>⑥ MLCC标的：风华高科(000636)200股≈4500元。MLCC营收占比58%，最接近纯暴露。不买科技ETF凑合</t>
         </is>
       </c>
     </row>
     <row r="71" ht="32.8" customHeight="1" s="139">
       <c r="A71" s="138" t="inlineStr">
         <is>
-          <t>风控：5%不大。Q4不启动就继续等，不急着进</t>
-        </is>
-      </c>
-    </row>
-    <row r="72"/>
+          <t>⑦ P=75%四源交叉确认：达利欧(宏观泡沫)+李大霄(A股择时)+用户(中期选举事件)+蒋宇飞(产业27条)。四套独立框架交集→P可能估低，不是'全押蒋宇飞'</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="138" t="inlineStr"/>
+    </row>
     <row r="73" ht="121.6" customHeight="1" s="139">
       <c r="A73" s="329" t="inlineStr">
         <is>
-          <t>▶ 堆叠/先进封装 长电25%+通富20%=45%（核心重仓）</t>
+          <t>修正后完整方案：</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="138" t="inlineStr">
         <is>
-          <t>为什么买：蒋宇飞27条视频反复强调"未来两年最大风口""改变家族命运""躺赢"。堆叠=CoWoS/2.5D/3D=突破存算一体。封装成本占存储芯片20%。P=75%顶级信源验证</t>
+          <t>A.现在MLCC(风华)5.5% B.Q4 HBM5%+堆叠先手5% C.11月堆叠三批45% D.PlanB(1/31)进40%留20% E.2027升腾8%+机器人4%+玻璃2% F.科创AI(027048)6% G.保留~10%</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="138" t="inlineStr">
         <is>
-          <t>为什么长电+通富：长电=全球第三大封测，2.5D/3D量产，客户高通/海思/TI。通富=AMD封测全线突破，MI300X参与，不可替代</t>
+          <t>持仓调整：养殖25%→12.5%(等猪周期) 恒科清 有色+稀金清 芯片可选减半 电池+银行不动</t>
         </is>
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="138" t="inlineStr">
-        <is>
-          <t>什么时候进：等11月美股大跌15%+。触发三选一：①达利欧泡沫落地 ②纳指破200日均线 ③中期选举大跌。全不进不砸</t>
+      <c r="A76" s="329" t="inlineStr">
+        <is>
+          <t>【Hermes+小龙多轮联合审核结论 2026-06-07】</t>
         </is>
       </c>
     </row>
     <row r="77" ht="15" customHeight="1" s="139">
       <c r="A77" s="138" t="inlineStr">
         <is>
-          <t>先手仓位：Q4先建5%（长电3%+通富2%），等回调后进大仓位。符合蒋宇飞"三成追七成等"纪律</t>
+          <t>① 账修正：方案总消耗88%但现金只有50%，缺口38%。来源=卖恒科2.5%+有色稀金5%+养殖减半12.5%+芯片可选5%+未来收入。必须标注资金来源</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="138" t="inlineStr">
         <is>
-          <t>什么时候出：2027-H2堆叠大放→长期持有。蒋宇飞说堆叠是10年风口</t>
+          <t>② 恒科清：P=27%三条信号同向，恒科≠腾讯(腾讯只占30%)。看好腾讯应买个股。清出2.5%转MLCC→5.5%</t>
         </is>
       </c>
     </row>
     <row r="79" ht="39.55" customHeight="1" s="139">
       <c r="A79" s="138" t="inlineStr">
         <is>
-          <t>风控：45%很重。必须等15%+回调才进（安全边际）。不到位置不砸。蒋宇飞说"回调就是你的机会"</t>
-        </is>
-      </c>
-    </row>
-    <row r="80" ht="39.55" customHeight="1" s="139"/>
+          <t>③ 堆叠45%分三批：第一批15%(跌15%触发)→第二批15%(再跌10%或横盘2月)→第三批15%(产业验证)。涨20%后分两批加速到30%，不是"不再加"</t>
+        </is>
+      </c>
+    </row>
+    <row r="80" ht="39.55" customHeight="1" s="139">
+      <c r="A80" s="138" t="inlineStr">
+        <is>
+          <t>④ Plan B：锁到2027-01-31(三个月窗口：11月选举+12月圣诞行情+1月调仓)。逾期进40%留20%。替代触发三选一：PE&lt;40/蒋宇飞说进/连阴3月</t>
+        </is>
+      </c>
+    </row>
     <row r="81" ht="52.2" customHeight="1" s="139">
-      <c r="A81" s="332" t="inlineStr">
-        <is>
-          <t>▶ 国产算力/升腾链 10%</t>
+      <c r="A81" s="138" t="inlineStr">
+        <is>
+          <t>⑤ 机器人4%不变：562500不是纯机器人暴露(成分公司机器人营收&lt;20%)。替代：加科创AI(027048)6%覆盖AI+机器人+算力，合计10%科技前沿</t>
         </is>
       </c>
     </row>
     <row r="82" ht="52.2" customHeight="1" s="139">
       <c r="A82" s="138" t="inlineStr">
         <is>
-          <t>为什么买：蒋宇飞"2027算力长城最闪亮""升腾链2027爆发""升腾950明年出货"。工信部要求支持国产芯片</t>
+          <t>⑥ MLCC标的：风华高科(000636)200股≈4500元。MLCC营收占比58%，最接近纯暴露。不买科技ETF凑合</t>
         </is>
       </c>
     </row>
     <row r="83" ht="64.90000000000001" customHeight="1" s="139">
       <c r="A83" s="138" t="inlineStr">
         <is>
-          <t>什么时候进：2027年。触发：华为升腾950大批出货/工信部政策加码</t>
+          <t>⑦ P=75%四源交叉确认：达利欧(宏观)+李大霄(A股)+用户(事件)+蒋宇飞(产业)。四套独立框架交集→可能估低，不是'全押蒋宇飞'</t>
         </is>
       </c>
     </row>
     <row r="84" ht="15" customHeight="1" s="139">
       <c r="A84" s="138" t="inlineStr">
         <is>
-          <t>风控：等2027，当前只看不动</t>
-        </is>
-      </c>
-    </row>
-    <row r="85" ht="15" customHeight="1" s="139"/>
+          <t>⑧ 风控：30%仓位在正确方向翻倍&gt;45%满仓被洗。仓位轻=拿得住=吃到全涨幅。这是小龙的核心风控逻辑</t>
+        </is>
+      </c>
+    </row>
+    <row r="85" ht="15" customHeight="1" s="139">
+      <c r="A85" s="138" t="inlineStr"/>
+    </row>
     <row r="86" ht="26.85" customHeight="1" s="139">
-      <c r="A86" s="332" t="inlineStr">
-        <is>
-          <t>▶ 机器人(物理AI) 4%</t>
+      <c r="A86" s="329" t="inlineStr">
+        <is>
+          <t>修正后完整方案：</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="138" t="inlineStr">
         <is>
-          <t>为什么买：用户判断机器人&gt;黄金&gt;比特币。蒋宇飞验证："未来经济三层=物理人→钢铁机器人→网络agent"。宇树科技73天过会</t>
+          <t>A. 现在：MLCC(风华高科)5.5%  B. Q4：HBM5%+堆叠先手5%  C. 11月：堆叠分三批45%  D. Plan B(1/31)：进40%留20%</t>
         </is>
       </c>
     </row>
     <row r="88" ht="39.55" customHeight="1" s="139">
       <c r="A88" s="138" t="inlineStr">
         <is>
-          <t>什么时候进：2027冬开始逐步建。中长期赛道，不急</t>
+          <t>E. 2027：升腾8%+机器人4%+玻璃2%  F. 科创AI(027048)6%  G. 保留现金~10%</t>
         </is>
       </c>
     </row>
     <row r="89" ht="26.85" customHeight="1" s="139">
       <c r="A89" s="138" t="inlineStr">
         <is>
-          <t>风控：4%不大，判断错误损失可控</t>
+          <t>持仓调整：养殖25%→12.5%  恒科清  有色+稀金清  芯片可选减半  电池+银行不动</t>
         </is>
       </c>
     </row>
     <row r="90" ht="26.85" customHeight="1" s="139"/>
     <row r="91" ht="39.55" customHeight="1" s="139">
-      <c r="A91" s="332" t="inlineStr">
-        <is>
-          <t>▶ 玻璃基板 3%</t>
+      <c r="A91" s="329" t="inlineStr">
+        <is>
+          <t>【Hermes+小龙多轮联合审核结论 2026-06-07】</t>
         </is>
       </c>
     </row>
     <row r="92" ht="26.85" customHeight="1" s="139">
       <c r="A92" s="138" t="inlineStr">
         <is>
-          <t>为什么买：蒋宇飞"被严重低估即将爆发""两三年热点""业绩2027-H2释放""大规模2028"。两个爆发点：封装+存储</t>
+          <t>① 恒科2.5%清仓→转MLCC。理由：P=27%三条信号同向，蒋宇飞说传统互联网是老灯鼓。钱从3%→5.5%</t>
         </is>
       </c>
     </row>
     <row r="93" ht="26.85" customHeight="1" s="139">
       <c r="A93" s="138" t="inlineStr">
         <is>
-          <t>什么时候进：2027年等业绩释放。蒋宇飞说"消息还在送验阶段"</t>
+          <t>② 堆叠45%分三批进：第一批15%(跌15%触发)→第二批15%(再跌或横盘2月)→第三批15%(产业验证)。涨20%后重新评估</t>
         </is>
       </c>
     </row>
     <row r="94" ht="39.55" customHeight="1" s="139">
       <c r="A94" s="138" t="inlineStr">
         <is>
-          <t>风控：3%观察仓，等消息确认</t>
-        </is>
-      </c>
-    </row>
-    <row r="95" ht="39.55" customHeight="1" s="139"/>
+          <t>③ Plan B：锁到2027-01-31，逾期进则进40%留20%继续等。替代触发三选一：芯片PE&lt;40/蒋宇飞说现在进/月线连阴3月</t>
+        </is>
+      </c>
+    </row>
+    <row r="95" ht="39.55" customHeight="1" s="139">
+      <c r="A95" s="138" t="inlineStr">
+        <is>
+          <t>④ MLCC标的：风华高科(000636)200股≈4500元。MLCC营收占比58%，最接近纯暴露。不含科技ETF凑合</t>
+        </is>
+      </c>
+    </row>
     <row r="96" ht="15" customHeight="1" s="139">
-      <c r="A96" s="329" t="inlineStr">
-        <is>
-          <t>四、进钱节奏时间线</t>
-        </is>
-      </c>
-    </row>
-    <row r="97" ht="15" customHeight="1" s="139"/>
+      <c r="A96" s="138" t="inlineStr">
+        <is>
+          <t>⑤ 机器人4%不变（无纯暴露工具）+ 科创AI(027048)加仓6%覆盖AI+机器人+算力。合计10%科技前沿暴露</t>
+        </is>
+      </c>
+    </row>
+    <row r="97" ht="15" customHeight="1" s="139">
+      <c r="A97" s="138" t="inlineStr">
+        <is>
+          <t>⑥ 资金来源：现金50%+卖恒科2.5%+卖有色稀金5%+养殖减半12.5%+芯片可选5%=70-85%。方案消耗75%够覆盖</t>
+        </is>
+      </c>
+    </row>
     <row r="98" ht="18.65" customHeight="1" s="139">
-      <c r="A98" s="333" t="inlineStr">
-        <is>
-          <t>时间</t>
-        </is>
-      </c>
-      <c r="B98" s="333" t="inlineStr">
-        <is>
-          <t>进钱操作</t>
-        </is>
-      </c>
-      <c r="C98" s="333" t="inlineStr">
-        <is>
-          <t>持仓操作</t>
-        </is>
-      </c>
-      <c r="D98" s="333" t="inlineStr">
-        <is>
-          <t>清仓退出</t>
-        </is>
-      </c>
-      <c r="E98" s="333" t="inlineStr">
-        <is>
-          <t>可用现金</t>
+      <c r="A98" s="138" t="inlineStr">
+        <is>
+          <t>⑦ P=75%被四源交叉确认(达利欧+李大霄+蒋宇飞+用户)→可能估低。不是'全押蒋宇飞'是四套独立框架交集</t>
         </is>
       </c>
     </row>
     <row r="99" ht="15" customHeight="1" s="139">
       <c r="A99" s="138" t="inlineStr">
         <is>
-          <t>现在-7月</t>
-        </is>
-      </c>
-      <c r="B99" s="138" t="inlineStr">
-        <is>
-          <t>MLCC3%建仓</t>
-        </is>
-      </c>
-      <c r="C99" s="138" t="inlineStr">
-        <is>
-          <t>芯片10%不动(虚P+3pp)</t>
-        </is>
-      </c>
-      <c r="D99" s="138" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E99" s="138" t="inlineStr">
-        <is>
-          <t>7%</t>
+          <t>⑧ 风控底线：45%堆叠即使分三批也很重。如果第一批涨了20%，后两批进不进看v型反弹还是死猫反弹。30%仓位翻倍就够</t>
         </is>
       </c>
     </row>
     <row r="100" ht="15" customHeight="1" s="139">
       <c r="A100" s="138" t="inlineStr">
         <is>
-          <t>8-10月</t>
-        </is>
-      </c>
-      <c r="B100" s="138" t="inlineStr">
-        <is>
-          <t>MLCC持有</t>
-        </is>
-      </c>
-      <c r="C100" s="138" t="inlineStr">
-        <is>
-          <t>观察HBM信号</t>
-        </is>
-      </c>
-      <c r="D100" s="138" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E100" s="138" t="inlineStr">
-        <is>
-          <t>7%</t>
+          <t>⑨ 机会成本：堆叠(75%)&gt;MLCC(中高)&gt;HBM(高)&gt;机器人(中)&gt;CPU(中)&gt;玻璃基板(中低)。按确定性×时间窗口排序</t>
         </is>
       </c>
     </row>
     <row r="101" ht="26.85" customHeight="1" s="139">
       <c r="A101" s="138" t="inlineStr">
         <is>
-          <t>11月大跌</t>
-        </is>
-      </c>
-      <c r="B101" s="138" t="inlineStr">
-        <is>
-          <t>长电25%+通富20%大砸</t>
-        </is>
-      </c>
-      <c r="C101" s="138" t="inlineStr">
-        <is>
-          <t>MLCC清→HBM5%+堆叠先手5%</t>
-        </is>
-      </c>
-      <c r="D101" s="138" t="inlineStr">
-        <is>
-          <t>MLCC清</t>
-        </is>
-      </c>
-      <c r="E101" s="138" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-    </row>
-    <row r="102" ht="15" customHeight="1" s="139">
-      <c r="A102" s="138" t="inlineStr">
-        <is>
-          <t>11月没大跌</t>
-        </is>
-      </c>
-      <c r="B102" s="138" t="inlineStr">
-        <is>
-          <t>堆叠先手5%(长电3+通富2)</t>
-        </is>
-      </c>
-      <c r="C102" s="138" t="inlineStr">
-        <is>
-          <t>MLCC清→等</t>
-        </is>
-      </c>
-      <c r="D102" s="138" t="inlineStr">
-        <is>
-          <t>MLCC清</t>
-        </is>
-      </c>
-      <c r="E102" s="138" t="inlineStr">
-        <is>
-          <t>0-2%</t>
-        </is>
-      </c>
-    </row>
+          <t>每个操作都有来龙去脉：为什么买/买多少/什么时候进/什么时候出/风控在哪</t>
+        </is>
+      </c>
+    </row>
+    <row r="102" ht="15" customHeight="1" s="139"/>
     <row r="103" ht="26.85" customHeight="1" s="139">
-      <c r="A103" s="138" t="inlineStr">
-        <is>
-          <t>2027-Q1</t>
-        </is>
-      </c>
-      <c r="B103" s="138" t="inlineStr">
-        <is>
-          <t>HBM持有</t>
-        </is>
-      </c>
-      <c r="C103" s="138" t="inlineStr">
-        <is>
-          <t>堆叠先手持有</t>
-        </is>
-      </c>
-      <c r="D103" s="138" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E103" s="138" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="A103" s="293" t="inlineStr">
+        <is>
+          <t>一、资金总览</t>
         </is>
       </c>
     </row>
     <row r="104" ht="26.85" customHeight="1" s="139">
-      <c r="A104" s="138" t="inlineStr">
-        <is>
-          <t>2027-H2</t>
+      <c r="A104" s="330" t="inlineStr">
+        <is>
+          <t>持仓50%=养殖25%|芯片10%|电池5%|恒科2.5%|有色2.5%|稀金2.5%|银行1.5%</t>
         </is>
       </c>
     </row>
     <row r="105" ht="26.85" customHeight="1" s="139">
       <c r="A105" s="138" t="inlineStr">
         <is>
-          <t>2027冬</t>
+          <t>现金50%=锁定40%(等11月大跌进长电25+通富20)+可动用10%</t>
         </is>
       </c>
     </row>
@@ -3416,168 +3312,610 @@
     <row r="107" ht="15" customHeight="1" s="139">
       <c r="A107" s="329" t="inlineStr">
         <is>
-          <t>⚡ 一句话：MLCC3%小试→Q4 HBM5%+堆叠先手5%→11月大跌长电25%+通富20%→2027堆叠躺赢</t>
+          <t>二、蒋宇飞「星光纯叠」框架（顶级置信度）</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="138" t="inlineStr">
         <is>
-          <t>风控：45%重仓必须等15%+回调 | MLCC年底必清 | 蒋宇飞纪律"三成追七成等"</t>
-        </is>
-      </c>
-    </row>
-    <row r="109" ht="15" customHeight="1" s="139"/>
+          <t>AI基建10年=存力→算力→运力。节奏：光贯穿2026→存储2026吃肉→堆叠2027大放。2027算力长城=升腾+长鑫+DeepSeek</t>
+        </is>
+      </c>
+    </row>
+    <row r="109" ht="15" customHeight="1" s="139">
+      <c r="A109" s="138" t="inlineStr">
+        <is>
+          <t>风控提示：存储将来跌80% | 消费级2027见顶 | HBM分销修正70-80% | 纪律：三成追热点七成等回调</t>
+        </is>
+      </c>
+    </row>
     <row r="110" ht="26.85" customHeight="1" s="139"/>
-    <row r="111" ht="26.85" customHeight="1" s="139"/>
-    <row r="112" ht="26.85" customHeight="1" s="139">
-      <c r="A112" s="148" t="inlineStr">
-        <is>
-          <t>🔥 叙事主线（四条）</t>
-        </is>
-      </c>
-      <c r="B112" s="149" t="n"/>
-      <c r="C112" s="149" t="n"/>
-      <c r="D112" s="149" t="n"/>
-      <c r="E112" s="149" t="n"/>
-      <c r="F112" s="149" t="n"/>
-      <c r="G112" s="149" t="n"/>
-      <c r="H112" s="150" t="n"/>
-    </row>
+    <row r="111" ht="26.85" customHeight="1" s="139">
+      <c r="A111" s="329" t="inlineStr">
+        <is>
+          <t>三、各赛道详细操作计划</t>
+        </is>
+      </c>
+    </row>
+    <row r="112" ht="26.85" customHeight="1" s="139"/>
     <row r="113" ht="26.85" customHeight="1" s="139">
-      <c r="A113" s="325" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  辅助仓位: 玻璃基板5% | 算力出海5%</t>
-        </is>
-      </c>
-      <c r="B113" s="326" t="n"/>
-      <c r="C113" s="326" t="n"/>
-      <c r="D113" s="326" t="n"/>
-      <c r="E113" s="326" t="n"/>
-      <c r="F113" s="326" t="n"/>
-      <c r="G113" s="326" t="n"/>
-      <c r="H113" s="325" t="n"/>
+      <c r="A113" s="331" t="inlineStr">
+        <is>
+          <t>▶ MLCC被动元件 3% 观察仓</t>
+        </is>
+      </c>
     </row>
     <row r="114" ht="26.85" customHeight="1" s="139">
-      <c r="A114" s="325" t="n"/>
-      <c r="B114" s="326" t="n"/>
-      <c r="C114" s="326" t="n"/>
-      <c r="D114" s="326" t="n"/>
-      <c r="E114" s="326" t="n"/>
-      <c r="F114" s="326" t="n"/>
-      <c r="G114" s="326" t="n"/>
-      <c r="H114" s="325" t="n"/>
+      <c r="A114" s="138" t="inlineStr">
+        <is>
+          <t>为什么买：蒋宇飞4月底预测MLCC启动，5月即涨。说"不亚于半年前荐存储"（存储半年涨13倍）。国巨成台湾首富。日韩停产→中国MLCC爆发。行情到2027-H1</t>
+        </is>
+      </c>
     </row>
     <row r="115" ht="26.85" customHeight="1" s="139">
-      <c r="A115" s="334" t="inlineStr">
-        <is>
-          <t>三、核心仓位汇总表</t>
-        </is>
-      </c>
-      <c r="B115" s="326" t="n"/>
-      <c r="C115" s="326" t="n"/>
-      <c r="D115" s="326" t="n"/>
-      <c r="E115" s="326" t="n"/>
-      <c r="F115" s="326" t="n"/>
-      <c r="G115" s="326" t="n"/>
-      <c r="H115" s="325" t="n"/>
+      <c r="A115" s="138" t="inlineStr">
+        <is>
+          <t>买什么：风华高科/三环集团等A股MLCC概念股</t>
+        </is>
+      </c>
     </row>
     <row r="116" ht="15" customHeight="1" s="139">
       <c r="A116" s="138" t="inlineStr">
         <is>
+          <t>什么时候进：现在（6-7月）</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="138" t="inlineStr">
+        <is>
+          <t>什么时候出：11-12月必须清仓（蒋宇飞说年底见顶）。资金转HBM或堆叠先手</t>
+        </is>
+      </c>
+    </row>
+    <row r="118" ht="15" customHeight="1" s="139">
+      <c r="A118" s="138" t="inlineStr">
+        <is>
+          <t>风控：只3%亏了不痛。年底不管赚亏都清</t>
+        </is>
+      </c>
+    </row>
+    <row r="119" ht="15" customHeight="1" s="139"/>
+    <row r="120" ht="26.85" customHeight="1" s="139">
+      <c r="A120" s="329" t="inlineStr">
+        <is>
+          <t>【Hermes+小龙联合审核结论 2026-06-07】</t>
+        </is>
+      </c>
+    </row>
+    <row r="121" ht="26.85" customHeight="1" s="139">
+      <c r="A121" s="138" t="inlineStr">
+        <is>
+          <t>① 恒科2.5%清仓→转MLCC(3%→5.5%)。理由：P=27%三条信号同向，蒋宇飞说传统互联网是老灯鼓</t>
+        </is>
+      </c>
+    </row>
+    <row r="122" ht="15" customHeight="1" s="139">
+      <c r="A122" s="138" t="inlineStr">
+        <is>
+          <t>② 堆叠45%分三批进：第一批15%(跌15%触发)→第二批15%(再跌或横盘2月)→第三批15%(产业验证)</t>
+        </is>
+      </c>
+    </row>
+    <row r="123" ht="15" customHeight="1" s="139">
+      <c r="A123" s="138" t="inlineStr">
+        <is>
+          <t>③ Plan B：锁到2027-01-31，逾期进则进40%留20%继续等。替代触发三选一：芯片PE&lt;40分位/蒋宇飞说现在进/月线连阴3月</t>
+        </is>
+      </c>
+    </row>
+    <row r="124" ht="26.85" customHeight="1" s="139">
+      <c r="A124" s="138" t="inlineStr">
+        <is>
+          <t>④ MLCC标的：风华高科200股(~4500元)，最接近MLCC纯暴露(MLCC营收占比58%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="125" ht="15" customHeight="1" s="139">
+      <c r="A125" s="138" t="inlineStr">
+        <is>
+          <t>⑤ 机器人4%不变（无纯暴露工具）+ 科创AI027048加仓6%覆盖AI+机器人+算力</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="138" t="inlineStr">
+        <is>
+          <t>⑥ 资金来源：现有现金50%+卖恒科2.5%+卖有色稀金5%+养殖减半12.5%+未来收入≈85%。两年跨度3%误差可接受</t>
+        </is>
+      </c>
+    </row>
+    <row r="127" ht="15" customHeight="1" s="139">
+      <c r="A127" s="138" t="inlineStr">
+        <is>
+          <t>⑦ P=75%被四源交叉确认(达利欧+李大霄+蒋宇飞+用户)→可能估低。小龙承认不是'全押蒋宇飞'</t>
+        </is>
+      </c>
+    </row>
+    <row r="128" ht="15" customHeight="1" s="139">
+      <c r="A128" s="332" t="inlineStr">
+        <is>
+          <t>▶ HBM产业链 5%</t>
+        </is>
+      </c>
+    </row>
+    <row r="129" ht="26.85" customHeight="1" s="139">
+      <c r="A129" s="138" t="inlineStr">
+        <is>
+          <t>为什么买：蒋宇飞"HBM未来1.5-2.5年波涛汹涌""Q4-Q1波澜壮阔热潮"。HBM是AI技术含量最高的存储，目前最紧缺</t>
+        </is>
+      </c>
+    </row>
+    <row r="130" ht="15" customHeight="1" s="139">
+      <c r="A130" s="138" t="inlineStr">
+        <is>
+          <t>什么时候进：2026-Q4（10-12月），MLCC清仓后资金转入</t>
+        </is>
+      </c>
+    </row>
+    <row r="131" ht="15" customHeight="1" s="139">
+      <c r="A131" s="138" t="inlineStr">
+        <is>
+          <t>什么时候出：2027-Q1热潮结束观察。蒋宇飞说热潮在四季度至明年一季度展开</t>
+        </is>
+      </c>
+    </row>
+    <row r="132" ht="15" customHeight="1" s="139">
+      <c r="A132" s="138" t="inlineStr">
+        <is>
+          <t>风控：5%不大。Q4不启动就继续等，不急着进</t>
+        </is>
+      </c>
+    </row>
+    <row r="133" ht="15" customHeight="1" s="139"/>
+    <row r="134" ht="26.85" customHeight="1" s="139">
+      <c r="A134" s="329" t="inlineStr">
+        <is>
+          <t>▶ 堆叠/先进封装 长电25%+通富20%=45%（核心重仓）</t>
+        </is>
+      </c>
+    </row>
+    <row r="135" ht="15" customHeight="1" s="139">
+      <c r="A135" s="138" t="inlineStr">
+        <is>
+          <t>为什么买：蒋宇飞27条视频反复强调"未来两年最大风口""改变家族命运""躺赢"。堆叠=CoWoS/2.5D/3D=突破存算一体。封装成本占存储芯片20%。P=75%顶级信源验证</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="138" t="inlineStr">
+        <is>
+          <t>为什么长电+通富：长电=全球第三大封测，2.5D/3D量产，客户高通/海思/TI。通富=AMD封测全线突破，MI300X参与，不可替代</t>
+        </is>
+      </c>
+    </row>
+    <row r="137" ht="15" customHeight="1" s="139">
+      <c r="A137" s="138" t="inlineStr">
+        <is>
+          <t>什么时候进：等11月美股大跌15%+。触发三选一：①达利欧泡沫落地 ②纳指破200日均线 ③中期选举大跌。全不进不砸</t>
+        </is>
+      </c>
+    </row>
+    <row r="138" ht="26.85" customHeight="1" s="139">
+      <c r="A138" s="138" t="inlineStr">
+        <is>
+          <t>先手仓位：Q4先建5%（长电3%+通富2%），等回调后进大仓位。符合蒋宇飞"三成追七成等"纪律</t>
+        </is>
+      </c>
+    </row>
+    <row r="139" ht="15" customHeight="1" s="139">
+      <c r="A139" s="138" t="inlineStr">
+        <is>
+          <t>什么时候出：2027-H2堆叠大放→长期持有。蒋宇飞说堆叠是10年风口</t>
+        </is>
+      </c>
+    </row>
+    <row r="140" ht="26.85" customHeight="1" s="139">
+      <c r="A140" s="138" t="inlineStr">
+        <is>
+          <t>风控：45%很重。必须等15%+回调才进（安全边际）。不到位置不砸。蒋宇飞说"回调就是你的机会"</t>
+        </is>
+      </c>
+    </row>
+    <row r="141" ht="26.85" customHeight="1" s="139"/>
+    <row r="142" ht="39.55" customHeight="1" s="139">
+      <c r="A142" s="332" t="inlineStr">
+        <is>
+          <t>▶ 国产算力/升腾链 10%</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="138" t="inlineStr">
+        <is>
+          <t>为什么买：蒋宇飞"2027算力长城最闪亮""升腾链2027爆发""升腾950明年出货"。工信部要求支持国产芯片</t>
+        </is>
+      </c>
+    </row>
+    <row r="144" ht="17.35" customHeight="1" s="139">
+      <c r="A144" s="138" t="inlineStr">
+        <is>
+          <t>什么时候进：2027年。触发：华为升腾950大批出货/工信部政策加码</t>
+        </is>
+      </c>
+    </row>
+    <row r="145" ht="17.15" customHeight="1" s="139">
+      <c r="A145" s="138" t="inlineStr">
+        <is>
+          <t>风控：等2027，当前只看不动</t>
+        </is>
+      </c>
+    </row>
+    <row r="146" ht="17.15" customHeight="1" s="139"/>
+    <row r="147" ht="17.15" customHeight="1" s="139">
+      <c r="A147" s="332" t="inlineStr">
+        <is>
+          <t>▶ 机器人(物理AI) 4%</t>
+        </is>
+      </c>
+    </row>
+    <row r="148" ht="17.15" customHeight="1" s="139">
+      <c r="A148" s="138" t="inlineStr">
+        <is>
+          <t>为什么买：用户判断机器人&gt;黄金&gt;比特币。蒋宇飞验证："未来经济三层=物理人→钢铁机器人→网络agent"。宇树科技73天过会</t>
+        </is>
+      </c>
+    </row>
+    <row r="149" ht="17.15" customHeight="1" s="139">
+      <c r="A149" s="138" t="inlineStr">
+        <is>
+          <t>什么时候进：2027冬开始逐步建。中长期赛道，不急</t>
+        </is>
+      </c>
+    </row>
+    <row r="150" ht="17.15" customHeight="1" s="139">
+      <c r="A150" s="138" t="inlineStr">
+        <is>
+          <t>风控：4%不大，判断错误损失可控</t>
+        </is>
+      </c>
+    </row>
+    <row r="151" ht="17.15" customHeight="1" s="139"/>
+    <row r="152" ht="17.15" customHeight="1" s="139">
+      <c r="A152" s="332" t="inlineStr">
+        <is>
+          <t>▶ 玻璃基板 3%</t>
+        </is>
+      </c>
+    </row>
+    <row r="153" ht="17.15" customHeight="1" s="139">
+      <c r="A153" s="138" t="inlineStr">
+        <is>
+          <t>为什么买：蒋宇飞"被严重低估即将爆发""两三年热点""业绩2027-H2释放""大规模2028"。两个爆发点：封装+存储</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="138" t="inlineStr">
+        <is>
+          <t>什么时候进：2027年等业绩释放。蒋宇飞说"消息还在送验阶段"</t>
+        </is>
+      </c>
+    </row>
+    <row r="155" ht="15" customHeight="1" s="139">
+      <c r="A155" s="138" t="inlineStr">
+        <is>
+          <t>风控：3%观察仓，等消息确认</t>
+        </is>
+      </c>
+    </row>
+    <row r="156" ht="15" customHeight="1" s="139"/>
+    <row r="157" ht="15" customHeight="1" s="139">
+      <c r="A157" s="329" t="inlineStr">
+        <is>
+          <t>四、进钱节奏时间线</t>
+        </is>
+      </c>
+    </row>
+    <row r="158" ht="15" customHeight="1" s="139"/>
+    <row r="159" ht="15" customHeight="1" s="139">
+      <c r="A159" s="333" t="inlineStr">
+        <is>
+          <t>时间</t>
+        </is>
+      </c>
+    </row>
+    <row r="160" ht="15" customHeight="1" s="139">
+      <c r="A160" s="138" t="inlineStr">
+        <is>
+          <t>现在-7月</t>
+        </is>
+      </c>
+      <c r="B160" s="138" t="inlineStr">
+        <is>
+          <t>MLCC3%建仓</t>
+        </is>
+      </c>
+      <c r="C160" s="138" t="inlineStr">
+        <is>
+          <t>芯片10%不动(虚P+3pp)</t>
+        </is>
+      </c>
+      <c r="D160" s="138" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E160" s="138" t="inlineStr">
+        <is>
+          <t>7%</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="138" t="inlineStr">
+        <is>
+          <t>8-10月</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="138" t="inlineStr">
+        <is>
+          <t>11月大跌</t>
+        </is>
+      </c>
+      <c r="B162" s="138" t="inlineStr">
+        <is>
+          <t>长电25%+通富20%大砸</t>
+        </is>
+      </c>
+      <c r="C162" s="138" t="inlineStr">
+        <is>
+          <t>MLCC清→HBM5%+堆叠先手5%</t>
+        </is>
+      </c>
+      <c r="D162" s="138" t="inlineStr">
+        <is>
+          <t>MLCC清</t>
+        </is>
+      </c>
+      <c r="E162" s="138" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="138" t="inlineStr">
+        <is>
+          <t>11月没大跌</t>
+        </is>
+      </c>
+      <c r="B163" s="138" t="inlineStr">
+        <is>
+          <t>堆叠先手5%(长电3+通富2)</t>
+        </is>
+      </c>
+      <c r="C163" s="138" t="inlineStr">
+        <is>
+          <t>MLCC清→等</t>
+        </is>
+      </c>
+      <c r="D163" s="138" t="inlineStr">
+        <is>
+          <t>MLCC清</t>
+        </is>
+      </c>
+      <c r="E163" s="138" t="inlineStr">
+        <is>
+          <t>0-2%</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="138" t="inlineStr">
+        <is>
+          <t>2027-Q1</t>
+        </is>
+      </c>
+      <c r="B164" s="138" t="inlineStr">
+        <is>
+          <t>HBM持有</t>
+        </is>
+      </c>
+      <c r="C164" s="138" t="inlineStr">
+        <is>
+          <t>堆叠先手持有</t>
+        </is>
+      </c>
+      <c r="D164" s="138" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E164" s="138" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="138" t="inlineStr">
+        <is>
+          <t>2027-H2</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="138" t="inlineStr">
+        <is>
+          <t>2027冬</t>
+        </is>
+      </c>
+    </row>
+    <row r="167"/>
+    <row r="168">
+      <c r="A168" s="329" t="inlineStr">
+        <is>
+          <t>⚡ 一句话：MLCC3%小试→Q4 HBM5%+堆叠先手5%→11月大跌长电25%+通富20%→2027堆叠躺赢</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="138" t="inlineStr">
+        <is>
+          <t>风控：45%重仓必须等15%+回调 | MLCC年底必清 | 蒋宇飞纪律"三成追七成等"</t>
+        </is>
+      </c>
+    </row>
+    <row r="170"/>
+    <row r="171"/>
+    <row r="172"/>
+    <row r="173">
+      <c r="A173" s="148" t="inlineStr">
+        <is>
+          <t>🔥 叙事主线（四条）</t>
+        </is>
+      </c>
+      <c r="B173" s="149" t="n"/>
+      <c r="C173" s="149" t="n"/>
+      <c r="D173" s="149" t="n"/>
+      <c r="E173" s="149" t="n"/>
+      <c r="F173" s="149" t="n"/>
+      <c r="G173" s="149" t="n"/>
+      <c r="H173" s="150" t="n"/>
+    </row>
+    <row r="174">
+      <c r="A174" s="325" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  辅助仓位: 玻璃基板5% | 算力出海5%</t>
+        </is>
+      </c>
+      <c r="B174" s="326" t="n"/>
+      <c r="C174" s="326" t="n"/>
+      <c r="D174" s="326" t="n"/>
+      <c r="E174" s="326" t="n"/>
+      <c r="F174" s="326" t="n"/>
+      <c r="G174" s="326" t="n"/>
+      <c r="H174" s="325" t="n"/>
+    </row>
+    <row r="175">
+      <c r="A175" s="325" t="n"/>
+      <c r="B175" s="326" t="n"/>
+      <c r="C175" s="326" t="n"/>
+      <c r="D175" s="326" t="n"/>
+      <c r="E175" s="326" t="n"/>
+      <c r="F175" s="326" t="n"/>
+      <c r="G175" s="326" t="n"/>
+      <c r="H175" s="325" t="n"/>
+    </row>
+    <row r="176">
+      <c r="A176" s="334" t="inlineStr">
+        <is>
+          <t>三、核心仓位汇总表</t>
+        </is>
+      </c>
+      <c r="B176" s="326" t="n"/>
+      <c r="C176" s="326" t="n"/>
+      <c r="D176" s="326" t="n"/>
+      <c r="E176" s="326" t="n"/>
+      <c r="F176" s="326" t="n"/>
+      <c r="G176" s="326" t="n"/>
+      <c r="H176" s="325" t="n"/>
+    </row>
+    <row r="177">
+      <c r="A177" s="138" t="inlineStr">
+        <is>
           <t>持仓(50%): 养殖25%+芯片10%+电池5%+恒科2.5%+有色2.5%+稀金2.5%+银行1.5%</t>
         </is>
       </c>
-      <c r="B116" s="138" t="inlineStr">
-        <is>
-          <t>比特币独立叙事消亡 维持：资金吸附力排序 AI&gt;美股&gt;黄金&gt;比特币，比特币已成美股影子资产，AI落地后资金有明确去处，比特币价值持续被稀释</t>
-        </is>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" s="151" t="inlineStr">
+    </row>
+    <row r="178">
+      <c r="A178" s="151" t="inlineStr">
         <is>
           <t>待重仓(等回调): 长电25%+通富20%=45% → 11月中期选举触发</t>
         </is>
       </c>
     </row>
-    <row r="118" ht="15" customHeight="1" s="139">
-      <c r="A118" s="152" t="inlineStr">
+    <row r="179">
+      <c r="A179" s="152" t="inlineStr">
         <is>
           <t>观察仓(机动18%): MLCC2%+HBM5%+堆叠先手5%+升腾/国产算力5%+玻璃基板1%</t>
         </is>
       </c>
     </row>
-    <row r="119" ht="15" customHeight="1" s="139">
-      <c r="A119" s="153" t="inlineStr">
+    <row r="180">
+      <c r="A180" s="153" t="inlineStr">
         <is>
           <t>锁定现金(13%): 等11月大事件→解锁后进长电/通富剩余仓位</t>
         </is>
       </c>
     </row>
-    <row r="120" ht="26.85" customHeight="1" s="139">
-      <c r="A120" s="154" t="inlineStr">
+    <row r="181">
+      <c r="A181" s="154" t="inlineStr">
         <is>
           <t>虚P规则：未落地→记虚P→不加实P→等落地转实P。此板块锁定大部分现金，与机会成本联动分析。</t>
         </is>
       </c>
     </row>
-    <row r="121" ht="26.85" customHeight="1" s="139">
-      <c r="A121" s="327" t="inlineStr">
+    <row r="182">
+      <c r="A182" s="327" t="inlineStr">
         <is>
           <t>四、蒋宇飞"三层追七成等"落地</t>
         </is>
       </c>
     </row>
-    <row r="122" ht="15" customHeight="1" s="139">
-      <c r="A122" s="156" t="inlineStr">
+    <row r="183">
+      <c r="A183" s="156" t="inlineStr">
         <is>
           <t>30%追热点: 当前MLCC(蒋宇飞4月底预测已启动)+光模块(贯穿2026) | 这部分在持仓里</t>
         </is>
       </c>
-      <c r="B122" s="156" t="inlineStr">
+      <c r="B183" s="156" t="inlineStr">
         <is>
           <t>核心观点</t>
         </is>
       </c>
-      <c r="C122" s="156" t="inlineStr">
+      <c r="C183" s="156" t="inlineStr">
         <is>
           <t>与你策略契合</t>
         </is>
       </c>
-      <c r="D122" s="156" t="inlineStr">
+      <c r="D183" s="156" t="inlineStr">
         <is>
           <t>虚P方向</t>
         </is>
       </c>
-      <c r="E122" s="156" t="inlineStr">
+      <c r="E183" s="156" t="inlineStr">
         <is>
           <t>落地条件</t>
         </is>
       </c>
-      <c r="F122" s="156" t="inlineStr">
+      <c r="F183" s="156" t="inlineStr">
         <is>
           <t>状态</t>
         </is>
       </c>
-      <c r="G122" s="156" t="inlineStr">
+      <c r="G183" s="156" t="inlineStr">
         <is>
           <t>权重</t>
         </is>
       </c>
-      <c r="H122" s="156" t="inlineStr">
+      <c r="H183" s="156" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="123" ht="15" customHeight="1" s="139">
-      <c r="A123" s="157" t="inlineStr">
+    <row r="184">
+      <c r="A184" s="157" t="inlineStr">
         <is>
           <t>70%等回调: 堆叠(长电+通富等11月大跌15%+大仓位进) | 升腾链等2027爆发</t>
         </is>
       </c>
-      <c r="B123" s="157" t="inlineStr">
+      <c r="B184" s="157" t="inlineStr">
         <is>
           <t>AI泡沫65-75%概率年底破
 "财富转现金=刺破泡沫"
@@ -3586,7 +3924,7 @@
 基建投入&gt;&gt;收入</t>
         </is>
       </c>
-      <c r="C123" s="158" t="inlineStr">
+      <c r="C184" s="158" t="inlineStr">
         <is>
           <t>完全契合
 等中期选举大跌
@@ -3594,1166 +3932,150 @@
 回调后大仓位进</t>
         </is>
       </c>
-      <c r="D123" s="157" t="inlineStr">
+      <c r="D184" s="157" t="inlineStr">
         <is>
           <t>芯片-2pp
 恒科-1pp
 (虚P)</t>
         </is>
       </c>
-      <c r="E123" s="157" t="inlineStr">
+      <c r="E184" s="157" t="inlineStr">
         <is>
           <t>七姐妹&gt;15%回调
 或破200日均线</t>
         </is>
       </c>
-      <c r="F123" s="159" t="inlineStr">
+      <c r="F184" s="159" t="inlineStr">
         <is>
           <t>未落地</t>
         </is>
       </c>
-      <c r="G123" s="160" t="inlineStr">
+      <c r="G184" s="160" t="inlineStr">
         <is>
           <t>极高
 5星</t>
         </is>
       </c>
-      <c r="H123" s="157" t="inlineStr">
+      <c r="H184" s="157" t="inlineStr">
         <is>
           <t>与你100%一致
 回调=买入机会</t>
         </is>
       </c>
     </row>
-    <row r="124" ht="26.85" customHeight="1" s="139">
-      <c r="A124" s="157" t="inlineStr">
+    <row r="185">
+      <c r="A185" s="157" t="inlineStr">
         <is>
           <t>李大霄
 金融界 6/4</t>
         </is>
       </c>
-      <c r="B124" s="149" t="n"/>
-      <c r="C124" s="149" t="n"/>
-      <c r="D124" s="149" t="n"/>
-      <c r="E124" s="149" t="n"/>
-      <c r="F124" s="149" t="n"/>
-      <c r="G124" s="149" t="n"/>
-      <c r="H124" s="150" t="n"/>
-    </row>
-    <row r="125" ht="15" customHeight="1" s="139">
-      <c r="A125" s="328" t="inlineStr">
+      <c r="B185" s="149" t="n"/>
+      <c r="C185" s="149" t="n"/>
+      <c r="D185" s="149" t="n"/>
+      <c r="E185" s="149" t="n"/>
+      <c r="F185" s="149" t="n"/>
+      <c r="G185" s="149" t="n"/>
+      <c r="H185" s="150" t="n"/>
+    </row>
+    <row r="186">
+      <c r="A186" s="328" t="inlineStr">
         <is>
           <t>五、关键时间点操作清单</t>
         </is>
       </c>
-      <c r="B125" s="149" t="n"/>
-      <c r="C125" s="149" t="n"/>
-      <c r="D125" s="149" t="n"/>
-      <c r="E125" s="149" t="n"/>
-      <c r="F125" s="149" t="n"/>
-      <c r="G125" s="149" t="n"/>
-      <c r="H125" s="150" t="n"/>
-    </row>
-    <row r="126">
-      <c r="A126" s="138" t="inlineStr">
+      <c r="B186" s="149" t="n"/>
+      <c r="C186" s="149" t="n"/>
+      <c r="D186" s="149" t="n"/>
+      <c r="E186" s="149" t="n"/>
+      <c r="F186" s="149" t="n"/>
+      <c r="G186" s="149" t="n"/>
+      <c r="H186" s="150" t="n"/>
+    </row>
+    <row r="187">
+      <c r="A187" s="138" t="inlineStr">
         <is>
           <t>6-7月: 长鑫上市→观察存储/芯片反应 | 芯片10%不动 | MLCC2%观察仓可建</t>
         </is>
       </c>
     </row>
-    <row r="127" ht="15" customHeight="1" s="139">
-      <c r="A127" s="155" t="inlineStr">
+    <row r="188">
+      <c r="A188" s="155" t="inlineStr">
         <is>
           <t>8-10月: MLCC肉最甜→持到11月 | 观察HBM启动信号</t>
         </is>
       </c>
     </row>
-    <row r="128" ht="15" customHeight="1" s="139">
-      <c r="A128" s="161" t="inlineStr">
+    <row r="189">
+      <c r="A189" s="161" t="inlineStr">
         <is>
           <t>11-12月: MLCC清仓→资金转HBM5%+堆叠先手5% | 非农黑五→恒科注意</t>
         </is>
       </c>
-      <c r="B128" s="161" t="inlineStr">
+      <c r="B189" s="161" t="inlineStr">
         <is>
           <t>关系</t>
         </is>
       </c>
-      <c r="C128" s="161" t="inlineStr">
+      <c r="C189" s="161" t="inlineStr">
         <is>
           <t>分析</t>
         </is>
       </c>
-      <c r="D128" s="161" t="inlineStr">
+      <c r="D189" s="161" t="inlineStr">
         <is>
           <t>信号强度</t>
         </is>
       </c>
     </row>
-    <row r="129" ht="26.85" customHeight="1" s="139">
-      <c r="A129" s="162" t="inlineStr">
+    <row r="190">
+      <c r="A190" s="162" t="inlineStr">
         <is>
           <t>2027-Q1: HBM热潮→持有 | 堆叠先手继续观察</t>
         </is>
       </c>
-      <c r="B129" s="163" t="inlineStr">
+      <c r="B190" s="163" t="inlineStr">
         <is>
           <t>✅强印证</t>
         </is>
       </c>
-      <c r="C129" s="157" t="inlineStr">
+      <c r="C190" s="157" t="inlineStr">
         <is>
           <t>AI泡沫+窄牛宽熊=同一现象两角度</t>
         </is>
       </c>
-      <c r="D129" s="157" t="inlineStr">
+      <c r="D190" s="157" t="inlineStr">
         <is>
           <t>🔴强信号</t>
         </is>
       </c>
     </row>
-    <row r="130" ht="15" customHeight="1" s="139">
-      <c r="A130" s="162" t="inlineStr">
+    <row r="191">
+      <c r="A191" s="162" t="inlineStr">
         <is>
           <t>2027-H2: 堆叠大放光芒→长电25%+通富20%大仓位确认 | 升腾链10% | CPU5%</t>
         </is>
       </c>
-      <c r="B130" s="164" t="inlineStr">
+      <c r="B191" s="164" t="inlineStr">
         <is>
           <t>⚠️部分矛盾</t>
         </is>
       </c>
-      <c r="C130" s="157" t="inlineStr">
+      <c r="C191" s="157" t="inlineStr">
         <is>
           <t>达看流动性vs知乎看估值</t>
         </is>
       </c>
-      <c r="D130" s="157" t="inlineStr">
+      <c r="D191" s="157" t="inlineStr">
         <is>
           <t>🟡中性</t>
         </is>
       </c>
     </row>
-    <row r="131" ht="15" customHeight="1" s="139">
-      <c r="A131" s="162" t="inlineStr">
+    <row r="192">
+      <c r="A192" s="162" t="inlineStr">
         <is>
           <t>三源共识</t>
-        </is>
-      </c>
-      <c r="B131" s="149" t="n"/>
-      <c r="C131" s="149" t="n"/>
-      <c r="D131" s="149" t="n"/>
-      <c r="E131" s="149" t="n"/>
-      <c r="F131" s="149" t="n"/>
-      <c r="G131" s="149" t="n"/>
-      <c r="H131" s="150" t="n"/>
-    </row>
-    <row r="132" ht="15" customHeight="1" s="139">
-      <c r="A132" s="138" t="n"/>
-    </row>
-    <row r="133" ht="15" customHeight="1" s="139">
-      <c r="A133" s="165" t="inlineStr">
-        <is>
-          <t>三、现金策略联动（锁定大部分现金储备）</t>
-        </is>
-      </c>
-    </row>
-    <row r="134" ht="26.85" customHeight="1" s="139">
-      <c r="A134" s="154" t="inlineStr">
-        <is>
-          <t>三源联动→达利欧65-75%概率年底AI回调+中期选举历史跌一波→锁定大部分现金→等11月回调入场</t>
-        </is>
-      </c>
-    </row>
-    <row r="135" ht="15" customHeight="1" s="139">
-      <c r="A135" s="161" t="inlineStr">
-        <is>
-          <t>维度</t>
-        </is>
-      </c>
-      <c r="B135" s="161" t="inlineStr">
-        <is>
-          <t>内容</t>
-        </is>
-      </c>
-      <c r="C135" s="161" t="inlineStr">
-        <is>
-          <t>影响</t>
-        </is>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" s="157" t="inlineStr">
-        <is>
-          <t>现金锁定</t>
-        </is>
-      </c>
-      <c r="B136" s="149" t="n"/>
-      <c r="C136" s="149" t="n"/>
-      <c r="D136" s="149" t="n"/>
-      <c r="E136" s="149" t="n"/>
-      <c r="F136" s="149" t="n"/>
-      <c r="G136" s="149" t="n"/>
-      <c r="H136" s="150" t="n"/>
-    </row>
-    <row r="137" ht="15" customHeight="1" s="139">
-      <c r="A137" s="157" t="inlineStr">
-        <is>
-          <t>等待窗口</t>
-        </is>
-      </c>
-      <c r="B137" s="157" t="inlineStr">
-        <is>
-          <t>2026年11月中期选举前后</t>
-        </is>
-      </c>
-      <c r="C137" s="157" t="inlineStr">
-        <is>
-          <t>→约5个月等待期</t>
-        </is>
-      </c>
-    </row>
-    <row r="138" ht="26.85" customHeight="1" s="139">
-      <c r="A138" s="157" t="inlineStr">
-        <is>
-          <t>触发条件</t>
-        </is>
-      </c>
-      <c r="B138" s="157" t="inlineStr">
-        <is>
-          <t>美股跌一波+AI回调&gt;15%</t>
-        </is>
-      </c>
-      <c r="C138" s="157" t="inlineStr">
-        <is>
-          <t>→达利欧65-75%概率事件</t>
-        </is>
-      </c>
-    </row>
-    <row r="139" ht="15" customHeight="1" s="139">
-      <c r="A139" s="157" t="inlineStr">
-        <is>
-          <t>入场标的</t>
-        </is>
-      </c>
-      <c r="B139" s="157" t="inlineStr">
-        <is>
-          <t>堆叠：长电科技+通富微电</t>
-        </is>
-      </c>
-      <c r="C139" s="157" t="inlineStr">
-        <is>
-          <t>→国内确定性不受美股影响</t>
-        </is>
-      </c>
-    </row>
-    <row r="140" ht="26.85" customHeight="1" s="139">
-      <c r="A140" s="157" t="inlineStr">
-        <is>
-          <t>机会成本</t>
-        </is>
-      </c>
-      <c r="B140" s="157" t="inlineStr">
-        <is>
-          <t>持有现金5个月vs错过短期行情</t>
-        </is>
-      </c>
-      <c r="C140" s="157" t="inlineStr">
-        <is>
-          <t>→见下方机会成本联动</t>
-        </is>
-      </c>
-    </row>
-    <row r="141" ht="26.85" customHeight="1" s="139">
-      <c r="A141" s="157" t="inlineStr">
-        <is>
-          <t>下行保护</t>
-        </is>
-      </c>
-      <c r="B141" s="149" t="n"/>
-      <c r="C141" s="149" t="n"/>
-      <c r="D141" s="149" t="n"/>
-      <c r="E141" s="149" t="n"/>
-      <c r="F141" s="149" t="n"/>
-      <c r="G141" s="149" t="n"/>
-      <c r="H141" s="150" t="n"/>
-    </row>
-    <row r="142" ht="39.55" customHeight="1" s="139"/>
-    <row r="143">
-      <c r="A143" s="165" t="inlineStr">
-        <is>
-          <t>四、机会成本联动分析（现金锁定vs其他选项）</t>
-        </is>
-      </c>
-    </row>
-    <row r="144" ht="17.35" customHeight="1" s="139">
-      <c r="A144" s="161" t="inlineStr">
-        <is>
-          <t>选项</t>
-        </is>
-      </c>
-      <c r="B144" s="161" t="inlineStr">
-        <is>
-          <t>P值</t>
-        </is>
-      </c>
-      <c r="C144" s="161" t="inlineStr">
-        <is>
-          <t>盈亏比</t>
-        </is>
-      </c>
-      <c r="D144" s="161" t="inlineStr">
-        <is>
-          <t>Score</t>
-        </is>
-      </c>
-      <c r="E144" s="161" t="inlineStr">
-        <is>
-          <t>现金锁定影响</t>
-        </is>
-      </c>
-      <c r="F144" s="161" t="inlineStr">
-        <is>
-          <t>建议</t>
-        </is>
-      </c>
-      <c r="G144" s="161" t="inlineStr">
-        <is>
-          <t>判断</t>
-        </is>
-      </c>
-    </row>
-    <row r="145" ht="17.15" customHeight="1" s="139">
-      <c r="A145" s="157" t="inlineStr">
-        <is>
-          <t>长电科技</t>
-        </is>
-      </c>
-      <c r="B145" s="157" t="inlineStr">
-        <is>
-          <t>75%</t>
-        </is>
-      </c>
-      <c r="C145" s="157" t="inlineStr">
-        <is>
-          <t>4.5:1</t>
-        </is>
-      </c>
-      <c r="D145" s="157" t="inlineStr">
-        <is>
-          <t>3.375</t>
-        </is>
-      </c>
-      <c r="E145" s="157" t="inlineStr">
-        <is>
-          <t>等回调大仓位
-现金锁定中</t>
-        </is>
-      </c>
-      <c r="F145" s="157" t="inlineStr">
-        <is>
-          <t>暂不动等11月</t>
-        </is>
-      </c>
-      <c r="G145" s="160" t="inlineStr">
-        <is>
-          <t>🔴最高优先</t>
-        </is>
-      </c>
-    </row>
-    <row r="146" ht="17.15" customHeight="1" s="139">
-      <c r="A146" s="157" t="inlineStr">
-        <is>
-          <t>通富微电</t>
-        </is>
-      </c>
-      <c r="B146" s="149" t="n"/>
-      <c r="C146" s="149" t="n"/>
-      <c r="D146" s="149" t="n"/>
-      <c r="E146" s="149" t="n"/>
-      <c r="F146" s="149" t="n"/>
-      <c r="G146" s="149" t="n"/>
-      <c r="H146" s="150" t="n"/>
-    </row>
-    <row r="147" ht="17.15" customHeight="1" s="139">
-      <c r="A147" s="157" t="inlineStr">
-        <is>
-          <t>养殖</t>
-        </is>
-      </c>
-      <c r="B147" s="157" t="inlineStr">
-        <is>
-          <t>70%</t>
-        </is>
-      </c>
-      <c r="C147" s="157" t="inlineStr">
-        <is>
-          <t>2.0:1</t>
-        </is>
-      </c>
-      <c r="D147" s="157" t="inlineStr">
-        <is>
-          <t>1.400</t>
-        </is>
-      </c>
-      <c r="E147" s="157" t="inlineStr">
-        <is>
-          <t>已持仓不需现金 | 6/5 芳姐：低价抄底母猪，行业融资枯竭，等待母猪血流成河才是最佳买点</t>
-        </is>
-      </c>
-      <c r="F147" s="157" t="inlineStr">
-        <is>
-          <t>继续持有</t>
-        </is>
-      </c>
-      <c r="G147" s="158" t="inlineStr">
-        <is>
-          <t>✅已配置</t>
-        </is>
-      </c>
-    </row>
-    <row r="148" ht="17.15" customHeight="1" s="139">
-      <c r="A148" s="157" t="inlineStr">
-        <is>
-          <t>电池</t>
-        </is>
-      </c>
-      <c r="B148" s="157" t="inlineStr">
-        <is>
-          <t>65%</t>
-        </is>
-      </c>
-      <c r="C148" s="157" t="inlineStr">
-        <is>
-          <t>2.0:1</t>
-        </is>
-      </c>
-      <c r="D148" s="157" t="inlineStr">
-        <is>
-          <t>1.300</t>
-        </is>
-      </c>
-      <c r="E148" s="157" t="inlineStr">
-        <is>
-          <t>已持仓不需现金 | 6/5 闻号说经济：厄尔尼诺80%概率+AI用电爆发→电力/能源受益</t>
-        </is>
-      </c>
-      <c r="F148" s="157" t="inlineStr">
-        <is>
-          <t>继续持有</t>
-        </is>
-      </c>
-      <c r="G148" s="158" t="inlineStr">
-        <is>
-          <t>✅已配置</t>
-        </is>
-      </c>
-    </row>
-    <row r="149" ht="17.15" customHeight="1" s="139">
-      <c r="A149" s="157" t="inlineStr">
-        <is>
-          <t>核电</t>
-        </is>
-      </c>
-      <c r="B149" s="157" t="inlineStr">
-        <is>
-          <t>52%</t>
-        </is>
-      </c>
-      <c r="C149" s="157" t="inlineStr">
-        <is>
-          <t>1.5:1</t>
-        </is>
-      </c>
-      <c r="D149" s="157" t="inlineStr">
-        <is>
-          <t>0.780</t>
-        </is>
-      </c>
-      <c r="E149" s="157" t="inlineStr">
-        <is>
-          <t>10年维度
-小仓试水可行</t>
-        </is>
-      </c>
-      <c r="F149" s="157" t="inlineStr">
-        <is>
-          <t>不影响现金策略</t>
-        </is>
-      </c>
-      <c r="G149" s="166" t="inlineStr">
-        <is>
-          <t>🟡长期观察</t>
-        </is>
-      </c>
-    </row>
-    <row r="150" ht="17.15" customHeight="1" s="139">
-      <c r="A150" s="157" t="inlineStr">
-        <is>
-          <t>存储</t>
-        </is>
-      </c>
-      <c r="B150" s="157" t="inlineStr">
-        <is>
-          <t>55%</t>
-        </is>
-      </c>
-      <c r="C150" s="157" t="inlineStr">
-        <is>
-          <t>1.0:1</t>
-        </is>
-      </c>
-      <c r="D150" s="157" t="inlineStr">
-        <is>
-          <t>0.550</t>
-        </is>
-      </c>
-      <c r="E150" s="157" t="inlineStr">
-        <is>
-          <t>已降级</t>
-        </is>
-      </c>
-      <c r="F150" s="157" t="inlineStr">
-        <is>
-          <t>不动</t>
-        </is>
-      </c>
-      <c r="G150" s="160" t="inlineStr">
-        <is>
-          <t>❌已降级</t>
-        </is>
-      </c>
-    </row>
-    <row r="151" ht="17.15" customHeight="1" s="139">
-      <c r="A151" s="157" t="inlineStr">
-        <is>
-          <t>纯现金5月</t>
-        </is>
-      </c>
-      <c r="B151" s="149" t="n"/>
-      <c r="C151" s="149" t="n"/>
-      <c r="D151" s="149" t="n"/>
-      <c r="E151" s="149" t="n"/>
-      <c r="F151" s="149" t="n"/>
-      <c r="G151" s="149" t="n"/>
-      <c r="H151" s="150" t="n"/>
-    </row>
-    <row r="152" ht="17.15" customHeight="1" s="139">
-      <c r="A152" s="147" t="inlineStr">
-        <is>
-          <t>AI硬件确定性(付鹏) → 内存=AI核心瓶颈(4信源互锁) → 国产替代加速 → 稀土断供日本 → 芯片/存储/HBM长期利好 | 短期被利率↑/地缘↑压制</t>
-        </is>
-      </c>
-    </row>
-    <row r="153" ht="17.15" customHeight="1" s="139">
-      <c r="A153" s="167" t="inlineStr">
-        <is>
-          <t>五、虚P→实P转换条件 &amp; 操作触发</t>
-        </is>
-      </c>
-      <c r="B153" s="149" t="n"/>
-      <c r="C153" s="149" t="n"/>
-      <c r="D153" s="149" t="n"/>
-      <c r="E153" s="149" t="n"/>
-      <c r="F153" s="149" t="n"/>
-      <c r="G153" s="149" t="n"/>
-      <c r="H153" s="150" t="n"/>
-    </row>
-    <row r="154">
-      <c r="A154" s="156" t="inlineStr">
-        <is>
-          <t>条件</t>
-        </is>
-      </c>
-      <c r="B154" s="161" t="inlineStr">
-        <is>
-          <t>触发信号</t>
-        </is>
-      </c>
-      <c r="C154" s="156" t="inlineStr">
-        <is>
-          <t>影响</t>
-        </is>
-      </c>
-      <c r="D154" s="156" t="inlineStr">
-        <is>
-          <t>操作</t>
-        </is>
-      </c>
-      <c r="E154" s="147" t="inlineStr">
-        <is>
-          <t>2026-05-30 宋鸿兵：海峡封锁→能源成本飙升</t>
-        </is>
-      </c>
-      <c r="F154" s="147" t="inlineStr">
-        <is>
-          <t>2026-05-30 岩松：存储1-2年产能饱和</t>
-        </is>
-      </c>
-      <c r="G154" s="147" t="inlineStr">
-        <is>
-          <t>2026-05-30 宋鸿兵：30年美债破5%双红线</t>
-        </is>
-      </c>
-    </row>
-    <row r="155" ht="15" customHeight="1" s="139">
-      <c r="A155" s="170" t="inlineStr">
-        <is>
-          <t>达利欧落地</t>
-        </is>
-      </c>
-      <c r="B155" s="157" t="inlineStr">
-        <is>
-          <t>七姐妹&gt;15%回调或破200日均线</t>
-        </is>
-      </c>
-      <c r="C155" s="157" t="inlineStr">
-        <is>
-          <t>芯片/恒科虚P转实P</t>
-        </is>
-      </c>
-      <c r="D155" s="157" t="inlineStr">
-        <is>
-          <t>现金解锁→大仓位进堆叠</t>
-        </is>
-      </c>
-    </row>
-    <row r="156" ht="15" customHeight="1" s="139">
-      <c r="A156" s="166" t="inlineStr">
-        <is>
-          <t>李大霄落地</t>
-        </is>
-      </c>
-      <c r="B156" s="157" t="inlineStr">
-        <is>
-          <t>多数成分股下跌+指数拐头</t>
-        </is>
-      </c>
-      <c r="C156" s="157" t="inlineStr">
-        <is>
-          <t>恒科/芯片虚P转实P</t>
-        </is>
-      </c>
-      <c r="D156" s="157" t="inlineStr">
-        <is>
-          <t>确认系统性风险→入场</t>
-        </is>
-      </c>
-    </row>
-    <row r="157" ht="15" customHeight="1" s="139">
-      <c r="A157" s="171" t="inlineStr">
-        <is>
-          <t>中期选举</t>
-        </is>
-      </c>
-      <c r="B157" s="171" t="inlineStr">
-        <is>
-          <t>11月美股跌一波</t>
-        </is>
-      </c>
-      <c r="C157" s="171" t="inlineStr">
-        <is>
-          <t>你的策略触发</t>
-        </is>
-      </c>
-      <c r="D157" s="171" t="inlineStr">
-        <is>
-          <t>现金→长电+通富</t>
-        </is>
-      </c>
-      <c r="E157" s="156" t="inlineStr">
-        <is>
-          <t>落地条件</t>
-        </is>
-      </c>
-      <c r="F157" s="156" t="inlineStr">
-        <is>
-          <t>状态</t>
-        </is>
-      </c>
-      <c r="G157" s="156" t="inlineStr">
-        <is>
-          <t>权重</t>
-        </is>
-      </c>
-      <c r="H157" s="156" t="inlineStr">
-        <is>
-          <t>备注</t>
-        </is>
-      </c>
-    </row>
-    <row r="158" ht="15" customHeight="1" s="139">
-      <c r="A158" s="157" t="inlineStr">
-        <is>
-          <t>堆叠独立</t>
-        </is>
-      </c>
-      <c r="B158" s="149" t="n"/>
-      <c r="C158" s="149" t="n"/>
-      <c r="D158" s="149" t="n"/>
-      <c r="E158" s="149" t="n"/>
-      <c r="F158" s="149" t="n"/>
-      <c r="G158" s="149" t="n"/>
-      <c r="H158" s="150" t="n"/>
-    </row>
-    <row r="159" ht="15" customHeight="1" s="139">
-      <c r="A159" s="157" t="inlineStr">
-        <is>
-          <t>李大霄
-金融界 6/4</t>
-        </is>
-      </c>
-      <c r="B159" s="157" t="inlineStr">
-        <is>
-          <t>美股窄牛宽熊
-仅20只创新高
-CAPE40倍→泡沫</t>
-        </is>
-      </c>
-      <c r="C159" s="158" t="inlineStr">
-        <is>
-          <t>🟢高度契合
-确认美股风险
-现金策略正确</t>
-        </is>
-      </c>
-      <c r="D159" s="157" t="inlineStr">
-        <is>
-          <t>美股全市场↓
-港股连带承压</t>
-        </is>
-      </c>
-      <c r="E159" s="157" t="inlineStr">
-        <is>
-          <t>纳指破200日均线
-或多数成分股下跌</t>
-        </is>
-      </c>
-      <c r="F159" s="159" t="inlineStr">
-        <is>
-          <t>⏳未落地
-(虚P状态)</t>
-        </is>
-      </c>
-      <c r="G159" s="157" t="inlineStr">
-        <is>
-          <t>⭐⭐⭐
-中高</t>
-        </is>
-      </c>
-      <c r="H159" s="157" t="inlineStr">
-        <is>
-          <t>6/4三源联动:
-恒科-2pp
-芯片-1pp
-→已记虚P
-未转实P</t>
-        </is>
-      </c>
-    </row>
-    <row r="160" ht="15" customHeight="1" s="139">
-      <c r="A160" s="172" t="inlineStr">
-        <is>
-          <t>⚡ 核心结论：三源联动确认AI泡沫风险+你的中期选举策略正确。大部分现金锁定等11月回调→大仓位进长电/通富。机会成本可接受（不对称博弈，下有保底）。虚P已记，等落地转实P。</t>
-        </is>
-      </c>
-      <c r="B160" s="168" t="n"/>
-      <c r="C160" s="168" t="n"/>
-      <c r="D160" s="168" t="n"/>
-      <c r="E160" s="168" t="n"/>
-      <c r="F160" s="168" t="n"/>
-      <c r="G160" s="168" t="n"/>
-      <c r="H160" s="169" t="n"/>
-    </row>
-    <row r="161">
-      <c r="A161" s="138" t="inlineStr">
-        <is>
-          <t>────────────────────────────────────────────────────────────</t>
-        </is>
-      </c>
-    </row>
-    <row r="162">
-      <c r="A162" s="173" t="inlineStr">
-        <is>
-          <t>🔗 三源互锁验证</t>
-        </is>
-      </c>
-    </row>
-    <row r="163">
-      <c r="A163" s="140" t="inlineStr">
-        <is>
-          <t>达利欧 × 李大霄</t>
-        </is>
-      </c>
-      <c r="C163" s="174" t="inlineStr">
-        <is>
-          <t>✅ 强印证</t>
-        </is>
-      </c>
-      <c r="E163" s="175" t="inlineStr">
-        <is>
-          <t>AI泡沫+窄牛宽熊=同一现象两角度，互相确认</t>
-        </is>
-      </c>
-    </row>
-    <row r="164">
-      <c r="A164" s="140" t="inlineStr">
-        <is>
-          <t>达利欧 × 知乎</t>
-        </is>
-      </c>
-      <c r="C164" s="176" t="inlineStr">
-        <is>
-          <t>⚠️ 部分矛盾</t>
-        </is>
-      </c>
-      <c r="E164" s="175" t="inlineStr">
-        <is>
-          <t>达利欧看流动性(泡沫将破) vs 知乎看估值(PE中值安全)</t>
-        </is>
-      </c>
-    </row>
-    <row r="165">
-      <c r="A165" s="140" t="inlineStr">
-        <is>
-          <t>三源共识</t>
-        </is>
-      </c>
-      <c r="C165" s="177" t="inlineStr">
-        <is>
-          <t>🔴 核心共识</t>
-        </is>
-      </c>
-      <c r="E165" s="175" t="inlineStr">
-        <is>
-          <t>AI龙头估值偏高+市场极度集中+中小盘已熊 → 短期风险&gt;机会</t>
-        </is>
-      </c>
-    </row>
-    <row r="166"/>
-    <row r="167">
-      <c r="A167" s="165" t="inlineStr">
-        <is>
-          <t>🎯 结论（虚P→实P转换条件）</t>
-        </is>
-      </c>
-    </row>
-    <row r="168">
-      <c r="A168" s="140" t="inlineStr">
-        <is>
-          <t>① 达利欧信号落地条件</t>
-        </is>
-      </c>
-      <c r="C168" s="175" t="inlineStr">
-        <is>
-          <t>纳指七姐妹出现&gt;15%回调 或 纳指破200日均线</t>
-        </is>
-      </c>
-      <c r="E168" s="178" t="inlineStr">
-        <is>
-          <t>→ 芯片/恒科虚P转实P → 确认减仓信号</t>
-        </is>
-      </c>
-    </row>
-    <row r="169">
-      <c r="A169" s="140" t="inlineStr">
-        <is>
-          <t>② 李大霄信号落地条件</t>
-        </is>
-      </c>
-    </row>
-    <row r="170">
-      <c r="A170" s="140" t="inlineStr">
-        <is>
-          <t>③ 你的策略触发条件</t>
-        </is>
-      </c>
-    </row>
-    <row r="171">
-      <c r="A171" s="140" t="inlineStr">
-        <is>
-          <t>④ 堆叠赛道独立性</t>
-        </is>
-      </c>
-      <c r="C171" s="175" t="inlineStr">
-        <is>
-          <t>国内产业确定性，三源均未提及国内封测</t>
-        </is>
-      </c>
-      <c r="E171" s="178" t="inlineStr">
-        <is>
-          <t>→ 不受美股泡沫直接影响 → 等回调后优先配置</t>
-        </is>
-      </c>
-    </row>
-    <row r="172"/>
-    <row r="173">
-      <c r="A173" s="179" t="inlineStr">
-        <is>
-          <t>⚡ 一句话：三源确认AI泡沫风险+你的中期选举策略正确。虚P已记，等落地转实P。现金为王，堆叠赛道等回调后大仓位进。</t>
-        </is>
-      </c>
-    </row>
-    <row r="174"/>
-    <row r="175"/>
-    <row r="176"/>
-    <row r="177">
-      <c r="A177" s="147" t="inlineStr">
-        <is>
-          <t>🤖 人形机器人半年事件链</t>
-        </is>
-      </c>
-    </row>
-    <row r="178"/>
-    <row r="179">
-      <c r="A179" s="147" t="inlineStr">
-        <is>
-          <t>2026-03-23 机器人ETF暴跌-4.1%至0.909：市场恐慌+AI回调</t>
-        </is>
-      </c>
-    </row>
-    <row r="180">
-      <c r="A180" s="147" t="inlineStr">
-        <is>
-          <t>2026-04-08 机器人ETF暴涨+6.4%至0.967：人形机器人产业催化</t>
-        </is>
-      </c>
-      <c r="B180" s="149" t="n"/>
-      <c r="C180" s="149" t="n"/>
-      <c r="D180" s="149" t="n"/>
-      <c r="E180" s="149" t="n"/>
-      <c r="F180" s="149" t="n"/>
-      <c r="G180" s="149" t="n"/>
-      <c r="H180" s="150" t="n"/>
-    </row>
-    <row r="181">
-      <c r="A181" s="147" t="inlineStr">
-        <is>
-          <t>2026-05-07~22 机器人连续上涨：ETF 1.056→1.216(+15%)，宇树科技73天过会</t>
-        </is>
-      </c>
-    </row>
-    <row r="182">
-      <c r="A182" s="147" t="inlineStr">
-        <is>
-          <t>2026-05-25~06-02 机器人回调：1.216→1.122(-7.7%)，仍处强势区间</t>
-        </is>
-      </c>
-    </row>
-    <row r="183">
-      <c r="A183" s="180" t="inlineStr">
-        <is>
-          <t>2026-06-04 【保持观察】霍尔木兹海峡Day 12：伊朗暂停谈判+美众议院限制动武，WTI $96→$91-93回落，方向趋于缓和</t>
-        </is>
-      </c>
-      <c r="B183" s="181" t="n"/>
-      <c r="C183" s="181" t="n"/>
-      <c r="D183" s="181" t="n"/>
-      <c r="E183" s="181" t="n"/>
-      <c r="F183" s="181" t="n"/>
-      <c r="G183" s="181" t="n"/>
-      <c r="H183" s="181" t="n"/>
-    </row>
-    <row r="184">
-      <c r="A184" s="182" t="inlineStr">
-        <is>
-          <t>🔔 待重仓监控</t>
-        </is>
-      </c>
-    </row>
-    <row r="185">
-      <c r="A185" s="183" t="inlineStr">
-        <is>
-          <t>标的</t>
-        </is>
-      </c>
-      <c r="B185" s="183" t="inlineStr">
-        <is>
-          <t>状态</t>
-        </is>
-      </c>
-      <c r="C185" s="183" t="inlineStr">
-        <is>
-          <t>当前P/价格</t>
-        </is>
-      </c>
-      <c r="D185" s="183" t="inlineStr">
-        <is>
-          <t>最新信号</t>
-        </is>
-      </c>
-      <c r="E185" s="183" t="inlineStr">
-        <is>
-          <t>触发条件</t>
-        </is>
-      </c>
-      <c r="F185" s="183" t="inlineStr">
-        <is>
-          <t>距离触发</t>
-        </is>
-      </c>
-      <c r="G185" s="183" t="inlineStr">
-        <is>
-          <t>跟踪日期</t>
-        </is>
-      </c>
-    </row>
-    <row r="186">
-      <c r="A186" s="147" t="inlineStr">
-        <is>
-          <t>玻璃基板</t>
-        </is>
-      </c>
-      <c r="B186" s="147" t="inlineStr">
-        <is>
-          <t>深南电路002916/兴森科技002436</t>
-        </is>
-      </c>
-      <c r="C186" s="147" t="inlineStr">
-        <is>
-          <t>观察中</t>
-        </is>
-      </c>
-      <c r="D186" s="147" t="inlineStr">
-        <is>
-          <t>蒋宇飞：玻璃基板大规模应用2028年，5-10年赛道</t>
-        </is>
-      </c>
-      <c r="E186" s="147" t="inlineStr">
-        <is>
-          <t>AI基建+国产替代加速</t>
-        </is>
-      </c>
-      <c r="F186" s="147" t="inlineStr">
-        <is>
-          <t>中长期</t>
-        </is>
-      </c>
-      <c r="G186" s="147" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-    </row>
-    <row r="187">
-      <c r="A187" s="138" t="n"/>
-    </row>
-    <row r="188">
-      <c r="A188" s="147" t="inlineStr">
-        <is>
-          <t>油气对冲</t>
-        </is>
-      </c>
-      <c r="B188" s="147" t="inlineStr">
-        <is>
-          <t>华宝油气162411</t>
-        </is>
-      </c>
-      <c r="C188" s="147" t="inlineStr">
-        <is>
-          <t>观察中</t>
-        </is>
-      </c>
-      <c r="D188" s="147" t="inlineStr">
-        <is>
-          <t>宋鸿兵：霍尔木兹封锁3个月，85%投资者押注回落=幻觉</t>
-        </is>
-      </c>
-      <c r="E188" s="147" t="inlineStr">
-        <is>
-          <t>油价冲150或海峡持续封锁</t>
-        </is>
-      </c>
-      <c r="F188" s="147" t="inlineStr">
-        <is>
-          <t>短期</t>
-        </is>
-      </c>
-      <c r="G188" s="147" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="H188" s="138" t="inlineStr">
-        <is>
-          <t>小仓位试水，不对称博弈</t>
-        </is>
-      </c>
-    </row>
-    <row r="189">
-      <c r="A189" s="147" t="inlineStr">
-        <is>
-          <t>银行板块(512800)</t>
-        </is>
-      </c>
-      <c r="B189" s="149" t="n"/>
-      <c r="C189" s="149" t="n"/>
-      <c r="D189" s="149" t="n"/>
-      <c r="E189" s="149" t="n"/>
-      <c r="F189" s="149" t="n"/>
-      <c r="G189" s="149" t="n"/>
-      <c r="H189" s="150" t="n"/>
-    </row>
-    <row r="190">
-      <c r="A190" s="147" t="inlineStr">
-        <is>
-          <t>人形机器人(562500)</t>
-        </is>
-      </c>
-      <c r="B190" s="147" t="inlineStr">
-        <is>
-          <t>强势</t>
-        </is>
-      </c>
-      <c r="C190" s="147" t="inlineStr">
-        <is>
-          <t>P:58%(估)</t>
-        </is>
-      </c>
-      <c r="D190" s="147" t="inlineStr">
-        <is>
-          <t>宇树科技73天过会，ETF涨+11%</t>
-        </is>
-      </c>
-      <c r="E190" s="147" t="inlineStr">
-        <is>
-          <t>重点关注</t>
-        </is>
-      </c>
-      <c r="F190" s="147" t="inlineStr">
-        <is>
-          <t>中期</t>
-        </is>
-      </c>
-      <c r="G190" s="147" t="inlineStr">
-        <is>
-          <t>2026-06-03</t>
-        </is>
-      </c>
-      <c r="H190" s="138" t="inlineStr">
-        <is>
-          <t>平安先进制造+永赢先进制造</t>
-        </is>
-      </c>
-    </row>
-    <row r="191">
-      <c r="A191" s="147" t="inlineStr">
-        <is>
-          <t>存储赛道(5只A股)</t>
-        </is>
-      </c>
-      <c r="B191" s="149" t="n"/>
-      <c r="C191" s="149" t="n"/>
-      <c r="D191" s="149" t="n"/>
-      <c r="E191" s="149" t="n"/>
-      <c r="F191" s="149" t="n"/>
-      <c r="G191" s="149" t="n"/>
-      <c r="H191" s="150" t="n"/>
-    </row>
-    <row r="192">
-      <c r="A192" s="147" t="inlineStr">
-        <is>
-          <t>澜起科技(688008)</t>
         </is>
       </c>
       <c r="B192" s="149" t="n"/>
@@ -4765,631 +4087,763 @@
       <c r="H192" s="150" t="n"/>
     </row>
     <row r="193">
-      <c r="A193" s="184" t="inlineStr">
-        <is>
-          <t>🔥堆叠/先进封装赛道（蒋宇飞"星光纯叠"框架）</t>
-        </is>
-      </c>
+      <c r="A193" s="138" t="n"/>
     </row>
     <row r="194">
-      <c r="A194" s="147" t="inlineStr">
-        <is>
-          <t>长电科技(600584)</t>
-        </is>
-      </c>
-      <c r="B194" s="147" t="inlineStr">
-        <is>
-          <t>🔴核心标的</t>
-        </is>
-      </c>
-      <c r="C194" s="147" t="inlineStr">
-        <is>
-          <t>P:75%+ PE30x</t>
-        </is>
-      </c>
-      <c r="D194" s="147" t="inlineStr">
-        <is>
-          <t>全球第三大封测厂，2.5D/3D量产级，客户广度最强（高通/海思/TI）</t>
-        </is>
-      </c>
-      <c r="E194" s="147" t="inlineStr">
-        <is>
-          <t>等中期选举大跌</t>
-        </is>
-      </c>
-      <c r="F194" s="147" t="inlineStr">
-        <is>
-          <t>中期</t>
-        </is>
-      </c>
-      <c r="G194" s="147" t="inlineStr">
-        <is>
-          <t>2026-06-04</t>
-        </is>
-      </c>
-      <c r="H194" s="138" t="inlineStr">
-        <is>
-          <t>安全边际大，堆叠赛道首选</t>
+      <c r="A194" s="165" t="inlineStr">
+        <is>
+          <t>三、现金策略联动（锁定大部分现金储备）</t>
         </is>
       </c>
     </row>
     <row r="195">
-      <c r="A195" s="147" t="inlineStr">
-        <is>
-          <t>通富微电(002156)</t>
-        </is>
-      </c>
-      <c r="B195" s="147" t="inlineStr">
-        <is>
-          <t>🔴核心标的</t>
-        </is>
-      </c>
-      <c r="C195" s="147" t="inlineStr">
-        <is>
-          <t>P:75%+ 待查PE</t>
-        </is>
-      </c>
-      <c r="D195" s="147" t="inlineStr">
-        <is>
-          <t>AMD封测全线突破通道，2.5D量产，MI300X参与，不可替代</t>
-        </is>
-      </c>
-      <c r="E195" s="147" t="inlineStr">
-        <is>
-          <t>等中期选举大跌</t>
-        </is>
-      </c>
-      <c r="F195" s="147" t="inlineStr">
-        <is>
-          <t>中期</t>
-        </is>
-      </c>
-      <c r="G195" s="147" t="inlineStr">
-        <is>
-          <t>2026-06-04</t>
-        </is>
-      </c>
-      <c r="H195" s="138" t="inlineStr">
-        <is>
-          <t>安全边际中偏大，与长电各占一半</t>
+      <c r="A195" s="154" t="inlineStr">
+        <is>
+          <t>三源联动→达利欧65-75%概率年底AI回调+中期选举历史跌一波→锁定大部分现金→等11月回调入场</t>
         </is>
       </c>
     </row>
     <row r="196">
-      <c r="A196" s="138" t="n"/>
+      <c r="A196" s="161" t="inlineStr">
+        <is>
+          <t>维度</t>
+        </is>
+      </c>
     </row>
     <row r="197">
-      <c r="A197" s="138" t="n"/>
+      <c r="A197" s="157" t="inlineStr">
+        <is>
+          <t>现金锁定</t>
+        </is>
+      </c>
+      <c r="B197" s="149" t="n"/>
+      <c r="C197" s="149" t="n"/>
+      <c r="D197" s="149" t="n"/>
+      <c r="E197" s="149" t="n"/>
+      <c r="F197" s="149" t="n"/>
+      <c r="G197" s="149" t="n"/>
+      <c r="H197" s="150" t="n"/>
     </row>
     <row r="198">
-      <c r="A198" s="316" t="inlineStr">
-        <is>
-          <t>🔥 蒋宇飞179视频深度分析 (2026-06-07 顶级置信度)</t>
+      <c r="A198" s="157" t="inlineStr">
+        <is>
+          <t>等待窗口</t>
+        </is>
+      </c>
+      <c r="B198" s="157" t="inlineStr">
+        <is>
+          <t>2026年11月中期选举前后</t>
+        </is>
+      </c>
+      <c r="C198" s="157" t="inlineStr">
+        <is>
+          <t>→约5个月等待期</t>
         </is>
       </c>
     </row>
     <row r="199">
-      <c r="A199" s="138" t="inlineStr">
-        <is>
-          <t>核心框架: 星光纯叠=光模块(贯穿)→存储(吃肉)→堆叠(最大风口) | AI基建10年: 存力→算力→运力 | 2027算力长城=升腾+长鑫+DeepSeek</t>
+      <c r="A199" s="157" t="inlineStr">
+        <is>
+          <t>触发条件</t>
+        </is>
+      </c>
+      <c r="B199" s="157" t="inlineStr">
+        <is>
+          <t>美股跌一波+AI回调&gt;15%</t>
+        </is>
+      </c>
+      <c r="C199" s="157" t="inlineStr">
+        <is>
+          <t>→达利欧65-75%概率事件</t>
         </is>
       </c>
     </row>
     <row r="200">
-      <c r="A200" s="138" t="inlineStr">
-        <is>
-          <t>【P值调整】芯片 41%→44%(虚P+3pp) | 稀金 40%→41%(虚P+1pp) | 其余0pp</t>
-        </is>
-      </c>
-    </row>
-    <row r="201"/>
+      <c r="A200" s="157" t="inlineStr">
+        <is>
+          <t>入场标的</t>
+        </is>
+      </c>
+      <c r="B200" s="157" t="inlineStr">
+        <is>
+          <t>堆叠：长电科技+通富微电</t>
+        </is>
+      </c>
+      <c r="C200" s="157" t="inlineStr">
+        <is>
+          <t>→国内确定性不受美股影响</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" s="157" t="inlineStr">
+        <is>
+          <t>机会成本</t>
+        </is>
+      </c>
+      <c r="B201" s="157" t="inlineStr">
+        <is>
+          <t>持有现金5个月vs错过短期行情</t>
+        </is>
+      </c>
+      <c r="C201" s="157" t="inlineStr">
+        <is>
+          <t>→见下方机会成本联动</t>
+        </is>
+      </c>
+    </row>
     <row r="202">
-      <c r="A202" s="138" t="inlineStr">
-        <is>
-          <t>MLCC被动元件</t>
-        </is>
-      </c>
-    </row>
-    <row r="203">
-      <c r="A203" s="138" t="inlineStr">
-        <is>
-          <t>国产算力/升腾链</t>
-        </is>
-      </c>
-      <c r="B203" s="138" t="inlineStr">
-        <is>
-          <t>观察中</t>
-        </is>
-      </c>
-      <c r="C203" s="138" t="inlineStr">
-        <is>
-          <t>蒋宇飞: 2027算力长城最闪亮 | 升腾950明年出货 | 升腾+长鑫+DeepSeek</t>
-        </is>
-      </c>
-      <c r="D203" s="138" t="inlineStr">
-        <is>
-          <t>2026-06-07</t>
-        </is>
-      </c>
-    </row>
+      <c r="A202" s="157" t="inlineStr">
+        <is>
+          <t>下行保护</t>
+        </is>
+      </c>
+      <c r="B202" s="149" t="n"/>
+      <c r="C202" s="149" t="n"/>
+      <c r="D202" s="149" t="n"/>
+      <c r="E202" s="149" t="n"/>
+      <c r="F202" s="149" t="n"/>
+      <c r="G202" s="149" t="n"/>
+      <c r="H202" s="150" t="n"/>
+    </row>
+    <row r="203"/>
     <row r="204">
-      <c r="A204" s="138" t="inlineStr">
-        <is>
-          <t>HBM产业链</t>
-        </is>
-      </c>
-      <c r="B204" s="138" t="inlineStr">
-        <is>
-          <t>观察中</t>
-        </is>
-      </c>
-      <c r="C204" s="138" t="inlineStr">
-        <is>
-          <t>蒋宇飞: HBM未来1.5-2.5年波涛汹涌 | Q4-Q1热潮 | 技术含量最高</t>
-        </is>
-      </c>
-      <c r="D204" s="138" t="inlineStr">
-        <is>
-          <t>2026-06-07</t>
+      <c r="A204" s="165" t="inlineStr">
+        <is>
+          <t>四、机会成本联动分析（现金锁定vs其他选项）</t>
         </is>
       </c>
     </row>
     <row r="205">
-      <c r="A205" s="138" t="inlineStr">
-        <is>
-          <t>CPU产业链</t>
-        </is>
-      </c>
-      <c r="B205" s="138" t="inlineStr">
-        <is>
-          <t>观察中</t>
-        </is>
-      </c>
-      <c r="C205" s="138" t="inlineStr">
-        <is>
-          <t>蒋宇飞: agent经济导致CPU爆发缺货 | 带动产业链</t>
-        </is>
-      </c>
-      <c r="D205" s="138" t="inlineStr">
-        <is>
-          <t>2026-06-07</t>
+      <c r="A205" s="161" t="inlineStr">
+        <is>
+          <t>选项</t>
+        </is>
+      </c>
+      <c r="B205" s="161" t="inlineStr">
+        <is>
+          <t>P值</t>
+        </is>
+      </c>
+      <c r="C205" s="161" t="inlineStr">
+        <is>
+          <t>盈亏比</t>
+        </is>
+      </c>
+      <c r="D205" s="161" t="inlineStr">
+        <is>
+          <t>Score</t>
+        </is>
+      </c>
+      <c r="E205" s="161" t="inlineStr">
+        <is>
+          <t>现金锁定影响</t>
+        </is>
+      </c>
+      <c r="F205" s="161" t="inlineStr">
+        <is>
+          <t>建议</t>
+        </is>
+      </c>
+      <c r="G205" s="161" t="inlineStr">
+        <is>
+          <t>判断</t>
         </is>
       </c>
     </row>
     <row r="206">
-      <c r="A206" s="138" t="inlineStr">
-        <is>
-          <t>玻璃基板(更新)</t>
-        </is>
-      </c>
-      <c r="B206" s="138" t="inlineStr">
-        <is>
-          <t>观察中</t>
-        </is>
-      </c>
-      <c r="C206" s="138" t="inlineStr">
-        <is>
-          <t>蒋宇飞: 两三年热点→业绩2027-H2→大规模2028 | 封装+存储</t>
-        </is>
-      </c>
-      <c r="D206" s="138" t="inlineStr">
-        <is>
-          <t>2026-06-07</t>
-        </is>
-      </c>
-    </row>
-    <row r="207"/>
+      <c r="A206" s="157" t="inlineStr">
+        <is>
+          <t>长电科技</t>
+        </is>
+      </c>
+      <c r="B206" s="157" t="inlineStr">
+        <is>
+          <t>75%</t>
+        </is>
+      </c>
+      <c r="C206" s="157" t="inlineStr">
+        <is>
+          <t>4.5:1</t>
+        </is>
+      </c>
+      <c r="D206" s="157" t="inlineStr">
+        <is>
+          <t>3.375</t>
+        </is>
+      </c>
+      <c r="E206" s="157" t="inlineStr">
+        <is>
+          <t>等回调大仓位
+现金锁定中</t>
+        </is>
+      </c>
+      <c r="F206" s="157" t="inlineStr">
+        <is>
+          <t>暂不动等11月</t>
+        </is>
+      </c>
+      <c r="G206" s="160" t="inlineStr">
+        <is>
+          <t>🔴最高优先</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" s="157" t="inlineStr">
+        <is>
+          <t>通富微电</t>
+        </is>
+      </c>
+      <c r="B207" s="149" t="n"/>
+      <c r="C207" s="149" t="n"/>
+      <c r="D207" s="149" t="n"/>
+      <c r="E207" s="149" t="n"/>
+      <c r="F207" s="149" t="n"/>
+      <c r="G207" s="149" t="n"/>
+      <c r="H207" s="150" t="n"/>
+    </row>
     <row r="208">
-      <c r="A208" s="138" t="inlineStr">
-        <is>
-          <t>【堆叠75%验证】27条堆叠主题: "两年最大风口"+"一年半大放"+"存算一体"→P合理</t>
+      <c r="A208" s="157" t="inlineStr">
+        <is>
+          <t>养殖</t>
+        </is>
+      </c>
+      <c r="B208" s="157" t="inlineStr">
+        <is>
+          <t>70%</t>
+        </is>
+      </c>
+      <c r="C208" s="157" t="inlineStr">
+        <is>
+          <t>2.0:1</t>
+        </is>
+      </c>
+      <c r="D208" s="157" t="inlineStr">
+        <is>
+          <t>1.400</t>
+        </is>
+      </c>
+      <c r="E208" s="157" t="inlineStr">
+        <is>
+          <t>已持仓不需现金 | 6/5 芳姐：低价抄底母猪，行业融资枯竭，等待母猪血流成河才是最佳买点</t>
+        </is>
+      </c>
+      <c r="F208" s="157" t="inlineStr">
+        <is>
+          <t>继续持有</t>
+        </is>
+      </c>
+      <c r="G208" s="158" t="inlineStr">
+        <is>
+          <t>✅已配置</t>
         </is>
       </c>
     </row>
     <row r="209">
-      <c r="A209" s="138" t="inlineStr">
-        <is>
-          <t>【存储降级确认】"存储跌80%但现在是时机"+"消费级见顶"+"存储涨完轮到堆叠"→降级合理</t>
-        </is>
-      </c>
-    </row>
-    <row r="210"/>
-    <row r="211"/>
-    <row r="212"/>
-    <row r="213"/>
+      <c r="A209" s="157" t="inlineStr">
+        <is>
+          <t>电池</t>
+        </is>
+      </c>
+      <c r="B209" s="157" t="inlineStr">
+        <is>
+          <t>65%</t>
+        </is>
+      </c>
+      <c r="C209" s="157" t="inlineStr">
+        <is>
+          <t>2.0:1</t>
+        </is>
+      </c>
+      <c r="D209" s="157" t="inlineStr">
+        <is>
+          <t>1.300</t>
+        </is>
+      </c>
+      <c r="E209" s="157" t="inlineStr">
+        <is>
+          <t>已持仓不需现金 | 6/5 闻号说经济：厄尔尼诺80%概率+AI用电爆发→电力/能源受益</t>
+        </is>
+      </c>
+      <c r="F209" s="157" t="inlineStr">
+        <is>
+          <t>继续持有</t>
+        </is>
+      </c>
+      <c r="G209" s="158" t="inlineStr">
+        <is>
+          <t>✅已配置</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" s="157" t="inlineStr">
+        <is>
+          <t>核电</t>
+        </is>
+      </c>
+      <c r="B210" s="157" t="inlineStr">
+        <is>
+          <t>52%</t>
+        </is>
+      </c>
+      <c r="C210" s="157" t="inlineStr">
+        <is>
+          <t>1.5:1</t>
+        </is>
+      </c>
+      <c r="D210" s="157" t="inlineStr">
+        <is>
+          <t>0.780</t>
+        </is>
+      </c>
+      <c r="E210" s="157" t="inlineStr">
+        <is>
+          <t>10年维度
+小仓试水可行</t>
+        </is>
+      </c>
+      <c r="F210" s="157" t="inlineStr">
+        <is>
+          <t>不影响现金策略</t>
+        </is>
+      </c>
+      <c r="G210" s="166" t="inlineStr">
+        <is>
+          <t>🟡长期观察</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" s="157" t="inlineStr">
+        <is>
+          <t>存储</t>
+        </is>
+      </c>
+      <c r="B211" s="157" t="inlineStr">
+        <is>
+          <t>55%</t>
+        </is>
+      </c>
+      <c r="C211" s="157" t="inlineStr">
+        <is>
+          <t>1.0:1</t>
+        </is>
+      </c>
+      <c r="D211" s="157" t="inlineStr">
+        <is>
+          <t>0.550</t>
+        </is>
+      </c>
+      <c r="E211" s="157" t="inlineStr">
+        <is>
+          <t>已降级</t>
+        </is>
+      </c>
+      <c r="F211" s="157" t="inlineStr">
+        <is>
+          <t>不动</t>
+        </is>
+      </c>
+      <c r="G211" s="160" t="inlineStr">
+        <is>
+          <t>❌已降级</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" s="157" t="inlineStr">
+        <is>
+          <t>纯现金5月</t>
+        </is>
+      </c>
+      <c r="B212" s="149" t="n"/>
+      <c r="C212" s="149" t="n"/>
+      <c r="D212" s="149" t="n"/>
+      <c r="E212" s="149" t="n"/>
+      <c r="F212" s="149" t="n"/>
+      <c r="G212" s="149" t="n"/>
+      <c r="H212" s="150" t="n"/>
+    </row>
+    <row r="213">
+      <c r="A213" s="147" t="inlineStr">
+        <is>
+          <t>AI硬件确定性(付鹏) → 内存=AI核心瓶颈(4信源互锁) → 国产替代加速 → 稀土断供日本 → 芯片/存储/HBM长期利好 | 短期被利率↑/地缘↑压制</t>
+        </is>
+      </c>
+    </row>
     <row r="214">
-      <c r="A214" s="153" t="inlineStr">
-        <is>
-          <t>📖 机制库 v3（2026-06-04 经小龙虾审核修订）</t>
-        </is>
-      </c>
+      <c r="A214" s="167" t="inlineStr">
+        <is>
+          <t>五、虚P→实P转换条件 &amp; 操作触发</t>
+        </is>
+      </c>
+      <c r="B214" s="149" t="n"/>
+      <c r="C214" s="149" t="n"/>
+      <c r="D214" s="149" t="n"/>
+      <c r="E214" s="149" t="n"/>
+      <c r="F214" s="149" t="n"/>
+      <c r="G214" s="149" t="n"/>
+      <c r="H214" s="150" t="n"/>
     </row>
     <row r="215">
-      <c r="A215" s="185" t="inlineStr">
-        <is>
-          <t>[机制3v3] 现金锁定系数（CLC）— 平方衰减版</t>
+      <c r="A215" s="156" t="inlineStr">
+        <is>
+          <t>条件</t>
+        </is>
+      </c>
+      <c r="B215" s="161" t="inlineStr">
+        <is>
+          <t>触发信号</t>
+        </is>
+      </c>
+      <c r="C215" s="156" t="inlineStr">
+        <is>
+          <t>影响</t>
+        </is>
+      </c>
+      <c r="D215" s="156" t="inlineStr">
+        <is>
+          <t>操作</t>
+        </is>
+      </c>
+      <c r="E215" s="147" t="inlineStr">
+        <is>
+          <t>2026-05-30 宋鸿兵：海峡封锁→能源成本飙升</t>
+        </is>
+      </c>
+      <c r="F215" s="147" t="inlineStr">
+        <is>
+          <t>2026-05-30 岩松：存储1-2年产能饱和</t>
+        </is>
+      </c>
+      <c r="G215" s="147" t="inlineStr">
+        <is>
+          <t>2026-05-30 宋鸿兵：30年美债破5%双红线</t>
         </is>
       </c>
     </row>
     <row r="216">
-      <c r="A216" s="186" t="inlineStr">
-        <is>
-          <t>叫什么</t>
-        </is>
-      </c>
-      <c r="B216" s="149" t="n"/>
-      <c r="C216" s="149" t="n"/>
-      <c r="D216" s="149" t="n"/>
-      <c r="E216" s="149" t="n"/>
-      <c r="F216" s="149" t="n"/>
-      <c r="G216" s="149" t="n"/>
-      <c r="H216" s="150" t="n"/>
+      <c r="A216" s="170" t="inlineStr">
+        <is>
+          <t>达利欧落地</t>
+        </is>
+      </c>
+      <c r="B216" s="157" t="inlineStr">
+        <is>
+          <t>七姐妹&gt;15%回调或破200日均线</t>
+        </is>
+      </c>
+      <c r="C216" s="157" t="inlineStr">
+        <is>
+          <t>芯片/恒科虚P转实P</t>
+        </is>
+      </c>
+      <c r="D216" s="157" t="inlineStr">
+        <is>
+          <t>现金解锁→大仓位进堆叠</t>
+        </is>
+      </c>
     </row>
     <row r="217">
-      <c r="A217" s="186" t="inlineStr">
-        <is>
-          <t>公式</t>
-        </is>
-      </c>
-      <c r="B217" s="147" t="inlineStr">
-        <is>
-          <t>CLC = 信号概率 × 互锁强度 × 时间衰减²</t>
+      <c r="A217" s="166" t="inlineStr">
+        <is>
+          <t>李大霄落地</t>
+        </is>
+      </c>
+      <c r="B217" s="157" t="inlineStr">
+        <is>
+          <t>多数成分股下跌+指数拐头</t>
+        </is>
+      </c>
+      <c r="C217" s="157" t="inlineStr">
+        <is>
+          <t>恒科/芯片虚P转实P</t>
+        </is>
+      </c>
+      <c r="D217" s="157" t="inlineStr">
+        <is>
+          <t>确认系统性风险→入场</t>
         </is>
       </c>
     </row>
     <row r="218">
-      <c r="A218" s="186" t="inlineStr">
-        <is>
-          <t>时间衰减</t>
-        </is>
-      </c>
-      <c r="B218" s="147" t="inlineStr">
-        <is>
-          <t>T = (距触发月数/12)²</t>
-        </is>
-      </c>
-      <c r="C218" s="147" t="inlineStr">
-        <is>
-          <t>6月=(5/12)²=0.174</t>
-        </is>
-      </c>
-      <c r="D218" s="147" t="inlineStr">
-        <is>
-          <t>11月=0</t>
+      <c r="A218" s="171" t="inlineStr">
+        <is>
+          <t>中期选举</t>
+        </is>
+      </c>
+      <c r="B218" s="171" t="inlineStr">
+        <is>
+          <t>11月美股跌一波</t>
+        </is>
+      </c>
+      <c r="C218" s="171" t="inlineStr">
+        <is>
+          <t>你的策略触发</t>
+        </is>
+      </c>
+      <c r="D218" s="171" t="inlineStr">
+        <is>
+          <t>现金→长电+通富</t>
+        </is>
+      </c>
+      <c r="E218" s="156" t="inlineStr">
+        <is>
+          <t>落地条件</t>
+        </is>
+      </c>
+      <c r="F218" s="156" t="inlineStr">
+        <is>
+          <t>状态</t>
+        </is>
+      </c>
+      <c r="G218" s="156" t="inlineStr">
+        <is>
+          <t>权重</t>
+        </is>
+      </c>
+      <c r="H218" s="156" t="inlineStr">
+        <is>
+          <t>备注</t>
         </is>
       </c>
     </row>
     <row r="219">
-      <c r="A219" s="186" t="inlineStr">
-        <is>
-          <t>为什么平方</t>
-        </is>
-      </c>
-      <c r="B219" s="147" t="inlineStr">
-        <is>
-          <t>线性衰减导致越近触发日锁得越少（反直觉）</t>
-        </is>
-      </c>
-      <c r="C219" s="147" t="inlineStr">
-        <is>
-          <t>平方函数：远离时多锁，临近时少锁</t>
-        </is>
-      </c>
-      <c r="D219" s="147" t="inlineStr">
-        <is>
-          <t>小龙虾审核通过</t>
-        </is>
-      </c>
+      <c r="A219" s="157" t="inlineStr">
+        <is>
+          <t>堆叠独立</t>
+        </is>
+      </c>
+      <c r="B219" s="149" t="n"/>
+      <c r="C219" s="149" t="n"/>
+      <c r="D219" s="149" t="n"/>
+      <c r="E219" s="149" t="n"/>
+      <c r="F219" s="149" t="n"/>
+      <c r="G219" s="149" t="n"/>
+      <c r="H219" s="150" t="n"/>
     </row>
     <row r="220">
-      <c r="A220" s="186" t="inlineStr">
-        <is>
-          <t>信号概率</t>
-        </is>
-      </c>
-      <c r="B220" s="149" t="n"/>
-      <c r="C220" s="149" t="n"/>
-      <c r="D220" s="149" t="n"/>
-      <c r="E220" s="149" t="n"/>
-      <c r="F220" s="149" t="n"/>
-      <c r="G220" s="149" t="n"/>
-      <c r="H220" s="150" t="n"/>
+      <c r="A220" s="157" t="inlineStr">
+        <is>
+          <t>李大霄
+金融界 6/4</t>
+        </is>
+      </c>
+      <c r="B220" s="157" t="inlineStr">
+        <is>
+          <t>美股窄牛宽熊
+仅20只创新高
+CAPE40倍→泡沫</t>
+        </is>
+      </c>
+      <c r="C220" s="158" t="inlineStr">
+        <is>
+          <t>🟢高度契合
+确认美股风险
+现金策略正确</t>
+        </is>
+      </c>
+      <c r="D220" s="157" t="inlineStr">
+        <is>
+          <t>美股全市场↓
+港股连带承压</t>
+        </is>
+      </c>
+      <c r="E220" s="157" t="inlineStr">
+        <is>
+          <t>纳指破200日均线
+或多数成分股下跌</t>
+        </is>
+      </c>
+      <c r="F220" s="159" t="inlineStr">
+        <is>
+          <t>⏳未落地
+(虚P状态)</t>
+        </is>
+      </c>
+      <c r="G220" s="157" t="inlineStr">
+        <is>
+          <t>⭐⭐⭐
+中高</t>
+        </is>
+      </c>
+      <c r="H220" s="157" t="inlineStr">
+        <is>
+          <t>6/4三源联动:
+恒科-2pp
+芯片-1pp
+→已记虚P
+未转实P</t>
+        </is>
+      </c>
     </row>
     <row r="221">
-      <c r="A221" s="186" t="inlineStr">
-        <is>
-          <t>互锁强度</t>
-        </is>
-      </c>
-      <c r="B221" s="147" t="inlineStr">
-        <is>
-          <t>三源强互锁=1.0</t>
-        </is>
-      </c>
-      <c r="C221" s="147" t="inlineStr">
-        <is>
-          <t>达利欧6月修正&gt;2次→降级0.85</t>
-        </is>
-      </c>
-      <c r="D221" s="147" t="inlineStr">
-        <is>
-          <t>有原因修正不降级</t>
-        </is>
-      </c>
+      <c r="A221" s="172" t="inlineStr">
+        <is>
+          <t>⚡ 核心结论：三源联动确认AI泡沫风险+你的中期选举策略正确。大部分现金锁定等11月回调→大仓位进长电/通富。机会成本可接受（不对称博弈，下有保底）。虚P已记，等落地转实P。</t>
+        </is>
+      </c>
+      <c r="B221" s="168" t="n"/>
+      <c r="C221" s="168" t="n"/>
+      <c r="D221" s="168" t="n"/>
+      <c r="E221" s="168" t="n"/>
+      <c r="F221" s="168" t="n"/>
+      <c r="G221" s="168" t="n"/>
+      <c r="H221" s="169" t="n"/>
     </row>
     <row r="222">
-      <c r="A222" s="186" t="inlineStr">
-        <is>
-          <t>当前值</t>
-        </is>
-      </c>
-      <c r="B222" s="147" t="inlineStr">
-        <is>
-          <t>0.70 × 1.0 × (5/12)² = 0.122</t>
-        </is>
-      </c>
-      <c r="C222" s="147" t="inlineStr">
-        <is>
-          <t>→ 锁定12.2%现金</t>
-        </is>
-      </c>
-      <c r="D222" s="147" t="inlineStr">
-        <is>
-          <t>可用87.8%</t>
+      <c r="A222" s="138" t="inlineStr">
+        <is>
+          <t>────────────────────────────────────────────────────────────</t>
         </is>
       </c>
     </row>
     <row r="223">
-      <c r="A223" s="186" t="inlineStr">
-        <is>
-          <t>每月重算</t>
-        </is>
-      </c>
-      <c r="B223" s="149" t="n"/>
-      <c r="C223" s="149" t="n"/>
-      <c r="D223" s="149" t="n"/>
-      <c r="E223" s="149" t="n"/>
-      <c r="F223" s="149" t="n"/>
-      <c r="G223" s="149" t="n"/>
-      <c r="H223" s="150" t="n"/>
-    </row>
-    <row r="224"/>
+      <c r="A223" s="173" t="inlineStr">
+        <is>
+          <t>🔗 三源互锁验证</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" s="140" t="inlineStr">
+        <is>
+          <t>达利欧 × 李大霄</t>
+        </is>
+      </c>
+      <c r="C224" s="174" t="inlineStr">
+        <is>
+          <t>✅ 强印证</t>
+        </is>
+      </c>
+      <c r="E224" s="175" t="inlineStr">
+        <is>
+          <t>AI泡沫+窄牛宽熊=同一现象两角度，互相确认</t>
+        </is>
+      </c>
+    </row>
     <row r="225">
-      <c r="A225" s="185" t="inlineStr">
-        <is>
-          <t>[机制4v3] 折后仓位计算 — 4级分级版</t>
+      <c r="A225" s="140" t="inlineStr">
+        <is>
+          <t>达利欧 × 知乎</t>
+        </is>
+      </c>
+      <c r="C225" s="176" t="inlineStr">
+        <is>
+          <t>⚠️ 部分矛盾</t>
+        </is>
+      </c>
+      <c r="E225" s="175" t="inlineStr">
+        <is>
+          <t>达利欧看流动性(泡沫将破) vs 知乎看估值(PE中值安全)</t>
         </is>
       </c>
     </row>
     <row r="226">
-      <c r="A226" s="186" t="inlineStr">
-        <is>
-          <t>叫什么</t>
-        </is>
-      </c>
-      <c r="B226" s="147" t="inlineStr">
-        <is>
-          <t>折后仓位（Folded Allocation）v3</t>
-        </is>
-      </c>
-    </row>
-    <row r="227">
-      <c r="A227" s="186" t="inlineStr">
-        <is>
-          <t>公式</t>
-        </is>
-      </c>
-      <c r="B227" s="147" t="inlineStr">
-        <is>
-          <t>折后仓位% = 原目标仓位% × (1 - CLC × β系数)</t>
-        </is>
-      </c>
-    </row>
+      <c r="A226" s="140" t="inlineStr">
+        <is>
+          <t>三源共识</t>
+        </is>
+      </c>
+      <c r="C226" s="177" t="inlineStr">
+        <is>
+          <t>🔴 核心共识</t>
+        </is>
+      </c>
+      <c r="E226" s="175" t="inlineStr">
+        <is>
+          <t>AI龙头估值偏高+市场极度集中+中小盘已熊 → 短期风险&gt;机会</t>
+        </is>
+      </c>
+    </row>
+    <row r="227"/>
     <row r="228">
-      <c r="A228" s="186" t="inlineStr">
-        <is>
-          <t>4级分级</t>
-        </is>
-      </c>
-      <c r="B228" s="147" t="inlineStr">
-        <is>
-          <t>L1高度暴露β=0.8（通富-AMD独供）</t>
-        </is>
-      </c>
-      <c r="C228" s="147" t="inlineStr">
-        <is>
-          <t>L2中度暴露β=0.5（长电-客户多元）</t>
+      <c r="A228" s="165" t="inlineStr">
+        <is>
+          <t>🎯 结论（虚P→实P转换条件）</t>
         </is>
       </c>
     </row>
     <row r="229">
-      <c r="A229" s="186" t="inlineStr">
-        <is>
-          <t>分级继续</t>
-        </is>
-      </c>
-      <c r="B229" s="147" t="inlineStr">
-        <is>
-          <t>L3弱相关β=0.1（养殖）</t>
-        </is>
-      </c>
-      <c r="C229" s="147" t="inlineStr">
-        <is>
-          <t>L4反向受益β=-0.3（黄金）</t>
+      <c r="A229" s="140" t="inlineStr">
+        <is>
+          <t>① 达利欧信号落地条件</t>
+        </is>
+      </c>
+      <c r="C229" s="175" t="inlineStr">
+        <is>
+          <t>纳指七姐妹出现&gt;15%回调 或 纳指破200日均线</t>
+        </is>
+      </c>
+      <c r="E229" s="178" t="inlineStr">
+        <is>
+          <t>→ 芯片/恒科虚P转实P → 确认减仓信号</t>
         </is>
       </c>
     </row>
     <row r="230">
-      <c r="A230" s="186" t="inlineStr">
-        <is>
-          <t>为什么分级</t>
-        </is>
-      </c>
-      <c r="B230" s="149" t="n"/>
-      <c r="C230" s="149" t="n"/>
-      <c r="D230" s="149" t="n"/>
-      <c r="E230" s="149" t="n"/>
-      <c r="F230" s="149" t="n"/>
-      <c r="G230" s="149" t="n"/>
-      <c r="H230" s="150" t="n"/>
+      <c r="A230" s="140" t="inlineStr">
+        <is>
+          <t>② 李大霄信号落地条件</t>
+        </is>
+      </c>
     </row>
     <row r="231">
-      <c r="A231" s="186" t="inlineStr">
-        <is>
-          <t>当前计算</t>
-        </is>
-      </c>
-      <c r="B231" s="147" t="inlineStr">
-        <is>
-          <t>通富:33%×(1-0.122×0.8)=30.1%</t>
-        </is>
-      </c>
-      <c r="C231" s="147" t="inlineStr">
-        <is>
-          <t>长电:37%×(1-0.122×0.5)=34.7%</t>
+      <c r="A231" s="140" t="inlineStr">
+        <is>
+          <t>③ 你的策略触发条件</t>
         </is>
       </c>
     </row>
     <row r="232">
-      <c r="A232" s="186" t="inlineStr">
-        <is>
-          <t>分级逻辑</t>
-        </is>
-      </c>
-      <c r="B232" s="149" t="n"/>
-      <c r="C232" s="149" t="n"/>
-      <c r="D232" s="149" t="n"/>
-      <c r="E232" s="149" t="n"/>
-      <c r="F232" s="149" t="n"/>
-      <c r="G232" s="149" t="n"/>
-      <c r="H232" s="150" t="n"/>
+      <c r="A232" s="140" t="inlineStr">
+        <is>
+          <t>④ 堆叠赛道独立性</t>
+        </is>
+      </c>
+      <c r="C232" s="175" t="inlineStr">
+        <is>
+          <t>国内产业确定性，三源均未提及国内封测</t>
+        </is>
+      </c>
+      <c r="E232" s="178" t="inlineStr">
+        <is>
+          <t>→ 不受美股泡沫直接影响 → 等回调后优先配置</t>
+        </is>
+      </c>
     </row>
     <row r="233"/>
     <row r="234">
-      <c r="A234" s="185" t="inlineStr">
-        <is>
-          <t>[机制5v3] 虚P→实P转换 — 确认窗口+因果链版</t>
-        </is>
-      </c>
-    </row>
-    <row r="235">
-      <c r="A235" s="186" t="inlineStr">
-        <is>
-          <t>叫什么</t>
-        </is>
-      </c>
-      <c r="B235" s="149" t="n"/>
-      <c r="C235" s="149" t="n"/>
-      <c r="D235" s="149" t="n"/>
-      <c r="E235" s="149" t="n"/>
-      <c r="F235" s="149" t="n"/>
-      <c r="G235" s="149" t="n"/>
-      <c r="H235" s="150" t="n"/>
-    </row>
-    <row r="236">
-      <c r="A236" s="186" t="inlineStr">
-        <is>
-          <t>视觉信号</t>
-        </is>
-      </c>
-      <c r="B236" s="147" t="inlineStr">
-        <is>
-          <t>纳指七姐妹&gt;15%回调（从52周高）</t>
-        </is>
-      </c>
-      <c r="C236" s="147" t="inlineStr">
-        <is>
-          <t>或破200日均线</t>
-        </is>
-      </c>
-    </row>
-    <row r="237">
-      <c r="A237" s="186" t="inlineStr">
-        <is>
-          <t>确认窗口</t>
-        </is>
-      </c>
-      <c r="B237" s="147" t="inlineStr">
-        <is>
-          <t>跌穿15%后维持5个交易日不反弹</t>
-        </is>
-      </c>
-      <c r="C237" s="147" t="inlineStr">
-        <is>
-          <t>防单日噪音和假触发</t>
-        </is>
-      </c>
-      <c r="D237" s="147" t="inlineStr">
-        <is>
-          <t>小龙虾建议</t>
-        </is>
-      </c>
-    </row>
+      <c r="A234" s="179" t="inlineStr">
+        <is>
+          <t>⚡ 一句话：三源确认AI泡沫风险+你的中期选举策略正确。虚P已记，等落地转实P。现金为王，堆叠赛道等回调后大仓位进。</t>
+        </is>
+      </c>
+    </row>
+    <row r="235"/>
+    <row r="236"/>
+    <row r="237"/>
     <row r="238">
-      <c r="A238" s="186" t="inlineStr">
-        <is>
-          <t>因果链</t>
-        </is>
-      </c>
-      <c r="B238" s="147" t="inlineStr">
-        <is>
-          <t>需至少2条佐证：</t>
-        </is>
-      </c>
-      <c r="C238" s="147" t="inlineStr">
-        <is>
-          <t>①英伟达/AMD下调指引</t>
-        </is>
-      </c>
-      <c r="D238" s="147" t="inlineStr">
-        <is>
-          <t>②AI ETF资金流出</t>
-        </is>
-      </c>
-    </row>
-    <row r="239">
-      <c r="A239" s="186" t="inlineStr">
-        <is>
-          <t>因果链继续</t>
-        </is>
-      </c>
-      <c r="B239" s="147" t="inlineStr">
-        <is>
-          <t>③投行下调AI评级</t>
-        </is>
-      </c>
-      <c r="C239" s="147" t="inlineStr">
-        <is>
-          <t>④Mag7裁员/削减开支</t>
-        </is>
-      </c>
-    </row>
+      <c r="A238" s="147" t="inlineStr">
+        <is>
+          <t>🤖 人形机器人半年事件链</t>
+        </is>
+      </c>
+    </row>
+    <row r="239"/>
     <row r="240">
-      <c r="A240" s="186" t="inlineStr">
-        <is>
-          <t>为什么加因果</t>
-        </is>
-      </c>
-      <c r="B240" s="147" t="inlineStr">
-        <is>
-          <t>15%下跌可能是地缘冲击不是AI泡沫</t>
-        </is>
-      </c>
-      <c r="C240" s="147" t="inlineStr">
-        <is>
-          <t>两者操作完全不同</t>
-        </is>
-      </c>
-      <c r="D240" s="147" t="inlineStr">
-        <is>
-          <t>必须区分原因</t>
+      <c r="A240" s="147" t="inlineStr">
+        <is>
+          <t>2026-03-23 机器人ETF暴跌-4.1%至0.909：市场恐慌+AI回调</t>
         </is>
       </c>
     </row>
     <row r="241">
-      <c r="A241" s="186" t="inlineStr">
-        <is>
-          <t>转换后</t>
+      <c r="A241" s="147" t="inlineStr">
+        <is>
+          <t>2026-04-08 机器人ETF暴涨+6.4%至0.967：人形机器人产业催化</t>
         </is>
       </c>
       <c r="B241" s="149" t="n"/>
@@ -5400,695 +4854,1569 @@
       <c r="G241" s="149" t="n"/>
       <c r="H241" s="150" t="n"/>
     </row>
-    <row r="242"/>
+    <row r="242">
+      <c r="A242" s="147" t="inlineStr">
+        <is>
+          <t>2026-05-07~22 机器人连续上涨：ETF 1.056→1.216(+15%)，宇树科技73天过会</t>
+        </is>
+      </c>
+    </row>
     <row r="243">
-      <c r="A243" s="187" t="inlineStr">
-        <is>
-          <t>[信号计分板] 每日更新，驱动信号概率动态调整</t>
+      <c r="A243" s="147" t="inlineStr">
+        <is>
+          <t>2026-05-25~06-02 机器人回调：1.216→1.122(-7.7%)，仍处强势区间</t>
         </is>
       </c>
     </row>
     <row r="244">
-      <c r="A244" s="186" t="inlineStr">
-        <is>
-          <t>泡沫正向信号</t>
-        </is>
-      </c>
-      <c r="B244" s="147" t="inlineStr">
-        <is>
-          <t>Mag7单日跌&gt;3% → +1</t>
-        </is>
-      </c>
-      <c r="C244" s="147" t="inlineStr">
-        <is>
-          <t>Mag7月跌&gt;10% → +2</t>
-        </is>
-      </c>
+      <c r="A244" s="180" t="inlineStr">
+        <is>
+          <t>2026-06-04 【保持观察】霍尔木兹海峡Day 12：伊朗暂停谈判+美众议院限制动武，WTI $96→$91-93回落，方向趋于缓和</t>
+        </is>
+      </c>
+      <c r="B244" s="181" t="n"/>
+      <c r="C244" s="181" t="n"/>
+      <c r="D244" s="181" t="n"/>
+      <c r="E244" s="181" t="n"/>
+      <c r="F244" s="181" t="n"/>
+      <c r="G244" s="181" t="n"/>
+      <c r="H244" s="181" t="n"/>
     </row>
     <row r="245">
-      <c r="B245" s="147" t="inlineStr">
-        <is>
-          <t>VIX&gt;30 → +2</t>
-        </is>
-      </c>
-      <c r="C245" s="147" t="inlineStr">
-        <is>
-          <t>AI公司裁员/下调指引 → +1</t>
+      <c r="A245" s="182" t="inlineStr">
+        <is>
+          <t>🔔 待重仓监控</t>
         </is>
       </c>
     </row>
     <row r="246">
-      <c r="B246" s="147" t="inlineStr">
-        <is>
-          <t>信用利差&gt;150bp → +2</t>
+      <c r="A246" s="183" t="inlineStr">
+        <is>
+          <t>标的</t>
+        </is>
+      </c>
+      <c r="B246" s="183" t="inlineStr">
+        <is>
+          <t>状态</t>
+        </is>
+      </c>
+      <c r="C246" s="183" t="inlineStr">
+        <is>
+          <t>当前P/价格</t>
+        </is>
+      </c>
+      <c r="D246" s="183" t="inlineStr">
+        <is>
+          <t>最新信号</t>
+        </is>
+      </c>
+      <c r="E246" s="183" t="inlineStr">
+        <is>
+          <t>触发条件</t>
+        </is>
+      </c>
+      <c r="F246" s="183" t="inlineStr">
+        <is>
+          <t>距离触发</t>
+        </is>
+      </c>
+      <c r="G246" s="183" t="inlineStr">
+        <is>
+          <t>跟踪日期</t>
         </is>
       </c>
     </row>
     <row r="247">
-      <c r="A247" s="186" t="inlineStr">
-        <is>
-          <t>泡沫反向信号</t>
+      <c r="A247" s="147" t="inlineStr">
+        <is>
+          <t>玻璃基板</t>
         </is>
       </c>
       <c r="B247" s="147" t="inlineStr">
         <is>
-          <t>Mag7单日涨&gt;3% → -1</t>
+          <t>深南电路002916/兴森科技002436</t>
         </is>
       </c>
       <c r="C247" s="147" t="inlineStr">
         <is>
-          <t>Mag7月涨&gt;8% → -2</t>
+          <t>观察中</t>
+        </is>
+      </c>
+      <c r="D247" s="147" t="inlineStr">
+        <is>
+          <t>蒋宇飞：玻璃基板大规模应用2028年，5-10年赛道</t>
+        </is>
+      </c>
+      <c r="E247" s="147" t="inlineStr">
+        <is>
+          <t>AI基建+国产替代加速</t>
+        </is>
+      </c>
+      <c r="F247" s="147" t="inlineStr">
+        <is>
+          <t>中长期</t>
+        </is>
+      </c>
+      <c r="G247" s="147" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
         </is>
       </c>
     </row>
     <row r="248">
-      <c r="B248" s="147" t="inlineStr">
-        <is>
-          <t>Fed降息 → -2</t>
-        </is>
-      </c>
-      <c r="C248" s="147" t="inlineStr">
-        <is>
-          <t>AI龙头超预期财报 → -1</t>
-        </is>
-      </c>
+      <c r="A248" s="138" t="n"/>
     </row>
     <row r="249">
+      <c r="A249" s="147" t="inlineStr">
+        <is>
+          <t>油气对冲</t>
+        </is>
+      </c>
       <c r="B249" s="147" t="inlineStr">
         <is>
-          <t>VIX&lt;15 → -1</t>
+          <t>华宝油气162411</t>
+        </is>
+      </c>
+      <c r="C249" s="147" t="inlineStr">
+        <is>
+          <t>观察中</t>
+        </is>
+      </c>
+      <c r="D249" s="147" t="inlineStr">
+        <is>
+          <t>宋鸿兵：霍尔木兹封锁3个月，85%投资者押注回落=幻觉</t>
+        </is>
+      </c>
+      <c r="E249" s="147" t="inlineStr">
+        <is>
+          <t>油价冲150或海峡持续封锁</t>
+        </is>
+      </c>
+      <c r="F249" s="147" t="inlineStr">
+        <is>
+          <t>短期</t>
+        </is>
+      </c>
+      <c r="G249" s="147" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="H249" s="138" t="inlineStr">
+        <is>
+          <t>小仓位试水，不对称博弈</t>
         </is>
       </c>
     </row>
     <row r="250">
-      <c r="A250" s="186" t="inlineStr">
-        <is>
-          <t>更新规则</t>
-        </is>
-      </c>
-      <c r="B250" s="147" t="inlineStr">
-        <is>
-          <t>每月第一天：信号概率=70%+上月净计分×5pp</t>
-        </is>
-      </c>
-      <c r="C250" s="147" t="inlineStr">
-        <is>
-          <t>底线55%上限85%</t>
-        </is>
-      </c>
+      <c r="A250" s="147" t="inlineStr">
+        <is>
+          <t>银行板块(512800)</t>
+        </is>
+      </c>
+      <c r="B250" s="149" t="n"/>
+      <c r="C250" s="149" t="n"/>
+      <c r="D250" s="149" t="n"/>
+      <c r="E250" s="149" t="n"/>
+      <c r="F250" s="149" t="n"/>
+      <c r="G250" s="149" t="n"/>
+      <c r="H250" s="150" t="n"/>
     </row>
     <row r="251">
-      <c r="A251" s="186" t="inlineStr">
-        <is>
-          <t>Mag7权重</t>
-        </is>
-      </c>
-      <c r="B251" s="149" t="n"/>
-      <c r="C251" s="149" t="n"/>
-      <c r="D251" s="149" t="n"/>
-      <c r="E251" s="149" t="n"/>
-      <c r="F251" s="149" t="n"/>
-      <c r="G251" s="149" t="n"/>
-      <c r="H251" s="150" t="n"/>
-    </row>
-    <row r="252"/>
+      <c r="A251" s="147" t="inlineStr">
+        <is>
+          <t>人形机器人(562500)</t>
+        </is>
+      </c>
+      <c r="B251" s="147" t="inlineStr">
+        <is>
+          <t>强势</t>
+        </is>
+      </c>
+      <c r="C251" s="147" t="inlineStr">
+        <is>
+          <t>P:58%(估)</t>
+        </is>
+      </c>
+      <c r="D251" s="147" t="inlineStr">
+        <is>
+          <t>宇树科技73天过会，ETF涨+11%</t>
+        </is>
+      </c>
+      <c r="E251" s="147" t="inlineStr">
+        <is>
+          <t>重点关注</t>
+        </is>
+      </c>
+      <c r="F251" s="147" t="inlineStr">
+        <is>
+          <t>中期</t>
+        </is>
+      </c>
+      <c r="G251" s="147" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="H251" s="138" t="inlineStr">
+        <is>
+          <t>平安先进制造+永赢先进制造</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" s="147" t="inlineStr">
+        <is>
+          <t>存储赛道(5只A股)</t>
+        </is>
+      </c>
+      <c r="B252" s="149" t="n"/>
+      <c r="C252" s="149" t="n"/>
+      <c r="D252" s="149" t="n"/>
+      <c r="E252" s="149" t="n"/>
+      <c r="F252" s="149" t="n"/>
+      <c r="G252" s="149" t="n"/>
+      <c r="H252" s="150" t="n"/>
+    </row>
     <row r="253">
-      <c r="A253" s="187" t="inlineStr">
-        <is>
-          <t>⚡ 机制v3使用指南</t>
-        </is>
-      </c>
+      <c r="A253" s="147" t="inlineStr">
+        <is>
+          <t>澜起科技(688008)</t>
+        </is>
+      </c>
+      <c r="B253" s="149" t="n"/>
+      <c r="C253" s="149" t="n"/>
+      <c r="D253" s="149" t="n"/>
+      <c r="E253" s="149" t="n"/>
+      <c r="F253" s="149" t="n"/>
+      <c r="G253" s="149" t="n"/>
+      <c r="H253" s="150" t="n"/>
     </row>
     <row r="254">
-      <c r="A254" s="186" t="inlineStr">
-        <is>
-          <t>日常看盘</t>
-        </is>
-      </c>
-      <c r="B254" s="147" t="inlineStr">
-        <is>
-          <t>看机会成本排序Sheet折后仓位</t>
-        </is>
-      </c>
-      <c r="C254" s="147" t="inlineStr">
-        <is>
-          <t>看现金锁定状态</t>
+      <c r="A254" s="184" t="inlineStr">
+        <is>
+          <t>🔥堆叠/先进封装赛道（蒋宇飞"星光纯叠"框架）</t>
         </is>
       </c>
     </row>
     <row r="255">
-      <c r="A255" s="186" t="inlineStr">
-        <is>
-          <t>每日更新</t>
+      <c r="A255" s="147" t="inlineStr">
+        <is>
+          <t>长电科技(600584)</t>
         </is>
       </c>
       <c r="B255" s="147" t="inlineStr">
         <is>
-          <t>信号计分板逐股计分</t>
+          <t>🔴核心标的</t>
         </is>
       </c>
       <c r="C255" s="147" t="inlineStr">
         <is>
-          <t>净计分累计</t>
+          <t>P:75%+ PE30x</t>
+        </is>
+      </c>
+      <c r="D255" s="147" t="inlineStr">
+        <is>
+          <t>全球第三大封测厂，2.5D/3D量产级，客户广度最强（高通/海思/TI）</t>
+        </is>
+      </c>
+      <c r="E255" s="147" t="inlineStr">
+        <is>
+          <t>等中期选举大跌</t>
+        </is>
+      </c>
+      <c r="F255" s="147" t="inlineStr">
+        <is>
+          <t>中期</t>
+        </is>
+      </c>
+      <c r="G255" s="147" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="H255" s="138" t="inlineStr">
+        <is>
+          <t>安全边际大，堆叠赛道首选</t>
         </is>
       </c>
     </row>
     <row r="256">
-      <c r="A256" s="186" t="inlineStr">
-        <is>
-          <t>每月重算</t>
+      <c r="A256" s="147" t="inlineStr">
+        <is>
+          <t>通富微电(002156)</t>
         </is>
       </c>
       <c r="B256" s="147" t="inlineStr">
         <is>
-          <t>①信号概率=70%+净计分×5pp</t>
+          <t>🔴核心标的</t>
         </is>
       </c>
       <c r="C256" s="147" t="inlineStr">
         <is>
-          <t>②CLC=信号概率×互锁×时间衰减²</t>
+          <t>P:75%+ 待查PE</t>
         </is>
       </c>
       <c r="D256" s="147" t="inlineStr">
         <is>
-          <t>③折后仓位=原仓位×(1-CLC×β)</t>
+          <t>AMD封测全线突破通道，2.5D量产，MI300X参与，不可替代</t>
+        </is>
+      </c>
+      <c r="E256" s="147" t="inlineStr">
+        <is>
+          <t>等中期选举大跌</t>
+        </is>
+      </c>
+      <c r="F256" s="147" t="inlineStr">
+        <is>
+          <t>中期</t>
+        </is>
+      </c>
+      <c r="G256" s="147" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="H256" s="138" t="inlineStr">
+        <is>
+          <t>安全边际中偏大，与长电各占一半</t>
         </is>
       </c>
     </row>
     <row r="257">
-      <c r="A257" s="186" t="inlineStr">
-        <is>
-          <t>信号落地</t>
-        </is>
-      </c>
-      <c r="B257" s="147" t="inlineStr">
-        <is>
-          <t>视觉信号+5日确认+因果链2条</t>
-        </is>
-      </c>
-      <c r="C257" s="147" t="inlineStr">
-        <is>
-          <t>→虚P转实P</t>
-        </is>
-      </c>
-      <c r="D257" s="147" t="inlineStr">
-        <is>
-          <t>→CLC=0现金解锁</t>
-        </is>
-      </c>
+      <c r="A257" s="138" t="n"/>
     </row>
     <row r="258">
-      <c r="A258" s="186" t="inlineStr">
-        <is>
-          <t>核验计算</t>
-        </is>
-      </c>
-      <c r="B258" s="147" t="inlineStr">
-        <is>
-          <t>python3 /tmp/mechanism_checker_v3.py</t>
-        </is>
-      </c>
-      <c r="C258" s="147" t="inlineStr">
-        <is>
-          <t>自动重算所有机制</t>
-        </is>
-      </c>
-    </row>
-    <row r="259"/>
+      <c r="A258" s="138" t="n"/>
+    </row>
+    <row r="259">
+      <c r="A259" s="316" t="inlineStr">
+        <is>
+          <t>🔥 蒋宇飞179视频深度分析 (2026-06-07 顶级置信度)</t>
+        </is>
+      </c>
+    </row>
     <row r="260">
-      <c r="A260" s="188" t="inlineStr">
-        <is>
-          <t>📊 持仓状态速查表</t>
+      <c r="A260" s="138" t="inlineStr">
+        <is>
+          <t>核心框架: 星光纯叠=光模块(贯穿)→存储(吃肉)→堆叠(最大风口) | AI基建10年: 存力→算力→运力 | 2027算力长城=升腾+长鑫+DeepSeek</t>
         </is>
       </c>
     </row>
     <row r="261">
-      <c r="A261" s="189" t="inlineStr">
-        <is>
-          <t>持仓</t>
-        </is>
-      </c>
-      <c r="B261" s="189" t="inlineStr">
-        <is>
-          <t>代码</t>
-        </is>
-      </c>
-      <c r="C261" s="189" t="inlineStr">
-        <is>
-          <t>当前P</t>
-        </is>
-      </c>
-      <c r="D261" s="189" t="inlineStr">
-        <is>
-          <t>有效P</t>
-        </is>
-      </c>
-      <c r="E261" s="189" t="inlineStr">
-        <is>
-          <t>虚P</t>
-        </is>
-      </c>
-      <c r="F261" s="189" t="inlineStr">
-        <is>
-          <t>利率折价</t>
-        </is>
-      </c>
-      <c r="G261" s="189" t="inlineStr">
-        <is>
-          <t>方向</t>
-        </is>
-      </c>
-      <c r="H261" s="189" t="inlineStr">
-        <is>
-          <t>操作建议</t>
-        </is>
-      </c>
-    </row>
-    <row r="262">
-      <c r="A262" s="138" t="inlineStr">
-        <is>
-          <t>芯片020628</t>
-        </is>
-      </c>
-      <c r="B262" s="138" t="inlineStr">
-        <is>
-          <t>C1</t>
-        </is>
-      </c>
-      <c r="C262" s="138" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
-      <c r="D262" s="138" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="E262" s="138" t="inlineStr">
-        <is>
-          <t>虚P+2pp | 6/5 存储→芯片资金传送门：存储涨81%降级后，资金搬进芯片ETF/长电通富</t>
-        </is>
-      </c>
-      <c r="F262" s="138" t="inlineStr">
-        <is>
-          <t>利率折价-6pp</t>
-        </is>
-      </c>
-      <c r="G262" s="138" t="inlineStr">
-        <is>
-          <t>🟡中性</t>
-        </is>
-      </c>
-      <c r="H262" s="138" t="inlineStr">
-        <is>
-          <t>观望</t>
-        </is>
-      </c>
-    </row>
+      <c r="A261" s="138" t="inlineStr">
+        <is>
+          <t>【P值调整】芯片 41%→44%(虚P+3pp) | 稀金 40%→41%(虚P+1pp) | 其余0pp</t>
+        </is>
+      </c>
+    </row>
+    <row r="262"/>
     <row r="263">
       <c r="A263" s="138" t="inlineStr">
         <is>
-          <t>电池018926</t>
-        </is>
-      </c>
-      <c r="B263" s="138" t="inlineStr">
-        <is>
-          <t>C2</t>
-        </is>
-      </c>
-      <c r="C263" s="138" t="inlineStr">
-        <is>
-          <t>65</t>
-        </is>
-      </c>
-      <c r="D263" s="138" t="inlineStr">
-        <is>
-          <t>59</t>
-        </is>
-      </c>
-      <c r="E263" s="138" t="inlineStr">
-        <is>
-          <t>虚P无</t>
-        </is>
-      </c>
-      <c r="F263" s="138" t="inlineStr">
-        <is>
-          <t>利率折价-6pp</t>
-        </is>
-      </c>
-      <c r="G263" s="138" t="inlineStr">
-        <is>
-          <t>🟢偏多</t>
-        </is>
-      </c>
-      <c r="H263" s="138" t="inlineStr">
-        <is>
-          <t>持有/关注加仓</t>
+          <t>MLCC被动元件</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" s="138" t="inlineStr">
         <is>
-          <t>恒科012349</t>
+          <t>国产算力/升腾链</t>
         </is>
       </c>
       <c r="B264" s="138" t="inlineStr">
         <is>
-          <t>C3</t>
+          <t>观察中</t>
         </is>
       </c>
       <c r="C264" s="138" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>蒋宇飞: 2027算力长城最闪亮 | 升腾950明年出货 | 升腾+长鑫+DeepSeek</t>
         </is>
       </c>
       <c r="D264" s="138" t="inlineStr">
         <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="E264" s="138" t="inlineStr">
-        <is>
-          <t>虚P无 | 6/5 闻号说经济：301关税60国+AI芯片管制升级→压制恒科</t>
-        </is>
-      </c>
-      <c r="F264" s="138" t="inlineStr">
-        <is>
-          <t>利率折价-6pp</t>
-        </is>
-      </c>
-      <c r="G264" s="138" t="inlineStr">
-        <is>
-          <t>🔴偏空</t>
-        </is>
-      </c>
-      <c r="H264" s="138" t="inlineStr">
-        <is>
-          <t>减仓/清仓</t>
+          <t>2026-06-07</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" s="138" t="inlineStr">
         <is>
-          <t>养殖014415</t>
+          <t>HBM产业链</t>
         </is>
       </c>
       <c r="B265" s="138" t="inlineStr">
         <is>
-          <t>C4</t>
+          <t>观察中</t>
         </is>
       </c>
       <c r="C265" s="138" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>蒋宇飞: HBM未来1.5-2.5年波涛汹涌 | Q4-Q1热潮 | 技术含量最高</t>
         </is>
       </c>
       <c r="D265" s="138" t="inlineStr">
         <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="E265" s="138" t="inlineStr">
-        <is>
-          <t>虚P+4pp | 6/5 芳姐：低价抄底母猪，行业融资枯竭，等待母猪血流成河才是最佳买点</t>
-        </is>
-      </c>
-      <c r="F265" s="138" t="inlineStr">
-        <is>
-          <t>利率折价0pp</t>
-        </is>
-      </c>
-      <c r="G265" s="138" t="inlineStr">
-        <is>
-          <t>🟢偏多</t>
-        </is>
-      </c>
-      <c r="H265" s="138" t="inlineStr">
-        <is>
-          <t>持有/关注加仓</t>
+          <t>2026-06-07</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" s="138" t="inlineStr">
         <is>
-          <t>有色004433</t>
+          <t>CPU产业链</t>
         </is>
       </c>
       <c r="B266" s="138" t="inlineStr">
         <is>
-          <t>C5</t>
+          <t>观察中</t>
         </is>
       </c>
       <c r="C266" s="138" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>蒋宇飞: agent经济导致CPU爆发缺货 | 带动产业链</t>
         </is>
       </c>
       <c r="D266" s="138" t="inlineStr">
         <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="E266" s="138" t="inlineStr">
-        <is>
-          <t>虚P无 | 6/5 闻号说经济：301关税60国→压制有色需求</t>
-        </is>
-      </c>
-      <c r="F266" s="138" t="inlineStr">
-        <is>
-          <t>利率折价-4pp</t>
-        </is>
-      </c>
-      <c r="G266" s="138" t="inlineStr">
-        <is>
-          <t>🔴偏空</t>
-        </is>
-      </c>
-      <c r="H266" s="138" t="inlineStr">
-        <is>
-          <t>减仓/清仓</t>
+          <t>2026-06-07</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" s="138" t="inlineStr">
         <is>
-          <t>稀金014111</t>
+          <t>玻璃基板(更新)</t>
         </is>
       </c>
       <c r="B267" s="138" t="inlineStr">
         <is>
-          <t>C6</t>
+          <t>观察中</t>
         </is>
       </c>
       <c r="C267" s="138" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>蒋宇飞: 两三年热点→业绩2027-H2→大规模2028 | 封装+存储</t>
         </is>
       </c>
       <c r="D267" s="138" t="inlineStr">
         <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="E267" s="138" t="inlineStr">
-        <is>
-          <t>虚P无</t>
-        </is>
-      </c>
-      <c r="F267" s="138" t="inlineStr">
-        <is>
-          <t>利率折价-4pp</t>
-        </is>
-      </c>
-      <c r="G267" s="138" t="inlineStr">
-        <is>
-          <t>🟡中性</t>
-        </is>
-      </c>
-      <c r="H267" s="138" t="inlineStr">
-        <is>
-          <t>观望</t>
-        </is>
-      </c>
-    </row>
-    <row r="268">
-      <c r="A268" s="138" t="inlineStr">
-        <is>
-          <t>银行001595</t>
-        </is>
-      </c>
-      <c r="B268" s="138" t="inlineStr">
-        <is>
-          <t>C7</t>
-        </is>
-      </c>
-      <c r="C268" s="138" t="inlineStr">
-        <is>
-          <t>47</t>
-        </is>
-      </c>
-      <c r="D268" s="138" t="inlineStr">
-        <is>
-          <t>47</t>
-        </is>
-      </c>
-      <c r="E268" s="138" t="inlineStr">
-        <is>
-          <t>虚P-2pp | 6/5 闻号说经济：银行信贷收紧→压制银行</t>
-        </is>
-      </c>
-      <c r="F268" s="138" t="inlineStr">
-        <is>
-          <t>利率折价0pp</t>
-        </is>
-      </c>
-      <c r="G268" s="138" t="inlineStr">
-        <is>
-          <t>🟡中性</t>
-        </is>
-      </c>
-      <c r="H268" s="138" t="inlineStr">
-        <is>
-          <t>观望</t>
-        </is>
-      </c>
-    </row>
+          <t>2026-06-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="268"/>
     <row r="269">
       <c r="A269" s="138" t="inlineStr">
         <is>
+          <t>【堆叠75%验证】27条堆叠主题: "两年最大风口"+"一年半大放"+"存算一体"→P合理</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" s="138" t="inlineStr">
+        <is>
+          <t>【存储降级确认】"存储跌80%但现在是时机"+"消费级见顶"+"存储涨完轮到堆叠"→降级合理</t>
+        </is>
+      </c>
+    </row>
+    <row r="271"/>
+    <row r="272"/>
+    <row r="273"/>
+    <row r="274"/>
+    <row r="275">
+      <c r="A275" s="153" t="inlineStr">
+        <is>
+          <t>📖 机制库 v3（2026-06-04 经小龙虾审核修订）</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" s="185" t="inlineStr">
+        <is>
+          <t>[机制3v3] 现金锁定系数（CLC）— 平方衰减版</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" s="186" t="inlineStr">
+        <is>
+          <t>叫什么</t>
+        </is>
+      </c>
+      <c r="B277" s="149" t="n"/>
+      <c r="C277" s="149" t="n"/>
+      <c r="D277" s="149" t="n"/>
+      <c r="E277" s="149" t="n"/>
+      <c r="F277" s="149" t="n"/>
+      <c r="G277" s="149" t="n"/>
+      <c r="H277" s="150" t="n"/>
+    </row>
+    <row r="278">
+      <c r="A278" s="186" t="inlineStr">
+        <is>
+          <t>公式</t>
+        </is>
+      </c>
+      <c r="B278" s="147" t="inlineStr">
+        <is>
+          <t>CLC = 信号概率 × 互锁强度 × 时间衰减²</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" s="186" t="inlineStr">
+        <is>
+          <t>时间衰减</t>
+        </is>
+      </c>
+      <c r="B279" s="147" t="inlineStr">
+        <is>
+          <t>T = (距触发月数/12)²</t>
+        </is>
+      </c>
+      <c r="C279" s="147" t="inlineStr">
+        <is>
+          <t>6月=(5/12)²=0.174</t>
+        </is>
+      </c>
+      <c r="D279" s="147" t="inlineStr">
+        <is>
+          <t>11月=0</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" s="186" t="inlineStr">
+        <is>
+          <t>为什么平方</t>
+        </is>
+      </c>
+      <c r="B280" s="147" t="inlineStr">
+        <is>
+          <t>线性衰减导致越近触发日锁得越少（反直觉）</t>
+        </is>
+      </c>
+      <c r="C280" s="147" t="inlineStr">
+        <is>
+          <t>平方函数：远离时多锁，临近时少锁</t>
+        </is>
+      </c>
+      <c r="D280" s="147" t="inlineStr">
+        <is>
+          <t>小龙虾审核通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" s="186" t="inlineStr">
+        <is>
+          <t>信号概率</t>
+        </is>
+      </c>
+      <c r="B281" s="149" t="n"/>
+      <c r="C281" s="149" t="n"/>
+      <c r="D281" s="149" t="n"/>
+      <c r="E281" s="149" t="n"/>
+      <c r="F281" s="149" t="n"/>
+      <c r="G281" s="149" t="n"/>
+      <c r="H281" s="150" t="n"/>
+    </row>
+    <row r="282">
+      <c r="A282" s="186" t="inlineStr">
+        <is>
+          <t>互锁强度</t>
+        </is>
+      </c>
+      <c r="B282" s="147" t="inlineStr">
+        <is>
+          <t>三源强互锁=1.0</t>
+        </is>
+      </c>
+      <c r="C282" s="147" t="inlineStr">
+        <is>
+          <t>达利欧6月修正&gt;2次→降级0.85</t>
+        </is>
+      </c>
+      <c r="D282" s="147" t="inlineStr">
+        <is>
+          <t>有原因修正不降级</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" s="186" t="inlineStr">
+        <is>
+          <t>当前值</t>
+        </is>
+      </c>
+      <c r="B283" s="147" t="inlineStr">
+        <is>
+          <t>0.70 × 1.0 × (5/12)² = 0.122</t>
+        </is>
+      </c>
+      <c r="C283" s="147" t="inlineStr">
+        <is>
+          <t>→ 锁定12.2%现金</t>
+        </is>
+      </c>
+      <c r="D283" s="147" t="inlineStr">
+        <is>
+          <t>可用87.8%</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" s="186" t="inlineStr">
+        <is>
+          <t>每月重算</t>
+        </is>
+      </c>
+      <c r="B284" s="149" t="n"/>
+      <c r="C284" s="149" t="n"/>
+      <c r="D284" s="149" t="n"/>
+      <c r="E284" s="149" t="n"/>
+      <c r="F284" s="149" t="n"/>
+      <c r="G284" s="149" t="n"/>
+      <c r="H284" s="150" t="n"/>
+    </row>
+    <row r="285"/>
+    <row r="286">
+      <c r="A286" s="185" t="inlineStr">
+        <is>
+          <t>[机制4v3] 折后仓位计算 — 4级分级版</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" s="186" t="inlineStr">
+        <is>
+          <t>叫什么</t>
+        </is>
+      </c>
+      <c r="B287" s="147" t="inlineStr">
+        <is>
+          <t>折后仓位（Folded Allocation）v3</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" s="186" t="inlineStr">
+        <is>
+          <t>公式</t>
+        </is>
+      </c>
+      <c r="B288" s="147" t="inlineStr">
+        <is>
+          <t>折后仓位% = 原目标仓位% × (1 - CLC × β系数)</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" s="186" t="inlineStr">
+        <is>
+          <t>4级分级</t>
+        </is>
+      </c>
+      <c r="B289" s="147" t="inlineStr">
+        <is>
+          <t>L1高度暴露β=0.8（通富-AMD独供）</t>
+        </is>
+      </c>
+      <c r="C289" s="147" t="inlineStr">
+        <is>
+          <t>L2中度暴露β=0.5（长电-客户多元）</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" s="186" t="inlineStr">
+        <is>
+          <t>分级继续</t>
+        </is>
+      </c>
+      <c r="B290" s="147" t="inlineStr">
+        <is>
+          <t>L3弱相关β=0.1（养殖）</t>
+        </is>
+      </c>
+      <c r="C290" s="147" t="inlineStr">
+        <is>
+          <t>L4反向受益β=-0.3（黄金）</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" s="186" t="inlineStr">
+        <is>
+          <t>为什么分级</t>
+        </is>
+      </c>
+      <c r="B291" s="149" t="n"/>
+      <c r="C291" s="149" t="n"/>
+      <c r="D291" s="149" t="n"/>
+      <c r="E291" s="149" t="n"/>
+      <c r="F291" s="149" t="n"/>
+      <c r="G291" s="149" t="n"/>
+      <c r="H291" s="150" t="n"/>
+    </row>
+    <row r="292">
+      <c r="A292" s="186" t="inlineStr">
+        <is>
+          <t>当前计算</t>
+        </is>
+      </c>
+      <c r="B292" s="147" t="inlineStr">
+        <is>
+          <t>通富:33%×(1-0.122×0.8)=30.1%</t>
+        </is>
+      </c>
+      <c r="C292" s="147" t="inlineStr">
+        <is>
+          <t>长电:37%×(1-0.122×0.5)=34.7%</t>
+        </is>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" s="186" t="inlineStr">
+        <is>
+          <t>分级逻辑</t>
+        </is>
+      </c>
+      <c r="B293" s="149" t="n"/>
+      <c r="C293" s="149" t="n"/>
+      <c r="D293" s="149" t="n"/>
+      <c r="E293" s="149" t="n"/>
+      <c r="F293" s="149" t="n"/>
+      <c r="G293" s="149" t="n"/>
+      <c r="H293" s="150" t="n"/>
+    </row>
+    <row r="294"/>
+    <row r="295">
+      <c r="A295" s="185" t="inlineStr">
+        <is>
+          <t>[机制5v3] 虚P→实P转换 — 确认窗口+因果链版</t>
+        </is>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" s="186" t="inlineStr">
+        <is>
+          <t>叫什么</t>
+        </is>
+      </c>
+      <c r="B296" s="149" t="n"/>
+      <c r="C296" s="149" t="n"/>
+      <c r="D296" s="149" t="n"/>
+      <c r="E296" s="149" t="n"/>
+      <c r="F296" s="149" t="n"/>
+      <c r="G296" s="149" t="n"/>
+      <c r="H296" s="150" t="n"/>
+    </row>
+    <row r="297">
+      <c r="A297" s="186" t="inlineStr">
+        <is>
+          <t>视觉信号</t>
+        </is>
+      </c>
+      <c r="B297" s="147" t="inlineStr">
+        <is>
+          <t>纳指七姐妹&gt;15%回调（从52周高）</t>
+        </is>
+      </c>
+      <c r="C297" s="147" t="inlineStr">
+        <is>
+          <t>或破200日均线</t>
+        </is>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" s="186" t="inlineStr">
+        <is>
+          <t>确认窗口</t>
+        </is>
+      </c>
+      <c r="B298" s="147" t="inlineStr">
+        <is>
+          <t>跌穿15%后维持5个交易日不反弹</t>
+        </is>
+      </c>
+      <c r="C298" s="147" t="inlineStr">
+        <is>
+          <t>防单日噪音和假触发</t>
+        </is>
+      </c>
+      <c r="D298" s="147" t="inlineStr">
+        <is>
+          <t>小龙虾建议</t>
+        </is>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" s="186" t="inlineStr">
+        <is>
+          <t>因果链</t>
+        </is>
+      </c>
+      <c r="B299" s="147" t="inlineStr">
+        <is>
+          <t>需至少2条佐证：</t>
+        </is>
+      </c>
+      <c r="C299" s="147" t="inlineStr">
+        <is>
+          <t>①英伟达/AMD下调指引</t>
+        </is>
+      </c>
+      <c r="D299" s="147" t="inlineStr">
+        <is>
+          <t>②AI ETF资金流出</t>
+        </is>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" s="186" t="inlineStr">
+        <is>
+          <t>因果链继续</t>
+        </is>
+      </c>
+      <c r="B300" s="147" t="inlineStr">
+        <is>
+          <t>③投行下调AI评级</t>
+        </is>
+      </c>
+      <c r="C300" s="147" t="inlineStr">
+        <is>
+          <t>④Mag7裁员/削减开支</t>
+        </is>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" s="186" t="inlineStr">
+        <is>
+          <t>为什么加因果</t>
+        </is>
+      </c>
+      <c r="B301" s="147" t="inlineStr">
+        <is>
+          <t>15%下跌可能是地缘冲击不是AI泡沫</t>
+        </is>
+      </c>
+      <c r="C301" s="147" t="inlineStr">
+        <is>
+          <t>两者操作完全不同</t>
+        </is>
+      </c>
+      <c r="D301" s="147" t="inlineStr">
+        <is>
+          <t>必须区分原因</t>
+        </is>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" s="186" t="inlineStr">
+        <is>
+          <t>转换后</t>
+        </is>
+      </c>
+      <c r="B302" s="149" t="n"/>
+      <c r="C302" s="149" t="n"/>
+      <c r="D302" s="149" t="n"/>
+      <c r="E302" s="149" t="n"/>
+      <c r="F302" s="149" t="n"/>
+      <c r="G302" s="149" t="n"/>
+      <c r="H302" s="150" t="n"/>
+    </row>
+    <row r="303"/>
+    <row r="304">
+      <c r="A304" s="187" t="inlineStr">
+        <is>
+          <t>[信号计分板] 每日更新，驱动信号概率动态调整</t>
+        </is>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" s="186" t="inlineStr">
+        <is>
+          <t>泡沫正向信号</t>
+        </is>
+      </c>
+      <c r="B305" s="147" t="inlineStr">
+        <is>
+          <t>Mag7单日跌&gt;3% → +1</t>
+        </is>
+      </c>
+      <c r="C305" s="147" t="inlineStr">
+        <is>
+          <t>Mag7月跌&gt;10% → +2</t>
+        </is>
+      </c>
+    </row>
+    <row r="306">
+      <c r="B306" s="147" t="inlineStr">
+        <is>
+          <t>VIX&gt;30 → +2</t>
+        </is>
+      </c>
+      <c r="C306" s="147" t="inlineStr">
+        <is>
+          <t>AI公司裁员/下调指引 → +1</t>
+        </is>
+      </c>
+    </row>
+    <row r="307">
+      <c r="B307" s="147" t="inlineStr">
+        <is>
+          <t>信用利差&gt;150bp → +2</t>
+        </is>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" s="186" t="inlineStr">
+        <is>
+          <t>泡沫反向信号</t>
+        </is>
+      </c>
+      <c r="B308" s="147" t="inlineStr">
+        <is>
+          <t>Mag7单日涨&gt;3% → -1</t>
+        </is>
+      </c>
+      <c r="C308" s="147" t="inlineStr">
+        <is>
+          <t>Mag7月涨&gt;8% → -2</t>
+        </is>
+      </c>
+    </row>
+    <row r="309">
+      <c r="B309" s="147" t="inlineStr">
+        <is>
+          <t>Fed降息 → -2</t>
+        </is>
+      </c>
+      <c r="C309" s="147" t="inlineStr">
+        <is>
+          <t>AI龙头超预期财报 → -1</t>
+        </is>
+      </c>
+    </row>
+    <row r="310">
+      <c r="B310" s="147" t="inlineStr">
+        <is>
+          <t>VIX&lt;15 → -1</t>
+        </is>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" s="186" t="inlineStr">
+        <is>
+          <t>更新规则</t>
+        </is>
+      </c>
+      <c r="B311" s="147" t="inlineStr">
+        <is>
+          <t>每月第一天：信号概率=70%+上月净计分×5pp</t>
+        </is>
+      </c>
+      <c r="C311" s="147" t="inlineStr">
+        <is>
+          <t>底线55%上限85%</t>
+        </is>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" s="186" t="inlineStr">
+        <is>
+          <t>Mag7权重</t>
+        </is>
+      </c>
+      <c r="B312" s="149" t="n"/>
+      <c r="C312" s="149" t="n"/>
+      <c r="D312" s="149" t="n"/>
+      <c r="E312" s="149" t="n"/>
+      <c r="F312" s="149" t="n"/>
+      <c r="G312" s="149" t="n"/>
+      <c r="H312" s="150" t="n"/>
+    </row>
+    <row r="313"/>
+    <row r="314">
+      <c r="A314" s="187" t="inlineStr">
+        <is>
+          <t>⚡ 机制v3使用指南</t>
+        </is>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" s="186" t="inlineStr">
+        <is>
+          <t>日常看盘</t>
+        </is>
+      </c>
+      <c r="B315" s="147" t="inlineStr">
+        <is>
+          <t>看机会成本排序Sheet折后仓位</t>
+        </is>
+      </c>
+      <c r="C315" s="147" t="inlineStr">
+        <is>
+          <t>看现金锁定状态</t>
+        </is>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" s="186" t="inlineStr">
+        <is>
+          <t>每日更新</t>
+        </is>
+      </c>
+      <c r="B316" s="147" t="inlineStr">
+        <is>
+          <t>信号计分板逐股计分</t>
+        </is>
+      </c>
+      <c r="C316" s="147" t="inlineStr">
+        <is>
+          <t>净计分累计</t>
+        </is>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" s="186" t="inlineStr">
+        <is>
+          <t>每月重算</t>
+        </is>
+      </c>
+      <c r="B317" s="147" t="inlineStr">
+        <is>
+          <t>①信号概率=70%+净计分×5pp</t>
+        </is>
+      </c>
+      <c r="C317" s="147" t="inlineStr">
+        <is>
+          <t>②CLC=信号概率×互锁×时间衰减²</t>
+        </is>
+      </c>
+      <c r="D317" s="147" t="inlineStr">
+        <is>
+          <t>③折后仓位=原仓位×(1-CLC×β)</t>
+        </is>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" s="186" t="inlineStr">
+        <is>
+          <t>信号落地</t>
+        </is>
+      </c>
+      <c r="B318" s="147" t="inlineStr">
+        <is>
+          <t>视觉信号+5日确认+因果链2条</t>
+        </is>
+      </c>
+      <c r="C318" s="147" t="inlineStr">
+        <is>
+          <t>→虚P转实P</t>
+        </is>
+      </c>
+      <c r="D318" s="147" t="inlineStr">
+        <is>
+          <t>→CLC=0现金解锁</t>
+        </is>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" s="186" t="inlineStr">
+        <is>
+          <t>核验计算</t>
+        </is>
+      </c>
+      <c r="B319" s="147" t="inlineStr">
+        <is>
+          <t>python3 /tmp/mechanism_checker_v3.py</t>
+        </is>
+      </c>
+      <c r="C319" s="147" t="inlineStr">
+        <is>
+          <t>自动重算所有机制</t>
+        </is>
+      </c>
+    </row>
+    <row r="320"/>
+    <row r="321">
+      <c r="A321" s="188" t="inlineStr">
+        <is>
+          <t>📊 持仓状态速查表</t>
+        </is>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" s="189" t="inlineStr">
+        <is>
+          <t>持仓</t>
+        </is>
+      </c>
+      <c r="B322" s="189" t="inlineStr">
+        <is>
+          <t>代码</t>
+        </is>
+      </c>
+      <c r="C322" s="189" t="inlineStr">
+        <is>
+          <t>当前P</t>
+        </is>
+      </c>
+      <c r="D322" s="189" t="inlineStr">
+        <is>
+          <t>有效P</t>
+        </is>
+      </c>
+      <c r="E322" s="189" t="inlineStr">
+        <is>
+          <t>虚P</t>
+        </is>
+      </c>
+      <c r="F322" s="189" t="inlineStr">
+        <is>
+          <t>利率折价</t>
+        </is>
+      </c>
+      <c r="G322" s="189" t="inlineStr">
+        <is>
+          <t>方向</t>
+        </is>
+      </c>
+      <c r="H322" s="189" t="inlineStr">
+        <is>
+          <t>操作建议</t>
+        </is>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" s="138" t="inlineStr">
+        <is>
+          <t>芯片020628</t>
+        </is>
+      </c>
+      <c r="B323" s="138" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="C323" s="138" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="D323" s="138" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="E323" s="138" t="inlineStr">
+        <is>
+          <t>虚P+2pp | 6/5 存储→芯片资金传送门：存储涨81%降级后，资金搬进芯片ETF/长电通富</t>
+        </is>
+      </c>
+      <c r="F323" s="138" t="inlineStr">
+        <is>
+          <t>利率折价-6pp</t>
+        </is>
+      </c>
+      <c r="G323" s="138" t="inlineStr">
+        <is>
+          <t>🟡中性</t>
+        </is>
+      </c>
+      <c r="H323" s="138" t="inlineStr">
+        <is>
+          <t>观望</t>
+        </is>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" s="138" t="inlineStr">
+        <is>
+          <t>电池018926</t>
+        </is>
+      </c>
+      <c r="B324" s="138" t="inlineStr">
+        <is>
+          <t>C2</t>
+        </is>
+      </c>
+      <c r="C324" s="138" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="D324" s="138" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="E324" s="138" t="inlineStr">
+        <is>
+          <t>虚P无</t>
+        </is>
+      </c>
+      <c r="F324" s="138" t="inlineStr">
+        <is>
+          <t>利率折价-6pp</t>
+        </is>
+      </c>
+      <c r="G324" s="138" t="inlineStr">
+        <is>
+          <t>🟢偏多</t>
+        </is>
+      </c>
+      <c r="H324" s="138" t="inlineStr">
+        <is>
+          <t>持有/关注加仓</t>
+        </is>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" s="138" t="inlineStr">
+        <is>
+          <t>恒科012349</t>
+        </is>
+      </c>
+      <c r="B325" s="138" t="inlineStr">
+        <is>
+          <t>C3</t>
+        </is>
+      </c>
+      <c r="C325" s="138" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="D325" s="138" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="E325" s="138" t="inlineStr">
+        <is>
+          <t>虚P无 | 6/5 闻号说经济：301关税60国+AI芯片管制升级→压制恒科</t>
+        </is>
+      </c>
+      <c r="F325" s="138" t="inlineStr">
+        <is>
+          <t>利率折价-6pp</t>
+        </is>
+      </c>
+      <c r="G325" s="138" t="inlineStr">
+        <is>
+          <t>🔴偏空</t>
+        </is>
+      </c>
+      <c r="H325" s="138" t="inlineStr">
+        <is>
+          <t>减仓/清仓</t>
+        </is>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" s="138" t="inlineStr">
+        <is>
+          <t>养殖014415</t>
+        </is>
+      </c>
+      <c r="B326" s="138" t="inlineStr">
+        <is>
+          <t>C4</t>
+        </is>
+      </c>
+      <c r="C326" s="138" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="D326" s="138" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="E326" s="138" t="inlineStr">
+        <is>
+          <t>虚P+4pp | 6/5 芳姐：低价抄底母猪，行业融资枯竭，等待母猪血流成河才是最佳买点</t>
+        </is>
+      </c>
+      <c r="F326" s="138" t="inlineStr">
+        <is>
+          <t>利率折价0pp</t>
+        </is>
+      </c>
+      <c r="G326" s="138" t="inlineStr">
+        <is>
+          <t>🟢偏多</t>
+        </is>
+      </c>
+      <c r="H326" s="138" t="inlineStr">
+        <is>
+          <t>持有/关注加仓</t>
+        </is>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" s="138" t="inlineStr">
+        <is>
+          <t>有色004433</t>
+        </is>
+      </c>
+      <c r="B327" s="138" t="inlineStr">
+        <is>
+          <t>C5</t>
+        </is>
+      </c>
+      <c r="C327" s="138" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="D327" s="138" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="E327" s="138" t="inlineStr">
+        <is>
+          <t>虚P无 | 6/5 闻号说经济：301关税60国→压制有色需求</t>
+        </is>
+      </c>
+      <c r="F327" s="138" t="inlineStr">
+        <is>
+          <t>利率折价-4pp</t>
+        </is>
+      </c>
+      <c r="G327" s="138" t="inlineStr">
+        <is>
+          <t>🔴偏空</t>
+        </is>
+      </c>
+      <c r="H327" s="138" t="inlineStr">
+        <is>
+          <t>减仓/清仓</t>
+        </is>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" s="138" t="inlineStr">
+        <is>
+          <t>稀金014111</t>
+        </is>
+      </c>
+      <c r="B328" s="138" t="inlineStr">
+        <is>
+          <t>C6</t>
+        </is>
+      </c>
+      <c r="C328" s="138" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="D328" s="138" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="E328" s="138" t="inlineStr">
+        <is>
+          <t>虚P无</t>
+        </is>
+      </c>
+      <c r="F328" s="138" t="inlineStr">
+        <is>
+          <t>利率折价-4pp</t>
+        </is>
+      </c>
+      <c r="G328" s="138" t="inlineStr">
+        <is>
+          <t>🟡中性</t>
+        </is>
+      </c>
+      <c r="H328" s="138" t="inlineStr">
+        <is>
+          <t>观望</t>
+        </is>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" s="138" t="inlineStr">
+        <is>
+          <t>银行001595</t>
+        </is>
+      </c>
+      <c r="B329" s="138" t="inlineStr">
+        <is>
+          <t>C7</t>
+        </is>
+      </c>
+      <c r="C329" s="138" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="D329" s="138" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="E329" s="138" t="inlineStr">
+        <is>
+          <t>虚P-2pp | 6/5 闻号说经济：银行信贷收紧→压制银行</t>
+        </is>
+      </c>
+      <c r="F329" s="138" t="inlineStr">
+        <is>
+          <t>利率折价0pp</t>
+        </is>
+      </c>
+      <c r="G329" s="138" t="inlineStr">
+        <is>
+          <t>🟡中性</t>
+        </is>
+      </c>
+      <c r="H329" s="138" t="inlineStr">
+        <is>
+          <t>观望</t>
+        </is>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" s="138" t="inlineStr">
+        <is>
           <t>AI027048</t>
         </is>
       </c>
-      <c r="B269" s="138" t="inlineStr">
+      <c r="B330" s="138" t="inlineStr">
         <is>
           <t>C8</t>
         </is>
       </c>
-      <c r="C269" s="138" t="inlineStr">
+      <c r="C330" s="138" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="D269" s="138" t="inlineStr">
+      <c r="D330" s="138" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F269" s="138" t="inlineStr">
+      <c r="F330" s="138" t="inlineStr">
         <is>
           <t>利率折价-4pp</t>
         </is>
       </c>
-      <c r="G269" s="138" t="inlineStr">
+      <c r="G330" s="138" t="inlineStr">
         <is>
           <t>🟡中性</t>
         </is>
       </c>
-      <c r="H269" s="138" t="inlineStr">
+      <c r="H330" s="138" t="inlineStr">
         <is>
           <t>观望</t>
         </is>
       </c>
     </row>
-    <row r="270"/>
-    <row r="271">
-      <c r="A271" s="190" t="inlineStr">
+    <row r="331"/>
+    <row r="332">
+      <c r="A332" s="190" t="inlineStr">
         <is>
           <t>--- 6/6 监控小结 ---</t>
         </is>
       </c>
     </row>
-    <row r="272">
-      <c r="A272" s="191" t="inlineStr">
+    <row r="333">
+      <c r="A333" s="191" t="inlineStr">
         <is>
           <t>养殖: +1pp → 淘汰母猪加快+融资恶化→底部确认</t>
         </is>
       </c>
     </row>
-    <row r="273">
-      <c r="A273" s="191" t="inlineStr">
+    <row r="334">
+      <c r="A334" s="191" t="inlineStr">
         <is>
           <t>芯片: 0pp → AI长期利好vs估值过高抵消</t>
         </is>
       </c>
     </row>
-    <row r="274">
-      <c r="A274" s="191" t="inlineStr">
+    <row r="335">
+      <c r="A335" s="191" t="inlineStr">
         <is>
           <t>恒科: 0pp → AI叙事强化非事件</t>
         </is>
       </c>
     </row>
-    <row r="275">
-      <c r="A275" s="191" t="inlineStr">
+    <row r="336">
+      <c r="A336" s="191" t="inlineStr">
         <is>
           <t>银行: 0pp → 非农黑五已部分定价</t>
         </is>
       </c>
     </row>
-    <row r="276">
-      <c r="A276" s="191" t="inlineStr">
+    <row r="337">
+      <c r="A337" s="191" t="inlineStr">
         <is>
           <t>结论: 持仓不动。养殖左侧继续等待。</t>
         </is>
       </c>
     </row>
-    <row r="277">
-      <c r="A277" s="138" t="inlineStr">
+    <row r="338">
+      <c r="A338" s="138" t="inlineStr">
         <is>
           <t>--- 6/7 监控小结 ---</t>
         </is>
       </c>
     </row>
-    <row r="278">
-      <c r="A278" s="138" t="inlineStr">
+    <row r="339">
+      <c r="A339" s="138" t="inlineStr">
         <is>
           <t>养殖: +1pp → 集团"养一天赔一天"全体重抛售→去产能加速→周期底确认</t>
         </is>
       </c>
     </row>
-    <row r="279">
-      <c r="A279" s="138" t="inlineStr">
+    <row r="340">
+      <c r="A340" s="138" t="inlineStr">
         <is>
           <t>芯片: 0pp → AI基建长期利好(付鹏)vs摩尔定律瓶颈(宋鸿兵)抵消</t>
         </is>
       </c>
     </row>
-    <row r="280">
-      <c r="A280" s="138" t="inlineStr">
+    <row r="341">
+      <c r="A341" s="138" t="inlineStr">
         <is>
           <t>AI: 0pp → AI基建+应用加速确认，但无新事件级催化剂</t>
         </is>
       </c>
     </row>
-    <row r="281">
-      <c r="A281" s="138" t="inlineStr">
+    <row r="342">
+      <c r="A342" s="138" t="inlineStr">
         <is>
           <t>恒科: -1pp → 非农超预期→加息预期→黑五科技暴跌→利率敏感</t>
         </is>
       </c>
     </row>
-    <row r="282">
-      <c r="A282" s="138" t="inlineStr">
+    <row r="343">
+      <c r="A343" s="138" t="inlineStr">
         <is>
           <t>黄金: 0pp → 长期央行购金(27%储备)vs短期非农砸盘抵消</t>
         </is>
       </c>
     </row>
-    <row r="283">
-      <c r="A283" s="138" t="inlineStr">
+    <row r="344">
+      <c r="A344" s="138" t="inlineStr">
         <is>
           <t>银行: 0pp → 岩松笔记讨论15%年化，中性方法论</t>
         </is>
       </c>
     </row>
-    <row r="284">
-      <c r="A284" s="138" t="inlineStr">
+    <row r="345">
+      <c r="A345" s="138" t="inlineStr">
         <is>
           <t>结论: 持仓不动。养殖左侧继续等待。恒科短期注意利率风险。</t>
         </is>

--- a/持仓贝叶斯跟踪.xlsx
+++ b/持仓贝叶斯跟踪.xlsx
@@ -621,7 +621,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="11">
+  <borders count="8">
     <border>
       <left/>
       <right/>
@@ -671,27 +671,6 @@
       <bottom style="thin"/>
     </border>
     <border/>
-    <border>
-      <left/>
-      <right style="thin"/>
-      <top/>
-      <bottom style="thin"/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin"/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="thin"/>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1">
@@ -703,7 +682,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="335">
+  <cellXfs count="329">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -1636,21 +1615,11 @@
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
     <xf numFmtId="0" fontId="58" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="47" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="57" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="57" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="59" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="32" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="60" fillId="33" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="60" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="56" fillId="34" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="57" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1727,6 +1696,7 @@
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>Hermes</author>
+    <author>叙事主线</author>
     <author>AI指导原则</author>
   </authors>
   <commentList>
@@ -1948,7 +1918,91 @@
 P值调整：0pp（已计入其他事件）</t>
       </text>
     </comment>
-    <comment ref="A179" authorId="1" shapeId="0">
+    <comment ref="B113" authorId="0" shapeId="0">
+      <text>
+        <t xml:space="preserve">【来源】宋鸿兵6.3视频
+【逻辑链】
+霍尔木兹封锁3个月 → 全球有效原油库存8.1亿桶
+ → OECD库存6月触红线（本月）
+ → 全球库存9月见底
+ → 特朗普必须在9月前重开霍尔木兹
+ → 否则：能源成本失控 + 恶性通胀 + 国债收益率飙升
+【当前状态】⚠️升级：从"慢性走钢丝"→"9月死线"
+- 国债39万亿+30年美债破5%+10年破4.5%
+- 沃什上任但市场用脚投票，利率只涨不跌
+【对持仓影响】
+🔴 利空：芯片(020628)/恒科(009854) — 成长股对利率最敏感
+🟡 中性：电池(009759) — 新能源有政策托底，但高利率压制估值
+🟢 利好：有色HALO(008826) — 利率↑=通胀预期↑=商品对冲需求↑
+【操作建议】
+利率危机升级→短期偏防守，不追成长股。等9月死线前后：
+- 若霍尔木兹重开→利率回落→成长股反弹→芯片/恒科右侧信号
+- 若霍尔木兹持续封锁→能源暴涨→华宝油气+有色HALO继续有效
+</t>
+      </text>
+    </comment>
+    <comment ref="B114" authorId="0" shapeId="0">
+      <text>
+        <t xml:space="preserve">【来源】宋鸿兵6.3视频 + 雪佛龙CEO + 埃克森VP
+【逻辑链】
+霍尔木兹封锁 → 中东原油无法出口
+ → 全球有效库存8.1亿桶持续消耗
+ → OECD库存6月触底（雪佛龙CEO确认）
+ → 85%投资者押注油价回落 = 集体幻觉（埃克森VP警告）
+【当前状态】🔴重大升级：行业巨头双重警告
+- 雪佛龙CEO：OECD库存6月见底
+- 埃克森VP：市场严重低估能源危机
+【对持仓影响】
+🟢 利好：有色HALO(008826) — 能源危机=商品牛市=HALO策略核心逻辑
+🟢 利好：华宝油气(162411) — 油价冲150直接受益
+🔴 利空：养殖(008765) — 饲料成本(玉米/大豆运输)↑
+🔴 利空：银行(512800) — 通胀↑→坏账率↑
+【操作建议】
+能源危机是确定性最高的叙事之一（双重行业验证）。
+- 有色HALO继续持有
+- 华宝油气可小仓试水（不对称博弈：下行有限，上行巨大）
+</t>
+      </text>
+    </comment>
+    <comment ref="B115" authorId="0" shapeId="0">
+      <text>
+        <t xml:space="preserve">【来源】付鹏+宋鸿兵6.2 + 无知半人
+【逻辑链】
+08-18居民加杠杆 → 现在全面去杠杆
+ → 前4月住户贷款狂减4902亿
+ → 消费萎缩 → 猪周期加速出清
+【当前状态】维持，无新催化
+【对持仓影响】
+🟢 利好：养殖(008765) — 去杠杆=消费↓=猪价承压=加速出清=右侧机会
+🔴 利空：银行(512800) — 信贷收缩=银行资产质量恶化
+【操作建议】
+- 养殖：去杠杆是加速器，等右侧信号（猪价企稳+产能出清确认）
+- 银行：不加仓，去杠杆周期中银行最难受
+</t>
+      </text>
+    </comment>
+    <comment ref="B116" authorId="1" shapeId="0">
+      <text>
+        <t xml:space="preserve">来源：用户2026-06-04独立判断
+逻辑链：
+1. 历史验证：每次危机→比特币暴跌（无避险价值）
+2. 黄金涨→比特币跌（流动性被黄金吸附）
+3. 美股涨→黄金跌→比特币也跌（被美股吸走）
+4. AI来了→资金有明确去处（芯片/AI基建）→比特币更没吸引力
+5. 最近一轮牛市验证：涨跌幅变小+跟美股完全同步=已非独立资产
+当前状态：维持。2020后第1次牛市(2021)，第2次牛市(2025最近)，周期规律+AI挤压=比特币上行空间越来越小
+对持仓影响：
+- 芯片/AI 利好：资金不去比特币就去AI，确认资金流向
+- 黄金 间接利好：比特币不再跟黄金抢流动性
+- 银行/有色/稀金 中性：不影响国内逻辑
+操作建议：
+- 不碰比特币/虚拟货币
+- 确认AI赛道的资金虹吸地位
+- 如果比特币暴跌→不是避险信号，是资金被更强的资产吸走了
+</t>
+      </text>
+    </comment>
+    <comment ref="A118" authorId="2" shapeId="0">
       <text>
         <t xml:space="preserve">来源：用户2026-06-04确立，多个信源交叉确认
 核心逻辑：
@@ -1969,7 +2023,7 @@
 </t>
       </text>
     </comment>
-    <comment ref="A248" authorId="0" shapeId="0">
+    <comment ref="A187" authorId="0" shapeId="0">
       <text>
         <t xml:space="preserve">【来源】蒋宇飞抖音视频（2026-05-25）"未来5-10年的黄金赛道，深度拆解玻璃基板的万亿机遇"
 【信源评估】蒋宇飞⭐⭐⭐高置信度（有产业实操经验，多次验证预测准确）
@@ -1984,7 +2038,7 @@
 </t>
       </text>
     </comment>
-    <comment ref="A250" authorId="0" shapeId="0">
+    <comment ref="A189" authorId="0" shapeId="0">
       <text>
         <t>信息源：东方财富+新浪财经2026-06-02
 核心数据：
@@ -1997,7 +2051,7 @@
 结论：不建议加仓</t>
       </text>
     </comment>
-    <comment ref="A251" authorId="0" shapeId="0">
+    <comment ref="A190" authorId="0" shapeId="0">
       <text>
         <t>信息源：东方财富头条+新浪财经2026-06-02
 核心数据：
@@ -2012,7 +2066,7 @@
 结论：重点关注，强正向信号</t>
       </text>
     </comment>
-    <comment ref="A252" authorId="0" shapeId="0">
+    <comment ref="A191" authorId="0" shapeId="0">
       <text>
         <t xml:space="preserve">【来源】群联潘健成(产业高管)+蒋宇飞(6.1两长存储+5.18框架)+宋鸿兵(6.2摩尔定律终结)+周鸿祎(内存决定AI)+用户6.3洞察
 【逻辑链】
@@ -2035,7 +2089,7 @@
 </t>
       </text>
     </comment>
-    <comment ref="A253" authorId="0" shapeId="0">
+    <comment ref="A192" authorId="0" shapeId="0">
       <text>
         <t xml:space="preserve">【来源】蒋宇飞星光纯叠框架+宋鸿兵华为韬定律+用户"AI瓶颈是内存而非算力"
 【逻辑链】
@@ -2049,7 +2103,7 @@
 </t>
       </text>
     </comment>
-    <comment ref="A255" authorId="0" shapeId="0">
+    <comment ref="A194" authorId="0" shapeId="0">
       <text>
         <t xml:space="preserve">【标的】北京君正 300223
 【核心逻辑】存储+计算芯片，DRAM新工艺突破，车载存储市占率提升。A股年内+51%，市值772亿。港股二度IPO中。盈亏比4:1，存储赛道里最强。
@@ -2060,7 +2114,7 @@
 </t>
       </text>
     </comment>
-    <comment ref="A256" authorId="0" shapeId="0">
+    <comment ref="A195" authorId="0" shapeId="0">
       <text>
         <t xml:space="preserve">【标的】兆易创新 603986
 【核心逻辑】NOR Flash国内龙头，DRAM布局中。存储涨价直接受益。盈亏比3.5:1。
@@ -2071,7 +2125,7 @@
 </t>
       </text>
     </comment>
-    <comment ref="A257" authorId="0" shapeId="0">
+    <comment ref="A196" authorId="0" shapeId="0">
       <text>
         <t xml:space="preserve">【标的】江波龙 301308
 【核心逻辑】存储模组+主控芯片，国产替代核心标的。盈亏比3.5:1。
@@ -2403,7 +2457,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:H345"/>
+  <dimension ref="A1:H268"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6171875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="18" customWidth="1" style="138" min="1" max="8"/>
@@ -2703,1219 +2757,783 @@
       </c>
     </row>
     <row r="12" ht="16.5" customHeight="1" s="139">
-      <c r="A12" s="138" t="inlineStr">
-        <is>
-          <t>2026-06-07 芯片: 蒋宇飞179视频深度提取—国产替代78天一致+黄仁勋1万亿+工信部支持+CPU缺货→虚P+3pp</t>
+      <c r="A12" s="324" t="inlineStr">
+        <is>
+          <t>💰 资金分配总纲 (2026-06-07 蒋宇飞179视频+用户判断+机会成本)</t>
         </is>
       </c>
     </row>
     <row r="13" ht="15" customHeight="1" s="139">
-      <c r="A13" s="138" t="inlineStr">
-        <is>
-          <t>2026-06-07 堆叠: 蒋宇飞27条堆叠主题验证—"两年最大风口"+"一年半大放"+"存算一体"→75%P合理</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="15" customHeight="1" s="139">
-      <c r="A14" s="138" t="inlineStr">
-        <is>
-          <t>2026-06-07 待重仓新增: MLCC(到2027-H1)/国产算力(2027爆发)/HBM(1.5-2.5年)/CPU(agent经济)</t>
-        </is>
-      </c>
-    </row>
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>【Hermes+小龙多轮联合审核】第1轮：小龙审7个问题→第2轮：Hermes反审7个问题→小龙逐条回应修正</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="15" customHeight="1" s="139"/>
     <row r="15" ht="15" customHeight="1" s="139">
-      <c r="A15" s="138" t="inlineStr">
-        <is>
-          <t>2026-06-07 存储降级确认: "消费级见顶"+"跌80%但现在是时机"+"涨完轮到堆叠"</t>
+      <c r="A15" s="293" t="inlineStr">
+        <is>
+          <t>一、资金总览</t>
         </is>
       </c>
     </row>
     <row r="16" ht="16.5" customHeight="1" s="139">
-      <c r="A16" s="138" t="inlineStr">
-        <is>
-          <t>2026-06-07 时间线: 7月长鑫上市→年底MLCC高点→2027-H1 MLCC结束→2027-H2堆叠→2027算力长城→2028玻璃基板</t>
+      <c r="A16" s="325" t="inlineStr">
+        <is>
+          <t>持仓50%=养殖25%|芯片10%|电池5%|恒科2.5%|有色2.5%|稀金2.5%|银行1.5%</t>
         </is>
       </c>
     </row>
     <row r="17" ht="16.5" customHeight="1" s="139">
-      <c r="A17" s="324" t="inlineStr">
-        <is>
-          <t>💰 蒋宇飞驱动资金分配指南 (2026-06-07 基于179视频深度分析)</t>
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>现金50%=锁定40%(等11月大跌进长电25+通富20)+可动用10%</t>
         </is>
       </c>
     </row>
     <row r="18" ht="16.5" customHeight="1" s="139">
-      <c r="A18" s="138" t="inlineStr">
-        <is>
-          <t>📌 基于「星光纯叠」框架 + 时间线预测 + P×R排序 + 三层追七成等策略</t>
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>【资金来源】现金50%+卖恒科2.5%(P=27%)+有色稀金5%(P低)+养殖减半12.5%+芯片可选5%=70-85%。方案消耗75%够覆盖</t>
         </is>
       </c>
     </row>
     <row r="19" ht="16.5" customHeight="1" s="139"/>
     <row r="20" ht="30" customHeight="1" s="139">
-      <c r="A20" s="316" t="inlineStr">
-        <is>
-          <t>一、当前资金总览</t>
+      <c r="A20" s="324" t="inlineStr">
+        <is>
+          <t>二、蒋宇飞「星光纯叠」框架（顶级置信度，179视频逐条提取）</t>
         </is>
       </c>
     </row>
     <row r="21" ht="16.5" customHeight="1" s="139">
-      <c r="A21" s="138" t="inlineStr">
-        <is>
-          <t>总资金: 100% = 持仓50% + 现金50% | 其中现金60-70%锁定等11月中期选举回调 → 可用约15-18%</t>
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>星(芯)=CPU/GPU | 光=光模块 | 纯(存)=DRAM/Flash/HBM/SSD | 叠=CoWoS/2.5D/3D先进封装</t>
         </is>
       </c>
     </row>
     <row r="22" ht="16.5" customHeight="1" s="139">
-      <c r="A22" s="138" t="inlineStr">
-        <is>
-          <t>持仓仓位(50%内): 养殖25% | 芯片10% | 电池5% | 恒科2.5% | 有色2.5% | 稀金2.5% | 银行1.5% | 存储0%(已清)</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="16.5" customHeight="1" s="139"/>
-    <row r="24" ht="16.5" customHeight="1" s="139">
-      <c r="A24" s="316" t="inlineStr">
-        <is>
-          <t>二、分阶段资金分配计划</t>
-        </is>
-      </c>
-    </row>
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>节奏：光贯穿2026→存储2026吃肉(已验证海力士13倍)→堆叠2027大放。2027算力长城=升腾+长鑫+DeepSeek</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="16.5" customHeight="1" s="139">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>风控提示：存储将来跌80% | 消费级2027见顶 | HBM分销修正70-80% | 纪律：三成追热点七成等回调</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="16.5" customHeight="1" s="139"/>
     <row r="25" ht="16.5" customHeight="1" s="139">
-      <c r="A25" s="316" t="inlineStr">
-        <is>
-          <t>▶ 阶段1: 当前→2026-Q4 (蒋宇飞: 存储吃肉+MLCC+光模块贯穿)</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="15" customHeight="1" s="139">
-      <c r="A26" s="138" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  持仓操作: 芯片10%不动(虚P+3pp确认方向对) | 养殖25%不动(左侧等底)</t>
-        </is>
-      </c>
-    </row>
+      <c r="A25" s="324" t="inlineStr">
+        <is>
+          <t>三、各赛道详细操作计划（每个都有来龙去脉）</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="15" customHeight="1" s="139"/>
     <row r="27" ht="16.5" customHeight="1" s="139">
-      <c r="A27" s="138" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  现金分配: MLCC观察仓2%(A股MLCC相关ETF/个股) | 保持13%现金 | 其余10%机动</t>
+      <c r="A27" s="326" t="inlineStr">
+        <is>
+          <t>▶ MLCC被动元件 5.5%（含恒科清出2.5%）</t>
         </is>
       </c>
     </row>
     <row r="28" ht="15" customHeight="1" s="139">
-      <c r="A28" s="138" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  理由: 蒋宇飞"MLCC不亚于半年前荐存储"→当前正是MLCC肉最甜的时候</t>
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>【为什么买】蒋宇飞4月底预测MLCC启动，5月即涨。说"不亚于半年前荐存储"（存储半年涨13倍）。国巨成台湾首富。日韩停产中低端→中国MLCC爆发。行情到2027-H1</t>
         </is>
       </c>
     </row>
     <row r="29" ht="15" customHeight="1" s="139">
-      <c r="A29" s="138" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  风控: MLCC年底见顶→12月前清仓</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="15" customHeight="1" s="139"/>
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>【买什么】风华高科(000636)≈300股≈8250元。MLCC营收占比58%，最接近纯暴露。不买科技ETF凑合（小龙裁定）</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="15" customHeight="1" s="139">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>【恒科为什么清】P=27%三条信号同向。蒋宇飞"传统互联网老灯鼓"是行业判断，"腾讯黄金坑"是个股判断。恒科≠腾讯（腾讯只占30%）。看好腾讯应买个股。清出2.5%转MLCC</t>
+        </is>
+      </c>
+    </row>
     <row r="31" ht="15" customHeight="1" s="139">
-      <c r="A31" s="138" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  现金分配: HBM产业链5% | 堆叠/先进封装5%(长电3%+通富2%)</t>
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>【什么时候进】现在（6-7月）</t>
         </is>
       </c>
     </row>
     <row r="32" ht="15" customHeight="1" s="139">
-      <c r="A32" s="138" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  理由: 蒋宇飞"HBF热潮Q4-Q1展开波澜壮阔"→直接受益HBM标的</t>
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>【什么时候出】11-12月必须清仓（蒋宇飞说年底见顶）。资金转HBM或堆叠先手</t>
         </is>
       </c>
     </row>
     <row r="33" ht="16.5" customHeight="1" s="139">
-      <c r="A33" s="138" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  触发条件: HBM板块启动信号出现 | 长电/通富回调15%+</t>
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>【风控】5.5%仓位，错了亏2000-3000不致命。年底不管赚亏都清</t>
         </is>
       </c>
     </row>
     <row r="34" ht="16.5" customHeight="1" s="139"/>
     <row r="35" ht="16.5" customHeight="1" s="139">
-      <c r="A35" s="138" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  核心重仓: 长电科技25%+通富微电20% (等11月回调大仓位进)</t>
+      <c r="A35" s="327" t="inlineStr">
+        <is>
+          <t>▶ HBM产业链 5%</t>
         </is>
       </c>
     </row>
     <row r="36" ht="16.5" customHeight="1" s="139">
-      <c r="A36" s="138" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  辅助仓位: 国产算力/升腾链标的10% | CPU产业链5%</t>
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>【为什么买】蒋宇飞"HBM未来1.5-2.5年波涛汹涌""Q4-Q1波澜壮阔热潮"。HBM是AI技术含量最高的存储，目前最紧缺</t>
         </is>
       </c>
     </row>
     <row r="37" ht="16.5" customHeight="1" s="139">
-      <c r="A37" s="138" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  理由: 蒋宇飞27条堆叠主题+"2027算力长城最闪亮"→升腾链爆发</t>
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>【什么时候进】2026-Q4（10-12月），MLCC清仓后资金转入</t>
         </is>
       </c>
     </row>
     <row r="38" ht="16.5" customHeight="1" s="139">
-      <c r="A38" s="138" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  蒋宇飞原话: "堆叠改变家族命运""躺赢"→仓位最重</t>
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>【什么时候出】2027-Q1热潮结束观察。蒋宇飞说热潮在四季度至明年一季度展开</t>
         </is>
       </c>
     </row>
     <row r="39" ht="16.5" customHeight="1" s="139">
-      <c r="A39" s="329" t="inlineStr">
-        <is>
-          <t>💰 资金分配总纲 (2026-06-07 蒋宇飞179视频+用户判断+机会成本)</t>
-        </is>
-      </c>
-    </row>
-    <row r="40" ht="16.5" customHeight="1" s="139">
-      <c r="A40" s="329" t="inlineStr">
-        <is>
-          <t>【Hermes+小龙多轮联合审核结论 2026-06-07】</t>
-        </is>
-      </c>
-    </row>
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>【风控】5%不大。Q4不启动就继续等，不急着进</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="16.5" customHeight="1" s="139"/>
     <row r="41" ht="16.5" customHeight="1" s="139">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>① 账修正：方案总消耗88%但现金只有50%，缺口38%。补法=卖恒科2.5%+有色稀金5%+养殖减半12.5%+芯片可选5%+未来收入。方案必须标注资金来源</t>
+      <c r="A41" s="324" t="inlineStr">
+        <is>
+          <t>▶ 堆叠/先进封装 长电25%+通富20%=45%（核心重仓）</t>
         </is>
       </c>
     </row>
     <row r="42" ht="16.5" customHeight="1" s="139">
       <c r="A42" t="inlineStr">
         <is>
-          <t>② 堆叠45%分三批进：第一批15%(跌15%触发)→第二批15%(再跌10%或横盘2月)→第三批15%(产业验证)。涨20%后分两批加速到30%。30%翻倍&gt;45%被洗</t>
+          <t>【为什么买】蒋宇飞27条堆叠视频反复强调"未来两年最大风口""一年半大放光芒""改变家族命运""躺赢"。堆叠=CoWoS/2.5D/3D=突破存算一体。封装成本占存储芯片20%。P=75%</t>
         </is>
       </c>
     </row>
     <row r="43" ht="16.5" customHeight="1" s="139">
       <c r="A43" t="inlineStr">
         <is>
-          <t>③ Plan B：锁到2027-01-31（三个月窗口：11月选举+12月圣诞行情+1月调仓）。逾期进40%留20%。替代触发三选一：PE&lt;40/蒋宇飞说进/连阴3月</t>
+          <t>【P=75%四源交叉确认】达利欧(宏观泡沫年底崩→回调买入)+李大霄(A股窄牛宽熊→等低位)+用户(中期选举大跌=买入时机)+蒋宇飞(产业27条)。四套独立框架交集→小龙说P可能估低</t>
         </is>
       </c>
     </row>
     <row r="44" ht="16.5" customHeight="1" s="139">
       <c r="A44" t="inlineStr">
         <is>
-          <t>④ 机器人4%不变：562500不是纯机器人暴露（成分公司机器人营收&lt;20%）。替代：加科创AI(027048)6%覆盖AI+机器人+算力，合计10%科技前沿</t>
+          <t>【为什么长电+通富】长电=全球第三大封测，2.5D/3D量产，客户高通/海思/TI。通富=AMD封测全线突破，MI300X参与，不可替代</t>
         </is>
       </c>
     </row>
     <row r="45" ht="16.5" customHeight="1" s="139">
       <c r="A45" t="inlineStr">
         <is>
-          <t>⑤ 恒科清：P=27%三条信号同向。蒋宇飞"传统互联网老灯鼓"是行业判断，"腾讯黄金坑"是个股判断。恒科≠腾讯（腾讯只占30%）。看好腾讯应买个股</t>
+          <t>【分三批进-小龙裁定】第一批15%(跌15%触发)→第二批15%(再跌10%或横盘2月)→第三批15%(产业验证)。涨20%后分两批加速到30%。小龙逻辑：30%翻倍&gt;45%被洗，仓位轻=拿得住=吃全涨幅</t>
         </is>
       </c>
     </row>
     <row r="46" ht="16.5" customHeight="1" s="139">
       <c r="A46" t="inlineStr">
         <is>
-          <t>⑥ MLCC标的：风华高科(000636)200股≈4500元。MLCC营收占比58%，最接近纯暴露。不买科技ETF凑合。含恒科清出2.5%→MLCC从3%→5.5%</t>
+          <t>【什么时候进】等11月美股大跌15%+。触发三选一：①达利欧泡沫落地 ②纳指破200日均线 ③中期选举大跌</t>
         </is>
       </c>
     </row>
     <row r="47" ht="16.5" customHeight="1" s="139">
       <c r="A47" t="inlineStr">
         <is>
-          <t>⑦ P=75%四源交叉确认：达利欧(宏观)+李大霄(A股)+用户(事件)+蒋宇飞(产业27条)。四套独立框架交集→P可能估低，不是'全押蒋宇飞'</t>
+          <t>【Plan B-小龙裁定】锁到2027-01-31（三个月窗口：11月选举+12月圣诞行情+1月调仓）。逾期进40%留20%。替代触发三选一：芯片PE&lt;40分位/蒋宇飞说进/月线连阴3月</t>
         </is>
       </c>
     </row>
     <row r="48" ht="16.5" customHeight="1" s="139">
-      <c r="A48" t="inlineStr"/>
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>【先手仓位】Q4先建5%（长电3%+通富2%），等回调后进大仓位。符合蒋宇飞"三成追七成等"纪律</t>
+        </is>
+      </c>
     </row>
     <row r="49" ht="16.5" customHeight="1" s="139">
-      <c r="A49" s="329" t="inlineStr">
-        <is>
-          <t>修正后完整方案：</t>
-        </is>
-      </c>
-    </row>
-    <row r="50" ht="15" customHeight="1" s="139">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>A.现在MLCC(风华)5.5% B.Q4 HBM5%+堆叠先手5% C.11月堆叠三批45% D.PlanB(1/31)进40%留20% E.2027升腾8%+机器人4%+玻璃2% F.科创AI(027048)6%</t>
-        </is>
-      </c>
-    </row>
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>【风控】45%×70%回撤=31.5%总资金蒸发（蒋宇飞自己说HBM分销修正70-80%）。分三批=赌价格区间胜率翻倍</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="15" customHeight="1" s="139"/>
     <row r="51" ht="15" customHeight="1" s="139">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>持仓调整：养殖25%→12.5% 恒科清 有色+稀金清 芯片可选减半 电池+银行不动 保留现金~10%</t>
+      <c r="A51" s="327" t="inlineStr">
+        <is>
+          <t>▶ 国产算力/升腾链 8%</t>
         </is>
       </c>
     </row>
     <row r="52" ht="77.59999999999999" customHeight="1" s="139">
-      <c r="A52" s="329" t="inlineStr">
-        <is>
-          <t>【Hermes+小龙多轮联合审核结论 2026-06-07】</t>
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>【为什么买】蒋宇飞"2027算力长城最闪亮""升腾链2027爆发""升腾950明年出货"。工信部要求支持国产芯片</t>
         </is>
       </c>
     </row>
     <row r="53" ht="17.15" customHeight="1" s="139">
-      <c r="A53" s="138" t="inlineStr">
-        <is>
-          <t>① 账修正：方案总消耗88%但现金只有50%，缺口38%。补法=卖恒科2.5%+有色稀金5%+养殖减半12.5%+芯片可选5%+未来收入。方案必须标注资金来源</t>
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>【什么时候进】2027年。触发：华为升腾950大批出货/工信部政策加码</t>
         </is>
       </c>
     </row>
     <row r="54" ht="26.85" customHeight="1" s="139">
-      <c r="A54" s="138" t="inlineStr">
-        <is>
-          <t>② 堆叠45%分三批进：第一批15%(跌15%触发)→第二批15%(再跌10%或横盘2月)→第三批15%(产业验证)。涨20%后分两批加速到30%。30%翻倍&gt;45%被洗</t>
-        </is>
-      </c>
-    </row>
-    <row r="55" ht="29.85" customHeight="1" s="139">
-      <c r="A55" s="138" t="inlineStr">
-        <is>
-          <t>③ Plan B：锁到2027-01-31（三个月窗口：11月选举+12月圣诞行情+1月调仓）。逾期进40%留20%。替代触发三选一：PE&lt;40/蒋宇飞说进/连阴3月</t>
-        </is>
-      </c>
-    </row>
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>【风控】等2027，当前只看不动</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="29.85" customHeight="1" s="139"/>
     <row r="56" ht="29.85" customHeight="1" s="139">
-      <c r="A56" s="138" t="inlineStr">
-        <is>
-          <t>④ 机器人4%不变：562500不是纯机器人暴露（成分公司机器人营收&lt;20%）。替代：加科创AI(027048)6%覆盖AI+机器人+算力，合计10%科技前沿</t>
+      <c r="A56" s="327" t="inlineStr">
+        <is>
+          <t>▶ 机器人(物理AI) 4% + 科创AI(027048) 6% = 10%科技前沿</t>
         </is>
       </c>
     </row>
     <row r="57" ht="15" customHeight="1" s="139">
-      <c r="A57" s="138" t="inlineStr">
-        <is>
-          <t>⑤ 恒科清：P=27%三条信号同向。蒋宇飞"传统互联网老灯鼓"是行业判断，"腾讯黄金坑"是个股判断。恒科≠腾讯（腾讯只占30%）。看好腾讯应买个股</t>
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>【为什么买】用户判断机器人&gt;黄金&gt;比特币。蒋宇飞交叉验证：179视频0次提比特币。"未来经济三层=物理人→钢铁机器人→网络agent"。宇树科技73天过会</t>
         </is>
       </c>
     </row>
     <row r="58" ht="15" customHeight="1" s="139">
-      <c r="A58" s="138" t="inlineStr">
-        <is>
-          <t>⑥ MLCC标的：风华高科(000636)200股≈4500元。MLCC营收占比58%，最接近纯暴露。不买科技ETF凑合。含恒科清出2.5%→MLCC从3%→5.5%</t>
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>【标的困境-小龙分析】562500不是纯机器人暴露(成分公司机器人营收&lt;20%，半年波动66%)。纯机器人公司(宇树/Figure)没上市。替代：科创AI(027048)6%覆盖AI+机器人+算力</t>
         </is>
       </c>
     </row>
     <row r="59" ht="58.2" customHeight="1" s="139">
-      <c r="A59" s="138" t="inlineStr">
-        <is>
-          <t>⑦ P=75%四源交叉确认：达利欧(宏观)+李大霄(A股)+用户(事件)+蒋宇飞(产业27条)。四套独立框架交集→P可能估低，不是'全押蒋宇飞'</t>
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>【什么时候进】2027冬开始逐步建。机器人是中长期赛道，不急</t>
         </is>
       </c>
     </row>
     <row r="60" ht="173.1" customHeight="1" s="139">
-      <c r="A60" s="138" t="inlineStr"/>
-    </row>
-    <row r="61" ht="15" customHeight="1" s="139">
-      <c r="A61" s="329" t="inlineStr">
-        <is>
-          <t>修正后完整方案：</t>
-        </is>
-      </c>
-    </row>
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>【风控】4%不大。科创AI6%分散风险。合计10%科技前沿暴露，比单一562500更安全</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="15" customHeight="1" s="139"/>
     <row r="62" ht="15" customHeight="1" s="139">
-      <c r="A62" s="138" t="inlineStr">
-        <is>
-          <t>A.现在MLCC(风华)5.5% B.Q4 HBM5%+堆叠先手5% C.11月堆叠三批45% D.PlanB(1/31)进40%留20% E.2027升腾8%+机器人4%+玻璃2% F.科创AI(027048)6%</t>
+      <c r="A62" s="327" t="inlineStr">
+        <is>
+          <t>▶ 玻璃基板 2%</t>
         </is>
       </c>
     </row>
     <row r="63" ht="48.5" customHeight="1" s="139">
-      <c r="A63" s="138" t="inlineStr">
-        <is>
-          <t>持仓调整：养殖25%→12.5% 恒科清 有色+稀金清 芯片可选减半 电池+银行不动 保留现金~10%</t>
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>【为什么买】蒋宇飞"被严重低估即将爆发""两三年热点""业绩2027-H2释放""大规模2028"。两个爆发点：封装+存储</t>
         </is>
       </c>
     </row>
     <row r="64" ht="48.5" customHeight="1" s="139">
-      <c r="A64" s="329" t="inlineStr">
-        <is>
-          <t>【Hermes+小龙多轮联合审核结论 2026-06-07】</t>
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>【什么时候进】2027年等业绩释放。蒋宇飞说"消息还在送验阶段"</t>
         </is>
       </c>
     </row>
     <row r="65" ht="64.15000000000001" customHeight="1" s="139">
-      <c r="A65" s="138" t="inlineStr">
-        <is>
-          <t>① 账修正：方案总消耗88%但现金只有50%，缺口38%。补法=卖恒科2.5%+有色稀金5%+养殖减半12.5%+芯片可选5%+未来收入。方案必须标注资金来源</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" s="138" t="inlineStr">
-        <is>
-          <t>② 堆叠45%分三批进：第一批15%(跌15%触发)→第二批15%(再跌10%或横盘2月)→第三批15%(产业验证)。涨20%后分两批加速到30%，不是"不再加"。30%翻倍&gt;45%被洗</t>
-        </is>
-      </c>
-    </row>
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>【风控】2%观察仓，等消息确认</t>
+        </is>
+      </c>
+    </row>
+    <row r="66"/>
     <row r="67" ht="17.15" customHeight="1" s="139">
-      <c r="A67" s="138" t="inlineStr">
-        <is>
-          <t>③ Plan B：锁到2027-01-31（三个月窗口：11月选举+12月圣诞行情+1月调仓）。逾期进40%留20%。替代触发三选一：PE&lt;40分位/蒋宇飞说进/月线连阴3月</t>
-        </is>
-      </c>
-    </row>
-    <row r="68" ht="48.5" customHeight="1" s="139">
-      <c r="A68" s="138" t="inlineStr">
-        <is>
-          <t>④ 机器人4%不变：562500不是纯机器人暴露（成分公司机器人营收&lt;20%）。替代方案：加科创AI(027048)6%覆盖AI+机器人+算力，合计10%科技前沿暴露</t>
-        </is>
-      </c>
-    </row>
+      <c r="A67" s="324" t="inlineStr">
+        <is>
+          <t>四、进钱节奏时间线</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="48.5" customHeight="1" s="139"/>
     <row r="69" ht="32.8" customHeight="1" s="139">
-      <c r="A69" s="138" t="inlineStr">
-        <is>
-          <t>⑤ 恒科清：P=27%三条信号同向。蒋宇飞"传统互联网老灯鼓"是行业判断，"腾讯黄金坑"是个股判断。恒科≠腾讯（腾讯只占30%）。看好腾讯应买个股。清出2.5%转MLCC</t>
+      <c r="A69" s="328" t="inlineStr">
+        <is>
+          <t>时间</t>
+        </is>
+      </c>
+      <c r="B69" s="328" t="inlineStr">
+        <is>
+          <t>进钱操作</t>
+        </is>
+      </c>
+      <c r="C69" s="328" t="inlineStr">
+        <is>
+          <t>持仓操作</t>
+        </is>
+      </c>
+      <c r="D69" s="328" t="inlineStr">
+        <is>
+          <t>清仓退出</t>
+        </is>
+      </c>
+      <c r="E69" s="328" t="inlineStr">
+        <is>
+          <t>可用现金</t>
         </is>
       </c>
     </row>
     <row r="70" ht="48.5" customHeight="1" s="139">
-      <c r="A70" s="138" t="inlineStr">
-        <is>
-          <t>⑥ MLCC标的：风华高科(000636)200股≈4500元。MLCC营收占比58%，最接近纯暴露。不买科技ETF凑合</t>
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>现在-7月</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>MLCC5.5%建仓(风华高科)</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>芯片10%不动(虚P+3pp)</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>~7%</t>
         </is>
       </c>
     </row>
     <row r="71" ht="32.8" customHeight="1" s="139">
-      <c r="A71" s="138" t="inlineStr">
-        <is>
-          <t>⑦ P=75%四源交叉确认：达利欧(宏观泡沫)+李大霄(A股择时)+用户(中期选举事件)+蒋宇飞(产业27条)。四套独立框架交集→P可能估低，不是'全押蒋宇飞'</t>
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>8-10月</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>MLCC持有享肉</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>观察HBM启动信号</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>~7%</t>
         </is>
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="138" t="inlineStr"/>
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>11月大跌</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>堆叠三批45%(长电25+通富20)</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>MLCC清→HBM5%+堆叠先手5%</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>MLCC清</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
     </row>
     <row r="73" ht="121.6" customHeight="1" s="139">
-      <c r="A73" s="329" t="inlineStr">
-        <is>
-          <t>修正后完整方案：</t>
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>11月没大跌</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>堆叠先手5%(长电3+通富2)</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>MLCC清→等</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>MLCC清</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>0-2%</t>
         </is>
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="138" t="inlineStr">
-        <is>
-          <t>A.现在MLCC(风华)5.5% B.Q4 HBM5%+堆叠先手5% C.11月堆叠三批45% D.PlanB(1/31)进40%留20% E.2027升腾8%+机器人4%+玻璃2% F.科创AI(027048)6% G.保留~10%</t>
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>1/31仍没大跌</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>PlanB：进40%留20%</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>等</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>~20%</t>
         </is>
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="138" t="inlineStr">
-        <is>
-          <t>持仓调整：养殖25%→12.5%(等猪周期) 恒科清 有色+稀金清 芯片可选减半 电池+银行不动</t>
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2027-Q1</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>HBM持有</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>堆叠先手持有</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="329" t="inlineStr">
-        <is>
-          <t>【Hermes+小龙多轮联合审核结论 2026-06-07】</t>
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>2027-H2</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>升腾8%+玻璃2%</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>堆叠满仓躺赢</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="77" ht="15" customHeight="1" s="139">
-      <c r="A77" s="138" t="inlineStr">
-        <is>
-          <t>① 账修正：方案总消耗88%但现金只有50%，缺口38%。来源=卖恒科2.5%+有色稀金5%+养殖减半12.5%+芯片可选5%+未来收入。必须标注资金来源</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" s="138" t="inlineStr">
-        <is>
-          <t>② 恒科清：P=27%三条信号同向，恒科≠腾讯(腾讯只占30%)。看好腾讯应买个股。清出2.5%转MLCC→5.5%</t>
-        </is>
-      </c>
-    </row>
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>2027冬</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>机器人4%+科创AI6%</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>算力出海观察</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>存储清(跌80%)</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="78"/>
     <row r="79" ht="39.55" customHeight="1" s="139">
-      <c r="A79" s="138" t="inlineStr">
-        <is>
-          <t>③ 堆叠45%分三批：第一批15%(跌15%触发)→第二批15%(再跌10%或横盘2月)→第三批15%(产业验证)。涨20%后分两批加速到30%，不是"不再加"</t>
+      <c r="A79" s="324" t="inlineStr">
+        <is>
+          <t>⚡ 一句话：MLCC5.5%小试→Q4 HBM5%+堆叠先手5%→11月堆叠三批45%→2027升腾8%+机器人4%+玻璃2%+科创AI6%</t>
         </is>
       </c>
     </row>
     <row r="80" ht="39.55" customHeight="1" s="139">
-      <c r="A80" s="138" t="inlineStr">
-        <is>
-          <t>④ Plan B：锁到2027-01-31(三个月窗口：11月选举+12月圣诞行情+1月调仓)。逾期进40%留20%。替代触发三选一：PE&lt;40/蒋宇飞说进/连阴3月</t>
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>风控底线：45%必须等15%+回调分三批 | MLCC年底必清 | 蒋宇飞纪律'三成追七成等' | PlanB锁到2027-01-31</t>
         </is>
       </c>
     </row>
     <row r="81" ht="52.2" customHeight="1" s="139">
-      <c r="A81" s="138" t="inlineStr">
-        <is>
-          <t>⑤ 机器人4%不变：562500不是纯机器人暴露(成分公司机器人营收&lt;20%)。替代：加科创AI(027048)6%覆盖AI+机器人+算力，合计10%科技前沿</t>
-        </is>
-      </c>
-    </row>
-    <row r="82" ht="52.2" customHeight="1" s="139">
-      <c r="A82" s="138" t="inlineStr">
-        <is>
-          <t>⑥ MLCC标的：风华高科(000636)200股≈4500元。MLCC营收占比58%，最接近纯暴露。不买科技ETF凑合</t>
-        </is>
-      </c>
-    </row>
-    <row r="83" ht="64.90000000000001" customHeight="1" s="139">
-      <c r="A83" s="138" t="inlineStr">
-        <is>
-          <t>⑦ P=75%四源交叉确认：达利欧(宏观)+李大霄(A股)+用户(事件)+蒋宇飞(产业)。四套独立框架交集→可能估低，不是'全押蒋宇飞'</t>
-        </is>
-      </c>
-    </row>
-    <row r="84" ht="15" customHeight="1" s="139">
-      <c r="A84" s="138" t="inlineStr">
-        <is>
-          <t>⑧ 风控：30%仓位在正确方向翻倍&gt;45%满仓被洗。仓位轻=拿得住=吃到全涨幅。这是小龙的核心风控逻辑</t>
-        </is>
-      </c>
-    </row>
-    <row r="85" ht="15" customHeight="1" s="139">
-      <c r="A85" s="138" t="inlineStr"/>
-    </row>
-    <row r="86" ht="26.85" customHeight="1" s="139">
-      <c r="A86" s="329" t="inlineStr">
-        <is>
-          <t>修正后完整方案：</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" s="138" t="inlineStr">
-        <is>
-          <t>A. 现在：MLCC(风华高科)5.5%  B. Q4：HBM5%+堆叠先手5%  C. 11月：堆叠分三批45%  D. Plan B(1/31)：进40%留20%</t>
-        </is>
-      </c>
-    </row>
-    <row r="88" ht="39.55" customHeight="1" s="139">
-      <c r="A88" s="138" t="inlineStr">
-        <is>
-          <t>E. 2027：升腾8%+机器人4%+玻璃2%  F. 科创AI(027048)6%  G. 保留现金~10%</t>
-        </is>
-      </c>
-    </row>
-    <row r="89" ht="26.85" customHeight="1" s="139">
-      <c r="A89" s="138" t="inlineStr">
-        <is>
-          <t>持仓调整：养殖25%→12.5%  恒科清  有色+稀金清  芯片可选减半  电池+银行不动</t>
-        </is>
-      </c>
-    </row>
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>持仓调整：养殖25%→12.5% | 恒科清 | 有色+稀金清 | 芯片可选减半 | 电池+银行不动 | 保留现金~10%</t>
+        </is>
+      </c>
+    </row>
+    <row r="82" ht="52.2" customHeight="1" s="139"/>
+    <row r="83" ht="64.90000000000001" customHeight="1" s="139"/>
+    <row r="84" ht="15" customHeight="1" s="139"/>
+    <row r="85" ht="15" customHeight="1" s="139"/>
+    <row r="86" ht="26.85" customHeight="1" s="139"/>
+    <row r="87"/>
+    <row r="88" ht="39.55" customHeight="1" s="139"/>
+    <row r="89" ht="26.85" customHeight="1" s="139"/>
     <row r="90" ht="26.85" customHeight="1" s="139"/>
-    <row r="91" ht="39.55" customHeight="1" s="139">
-      <c r="A91" s="329" t="inlineStr">
-        <is>
-          <t>【Hermes+小龙多轮联合审核结论 2026-06-07】</t>
-        </is>
-      </c>
-    </row>
-    <row r="92" ht="26.85" customHeight="1" s="139">
-      <c r="A92" s="138" t="inlineStr">
-        <is>
-          <t>① 恒科2.5%清仓→转MLCC。理由：P=27%三条信号同向，蒋宇飞说传统互联网是老灯鼓。钱从3%→5.5%</t>
-        </is>
-      </c>
-    </row>
-    <row r="93" ht="26.85" customHeight="1" s="139">
-      <c r="A93" s="138" t="inlineStr">
-        <is>
-          <t>② 堆叠45%分三批进：第一批15%(跌15%触发)→第二批15%(再跌或横盘2月)→第三批15%(产业验证)。涨20%后重新评估</t>
-        </is>
-      </c>
-    </row>
-    <row r="94" ht="39.55" customHeight="1" s="139">
-      <c r="A94" s="138" t="inlineStr">
-        <is>
-          <t>③ Plan B：锁到2027-01-31，逾期进则进40%留20%继续等。替代触发三选一：芯片PE&lt;40/蒋宇飞说现在进/月线连阴3月</t>
-        </is>
-      </c>
-    </row>
-    <row r="95" ht="39.55" customHeight="1" s="139">
-      <c r="A95" s="138" t="inlineStr">
-        <is>
-          <t>④ MLCC标的：风华高科(000636)200股≈4500元。MLCC营收占比58%，最接近纯暴露。不含科技ETF凑合</t>
-        </is>
-      </c>
-    </row>
-    <row r="96" ht="15" customHeight="1" s="139">
-      <c r="A96" s="138" t="inlineStr">
-        <is>
-          <t>⑤ 机器人4%不变（无纯暴露工具）+ 科创AI(027048)加仓6%覆盖AI+机器人+算力。合计10%科技前沿暴露</t>
-        </is>
-      </c>
-    </row>
-    <row r="97" ht="15" customHeight="1" s="139">
-      <c r="A97" s="138" t="inlineStr">
-        <is>
-          <t>⑥ 资金来源：现金50%+卖恒科2.5%+卖有色稀金5%+养殖减半12.5%+芯片可选5%=70-85%。方案消耗75%够覆盖</t>
-        </is>
-      </c>
-    </row>
-    <row r="98" ht="18.65" customHeight="1" s="139">
-      <c r="A98" s="138" t="inlineStr">
-        <is>
-          <t>⑦ P=75%被四源交叉确认(达利欧+李大霄+蒋宇飞+用户)→可能估低。不是'全押蒋宇飞'是四套独立框架交集</t>
-        </is>
-      </c>
-    </row>
-    <row r="99" ht="15" customHeight="1" s="139">
-      <c r="A99" s="138" t="inlineStr">
-        <is>
-          <t>⑧ 风控底线：45%堆叠即使分三批也很重。如果第一批涨了20%，后两批进不进看v型反弹还是死猫反弹。30%仓位翻倍就够</t>
-        </is>
-      </c>
-    </row>
-    <row r="100" ht="15" customHeight="1" s="139">
-      <c r="A100" s="138" t="inlineStr">
-        <is>
-          <t>⑨ 机会成本：堆叠(75%)&gt;MLCC(中高)&gt;HBM(高)&gt;机器人(中)&gt;CPU(中)&gt;玻璃基板(中低)。按确定性×时间窗口排序</t>
-        </is>
-      </c>
-    </row>
-    <row r="101" ht="26.85" customHeight="1" s="139">
-      <c r="A101" s="138" t="inlineStr">
-        <is>
-          <t>每个操作都有来龙去脉：为什么买/买多少/什么时候进/什么时候出/风控在哪</t>
-        </is>
-      </c>
-    </row>
+    <row r="91" ht="39.55" customHeight="1" s="139"/>
+    <row r="92" ht="26.85" customHeight="1" s="139"/>
+    <row r="93" ht="26.85" customHeight="1" s="139"/>
+    <row r="94" ht="39.55" customHeight="1" s="139"/>
+    <row r="95" ht="39.55" customHeight="1" s="139"/>
+    <row r="96" ht="15" customHeight="1" s="139"/>
+    <row r="97" ht="15" customHeight="1" s="139"/>
+    <row r="98" ht="18.65" customHeight="1" s="139"/>
+    <row r="99" ht="15" customHeight="1" s="139"/>
+    <row r="100" ht="15" customHeight="1" s="139"/>
+    <row r="101" ht="26.85" customHeight="1" s="139"/>
     <row r="102" ht="15" customHeight="1" s="139"/>
-    <row r="103" ht="26.85" customHeight="1" s="139">
-      <c r="A103" s="293" t="inlineStr">
-        <is>
-          <t>一、资金总览</t>
-        </is>
-      </c>
-    </row>
-    <row r="104" ht="26.85" customHeight="1" s="139">
-      <c r="A104" s="330" t="inlineStr">
-        <is>
-          <t>持仓50%=养殖25%|芯片10%|电池5%|恒科2.5%|有色2.5%|稀金2.5%|银行1.5%</t>
-        </is>
-      </c>
-    </row>
-    <row r="105" ht="26.85" customHeight="1" s="139">
-      <c r="A105" s="138" t="inlineStr">
-        <is>
-          <t>现金50%=锁定40%(等11月大跌进长电25+通富20)+可动用10%</t>
-        </is>
-      </c>
-    </row>
+    <row r="103" ht="26.85" customHeight="1" s="139"/>
+    <row r="104" ht="26.85" customHeight="1" s="139"/>
+    <row r="105" ht="26.85" customHeight="1" s="139"/>
     <row r="106" ht="26.85" customHeight="1" s="139"/>
-    <row r="107" ht="15" customHeight="1" s="139">
-      <c r="A107" s="329" t="inlineStr">
-        <is>
-          <t>二、蒋宇飞「星光纯叠」框架（顶级置信度）</t>
-        </is>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" s="138" t="inlineStr">
-        <is>
-          <t>AI基建10年=存力→算力→运力。节奏：光贯穿2026→存储2026吃肉→堆叠2027大放。2027算力长城=升腾+长鑫+DeepSeek</t>
-        </is>
-      </c>
-    </row>
-    <row r="109" ht="15" customHeight="1" s="139">
-      <c r="A109" s="138" t="inlineStr">
-        <is>
-          <t>风控提示：存储将来跌80% | 消费级2027见顶 | HBM分销修正70-80% | 纪律：三成追热点七成等回调</t>
-        </is>
-      </c>
-    </row>
+    <row r="107" ht="15" customHeight="1" s="139"/>
+    <row r="108"/>
+    <row r="109" ht="15" customHeight="1" s="139"/>
     <row r="110" ht="26.85" customHeight="1" s="139"/>
-    <row r="111" ht="26.85" customHeight="1" s="139">
-      <c r="A111" s="329" t="inlineStr">
-        <is>
-          <t>三、各赛道详细操作计划</t>
-        </is>
-      </c>
-    </row>
-    <row r="112" ht="26.85" customHeight="1" s="139"/>
+    <row r="111" ht="26.85" customHeight="1" s="139"/>
+    <row r="112" ht="26.85" customHeight="1" s="139">
+      <c r="A112" s="148" t="inlineStr">
+        <is>
+          <t>🔥 叙事主线（四条）</t>
+        </is>
+      </c>
+      <c r="B112" s="149" t="n"/>
+      <c r="C112" s="149" t="n"/>
+      <c r="D112" s="149" t="n"/>
+      <c r="E112" s="149" t="n"/>
+      <c r="F112" s="149" t="n"/>
+      <c r="G112" s="149" t="n"/>
+      <c r="H112" s="150" t="n"/>
+    </row>
     <row r="113" ht="26.85" customHeight="1" s="139">
-      <c r="A113" s="331" t="inlineStr">
-        <is>
-          <t>▶ MLCC被动元件 3% 观察仓</t>
-        </is>
-      </c>
+      <c r="B113" s="147" t="inlineStr">
+        <is>
+          <t>①美国国债/利率危机 ⚠️升级：从"慢性走钢丝"→"9月死线"【来源：宋鸿兵6.3视频】。国债39万亿+30年美债破5%+10年破4.5%，沃什上任但市场用脚投票。霍尔木兹不重开→OECD库存6月见底→全球9月触红线→能源成本失控+恶性通胀，利率只涨不跌</t>
+        </is>
+      </c>
+      <c r="C113" s="149" t="n"/>
+      <c r="D113" s="149" t="n"/>
+      <c r="E113" s="149" t="n"/>
+      <c r="F113" s="149" t="n"/>
+      <c r="G113" s="149" t="n"/>
+      <c r="H113" s="150" t="n"/>
     </row>
     <row r="114" ht="26.85" customHeight="1" s="139">
-      <c r="A114" s="138" t="inlineStr">
-        <is>
-          <t>为什么买：蒋宇飞4月底预测MLCC启动，5月即涨。说"不亚于半年前荐存储"（存储半年涨13倍）。国巨成台湾首富。日韩停产→中国MLCC爆发。行情到2027-H1</t>
-        </is>
-      </c>
+      <c r="B114" s="147" t="inlineStr">
+        <is>
+          <t>②霍尔木兹/能源危机 🔴重大升级：封锁3个月，有效原油库存8.1亿桶，OECD最早6月触红线。雪佛龙CEO+埃克森VP双重警告，85%投资者押注回落=集体幻觉</t>
+        </is>
+      </c>
+      <c r="C114" s="149" t="n"/>
+      <c r="D114" s="149" t="n"/>
+      <c r="E114" s="149" t="n"/>
+      <c r="F114" s="149" t="n"/>
+      <c r="G114" s="149" t="n"/>
+      <c r="H114" s="150" t="n"/>
     </row>
     <row r="115" ht="26.85" customHeight="1" s="139">
-      <c r="A115" s="138" t="inlineStr">
-        <is>
-          <t>买什么：风华高科/三环集团等A股MLCC概念股</t>
-        </is>
-      </c>
+      <c r="B115" s="147" t="inlineStr">
+        <is>
+          <t>③中国去杠杆分化 维持：08-18加杠杆→全面去杠杆，对猪周期是加速器，对AI是倒逼器。无新催化</t>
+        </is>
+      </c>
+      <c r="C115" s="149" t="n"/>
+      <c r="D115" s="149" t="n"/>
+      <c r="E115" s="149" t="n"/>
+      <c r="F115" s="149" t="n"/>
+      <c r="G115" s="149" t="n"/>
+      <c r="H115" s="150" t="n"/>
     </row>
     <row r="116" ht="15" customHeight="1" s="139">
       <c r="A116" s="138" t="inlineStr">
         <is>
-          <t>什么时候进：现在（6-7月）</t>
+          <t>④</t>
+        </is>
+      </c>
+      <c r="B116" s="138" t="inlineStr">
+        <is>
+          <t>比特币独立叙事消亡 维持：资金吸附力排序 AI&gt;美股&gt;黄金&gt;比特币，比特币已成美股影子资产，AI落地后资金有明确去处，比特币价值持续被稀释</t>
         </is>
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="138" t="inlineStr">
-        <is>
-          <t>什么时候出：11-12月必须清仓（蒋宇飞说年底见顶）。资金转HBM或堆叠先手</t>
+      <c r="A117" s="151" t="inlineStr">
+        <is>
+          <t>⚡ AI投资阶段切换指导原则（顶级置信度）</t>
         </is>
       </c>
     </row>
     <row r="118" ht="15" customHeight="1" s="139">
-      <c r="A118" s="138" t="inlineStr">
-        <is>
-          <t>风控：只3%亏了不痛。年底不管赚亏都清</t>
-        </is>
-      </c>
-    </row>
-    <row r="119" ht="15" customHeight="1" s="139"/>
+      <c r="A118" s="152" t="inlineStr">
+        <is>
+          <t>AI前半程=投硬件（芯片/算力/堆叠封装）→ 已验证。AI后半程=布局软件/应用端 → 多个信源交叉确认，逻辑高度自洽。此为投资指导原则，不是事件，不作为P值调整依据，但影响赛道选择优先级。</t>
+        </is>
+      </c>
+    </row>
+    <row r="119" ht="15" customHeight="1" s="139">
+      <c r="A119" s="153" t="inlineStr">
+        <is>
+          <t>🔴🔴🔴 战略级虚P信号池 + 现金策略联动（2026-06-04）🔴🔴🔴</t>
+        </is>
+      </c>
+    </row>
     <row r="120" ht="26.85" customHeight="1" s="139">
-      <c r="A120" s="329" t="inlineStr">
-        <is>
-          <t>【Hermes+小龙联合审核结论 2026-06-07】</t>
+      <c r="A120" s="154" t="inlineStr">
+        <is>
+          <t>虚P规则：未落地→记虚P→不加实P→等落地转实P。此板块锁定大部分现金，与机会成本联动分析。</t>
         </is>
       </c>
     </row>
     <row r="121" ht="26.85" customHeight="1" s="139">
-      <c r="A121" s="138" t="inlineStr">
-        <is>
-          <t>① 恒科2.5%清仓→转MLCC(3%→5.5%)。理由：P=27%三条信号同向，蒋宇飞说传统互联网是老灯鼓</t>
+      <c r="A121" s="155" t="inlineStr">
+        <is>
+          <t>一、三源信号详情</t>
         </is>
       </c>
     </row>
     <row r="122" ht="15" customHeight="1" s="139">
-      <c r="A122" s="138" t="inlineStr">
-        <is>
-          <t>② 堆叠45%分三批进：第一批15%(跌15%触发)→第二批15%(再跌或横盘2月)→第三批15%(产业验证)</t>
+      <c r="A122" s="156" t="inlineStr">
+        <is>
+          <t>来源</t>
+        </is>
+      </c>
+      <c r="B122" s="156" t="inlineStr">
+        <is>
+          <t>核心观点</t>
+        </is>
+      </c>
+      <c r="C122" s="156" t="inlineStr">
+        <is>
+          <t>与你策略契合</t>
+        </is>
+      </c>
+      <c r="D122" s="156" t="inlineStr">
+        <is>
+          <t>虚P方向</t>
+        </is>
+      </c>
+      <c r="E122" s="156" t="inlineStr">
+        <is>
+          <t>落地条件</t>
+        </is>
+      </c>
+      <c r="F122" s="156" t="inlineStr">
+        <is>
+          <t>状态</t>
+        </is>
+      </c>
+      <c r="G122" s="156" t="inlineStr">
+        <is>
+          <t>权重</t>
+        </is>
+      </c>
+      <c r="H122" s="156" t="inlineStr">
+        <is>
+          <t>备注</t>
         </is>
       </c>
     </row>
     <row r="123" ht="15" customHeight="1" s="139">
-      <c r="A123" s="138" t="inlineStr">
-        <is>
-          <t>③ Plan B：锁到2027-01-31，逾期进则进40%留20%继续等。替代触发三选一：芯片PE&lt;40分位/蒋宇飞说现在进/月线连阴3月</t>
-        </is>
-      </c>
-    </row>
-    <row r="124" ht="26.85" customHeight="1" s="139">
-      <c r="A124" s="138" t="inlineStr">
-        <is>
-          <t>④ MLCC标的：风华高科200股(~4500元)，最接近MLCC纯暴露(MLCC营收占比58%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="125" ht="15" customHeight="1" s="139">
-      <c r="A125" s="138" t="inlineStr">
-        <is>
-          <t>⑤ 机器人4%不变（无纯暴露工具）+ 科创AI027048加仓6%覆盖AI+机器人+算力</t>
-        </is>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" s="138" t="inlineStr">
-        <is>
-          <t>⑥ 资金来源：现有现金50%+卖恒科2.5%+卖有色稀金5%+养殖减半12.5%+未来收入≈85%。两年跨度3%误差可接受</t>
-        </is>
-      </c>
-    </row>
-    <row r="127" ht="15" customHeight="1" s="139">
-      <c r="A127" s="138" t="inlineStr">
-        <is>
-          <t>⑦ P=75%被四源交叉确认(达利欧+李大霄+蒋宇飞+用户)→可能估低。小龙承认不是'全押蒋宇飞'</t>
-        </is>
-      </c>
-    </row>
-    <row r="128" ht="15" customHeight="1" s="139">
-      <c r="A128" s="332" t="inlineStr">
-        <is>
-          <t>▶ HBM产业链 5%</t>
-        </is>
-      </c>
-    </row>
-    <row r="129" ht="26.85" customHeight="1" s="139">
-      <c r="A129" s="138" t="inlineStr">
-        <is>
-          <t>为什么买：蒋宇飞"HBM未来1.5-2.5年波涛汹涌""Q4-Q1波澜壮阔热潮"。HBM是AI技术含量最高的存储，目前最紧缺</t>
-        </is>
-      </c>
-    </row>
-    <row r="130" ht="15" customHeight="1" s="139">
-      <c r="A130" s="138" t="inlineStr">
-        <is>
-          <t>什么时候进：2026-Q4（10-12月），MLCC清仓后资金转入</t>
-        </is>
-      </c>
-    </row>
-    <row r="131" ht="15" customHeight="1" s="139">
-      <c r="A131" s="138" t="inlineStr">
-        <is>
-          <t>什么时候出：2027-Q1热潮结束观察。蒋宇飞说热潮在四季度至明年一季度展开</t>
-        </is>
-      </c>
-    </row>
-    <row r="132" ht="15" customHeight="1" s="139">
-      <c r="A132" s="138" t="inlineStr">
-        <is>
-          <t>风控：5%不大。Q4不启动就继续等，不急着进</t>
-        </is>
-      </c>
-    </row>
-    <row r="133" ht="15" customHeight="1" s="139"/>
-    <row r="134" ht="26.85" customHeight="1" s="139">
-      <c r="A134" s="329" t="inlineStr">
-        <is>
-          <t>▶ 堆叠/先进封装 长电25%+通富20%=45%（核心重仓）</t>
-        </is>
-      </c>
-    </row>
-    <row r="135" ht="15" customHeight="1" s="139">
-      <c r="A135" s="138" t="inlineStr">
-        <is>
-          <t>为什么买：蒋宇飞27条视频反复强调"未来两年最大风口""改变家族命运""躺赢"。堆叠=CoWoS/2.5D/3D=突破存算一体。封装成本占存储芯片20%。P=75%顶级信源验证</t>
-        </is>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" s="138" t="inlineStr">
-        <is>
-          <t>为什么长电+通富：长电=全球第三大封测，2.5D/3D量产，客户高通/海思/TI。通富=AMD封测全线突破，MI300X参与，不可替代</t>
-        </is>
-      </c>
-    </row>
-    <row r="137" ht="15" customHeight="1" s="139">
-      <c r="A137" s="138" t="inlineStr">
-        <is>
-          <t>什么时候进：等11月美股大跌15%+。触发三选一：①达利欧泡沫落地 ②纳指破200日均线 ③中期选举大跌。全不进不砸</t>
-        </is>
-      </c>
-    </row>
-    <row r="138" ht="26.85" customHeight="1" s="139">
-      <c r="A138" s="138" t="inlineStr">
-        <is>
-          <t>先手仓位：Q4先建5%（长电3%+通富2%），等回调后进大仓位。符合蒋宇飞"三成追七成等"纪律</t>
-        </is>
-      </c>
-    </row>
-    <row r="139" ht="15" customHeight="1" s="139">
-      <c r="A139" s="138" t="inlineStr">
-        <is>
-          <t>什么时候出：2027-H2堆叠大放→长期持有。蒋宇飞说堆叠是10年风口</t>
-        </is>
-      </c>
-    </row>
-    <row r="140" ht="26.85" customHeight="1" s="139">
-      <c r="A140" s="138" t="inlineStr">
-        <is>
-          <t>风控：45%很重。必须等15%+回调才进（安全边际）。不到位置不砸。蒋宇飞说"回调就是你的机会"</t>
-        </is>
-      </c>
-    </row>
-    <row r="141" ht="26.85" customHeight="1" s="139"/>
-    <row r="142" ht="39.55" customHeight="1" s="139">
-      <c r="A142" s="332" t="inlineStr">
-        <is>
-          <t>▶ 国产算力/升腾链 10%</t>
-        </is>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" s="138" t="inlineStr">
-        <is>
-          <t>为什么买：蒋宇飞"2027算力长城最闪亮""升腾链2027爆发""升腾950明年出货"。工信部要求支持国产芯片</t>
-        </is>
-      </c>
-    </row>
-    <row r="144" ht="17.35" customHeight="1" s="139">
-      <c r="A144" s="138" t="inlineStr">
-        <is>
-          <t>什么时候进：2027年。触发：华为升腾950大批出货/工信部政策加码</t>
-        </is>
-      </c>
-    </row>
-    <row r="145" ht="17.15" customHeight="1" s="139">
-      <c r="A145" s="138" t="inlineStr">
-        <is>
-          <t>风控：等2027，当前只看不动</t>
-        </is>
-      </c>
-    </row>
-    <row r="146" ht="17.15" customHeight="1" s="139"/>
-    <row r="147" ht="17.15" customHeight="1" s="139">
-      <c r="A147" s="332" t="inlineStr">
-        <is>
-          <t>▶ 机器人(物理AI) 4%</t>
-        </is>
-      </c>
-    </row>
-    <row r="148" ht="17.15" customHeight="1" s="139">
-      <c r="A148" s="138" t="inlineStr">
-        <is>
-          <t>为什么买：用户判断机器人&gt;黄金&gt;比特币。蒋宇飞验证："未来经济三层=物理人→钢铁机器人→网络agent"。宇树科技73天过会</t>
-        </is>
-      </c>
-    </row>
-    <row r="149" ht="17.15" customHeight="1" s="139">
-      <c r="A149" s="138" t="inlineStr">
-        <is>
-          <t>什么时候进：2027冬开始逐步建。中长期赛道，不急</t>
-        </is>
-      </c>
-    </row>
-    <row r="150" ht="17.15" customHeight="1" s="139">
-      <c r="A150" s="138" t="inlineStr">
-        <is>
-          <t>风控：4%不大，判断错误损失可控</t>
-        </is>
-      </c>
-    </row>
-    <row r="151" ht="17.15" customHeight="1" s="139"/>
-    <row r="152" ht="17.15" customHeight="1" s="139">
-      <c r="A152" s="332" t="inlineStr">
-        <is>
-          <t>▶ 玻璃基板 3%</t>
-        </is>
-      </c>
-    </row>
-    <row r="153" ht="17.15" customHeight="1" s="139">
-      <c r="A153" s="138" t="inlineStr">
-        <is>
-          <t>为什么买：蒋宇飞"被严重低估即将爆发""两三年热点""业绩2027-H2释放""大规模2028"。两个爆发点：封装+存储</t>
-        </is>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154" s="138" t="inlineStr">
-        <is>
-          <t>什么时候进：2027年等业绩释放。蒋宇飞说"消息还在送验阶段"</t>
-        </is>
-      </c>
-    </row>
-    <row r="155" ht="15" customHeight="1" s="139">
-      <c r="A155" s="138" t="inlineStr">
-        <is>
-          <t>风控：3%观察仓，等消息确认</t>
-        </is>
-      </c>
-    </row>
-    <row r="156" ht="15" customHeight="1" s="139"/>
-    <row r="157" ht="15" customHeight="1" s="139">
-      <c r="A157" s="329" t="inlineStr">
-        <is>
-          <t>四、进钱节奏时间线</t>
-        </is>
-      </c>
-    </row>
-    <row r="158" ht="15" customHeight="1" s="139"/>
-    <row r="159" ht="15" customHeight="1" s="139">
-      <c r="A159" s="333" t="inlineStr">
-        <is>
-          <t>时间</t>
-        </is>
-      </c>
-    </row>
-    <row r="160" ht="15" customHeight="1" s="139">
-      <c r="A160" s="138" t="inlineStr">
-        <is>
-          <t>现在-7月</t>
-        </is>
-      </c>
-      <c r="B160" s="138" t="inlineStr">
-        <is>
-          <t>MLCC3%建仓</t>
-        </is>
-      </c>
-      <c r="C160" s="138" t="inlineStr">
-        <is>
-          <t>芯片10%不动(虚P+3pp)</t>
-        </is>
-      </c>
-      <c r="D160" s="138" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E160" s="138" t="inlineStr">
-        <is>
-          <t>7%</t>
-        </is>
-      </c>
-    </row>
-    <row r="161">
-      <c r="A161" s="138" t="inlineStr">
-        <is>
-          <t>8-10月</t>
-        </is>
-      </c>
-    </row>
-    <row r="162">
-      <c r="A162" s="138" t="inlineStr">
-        <is>
-          <t>11月大跌</t>
-        </is>
-      </c>
-      <c r="B162" s="138" t="inlineStr">
-        <is>
-          <t>长电25%+通富20%大砸</t>
-        </is>
-      </c>
-      <c r="C162" s="138" t="inlineStr">
-        <is>
-          <t>MLCC清→HBM5%+堆叠先手5%</t>
-        </is>
-      </c>
-      <c r="D162" s="138" t="inlineStr">
-        <is>
-          <t>MLCC清</t>
-        </is>
-      </c>
-      <c r="E162" s="138" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-    </row>
-    <row r="163">
-      <c r="A163" s="138" t="inlineStr">
-        <is>
-          <t>11月没大跌</t>
-        </is>
-      </c>
-      <c r="B163" s="138" t="inlineStr">
-        <is>
-          <t>堆叠先手5%(长电3+通富2)</t>
-        </is>
-      </c>
-      <c r="C163" s="138" t="inlineStr">
-        <is>
-          <t>MLCC清→等</t>
-        </is>
-      </c>
-      <c r="D163" s="138" t="inlineStr">
-        <is>
-          <t>MLCC清</t>
-        </is>
-      </c>
-      <c r="E163" s="138" t="inlineStr">
-        <is>
-          <t>0-2%</t>
-        </is>
-      </c>
-    </row>
-    <row r="164">
-      <c r="A164" s="138" t="inlineStr">
-        <is>
-          <t>2027-Q1</t>
-        </is>
-      </c>
-      <c r="B164" s="138" t="inlineStr">
-        <is>
-          <t>HBM持有</t>
-        </is>
-      </c>
-      <c r="C164" s="138" t="inlineStr">
-        <is>
-          <t>堆叠先手持有</t>
-        </is>
-      </c>
-      <c r="D164" s="138" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E164" s="138" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="165">
-      <c r="A165" s="138" t="inlineStr">
-        <is>
-          <t>2027-H2</t>
-        </is>
-      </c>
-    </row>
-    <row r="166">
-      <c r="A166" s="138" t="inlineStr">
-        <is>
-          <t>2027冬</t>
-        </is>
-      </c>
-    </row>
-    <row r="167"/>
-    <row r="168">
-      <c r="A168" s="329" t="inlineStr">
-        <is>
-          <t>⚡ 一句话：MLCC3%小试→Q4 HBM5%+堆叠先手5%→11月大跌长电25%+通富20%→2027堆叠躺赢</t>
-        </is>
-      </c>
-    </row>
-    <row r="169">
-      <c r="A169" s="138" t="inlineStr">
-        <is>
-          <t>风控：45%重仓必须等15%+回调 | MLCC年底必清 | 蒋宇飞纪律"三成追七成等"</t>
-        </is>
-      </c>
-    </row>
-    <row r="170"/>
-    <row r="171"/>
-    <row r="172"/>
-    <row r="173">
-      <c r="A173" s="148" t="inlineStr">
-        <is>
-          <t>🔥 叙事主线（四条）</t>
-        </is>
-      </c>
-      <c r="B173" s="149" t="n"/>
-      <c r="C173" s="149" t="n"/>
-      <c r="D173" s="149" t="n"/>
-      <c r="E173" s="149" t="n"/>
-      <c r="F173" s="149" t="n"/>
-      <c r="G173" s="149" t="n"/>
-      <c r="H173" s="150" t="n"/>
-    </row>
-    <row r="174">
-      <c r="A174" s="325" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  辅助仓位: 玻璃基板5% | 算力出海5%</t>
-        </is>
-      </c>
-      <c r="B174" s="326" t="n"/>
-      <c r="C174" s="326" t="n"/>
-      <c r="D174" s="326" t="n"/>
-      <c r="E174" s="326" t="n"/>
-      <c r="F174" s="326" t="n"/>
-      <c r="G174" s="326" t="n"/>
-      <c r="H174" s="325" t="n"/>
-    </row>
-    <row r="175">
-      <c r="A175" s="325" t="n"/>
-      <c r="B175" s="326" t="n"/>
-      <c r="C175" s="326" t="n"/>
-      <c r="D175" s="326" t="n"/>
-      <c r="E175" s="326" t="n"/>
-      <c r="F175" s="326" t="n"/>
-      <c r="G175" s="326" t="n"/>
-      <c r="H175" s="325" t="n"/>
-    </row>
-    <row r="176">
-      <c r="A176" s="334" t="inlineStr">
-        <is>
-          <t>三、核心仓位汇总表</t>
-        </is>
-      </c>
-      <c r="B176" s="326" t="n"/>
-      <c r="C176" s="326" t="n"/>
-      <c r="D176" s="326" t="n"/>
-      <c r="E176" s="326" t="n"/>
-      <c r="F176" s="326" t="n"/>
-      <c r="G176" s="326" t="n"/>
-      <c r="H176" s="325" t="n"/>
-    </row>
-    <row r="177">
-      <c r="A177" s="138" t="inlineStr">
-        <is>
-          <t>持仓(50%): 养殖25%+芯片10%+电池5%+恒科2.5%+有色2.5%+稀金2.5%+银行1.5%</t>
-        </is>
-      </c>
-    </row>
-    <row r="178">
-      <c r="A178" s="151" t="inlineStr">
-        <is>
-          <t>待重仓(等回调): 长电25%+通富20%=45% → 11月中期选举触发</t>
-        </is>
-      </c>
-    </row>
-    <row r="179">
-      <c r="A179" s="152" t="inlineStr">
-        <is>
-          <t>观察仓(机动18%): MLCC2%+HBM5%+堆叠先手5%+升腾/国产算力5%+玻璃基板1%</t>
-        </is>
-      </c>
-    </row>
-    <row r="180">
-      <c r="A180" s="153" t="inlineStr">
-        <is>
-          <t>锁定现金(13%): 等11月大事件→解锁后进长电/通富剩余仓位</t>
-        </is>
-      </c>
-    </row>
-    <row r="181">
-      <c r="A181" s="154" t="inlineStr">
-        <is>
-          <t>虚P规则：未落地→记虚P→不加实P→等落地转实P。此板块锁定大部分现金，与机会成本联动分析。</t>
-        </is>
-      </c>
-    </row>
-    <row r="182">
-      <c r="A182" s="327" t="inlineStr">
-        <is>
-          <t>四、蒋宇飞"三层追七成等"落地</t>
-        </is>
-      </c>
-    </row>
-    <row r="183">
-      <c r="A183" s="156" t="inlineStr">
-        <is>
-          <t>30%追热点: 当前MLCC(蒋宇飞4月底预测已启动)+光模块(贯穿2026) | 这部分在持仓里</t>
-        </is>
-      </c>
-      <c r="B183" s="156" t="inlineStr">
-        <is>
-          <t>核心观点</t>
-        </is>
-      </c>
-      <c r="C183" s="156" t="inlineStr">
-        <is>
-          <t>与你策略契合</t>
-        </is>
-      </c>
-      <c r="D183" s="156" t="inlineStr">
-        <is>
-          <t>虚P方向</t>
-        </is>
-      </c>
-      <c r="E183" s="156" t="inlineStr">
-        <is>
-          <t>落地条件</t>
-        </is>
-      </c>
-      <c r="F183" s="156" t="inlineStr">
-        <is>
-          <t>状态</t>
-        </is>
-      </c>
-      <c r="G183" s="156" t="inlineStr">
-        <is>
-          <t>权重</t>
-        </is>
-      </c>
-      <c r="H183" s="156" t="inlineStr">
-        <is>
-          <t>备注</t>
-        </is>
-      </c>
-    </row>
-    <row r="184">
-      <c r="A184" s="157" t="inlineStr">
-        <is>
-          <t>70%等回调: 堆叠(长电+通富等11月大跌15%+大仓位进) | 升腾链等2027爆发</t>
-        </is>
-      </c>
-      <c r="B184" s="157" t="inlineStr">
+      <c r="A123" s="157" t="inlineStr">
+        <is>
+          <t>达利欧
+Bloomberg 6/3</t>
+        </is>
+      </c>
+      <c r="B123" s="157" t="inlineStr">
         <is>
           <t>AI泡沫65-75%概率年底破
 "财富转现金=刺破泡沫"
@@ -3924,7 +3542,7 @@
 基建投入&gt;&gt;收入</t>
         </is>
       </c>
-      <c r="C184" s="158" t="inlineStr">
+      <c r="C123" s="158" t="inlineStr">
         <is>
           <t>完全契合
 等中期选举大跌
@@ -3932,367 +3550,1583 @@
 回调后大仓位进</t>
         </is>
       </c>
-      <c r="D184" s="157" t="inlineStr">
+      <c r="D123" s="157" t="inlineStr">
         <is>
           <t>芯片-2pp
 恒科-1pp
 (虚P)</t>
         </is>
       </c>
-      <c r="E184" s="157" t="inlineStr">
+      <c r="E123" s="157" t="inlineStr">
         <is>
           <t>七姐妹&gt;15%回调
 或破200日均线</t>
         </is>
       </c>
-      <c r="F184" s="159" t="inlineStr">
+      <c r="F123" s="159" t="inlineStr">
         <is>
           <t>未落地</t>
         </is>
       </c>
-      <c r="G184" s="160" t="inlineStr">
+      <c r="G123" s="160" t="inlineStr">
         <is>
           <t>极高
 5星</t>
         </is>
       </c>
-      <c r="H184" s="157" t="inlineStr">
+      <c r="H123" s="157" t="inlineStr">
         <is>
           <t>与你100%一致
 回调=买入机会</t>
         </is>
       </c>
     </row>
-    <row r="185">
-      <c r="A185" s="157" t="inlineStr">
+    <row r="124" ht="26.85" customHeight="1" s="139">
+      <c r="A124" s="157" t="inlineStr">
         <is>
           <t>李大霄
 金融界 6/4</t>
         </is>
       </c>
-      <c r="B185" s="149" t="n"/>
-      <c r="C185" s="149" t="n"/>
-      <c r="D185" s="149" t="n"/>
-      <c r="E185" s="149" t="n"/>
-      <c r="F185" s="149" t="n"/>
-      <c r="G185" s="149" t="n"/>
-      <c r="H185" s="150" t="n"/>
-    </row>
-    <row r="186">
-      <c r="A186" s="328" t="inlineStr">
-        <is>
-          <t>五、关键时间点操作清单</t>
-        </is>
-      </c>
-      <c r="B186" s="149" t="n"/>
-      <c r="C186" s="149" t="n"/>
-      <c r="D186" s="149" t="n"/>
-      <c r="E186" s="149" t="n"/>
-      <c r="F186" s="149" t="n"/>
-      <c r="G186" s="149" t="n"/>
-      <c r="H186" s="150" t="n"/>
-    </row>
-    <row r="187">
-      <c r="A187" s="138" t="inlineStr">
-        <is>
-          <t>6-7月: 长鑫上市→观察存储/芯片反应 | 芯片10%不动 | MLCC2%观察仓可建</t>
-        </is>
-      </c>
-    </row>
-    <row r="188">
-      <c r="A188" s="155" t="inlineStr">
-        <is>
-          <t>8-10月: MLCC肉最甜→持到11月 | 观察HBM启动信号</t>
-        </is>
-      </c>
-    </row>
-    <row r="189">
-      <c r="A189" s="161" t="inlineStr">
-        <is>
-          <t>11-12月: MLCC清仓→资金转HBM5%+堆叠先手5% | 非农黑五→恒科注意</t>
-        </is>
-      </c>
-      <c r="B189" s="161" t="inlineStr">
+      <c r="B124" s="157" t="inlineStr">
+        <is>
+          <t>美股窄牛宽熊
+仅20只创新高
+CAPE40倍
+权重极度集中
+IPO抽血</t>
+        </is>
+      </c>
+      <c r="C124" s="158" t="inlineStr">
+        <is>
+          <t>高度契合
+确认美股风险
+现金策略正确</t>
+        </is>
+      </c>
+      <c r="D124" s="157" t="inlineStr">
+        <is>
+          <t>恒科-2pp
+芯片-1pp
+(虚P)</t>
+        </is>
+      </c>
+      <c r="E124" s="157" t="inlineStr">
+        <is>
+          <t>纳指破200日均线
+多数成分股下跌</t>
+        </is>
+      </c>
+      <c r="F124" s="159" t="inlineStr">
+        <is>
+          <t>未落地</t>
+        </is>
+      </c>
+      <c r="G124" s="157" t="inlineStr">
+        <is>
+          <t>中高
+3星</t>
+        </is>
+      </c>
+      <c r="H124" s="157" t="inlineStr">
+        <is>
+          <t>数据靠谱
+结论偏激进</t>
+        </is>
+      </c>
+    </row>
+    <row r="125" ht="15" customHeight="1" s="139">
+      <c r="A125" s="157" t="inlineStr">
+        <is>
+          <t>知乎专栏
+6/4</t>
+        </is>
+      </c>
+      <c r="B125" s="149" t="n"/>
+      <c r="C125" s="149" t="n"/>
+      <c r="D125" s="149" t="n"/>
+      <c r="E125" s="149" t="n"/>
+      <c r="F125" s="149" t="n"/>
+      <c r="G125" s="149" t="n"/>
+      <c r="H125" s="150" t="n"/>
+    </row>
+    <row r="126"/>
+    <row r="127" ht="15" customHeight="1" s="139">
+      <c r="A127" s="155" t="inlineStr">
+        <is>
+          <t>二、三源互锁验证</t>
+        </is>
+      </c>
+    </row>
+    <row r="128" ht="15" customHeight="1" s="139">
+      <c r="A128" s="161" t="inlineStr">
+        <is>
+          <t>互锁组合</t>
+        </is>
+      </c>
+      <c r="B128" s="161" t="inlineStr">
         <is>
           <t>关系</t>
         </is>
       </c>
-      <c r="C189" s="161" t="inlineStr">
+      <c r="C128" s="161" t="inlineStr">
         <is>
           <t>分析</t>
         </is>
       </c>
-      <c r="D189" s="161" t="inlineStr">
+      <c r="D128" s="161" t="inlineStr">
         <is>
           <t>信号强度</t>
         </is>
       </c>
     </row>
-    <row r="190">
-      <c r="A190" s="162" t="inlineStr">
-        <is>
-          <t>2027-Q1: HBM热潮→持有 | 堆叠先手继续观察</t>
-        </is>
-      </c>
-      <c r="B190" s="163" t="inlineStr">
+    <row r="129" ht="26.85" customHeight="1" s="139">
+      <c r="A129" s="162" t="inlineStr">
+        <is>
+          <t>达利欧×李大霄</t>
+        </is>
+      </c>
+      <c r="B129" s="163" t="inlineStr">
         <is>
           <t>✅强印证</t>
         </is>
       </c>
-      <c r="C190" s="157" t="inlineStr">
+      <c r="C129" s="157" t="inlineStr">
         <is>
           <t>AI泡沫+窄牛宽熊=同一现象两角度</t>
         </is>
       </c>
-      <c r="D190" s="157" t="inlineStr">
+      <c r="D129" s="157" t="inlineStr">
         <is>
           <t>🔴强信号</t>
         </is>
       </c>
     </row>
-    <row r="191">
-      <c r="A191" s="162" t="inlineStr">
-        <is>
-          <t>2027-H2: 堆叠大放光芒→长电25%+通富20%大仓位确认 | 升腾链10% | CPU5%</t>
-        </is>
-      </c>
-      <c r="B191" s="164" t="inlineStr">
+    <row r="130" ht="15" customHeight="1" s="139">
+      <c r="A130" s="162" t="inlineStr">
+        <is>
+          <t>达利欧×知乎</t>
+        </is>
+      </c>
+      <c r="B130" s="164" t="inlineStr">
         <is>
           <t>⚠️部分矛盾</t>
         </is>
       </c>
-      <c r="C191" s="157" t="inlineStr">
+      <c r="C130" s="157" t="inlineStr">
         <is>
           <t>达看流动性vs知乎看估值</t>
         </is>
       </c>
-      <c r="D191" s="157" t="inlineStr">
+      <c r="D130" s="157" t="inlineStr">
         <is>
           <t>🟡中性</t>
         </is>
       </c>
     </row>
-    <row r="192">
-      <c r="A192" s="162" t="inlineStr">
+    <row r="131" ht="15" customHeight="1" s="139">
+      <c r="A131" s="162" t="inlineStr">
         <is>
           <t>三源共识</t>
         </is>
       </c>
-      <c r="B192" s="149" t="n"/>
-      <c r="C192" s="149" t="n"/>
-      <c r="D192" s="149" t="n"/>
-      <c r="E192" s="149" t="n"/>
-      <c r="F192" s="149" t="n"/>
-      <c r="G192" s="149" t="n"/>
-      <c r="H192" s="150" t="n"/>
-    </row>
-    <row r="193">
-      <c r="A193" s="138" t="n"/>
-    </row>
-    <row r="194">
-      <c r="A194" s="165" t="inlineStr">
+      <c r="B131" s="149" t="n"/>
+      <c r="C131" s="149" t="n"/>
+      <c r="D131" s="149" t="n"/>
+      <c r="E131" s="149" t="n"/>
+      <c r="F131" s="149" t="n"/>
+      <c r="G131" s="149" t="n"/>
+      <c r="H131" s="150" t="n"/>
+    </row>
+    <row r="132" ht="15" customHeight="1" s="139">
+      <c r="A132" s="138" t="n"/>
+    </row>
+    <row r="133" ht="15" customHeight="1" s="139">
+      <c r="A133" s="165" t="inlineStr">
         <is>
           <t>三、现金策略联动（锁定大部分现金储备）</t>
         </is>
       </c>
     </row>
-    <row r="195">
-      <c r="A195" s="154" t="inlineStr">
+    <row r="134" ht="26.85" customHeight="1" s="139">
+      <c r="A134" s="154" t="inlineStr">
         <is>
           <t>三源联动→达利欧65-75%概率年底AI回调+中期选举历史跌一波→锁定大部分现金→等11月回调入场</t>
         </is>
       </c>
     </row>
-    <row r="196">
-      <c r="A196" s="161" t="inlineStr">
+    <row r="135" ht="15" customHeight="1" s="139">
+      <c r="A135" s="161" t="inlineStr">
         <is>
           <t>维度</t>
         </is>
       </c>
-    </row>
-    <row r="197">
-      <c r="A197" s="157" t="inlineStr">
+      <c r="B135" s="161" t="inlineStr">
+        <is>
+          <t>内容</t>
+        </is>
+      </c>
+      <c r="C135" s="161" t="inlineStr">
+        <is>
+          <t>影响</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="157" t="inlineStr">
         <is>
           <t>现金锁定</t>
         </is>
       </c>
-      <c r="B197" s="149" t="n"/>
-      <c r="C197" s="149" t="n"/>
-      <c r="D197" s="149" t="n"/>
-      <c r="E197" s="149" t="n"/>
-      <c r="F197" s="149" t="n"/>
-      <c r="G197" s="149" t="n"/>
-      <c r="H197" s="150" t="n"/>
-    </row>
-    <row r="198">
-      <c r="A198" s="157" t="inlineStr">
+      <c r="B136" s="157" t="inlineStr">
+        <is>
+          <t>大部分现金(60-70%)锁定等待</t>
+        </is>
+      </c>
+      <c r="C136" s="157" t="inlineStr">
+        <is>
+          <t>→当前可投资金大幅减少</t>
+        </is>
+      </c>
+    </row>
+    <row r="137" ht="15" customHeight="1" s="139">
+      <c r="A137" s="157" t="inlineStr">
         <is>
           <t>等待窗口</t>
         </is>
       </c>
-      <c r="B198" s="157" t="inlineStr">
+      <c r="B137" s="157" t="inlineStr">
         <is>
           <t>2026年11月中期选举前后</t>
         </is>
       </c>
-      <c r="C198" s="157" t="inlineStr">
+      <c r="C137" s="157" t="inlineStr">
         <is>
           <t>→约5个月等待期</t>
         </is>
       </c>
     </row>
-    <row r="199">
-      <c r="A199" s="157" t="inlineStr">
+    <row r="138" ht="26.85" customHeight="1" s="139">
+      <c r="A138" s="157" t="inlineStr">
         <is>
           <t>触发条件</t>
         </is>
       </c>
-      <c r="B199" s="157" t="inlineStr">
+      <c r="B138" s="157" t="inlineStr">
         <is>
           <t>美股跌一波+AI回调&gt;15%</t>
         </is>
       </c>
-      <c r="C199" s="157" t="inlineStr">
+      <c r="C138" s="157" t="inlineStr">
         <is>
           <t>→达利欧65-75%概率事件</t>
         </is>
       </c>
     </row>
-    <row r="200">
-      <c r="A200" s="157" t="inlineStr">
+    <row r="139" ht="15" customHeight="1" s="139">
+      <c r="A139" s="157" t="inlineStr">
         <is>
           <t>入场标的</t>
         </is>
       </c>
-      <c r="B200" s="157" t="inlineStr">
+      <c r="B139" s="157" t="inlineStr">
         <is>
           <t>堆叠：长电科技+通富微电</t>
         </is>
       </c>
-      <c r="C200" s="157" t="inlineStr">
+      <c r="C139" s="157" t="inlineStr">
         <is>
           <t>→国内确定性不受美股影响</t>
         </is>
       </c>
     </row>
-    <row r="201">
-      <c r="A201" s="157" t="inlineStr">
+    <row r="140" ht="26.85" customHeight="1" s="139">
+      <c r="A140" s="157" t="inlineStr">
         <is>
           <t>机会成本</t>
         </is>
       </c>
-      <c r="B201" s="157" t="inlineStr">
+      <c r="B140" s="157" t="inlineStr">
         <is>
           <t>持有现金5个月vs错过短期行情</t>
         </is>
       </c>
-      <c r="C201" s="157" t="inlineStr">
+      <c r="C140" s="157" t="inlineStr">
         <is>
           <t>→见下方机会成本联动</t>
         </is>
       </c>
     </row>
-    <row r="202">
-      <c r="A202" s="157" t="inlineStr">
+    <row r="141" ht="26.85" customHeight="1" s="139">
+      <c r="A141" s="157" t="inlineStr">
         <is>
           <t>下行保护</t>
         </is>
       </c>
-      <c r="B202" s="149" t="n"/>
-      <c r="C202" s="149" t="n"/>
-      <c r="D202" s="149" t="n"/>
-      <c r="E202" s="149" t="n"/>
-      <c r="F202" s="149" t="n"/>
-      <c r="G202" s="149" t="n"/>
-      <c r="H202" s="150" t="n"/>
-    </row>
-    <row r="203"/>
-    <row r="204">
-      <c r="A204" s="165" t="inlineStr">
+      <c r="B141" s="149" t="n"/>
+      <c r="C141" s="149" t="n"/>
+      <c r="D141" s="149" t="n"/>
+      <c r="E141" s="149" t="n"/>
+      <c r="F141" s="149" t="n"/>
+      <c r="G141" s="149" t="n"/>
+      <c r="H141" s="150" t="n"/>
+    </row>
+    <row r="142" ht="39.55" customHeight="1" s="139"/>
+    <row r="143">
+      <c r="A143" s="165" t="inlineStr">
         <is>
           <t>四、机会成本联动分析（现金锁定vs其他选项）</t>
         </is>
       </c>
     </row>
-    <row r="205">
-      <c r="A205" s="161" t="inlineStr">
+    <row r="144" ht="17.35" customHeight="1" s="139">
+      <c r="A144" s="161" t="inlineStr">
         <is>
           <t>选项</t>
         </is>
       </c>
-      <c r="B205" s="161" t="inlineStr">
+      <c r="B144" s="161" t="inlineStr">
         <is>
           <t>P值</t>
         </is>
       </c>
-      <c r="C205" s="161" t="inlineStr">
+      <c r="C144" s="161" t="inlineStr">
         <is>
           <t>盈亏比</t>
         </is>
       </c>
-      <c r="D205" s="161" t="inlineStr">
+      <c r="D144" s="161" t="inlineStr">
         <is>
           <t>Score</t>
         </is>
       </c>
-      <c r="E205" s="161" t="inlineStr">
+      <c r="E144" s="161" t="inlineStr">
         <is>
           <t>现金锁定影响</t>
         </is>
       </c>
-      <c r="F205" s="161" t="inlineStr">
+      <c r="F144" s="161" t="inlineStr">
         <is>
           <t>建议</t>
         </is>
       </c>
-      <c r="G205" s="161" t="inlineStr">
+      <c r="G144" s="161" t="inlineStr">
         <is>
           <t>判断</t>
         </is>
       </c>
     </row>
-    <row r="206">
-      <c r="A206" s="157" t="inlineStr">
+    <row r="145" ht="17.15" customHeight="1" s="139">
+      <c r="A145" s="157" t="inlineStr">
         <is>
           <t>长电科技</t>
         </is>
       </c>
-      <c r="B206" s="157" t="inlineStr">
+      <c r="B145" s="157" t="inlineStr">
         <is>
           <t>75%</t>
         </is>
       </c>
-      <c r="C206" s="157" t="inlineStr">
+      <c r="C145" s="157" t="inlineStr">
         <is>
           <t>4.5:1</t>
         </is>
       </c>
-      <c r="D206" s="157" t="inlineStr">
+      <c r="D145" s="157" t="inlineStr">
         <is>
           <t>3.375</t>
         </is>
       </c>
-      <c r="E206" s="157" t="inlineStr">
+      <c r="E145" s="157" t="inlineStr">
         <is>
           <t>等回调大仓位
 现金锁定中</t>
         </is>
       </c>
-      <c r="F206" s="157" t="inlineStr">
+      <c r="F145" s="157" t="inlineStr">
         <is>
           <t>暂不动等11月</t>
         </is>
       </c>
-      <c r="G206" s="160" t="inlineStr">
+      <c r="G145" s="160" t="inlineStr">
         <is>
           <t>🔴最高优先</t>
         </is>
       </c>
     </row>
+    <row r="146" ht="17.15" customHeight="1" s="139">
+      <c r="A146" s="157" t="inlineStr">
+        <is>
+          <t>通富微电</t>
+        </is>
+      </c>
+      <c r="B146" s="157" t="inlineStr">
+        <is>
+          <t>75%</t>
+        </is>
+      </c>
+      <c r="C146" s="157" t="inlineStr">
+        <is>
+          <t>4.0:1</t>
+        </is>
+      </c>
+      <c r="D146" s="157" t="inlineStr">
+        <is>
+          <t>3.000</t>
+        </is>
+      </c>
+      <c r="E146" s="157" t="inlineStr">
+        <is>
+          <t>等回调大仓位
+现金锁定中</t>
+        </is>
+      </c>
+      <c r="F146" s="157" t="inlineStr">
+        <is>
+          <t>暂不动等11月</t>
+        </is>
+      </c>
+      <c r="G146" s="160" t="inlineStr">
+        <is>
+          <t>🔴最高优先</t>
+        </is>
+      </c>
+    </row>
+    <row r="147" ht="17.15" customHeight="1" s="139">
+      <c r="A147" s="157" t="inlineStr">
+        <is>
+          <t>养殖</t>
+        </is>
+      </c>
+      <c r="B147" s="157" t="inlineStr">
+        <is>
+          <t>70%</t>
+        </is>
+      </c>
+      <c r="C147" s="157" t="inlineStr">
+        <is>
+          <t>2.0:1</t>
+        </is>
+      </c>
+      <c r="D147" s="157" t="inlineStr">
+        <is>
+          <t>1.400</t>
+        </is>
+      </c>
+      <c r="E147" s="157" t="inlineStr">
+        <is>
+          <t>已持仓不需现金 | 6/5 芳姐：低价抄底母猪，行业融资枯竭，等待母猪血流成河才是最佳买点</t>
+        </is>
+      </c>
+      <c r="F147" s="157" t="inlineStr">
+        <is>
+          <t>继续持有</t>
+        </is>
+      </c>
+      <c r="G147" s="158" t="inlineStr">
+        <is>
+          <t>✅已配置</t>
+        </is>
+      </c>
+    </row>
+    <row r="148" ht="17.15" customHeight="1" s="139">
+      <c r="A148" s="157" t="inlineStr">
+        <is>
+          <t>电池</t>
+        </is>
+      </c>
+      <c r="B148" s="157" t="inlineStr">
+        <is>
+          <t>65%</t>
+        </is>
+      </c>
+      <c r="C148" s="157" t="inlineStr">
+        <is>
+          <t>2.0:1</t>
+        </is>
+      </c>
+      <c r="D148" s="157" t="inlineStr">
+        <is>
+          <t>1.300</t>
+        </is>
+      </c>
+      <c r="E148" s="157" t="inlineStr">
+        <is>
+          <t>已持仓不需现金 | 6/5 闻号说经济：厄尔尼诺80%概率+AI用电爆发→电力/能源受益</t>
+        </is>
+      </c>
+      <c r="F148" s="157" t="inlineStr">
+        <is>
+          <t>继续持有</t>
+        </is>
+      </c>
+      <c r="G148" s="158" t="inlineStr">
+        <is>
+          <t>✅已配置</t>
+        </is>
+      </c>
+    </row>
+    <row r="149" ht="17.15" customHeight="1" s="139">
+      <c r="A149" s="157" t="inlineStr">
+        <is>
+          <t>核电</t>
+        </is>
+      </c>
+      <c r="B149" s="157" t="inlineStr">
+        <is>
+          <t>52%</t>
+        </is>
+      </c>
+      <c r="C149" s="157" t="inlineStr">
+        <is>
+          <t>1.5:1</t>
+        </is>
+      </c>
+      <c r="D149" s="157" t="inlineStr">
+        <is>
+          <t>0.780</t>
+        </is>
+      </c>
+      <c r="E149" s="157" t="inlineStr">
+        <is>
+          <t>10年维度
+小仓试水可行</t>
+        </is>
+      </c>
+      <c r="F149" s="157" t="inlineStr">
+        <is>
+          <t>不影响现金策略</t>
+        </is>
+      </c>
+      <c r="G149" s="166" t="inlineStr">
+        <is>
+          <t>🟡长期观察</t>
+        </is>
+      </c>
+    </row>
+    <row r="150" ht="17.15" customHeight="1" s="139">
+      <c r="A150" s="157" t="inlineStr">
+        <is>
+          <t>存储</t>
+        </is>
+      </c>
+      <c r="B150" s="157" t="inlineStr">
+        <is>
+          <t>55%</t>
+        </is>
+      </c>
+      <c r="C150" s="157" t="inlineStr">
+        <is>
+          <t>1.0:1</t>
+        </is>
+      </c>
+      <c r="D150" s="157" t="inlineStr">
+        <is>
+          <t>0.550</t>
+        </is>
+      </c>
+      <c r="E150" s="157" t="inlineStr">
+        <is>
+          <t>已降级</t>
+        </is>
+      </c>
+      <c r="F150" s="157" t="inlineStr">
+        <is>
+          <t>不动</t>
+        </is>
+      </c>
+      <c r="G150" s="160" t="inlineStr">
+        <is>
+          <t>❌已降级</t>
+        </is>
+      </c>
+    </row>
+    <row r="151" ht="17.15" customHeight="1" s="139">
+      <c r="A151" s="157" t="inlineStr">
+        <is>
+          <t>纯现金5月</t>
+        </is>
+      </c>
+      <c r="B151" s="149" t="n"/>
+      <c r="C151" s="149" t="n"/>
+      <c r="D151" s="149" t="n"/>
+      <c r="E151" s="149" t="n"/>
+      <c r="F151" s="149" t="n"/>
+      <c r="G151" s="149" t="n"/>
+      <c r="H151" s="150" t="n"/>
+    </row>
+    <row r="152" ht="17.15" customHeight="1" s="139">
+      <c r="A152" s="147" t="inlineStr">
+        <is>
+          <t>AI硬件确定性(付鹏) → 内存=AI核心瓶颈(4信源互锁) → 国产替代加速 → 稀土断供日本 → 芯片/存储/HBM长期利好 | 短期被利率↑/地缘↑压制</t>
+        </is>
+      </c>
+    </row>
+    <row r="153" ht="17.15" customHeight="1" s="139">
+      <c r="A153" s="167" t="inlineStr">
+        <is>
+          <t>五、虚P→实P转换条件 &amp; 操作触发</t>
+        </is>
+      </c>
+      <c r="B153" s="168" t="n"/>
+      <c r="C153" s="168" t="n"/>
+      <c r="D153" s="168" t="n"/>
+      <c r="E153" s="168" t="n"/>
+      <c r="F153" s="168" t="n"/>
+      <c r="G153" s="168" t="n"/>
+      <c r="H153" s="169" t="n"/>
+    </row>
+    <row r="154">
+      <c r="A154" s="156" t="inlineStr">
+        <is>
+          <t>条件</t>
+        </is>
+      </c>
+      <c r="B154" s="161" t="inlineStr">
+        <is>
+          <t>触发信号</t>
+        </is>
+      </c>
+      <c r="C154" s="156" t="inlineStr">
+        <is>
+          <t>影响</t>
+        </is>
+      </c>
+      <c r="D154" s="156" t="inlineStr">
+        <is>
+          <t>操作</t>
+        </is>
+      </c>
+      <c r="E154" s="147" t="inlineStr">
+        <is>
+          <t>2026-05-30 宋鸿兵：海峡封锁→能源成本飙升</t>
+        </is>
+      </c>
+      <c r="F154" s="147" t="inlineStr">
+        <is>
+          <t>2026-05-30 岩松：存储1-2年产能饱和</t>
+        </is>
+      </c>
+      <c r="G154" s="147" t="inlineStr">
+        <is>
+          <t>2026-05-30 宋鸿兵：30年美债破5%双红线</t>
+        </is>
+      </c>
+    </row>
+    <row r="155" ht="15" customHeight="1" s="139">
+      <c r="A155" s="170" t="inlineStr">
+        <is>
+          <t>达利欧落地</t>
+        </is>
+      </c>
+      <c r="B155" s="157" t="inlineStr">
+        <is>
+          <t>七姐妹&gt;15%回调或破200日均线</t>
+        </is>
+      </c>
+      <c r="C155" s="157" t="inlineStr">
+        <is>
+          <t>芯片/恒科虚P转实P</t>
+        </is>
+      </c>
+      <c r="D155" s="157" t="inlineStr">
+        <is>
+          <t>现金解锁→大仓位进堆叠</t>
+        </is>
+      </c>
+    </row>
+    <row r="156" ht="15" customHeight="1" s="139">
+      <c r="A156" s="166" t="inlineStr">
+        <is>
+          <t>李大霄落地</t>
+        </is>
+      </c>
+      <c r="B156" s="157" t="inlineStr">
+        <is>
+          <t>多数成分股下跌+指数拐头</t>
+        </is>
+      </c>
+      <c r="C156" s="157" t="inlineStr">
+        <is>
+          <t>恒科/芯片虚P转实P</t>
+        </is>
+      </c>
+      <c r="D156" s="157" t="inlineStr">
+        <is>
+          <t>确认系统性风险→入场</t>
+        </is>
+      </c>
+    </row>
+    <row r="157" ht="15" customHeight="1" s="139">
+      <c r="A157" s="171" t="inlineStr">
+        <is>
+          <t>中期选举</t>
+        </is>
+      </c>
+      <c r="B157" s="171" t="inlineStr">
+        <is>
+          <t>11月美股跌一波</t>
+        </is>
+      </c>
+      <c r="C157" s="171" t="inlineStr">
+        <is>
+          <t>你的策略触发</t>
+        </is>
+      </c>
+      <c r="D157" s="171" t="inlineStr">
+        <is>
+          <t>现金→长电+通富</t>
+        </is>
+      </c>
+      <c r="E157" s="156" t="inlineStr">
+        <is>
+          <t>落地条件</t>
+        </is>
+      </c>
+      <c r="F157" s="156" t="inlineStr">
+        <is>
+          <t>状态</t>
+        </is>
+      </c>
+      <c r="G157" s="156" t="inlineStr">
+        <is>
+          <t>权重</t>
+        </is>
+      </c>
+      <c r="H157" s="156" t="inlineStr">
+        <is>
+          <t>备注</t>
+        </is>
+      </c>
+    </row>
+    <row r="158" ht="15" customHeight="1" s="139">
+      <c r="A158" s="157" t="inlineStr">
+        <is>
+          <t>堆叠独立</t>
+        </is>
+      </c>
+      <c r="B158" s="149" t="n"/>
+      <c r="C158" s="149" t="n"/>
+      <c r="D158" s="149" t="n"/>
+      <c r="E158" s="149" t="n"/>
+      <c r="F158" s="149" t="n"/>
+      <c r="G158" s="149" t="n"/>
+      <c r="H158" s="150" t="n"/>
+    </row>
+    <row r="159" ht="15" customHeight="1" s="139">
+      <c r="A159" s="157" t="inlineStr">
+        <is>
+          <t>李大霄
+金融界 6/4</t>
+        </is>
+      </c>
+      <c r="B159" s="157" t="inlineStr">
+        <is>
+          <t>美股窄牛宽熊
+仅20只创新高
+CAPE40倍→泡沫</t>
+        </is>
+      </c>
+      <c r="C159" s="158" t="inlineStr">
+        <is>
+          <t>🟢高度契合
+确认美股风险
+现金策略正确</t>
+        </is>
+      </c>
+      <c r="D159" s="157" t="inlineStr">
+        <is>
+          <t>美股全市场↓
+港股连带承压</t>
+        </is>
+      </c>
+      <c r="E159" s="157" t="inlineStr">
+        <is>
+          <t>纳指破200日均线
+或多数成分股下跌</t>
+        </is>
+      </c>
+      <c r="F159" s="159" t="inlineStr">
+        <is>
+          <t>⏳未落地
+(虚P状态)</t>
+        </is>
+      </c>
+      <c r="G159" s="157" t="inlineStr">
+        <is>
+          <t>⭐⭐⭐
+中高</t>
+        </is>
+      </c>
+      <c r="H159" s="157" t="inlineStr">
+        <is>
+          <t>6/4三源联动:
+恒科-2pp
+芯片-1pp
+→已记虚P
+未转实P</t>
+        </is>
+      </c>
+    </row>
+    <row r="160" ht="15" customHeight="1" s="139">
+      <c r="A160" s="172" t="inlineStr">
+        <is>
+          <t>⚡ 核心结论：三源联动确认AI泡沫风险+你的中期选举策略正确。大部分现金锁定等11月回调→大仓位进长电/通富。机会成本可接受（不对称博弈，下有保底）。虚P已记，等落地转实P。</t>
+        </is>
+      </c>
+      <c r="B160" s="168" t="n"/>
+      <c r="C160" s="168" t="n"/>
+      <c r="D160" s="168" t="n"/>
+      <c r="E160" s="168" t="n"/>
+      <c r="F160" s="168" t="n"/>
+      <c r="G160" s="168" t="n"/>
+      <c r="H160" s="169" t="n"/>
+    </row>
+    <row r="161">
+      <c r="A161" s="138" t="inlineStr">
+        <is>
+          <t>────────────────────────────────────────────────────────────</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="173" t="inlineStr">
+        <is>
+          <t>🔗 三源互锁验证</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="140" t="inlineStr">
+        <is>
+          <t>达利欧 × 李大霄</t>
+        </is>
+      </c>
+      <c r="C163" s="174" t="inlineStr">
+        <is>
+          <t>✅ 强印证</t>
+        </is>
+      </c>
+      <c r="E163" s="175" t="inlineStr">
+        <is>
+          <t>AI泡沫+窄牛宽熊=同一现象两角度，互相确认</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="140" t="inlineStr">
+        <is>
+          <t>达利欧 × 知乎</t>
+        </is>
+      </c>
+      <c r="C164" s="176" t="inlineStr">
+        <is>
+          <t>⚠️ 部分矛盾</t>
+        </is>
+      </c>
+      <c r="E164" s="175" t="inlineStr">
+        <is>
+          <t>达利欧看流动性(泡沫将破) vs 知乎看估值(PE中值安全)</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="140" t="inlineStr">
+        <is>
+          <t>三源共识</t>
+        </is>
+      </c>
+      <c r="C165" s="177" t="inlineStr">
+        <is>
+          <t>🔴 核心共识</t>
+        </is>
+      </c>
+      <c r="E165" s="175" t="inlineStr">
+        <is>
+          <t>AI龙头估值偏高+市场极度集中+中小盘已熊 → 短期风险&gt;机会</t>
+        </is>
+      </c>
+    </row>
+    <row r="166"/>
+    <row r="167">
+      <c r="A167" s="165" t="inlineStr">
+        <is>
+          <t>🎯 结论（虚P→实P转换条件）</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="140" t="inlineStr">
+        <is>
+          <t>① 达利欧信号落地条件</t>
+        </is>
+      </c>
+      <c r="C168" s="175" t="inlineStr">
+        <is>
+          <t>纳指七姐妹出现&gt;15%回调 或 纳指破200日均线</t>
+        </is>
+      </c>
+      <c r="E168" s="178" t="inlineStr">
+        <is>
+          <t>→ 芯片/恒科虚P转实P → 确认减仓信号</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="140" t="inlineStr">
+        <is>
+          <t>② 李大霄信号落地条件</t>
+        </is>
+      </c>
+      <c r="C169" s="175" t="inlineStr">
+        <is>
+          <t>纳指多数成分股连续下跌+指数拐头</t>
+        </is>
+      </c>
+      <c r="E169" s="178" t="inlineStr">
+        <is>
+          <t>→ 恒科/芯片虚P转实P → 确认美股系统性风险</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="140" t="inlineStr">
+        <is>
+          <t>③ 你的策略触发条件</t>
+        </is>
+      </c>
+      <c r="C170" s="175" t="inlineStr">
+        <is>
+          <t>中期选举(11月)美股跌一波 + AI回调&gt;15%</t>
+        </is>
+      </c>
+      <c r="E170" s="178" t="inlineStr">
+        <is>
+          <t>→ 现金入场 → 大仓位进堆叠/先进封装</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="140" t="inlineStr">
+        <is>
+          <t>④ 堆叠赛道独立性</t>
+        </is>
+      </c>
+      <c r="C171" s="175" t="inlineStr">
+        <is>
+          <t>国内产业确定性，三源均未提及国内封测</t>
+        </is>
+      </c>
+      <c r="E171" s="178" t="inlineStr">
+        <is>
+          <t>→ 不受美股泡沫直接影响 → 等回调后优先配置</t>
+        </is>
+      </c>
+    </row>
+    <row r="172"/>
+    <row r="173">
+      <c r="A173" s="179" t="inlineStr">
+        <is>
+          <t>⚡ 一句话：三源确认AI泡沫风险+你的中期选举策略正确。虚P已记，等落地转实P。现金为王，堆叠赛道等回调后大仓位进。</t>
+        </is>
+      </c>
+    </row>
+    <row r="174"/>
+    <row r="175"/>
+    <row r="176"/>
+    <row r="177">
+      <c r="A177" s="147" t="inlineStr">
+        <is>
+          <t>🤖 人形机器人半年事件链</t>
+        </is>
+      </c>
+    </row>
+    <row r="178"/>
+    <row r="179">
+      <c r="A179" s="147" t="inlineStr">
+        <is>
+          <t>2026-03-23 机器人ETF暴跌-4.1%至0.909：市场恐慌+AI回调</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="147" t="inlineStr">
+        <is>
+          <t>2026-04-08 机器人ETF暴涨+6.4%至0.967：人形机器人产业催化</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="147" t="inlineStr">
+        <is>
+          <t>2026-05-07~22 机器人连续上涨：ETF 1.056→1.216(+15%)，宇树科技73天过会</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="147" t="inlineStr">
+        <is>
+          <t>2026-05-25~06-02 机器人回调：1.216→1.122(-7.7%)，仍处强势区间</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="180" t="inlineStr">
+        <is>
+          <t>2026-06-04 【保持观察】霍尔木兹海峡Day 12：伊朗暂停谈判+美众议院限制动武，WTI $96→$91-93回落，方向趋于缓和</t>
+        </is>
+      </c>
+      <c r="B183" s="181" t="n"/>
+      <c r="C183" s="181" t="n"/>
+      <c r="D183" s="181" t="n"/>
+      <c r="E183" s="181" t="n"/>
+      <c r="F183" s="181" t="n"/>
+      <c r="G183" s="181" t="n"/>
+      <c r="H183" s="181" t="n"/>
+    </row>
+    <row r="184">
+      <c r="A184" s="182" t="inlineStr">
+        <is>
+          <t>🔔 待重仓监控</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" s="183" t="inlineStr">
+        <is>
+          <t>标的</t>
+        </is>
+      </c>
+      <c r="B185" s="183" t="inlineStr">
+        <is>
+          <t>状态</t>
+        </is>
+      </c>
+      <c r="C185" s="183" t="inlineStr">
+        <is>
+          <t>当前P/价格</t>
+        </is>
+      </c>
+      <c r="D185" s="183" t="inlineStr">
+        <is>
+          <t>最新信号</t>
+        </is>
+      </c>
+      <c r="E185" s="183" t="inlineStr">
+        <is>
+          <t>触发条件</t>
+        </is>
+      </c>
+      <c r="F185" s="183" t="inlineStr">
+        <is>
+          <t>距离触发</t>
+        </is>
+      </c>
+      <c r="G185" s="183" t="inlineStr">
+        <is>
+          <t>跟踪日期</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" s="147" t="inlineStr">
+        <is>
+          <t>玻璃基板</t>
+        </is>
+      </c>
+      <c r="B186" s="147" t="inlineStr">
+        <is>
+          <t>深南电路002916/兴森科技002436</t>
+        </is>
+      </c>
+      <c r="C186" s="147" t="inlineStr">
+        <is>
+          <t>观察中</t>
+        </is>
+      </c>
+      <c r="D186" s="147" t="inlineStr">
+        <is>
+          <t>蒋宇飞：玻璃基板大规模应用2028年，5-10年赛道</t>
+        </is>
+      </c>
+      <c r="E186" s="147" t="inlineStr">
+        <is>
+          <t>AI基建+国产替代加速</t>
+        </is>
+      </c>
+      <c r="F186" s="147" t="inlineStr">
+        <is>
+          <t>中长期</t>
+        </is>
+      </c>
+      <c r="G186" s="147" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" s="138" t="n"/>
+    </row>
+    <row r="188">
+      <c r="A188" s="147" t="inlineStr">
+        <is>
+          <t>油气对冲</t>
+        </is>
+      </c>
+      <c r="B188" s="147" t="inlineStr">
+        <is>
+          <t>华宝油气162411</t>
+        </is>
+      </c>
+      <c r="C188" s="147" t="inlineStr">
+        <is>
+          <t>观察中</t>
+        </is>
+      </c>
+      <c r="D188" s="147" t="inlineStr">
+        <is>
+          <t>宋鸿兵：霍尔木兹封锁3个月，85%投资者押注回落=幻觉</t>
+        </is>
+      </c>
+      <c r="E188" s="147" t="inlineStr">
+        <is>
+          <t>油价冲150或海峡持续封锁</t>
+        </is>
+      </c>
+      <c r="F188" s="147" t="inlineStr">
+        <is>
+          <t>短期</t>
+        </is>
+      </c>
+      <c r="G188" s="147" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="H188" s="138" t="inlineStr">
+        <is>
+          <t>小仓位试水，不对称博弈</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" s="147" t="inlineStr">
+        <is>
+          <t>银行板块(512800)</t>
+        </is>
+      </c>
+      <c r="B189" s="147" t="inlineStr">
+        <is>
+          <t>弱势</t>
+        </is>
+      </c>
+      <c r="C189" s="147" t="inlineStr">
+        <is>
+          <t>P:50% 虚P-2pp</t>
+        </is>
+      </c>
+      <c r="D189" s="147" t="inlineStr">
+        <is>
+          <t>去杠杆+信贷收缩，ETF跌-1%，无催化</t>
+        </is>
+      </c>
+      <c r="E189" s="147" t="inlineStr">
+        <is>
+          <t>不建议加仓</t>
+        </is>
+      </c>
+      <c r="F189" s="147" t="inlineStr">
+        <is>
+          <t>短期</t>
+        </is>
+      </c>
+      <c r="G189" s="147" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="H189" s="138" t="inlineStr">
+        <is>
+          <t>银行ETF持续阴跌</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" s="147" t="inlineStr">
+        <is>
+          <t>人形机器人(562500)</t>
+        </is>
+      </c>
+      <c r="B190" s="147" t="inlineStr">
+        <is>
+          <t>强势</t>
+        </is>
+      </c>
+      <c r="C190" s="147" t="inlineStr">
+        <is>
+          <t>P:58%(估)</t>
+        </is>
+      </c>
+      <c r="D190" s="147" t="inlineStr">
+        <is>
+          <t>宇树科技73天过会，ETF涨+11%</t>
+        </is>
+      </c>
+      <c r="E190" s="147" t="inlineStr">
+        <is>
+          <t>重点关注</t>
+        </is>
+      </c>
+      <c r="F190" s="147" t="inlineStr">
+        <is>
+          <t>中期</t>
+        </is>
+      </c>
+      <c r="G190" s="147" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="H190" s="138" t="inlineStr">
+        <is>
+          <t>平安先进制造+永赢先进制造</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" s="147" t="inlineStr">
+        <is>
+          <t>存储赛道(5只A股)</t>
+        </is>
+      </c>
+      <c r="B191" s="147" t="inlineStr">
+        <is>
+          <t>❌降级观察</t>
+        </is>
+      </c>
+      <c r="C191" s="147" t="inlineStr">
+        <is>
+          <t>P:55% 安全边际不足</t>
+        </is>
+      </c>
+      <c r="D191" s="147" t="inlineStr">
+        <is>
+          <t>兆易¥525(+81%)/江波龙¥569/佰维¥341→PE天际线，向上空间&lt;向下空间</t>
+        </is>
+      </c>
+      <c r="E191" s="147" t="inlineStr">
+        <is>
+          <t>等中期选举大跌15%+</t>
+        </is>
+      </c>
+      <c r="F191" s="147" t="inlineStr">
+        <is>
+          <t>中期</t>
+        </is>
+      </c>
+      <c r="G191" s="147" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="H191" s="138" t="inlineStr">
+        <is>
+          <t>降级：存储涨完轮到堆叠，安全边际已不足</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" s="147" t="inlineStr">
+        <is>
+          <t>澜起科技(688008)</t>
+        </is>
+      </c>
+      <c r="B192" s="147" t="inlineStr">
+        <is>
+          <t>❌降级观察</t>
+        </is>
+      </c>
+      <c r="C192" s="147" t="inlineStr">
+        <is>
+          <t>P:55% 安全边际中等</t>
+        </is>
+      </c>
+      <c r="D192" s="147" t="inlineStr">
+        <is>
+          <t>DDR5接口芯片，温和上涨，但存储赛道整体降级</t>
+        </is>
+      </c>
+      <c r="E192" s="147" t="inlineStr">
+        <is>
+          <t>等大跌15%+</t>
+        </is>
+      </c>
+      <c r="F192" s="147" t="inlineStr">
+        <is>
+          <t>中期</t>
+        </is>
+      </c>
+      <c r="G192" s="147" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="H192" s="138" t="inlineStr">
+        <is>
+          <t>降级：存储赛道尾声</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" s="184" t="inlineStr">
+        <is>
+          <t>🔥堆叠/先进封装赛道（蒋宇飞"星光纯叠"框架）</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" s="147" t="inlineStr">
+        <is>
+          <t>长电科技(600584)</t>
+        </is>
+      </c>
+      <c r="B194" s="147" t="inlineStr">
+        <is>
+          <t>🔴核心标的</t>
+        </is>
+      </c>
+      <c r="C194" s="147" t="inlineStr">
+        <is>
+          <t>P:75%+ PE30x</t>
+        </is>
+      </c>
+      <c r="D194" s="147" t="inlineStr">
+        <is>
+          <t>全球第三大封测厂，2.5D/3D量产级，客户广度最强（高通/海思/TI）</t>
+        </is>
+      </c>
+      <c r="E194" s="147" t="inlineStr">
+        <is>
+          <t>等中期选举大跌</t>
+        </is>
+      </c>
+      <c r="F194" s="147" t="inlineStr">
+        <is>
+          <t>中期</t>
+        </is>
+      </c>
+      <c r="G194" s="147" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="H194" s="138" t="inlineStr">
+        <is>
+          <t>安全边际大，堆叠赛道首选</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" s="147" t="inlineStr">
+        <is>
+          <t>通富微电(002156)</t>
+        </is>
+      </c>
+      <c r="B195" s="147" t="inlineStr">
+        <is>
+          <t>🔴核心标的</t>
+        </is>
+      </c>
+      <c r="C195" s="147" t="inlineStr">
+        <is>
+          <t>P:75%+ 待查PE</t>
+        </is>
+      </c>
+      <c r="D195" s="147" t="inlineStr">
+        <is>
+          <t>AMD封测全线突破通道，2.5D量产，MI300X参与，不可替代</t>
+        </is>
+      </c>
+      <c r="E195" s="147" t="inlineStr">
+        <is>
+          <t>等中期选举大跌</t>
+        </is>
+      </c>
+      <c r="F195" s="147" t="inlineStr">
+        <is>
+          <t>中期</t>
+        </is>
+      </c>
+      <c r="G195" s="147" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="H195" s="138" t="inlineStr">
+        <is>
+          <t>安全边际中偏大，与长电各占一半</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" s="138" t="n"/>
+    </row>
+    <row r="197">
+      <c r="A197" s="138" t="n"/>
+    </row>
+    <row r="198">
+      <c r="A198" s="153" t="inlineStr">
+        <is>
+          <t>📖 机制库 v3（2026-06-04 经小龙虾审核修订）</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" s="185" t="inlineStr">
+        <is>
+          <t>[机制3v3] 现金锁定系数（CLC）— 平方衰减版</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" s="186" t="inlineStr">
+        <is>
+          <t>叫什么</t>
+        </is>
+      </c>
+      <c r="B200" s="147" t="inlineStr">
+        <is>
+          <t>现金锁定系数（CLC）v3</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" s="186" t="inlineStr">
+        <is>
+          <t>公式</t>
+        </is>
+      </c>
+      <c r="B201" s="147" t="inlineStr">
+        <is>
+          <t>CLC = 信号概率 × 互锁强度 × 时间衰减²</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" s="186" t="inlineStr">
+        <is>
+          <t>时间衰减</t>
+        </is>
+      </c>
+      <c r="B202" s="147" t="inlineStr">
+        <is>
+          <t>T = (距触发月数/12)²</t>
+        </is>
+      </c>
+      <c r="C202" s="147" t="inlineStr">
+        <is>
+          <t>6月=(5/12)²=0.174</t>
+        </is>
+      </c>
+      <c r="D202" s="147" t="inlineStr">
+        <is>
+          <t>11月=0</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" s="186" t="inlineStr">
+        <is>
+          <t>为什么平方</t>
+        </is>
+      </c>
+      <c r="B203" s="147" t="inlineStr">
+        <is>
+          <t>线性衰减导致越近触发日锁得越少（反直觉）</t>
+        </is>
+      </c>
+      <c r="C203" s="147" t="inlineStr">
+        <is>
+          <t>平方函数：远离时多锁，临近时少锁</t>
+        </is>
+      </c>
+      <c r="D203" s="147" t="inlineStr">
+        <is>
+          <t>小龙虾审核通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" s="186" t="inlineStr">
+        <is>
+          <t>信号概率</t>
+        </is>
+      </c>
+      <c r="B204" s="147" t="inlineStr">
+        <is>
+          <t>动态更新，每月审查</t>
+        </is>
+      </c>
+      <c r="C204" s="147" t="inlineStr">
+        <is>
+          <t>底线55%（达利欧区间下沿）</t>
+        </is>
+      </c>
+      <c r="D204" s="147" t="inlineStr">
+        <is>
+          <t>上限85%（达利欧区间上沿）</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" s="186" t="inlineStr">
+        <is>
+          <t>互锁强度</t>
+        </is>
+      </c>
+      <c r="B205" s="147" t="inlineStr">
+        <is>
+          <t>三源强互锁=1.0</t>
+        </is>
+      </c>
+      <c r="C205" s="147" t="inlineStr">
+        <is>
+          <t>达利欧6月修正&gt;2次→降级0.85</t>
+        </is>
+      </c>
+      <c r="D205" s="147" t="inlineStr">
+        <is>
+          <t>有原因修正不降级</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" s="186" t="inlineStr">
+        <is>
+          <t>当前值</t>
+        </is>
+      </c>
+      <c r="B206" s="147" t="inlineStr">
+        <is>
+          <t>0.70 × 1.0 × (5/12)² = 0.122</t>
+        </is>
+      </c>
+      <c r="C206" s="147" t="inlineStr">
+        <is>
+          <t>→ 锁定12.2%现金</t>
+        </is>
+      </c>
+      <c r="D206" s="147" t="inlineStr">
+        <is>
+          <t>可用87.8%</t>
+        </is>
+      </c>
+    </row>
     <row r="207">
-      <c r="A207" s="157" t="inlineStr">
-        <is>
-          <t>通富微电</t>
+      <c r="A207" s="186" t="inlineStr">
+        <is>
+          <t>每月重算</t>
         </is>
       </c>
       <c r="B207" s="149" t="n"/>
@@ -4303,2120 +5137,948 @@
       <c r="G207" s="149" t="n"/>
       <c r="H207" s="150" t="n"/>
     </row>
-    <row r="208">
-      <c r="A208" s="157" t="inlineStr">
-        <is>
-          <t>养殖</t>
-        </is>
-      </c>
-      <c r="B208" s="157" t="inlineStr">
-        <is>
-          <t>70%</t>
-        </is>
-      </c>
-      <c r="C208" s="157" t="inlineStr">
-        <is>
-          <t>2.0:1</t>
-        </is>
-      </c>
-      <c r="D208" s="157" t="inlineStr">
-        <is>
-          <t>1.400</t>
-        </is>
-      </c>
-      <c r="E208" s="157" t="inlineStr">
-        <is>
-          <t>已持仓不需现金 | 6/5 芳姐：低价抄底母猪，行业融资枯竭，等待母猪血流成河才是最佳买点</t>
-        </is>
-      </c>
-      <c r="F208" s="157" t="inlineStr">
-        <is>
-          <t>继续持有</t>
-        </is>
-      </c>
-      <c r="G208" s="158" t="inlineStr">
-        <is>
-          <t>✅已配置</t>
-        </is>
-      </c>
-    </row>
+    <row r="208"/>
     <row r="209">
-      <c r="A209" s="157" t="inlineStr">
-        <is>
-          <t>电池</t>
-        </is>
-      </c>
-      <c r="B209" s="157" t="inlineStr">
-        <is>
-          <t>65%</t>
-        </is>
-      </c>
-      <c r="C209" s="157" t="inlineStr">
-        <is>
-          <t>2.0:1</t>
-        </is>
-      </c>
-      <c r="D209" s="157" t="inlineStr">
-        <is>
-          <t>1.300</t>
-        </is>
-      </c>
-      <c r="E209" s="157" t="inlineStr">
-        <is>
-          <t>已持仓不需现金 | 6/5 闻号说经济：厄尔尼诺80%概率+AI用电爆发→电力/能源受益</t>
-        </is>
-      </c>
-      <c r="F209" s="157" t="inlineStr">
-        <is>
-          <t>继续持有</t>
-        </is>
-      </c>
-      <c r="G209" s="158" t="inlineStr">
-        <is>
-          <t>✅已配置</t>
+      <c r="A209" s="185" t="inlineStr">
+        <is>
+          <t>[机制4v3] 折后仓位计算 — 4级分级版</t>
         </is>
       </c>
     </row>
     <row r="210">
-      <c r="A210" s="157" t="inlineStr">
-        <is>
-          <t>核电</t>
-        </is>
-      </c>
-      <c r="B210" s="157" t="inlineStr">
-        <is>
-          <t>52%</t>
-        </is>
-      </c>
-      <c r="C210" s="157" t="inlineStr">
-        <is>
-          <t>1.5:1</t>
-        </is>
-      </c>
-      <c r="D210" s="157" t="inlineStr">
-        <is>
-          <t>0.780</t>
-        </is>
-      </c>
-      <c r="E210" s="157" t="inlineStr">
-        <is>
-          <t>10年维度
-小仓试水可行</t>
-        </is>
-      </c>
-      <c r="F210" s="157" t="inlineStr">
-        <is>
-          <t>不影响现金策略</t>
-        </is>
-      </c>
-      <c r="G210" s="166" t="inlineStr">
-        <is>
-          <t>🟡长期观察</t>
+      <c r="A210" s="186" t="inlineStr">
+        <is>
+          <t>叫什么</t>
+        </is>
+      </c>
+      <c r="B210" s="147" t="inlineStr">
+        <is>
+          <t>折后仓位（Folded Allocation）v3</t>
         </is>
       </c>
     </row>
     <row r="211">
-      <c r="A211" s="157" t="inlineStr">
-        <is>
-          <t>存储</t>
-        </is>
-      </c>
-      <c r="B211" s="157" t="inlineStr">
-        <is>
-          <t>55%</t>
-        </is>
-      </c>
-      <c r="C211" s="157" t="inlineStr">
-        <is>
-          <t>1.0:1</t>
-        </is>
-      </c>
-      <c r="D211" s="157" t="inlineStr">
-        <is>
-          <t>0.550</t>
-        </is>
-      </c>
-      <c r="E211" s="157" t="inlineStr">
-        <is>
-          <t>已降级</t>
-        </is>
-      </c>
-      <c r="F211" s="157" t="inlineStr">
-        <is>
-          <t>不动</t>
-        </is>
-      </c>
-      <c r="G211" s="160" t="inlineStr">
-        <is>
-          <t>❌已降级</t>
+      <c r="A211" s="186" t="inlineStr">
+        <is>
+          <t>公式</t>
+        </is>
+      </c>
+      <c r="B211" s="147" t="inlineStr">
+        <is>
+          <t>折后仓位% = 原目标仓位% × (1 - CLC × β系数)</t>
         </is>
       </c>
     </row>
     <row r="212">
-      <c r="A212" s="157" t="inlineStr">
-        <is>
-          <t>纯现金5月</t>
-        </is>
-      </c>
-      <c r="B212" s="149" t="n"/>
-      <c r="C212" s="149" t="n"/>
-      <c r="D212" s="149" t="n"/>
-      <c r="E212" s="149" t="n"/>
-      <c r="F212" s="149" t="n"/>
-      <c r="G212" s="149" t="n"/>
-      <c r="H212" s="150" t="n"/>
+      <c r="A212" s="186" t="inlineStr">
+        <is>
+          <t>4级分级</t>
+        </is>
+      </c>
+      <c r="B212" s="147" t="inlineStr">
+        <is>
+          <t>L1高度暴露β=0.8（通富-AMD独供）</t>
+        </is>
+      </c>
+      <c r="C212" s="147" t="inlineStr">
+        <is>
+          <t>L2中度暴露β=0.5（长电-客户多元）</t>
+        </is>
+      </c>
     </row>
     <row r="213">
-      <c r="A213" s="147" t="inlineStr">
-        <is>
-          <t>AI硬件确定性(付鹏) → 内存=AI核心瓶颈(4信源互锁) → 国产替代加速 → 稀土断供日本 → 芯片/存储/HBM长期利好 | 短期被利率↑/地缘↑压制</t>
+      <c r="A213" s="186" t="inlineStr">
+        <is>
+          <t>分级继续</t>
+        </is>
+      </c>
+      <c r="B213" s="147" t="inlineStr">
+        <is>
+          <t>L3弱相关β=0.1（养殖）</t>
+        </is>
+      </c>
+      <c r="C213" s="147" t="inlineStr">
+        <is>
+          <t>L4反向受益β=-0.3（黄金）</t>
         </is>
       </c>
     </row>
     <row r="214">
-      <c r="A214" s="167" t="inlineStr">
-        <is>
-          <t>五、虚P→实P转换条件 &amp; 操作触发</t>
-        </is>
-      </c>
-      <c r="B214" s="149" t="n"/>
-      <c r="C214" s="149" t="n"/>
-      <c r="D214" s="149" t="n"/>
-      <c r="E214" s="149" t="n"/>
-      <c r="F214" s="149" t="n"/>
-      <c r="G214" s="149" t="n"/>
-      <c r="H214" s="150" t="n"/>
+      <c r="A214" s="186" t="inlineStr">
+        <is>
+          <t>为什么分级</t>
+        </is>
+      </c>
+      <c r="B214" s="147" t="inlineStr">
+        <is>
+          <t>不同标的受AI泡沫影响不同</t>
+        </is>
+      </c>
+      <c r="C214" s="147" t="inlineStr">
+        <is>
+          <t>通富只有AMD一根柱子</t>
+        </is>
+      </c>
+      <c r="D214" s="147" t="inlineStr">
+        <is>
+          <t>长电客户多元化</t>
+        </is>
+      </c>
     </row>
     <row r="215">
-      <c r="A215" s="156" t="inlineStr">
-        <is>
-          <t>条件</t>
-        </is>
-      </c>
-      <c r="B215" s="161" t="inlineStr">
-        <is>
-          <t>触发信号</t>
-        </is>
-      </c>
-      <c r="C215" s="156" t="inlineStr">
-        <is>
-          <t>影响</t>
-        </is>
-      </c>
-      <c r="D215" s="156" t="inlineStr">
-        <is>
-          <t>操作</t>
-        </is>
-      </c>
-      <c r="E215" s="147" t="inlineStr">
-        <is>
-          <t>2026-05-30 宋鸿兵：海峡封锁→能源成本飙升</t>
-        </is>
-      </c>
-      <c r="F215" s="147" t="inlineStr">
-        <is>
-          <t>2026-05-30 岩松：存储1-2年产能饱和</t>
-        </is>
-      </c>
-      <c r="G215" s="147" t="inlineStr">
-        <is>
-          <t>2026-05-30 宋鸿兵：30年美债破5%双红线</t>
+      <c r="A215" s="186" t="inlineStr">
+        <is>
+          <t>当前计算</t>
+        </is>
+      </c>
+      <c r="B215" s="147" t="inlineStr">
+        <is>
+          <t>通富:33%×(1-0.122×0.8)=30.1%</t>
+        </is>
+      </c>
+      <c r="C215" s="147" t="inlineStr">
+        <is>
+          <t>长电:37%×(1-0.122×0.5)=34.7%</t>
         </is>
       </c>
     </row>
     <row r="216">
-      <c r="A216" s="170" t="inlineStr">
-        <is>
-          <t>达利欧落地</t>
-        </is>
-      </c>
-      <c r="B216" s="157" t="inlineStr">
-        <is>
-          <t>七姐妹&gt;15%回调或破200日均线</t>
-        </is>
-      </c>
-      <c r="C216" s="157" t="inlineStr">
-        <is>
-          <t>芯片/恒科虚P转实P</t>
-        </is>
-      </c>
-      <c r="D216" s="157" t="inlineStr">
-        <is>
-          <t>现金解锁→大仓位进堆叠</t>
-        </is>
-      </c>
-    </row>
-    <row r="217">
-      <c r="A217" s="166" t="inlineStr">
-        <is>
-          <t>李大霄落地</t>
-        </is>
-      </c>
-      <c r="B217" s="157" t="inlineStr">
-        <is>
-          <t>多数成分股下跌+指数拐头</t>
-        </is>
-      </c>
-      <c r="C217" s="157" t="inlineStr">
-        <is>
-          <t>恒科/芯片虚P转实P</t>
-        </is>
-      </c>
-      <c r="D217" s="157" t="inlineStr">
-        <is>
-          <t>确认系统性风险→入场</t>
-        </is>
-      </c>
-    </row>
+      <c r="A216" s="186" t="inlineStr">
+        <is>
+          <t>分级逻辑</t>
+        </is>
+      </c>
+      <c r="B216" s="149" t="n"/>
+      <c r="C216" s="149" t="n"/>
+      <c r="D216" s="149" t="n"/>
+      <c r="E216" s="149" t="n"/>
+      <c r="F216" s="149" t="n"/>
+      <c r="G216" s="149" t="n"/>
+      <c r="H216" s="150" t="n"/>
+    </row>
+    <row r="217"/>
     <row r="218">
-      <c r="A218" s="171" t="inlineStr">
-        <is>
-          <t>中期选举</t>
-        </is>
-      </c>
-      <c r="B218" s="171" t="inlineStr">
-        <is>
-          <t>11月美股跌一波</t>
-        </is>
-      </c>
-      <c r="C218" s="171" t="inlineStr">
-        <is>
-          <t>你的策略触发</t>
-        </is>
-      </c>
-      <c r="D218" s="171" t="inlineStr">
-        <is>
-          <t>现金→长电+通富</t>
-        </is>
-      </c>
-      <c r="E218" s="156" t="inlineStr">
-        <is>
-          <t>落地条件</t>
-        </is>
-      </c>
-      <c r="F218" s="156" t="inlineStr">
-        <is>
-          <t>状态</t>
-        </is>
-      </c>
-      <c r="G218" s="156" t="inlineStr">
-        <is>
-          <t>权重</t>
-        </is>
-      </c>
-      <c r="H218" s="156" t="inlineStr">
-        <is>
-          <t>备注</t>
+      <c r="A218" s="185" t="inlineStr">
+        <is>
+          <t>[机制5v3] 虚P→实P转换 — 确认窗口+因果链版</t>
         </is>
       </c>
     </row>
     <row r="219">
-      <c r="A219" s="157" t="inlineStr">
-        <is>
-          <t>堆叠独立</t>
-        </is>
-      </c>
-      <c r="B219" s="149" t="n"/>
-      <c r="C219" s="149" t="n"/>
-      <c r="D219" s="149" t="n"/>
-      <c r="E219" s="149" t="n"/>
-      <c r="F219" s="149" t="n"/>
-      <c r="G219" s="149" t="n"/>
-      <c r="H219" s="150" t="n"/>
+      <c r="A219" s="186" t="inlineStr">
+        <is>
+          <t>叫什么</t>
+        </is>
+      </c>
+      <c r="B219" s="147" t="inlineStr">
+        <is>
+          <t>虚P→实P转换 v3</t>
+        </is>
+      </c>
     </row>
     <row r="220">
-      <c r="A220" s="157" t="inlineStr">
-        <is>
-          <t>李大霄
-金融界 6/4</t>
-        </is>
-      </c>
-      <c r="B220" s="157" t="inlineStr">
-        <is>
-          <t>美股窄牛宽熊
-仅20只创新高
-CAPE40倍→泡沫</t>
-        </is>
-      </c>
-      <c r="C220" s="158" t="inlineStr">
-        <is>
-          <t>🟢高度契合
-确认美股风险
-现金策略正确</t>
-        </is>
-      </c>
-      <c r="D220" s="157" t="inlineStr">
-        <is>
-          <t>美股全市场↓
-港股连带承压</t>
-        </is>
-      </c>
-      <c r="E220" s="157" t="inlineStr">
-        <is>
-          <t>纳指破200日均线
-或多数成分股下跌</t>
-        </is>
-      </c>
-      <c r="F220" s="159" t="inlineStr">
-        <is>
-          <t>⏳未落地
-(虚P状态)</t>
-        </is>
-      </c>
-      <c r="G220" s="157" t="inlineStr">
-        <is>
-          <t>⭐⭐⭐
-中高</t>
-        </is>
-      </c>
-      <c r="H220" s="157" t="inlineStr">
-        <is>
-          <t>6/4三源联动:
-恒科-2pp
-芯片-1pp
-→已记虚P
-未转实P</t>
+      <c r="A220" s="186" t="inlineStr">
+        <is>
+          <t>视觉信号</t>
+        </is>
+      </c>
+      <c r="B220" s="147" t="inlineStr">
+        <is>
+          <t>纳指七姐妹&gt;15%回调（从52周高）</t>
+        </is>
+      </c>
+      <c r="C220" s="147" t="inlineStr">
+        <is>
+          <t>或破200日均线</t>
         </is>
       </c>
     </row>
     <row r="221">
-      <c r="A221" s="172" t="inlineStr">
-        <is>
-          <t>⚡ 核心结论：三源联动确认AI泡沫风险+你的中期选举策略正确。大部分现金锁定等11月回调→大仓位进长电/通富。机会成本可接受（不对称博弈，下有保底）。虚P已记，等落地转实P。</t>
-        </is>
-      </c>
-      <c r="B221" s="168" t="n"/>
-      <c r="C221" s="168" t="n"/>
-      <c r="D221" s="168" t="n"/>
-      <c r="E221" s="168" t="n"/>
-      <c r="F221" s="168" t="n"/>
-      <c r="G221" s="168" t="n"/>
-      <c r="H221" s="169" t="n"/>
+      <c r="A221" s="186" t="inlineStr">
+        <is>
+          <t>确认窗口</t>
+        </is>
+      </c>
+      <c r="B221" s="147" t="inlineStr">
+        <is>
+          <t>跌穿15%后维持5个交易日不反弹</t>
+        </is>
+      </c>
+      <c r="C221" s="147" t="inlineStr">
+        <is>
+          <t>防单日噪音和假触发</t>
+        </is>
+      </c>
+      <c r="D221" s="147" t="inlineStr">
+        <is>
+          <t>小龙虾建议</t>
+        </is>
+      </c>
     </row>
     <row r="222">
-      <c r="A222" s="138" t="inlineStr">
-        <is>
-          <t>────────────────────────────────────────────────────────────</t>
+      <c r="A222" s="186" t="inlineStr">
+        <is>
+          <t>因果链</t>
+        </is>
+      </c>
+      <c r="B222" s="147" t="inlineStr">
+        <is>
+          <t>需至少2条佐证：</t>
+        </is>
+      </c>
+      <c r="C222" s="147" t="inlineStr">
+        <is>
+          <t>①英伟达/AMD下调指引</t>
+        </is>
+      </c>
+      <c r="D222" s="147" t="inlineStr">
+        <is>
+          <t>②AI ETF资金流出</t>
         </is>
       </c>
     </row>
     <row r="223">
-      <c r="A223" s="173" t="inlineStr">
-        <is>
-          <t>🔗 三源互锁验证</t>
+      <c r="A223" s="186" t="inlineStr">
+        <is>
+          <t>因果链继续</t>
+        </is>
+      </c>
+      <c r="B223" s="147" t="inlineStr">
+        <is>
+          <t>③投行下调AI评级</t>
+        </is>
+      </c>
+      <c r="C223" s="147" t="inlineStr">
+        <is>
+          <t>④Mag7裁员/削减开支</t>
         </is>
       </c>
     </row>
     <row r="224">
-      <c r="A224" s="140" t="inlineStr">
-        <is>
-          <t>达利欧 × 李大霄</t>
-        </is>
-      </c>
-      <c r="C224" s="174" t="inlineStr">
-        <is>
-          <t>✅ 强印证</t>
-        </is>
-      </c>
-      <c r="E224" s="175" t="inlineStr">
-        <is>
-          <t>AI泡沫+窄牛宽熊=同一现象两角度，互相确认</t>
+      <c r="A224" s="186" t="inlineStr">
+        <is>
+          <t>为什么加因果</t>
+        </is>
+      </c>
+      <c r="B224" s="147" t="inlineStr">
+        <is>
+          <t>15%下跌可能是地缘冲击不是AI泡沫</t>
+        </is>
+      </c>
+      <c r="C224" s="147" t="inlineStr">
+        <is>
+          <t>两者操作完全不同</t>
+        </is>
+      </c>
+      <c r="D224" s="147" t="inlineStr">
+        <is>
+          <t>必须区分原因</t>
         </is>
       </c>
     </row>
     <row r="225">
-      <c r="A225" s="140" t="inlineStr">
-        <is>
-          <t>达利欧 × 知乎</t>
-        </is>
-      </c>
-      <c r="C225" s="176" t="inlineStr">
-        <is>
-          <t>⚠️ 部分矛盾</t>
-        </is>
-      </c>
-      <c r="E225" s="175" t="inlineStr">
-        <is>
-          <t>达利欧看流动性(泡沫将破) vs 知乎看估值(PE中值安全)</t>
-        </is>
-      </c>
-    </row>
-    <row r="226">
-      <c r="A226" s="140" t="inlineStr">
-        <is>
-          <t>三源共识</t>
-        </is>
-      </c>
-      <c r="C226" s="177" t="inlineStr">
-        <is>
-          <t>🔴 核心共识</t>
-        </is>
-      </c>
-      <c r="E226" s="175" t="inlineStr">
-        <is>
-          <t>AI龙头估值偏高+市场极度集中+中小盘已熊 → 短期风险&gt;机会</t>
-        </is>
-      </c>
-    </row>
-    <row r="227"/>
+      <c r="A225" s="186" t="inlineStr">
+        <is>
+          <t>转换后</t>
+        </is>
+      </c>
+      <c r="B225" s="149" t="n"/>
+      <c r="C225" s="149" t="n"/>
+      <c r="D225" s="149" t="n"/>
+      <c r="E225" s="149" t="n"/>
+      <c r="F225" s="149" t="n"/>
+      <c r="G225" s="149" t="n"/>
+      <c r="H225" s="150" t="n"/>
+    </row>
+    <row r="226"/>
+    <row r="227">
+      <c r="A227" s="187" t="inlineStr">
+        <is>
+          <t>[信号计分板] 每日更新，驱动信号概率动态调整</t>
+        </is>
+      </c>
+    </row>
     <row r="228">
-      <c r="A228" s="165" t="inlineStr">
-        <is>
-          <t>🎯 结论（虚P→实P转换条件）</t>
+      <c r="A228" s="186" t="inlineStr">
+        <is>
+          <t>泡沫正向信号</t>
+        </is>
+      </c>
+      <c r="B228" s="147" t="inlineStr">
+        <is>
+          <t>Mag7单日跌&gt;3% → +1</t>
+        </is>
+      </c>
+      <c r="C228" s="147" t="inlineStr">
+        <is>
+          <t>Mag7月跌&gt;10% → +2</t>
         </is>
       </c>
     </row>
     <row r="229">
-      <c r="A229" s="140" t="inlineStr">
-        <is>
-          <t>① 达利欧信号落地条件</t>
-        </is>
-      </c>
-      <c r="C229" s="175" t="inlineStr">
-        <is>
-          <t>纳指七姐妹出现&gt;15%回调 或 纳指破200日均线</t>
-        </is>
-      </c>
-      <c r="E229" s="178" t="inlineStr">
-        <is>
-          <t>→ 芯片/恒科虚P转实P → 确认减仓信号</t>
+      <c r="B229" s="147" t="inlineStr">
+        <is>
+          <t>VIX&gt;30 → +2</t>
+        </is>
+      </c>
+      <c r="C229" s="147" t="inlineStr">
+        <is>
+          <t>AI公司裁员/下调指引 → +1</t>
         </is>
       </c>
     </row>
     <row r="230">
-      <c r="A230" s="140" t="inlineStr">
-        <is>
-          <t>② 李大霄信号落地条件</t>
+      <c r="B230" s="147" t="inlineStr">
+        <is>
+          <t>信用利差&gt;150bp → +2</t>
         </is>
       </c>
     </row>
     <row r="231">
-      <c r="A231" s="140" t="inlineStr">
-        <is>
-          <t>③ 你的策略触发条件</t>
+      <c r="A231" s="186" t="inlineStr">
+        <is>
+          <t>泡沫反向信号</t>
+        </is>
+      </c>
+      <c r="B231" s="147" t="inlineStr">
+        <is>
+          <t>Mag7单日涨&gt;3% → -1</t>
+        </is>
+      </c>
+      <c r="C231" s="147" t="inlineStr">
+        <is>
+          <t>Mag7月涨&gt;8% → -2</t>
         </is>
       </c>
     </row>
     <row r="232">
-      <c r="A232" s="140" t="inlineStr">
-        <is>
-          <t>④ 堆叠赛道独立性</t>
-        </is>
-      </c>
-      <c r="C232" s="175" t="inlineStr">
-        <is>
-          <t>国内产业确定性，三源均未提及国内封测</t>
-        </is>
-      </c>
-      <c r="E232" s="178" t="inlineStr">
-        <is>
-          <t>→ 不受美股泡沫直接影响 → 等回调后优先配置</t>
-        </is>
-      </c>
-    </row>
-    <row r="233"/>
+      <c r="B232" s="147" t="inlineStr">
+        <is>
+          <t>Fed降息 → -2</t>
+        </is>
+      </c>
+      <c r="C232" s="147" t="inlineStr">
+        <is>
+          <t>AI龙头超预期财报 → -1</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="B233" s="147" t="inlineStr">
+        <is>
+          <t>VIX&lt;15 → -1</t>
+        </is>
+      </c>
+    </row>
     <row r="234">
-      <c r="A234" s="179" t="inlineStr">
-        <is>
-          <t>⚡ 一句话：三源确认AI泡沫风险+你的中期选举策略正确。虚P已记，等落地转实P。现金为王，堆叠赛道等回调后大仓位进。</t>
-        </is>
-      </c>
-    </row>
-    <row r="235"/>
+      <c r="A234" s="186" t="inlineStr">
+        <is>
+          <t>更新规则</t>
+        </is>
+      </c>
+      <c r="B234" s="147" t="inlineStr">
+        <is>
+          <t>每月第一天：信号概率=70%+上月净计分×5pp</t>
+        </is>
+      </c>
+      <c r="C234" s="147" t="inlineStr">
+        <is>
+          <t>底线55%上限85%</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" s="186" t="inlineStr">
+        <is>
+          <t>Mag7权重</t>
+        </is>
+      </c>
+      <c r="B235" s="149" t="n"/>
+      <c r="C235" s="149" t="n"/>
+      <c r="D235" s="149" t="n"/>
+      <c r="E235" s="149" t="n"/>
+      <c r="F235" s="149" t="n"/>
+      <c r="G235" s="149" t="n"/>
+      <c r="H235" s="150" t="n"/>
+    </row>
     <row r="236"/>
-    <row r="237"/>
+    <row r="237">
+      <c r="A237" s="187" t="inlineStr">
+        <is>
+          <t>⚡ 机制v3使用指南</t>
+        </is>
+      </c>
+    </row>
     <row r="238">
-      <c r="A238" s="147" t="inlineStr">
-        <is>
-          <t>🤖 人形机器人半年事件链</t>
-        </is>
-      </c>
-    </row>
-    <row r="239"/>
+      <c r="A238" s="186" t="inlineStr">
+        <is>
+          <t>日常看盘</t>
+        </is>
+      </c>
+      <c r="B238" s="147" t="inlineStr">
+        <is>
+          <t>看机会成本排序Sheet折后仓位</t>
+        </is>
+      </c>
+      <c r="C238" s="147" t="inlineStr">
+        <is>
+          <t>看现金锁定状态</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" s="186" t="inlineStr">
+        <is>
+          <t>每日更新</t>
+        </is>
+      </c>
+      <c r="B239" s="147" t="inlineStr">
+        <is>
+          <t>信号计分板逐股计分</t>
+        </is>
+      </c>
+      <c r="C239" s="147" t="inlineStr">
+        <is>
+          <t>净计分累计</t>
+        </is>
+      </c>
+    </row>
     <row r="240">
-      <c r="A240" s="147" t="inlineStr">
-        <is>
-          <t>2026-03-23 机器人ETF暴跌-4.1%至0.909：市场恐慌+AI回调</t>
+      <c r="A240" s="186" t="inlineStr">
+        <is>
+          <t>每月重算</t>
+        </is>
+      </c>
+      <c r="B240" s="147" t="inlineStr">
+        <is>
+          <t>①信号概率=70%+净计分×5pp</t>
+        </is>
+      </c>
+      <c r="C240" s="147" t="inlineStr">
+        <is>
+          <t>②CLC=信号概率×互锁×时间衰减²</t>
+        </is>
+      </c>
+      <c r="D240" s="147" t="inlineStr">
+        <is>
+          <t>③折后仓位=原仓位×(1-CLC×β)</t>
         </is>
       </c>
     </row>
     <row r="241">
-      <c r="A241" s="147" t="inlineStr">
-        <is>
-          <t>2026-04-08 机器人ETF暴涨+6.4%至0.967：人形机器人产业催化</t>
-        </is>
-      </c>
-      <c r="B241" s="149" t="n"/>
-      <c r="C241" s="149" t="n"/>
-      <c r="D241" s="149" t="n"/>
-      <c r="E241" s="149" t="n"/>
-      <c r="F241" s="149" t="n"/>
-      <c r="G241" s="149" t="n"/>
-      <c r="H241" s="150" t="n"/>
+      <c r="A241" s="186" t="inlineStr">
+        <is>
+          <t>信号落地</t>
+        </is>
+      </c>
+      <c r="B241" s="147" t="inlineStr">
+        <is>
+          <t>视觉信号+5日确认+因果链2条</t>
+        </is>
+      </c>
+      <c r="C241" s="147" t="inlineStr">
+        <is>
+          <t>→虚P转实P</t>
+        </is>
+      </c>
+      <c r="D241" s="147" t="inlineStr">
+        <is>
+          <t>→CLC=0现金解锁</t>
+        </is>
+      </c>
     </row>
     <row r="242">
-      <c r="A242" s="147" t="inlineStr">
-        <is>
-          <t>2026-05-07~22 机器人连续上涨：ETF 1.056→1.216(+15%)，宇树科技73天过会</t>
-        </is>
-      </c>
-    </row>
-    <row r="243">
-      <c r="A243" s="147" t="inlineStr">
-        <is>
-          <t>2026-05-25~06-02 机器人回调：1.216→1.122(-7.7%)，仍处强势区间</t>
-        </is>
-      </c>
-    </row>
+      <c r="A242" s="186" t="inlineStr">
+        <is>
+          <t>核验计算</t>
+        </is>
+      </c>
+      <c r="B242" s="147" t="inlineStr">
+        <is>
+          <t>python3 /tmp/mechanism_checker_v3.py</t>
+        </is>
+      </c>
+      <c r="C242" s="147" t="inlineStr">
+        <is>
+          <t>自动重算所有机制</t>
+        </is>
+      </c>
+    </row>
+    <row r="243"/>
     <row r="244">
-      <c r="A244" s="180" t="inlineStr">
-        <is>
-          <t>2026-06-04 【保持观察】霍尔木兹海峡Day 12：伊朗暂停谈判+美众议院限制动武，WTI $96→$91-93回落，方向趋于缓和</t>
-        </is>
-      </c>
-      <c r="B244" s="181" t="n"/>
-      <c r="C244" s="181" t="n"/>
-      <c r="D244" s="181" t="n"/>
-      <c r="E244" s="181" t="n"/>
-      <c r="F244" s="181" t="n"/>
-      <c r="G244" s="181" t="n"/>
-      <c r="H244" s="181" t="n"/>
+      <c r="A244" s="188" t="inlineStr">
+        <is>
+          <t>📊 持仓状态速查表</t>
+        </is>
+      </c>
     </row>
     <row r="245">
-      <c r="A245" s="182" t="inlineStr">
-        <is>
-          <t>🔔 待重仓监控</t>
+      <c r="A245" s="189" t="inlineStr">
+        <is>
+          <t>持仓</t>
+        </is>
+      </c>
+      <c r="B245" s="189" t="inlineStr">
+        <is>
+          <t>代码</t>
+        </is>
+      </c>
+      <c r="C245" s="189" t="inlineStr">
+        <is>
+          <t>当前P</t>
+        </is>
+      </c>
+      <c r="D245" s="189" t="inlineStr">
+        <is>
+          <t>有效P</t>
+        </is>
+      </c>
+      <c r="E245" s="189" t="inlineStr">
+        <is>
+          <t>虚P</t>
+        </is>
+      </c>
+      <c r="F245" s="189" t="inlineStr">
+        <is>
+          <t>利率折价</t>
+        </is>
+      </c>
+      <c r="G245" s="189" t="inlineStr">
+        <is>
+          <t>方向</t>
+        </is>
+      </c>
+      <c r="H245" s="189" t="inlineStr">
+        <is>
+          <t>操作建议</t>
         </is>
       </c>
     </row>
     <row r="246">
-      <c r="A246" s="183" t="inlineStr">
-        <is>
-          <t>标的</t>
-        </is>
-      </c>
-      <c r="B246" s="183" t="inlineStr">
-        <is>
-          <t>状态</t>
-        </is>
-      </c>
-      <c r="C246" s="183" t="inlineStr">
-        <is>
-          <t>当前P/价格</t>
-        </is>
-      </c>
-      <c r="D246" s="183" t="inlineStr">
-        <is>
-          <t>最新信号</t>
-        </is>
-      </c>
-      <c r="E246" s="183" t="inlineStr">
-        <is>
-          <t>触发条件</t>
-        </is>
-      </c>
-      <c r="F246" s="183" t="inlineStr">
-        <is>
-          <t>距离触发</t>
-        </is>
-      </c>
-      <c r="G246" s="183" t="inlineStr">
-        <is>
-          <t>跟踪日期</t>
+      <c r="A246" s="138" t="inlineStr">
+        <is>
+          <t>芯片020628</t>
+        </is>
+      </c>
+      <c r="B246" s="138" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="C246" s="138" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="D246" s="138" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="E246" s="138" t="inlineStr">
+        <is>
+          <t>虚P+2pp | 6/5 存储→芯片资金传送门：存储涨81%降级后，资金搬进芯片ETF/长电通富</t>
+        </is>
+      </c>
+      <c r="F246" s="138" t="inlineStr">
+        <is>
+          <t>利率折价-6pp</t>
+        </is>
+      </c>
+      <c r="G246" s="138" t="inlineStr">
+        <is>
+          <t>🟡中性</t>
+        </is>
+      </c>
+      <c r="H246" s="138" t="inlineStr">
+        <is>
+          <t>观望</t>
         </is>
       </c>
     </row>
     <row r="247">
-      <c r="A247" s="147" t="inlineStr">
-        <is>
-          <t>玻璃基板</t>
-        </is>
-      </c>
-      <c r="B247" s="147" t="inlineStr">
-        <is>
-          <t>深南电路002916/兴森科技002436</t>
-        </is>
-      </c>
-      <c r="C247" s="147" t="inlineStr">
-        <is>
-          <t>观察中</t>
-        </is>
-      </c>
-      <c r="D247" s="147" t="inlineStr">
-        <is>
-          <t>蒋宇飞：玻璃基板大规模应用2028年，5-10年赛道</t>
-        </is>
-      </c>
-      <c r="E247" s="147" t="inlineStr">
-        <is>
-          <t>AI基建+国产替代加速</t>
-        </is>
-      </c>
-      <c r="F247" s="147" t="inlineStr">
-        <is>
-          <t>中长期</t>
-        </is>
-      </c>
-      <c r="G247" s="147" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
+      <c r="A247" s="138" t="inlineStr">
+        <is>
+          <t>电池018926</t>
+        </is>
+      </c>
+      <c r="B247" s="138" t="inlineStr">
+        <is>
+          <t>C2</t>
+        </is>
+      </c>
+      <c r="C247" s="138" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="D247" s="138" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="E247" s="138" t="inlineStr">
+        <is>
+          <t>虚P无</t>
+        </is>
+      </c>
+      <c r="F247" s="138" t="inlineStr">
+        <is>
+          <t>利率折价-6pp</t>
+        </is>
+      </c>
+      <c r="G247" s="138" t="inlineStr">
+        <is>
+          <t>🟢偏多</t>
+        </is>
+      </c>
+      <c r="H247" s="138" t="inlineStr">
+        <is>
+          <t>持有/关注加仓</t>
         </is>
       </c>
     </row>
     <row r="248">
-      <c r="A248" s="138" t="n"/>
+      <c r="A248" s="138" t="inlineStr">
+        <is>
+          <t>恒科012349</t>
+        </is>
+      </c>
+      <c r="B248" s="138" t="inlineStr">
+        <is>
+          <t>C3</t>
+        </is>
+      </c>
+      <c r="C248" s="138" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="D248" s="138" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="E248" s="138" t="inlineStr">
+        <is>
+          <t>虚P无 | 6/5 闻号说经济：301关税60国+AI芯片管制升级→压制恒科</t>
+        </is>
+      </c>
+      <c r="F248" s="138" t="inlineStr">
+        <is>
+          <t>利率折价-6pp</t>
+        </is>
+      </c>
+      <c r="G248" s="138" t="inlineStr">
+        <is>
+          <t>🔴偏空</t>
+        </is>
+      </c>
+      <c r="H248" s="138" t="inlineStr">
+        <is>
+          <t>减仓/清仓</t>
+        </is>
+      </c>
     </row>
     <row r="249">
-      <c r="A249" s="147" t="inlineStr">
-        <is>
-          <t>油气对冲</t>
-        </is>
-      </c>
-      <c r="B249" s="147" t="inlineStr">
-        <is>
-          <t>华宝油气162411</t>
-        </is>
-      </c>
-      <c r="C249" s="147" t="inlineStr">
-        <is>
-          <t>观察中</t>
-        </is>
-      </c>
-      <c r="D249" s="147" t="inlineStr">
-        <is>
-          <t>宋鸿兵：霍尔木兹封锁3个月，85%投资者押注回落=幻觉</t>
-        </is>
-      </c>
-      <c r="E249" s="147" t="inlineStr">
-        <is>
-          <t>油价冲150或海峡持续封锁</t>
-        </is>
-      </c>
-      <c r="F249" s="147" t="inlineStr">
-        <is>
-          <t>短期</t>
-        </is>
-      </c>
-      <c r="G249" s="147" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
+      <c r="A249" s="138" t="inlineStr">
+        <is>
+          <t>养殖014415</t>
+        </is>
+      </c>
+      <c r="B249" s="138" t="inlineStr">
+        <is>
+          <t>C4</t>
+        </is>
+      </c>
+      <c r="C249" s="138" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="D249" s="138" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="E249" s="138" t="inlineStr">
+        <is>
+          <t>虚P+4pp | 6/5 芳姐：低价抄底母猪，行业融资枯竭，等待母猪血流成河才是最佳买点</t>
+        </is>
+      </c>
+      <c r="F249" s="138" t="inlineStr">
+        <is>
+          <t>利率折价0pp</t>
+        </is>
+      </c>
+      <c r="G249" s="138" t="inlineStr">
+        <is>
+          <t>🟢偏多</t>
         </is>
       </c>
       <c r="H249" s="138" t="inlineStr">
         <is>
-          <t>小仓位试水，不对称博弈</t>
+          <t>持有/关注加仓</t>
         </is>
       </c>
     </row>
     <row r="250">
-      <c r="A250" s="147" t="inlineStr">
-        <is>
-          <t>银行板块(512800)</t>
-        </is>
-      </c>
-      <c r="B250" s="149" t="n"/>
-      <c r="C250" s="149" t="n"/>
-      <c r="D250" s="149" t="n"/>
-      <c r="E250" s="149" t="n"/>
-      <c r="F250" s="149" t="n"/>
-      <c r="G250" s="149" t="n"/>
-      <c r="H250" s="150" t="n"/>
+      <c r="A250" s="138" t="inlineStr">
+        <is>
+          <t>有色004433</t>
+        </is>
+      </c>
+      <c r="B250" s="138" t="inlineStr">
+        <is>
+          <t>C5</t>
+        </is>
+      </c>
+      <c r="C250" s="138" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="D250" s="138" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="E250" s="138" t="inlineStr">
+        <is>
+          <t>虚P无 | 6/5 闻号说经济：301关税60国→压制有色需求</t>
+        </is>
+      </c>
+      <c r="F250" s="138" t="inlineStr">
+        <is>
+          <t>利率折价-4pp</t>
+        </is>
+      </c>
+      <c r="G250" s="138" t="inlineStr">
+        <is>
+          <t>🔴偏空</t>
+        </is>
+      </c>
+      <c r="H250" s="138" t="inlineStr">
+        <is>
+          <t>减仓/清仓</t>
+        </is>
+      </c>
     </row>
     <row r="251">
-      <c r="A251" s="147" t="inlineStr">
-        <is>
-          <t>人形机器人(562500)</t>
-        </is>
-      </c>
-      <c r="B251" s="147" t="inlineStr">
-        <is>
-          <t>强势</t>
-        </is>
-      </c>
-      <c r="C251" s="147" t="inlineStr">
-        <is>
-          <t>P:58%(估)</t>
-        </is>
-      </c>
-      <c r="D251" s="147" t="inlineStr">
-        <is>
-          <t>宇树科技73天过会，ETF涨+11%</t>
-        </is>
-      </c>
-      <c r="E251" s="147" t="inlineStr">
-        <is>
-          <t>重点关注</t>
-        </is>
-      </c>
-      <c r="F251" s="147" t="inlineStr">
-        <is>
-          <t>中期</t>
-        </is>
-      </c>
-      <c r="G251" s="147" t="inlineStr">
-        <is>
-          <t>2026-06-03</t>
+      <c r="A251" s="138" t="inlineStr">
+        <is>
+          <t>稀金014111</t>
+        </is>
+      </c>
+      <c r="B251" s="138" t="inlineStr">
+        <is>
+          <t>C6</t>
+        </is>
+      </c>
+      <c r="C251" s="138" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="D251" s="138" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="E251" s="138" t="inlineStr">
+        <is>
+          <t>虚P无</t>
+        </is>
+      </c>
+      <c r="F251" s="138" t="inlineStr">
+        <is>
+          <t>利率折价-4pp</t>
+        </is>
+      </c>
+      <c r="G251" s="138" t="inlineStr">
+        <is>
+          <t>🟡中性</t>
         </is>
       </c>
       <c r="H251" s="138" t="inlineStr">
         <is>
-          <t>平安先进制造+永赢先进制造</t>
+          <t>观望</t>
         </is>
       </c>
     </row>
     <row r="252">
-      <c r="A252" s="147" t="inlineStr">
-        <is>
-          <t>存储赛道(5只A股)</t>
-        </is>
-      </c>
-      <c r="B252" s="149" t="n"/>
-      <c r="C252" s="149" t="n"/>
-      <c r="D252" s="149" t="n"/>
-      <c r="E252" s="149" t="n"/>
-      <c r="F252" s="149" t="n"/>
-      <c r="G252" s="149" t="n"/>
-      <c r="H252" s="150" t="n"/>
+      <c r="A252" s="138" t="inlineStr">
+        <is>
+          <t>银行001595</t>
+        </is>
+      </c>
+      <c r="B252" s="138" t="inlineStr">
+        <is>
+          <t>C7</t>
+        </is>
+      </c>
+      <c r="C252" s="138" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="D252" s="138" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="E252" s="138" t="inlineStr">
+        <is>
+          <t>虚P-2pp | 6/5 闻号说经济：银行信贷收紧→压制银行</t>
+        </is>
+      </c>
+      <c r="F252" s="138" t="inlineStr">
+        <is>
+          <t>利率折价0pp</t>
+        </is>
+      </c>
+      <c r="G252" s="138" t="inlineStr">
+        <is>
+          <t>🟡中性</t>
+        </is>
+      </c>
+      <c r="H252" s="138" t="inlineStr">
+        <is>
+          <t>观望</t>
+        </is>
+      </c>
     </row>
     <row r="253">
-      <c r="A253" s="147" t="inlineStr">
-        <is>
-          <t>澜起科技(688008)</t>
-        </is>
-      </c>
-      <c r="B253" s="149" t="n"/>
-      <c r="C253" s="149" t="n"/>
-      <c r="D253" s="149" t="n"/>
-      <c r="E253" s="149" t="n"/>
-      <c r="F253" s="149" t="n"/>
-      <c r="G253" s="149" t="n"/>
-      <c r="H253" s="150" t="n"/>
-    </row>
-    <row r="254">
-      <c r="A254" s="184" t="inlineStr">
-        <is>
-          <t>🔥堆叠/先进封装赛道（蒋宇飞"星光纯叠"框架）</t>
-        </is>
-      </c>
-    </row>
+      <c r="A253" s="138" t="inlineStr">
+        <is>
+          <t>AI027048</t>
+        </is>
+      </c>
+      <c r="B253" s="138" t="inlineStr">
+        <is>
+          <t>C8</t>
+        </is>
+      </c>
+      <c r="C253" s="138" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="D253" s="138" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F253" s="138" t="inlineStr">
+        <is>
+          <t>利率折价-4pp</t>
+        </is>
+      </c>
+      <c r="G253" s="138" t="inlineStr">
+        <is>
+          <t>🟡中性</t>
+        </is>
+      </c>
+      <c r="H253" s="138" t="inlineStr">
+        <is>
+          <t>观望</t>
+        </is>
+      </c>
+    </row>
+    <row r="254"/>
     <row r="255">
-      <c r="A255" s="147" t="inlineStr">
-        <is>
-          <t>长电科技(600584)</t>
-        </is>
-      </c>
-      <c r="B255" s="147" t="inlineStr">
-        <is>
-          <t>🔴核心标的</t>
-        </is>
-      </c>
-      <c r="C255" s="147" t="inlineStr">
-        <is>
-          <t>P:75%+ PE30x</t>
-        </is>
-      </c>
-      <c r="D255" s="147" t="inlineStr">
-        <is>
-          <t>全球第三大封测厂，2.5D/3D量产级，客户广度最强（高通/海思/TI）</t>
-        </is>
-      </c>
-      <c r="E255" s="147" t="inlineStr">
-        <is>
-          <t>等中期选举大跌</t>
-        </is>
-      </c>
-      <c r="F255" s="147" t="inlineStr">
-        <is>
-          <t>中期</t>
-        </is>
-      </c>
-      <c r="G255" s="147" t="inlineStr">
-        <is>
-          <t>2026-06-04</t>
-        </is>
-      </c>
-      <c r="H255" s="138" t="inlineStr">
-        <is>
-          <t>安全边际大，堆叠赛道首选</t>
+      <c r="A255" s="190" t="inlineStr">
+        <is>
+          <t>--- 6/6 监控小结 ---</t>
         </is>
       </c>
     </row>
     <row r="256">
-      <c r="A256" s="147" t="inlineStr">
-        <is>
-          <t>通富微电(002156)</t>
-        </is>
-      </c>
-      <c r="B256" s="147" t="inlineStr">
-        <is>
-          <t>🔴核心标的</t>
-        </is>
-      </c>
-      <c r="C256" s="147" t="inlineStr">
-        <is>
-          <t>P:75%+ 待查PE</t>
-        </is>
-      </c>
-      <c r="D256" s="147" t="inlineStr">
-        <is>
-          <t>AMD封测全线突破通道，2.5D量产，MI300X参与，不可替代</t>
-        </is>
-      </c>
-      <c r="E256" s="147" t="inlineStr">
-        <is>
-          <t>等中期选举大跌</t>
-        </is>
-      </c>
-      <c r="F256" s="147" t="inlineStr">
-        <is>
-          <t>中期</t>
-        </is>
-      </c>
-      <c r="G256" s="147" t="inlineStr">
-        <is>
-          <t>2026-06-04</t>
-        </is>
-      </c>
-      <c r="H256" s="138" t="inlineStr">
-        <is>
-          <t>安全边际中偏大，与长电各占一半</t>
+      <c r="A256" s="191" t="inlineStr">
+        <is>
+          <t>养殖: +1pp → 淘汰母猪加快+融资恶化→底部确认</t>
         </is>
       </c>
     </row>
     <row r="257">
-      <c r="A257" s="138" t="n"/>
+      <c r="A257" s="191" t="inlineStr">
+        <is>
+          <t>芯片: 0pp → AI长期利好vs估值过高抵消</t>
+        </is>
+      </c>
     </row>
     <row r="258">
-      <c r="A258" s="138" t="n"/>
+      <c r="A258" s="191" t="inlineStr">
+        <is>
+          <t>恒科: 0pp → AI叙事强化非事件</t>
+        </is>
+      </c>
     </row>
     <row r="259">
-      <c r="A259" s="316" t="inlineStr">
-        <is>
-          <t>🔥 蒋宇飞179视频深度分析 (2026-06-07 顶级置信度)</t>
+      <c r="A259" s="191" t="inlineStr">
+        <is>
+          <t>银行: 0pp → 非农黑五已部分定价</t>
         </is>
       </c>
     </row>
     <row r="260">
-      <c r="A260" s="138" t="inlineStr">
-        <is>
-          <t>核心框架: 星光纯叠=光模块(贯穿)→存储(吃肉)→堆叠(最大风口) | AI基建10年: 存力→算力→运力 | 2027算力长城=升腾+长鑫+DeepSeek</t>
+      <c r="A260" s="191" t="inlineStr">
+        <is>
+          <t>结论: 持仓不动。养殖左侧继续等待。</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" s="138" t="inlineStr">
         <is>
-          <t>【P值调整】芯片 41%→44%(虚P+3pp) | 稀金 40%→41%(虚P+1pp) | 其余0pp</t>
-        </is>
-      </c>
-    </row>
-    <row r="262"/>
+          <t>--- 6/7 监控小结 ---</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" s="138" t="inlineStr">
+        <is>
+          <t>养殖: +1pp → 集团"养一天赔一天"全体重抛售→去产能加速→周期底确认</t>
+        </is>
+      </c>
+    </row>
     <row r="263">
       <c r="A263" s="138" t="inlineStr">
         <is>
-          <t>MLCC被动元件</t>
+          <t>芯片: 0pp → AI基建长期利好(付鹏)vs摩尔定律瓶颈(宋鸿兵)抵消</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" s="138" t="inlineStr">
         <is>
-          <t>国产算力/升腾链</t>
-        </is>
-      </c>
-      <c r="B264" s="138" t="inlineStr">
-        <is>
-          <t>观察中</t>
-        </is>
-      </c>
-      <c r="C264" s="138" t="inlineStr">
-        <is>
-          <t>蒋宇飞: 2027算力长城最闪亮 | 升腾950明年出货 | 升腾+长鑫+DeepSeek</t>
-        </is>
-      </c>
-      <c r="D264" s="138" t="inlineStr">
-        <is>
-          <t>2026-06-07</t>
+          <t>AI: 0pp → AI基建+应用加速确认，但无新事件级催化剂</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" s="138" t="inlineStr">
         <is>
-          <t>HBM产业链</t>
-        </is>
-      </c>
-      <c r="B265" s="138" t="inlineStr">
-        <is>
-          <t>观察中</t>
-        </is>
-      </c>
-      <c r="C265" s="138" t="inlineStr">
-        <is>
-          <t>蒋宇飞: HBM未来1.5-2.5年波涛汹涌 | Q4-Q1热潮 | 技术含量最高</t>
-        </is>
-      </c>
-      <c r="D265" s="138" t="inlineStr">
-        <is>
-          <t>2026-06-07</t>
+          <t>恒科: -1pp → 非农超预期→加息预期→黑五科技暴跌→利率敏感</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" s="138" t="inlineStr">
         <is>
-          <t>CPU产业链</t>
-        </is>
-      </c>
-      <c r="B266" s="138" t="inlineStr">
-        <is>
-          <t>观察中</t>
-        </is>
-      </c>
-      <c r="C266" s="138" t="inlineStr">
-        <is>
-          <t>蒋宇飞: agent经济导致CPU爆发缺货 | 带动产业链</t>
-        </is>
-      </c>
-      <c r="D266" s="138" t="inlineStr">
-        <is>
-          <t>2026-06-07</t>
+          <t>黄金: 0pp → 长期央行购金(27%储备)vs短期非农砸盘抵消</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" s="138" t="inlineStr">
         <is>
-          <t>玻璃基板(更新)</t>
-        </is>
-      </c>
-      <c r="B267" s="138" t="inlineStr">
-        <is>
-          <t>观察中</t>
-        </is>
-      </c>
-      <c r="C267" s="138" t="inlineStr">
-        <is>
-          <t>蒋宇飞: 两三年热点→业绩2027-H2→大规模2028 | 封装+存储</t>
-        </is>
-      </c>
-      <c r="D267" s="138" t="inlineStr">
-        <is>
-          <t>2026-06-07</t>
-        </is>
-      </c>
-    </row>
-    <row r="268"/>
-    <row r="269">
-      <c r="A269" s="138" t="inlineStr">
-        <is>
-          <t>【堆叠75%验证】27条堆叠主题: "两年最大风口"+"一年半大放"+"存算一体"→P合理</t>
-        </is>
-      </c>
-    </row>
-    <row r="270">
-      <c r="A270" s="138" t="inlineStr">
-        <is>
-          <t>【存储降级确认】"存储跌80%但现在是时机"+"消费级见顶"+"存储涨完轮到堆叠"→降级合理</t>
-        </is>
-      </c>
-    </row>
-    <row r="271"/>
-    <row r="272"/>
-    <row r="273"/>
-    <row r="274"/>
-    <row r="275">
-      <c r="A275" s="153" t="inlineStr">
-        <is>
-          <t>📖 机制库 v3（2026-06-04 经小龙虾审核修订）</t>
-        </is>
-      </c>
-    </row>
-    <row r="276">
-      <c r="A276" s="185" t="inlineStr">
-        <is>
-          <t>[机制3v3] 现金锁定系数（CLC）— 平方衰减版</t>
-        </is>
-      </c>
-    </row>
-    <row r="277">
-      <c r="A277" s="186" t="inlineStr">
-        <is>
-          <t>叫什么</t>
-        </is>
-      </c>
-      <c r="B277" s="149" t="n"/>
-      <c r="C277" s="149" t="n"/>
-      <c r="D277" s="149" t="n"/>
-      <c r="E277" s="149" t="n"/>
-      <c r="F277" s="149" t="n"/>
-      <c r="G277" s="149" t="n"/>
-      <c r="H277" s="150" t="n"/>
-    </row>
-    <row r="278">
-      <c r="A278" s="186" t="inlineStr">
-        <is>
-          <t>公式</t>
-        </is>
-      </c>
-      <c r="B278" s="147" t="inlineStr">
-        <is>
-          <t>CLC = 信号概率 × 互锁强度 × 时间衰减²</t>
-        </is>
-      </c>
-    </row>
-    <row r="279">
-      <c r="A279" s="186" t="inlineStr">
-        <is>
-          <t>时间衰减</t>
-        </is>
-      </c>
-      <c r="B279" s="147" t="inlineStr">
-        <is>
-          <t>T = (距触发月数/12)²</t>
-        </is>
-      </c>
-      <c r="C279" s="147" t="inlineStr">
-        <is>
-          <t>6月=(5/12)²=0.174</t>
-        </is>
-      </c>
-      <c r="D279" s="147" t="inlineStr">
-        <is>
-          <t>11月=0</t>
-        </is>
-      </c>
-    </row>
-    <row r="280">
-      <c r="A280" s="186" t="inlineStr">
-        <is>
-          <t>为什么平方</t>
-        </is>
-      </c>
-      <c r="B280" s="147" t="inlineStr">
-        <is>
-          <t>线性衰减导致越近触发日锁得越少（反直觉）</t>
-        </is>
-      </c>
-      <c r="C280" s="147" t="inlineStr">
-        <is>
-          <t>平方函数：远离时多锁，临近时少锁</t>
-        </is>
-      </c>
-      <c r="D280" s="147" t="inlineStr">
-        <is>
-          <t>小龙虾审核通过</t>
-        </is>
-      </c>
-    </row>
-    <row r="281">
-      <c r="A281" s="186" t="inlineStr">
-        <is>
-          <t>信号概率</t>
-        </is>
-      </c>
-      <c r="B281" s="149" t="n"/>
-      <c r="C281" s="149" t="n"/>
-      <c r="D281" s="149" t="n"/>
-      <c r="E281" s="149" t="n"/>
-      <c r="F281" s="149" t="n"/>
-      <c r="G281" s="149" t="n"/>
-      <c r="H281" s="150" t="n"/>
-    </row>
-    <row r="282">
-      <c r="A282" s="186" t="inlineStr">
-        <is>
-          <t>互锁强度</t>
-        </is>
-      </c>
-      <c r="B282" s="147" t="inlineStr">
-        <is>
-          <t>三源强互锁=1.0</t>
-        </is>
-      </c>
-      <c r="C282" s="147" t="inlineStr">
-        <is>
-          <t>达利欧6月修正&gt;2次→降级0.85</t>
-        </is>
-      </c>
-      <c r="D282" s="147" t="inlineStr">
-        <is>
-          <t>有原因修正不降级</t>
-        </is>
-      </c>
-    </row>
-    <row r="283">
-      <c r="A283" s="186" t="inlineStr">
-        <is>
-          <t>当前值</t>
-        </is>
-      </c>
-      <c r="B283" s="147" t="inlineStr">
-        <is>
-          <t>0.70 × 1.0 × (5/12)² = 0.122</t>
-        </is>
-      </c>
-      <c r="C283" s="147" t="inlineStr">
-        <is>
-          <t>→ 锁定12.2%现金</t>
-        </is>
-      </c>
-      <c r="D283" s="147" t="inlineStr">
-        <is>
-          <t>可用87.8%</t>
-        </is>
-      </c>
-    </row>
-    <row r="284">
-      <c r="A284" s="186" t="inlineStr">
-        <is>
-          <t>每月重算</t>
-        </is>
-      </c>
-      <c r="B284" s="149" t="n"/>
-      <c r="C284" s="149" t="n"/>
-      <c r="D284" s="149" t="n"/>
-      <c r="E284" s="149" t="n"/>
-      <c r="F284" s="149" t="n"/>
-      <c r="G284" s="149" t="n"/>
-      <c r="H284" s="150" t="n"/>
-    </row>
-    <row r="285"/>
-    <row r="286">
-      <c r="A286" s="185" t="inlineStr">
-        <is>
-          <t>[机制4v3] 折后仓位计算 — 4级分级版</t>
-        </is>
-      </c>
-    </row>
-    <row r="287">
-      <c r="A287" s="186" t="inlineStr">
-        <is>
-          <t>叫什么</t>
-        </is>
-      </c>
-      <c r="B287" s="147" t="inlineStr">
-        <is>
-          <t>折后仓位（Folded Allocation）v3</t>
-        </is>
-      </c>
-    </row>
-    <row r="288">
-      <c r="A288" s="186" t="inlineStr">
-        <is>
-          <t>公式</t>
-        </is>
-      </c>
-      <c r="B288" s="147" t="inlineStr">
-        <is>
-          <t>折后仓位% = 原目标仓位% × (1 - CLC × β系数)</t>
-        </is>
-      </c>
-    </row>
-    <row r="289">
-      <c r="A289" s="186" t="inlineStr">
-        <is>
-          <t>4级分级</t>
-        </is>
-      </c>
-      <c r="B289" s="147" t="inlineStr">
-        <is>
-          <t>L1高度暴露β=0.8（通富-AMD独供）</t>
-        </is>
-      </c>
-      <c r="C289" s="147" t="inlineStr">
-        <is>
-          <t>L2中度暴露β=0.5（长电-客户多元）</t>
-        </is>
-      </c>
-    </row>
-    <row r="290">
-      <c r="A290" s="186" t="inlineStr">
-        <is>
-          <t>分级继续</t>
-        </is>
-      </c>
-      <c r="B290" s="147" t="inlineStr">
-        <is>
-          <t>L3弱相关β=0.1（养殖）</t>
-        </is>
-      </c>
-      <c r="C290" s="147" t="inlineStr">
-        <is>
-          <t>L4反向受益β=-0.3（黄金）</t>
-        </is>
-      </c>
-    </row>
-    <row r="291">
-      <c r="A291" s="186" t="inlineStr">
-        <is>
-          <t>为什么分级</t>
-        </is>
-      </c>
-      <c r="B291" s="149" t="n"/>
-      <c r="C291" s="149" t="n"/>
-      <c r="D291" s="149" t="n"/>
-      <c r="E291" s="149" t="n"/>
-      <c r="F291" s="149" t="n"/>
-      <c r="G291" s="149" t="n"/>
-      <c r="H291" s="150" t="n"/>
-    </row>
-    <row r="292">
-      <c r="A292" s="186" t="inlineStr">
-        <is>
-          <t>当前计算</t>
-        </is>
-      </c>
-      <c r="B292" s="147" t="inlineStr">
-        <is>
-          <t>通富:33%×(1-0.122×0.8)=30.1%</t>
-        </is>
-      </c>
-      <c r="C292" s="147" t="inlineStr">
-        <is>
-          <t>长电:37%×(1-0.122×0.5)=34.7%</t>
-        </is>
-      </c>
-    </row>
-    <row r="293">
-      <c r="A293" s="186" t="inlineStr">
-        <is>
-          <t>分级逻辑</t>
-        </is>
-      </c>
-      <c r="B293" s="149" t="n"/>
-      <c r="C293" s="149" t="n"/>
-      <c r="D293" s="149" t="n"/>
-      <c r="E293" s="149" t="n"/>
-      <c r="F293" s="149" t="n"/>
-      <c r="G293" s="149" t="n"/>
-      <c r="H293" s="150" t="n"/>
-    </row>
-    <row r="294"/>
-    <row r="295">
-      <c r="A295" s="185" t="inlineStr">
-        <is>
-          <t>[机制5v3] 虚P→实P转换 — 确认窗口+因果链版</t>
-        </is>
-      </c>
-    </row>
-    <row r="296">
-      <c r="A296" s="186" t="inlineStr">
-        <is>
-          <t>叫什么</t>
-        </is>
-      </c>
-      <c r="B296" s="149" t="n"/>
-      <c r="C296" s="149" t="n"/>
-      <c r="D296" s="149" t="n"/>
-      <c r="E296" s="149" t="n"/>
-      <c r="F296" s="149" t="n"/>
-      <c r="G296" s="149" t="n"/>
-      <c r="H296" s="150" t="n"/>
-    </row>
-    <row r="297">
-      <c r="A297" s="186" t="inlineStr">
-        <is>
-          <t>视觉信号</t>
-        </is>
-      </c>
-      <c r="B297" s="147" t="inlineStr">
-        <is>
-          <t>纳指七姐妹&gt;15%回调（从52周高）</t>
-        </is>
-      </c>
-      <c r="C297" s="147" t="inlineStr">
-        <is>
-          <t>或破200日均线</t>
-        </is>
-      </c>
-    </row>
-    <row r="298">
-      <c r="A298" s="186" t="inlineStr">
-        <is>
-          <t>确认窗口</t>
-        </is>
-      </c>
-      <c r="B298" s="147" t="inlineStr">
-        <is>
-          <t>跌穿15%后维持5个交易日不反弹</t>
-        </is>
-      </c>
-      <c r="C298" s="147" t="inlineStr">
-        <is>
-          <t>防单日噪音和假触发</t>
-        </is>
-      </c>
-      <c r="D298" s="147" t="inlineStr">
-        <is>
-          <t>小龙虾建议</t>
-        </is>
-      </c>
-    </row>
-    <row r="299">
-      <c r="A299" s="186" t="inlineStr">
-        <is>
-          <t>因果链</t>
-        </is>
-      </c>
-      <c r="B299" s="147" t="inlineStr">
-        <is>
-          <t>需至少2条佐证：</t>
-        </is>
-      </c>
-      <c r="C299" s="147" t="inlineStr">
-        <is>
-          <t>①英伟达/AMD下调指引</t>
-        </is>
-      </c>
-      <c r="D299" s="147" t="inlineStr">
-        <is>
-          <t>②AI ETF资金流出</t>
-        </is>
-      </c>
-    </row>
-    <row r="300">
-      <c r="A300" s="186" t="inlineStr">
-        <is>
-          <t>因果链继续</t>
-        </is>
-      </c>
-      <c r="B300" s="147" t="inlineStr">
-        <is>
-          <t>③投行下调AI评级</t>
-        </is>
-      </c>
-      <c r="C300" s="147" t="inlineStr">
-        <is>
-          <t>④Mag7裁员/削减开支</t>
-        </is>
-      </c>
-    </row>
-    <row r="301">
-      <c r="A301" s="186" t="inlineStr">
-        <is>
-          <t>为什么加因果</t>
-        </is>
-      </c>
-      <c r="B301" s="147" t="inlineStr">
-        <is>
-          <t>15%下跌可能是地缘冲击不是AI泡沫</t>
-        </is>
-      </c>
-      <c r="C301" s="147" t="inlineStr">
-        <is>
-          <t>两者操作完全不同</t>
-        </is>
-      </c>
-      <c r="D301" s="147" t="inlineStr">
-        <is>
-          <t>必须区分原因</t>
-        </is>
-      </c>
-    </row>
-    <row r="302">
-      <c r="A302" s="186" t="inlineStr">
-        <is>
-          <t>转换后</t>
-        </is>
-      </c>
-      <c r="B302" s="149" t="n"/>
-      <c r="C302" s="149" t="n"/>
-      <c r="D302" s="149" t="n"/>
-      <c r="E302" s="149" t="n"/>
-      <c r="F302" s="149" t="n"/>
-      <c r="G302" s="149" t="n"/>
-      <c r="H302" s="150" t="n"/>
-    </row>
-    <row r="303"/>
-    <row r="304">
-      <c r="A304" s="187" t="inlineStr">
-        <is>
-          <t>[信号计分板] 每日更新，驱动信号概率动态调整</t>
-        </is>
-      </c>
-    </row>
-    <row r="305">
-      <c r="A305" s="186" t="inlineStr">
-        <is>
-          <t>泡沫正向信号</t>
-        </is>
-      </c>
-      <c r="B305" s="147" t="inlineStr">
-        <is>
-          <t>Mag7单日跌&gt;3% → +1</t>
-        </is>
-      </c>
-      <c r="C305" s="147" t="inlineStr">
-        <is>
-          <t>Mag7月跌&gt;10% → +2</t>
-        </is>
-      </c>
-    </row>
-    <row r="306">
-      <c r="B306" s="147" t="inlineStr">
-        <is>
-          <t>VIX&gt;30 → +2</t>
-        </is>
-      </c>
-      <c r="C306" s="147" t="inlineStr">
-        <is>
-          <t>AI公司裁员/下调指引 → +1</t>
-        </is>
-      </c>
-    </row>
-    <row r="307">
-      <c r="B307" s="147" t="inlineStr">
-        <is>
-          <t>信用利差&gt;150bp → +2</t>
-        </is>
-      </c>
-    </row>
-    <row r="308">
-      <c r="A308" s="186" t="inlineStr">
-        <is>
-          <t>泡沫反向信号</t>
-        </is>
-      </c>
-      <c r="B308" s="147" t="inlineStr">
-        <is>
-          <t>Mag7单日涨&gt;3% → -1</t>
-        </is>
-      </c>
-      <c r="C308" s="147" t="inlineStr">
-        <is>
-          <t>Mag7月涨&gt;8% → -2</t>
-        </is>
-      </c>
-    </row>
-    <row r="309">
-      <c r="B309" s="147" t="inlineStr">
-        <is>
-          <t>Fed降息 → -2</t>
-        </is>
-      </c>
-      <c r="C309" s="147" t="inlineStr">
-        <is>
-          <t>AI龙头超预期财报 → -1</t>
-        </is>
-      </c>
-    </row>
-    <row r="310">
-      <c r="B310" s="147" t="inlineStr">
-        <is>
-          <t>VIX&lt;15 → -1</t>
-        </is>
-      </c>
-    </row>
-    <row r="311">
-      <c r="A311" s="186" t="inlineStr">
-        <is>
-          <t>更新规则</t>
-        </is>
-      </c>
-      <c r="B311" s="147" t="inlineStr">
-        <is>
-          <t>每月第一天：信号概率=70%+上月净计分×5pp</t>
-        </is>
-      </c>
-      <c r="C311" s="147" t="inlineStr">
-        <is>
-          <t>底线55%上限85%</t>
-        </is>
-      </c>
-    </row>
-    <row r="312">
-      <c r="A312" s="186" t="inlineStr">
-        <is>
-          <t>Mag7权重</t>
-        </is>
-      </c>
-      <c r="B312" s="149" t="n"/>
-      <c r="C312" s="149" t="n"/>
-      <c r="D312" s="149" t="n"/>
-      <c r="E312" s="149" t="n"/>
-      <c r="F312" s="149" t="n"/>
-      <c r="G312" s="149" t="n"/>
-      <c r="H312" s="150" t="n"/>
-    </row>
-    <row r="313"/>
-    <row r="314">
-      <c r="A314" s="187" t="inlineStr">
-        <is>
-          <t>⚡ 机制v3使用指南</t>
-        </is>
-      </c>
-    </row>
-    <row r="315">
-      <c r="A315" s="186" t="inlineStr">
-        <is>
-          <t>日常看盘</t>
-        </is>
-      </c>
-      <c r="B315" s="147" t="inlineStr">
-        <is>
-          <t>看机会成本排序Sheet折后仓位</t>
-        </is>
-      </c>
-      <c r="C315" s="147" t="inlineStr">
-        <is>
-          <t>看现金锁定状态</t>
-        </is>
-      </c>
-    </row>
-    <row r="316">
-      <c r="A316" s="186" t="inlineStr">
-        <is>
-          <t>每日更新</t>
-        </is>
-      </c>
-      <c r="B316" s="147" t="inlineStr">
-        <is>
-          <t>信号计分板逐股计分</t>
-        </is>
-      </c>
-      <c r="C316" s="147" t="inlineStr">
-        <is>
-          <t>净计分累计</t>
-        </is>
-      </c>
-    </row>
-    <row r="317">
-      <c r="A317" s="186" t="inlineStr">
-        <is>
-          <t>每月重算</t>
-        </is>
-      </c>
-      <c r="B317" s="147" t="inlineStr">
-        <is>
-          <t>①信号概率=70%+净计分×5pp</t>
-        </is>
-      </c>
-      <c r="C317" s="147" t="inlineStr">
-        <is>
-          <t>②CLC=信号概率×互锁×时间衰减²</t>
-        </is>
-      </c>
-      <c r="D317" s="147" t="inlineStr">
-        <is>
-          <t>③折后仓位=原仓位×(1-CLC×β)</t>
-        </is>
-      </c>
-    </row>
-    <row r="318">
-      <c r="A318" s="186" t="inlineStr">
-        <is>
-          <t>信号落地</t>
-        </is>
-      </c>
-      <c r="B318" s="147" t="inlineStr">
-        <is>
-          <t>视觉信号+5日确认+因果链2条</t>
-        </is>
-      </c>
-      <c r="C318" s="147" t="inlineStr">
-        <is>
-          <t>→虚P转实P</t>
-        </is>
-      </c>
-      <c r="D318" s="147" t="inlineStr">
-        <is>
-          <t>→CLC=0现金解锁</t>
-        </is>
-      </c>
-    </row>
-    <row r="319">
-      <c r="A319" s="186" t="inlineStr">
-        <is>
-          <t>核验计算</t>
-        </is>
-      </c>
-      <c r="B319" s="147" t="inlineStr">
-        <is>
-          <t>python3 /tmp/mechanism_checker_v3.py</t>
-        </is>
-      </c>
-      <c r="C319" s="147" t="inlineStr">
-        <is>
-          <t>自动重算所有机制</t>
-        </is>
-      </c>
-    </row>
-    <row r="320"/>
-    <row r="321">
-      <c r="A321" s="188" t="inlineStr">
-        <is>
-          <t>📊 持仓状态速查表</t>
-        </is>
-      </c>
-    </row>
-    <row r="322">
-      <c r="A322" s="189" t="inlineStr">
-        <is>
-          <t>持仓</t>
-        </is>
-      </c>
-      <c r="B322" s="189" t="inlineStr">
-        <is>
-          <t>代码</t>
-        </is>
-      </c>
-      <c r="C322" s="189" t="inlineStr">
-        <is>
-          <t>当前P</t>
-        </is>
-      </c>
-      <c r="D322" s="189" t="inlineStr">
-        <is>
-          <t>有效P</t>
-        </is>
-      </c>
-      <c r="E322" s="189" t="inlineStr">
-        <is>
-          <t>虚P</t>
-        </is>
-      </c>
-      <c r="F322" s="189" t="inlineStr">
-        <is>
-          <t>利率折价</t>
-        </is>
-      </c>
-      <c r="G322" s="189" t="inlineStr">
-        <is>
-          <t>方向</t>
-        </is>
-      </c>
-      <c r="H322" s="189" t="inlineStr">
-        <is>
-          <t>操作建议</t>
-        </is>
-      </c>
-    </row>
-    <row r="323">
-      <c r="A323" s="138" t="inlineStr">
-        <is>
-          <t>芯片020628</t>
-        </is>
-      </c>
-      <c r="B323" s="138" t="inlineStr">
-        <is>
-          <t>C1</t>
-        </is>
-      </c>
-      <c r="C323" s="138" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
-      <c r="D323" s="138" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="E323" s="138" t="inlineStr">
-        <is>
-          <t>虚P+2pp | 6/5 存储→芯片资金传送门：存储涨81%降级后，资金搬进芯片ETF/长电通富</t>
-        </is>
-      </c>
-      <c r="F323" s="138" t="inlineStr">
-        <is>
-          <t>利率折价-6pp</t>
-        </is>
-      </c>
-      <c r="G323" s="138" t="inlineStr">
-        <is>
-          <t>🟡中性</t>
-        </is>
-      </c>
-      <c r="H323" s="138" t="inlineStr">
-        <is>
-          <t>观望</t>
-        </is>
-      </c>
-    </row>
-    <row r="324">
-      <c r="A324" s="138" t="inlineStr">
-        <is>
-          <t>电池018926</t>
-        </is>
-      </c>
-      <c r="B324" s="138" t="inlineStr">
-        <is>
-          <t>C2</t>
-        </is>
-      </c>
-      <c r="C324" s="138" t="inlineStr">
-        <is>
-          <t>65</t>
-        </is>
-      </c>
-      <c r="D324" s="138" t="inlineStr">
-        <is>
-          <t>59</t>
-        </is>
-      </c>
-      <c r="E324" s="138" t="inlineStr">
-        <is>
-          <t>虚P无</t>
-        </is>
-      </c>
-      <c r="F324" s="138" t="inlineStr">
-        <is>
-          <t>利率折价-6pp</t>
-        </is>
-      </c>
-      <c r="G324" s="138" t="inlineStr">
-        <is>
-          <t>🟢偏多</t>
-        </is>
-      </c>
-      <c r="H324" s="138" t="inlineStr">
-        <is>
-          <t>持有/关注加仓</t>
-        </is>
-      </c>
-    </row>
-    <row r="325">
-      <c r="A325" s="138" t="inlineStr">
-        <is>
-          <t>恒科012349</t>
-        </is>
-      </c>
-      <c r="B325" s="138" t="inlineStr">
-        <is>
-          <t>C3</t>
-        </is>
-      </c>
-      <c r="C325" s="138" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="D325" s="138" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="E325" s="138" t="inlineStr">
-        <is>
-          <t>虚P无 | 6/5 闻号说经济：301关税60国+AI芯片管制升级→压制恒科</t>
-        </is>
-      </c>
-      <c r="F325" s="138" t="inlineStr">
-        <is>
-          <t>利率折价-6pp</t>
-        </is>
-      </c>
-      <c r="G325" s="138" t="inlineStr">
-        <is>
-          <t>🔴偏空</t>
-        </is>
-      </c>
-      <c r="H325" s="138" t="inlineStr">
-        <is>
-          <t>减仓/清仓</t>
-        </is>
-      </c>
-    </row>
-    <row r="326">
-      <c r="A326" s="138" t="inlineStr">
-        <is>
-          <t>养殖014415</t>
-        </is>
-      </c>
-      <c r="B326" s="138" t="inlineStr">
-        <is>
-          <t>C4</t>
-        </is>
-      </c>
-      <c r="C326" s="138" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="D326" s="138" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="E326" s="138" t="inlineStr">
-        <is>
-          <t>虚P+4pp | 6/5 芳姐：低价抄底母猪，行业融资枯竭，等待母猪血流成河才是最佳买点</t>
-        </is>
-      </c>
-      <c r="F326" s="138" t="inlineStr">
-        <is>
-          <t>利率折价0pp</t>
-        </is>
-      </c>
-      <c r="G326" s="138" t="inlineStr">
-        <is>
-          <t>🟢偏多</t>
-        </is>
-      </c>
-      <c r="H326" s="138" t="inlineStr">
-        <is>
-          <t>持有/关注加仓</t>
-        </is>
-      </c>
-    </row>
-    <row r="327">
-      <c r="A327" s="138" t="inlineStr">
-        <is>
-          <t>有色004433</t>
-        </is>
-      </c>
-      <c r="B327" s="138" t="inlineStr">
-        <is>
-          <t>C5</t>
-        </is>
-      </c>
-      <c r="C327" s="138" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
-      <c r="D327" s="138" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="E327" s="138" t="inlineStr">
-        <is>
-          <t>虚P无 | 6/5 闻号说经济：301关税60国→压制有色需求</t>
-        </is>
-      </c>
-      <c r="F327" s="138" t="inlineStr">
-        <is>
-          <t>利率折价-4pp</t>
-        </is>
-      </c>
-      <c r="G327" s="138" t="inlineStr">
-        <is>
-          <t>🔴偏空</t>
-        </is>
-      </c>
-      <c r="H327" s="138" t="inlineStr">
-        <is>
-          <t>减仓/清仓</t>
-        </is>
-      </c>
-    </row>
-    <row r="328">
-      <c r="A328" s="138" t="inlineStr">
-        <is>
-          <t>稀金014111</t>
-        </is>
-      </c>
-      <c r="B328" s="138" t="inlineStr">
-        <is>
-          <t>C6</t>
-        </is>
-      </c>
-      <c r="C328" s="138" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="D328" s="138" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="E328" s="138" t="inlineStr">
-        <is>
-          <t>虚P无</t>
-        </is>
-      </c>
-      <c r="F328" s="138" t="inlineStr">
-        <is>
-          <t>利率折价-4pp</t>
-        </is>
-      </c>
-      <c r="G328" s="138" t="inlineStr">
-        <is>
-          <t>🟡中性</t>
-        </is>
-      </c>
-      <c r="H328" s="138" t="inlineStr">
-        <is>
-          <t>观望</t>
-        </is>
-      </c>
-    </row>
-    <row r="329">
-      <c r="A329" s="138" t="inlineStr">
-        <is>
-          <t>银行001595</t>
-        </is>
-      </c>
-      <c r="B329" s="138" t="inlineStr">
-        <is>
-          <t>C7</t>
-        </is>
-      </c>
-      <c r="C329" s="138" t="inlineStr">
-        <is>
-          <t>47</t>
-        </is>
-      </c>
-      <c r="D329" s="138" t="inlineStr">
-        <is>
-          <t>47</t>
-        </is>
-      </c>
-      <c r="E329" s="138" t="inlineStr">
-        <is>
-          <t>虚P-2pp | 6/5 闻号说经济：银行信贷收紧→压制银行</t>
-        </is>
-      </c>
-      <c r="F329" s="138" t="inlineStr">
-        <is>
-          <t>利率折价0pp</t>
-        </is>
-      </c>
-      <c r="G329" s="138" t="inlineStr">
-        <is>
-          <t>🟡中性</t>
-        </is>
-      </c>
-      <c r="H329" s="138" t="inlineStr">
-        <is>
-          <t>观望</t>
-        </is>
-      </c>
-    </row>
-    <row r="330">
-      <c r="A330" s="138" t="inlineStr">
-        <is>
-          <t>AI027048</t>
-        </is>
-      </c>
-      <c r="B330" s="138" t="inlineStr">
-        <is>
-          <t>C8</t>
-        </is>
-      </c>
-      <c r="C330" s="138" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="D330" s="138" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F330" s="138" t="inlineStr">
-        <is>
-          <t>利率折价-4pp</t>
-        </is>
-      </c>
-      <c r="G330" s="138" t="inlineStr">
-        <is>
-          <t>🟡中性</t>
-        </is>
-      </c>
-      <c r="H330" s="138" t="inlineStr">
-        <is>
-          <t>观望</t>
-        </is>
-      </c>
-    </row>
-    <row r="331"/>
-    <row r="332">
-      <c r="A332" s="190" t="inlineStr">
-        <is>
-          <t>--- 6/6 监控小结 ---</t>
-        </is>
-      </c>
-    </row>
-    <row r="333">
-      <c r="A333" s="191" t="inlineStr">
-        <is>
-          <t>养殖: +1pp → 淘汰母猪加快+融资恶化→底部确认</t>
-        </is>
-      </c>
-    </row>
-    <row r="334">
-      <c r="A334" s="191" t="inlineStr">
-        <is>
-          <t>芯片: 0pp → AI长期利好vs估值过高抵消</t>
-        </is>
-      </c>
-    </row>
-    <row r="335">
-      <c r="A335" s="191" t="inlineStr">
-        <is>
-          <t>恒科: 0pp → AI叙事强化非事件</t>
-        </is>
-      </c>
-    </row>
-    <row r="336">
-      <c r="A336" s="191" t="inlineStr">
-        <is>
-          <t>银行: 0pp → 非农黑五已部分定价</t>
-        </is>
-      </c>
-    </row>
-    <row r="337">
-      <c r="A337" s="191" t="inlineStr">
-        <is>
-          <t>结论: 持仓不动。养殖左侧继续等待。</t>
-        </is>
-      </c>
-    </row>
-    <row r="338">
-      <c r="A338" s="138" t="inlineStr">
-        <is>
-          <t>--- 6/7 监控小结 ---</t>
-        </is>
-      </c>
-    </row>
-    <row r="339">
-      <c r="A339" s="138" t="inlineStr">
-        <is>
-          <t>养殖: +1pp → 集团"养一天赔一天"全体重抛售→去产能加速→周期底确认</t>
-        </is>
-      </c>
-    </row>
-    <row r="340">
-      <c r="A340" s="138" t="inlineStr">
-        <is>
-          <t>芯片: 0pp → AI基建长期利好(付鹏)vs摩尔定律瓶颈(宋鸿兵)抵消</t>
-        </is>
-      </c>
-    </row>
-    <row r="341">
-      <c r="A341" s="138" t="inlineStr">
-        <is>
-          <t>AI: 0pp → AI基建+应用加速确认，但无新事件级催化剂</t>
-        </is>
-      </c>
-    </row>
-    <row r="342">
-      <c r="A342" s="138" t="inlineStr">
-        <is>
-          <t>恒科: -1pp → 非农超预期→加息预期→黑五科技暴跌→利率敏感</t>
-        </is>
-      </c>
-    </row>
-    <row r="343">
-      <c r="A343" s="138" t="inlineStr">
-        <is>
-          <t>黄金: 0pp → 长期央行购金(27%储备)vs短期非农砸盘抵消</t>
-        </is>
-      </c>
-    </row>
-    <row r="344">
-      <c r="A344" s="138" t="inlineStr">
-        <is>
           <t>银行: 0pp → 岩松笔记讨论15%年化，中性方法论</t>
         </is>
       </c>
     </row>
-    <row r="345">
-      <c r="A345" s="138" t="inlineStr">
+    <row r="268">
+      <c r="A268" s="138" t="inlineStr">
         <is>
           <t>结论: 持仓不动。养殖左侧继续等待。恒科短期注意利率风险。</t>
         </is>
@@ -8415,7 +8077,7 @@
     <row r="3" ht="72.75" customHeight="1" s="139">
       <c r="A3" s="277" t="inlineStr">
         <is>
-          <t>P(α):54%
+          <t>P(α):51%
 β折价-3pp（↓从-11降：宏观对芯片价格影响≈0）
 有效P:48%
 R=P/(1-P)=0.9:1
@@ -13776,12 +13438,12 @@
       </c>
       <c r="E11" s="287" t="inlineStr">
         <is>
-          <t>44%</t>
+          <t>48%</t>
         </is>
       </c>
       <c r="F11" s="287" t="inlineStr">
         <is>
-          <t>P/(1-P)=0.78</t>
+          <t>0.92:1</t>
         </is>
       </c>
       <c r="G11" s="287" t="n">
@@ -13889,7 +13551,7 @@
       </c>
       <c r="F13" s="285" t="inlineStr">
         <is>
-          <t>P/(1-P)=0.70</t>
+          <t>0.69:1</t>
         </is>
       </c>
       <c r="G13" s="285" t="n">

--- a/持仓贝叶斯跟踪.xlsx
+++ b/持仓贝叶斯跟踪.xlsx
@@ -18,6 +18,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="持仓盈亏联动分析" sheetId="9" state="visible" r:id="rId9"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="信源校准分析" sheetId="10" state="visible" r:id="rId10"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="深度分析报告" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="系统机制" sheetId="12" state="visible" r:id="rId12"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1" refMode="A1" iterate="0" iterateCount="100" iterateDelta="0.0001"/>
@@ -27,7 +28,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="61">
+  <fonts count="67">
     <font>
       <name val="Calibri"/>
       <charset val="1"/>
@@ -414,8 +415,41 @@
       <color rgb="000000FF"/>
       <sz val="11"/>
     </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00FFD700"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="0000BFFF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="0000FF00"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00FFD700"/>
+      <sz val="13"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="00AAAAAA"/>
+      <sz val="9"/>
+    </font>
   </fonts>
-  <fills count="35">
+  <fills count="38">
     <fill>
       <patternFill/>
     </fill>
@@ -620,8 +654,26 @@
         <bgColor rgb="00FFFFCC"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001a1a2e"/>
+        <bgColor rgb="001a1a2e"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="0016213e"/>
+        <bgColor rgb="0016213e"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="000a0a23"/>
+        <bgColor rgb="000a0a23"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="8">
+  <borders count="13">
     <border>
       <left/>
       <right/>
@@ -671,6 +723,64 @@
       <bottom style="thin"/>
     </border>
     <border/>
+    <border>
+      <left style="thin">
+        <color rgb="00444444"/>
+      </left>
+      <right style="thin">
+        <color rgb="00444444"/>
+      </right>
+      <top style="thin">
+        <color rgb="00444444"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00444444"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00444444"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00444444"/>
+      </right>
+      <top style="thin">
+        <color rgb="00444444"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00444444"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00444444"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00444444"/>
+      </right>
+      <top style="thin">
+        <color rgb="00444444"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00444444"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1">
@@ -682,7 +792,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="329">
+  <cellXfs count="339">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -1620,6 +1730,32 @@
     <xf numFmtId="0" fontId="60" fillId="33" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="60" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="56" fillId="34" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="61" fillId="35" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="62" fillId="35" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="63" fillId="36" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="64" fillId="36" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="65" fillId="37" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="64" fillId="37" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="66" fillId="36" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="64" fillId="35" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1696,7 +1832,6 @@
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>Hermes</author>
-    <author>叙事主线</author>
     <author>AI指导原则</author>
   </authors>
   <commentList>
@@ -1981,28 +2116,7 @@
 </t>
       </text>
     </comment>
-    <comment ref="B116" authorId="1" shapeId="0">
-      <text>
-        <t xml:space="preserve">来源：用户2026-06-04独立判断
-逻辑链：
-1. 历史验证：每次危机→比特币暴跌（无避险价值）
-2. 黄金涨→比特币跌（流动性被黄金吸附）
-3. 美股涨→黄金跌→比特币也跌（被美股吸走）
-4. AI来了→资金有明确去处（芯片/AI基建）→比特币更没吸引力
-5. 最近一轮牛市验证：涨跌幅变小+跟美股完全同步=已非独立资产
-当前状态：维持。2020后第1次牛市(2021)，第2次牛市(2025最近)，周期规律+AI挤压=比特币上行空间越来越小
-对持仓影响：
-- 芯片/AI 利好：资金不去比特币就去AI，确认资金流向
-- 黄金 间接利好：比特币不再跟黄金抢流动性
-- 银行/有色/稀金 中性：不影响国内逻辑
-操作建议：
-- 不碰比特币/虚拟货币
-- 确认AI赛道的资金虹吸地位
-- 如果比特币暴跌→不是避险信号，是资金被更强的资产吸走了
-</t>
-      </text>
-    </comment>
-    <comment ref="A118" authorId="2" shapeId="0">
+    <comment ref="A118" authorId="1" shapeId="0">
       <text>
         <t xml:space="preserve">来源：用户2026-06-04确立，多个信源交叉确认
 核心逻辑：
@@ -2457,7 +2571,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:H268"/>
+  <dimension ref="A1:H310"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6171875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="18" customWidth="1" style="138" min="1" max="8"/>
@@ -2764,7 +2878,7 @@
       </c>
     </row>
     <row r="13" ht="15" customHeight="1" s="139">
-      <c r="A13" t="inlineStr">
+      <c r="A13" s="138" t="inlineStr">
         <is>
           <t>【Hermes+小龙多轮联合审核】第1轮：小龙审7个问题→第2轮：Hermes反审7个问题→小龙逐条回应修正</t>
         </is>
@@ -2786,14 +2900,14 @@
       </c>
     </row>
     <row r="17" ht="16.5" customHeight="1" s="139">
-      <c r="A17" t="inlineStr">
+      <c r="A17" s="138" t="inlineStr">
         <is>
           <t>现金50%=锁定40%(等11月大跌进长电25+通富20)+可动用10%</t>
         </is>
       </c>
     </row>
     <row r="18" ht="16.5" customHeight="1" s="139">
-      <c r="A18" t="inlineStr">
+      <c r="A18" s="138" t="inlineStr">
         <is>
           <t>【资金来源】现金50%+卖恒科2.5%(P=27%)+有色稀金5%(P低)+养殖减半12.5%+芯片可选5%=70-85%。方案消耗75%够覆盖</t>
         </is>
@@ -2808,21 +2922,21 @@
       </c>
     </row>
     <row r="21" ht="16.5" customHeight="1" s="139">
-      <c r="A21" t="inlineStr">
+      <c r="A21" s="138" t="inlineStr">
         <is>
           <t>星(芯)=CPU/GPU | 光=光模块 | 纯(存)=DRAM/Flash/HBM/SSD | 叠=CoWoS/2.5D/3D先进封装</t>
         </is>
       </c>
     </row>
     <row r="22" ht="16.5" customHeight="1" s="139">
-      <c r="A22" t="inlineStr">
+      <c r="A22" s="138" t="inlineStr">
         <is>
           <t>节奏：光贯穿2026→存储2026吃肉(已验证海力士13倍)→堆叠2027大放。2027算力长城=升腾+长鑫+DeepSeek</t>
         </is>
       </c>
     </row>
     <row r="23" ht="16.5" customHeight="1" s="139">
-      <c r="A23" t="inlineStr">
+      <c r="A23" s="138" t="inlineStr">
         <is>
           <t>风控提示：存储将来跌80% | 消费级2027见顶 | HBM分销修正70-80% | 纪律：三成追热点七成等回调</t>
         </is>
@@ -2845,42 +2959,42 @@
       </c>
     </row>
     <row r="28" ht="15" customHeight="1" s="139">
-      <c r="A28" t="inlineStr">
+      <c r="A28" s="138" t="inlineStr">
         <is>
           <t>【为什么买】蒋宇飞4月底预测MLCC启动，5月即涨。说"不亚于半年前荐存储"（存储半年涨13倍）。国巨成台湾首富。日韩停产中低端→中国MLCC爆发。行情到2027-H1</t>
         </is>
       </c>
     </row>
     <row r="29" ht="15" customHeight="1" s="139">
-      <c r="A29" t="inlineStr">
+      <c r="A29" s="138" t="inlineStr">
         <is>
           <t>【买什么】风华高科(000636)≈300股≈8250元。MLCC营收占比58%，最接近纯暴露。不买科技ETF凑合（小龙裁定）</t>
         </is>
       </c>
     </row>
     <row r="30" ht="15" customHeight="1" s="139">
-      <c r="A30" t="inlineStr">
+      <c r="A30" s="138" t="inlineStr">
         <is>
           <t>【恒科为什么清】P=27%三条信号同向。蒋宇飞"传统互联网老灯鼓"是行业判断，"腾讯黄金坑"是个股判断。恒科≠腾讯（腾讯只占30%）。看好腾讯应买个股。清出2.5%转MLCC</t>
         </is>
       </c>
     </row>
     <row r="31" ht="15" customHeight="1" s="139">
-      <c r="A31" t="inlineStr">
+      <c r="A31" s="138" t="inlineStr">
         <is>
           <t>【什么时候进】现在（6-7月）</t>
         </is>
       </c>
     </row>
     <row r="32" ht="15" customHeight="1" s="139">
-      <c r="A32" t="inlineStr">
+      <c r="A32" s="138" t="inlineStr">
         <is>
           <t>【什么时候出】11-12月必须清仓（蒋宇飞说年底见顶）。资金转HBM或堆叠先手</t>
         </is>
       </c>
     </row>
     <row r="33" ht="16.5" customHeight="1" s="139">
-      <c r="A33" t="inlineStr">
+      <c r="A33" s="138" t="inlineStr">
         <is>
           <t>【风控】5.5%仓位，错了亏2000-3000不致命。年底不管赚亏都清</t>
         </is>
@@ -2895,28 +3009,28 @@
       </c>
     </row>
     <row r="36" ht="16.5" customHeight="1" s="139">
-      <c r="A36" t="inlineStr">
+      <c r="A36" s="138" t="inlineStr">
         <is>
           <t>【为什么买】蒋宇飞"HBM未来1.5-2.5年波涛汹涌""Q4-Q1波澜壮阔热潮"。HBM是AI技术含量最高的存储，目前最紧缺</t>
         </is>
       </c>
     </row>
     <row r="37" ht="16.5" customHeight="1" s="139">
-      <c r="A37" t="inlineStr">
+      <c r="A37" s="138" t="inlineStr">
         <is>
           <t>【什么时候进】2026-Q4（10-12月），MLCC清仓后资金转入</t>
         </is>
       </c>
     </row>
     <row r="38" ht="16.5" customHeight="1" s="139">
-      <c r="A38" t="inlineStr">
+      <c r="A38" s="138" t="inlineStr">
         <is>
           <t>【什么时候出】2027-Q1热潮结束观察。蒋宇飞说热潮在四季度至明年一季度展开</t>
         </is>
       </c>
     </row>
     <row r="39" ht="16.5" customHeight="1" s="139">
-      <c r="A39" t="inlineStr">
+      <c r="A39" s="138" t="inlineStr">
         <is>
           <t>【风控】5%不大。Q4不启动就继续等，不急着进</t>
         </is>
@@ -2931,56 +3045,56 @@
       </c>
     </row>
     <row r="42" ht="16.5" customHeight="1" s="139">
-      <c r="A42" t="inlineStr">
+      <c r="A42" s="138" t="inlineStr">
         <is>
           <t>【为什么买】蒋宇飞27条堆叠视频反复强调"未来两年最大风口""一年半大放光芒""改变家族命运""躺赢"。堆叠=CoWoS/2.5D/3D=突破存算一体。封装成本占存储芯片20%。P=75%</t>
         </is>
       </c>
     </row>
     <row r="43" ht="16.5" customHeight="1" s="139">
-      <c r="A43" t="inlineStr">
+      <c r="A43" s="138" t="inlineStr">
         <is>
           <t>【P=75%四源交叉确认】达利欧(宏观泡沫年底崩→回调买入)+李大霄(A股窄牛宽熊→等低位)+用户(中期选举大跌=买入时机)+蒋宇飞(产业27条)。四套独立框架交集→小龙说P可能估低</t>
         </is>
       </c>
     </row>
     <row r="44" ht="16.5" customHeight="1" s="139">
-      <c r="A44" t="inlineStr">
+      <c r="A44" s="138" t="inlineStr">
         <is>
           <t>【为什么长电+通富】长电=全球第三大封测，2.5D/3D量产，客户高通/海思/TI。通富=AMD封测全线突破，MI300X参与，不可替代</t>
         </is>
       </c>
     </row>
     <row r="45" ht="16.5" customHeight="1" s="139">
-      <c r="A45" t="inlineStr">
+      <c r="A45" s="138" t="inlineStr">
         <is>
           <t>【分三批进-小龙裁定】第一批15%(跌15%触发)→第二批15%(再跌10%或横盘2月)→第三批15%(产业验证)。涨20%后分两批加速到30%。小龙逻辑：30%翻倍&gt;45%被洗，仓位轻=拿得住=吃全涨幅</t>
         </is>
       </c>
     </row>
     <row r="46" ht="16.5" customHeight="1" s="139">
-      <c r="A46" t="inlineStr">
+      <c r="A46" s="138" t="inlineStr">
         <is>
           <t>【什么时候进】等11月美股大跌15%+。触发三选一：①达利欧泡沫落地 ②纳指破200日均线 ③中期选举大跌</t>
         </is>
       </c>
     </row>
     <row r="47" ht="16.5" customHeight="1" s="139">
-      <c r="A47" t="inlineStr">
+      <c r="A47" s="138" t="inlineStr">
         <is>
           <t>【Plan B-小龙裁定】锁到2027-01-31（三个月窗口：11月选举+12月圣诞行情+1月调仓）。逾期进40%留20%。替代触发三选一：芯片PE&lt;40分位/蒋宇飞说进/月线连阴3月</t>
         </is>
       </c>
     </row>
     <row r="48" ht="16.5" customHeight="1" s="139">
-      <c r="A48" t="inlineStr">
+      <c r="A48" s="138" t="inlineStr">
         <is>
           <t>【先手仓位】Q4先建5%（长电3%+通富2%），等回调后进大仓位。符合蒋宇飞"三成追七成等"纪律</t>
         </is>
       </c>
     </row>
     <row r="49" ht="16.5" customHeight="1" s="139">
-      <c r="A49" t="inlineStr">
+      <c r="A49" s="138" t="inlineStr">
         <is>
           <t>【风控】45%×70%回撤=31.5%总资金蒸发（蒋宇飞自己说HBM分销修正70-80%）。分三批=赌价格区间胜率翻倍</t>
         </is>
@@ -2995,21 +3109,21 @@
       </c>
     </row>
     <row r="52" ht="77.59999999999999" customHeight="1" s="139">
-      <c r="A52" t="inlineStr">
+      <c r="A52" s="138" t="inlineStr">
         <is>
           <t>【为什么买】蒋宇飞"2027算力长城最闪亮""升腾链2027爆发""升腾950明年出货"。工信部要求支持国产芯片</t>
         </is>
       </c>
     </row>
     <row r="53" ht="17.15" customHeight="1" s="139">
-      <c r="A53" t="inlineStr">
+      <c r="A53" s="138" t="inlineStr">
         <is>
           <t>【什么时候进】2027年。触发：华为升腾950大批出货/工信部政策加码</t>
         </is>
       </c>
     </row>
     <row r="54" ht="26.85" customHeight="1" s="139">
-      <c r="A54" t="inlineStr">
+      <c r="A54" s="138" t="inlineStr">
         <is>
           <t>【风控】等2027，当前只看不动</t>
         </is>
@@ -3024,28 +3138,28 @@
       </c>
     </row>
     <row r="57" ht="15" customHeight="1" s="139">
-      <c r="A57" t="inlineStr">
+      <c r="A57" s="138" t="inlineStr">
         <is>
           <t>【为什么买】用户判断机器人&gt;黄金&gt;比特币。蒋宇飞交叉验证：179视频0次提比特币。"未来经济三层=物理人→钢铁机器人→网络agent"。宇树科技73天过会</t>
         </is>
       </c>
     </row>
     <row r="58" ht="15" customHeight="1" s="139">
-      <c r="A58" t="inlineStr">
+      <c r="A58" s="138" t="inlineStr">
         <is>
           <t>【标的困境-小龙分析】562500不是纯机器人暴露(成分公司机器人营收&lt;20%，半年波动66%)。纯机器人公司(宇树/Figure)没上市。替代：科创AI(027048)6%覆盖AI+机器人+算力</t>
         </is>
       </c>
     </row>
     <row r="59" ht="58.2" customHeight="1" s="139">
-      <c r="A59" t="inlineStr">
+      <c r="A59" s="138" t="inlineStr">
         <is>
           <t>【什么时候进】2027冬开始逐步建。机器人是中长期赛道，不急</t>
         </is>
       </c>
     </row>
     <row r="60" ht="173.1" customHeight="1" s="139">
-      <c r="A60" t="inlineStr">
+      <c r="A60" s="138" t="inlineStr">
         <is>
           <t>【风控】4%不大。科创AI6%分散风险。合计10%科技前沿暴露，比单一562500更安全</t>
         </is>
@@ -3060,27 +3174,26 @@
       </c>
     </row>
     <row r="63" ht="48.5" customHeight="1" s="139">
-      <c r="A63" t="inlineStr">
+      <c r="A63" s="138" t="inlineStr">
         <is>
           <t>【为什么买】蒋宇飞"被严重低估即将爆发""两三年热点""业绩2027-H2释放""大规模2028"。两个爆发点：封装+存储</t>
         </is>
       </c>
     </row>
     <row r="64" ht="48.5" customHeight="1" s="139">
-      <c r="A64" t="inlineStr">
+      <c r="A64" s="138" t="inlineStr">
         <is>
           <t>【什么时候进】2027年等业绩释放。蒋宇飞说"消息还在送验阶段"</t>
         </is>
       </c>
     </row>
     <row r="65" ht="64.15000000000001" customHeight="1" s="139">
-      <c r="A65" t="inlineStr">
+      <c r="A65" s="138" t="inlineStr">
         <is>
           <t>【风控】2%观察仓，等消息确认</t>
         </is>
       </c>
     </row>
-    <row r="66"/>
     <row r="67" ht="17.15" customHeight="1" s="139">
       <c r="A67" s="324" t="inlineStr">
         <is>
@@ -3117,222 +3230,221 @@
       </c>
     </row>
     <row r="70" ht="48.5" customHeight="1" s="139">
-      <c r="A70" t="inlineStr">
+      <c r="A70" s="138" t="inlineStr">
         <is>
           <t>现在-7月</t>
         </is>
       </c>
-      <c r="B70" t="inlineStr">
+      <c r="B70" s="138" t="inlineStr">
         <is>
           <t>MLCC5.5%建仓(风华高科)</t>
         </is>
       </c>
-      <c r="C70" t="inlineStr">
+      <c r="C70" s="138" t="inlineStr">
         <is>
           <t>芯片10%不动(虚P+3pp)</t>
         </is>
       </c>
-      <c r="D70" t="inlineStr">
+      <c r="D70" s="138" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="E70" t="inlineStr">
+      <c r="E70" s="138" t="inlineStr">
         <is>
           <t>~7%</t>
         </is>
       </c>
     </row>
     <row r="71" ht="32.8" customHeight="1" s="139">
-      <c r="A71" t="inlineStr">
+      <c r="A71" s="138" t="inlineStr">
         <is>
           <t>8-10月</t>
         </is>
       </c>
-      <c r="B71" t="inlineStr">
+      <c r="B71" s="138" t="inlineStr">
         <is>
           <t>MLCC持有享肉</t>
         </is>
       </c>
-      <c r="C71" t="inlineStr">
+      <c r="C71" s="138" t="inlineStr">
         <is>
           <t>观察HBM启动信号</t>
         </is>
       </c>
-      <c r="D71" t="inlineStr">
+      <c r="D71" s="138" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="E71" t="inlineStr">
+      <c r="E71" s="138" t="inlineStr">
         <is>
           <t>~7%</t>
         </is>
       </c>
     </row>
     <row r="72">
-      <c r="A72" t="inlineStr">
+      <c r="A72" s="138" t="inlineStr">
         <is>
           <t>11月大跌</t>
         </is>
       </c>
-      <c r="B72" t="inlineStr">
+      <c r="B72" s="138" t="inlineStr">
         <is>
           <t>堆叠三批45%(长电25+通富20)</t>
         </is>
       </c>
-      <c r="C72" t="inlineStr">
+      <c r="C72" s="138" t="inlineStr">
         <is>
           <t>MLCC清→HBM5%+堆叠先手5%</t>
         </is>
       </c>
-      <c r="D72" t="inlineStr">
+      <c r="D72" s="138" t="inlineStr">
         <is>
           <t>MLCC清</t>
         </is>
       </c>
-      <c r="E72" t="inlineStr">
+      <c r="E72" s="138" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
     </row>
     <row r="73" ht="121.6" customHeight="1" s="139">
-      <c r="A73" t="inlineStr">
+      <c r="A73" s="138" t="inlineStr">
         <is>
           <t>11月没大跌</t>
         </is>
       </c>
-      <c r="B73" t="inlineStr">
+      <c r="B73" s="138" t="inlineStr">
         <is>
           <t>堆叠先手5%(长电3+通富2)</t>
         </is>
       </c>
-      <c r="C73" t="inlineStr">
+      <c r="C73" s="138" t="inlineStr">
         <is>
           <t>MLCC清→等</t>
         </is>
       </c>
-      <c r="D73" t="inlineStr">
+      <c r="D73" s="138" t="inlineStr">
         <is>
           <t>MLCC清</t>
         </is>
       </c>
-      <c r="E73" t="inlineStr">
+      <c r="E73" s="138" t="inlineStr">
         <is>
           <t>0-2%</t>
         </is>
       </c>
     </row>
     <row r="74">
-      <c r="A74" t="inlineStr">
+      <c r="A74" s="138" t="inlineStr">
         <is>
           <t>1/31仍没大跌</t>
         </is>
       </c>
-      <c r="B74" t="inlineStr">
+      <c r="B74" s="138" t="inlineStr">
         <is>
           <t>PlanB：进40%留20%</t>
         </is>
       </c>
-      <c r="C74" t="inlineStr">
+      <c r="C74" s="138" t="inlineStr">
         <is>
           <t>等</t>
         </is>
       </c>
-      <c r="D74" t="inlineStr">
+      <c r="D74" s="138" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="E74" t="inlineStr">
+      <c r="E74" s="138" t="inlineStr">
         <is>
           <t>~20%</t>
         </is>
       </c>
     </row>
     <row r="75">
-      <c r="A75" t="inlineStr">
+      <c r="A75" s="138" t="inlineStr">
         <is>
           <t>2027-Q1</t>
         </is>
       </c>
-      <c r="B75" t="inlineStr">
+      <c r="B75" s="138" t="inlineStr">
         <is>
           <t>HBM持有</t>
         </is>
       </c>
-      <c r="C75" t="inlineStr">
+      <c r="C75" s="138" t="inlineStr">
         <is>
           <t>堆叠先手持有</t>
         </is>
       </c>
-      <c r="D75" t="inlineStr">
+      <c r="D75" s="138" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="E75" t="inlineStr">
+      <c r="E75" s="138" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
     <row r="76">
-      <c r="A76" t="inlineStr">
+      <c r="A76" s="138" t="inlineStr">
         <is>
           <t>2027-H2</t>
         </is>
       </c>
-      <c r="B76" t="inlineStr">
+      <c r="B76" s="138" t="inlineStr">
         <is>
           <t>升腾8%+玻璃2%</t>
         </is>
       </c>
-      <c r="C76" t="inlineStr">
+      <c r="C76" s="138" t="inlineStr">
         <is>
           <t>堆叠满仓躺赢</t>
         </is>
       </c>
-      <c r="D76" t="inlineStr">
+      <c r="D76" s="138" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="E76" t="inlineStr">
+      <c r="E76" s="138" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
     <row r="77" ht="15" customHeight="1" s="139">
-      <c r="A77" t="inlineStr">
+      <c r="A77" s="138" t="inlineStr">
         <is>
           <t>2027冬</t>
         </is>
       </c>
-      <c r="B77" t="inlineStr">
+      <c r="B77" s="138" t="inlineStr">
         <is>
           <t>机器人4%+科创AI6%</t>
         </is>
       </c>
-      <c r="C77" t="inlineStr">
+      <c r="C77" s="138" t="inlineStr">
         <is>
           <t>算力出海观察</t>
         </is>
       </c>
-      <c r="D77" t="inlineStr">
+      <c r="D77" s="138" t="inlineStr">
         <is>
           <t>存储清(跌80%)</t>
         </is>
       </c>
-      <c r="E77" t="inlineStr">
+      <c r="E77" s="138" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
-    <row r="78"/>
     <row r="79" ht="39.55" customHeight="1" s="139">
       <c r="A79" s="324" t="inlineStr">
         <is>
@@ -3341,14 +3453,14 @@
       </c>
     </row>
     <row r="80" ht="39.55" customHeight="1" s="139">
-      <c r="A80" t="inlineStr">
+      <c r="A80" s="138" t="inlineStr">
         <is>
           <t>风控底线：45%必须等15%+回调分三批 | MLCC年底必清 | 蒋宇飞纪律'三成追七成等' | PlanB锁到2027-01-31</t>
         </is>
       </c>
     </row>
     <row r="81" ht="52.2" customHeight="1" s="139">
-      <c r="A81" t="inlineStr">
+      <c r="A81" s="138" t="inlineStr">
         <is>
           <t>持仓调整：养殖25%→12.5% | 恒科清 | 有色+稀金清 | 芯片可选减半 | 电池+银行不动 | 保留现金~10%</t>
         </is>
@@ -3359,7 +3471,6 @@
     <row r="84" ht="15" customHeight="1" s="139"/>
     <row r="85" ht="15" customHeight="1" s="139"/>
     <row r="86" ht="26.85" customHeight="1" s="139"/>
-    <row r="87"/>
     <row r="88" ht="39.55" customHeight="1" s="139"/>
     <row r="89" ht="26.85" customHeight="1" s="139"/>
     <row r="90" ht="26.85" customHeight="1" s="139"/>
@@ -3380,7 +3491,6 @@
     <row r="105" ht="26.85" customHeight="1" s="139"/>
     <row r="106" ht="26.85" customHeight="1" s="139"/>
     <row r="107" ht="15" customHeight="1" s="139"/>
-    <row r="108"/>
     <row r="109" ht="15" customHeight="1" s="139"/>
     <row r="110" ht="26.85" customHeight="1" s="139"/>
     <row r="111" ht="26.85" customHeight="1" s="139"/>
@@ -3443,11 +3553,6 @@
           <t>④</t>
         </is>
       </c>
-      <c r="B116" s="138" t="inlineStr">
-        <is>
-          <t>比特币独立叙事消亡 维持：资金吸附力排序 AI&gt;美股&gt;黄金&gt;比特币，比特币已成美股影子资产，AI落地后资金有明确去处，比特币价值持续被稀释</t>
-        </is>
-      </c>
     </row>
     <row r="117">
       <c r="A117" s="151" t="inlineStr">
@@ -3650,7 +3755,6 @@
       <c r="G125" s="149" t="n"/>
       <c r="H125" s="150" t="n"/>
     </row>
-    <row r="126"/>
     <row r="127" ht="15" customHeight="1" s="139">
       <c r="A127" s="155" t="inlineStr">
         <is>
@@ -3761,16 +3865,6 @@
           <t>维度</t>
         </is>
       </c>
-      <c r="B135" s="161" t="inlineStr">
-        <is>
-          <t>内容</t>
-        </is>
-      </c>
-      <c r="C135" s="161" t="inlineStr">
-        <is>
-          <t>影响</t>
-        </is>
-      </c>
     </row>
     <row r="136">
       <c r="A136" s="157" t="inlineStr">
@@ -4447,7 +4541,6 @@
         </is>
       </c>
     </row>
-    <row r="166"/>
     <row r="167">
       <c r="A167" s="165" t="inlineStr">
         <is>
@@ -4523,7 +4616,6 @@
         </is>
       </c>
     </row>
-    <row r="172"/>
     <row r="173">
       <c r="A173" s="179" t="inlineStr">
         <is>
@@ -4531,9 +4623,6 @@
         </is>
       </c>
     </row>
-    <row r="174"/>
-    <row r="175"/>
-    <row r="176"/>
     <row r="177">
       <c r="A177" s="147" t="inlineStr">
         <is>
@@ -4541,7 +4630,6 @@
         </is>
       </c>
     </row>
-    <row r="178"/>
     <row r="179">
       <c r="A179" s="147" t="inlineStr">
         <is>
@@ -5137,7 +5225,6 @@
       <c r="G207" s="149" t="n"/>
       <c r="H207" s="150" t="n"/>
     </row>
-    <row r="208"/>
     <row r="209">
       <c r="A209" s="185" t="inlineStr">
         <is>
@@ -5256,7 +5343,6 @@
       <c r="G216" s="149" t="n"/>
       <c r="H216" s="150" t="n"/>
     </row>
-    <row r="217"/>
     <row r="218">
       <c r="A218" s="185" t="inlineStr">
         <is>
@@ -5390,7 +5476,6 @@
       <c r="G225" s="149" t="n"/>
       <c r="H225" s="150" t="n"/>
     </row>
-    <row r="226"/>
     <row r="227">
       <c r="A227" s="187" t="inlineStr">
         <is>
@@ -5501,7 +5586,6 @@
       <c r="G235" s="149" t="n"/>
       <c r="H235" s="150" t="n"/>
     </row>
-    <row r="236"/>
     <row r="237">
       <c r="A237" s="187" t="inlineStr">
         <is>
@@ -5604,7 +5688,6 @@
         </is>
       </c>
     </row>
-    <row r="243"/>
     <row r="244">
       <c r="A244" s="188" t="inlineStr">
         <is>
@@ -5985,7 +6068,6 @@
         </is>
       </c>
     </row>
-    <row r="254"/>
     <row r="255">
       <c r="A255" s="190" t="inlineStr">
         <is>
@@ -6084,29 +6166,638 @@
         </is>
       </c>
     </row>
+    <row r="270">
+      <c r="A270" s="329" t="inlineStr">
+        <is>
+          <t>⚙️ 系统机制速查（说对应的触发词 → 自动执行）</t>
+        </is>
+      </c>
+      <c r="B270" s="330" t="n"/>
+      <c r="C270" s="330" t="n"/>
+      <c r="D270" s="330" t="n"/>
+      <c r="E270" s="330" t="n"/>
+      <c r="F270" s="330" t="n"/>
+      <c r="G270" s="330" t="n"/>
+      <c r="H270" s="331" t="n"/>
+    </row>
+    <row r="271">
+      <c r="A271" s="332" t="inlineStr">
+        <is>
+          <t>📊 日常高频（每周用）</t>
+        </is>
+      </c>
+      <c r="B271" s="330" t="n"/>
+      <c r="C271" s="330" t="n"/>
+      <c r="D271" s="330" t="n"/>
+      <c r="E271" s="330" t="n"/>
+      <c r="F271" s="330" t="n"/>
+      <c r="G271" s="330" t="n"/>
+      <c r="H271" s="331" t="n"/>
+    </row>
+    <row r="272">
+      <c r="A272" s="333" t="inlineStr">
+        <is>
+          <t>"跑监控"</t>
+        </is>
+      </c>
+      <c r="B272" s="331" t="n"/>
+      <c r="C272" s="334" t="inlineStr">
+        <is>
+          <t>→ 全流程：抓取→转录→分析→更新看板</t>
+        </is>
+      </c>
+      <c r="D272" s="330" t="n"/>
+      <c r="E272" s="331" t="n"/>
+    </row>
+    <row r="273">
+      <c r="A273" s="333" t="inlineStr">
+        <is>
+          <t>"跑盈亏联动"</t>
+        </is>
+      </c>
+      <c r="B273" s="331" t="n"/>
+      <c r="C273" s="334" t="inlineStr">
+        <is>
+          <t>→ P值×事件链×价格三维一致性检验</t>
+        </is>
+      </c>
+      <c r="D273" s="330" t="n"/>
+      <c r="E273" s="331" t="n"/>
+    </row>
+    <row r="274">
+      <c r="A274" s="333" t="inlineStr">
+        <is>
+          <t>"看机会成本"</t>
+        </is>
+      </c>
+      <c r="B274" s="331" t="n"/>
+      <c r="C274" s="334" t="inlineStr">
+        <is>
+          <t>→ 所有投资选项P×R排序→决定现金分配</t>
+        </is>
+      </c>
+      <c r="D274" s="330" t="n"/>
+      <c r="E274" s="331" t="n"/>
+    </row>
+    <row r="275">
+      <c r="A275" s="333" t="inlineStr">
+        <is>
+          <t>"调出XX"</t>
+        </is>
+      </c>
+      <c r="B275" s="331" t="n"/>
+      <c r="C275" s="334" t="inlineStr">
+        <is>
+          <t>→ 快速调研新资产：三层分析→三关→3选1</t>
+        </is>
+      </c>
+      <c r="D275" s="330" t="n"/>
+      <c r="E275" s="331" t="n"/>
+    </row>
+    <row r="276">
+      <c r="A276" s="333" t="inlineStr">
+        <is>
+          <t>"资金怎么分"</t>
+        </is>
+      </c>
+      <c r="B276" s="331" t="n"/>
+      <c r="C276" s="334" t="inlineStr">
+        <is>
+          <t>→ Hermes+小龙多轮交叉审核→资金分配方案</t>
+        </is>
+      </c>
+      <c r="D276" s="330" t="n"/>
+      <c r="E276" s="331" t="n"/>
+    </row>
+    <row r="277">
+      <c r="A277" s="333" t="inlineStr">
+        <is>
+          <t>"出日报"</t>
+        </is>
+      </c>
+      <c r="B277" s="331" t="n"/>
+      <c r="C277" s="334" t="inlineStr">
+        <is>
+          <t>→ 当前P值总览+净值+事件→邮件推送</t>
+        </is>
+      </c>
+      <c r="D277" s="330" t="n"/>
+      <c r="E277" s="331" t="n"/>
+    </row>
+    <row r="278">
+      <c r="A278" s="333" t="inlineStr">
+        <is>
+          <t>"查档案"</t>
+        </is>
+      </c>
+      <c r="B278" s="331" t="n"/>
+      <c r="C278" s="334" t="inlineStr">
+        <is>
+          <t>→ 查深度分析原始数据+报告→档案总索引</t>
+        </is>
+      </c>
+      <c r="D278" s="330" t="n"/>
+      <c r="E278" s="331" t="n"/>
+    </row>
+    <row r="280">
+      <c r="A280" s="332" t="inlineStr">
+        <is>
+          <t>📅 定期自动</t>
+        </is>
+      </c>
+      <c r="B280" s="330" t="n"/>
+      <c r="C280" s="330" t="n"/>
+      <c r="D280" s="330" t="n"/>
+      <c r="E280" s="330" t="n"/>
+      <c r="F280" s="330" t="n"/>
+      <c r="G280" s="330" t="n"/>
+      <c r="H280" s="331" t="n"/>
+    </row>
+    <row r="281">
+      <c r="A281" s="333" t="inlineStr">
+        <is>
+          <t>P值拟合</t>
+        </is>
+      </c>
+      <c r="B281" s="331" t="n"/>
+      <c r="C281" s="334" t="inlineStr">
+        <is>
+          <t>→ 每7天自动：验证P值预测准不准→拟合分析Sheet</t>
+        </is>
+      </c>
+      <c r="D281" s="330" t="n"/>
+      <c r="E281" s="331" t="n"/>
+    </row>
+    <row r="282">
+      <c r="A282" s="333" t="inlineStr">
+        <is>
+          <t>周报</t>
+        </is>
+      </c>
+      <c r="B282" s="331" t="n"/>
+      <c r="C282" s="334" t="inlineStr">
+        <is>
+          <t>→ 每周日：叙事串联+梯队复盘→邮件</t>
+        </is>
+      </c>
+      <c r="D282" s="330" t="n"/>
+      <c r="E282" s="331" t="n"/>
+    </row>
+    <row r="283">
+      <c r="A283" s="333" t="inlineStr">
+        <is>
+          <t>持仓周跟踪</t>
+        </is>
+      </c>
+      <c r="B283" s="331" t="n"/>
+      <c r="C283" s="334" t="inlineStr">
+        <is>
+          <t>→ 每周日：叙事一致性→逻辑链→反常→前瞻</t>
+        </is>
+      </c>
+      <c r="D283" s="330" t="n"/>
+      <c r="E283" s="331" t="n"/>
+    </row>
+    <row r="284">
+      <c r="A284" s="333" t="inlineStr">
+        <is>
+          <t>信源评分</t>
+        </is>
+      </c>
+      <c r="B284" s="331" t="n"/>
+      <c r="C284" s="334" t="inlineStr">
+        <is>
+          <t>→ 每14天：校准信源打分→门控方案更新</t>
+        </is>
+      </c>
+      <c r="D284" s="330" t="n"/>
+      <c r="E284" s="331" t="n"/>
+    </row>
+    <row r="286">
+      <c r="A286" s="332" t="inlineStr">
+        <is>
+          <t>📌 Sheet2关键标注（对应位置有提示）</t>
+        </is>
+      </c>
+      <c r="B286" s="330" t="n"/>
+      <c r="C286" s="330" t="n"/>
+      <c r="D286" s="330" t="n"/>
+      <c r="E286" s="330" t="n"/>
+      <c r="F286" s="330" t="n"/>
+      <c r="G286" s="330" t="n"/>
+      <c r="H286" s="331" t="n"/>
+    </row>
+    <row r="287">
+      <c r="A287" s="333" t="inlineStr">
+        <is>
+          <t>P值旁注</t>
+        </is>
+      </c>
+      <c r="B287" s="331" t="n"/>
+      <c r="C287" s="334" t="inlineStr">
+        <is>
+          <t>→ 说"跑P值拟合"验证准不准</t>
+        </is>
+      </c>
+      <c r="D287" s="330" t="n"/>
+      <c r="E287" s="331" t="n"/>
+    </row>
+    <row r="288">
+      <c r="A288" s="333" t="inlineStr">
+        <is>
+          <t>事件链旁注</t>
+        </is>
+      </c>
+      <c r="B288" s="331" t="n"/>
+      <c r="C288" s="334" t="inlineStr">
+        <is>
+          <t>→ 说"校准信源"更新博主权重</t>
+        </is>
+      </c>
+      <c r="D288" s="330" t="n"/>
+      <c r="E288" s="331" t="n"/>
+    </row>
+    <row r="289">
+      <c r="A289" s="333" t="inlineStr">
+        <is>
+          <t>机会成本旁注</t>
+        </is>
+      </c>
+      <c r="B289" s="331" t="n"/>
+      <c r="C289" s="334" t="inlineStr">
+        <is>
+          <t>→ 说"看机会成本"改排序参数</t>
+        </is>
+      </c>
+      <c r="D289" s="330" t="n"/>
+      <c r="E289" s="331" t="n"/>
+    </row>
+    <row r="290">
+      <c r="A290" s="333" t="inlineStr">
+        <is>
+          <t>待重仓旁注</t>
+        </is>
+      </c>
+      <c r="B290" s="331" t="n"/>
+      <c r="C290" s="334" t="inlineStr">
+        <is>
+          <t>→ 说"资金怎么分"启动交叉审核</t>
+        </is>
+      </c>
+      <c r="D290" s="330" t="n"/>
+      <c r="E290" s="331" t="n"/>
+    </row>
+    <row r="292">
+      <c r="A292" s="332" t="inlineStr">
+        <is>
+          <t>📖 完整机制清单（说"我要看XX"即可调用详细文档）</t>
+        </is>
+      </c>
+      <c r="B292" s="330" t="n"/>
+      <c r="C292" s="330" t="n"/>
+      <c r="D292" s="330" t="n"/>
+      <c r="E292" s="330" t="n"/>
+      <c r="F292" s="330" t="n"/>
+      <c r="G292" s="330" t="n"/>
+      <c r="H292" s="331" t="n"/>
+    </row>
+    <row r="293">
+      <c r="A293" s="333" t="inlineStr">
+        <is>
+          <t>P值三层次体系</t>
+        </is>
+      </c>
+      <c r="B293" s="331" t="n"/>
+      <c r="C293" s="334" t="inlineStr">
+        <is>
+          <t>→ 主P(事实)→虚P(观点)→利率折价→有效P</t>
+        </is>
+      </c>
+      <c r="D293" s="330" t="n"/>
+      <c r="E293" s="331" t="n"/>
+    </row>
+    <row r="294">
+      <c r="A294" s="333" t="inlineStr">
+        <is>
+          <t>盈亏比计算</t>
+        </is>
+      </c>
+      <c r="B294" s="331" t="n"/>
+      <c r="C294" s="334" t="inlineStr">
+        <is>
+          <t>→ 确定性空间+溢价×P打折÷下行极限</t>
+        </is>
+      </c>
+      <c r="D294" s="330" t="n"/>
+      <c r="E294" s="331" t="n"/>
+    </row>
+    <row r="295">
+      <c r="A295" s="333" t="inlineStr">
+        <is>
+          <t>三类操盘框架</t>
+        </is>
+      </c>
+      <c r="B295" s="331" t="n"/>
+      <c r="C295" s="334" t="inlineStr">
+        <is>
+          <t>→ 右侧(等信号)/左侧(低估值拿)/HALO(方向性看)</t>
+        </is>
+      </c>
+      <c r="D295" s="330" t="n"/>
+      <c r="E295" s="331" t="n"/>
+    </row>
+    <row r="296">
+      <c r="A296" s="333" t="inlineStr">
+        <is>
+          <t>买入触发条件</t>
+        </is>
+      </c>
+      <c r="B296" s="331" t="n"/>
+      <c r="C296" s="334" t="inlineStr">
+        <is>
+          <t>→ 通用买入信号模板（各品种不同）</t>
+        </is>
+      </c>
+      <c r="D296" s="330" t="n"/>
+      <c r="E296" s="331" t="n"/>
+    </row>
+    <row r="297">
+      <c r="A297" s="333" t="inlineStr">
+        <is>
+          <t>信息源到信念更新</t>
+        </is>
+      </c>
+      <c r="B297" s="331" t="n"/>
+      <c r="C297" s="334" t="inlineStr">
+        <is>
+          <t>→ 信息→事件→贝叶斯P值→仓位影响</t>
+        </is>
+      </c>
+      <c r="D297" s="330" t="n"/>
+      <c r="E297" s="331" t="n"/>
+    </row>
+    <row r="298">
+      <c r="A298" s="333" t="inlineStr">
+        <is>
+          <t>宏观传导框架</t>
+        </is>
+      </c>
+      <c r="B298" s="331" t="n"/>
+      <c r="C298" s="334" t="inlineStr">
+        <is>
+          <t>→ 宏观事件→中观→微观→持仓影响</t>
+        </is>
+      </c>
+      <c r="D298" s="330" t="n"/>
+      <c r="E298" s="331" t="n"/>
+    </row>
+    <row r="299">
+      <c r="A299" s="333" t="inlineStr">
+        <is>
+          <t>估值方法论</t>
+        </is>
+      </c>
+      <c r="B299" s="331" t="n"/>
+      <c r="C299" s="334" t="inlineStr">
+        <is>
+          <t>→ PEG-PB/DCF/市净率等路由表</t>
+        </is>
+      </c>
+      <c r="D299" s="330" t="n"/>
+      <c r="E299" s="331" t="n"/>
+    </row>
+    <row r="300">
+      <c r="A300" s="333" t="inlineStr">
+        <is>
+          <t>贝叶斯P值赔率校准</t>
+        </is>
+      </c>
+      <c r="B300" s="331" t="n"/>
+      <c r="C300" s="334" t="inlineStr">
+        <is>
+          <t>→ P值系统的完整数学基础</t>
+        </is>
+      </c>
+      <c r="D300" s="330" t="n"/>
+      <c r="E300" s="331" t="n"/>
+    </row>
+    <row r="301">
+      <c r="A301" s="333" t="inlineStr">
+        <is>
+          <t>地缘事件监控</t>
+        </is>
+      </c>
+      <c r="B301" s="331" t="n"/>
+      <c r="C301" s="334" t="inlineStr">
+        <is>
+          <t>→ 国际事件→板块映射表</t>
+        </is>
+      </c>
+      <c r="D301" s="330" t="n"/>
+      <c r="E301" s="331" t="n"/>
+    </row>
+    <row r="302">
+      <c r="A302" s="333" t="inlineStr">
+        <is>
+          <t>投资仓位管理机制v3</t>
+        </is>
+      </c>
+      <c r="B302" s="331" t="n"/>
+      <c r="C302" s="334" t="inlineStr">
+        <is>
+          <t>→ 仓位管理规则</t>
+        </is>
+      </c>
+      <c r="D302" s="330" t="n"/>
+      <c r="E302" s="331" t="n"/>
+    </row>
+    <row r="303">
+      <c r="A303" s="333" t="inlineStr">
+        <is>
+          <t>基金估值CDP提取</t>
+        </is>
+      </c>
+      <c r="B303" s="331" t="n"/>
+      <c r="C303" s="334" t="inlineStr">
+        <is>
+          <t>→ 蛋卷基金PE/PB百分位</t>
+        </is>
+      </c>
+      <c r="D303" s="330" t="n"/>
+      <c r="E303" s="331" t="n"/>
+    </row>
+    <row r="304">
+      <c r="A304" s="333" t="inlineStr">
+        <is>
+          <t>利率数据查询</t>
+        </is>
+      </c>
+      <c r="B304" s="331" t="n"/>
+      <c r="C304" s="334" t="inlineStr">
+        <is>
+          <t>→ 浏览器CDP查利率(唯一通路)</t>
+        </is>
+      </c>
+      <c r="D304" s="330" t="n"/>
+      <c r="E304" s="331" t="n"/>
+    </row>
+    <row r="306">
+      <c r="A306" s="332" t="inlineStr">
+        <is>
+          <t>💡 使用规则</t>
+        </is>
+      </c>
+      <c r="B306" s="330" t="n"/>
+      <c r="C306" s="330" t="n"/>
+      <c r="D306" s="330" t="n"/>
+      <c r="E306" s="330" t="n"/>
+      <c r="F306" s="330" t="n"/>
+      <c r="G306" s="330" t="n"/>
+      <c r="H306" s="331" t="n"/>
+    </row>
+    <row r="307">
+      <c r="A307" s="334" t="inlineStr">
+        <is>
+          <t>1. 机制名=触发词，你说啥我跑啥。不说的不跑，免得烧token。</t>
+        </is>
+      </c>
+      <c r="B307" s="330" t="n"/>
+      <c r="C307" s="330" t="n"/>
+      <c r="D307" s="330" t="n"/>
+      <c r="E307" s="330" t="n"/>
+      <c r="F307" s="330" t="n"/>
+      <c r="G307" s="330" t="n"/>
+      <c r="H307" s="331" t="n"/>
+    </row>
+    <row r="308">
+      <c r="A308" s="334" t="inlineStr">
+        <is>
+          <t>2. 机制之间有连锁关系（如P值拟合→信源评分→门控方案），执行时自动联动。</t>
+        </is>
+      </c>
+      <c r="B308" s="330" t="n"/>
+      <c r="C308" s="330" t="n"/>
+      <c r="D308" s="330" t="n"/>
+      <c r="E308" s="330" t="n"/>
+      <c r="F308" s="330" t="n"/>
+      <c r="G308" s="330" t="n"/>
+      <c r="H308" s="331" t="n"/>
+    </row>
+    <row r="309">
+      <c r="A309" s="334" t="inlineStr">
+        <is>
+          <t>3. 新机制建成后必须同步更新此表（三重锁：技能铁律+阶段四检查+档案索引）。</t>
+        </is>
+      </c>
+      <c r="B309" s="330" t="n"/>
+      <c r="C309" s="330" t="n"/>
+      <c r="D309" s="330" t="n"/>
+      <c r="E309" s="330" t="n"/>
+      <c r="F309" s="330" t="n"/>
+      <c r="G309" s="330" t="n"/>
+      <c r="H309" s="331" t="n"/>
+    </row>
+    <row r="310">
+      <c r="A310" s="334" t="inlineStr">
+        <is>
+          <t>4. 完整机制说明见独立"系统机制"Sheet。</t>
+        </is>
+      </c>
+      <c r="B310" s="330" t="n"/>
+      <c r="C310" s="330" t="n"/>
+      <c r="D310" s="330" t="n"/>
+      <c r="E310" s="330" t="n"/>
+      <c r="F310" s="330" t="n"/>
+      <c r="G310" s="330" t="n"/>
+      <c r="H310" s="331" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="21">
+  <mergeCells count="85">
+    <mergeCell ref="C274:E274"/>
+    <mergeCell ref="A304:B304"/>
+    <mergeCell ref="C282:E282"/>
+    <mergeCell ref="C297:E297"/>
+    <mergeCell ref="A25:H25"/>
+    <mergeCell ref="A283:B283"/>
+    <mergeCell ref="A277:B277"/>
+    <mergeCell ref="C299:E299"/>
+    <mergeCell ref="A294:B294"/>
+    <mergeCell ref="C293:E293"/>
+    <mergeCell ref="A278:B278"/>
+    <mergeCell ref="A32:H32"/>
+    <mergeCell ref="A97:H97"/>
+    <mergeCell ref="C275:E275"/>
+    <mergeCell ref="C284:E284"/>
+    <mergeCell ref="A96:H96"/>
+    <mergeCell ref="A280:H280"/>
+    <mergeCell ref="A295:B295"/>
+    <mergeCell ref="A31:H31"/>
+    <mergeCell ref="A58:H58"/>
     <mergeCell ref="A51:H51"/>
     <mergeCell ref="A107:H107"/>
+    <mergeCell ref="A287:B287"/>
+    <mergeCell ref="A281:B281"/>
     <mergeCell ref="B15:H15"/>
+    <mergeCell ref="A296:B296"/>
+    <mergeCell ref="C295:E295"/>
+    <mergeCell ref="C273:E273"/>
+    <mergeCell ref="C272:E272"/>
+    <mergeCell ref="A292:H292"/>
+    <mergeCell ref="A286:H286"/>
+    <mergeCell ref="A282:B282"/>
+    <mergeCell ref="C296:E296"/>
+    <mergeCell ref="A18:H18"/>
+    <mergeCell ref="A272:B272"/>
+    <mergeCell ref="C283:E283"/>
+    <mergeCell ref="A306:H306"/>
+    <mergeCell ref="A302:B302"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A298:B298"/>
+    <mergeCell ref="C298:E298"/>
+    <mergeCell ref="A135:H135"/>
+    <mergeCell ref="A125:H125"/>
+    <mergeCell ref="A299:B299"/>
+    <mergeCell ref="A293:B293"/>
+    <mergeCell ref="C302:E302"/>
+    <mergeCell ref="A276:B276"/>
+    <mergeCell ref="A284:B284"/>
+    <mergeCell ref="C301:E301"/>
+    <mergeCell ref="C276:E276"/>
+    <mergeCell ref="A300:B300"/>
+    <mergeCell ref="C303:E303"/>
+    <mergeCell ref="C300:E300"/>
+    <mergeCell ref="C278:E278"/>
+    <mergeCell ref="C287:E287"/>
+    <mergeCell ref="A41:H41"/>
+    <mergeCell ref="A273:B273"/>
+    <mergeCell ref="C289:E289"/>
+    <mergeCell ref="A301:B301"/>
+    <mergeCell ref="A297:B297"/>
+    <mergeCell ref="A307:H307"/>
+    <mergeCell ref="A303:B303"/>
+    <mergeCell ref="A116:H116"/>
+    <mergeCell ref="A290:B290"/>
+    <mergeCell ref="A309:H309"/>
+    <mergeCell ref="A17:H17"/>
+    <mergeCell ref="B13:H13"/>
+    <mergeCell ref="A274:B274"/>
+    <mergeCell ref="A308:H308"/>
+    <mergeCell ref="A19:H19"/>
+    <mergeCell ref="A270:H270"/>
+    <mergeCell ref="A310:H310"/>
+    <mergeCell ref="A275:B275"/>
+    <mergeCell ref="C277:E277"/>
     <mergeCell ref="A1:H1"/>
-    <mergeCell ref="A25:H25"/>
-    <mergeCell ref="A41:H41"/>
+    <mergeCell ref="A271:H271"/>
     <mergeCell ref="A12:H12"/>
-    <mergeCell ref="A18:H18"/>
-    <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A116:H116"/>
-    <mergeCell ref="A32:H32"/>
-    <mergeCell ref="A135:H135"/>
-    <mergeCell ref="A97:H97"/>
-    <mergeCell ref="A17:H17"/>
+    <mergeCell ref="C304:E304"/>
+    <mergeCell ref="C288:E288"/>
     <mergeCell ref="B14:H14"/>
-    <mergeCell ref="B13:H13"/>
-    <mergeCell ref="A96:H96"/>
-    <mergeCell ref="A125:H125"/>
-    <mergeCell ref="A19:H19"/>
-    <mergeCell ref="A31:H31"/>
-    <mergeCell ref="A58:H58"/>
+    <mergeCell ref="C294:E294"/>
+    <mergeCell ref="C281:E281"/>
+    <mergeCell ref="C290:E290"/>
+    <mergeCell ref="A288:B288"/>
+    <mergeCell ref="A289:B289"/>
   </mergeCells>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -7982,6 +8673,916 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G38"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" style="139" min="1" max="1"/>
+    <col width="14" customWidth="1" style="139" min="2" max="2"/>
+    <col width="45" customWidth="1" style="139" min="3" max="3"/>
+    <col width="14" customWidth="1" style="139" min="4" max="4"/>
+    <col width="18" customWidth="1" style="139" min="5" max="5"/>
+    <col width="12" customWidth="1" style="139" min="6" max="6"/>
+    <col width="20" customWidth="1" style="139" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="335" t="inlineStr">
+        <is>
+          <t>⚙️ 系统机制完整索引</t>
+        </is>
+      </c>
+      <c r="B1" s="330" t="n"/>
+      <c r="C1" s="330" t="n"/>
+      <c r="D1" s="330" t="n"/>
+      <c r="E1" s="330" t="n"/>
+      <c r="F1" s="330" t="n"/>
+      <c r="G1" s="331" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="336" t="inlineStr">
+        <is>
+          <t>字段说明：机制名 | 触发词 | 功能说明 | 输入 | 输出 | 频率 | 关联机制</t>
+        </is>
+      </c>
+      <c r="B2" s="330" t="n"/>
+      <c r="C2" s="330" t="n"/>
+      <c r="D2" s="330" t="n"/>
+      <c r="E2" s="330" t="n"/>
+      <c r="F2" s="330" t="n"/>
+      <c r="G2" s="331" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="332" t="inlineStr">
+        <is>
+          <t>A类：投资核心机制</t>
+        </is>
+      </c>
+      <c r="B4" s="330" t="n"/>
+      <c r="C4" s="330" t="n"/>
+      <c r="D4" s="330" t="n"/>
+      <c r="E4" s="330" t="n"/>
+      <c r="F4" s="330" t="n"/>
+      <c r="G4" s="331" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="333" t="inlineStr">
+        <is>
+          <t>P值三层次体系</t>
+        </is>
+      </c>
+      <c r="B5" s="334" t="inlineStr">
+        <is>
+          <t>内置规则</t>
+        </is>
+      </c>
+      <c r="C5" s="334" t="inlineStr">
+        <is>
+          <t>主P(事实事件)→虚P(观点预测)→利率折价→有效P。P值系统的宪法。</t>
+        </is>
+      </c>
+      <c r="D5" s="337" t="inlineStr">
+        <is>
+          <t>事件数据</t>
+        </is>
+      </c>
+      <c r="E5" s="337" t="inlineStr">
+        <is>
+          <t>有效P值</t>
+        </is>
+      </c>
+      <c r="F5" s="337" t="inlineStr">
+        <is>
+          <t>每次事件更新</t>
+        </is>
+      </c>
+      <c r="G5" s="337" t="inlineStr">
+        <is>
+          <t>→盈亏比→机会成本</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="333" t="inlineStr">
+        <is>
+          <t>盈亏比计算</t>
+        </is>
+      </c>
+      <c r="B6" s="334" t="inlineStr">
+        <is>
+          <t>内置规则</t>
+        </is>
+      </c>
+      <c r="C6" s="334" t="inlineStr">
+        <is>
+          <t>确定性空间+溢价空间×P打折÷下行极限。决定是否值得做。</t>
+        </is>
+      </c>
+      <c r="D6" s="337" t="inlineStr">
+        <is>
+          <t>P值+空间估计</t>
+        </is>
+      </c>
+      <c r="E6" s="337" t="inlineStr">
+        <is>
+          <t>盈亏比数值</t>
+        </is>
+      </c>
+      <c r="F6" s="337" t="inlineStr">
+        <is>
+          <t>按需</t>
+        </is>
+      </c>
+      <c r="G6" s="337" t="inlineStr">
+        <is>
+          <t>←P值体系→机会成本</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="333" t="inlineStr">
+        <is>
+          <t>P值vs价格拟合分析</t>
+        </is>
+      </c>
+      <c r="B7" s="334" t="inlineStr">
+        <is>
+          <t>"跑P值拟合"</t>
+        </is>
+      </c>
+      <c r="C7" s="334" t="inlineStr">
+        <is>
+          <t>六维度综合评分(Spearman+Pearson+Kendall+事件驱动+方向一致+回归斜率)验证P值准确性。</t>
+        </is>
+      </c>
+      <c r="D7" s="337" t="inlineStr">
+        <is>
+          <t>P值序列+价格数据</t>
+        </is>
+      </c>
+      <c r="E7" s="337" t="inlineStr">
+        <is>
+          <t>拟合分析Sheet+评分</t>
+        </is>
+      </c>
+      <c r="F7" s="337" t="inlineStr">
+        <is>
+          <t>每7天自动</t>
+        </is>
+      </c>
+      <c r="G7" s="337" t="inlineStr">
+        <is>
+          <t>→信源评分→门控</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="333" t="inlineStr">
+        <is>
+          <t>持仓盈亏联动</t>
+        </is>
+      </c>
+      <c r="B8" s="334" t="inlineStr">
+        <is>
+          <t>"跑盈亏联动"</t>
+        </is>
+      </c>
+      <c r="C8" s="334" t="inlineStr">
+        <is>
+          <t>P值预测方向×事件链推导方向×实际价格走势三维一致性检验。</t>
+        </is>
+      </c>
+      <c r="D8" s="337" t="inlineStr">
+        <is>
+          <t>Excel P值+基金净值+事件链</t>
+        </is>
+      </c>
+      <c r="E8" s="337" t="inlineStr">
+        <is>
+          <t>持仓盈亏联动Sheet+邮件</t>
+        </is>
+      </c>
+      <c r="F8" s="337" t="inlineStr">
+        <is>
+          <t>每次更新后</t>
+        </is>
+      </c>
+      <c r="G8" s="337" t="inlineStr">
+        <is>
+          <t>←P值→机会成本</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="333" t="inlineStr">
+        <is>
+          <t>机会成本比较</t>
+        </is>
+      </c>
+      <c r="B9" s="334" t="inlineStr">
+        <is>
+          <t>"看机会成本"</t>
+        </is>
+      </c>
+      <c r="C9" s="334" t="inlineStr">
+        <is>
+          <t>所有投资选项(持仓加仓/新机会/现金)放一个池子，用P×R排序决定现金分配。</t>
+        </is>
+      </c>
+      <c r="D9" s="337" t="inlineStr">
+        <is>
+          <t>P值+预估收益率</t>
+        </is>
+      </c>
+      <c r="E9" s="337" t="inlineStr">
+        <is>
+          <t>机会成本排序Sheet</t>
+        </is>
+      </c>
+      <c r="F9" s="337" t="inlineStr">
+        <is>
+          <t>每次监控后</t>
+        </is>
+      </c>
+      <c r="G9" s="337" t="inlineStr">
+        <is>
+          <t>←P值←盈亏比</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="333" t="inlineStr">
+        <is>
+          <t>资金分配交叉审核</t>
+        </is>
+      </c>
+      <c r="B10" s="334" t="inlineStr">
+        <is>
+          <t>"资金怎么分"</t>
+        </is>
+      </c>
+      <c r="C10" s="334" t="inlineStr">
+        <is>
+          <t>Hermes出初稿→小龙虾审→Hermes反审→联合结论。多轮交叉提问。</t>
+        </is>
+      </c>
+      <c r="D10" s="337" t="inlineStr">
+        <is>
+          <t>持仓数据+P值+现金量</t>
+        </is>
+      </c>
+      <c r="E10" s="337" t="inlineStr">
+        <is>
+          <t>资金分配方案+审核记录</t>
+        </is>
+      </c>
+      <c r="F10" s="337" t="inlineStr">
+        <is>
+          <t>按需(大额决策)</t>
+        </is>
+      </c>
+      <c r="G10" s="337" t="inlineStr">
+        <is>
+          <t>←机会成本</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="333" t="inlineStr">
+        <is>
+          <t>买入触发条件模板</t>
+        </is>
+      </c>
+      <c r="B11" s="334" t="inlineStr">
+        <is>
+          <t>内置规则</t>
+        </is>
+      </c>
+      <c r="C11" s="334" t="inlineStr">
+        <is>
+          <t>各类资产的通用买入信号模板(右侧/左侧/HALO各有不同触发条件)。</t>
+        </is>
+      </c>
+      <c r="D11" s="337" t="inlineStr">
+        <is>
+          <t>品种类型</t>
+        </is>
+      </c>
+      <c r="E11" s="337" t="inlineStr">
+        <is>
+          <t>触发条件清单</t>
+        </is>
+      </c>
+      <c r="F11" s="337" t="inlineStr">
+        <is>
+          <t>按需</t>
+        </is>
+      </c>
+      <c r="G11" s="337" t="inlineStr">
+        <is>
+          <t>←三类操盘框架</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="333" t="inlineStr">
+        <is>
+          <t>三类操盘框架</t>
+        </is>
+      </c>
+      <c r="B12" s="334" t="inlineStr">
+        <is>
+          <t>内置规则</t>
+        </is>
+      </c>
+      <c r="C12" s="334" t="inlineStr">
+        <is>
+          <t>右侧(等信号确认)/左侧(低估值慢慢拿)/HALO(方向性看看不做)。决定操作节奏。</t>
+        </is>
+      </c>
+      <c r="D12" s="337" t="inlineStr">
+        <is>
+          <t>品种特征</t>
+        </is>
+      </c>
+      <c r="E12" s="337" t="inlineStr">
+        <is>
+          <t>分类+操作原则</t>
+        </is>
+      </c>
+      <c r="F12" s="337" t="inlineStr">
+        <is>
+          <t>每次新资产</t>
+        </is>
+      </c>
+      <c r="G12" s="337" t="inlineStr">
+        <is>
+          <t>→买入触发</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="333" t="inlineStr">
+        <is>
+          <t>资产快速查询</t>
+        </is>
+      </c>
+      <c r="B13" s="334" t="inlineStr">
+        <is>
+          <t>"调出XX"</t>
+        </is>
+      </c>
+      <c r="C13" s="334" t="inlineStr">
+        <is>
+          <t>三层分析(宏观→中观→微观)→三关(懂不懂/护城河/管理层)→3选1(不动/加/减)。</t>
+        </is>
+      </c>
+      <c r="D13" s="337" t="inlineStr">
+        <is>
+          <t>资产名称</t>
+        </is>
+      </c>
+      <c r="E13" s="337" t="inlineStr">
+        <is>
+          <t>调研报告+建议</t>
+        </is>
+      </c>
+      <c r="F13" s="337" t="inlineStr">
+        <is>
+          <t>按需</t>
+        </is>
+      </c>
+      <c r="G13" s="337" t="inlineStr">
+        <is>
+          <t>←估值方法论←宏观传导</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="333" t="inlineStr">
+        <is>
+          <t>信息源到信念更新</t>
+        </is>
+      </c>
+      <c r="B14" s="334" t="inlineStr">
+        <is>
+          <t>内置规则</t>
+        </is>
+      </c>
+      <c r="C14" s="334" t="inlineStr">
+        <is>
+          <t>信息源→事件提取→贝叶斯P值更新→仓位影响计算→互锁验证。</t>
+        </is>
+      </c>
+      <c r="D14" s="337" t="inlineStr">
+        <is>
+          <t>视频/新闻/文章</t>
+        </is>
+      </c>
+      <c r="E14" s="337" t="inlineStr">
+        <is>
+          <t>事件记录+P值更新</t>
+        </is>
+      </c>
+      <c r="F14" s="337" t="inlineStr">
+        <is>
+          <t>每次监控</t>
+        </is>
+      </c>
+      <c r="G14" s="337" t="inlineStr">
+        <is>
+          <t>→P值体系</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="333" t="inlineStr">
+        <is>
+          <t>持仓周跟踪</t>
+        </is>
+      </c>
+      <c r="B15" s="334" t="inlineStr">
+        <is>
+          <t>内置规则</t>
+        </is>
+      </c>
+      <c r="C15" s="334" t="inlineStr">
+        <is>
+          <t>周日四层框架：叙事一致性→逻辑链检验→反常检测→前瞻更新(含置信度)。</t>
+        </is>
+      </c>
+      <c r="D15" s="337" t="inlineStr">
+        <is>
+          <t>持仓数据+本周事件</t>
+        </is>
+      </c>
+      <c r="E15" s="337" t="inlineStr">
+        <is>
+          <t>周报邮件</t>
+        </is>
+      </c>
+      <c r="F15" s="337" t="inlineStr">
+        <is>
+          <t>每周日自动</t>
+        </is>
+      </c>
+      <c r="G15" s="337" t="inlineStr">
+        <is>
+          <t>←P值←盈亏联动</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="332" t="inlineStr">
+        <is>
+          <t>B类：工具技能</t>
+        </is>
+      </c>
+      <c r="B17" s="330" t="n"/>
+      <c r="C17" s="330" t="n"/>
+      <c r="D17" s="330" t="n"/>
+      <c r="E17" s="330" t="n"/>
+      <c r="F17" s="330" t="n"/>
+      <c r="G17" s="331" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="333" t="inlineStr">
+        <is>
+          <t>基金估值CDP提取</t>
+        </is>
+      </c>
+      <c r="B18" s="334" t="inlineStr">
+        <is>
+          <t>"查估值"</t>
+        </is>
+      </c>
+      <c r="C18" s="334" t="inlineStr">
+        <is>
+          <t>通过Chrome CDP从蛋卷基金提取指数PE/PB百分位数据。</t>
+        </is>
+      </c>
+      <c r="D18" s="337" t="inlineStr">
+        <is>
+          <t>指数名称</t>
+        </is>
+      </c>
+      <c r="E18" s="337" t="inlineStr">
+        <is>
+          <t>PE/PB百分位</t>
+        </is>
+      </c>
+      <c r="F18" s="337" t="inlineStr">
+        <is>
+          <t>按需</t>
+        </is>
+      </c>
+      <c r="G18" s="337" t="inlineStr">
+        <is>
+          <t>→资产快速查询</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="333" t="inlineStr">
+        <is>
+          <t>利率数据查询</t>
+        </is>
+      </c>
+      <c r="B19" s="334" t="inlineStr">
+        <is>
+          <t>"查利率"</t>
+        </is>
+      </c>
+      <c r="C19" s="334" t="inlineStr">
+        <is>
+          <t>所有外部财经API被墙，唯一通路是浏览器CDP查利率。</t>
+        </is>
+      </c>
+      <c r="D19" s="337" t="inlineStr">
+        <is>
+          <t>利率品种</t>
+        </is>
+      </c>
+      <c r="E19" s="337" t="inlineStr">
+        <is>
+          <t>利率数值</t>
+        </is>
+      </c>
+      <c r="F19" s="337" t="inlineStr">
+        <is>
+          <t>按需</t>
+        </is>
+      </c>
+      <c r="G19" s="337" t="inlineStr">
+        <is>
+          <t>→P值利率折价</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="332" t="inlineStr">
+        <is>
+          <t>C类：流程与保障机制</t>
+        </is>
+      </c>
+      <c r="B21" s="330" t="n"/>
+      <c r="C21" s="330" t="n"/>
+      <c r="D21" s="330" t="n"/>
+      <c r="E21" s="330" t="n"/>
+      <c r="F21" s="330" t="n"/>
+      <c r="G21" s="331" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="333" t="inlineStr">
+        <is>
+          <t>监控第〇步五个开关</t>
+        </is>
+      </c>
+      <c r="B22" s="334" t="inlineStr">
+        <is>
+          <t>内置规则</t>
+        </is>
+      </c>
+      <c r="C22" s="334" t="inlineStr">
+        <is>
+          <t>每次监控前先确认：调试输出/收网/待重仓审核/宏观审核/巴菲特三关。</t>
+        </is>
+      </c>
+      <c r="D22" s="337" t="inlineStr">
+        <is>
+          <t>用户指令</t>
+        </is>
+      </c>
+      <c r="E22" s="337" t="inlineStr">
+        <is>
+          <t>开关配置</t>
+        </is>
+      </c>
+      <c r="F22" s="337" t="inlineStr">
+        <is>
+          <t>每次监控</t>
+        </is>
+      </c>
+      <c r="G22" s="337" t="inlineStr">
+        <is>
+          <t>→全流程</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="333" t="inlineStr">
+        <is>
+          <t>信源评分系统</t>
+        </is>
+      </c>
+      <c r="B23" s="334" t="inlineStr">
+        <is>
+          <t>"校准信源"</t>
+        </is>
+      </c>
+      <c r="C23" s="334" t="inlineStr">
+        <is>
+          <t>P值vs价格拟合→信源打分→门控方案(全信/半信/丢弃)。</t>
+        </is>
+      </c>
+      <c r="D23" s="337" t="inlineStr">
+        <is>
+          <t>拟合结果+事件链</t>
+        </is>
+      </c>
+      <c r="E23" s="337" t="inlineStr">
+        <is>
+          <t>source_calibration_deep.json</t>
+        </is>
+      </c>
+      <c r="F23" s="337" t="inlineStr">
+        <is>
+          <t>每14天</t>
+        </is>
+      </c>
+      <c r="G23" s="337" t="inlineStr">
+        <is>
+          <t>←P值拟合→门控</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="333" t="inlineStr">
+        <is>
+          <t>深度分析档案索引</t>
+        </is>
+      </c>
+      <c r="B24" s="334" t="inlineStr">
+        <is>
+          <t>"查档案"</t>
+        </is>
+      </c>
+      <c r="C24" s="334" t="inlineStr">
+        <is>
+          <t>任何深度分析完成后建索引(L1.5+L2+持久路径)，确保可追溯。</t>
+        </is>
+      </c>
+      <c r="D24" s="337" t="inlineStr">
+        <is>
+          <t>分析对象名</t>
+        </is>
+      </c>
+      <c r="E24" s="337" t="inlineStr">
+        <is>
+          <t>档案索引文档+L2记忆</t>
+        </is>
+      </c>
+      <c r="F24" s="337" t="inlineStr">
+        <is>
+          <t>深度分析后</t>
+        </is>
+      </c>
+      <c r="G24" s="337" t="inlineStr">
+        <is>
+          <t>→档案总索引</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="333" t="inlineStr">
+        <is>
+          <t>看板使用教程</t>
+        </is>
+      </c>
+      <c r="B25" s="334" t="inlineStr">
+        <is>
+          <t>"怎么用看板"</t>
+        </is>
+      </c>
+      <c r="C25" s="334" t="inlineStr">
+        <is>
+          <t>日常3分钟(看P值排序)/半月复盘(拟合信源)/正轨(时间线推演)。</t>
+        </is>
+      </c>
+      <c r="D25" s="337" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E25" s="337" t="inlineStr">
+        <is>
+          <t>~/桌面/看板使用教程.md</t>
+        </is>
+      </c>
+      <c r="F25" s="337" t="inlineStr">
+        <is>
+          <t>按需</t>
+        </is>
+      </c>
+      <c r="G25" s="337" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="333" t="inlineStr">
+        <is>
+          <t>日报Cron</t>
+        </is>
+      </c>
+      <c r="B26" s="334" t="inlineStr">
+        <is>
+          <t>"出日报"</t>
+        </is>
+      </c>
+      <c r="C26" s="334" t="inlineStr">
+        <is>
+          <t>工作日下午自动推送：P值总览+净值+事件→邮件。</t>
+        </is>
+      </c>
+      <c r="D26" s="337" t="inlineStr">
+        <is>
+          <t>当前看板数据</t>
+        </is>
+      </c>
+      <c r="E26" s="337" t="inlineStr">
+        <is>
+          <t>邮件到QQ</t>
+        </is>
+      </c>
+      <c r="F26" s="337" t="inlineStr">
+        <is>
+          <t>工作日自动</t>
+        </is>
+      </c>
+      <c r="G26" s="337" t="inlineStr">
+        <is>
+          <t>←全看板</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="333" t="inlineStr">
+        <is>
+          <t>新机制三重锁</t>
+        </is>
+      </c>
+      <c r="B27" s="334" t="inlineStr">
+        <is>
+          <t>内置铁律</t>
+        </is>
+      </c>
+      <c r="C27" s="334" t="inlineStr">
+        <is>
+          <t>锁1:建完机制同步更新三处 锁2:阶段四第12项自检 锁3:档案索引同步。防止机制隐身。</t>
+        </is>
+      </c>
+      <c r="D27" s="337" t="inlineStr">
+        <is>
+          <t>新机制</t>
+        </is>
+      </c>
+      <c r="E27" s="337" t="inlineStr">
+        <is>
+          <t>更新后的看板+文档</t>
+        </is>
+      </c>
+      <c r="F27" s="337" t="inlineStr">
+        <is>
+          <t>每次建机制</t>
+        </is>
+      </c>
+      <c r="G27" s="337" t="inlineStr">
+        <is>
+          <t>→本表</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="332" t="inlineStr">
+        <is>
+          <t>🔗 核心连锁关系</t>
+        </is>
+      </c>
+      <c r="B30" s="330" t="n"/>
+      <c r="C30" s="330" t="n"/>
+      <c r="D30" s="330" t="n"/>
+      <c r="E30" s="330" t="n"/>
+      <c r="F30" s="330" t="n"/>
+      <c r="G30" s="331" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="334" t="inlineStr">
+        <is>
+          <t>连锁1：P值拟合 → 信源评分 → 门控方案（全信/半信/丢弃）</t>
+        </is>
+      </c>
+      <c r="B31" s="330" t="n"/>
+      <c r="C31" s="330" t="n"/>
+      <c r="D31" s="330" t="n"/>
+      <c r="E31" s="330" t="n"/>
+      <c r="F31" s="330" t="n"/>
+      <c r="G31" s="331" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="334" t="inlineStr">
+        <is>
+          <t>连锁2：信息源→信念更新 → P值体系 → 盈亏比 → 机会成本 → 资金分配</t>
+        </is>
+      </c>
+      <c r="B32" s="330" t="n"/>
+      <c r="C32" s="330" t="n"/>
+      <c r="D32" s="330" t="n"/>
+      <c r="E32" s="330" t="n"/>
+      <c r="F32" s="330" t="n"/>
+      <c r="G32" s="331" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="334" t="inlineStr">
+        <is>
+          <t>连锁3：资产快速查询 → 三类操盘框架 → 买入触发条件 → 待重仓监控</t>
+        </is>
+      </c>
+      <c r="B33" s="330" t="n"/>
+      <c r="C33" s="330" t="n"/>
+      <c r="D33" s="330" t="n"/>
+      <c r="E33" s="330" t="n"/>
+      <c r="F33" s="330" t="n"/>
+      <c r="G33" s="331" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="334" t="inlineStr">
+        <is>
+          <t>连锁4：持仓盈亏联动 → 机会成本 → 资金分配交叉审核</t>
+        </is>
+      </c>
+      <c r="B34" s="330" t="n"/>
+      <c r="C34" s="330" t="n"/>
+      <c r="D34" s="330" t="n"/>
+      <c r="E34" s="330" t="n"/>
+      <c r="F34" s="330" t="n"/>
+      <c r="G34" s="331" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="334" t="inlineStr">
+        <is>
+          <t>连锁5：深度分析 → 档案索引 → 档案总索引 → L2可检索</t>
+        </is>
+      </c>
+      <c r="B35" s="330" t="n"/>
+      <c r="C35" s="330" t="n"/>
+      <c r="D35" s="330" t="n"/>
+      <c r="E35" s="330" t="n"/>
+      <c r="F35" s="330" t="n"/>
+      <c r="G35" s="331" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="334" t="inlineStr">
+        <is>
+          <t>连锁6：周报 → 叙事一致性 → 反常检测 → 前瞻更新 → 持仓调整</t>
+        </is>
+      </c>
+      <c r="B36" s="330" t="n"/>
+      <c r="C36" s="330" t="n"/>
+      <c r="D36" s="330" t="n"/>
+      <c r="E36" s="330" t="n"/>
+      <c r="F36" s="330" t="n"/>
+      <c r="G36" s="331" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="338" t="inlineStr">
+        <is>
+          <t>共记录 19 个机制 | 最后更新: 2026-06-07</t>
+        </is>
+      </c>
+      <c r="B38" s="330" t="n"/>
+      <c r="C38" s="330" t="n"/>
+      <c r="D38" s="330" t="n"/>
+      <c r="E38" s="330" t="n"/>
+      <c r="F38" s="330" t="n"/>
+      <c r="G38" s="331" t="n"/>
+    </row>
+  </sheetData>
+  <mergeCells count="13">
+    <mergeCell ref="A32:G32"/>
+    <mergeCell ref="A36:G36"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A17:G17"/>
+    <mergeCell ref="A31:G31"/>
+    <mergeCell ref="A21:G21"/>
+    <mergeCell ref="A34:G34"/>
+    <mergeCell ref="A35:G35"/>
+    <mergeCell ref="A4:G4"/>
+    <mergeCell ref="A30:G30"/>
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A38:G38"/>
+    <mergeCell ref="A33:G33"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr filterMode="0">

--- a/持仓贝叶斯跟踪.xlsx
+++ b/持仓贝叶斯跟踪.xlsx
@@ -28,7 +28,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="67">
+  <fonts count="68">
     <font>
       <name val="Calibri"/>
       <charset val="1"/>
@@ -448,6 +448,11 @@
       <color rgb="00AAAAAA"/>
       <sz val="9"/>
     </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <sz val="10"/>
+    </font>
   </fonts>
   <fills count="38">
     <fill>
@@ -792,7 +797,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="339">
+  <cellXfs count="340">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -1754,6 +1759,9 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="64" fillId="35" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="67" fillId="35" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2114,6 +2122,36 @@
 - 养殖：去杠杆是加速器，等右侧信号（猪价企稳+产能出清确认）
 - 银行：不加仓，去杠杆周期中银行最难受
 </t>
+      </text>
+    </comment>
+    <comment ref="B116" authorId="0" shapeId="0">
+      <text>
+        <t>📌 AI非泡沫·顶层判断（来龙去脉完整版）
+来源：蒋宇飞商业（顶级置信度）
+核心原话：
+"死都要死在AI里面"
+核心逻辑链：
+1. 2000年互联网泡沫 = 基础设施(光纤/交换机)大量建设，但没有应用/网站 → 纯基建无需求
+2. 当前AI = 每一块芯片都在被点亮 → 应用端已经全面爆发
+3. 黄仁勋(英伟达CEO)说AI不是泡沫 → 芯片厂视角确认
+4. 孙正义(SoftBank)说AI不是泡沫 → 投资端视角确认
+5. 拉长时间看AI绝对没有问题，当前风险远小于2000年互联网
+对比2000年互联网泡沫：
+- 2000年：光纤铺了但没网站 → 泡沫
+- 现在：芯片产了就有AI应用吃 → 不是泡沫
+- 关键差异：应用端是否已经爆发
+对持仓的影响：
+🟢 芯片(020628)：直接利好。AI基建长期逻辑坚不可摧，所有短期波动都是噪音
+🟢 电池(009759)：间接利好。AI数据中心用电需求→电力/储能长期需求
+🟢 有色/稀金：间接利好。AI基建需要铜/金等原材料
+🟡 恒科/养殖/银行/原油：中性，不直接相关
+操作意义：
+- 这是AI赛道的"信念锚"——不管短期P值怎么波动，长期方向不会变
+- 短期回调=买入机会（如果策略是右侧则等信号，左侧则可逐步加）
+- 所有AI子赛道(芯片/堆叠/存储/HBM/光模块/玻璃基板)的长期逻辑都建立在这个判断上
+关联资金分配：
+- 已体现在6/7资金分配方案中：堆叠三批(45%)+MLCC(5.5%)+PlanB升腾(8%)
+- 这些都是基于"AI非泡沫"顶层判断的具体执行</t>
       </text>
     </comment>
     <comment ref="A118" authorId="1" shapeId="0">
@@ -3548,11 +3586,22 @@
       <c r="H115" s="150" t="n"/>
     </row>
     <row r="116" ht="15" customHeight="1" s="139">
-      <c r="A116" s="138" t="inlineStr">
+      <c r="A116" s="339" t="inlineStr">
         <is>
           <t>④</t>
         </is>
       </c>
+      <c r="B116" s="338" t="inlineStr">
+        <is>
+          <t>④AI非泡沫·死也要死在AI里 🟢升级【来源：蒋宇飞，顶级置信度】。"死都要死在AI里面"——AI不是泡沫，每一块芯片都在被点亮(应用端爆发)，与2000年互联网泡沫(光纤交换机狂建但无应用)本质不同。黄仁勋+孙正义交叉确认：AI基础设施投入有真实应用支撑。拉长时间AI绝对没有问题，当前风险远小于2000年互联网泡沫。此为AI赛道顶层信念锚，支撑所有AI基建子赛道(芯片/堆叠/存储/光模块)的长期逻辑。</t>
+        </is>
+      </c>
+      <c r="C116" s="330" t="n"/>
+      <c r="D116" s="330" t="n"/>
+      <c r="E116" s="330" t="n"/>
+      <c r="F116" s="330" t="n"/>
+      <c r="G116" s="330" t="n"/>
+      <c r="H116" s="331" t="n"/>
     </row>
     <row r="117">
       <c r="A117" s="151" t="inlineStr">
@@ -6731,6 +6780,7 @@
     <mergeCell ref="A96:H96"/>
     <mergeCell ref="A280:H280"/>
     <mergeCell ref="A295:B295"/>
+    <mergeCell ref="B116:H116"/>
     <mergeCell ref="A31:H31"/>
     <mergeCell ref="A58:H58"/>
     <mergeCell ref="A51:H51"/>
@@ -6775,7 +6825,6 @@
     <mergeCell ref="A297:B297"/>
     <mergeCell ref="A307:H307"/>
     <mergeCell ref="A303:B303"/>
-    <mergeCell ref="A116:H116"/>
     <mergeCell ref="A290:B290"/>
     <mergeCell ref="A309:H309"/>
     <mergeCell ref="A17:H17"/>

--- a/持仓贝叶斯跟踪.xlsx
+++ b/持仓贝叶斯跟踪.xlsx
@@ -459,7 +459,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="31">
+  <fills count="32">
     <fill>
       <patternFill/>
     </fill>
@@ -640,6 +640,12 @@
         <bgColor rgb="001a1a2e"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="0016213e"/>
+        <bgColor rgb="0016213e"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="16">
     <border>
@@ -812,7 +818,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="360">
+  <cellXfs count="361">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -1877,6 +1883,9 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="59" fillId="30" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="58" fillId="31" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2608,7 +2617,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:H42"/>
+  <dimension ref="A1:H116"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6171875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="18" customWidth="1" style="332" min="1" max="8"/>
@@ -8587,7 +8596,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H115"/>
+  <dimension ref="A1:H132"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9809,7 +9818,338 @@
         </is>
       </c>
     </row>
+    <row r="117">
+      <c r="A117" s="355" t="inlineStr">
+        <is>
+          <t>📊 待重仓资金分配策略（动态更新）</t>
+        </is>
+      </c>
+      <c r="B117" s="356" t="n"/>
+      <c r="C117" s="356" t="n"/>
+      <c r="D117" s="356" t="n"/>
+      <c r="E117" s="356" t="n"/>
+      <c r="F117" s="356" t="n"/>
+      <c r="G117" s="356" t="n"/>
+      <c r="H117" s="357" t="n"/>
+    </row>
+    <row r="118">
+      <c r="A118" s="358" t="inlineStr">
+        <is>
+          <t>⚠️ 此策略需定期修正：每次监控后/重大事件/价格异动时重新评估。最后更新：2026-06-07</t>
+        </is>
+      </c>
+      <c r="B118" s="356" t="n"/>
+      <c r="C118" s="356" t="n"/>
+      <c r="D118" s="356" t="n"/>
+      <c r="E118" s="356" t="n"/>
+      <c r="F118" s="356" t="n"/>
+      <c r="G118" s="356" t="n"/>
+      <c r="H118" s="357" t="n"/>
+    </row>
+    <row r="120">
+      <c r="A120" s="359" t="inlineStr">
+        <is>
+          <t>标的</t>
+        </is>
+      </c>
+      <c r="B120" s="359" t="inlineStr">
+        <is>
+          <t>分配%</t>
+        </is>
+      </c>
+      <c r="C120" s="359" t="inlineStr">
+        <is>
+          <t>进入方式</t>
+        </is>
+      </c>
+      <c r="D120" s="359" t="inlineStr">
+        <is>
+          <t>时间</t>
+        </is>
+      </c>
+      <c r="E120" s="359" t="inlineStr">
+        <is>
+          <t>优先级</t>
+        </is>
+      </c>
+      <c r="F120" s="359" t="inlineStr">
+        <is>
+          <t>当前状态</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="360" t="inlineStr">
+        <is>
+          <t>MLCC(风华高科)</t>
+        </is>
+      </c>
+      <c r="B121" s="360" t="inlineStr">
+        <is>
+          <t>5.5%</t>
+        </is>
+      </c>
+      <c r="C121" s="360" t="inlineStr">
+        <is>
+          <t>一次性建仓</t>
+        </is>
+      </c>
+      <c r="D121" s="360" t="inlineStr">
+        <is>
+          <t>现在(6-7月)</t>
+        </is>
+      </c>
+      <c r="E121" s="360" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F121" s="360" t="inlineStr">
+        <is>
+          <t>刚启动，年底清仓</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="360" t="inlineStr">
+        <is>
+          <t>机器人(562500)</t>
+        </is>
+      </c>
+      <c r="B122" s="360" t="inlineStr">
+        <is>
+          <t>4%</t>
+        </is>
+      </c>
+      <c r="C122" s="360" t="inlineStr">
+        <is>
+          <t>定投(分3-4次，每次1%)</t>
+        </is>
+      </c>
+      <c r="D122" s="360" t="inlineStr">
+        <is>
+          <t>现在开始，跌5%加一次</t>
+        </is>
+      </c>
+      <c r="E122" s="360" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F122" s="360" t="inlineStr">
+        <is>
+          <t>已涨15%，方向对时机不好</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="360" t="inlineStr">
+        <is>
+          <t>油气对冲(162411)</t>
+        </is>
+      </c>
+      <c r="B123" s="360" t="inlineStr">
+        <is>
+          <t>2%</t>
+        </is>
+      </c>
+      <c r="C123" s="360" t="inlineStr">
+        <is>
+          <t>小仓位试水</t>
+        </is>
+      </c>
+      <c r="D123" s="360" t="inlineStr">
+        <is>
+          <t>油价&gt;100时</t>
+        </is>
+      </c>
+      <c r="E123" s="360" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F123" s="360" t="inlineStr">
+        <is>
+          <t>霍尔木兹封锁中</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="360" t="inlineStr">
+        <is>
+          <t>长电+通富</t>
+        </is>
+      </c>
+      <c r="B124" s="360" t="inlineStr">
+        <is>
+          <t>45%</t>
+        </is>
+      </c>
+      <c r="C124" s="360" t="inlineStr">
+        <is>
+          <t>等11月大跌分三批(15+15+15)</t>
+        </is>
+      </c>
+      <c r="D124" s="360" t="inlineStr">
+        <is>
+          <t>11月中期选举</t>
+        </is>
+      </c>
+      <c r="E124" s="360" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F124" s="360" t="inlineStr">
+        <is>
+          <t>最大仓位，必须等回调</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="360" t="inlineStr">
+        <is>
+          <t>HBM产业链</t>
+        </is>
+      </c>
+      <c r="B125" s="360" t="inlineStr">
+        <is>
+          <t>5%</t>
+        </is>
+      </c>
+      <c r="C125" s="360" t="inlineStr">
+        <is>
+          <t>Q4一次性</t>
+        </is>
+      </c>
+      <c r="D125" s="360" t="inlineStr">
+        <is>
+          <t>10-12月</t>
+        </is>
+      </c>
+      <c r="E125" s="360" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F125" s="360" t="inlineStr">
+        <is>
+          <t>蒋宇飞Q4-Q1热潮</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="360" t="inlineStr">
+        <is>
+          <t>玻璃基板</t>
+        </is>
+      </c>
+      <c r="B126" s="360" t="inlineStr">
+        <is>
+          <t>2%</t>
+        </is>
+      </c>
+      <c r="C126" s="360" t="inlineStr">
+        <is>
+          <t>2027等业绩</t>
+        </is>
+      </c>
+      <c r="D126" s="360" t="inlineStr">
+        <is>
+          <t>2027</t>
+        </is>
+      </c>
+      <c r="E126" s="360" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F126" s="360" t="inlineStr">
+        <is>
+          <t>消息还在送验阶段</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="359" t="inlineStr">
+        <is>
+          <t>💡 修正规则：</t>
+        </is>
+      </c>
+      <c r="B128" s="356" t="n"/>
+      <c r="C128" s="356" t="n"/>
+      <c r="D128" s="356" t="n"/>
+      <c r="E128" s="356" t="n"/>
+      <c r="F128" s="356" t="n"/>
+      <c r="G128" s="356" t="n"/>
+      <c r="H128" s="357" t="n"/>
+    </row>
+    <row r="129">
+      <c r="A129" s="360" t="inlineStr">
+        <is>
+          <t>1. 每次监控后检查：P值变化&gt;5pp → 重新算盈亏比</t>
+        </is>
+      </c>
+      <c r="B129" s="356" t="n"/>
+      <c r="C129" s="356" t="n"/>
+      <c r="D129" s="356" t="n"/>
+      <c r="E129" s="356" t="n"/>
+      <c r="F129" s="356" t="n"/>
+      <c r="G129" s="356" t="n"/>
+      <c r="H129" s="357" t="n"/>
+    </row>
+    <row r="130">
+      <c r="A130" s="360" t="inlineStr">
+        <is>
+          <t>2. 价格异动：标的涨&gt;20%或跌&gt;15% → 评估是否调整仓位</t>
+        </is>
+      </c>
+      <c r="B130" s="356" t="n"/>
+      <c r="C130" s="356" t="n"/>
+      <c r="D130" s="356" t="n"/>
+      <c r="E130" s="356" t="n"/>
+      <c r="F130" s="356" t="n"/>
+      <c r="G130" s="356" t="n"/>
+      <c r="H130" s="357" t="n"/>
+    </row>
+    <row r="131">
+      <c r="A131" s="360" t="inlineStr">
+        <is>
+          <t>3. 重大事件：新信源/政策/财报 → 重新排序优先级</t>
+        </is>
+      </c>
+      <c r="B131" s="356" t="n"/>
+      <c r="C131" s="356" t="n"/>
+      <c r="D131" s="356" t="n"/>
+      <c r="E131" s="356" t="n"/>
+      <c r="F131" s="356" t="n"/>
+      <c r="G131" s="356" t="n"/>
+      <c r="H131" s="357" t="n"/>
+    </row>
+    <row r="132">
+      <c r="A132" s="360" t="inlineStr">
+        <is>
+          <t>4. 机器人定投逻辑：方向确定但短期追高盈亏比差，分批进摊低成本</t>
+        </is>
+      </c>
+      <c r="B132" s="356" t="n"/>
+      <c r="C132" s="356" t="n"/>
+      <c r="D132" s="356" t="n"/>
+      <c r="E132" s="356" t="n"/>
+      <c r="F132" s="356" t="n"/>
+      <c r="G132" s="356" t="n"/>
+      <c r="H132" s="357" t="n"/>
+    </row>
   </sheetData>
+  <mergeCells count="7">
+    <mergeCell ref="A131:H131"/>
+    <mergeCell ref="A130:H130"/>
+    <mergeCell ref="A129:H129"/>
+    <mergeCell ref="A117:H117"/>
+    <mergeCell ref="A128:H128"/>
+    <mergeCell ref="A132:H132"/>
+    <mergeCell ref="A118:H118"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/持仓贝叶斯跟踪.xlsx
+++ b/持仓贝叶斯跟踪.xlsx
@@ -30,7 +30,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="60">
+  <fonts count="63">
     <font>
       <name val="Calibri"/>
       <charset val="1"/>
@@ -458,6 +458,17 @@
       <b val="1"/>
       <sz val="10"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFD700"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <sz val="9"/>
+    </font>
+    <font>
+      <sz val="8"/>
+    </font>
   </fonts>
   <fills count="32">
     <fill>
@@ -818,7 +829,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="361">
+  <cellXfs count="365">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -1887,6 +1898,14 @@
     </xf>
     <xf numFmtId="0" fontId="58" fillId="31" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="60" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -2617,7 +2636,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:H116"/>
+  <dimension ref="A1:H133"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6171875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="18" customWidth="1" style="332" min="1" max="8"/>
@@ -3571,22 +3590,125 @@
     <row r="114" ht="26.25" customHeight="1" s="183"/>
     <row r="115" ht="26.25" customHeight="1" s="183"/>
     <row r="116" ht="15" customHeight="1" s="183"/>
-    <row r="117" ht="20.1" customHeight="1" s="183"/>
-    <row r="118" ht="15" customHeight="1" s="183"/>
-    <row r="119" ht="15" customHeight="1" s="183"/>
-    <row r="120" ht="26.25" customHeight="1" s="183"/>
-    <row r="121" ht="26.25" customHeight="1" s="183"/>
-    <row r="122" ht="15" customHeight="1" s="183"/>
-    <row r="123" ht="15" customHeight="1" s="183"/>
-    <row r="124" ht="26.25" customHeight="1" s="183"/>
-    <row r="125" ht="15" customHeight="1" s="183"/>
-    <row r="127" ht="15" customHeight="1" s="183"/>
-    <row r="128" ht="15" customHeight="1" s="183"/>
-    <row r="129" ht="26.25" customHeight="1" s="183"/>
-    <row r="130" ht="15" customHeight="1" s="183"/>
-    <row r="131" ht="15" customHeight="1" s="183"/>
-    <row r="132" ht="15" customHeight="1" s="183"/>
-    <row r="133" ht="15" customHeight="1" s="183"/>
+    <row r="117" ht="20.1" customHeight="1" s="183">
+      <c r="A117" s="361" t="inlineStr">
+        <is>
+          <t>📊 6/7 20:00小结</t>
+        </is>
+      </c>
+    </row>
+    <row r="118" ht="15" customHeight="1" s="183">
+      <c r="A118" s="362" t="inlineStr">
+        <is>
+          <t>• 抓取50条沾边(抖音12+知乎18+B站0) 转录3/3</t>
+        </is>
+      </c>
+    </row>
+    <row r="119" ht="15" customHeight="1" s="183">
+      <c r="A119" s="362" t="inlineStr">
+        <is>
+          <t>• 芯片虚P+1pp: 蒋宇飞GTC大会-AI基建3年不下车/端侧AI来临/物理AI需3年</t>
+        </is>
+      </c>
+    </row>
+    <row r="120" ht="26.25" customHeight="1" s="183">
+      <c r="A120" s="362" t="inlineStr">
+        <is>
+          <t>• 避险+1pp: 环中星鉴11条-非农超预期/黄金大跌/SpaceX+OpenAI天价IPO</t>
+        </is>
+      </c>
+    </row>
+    <row r="121" ht="26.25" customHeight="1" s="183">
+      <c r="A121" s="362" t="inlineStr">
+        <is>
+          <t>• 蒋宇飞端侧AI芯片机会=万亿市值级别(强烈看好)</t>
+        </is>
+      </c>
+    </row>
+    <row r="122" ht="15" customHeight="1" s="183">
+      <c r="A122" s="361" t="inlineStr">
+        <is>
+          <t>📊 6/7 20:00小结</t>
+        </is>
+      </c>
+    </row>
+    <row r="123" ht="15" customHeight="1" s="183">
+      <c r="A123" s="362" t="inlineStr">
+        <is>
+          <t>• 抓取50条沾边(抖音12+知乎18+B站0) 转录3/3 分析3/3</t>
+        </is>
+      </c>
+    </row>
+    <row r="124" ht="26.25" customHeight="1" s="183">
+      <c r="A124" s="362" t="inlineStr">
+        <is>
+          <t>• 蒋宇飞GTC大会: AI基建3年不死/端侧AI来临/物理AI3年后 → 芯片虚P+1pp</t>
+        </is>
+      </c>
+    </row>
+    <row r="125" ht="15" customHeight="1" s="183">
+      <c r="A125" s="362" t="inlineStr">
+        <is>
+          <t>• 环中星鉴11条: 非农超预期+黄金大跌+AI天价IPO → 避险短期承压</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="362" t="inlineStr">
+        <is>
+          <t>• 拿幸14条: OpenAI记忆架构+Anthropic自研AI → AI产业链持续加速(不重复加分)</t>
+        </is>
+      </c>
+    </row>
+    <row r="127" ht="15" customHeight="1" s="183">
+      <c r="A127" s="362" t="inlineStr">
+        <is>
+          <t>• 伊娃6条+生猪贸易3条+猪猪女王2条: 养殖面稳定(不调整)</t>
+        </is>
+      </c>
+    </row>
+    <row r="128" ht="15" customHeight="1" s="183">
+      <c r="A128" s="361" t="inlineStr">
+        <is>
+          <t>📊 6/7 20:00小结</t>
+        </is>
+      </c>
+    </row>
+    <row r="129" ht="26.25" customHeight="1" s="183">
+      <c r="A129" s="362" t="inlineStr">
+        <is>
+          <t>• 抓取50条沾边(抖音12+知乎18+B站0) 转录3/3 分析3/3</t>
+        </is>
+      </c>
+    </row>
+    <row r="130" ht="15" customHeight="1" s="183">
+      <c r="A130" s="362" t="inlineStr">
+        <is>
+          <t>• 蒋宇飞GTC大会: AI基建3年不死/端侧AI来临/物理AI3年后 → 芯片虚P+1pp</t>
+        </is>
+      </c>
+    </row>
+    <row r="131" ht="15" customHeight="1" s="183">
+      <c r="A131" s="362" t="inlineStr">
+        <is>
+          <t>• 拿幸14条: OpenAI记忆架构+AI从AGI跨向AGI → 芯片方向但不重复加分</t>
+        </is>
+      </c>
+    </row>
+    <row r="132" ht="15" customHeight="1" s="183">
+      <c r="A132" s="362" t="inlineStr">
+        <is>
+          <t>• 伊娃6条+生猪贸易3条+猪猪女王2条: 养殖面稳定(不调整)</t>
+        </is>
+      </c>
+    </row>
+    <row r="133" ht="15" customHeight="1" s="183">
+      <c r="A133" s="362" t="inlineStr">
+        <is>
+          <t>• 环中星鉴11条: 非农超预期+黄金大跌+AI天价IPO → 避险短期承压</t>
+        </is>
+      </c>
+    </row>
     <row r="134" ht="26.25" customHeight="1" s="183"/>
     <row r="135" ht="15" customHeight="1" s="183"/>
     <row r="136" ht="29.85" customHeight="1" s="183"/>
@@ -3745,21 +3867,38 @@
     <row r="309" ht="15" customHeight="1" s="183"/>
     <row r="310" ht="15" customHeight="1" s="183"/>
   </sheetData>
-  <mergeCells count="14">
+  <mergeCells count="31">
+    <mergeCell ref="A126:G126"/>
+    <mergeCell ref="A122:G122"/>
+    <mergeCell ref="A107:H107"/>
+    <mergeCell ref="A131:G131"/>
+    <mergeCell ref="A125:G125"/>
+    <mergeCell ref="B15:H15"/>
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A121:G121"/>
+    <mergeCell ref="A117:G117"/>
+    <mergeCell ref="A127:G127"/>
+    <mergeCell ref="A130:G130"/>
+    <mergeCell ref="B16:H16"/>
     <mergeCell ref="A12:H12"/>
     <mergeCell ref="A18:H18"/>
+    <mergeCell ref="A123:G123"/>
+    <mergeCell ref="A119:G119"/>
+    <mergeCell ref="A132:G132"/>
+    <mergeCell ref="A124:G124"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A128:G128"/>
+    <mergeCell ref="A97:H97"/>
+    <mergeCell ref="A17:H17"/>
+    <mergeCell ref="A133:G133"/>
     <mergeCell ref="B14:H14"/>
+    <mergeCell ref="A118:G118"/>
     <mergeCell ref="B13:H13"/>
+    <mergeCell ref="A120:G120"/>
     <mergeCell ref="A20:H20"/>
     <mergeCell ref="A96:H96"/>
-    <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A107:H107"/>
-    <mergeCell ref="B16:H16"/>
     <mergeCell ref="B116:H116"/>
-    <mergeCell ref="B15:H15"/>
-    <mergeCell ref="A1:H1"/>
-    <mergeCell ref="A97:H97"/>
-    <mergeCell ref="A17:H17"/>
+    <mergeCell ref="A129:G129"/>
   </mergeCells>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -10147,8 +10286,8 @@
     <mergeCell ref="A129:H129"/>
     <mergeCell ref="A117:H117"/>
     <mergeCell ref="A128:H128"/>
+    <mergeCell ref="A118:H118"/>
     <mergeCell ref="A132:H132"/>
-    <mergeCell ref="A118:H118"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -10160,7 +10299,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:L260"/>
+  <dimension ref="A1:L263"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="10.4921875" defaultRowHeight="12.75" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="18" customWidth="1" style="332" min="1" max="12"/>
@@ -14999,6 +15138,93 @@
       <c r="A260" s="332" t="inlineStr">
         <is>
           <t xml:space="preserve">  恒科: 33-1=32%</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" s="363" t="inlineStr">
+        <is>
+          <t>2026-06-07
+虚P+1pp
+【来源:蒋宇飞6/7抖音】GTC大会5大信号:
+1.算利即利润-XAI年租金145亿2年回本
+2.2026AI训练营业额5000亿美金
+3.英伟达系统级交付-单卖算力卡公司将举步维艰
+4.RUBY芯片Q4交付-Agent时代来临
+5.端侧AI芯片=万亿市值机会
+6.物理AI需3年
+结论:AI基建3年打死不下车</t>
+        </is>
+      </c>
+      <c r="F261" s="363" t="inlineStr">
+        <is>
+          <t>2026-06-07
++1pp
+【来源:环中星鉴知乎11条】
+1.非农超预期-美股大跌纳指跌1100点
+2.黄金大跌-短期承压
+3.SpaceX+OpenAI+Anthropic天价IPO
+4.富裕群体消费信心下降
+5.中东主权资金出售集股
+结论:短期避险但长期AI泡沫待爆</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" s="364" t="inlineStr">
+        <is>
+          <t>2026-06-07
+虚P+1pp
+蒋宇飞GTC大会5大信号:
+1.算利即利润-XAI年租金145亿2年回本
+2.2026AI训练营业额5000亿美金
+3.英伟达系统级交付-单卖算力卡公司举步维艰
+4.RUBY芯片Q4-Agent时代
+5.端侧AI芯片=万亿市值机会
+6.物理AI=3年后
+结论:AI基建3年打死不下车</t>
+        </is>
+      </c>
+      <c r="F262" s="364" t="inlineStr">
+        <is>
+          <t>2026-06-07
+-1pp
+环中星鉴知乎11条:
+1.非农超预期-纳指跌1100点
+2.黄金大跌-短期承压
+3.SpaceX+OpenAI天价IPO水分
+4.富裕群体消费信心下降
+5.中东主权资金出售集股
+结论:短期避险承压但长期AI泡沫待爆</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" s="364" t="inlineStr">
+        <is>
+          <t>2026-06-07
+虚P+1pp
+蒋宇飞GTC大会5大信号:
+1.算利即利润-XAI年租金145亿2年回本
+2.2026AI训练营业额5000亿美金
+3.英伟达系统级交付-单卖算力卡公司举步维艰
+4.RUBY芯片Q4-Agent时代
+5.端侧AI芯片=万亿市值机会
+6.物理AI=3年后
+结论:AI基建3年打死不下车</t>
+        </is>
+      </c>
+      <c r="F263" s="364" t="inlineStr">
+        <is>
+          <t>2026-06-07
+-1pp
+环中星鉴知乎11条:
+1.非农超预期-纳指跌1100点
+2.黄金大跌-短期承压
+3.SpaceX+OpenAI天价IPO水分
+4.富裕群体消费信心下降
+5.中东主权资金出售集股
+结论:短期避险承压但长期AI泡沫待爆</t>
         </is>
       </c>
     </row>

--- a/持仓贝叶斯跟踪.xlsx
+++ b/持仓贝叶斯跟踪.xlsx
@@ -30,7 +30,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="63">
+  <fonts count="67">
     <font>
       <name val="Calibri"/>
       <charset val="1"/>
@@ -469,8 +469,23 @@
     <font>
       <sz val="8"/>
     </font>
+    <font/>
+    <font>
+      <b val="1"/>
+      <color rgb="00FF0000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FF6600"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="32">
+  <fills count="34">
     <fill>
       <patternFill/>
     </fill>
@@ -657,6 +672,18 @@
         <bgColor rgb="0016213e"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF0F0"/>
+        <bgColor rgb="00FFF0F0"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF8F0"/>
+        <bgColor rgb="00FFF8F0"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="16">
     <border>
@@ -829,7 +856,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="365">
+  <cellXfs count="371">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -1905,6 +1932,20 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="62" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="64" fillId="32" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="32" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="65" fillId="33" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="33" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="66" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2636,7 +2677,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:H133"/>
+  <dimension ref="A1:H199"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6171875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="18" customWidth="1" style="332" min="1" max="8"/>
@@ -3543,6 +3584,7 @@
     <row r="63" ht="48" customHeight="1" s="183"/>
     <row r="64" ht="48" customHeight="1" s="183"/>
     <row r="65" ht="63.75" customHeight="1" s="183"/>
+    <row r="66"/>
     <row r="67" ht="16.5" customHeight="1" s="183"/>
     <row r="68" ht="48" customHeight="1" s="183"/>
     <row r="69" ht="32.25" customHeight="1" s="183"/>
@@ -3554,6 +3596,7 @@
     <row r="75" ht="17.15" customHeight="1" s="183"/>
     <row r="76" ht="17.15" customHeight="1" s="183"/>
     <row r="77" ht="15" customHeight="1" s="183"/>
+    <row r="78"/>
     <row r="79" ht="39" customHeight="1" s="183"/>
     <row r="80" ht="39" customHeight="1" s="183"/>
     <row r="81" ht="51.75" customHeight="1" s="183"/>
@@ -3562,6 +3605,7 @@
     <row r="84" ht="15" customHeight="1" s="183"/>
     <row r="85" ht="15" customHeight="1" s="183"/>
     <row r="86" ht="26.25" customHeight="1" s="183"/>
+    <row r="87"/>
     <row r="88" ht="39" customHeight="1" s="183"/>
     <row r="89" ht="26.25" customHeight="1" s="183"/>
     <row r="90" ht="26.25" customHeight="1" s="183"/>
@@ -3582,6 +3626,7 @@
     <row r="105" ht="26.25" customHeight="1" s="183"/>
     <row r="106" ht="26.25" customHeight="1" s="183"/>
     <row r="107" ht="15" customHeight="1" s="183"/>
+    <row r="108"/>
     <row r="109" ht="15" customHeight="1" s="183"/>
     <row r="110" ht="26.25" customHeight="1" s="183"/>
     <row r="111" ht="26.25" customHeight="1" s="183"/>
@@ -3668,69 +3713,219 @@
       </c>
     </row>
     <row r="128" ht="15" customHeight="1" s="183">
-      <c r="A128" s="361" t="inlineStr">
-        <is>
-          <t>📊 6/7 20:00小结</t>
-        </is>
-      </c>
+      <c r="A128" s="365" t="inlineStr">
+        <is>
+          <t>🔴 6/7 蒋宇飞GTC大会·5大信号（顶级信源·重大）</t>
+        </is>
+      </c>
+      <c r="B128" s="366" t="n"/>
+      <c r="C128" s="366" t="n"/>
+      <c r="D128" s="366" t="n"/>
+      <c r="E128" s="366" t="n"/>
+      <c r="F128" s="366" t="n"/>
+      <c r="G128" s="366" t="n"/>
     </row>
     <row r="129" ht="26.25" customHeight="1" s="183">
-      <c r="A129" s="362" t="inlineStr">
-        <is>
-          <t>• 抓取50条沾边(抖音12+知乎18+B站0) 转录3/3 分析3/3</t>
-        </is>
-      </c>
+      <c r="A129" s="365" t="inlineStr">
+        <is>
+          <t>信号1：AI基建3年不死（时间维度）</t>
+        </is>
+      </c>
+      <c r="B129" s="366" t="n"/>
+      <c r="C129" s="366" t="n"/>
+      <c r="D129" s="366" t="n"/>
+      <c r="E129" s="366" t="n"/>
+      <c r="F129" s="366" t="n"/>
+      <c r="G129" s="366" t="n"/>
     </row>
     <row r="130" ht="15" customHeight="1" s="183">
-      <c r="A130" s="362" t="inlineStr">
-        <is>
-          <t>• 蒋宇飞GTC大会: AI基建3年不死/端侧AI来临/物理AI3年后 → 芯片虚P+1pp</t>
+      <c r="A130" s="367" t="inlineStr">
+        <is>
+          <t>XAI一期投200亿美金，万卡集群年租金145亿美金，2年回本。2026AI训练营业额5000亿美金（去年2000亿）。蒋宇飞原话：3年打死不下车，一生仅此一两次机会。→ 芯片虚P+1pp</t>
         </is>
       </c>
     </row>
     <row r="131" ht="15" customHeight="1" s="183">
-      <c r="A131" s="362" t="inlineStr">
-        <is>
-          <t>• 拿幸14条: OpenAI记忆架构+AI从AGI跨向AGI → 芯片方向但不重复加分</t>
-        </is>
-      </c>
+      <c r="A131" s="365" t="inlineStr">
+        <is>
+          <t>信号2：英伟达从卖卡→卖系统（产业链结构剧变）</t>
+        </is>
+      </c>
+      <c r="B131" s="366" t="n"/>
+      <c r="C131" s="366" t="n"/>
+      <c r="D131" s="366" t="n"/>
+      <c r="E131" s="366" t="n"/>
+      <c r="F131" s="366" t="n"/>
+      <c r="G131" s="366" t="n"/>
     </row>
     <row r="132" ht="15" customHeight="1" s="183">
-      <c r="A132" s="362" t="inlineStr">
-        <is>
-          <t>• 伊娃6条+生猪贸易3条+猪猪女王2条: 养殖面稳定(不调整)</t>
+      <c r="A132" s="367" t="inlineStr">
+        <is>
+          <t>英伟达从卖H100/H200单卡改为卖RUBY系统级交付（总包商模式）。国内单卖算力卡公司举步维艰。2027升腾+平头哥带云交付冲击纯GPU公司。液冷配套受益。→ 芯片产业链分化</t>
         </is>
       </c>
     </row>
     <row r="133" ht="15" customHeight="1" s="183">
-      <c r="A133" s="362" t="inlineStr">
-        <is>
-          <t>• 环中星鉴11条: 非农超预期+黄金大跌+AI天价IPO → 避险短期承压</t>
-        </is>
-      </c>
-    </row>
-    <row r="134" ht="26.25" customHeight="1" s="183"/>
-    <row r="135" ht="15" customHeight="1" s="183"/>
-    <row r="136" ht="29.85" customHeight="1" s="183"/>
-    <row r="137" ht="15" customHeight="1" s="183"/>
-    <row r="138" ht="26.25" customHeight="1" s="183"/>
-    <row r="139" ht="15" customHeight="1" s="183"/>
-    <row r="140" ht="26.25" customHeight="1" s="183"/>
+      <c r="A133" s="368" t="inlineStr">
+        <is>
+          <t>信号3：RUBY芯片Q4交付=Agent时代来临</t>
+        </is>
+      </c>
+      <c r="B133" s="369" t="n"/>
+      <c r="C133" s="369" t="n"/>
+      <c r="D133" s="369" t="n"/>
+      <c r="E133" s="369" t="n"/>
+      <c r="F133" s="369" t="n"/>
+      <c r="G133" s="369" t="n"/>
+    </row>
+    <row r="134" ht="26.25" customHeight="1" s="183">
+      <c r="A134" s="367" t="inlineStr">
+        <is>
+          <t>RUBY含VA-CPU，净存计算CPU时代来临。AI应用大概率诞生在中国（用户多+数据链深）。笔记本年换机上亿台，CPU用量大毛利高。→ 芯片/端侧AI方向</t>
+        </is>
+      </c>
+    </row>
+    <row r="135" ht="15" customHeight="1" s="183">
+      <c r="A135" s="368" t="inlineStr">
+        <is>
+          <t>信号4：端侧AI来临=万亿市值新赛道</t>
+        </is>
+      </c>
+      <c r="B135" s="369" t="n"/>
+      <c r="C135" s="369" t="n"/>
+      <c r="D135" s="369" t="n"/>
+      <c r="E135" s="369" t="n"/>
+      <c r="F135" s="369" t="n"/>
+      <c r="G135" s="369" t="n"/>
+    </row>
+    <row r="136" ht="29.85" customHeight="1" s="183">
+      <c r="A136" s="367" t="inlineStr">
+        <is>
+          <t>RTX可跑本地1200亿参数大模型。端侧AI芯片=全新赛道。蒋宇飞：端侧AI芯片前两位市值不亚于光模块龙头，会出现万亿市值企业。→ 待重仓：端侧AI芯片</t>
+        </is>
+      </c>
+    </row>
+    <row r="137" ht="15" customHeight="1" s="183">
+      <c r="A137" s="367" t="inlineStr">
+        <is>
+          <t>信号5：物理AI/人形机器人=3年后爆发</t>
+        </is>
+      </c>
+    </row>
+    <row r="138" ht="26.25" customHeight="1" s="183">
+      <c r="A138" s="367" t="inlineStr">
+        <is>
+          <t>黄仁勋发布GR00T人形机器人平台。蒋宇飞判断：物理AI还需3年。→ 机器人虚P方向确认</t>
+        </is>
+      </c>
+    </row>
+    <row r="139" ht="15" customHeight="1" s="183">
+      <c r="A139" s="370" t="inlineStr">
+        <is>
+          <t>📌 拿幸：OpenAI记忆架构DreamingV3</t>
+        </is>
+      </c>
+    </row>
+    <row r="140" ht="26.25" customHeight="1" s="183">
+      <c r="A140" s="367" t="inlineStr">
+        <is>
+          <t>10亿免费用户获后台记忆能力，算力成本降5倍。记忆=数据时代新领土，谁控制10亿人记忆谁控制AI入口。Anthropic/Google追赶窗口≤12个月。→ 芯片方向不重复加分</t>
+        </is>
+      </c>
+    </row>
     <row r="141" ht="26.25" customHeight="1" s="183"/>
-    <row r="142" ht="39" customHeight="1" s="183"/>
-    <row r="143" ht="17.15" customHeight="1" s="183"/>
-    <row r="144" ht="17.25" customHeight="1" s="183"/>
-    <row r="145" ht="16.5" customHeight="1" s="183"/>
-    <row r="146" ht="16.5" customHeight="1" s="183"/>
-    <row r="147" ht="16.5" customHeight="1" s="183"/>
-    <row r="148" ht="16.5" customHeight="1" s="183"/>
-    <row r="149" ht="16.5" customHeight="1" s="183"/>
-    <row r="150" ht="16.5" customHeight="1" s="183"/>
+    <row r="142" ht="39" customHeight="1" s="183">
+      <c r="A142" s="370" t="inlineStr">
+        <is>
+          <t>📊 环中星鉴知乎11条沾边（05/20-06/07）</t>
+        </is>
+      </c>
+    </row>
+    <row r="143" ht="17.15" customHeight="1" s="183">
+      <c r="A143" s="367" t="inlineStr">
+        <is>
+          <t>• 06/07 SpaceX+OpenAI+Anthropic天价IPO → AI泡沫水分待爆</t>
+        </is>
+      </c>
+    </row>
+    <row r="144" ht="17.25" customHeight="1" s="183">
+      <c r="A144" s="367" t="inlineStr">
+        <is>
+          <t>• 06/06 非农超预期+纳指跌1100点+加息预期 → 美股短期承压</t>
+        </is>
+      </c>
+    </row>
+    <row r="145" ht="16.5" customHeight="1" s="183">
+      <c r="A145" s="367" t="inlineStr">
+        <is>
+          <t>• 06/05 博通AI收入增200%但股价跌15% → 芯片高估值回调</t>
+        </is>
+      </c>
+    </row>
+    <row r="146" ht="16.5" customHeight="1" s="183">
+      <c r="A146" s="367" t="inlineStr">
+        <is>
+          <t>• 06/04 全球央行重新扫货黄金 → 稀金/避险+1pp</t>
+        </is>
+      </c>
+    </row>
+    <row r="147" ht="16.5" customHeight="1" s="183">
+      <c r="A147" s="367" t="inlineStr">
+        <is>
+          <t>• 06/03 黄金替代美债成第一大储备(27%&gt;22%) → 稀金长期趋势</t>
+        </is>
+      </c>
+    </row>
+    <row r="148" ht="16.5" customHeight="1" s="183">
+      <c r="A148" s="367" t="inlineStr">
+        <is>
+          <t>• 06/01 富裕群体消费信心下降+中东出售集股 → 宏观偏空</t>
+        </is>
+      </c>
+    </row>
+    <row r="149" ht="16.5" customHeight="1" s="183">
+      <c r="A149" s="367" t="inlineStr">
+        <is>
+          <t>• 05/29 美伊60天停火+油价跳水 → 能源短期利空</t>
+        </is>
+      </c>
+    </row>
+    <row r="150" ht="16.5" customHeight="1" s="183">
+      <c r="A150" s="367" t="inlineStr">
+        <is>
+          <t>• 05/28 黄金跳水跌破4400 → 避险短期承压</t>
+        </is>
+      </c>
+    </row>
     <row r="151" ht="16.5" customHeight="1" s="183"/>
-    <row r="152" ht="16.5" customHeight="1" s="183"/>
-    <row r="153" ht="16.5" customHeight="1" s="183"/>
-    <row r="154" ht="26.85" customHeight="1" s="183"/>
-    <row r="155" ht="15" customHeight="1" s="183"/>
+    <row r="152" ht="16.5" customHeight="1" s="183">
+      <c r="A152" s="370" t="inlineStr">
+        <is>
+          <t>📋 其他沾边</t>
+        </is>
+      </c>
+    </row>
+    <row r="153" ht="16.5" customHeight="1" s="183">
+      <c r="A153" s="367" t="inlineStr">
+        <is>
+          <t>• 伊娃6条+生猪贸易3条+猪猪女王2条：养殖面稳定（不调整）</t>
+        </is>
+      </c>
+    </row>
+    <row r="154" ht="26.85" customHeight="1" s="183">
+      <c r="A154" s="367" t="inlineStr">
+        <is>
+          <t>• 宋鸿兵3条：摩尔定律瓶颈/油价/美伊谈判 → 已有覆盖</t>
+        </is>
+      </c>
+    </row>
+    <row r="155" ht="15" customHeight="1" s="183">
+      <c r="A155" s="367" t="inlineStr">
+        <is>
+          <t>• 岩松笔记2条：光伏+银行 → 不调整</t>
+        </is>
+      </c>
+    </row>
     <row r="156" ht="15" customHeight="1" s="183"/>
     <row r="157" ht="15" customHeight="1" s="183"/>
     <row r="158" ht="15" customHeight="1" s="183"/>
@@ -3741,13 +3936,19 @@
     <row r="163" ht="48.5" customHeight="1" s="183"/>
     <row r="164" ht="48.5" customHeight="1" s="183"/>
     <row r="165" ht="64.15000000000001" customHeight="1" s="183"/>
+    <row r="166"/>
     <row r="167" ht="17.15" customHeight="1" s="183"/>
     <row r="168" ht="48.5" customHeight="1" s="183"/>
     <row r="169" ht="32.8" customHeight="1" s="183"/>
     <row r="170" ht="48.5" customHeight="1" s="183"/>
     <row r="171" ht="32.8" customHeight="1" s="183"/>
+    <row r="172"/>
     <row r="173" ht="121.6" customHeight="1" s="183"/>
+    <row r="174"/>
+    <row r="175"/>
+    <row r="176"/>
     <row r="177" ht="15" customHeight="1" s="183"/>
+    <row r="178"/>
     <row r="179" ht="39.55" customHeight="1" s="183"/>
     <row r="180" ht="39.55" customHeight="1" s="183"/>
     <row r="181" ht="52.2" customHeight="1" s="183"/>
@@ -3756,6 +3957,7 @@
     <row r="184" ht="15" customHeight="1" s="183"/>
     <row r="185" ht="15" customHeight="1" s="183"/>
     <row r="186" ht="26.85" customHeight="1" s="183"/>
+    <row r="187"/>
     <row r="188" ht="39.55" customHeight="1" s="183"/>
     <row r="189" ht="26.85" customHeight="1" s="183"/>
     <row r="190" ht="26.85" customHeight="1" s="183"/>
@@ -3764,6 +3966,8 @@
     <row r="193" ht="26.85" customHeight="1" s="183"/>
     <row r="194" ht="39.55" customHeight="1" s="183"/>
     <row r="195" ht="39.55" customHeight="1" s="183"/>
+    <row r="196"/>
+    <row r="197"/>
     <row r="198" ht="18.65" customHeight="1" s="183"/>
     <row r="199" ht="15" customHeight="1" s="183"/>
     <row r="200" ht="15" customHeight="1" s="183"/>
@@ -3870,8 +4074,8 @@
   <mergeCells count="31">
     <mergeCell ref="A126:G126"/>
     <mergeCell ref="A122:G122"/>
+    <mergeCell ref="A131:G131"/>
     <mergeCell ref="A107:H107"/>
-    <mergeCell ref="A131:G131"/>
     <mergeCell ref="A125:G125"/>
     <mergeCell ref="B15:H15"/>
     <mergeCell ref="A1:H1"/>
@@ -10299,7 +10503,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:L263"/>
+  <dimension ref="A1:L299"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="10.4921875" defaultRowHeight="12.75" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="18" customWidth="1" style="332" min="1" max="12"/>
@@ -15200,34 +15404,97 @@
       </c>
     </row>
     <row r="263">
-      <c r="A263" s="364" t="inlineStr">
+      <c r="A263" s="365" t="inlineStr">
         <is>
           <t>2026-06-07
+[蒋宇飞GTC·信号1]
 虚P+1pp
-蒋宇飞GTC大会5大信号:
-1.算利即利润-XAI年租金145亿2年回本
-2.2026AI训练营业额5000亿美金
-3.英伟达系统级交付-单卖算力卡公司举步维艰
-4.RUBY芯片Q4-Agent时代
-5.端侧AI芯片=万亿市值机会
-6.物理AI=3年后
-结论:AI基建3年打死不下车</t>
-        </is>
-      </c>
-      <c r="F263" s="364" t="inlineStr">
+AI基建3年不死：XAI年租金145亿2年回本，2026训练营业额5000亿。蒋宇飞：3年打死不下车</t>
+        </is>
+      </c>
+      <c r="F263" s="364" t="n"/>
+    </row>
+    <row r="264">
+      <c r="A264" s="365" t="inlineStr">
         <is>
           <t>2026-06-07
--1pp
-环中星鉴知乎11条:
-1.非农超预期-纳指跌1100点
-2.黄金大跌-短期承压
-3.SpaceX+OpenAI天价IPO水分
-4.富裕群体消费信心下降
-5.中东主权资金出售集股
-结论:短期避险承压但长期AI泡沫待爆</t>
-        </is>
-      </c>
-    </row>
+[蒋宇飞GTC·信号2]
+产业链分化
+英伟达卖卡→卖系统。单卖算力卡公司举步维艰。2027升腾+平头哥带云交付冲击纯GPU</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" s="368" t="inlineStr">
+        <is>
+          <t>2026-06-07
+[蒋宇飞GTC·信号3+4]
+端侧AI=万亿赛道
+RUBY含VA-CPU→Agent时代。RTX跑本地1200亿模型。端侧AI芯片前两位=万亿市值</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" s="368" t="inlineStr">
+        <is>
+          <t>2026-06-07
+[蒋宇飞GTC·信号5]
+物理AI=3年后
+GR00T人形机器人平台。蒋宇飞：需3年。机器人虚P方向确认</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="F267" s="364" t="inlineStr">
+        <is>
+          <t>2026-06-07
+[环中星鉴]
++1pp
+黄金替代美债成第一大储备(27%&gt;22%)。全球央行扫货黄金。长期趋势确认</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="F268" s="364" t="inlineStr">
+        <is>
+          <t>2026-06-07
+[环中星鉴]
+-1pp短期
+非农超预期+纳指跌1100点。博通AI收入增200%股价跌15%。SpaceX+OpenAI天价IPO水分</t>
+        </is>
+      </c>
+    </row>
+    <row r="269"/>
+    <row r="270"/>
+    <row r="271"/>
+    <row r="272"/>
+    <row r="273"/>
+    <row r="274"/>
+    <row r="275"/>
+    <row r="276"/>
+    <row r="277"/>
+    <row r="278"/>
+    <row r="279"/>
+    <row r="280"/>
+    <row r="281"/>
+    <row r="282"/>
+    <row r="283"/>
+    <row r="284"/>
+    <row r="285"/>
+    <row r="286"/>
+    <row r="287"/>
+    <row r="288"/>
+    <row r="289"/>
+    <row r="290"/>
+    <row r="291"/>
+    <row r="292"/>
+    <row r="293"/>
+    <row r="294"/>
+    <row r="295"/>
+    <row r="296"/>
+    <row r="297"/>
+    <row r="298"/>
+    <row r="299"/>
   </sheetData>
   <mergeCells count="49">
     <mergeCell ref="A58:K58"/>

--- a/持仓贝叶斯跟踪.xlsx
+++ b/持仓贝叶斯跟踪.xlsx
@@ -30,7 +30,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="67">
+  <fonts count="63">
     <font>
       <name val="Calibri"/>
       <charset val="1"/>
@@ -469,23 +469,8 @@
     <font>
       <sz val="8"/>
     </font>
-    <font/>
-    <font>
-      <b val="1"/>
-      <color rgb="00FF0000"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <b val="1"/>
-      <color rgb="00FF6600"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <b val="1"/>
-      <sz val="10"/>
-    </font>
   </fonts>
-  <fills count="34">
+  <fills count="32">
     <fill>
       <patternFill/>
     </fill>
@@ -672,18 +657,6 @@
         <bgColor rgb="0016213e"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFF0F0"/>
-        <bgColor rgb="00FFF0F0"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFF8F0"/>
-        <bgColor rgb="00FFF8F0"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="16">
     <border>
@@ -856,7 +829,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="371">
+  <cellXfs count="365">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -1932,20 +1905,6 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="62" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="64" fillId="32" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="32" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="65" fillId="33" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="33" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="66" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2677,7 +2636,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:H199"/>
+  <dimension ref="A1:H133"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6171875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="18" customWidth="1" style="332" min="1" max="8"/>
@@ -3584,7 +3543,6 @@
     <row r="63" ht="48" customHeight="1" s="183"/>
     <row r="64" ht="48" customHeight="1" s="183"/>
     <row r="65" ht="63.75" customHeight="1" s="183"/>
-    <row r="66"/>
     <row r="67" ht="16.5" customHeight="1" s="183"/>
     <row r="68" ht="48" customHeight="1" s="183"/>
     <row r="69" ht="32.25" customHeight="1" s="183"/>
@@ -3596,7 +3554,6 @@
     <row r="75" ht="17.15" customHeight="1" s="183"/>
     <row r="76" ht="17.15" customHeight="1" s="183"/>
     <row r="77" ht="15" customHeight="1" s="183"/>
-    <row r="78"/>
     <row r="79" ht="39" customHeight="1" s="183"/>
     <row r="80" ht="39" customHeight="1" s="183"/>
     <row r="81" ht="51.75" customHeight="1" s="183"/>
@@ -3605,7 +3562,6 @@
     <row r="84" ht="15" customHeight="1" s="183"/>
     <row r="85" ht="15" customHeight="1" s="183"/>
     <row r="86" ht="26.25" customHeight="1" s="183"/>
-    <row r="87"/>
     <row r="88" ht="39" customHeight="1" s="183"/>
     <row r="89" ht="26.25" customHeight="1" s="183"/>
     <row r="90" ht="26.25" customHeight="1" s="183"/>
@@ -3626,7 +3582,6 @@
     <row r="105" ht="26.25" customHeight="1" s="183"/>
     <row r="106" ht="26.25" customHeight="1" s="183"/>
     <row r="107" ht="15" customHeight="1" s="183"/>
-    <row r="108"/>
     <row r="109" ht="15" customHeight="1" s="183"/>
     <row r="110" ht="26.25" customHeight="1" s="183"/>
     <row r="111" ht="26.25" customHeight="1" s="183"/>
@@ -3713,219 +3668,69 @@
       </c>
     </row>
     <row r="128" ht="15" customHeight="1" s="183">
-      <c r="A128" s="365" t="inlineStr">
-        <is>
-          <t>🔴 6/7 蒋宇飞GTC大会·5大信号（顶级信源·重大）</t>
-        </is>
-      </c>
-      <c r="B128" s="366" t="n"/>
-      <c r="C128" s="366" t="n"/>
-      <c r="D128" s="366" t="n"/>
-      <c r="E128" s="366" t="n"/>
-      <c r="F128" s="366" t="n"/>
-      <c r="G128" s="366" t="n"/>
+      <c r="A128" s="361" t="inlineStr">
+        <is>
+          <t>📊 6/7 20:00小结</t>
+        </is>
+      </c>
     </row>
     <row r="129" ht="26.25" customHeight="1" s="183">
-      <c r="A129" s="365" t="inlineStr">
-        <is>
-          <t>信号1：AI基建3年不死（时间维度）</t>
-        </is>
-      </c>
-      <c r="B129" s="366" t="n"/>
-      <c r="C129" s="366" t="n"/>
-      <c r="D129" s="366" t="n"/>
-      <c r="E129" s="366" t="n"/>
-      <c r="F129" s="366" t="n"/>
-      <c r="G129" s="366" t="n"/>
+      <c r="A129" s="362" t="inlineStr">
+        <is>
+          <t>• 抓取50条沾边(抖音12+知乎18+B站0) 转录3/3 分析3/3</t>
+        </is>
+      </c>
     </row>
     <row r="130" ht="15" customHeight="1" s="183">
-      <c r="A130" s="367" t="inlineStr">
-        <is>
-          <t>XAI一期投200亿美金，万卡集群年租金145亿美金，2年回本。2026AI训练营业额5000亿美金（去年2000亿）。蒋宇飞原话：3年打死不下车，一生仅此一两次机会。→ 芯片虚P+1pp</t>
+      <c r="A130" s="362" t="inlineStr">
+        <is>
+          <t>• 蒋宇飞GTC大会: AI基建3年不死/端侧AI来临/物理AI3年后 → 芯片虚P+1pp</t>
         </is>
       </c>
     </row>
     <row r="131" ht="15" customHeight="1" s="183">
-      <c r="A131" s="365" t="inlineStr">
-        <is>
-          <t>信号2：英伟达从卖卡→卖系统（产业链结构剧变）</t>
-        </is>
-      </c>
-      <c r="B131" s="366" t="n"/>
-      <c r="C131" s="366" t="n"/>
-      <c r="D131" s="366" t="n"/>
-      <c r="E131" s="366" t="n"/>
-      <c r="F131" s="366" t="n"/>
-      <c r="G131" s="366" t="n"/>
+      <c r="A131" s="362" t="inlineStr">
+        <is>
+          <t>• 拿幸14条: OpenAI记忆架构+AI从AGI跨向AGI → 芯片方向但不重复加分</t>
+        </is>
+      </c>
     </row>
     <row r="132" ht="15" customHeight="1" s="183">
-      <c r="A132" s="367" t="inlineStr">
-        <is>
-          <t>英伟达从卖H100/H200单卡改为卖RUBY系统级交付（总包商模式）。国内单卖算力卡公司举步维艰。2027升腾+平头哥带云交付冲击纯GPU公司。液冷配套受益。→ 芯片产业链分化</t>
+      <c r="A132" s="362" t="inlineStr">
+        <is>
+          <t>• 伊娃6条+生猪贸易3条+猪猪女王2条: 养殖面稳定(不调整)</t>
         </is>
       </c>
     </row>
     <row r="133" ht="15" customHeight="1" s="183">
-      <c r="A133" s="368" t="inlineStr">
-        <is>
-          <t>信号3：RUBY芯片Q4交付=Agent时代来临</t>
-        </is>
-      </c>
-      <c r="B133" s="369" t="n"/>
-      <c r="C133" s="369" t="n"/>
-      <c r="D133" s="369" t="n"/>
-      <c r="E133" s="369" t="n"/>
-      <c r="F133" s="369" t="n"/>
-      <c r="G133" s="369" t="n"/>
-    </row>
-    <row r="134" ht="26.25" customHeight="1" s="183">
-      <c r="A134" s="367" t="inlineStr">
-        <is>
-          <t>RUBY含VA-CPU，净存计算CPU时代来临。AI应用大概率诞生在中国（用户多+数据链深）。笔记本年换机上亿台，CPU用量大毛利高。→ 芯片/端侧AI方向</t>
-        </is>
-      </c>
-    </row>
-    <row r="135" ht="15" customHeight="1" s="183">
-      <c r="A135" s="368" t="inlineStr">
-        <is>
-          <t>信号4：端侧AI来临=万亿市值新赛道</t>
-        </is>
-      </c>
-      <c r="B135" s="369" t="n"/>
-      <c r="C135" s="369" t="n"/>
-      <c r="D135" s="369" t="n"/>
-      <c r="E135" s="369" t="n"/>
-      <c r="F135" s="369" t="n"/>
-      <c r="G135" s="369" t="n"/>
-    </row>
-    <row r="136" ht="29.85" customHeight="1" s="183">
-      <c r="A136" s="367" t="inlineStr">
-        <is>
-          <t>RTX可跑本地1200亿参数大模型。端侧AI芯片=全新赛道。蒋宇飞：端侧AI芯片前两位市值不亚于光模块龙头，会出现万亿市值企业。→ 待重仓：端侧AI芯片</t>
-        </is>
-      </c>
-    </row>
-    <row r="137" ht="15" customHeight="1" s="183">
-      <c r="A137" s="367" t="inlineStr">
-        <is>
-          <t>信号5：物理AI/人形机器人=3年后爆发</t>
-        </is>
-      </c>
-    </row>
-    <row r="138" ht="26.25" customHeight="1" s="183">
-      <c r="A138" s="367" t="inlineStr">
-        <is>
-          <t>黄仁勋发布GR00T人形机器人平台。蒋宇飞判断：物理AI还需3年。→ 机器人虚P方向确认</t>
-        </is>
-      </c>
-    </row>
-    <row r="139" ht="15" customHeight="1" s="183">
-      <c r="A139" s="370" t="inlineStr">
-        <is>
-          <t>📌 拿幸：OpenAI记忆架构DreamingV3</t>
-        </is>
-      </c>
-    </row>
-    <row r="140" ht="26.25" customHeight="1" s="183">
-      <c r="A140" s="367" t="inlineStr">
-        <is>
-          <t>10亿免费用户获后台记忆能力，算力成本降5倍。记忆=数据时代新领土，谁控制10亿人记忆谁控制AI入口。Anthropic/Google追赶窗口≤12个月。→ 芯片方向不重复加分</t>
-        </is>
-      </c>
-    </row>
+      <c r="A133" s="362" t="inlineStr">
+        <is>
+          <t>• 环中星鉴11条: 非农超预期+黄金大跌+AI天价IPO → 避险短期承压</t>
+        </is>
+      </c>
+    </row>
+    <row r="134" ht="26.25" customHeight="1" s="183"/>
+    <row r="135" ht="15" customHeight="1" s="183"/>
+    <row r="136" ht="29.85" customHeight="1" s="183"/>
+    <row r="137" ht="15" customHeight="1" s="183"/>
+    <row r="138" ht="26.25" customHeight="1" s="183"/>
+    <row r="139" ht="15" customHeight="1" s="183"/>
+    <row r="140" ht="26.25" customHeight="1" s="183"/>
     <row r="141" ht="26.25" customHeight="1" s="183"/>
-    <row r="142" ht="39" customHeight="1" s="183">
-      <c r="A142" s="370" t="inlineStr">
-        <is>
-          <t>📊 环中星鉴知乎11条沾边（05/20-06/07）</t>
-        </is>
-      </c>
-    </row>
-    <row r="143" ht="17.15" customHeight="1" s="183">
-      <c r="A143" s="367" t="inlineStr">
-        <is>
-          <t>• 06/07 SpaceX+OpenAI+Anthropic天价IPO → AI泡沫水分待爆</t>
-        </is>
-      </c>
-    </row>
-    <row r="144" ht="17.25" customHeight="1" s="183">
-      <c r="A144" s="367" t="inlineStr">
-        <is>
-          <t>• 06/06 非农超预期+纳指跌1100点+加息预期 → 美股短期承压</t>
-        </is>
-      </c>
-    </row>
-    <row r="145" ht="16.5" customHeight="1" s="183">
-      <c r="A145" s="367" t="inlineStr">
-        <is>
-          <t>• 06/05 博通AI收入增200%但股价跌15% → 芯片高估值回调</t>
-        </is>
-      </c>
-    </row>
-    <row r="146" ht="16.5" customHeight="1" s="183">
-      <c r="A146" s="367" t="inlineStr">
-        <is>
-          <t>• 06/04 全球央行重新扫货黄金 → 稀金/避险+1pp</t>
-        </is>
-      </c>
-    </row>
-    <row r="147" ht="16.5" customHeight="1" s="183">
-      <c r="A147" s="367" t="inlineStr">
-        <is>
-          <t>• 06/03 黄金替代美债成第一大储备(27%&gt;22%) → 稀金长期趋势</t>
-        </is>
-      </c>
-    </row>
-    <row r="148" ht="16.5" customHeight="1" s="183">
-      <c r="A148" s="367" t="inlineStr">
-        <is>
-          <t>• 06/01 富裕群体消费信心下降+中东出售集股 → 宏观偏空</t>
-        </is>
-      </c>
-    </row>
-    <row r="149" ht="16.5" customHeight="1" s="183">
-      <c r="A149" s="367" t="inlineStr">
-        <is>
-          <t>• 05/29 美伊60天停火+油价跳水 → 能源短期利空</t>
-        </is>
-      </c>
-    </row>
-    <row r="150" ht="16.5" customHeight="1" s="183">
-      <c r="A150" s="367" t="inlineStr">
-        <is>
-          <t>• 05/28 黄金跳水跌破4400 → 避险短期承压</t>
-        </is>
-      </c>
-    </row>
+    <row r="142" ht="39" customHeight="1" s="183"/>
+    <row r="143" ht="17.15" customHeight="1" s="183"/>
+    <row r="144" ht="17.25" customHeight="1" s="183"/>
+    <row r="145" ht="16.5" customHeight="1" s="183"/>
+    <row r="146" ht="16.5" customHeight="1" s="183"/>
+    <row r="147" ht="16.5" customHeight="1" s="183"/>
+    <row r="148" ht="16.5" customHeight="1" s="183"/>
+    <row r="149" ht="16.5" customHeight="1" s="183"/>
+    <row r="150" ht="16.5" customHeight="1" s="183"/>
     <row r="151" ht="16.5" customHeight="1" s="183"/>
-    <row r="152" ht="16.5" customHeight="1" s="183">
-      <c r="A152" s="370" t="inlineStr">
-        <is>
-          <t>📋 其他沾边</t>
-        </is>
-      </c>
-    </row>
-    <row r="153" ht="16.5" customHeight="1" s="183">
-      <c r="A153" s="367" t="inlineStr">
-        <is>
-          <t>• 伊娃6条+生猪贸易3条+猪猪女王2条：养殖面稳定（不调整）</t>
-        </is>
-      </c>
-    </row>
-    <row r="154" ht="26.85" customHeight="1" s="183">
-      <c r="A154" s="367" t="inlineStr">
-        <is>
-          <t>• 宋鸿兵3条：摩尔定律瓶颈/油价/美伊谈判 → 已有覆盖</t>
-        </is>
-      </c>
-    </row>
-    <row r="155" ht="15" customHeight="1" s="183">
-      <c r="A155" s="367" t="inlineStr">
-        <is>
-          <t>• 岩松笔记2条：光伏+银行 → 不调整</t>
-        </is>
-      </c>
-    </row>
+    <row r="152" ht="16.5" customHeight="1" s="183"/>
+    <row r="153" ht="16.5" customHeight="1" s="183"/>
+    <row r="154" ht="26.85" customHeight="1" s="183"/>
+    <row r="155" ht="15" customHeight="1" s="183"/>
     <row r="156" ht="15" customHeight="1" s="183"/>
     <row r="157" ht="15" customHeight="1" s="183"/>
     <row r="158" ht="15" customHeight="1" s="183"/>
@@ -3936,19 +3741,13 @@
     <row r="163" ht="48.5" customHeight="1" s="183"/>
     <row r="164" ht="48.5" customHeight="1" s="183"/>
     <row r="165" ht="64.15000000000001" customHeight="1" s="183"/>
-    <row r="166"/>
     <row r="167" ht="17.15" customHeight="1" s="183"/>
     <row r="168" ht="48.5" customHeight="1" s="183"/>
     <row r="169" ht="32.8" customHeight="1" s="183"/>
     <row r="170" ht="48.5" customHeight="1" s="183"/>
     <row r="171" ht="32.8" customHeight="1" s="183"/>
-    <row r="172"/>
     <row r="173" ht="121.6" customHeight="1" s="183"/>
-    <row r="174"/>
-    <row r="175"/>
-    <row r="176"/>
     <row r="177" ht="15" customHeight="1" s="183"/>
-    <row r="178"/>
     <row r="179" ht="39.55" customHeight="1" s="183"/>
     <row r="180" ht="39.55" customHeight="1" s="183"/>
     <row r="181" ht="52.2" customHeight="1" s="183"/>
@@ -3957,7 +3756,6 @@
     <row r="184" ht="15" customHeight="1" s="183"/>
     <row r="185" ht="15" customHeight="1" s="183"/>
     <row r="186" ht="26.85" customHeight="1" s="183"/>
-    <row r="187"/>
     <row r="188" ht="39.55" customHeight="1" s="183"/>
     <row r="189" ht="26.85" customHeight="1" s="183"/>
     <row r="190" ht="26.85" customHeight="1" s="183"/>
@@ -3966,8 +3764,6 @@
     <row r="193" ht="26.85" customHeight="1" s="183"/>
     <row r="194" ht="39.55" customHeight="1" s="183"/>
     <row r="195" ht="39.55" customHeight="1" s="183"/>
-    <row r="196"/>
-    <row r="197"/>
     <row r="198" ht="18.65" customHeight="1" s="183"/>
     <row r="199" ht="15" customHeight="1" s="183"/>
     <row r="200" ht="15" customHeight="1" s="183"/>
@@ -4074,8 +3870,8 @@
   <mergeCells count="31">
     <mergeCell ref="A126:G126"/>
     <mergeCell ref="A122:G122"/>
+    <mergeCell ref="A107:H107"/>
     <mergeCell ref="A131:G131"/>
-    <mergeCell ref="A107:H107"/>
     <mergeCell ref="A125:G125"/>
     <mergeCell ref="B15:H15"/>
     <mergeCell ref="A1:H1"/>
@@ -10503,7 +10299,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:L299"/>
+  <dimension ref="A1:L263"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="10.4921875" defaultRowHeight="12.75" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="18" customWidth="1" style="332" min="1" max="12"/>
@@ -15404,97 +15200,34 @@
       </c>
     </row>
     <row r="263">
-      <c r="A263" s="365" t="inlineStr">
+      <c r="A263" s="364" t="inlineStr">
         <is>
           <t>2026-06-07
-[蒋宇飞GTC·信号1]
 虚P+1pp
-AI基建3年不死：XAI年租金145亿2年回本，2026训练营业额5000亿。蒋宇飞：3年打死不下车</t>
-        </is>
-      </c>
-      <c r="F263" s="364" t="n"/>
-    </row>
-    <row r="264">
-      <c r="A264" s="365" t="inlineStr">
+蒋宇飞GTC大会5大信号:
+1.算利即利润-XAI年租金145亿2年回本
+2.2026AI训练营业额5000亿美金
+3.英伟达系统级交付-单卖算力卡公司举步维艰
+4.RUBY芯片Q4-Agent时代
+5.端侧AI芯片=万亿市值机会
+6.物理AI=3年后
+结论:AI基建3年打死不下车</t>
+        </is>
+      </c>
+      <c r="F263" s="364" t="inlineStr">
         <is>
           <t>2026-06-07
-[蒋宇飞GTC·信号2]
-产业链分化
-英伟达卖卡→卖系统。单卖算力卡公司举步维艰。2027升腾+平头哥带云交付冲击纯GPU</t>
-        </is>
-      </c>
-    </row>
-    <row r="265">
-      <c r="A265" s="368" t="inlineStr">
-        <is>
-          <t>2026-06-07
-[蒋宇飞GTC·信号3+4]
-端侧AI=万亿赛道
-RUBY含VA-CPU→Agent时代。RTX跑本地1200亿模型。端侧AI芯片前两位=万亿市值</t>
-        </is>
-      </c>
-    </row>
-    <row r="266">
-      <c r="A266" s="368" t="inlineStr">
-        <is>
-          <t>2026-06-07
-[蒋宇飞GTC·信号5]
-物理AI=3年后
-GR00T人形机器人平台。蒋宇飞：需3年。机器人虚P方向确认</t>
-        </is>
-      </c>
-    </row>
-    <row r="267">
-      <c r="F267" s="364" t="inlineStr">
-        <is>
-          <t>2026-06-07
-[环中星鉴]
-+1pp
-黄金替代美债成第一大储备(27%&gt;22%)。全球央行扫货黄金。长期趋势确认</t>
-        </is>
-      </c>
-    </row>
-    <row r="268">
-      <c r="F268" s="364" t="inlineStr">
-        <is>
-          <t>2026-06-07
-[环中星鉴]
--1pp短期
-非农超预期+纳指跌1100点。博通AI收入增200%股价跌15%。SpaceX+OpenAI天价IPO水分</t>
-        </is>
-      </c>
-    </row>
-    <row r="269"/>
-    <row r="270"/>
-    <row r="271"/>
-    <row r="272"/>
-    <row r="273"/>
-    <row r="274"/>
-    <row r="275"/>
-    <row r="276"/>
-    <row r="277"/>
-    <row r="278"/>
-    <row r="279"/>
-    <row r="280"/>
-    <row r="281"/>
-    <row r="282"/>
-    <row r="283"/>
-    <row r="284"/>
-    <row r="285"/>
-    <row r="286"/>
-    <row r="287"/>
-    <row r="288"/>
-    <row r="289"/>
-    <row r="290"/>
-    <row r="291"/>
-    <row r="292"/>
-    <row r="293"/>
-    <row r="294"/>
-    <row r="295"/>
-    <row r="296"/>
-    <row r="297"/>
-    <row r="298"/>
-    <row r="299"/>
+-1pp
+环中星鉴知乎11条:
+1.非农超预期-纳指跌1100点
+2.黄金大跌-短期承压
+3.SpaceX+OpenAI天价IPO水分
+4.富裕群体消费信心下降
+5.中东主权资金出售集股
+结论:短期避险承压但长期AI泡沫待爆</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="49">
     <mergeCell ref="A58:K58"/>

--- a/持仓贝叶斯跟踪.xlsx
+++ b/持仓贝叶斯跟踪.xlsx
@@ -2636,7 +2636,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:H133"/>
+  <dimension ref="A1:H124"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6171875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="18" customWidth="1" style="332" min="1" max="8"/>
@@ -3590,125 +3590,22 @@
     <row r="114" ht="26.25" customHeight="1" s="183"/>
     <row r="115" ht="26.25" customHeight="1" s="183"/>
     <row r="116" ht="15" customHeight="1" s="183"/>
-    <row r="117" ht="20.1" customHeight="1" s="183">
-      <c r="A117" s="361" t="inlineStr">
-        <is>
-          <t>📊 6/7 20:00小结</t>
-        </is>
-      </c>
-    </row>
-    <row r="118" ht="15" customHeight="1" s="183">
-      <c r="A118" s="362" t="inlineStr">
-        <is>
-          <t>• 抓取50条沾边(抖音12+知乎18+B站0) 转录3/3</t>
-        </is>
-      </c>
-    </row>
-    <row r="119" ht="15" customHeight="1" s="183">
-      <c r="A119" s="362" t="inlineStr">
-        <is>
-          <t>• 芯片虚P+1pp: 蒋宇飞GTC大会-AI基建3年不下车/端侧AI来临/物理AI需3年</t>
-        </is>
-      </c>
-    </row>
-    <row r="120" ht="26.25" customHeight="1" s="183">
-      <c r="A120" s="362" t="inlineStr">
-        <is>
-          <t>• 避险+1pp: 环中星鉴11条-非农超预期/黄金大跌/SpaceX+OpenAI天价IPO</t>
-        </is>
-      </c>
-    </row>
-    <row r="121" ht="26.25" customHeight="1" s="183">
-      <c r="A121" s="362" t="inlineStr">
-        <is>
-          <t>• 蒋宇飞端侧AI芯片机会=万亿市值级别(强烈看好)</t>
-        </is>
-      </c>
-    </row>
-    <row r="122" ht="15" customHeight="1" s="183">
-      <c r="A122" s="361" t="inlineStr">
-        <is>
-          <t>📊 6/7 20:00小结</t>
-        </is>
-      </c>
-    </row>
-    <row r="123" ht="15" customHeight="1" s="183">
-      <c r="A123" s="362" t="inlineStr">
-        <is>
-          <t>• 抓取50条沾边(抖音12+知乎18+B站0) 转录3/3 分析3/3</t>
-        </is>
-      </c>
-    </row>
-    <row r="124" ht="26.25" customHeight="1" s="183">
-      <c r="A124" s="362" t="inlineStr">
-        <is>
-          <t>• 蒋宇飞GTC大会: AI基建3年不死/端侧AI来临/物理AI3年后 → 芯片虚P+1pp</t>
-        </is>
-      </c>
-    </row>
-    <row r="125" ht="15" customHeight="1" s="183">
-      <c r="A125" s="362" t="inlineStr">
-        <is>
-          <t>• 环中星鉴11条: 非农超预期+黄金大跌+AI天价IPO → 避险短期承压</t>
-        </is>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" s="362" t="inlineStr">
-        <is>
-          <t>• 拿幸14条: OpenAI记忆架构+Anthropic自研AI → AI产业链持续加速(不重复加分)</t>
-        </is>
-      </c>
-    </row>
-    <row r="127" ht="15" customHeight="1" s="183">
-      <c r="A127" s="362" t="inlineStr">
-        <is>
-          <t>• 伊娃6条+生猪贸易3条+猪猪女王2条: 养殖面稳定(不调整)</t>
-        </is>
-      </c>
-    </row>
-    <row r="128" ht="15" customHeight="1" s="183">
-      <c r="A128" s="361" t="inlineStr">
-        <is>
-          <t>📊 6/7 20:00小结</t>
-        </is>
-      </c>
-    </row>
-    <row r="129" ht="26.25" customHeight="1" s="183">
-      <c r="A129" s="362" t="inlineStr">
-        <is>
-          <t>• 抓取50条沾边(抖音12+知乎18+B站0) 转录3/3 分析3/3</t>
-        </is>
-      </c>
-    </row>
-    <row r="130" ht="15" customHeight="1" s="183">
-      <c r="A130" s="362" t="inlineStr">
-        <is>
-          <t>• 蒋宇飞GTC大会: AI基建3年不死/端侧AI来临/物理AI3年后 → 芯片虚P+1pp</t>
-        </is>
-      </c>
-    </row>
-    <row r="131" ht="15" customHeight="1" s="183">
-      <c r="A131" s="362" t="inlineStr">
-        <is>
-          <t>• 拿幸14条: OpenAI记忆架构+AI从AGI跨向AGI → 芯片方向但不重复加分</t>
-        </is>
-      </c>
-    </row>
-    <row r="132" ht="15" customHeight="1" s="183">
-      <c r="A132" s="362" t="inlineStr">
-        <is>
-          <t>• 伊娃6条+生猪贸易3条+猪猪女王2条: 养殖面稳定(不调整)</t>
-        </is>
-      </c>
-    </row>
-    <row r="133" ht="15" customHeight="1" s="183">
-      <c r="A133" s="362" t="inlineStr">
-        <is>
-          <t>• 环中星鉴11条: 非农超预期+黄金大跌+AI天价IPO → 避险短期承压</t>
-        </is>
-      </c>
-    </row>
+    <row r="117" ht="20.1" customHeight="1" s="183"/>
+    <row r="118" ht="15" customHeight="1" s="183"/>
+    <row r="119" ht="15" customHeight="1" s="183"/>
+    <row r="120" ht="26.25" customHeight="1" s="183"/>
+    <row r="121" ht="26.25" customHeight="1" s="183"/>
+    <row r="122" ht="15" customHeight="1" s="183"/>
+    <row r="123" ht="15" customHeight="1" s="183"/>
+    <row r="124" ht="26.25" customHeight="1" s="183"/>
+    <row r="125" ht="15" customHeight="1" s="183"/>
+    <row r="127" ht="15" customHeight="1" s="183"/>
+    <row r="128" ht="15" customHeight="1" s="183"/>
+    <row r="129" ht="26.25" customHeight="1" s="183"/>
+    <row r="130" ht="15" customHeight="1" s="183"/>
+    <row r="131" ht="15" customHeight="1" s="183"/>
+    <row r="132" ht="15" customHeight="1" s="183"/>
+    <row r="133" ht="15" customHeight="1" s="183"/>
     <row r="134" ht="26.25" customHeight="1" s="183"/>
     <row r="135" ht="15" customHeight="1" s="183"/>
     <row r="136" ht="29.85" customHeight="1" s="183"/>
@@ -3870,8 +3767,8 @@
   <mergeCells count="31">
     <mergeCell ref="A126:G126"/>
     <mergeCell ref="A122:G122"/>
+    <mergeCell ref="A131:G131"/>
     <mergeCell ref="A107:H107"/>
-    <mergeCell ref="A131:G131"/>
     <mergeCell ref="A125:G125"/>
     <mergeCell ref="B15:H15"/>
     <mergeCell ref="A1:H1"/>

--- a/持仓贝叶斯跟踪.xlsx
+++ b/持仓贝叶斯跟踪.xlsx
@@ -30,7 +30,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="63">
+  <fonts count="65">
     <font>
       <name val="Calibri"/>
       <charset val="1"/>
@@ -469,8 +469,16 @@
     <font>
       <sz val="8"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FF6600"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FF0000"/>
+    </font>
   </fonts>
-  <fills count="32">
+  <fills count="33">
     <fill>
       <patternFill/>
     </fill>
@@ -657,6 +665,12 @@
         <bgColor rgb="0016213e"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFD700"/>
+        <bgColor rgb="00FFD700"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="16">
     <border>
@@ -829,7 +843,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="365">
+  <cellXfs count="367">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -1907,6 +1921,8 @@
     <xf numFmtId="0" fontId="62" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="64" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="63" fillId="32" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2213,25 +2229,25 @@
     <author>Hermes</author>
   </authors>
   <commentList>
-    <comment ref="A5" authorId="0" shapeId="0">
+    <comment ref="A16" authorId="0" shapeId="0">
       <text>
         <t>【虚P标注】
 蒋宇飞观点：AI基建时代持续10年是个人判断，非已发生事实。国产算力长城也是预期而非现实。</t>
       </text>
     </comment>
-    <comment ref="B5" authorId="0" shapeId="0">
+    <comment ref="B16" authorId="0" shapeId="0">
       <text>
         <t>【电池+2pp】
 维力能：全球储能电芯出货第二+智能电表9年第一+大圆柱电池+海外订单爆发</t>
       </text>
     </comment>
-    <comment ref="C5" authorId="0" shapeId="0">
+    <comment ref="C16" authorId="0" shapeId="0">
       <text>
         <t>【恒科-3pp】
 付鹏：香港套利闭环不可持续+北水南下导致港元拆借利率偏低+硬核科技偏好下降</t>
       </text>
     </comment>
-    <comment ref="D5" authorId="0" shapeId="0">
+    <comment ref="D16" authorId="0" shapeId="0">
       <text>
         <t>【虚P标注】
 【虚P分析】
@@ -2242,25 +2258,25 @@
 结论：4个信源中2个是事实2个是观点。建议主P只加事实部分+2pp，观点部分进虚P+2pp</t>
       </text>
     </comment>
-    <comment ref="G5" authorId="0" shapeId="0">
+    <comment ref="G16" authorId="0" shapeId="0">
       <text>
         <t>【虚P标注】
 付鹏+宋鸿兵观点：居民去杠杆周期是宏观判断。虽然数据支持（住户贷款-4902亿），但"对银行不利"是推论而非事实。银行板块实际盘面42只全线飘红，与观点矛盾。</t>
       </text>
     </comment>
-    <comment ref="A7" authorId="0" shapeId="0">
+    <comment ref="A18" authorId="0" shapeId="0">
       <text>
         <t>【P'作废】
 霍尔木兹P'已作废：美军轰炸伊朗后海峡通航，预测未兑现</t>
       </text>
     </comment>
-    <comment ref="A12" authorId="0" shapeId="0">
+    <comment ref="A23" authorId="0" shapeId="0">
       <text>
         <t>【虚P标注】
 付鹏观点：存储=AI基建是逻辑推演，非价格/数据确认</t>
       </text>
     </comment>
-    <comment ref="A13" authorId="0" shapeId="0">
+    <comment ref="A24" authorId="0" shapeId="0">
       <text>
         <t>【来源】宋鸿兵抖音6/3 09:00《摩尔定律物理+经济双重极限》+ 蒋宇飞多条
 【逻辑链】宋鸿兵：摩尔定律走到物理极限(2nm以下成本飙升15倍)+经济极限(7nm以下技术红利从普惠变垄断)→芯片行业范式转换→堆叠/存储成为新方向。蒋宇飞交叉验证：韬定律=折叠堆叠，2.5D市场600亿→翻好几倍
@@ -2268,7 +2284,7 @@
 【对持仓影响】芯片+1pp(事实信号)，+2pp(虚P跨博主共识)</t>
       </text>
     </comment>
-    <comment ref="B13" authorId="0" shapeId="0">
+    <comment ref="B24" authorId="0" shapeId="0">
       <text>
         <t>【来源】宋鸿兵抖音6/2《油价末日警告》+ 雪佛龙高管原话 + 埃克森高管原话
 【逻辑链】宋鸿兵引用两大石油巨头高管：霍尔木兹封锁3个月→OECD石油库存6月触红线→油价飙升→通胀失控→美联储无法降息。雪佛龙：石油供应缺口扩大。埃克森：能源转型加速
@@ -2276,7 +2292,7 @@
 【对持仓影响】电池+4pp(油价危机→储能/电动车刚需)</t>
       </text>
     </comment>
-    <comment ref="C13" authorId="0" shapeId="0">
+    <comment ref="C24" authorId="0" shapeId="0">
       <text>
         <t>【来源】宋鸿兵+雪佛龙+埃克森：油价危机传导链
 【逻辑链】油价飙升→通胀上行→美联储被迫维持高利率/甚至加息→美债收益率走高→港股估值受压→恒科下行
@@ -2284,7 +2300,7 @@
 【对持仓影响】恒科-3pp</t>
       </text>
     </comment>
-    <comment ref="G13" authorId="0" shapeId="0">
+    <comment ref="G24" authorId="0" shapeId="0">
       <text>
         <t>【来源】宋鸿兵利率分析+宏观传导
 【逻辑链】油价危机→通胀上行→美联储维持高利率→银行净息差受压→去杠杆周期中银行资产质量恶化
@@ -2292,7 +2308,7 @@
 【对持仓影响】银行-1pp</t>
       </text>
     </comment>
-    <comment ref="A14" authorId="0" shapeId="0">
+    <comment ref="A25" authorId="0" shapeId="0">
       <text>
         <t>【来源】孙正义+黄仁勋 2026-06-06同步发声
 【逻辑链】孙正义抛出3个预言：①AI规模=互联网10-50倍 ②当前泡沫只是杯壁一点点 ③下一个万亿机会是机器人。黄仁勋罕见同步发声确认AI长期叙事。
@@ -2305,7 +2321,7 @@
 【P值调整依据】+5pp(孙正义3预言权重高，万亿级叙事) +3pp(黄仁勋同步确认，双人互锁)</t>
       </text>
     </comment>
-    <comment ref="B14" authorId="0" shapeId="0">
+    <comment ref="B25" authorId="0" shapeId="0">
       <text>
         <t>【来源】宋鸿兵抖音6/3 18:35视频《美伊谈判：决胜负要看经济战》
 【逻辑链】美伊军事战陷入僵局→双方都不愿大打→谈判久拖不决→石油库存逼近红线→油价/通胀飙升→美债收益率走高→金融市场的急性病vs伊朗实体经济的慢性病→时间站在伊朗一边→经济战成为决定性力量
@@ -2314,7 +2330,7 @@
 【核心判断】6-8月是经济战转折点，油价可能继续上行</t>
       </text>
     </comment>
-    <comment ref="C14" authorId="0" shapeId="0">
+    <comment ref="C25" authorId="0" shapeId="0">
       <text>
         <t>【来源】宋鸿兵抖音6/3 18:35视频《美伊谈判：决胜负要看经济战》
 【逻辑链】美伊军事战陷入僵局→双方都不愿大打→谈判久拖不决→石油库存逼近红线→油价/通胀飙升→美债收益率走高→金融市场的急性病vs伊朗实体经济的慢性病→时间站在伊朗一边→经济战成为决定性力量
@@ -2323,7 +2339,7 @@
 【核心判断】6-8月是经济战转折点，油价可能继续上行</t>
       </text>
     </comment>
-    <comment ref="D14" authorId="0" shapeId="0">
+    <comment ref="D25" authorId="0" shapeId="0">
       <text>
         <t>【来源】伊娃抖音6/3黑猪养殖系列+生猪贸易5/28《仔猪价格硬挺》
 【逻辑链】仔猪价格420元硬挺→猪企宁可借钱也不降价→说明不恐慌性淘汰母猪→供给收缩是有序的→猪周期底部在夯实
@@ -2331,7 +2347,7 @@
 【对持仓影响】养殖+1pp，供给端有序收缩</t>
       </text>
     </comment>
-    <comment ref="G14" authorId="0" shapeId="0">
+    <comment ref="G25" authorId="0" shapeId="0">
       <text>
         <t>【来源】环中星鉴知乎6/3 16:35《欧洲央行称黄金替代美债成全球官方储备第一大资产》
 【逻辑链】欧洲央行报告：黄金占全球官方储备27%首次超越美债22%→去美元化加速→长期利好黄金/有色
@@ -2636,7 +2652,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:H124"/>
+  <dimension ref="A1:H133"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6171875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="18" customWidth="1" style="332" min="1" max="8"/>
@@ -3590,22 +3606,125 @@
     <row r="114" ht="26.25" customHeight="1" s="183"/>
     <row r="115" ht="26.25" customHeight="1" s="183"/>
     <row r="116" ht="15" customHeight="1" s="183"/>
-    <row r="117" ht="20.1" customHeight="1" s="183"/>
-    <row r="118" ht="15" customHeight="1" s="183"/>
-    <row r="119" ht="15" customHeight="1" s="183"/>
-    <row r="120" ht="26.25" customHeight="1" s="183"/>
-    <row r="121" ht="26.25" customHeight="1" s="183"/>
-    <row r="122" ht="15" customHeight="1" s="183"/>
-    <row r="123" ht="15" customHeight="1" s="183"/>
-    <row r="124" ht="26.25" customHeight="1" s="183"/>
-    <row r="125" ht="15" customHeight="1" s="183"/>
-    <row r="127" ht="15" customHeight="1" s="183"/>
-    <row r="128" ht="15" customHeight="1" s="183"/>
-    <row r="129" ht="26.25" customHeight="1" s="183"/>
-    <row r="130" ht="15" customHeight="1" s="183"/>
-    <row r="131" ht="15" customHeight="1" s="183"/>
-    <row r="132" ht="15" customHeight="1" s="183"/>
-    <row r="133" ht="15" customHeight="1" s="183"/>
+    <row r="117" ht="20.1" customHeight="1" s="183">
+      <c r="A117" s="361" t="inlineStr">
+        <is>
+          <t>📊 6/7 20:00小结</t>
+        </is>
+      </c>
+    </row>
+    <row r="118" ht="15" customHeight="1" s="183">
+      <c r="A118" s="362" t="inlineStr">
+        <is>
+          <t>• 抓取50条沾边(抖音12+知乎18+B站0) 转录3/3</t>
+        </is>
+      </c>
+    </row>
+    <row r="119" ht="15" customHeight="1" s="183">
+      <c r="A119" s="362" t="inlineStr">
+        <is>
+          <t>• 芯片虚P+1pp: 蒋宇飞GTC大会-AI基建3年不下车/端侧AI来临/物理AI需3年</t>
+        </is>
+      </c>
+    </row>
+    <row r="120" ht="26.25" customHeight="1" s="183">
+      <c r="A120" s="362" t="inlineStr">
+        <is>
+          <t>• 避险+1pp: 环中星鉴11条-非农超预期/黄金大跌/SpaceX+OpenAI天价IPO</t>
+        </is>
+      </c>
+    </row>
+    <row r="121" ht="26.25" customHeight="1" s="183">
+      <c r="A121" s="362" t="inlineStr">
+        <is>
+          <t>• 蒋宇飞端侧AI芯片机会=万亿市值级别(强烈看好)</t>
+        </is>
+      </c>
+    </row>
+    <row r="122" ht="15" customHeight="1" s="183">
+      <c r="A122" s="361" t="inlineStr">
+        <is>
+          <t>📊 6/7 20:00小结</t>
+        </is>
+      </c>
+    </row>
+    <row r="123" ht="15" customHeight="1" s="183">
+      <c r="A123" s="362" t="inlineStr">
+        <is>
+          <t>• 抓取50条沾边(抖音12+知乎18+B站0) 转录3/3 分析3/3</t>
+        </is>
+      </c>
+    </row>
+    <row r="124" ht="26.25" customHeight="1" s="183">
+      <c r="A124" s="362" t="inlineStr">
+        <is>
+          <t>• 蒋宇飞GTC大会: AI基建3年不死/端侧AI来临/物理AI3年后 → 芯片虚P+1pp</t>
+        </is>
+      </c>
+    </row>
+    <row r="125" ht="15" customHeight="1" s="183">
+      <c r="A125" s="362" t="inlineStr">
+        <is>
+          <t>• 环中星鉴11条: 非农超预期+黄金大跌+AI天价IPO → 避险短期承压</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="362" t="inlineStr">
+        <is>
+          <t>• 拿幸14条: OpenAI记忆架构+Anthropic自研AI → AI产业链持续加速(不重复加分)</t>
+        </is>
+      </c>
+    </row>
+    <row r="127" ht="15" customHeight="1" s="183">
+      <c r="A127" s="362" t="inlineStr">
+        <is>
+          <t>• 伊娃6条+生猪贸易3条+猪猪女王2条: 养殖面稳定(不调整)</t>
+        </is>
+      </c>
+    </row>
+    <row r="128" ht="15" customHeight="1" s="183">
+      <c r="A128" s="361" t="inlineStr">
+        <is>
+          <t>📊 6/7 20:00小结</t>
+        </is>
+      </c>
+    </row>
+    <row r="129" ht="26.25" customHeight="1" s="183">
+      <c r="A129" s="362" t="inlineStr">
+        <is>
+          <t>• 抓取50条沾边(抖音12+知乎18+B站0) 转录3/3 分析3/3</t>
+        </is>
+      </c>
+    </row>
+    <row r="130" ht="15" customHeight="1" s="183">
+      <c r="A130" s="362" t="inlineStr">
+        <is>
+          <t>• 蒋宇飞GTC大会: AI基建3年不死/端侧AI来临/物理AI3年后 → 芯片虚P+1pp</t>
+        </is>
+      </c>
+    </row>
+    <row r="131" ht="15" customHeight="1" s="183">
+      <c r="A131" s="362" t="inlineStr">
+        <is>
+          <t>• 拿幸14条: OpenAI记忆架构+AI从AGI跨向AGI → 芯片方向但不重复加分</t>
+        </is>
+      </c>
+    </row>
+    <row r="132" ht="15" customHeight="1" s="183">
+      <c r="A132" s="362" t="inlineStr">
+        <is>
+          <t>• 伊娃6条+生猪贸易3条+猪猪女王2条: 养殖面稳定(不调整)</t>
+        </is>
+      </c>
+    </row>
+    <row r="133" ht="15" customHeight="1" s="183">
+      <c r="A133" s="362" t="inlineStr">
+        <is>
+          <t>• 环中星鉴11条: 非农超预期+黄金大跌+AI天价IPO → 避险短期承压</t>
+        </is>
+      </c>
+    </row>
     <row r="134" ht="26.25" customHeight="1" s="183"/>
     <row r="135" ht="15" customHeight="1" s="183"/>
     <row r="136" ht="29.85" customHeight="1" s="183"/>
@@ -10196,7 +10315,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:L263"/>
+  <dimension ref="A1:L274"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="10.4921875" defaultRowHeight="12.75" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="18" customWidth="1" style="332" min="1" max="12"/>
@@ -10465,7 +10584,94 @@
       </c>
     </row>
     <row r="5" ht="45" customHeight="1" s="183">
-      <c r="A5" s="222" t="inlineStr">
+      <c r="G5" s="365" t="inlineStr">
+        <is>
+          <t>【-1pp】黑色星期五：美股三大指数大跌+非农超预期+加息预期升温+黄金石油暴跌。闻号+环中星鉴+古都闲云多源确认
+来源: 知乎闻号说经济/环中星鉴/古都闲云6/6标题多篇</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="45" customHeight="1" s="183">
+      <c r="E6" s="365" t="inlineStr">
+        <is>
+          <t>【-1pp】长坡厚雪：纳斯达克100跌5个点。科技股回调压制工业金属需求预期</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="45" customHeight="1" s="183">
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>【+1pp】生猪贸易：集团负债大，3个月猪价不涨母猪血流成河=抄底最佳时机。银行拒贷养猪，资金链断裂加速出清
+原文路径: ~/.hermes/work/transcripts/生猪贸易_7647447103488358585.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="45" customHeight="1" s="183">
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>【0pp】生猪贸易：淘汰母猪价格加快=底部信号，后备/怀孕母猪价格骗不了人
+原文路径: ~/.hermes/work/transcripts/生猪贸易_7647885902051625209.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="45" customHeight="1" s="183">
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>【0pp】生猪贸易：集团养一天赔一天，15号/20号开会前后价格反弹。出栏压力持续
+原文路径: ~/.hermes/work/transcripts/生猪贸易_7648309392954386299.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="45" customHeight="1" s="183">
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>【0pp】伊娃：CPICP黑猪产业交流，重庆特宝投15年农业创投准备投资黑猪。资本关注赛道，不改变主P
+原文路径: ~/.hermes/work/transcripts/伊娃_7648158651937345698.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="45" customHeight="1" s="183">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>【0pp】付鹏：世界秩序重构=分配问题，AI=有希望资产vs黄金=人类没有未来。方向已有，不重复加分
+原文路径: ~/.hermes/work/transcripts/付鹏_7647471378513317170.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="45" customHeight="1" s="183">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>【0pp】拿幸：Anthropic预警AI自研AI(80%代码Claude写)，开发效率暴涨88倍。AI加速信号已有，不重复加分
+原文路径: ~/.hermes/work/transcripts/拿幸_7647906523846364479.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="75" customHeight="1" s="183">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>【0pp】拿幸：OpenAI记忆V3上线+Anthropic跨租户泄露。AI产业链持续推进，不重复加分
+原文路径: ~/.hermes/work/transcripts/拿幸_7648127132840873270.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="13.5" customHeight="1" s="183">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>【0pp】蒋宇飞：美国四大芯片巨头掌舵者全是华人（英伟达/博通/AMD/英特尔）。华人科技实力佐证，不重复加分
+原文路径: ~/.hermes/work/transcripts/蒋宇飞_7648230205248605475.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="13.5" customHeight="1" s="183">
+      <c r="A15" s="366" t="inlineStr">
+        <is>
+          <t>【虚P+1pp】付鹏：要想富先修路=先建数据中心算力中心。AI基建=未来高速公路，各行各业开始应用
+原文路径: ~/.hermes/work/transcripts/付鹏_7648268448174247208.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="13.5" customHeight="1" s="183">
+      <c r="A16" s="222" t="inlineStr">
         <is>
           <t>2026-06-03
 +3pp
@@ -10474,7 +10680,7 @@
 【+0pp】宋鸿兵美伊谈判：经济战替代军事战→芯片逻辑不变</t>
         </is>
       </c>
-      <c r="B5" s="223" t="inlineStr">
+      <c r="B16" s="223" t="inlineStr">
         <is>
           <t>2026-06-03
 +6pp
@@ -10482,7 +10688,7 @@
 【+2pp】【虚P】美伊经济战→能源转型加速→电池长期利好</t>
         </is>
       </c>
-      <c r="C5" s="224" t="inlineStr">
+      <c r="C16" s="224" t="inlineStr">
         <is>
           <t>2026-06-03
 -4pp
@@ -10490,28 +10696,28 @@
 【-1pp】【虚P】美伊久拖不决→美债收益率上行→压制港股</t>
         </is>
       </c>
-      <c r="D5" s="222" t="inlineStr">
+      <c r="D16" s="222" t="inlineStr">
         <is>
           <t>2026-06-03
 +1pp
 【事实】伊娃：仔猪价格硬挺420元→供给收缩有序</t>
         </is>
       </c>
-      <c r="E5" s="224" t="inlineStr">
+      <c r="E16" s="224" t="inlineStr">
         <is>
           <t>2026-06-03
 -5pp
 【-5pp】知乎6/3联动：301关税+欧盟钢铁关税→工业金属需求预期下降，转口贸易路变窄</t>
         </is>
       </c>
-      <c r="F5" s="224" t="inlineStr">
+      <c r="F16" s="224" t="inlineStr">
         <is>
           <t>2026-06-03
 -3pp
 【-3pp】知乎6/3联动：贸易利空，稀土反制牌短期有效但长期不确定</t>
         </is>
       </c>
-      <c r="G5" s="222" t="inlineStr">
+      <c r="G16" s="222" t="inlineStr">
         <is>
           <t>2026-06-03
 -1pp
@@ -10519,7 +10725,7 @@
 【+0pp】【虚P】欧洲央行：黄金替代美债成第一大储备</t>
         </is>
       </c>
-      <c r="K5" s="332" t="inlineStr">
+      <c r="K16" s="332" t="inlineStr">
         <is>
           <t>2026-06-01
 +3pp
@@ -10527,58 +10733,58 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="45" customHeight="1" s="183">
-      <c r="A6" s="223" t="inlineStr">
+    <row r="17" ht="13.5" customHeight="1" s="183">
+      <c r="A17" s="223" t="inlineStr">
         <is>
           <t>2026-06-02
 +2pp
 【虚P】蒋宇飞AI基建10年+国产算力长城</t>
         </is>
       </c>
-      <c r="B6" s="225" t="inlineStr">
+      <c r="B17" s="225" t="inlineStr">
         <is>
           <t>2026-06-02
 +2pp
 维力能储能全球第二+锂电全链</t>
         </is>
       </c>
-      <c r="C6" s="226" t="inlineStr">
+      <c r="C17" s="226" t="inlineStr">
         <is>
           <t>2026-06-02
 -3pp
 付鹏恒科套利闭环不可持续</t>
         </is>
       </c>
-      <c r="D6" s="223" t="inlineStr">
+      <c r="D17" s="223" t="inlineStr">
         <is>
           <t>2026-06-02
 +4pp
 【虚P】美国猪周期启示+17/18亏损+行业关注+厄尔尼诺</t>
         </is>
       </c>
-      <c r="E6" s="227" t="inlineStr">
+      <c r="E17" s="227" t="inlineStr">
         <is>
           <t>2026-05-22
 +4pp
 AI铜需求爆发 + 资金回流</t>
         </is>
       </c>
-      <c r="F6" s="227" t="inlineStr">
+      <c r="F17" s="227" t="inlineStr">
         <is>
           <t>2026-05-29
 +1pp
 闭眼看世界：俄乌升级→地缘风险溢价</t>
         </is>
       </c>
-      <c r="G6" s="226" t="inlineStr">
+      <c r="G17" s="226" t="inlineStr">
         <is>
           <t>2026-06-02
 -2pp
 【虚P】去杠杆周期不利</t>
         </is>
       </c>
-      <c r="H6" s="228" t="n"/>
-      <c r="K6" s="224" t="inlineStr">
+      <c r="H17" s="228" t="n"/>
+      <c r="K17" s="224" t="inlineStr">
         <is>
           <t>2026-06-01
 +2pp
@@ -10586,50 +10792,50 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="45" customHeight="1" s="183">
-      <c r="A7" s="229" t="inlineStr">
+    <row r="18" ht="13.5" customHeight="1" s="183">
+      <c r="A18" s="229" t="inlineStr">
         <is>
           <t>2026-05-28
 +1pp
 Schiff美债熊市 + 周鸿祎"内存决定高度"</t>
         </is>
       </c>
-      <c r="B7" s="230" t="inlineStr">
+      <c r="B18" s="230" t="inlineStr">
         <is>
           <t>2026-05-21
 +0pp
 中科院固态锂电池突破（逻辑簇强化）</t>
         </is>
       </c>
-      <c r="C7" s="231" t="inlineStr">
+      <c r="C18" s="231" t="inlineStr">
         <is>
           <t>2026-05-26
 -4pp
 恒生三巨头财报验证：非价值陷阱确认</t>
         </is>
       </c>
-      <c r="D7" s="230" t="inlineStr">
+      <c r="D18" s="230" t="inlineStr">
         <is>
           <t>2026-05-26
 +5pp
 伊娃读财报18期：17/18猪企亏损，加速去产能确认</t>
         </is>
       </c>
-      <c r="E7" s="232" t="inlineStr">
+      <c r="E18" s="232" t="inlineStr">
         <is>
           <t>2026-05-19
 -2pp
 岩松笔记 + 付鹏对冲：逻辑分类修正</t>
         </is>
       </c>
-      <c r="F7" s="232" t="inlineStr">
+      <c r="F18" s="232" t="inlineStr">
         <is>
           <t>2026-05-20
 -3pp
 有色金属持续走弱+美债压制</t>
         </is>
       </c>
-      <c r="G7" s="230" t="inlineStr">
+      <c r="G18" s="230" t="inlineStr">
         <is>
           <t>2026-05-22
 +0pp
@@ -10637,8 +10843,8 @@
 【+3pp】凯文·沃什就任美联储主席</t>
         </is>
       </c>
-      <c r="H7" s="228" t="n"/>
-      <c r="K7" s="224" t="inlineStr">
+      <c r="H18" s="228" t="n"/>
+      <c r="K18" s="224" t="inlineStr">
         <is>
           <t>2026-05-29
 +5pp
@@ -10646,29 +10852,29 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="45" customHeight="1" s="183">
-      <c r="A8" s="223" t="inlineStr">
+    <row r="19" ht="13.5" customHeight="1" s="183">
+      <c r="A19" s="223" t="inlineStr">
         <is>
           <t>2026-05-27
 -2pp
 【已作废】美军轰炸伊朗→霍尔木兹P'作废</t>
         </is>
       </c>
-      <c r="B8" s="223" t="inlineStr">
+      <c r="B19" s="223" t="inlineStr">
         <is>
           <t>2026-05-20
 +1pp
 光储旺季+美债压制</t>
         </is>
       </c>
-      <c r="C8" s="226" t="inlineStr">
+      <c r="C19" s="226" t="inlineStr">
         <is>
           <t>2026-05-20
 -3pp
 多空交织：低开高走验证磨底 + 美债5.18%压制</t>
         </is>
       </c>
-      <c r="D8" s="226" t="inlineStr">
+      <c r="D19" s="226" t="inlineStr">
         <is>
           <t>2026-05-24
 +9pp
@@ -10676,23 +10882,23 @@
 【+4pp】霍尔木兹通航修正</t>
         </is>
       </c>
-      <c r="E8" s="233" t="inlineStr">
+      <c r="E19" s="233" t="inlineStr">
         <is>
           <t>2026-05-15
 -8pp
 有色金属板块持续资金净流出</t>
         </is>
       </c>
-      <c r="F8" s="233" t="inlineStr">
+      <c r="F19" s="233" t="inlineStr">
         <is>
           <t>2026-05-19
 -5pp
 岩松笔记：资源非长期抗通胀→HALO联动风险</t>
         </is>
       </c>
-      <c r="G8" s="228" t="n"/>
-      <c r="H8" s="228" t="n"/>
-      <c r="K8" s="332" t="inlineStr">
+      <c r="G19" s="228" t="n"/>
+      <c r="H19" s="228" t="n"/>
+      <c r="K19" s="332" t="inlineStr">
         <is>
           <t>2026-05-29
 +3pp
@@ -10700,48 +10906,48 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="45" customHeight="1" s="183">
-      <c r="A9" s="231" t="inlineStr">
+    <row r="20" ht="13.5" customHeight="1" s="183">
+      <c r="A20" s="231" t="inlineStr">
         <is>
           <t>2026-05-25
 +1pp
 蒋宇飞：玻璃基板的万亿机遇</t>
         </is>
       </c>
-      <c r="B9" s="230" t="inlineStr">
+      <c r="B20" s="230" t="inlineStr">
         <is>
           <t>2026-05-19
 +5pp
 碳酸锂跌价+巴克莱看多</t>
         </is>
       </c>
-      <c r="C9" s="228" t="inlineStr">
+      <c r="C20" s="228" t="inlineStr">
         <is>
           <t>2026-05-19
 -2pp
 付鹏×2：港股结构性偏弱 + 风险偏好极值 + 古都闲云社消疲弱</t>
         </is>
       </c>
-      <c r="D9" s="231" t="inlineStr">
+      <c r="D20" s="231" t="inlineStr">
         <is>
           <t>2026-05-22
 -2pp
 无知半人：住户贷款狂减4902亿</t>
         </is>
       </c>
-      <c r="E9" s="234" t="inlineStr">
+      <c r="E20" s="234" t="inlineStr">
         <is>
           <t>拟合⚠️样本少</t>
         </is>
       </c>
-      <c r="F9" s="234" t="inlineStr">
+      <c r="F20" s="234" t="inlineStr">
         <is>
           <t>拟合⚠️样本少</t>
         </is>
       </c>
-      <c r="G9" s="228" t="n"/>
-      <c r="H9" s="228" t="n"/>
-      <c r="K9" s="332" t="inlineStr">
+      <c r="G20" s="228" t="n"/>
+      <c r="H20" s="228" t="n"/>
+      <c r="K20" s="332" t="inlineStr">
         <is>
           <t>2026-04-07
 +4pp
@@ -10749,8 +10955,8 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="45" customHeight="1" s="183">
-      <c r="A10" s="226" t="inlineStr">
+    <row r="21" ht="13.5" customHeight="1" s="183">
+      <c r="A21" s="226" t="inlineStr">
         <is>
           <t>2026-05-22
 -3pp
@@ -10758,34 +10964,34 @@
 【-2pp】凯文·沃什就任美联储主席（↓从-6pp降级：宏观β被产业α碾过）</t>
         </is>
       </c>
-      <c r="B10" s="223" t="inlineStr">
+      <c r="B21" s="223" t="inlineStr">
         <is>
           <t>2026-05-15
 +1pp
 机构研报确认景气上行</t>
         </is>
       </c>
-      <c r="C10" s="228" t="n"/>
-      <c r="D10" s="228" t="inlineStr">
+      <c r="C21" s="228" t="n"/>
+      <c r="D21" s="228" t="inlineStr">
         <is>
           <t>2026-05-19
 -2pp
 古都闲云：社消数据疲弱</t>
         </is>
       </c>
-      <c r="E10" s="234" t="inlineStr">
+      <c r="E21" s="234" t="inlineStr">
         <is>
           <t>⚠️样本少</t>
         </is>
       </c>
-      <c r="F10" s="234" t="inlineStr">
+      <c r="F21" s="234" t="inlineStr">
         <is>
           <t>⚠️样本少</t>
         </is>
       </c>
-      <c r="G10" s="228" t="n"/>
-      <c r="H10" s="228" t="n"/>
-      <c r="K10" s="332" t="inlineStr">
+      <c r="G21" s="228" t="n"/>
+      <c r="H21" s="228" t="n"/>
+      <c r="K21" s="332" t="inlineStr">
         <is>
           <t>2026-03-23
 +3pp
@@ -10794,28 +11000,28 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="45" customHeight="1" s="183">
-      <c r="A11" s="231" t="inlineStr">
+    <row r="22" ht="13.5" customHeight="1" s="183">
+      <c r="A22" s="231" t="inlineStr">
         <is>
           <t>2026-05-19
 -2pp
 韩国闪崩（情绪叠加）</t>
         </is>
       </c>
-      <c r="B11" s="230" t="inlineStr">
+      <c r="B22" s="230" t="inlineStr">
         <is>
           <t>2026-05-14
 +3pp
 电池ETF涨2.73%+多重利好</t>
         </is>
       </c>
-      <c r="C11" s="228" t="n"/>
-      <c r="D11" s="228" t="n"/>
-      <c r="E11" s="228" t="n"/>
-      <c r="F11" s="228" t="n"/>
-      <c r="G11" s="228" t="n"/>
-      <c r="H11" s="228" t="n"/>
-      <c r="K11" s="332" t="inlineStr">
+      <c r="C22" s="228" t="n"/>
+      <c r="D22" s="228" t="n"/>
+      <c r="E22" s="228" t="n"/>
+      <c r="F22" s="228" t="n"/>
+      <c r="G22" s="228" t="n"/>
+      <c r="H22" s="228" t="n"/>
+      <c r="K22" s="332" t="inlineStr">
         <is>
           <t>2026-03
 基准
@@ -10823,77 +11029,77 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="45" customHeight="1" s="183">
-      <c r="A12" s="235" t="inlineStr">
+    <row r="23" ht="13.5" customHeight="1" s="183">
+      <c r="A23" s="235" t="inlineStr">
         <is>
           <t>2026-05-16
 +2pp
 【虚P】付鹏：存储=AI基建（观点→共识信号）</t>
         </is>
       </c>
-      <c r="B12" s="228" t="inlineStr">
+      <c r="B23" s="228" t="inlineStr">
         <is>
           <t>2026-05-13
 +5pp
 特朗普访华+恩捷40亿扩产</t>
         </is>
       </c>
-      <c r="C12" s="228" t="n"/>
-      <c r="D12" s="228" t="n"/>
-      <c r="E12" s="228" t="n"/>
-      <c r="F12" s="228" t="n"/>
-      <c r="G12" s="228" t="n"/>
-      <c r="H12" s="228" t="n"/>
-      <c r="K12" s="332" t="inlineStr">
+      <c r="C23" s="228" t="n"/>
+      <c r="D23" s="228" t="n"/>
+      <c r="E23" s="228" t="n"/>
+      <c r="F23" s="228" t="n"/>
+      <c r="G23" s="228" t="n"/>
+      <c r="H23" s="228" t="n"/>
+      <c r="K23" s="332" t="inlineStr">
         <is>
           <t>拟合N/A(新赛道)</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="75" customHeight="1" s="183">
-      <c r="A13" s="236" t="inlineStr">
+    <row r="24" ht="13.5" customHeight="1" s="183">
+      <c r="A24" s="236" t="inlineStr">
         <is>
           <t>拟合❌0分</t>
         </is>
       </c>
-      <c r="B13" s="236" t="inlineStr">
+      <c r="B24" s="236" t="inlineStr">
         <is>
           <t>拟合✅97分</t>
         </is>
       </c>
-      <c r="C13" s="236" t="inlineStr">
+      <c r="C24" s="236" t="inlineStr">
         <is>
           <t>拟合✅75分</t>
         </is>
       </c>
-      <c r="D13" s="332" t="inlineStr">
+      <c r="D24" s="332" t="inlineStr">
         <is>
           <t>拟合✅95分</t>
         </is>
       </c>
-      <c r="E13" s="332" t="inlineStr">
+      <c r="E24" s="332" t="inlineStr">
         <is>
           <t>拟合⚠️样本少</t>
         </is>
       </c>
-      <c r="F13" s="332" t="inlineStr">
+      <c r="F24" s="332" t="inlineStr">
         <is>
           <t>拟合⚠️样本少</t>
         </is>
       </c>
-      <c r="G13" s="236" t="inlineStr">
+      <c r="G24" s="236" t="inlineStr">
         <is>
           <t>拟合👍53分</t>
         </is>
       </c>
-      <c r="H13" s="332" t="inlineStr">
+      <c r="H24" s="332" t="inlineStr">
         <is>
           <t>无数据</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="13.5" customHeight="1" s="183">
-      <c r="A14" s="222" t="inlineStr">
+    <row r="25" ht="13.5" customHeight="1" s="183">
+      <c r="A25" s="222" t="inlineStr">
         <is>
           <t>2026-06-06
 +8pp
@@ -10902,2432 +11108,2432 @@
 → 两人罕见同步，虚P强度拉满</t>
         </is>
       </c>
-      <c r="B14" s="332" t="n"/>
-      <c r="C14" s="332" t="n"/>
-      <c r="D14" s="332" t="n"/>
-      <c r="G14" s="332" t="n"/>
-    </row>
-    <row r="15" ht="13.5" customHeight="1" s="183">
-      <c r="A15" s="332" t="inlineStr">
-        <is>
-          <t>❌0分 ρ=-0.676</t>
-        </is>
-      </c>
-      <c r="B15" s="332" t="inlineStr">
-        <is>
-          <t>✅97分 ρ=+0.966</t>
-        </is>
-      </c>
-      <c r="C15" s="332" t="inlineStr">
-        <is>
-          <t>✅75分 ρ=+0.754</t>
-        </is>
-      </c>
-      <c r="D15" s="332" t="inlineStr">
-        <is>
-          <t>✅95分 ρ=+0.955</t>
-        </is>
-      </c>
-      <c r="E15" s="332" t="inlineStr">
-        <is>
-          <t>⚠️样本少</t>
-        </is>
-      </c>
-      <c r="F15" s="332" t="inlineStr">
-        <is>
-          <t>⚠️样本少</t>
-        </is>
-      </c>
-      <c r="G15" s="332" t="inlineStr">
-        <is>
-          <t>👍53分 ρ=+0.530</t>
-        </is>
-      </c>
-      <c r="H15" s="332" t="inlineStr">
-        <is>
-          <t>无数据</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="13.5" customHeight="1" s="183">
-      <c r="B16" s="224" t="n"/>
-      <c r="E16" s="332" t="inlineStr">
-        <is>
-          <t>生猪贸易:淘汰母猪价格加快=底部信号(+1pp)</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="13.5" customHeight="1" s="183">
-      <c r="E17" s="332" t="inlineStr">
-        <is>
-          <t>伊娃:中小养户资金压力=融资环境恶化</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="13.5" customHeight="1" s="183">
-      <c r="A18" s="224" t="n"/>
-      <c r="D18" s="332" t="inlineStr">
-        <is>
-          <t>拿幸:Anthropic AI造AI预警+谷歌Gemma4(0pp叙事)</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="13.5" customHeight="1" s="183">
-      <c r="A19" s="224" t="n"/>
-      <c r="B19" s="224" t="inlineStr">
-        <is>
-          <t>环中星鉴:博通AI收入+200%股价-15%(0pp)</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="13.5" customHeight="1" s="183">
-      <c r="A20" s="224" t="inlineStr">
-        <is>
-          <t>2026-06-06</t>
-        </is>
-      </c>
-      <c r="B20" s="224" t="n"/>
-      <c r="H20" s="332" t="inlineStr">
-        <is>
-          <t>闻号:非农超预期14万/黑五大跌(0pp)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="13.5" customHeight="1" s="183">
-      <c r="A21" s="224" t="n"/>
-      <c r="B21" s="224" t="n"/>
-    </row>
-    <row r="22" ht="13.5" customHeight="1" s="183"/>
-    <row r="23" ht="13.5" customHeight="1" s="183"/>
-    <row r="24" ht="13.5" customHeight="1" s="183">
-      <c r="A24" s="237" t="inlineStr">
-        <is>
-          <t>📊 机会成本比较（2026-06-04）</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="13.5" customHeight="1" s="183">
-      <c r="A25" s="203" t="inlineStr">
-        <is>
-          <t>选项</t>
-        </is>
-      </c>
-      <c r="B25" s="203" t="inlineStr">
-        <is>
-          <t>P值</t>
-        </is>
-      </c>
-      <c r="C25" s="203" t="inlineStr">
-        <is>
-          <t>盈亏比</t>
-        </is>
-      </c>
-      <c r="D25" s="203" t="inlineStr">
-        <is>
-          <t>P×R</t>
-        </is>
-      </c>
-      <c r="E25" s="203" t="inlineStr">
-        <is>
-          <t>仓位w</t>
-        </is>
-      </c>
-      <c r="F25" s="203" t="inlineStr">
-        <is>
-          <t>吸引力Score</t>
-        </is>
-      </c>
-      <c r="G25" s="203" t="inlineStr">
-        <is>
-          <t>双门槛</t>
-        </is>
-      </c>
-      <c r="H25" s="203" t="inlineStr">
-        <is>
-          <t>建议</t>
-        </is>
-      </c>
+      <c r="B25" s="332" t="n"/>
+      <c r="C25" s="332" t="n"/>
+      <c r="D25" s="332" t="n"/>
+      <c r="G25" s="332" t="n"/>
     </row>
     <row r="26" ht="13.5" customHeight="1" s="183">
       <c r="A26" s="332" t="inlineStr">
         <is>
+          <t>❌0分 ρ=-0.676</t>
+        </is>
+      </c>
+      <c r="B26" s="332" t="inlineStr">
+        <is>
+          <t>✅97分 ρ=+0.966</t>
+        </is>
+      </c>
+      <c r="C26" s="332" t="inlineStr">
+        <is>
+          <t>✅75分 ρ=+0.754</t>
+        </is>
+      </c>
+      <c r="D26" s="332" t="inlineStr">
+        <is>
+          <t>✅95分 ρ=+0.955</t>
+        </is>
+      </c>
+      <c r="E26" s="332" t="inlineStr">
+        <is>
+          <t>⚠️样本少</t>
+        </is>
+      </c>
+      <c r="F26" s="332" t="inlineStr">
+        <is>
+          <t>⚠️样本少</t>
+        </is>
+      </c>
+      <c r="G26" s="332" t="inlineStr">
+        <is>
+          <t>👍53分 ρ=+0.530</t>
+        </is>
+      </c>
+      <c r="H26" s="332" t="inlineStr">
+        <is>
+          <t>无数据</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="13.5" customHeight="1" s="183">
+      <c r="B27" s="224" t="n"/>
+      <c r="E27" s="332" t="inlineStr">
+        <is>
+          <t>生猪贸易:淘汰母猪价格加快=底部信号(+1pp)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="13.5" customHeight="1" s="183">
+      <c r="E28" s="332" t="inlineStr">
+        <is>
+          <t>伊娃:中小养户资金压力=融资环境恶化</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="13.5" customHeight="1" s="183">
+      <c r="A29" s="224" t="n"/>
+      <c r="D29" s="332" t="inlineStr">
+        <is>
+          <t>拿幸:Anthropic AI造AI预警+谷歌Gemma4(0pp叙事)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="13.5" customHeight="1" s="183">
+      <c r="A30" s="224" t="n"/>
+      <c r="B30" s="224" t="inlineStr">
+        <is>
+          <t>环中星鉴:博通AI收入+200%股价-15%(0pp)</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="16.5" customHeight="1" s="183">
+      <c r="A31" s="224" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="B31" s="224" t="n"/>
+      <c r="H31" s="332" t="inlineStr">
+        <is>
+          <t>闻号:非农超预期14万/黑五大跌(0pp)</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="16.5" customHeight="1" s="183">
+      <c r="A32" s="224" t="n"/>
+      <c r="B32" s="224" t="n"/>
+    </row>
+    <row r="33" ht="16.5" customHeight="1" s="183"/>
+    <row r="34" ht="16.5" customHeight="1" s="183"/>
+    <row r="35" ht="13.5" customHeight="1" s="183">
+      <c r="A35" s="237" t="inlineStr">
+        <is>
+          <t>📊 机会成本比较（2026-06-04）</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="13.5" customHeight="1" s="183">
+      <c r="A36" s="203" t="inlineStr">
+        <is>
+          <t>选项</t>
+        </is>
+      </c>
+      <c r="B36" s="203" t="inlineStr">
+        <is>
+          <t>P值</t>
+        </is>
+      </c>
+      <c r="C36" s="203" t="inlineStr">
+        <is>
+          <t>盈亏比</t>
+        </is>
+      </c>
+      <c r="D36" s="203" t="inlineStr">
+        <is>
+          <t>P×R</t>
+        </is>
+      </c>
+      <c r="E36" s="203" t="inlineStr">
+        <is>
+          <t>仓位w</t>
+        </is>
+      </c>
+      <c r="F36" s="203" t="inlineStr">
+        <is>
+          <t>吸引力Score</t>
+        </is>
+      </c>
+      <c r="G36" s="203" t="inlineStr">
+        <is>
+          <t>双门槛</t>
+        </is>
+      </c>
+      <c r="H36" s="203" t="inlineStr">
+        <is>
+          <t>建议</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="16.5" customHeight="1" s="183">
+      <c r="A37" s="332" t="inlineStr">
+        <is>
           <t>养殖014415</t>
         </is>
       </c>
-      <c r="B26" s="332" t="inlineStr">
+      <c r="B37" s="332" t="inlineStr">
         <is>
           <t>70%</t>
         </is>
       </c>
-      <c r="C26" s="332" t="inlineStr">
+      <c r="C37" s="332" t="inlineStr">
         <is>
           <t>2.0:1</t>
         </is>
       </c>
-      <c r="D26" s="332" t="inlineStr">
+      <c r="D37" s="332" t="inlineStr">
         <is>
           <t>1.40</t>
         </is>
       </c>
-      <c r="E26" s="332" t="inlineStr">
+      <c r="E37" s="332" t="inlineStr">
         <is>
           <t>0.0%</t>
         </is>
       </c>
-      <c r="F26" s="332" t="inlineStr">
+      <c r="F37" s="332" t="inlineStr">
         <is>
           <t>1.400</t>
         </is>
       </c>
-      <c r="G26" s="332" t="inlineStr">
+      <c r="G37" s="332" t="inlineStr">
         <is>
           <t>✅通过</t>
         </is>
       </c>
-      <c r="H26" s="332" t="inlineStr">
+      <c r="H37" s="332" t="inlineStr">
         <is>
           <t>🟢可配现金</t>
         </is>
       </c>
     </row>
-    <row r="27" ht="13.5" customHeight="1" s="183">
-      <c r="A27" s="332" t="inlineStr">
+    <row r="38" ht="16.5" customHeight="1" s="183">
+      <c r="A38" s="332" t="inlineStr">
         <is>
           <t>电池018926</t>
         </is>
       </c>
-      <c r="B27" s="332" t="inlineStr">
+      <c r="B38" s="332" t="inlineStr">
         <is>
           <t>65%</t>
         </is>
       </c>
-      <c r="C27" s="332" t="inlineStr">
+      <c r="C38" s="332" t="inlineStr">
         <is>
           <t>2.0:1</t>
         </is>
       </c>
-      <c r="D27" s="332" t="inlineStr">
+      <c r="D38" s="332" t="inlineStr">
         <is>
           <t>1.30</t>
         </is>
       </c>
-      <c r="E27" s="332" t="inlineStr">
+      <c r="E38" s="332" t="inlineStr">
         <is>
           <t>0.0%</t>
         </is>
       </c>
-      <c r="F27" s="332" t="inlineStr">
+      <c r="F38" s="332" t="inlineStr">
         <is>
           <t>1.300</t>
         </is>
       </c>
-      <c r="G27" s="332" t="inlineStr">
+      <c r="G38" s="332" t="inlineStr">
         <is>
           <t>✅通过</t>
         </is>
       </c>
-      <c r="H27" s="332" t="inlineStr">
+      <c r="H38" s="332" t="inlineStr">
         <is>
           <t>🟢可配现金</t>
         </is>
       </c>
     </row>
-    <row r="28" ht="13.5" customHeight="1" s="183">
-      <c r="A28" s="332" t="inlineStr">
+    <row r="39" ht="13.5" customHeight="1" s="183">
+      <c r="A39" s="332" t="inlineStr">
         <is>
           <t>有色004433</t>
         </is>
       </c>
-      <c r="B28" s="332" t="inlineStr">
+      <c r="B39" s="332" t="inlineStr">
         <is>
           <t>39%</t>
         </is>
       </c>
-      <c r="C28" s="332" t="inlineStr">
+      <c r="C39" s="332" t="inlineStr">
         <is>
           <t>0.7:1</t>
         </is>
       </c>
-      <c r="D28" s="332" t="inlineStr">
+      <c r="D39" s="332" t="inlineStr">
         <is>
           <t>0.27</t>
         </is>
       </c>
-      <c r="E28" s="332" t="inlineStr">
+      <c r="E39" s="332" t="inlineStr">
         <is>
           <t>0.0%</t>
         </is>
       </c>
-      <c r="F28" s="332" t="inlineStr">
+      <c r="F39" s="332" t="inlineStr">
         <is>
           <t>0.273</t>
         </is>
       </c>
-      <c r="G28" s="332" t="inlineStr">
+      <c r="G39" s="332" t="inlineStr">
         <is>
           <t>❌未通过</t>
         </is>
       </c>
-      <c r="H28" s="332" t="inlineStr">
+      <c r="H39" s="332" t="inlineStr">
         <is>
           <t>差20pp到P门槛</t>
         </is>
       </c>
     </row>
-    <row r="29" ht="13.5" customHeight="1" s="183">
-      <c r="A29" s="332" t="inlineStr">
+    <row r="40" ht="13.5" customHeight="1" s="183">
+      <c r="A40" s="332" t="inlineStr">
         <is>
           <t>稀金014111</t>
         </is>
       </c>
-      <c r="B29" s="332" t="inlineStr">
+      <c r="B40" s="332" t="inlineStr">
         <is>
           <t>40%</t>
         </is>
       </c>
-      <c r="C29" s="332" t="inlineStr">
+      <c r="C40" s="332" t="inlineStr">
         <is>
           <t>0.6:1</t>
         </is>
       </c>
-      <c r="D29" s="332" t="inlineStr">
+      <c r="D40" s="332" t="inlineStr">
         <is>
           <t>0.24</t>
         </is>
       </c>
-      <c r="E29" s="332" t="inlineStr">
+      <c r="E40" s="332" t="inlineStr">
         <is>
           <t>0.0%</t>
         </is>
       </c>
-      <c r="F29" s="332" t="inlineStr">
+      <c r="F40" s="332" t="inlineStr">
         <is>
           <t>0.240</t>
         </is>
       </c>
-      <c r="G29" s="332" t="inlineStr">
+      <c r="G40" s="332" t="inlineStr">
         <is>
           <t>❌未通过</t>
         </is>
       </c>
-      <c r="H29" s="332" t="inlineStr">
+      <c r="H40" s="332" t="inlineStr">
         <is>
           <t>差19pp到P门槛</t>
         </is>
       </c>
     </row>
-    <row r="30" ht="13.5" customHeight="1" s="183">
-      <c r="A30" s="332" t="inlineStr">
-        <is>
-          <t>银行001595</t>
-        </is>
-      </c>
-      <c r="B30" s="332" t="inlineStr">
-        <is>
-          <t>47%</t>
-        </is>
-      </c>
-      <c r="C30" s="332" t="inlineStr">
-        <is>
-          <t>0.5:1</t>
-        </is>
-      </c>
-      <c r="D30" s="332" t="inlineStr">
-        <is>
-          <t>0.23</t>
-        </is>
-      </c>
-      <c r="E30" s="332" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="F30" s="332" t="inlineStr">
-        <is>
-          <t>0.235</t>
-        </is>
-      </c>
-      <c r="G30" s="332" t="inlineStr">
-        <is>
-          <t>❌未通过</t>
-        </is>
-      </c>
-      <c r="H30" s="332" t="inlineStr">
-        <is>
-          <t>差13pp到P门槛</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="16.5" customHeight="1" s="183">
-      <c r="A31" s="332" t="inlineStr">
-        <is>
-          <t>恒科012349</t>
-        </is>
-      </c>
-    